--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,13 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D556"/>
+  <dimension ref="A1:E556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,10 +439,15 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>price_00:15</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -457,9 +463,12 @@
         <v>71444.39999999999</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>71444.39999999999</v>
+        <v>71530</v>
       </c>
       <c r="D2" s="1" t="n">
+        <v>71530</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>71444.39999999999</v>
       </c>
     </row>
@@ -473,9 +482,12 @@
         <v>2092.92</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>2092.92</v>
+        <v>2096.9</v>
       </c>
       <c r="D3" s="1" t="n">
+        <v>2096.9</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>2092.92</v>
       </c>
     </row>
@@ -489,9 +501,12 @@
         <v>87.86</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>87.86</v>
+        <v>87.95</v>
       </c>
       <c r="D4" s="1" t="n">
+        <v>87.95</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>87.86</v>
       </c>
     </row>
@@ -505,9 +520,12 @@
         <v>23.478</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>23.478</v>
+        <v>23.579</v>
       </c>
       <c r="D5" s="1" t="n">
+        <v>23.579</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>23.478</v>
       </c>
     </row>
@@ -521,9 +539,12 @@
         <v>0.001827</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>0.001827</v>
+        <v>0.001852</v>
       </c>
       <c r="D6" s="1" t="n">
+        <v>0.001852</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>0.001827</v>
       </c>
     </row>
@@ -542,6 +563,9 @@
       <c r="D7" s="1" t="n">
         <v>1.4149</v>
       </c>
+      <c r="E7" s="1" t="n">
+        <v>1.4149</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -553,9 +577,12 @@
         <v>0.011168</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>0.011168</v>
+        <v>0.011244</v>
       </c>
       <c r="D8" s="1" t="n">
+        <v>0.011244</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>0.011168</v>
       </c>
     </row>
@@ -569,9 +596,12 @@
         <v>3.955</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>3.955</v>
+        <v>3.968</v>
       </c>
       <c r="D9" s="1" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>3.955</v>
       </c>
     </row>
@@ -585,11 +615,14 @@
         <v>275.06</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>275.06</v>
+        <v>272.62</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>275.06</v>
       </c>
+      <c r="E10" s="1" t="n">
+        <v>272.62</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -601,9 +634,12 @@
         <v>0.07929</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>0.07929</v>
+        <v>0.08047</v>
       </c>
       <c r="D11" s="1" t="n">
+        <v>0.08047</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>0.07929</v>
       </c>
     </row>
@@ -617,9 +653,12 @@
         <v>227.3</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>227.3</v>
+        <v>227.69</v>
       </c>
       <c r="D12" s="1" t="n">
+        <v>227.69</v>
+      </c>
+      <c r="E12" s="1" t="n">
         <v>227.3</v>
       </c>
     </row>
@@ -633,9 +672,12 @@
         <v>0.09492</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>0.09492</v>
+        <v>0.09497</v>
       </c>
       <c r="D13" s="1" t="n">
+        <v>0.09497</v>
+      </c>
+      <c r="E13" s="1" t="n">
         <v>0.09492</v>
       </c>
     </row>
@@ -649,11 +691,14 @@
         <v>37.279</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>37.279</v>
+        <v>37.275</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>37.279</v>
       </c>
+      <c r="E14" s="1" t="n">
+        <v>37.275</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -665,9 +710,12 @@
         <v>0.09461</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>0.09461</v>
+        <v>0.09654</v>
       </c>
       <c r="D15" s="1" t="n">
+        <v>0.09654</v>
+      </c>
+      <c r="E15" s="1" t="n">
         <v>0.09461</v>
       </c>
     </row>
@@ -681,11 +729,14 @@
         <v>0.2339</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>0.2339</v>
+        <v>0.2305</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>0.2339</v>
       </c>
+      <c r="E16" s="1" t="n">
+        <v>0.2305</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -697,11 +748,14 @@
         <v>0.011538</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.011538</v>
+        <v>0.011513</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>0.011538</v>
       </c>
+      <c r="E17" s="1" t="n">
+        <v>0.011513</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -713,9 +767,12 @@
         <v>659.6799999999999</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>659.6799999999999</v>
+        <v>660.72</v>
       </c>
       <c r="D18" s="1" t="n">
+        <v>660.72</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>659.6799999999999</v>
       </c>
     </row>
@@ -729,9 +786,12 @@
         <v>0.0033412</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.0033412</v>
+        <v>0.0033451</v>
       </c>
       <c r="D19" s="1" t="n">
+        <v>0.0033451</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>0.0033412</v>
       </c>
     </row>
@@ -745,11 +805,14 @@
         <v>0.18017</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>0.18017</v>
+        <v>0.17762</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>0.18017</v>
       </c>
+      <c r="E20" s="1" t="n">
+        <v>0.17762</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -761,9 +824,12 @@
         <v>0.009778</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0.009778</v>
+        <v>0.009808000000000001</v>
       </c>
       <c r="D21" s="1" t="n">
+        <v>0.009808000000000001</v>
+      </c>
+      <c r="E21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -777,9 +843,12 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>1</v>
+        <v>1.0033</v>
       </c>
       <c r="D22" s="1" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -793,11 +862,14 @@
         <v>5012.25</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>5012.25</v>
+        <v>5007.01</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>5012.25</v>
       </c>
+      <c r="E23" s="1" t="n">
+        <v>5007.01</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -809,9 +881,12 @@
         <v>0.2635</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>0.2635</v>
+        <v>0.2643</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>0.2643</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>0.2635</v>
       </c>
     </row>
@@ -825,9 +900,12 @@
         <v>2.899</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>2.899</v>
+        <v>2.9</v>
       </c>
       <c r="D25" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>2.899</v>
       </c>
     </row>
@@ -841,9 +919,12 @@
         <v>0.3959</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>0.3959</v>
+        <v>0.4035</v>
       </c>
       <c r="D26" s="1" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>0.3959</v>
       </c>
     </row>
@@ -862,6 +943,9 @@
       <c r="D27" s="1" t="n">
         <v>0.885</v>
       </c>
+      <c r="E27" s="1" t="n">
+        <v>0.885</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -873,9 +957,12 @@
         <v>1.336</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>1.336</v>
+        <v>1.343</v>
       </c>
       <c r="D28" s="1" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="E28" s="1" t="n">
         <v>1.336</v>
       </c>
     </row>
@@ -889,9 +976,12 @@
         <v>9.151</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>9.151</v>
+        <v>9.179</v>
       </c>
       <c r="D29" s="1" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="E29" s="1" t="n">
         <v>9.151</v>
       </c>
     </row>
@@ -905,9 +995,12 @@
         <v>462.32</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>462.32</v>
+        <v>463.35</v>
       </c>
       <c r="D30" s="1" t="n">
+        <v>463.35</v>
+      </c>
+      <c r="E30" s="1" t="n">
         <v>462.32</v>
       </c>
     </row>
@@ -921,9 +1014,12 @@
         <v>9.711</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>9.711</v>
+        <v>9.728999999999999</v>
       </c>
       <c r="D31" s="1" t="n">
+        <v>9.728999999999999</v>
+      </c>
+      <c r="E31" s="1" t="n">
         <v>9.711</v>
       </c>
     </row>
@@ -937,11 +1033,14 @@
         <v>0.36683</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>0.36683</v>
+        <v>0.36424</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>0.36683</v>
       </c>
+      <c r="E32" s="1" t="n">
+        <v>0.36424</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -953,9 +1052,12 @@
         <v>1.416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>1.416</v>
+        <v>1.419</v>
       </c>
       <c r="D33" s="1" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>1.416</v>
       </c>
     </row>
@@ -969,9 +1071,12 @@
         <v>0.59283</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>0.59283</v>
+        <v>0.59391</v>
       </c>
       <c r="D34" s="1" t="n">
+        <v>0.59391</v>
+      </c>
+      <c r="E34" s="1" t="n">
         <v>0.59283</v>
       </c>
     </row>
@@ -985,9 +1090,12 @@
         <v>1.2198</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>1.2198</v>
+        <v>1.2228</v>
       </c>
       <c r="D35" s="1" t="n">
+        <v>1.2228</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>1.2198</v>
       </c>
     </row>
@@ -1001,11 +1109,14 @@
         <v>80.5</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>80.5</v>
+        <v>80.3</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>80.5</v>
       </c>
+      <c r="E36" s="1" t="n">
+        <v>80.3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1017,9 +1128,12 @@
         <v>0.1977</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>0.1977</v>
+        <v>0.204</v>
       </c>
       <c r="D37" s="1" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="E37" s="1" t="n">
         <v>0.1977</v>
       </c>
     </row>
@@ -1033,9 +1147,12 @@
         <v>1.844</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>1.844</v>
+        <v>1.865</v>
       </c>
       <c r="D38" s="1" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="E38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -1049,11 +1166,14 @@
         <v>0.3199</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>0.3199</v>
+        <v>0.3197</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>0.3199</v>
       </c>
+      <c r="E39" s="1" t="n">
+        <v>0.3197</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1065,9 +1185,12 @@
         <v>0.9022</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>0.9022</v>
+        <v>0.9077</v>
       </c>
       <c r="D40" s="1" t="n">
+        <v>0.9077</v>
+      </c>
+      <c r="E40" s="1" t="n">
         <v>0.9022</v>
       </c>
     </row>
@@ -1081,9 +1204,12 @@
         <v>0.7148</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>0.7148</v>
+        <v>0.7149</v>
       </c>
       <c r="D41" s="1" t="n">
+        <v>0.7149</v>
+      </c>
+      <c r="E41" s="1" t="n">
         <v>0.7148</v>
       </c>
     </row>
@@ -1097,11 +1223,14 @@
         <v>0.06769</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>0.06769</v>
+        <v>0.06714000000000001</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>0.06769</v>
       </c>
+      <c r="E42" s="1" t="n">
+        <v>0.06714000000000001</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1113,9 +1242,12 @@
         <v>112.81</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>112.81</v>
+        <v>113.57</v>
       </c>
       <c r="D43" s="1" t="n">
+        <v>113.57</v>
+      </c>
+      <c r="E43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -1129,11 +1261,14 @@
         <v>0.6623</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>0.6623</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>0.6623</v>
       </c>
+      <c r="E44" s="1" t="n">
+        <v>0.6578000000000001</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1145,9 +1280,12 @@
         <v>1.206</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>1.206</v>
+        <v>1.211</v>
       </c>
       <c r="D45" s="1" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="E45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -1161,9 +1299,12 @@
         <v>0.02382</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>0.02382</v>
+        <v>0.02392</v>
       </c>
       <c r="D46" s="1" t="n">
+        <v>0.02392</v>
+      </c>
+      <c r="E46" s="1" t="n">
         <v>0.02382</v>
       </c>
     </row>
@@ -1177,9 +1318,12 @@
         <v>55.06</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>55.06</v>
+        <v>55.17</v>
       </c>
       <c r="D47" s="1" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="E47" s="1" t="n">
         <v>55.06</v>
       </c>
     </row>
@@ -1193,9 +1337,12 @@
         <v>0.06018</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>0.06018</v>
+        <v>0.06081</v>
       </c>
       <c r="D48" s="1" t="n">
+        <v>0.06081</v>
+      </c>
+      <c r="E48" s="1" t="n">
         <v>0.06018</v>
       </c>
     </row>
@@ -1209,9 +1356,12 @@
         <v>0.108</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>0.108</v>
+        <v>0.1082</v>
       </c>
       <c r="D49" s="1" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="E49" s="1" t="n">
         <v>0.108</v>
       </c>
     </row>
@@ -1225,9 +1375,12 @@
         <v>0.018</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>0.018</v>
+        <v>0.01815</v>
       </c>
       <c r="D50" s="1" t="n">
+        <v>0.01815</v>
+      </c>
+      <c r="E50" s="1" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -1241,9 +1394,12 @@
         <v>1.4622</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>1.4622</v>
+        <v>1.4659</v>
       </c>
       <c r="D51" s="1" t="n">
+        <v>1.4659</v>
+      </c>
+      <c r="E51" s="1" t="n">
         <v>1.4622</v>
       </c>
     </row>
@@ -1257,9 +1413,12 @@
         <v>0.358</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>0.358</v>
+        <v>0.3603</v>
       </c>
       <c r="D52" s="1" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="E52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -1273,9 +1432,12 @@
         <v>0.001959</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>0.001959</v>
+        <v>0.001961</v>
       </c>
       <c r="D53" s="1" t="n">
+        <v>0.001961</v>
+      </c>
+      <c r="E53" s="1" t="n">
         <v>0.001959</v>
       </c>
     </row>
@@ -1289,9 +1451,12 @@
         <v>0.09524000000000001</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>0.09524000000000001</v>
+        <v>0.09569</v>
       </c>
       <c r="D54" s="1" t="n">
+        <v>0.09569</v>
+      </c>
+      <c r="E54" s="1" t="n">
         <v>0.09524000000000001</v>
       </c>
     </row>
@@ -1305,11 +1470,14 @@
         <v>0.04071</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>0.04071</v>
+        <v>0.04003</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>0.04071</v>
       </c>
+      <c r="E55" s="1" t="n">
+        <v>0.04003</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1321,11 +1489,14 @@
         <v>0.29861</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>0.29861</v>
+        <v>0.29838</v>
       </c>
       <c r="D56" s="1" t="n">
         <v>0.29861</v>
       </c>
+      <c r="E56" s="1" t="n">
+        <v>0.29838</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1337,11 +1508,14 @@
         <v>0.005824</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>0.005824</v>
+        <v>0.00581</v>
       </c>
       <c r="D57" s="1" t="n">
         <v>0.005824</v>
       </c>
+      <c r="E57" s="1" t="n">
+        <v>0.00581</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1353,11 +1527,14 @@
         <v>4998.37</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>4998.37</v>
+        <v>4997.14</v>
       </c>
       <c r="D58" s="1" t="n">
         <v>4998.37</v>
       </c>
+      <c r="E58" s="1" t="n">
+        <v>4997.14</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1369,11 +1546,14 @@
         <v>0.4246</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>0.4246</v>
+        <v>0.4177</v>
       </c>
       <c r="D59" s="1" t="n">
         <v>0.4246</v>
       </c>
+      <c r="E59" s="1" t="n">
+        <v>0.4177</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1385,9 +1565,12 @@
         <v>0.04598</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>0.04598</v>
+        <v>0.04658</v>
       </c>
       <c r="D60" s="1" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="E60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -1401,9 +1584,12 @@
         <v>0.21692</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>0.21692</v>
+        <v>0.21708</v>
       </c>
       <c r="D61" s="1" t="n">
+        <v>0.21708</v>
+      </c>
+      <c r="E61" s="1" t="n">
         <v>0.21692</v>
       </c>
     </row>
@@ -1417,9 +1603,12 @@
         <v>0.1072</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>0.1072</v>
+        <v>0.1076</v>
       </c>
       <c r="D62" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="E62" s="1" t="n">
         <v>0.1072</v>
       </c>
     </row>
@@ -1433,9 +1622,12 @@
         <v>0.7267</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>0.7267</v>
+        <v>0.7301</v>
       </c>
       <c r="D63" s="1" t="n">
+        <v>0.7301</v>
+      </c>
+      <c r="E63" s="1" t="n">
         <v>0.7267</v>
       </c>
     </row>
@@ -1449,9 +1641,12 @@
         <v>0.166</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>0.166</v>
+        <v>0.1667</v>
       </c>
       <c r="D64" s="1" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="E64" s="1" t="n">
         <v>0.166</v>
       </c>
     </row>
@@ -1465,9 +1660,12 @@
         <v>2.657</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>2.657</v>
+        <v>2.661</v>
       </c>
       <c r="D65" s="1" t="n">
+        <v>2.661</v>
+      </c>
+      <c r="E65" s="1" t="n">
         <v>2.657</v>
       </c>
     </row>
@@ -1481,9 +1679,12 @@
         <v>0.04018</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>0.04018</v>
+        <v>0.04048</v>
       </c>
       <c r="D66" s="1" t="n">
+        <v>0.04048</v>
+      </c>
+      <c r="E66" s="1" t="n">
         <v>0.04018</v>
       </c>
     </row>
@@ -1497,9 +1698,12 @@
         <v>0.04217</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>0.04217</v>
+        <v>0.04234</v>
       </c>
       <c r="D67" s="1" t="n">
+        <v>0.04234</v>
+      </c>
+      <c r="E67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -1513,9 +1717,12 @@
         <v>3.952</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>3.952</v>
+        <v>3.967</v>
       </c>
       <c r="D68" s="1" t="n">
+        <v>3.967</v>
+      </c>
+      <c r="E68" s="1" t="n">
         <v>3.952</v>
       </c>
     </row>
@@ -1529,9 +1736,12 @@
         <v>0.1253</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>0.1253</v>
+        <v>0.1261</v>
       </c>
       <c r="D69" s="1" t="n">
+        <v>0.1261</v>
+      </c>
+      <c r="E69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -1545,11 +1755,14 @@
         <v>6.128</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>6.128</v>
+        <v>6.114</v>
       </c>
       <c r="D70" s="1" t="n">
         <v>6.128</v>
       </c>
+      <c r="E70" s="1" t="n">
+        <v>6.114</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1561,9 +1774,12 @@
         <v>0.04997</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>0.04997</v>
+        <v>0.04999</v>
       </c>
       <c r="D71" s="1" t="n">
+        <v>0.04999</v>
+      </c>
+      <c r="E71" s="1" t="n">
         <v>0.04997</v>
       </c>
     </row>
@@ -1577,9 +1793,12 @@
         <v>0.004098</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>0.004098</v>
+        <v>0.004133</v>
       </c>
       <c r="D72" s="1" t="n">
+        <v>0.004133</v>
+      </c>
+      <c r="E72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -1593,9 +1812,12 @@
         <v>6.001</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>6.001</v>
+        <v>6.029</v>
       </c>
       <c r="D73" s="1" t="n">
+        <v>6.029</v>
+      </c>
+      <c r="E73" s="1" t="n">
         <v>6.001</v>
       </c>
     </row>
@@ -1609,9 +1831,12 @@
         <v>0.1629</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>0.1629</v>
+        <v>0.1633</v>
       </c>
       <c r="D74" s="1" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="E74" s="1" t="n">
         <v>0.1629</v>
       </c>
     </row>
@@ -1625,9 +1850,12 @@
         <v>0.007276</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>0.007276</v>
+        <v>0.007297</v>
       </c>
       <c r="D75" s="1" t="n">
+        <v>0.007297</v>
+      </c>
+      <c r="E75" s="1" t="n">
         <v>0.007276</v>
       </c>
     </row>
@@ -1641,9 +1869,12 @@
         <v>0.2024</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>0.2024</v>
+        <v>0.2086</v>
       </c>
       <c r="D76" s="1" t="n">
+        <v>0.2086</v>
+      </c>
+      <c r="E76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -1657,11 +1888,14 @@
         <v>0.005826</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>0.005826</v>
+        <v>0.005821</v>
       </c>
       <c r="D77" s="1" t="n">
         <v>0.005826</v>
       </c>
+      <c r="E77" s="1" t="n">
+        <v>0.005821</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1673,9 +1907,12 @@
         <v>0.1013</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>0.1013</v>
+        <v>0.1019</v>
       </c>
       <c r="D78" s="1" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="E78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -1689,9 +1926,12 @@
         <v>0.006256</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>0.006256</v>
+        <v>0.006292</v>
       </c>
       <c r="D79" s="1" t="n">
+        <v>0.006292</v>
+      </c>
+      <c r="E79" s="1" t="n">
         <v>0.006256</v>
       </c>
     </row>
@@ -1705,9 +1945,12 @@
         <v>33.33</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>33.33</v>
+        <v>33.51</v>
       </c>
       <c r="D80" s="1" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="E80" s="1" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -1721,9 +1964,12 @@
         <v>0.04037</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>0.04037</v>
+        <v>0.04043</v>
       </c>
       <c r="D81" s="1" t="n">
+        <v>0.04043</v>
+      </c>
+      <c r="E81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -1737,9 +1983,12 @@
         <v>0.16701</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>0.16701</v>
+        <v>0.1675</v>
       </c>
       <c r="D82" s="1" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="E82" s="1" t="n">
         <v>0.16701</v>
       </c>
     </row>
@@ -1753,11 +2002,14 @@
         <v>0.1035</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>0.1035</v>
+        <v>0.1033</v>
       </c>
       <c r="D83" s="1" t="n">
         <v>0.1035</v>
       </c>
+      <c r="E83" s="1" t="n">
+        <v>0.1033</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1769,9 +2021,12 @@
         <v>0.08810999999999999</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>0.08810999999999999</v>
+        <v>0.08841</v>
       </c>
       <c r="D84" s="1" t="n">
+        <v>0.08841</v>
+      </c>
+      <c r="E84" s="1" t="n">
         <v>0.08810999999999999</v>
       </c>
     </row>
@@ -1785,9 +2040,12 @@
         <v>0.02325</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>0.02325</v>
+        <v>0.02331</v>
       </c>
       <c r="D85" s="1" t="n">
+        <v>0.02331</v>
+      </c>
+      <c r="E85" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -1801,9 +2059,12 @@
         <v>0.236</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>0.236</v>
+        <v>0.238</v>
       </c>
       <c r="D86" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="E86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -1817,9 +2078,12 @@
         <v>355.75</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>355.75</v>
+        <v>357.12</v>
       </c>
       <c r="D87" s="1" t="n">
+        <v>357.12</v>
+      </c>
+      <c r="E87" s="1" t="n">
         <v>355.75</v>
       </c>
     </row>
@@ -1833,9 +2097,12 @@
         <v>0.00342</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>0.00342</v>
+        <v>0.00344</v>
       </c>
       <c r="D88" s="1" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="E88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -1849,9 +2116,12 @@
         <v>8.278</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>8.278</v>
+        <v>8.301</v>
       </c>
       <c r="D89" s="1" t="n">
+        <v>8.301</v>
+      </c>
+      <c r="E89" s="1" t="n">
         <v>8.278</v>
       </c>
     </row>
@@ -1865,9 +2135,12 @@
         <v>0.00593</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>0.00593</v>
+        <v>0.005945</v>
       </c>
       <c r="D90" s="1" t="n">
+        <v>0.005945</v>
+      </c>
+      <c r="E90" s="1" t="n">
         <v>0.00593</v>
       </c>
     </row>
@@ -1881,9 +2154,12 @@
         <v>0.06884999999999999</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>0.06884999999999999</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="D91" s="1" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="E91" s="1" t="n">
         <v>0.06884999999999999</v>
       </c>
     </row>
@@ -1897,9 +2173,12 @@
         <v>0.02879</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>0.02879</v>
+        <v>0.02894</v>
       </c>
       <c r="D92" s="1" t="n">
+        <v>0.02894</v>
+      </c>
+      <c r="E92" s="1" t="n">
         <v>0.02879</v>
       </c>
     </row>
@@ -1913,11 +2192,14 @@
         <v>5.202</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>5.202</v>
+        <v>5.189</v>
       </c>
       <c r="D93" s="1" t="n">
         <v>5.202</v>
       </c>
+      <c r="E93" s="1" t="n">
+        <v>5.189</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1929,9 +2211,12 @@
         <v>0.000226</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>0.000226</v>
+        <v>0.000228</v>
       </c>
       <c r="D94" s="1" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="E94" s="1" t="n">
         <v>0.000226</v>
       </c>
     </row>
@@ -1945,9 +2230,12 @@
         <v>0.919</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>0.919</v>
+        <v>0.9241</v>
       </c>
       <c r="D95" s="1" t="n">
+        <v>0.9241</v>
+      </c>
+      <c r="E95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -1961,11 +2249,14 @@
         <v>2.0774</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>2.0774</v>
+        <v>2.0598</v>
       </c>
       <c r="D96" s="1" t="n">
         <v>2.0774</v>
       </c>
+      <c r="E96" s="1" t="n">
+        <v>2.0598</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1977,9 +2268,12 @@
         <v>0.369</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>0.369</v>
+        <v>0.3711</v>
       </c>
       <c r="D97" s="1" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="E97" s="1" t="n">
         <v>0.369</v>
       </c>
     </row>
@@ -1993,9 +2287,12 @@
         <v>1.613</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>1.613</v>
+        <v>1.618</v>
       </c>
       <c r="D98" s="1" t="n">
+        <v>1.618</v>
+      </c>
+      <c r="E98" s="1" t="n">
         <v>1.613</v>
       </c>
     </row>
@@ -2009,9 +2306,12 @@
         <v>0.2351</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>0.2351</v>
+        <v>0.2368</v>
       </c>
       <c r="D99" s="1" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="E99" s="1" t="n">
         <v>0.2351</v>
       </c>
     </row>
@@ -2025,9 +2325,12 @@
         <v>0.13539</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>0.13539</v>
+        <v>0.13621</v>
       </c>
       <c r="D100" s="1" t="n">
+        <v>0.13621</v>
+      </c>
+      <c r="E100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -2041,9 +2344,12 @@
         <v>0.06851</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>0.06851</v>
+        <v>0.06908</v>
       </c>
       <c r="D101" s="1" t="n">
+        <v>0.06908</v>
+      </c>
+      <c r="E101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -2057,9 +2363,12 @@
         <v>0.001084</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>0.001084</v>
+        <v>0.001085</v>
       </c>
       <c r="D102" s="1" t="n">
+        <v>0.001085</v>
+      </c>
+      <c r="E102" s="1" t="n">
         <v>0.001084</v>
       </c>
     </row>
@@ -2073,9 +2382,12 @@
         <v>0.003414</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>0.003414</v>
+        <v>0.003424</v>
       </c>
       <c r="D103" s="1" t="n">
+        <v>0.003424</v>
+      </c>
+      <c r="E103" s="1" t="n">
         <v>0.003414</v>
       </c>
     </row>
@@ -2089,9 +2401,12 @@
         <v>0.27656</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>0.27656</v>
+        <v>0.27751</v>
       </c>
       <c r="D104" s="1" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="E104" s="1" t="n">
         <v>0.27656</v>
       </c>
     </row>
@@ -2105,9 +2420,12 @@
         <v>0.01247</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>0.01247</v>
+        <v>0.01257</v>
       </c>
       <c r="D105" s="1" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="E105" s="1" t="n">
         <v>0.01247</v>
       </c>
     </row>
@@ -2121,9 +2439,12 @@
         <v>0.13515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>0.13515</v>
+        <v>0.13569</v>
       </c>
       <c r="D106" s="1" t="n">
+        <v>0.13569</v>
+      </c>
+      <c r="E106" s="1" t="n">
         <v>0.13515</v>
       </c>
     </row>
@@ -2137,9 +2458,12 @@
         <v>0.3476</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>0.3476</v>
+        <v>0.3496</v>
       </c>
       <c r="D107" s="1" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="E107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -2153,9 +2477,12 @@
         <v>0.1426</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>0.1426</v>
+        <v>0.1436</v>
       </c>
       <c r="D108" s="1" t="n">
+        <v>0.1436</v>
+      </c>
+      <c r="E108" s="1" t="n">
         <v>0.1426</v>
       </c>
     </row>
@@ -2169,9 +2496,12 @@
         <v>0.928</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>0.928</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="D109" s="1" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="E109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -2185,9 +2515,12 @@
         <v>0.016258</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>0.016258</v>
+        <v>0.016308</v>
       </c>
       <c r="D110" s="1" t="n">
+        <v>0.016308</v>
+      </c>
+      <c r="E110" s="1" t="n">
         <v>0.016258</v>
       </c>
     </row>
@@ -2201,11 +2534,14 @@
         <v>0.038335</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>0.038335</v>
+        <v>0.03774</v>
       </c>
       <c r="D111" s="1" t="n">
         <v>0.038335</v>
       </c>
+      <c r="E111" s="1" t="n">
+        <v>0.03774</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2217,11 +2553,14 @@
         <v>0.11959</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>0.11959</v>
+        <v>0.11926</v>
       </c>
       <c r="D112" s="1" t="n">
         <v>0.11959</v>
       </c>
+      <c r="E112" s="1" t="n">
+        <v>0.11926</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2233,9 +2572,12 @@
         <v>0.09426</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>0.09426</v>
+        <v>0.09465</v>
       </c>
       <c r="D113" s="1" t="n">
+        <v>0.09465</v>
+      </c>
+      <c r="E113" s="1" t="n">
         <v>0.09426</v>
       </c>
     </row>
@@ -2249,9 +2591,12 @@
         <v>0.12945</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>0.12945</v>
+        <v>0.1299</v>
       </c>
       <c r="D114" s="1" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="E114" s="1" t="n">
         <v>0.12945</v>
       </c>
     </row>
@@ -2265,9 +2610,12 @@
         <v>0.264</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>0.264</v>
+        <v>0.2656</v>
       </c>
       <c r="D115" s="1" t="n">
+        <v>0.2656</v>
+      </c>
+      <c r="E115" s="1" t="n">
         <v>0.264</v>
       </c>
     </row>
@@ -2281,9 +2629,12 @@
         <v>0.05208</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>0.05208</v>
+        <v>0.0529</v>
       </c>
       <c r="D116" s="1" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="E116" s="1" t="n">
         <v>0.05208</v>
       </c>
     </row>
@@ -2297,9 +2648,12 @@
         <v>0.0914</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>0.0914</v>
+        <v>0.0916</v>
       </c>
       <c r="D117" s="1" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="E117" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -2313,11 +2667,14 @@
         <v>0.05545</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>0.05545</v>
+        <v>0.05516</v>
       </c>
       <c r="D118" s="1" t="n">
         <v>0.05545</v>
       </c>
+      <c r="E118" s="1" t="n">
+        <v>0.05516</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2329,9 +2686,12 @@
         <v>0.01511</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>0.01511</v>
+        <v>0.01515</v>
       </c>
       <c r="D119" s="1" t="n">
+        <v>0.01515</v>
+      </c>
+      <c r="E119" s="1" t="n">
         <v>0.01511</v>
       </c>
     </row>
@@ -2345,9 +2705,12 @@
         <v>3.049</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>3.049</v>
+        <v>3.06</v>
       </c>
       <c r="D120" s="1" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -2361,9 +2724,12 @@
         <v>1.85</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>1.85</v>
+        <v>1.855</v>
       </c>
       <c r="D121" s="1" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="E121" s="1" t="n">
         <v>1.85</v>
       </c>
     </row>
@@ -2377,11 +2743,14 @@
         <v>1.2965</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>1.2965</v>
+        <v>1.2964</v>
       </c>
       <c r="D122" s="1" t="n">
         <v>1.2965</v>
       </c>
+      <c r="E122" s="1" t="n">
+        <v>1.2964</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2393,11 +2762,14 @@
         <v>0.32</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>0.32</v>
+        <v>0.319</v>
       </c>
       <c r="D123" s="1" t="n">
         <v>0.32</v>
       </c>
+      <c r="E123" s="1" t="n">
+        <v>0.319</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2409,11 +2781,14 @@
         <v>0.12506</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>0.12506</v>
+        <v>0.12242</v>
       </c>
       <c r="D124" s="1" t="n">
         <v>0.12506</v>
       </c>
+      <c r="E124" s="1" t="n">
+        <v>0.12242</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2425,9 +2800,12 @@
         <v>0.008168999999999999</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>0.008168999999999999</v>
+        <v>0.008181000000000001</v>
       </c>
       <c r="D125" s="1" t="n">
+        <v>0.008181000000000001</v>
+      </c>
+      <c r="E125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -2441,9 +2819,12 @@
         <v>0.01574</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>0.01574</v>
+        <v>0.01576</v>
       </c>
       <c r="D126" s="1" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="E126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -2457,9 +2838,12 @@
         <v>0.04402</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>0.04402</v>
+        <v>0.04441</v>
       </c>
       <c r="D127" s="1" t="n">
+        <v>0.04441</v>
+      </c>
+      <c r="E127" s="1" t="n">
         <v>0.04402</v>
       </c>
     </row>
@@ -2473,9 +2857,12 @@
         <v>0.04577</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>0.04577</v>
+        <v>0.0458</v>
       </c>
       <c r="D128" s="1" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="E128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -2489,9 +2876,12 @@
         <v>0.0961</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>0.0961</v>
+        <v>0.09635000000000001</v>
       </c>
       <c r="D129" s="1" t="n">
+        <v>0.09635000000000001</v>
+      </c>
+      <c r="E129" s="1" t="n">
         <v>0.0961</v>
       </c>
     </row>
@@ -2505,11 +2895,14 @@
         <v>0.09927</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>0.09927</v>
+        <v>0.09896000000000001</v>
       </c>
       <c r="D130" s="1" t="n">
         <v>0.09927</v>
       </c>
+      <c r="E130" s="1" t="n">
+        <v>0.09896000000000001</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2521,9 +2914,12 @@
         <v>0.16444</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>0.16444</v>
+        <v>0.16577</v>
       </c>
       <c r="D131" s="1" t="n">
+        <v>0.16577</v>
+      </c>
+      <c r="E131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -2537,9 +2933,12 @@
         <v>0.01678</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>0.01678</v>
+        <v>0.01693</v>
       </c>
       <c r="D132" s="1" t="n">
+        <v>0.01693</v>
+      </c>
+      <c r="E132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -2553,9 +2952,12 @@
         <v>0.06635000000000001</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>0.06635000000000001</v>
+        <v>0.06652</v>
       </c>
       <c r="D133" s="1" t="n">
+        <v>0.06652</v>
+      </c>
+      <c r="E133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -2569,9 +2971,12 @@
         <v>0.3008</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>0.3008</v>
+        <v>0.3023</v>
       </c>
       <c r="D134" s="1" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="E134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -2585,11 +2990,14 @@
         <v>0.04515</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>0.04515</v>
+        <v>0.04514</v>
       </c>
       <c r="D135" s="1" t="n">
         <v>0.04515</v>
       </c>
+      <c r="E135" s="1" t="n">
+        <v>0.04514</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2601,9 +3009,12 @@
         <v>0.782</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="D136" s="1" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="E136" s="1" t="n">
         <v>0.782</v>
       </c>
     </row>
@@ -2617,9 +3028,12 @@
         <v>0.1164</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>0.1164</v>
+        <v>0.1168</v>
       </c>
       <c r="D137" s="1" t="n">
+        <v>0.1168</v>
+      </c>
+      <c r="E137" s="1" t="n">
         <v>0.1164</v>
       </c>
     </row>
@@ -2633,9 +3047,12 @@
         <v>0.14528</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>0.14528</v>
+        <v>0.146</v>
       </c>
       <c r="D138" s="1" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="E138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -2654,6 +3071,9 @@
       <c r="D139" s="1" t="n">
         <v>0.05719</v>
       </c>
+      <c r="E139" s="1" t="n">
+        <v>0.05719</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2665,9 +3085,12 @@
         <v>0.007274</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>0.007274</v>
+        <v>0.007295</v>
       </c>
       <c r="D140" s="1" t="n">
+        <v>0.007295</v>
+      </c>
+      <c r="E140" s="1" t="n">
         <v>0.007274</v>
       </c>
     </row>
@@ -2681,9 +3104,12 @@
         <v>0.09588000000000001</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>0.09588000000000001</v>
+        <v>0.09601</v>
       </c>
       <c r="D141" s="1" t="n">
+        <v>0.09601</v>
+      </c>
+      <c r="E141" s="1" t="n">
         <v>0.09588000000000001</v>
       </c>
     </row>
@@ -2697,9 +3123,12 @@
         <v>0.08314000000000001</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>0.08314000000000001</v>
+        <v>0.08348</v>
       </c>
       <c r="D142" s="1" t="n">
+        <v>0.08348</v>
+      </c>
+      <c r="E142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -2713,9 +3142,12 @@
         <v>0.00847</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>0.00847</v>
+        <v>0.00852</v>
       </c>
       <c r="D143" s="1" t="n">
+        <v>0.00852</v>
+      </c>
+      <c r="E143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -2729,9 +3161,12 @@
         <v>0.0726</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>0.0726</v>
+        <v>0.07288</v>
       </c>
       <c r="D144" s="1" t="n">
+        <v>0.07288</v>
+      </c>
+      <c r="E144" s="1" t="n">
         <v>0.0726</v>
       </c>
     </row>
@@ -2745,9 +3180,12 @@
         <v>0.4302</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>0.4302</v>
+        <v>0.4303</v>
       </c>
       <c r="D145" s="1" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="E145" s="1" t="n">
         <v>0.4302</v>
       </c>
     </row>
@@ -2761,11 +3199,14 @@
         <v>0.03276</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>0.03276</v>
+        <v>0.03252</v>
       </c>
       <c r="D146" s="1" t="n">
         <v>0.03276</v>
       </c>
+      <c r="E146" s="1" t="n">
+        <v>0.03252</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2777,9 +3218,12 @@
         <v>390.16</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>390.16</v>
+        <v>390.55</v>
       </c>
       <c r="D147" s="1" t="n">
+        <v>390.55</v>
+      </c>
+      <c r="E147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -2793,11 +3237,14 @@
         <v>0.033</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>0.033</v>
+        <v>0.0329</v>
       </c>
       <c r="D148" s="1" t="n">
         <v>0.033</v>
       </c>
+      <c r="E148" s="1" t="n">
+        <v>0.0329</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2809,9 +3256,12 @@
         <v>0.05304</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>0.05304</v>
+        <v>0.05322</v>
       </c>
       <c r="D149" s="1" t="n">
+        <v>0.05322</v>
+      </c>
+      <c r="E149" s="1" t="n">
         <v>0.05304</v>
       </c>
     </row>
@@ -2825,9 +3275,12 @@
         <v>0.0004396</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>0.0004396</v>
+        <v>0.000443</v>
       </c>
       <c r="D150" s="1" t="n">
+        <v>0.000443</v>
+      </c>
+      <c r="E150" s="1" t="n">
         <v>0.0004396</v>
       </c>
     </row>
@@ -2841,9 +3294,12 @@
         <v>0.02173</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>0.02173</v>
+        <v>0.02183</v>
       </c>
       <c r="D151" s="1" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="E151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -2857,9 +3313,12 @@
         <v>0.001781</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>0.001781</v>
+        <v>0.001783</v>
       </c>
       <c r="D152" s="1" t="n">
+        <v>0.001783</v>
+      </c>
+      <c r="E152" s="1" t="n">
         <v>0.001781</v>
       </c>
     </row>
@@ -2873,11 +3332,14 @@
         <v>6.4e-06</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>6.4e-06</v>
+        <v>6.2e-06</v>
       </c>
       <c r="D153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
+      <c r="E153" s="1" t="n">
+        <v>6.2e-06</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2889,9 +3351,12 @@
         <v>0.159</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>0.159</v>
+        <v>0.1598</v>
       </c>
       <c r="D154" s="1" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="E154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -2905,9 +3370,12 @@
         <v>0.03757</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>0.03757</v>
+        <v>0.03765</v>
       </c>
       <c r="D155" s="1" t="n">
+        <v>0.03765</v>
+      </c>
+      <c r="E155" s="1" t="n">
         <v>0.03757</v>
       </c>
     </row>
@@ -2921,9 +3389,12 @@
         <v>0.005379</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>0.005379</v>
+        <v>0.005402</v>
       </c>
       <c r="D156" s="1" t="n">
+        <v>0.005402</v>
+      </c>
+      <c r="E156" s="1" t="n">
         <v>0.005379</v>
       </c>
     </row>
@@ -2937,9 +3408,12 @@
         <v>0.02282</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>0.02282</v>
+        <v>0.02284</v>
       </c>
       <c r="D157" s="1" t="n">
+        <v>0.02284</v>
+      </c>
+      <c r="E157" s="1" t="n">
         <v>0.02282</v>
       </c>
     </row>
@@ -2953,9 +3427,12 @@
         <v>1.086</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>1.086</v>
+        <v>1.09</v>
       </c>
       <c r="D158" s="1" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -2969,9 +3446,12 @@
         <v>2.545</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>2.545</v>
+        <v>2.558</v>
       </c>
       <c r="D159" s="1" t="n">
+        <v>2.558</v>
+      </c>
+      <c r="E159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -2985,9 +3465,12 @@
         <v>4.836</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>4.836</v>
+        <v>4.852</v>
       </c>
       <c r="D160" s="1" t="n">
+        <v>4.852</v>
+      </c>
+      <c r="E160" s="1" t="n">
         <v>4.836</v>
       </c>
     </row>
@@ -3001,9 +3484,12 @@
         <v>0.159</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>0.159</v>
+        <v>0.1591</v>
       </c>
       <c r="D161" s="1" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="E161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -3017,11 +3503,14 @@
         <v>0.20604</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>0.20604</v>
+        <v>0.20584</v>
       </c>
       <c r="D162" s="1" t="n">
         <v>0.20604</v>
       </c>
+      <c r="E162" s="1" t="n">
+        <v>0.20584</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3033,9 +3522,12 @@
         <v>0.03927</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>0.03927</v>
+        <v>0.03939</v>
       </c>
       <c r="D163" s="1" t="n">
+        <v>0.03939</v>
+      </c>
+      <c r="E163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -3049,9 +3541,12 @@
         <v>0.06271</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>0.06271</v>
+        <v>0.0629</v>
       </c>
       <c r="D164" s="1" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="E164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -3065,11 +3560,14 @@
         <v>0.3542</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>0.3542</v>
+        <v>0.3525</v>
       </c>
       <c r="D165" s="1" t="n">
         <v>0.3542</v>
       </c>
+      <c r="E165" s="1" t="n">
+        <v>0.3525</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3081,9 +3579,12 @@
         <v>138.82</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>138.82</v>
+        <v>139.27</v>
       </c>
       <c r="D166" s="1" t="n">
+        <v>139.27</v>
+      </c>
+      <c r="E166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -3097,11 +3598,14 @@
         <v>0.0006477</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>0.0006477</v>
+        <v>0.0006471</v>
       </c>
       <c r="D167" s="1" t="n">
         <v>0.0006477</v>
       </c>
+      <c r="E167" s="1" t="n">
+        <v>0.0006471</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3113,9 +3617,12 @@
         <v>0.01664</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>0.01664</v>
+        <v>0.01673</v>
       </c>
       <c r="D168" s="1" t="n">
+        <v>0.01673</v>
+      </c>
+      <c r="E168" s="1" t="n">
         <v>0.01664</v>
       </c>
     </row>
@@ -3129,9 +3636,12 @@
         <v>0.04788</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>0.04788</v>
+        <v>0.04798</v>
       </c>
       <c r="D169" s="1" t="n">
+        <v>0.04798</v>
+      </c>
+      <c r="E169" s="1" t="n">
         <v>0.04788</v>
       </c>
     </row>
@@ -3145,9 +3655,12 @@
         <v>4.265</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>4.265</v>
+        <v>4.267</v>
       </c>
       <c r="D170" s="1" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="E170" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -3161,9 +3674,12 @@
         <v>0.03846</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>0.03846</v>
+        <v>0.03859</v>
       </c>
       <c r="D171" s="1" t="n">
+        <v>0.03859</v>
+      </c>
+      <c r="E171" s="1" t="n">
         <v>0.03846</v>
       </c>
     </row>
@@ -3182,6 +3698,9 @@
       <c r="D172" s="1" t="n">
         <v>0.0427</v>
       </c>
+      <c r="E172" s="1" t="n">
+        <v>0.0427</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3193,9 +3712,12 @@
         <v>0.02382</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>0.02382</v>
+        <v>0.023878</v>
       </c>
       <c r="D173" s="1" t="n">
+        <v>0.023878</v>
+      </c>
+      <c r="E173" s="1" t="n">
         <v>0.02382</v>
       </c>
     </row>
@@ -3209,11 +3731,14 @@
         <v>1.0705</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>1.0705</v>
+        <v>1.0704</v>
       </c>
       <c r="D174" s="1" t="n">
         <v>1.0705</v>
       </c>
+      <c r="E174" s="1" t="n">
+        <v>1.0704</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3225,9 +3750,12 @@
         <v>0.028947</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>0.028947</v>
+        <v>0.028967</v>
       </c>
       <c r="D175" s="1" t="n">
+        <v>0.028967</v>
+      </c>
+      <c r="E175" s="1" t="n">
         <v>0.028947</v>
       </c>
     </row>
@@ -3241,9 +3769,12 @@
         <v>0.02158</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>0.02158</v>
+        <v>0.02178</v>
       </c>
       <c r="D176" s="1" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="E176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -3257,9 +3788,12 @@
         <v>0.5416</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>0.5416</v>
+        <v>0.5444</v>
       </c>
       <c r="D177" s="1" t="n">
+        <v>0.5444</v>
+      </c>
+      <c r="E177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -3273,11 +3807,14 @@
         <v>0.08268</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>0.08268</v>
+        <v>0.08255999999999999</v>
       </c>
       <c r="D178" s="1" t="n">
         <v>0.08268</v>
       </c>
+      <c r="E178" s="1" t="n">
+        <v>0.08255999999999999</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3289,9 +3826,12 @@
         <v>0.02119</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>0.02119</v>
+        <v>0.0213</v>
       </c>
       <c r="D179" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="E179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -3305,9 +3845,12 @@
         <v>0.26951</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>0.26951</v>
+        <v>0.27033</v>
       </c>
       <c r="D180" s="1" t="n">
+        <v>0.27033</v>
+      </c>
+      <c r="E180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -3321,9 +3864,12 @@
         <v>0.00418</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>0.00418</v>
+        <v>0.0042</v>
       </c>
       <c r="D181" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="E181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -3337,11 +3883,14 @@
         <v>0.07978</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>0.07978</v>
+        <v>0.07931000000000001</v>
       </c>
       <c r="D182" s="1" t="n">
         <v>0.07978</v>
       </c>
+      <c r="E182" s="1" t="n">
+        <v>0.07931000000000001</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3353,9 +3902,12 @@
         <v>0.02334</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>0.02334</v>
+        <v>0.02357</v>
       </c>
       <c r="D183" s="1" t="n">
+        <v>0.02357</v>
+      </c>
+      <c r="E183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -3369,9 +3921,12 @@
         <v>6.957e-05</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>6.957e-05</v>
+        <v>6.981e-05</v>
       </c>
       <c r="D184" s="1" t="n">
+        <v>6.981e-05</v>
+      </c>
+      <c r="E184" s="1" t="n">
         <v>6.957e-05</v>
       </c>
     </row>
@@ -3385,9 +3940,12 @@
         <v>0.02123</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>0.02123</v>
+        <v>0.02124</v>
       </c>
       <c r="D185" s="1" t="n">
+        <v>0.02124</v>
+      </c>
+      <c r="E185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -3401,9 +3959,12 @@
         <v>0.01629</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>0.01629</v>
+        <v>0.01632</v>
       </c>
       <c r="D186" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="E186" s="1" t="n">
         <v>0.01629</v>
       </c>
     </row>
@@ -3417,9 +3978,12 @@
         <v>0.971</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>0.971</v>
+        <v>0.974</v>
       </c>
       <c r="D187" s="1" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E187" s="1" t="n">
         <v>0.971</v>
       </c>
     </row>
@@ -3433,9 +3997,12 @@
         <v>0.0237</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>0.0237</v>
+        <v>0.0239</v>
       </c>
       <c r="D188" s="1" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="E188" s="1" t="n">
         <v>0.0237</v>
       </c>
     </row>
@@ -3449,9 +4016,12 @@
         <v>1.8627</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>1.8627</v>
+        <v>1.8658</v>
       </c>
       <c r="D189" s="1" t="n">
+        <v>1.8658</v>
+      </c>
+      <c r="E189" s="1" t="n">
         <v>1.8627</v>
       </c>
     </row>
@@ -3465,9 +4035,12 @@
         <v>1.835</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>1.835</v>
+        <v>1.838</v>
       </c>
       <c r="D190" s="1" t="n">
+        <v>1.838</v>
+      </c>
+      <c r="E190" s="1" t="n">
         <v>1.835</v>
       </c>
     </row>
@@ -3481,9 +4054,12 @@
         <v>0.02669</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>0.02669</v>
+        <v>0.02671</v>
       </c>
       <c r="D191" s="1" t="n">
+        <v>0.02671</v>
+      </c>
+      <c r="E191" s="1" t="n">
         <v>0.02669</v>
       </c>
     </row>
@@ -3497,9 +4073,12 @@
         <v>0.0963</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>0.0963</v>
+        <v>0.0973</v>
       </c>
       <c r="D192" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="E192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -3513,9 +4092,12 @@
         <v>0.1668</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>0.1668</v>
+        <v>0.1675</v>
       </c>
       <c r="D193" s="1" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="E193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -3529,9 +4111,12 @@
         <v>16.237</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>16.237</v>
+        <v>16.294</v>
       </c>
       <c r="D194" s="1" t="n">
+        <v>16.294</v>
+      </c>
+      <c r="E194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -3545,11 +4130,14 @@
         <v>4.096</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>4.096</v>
+        <v>4.093</v>
       </c>
       <c r="D195" s="1" t="n">
         <v>4.096</v>
       </c>
+      <c r="E195" s="1" t="n">
+        <v>4.093</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3561,9 +4149,12 @@
         <v>1.2705</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>1.2705</v>
+        <v>1.2794</v>
       </c>
       <c r="D196" s="1" t="n">
+        <v>1.2794</v>
+      </c>
+      <c r="E196" s="1" t="n">
         <v>1.2705</v>
       </c>
     </row>
@@ -3577,11 +4168,14 @@
         <v>3.092</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>3.092</v>
+        <v>3.077</v>
       </c>
       <c r="D197" s="1" t="n">
         <v>3.092</v>
       </c>
+      <c r="E197" s="1" t="n">
+        <v>3.077</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3593,9 +4187,12 @@
         <v>0.01257</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>0.01257</v>
+        <v>0.01265</v>
       </c>
       <c r="D198" s="1" t="n">
+        <v>0.01265</v>
+      </c>
+      <c r="E198" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -3609,9 +4206,12 @@
         <v>0.0001756</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>0.0001756</v>
+        <v>0.0001762</v>
       </c>
       <c r="D199" s="1" t="n">
+        <v>0.0001762</v>
+      </c>
+      <c r="E199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -3625,9 +4225,12 @@
         <v>115.11</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>115.11</v>
+        <v>115.62</v>
       </c>
       <c r="D200" s="1" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="E200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -3641,9 +4244,12 @@
         <v>0.01023</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>0.01023</v>
+        <v>0.01027</v>
       </c>
       <c r="D201" s="1" t="n">
+        <v>0.01027</v>
+      </c>
+      <c r="E201" s="1" t="n">
         <v>0.01023</v>
       </c>
     </row>
@@ -3657,9 +4263,12 @@
         <v>0.01061</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>0.01061</v>
+        <v>0.01073</v>
       </c>
       <c r="D202" s="1" t="n">
+        <v>0.01073</v>
+      </c>
+      <c r="E202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -3673,9 +4282,12 @@
         <v>0.003137</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>0.003137</v>
+        <v>0.003153</v>
       </c>
       <c r="D203" s="1" t="n">
+        <v>0.003153</v>
+      </c>
+      <c r="E203" s="1" t="n">
         <v>0.003137</v>
       </c>
     </row>
@@ -3689,9 +4301,12 @@
         <v>28.32</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>28.32</v>
+        <v>28.38</v>
       </c>
       <c r="D204" s="1" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="E204" s="1" t="n">
         <v>28.32</v>
       </c>
     </row>
@@ -3705,11 +4320,14 @@
         <v>0.5636</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>0.5636</v>
+        <v>0.5627</v>
       </c>
       <c r="D205" s="1" t="n">
         <v>0.5636</v>
       </c>
+      <c r="E205" s="1" t="n">
+        <v>0.5627</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3721,9 +4339,12 @@
         <v>0.0004394</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>0.0004394</v>
+        <v>0.0004403</v>
       </c>
       <c r="D206" s="1" t="n">
+        <v>0.0004403</v>
+      </c>
+      <c r="E206" s="1" t="n">
         <v>0.0004394</v>
       </c>
     </row>
@@ -3737,9 +4358,12 @@
         <v>0.04651</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>0.04651</v>
+        <v>0.04667</v>
       </c>
       <c r="D207" s="1" t="n">
+        <v>0.04667</v>
+      </c>
+      <c r="E207" s="1" t="n">
         <v>0.04651</v>
       </c>
     </row>
@@ -3758,6 +4382,9 @@
       <c r="D208" s="1" t="n">
         <v>0.09</v>
       </c>
+      <c r="E208" s="1" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3769,9 +4396,12 @@
         <v>0.02561</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>0.02561</v>
+        <v>0.02567</v>
       </c>
       <c r="D209" s="1" t="n">
+        <v>0.02567</v>
+      </c>
+      <c r="E209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -3785,9 +4415,12 @@
         <v>0.012652</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>0.012652</v>
+        <v>0.012655</v>
       </c>
       <c r="D210" s="1" t="n">
+        <v>0.012655</v>
+      </c>
+      <c r="E210" s="1" t="n">
         <v>0.012652</v>
       </c>
     </row>
@@ -3801,9 +4434,12 @@
         <v>0.0914</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>0.0914</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="D211" s="1" t="n">
+        <v>0.09180000000000001</v>
+      </c>
+      <c r="E211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -3817,9 +4453,12 @@
         <v>0.007053</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>0.007053</v>
+        <v>0.007065</v>
       </c>
       <c r="D212" s="1" t="n">
+        <v>0.007065</v>
+      </c>
+      <c r="E212" s="1" t="n">
         <v>0.007053</v>
       </c>
     </row>
@@ -3833,9 +4472,12 @@
         <v>0.02958</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>0.02958</v>
+        <v>0.02966</v>
       </c>
       <c r="D213" s="1" t="n">
+        <v>0.02966</v>
+      </c>
+      <c r="E213" s="1" t="n">
         <v>0.02958</v>
       </c>
     </row>
@@ -3854,6 +4496,9 @@
       <c r="D214" s="1" t="n">
         <v>0.2708</v>
       </c>
+      <c r="E214" s="1" t="n">
+        <v>0.2708</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -3865,9 +4510,12 @@
         <v>0.0217</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>0.0217</v>
+        <v>0.02171</v>
       </c>
       <c r="D215" s="1" t="n">
+        <v>0.02171</v>
+      </c>
+      <c r="E215" s="1" t="n">
         <v>0.0217</v>
       </c>
     </row>
@@ -3881,9 +4529,12 @@
         <v>0.01475</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>0.01475</v>
+        <v>0.01492</v>
       </c>
       <c r="D216" s="1" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="E216" s="1" t="n">
         <v>0.01475</v>
       </c>
     </row>
@@ -3897,9 +4548,12 @@
         <v>0.2532</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>0.2532</v>
+        <v>0.2538</v>
       </c>
       <c r="D217" s="1" t="n">
+        <v>0.2538</v>
+      </c>
+      <c r="E217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -3913,9 +4567,12 @@
         <v>0.3065</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>0.3065</v>
+        <v>0.3087</v>
       </c>
       <c r="D218" s="1" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="E218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -3929,9 +4586,12 @@
         <v>0.1773</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>0.1773</v>
+        <v>0.1784</v>
       </c>
       <c r="D219" s="1" t="n">
+        <v>0.1784</v>
+      </c>
+      <c r="E219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -3945,9 +4605,12 @@
         <v>14.97</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>14.97</v>
+        <v>15</v>
       </c>
       <c r="D220" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E220" s="1" t="n">
         <v>14.97</v>
       </c>
     </row>
@@ -3961,9 +4624,12 @@
         <v>0.01592</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>0.01592</v>
+        <v>0.01594</v>
       </c>
       <c r="D221" s="1" t="n">
+        <v>0.01594</v>
+      </c>
+      <c r="E221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -3977,9 +4643,12 @@
         <v>66.17</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>66.17</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D222" s="1" t="n">
+        <v>66.70999999999999</v>
+      </c>
+      <c r="E222" s="1" t="n">
         <v>66.17</v>
       </c>
     </row>
@@ -3993,9 +4662,12 @@
         <v>0.09203</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>0.09203</v>
+        <v>0.09272</v>
       </c>
       <c r="D223" s="1" t="n">
+        <v>0.09272</v>
+      </c>
+      <c r="E223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -4009,9 +4681,12 @@
         <v>0.03913</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>0.03913</v>
+        <v>0.0393</v>
       </c>
       <c r="D224" s="1" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="E224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -4025,9 +4700,12 @@
         <v>0.5695</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>0.5695</v>
+        <v>0.5725</v>
       </c>
       <c r="D225" s="1" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="E225" s="1" t="n">
         <v>0.5695</v>
       </c>
     </row>
@@ -4046,6 +4724,9 @@
       <c r="D226" s="1" t="n">
         <v>0.1167</v>
       </c>
+      <c r="E226" s="1" t="n">
+        <v>0.1167</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4057,9 +4738,12 @@
         <v>0.3189</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>0.3189</v>
+        <v>0.3201</v>
       </c>
       <c r="D227" s="1" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="E227" s="1" t="n">
         <v>0.3189</v>
       </c>
     </row>
@@ -4073,9 +4757,12 @@
         <v>6.066</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>6.066</v>
+        <v>6.09</v>
       </c>
       <c r="D228" s="1" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="E228" s="1" t="n">
         <v>6.066</v>
       </c>
     </row>
@@ -4089,9 +4776,12 @@
         <v>0.0287</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>0.0287</v>
+        <v>0.0289</v>
       </c>
       <c r="D229" s="1" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="E229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -4105,11 +4795,14 @@
         <v>0.3297</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>0.3297</v>
+        <v>0.3294</v>
       </c>
       <c r="D230" s="1" t="n">
         <v>0.3297</v>
       </c>
+      <c r="E230" s="1" t="n">
+        <v>0.3294</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4121,9 +4814,12 @@
         <v>0.12024</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>0.12024</v>
+        <v>0.12041</v>
       </c>
       <c r="D231" s="1" t="n">
+        <v>0.12041</v>
+      </c>
+      <c r="E231" s="1" t="n">
         <v>0.12024</v>
       </c>
     </row>
@@ -4137,11 +4833,14 @@
         <v>0.1186</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>0.1186</v>
+        <v>0.1185</v>
       </c>
       <c r="D232" s="1" t="n">
         <v>0.1186</v>
       </c>
+      <c r="E232" s="1" t="n">
+        <v>0.1185</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4153,9 +4852,12 @@
         <v>0.03018</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>0.03018</v>
+        <v>0.03019</v>
       </c>
       <c r="D233" s="1" t="n">
+        <v>0.03019</v>
+      </c>
+      <c r="E233" s="1" t="n">
         <v>0.03018</v>
       </c>
     </row>
@@ -4169,11 +4871,14 @@
         <v>0.015715</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>0.015715</v>
+        <v>0.015644</v>
       </c>
       <c r="D234" s="1" t="n">
         <v>0.015715</v>
       </c>
+      <c r="E234" s="1" t="n">
+        <v>0.015644</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4185,9 +4890,12 @@
         <v>0.01275</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>0.01275</v>
+        <v>0.01279</v>
       </c>
       <c r="D235" s="1" t="n">
+        <v>0.01279</v>
+      </c>
+      <c r="E235" s="1" t="n">
         <v>0.01275</v>
       </c>
     </row>
@@ -4201,9 +4909,12 @@
         <v>0.01924</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>0.01924</v>
+        <v>0.01929</v>
       </c>
       <c r="D236" s="1" t="n">
+        <v>0.01929</v>
+      </c>
+      <c r="E236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -4217,11 +4928,14 @@
         <v>0.08509</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>0.08509</v>
+        <v>0.08469</v>
       </c>
       <c r="D237" s="1" t="n">
         <v>0.08509</v>
       </c>
+      <c r="E237" s="1" t="n">
+        <v>0.08469</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4233,9 +4947,12 @@
         <v>0.05884</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>0.05884</v>
+        <v>0.05892</v>
       </c>
       <c r="D238" s="1" t="n">
+        <v>0.05892</v>
+      </c>
+      <c r="E238" s="1" t="n">
         <v>0.05884</v>
       </c>
     </row>
@@ -4249,11 +4966,14 @@
         <v>0.009063</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>0.009063</v>
+        <v>0.009027</v>
       </c>
       <c r="D239" s="1" t="n">
         <v>0.009063</v>
       </c>
+      <c r="E239" s="1" t="n">
+        <v>0.009027</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4265,9 +4985,12 @@
         <v>0.004157</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>0.004157</v>
+        <v>0.004162</v>
       </c>
       <c r="D240" s="1" t="n">
+        <v>0.004162</v>
+      </c>
+      <c r="E240" s="1" t="n">
         <v>0.004157</v>
       </c>
     </row>
@@ -4281,9 +5004,12 @@
         <v>0.2392</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>0.2392</v>
+        <v>0.2404</v>
       </c>
       <c r="D241" s="1" t="n">
+        <v>0.2404</v>
+      </c>
+      <c r="E241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -4297,9 +5023,12 @@
         <v>0.058</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>0.058</v>
+        <v>0.0582</v>
       </c>
       <c r="D242" s="1" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="E242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -4313,9 +5042,12 @@
         <v>0.02331</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>0.02331</v>
+        <v>0.0234</v>
       </c>
       <c r="D243" s="1" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="E243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -4329,11 +5061,14 @@
         <v>0.05623</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>0.05623</v>
+        <v>0.05572</v>
       </c>
       <c r="D244" s="1" t="n">
         <v>0.05623</v>
       </c>
+      <c r="E244" s="1" t="n">
+        <v>0.05572</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4345,9 +5080,12 @@
         <v>0.03414</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>0.03414</v>
+        <v>0.03433</v>
       </c>
       <c r="D245" s="1" t="n">
+        <v>0.03433</v>
+      </c>
+      <c r="E245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -4361,9 +5099,12 @@
         <v>0.06004</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>0.06004</v>
+        <v>0.06011</v>
       </c>
       <c r="D246" s="1" t="n">
+        <v>0.06011</v>
+      </c>
+      <c r="E246" s="1" t="n">
         <v>0.06004</v>
       </c>
     </row>
@@ -4377,9 +5118,12 @@
         <v>0.384</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="D247" s="1" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E247" s="1" t="n">
         <v>0.384</v>
       </c>
     </row>
@@ -4393,9 +5137,12 @@
         <v>0.5167</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>0.5167</v>
+        <v>0.519</v>
       </c>
       <c r="D248" s="1" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="E248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -4409,9 +5156,12 @@
         <v>0.0277</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>0.0277</v>
+        <v>0.02797</v>
       </c>
       <c r="D249" s="1" t="n">
+        <v>0.02797</v>
+      </c>
+      <c r="E249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -4425,11 +5175,14 @@
         <v>0.01295</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>0.01295</v>
+        <v>0.01288</v>
       </c>
       <c r="D250" s="1" t="n">
         <v>0.01295</v>
       </c>
+      <c r="E250" s="1" t="n">
+        <v>0.01288</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4441,9 +5194,12 @@
         <v>0.1</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>0.1</v>
+        <v>0.1003</v>
       </c>
       <c r="D251" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="E251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4457,9 +5213,12 @@
         <v>0.00716</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>0.00716</v>
+        <v>0.00719</v>
       </c>
       <c r="D252" s="1" t="n">
+        <v>0.00719</v>
+      </c>
+      <c r="E252" s="1" t="n">
         <v>0.00716</v>
       </c>
     </row>
@@ -4473,11 +5232,14 @@
         <v>0.005561</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>0.005561</v>
+        <v>0.005554</v>
       </c>
       <c r="D253" s="1" t="n">
         <v>0.005561</v>
       </c>
+      <c r="E253" s="1" t="n">
+        <v>0.005554</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4489,9 +5251,12 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0646</v>
       </c>
       <c r="D254" s="1" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="E254" s="1" t="n">
         <v>0.06419999999999999</v>
       </c>
     </row>
@@ -4505,9 +5270,12 @@
         <v>0.01425</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>0.01425</v>
+        <v>0.01434</v>
       </c>
       <c r="D255" s="1" t="n">
+        <v>0.01434</v>
+      </c>
+      <c r="E255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -4521,9 +5289,12 @@
         <v>0.999296</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>0.999296</v>
+        <v>0.999297</v>
       </c>
       <c r="D256" s="1" t="n">
+        <v>0.999297</v>
+      </c>
+      <c r="E256" s="1" t="n">
         <v>0.999296</v>
       </c>
     </row>
@@ -4537,9 +5308,12 @@
         <v>0.02092</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>0.02092</v>
+        <v>0.02101</v>
       </c>
       <c r="D257" s="1" t="n">
+        <v>0.02101</v>
+      </c>
+      <c r="E257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -4553,9 +5327,12 @@
         <v>0.01133</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>0.01133</v>
+        <v>0.01142</v>
       </c>
       <c r="D258" s="1" t="n">
+        <v>0.01142</v>
+      </c>
+      <c r="E258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -4569,9 +5346,12 @@
         <v>0.5085</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>0.5085</v>
+        <v>0.5119</v>
       </c>
       <c r="D259" s="1" t="n">
+        <v>0.5119</v>
+      </c>
+      <c r="E259" s="1" t="n">
         <v>0.5085</v>
       </c>
     </row>
@@ -4585,9 +5365,12 @@
         <v>0.08436</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>0.08436</v>
+        <v>0.08459</v>
       </c>
       <c r="D260" s="1" t="n">
+        <v>0.08459</v>
+      </c>
+      <c r="E260" s="1" t="n">
         <v>0.08436</v>
       </c>
     </row>
@@ -4601,9 +5384,12 @@
         <v>0.0413</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>0.0413</v>
+        <v>0.04138</v>
       </c>
       <c r="D261" s="1" t="n">
+        <v>0.04138</v>
+      </c>
+      <c r="E261" s="1" t="n">
         <v>0.0413</v>
       </c>
     </row>
@@ -4622,6 +5408,9 @@
       <c r="D262" s="1" t="n">
         <v>2.288</v>
       </c>
+      <c r="E262" s="1" t="n">
+        <v>2.288</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -4633,9 +5422,12 @@
         <v>18.44</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>18.44</v>
+        <v>18.5</v>
       </c>
       <c r="D263" s="1" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -4649,9 +5441,12 @@
         <v>0.008377000000000001</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>0.008377000000000001</v>
+        <v>0.008404</v>
       </c>
       <c r="D264" s="1" t="n">
+        <v>0.008404</v>
+      </c>
+      <c r="E264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -4665,9 +5460,12 @@
         <v>0.3628</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>0.3628</v>
+        <v>0.363</v>
       </c>
       <c r="D265" s="1" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="E265" s="1" t="n">
         <v>0.3628</v>
       </c>
     </row>
@@ -4681,9 +5479,12 @@
         <v>0.053924</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>0.053924</v>
+        <v>0.054291</v>
       </c>
       <c r="D266" s="1" t="n">
+        <v>0.054291</v>
+      </c>
+      <c r="E266" s="1" t="n">
         <v>0.053924</v>
       </c>
     </row>
@@ -4697,9 +5498,12 @@
         <v>0.1313</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>0.1313</v>
+        <v>0.1321</v>
       </c>
       <c r="D267" s="1" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="E267" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -4713,9 +5517,12 @@
         <v>0.007759</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>0.007759</v>
+        <v>0.007845</v>
       </c>
       <c r="D268" s="1" t="n">
+        <v>0.007845</v>
+      </c>
+      <c r="E268" s="1" t="n">
         <v>0.007759</v>
       </c>
     </row>
@@ -4729,11 +5536,14 @@
         <v>0.00124</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>0.00124</v>
+        <v>0.001235</v>
       </c>
       <c r="D269" s="1" t="n">
         <v>0.00124</v>
       </c>
+      <c r="E269" s="1" t="n">
+        <v>0.001235</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -4745,11 +5555,14 @@
         <v>0.28997</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>0.28997</v>
+        <v>0.28989</v>
       </c>
       <c r="D270" s="1" t="n">
         <v>0.28997</v>
       </c>
+      <c r="E270" s="1" t="n">
+        <v>0.28989</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -4761,9 +5574,12 @@
         <v>0.03868</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>0.03868</v>
+        <v>0.03899</v>
       </c>
       <c r="D271" s="1" t="n">
+        <v>0.03899</v>
+      </c>
+      <c r="E271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -4777,9 +5593,12 @@
         <v>0.05111</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>0.05111</v>
+        <v>0.05133</v>
       </c>
       <c r="D272" s="1" t="n">
+        <v>0.05133</v>
+      </c>
+      <c r="E272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -4793,9 +5612,12 @@
         <v>0.00761</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>0.00761</v>
+        <v>0.0077</v>
       </c>
       <c r="D273" s="1" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="E273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -4809,9 +5631,12 @@
         <v>0.005721</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>0.005721</v>
+        <v>0.005745</v>
       </c>
       <c r="D274" s="1" t="n">
+        <v>0.005745</v>
+      </c>
+      <c r="E274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -4825,9 +5650,12 @@
         <v>0.0005868</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>0.0005868</v>
+        <v>0.0005895</v>
       </c>
       <c r="D275" s="1" t="n">
+        <v>0.0005895</v>
+      </c>
+      <c r="E275" s="1" t="n">
         <v>0.0005868</v>
       </c>
     </row>
@@ -4841,11 +5669,14 @@
         <v>0.15167</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>0.15167</v>
+        <v>0.15089</v>
       </c>
       <c r="D276" s="1" t="n">
         <v>0.15167</v>
       </c>
+      <c r="E276" s="1" t="n">
+        <v>0.15089</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -4857,9 +5688,12 @@
         <v>0.022666</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>0.022666</v>
+        <v>0.022677</v>
       </c>
       <c r="D277" s="1" t="n">
+        <v>0.022677</v>
+      </c>
+      <c r="E277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -4873,11 +5707,14 @@
         <v>0.0421</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>0.0421</v>
+        <v>0.04179</v>
       </c>
       <c r="D278" s="1" t="n">
         <v>0.0421</v>
       </c>
+      <c r="E278" s="1" t="n">
+        <v>0.04179</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -4889,9 +5726,12 @@
         <v>0.0003954</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>0.0003954</v>
+        <v>0.0003982</v>
       </c>
       <c r="D279" s="1" t="n">
+        <v>0.0003982</v>
+      </c>
+      <c r="E279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -4905,9 +5745,12 @@
         <v>0.02195</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>0.02195</v>
+        <v>0.02216</v>
       </c>
       <c r="D280" s="1" t="n">
+        <v>0.02216</v>
+      </c>
+      <c r="E280" s="1" t="n">
         <v>0.02195</v>
       </c>
     </row>
@@ -4921,11 +5764,14 @@
         <v>0.0694</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>0.0694</v>
+        <v>0.06936</v>
       </c>
       <c r="D281" s="1" t="n">
         <v>0.0694</v>
       </c>
+      <c r="E281" s="1" t="n">
+        <v>0.06936</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -4937,9 +5783,12 @@
         <v>0.006758</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>0.006758</v>
+        <v>0.006804</v>
       </c>
       <c r="D282" s="1" t="n">
+        <v>0.006804</v>
+      </c>
+      <c r="E282" s="1" t="n">
         <v>0.006758</v>
       </c>
     </row>
@@ -4958,6 +5807,9 @@
       <c r="D283" s="1" t="n">
         <v>0.12</v>
       </c>
+      <c r="E283" s="1" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -4969,9 +5821,12 @@
         <v>0.005456</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>0.005456</v>
+        <v>0.005475</v>
       </c>
       <c r="D284" s="1" t="n">
+        <v>0.005475</v>
+      </c>
+      <c r="E284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -4985,9 +5840,12 @@
         <v>1.237</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>1.237</v>
+        <v>1.251</v>
       </c>
       <c r="D285" s="1" t="n">
+        <v>1.251</v>
+      </c>
+      <c r="E285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -5001,9 +5859,12 @@
         <v>0.4437</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>0.4437</v>
+        <v>0.4441</v>
       </c>
       <c r="D286" s="1" t="n">
+        <v>0.4441</v>
+      </c>
+      <c r="E286" s="1" t="n">
         <v>0.4437</v>
       </c>
     </row>
@@ -5017,9 +5878,12 @@
         <v>0.007835</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>0.007835</v>
+        <v>0.007865</v>
       </c>
       <c r="D287" s="1" t="n">
+        <v>0.007865</v>
+      </c>
+      <c r="E287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -5038,6 +5902,9 @@
       <c r="D288" s="1" t="n">
         <v>0.02922</v>
       </c>
+      <c r="E288" s="1" t="n">
+        <v>0.02922</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5049,9 +5916,12 @@
         <v>0.28</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>0.28</v>
+        <v>0.2811</v>
       </c>
       <c r="D289" s="1" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="E289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -5070,6 +5940,9 @@
       <c r="D290" s="1" t="n">
         <v>2.764</v>
       </c>
+      <c r="E290" s="1" t="n">
+        <v>2.764</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5081,9 +5954,12 @@
         <v>0.003155</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>0.003155</v>
+        <v>0.003176</v>
       </c>
       <c r="D291" s="1" t="n">
+        <v>0.003176</v>
+      </c>
+      <c r="E291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -5097,9 +5973,12 @@
         <v>0.4475</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>0.4475</v>
+        <v>0.4488</v>
       </c>
       <c r="D292" s="1" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="E292" s="1" t="n">
         <v>0.4475</v>
       </c>
     </row>
@@ -5113,11 +5992,14 @@
         <v>0.08298</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>0.08298</v>
+        <v>0.08295</v>
       </c>
       <c r="D293" s="1" t="n">
         <v>0.08298</v>
       </c>
+      <c r="E293" s="1" t="n">
+        <v>0.08295</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -5129,9 +6011,12 @@
         <v>0.02779</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>0.02779</v>
+        <v>0.02784</v>
       </c>
       <c r="D294" s="1" t="n">
+        <v>0.02784</v>
+      </c>
+      <c r="E294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -5145,9 +6030,12 @@
         <v>0.953</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>0.953</v>
+        <v>0.958</v>
       </c>
       <c r="D295" s="1" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="E295" s="1" t="n">
         <v>0.953</v>
       </c>
     </row>
@@ -5161,9 +6049,12 @@
         <v>0.00679</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>0.00679</v>
+        <v>0.006871</v>
       </c>
       <c r="D296" s="1" t="n">
+        <v>0.006871</v>
+      </c>
+      <c r="E296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -5177,9 +6068,12 @@
         <v>0.1206</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>0.1206</v>
+        <v>0.1212</v>
       </c>
       <c r="D297" s="1" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="E297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -5193,9 +6087,12 @@
         <v>0.01526</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>0.01526</v>
+        <v>0.01535</v>
       </c>
       <c r="D298" s="1" t="n">
+        <v>0.01535</v>
+      </c>
+      <c r="E298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -5209,9 +6106,12 @@
         <v>0.4389</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>0.4389</v>
+        <v>0.4405</v>
       </c>
       <c r="D299" s="1" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="E299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -5225,9 +6125,12 @@
         <v>0.00923</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>0.00923</v>
+        <v>0.00924</v>
       </c>
       <c r="D300" s="1" t="n">
+        <v>0.00924</v>
+      </c>
+      <c r="E300" s="1" t="n">
         <v>0.00923</v>
       </c>
     </row>
@@ -5241,9 +6144,12 @@
         <v>0.1845</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>0.1845</v>
+        <v>0.1849</v>
       </c>
       <c r="D301" s="1" t="n">
+        <v>0.1849</v>
+      </c>
+      <c r="E301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -5257,9 +6163,12 @@
         <v>0.00744</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>0.00744</v>
+        <v>0.00754</v>
       </c>
       <c r="D302" s="1" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="E302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -5273,9 +6182,12 @@
         <v>0.0002164</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>0.0002164</v>
+        <v>0.0002171</v>
       </c>
       <c r="D303" s="1" t="n">
+        <v>0.0002171</v>
+      </c>
+      <c r="E303" s="1" t="n">
         <v>0.0002164</v>
       </c>
     </row>
@@ -5289,9 +6201,12 @@
         <v>0.01545</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>0.01545</v>
+        <v>0.01549</v>
       </c>
       <c r="D304" s="1" t="n">
+        <v>0.01549</v>
+      </c>
+      <c r="E304" s="1" t="n">
         <v>0.01545</v>
       </c>
     </row>
@@ -5305,9 +6220,12 @@
         <v>0.0738</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>0.0738</v>
+        <v>0.07389</v>
       </c>
       <c r="D305" s="1" t="n">
+        <v>0.07389</v>
+      </c>
+      <c r="E305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -5326,6 +6244,9 @@
       <c r="D306" s="1" t="n">
         <v>0.08275</v>
       </c>
+      <c r="E306" s="1" t="n">
+        <v>0.08275</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -5337,9 +6258,12 @@
         <v>0.01812</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>0.01812</v>
+        <v>0.01826</v>
       </c>
       <c r="D307" s="1" t="n">
+        <v>0.01826</v>
+      </c>
+      <c r="E307" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -5353,9 +6277,12 @@
         <v>0.0006215</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>0.0006215</v>
+        <v>0.0006255</v>
       </c>
       <c r="D308" s="1" t="n">
+        <v>0.0006255</v>
+      </c>
+      <c r="E308" s="1" t="n">
         <v>0.0006215</v>
       </c>
     </row>
@@ -5369,9 +6296,12 @@
         <v>0.08288</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>0.08288</v>
+        <v>0.08294</v>
       </c>
       <c r="D309" s="1" t="n">
+        <v>0.08294</v>
+      </c>
+      <c r="E309" s="1" t="n">
         <v>0.08288</v>
       </c>
     </row>
@@ -5385,9 +6315,12 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="D310" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="E310" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -5401,9 +6334,12 @@
         <v>0.2109</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>0.2109</v>
+        <v>0.2113</v>
       </c>
       <c r="D311" s="1" t="n">
+        <v>0.2113</v>
+      </c>
+      <c r="E311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -5417,9 +6353,12 @@
         <v>0.3878</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>0.3878</v>
+        <v>0.394</v>
       </c>
       <c r="D312" s="1" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="E312" s="1" t="n">
         <v>0.3878</v>
       </c>
     </row>
@@ -5433,9 +6372,12 @@
         <v>0.10492</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>0.10492</v>
+        <v>0.10542</v>
       </c>
       <c r="D313" s="1" t="n">
+        <v>0.10542</v>
+      </c>
+      <c r="E313" s="1" t="n">
         <v>0.10492</v>
       </c>
     </row>
@@ -5449,9 +6391,12 @@
         <v>0.08487</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>0.08487</v>
+        <v>0.08518000000000001</v>
       </c>
       <c r="D314" s="1" t="n">
+        <v>0.08518000000000001</v>
+      </c>
+      <c r="E314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -5465,9 +6410,12 @@
         <v>0.1178</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>0.1178</v>
+        <v>0.1185</v>
       </c>
       <c r="D315" s="1" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="E315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -5481,9 +6429,12 @@
         <v>0.03628</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>0.03628</v>
+        <v>0.03681</v>
       </c>
       <c r="D316" s="1" t="n">
+        <v>0.03681</v>
+      </c>
+      <c r="E316" s="1" t="n">
         <v>0.03628</v>
       </c>
     </row>
@@ -5497,9 +6448,12 @@
         <v>0.08081000000000001</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>0.08081000000000001</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="D317" s="1" t="n">
+        <v>0.08110000000000001</v>
+      </c>
+      <c r="E317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -5513,9 +6467,12 @@
         <v>0.03736</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>0.03736</v>
+        <v>0.03747</v>
       </c>
       <c r="D318" s="1" t="n">
+        <v>0.03747</v>
+      </c>
+      <c r="E318" s="1" t="n">
         <v>0.03736</v>
       </c>
     </row>
@@ -5529,9 +6486,12 @@
         <v>0.4308</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>0.4308</v>
+        <v>0.4347</v>
       </c>
       <c r="D319" s="1" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="E319" s="1" t="n">
         <v>0.4308</v>
       </c>
     </row>
@@ -5545,9 +6505,12 @@
         <v>0.1612</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>0.1612</v>
+        <v>0.1614</v>
       </c>
       <c r="D320" s="1" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="E320" s="1" t="n">
         <v>0.1612</v>
       </c>
     </row>
@@ -5566,6 +6529,9 @@
       <c r="D321" s="1" t="n">
         <v>5.68</v>
       </c>
+      <c r="E321" s="1" t="n">
+        <v>5.68</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -5577,9 +6543,12 @@
         <v>0.003715</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>0.003715</v>
+        <v>0.003735</v>
       </c>
       <c r="D322" s="1" t="n">
+        <v>0.003735</v>
+      </c>
+      <c r="E322" s="1" t="n">
         <v>0.003715</v>
       </c>
     </row>
@@ -5593,9 +6562,12 @@
         <v>0.001743</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>0.001743</v>
+        <v>0.001751</v>
       </c>
       <c r="D323" s="1" t="n">
+        <v>0.001751</v>
+      </c>
+      <c r="E323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -5614,6 +6586,9 @@
       <c r="D324" s="1" t="n">
         <v>1.2e-05</v>
       </c>
+      <c r="E324" s="1" t="n">
+        <v>1.2e-05</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -5625,9 +6600,12 @@
         <v>0.0864</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>0.0864</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="D325" s="1" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="E325" s="1" t="n">
         <v>0.0864</v>
       </c>
     </row>
@@ -5641,9 +6619,12 @@
         <v>0.01723</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>0.01723</v>
+        <v>0.01736</v>
       </c>
       <c r="D326" s="1" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="E326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -5657,9 +6638,12 @@
         <v>0.01687</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>0.01687</v>
+        <v>0.01689</v>
       </c>
       <c r="D327" s="1" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="E327" s="1" t="n">
         <v>0.01687</v>
       </c>
     </row>
@@ -5673,9 +6657,12 @@
         <v>4.446</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>4.446</v>
+        <v>4.462</v>
       </c>
       <c r="D328" s="1" t="n">
+        <v>4.462</v>
+      </c>
+      <c r="E328" s="1" t="n">
         <v>4.446</v>
       </c>
     </row>
@@ -5689,9 +6676,12 @@
         <v>0.009825</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>0.009825</v>
+        <v>0.009861</v>
       </c>
       <c r="D329" s="1" t="n">
+        <v>0.009861</v>
+      </c>
+      <c r="E329" s="1" t="n">
         <v>0.009825</v>
       </c>
     </row>
@@ -5705,11 +6695,14 @@
         <v>5192.9</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>5192.9</v>
+        <v>5185.8</v>
       </c>
       <c r="D330" s="1" t="n">
         <v>5192.9</v>
       </c>
+      <c r="E330" s="1" t="n">
+        <v>5185.8</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -5721,9 +6714,12 @@
         <v>0.07047</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>0.07047</v>
+        <v>0.07074</v>
       </c>
       <c r="D331" s="1" t="n">
+        <v>0.07074</v>
+      </c>
+      <c r="E331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -5737,9 +6733,12 @@
         <v>0.06063</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>0.06063</v>
+        <v>0.06098</v>
       </c>
       <c r="D332" s="1" t="n">
+        <v>0.06098</v>
+      </c>
+      <c r="E332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -5753,11 +6752,14 @@
         <v>0.10353</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>0.10353</v>
+        <v>0.10347</v>
       </c>
       <c r="D333" s="1" t="n">
         <v>0.10353</v>
       </c>
+      <c r="E333" s="1" t="n">
+        <v>0.10347</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -5769,11 +6771,14 @@
         <v>0.08837</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>0.08837</v>
+        <v>0.08831</v>
       </c>
       <c r="D334" s="1" t="n">
         <v>0.08837</v>
       </c>
+      <c r="E334" s="1" t="n">
+        <v>0.08831</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -5785,9 +6790,12 @@
         <v>0.01641</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>0.01641</v>
+        <v>0.016413</v>
       </c>
       <c r="D335" s="1" t="n">
+        <v>0.016413</v>
+      </c>
+      <c r="E335" s="1" t="n">
         <v>0.01641</v>
       </c>
     </row>
@@ -5801,9 +6809,12 @@
         <v>0.04587</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>0.04587</v>
+        <v>0.04594</v>
       </c>
       <c r="D336" s="1" t="n">
+        <v>0.04594</v>
+      </c>
+      <c r="E336" s="1" t="n">
         <v>0.04587</v>
       </c>
     </row>
@@ -5817,11 +6828,14 @@
         <v>0.1853</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>0.1853</v>
+        <v>0.1838</v>
       </c>
       <c r="D337" s="1" t="n">
         <v>0.1853</v>
       </c>
+      <c r="E337" s="1" t="n">
+        <v>0.1838</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -5833,9 +6847,12 @@
         <v>0.183</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>0.183</v>
+        <v>0.1836</v>
       </c>
       <c r="D338" s="1" t="n">
+        <v>0.1836</v>
+      </c>
+      <c r="E338" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -5849,9 +6866,12 @@
         <v>0.0183</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>0.0183</v>
+        <v>0.01837</v>
       </c>
       <c r="D339" s="1" t="n">
+        <v>0.01837</v>
+      </c>
+      <c r="E339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -5865,9 +6885,12 @@
         <v>0.02306</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>0.02306</v>
+        <v>0.02311</v>
       </c>
       <c r="D340" s="1" t="n">
+        <v>0.02311</v>
+      </c>
+      <c r="E340" s="1" t="n">
         <v>0.02306</v>
       </c>
     </row>
@@ -5881,9 +6904,12 @@
         <v>0.453</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>0.453</v>
+        <v>0.4548</v>
       </c>
       <c r="D341" s="1" t="n">
+        <v>0.4548</v>
+      </c>
+      <c r="E341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -5897,9 +6923,12 @@
         <v>0.01336</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>0.01336</v>
+        <v>0.01339</v>
       </c>
       <c r="D342" s="1" t="n">
+        <v>0.01339</v>
+      </c>
+      <c r="E342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -5913,9 +6942,12 @@
         <v>2.874</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>2.874</v>
+        <v>2.887</v>
       </c>
       <c r="D343" s="1" t="n">
+        <v>2.887</v>
+      </c>
+      <c r="E343" s="1" t="n">
         <v>2.874</v>
       </c>
     </row>
@@ -5929,9 +6961,12 @@
         <v>0.1482</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>0.1482</v>
+        <v>0.1551</v>
       </c>
       <c r="D344" s="1" t="n">
+        <v>0.1551</v>
+      </c>
+      <c r="E344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -5945,9 +6980,12 @@
         <v>0.005339</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>0.005339</v>
+        <v>0.005367</v>
       </c>
       <c r="D345" s="1" t="n">
+        <v>0.005367</v>
+      </c>
+      <c r="E345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -5961,9 +6999,12 @@
         <v>0.05755</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>0.05755</v>
+        <v>0.0578</v>
       </c>
       <c r="D346" s="1" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="E346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -5977,9 +7018,12 @@
         <v>2597</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>2597</v>
+        <v>2606</v>
       </c>
       <c r="D347" s="1" t="n">
+        <v>2606</v>
+      </c>
+      <c r="E347" s="1" t="n">
         <v>2597</v>
       </c>
     </row>
@@ -5993,11 +7037,14 @@
         <v>0.04621</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>0.04621</v>
+        <v>0.04619</v>
       </c>
       <c r="D348" s="1" t="n">
         <v>0.04621</v>
       </c>
+      <c r="E348" s="1" t="n">
+        <v>0.04619</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6009,11 +7056,14 @@
         <v>0.005707</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>0.005707</v>
+        <v>0.005682</v>
       </c>
       <c r="D349" s="1" t="n">
         <v>0.005707</v>
       </c>
+      <c r="E349" s="1" t="n">
+        <v>0.005682</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6025,9 +7075,12 @@
         <v>195.31</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>195.31</v>
+        <v>195.51</v>
       </c>
       <c r="D350" s="1" t="n">
+        <v>195.51</v>
+      </c>
+      <c r="E350" s="1" t="n">
         <v>195.31</v>
       </c>
     </row>
@@ -6041,9 +7094,12 @@
         <v>0.08193</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>0.08193</v>
+        <v>0.08205999999999999</v>
       </c>
       <c r="D351" s="1" t="n">
+        <v>0.08205999999999999</v>
+      </c>
+      <c r="E351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -6057,11 +7113,14 @@
         <v>0.007571</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>0.007571</v>
+        <v>0.007537</v>
       </c>
       <c r="D352" s="1" t="n">
         <v>0.007571</v>
       </c>
+      <c r="E352" s="1" t="n">
+        <v>0.007537</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6073,11 +7132,14 @@
         <v>1.486</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>1.486</v>
+        <v>1.4807</v>
       </c>
       <c r="D353" s="1" t="n">
         <v>1.486</v>
       </c>
+      <c r="E353" s="1" t="n">
+        <v>1.4807</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6089,9 +7151,12 @@
         <v>0.07597</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>0.07597</v>
+        <v>0.07643999999999999</v>
       </c>
       <c r="D354" s="1" t="n">
+        <v>0.07643999999999999</v>
+      </c>
+      <c r="E354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -6105,11 +7170,14 @@
         <v>0.04921</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>0.04921</v>
+        <v>0.04913</v>
       </c>
       <c r="D355" s="1" t="n">
         <v>0.04921</v>
       </c>
+      <c r="E355" s="1" t="n">
+        <v>0.04913</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6121,9 +7189,12 @@
         <v>0.2847</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>0.2847</v>
+        <v>0.2857</v>
       </c>
       <c r="D356" s="1" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="E356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -6137,9 +7208,12 @@
         <v>0.1462</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>0.1462</v>
+        <v>0.1467</v>
       </c>
       <c r="D357" s="1" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="E357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -6153,9 +7227,12 @@
         <v>1.35</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>1.35</v>
+        <v>1.355</v>
       </c>
       <c r="D358" s="1" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="E358" s="1" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -6169,9 +7246,12 @@
         <v>0.6116</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>0.6116</v>
+        <v>0.6117</v>
       </c>
       <c r="D359" s="1" t="n">
+        <v>0.6117</v>
+      </c>
+      <c r="E359" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -6185,9 +7265,12 @@
         <v>0.1142</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>0.1142</v>
+        <v>0.1145</v>
       </c>
       <c r="D360" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="E360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -6201,11 +7284,14 @@
         <v>0.02619</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>0.02619</v>
+        <v>0.026</v>
       </c>
       <c r="D361" s="1" t="n">
         <v>0.02619</v>
       </c>
+      <c r="E361" s="1" t="n">
+        <v>0.026</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -6217,9 +7303,12 @@
         <v>3.03e-05</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>3.03e-05</v>
+        <v>3.04e-05</v>
       </c>
       <c r="D362" s="1" t="n">
+        <v>3.04e-05</v>
+      </c>
+      <c r="E362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -6233,9 +7322,12 @@
         <v>0.01018</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>0.01018</v>
+        <v>0.01026</v>
       </c>
       <c r="D363" s="1" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="E363" s="1" t="n">
         <v>0.01018</v>
       </c>
     </row>
@@ -6249,9 +7341,12 @@
         <v>0.06199</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>0.06199</v>
+        <v>0.06208</v>
       </c>
       <c r="D364" s="1" t="n">
+        <v>0.06208</v>
+      </c>
+      <c r="E364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -6265,9 +7360,12 @@
         <v>0.03255</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>0.03255</v>
+        <v>0.03297</v>
       </c>
       <c r="D365" s="1" t="n">
+        <v>0.03297</v>
+      </c>
+      <c r="E365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -6281,9 +7379,12 @@
         <v>0.03288</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>0.03288</v>
+        <v>0.03296</v>
       </c>
       <c r="D366" s="1" t="n">
+        <v>0.03296</v>
+      </c>
+      <c r="E366" s="1" t="n">
         <v>0.03288</v>
       </c>
     </row>
@@ -6297,11 +7398,14 @@
         <v>0.012157</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>0.012157</v>
+        <v>0.012155</v>
       </c>
       <c r="D367" s="1" t="n">
         <v>0.012157</v>
       </c>
+      <c r="E367" s="1" t="n">
+        <v>0.012155</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -6313,9 +7417,12 @@
         <v>0.03513</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>0.03513</v>
+        <v>0.03534</v>
       </c>
       <c r="D368" s="1" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="E368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -6329,9 +7436,12 @@
         <v>0.6182</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>0.6182</v>
+        <v>0.6183</v>
       </c>
       <c r="D369" s="1" t="n">
+        <v>0.6183</v>
+      </c>
+      <c r="E369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -6345,9 +7455,12 @@
         <v>0.00843</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>0.00843</v>
+        <v>0.00847</v>
       </c>
       <c r="D370" s="1" t="n">
+        <v>0.00847</v>
+      </c>
+      <c r="E370" s="1" t="n">
         <v>0.00843</v>
       </c>
     </row>
@@ -6361,9 +7474,12 @@
         <v>0.003242</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>0.003242</v>
+        <v>0.003263</v>
       </c>
       <c r="D371" s="1" t="n">
+        <v>0.003263</v>
+      </c>
+      <c r="E371" s="1" t="n">
         <v>0.003242</v>
       </c>
     </row>
@@ -6377,9 +7493,12 @@
         <v>0.13227</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>0.13227</v>
+        <v>0.13235</v>
       </c>
       <c r="D372" s="1" t="n">
+        <v>0.13235</v>
+      </c>
+      <c r="E372" s="1" t="n">
         <v>0.13227</v>
       </c>
     </row>
@@ -6393,9 +7512,12 @@
         <v>0.007820000000000001</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>0.007820000000000001</v>
+        <v>0.007822000000000001</v>
       </c>
       <c r="D373" s="1" t="n">
+        <v>0.007822000000000001</v>
+      </c>
+      <c r="E373" s="1" t="n">
         <v>0.007820000000000001</v>
       </c>
     </row>
@@ -6409,9 +7531,12 @@
         <v>0.01972</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>0.01972</v>
+        <v>0.01978</v>
       </c>
       <c r="D374" s="1" t="n">
+        <v>0.01978</v>
+      </c>
+      <c r="E374" s="1" t="n">
         <v>0.01972</v>
       </c>
     </row>
@@ -6425,9 +7550,12 @@
         <v>0.0005914</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>0.0005914</v>
+        <v>0.0005921</v>
       </c>
       <c r="D375" s="1" t="n">
+        <v>0.0005921</v>
+      </c>
+      <c r="E375" s="1" t="n">
         <v>0.0005914</v>
       </c>
     </row>
@@ -6446,6 +7574,9 @@
       <c r="D376" s="1" t="n">
         <v>0.0362</v>
       </c>
+      <c r="E376" s="1" t="n">
+        <v>0.0362</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -6457,9 +7588,12 @@
         <v>0.0007848</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>0.0007848</v>
+        <v>0.0007909</v>
       </c>
       <c r="D377" s="1" t="n">
+        <v>0.0007909</v>
+      </c>
+      <c r="E377" s="1" t="n">
         <v>0.0007848</v>
       </c>
     </row>
@@ -6473,9 +7607,12 @@
         <v>1.973</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>1.973</v>
+        <v>1.98</v>
       </c>
       <c r="D378" s="1" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E378" s="1" t="n">
         <v>1.973</v>
       </c>
     </row>
@@ -6489,9 +7626,12 @@
         <v>0.0005888999999999999</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>0.0005888999999999999</v>
+        <v>0.0005913</v>
       </c>
       <c r="D379" s="1" t="n">
+        <v>0.0005913</v>
+      </c>
+      <c r="E379" s="1" t="n">
         <v>0.0005888999999999999</v>
       </c>
     </row>
@@ -6505,9 +7645,12 @@
         <v>0.03738</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>0.03738</v>
+        <v>0.03743</v>
       </c>
       <c r="D380" s="1" t="n">
+        <v>0.03743</v>
+      </c>
+      <c r="E380" s="1" t="n">
         <v>0.03738</v>
       </c>
     </row>
@@ -6521,9 +7664,12 @@
         <v>0.0546</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>0.0546</v>
+        <v>0.05477</v>
       </c>
       <c r="D381" s="1" t="n">
+        <v>0.05477</v>
+      </c>
+      <c r="E381" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -6537,9 +7683,12 @@
         <v>0.01202</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>0.01202</v>
+        <v>0.01207</v>
       </c>
       <c r="D382" s="1" t="n">
+        <v>0.01207</v>
+      </c>
+      <c r="E382" s="1" t="n">
         <v>0.01202</v>
       </c>
     </row>
@@ -6553,11 +7702,14 @@
         <v>0.001559</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>0.001559</v>
+        <v>0.001555</v>
       </c>
       <c r="D383" s="1" t="n">
         <v>0.001559</v>
       </c>
+      <c r="E383" s="1" t="n">
+        <v>0.001555</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -6569,9 +7721,12 @@
         <v>0.0002154</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>0.0002154</v>
+        <v>0.0002157</v>
       </c>
       <c r="D384" s="1" t="n">
+        <v>0.0002157</v>
+      </c>
+      <c r="E384" s="1" t="n">
         <v>0.0002154</v>
       </c>
     </row>
@@ -6585,9 +7740,12 @@
         <v>0.00241</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>0.00241</v>
+        <v>0.00242</v>
       </c>
       <c r="D385" s="1" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E385" s="1" t="n">
         <v>0.00241</v>
       </c>
     </row>
@@ -6601,9 +7759,12 @@
         <v>3.892</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>3.892</v>
+        <v>3.908</v>
       </c>
       <c r="D386" s="1" t="n">
+        <v>3.908</v>
+      </c>
+      <c r="E386" s="1" t="n">
         <v>3.892</v>
       </c>
     </row>
@@ -6617,9 +7778,12 @@
         <v>0.0006243000000000001</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>0.0006243000000000001</v>
+        <v>0.0006254</v>
       </c>
       <c r="D387" s="1" t="n">
+        <v>0.0006254</v>
+      </c>
+      <c r="E387" s="1" t="n">
         <v>0.0006243000000000001</v>
       </c>
     </row>
@@ -6633,11 +7797,14 @@
         <v>0.00654</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>0.00654</v>
+        <v>0.00653</v>
       </c>
       <c r="D388" s="1" t="n">
         <v>0.00654</v>
       </c>
+      <c r="E388" s="1" t="n">
+        <v>0.00653</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -6649,9 +7816,12 @@
         <v>0.1313</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>0.1313</v>
+        <v>0.1315</v>
       </c>
       <c r="D389" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="E389" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -6665,9 +7835,12 @@
         <v>0.03201</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>0.03201</v>
+        <v>0.03202</v>
       </c>
       <c r="D390" s="1" t="n">
+        <v>0.03202</v>
+      </c>
+      <c r="E390" s="1" t="n">
         <v>0.03201</v>
       </c>
     </row>
@@ -6686,6 +7859,9 @@
       <c r="D391" s="1" t="n">
         <v>0.06362</v>
       </c>
+      <c r="E391" s="1" t="n">
+        <v>0.06362</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -6697,9 +7873,12 @@
         <v>27.77</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>27.77</v>
+        <v>27.82</v>
       </c>
       <c r="D392" s="1" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="E392" s="1" t="n">
         <v>27.77</v>
       </c>
     </row>
@@ -6713,9 +7892,12 @@
         <v>0.000411</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>0.000411</v>
+        <v>0.000414</v>
       </c>
       <c r="D393" s="1" t="n">
+        <v>0.000414</v>
+      </c>
+      <c r="E393" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -6729,9 +7911,12 @@
         <v>0.06926</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>0.06926</v>
+        <v>0.06962</v>
       </c>
       <c r="D394" s="1" t="n">
+        <v>0.06962</v>
+      </c>
+      <c r="E394" s="1" t="n">
         <v>0.06926</v>
       </c>
     </row>
@@ -6745,9 +7930,12 @@
         <v>0.2581</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>0.2581</v>
+        <v>0.2589</v>
       </c>
       <c r="D395" s="1" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="E395" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -6761,9 +7949,12 @@
         <v>0.004677</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>0.004677</v>
+        <v>0.004687</v>
       </c>
       <c r="D396" s="1" t="n">
+        <v>0.004687</v>
+      </c>
+      <c r="E396" s="1" t="n">
         <v>0.004677</v>
       </c>
     </row>
@@ -6777,9 +7968,12 @@
         <v>0.233</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>0.233</v>
+        <v>0.2345</v>
       </c>
       <c r="D397" s="1" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="E397" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
@@ -6793,9 +7987,12 @@
         <v>0.18108</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>0.18108</v>
+        <v>0.18131</v>
       </c>
       <c r="D398" s="1" t="n">
+        <v>0.18131</v>
+      </c>
+      <c r="E398" s="1" t="n">
         <v>0.18108</v>
       </c>
     </row>
@@ -6809,9 +8006,12 @@
         <v>0.04108</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>0.04108</v>
+        <v>0.0412</v>
       </c>
       <c r="D399" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="E399" s="1" t="n">
         <v>0.04108</v>
       </c>
     </row>
@@ -6825,9 +8025,12 @@
         <v>0.075</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="D400" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E400" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -6841,9 +8044,12 @@
         <v>0.001739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>0.001739</v>
+        <v>0.001743</v>
       </c>
       <c r="D401" s="1" t="n">
+        <v>0.001743</v>
+      </c>
+      <c r="E401" s="1" t="n">
         <v>0.001739</v>
       </c>
     </row>
@@ -6857,9 +8063,12 @@
         <v>0.05362</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>0.05362</v>
+        <v>0.05391</v>
       </c>
       <c r="D402" s="1" t="n">
+        <v>0.05391</v>
+      </c>
+      <c r="E402" s="1" t="n">
         <v>0.05362</v>
       </c>
     </row>
@@ -6873,9 +8082,12 @@
         <v>2030.23</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>2030.23</v>
+        <v>2031.8</v>
       </c>
       <c r="D403" s="1" t="n">
+        <v>2031.8</v>
+      </c>
+      <c r="E403" s="1" t="n">
         <v>2030.23</v>
       </c>
     </row>
@@ -6889,9 +8101,12 @@
         <v>1.081</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>1.081</v>
+        <v>1.082</v>
       </c>
       <c r="D404" s="1" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="E404" s="1" t="n">
         <v>1.081</v>
       </c>
     </row>
@@ -6905,9 +8120,12 @@
         <v>7.65</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>7.65</v>
+        <v>7.658</v>
       </c>
       <c r="D405" s="1" t="n">
+        <v>7.658</v>
+      </c>
+      <c r="E405" s="1" t="n">
         <v>7.65</v>
       </c>
     </row>
@@ -6921,9 +8139,12 @@
         <v>3.238</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>3.238</v>
+        <v>3.257</v>
       </c>
       <c r="D406" s="1" t="n">
+        <v>3.257</v>
+      </c>
+      <c r="E406" s="1" t="n">
         <v>3.238</v>
       </c>
     </row>
@@ -6937,11 +8158,14 @@
         <v>0.1821</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>0.1821</v>
+        <v>0.1814</v>
       </c>
       <c r="D407" s="1" t="n">
         <v>0.1821</v>
       </c>
+      <c r="E407" s="1" t="n">
+        <v>0.1814</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -6953,9 +8177,12 @@
         <v>0.1526</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>0.1526</v>
+        <v>0.1533</v>
       </c>
       <c r="D408" s="1" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="E408" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -6969,9 +8196,12 @@
         <v>0.07315000000000001</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>0.07315000000000001</v>
+        <v>0.07346999999999999</v>
       </c>
       <c r="D409" s="1" t="n">
+        <v>0.07346999999999999</v>
+      </c>
+      <c r="E409" s="1" t="n">
         <v>0.07315000000000001</v>
       </c>
     </row>
@@ -6985,9 +8215,12 @@
         <v>0.02076</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>0.02076</v>
+        <v>0.0209</v>
       </c>
       <c r="D410" s="1" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="E410" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -7001,9 +8234,12 @@
         <v>0.2642</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>0.2642</v>
+        <v>0.2659</v>
       </c>
       <c r="D411" s="1" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="E411" s="1" t="n">
         <v>0.2642</v>
       </c>
     </row>
@@ -7017,9 +8253,12 @@
         <v>0.007302</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>0.007302</v>
+        <v>0.007369</v>
       </c>
       <c r="D412" s="1" t="n">
+        <v>0.007369</v>
+      </c>
+      <c r="E412" s="1" t="n">
         <v>0.007302</v>
       </c>
     </row>
@@ -7033,9 +8272,12 @@
         <v>0.01385</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>0.01385</v>
+        <v>0.01391</v>
       </c>
       <c r="D413" s="1" t="n">
+        <v>0.01391</v>
+      </c>
+      <c r="E413" s="1" t="n">
         <v>0.01385</v>
       </c>
     </row>
@@ -7054,6 +8296,9 @@
       <c r="D414" s="1" t="n">
         <v>0.093</v>
       </c>
+      <c r="E414" s="1" t="n">
+        <v>0.093</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -7065,9 +8310,12 @@
         <v>0.03998</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>0.03998</v>
+        <v>0.04007</v>
       </c>
       <c r="D415" s="1" t="n">
+        <v>0.04007</v>
+      </c>
+      <c r="E415" s="1" t="n">
         <v>0.03998</v>
       </c>
     </row>
@@ -7081,9 +8329,12 @@
         <v>0.2845</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>0.2845</v>
+        <v>0.2854</v>
       </c>
       <c r="D416" s="1" t="n">
+        <v>0.2854</v>
+      </c>
+      <c r="E416" s="1" t="n">
         <v>0.2845</v>
       </c>
     </row>
@@ -7097,9 +8348,12 @@
         <v>1.813</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>1.813</v>
+        <v>1.818</v>
       </c>
       <c r="D417" s="1" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="E417" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -7113,9 +8367,12 @@
         <v>0.06672</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>0.06672</v>
+        <v>0.06707</v>
       </c>
       <c r="D418" s="1" t="n">
+        <v>0.06707</v>
+      </c>
+      <c r="E418" s="1" t="n">
         <v>0.06672</v>
       </c>
     </row>
@@ -7129,11 +8386,14 @@
         <v>207.4</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>207.4</v>
+        <v>207.39</v>
       </c>
       <c r="D419" s="1" t="n">
         <v>207.4</v>
       </c>
+      <c r="E419" s="1" t="n">
+        <v>207.39</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -7145,11 +8405,14 @@
         <v>73.17</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>73.17</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="D420" s="1" t="n">
         <v>73.17</v>
       </c>
+      <c r="E420" s="1" t="n">
+        <v>73.15000000000001</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -7161,9 +8424,12 @@
         <v>0.07242</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>0.07242</v>
+        <v>0.0725</v>
       </c>
       <c r="D421" s="1" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="E421" s="1" t="n">
         <v>0.07242</v>
       </c>
     </row>
@@ -7177,11 +8443,14 @@
         <v>0.05005</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>0.05005</v>
+        <v>0.04998</v>
       </c>
       <c r="D422" s="1" t="n">
         <v>0.05005</v>
       </c>
+      <c r="E422" s="1" t="n">
+        <v>0.04998</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -7193,9 +8462,12 @@
         <v>0.001149</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>0.001149</v>
+        <v>0.00115</v>
       </c>
       <c r="D423" s="1" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="E423" s="1" t="n">
         <v>0.001149</v>
       </c>
     </row>
@@ -7209,9 +8481,12 @@
         <v>0.00502</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>0.00502</v>
+        <v>0.00505</v>
       </c>
       <c r="D424" s="1" t="n">
+        <v>0.00505</v>
+      </c>
+      <c r="E424" s="1" t="n">
         <v>0.00502</v>
       </c>
     </row>
@@ -7225,9 +8500,12 @@
         <v>0.126</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>0.126</v>
+        <v>0.1267</v>
       </c>
       <c r="D425" s="1" t="n">
+        <v>0.1267</v>
+      </c>
+      <c r="E425" s="1" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -7241,9 +8519,12 @@
         <v>1.294</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>1.294</v>
+        <v>1.299</v>
       </c>
       <c r="D426" s="1" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="E426" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -7257,9 +8538,12 @@
         <v>0.004399</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>0.004399</v>
+        <v>0.004408</v>
       </c>
       <c r="D427" s="1" t="n">
+        <v>0.004408</v>
+      </c>
+      <c r="E427" s="1" t="n">
         <v>0.004399</v>
       </c>
     </row>
@@ -7273,9 +8557,12 @@
         <v>0.005017</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>0.005017</v>
+        <v>0.005039</v>
       </c>
       <c r="D428" s="1" t="n">
+        <v>0.005039</v>
+      </c>
+      <c r="E428" s="1" t="n">
         <v>0.005017</v>
       </c>
     </row>
@@ -7289,9 +8576,12 @@
         <v>0.02288</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>0.02288</v>
+        <v>0.02323</v>
       </c>
       <c r="D429" s="1" t="n">
+        <v>0.02323</v>
+      </c>
+      <c r="E429" s="1" t="n">
         <v>0.02288</v>
       </c>
     </row>
@@ -7305,9 +8595,12 @@
         <v>0.02501</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>0.02501</v>
+        <v>0.02511</v>
       </c>
       <c r="D430" s="1" t="n">
+        <v>0.02511</v>
+      </c>
+      <c r="E430" s="1" t="n">
         <v>0.02501</v>
       </c>
     </row>
@@ -7321,9 +8614,12 @@
         <v>0.0158</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>0.0158</v>
+        <v>0.016</v>
       </c>
       <c r="D431" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E431" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -7337,9 +8633,12 @@
         <v>0.5439000000000001</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5455</v>
       </c>
       <c r="D432" s="1" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="E432" s="1" t="n">
         <v>0.5439000000000001</v>
       </c>
     </row>
@@ -7358,6 +8657,9 @@
       <c r="D433" s="1" t="n">
         <v>0.001383</v>
       </c>
+      <c r="E433" s="1" t="n">
+        <v>0.001383</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -7369,9 +8671,12 @@
         <v>0.3925</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>0.3925</v>
+        <v>0.3931</v>
       </c>
       <c r="D434" s="1" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="E434" s="1" t="n">
         <v>0.3925</v>
       </c>
     </row>
@@ -7385,11 +8690,14 @@
         <v>0.001393</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>0.001393</v>
+        <v>0.00139</v>
       </c>
       <c r="D435" s="1" t="n">
         <v>0.001393</v>
       </c>
+      <c r="E435" s="1" t="n">
+        <v>0.00139</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -7401,9 +8709,12 @@
         <v>0.00715</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>0.00715</v>
+        <v>0.00716</v>
       </c>
       <c r="D436" s="1" t="n">
+        <v>0.00716</v>
+      </c>
+      <c r="E436" s="1" t="n">
         <v>0.00715</v>
       </c>
     </row>
@@ -7417,9 +8728,12 @@
         <v>0.001982</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>0.001982</v>
+        <v>0.001991</v>
       </c>
       <c r="D437" s="1" t="n">
+        <v>0.001991</v>
+      </c>
+      <c r="E437" s="1" t="n">
         <v>0.001982</v>
       </c>
     </row>
@@ -7433,9 +8747,12 @@
         <v>0.3122</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>0.3122</v>
+        <v>0.3143</v>
       </c>
       <c r="D438" s="1" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="E438" s="1" t="n">
         <v>0.3122</v>
       </c>
     </row>
@@ -7449,11 +8766,14 @@
         <v>0.04435</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>0.04435</v>
+        <v>0.04434</v>
       </c>
       <c r="D439" s="1" t="n">
         <v>0.04435</v>
       </c>
+      <c r="E439" s="1" t="n">
+        <v>0.04434</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -7465,9 +8785,12 @@
         <v>0.906</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>0.906</v>
+        <v>0.907</v>
       </c>
       <c r="D440" s="1" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="E440" s="1" t="n">
         <v>0.906</v>
       </c>
     </row>
@@ -7481,9 +8804,12 @@
         <v>1549.67</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>1549.67</v>
+        <v>1550.68</v>
       </c>
       <c r="D441" s="1" t="n">
+        <v>1550.68</v>
+      </c>
+      <c r="E441" s="1" t="n">
         <v>1549.67</v>
       </c>
     </row>
@@ -7497,9 +8823,12 @@
         <v>0.0007877</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>0.0007877</v>
+        <v>0.0007951</v>
       </c>
       <c r="D442" s="1" t="n">
+        <v>0.0007951</v>
+      </c>
+      <c r="E442" s="1" t="n">
         <v>0.0007877</v>
       </c>
     </row>
@@ -7518,6 +8847,9 @@
       <c r="D443" s="1" t="n">
         <v>0.003558</v>
       </c>
+      <c r="E443" s="1" t="n">
+        <v>0.003558</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -7529,11 +8861,14 @@
         <v>1.989</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>1.989</v>
+        <v>1.986</v>
       </c>
       <c r="D444" s="1" t="n">
         <v>1.989</v>
       </c>
+      <c r="E444" s="1" t="n">
+        <v>1.986</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -7545,9 +8880,12 @@
         <v>1.302</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>1.302</v>
+        <v>1.31</v>
       </c>
       <c r="D445" s="1" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E445" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -7561,11 +8899,14 @@
         <v>0.06929</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>0.06929</v>
+        <v>0.06920999999999999</v>
       </c>
       <c r="D446" s="1" t="n">
         <v>0.06929</v>
       </c>
+      <c r="E446" s="1" t="n">
+        <v>0.06920999999999999</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -7577,9 +8918,12 @@
         <v>0.02347</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>0.02347</v>
+        <v>0.0236</v>
       </c>
       <c r="D447" s="1" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="E447" s="1" t="n">
         <v>0.02347</v>
       </c>
     </row>
@@ -7593,9 +8937,12 @@
         <v>0.01384</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>0.01384</v>
+        <v>0.01394</v>
       </c>
       <c r="D448" s="1" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="E448" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -7609,9 +8956,12 @@
         <v>3.726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>3.726</v>
+        <v>3.734</v>
       </c>
       <c r="D449" s="1" t="n">
+        <v>3.734</v>
+      </c>
+      <c r="E449" s="1" t="n">
         <v>3.726</v>
       </c>
     </row>
@@ -7625,11 +8975,14 @@
         <v>0.0115</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>0.0115</v>
+        <v>0.0114</v>
       </c>
       <c r="D450" s="1" t="n">
         <v>0.0115</v>
       </c>
+      <c r="E450" s="1" t="n">
+        <v>0.0114</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -7641,9 +8994,12 @@
         <v>0.01024</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>0.01024</v>
+        <v>0.01029</v>
       </c>
       <c r="D451" s="1" t="n">
+        <v>0.01029</v>
+      </c>
+      <c r="E451" s="1" t="n">
         <v>0.01024</v>
       </c>
     </row>
@@ -7657,9 +9013,12 @@
         <v>0.1522</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>0.1522</v>
+        <v>0.1525</v>
       </c>
       <c r="D452" s="1" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="E452" s="1" t="n">
         <v>0.1522</v>
       </c>
     </row>
@@ -7673,9 +9032,12 @@
         <v>150.88</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>150.88</v>
+        <v>150.98</v>
       </c>
       <c r="D453" s="1" t="n">
+        <v>150.98</v>
+      </c>
+      <c r="E453" s="1" t="n">
         <v>150.88</v>
       </c>
     </row>
@@ -7689,9 +9051,12 @@
         <v>0.008593999999999999</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>0.008593999999999999</v>
+        <v>0.008623</v>
       </c>
       <c r="D454" s="1" t="n">
+        <v>0.008623</v>
+      </c>
+      <c r="E454" s="1" t="n">
         <v>0.008593999999999999</v>
       </c>
     </row>
@@ -7705,9 +9070,12 @@
         <v>0.05234</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>0.05234</v>
+        <v>0.05246</v>
       </c>
       <c r="D455" s="1" t="n">
+        <v>0.05246</v>
+      </c>
+      <c r="E455" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -7721,9 +9089,12 @@
         <v>0.30269</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>0.30269</v>
+        <v>0.30429</v>
       </c>
       <c r="D456" s="1" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="E456" s="1" t="n">
         <v>0.30269</v>
       </c>
     </row>
@@ -7737,9 +9108,12 @@
         <v>0.00544</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>0.00544</v>
+        <v>0.00546</v>
       </c>
       <c r="D457" s="1" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="E457" s="1" t="n">
         <v>0.00544</v>
       </c>
     </row>
@@ -7753,9 +9127,12 @@
         <v>0.1003</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>0.1003</v>
+        <v>0.1007</v>
       </c>
       <c r="D458" s="1" t="n">
+        <v>0.1007</v>
+      </c>
+      <c r="E458" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -7769,9 +9146,12 @@
         <v>0.001825</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>0.001825</v>
+        <v>0.001828</v>
       </c>
       <c r="D459" s="1" t="n">
+        <v>0.001828</v>
+      </c>
+      <c r="E459" s="1" t="n">
         <v>0.001825</v>
       </c>
     </row>
@@ -7785,9 +9165,12 @@
         <v>0.01828</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>0.01828</v>
+        <v>0.01829</v>
       </c>
       <c r="D460" s="1" t="n">
+        <v>0.01829</v>
+      </c>
+      <c r="E460" s="1" t="n">
         <v>0.01828</v>
       </c>
     </row>
@@ -7801,11 +9184,14 @@
         <v>0.0004877</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>0.0004877</v>
+        <v>0.0004874</v>
       </c>
       <c r="D461" s="1" t="n">
         <v>0.0004877</v>
       </c>
+      <c r="E461" s="1" t="n">
+        <v>0.0004874</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -7817,9 +9203,12 @@
         <v>0.0956</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>0.0956</v>
+        <v>0.0958</v>
       </c>
       <c r="D462" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="E462" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -7833,9 +9222,12 @@
         <v>0.07888000000000001</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>0.07888000000000001</v>
+        <v>0.07926</v>
       </c>
       <c r="D463" s="1" t="n">
+        <v>0.07926</v>
+      </c>
+      <c r="E463" s="1" t="n">
         <v>0.07888000000000001</v>
       </c>
     </row>
@@ -7849,9 +9241,12 @@
         <v>0.03145</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>0.03145</v>
+        <v>0.03155</v>
       </c>
       <c r="D464" s="1" t="n">
+        <v>0.03155</v>
+      </c>
+      <c r="E464" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -7865,9 +9260,12 @@
         <v>0.01613</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>0.01613</v>
+        <v>0.01618</v>
       </c>
       <c r="D465" s="1" t="n">
+        <v>0.01618</v>
+      </c>
+      <c r="E465" s="1" t="n">
         <v>0.01613</v>
       </c>
     </row>
@@ -7881,9 +9279,12 @@
         <v>0.06777</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>0.06777</v>
+        <v>0.06781</v>
       </c>
       <c r="D466" s="1" t="n">
+        <v>0.06781</v>
+      </c>
+      <c r="E466" s="1" t="n">
         <v>0.06777</v>
       </c>
     </row>
@@ -7897,9 +9298,12 @@
         <v>0.04322</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>0.04322</v>
+        <v>0.04332</v>
       </c>
       <c r="D467" s="1" t="n">
+        <v>0.04332</v>
+      </c>
+      <c r="E467" s="1" t="n">
         <v>0.04322</v>
       </c>
     </row>
@@ -7913,9 +9317,12 @@
         <v>0.05587</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>0.05587</v>
+        <v>0.05624</v>
       </c>
       <c r="D468" s="1" t="n">
+        <v>0.05624</v>
+      </c>
+      <c r="E468" s="1" t="n">
         <v>0.05587</v>
       </c>
     </row>
@@ -7929,9 +9336,12 @@
         <v>0.2294</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>0.2294</v>
+        <v>0.2305</v>
       </c>
       <c r="D469" s="1" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="E469" s="1" t="n">
         <v>0.2294</v>
       </c>
     </row>
@@ -7945,9 +9355,12 @@
         <v>0.0902</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>0.0902</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="D470" s="1" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="E470" s="1" t="n">
         <v>0.0902</v>
       </c>
     </row>
@@ -7961,9 +9374,12 @@
         <v>0.06686</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>0.06686</v>
+        <v>0.0669</v>
       </c>
       <c r="D471" s="1" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="E471" s="1" t="n">
         <v>0.06686</v>
       </c>
     </row>
@@ -7977,9 +9393,12 @@
         <v>6.486</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>6.486</v>
+        <v>6.52</v>
       </c>
       <c r="D472" s="1" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="E472" s="1" t="n">
         <v>6.486</v>
       </c>
     </row>
@@ -7993,9 +9412,12 @@
         <v>0.01938</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>0.01938</v>
+        <v>0.01943</v>
       </c>
       <c r="D473" s="1" t="n">
+        <v>0.01943</v>
+      </c>
+      <c r="E473" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -8009,9 +9431,12 @@
         <v>1.422</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>1.422</v>
+        <v>1.423</v>
       </c>
       <c r="D474" s="1" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="E474" s="1" t="n">
         <v>1.422</v>
       </c>
     </row>
@@ -8030,6 +9455,9 @@
       <c r="D475" s="1" t="n">
         <v>0.0898</v>
       </c>
+      <c r="E475" s="1" t="n">
+        <v>0.0898</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -8041,9 +9469,12 @@
         <v>0.1058</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>0.1058</v>
+        <v>0.1062</v>
       </c>
       <c r="D476" s="1" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="E476" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -8057,9 +9488,12 @@
         <v>0.09427000000000001</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>0.09427000000000001</v>
+        <v>0.09429</v>
       </c>
       <c r="D477" s="1" t="n">
+        <v>0.09429</v>
+      </c>
+      <c r="E477" s="1" t="n">
         <v>0.09427000000000001</v>
       </c>
     </row>
@@ -8073,9 +9507,12 @@
         <v>0.0001624</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>0.0001624</v>
+        <v>0.0001629</v>
       </c>
       <c r="D478" s="1" t="n">
+        <v>0.0001629</v>
+      </c>
+      <c r="E478" s="1" t="n">
         <v>0.0001624</v>
       </c>
     </row>
@@ -8089,9 +9526,12 @@
         <v>0.04007</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>0.04007</v>
+        <v>0.04017</v>
       </c>
       <c r="D479" s="1" t="n">
+        <v>0.04017</v>
+      </c>
+      <c r="E479" s="1" t="n">
         <v>0.04007</v>
       </c>
     </row>
@@ -8105,9 +9545,12 @@
         <v>0.007389</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>0.007389</v>
+        <v>0.007422</v>
       </c>
       <c r="D480" s="1" t="n">
+        <v>0.007422</v>
+      </c>
+      <c r="E480" s="1" t="n">
         <v>0.007389</v>
       </c>
     </row>
@@ -8121,11 +9564,14 @@
         <v>0.0955</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>0.0955</v>
+        <v>0.0954</v>
       </c>
       <c r="D481" s="1" t="n">
         <v>0.0955</v>
       </c>
+      <c r="E481" s="1" t="n">
+        <v>0.0954</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -8137,9 +9583,12 @@
         <v>0.05595</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>0.05595</v>
+        <v>0.05621</v>
       </c>
       <c r="D482" s="1" t="n">
+        <v>0.05621</v>
+      </c>
+      <c r="E482" s="1" t="n">
         <v>0.05595</v>
       </c>
     </row>
@@ -8153,11 +9602,14 @@
         <v>0.006194</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>0.006194</v>
+        <v>0.006161</v>
       </c>
       <c r="D483" s="1" t="n">
         <v>0.006194</v>
       </c>
+      <c r="E483" s="1" t="n">
+        <v>0.006161</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -8169,9 +9621,12 @@
         <v>0.01487</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>0.01487</v>
+        <v>0.01492</v>
       </c>
       <c r="D484" s="1" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="E484" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -8185,9 +9640,12 @@
         <v>0.02404</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>0.02404</v>
+        <v>0.02427</v>
       </c>
       <c r="D485" s="1" t="n">
+        <v>0.02427</v>
+      </c>
+      <c r="E485" s="1" t="n">
         <v>0.02404</v>
       </c>
     </row>
@@ -8201,9 +9659,12 @@
         <v>0.0667</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>0.0667</v>
+        <v>0.06679</v>
       </c>
       <c r="D486" s="1" t="n">
+        <v>0.06679</v>
+      </c>
+      <c r="E486" s="1" t="n">
         <v>0.0667</v>
       </c>
     </row>
@@ -8217,11 +9678,14 @@
         <v>0.03705</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>0.03705</v>
+        <v>0.03683</v>
       </c>
       <c r="D487" s="1" t="n">
         <v>0.03705</v>
       </c>
+      <c r="E487" s="1" t="n">
+        <v>0.03683</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -8233,11 +9697,14 @@
         <v>0.0182</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>0.0182</v>
+        <v>0.01819</v>
       </c>
       <c r="D488" s="1" t="n">
         <v>0.0182</v>
       </c>
+      <c r="E488" s="1" t="n">
+        <v>0.01819</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -8249,11 +9716,14 @@
         <v>0.03278</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>0.03278</v>
+        <v>0.03258</v>
       </c>
       <c r="D489" s="1" t="n">
         <v>0.03278</v>
       </c>
+      <c r="E489" s="1" t="n">
+        <v>0.03258</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -8265,9 +9735,12 @@
         <v>0.01458</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>0.01458</v>
+        <v>0.01464</v>
       </c>
       <c r="D490" s="1" t="n">
+        <v>0.01464</v>
+      </c>
+      <c r="E490" s="1" t="n">
         <v>0.01458</v>
       </c>
     </row>
@@ -8281,9 +9754,12 @@
         <v>0.01851</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>0.01851</v>
+        <v>0.01859</v>
       </c>
       <c r="D491" s="1" t="n">
+        <v>0.01859</v>
+      </c>
+      <c r="E491" s="1" t="n">
         <v>0.01851</v>
       </c>
     </row>
@@ -8297,9 +9773,12 @@
         <v>0.08907</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>0.08907</v>
+        <v>0.08935</v>
       </c>
       <c r="D492" s="1" t="n">
+        <v>0.08935</v>
+      </c>
+      <c r="E492" s="1" t="n">
         <v>0.08907</v>
       </c>
     </row>
@@ -8313,9 +9792,12 @@
         <v>0.006498</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>0.006498</v>
+        <v>0.006514</v>
       </c>
       <c r="D493" s="1" t="n">
+        <v>0.006514</v>
+      </c>
+      <c r="E493" s="1" t="n">
         <v>0.006498</v>
       </c>
     </row>
@@ -8329,9 +9811,12 @@
         <v>0.132</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>0.132</v>
+        <v>0.1324</v>
       </c>
       <c r="D494" s="1" t="n">
+        <v>0.1324</v>
+      </c>
+      <c r="E494" s="1" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -8345,9 +9830,12 @@
         <v>0.284</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>0.284</v>
+        <v>0.2853</v>
       </c>
       <c r="D495" s="1" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="E495" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -8361,9 +9849,12 @@
         <v>0.004516</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>0.004516</v>
+        <v>0.004534</v>
       </c>
       <c r="D496" s="1" t="n">
+        <v>0.004534</v>
+      </c>
+      <c r="E496" s="1" t="n">
         <v>0.004516</v>
       </c>
     </row>
@@ -8377,9 +9868,12 @@
         <v>0.1272</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>0.1272</v>
+        <v>0.1283</v>
       </c>
       <c r="D497" s="1" t="n">
+        <v>0.1283</v>
+      </c>
+      <c r="E497" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -8393,9 +9887,12 @@
         <v>0.03431</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>0.03431</v>
+        <v>0.03439</v>
       </c>
       <c r="D498" s="1" t="n">
+        <v>0.03439</v>
+      </c>
+      <c r="E498" s="1" t="n">
         <v>0.03431</v>
       </c>
     </row>
@@ -8409,9 +9906,12 @@
         <v>0.03557</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>0.03557</v>
+        <v>0.03576</v>
       </c>
       <c r="D499" s="1" t="n">
+        <v>0.03576</v>
+      </c>
+      <c r="E499" s="1" t="n">
         <v>0.03557</v>
       </c>
     </row>
@@ -8425,9 +9925,12 @@
         <v>0.003417</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>0.003417</v>
+        <v>0.003421</v>
       </c>
       <c r="D500" s="1" t="n">
+        <v>0.003421</v>
+      </c>
+      <c r="E500" s="1" t="n">
         <v>0.003417</v>
       </c>
     </row>
@@ -8441,9 +9944,12 @@
         <v>0.0003786</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>0.0003786</v>
+        <v>0.0003799</v>
       </c>
       <c r="D501" s="1" t="n">
+        <v>0.0003799</v>
+      </c>
+      <c r="E501" s="1" t="n">
         <v>0.0003786</v>
       </c>
     </row>
@@ -8457,9 +9963,12 @@
         <v>0.2986</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>0.2986</v>
+        <v>0.3003</v>
       </c>
       <c r="D502" s="1" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="E502" s="1" t="n">
         <v>0.2986</v>
       </c>
     </row>
@@ -8473,9 +9982,12 @@
         <v>0.06501999999999999</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>0.06501999999999999</v>
+        <v>0.06507</v>
       </c>
       <c r="D503" s="1" t="n">
+        <v>0.06507</v>
+      </c>
+      <c r="E503" s="1" t="n">
         <v>0.06501999999999999</v>
       </c>
     </row>
@@ -8489,9 +10001,12 @@
         <v>0.1773</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>0.1773</v>
+        <v>0.1777</v>
       </c>
       <c r="D504" s="1" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="E504" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -8510,6 +10025,9 @@
       <c r="D505" s="1" t="n">
         <v>0.1512</v>
       </c>
+      <c r="E505" s="1" t="n">
+        <v>0.1512</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -8521,9 +10039,12 @@
         <v>0.01193</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>0.01193</v>
+        <v>0.01198</v>
       </c>
       <c r="D506" s="1" t="n">
+        <v>0.01198</v>
+      </c>
+      <c r="E506" s="1" t="n">
         <v>0.01193</v>
       </c>
     </row>
@@ -8537,9 +10058,12 @@
         <v>0.2875</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>0.2875</v>
+        <v>0.2883</v>
       </c>
       <c r="D507" s="1" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="E507" s="1" t="n">
         <v>0.2875</v>
       </c>
     </row>
@@ -8553,9 +10077,12 @@
         <v>0.009379999999999999</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>0.009379999999999999</v>
+        <v>0.0094</v>
       </c>
       <c r="D508" s="1" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="E508" s="1" t="n">
         <v>0.009379999999999999</v>
       </c>
     </row>
@@ -8569,9 +10096,12 @@
         <v>0.006801</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>0.006801</v>
+        <v>0.006816</v>
       </c>
       <c r="D509" s="1" t="n">
+        <v>0.006816</v>
+      </c>
+      <c r="E509" s="1" t="n">
         <v>0.006801</v>
       </c>
     </row>
@@ -8585,9 +10115,12 @@
         <v>0.2936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>0.2936</v>
+        <v>0.2951</v>
       </c>
       <c r="D510" s="1" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="E510" s="1" t="n">
         <v>0.2936</v>
       </c>
     </row>
@@ -8601,9 +10134,12 @@
         <v>0.01467</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>0.01467</v>
+        <v>0.01471</v>
       </c>
       <c r="D511" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="E511" s="1" t="n">
         <v>0.01467</v>
       </c>
     </row>
@@ -8617,9 +10153,12 @@
         <v>0.1395</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>0.1395</v>
+        <v>0.1398</v>
       </c>
       <c r="D512" s="1" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="E512" s="1" t="n">
         <v>0.1395</v>
       </c>
     </row>
@@ -8633,9 +10172,12 @@
         <v>0.08069</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>0.08069</v>
+        <v>0.08144999999999999</v>
       </c>
       <c r="D513" s="1" t="n">
+        <v>0.08144999999999999</v>
+      </c>
+      <c r="E513" s="1" t="n">
         <v>0.08069</v>
       </c>
     </row>
@@ -8649,9 +10191,12 @@
         <v>0.025</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>0.025</v>
+        <v>0.0251</v>
       </c>
       <c r="D514" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="E514" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -8665,9 +10210,12 @@
         <v>0.06301</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>0.06301</v>
+        <v>0.06319</v>
       </c>
       <c r="D515" s="1" t="n">
+        <v>0.06319</v>
+      </c>
+      <c r="E515" s="1" t="n">
         <v>0.06301</v>
       </c>
     </row>
@@ -8681,9 +10229,12 @@
         <v>0.04707</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>0.04707</v>
+        <v>0.04723</v>
       </c>
       <c r="D516" s="1" t="n">
+        <v>0.04723</v>
+      </c>
+      <c r="E516" s="1" t="n">
         <v>0.04707</v>
       </c>
     </row>
@@ -8697,9 +10248,12 @@
         <v>0.004906</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>0.004906</v>
+        <v>0.004907</v>
       </c>
       <c r="D517" s="1" t="n">
+        <v>0.004907</v>
+      </c>
+      <c r="E517" s="1" t="n">
         <v>0.004906</v>
       </c>
     </row>
@@ -8713,11 +10267,14 @@
         <v>0.009419</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>0.009419</v>
+        <v>0.00941</v>
       </c>
       <c r="D518" s="1" t="n">
         <v>0.009419</v>
       </c>
+      <c r="E518" s="1" t="n">
+        <v>0.00941</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -8729,9 +10286,12 @@
         <v>0.01803</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>0.01803</v>
+        <v>0.01807</v>
       </c>
       <c r="D519" s="1" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="E519" s="1" t="n">
         <v>0.01803</v>
       </c>
     </row>
@@ -8745,9 +10305,12 @@
         <v>0.06630999999999999</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>0.06630999999999999</v>
+        <v>0.06666999999999999</v>
       </c>
       <c r="D520" s="1" t="n">
+        <v>0.06666999999999999</v>
+      </c>
+      <c r="E520" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -8761,9 +10324,12 @@
         <v>0.136</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>0.136</v>
+        <v>0.1365</v>
       </c>
       <c r="D521" s="1" t="n">
+        <v>0.1365</v>
+      </c>
+      <c r="E521" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -8777,9 +10343,12 @@
         <v>0.04718</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>0.04718</v>
+        <v>0.04746</v>
       </c>
       <c r="D522" s="1" t="n">
+        <v>0.04746</v>
+      </c>
+      <c r="E522" s="1" t="n">
         <v>0.04718</v>
       </c>
     </row>
@@ -8793,9 +10362,12 @@
         <v>0.06793</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>0.06793</v>
+        <v>0.06809</v>
       </c>
       <c r="D523" s="1" t="n">
+        <v>0.06809</v>
+      </c>
+      <c r="E523" s="1" t="n">
         <v>0.06793</v>
       </c>
     </row>
@@ -8809,9 +10381,12 @@
         <v>0.6968</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>0.6968</v>
+        <v>0.6982</v>
       </c>
       <c r="D524" s="1" t="n">
+        <v>0.6982</v>
+      </c>
+      <c r="E524" s="1" t="n">
         <v>0.6968</v>
       </c>
     </row>
@@ -8830,6 +10405,9 @@
       <c r="D525" s="1" t="n">
         <v>0.00267</v>
       </c>
+      <c r="E525" s="1" t="n">
+        <v>0.00267</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -8841,9 +10419,12 @@
         <v>0.4856</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>0.4856</v>
+        <v>0.4868</v>
       </c>
       <c r="D526" s="1" t="n">
+        <v>0.4868</v>
+      </c>
+      <c r="E526" s="1" t="n">
         <v>0.4856</v>
       </c>
     </row>
@@ -8857,9 +10438,12 @@
         <v>45.76</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45.76</v>
+        <v>45.81</v>
       </c>
       <c r="D527" s="1" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="E527" s="1" t="n">
         <v>45.76</v>
       </c>
     </row>
@@ -8873,9 +10457,12 @@
         <v>0.02436</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>0.02436</v>
+        <v>0.02437</v>
       </c>
       <c r="D528" s="1" t="n">
+        <v>0.02437</v>
+      </c>
+      <c r="E528" s="1" t="n">
         <v>0.02436</v>
       </c>
     </row>
@@ -8889,11 +10476,14 @@
         <v>0.006388</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>0.006388</v>
+        <v>0.006384</v>
       </c>
       <c r="D529" s="1" t="n">
         <v>0.006388</v>
       </c>
+      <c r="E529" s="1" t="n">
+        <v>0.006384</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -8905,9 +10495,12 @@
         <v>0.1993</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>0.1993</v>
+        <v>0.2</v>
       </c>
       <c r="D530" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E530" s="1" t="n">
         <v>0.1993</v>
       </c>
     </row>
@@ -8921,11 +10514,14 @@
         <v>0.007727</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>0.007727</v>
+        <v>0.007657</v>
       </c>
       <c r="D531" s="1" t="n">
         <v>0.007727</v>
       </c>
+      <c r="E531" s="1" t="n">
+        <v>0.007657</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -8937,9 +10533,12 @@
         <v>2.275</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>2.275</v>
+        <v>2.285</v>
       </c>
       <c r="D532" s="1" t="n">
+        <v>2.285</v>
+      </c>
+      <c r="E532" s="1" t="n">
         <v>2.275</v>
       </c>
     </row>
@@ -8953,11 +10552,14 @@
         <v>0.04142</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>0.04142</v>
+        <v>0.04138</v>
       </c>
       <c r="D533" s="1" t="n">
         <v>0.04142</v>
       </c>
+      <c r="E533" s="1" t="n">
+        <v>0.04138</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -8969,9 +10571,12 @@
         <v>0.1811</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>0.1811</v>
+        <v>0.1816</v>
       </c>
       <c r="D534" s="1" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="E534" s="1" t="n">
         <v>0.1811</v>
       </c>
     </row>
@@ -8985,9 +10590,12 @@
         <v>0.04303</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>0.04303</v>
+        <v>0.04311</v>
       </c>
       <c r="D535" s="1" t="n">
+        <v>0.04311</v>
+      </c>
+      <c r="E535" s="1" t="n">
         <v>0.04303</v>
       </c>
     </row>
@@ -9001,9 +10609,12 @@
         <v>0.0542</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>0.0542</v>
+        <v>0.05438</v>
       </c>
       <c r="D536" s="1" t="n">
+        <v>0.05438</v>
+      </c>
+      <c r="E536" s="1" t="n">
         <v>0.0542</v>
       </c>
     </row>
@@ -9017,9 +10628,12 @@
         <v>0.1605</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>0.1605</v>
+        <v>0.1609</v>
       </c>
       <c r="D537" s="1" t="n">
+        <v>0.1609</v>
+      </c>
+      <c r="E537" s="1" t="n">
         <v>0.1605</v>
       </c>
     </row>
@@ -9033,11 +10647,14 @@
         <v>0.03687</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>0.03687</v>
+        <v>0.03683</v>
       </c>
       <c r="D538" s="1" t="n">
         <v>0.03687</v>
       </c>
+      <c r="E538" s="1" t="n">
+        <v>0.03683</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -9049,9 +10666,12 @@
         <v>0.0573</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>0.0573</v>
+        <v>0.05772</v>
       </c>
       <c r="D539" s="1" t="n">
+        <v>0.05772</v>
+      </c>
+      <c r="E539" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -9065,9 +10685,12 @@
         <v>0.04259</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>0.04259</v>
+        <v>0.04267</v>
       </c>
       <c r="D540" s="1" t="n">
+        <v>0.04267</v>
+      </c>
+      <c r="E540" s="1" t="n">
         <v>0.04259</v>
       </c>
     </row>
@@ -9081,9 +10704,12 @@
         <v>0.0172</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>0.0172</v>
+        <v>0.0173</v>
       </c>
       <c r="D541" s="1" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="E541" s="1" t="n">
         <v>0.0172</v>
       </c>
     </row>
@@ -9097,11 +10723,14 @@
         <v>0.003975</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>0.003975</v>
+        <v>0.003971</v>
       </c>
       <c r="D542" s="1" t="n">
         <v>0.003975</v>
       </c>
+      <c r="E542" s="1" t="n">
+        <v>0.003971</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -9113,11 +10742,14 @@
         <v>0.05817</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>0.05817</v>
+        <v>0.05735</v>
       </c>
       <c r="D543" s="1" t="n">
         <v>0.05817</v>
       </c>
+      <c r="E543" s="1" t="n">
+        <v>0.05735</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -9129,9 +10761,12 @@
         <v>0.05022</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>0.05022</v>
+        <v>0.05042</v>
       </c>
       <c r="D544" s="1" t="n">
+        <v>0.05042</v>
+      </c>
+      <c r="E544" s="1" t="n">
         <v>0.05022</v>
       </c>
     </row>
@@ -9145,9 +10780,12 @@
         <v>0.04038</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>0.04038</v>
+        <v>0.04064</v>
       </c>
       <c r="D545" s="1" t="n">
+        <v>0.04064</v>
+      </c>
+      <c r="E545" s="1" t="n">
         <v>0.04038</v>
       </c>
     </row>
@@ -9161,9 +10799,12 @@
         <v>0.007402</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>0.007402</v>
+        <v>0.007412</v>
       </c>
       <c r="D546" s="1" t="n">
+        <v>0.007412</v>
+      </c>
+      <c r="E546" s="1" t="n">
         <v>0.007402</v>
       </c>
     </row>
@@ -9177,11 +10818,14 @@
         <v>0.01461</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>0.01461</v>
+        <v>0.0146</v>
       </c>
       <c r="D547" s="1" t="n">
         <v>0.01461</v>
       </c>
+      <c r="E547" s="1" t="n">
+        <v>0.0146</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -9193,11 +10837,14 @@
         <v>0.01573</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>0.01573</v>
+        <v>0.01572</v>
       </c>
       <c r="D548" s="1" t="n">
         <v>0.01573</v>
       </c>
+      <c r="E548" s="1" t="n">
+        <v>0.01572</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -9209,9 +10856,12 @@
         <v>0.13271</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>0.13271</v>
+        <v>0.13283</v>
       </c>
       <c r="D549" s="1" t="n">
+        <v>0.13283</v>
+      </c>
+      <c r="E549" s="1" t="n">
         <v>0.13271</v>
       </c>
     </row>
@@ -9225,9 +10875,12 @@
         <v>0.1695</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>0.1695</v>
+        <v>0.1696</v>
       </c>
       <c r="D550" s="1" t="n">
+        <v>0.1696</v>
+      </c>
+      <c r="E550" s="1" t="n">
         <v>0.1695</v>
       </c>
     </row>
@@ -9241,11 +10894,14 @@
         <v>0.003583</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>0.003583</v>
+        <v>0.003577</v>
       </c>
       <c r="D551" s="1" t="n">
         <v>0.003583</v>
       </c>
+      <c r="E551" s="1" t="n">
+        <v>0.003577</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -9257,11 +10913,14 @@
         <v>0.03034</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>0.03034</v>
+        <v>0.03032</v>
       </c>
       <c r="D552" s="1" t="n">
         <v>0.03034</v>
       </c>
+      <c r="E552" s="1" t="n">
+        <v>0.03032</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -9273,9 +10932,12 @@
         <v>0.01324</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>0.01324</v>
+        <v>0.01325</v>
       </c>
       <c r="D553" s="1" t="n">
+        <v>0.01325</v>
+      </c>
+      <c r="E553" s="1" t="n">
         <v>0.01324</v>
       </c>
     </row>
@@ -9289,9 +10951,12 @@
         <v>0.1043</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>0.1043</v>
+        <v>0.1046</v>
       </c>
       <c r="D554" s="1" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="E554" s="1" t="n">
         <v>0.1043</v>
       </c>
     </row>
@@ -9305,9 +10970,12 @@
         <v>0.05291</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>0.05291</v>
+        <v>0.05319</v>
       </c>
       <c r="D555" s="1" t="n">
+        <v>0.05319</v>
+      </c>
+      <c r="E555" s="1" t="n">
         <v>0.05291</v>
       </c>
     </row>
@@ -9321,10 +10989,13 @@
         <v>0.01224</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>0.01224</v>
+        <v>0.01223</v>
       </c>
       <c r="D556" s="1" t="n">
         <v>0.01224</v>
+      </c>
+      <c r="E556" s="1" t="n">
+        <v>0.01223</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,14 +416,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E556"/>
+  <dimension ref="A1:F556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -444,10 +445,15 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>price_00:30</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -466,10 +472,13 @@
         <v>71530</v>
       </c>
       <c r="D2" s="1" t="n">
+        <v>71364.39999999999</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>71530</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>71444.39999999999</v>
+      <c r="F2" s="1" t="n">
+        <v>71364.39999999999</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +494,13 @@
         <v>2096.9</v>
       </c>
       <c r="D3" s="1" t="n">
+        <v>2091.71</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>2096.9</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>2092.92</v>
+      <c r="F3" s="1" t="n">
+        <v>2091.71</v>
       </c>
     </row>
     <row r="4">
@@ -504,10 +516,13 @@
         <v>87.95</v>
       </c>
       <c r="D4" s="1" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>87.95</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>87.86</v>
+      <c r="F4" s="1" t="n">
+        <v>87.68000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -523,9 +538,12 @@
         <v>23.579</v>
       </c>
       <c r="D5" s="1" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>23.579</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" s="1" t="n">
         <v>23.478</v>
       </c>
     </row>
@@ -542,9 +560,12 @@
         <v>0.001852</v>
       </c>
       <c r="D6" s="1" t="n">
+        <v>0.001831</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>0.001852</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.001827</v>
       </c>
     </row>
@@ -561,11 +582,14 @@
         <v>1.4149</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1.4149</v>
+        <v>1.4136</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>1.4149</v>
       </c>
+      <c r="F7" s="1" t="n">
+        <v>1.4136</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -580,10 +604,13 @@
         <v>0.011244</v>
       </c>
       <c r="D8" s="1" t="n">
+        <v>0.010969</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>0.011244</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>0.011168</v>
+      <c r="F8" s="1" t="n">
+        <v>0.010969</v>
       </c>
     </row>
     <row r="9">
@@ -599,10 +626,13 @@
         <v>3.968</v>
       </c>
       <c r="D9" s="1" t="n">
+        <v>3.954</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>3.968</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>3.955</v>
+      <c r="F9" s="1" t="n">
+        <v>3.954</v>
       </c>
     </row>
     <row r="10">
@@ -618,9 +648,12 @@
         <v>272.62</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>275.06</v>
+        <v>275.37</v>
       </c>
       <c r="E10" s="1" t="n">
+        <v>275.37</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>272.62</v>
       </c>
     </row>
@@ -637,9 +670,12 @@
         <v>0.08047</v>
       </c>
       <c r="D11" s="1" t="n">
+        <v>0.07988000000000001</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>0.08047</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="F11" s="1" t="n">
         <v>0.07929</v>
       </c>
     </row>
@@ -656,10 +692,13 @@
         <v>227.69</v>
       </c>
       <c r="D12" s="1" t="n">
+        <v>226.28</v>
+      </c>
+      <c r="E12" s="1" t="n">
         <v>227.69</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>227.3</v>
+      <c r="F12" s="1" t="n">
+        <v>226.28</v>
       </c>
     </row>
     <row r="13">
@@ -675,10 +714,13 @@
         <v>0.09497</v>
       </c>
       <c r="D13" s="1" t="n">
+        <v>0.09464</v>
+      </c>
+      <c r="E13" s="1" t="n">
         <v>0.09497</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>0.09492</v>
+      <c r="F13" s="1" t="n">
+        <v>0.09464</v>
       </c>
     </row>
     <row r="14">
@@ -694,10 +736,13 @@
         <v>37.275</v>
       </c>
       <c r="D14" s="1" t="n">
+        <v>37.222</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>37.279</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>37.275</v>
+      <c r="F14" s="1" t="n">
+        <v>37.222</v>
       </c>
     </row>
     <row r="15">
@@ -713,9 +758,12 @@
         <v>0.09654</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.09654</v>
+        <v>0.09845</v>
       </c>
       <c r="E15" s="1" t="n">
+        <v>0.09845</v>
+      </c>
+      <c r="F15" s="1" t="n">
         <v>0.09461</v>
       </c>
     </row>
@@ -732,10 +780,13 @@
         <v>0.2305</v>
       </c>
       <c r="D16" s="1" t="n">
+        <v>0.2291</v>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>0.2339</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>0.2305</v>
+      <c r="F16" s="1" t="n">
+        <v>0.2291</v>
       </c>
     </row>
     <row r="17">
@@ -751,9 +802,12 @@
         <v>0.011513</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.011538</v>
+        <v>0.011542</v>
       </c>
       <c r="E17" s="1" t="n">
+        <v>0.011542</v>
+      </c>
+      <c r="F17" s="1" t="n">
         <v>0.011513</v>
       </c>
     </row>
@@ -770,9 +824,12 @@
         <v>660.72</v>
       </c>
       <c r="D18" s="1" t="n">
+        <v>659.73</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>660.72</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="F18" s="1" t="n">
         <v>659.6799999999999</v>
       </c>
     </row>
@@ -789,10 +846,13 @@
         <v>0.0033451</v>
       </c>
       <c r="D19" s="1" t="n">
+        <v>0.0033295</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>0.0033451</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>0.0033412</v>
+      <c r="F19" s="1" t="n">
+        <v>0.0033295</v>
       </c>
     </row>
     <row r="20">
@@ -808,9 +868,12 @@
         <v>0.17762</v>
       </c>
       <c r="D20" s="1" t="n">
+        <v>0.17941</v>
+      </c>
+      <c r="E20" s="1" t="n">
         <v>0.18017</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="F20" s="1" t="n">
         <v>0.17762</v>
       </c>
     </row>
@@ -827,9 +890,12 @@
         <v>0.009808000000000001</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.009808000000000001</v>
+        <v>0.010012</v>
       </c>
       <c r="E21" s="1" t="n">
+        <v>0.010012</v>
+      </c>
+      <c r="F21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -846,9 +912,12 @@
         <v>1.0033</v>
       </c>
       <c r="D22" s="1" t="n">
+        <v>1.0011</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>1.0033</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="F22" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -865,10 +934,13 @@
         <v>5007.01</v>
       </c>
       <c r="D23" s="1" t="n">
+        <v>5003.45</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>5012.25</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>5007.01</v>
+      <c r="F23" s="1" t="n">
+        <v>5003.45</v>
       </c>
     </row>
     <row r="24">
@@ -884,10 +956,13 @@
         <v>0.2643</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>0.2643</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>0.2635</v>
+      <c r="F24" s="1" t="n">
+        <v>0.2633</v>
       </c>
     </row>
     <row r="25">
@@ -903,9 +978,12 @@
         <v>2.9</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>2.9</v>
+        <v>2.917</v>
       </c>
       <c r="E25" s="1" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="F25" s="1" t="n">
         <v>2.899</v>
       </c>
     </row>
@@ -922,9 +1000,12 @@
         <v>0.4035</v>
       </c>
       <c r="D26" s="1" t="n">
+        <v>0.4031</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>0.4035</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="F26" s="1" t="n">
         <v>0.3959</v>
       </c>
     </row>
@@ -941,11 +1022,14 @@
         <v>0.885</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.885</v>
+        <v>0.884</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>0.885</v>
       </c>
+      <c r="F27" s="1" t="n">
+        <v>0.884</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -960,9 +1044,12 @@
         <v>1.343</v>
       </c>
       <c r="D28" s="1" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="E28" s="1" t="n">
         <v>1.343</v>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="F28" s="1" t="n">
         <v>1.336</v>
       </c>
     </row>
@@ -979,10 +1066,13 @@
         <v>9.179</v>
       </c>
       <c r="D29" s="1" t="n">
+        <v>9.148999999999999</v>
+      </c>
+      <c r="E29" s="1" t="n">
         <v>9.179</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>9.151</v>
+      <c r="F29" s="1" t="n">
+        <v>9.148999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -998,10 +1088,13 @@
         <v>463.35</v>
       </c>
       <c r="D30" s="1" t="n">
+        <v>461.31</v>
+      </c>
+      <c r="E30" s="1" t="n">
         <v>463.35</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>462.32</v>
+      <c r="F30" s="1" t="n">
+        <v>461.31</v>
       </c>
     </row>
     <row r="31">
@@ -1017,10 +1110,13 @@
         <v>9.728999999999999</v>
       </c>
       <c r="D31" s="1" t="n">
+        <v>9.696999999999999</v>
+      </c>
+      <c r="E31" s="1" t="n">
         <v>9.728999999999999</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>9.711</v>
+      <c r="F31" s="1" t="n">
+        <v>9.696999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1036,10 +1132,13 @@
         <v>0.36424</v>
       </c>
       <c r="D32" s="1" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="E32" s="1" t="n">
         <v>0.36683</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>0.36424</v>
+      <c r="F32" s="1" t="n">
+        <v>0.36306</v>
       </c>
     </row>
     <row r="33">
@@ -1055,10 +1154,13 @@
         <v>1.419</v>
       </c>
       <c r="D33" s="1" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>1.419</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>1.416</v>
+      <c r="F33" s="1" t="n">
+        <v>1.412</v>
       </c>
     </row>
     <row r="34">
@@ -1074,10 +1176,13 @@
         <v>0.59391</v>
       </c>
       <c r="D34" s="1" t="n">
+        <v>0.5926900000000001</v>
+      </c>
+      <c r="E34" s="1" t="n">
         <v>0.59391</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>0.59283</v>
+      <c r="F34" s="1" t="n">
+        <v>0.5926900000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1093,10 +1198,13 @@
         <v>1.2228</v>
       </c>
       <c r="D35" s="1" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>1.2228</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>1.2198</v>
+      <c r="F35" s="1" t="n">
+        <v>1.2186</v>
       </c>
     </row>
     <row r="36">
@@ -1112,10 +1220,13 @@
         <v>80.3</v>
       </c>
       <c r="D36" s="1" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="E36" s="1" t="n">
         <v>80.5</v>
       </c>
-      <c r="E36" s="1" t="n">
-        <v>80.3</v>
+      <c r="F36" s="1" t="n">
+        <v>80.27</v>
       </c>
     </row>
     <row r="37">
@@ -1131,9 +1242,12 @@
         <v>0.204</v>
       </c>
       <c r="D37" s="1" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="E37" s="1" t="n">
         <v>0.204</v>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="F37" s="1" t="n">
         <v>0.1977</v>
       </c>
     </row>
@@ -1150,9 +1264,12 @@
         <v>1.865</v>
       </c>
       <c r="D38" s="1" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="E38" s="1" t="n">
         <v>1.865</v>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="F38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -1169,9 +1286,12 @@
         <v>0.3197</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.3199</v>
+        <v>0.3245</v>
       </c>
       <c r="E39" s="1" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="F39" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -1188,9 +1308,12 @@
         <v>0.9077</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.9077</v>
+        <v>0.9115</v>
       </c>
       <c r="E40" s="1" t="n">
+        <v>0.9115</v>
+      </c>
+      <c r="F40" s="1" t="n">
         <v>0.9022</v>
       </c>
     </row>
@@ -1207,10 +1330,13 @@
         <v>0.7149</v>
       </c>
       <c r="D41" s="1" t="n">
+        <v>0.7136</v>
+      </c>
+      <c r="E41" s="1" t="n">
         <v>0.7149</v>
       </c>
-      <c r="E41" s="1" t="n">
-        <v>0.7148</v>
+      <c r="F41" s="1" t="n">
+        <v>0.7136</v>
       </c>
     </row>
     <row r="42">
@@ -1226,10 +1352,13 @@
         <v>0.06714000000000001</v>
       </c>
       <c r="D42" s="1" t="n">
+        <v>0.0665</v>
+      </c>
+      <c r="E42" s="1" t="n">
         <v>0.06769</v>
       </c>
-      <c r="E42" s="1" t="n">
-        <v>0.06714000000000001</v>
+      <c r="F42" s="1" t="n">
+        <v>0.0665</v>
       </c>
     </row>
     <row r="43">
@@ -1245,9 +1374,12 @@
         <v>113.57</v>
       </c>
       <c r="D43" s="1" t="n">
+        <v>113.08</v>
+      </c>
+      <c r="E43" s="1" t="n">
         <v>113.57</v>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="F43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -1264,9 +1396,12 @@
         <v>0.6578000000000001</v>
       </c>
       <c r="D44" s="1" t="n">
+        <v>0.6617</v>
+      </c>
+      <c r="E44" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="F44" s="1" t="n">
         <v>0.6578000000000001</v>
       </c>
     </row>
@@ -1283,9 +1418,12 @@
         <v>1.211</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>1.211</v>
+        <v>1.215</v>
       </c>
       <c r="E45" s="1" t="n">
+        <v>1.215</v>
+      </c>
+      <c r="F45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -1302,9 +1440,12 @@
         <v>0.02392</v>
       </c>
       <c r="D46" s="1" t="n">
+        <v>0.02383</v>
+      </c>
+      <c r="E46" s="1" t="n">
         <v>0.02392</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="F46" s="1" t="n">
         <v>0.02382</v>
       </c>
     </row>
@@ -1321,9 +1462,12 @@
         <v>55.17</v>
       </c>
       <c r="D47" s="1" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="E47" s="1" t="n">
         <v>55.17</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="F47" s="1" t="n">
         <v>55.06</v>
       </c>
     </row>
@@ -1340,10 +1484,13 @@
         <v>0.06081</v>
       </c>
       <c r="D48" s="1" t="n">
+        <v>0.05994</v>
+      </c>
+      <c r="E48" s="1" t="n">
         <v>0.06081</v>
       </c>
-      <c r="E48" s="1" t="n">
-        <v>0.06018</v>
+      <c r="F48" s="1" t="n">
+        <v>0.05994</v>
       </c>
     </row>
     <row r="49">
@@ -1359,10 +1506,13 @@
         <v>0.1082</v>
       </c>
       <c r="D49" s="1" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="E49" s="1" t="n">
         <v>0.1082</v>
       </c>
-      <c r="E49" s="1" t="n">
-        <v>0.108</v>
+      <c r="F49" s="1" t="n">
+        <v>0.1079</v>
       </c>
     </row>
     <row r="50">
@@ -1378,9 +1528,12 @@
         <v>0.01815</v>
       </c>
       <c r="D50" s="1" t="n">
+        <v>0.01806</v>
+      </c>
+      <c r="E50" s="1" t="n">
         <v>0.01815</v>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="F50" s="1" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -1400,6 +1553,9 @@
         <v>1.4659</v>
       </c>
       <c r="E51" s="1" t="n">
+        <v>1.4659</v>
+      </c>
+      <c r="F51" s="1" t="n">
         <v>1.4622</v>
       </c>
     </row>
@@ -1416,9 +1572,12 @@
         <v>0.3603</v>
       </c>
       <c r="D52" s="1" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="E52" s="1" t="n">
         <v>0.3603</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="F52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -1435,10 +1594,13 @@
         <v>0.001961</v>
       </c>
       <c r="D53" s="1" t="n">
+        <v>0.001946</v>
+      </c>
+      <c r="E53" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="E53" s="1" t="n">
-        <v>0.001959</v>
+      <c r="F53" s="1" t="n">
+        <v>0.001946</v>
       </c>
     </row>
     <row r="54">
@@ -1454,9 +1616,12 @@
         <v>0.09569</v>
       </c>
       <c r="D54" s="1" t="n">
+        <v>0.09540999999999999</v>
+      </c>
+      <c r="E54" s="1" t="n">
         <v>0.09569</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="F54" s="1" t="n">
         <v>0.09524000000000001</v>
       </c>
     </row>
@@ -1473,9 +1638,12 @@
         <v>0.04003</v>
       </c>
       <c r="D55" s="1" t="n">
+        <v>0.04017</v>
+      </c>
+      <c r="E55" s="1" t="n">
         <v>0.04071</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="F55" s="1" t="n">
         <v>0.04003</v>
       </c>
     </row>
@@ -1492,10 +1660,13 @@
         <v>0.29838</v>
       </c>
       <c r="D56" s="1" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="E56" s="1" t="n">
         <v>0.29861</v>
       </c>
-      <c r="E56" s="1" t="n">
-        <v>0.29838</v>
+      <c r="F56" s="1" t="n">
+        <v>0.29831</v>
       </c>
     </row>
     <row r="57">
@@ -1511,10 +1682,13 @@
         <v>0.00581</v>
       </c>
       <c r="D57" s="1" t="n">
+        <v>0.00579</v>
+      </c>
+      <c r="E57" s="1" t="n">
         <v>0.005824</v>
       </c>
-      <c r="E57" s="1" t="n">
-        <v>0.00581</v>
+      <c r="F57" s="1" t="n">
+        <v>0.00579</v>
       </c>
     </row>
     <row r="58">
@@ -1530,10 +1704,13 @@
         <v>4997.14</v>
       </c>
       <c r="D58" s="1" t="n">
+        <v>4991.64</v>
+      </c>
+      <c r="E58" s="1" t="n">
         <v>4998.37</v>
       </c>
-      <c r="E58" s="1" t="n">
-        <v>4997.14</v>
+      <c r="F58" s="1" t="n">
+        <v>4991.64</v>
       </c>
     </row>
     <row r="59">
@@ -1549,10 +1726,13 @@
         <v>0.4177</v>
       </c>
       <c r="D59" s="1" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="E59" s="1" t="n">
         <v>0.4246</v>
       </c>
-      <c r="E59" s="1" t="n">
-        <v>0.4177</v>
+      <c r="F59" s="1" t="n">
+        <v>0.4171</v>
       </c>
     </row>
     <row r="60">
@@ -1568,9 +1748,12 @@
         <v>0.04658</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>0.04658</v>
+        <v>0.04683</v>
       </c>
       <c r="E60" s="1" t="n">
+        <v>0.04683</v>
+      </c>
+      <c r="F60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -1587,10 +1770,13 @@
         <v>0.21708</v>
       </c>
       <c r="D61" s="1" t="n">
+        <v>0.21618</v>
+      </c>
+      <c r="E61" s="1" t="n">
         <v>0.21708</v>
       </c>
-      <c r="E61" s="1" t="n">
-        <v>0.21692</v>
+      <c r="F61" s="1" t="n">
+        <v>0.21618</v>
       </c>
     </row>
     <row r="62">
@@ -1606,10 +1792,13 @@
         <v>0.1076</v>
       </c>
       <c r="D62" s="1" t="n">
+        <v>0.1068</v>
+      </c>
+      <c r="E62" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="E62" s="1" t="n">
-        <v>0.1072</v>
+      <c r="F62" s="1" t="n">
+        <v>0.1068</v>
       </c>
     </row>
     <row r="63">
@@ -1625,9 +1814,12 @@
         <v>0.7301</v>
       </c>
       <c r="D63" s="1" t="n">
+        <v>0.7272</v>
+      </c>
+      <c r="E63" s="1" t="n">
         <v>0.7301</v>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="F63" s="1" t="n">
         <v>0.7267</v>
       </c>
     </row>
@@ -1644,9 +1836,12 @@
         <v>0.1667</v>
       </c>
       <c r="D64" s="1" t="n">
+        <v>0.1662</v>
+      </c>
+      <c r="E64" s="1" t="n">
         <v>0.1667</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="F64" s="1" t="n">
         <v>0.166</v>
       </c>
     </row>
@@ -1663,10 +1858,13 @@
         <v>2.661</v>
       </c>
       <c r="D65" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E65" s="1" t="n">
         <v>2.661</v>
       </c>
-      <c r="E65" s="1" t="n">
-        <v>2.657</v>
+      <c r="F65" s="1" t="n">
+        <v>2.65</v>
       </c>
     </row>
     <row r="66">
@@ -1682,9 +1880,12 @@
         <v>0.04048</v>
       </c>
       <c r="D66" s="1" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="E66" s="1" t="n">
         <v>0.04048</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="F66" s="1" t="n">
         <v>0.04018</v>
       </c>
     </row>
@@ -1701,9 +1902,12 @@
         <v>0.04234</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>0.04234</v>
+        <v>0.04249</v>
       </c>
       <c r="E67" s="1" t="n">
+        <v>0.04249</v>
+      </c>
+      <c r="F67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -1720,9 +1924,12 @@
         <v>3.967</v>
       </c>
       <c r="D68" s="1" t="n">
+        <v>3.959</v>
+      </c>
+      <c r="E68" s="1" t="n">
         <v>3.967</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="F68" s="1" t="n">
         <v>3.952</v>
       </c>
     </row>
@@ -1739,9 +1946,12 @@
         <v>0.1261</v>
       </c>
       <c r="D69" s="1" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="E69" s="1" t="n">
         <v>0.1261</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="F69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -1758,9 +1968,12 @@
         <v>6.114</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>6.128</v>
+        <v>6.207</v>
       </c>
       <c r="E70" s="1" t="n">
+        <v>6.207</v>
+      </c>
+      <c r="F70" s="1" t="n">
         <v>6.114</v>
       </c>
     </row>
@@ -1777,10 +1990,13 @@
         <v>0.04999</v>
       </c>
       <c r="D71" s="1" t="n">
+        <v>0.04991</v>
+      </c>
+      <c r="E71" s="1" t="n">
         <v>0.04999</v>
       </c>
-      <c r="E71" s="1" t="n">
-        <v>0.04997</v>
+      <c r="F71" s="1" t="n">
+        <v>0.04991</v>
       </c>
     </row>
     <row r="72">
@@ -1796,9 +2012,12 @@
         <v>0.004133</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>0.004133</v>
+        <v>0.004181</v>
       </c>
       <c r="E72" s="1" t="n">
+        <v>0.004181</v>
+      </c>
+      <c r="F72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -1815,9 +2034,12 @@
         <v>6.029</v>
       </c>
       <c r="D73" s="1" t="n">
+        <v>6.018</v>
+      </c>
+      <c r="E73" s="1" t="n">
         <v>6.029</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="F73" s="1" t="n">
         <v>6.001</v>
       </c>
     </row>
@@ -1834,9 +2056,12 @@
         <v>0.1633</v>
       </c>
       <c r="D74" s="1" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="E74" s="1" t="n">
         <v>0.1633</v>
       </c>
-      <c r="E74" s="1" t="n">
+      <c r="F74" s="1" t="n">
         <v>0.1629</v>
       </c>
     </row>
@@ -1853,9 +2078,12 @@
         <v>0.007297</v>
       </c>
       <c r="D75" s="1" t="n">
+        <v>0.007281</v>
+      </c>
+      <c r="E75" s="1" t="n">
         <v>0.007297</v>
       </c>
-      <c r="E75" s="1" t="n">
+      <c r="F75" s="1" t="n">
         <v>0.007276</v>
       </c>
     </row>
@@ -1872,9 +2100,12 @@
         <v>0.2086</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>0.2086</v>
+        <v>0.2095</v>
       </c>
       <c r="E76" s="1" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="F76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -1891,10 +2122,13 @@
         <v>0.005821</v>
       </c>
       <c r="D77" s="1" t="n">
+        <v>0.005799</v>
+      </c>
+      <c r="E77" s="1" t="n">
         <v>0.005826</v>
       </c>
-      <c r="E77" s="1" t="n">
-        <v>0.005821</v>
+      <c r="F77" s="1" t="n">
+        <v>0.005799</v>
       </c>
     </row>
     <row r="78">
@@ -1910,9 +2144,12 @@
         <v>0.1019</v>
       </c>
       <c r="D78" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="E78" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="E78" s="1" t="n">
+      <c r="F78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -1929,9 +2166,12 @@
         <v>0.006292</v>
       </c>
       <c r="D79" s="1" t="n">
+        <v>0.006269</v>
+      </c>
+      <c r="E79" s="1" t="n">
         <v>0.006292</v>
       </c>
-      <c r="E79" s="1" t="n">
+      <c r="F79" s="1" t="n">
         <v>0.006256</v>
       </c>
     </row>
@@ -1948,9 +2188,12 @@
         <v>33.51</v>
       </c>
       <c r="D80" s="1" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="E80" s="1" t="n">
         <v>33.51</v>
       </c>
-      <c r="E80" s="1" t="n">
+      <c r="F80" s="1" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -1967,9 +2210,12 @@
         <v>0.04043</v>
       </c>
       <c r="D81" s="1" t="n">
+        <v>0.04042</v>
+      </c>
+      <c r="E81" s="1" t="n">
         <v>0.04043</v>
       </c>
-      <c r="E81" s="1" t="n">
+      <c r="F81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -1986,10 +2232,13 @@
         <v>0.1675</v>
       </c>
       <c r="D82" s="1" t="n">
+        <v>0.16688</v>
+      </c>
+      <c r="E82" s="1" t="n">
         <v>0.1675</v>
       </c>
-      <c r="E82" s="1" t="n">
-        <v>0.16701</v>
+      <c r="F82" s="1" t="n">
+        <v>0.16688</v>
       </c>
     </row>
     <row r="83">
@@ -2005,10 +2254,13 @@
         <v>0.1033</v>
       </c>
       <c r="D83" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="E83" s="1" t="n">
         <v>0.1035</v>
       </c>
-      <c r="E83" s="1" t="n">
-        <v>0.1033</v>
+      <c r="F83" s="1" t="n">
+        <v>0.1032</v>
       </c>
     </row>
     <row r="84">
@@ -2024,9 +2276,12 @@
         <v>0.08841</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>0.08841</v>
+        <v>0.08848</v>
       </c>
       <c r="E84" s="1" t="n">
+        <v>0.08848</v>
+      </c>
+      <c r="F84" s="1" t="n">
         <v>0.08810999999999999</v>
       </c>
     </row>
@@ -2043,10 +2298,13 @@
         <v>0.02331</v>
       </c>
       <c r="D85" s="1" t="n">
+        <v>0.02322</v>
+      </c>
+      <c r="E85" s="1" t="n">
         <v>0.02331</v>
       </c>
-      <c r="E85" s="1" t="n">
-        <v>0.02325</v>
+      <c r="F85" s="1" t="n">
+        <v>0.02322</v>
       </c>
     </row>
     <row r="86">
@@ -2065,6 +2323,9 @@
         <v>0.238</v>
       </c>
       <c r="E86" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="F86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -2081,9 +2342,12 @@
         <v>357.12</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>357.12</v>
+        <v>357.4</v>
       </c>
       <c r="E87" s="1" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="F87" s="1" t="n">
         <v>355.75</v>
       </c>
     </row>
@@ -2103,6 +2367,9 @@
         <v>0.00344</v>
       </c>
       <c r="E88" s="1" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="F88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -2119,10 +2386,13 @@
         <v>8.301</v>
       </c>
       <c r="D89" s="1" t="n">
+        <v>8.272</v>
+      </c>
+      <c r="E89" s="1" t="n">
         <v>8.301</v>
       </c>
-      <c r="E89" s="1" t="n">
-        <v>8.278</v>
+      <c r="F89" s="1" t="n">
+        <v>8.272</v>
       </c>
     </row>
     <row r="90">
@@ -2138,10 +2408,13 @@
         <v>0.005945</v>
       </c>
       <c r="D90" s="1" t="n">
+        <v>0.00591</v>
+      </c>
+      <c r="E90" s="1" t="n">
         <v>0.005945</v>
       </c>
-      <c r="E90" s="1" t="n">
-        <v>0.00593</v>
+      <c r="F90" s="1" t="n">
+        <v>0.00591</v>
       </c>
     </row>
     <row r="91">
@@ -2157,9 +2430,12 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="D91" s="1" t="n">
+        <v>0.06891</v>
+      </c>
+      <c r="E91" s="1" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="E91" s="1" t="n">
+      <c r="F91" s="1" t="n">
         <v>0.06884999999999999</v>
       </c>
     </row>
@@ -2176,9 +2452,12 @@
         <v>0.02894</v>
       </c>
       <c r="D92" s="1" t="n">
+        <v>0.02883</v>
+      </c>
+      <c r="E92" s="1" t="n">
         <v>0.02894</v>
       </c>
-      <c r="E92" s="1" t="n">
+      <c r="F92" s="1" t="n">
         <v>0.02879</v>
       </c>
     </row>
@@ -2195,10 +2474,13 @@
         <v>5.189</v>
       </c>
       <c r="D93" s="1" t="n">
+        <v>5.159</v>
+      </c>
+      <c r="E93" s="1" t="n">
         <v>5.202</v>
       </c>
-      <c r="E93" s="1" t="n">
-        <v>5.189</v>
+      <c r="F93" s="1" t="n">
+        <v>5.159</v>
       </c>
     </row>
     <row r="94">
@@ -2217,6 +2499,9 @@
         <v>0.000228</v>
       </c>
       <c r="E94" s="1" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="F94" s="1" t="n">
         <v>0.000226</v>
       </c>
     </row>
@@ -2233,9 +2518,12 @@
         <v>0.9241</v>
       </c>
       <c r="D95" s="1" t="n">
+        <v>0.9223</v>
+      </c>
+      <c r="E95" s="1" t="n">
         <v>0.9241</v>
       </c>
-      <c r="E95" s="1" t="n">
+      <c r="F95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -2252,9 +2540,12 @@
         <v>2.0598</v>
       </c>
       <c r="D96" s="1" t="n">
+        <v>2.0658</v>
+      </c>
+      <c r="E96" s="1" t="n">
         <v>2.0774</v>
       </c>
-      <c r="E96" s="1" t="n">
+      <c r="F96" s="1" t="n">
         <v>2.0598</v>
       </c>
     </row>
@@ -2271,9 +2562,12 @@
         <v>0.3711</v>
       </c>
       <c r="D97" s="1" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="E97" s="1" t="n">
         <v>0.3711</v>
       </c>
-      <c r="E97" s="1" t="n">
+      <c r="F97" s="1" t="n">
         <v>0.369</v>
       </c>
     </row>
@@ -2290,9 +2584,12 @@
         <v>1.618</v>
       </c>
       <c r="D98" s="1" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="E98" s="1" t="n">
         <v>1.618</v>
       </c>
-      <c r="E98" s="1" t="n">
+      <c r="F98" s="1" t="n">
         <v>1.613</v>
       </c>
     </row>
@@ -2309,9 +2606,12 @@
         <v>0.2368</v>
       </c>
       <c r="D99" s="1" t="n">
+        <v>0.2366</v>
+      </c>
+      <c r="E99" s="1" t="n">
         <v>0.2368</v>
       </c>
-      <c r="E99" s="1" t="n">
+      <c r="F99" s="1" t="n">
         <v>0.2351</v>
       </c>
     </row>
@@ -2328,9 +2628,12 @@
         <v>0.13621</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>0.13621</v>
+        <v>0.13665</v>
       </c>
       <c r="E100" s="1" t="n">
+        <v>0.13665</v>
+      </c>
+      <c r="F100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -2347,9 +2650,12 @@
         <v>0.06908</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>0.06908</v>
+        <v>0.07115</v>
       </c>
       <c r="E101" s="1" t="n">
+        <v>0.07115</v>
+      </c>
+      <c r="F101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -2369,6 +2675,9 @@
         <v>0.001085</v>
       </c>
       <c r="E102" s="1" t="n">
+        <v>0.001085</v>
+      </c>
+      <c r="F102" s="1" t="n">
         <v>0.001084</v>
       </c>
     </row>
@@ -2385,10 +2694,13 @@
         <v>0.003424</v>
       </c>
       <c r="D103" s="1" t="n">
+        <v>0.003409</v>
+      </c>
+      <c r="E103" s="1" t="n">
         <v>0.003424</v>
       </c>
-      <c r="E103" s="1" t="n">
-        <v>0.003414</v>
+      <c r="F103" s="1" t="n">
+        <v>0.003409</v>
       </c>
     </row>
     <row r="104">
@@ -2404,10 +2716,13 @@
         <v>0.27751</v>
       </c>
       <c r="D104" s="1" t="n">
+        <v>0.27584</v>
+      </c>
+      <c r="E104" s="1" t="n">
         <v>0.27751</v>
       </c>
-      <c r="E104" s="1" t="n">
-        <v>0.27656</v>
+      <c r="F104" s="1" t="n">
+        <v>0.27584</v>
       </c>
     </row>
     <row r="105">
@@ -2423,10 +2738,13 @@
         <v>0.01257</v>
       </c>
       <c r="D105" s="1" t="n">
+        <v>0.01243</v>
+      </c>
+      <c r="E105" s="1" t="n">
         <v>0.01257</v>
       </c>
-      <c r="E105" s="1" t="n">
-        <v>0.01247</v>
+      <c r="F105" s="1" t="n">
+        <v>0.01243</v>
       </c>
     </row>
     <row r="106">
@@ -2442,10 +2760,13 @@
         <v>0.13569</v>
       </c>
       <c r="D106" s="1" t="n">
+        <v>0.13413</v>
+      </c>
+      <c r="E106" s="1" t="n">
         <v>0.13569</v>
       </c>
-      <c r="E106" s="1" t="n">
-        <v>0.13515</v>
+      <c r="F106" s="1" t="n">
+        <v>0.13413</v>
       </c>
     </row>
     <row r="107">
@@ -2461,9 +2782,12 @@
         <v>0.3496</v>
       </c>
       <c r="D107" s="1" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="E107" s="1" t="n">
         <v>0.3496</v>
       </c>
-      <c r="E107" s="1" t="n">
+      <c r="F107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -2480,9 +2804,12 @@
         <v>0.1436</v>
       </c>
       <c r="D108" s="1" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="E108" s="1" t="n">
         <v>0.1436</v>
       </c>
-      <c r="E108" s="1" t="n">
+      <c r="F108" s="1" t="n">
         <v>0.1426</v>
       </c>
     </row>
@@ -2499,9 +2826,12 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="D109" s="1" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="E109" s="1" t="n">
         <v>0.9320000000000001</v>
       </c>
-      <c r="E109" s="1" t="n">
+      <c r="F109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -2518,10 +2848,13 @@
         <v>0.016308</v>
       </c>
       <c r="D110" s="1" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="E110" s="1" t="n">
         <v>0.016308</v>
       </c>
-      <c r="E110" s="1" t="n">
-        <v>0.016258</v>
+      <c r="F110" s="1" t="n">
+        <v>0.01624</v>
       </c>
     </row>
     <row r="111">
@@ -2537,9 +2870,12 @@
         <v>0.03774</v>
       </c>
       <c r="D111" s="1" t="n">
+        <v>0.038015</v>
+      </c>
+      <c r="E111" s="1" t="n">
         <v>0.038335</v>
       </c>
-      <c r="E111" s="1" t="n">
+      <c r="F111" s="1" t="n">
         <v>0.03774</v>
       </c>
     </row>
@@ -2556,9 +2892,12 @@
         <v>0.11926</v>
       </c>
       <c r="D112" s="1" t="n">
+        <v>0.11952</v>
+      </c>
+      <c r="E112" s="1" t="n">
         <v>0.11959</v>
       </c>
-      <c r="E112" s="1" t="n">
+      <c r="F112" s="1" t="n">
         <v>0.11926</v>
       </c>
     </row>
@@ -2575,9 +2914,12 @@
         <v>0.09465</v>
       </c>
       <c r="D113" s="1" t="n">
+        <v>0.0945</v>
+      </c>
+      <c r="E113" s="1" t="n">
         <v>0.09465</v>
       </c>
-      <c r="E113" s="1" t="n">
+      <c r="F113" s="1" t="n">
         <v>0.09426</v>
       </c>
     </row>
@@ -2594,10 +2936,13 @@
         <v>0.1299</v>
       </c>
       <c r="D114" s="1" t="n">
+        <v>0.12895</v>
+      </c>
+      <c r="E114" s="1" t="n">
         <v>0.1299</v>
       </c>
-      <c r="E114" s="1" t="n">
-        <v>0.12945</v>
+      <c r="F114" s="1" t="n">
+        <v>0.12895</v>
       </c>
     </row>
     <row r="115">
@@ -2613,9 +2958,12 @@
         <v>0.2656</v>
       </c>
       <c r="D115" s="1" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="E115" s="1" t="n">
         <v>0.2656</v>
       </c>
-      <c r="E115" s="1" t="n">
+      <c r="F115" s="1" t="n">
         <v>0.264</v>
       </c>
     </row>
@@ -2632,9 +2980,12 @@
         <v>0.0529</v>
       </c>
       <c r="D116" s="1" t="n">
+        <v>0.05223</v>
+      </c>
+      <c r="E116" s="1" t="n">
         <v>0.0529</v>
       </c>
-      <c r="E116" s="1" t="n">
+      <c r="F116" s="1" t="n">
         <v>0.05208</v>
       </c>
     </row>
@@ -2651,9 +3002,12 @@
         <v>0.0916</v>
       </c>
       <c r="D117" s="1" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="E117" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="E117" s="1" t="n">
+      <c r="F117" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -2670,10 +3024,13 @@
         <v>0.05516</v>
       </c>
       <c r="D118" s="1" t="n">
+        <v>0.05509</v>
+      </c>
+      <c r="E118" s="1" t="n">
         <v>0.05545</v>
       </c>
-      <c r="E118" s="1" t="n">
-        <v>0.05516</v>
+      <c r="F118" s="1" t="n">
+        <v>0.05509</v>
       </c>
     </row>
     <row r="119">
@@ -2689,9 +3046,12 @@
         <v>0.01515</v>
       </c>
       <c r="D119" s="1" t="n">
+        <v>0.01511</v>
+      </c>
+      <c r="E119" s="1" t="n">
         <v>0.01515</v>
       </c>
-      <c r="E119" s="1" t="n">
+      <c r="F119" s="1" t="n">
         <v>0.01511</v>
       </c>
     </row>
@@ -2708,9 +3068,12 @@
         <v>3.06</v>
       </c>
       <c r="D120" s="1" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="E120" s="1" t="n">
         <v>3.06</v>
       </c>
-      <c r="E120" s="1" t="n">
+      <c r="F120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -2727,9 +3090,12 @@
         <v>1.855</v>
       </c>
       <c r="D121" s="1" t="n">
+        <v>1.852</v>
+      </c>
+      <c r="E121" s="1" t="n">
         <v>1.855</v>
       </c>
-      <c r="E121" s="1" t="n">
+      <c r="F121" s="1" t="n">
         <v>1.85</v>
       </c>
     </row>
@@ -2746,10 +3112,13 @@
         <v>1.2964</v>
       </c>
       <c r="D122" s="1" t="n">
+        <v>1.2934</v>
+      </c>
+      <c r="E122" s="1" t="n">
         <v>1.2965</v>
       </c>
-      <c r="E122" s="1" t="n">
-        <v>1.2964</v>
+      <c r="F122" s="1" t="n">
+        <v>1.2934</v>
       </c>
     </row>
     <row r="123">
@@ -2765,10 +3134,13 @@
         <v>0.319</v>
       </c>
       <c r="D123" s="1" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="E123" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="E123" s="1" t="n">
-        <v>0.319</v>
+      <c r="F123" s="1" t="n">
+        <v>0.318</v>
       </c>
     </row>
     <row r="124">
@@ -2784,9 +3156,12 @@
         <v>0.12242</v>
       </c>
       <c r="D124" s="1" t="n">
+        <v>0.12363</v>
+      </c>
+      <c r="E124" s="1" t="n">
         <v>0.12506</v>
       </c>
-      <c r="E124" s="1" t="n">
+      <c r="F124" s="1" t="n">
         <v>0.12242</v>
       </c>
     </row>
@@ -2803,9 +3178,12 @@
         <v>0.008181000000000001</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>0.008181000000000001</v>
+        <v>0.008263</v>
       </c>
       <c r="E125" s="1" t="n">
+        <v>0.008263</v>
+      </c>
+      <c r="F125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -2822,9 +3200,12 @@
         <v>0.01576</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>0.01576</v>
+        <v>0.01582</v>
       </c>
       <c r="E126" s="1" t="n">
+        <v>0.01582</v>
+      </c>
+      <c r="F126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -2841,9 +3222,12 @@
         <v>0.04441</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>0.04441</v>
+        <v>0.04468</v>
       </c>
       <c r="E127" s="1" t="n">
+        <v>0.04468</v>
+      </c>
+      <c r="F127" s="1" t="n">
         <v>0.04402</v>
       </c>
     </row>
@@ -2860,9 +3244,12 @@
         <v>0.0458</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>0.0458</v>
+        <v>0.04618</v>
       </c>
       <c r="E128" s="1" t="n">
+        <v>0.04618</v>
+      </c>
+      <c r="F128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -2879,10 +3266,13 @@
         <v>0.09635000000000001</v>
       </c>
       <c r="D129" s="1" t="n">
+        <v>0.09544999999999999</v>
+      </c>
+      <c r="E129" s="1" t="n">
         <v>0.09635000000000001</v>
       </c>
-      <c r="E129" s="1" t="n">
-        <v>0.0961</v>
+      <c r="F129" s="1" t="n">
+        <v>0.09544999999999999</v>
       </c>
     </row>
     <row r="130">
@@ -2898,10 +3288,13 @@
         <v>0.09896000000000001</v>
       </c>
       <c r="D130" s="1" t="n">
+        <v>0.09877</v>
+      </c>
+      <c r="E130" s="1" t="n">
         <v>0.09927</v>
       </c>
-      <c r="E130" s="1" t="n">
-        <v>0.09896000000000001</v>
+      <c r="F130" s="1" t="n">
+        <v>0.09877</v>
       </c>
     </row>
     <row r="131">
@@ -2917,9 +3310,12 @@
         <v>0.16577</v>
       </c>
       <c r="D131" s="1" t="n">
+        <v>0.1651</v>
+      </c>
+      <c r="E131" s="1" t="n">
         <v>0.16577</v>
       </c>
-      <c r="E131" s="1" t="n">
+      <c r="F131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -2939,6 +3335,9 @@
         <v>0.01693</v>
       </c>
       <c r="E132" s="1" t="n">
+        <v>0.01693</v>
+      </c>
+      <c r="F132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -2955,9 +3354,12 @@
         <v>0.06652</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>0.06652</v>
+        <v>0.06655</v>
       </c>
       <c r="E133" s="1" t="n">
+        <v>0.06655</v>
+      </c>
+      <c r="F133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -2974,9 +3376,12 @@
         <v>0.3023</v>
       </c>
       <c r="D134" s="1" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="E134" s="1" t="n">
         <v>0.3023</v>
       </c>
-      <c r="E134" s="1" t="n">
+      <c r="F134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -2993,10 +3398,13 @@
         <v>0.04514</v>
       </c>
       <c r="D135" s="1" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="E135" s="1" t="n">
         <v>0.04515</v>
       </c>
-      <c r="E135" s="1" t="n">
-        <v>0.04514</v>
+      <c r="F135" s="1" t="n">
+        <v>0.0451</v>
       </c>
     </row>
     <row r="136">
@@ -3012,10 +3420,13 @@
         <v>0.783</v>
       </c>
       <c r="D136" s="1" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="E136" s="1" t="n">
         <v>0.783</v>
       </c>
-      <c r="E136" s="1" t="n">
-        <v>0.782</v>
+      <c r="F136" s="1" t="n">
+        <v>0.781</v>
       </c>
     </row>
     <row r="137">
@@ -3031,10 +3442,13 @@
         <v>0.1168</v>
       </c>
       <c r="D137" s="1" t="n">
+        <v>0.1162</v>
+      </c>
+      <c r="E137" s="1" t="n">
         <v>0.1168</v>
       </c>
-      <c r="E137" s="1" t="n">
-        <v>0.1164</v>
+      <c r="F137" s="1" t="n">
+        <v>0.1162</v>
       </c>
     </row>
     <row r="138">
@@ -3050,9 +3464,12 @@
         <v>0.146</v>
       </c>
       <c r="D138" s="1" t="n">
+        <v>0.14571</v>
+      </c>
+      <c r="E138" s="1" t="n">
         <v>0.146</v>
       </c>
-      <c r="E138" s="1" t="n">
+      <c r="F138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -3069,11 +3486,14 @@
         <v>0.05719</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>0.05719</v>
+        <v>0.05713</v>
       </c>
       <c r="E139" s="1" t="n">
         <v>0.05719</v>
       </c>
+      <c r="F139" s="1" t="n">
+        <v>0.05713</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3088,9 +3508,12 @@
         <v>0.007295</v>
       </c>
       <c r="D140" s="1" t="n">
+        <v>0.00728</v>
+      </c>
+      <c r="E140" s="1" t="n">
         <v>0.007295</v>
       </c>
-      <c r="E140" s="1" t="n">
+      <c r="F140" s="1" t="n">
         <v>0.007274</v>
       </c>
     </row>
@@ -3107,10 +3530,13 @@
         <v>0.09601</v>
       </c>
       <c r="D141" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="E141" s="1" t="n">
         <v>0.09601</v>
       </c>
-      <c r="E141" s="1" t="n">
-        <v>0.09588000000000001</v>
+      <c r="F141" s="1" t="n">
+        <v>0.0958</v>
       </c>
     </row>
     <row r="142">
@@ -3126,9 +3552,12 @@
         <v>0.08348</v>
       </c>
       <c r="D142" s="1" t="n">
+        <v>0.08323</v>
+      </c>
+      <c r="E142" s="1" t="n">
         <v>0.08348</v>
       </c>
-      <c r="E142" s="1" t="n">
+      <c r="F142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -3145,9 +3574,12 @@
         <v>0.00852</v>
       </c>
       <c r="D143" s="1" t="n">
+        <v>0.00851</v>
+      </c>
+      <c r="E143" s="1" t="n">
         <v>0.00852</v>
       </c>
-      <c r="E143" s="1" t="n">
+      <c r="F143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -3164,9 +3596,12 @@
         <v>0.07288</v>
       </c>
       <c r="D144" s="1" t="n">
+        <v>0.07267999999999999</v>
+      </c>
+      <c r="E144" s="1" t="n">
         <v>0.07288</v>
       </c>
-      <c r="E144" s="1" t="n">
+      <c r="F144" s="1" t="n">
         <v>0.0726</v>
       </c>
     </row>
@@ -3183,10 +3618,13 @@
         <v>0.4303</v>
       </c>
       <c r="D145" s="1" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="E145" s="1" t="n">
         <v>0.4303</v>
       </c>
-      <c r="E145" s="1" t="n">
-        <v>0.4302</v>
+      <c r="F145" s="1" t="n">
+        <v>0.4297</v>
       </c>
     </row>
     <row r="146">
@@ -3202,9 +3640,12 @@
         <v>0.03252</v>
       </c>
       <c r="D146" s="1" t="n">
+        <v>0.03259</v>
+      </c>
+      <c r="E146" s="1" t="n">
         <v>0.03276</v>
       </c>
-      <c r="E146" s="1" t="n">
+      <c r="F146" s="1" t="n">
         <v>0.03252</v>
       </c>
     </row>
@@ -3221,9 +3662,12 @@
         <v>390.55</v>
       </c>
       <c r="D147" s="1" t="n">
+        <v>390.43</v>
+      </c>
+      <c r="E147" s="1" t="n">
         <v>390.55</v>
       </c>
-      <c r="E147" s="1" t="n">
+      <c r="F147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -3240,9 +3684,12 @@
         <v>0.0329</v>
       </c>
       <c r="D148" s="1" t="n">
+        <v>0.03293</v>
+      </c>
+      <c r="E148" s="1" t="n">
         <v>0.033</v>
       </c>
-      <c r="E148" s="1" t="n">
+      <c r="F148" s="1" t="n">
         <v>0.0329</v>
       </c>
     </row>
@@ -3259,10 +3706,13 @@
         <v>0.05322</v>
       </c>
       <c r="D149" s="1" t="n">
+        <v>0.05298</v>
+      </c>
+      <c r="E149" s="1" t="n">
         <v>0.05322</v>
       </c>
-      <c r="E149" s="1" t="n">
-        <v>0.05304</v>
+      <c r="F149" s="1" t="n">
+        <v>0.05298</v>
       </c>
     </row>
     <row r="150">
@@ -3278,9 +3728,12 @@
         <v>0.000443</v>
       </c>
       <c r="D150" s="1" t="n">
+        <v>0.0004407</v>
+      </c>
+      <c r="E150" s="1" t="n">
         <v>0.000443</v>
       </c>
-      <c r="E150" s="1" t="n">
+      <c r="F150" s="1" t="n">
         <v>0.0004396</v>
       </c>
     </row>
@@ -3297,9 +3750,12 @@
         <v>0.02183</v>
       </c>
       <c r="D151" s="1" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="E151" s="1" t="n">
         <v>0.02183</v>
       </c>
-      <c r="E151" s="1" t="n">
+      <c r="F151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -3319,6 +3775,9 @@
         <v>0.001783</v>
       </c>
       <c r="E152" s="1" t="n">
+        <v>0.001783</v>
+      </c>
+      <c r="F152" s="1" t="n">
         <v>0.001781</v>
       </c>
     </row>
@@ -3335,9 +3794,12 @@
         <v>6.2e-06</v>
       </c>
       <c r="D153" s="1" t="n">
+        <v>6.2e-06</v>
+      </c>
+      <c r="E153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
-      <c r="E153" s="1" t="n">
+      <c r="F153" s="1" t="n">
         <v>6.2e-06</v>
       </c>
     </row>
@@ -3357,6 +3819,9 @@
         <v>0.1598</v>
       </c>
       <c r="E154" s="1" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="F154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -3373,10 +3838,13 @@
         <v>0.03765</v>
       </c>
       <c r="D155" s="1" t="n">
+        <v>0.03755</v>
+      </c>
+      <c r="E155" s="1" t="n">
         <v>0.03765</v>
       </c>
-      <c r="E155" s="1" t="n">
-        <v>0.03757</v>
+      <c r="F155" s="1" t="n">
+        <v>0.03755</v>
       </c>
     </row>
     <row r="156">
@@ -3392,9 +3860,12 @@
         <v>0.005402</v>
       </c>
       <c r="D156" s="1" t="n">
+        <v>0.005401</v>
+      </c>
+      <c r="E156" s="1" t="n">
         <v>0.005402</v>
       </c>
-      <c r="E156" s="1" t="n">
+      <c r="F156" s="1" t="n">
         <v>0.005379</v>
       </c>
     </row>
@@ -3411,10 +3882,13 @@
         <v>0.02284</v>
       </c>
       <c r="D157" s="1" t="n">
+        <v>0.02277</v>
+      </c>
+      <c r="E157" s="1" t="n">
         <v>0.02284</v>
       </c>
-      <c r="E157" s="1" t="n">
-        <v>0.02282</v>
+      <c r="F157" s="1" t="n">
+        <v>0.02277</v>
       </c>
     </row>
     <row r="158">
@@ -3433,6 +3907,9 @@
         <v>1.09</v>
       </c>
       <c r="E158" s="1" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -3449,9 +3926,12 @@
         <v>2.558</v>
       </c>
       <c r="D159" s="1" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="E159" s="1" t="n">
         <v>2.558</v>
       </c>
-      <c r="E159" s="1" t="n">
+      <c r="F159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -3468,9 +3948,12 @@
         <v>4.852</v>
       </c>
       <c r="D160" s="1" t="n">
-        <v>4.852</v>
+        <v>4.858</v>
       </c>
       <c r="E160" s="1" t="n">
+        <v>4.858</v>
+      </c>
+      <c r="F160" s="1" t="n">
         <v>4.836</v>
       </c>
     </row>
@@ -3487,9 +3970,12 @@
         <v>0.1591</v>
       </c>
       <c r="D161" s="1" t="n">
-        <v>0.1591</v>
+        <v>0.1596</v>
       </c>
       <c r="E161" s="1" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="F161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -3506,9 +3992,12 @@
         <v>0.20584</v>
       </c>
       <c r="D162" s="1" t="n">
-        <v>0.20604</v>
+        <v>0.20754</v>
       </c>
       <c r="E162" s="1" t="n">
+        <v>0.20754</v>
+      </c>
+      <c r="F162" s="1" t="n">
         <v>0.20584</v>
       </c>
     </row>
@@ -3525,9 +4014,12 @@
         <v>0.03939</v>
       </c>
       <c r="D163" s="1" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="E163" s="1" t="n">
         <v>0.03939</v>
       </c>
-      <c r="E163" s="1" t="n">
+      <c r="F163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -3544,9 +4036,12 @@
         <v>0.0629</v>
       </c>
       <c r="D164" s="1" t="n">
-        <v>0.0629</v>
+        <v>0.06308999999999999</v>
       </c>
       <c r="E164" s="1" t="n">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="F164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -3563,9 +4058,12 @@
         <v>0.3525</v>
       </c>
       <c r="D165" s="1" t="n">
-        <v>0.3542</v>
+        <v>0.355</v>
       </c>
       <c r="E165" s="1" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="F165" s="1" t="n">
         <v>0.3525</v>
       </c>
     </row>
@@ -3582,9 +4080,12 @@
         <v>139.27</v>
       </c>
       <c r="D166" s="1" t="n">
+        <v>139.1</v>
+      </c>
+      <c r="E166" s="1" t="n">
         <v>139.27</v>
       </c>
-      <c r="E166" s="1" t="n">
+      <c r="F166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -3601,10 +4102,13 @@
         <v>0.0006471</v>
       </c>
       <c r="D167" s="1" t="n">
+        <v>0.0006431</v>
+      </c>
+      <c r="E167" s="1" t="n">
         <v>0.0006477</v>
       </c>
-      <c r="E167" s="1" t="n">
-        <v>0.0006471</v>
+      <c r="F167" s="1" t="n">
+        <v>0.0006431</v>
       </c>
     </row>
     <row r="168">
@@ -3620,9 +4124,12 @@
         <v>0.01673</v>
       </c>
       <c r="D168" s="1" t="n">
-        <v>0.01673</v>
+        <v>0.01678</v>
       </c>
       <c r="E168" s="1" t="n">
+        <v>0.01678</v>
+      </c>
+      <c r="F168" s="1" t="n">
         <v>0.01664</v>
       </c>
     </row>
@@ -3639,9 +4146,12 @@
         <v>0.04798</v>
       </c>
       <c r="D169" s="1" t="n">
+        <v>0.04793</v>
+      </c>
+      <c r="E169" s="1" t="n">
         <v>0.04798</v>
       </c>
-      <c r="E169" s="1" t="n">
+      <c r="F169" s="1" t="n">
         <v>0.04788</v>
       </c>
     </row>
@@ -3658,9 +4168,12 @@
         <v>4.267</v>
       </c>
       <c r="D170" s="1" t="n">
-        <v>4.267</v>
+        <v>4.279</v>
       </c>
       <c r="E170" s="1" t="n">
+        <v>4.279</v>
+      </c>
+      <c r="F170" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -3677,9 +4190,12 @@
         <v>0.03859</v>
       </c>
       <c r="D171" s="1" t="n">
-        <v>0.03859</v>
+        <v>0.03874</v>
       </c>
       <c r="E171" s="1" t="n">
+        <v>0.03874</v>
+      </c>
+      <c r="F171" s="1" t="n">
         <v>0.03846</v>
       </c>
     </row>
@@ -3696,9 +4212,12 @@
         <v>0.0427</v>
       </c>
       <c r="D172" s="1" t="n">
-        <v>0.0427</v>
+        <v>0.0431</v>
       </c>
       <c r="E172" s="1" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="F172" s="1" t="n">
         <v>0.0427</v>
       </c>
     </row>
@@ -3715,9 +4234,12 @@
         <v>0.023878</v>
       </c>
       <c r="D173" s="1" t="n">
-        <v>0.023878</v>
+        <v>0.024201</v>
       </c>
       <c r="E173" s="1" t="n">
+        <v>0.024201</v>
+      </c>
+      <c r="F173" s="1" t="n">
         <v>0.02382</v>
       </c>
     </row>
@@ -3734,9 +4256,12 @@
         <v>1.0704</v>
       </c>
       <c r="D174" s="1" t="n">
-        <v>1.0705</v>
+        <v>1.0708</v>
       </c>
       <c r="E174" s="1" t="n">
+        <v>1.0708</v>
+      </c>
+      <c r="F174" s="1" t="n">
         <v>1.0704</v>
       </c>
     </row>
@@ -3753,10 +4278,13 @@
         <v>0.028967</v>
       </c>
       <c r="D175" s="1" t="n">
+        <v>0.028647</v>
+      </c>
+      <c r="E175" s="1" t="n">
         <v>0.028967</v>
       </c>
-      <c r="E175" s="1" t="n">
-        <v>0.028947</v>
+      <c r="F175" s="1" t="n">
+        <v>0.028647</v>
       </c>
     </row>
     <row r="176">
@@ -3772,9 +4300,12 @@
         <v>0.02178</v>
       </c>
       <c r="D176" s="1" t="n">
-        <v>0.02178</v>
+        <v>0.0218</v>
       </c>
       <c r="E176" s="1" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="F176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -3794,6 +4325,9 @@
         <v>0.5444</v>
       </c>
       <c r="E177" s="1" t="n">
+        <v>0.5444</v>
+      </c>
+      <c r="F177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -3810,9 +4344,12 @@
         <v>0.08255999999999999</v>
       </c>
       <c r="D178" s="1" t="n">
+        <v>0.08261</v>
+      </c>
+      <c r="E178" s="1" t="n">
         <v>0.08268</v>
       </c>
-      <c r="E178" s="1" t="n">
+      <c r="F178" s="1" t="n">
         <v>0.08255999999999999</v>
       </c>
     </row>
@@ -3829,9 +4366,12 @@
         <v>0.0213</v>
       </c>
       <c r="D179" s="1" t="n">
-        <v>0.0213</v>
+        <v>0.02133</v>
       </c>
       <c r="E179" s="1" t="n">
+        <v>0.02133</v>
+      </c>
+      <c r="F179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -3848,9 +4388,12 @@
         <v>0.27033</v>
       </c>
       <c r="D180" s="1" t="n">
-        <v>0.27033</v>
+        <v>0.27127</v>
       </c>
       <c r="E180" s="1" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="F180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -3867,9 +4410,12 @@
         <v>0.0042</v>
       </c>
       <c r="D181" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="E181" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="E181" s="1" t="n">
+      <c r="F181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -3886,9 +4432,12 @@
         <v>0.07931000000000001</v>
       </c>
       <c r="D182" s="1" t="n">
-        <v>0.07978</v>
+        <v>0.07981000000000001</v>
       </c>
       <c r="E182" s="1" t="n">
+        <v>0.07981000000000001</v>
+      </c>
+      <c r="F182" s="1" t="n">
         <v>0.07931000000000001</v>
       </c>
     </row>
@@ -3905,9 +4454,12 @@
         <v>0.02357</v>
       </c>
       <c r="D183" s="1" t="n">
+        <v>0.02346</v>
+      </c>
+      <c r="E183" s="1" t="n">
         <v>0.02357</v>
       </c>
-      <c r="E183" s="1" t="n">
+      <c r="F183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -3924,9 +4476,12 @@
         <v>6.981e-05</v>
       </c>
       <c r="D184" s="1" t="n">
+        <v>6.963e-05</v>
+      </c>
+      <c r="E184" s="1" t="n">
         <v>6.981e-05</v>
       </c>
-      <c r="E184" s="1" t="n">
+      <c r="F184" s="1" t="n">
         <v>6.957e-05</v>
       </c>
     </row>
@@ -3943,9 +4498,12 @@
         <v>0.02124</v>
       </c>
       <c r="D185" s="1" t="n">
-        <v>0.02124</v>
+        <v>0.02127</v>
       </c>
       <c r="E185" s="1" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="F185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -3962,10 +4520,13 @@
         <v>0.01632</v>
       </c>
       <c r="D186" s="1" t="n">
+        <v>0.01626</v>
+      </c>
+      <c r="E186" s="1" t="n">
         <v>0.01632</v>
       </c>
-      <c r="E186" s="1" t="n">
-        <v>0.01629</v>
+      <c r="F186" s="1" t="n">
+        <v>0.01626</v>
       </c>
     </row>
     <row r="187">
@@ -3981,9 +4542,12 @@
         <v>0.974</v>
       </c>
       <c r="D187" s="1" t="n">
-        <v>0.974</v>
+        <v>0.976</v>
       </c>
       <c r="E187" s="1" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="F187" s="1" t="n">
         <v>0.971</v>
       </c>
     </row>
@@ -4000,9 +4564,12 @@
         <v>0.0239</v>
       </c>
       <c r="D188" s="1" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="E188" s="1" t="n">
         <v>0.0239</v>
       </c>
-      <c r="E188" s="1" t="n">
+      <c r="F188" s="1" t="n">
         <v>0.0237</v>
       </c>
     </row>
@@ -4019,9 +4586,12 @@
         <v>1.8658</v>
       </c>
       <c r="D189" s="1" t="n">
+        <v>1.863</v>
+      </c>
+      <c r="E189" s="1" t="n">
         <v>1.8658</v>
       </c>
-      <c r="E189" s="1" t="n">
+      <c r="F189" s="1" t="n">
         <v>1.8627</v>
       </c>
     </row>
@@ -4038,9 +4608,12 @@
         <v>1.838</v>
       </c>
       <c r="D190" s="1" t="n">
+        <v>1.836</v>
+      </c>
+      <c r="E190" s="1" t="n">
         <v>1.838</v>
       </c>
-      <c r="E190" s="1" t="n">
+      <c r="F190" s="1" t="n">
         <v>1.835</v>
       </c>
     </row>
@@ -4057,9 +4630,12 @@
         <v>0.02671</v>
       </c>
       <c r="D191" s="1" t="n">
-        <v>0.02671</v>
+        <v>0.02677</v>
       </c>
       <c r="E191" s="1" t="n">
+        <v>0.02677</v>
+      </c>
+      <c r="F191" s="1" t="n">
         <v>0.02669</v>
       </c>
     </row>
@@ -4076,9 +4652,12 @@
         <v>0.0973</v>
       </c>
       <c r="D192" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="E192" s="1" t="n">
         <v>0.0973</v>
       </c>
-      <c r="E192" s="1" t="n">
+      <c r="F192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -4095,9 +4674,12 @@
         <v>0.1675</v>
       </c>
       <c r="D193" s="1" t="n">
-        <v>0.1675</v>
+        <v>0.1682</v>
       </c>
       <c r="E193" s="1" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="F193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -4114,9 +4696,12 @@
         <v>16.294</v>
       </c>
       <c r="D194" s="1" t="n">
+        <v>16.261</v>
+      </c>
+      <c r="E194" s="1" t="n">
         <v>16.294</v>
       </c>
-      <c r="E194" s="1" t="n">
+      <c r="F194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -4133,9 +4718,12 @@
         <v>4.093</v>
       </c>
       <c r="D195" s="1" t="n">
+        <v>4.094</v>
+      </c>
+      <c r="E195" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="E195" s="1" t="n">
+      <c r="F195" s="1" t="n">
         <v>4.093</v>
       </c>
     </row>
@@ -4152,10 +4740,13 @@
         <v>1.2794</v>
       </c>
       <c r="D196" s="1" t="n">
+        <v>1.2683</v>
+      </c>
+      <c r="E196" s="1" t="n">
         <v>1.2794</v>
       </c>
-      <c r="E196" s="1" t="n">
-        <v>1.2705</v>
+      <c r="F196" s="1" t="n">
+        <v>1.2683</v>
       </c>
     </row>
     <row r="197">
@@ -4171,10 +4762,13 @@
         <v>3.077</v>
       </c>
       <c r="D197" s="1" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E197" s="1" t="n">
         <v>3.092</v>
       </c>
-      <c r="E197" s="1" t="n">
-        <v>3.077</v>
+      <c r="F197" s="1" t="n">
+        <v>3.07</v>
       </c>
     </row>
     <row r="198">
@@ -4193,6 +4787,9 @@
         <v>0.01265</v>
       </c>
       <c r="E198" s="1" t="n">
+        <v>0.01265</v>
+      </c>
+      <c r="F198" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -4209,9 +4806,12 @@
         <v>0.0001762</v>
       </c>
       <c r="D199" s="1" t="n">
+        <v>0.000176</v>
+      </c>
+      <c r="E199" s="1" t="n">
         <v>0.0001762</v>
       </c>
-      <c r="E199" s="1" t="n">
+      <c r="F199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -4228,9 +4828,12 @@
         <v>115.62</v>
       </c>
       <c r="D200" s="1" t="n">
+        <v>115.55</v>
+      </c>
+      <c r="E200" s="1" t="n">
         <v>115.62</v>
       </c>
-      <c r="E200" s="1" t="n">
+      <c r="F200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -4247,9 +4850,12 @@
         <v>0.01027</v>
       </c>
       <c r="D201" s="1" t="n">
-        <v>0.01027</v>
+        <v>0.01028</v>
       </c>
       <c r="E201" s="1" t="n">
+        <v>0.01028</v>
+      </c>
+      <c r="F201" s="1" t="n">
         <v>0.01023</v>
       </c>
     </row>
@@ -4266,9 +4872,12 @@
         <v>0.01073</v>
       </c>
       <c r="D202" s="1" t="n">
+        <v>0.01072</v>
+      </c>
+      <c r="E202" s="1" t="n">
         <v>0.01073</v>
       </c>
-      <c r="E202" s="1" t="n">
+      <c r="F202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -4285,9 +4894,12 @@
         <v>0.003153</v>
       </c>
       <c r="D203" s="1" t="n">
+        <v>0.003149</v>
+      </c>
+      <c r="E203" s="1" t="n">
         <v>0.003153</v>
       </c>
-      <c r="E203" s="1" t="n">
+      <c r="F203" s="1" t="n">
         <v>0.003137</v>
       </c>
     </row>
@@ -4304,9 +4916,12 @@
         <v>28.38</v>
       </c>
       <c r="D204" s="1" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="E204" s="1" t="n">
         <v>28.38</v>
       </c>
-      <c r="E204" s="1" t="n">
+      <c r="F204" s="1" t="n">
         <v>28.32</v>
       </c>
     </row>
@@ -4323,10 +4938,13 @@
         <v>0.5627</v>
       </c>
       <c r="D205" s="1" t="n">
+        <v>0.5608</v>
+      </c>
+      <c r="E205" s="1" t="n">
         <v>0.5636</v>
       </c>
-      <c r="E205" s="1" t="n">
-        <v>0.5627</v>
+      <c r="F205" s="1" t="n">
+        <v>0.5608</v>
       </c>
     </row>
     <row r="206">
@@ -4342,10 +4960,13 @@
         <v>0.0004403</v>
       </c>
       <c r="D206" s="1" t="n">
+        <v>0.0004387</v>
+      </c>
+      <c r="E206" s="1" t="n">
         <v>0.0004403</v>
       </c>
-      <c r="E206" s="1" t="n">
-        <v>0.0004394</v>
+      <c r="F206" s="1" t="n">
+        <v>0.0004387</v>
       </c>
     </row>
     <row r="207">
@@ -4361,9 +4982,12 @@
         <v>0.04667</v>
       </c>
       <c r="D207" s="1" t="n">
+        <v>0.04656</v>
+      </c>
+      <c r="E207" s="1" t="n">
         <v>0.04667</v>
       </c>
-      <c r="E207" s="1" t="n">
+      <c r="F207" s="1" t="n">
         <v>0.04651</v>
       </c>
     </row>
@@ -4385,6 +5009,9 @@
       <c r="E208" s="1" t="n">
         <v>0.09</v>
       </c>
+      <c r="F208" s="1" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4399,9 +5026,12 @@
         <v>0.02567</v>
       </c>
       <c r="D209" s="1" t="n">
-        <v>0.02567</v>
+        <v>0.02572</v>
       </c>
       <c r="E209" s="1" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="F209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -4418,9 +5048,12 @@
         <v>0.012655</v>
       </c>
       <c r="D210" s="1" t="n">
-        <v>0.012655</v>
+        <v>0.012745</v>
       </c>
       <c r="E210" s="1" t="n">
+        <v>0.012745</v>
+      </c>
+      <c r="F210" s="1" t="n">
         <v>0.012652</v>
       </c>
     </row>
@@ -4437,9 +5070,12 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="D211" s="1" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="E211" s="1" t="n">
         <v>0.09180000000000001</v>
       </c>
-      <c r="E211" s="1" t="n">
+      <c r="F211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -4456,9 +5092,12 @@
         <v>0.007065</v>
       </c>
       <c r="D212" s="1" t="n">
-        <v>0.007065</v>
+        <v>0.007076</v>
       </c>
       <c r="E212" s="1" t="n">
+        <v>0.007076</v>
+      </c>
+      <c r="F212" s="1" t="n">
         <v>0.007053</v>
       </c>
     </row>
@@ -4475,10 +5114,13 @@
         <v>0.02966</v>
       </c>
       <c r="D213" s="1" t="n">
+        <v>0.02954</v>
+      </c>
+      <c r="E213" s="1" t="n">
         <v>0.02966</v>
       </c>
-      <c r="E213" s="1" t="n">
-        <v>0.02958</v>
+      <c r="F213" s="1" t="n">
+        <v>0.02954</v>
       </c>
     </row>
     <row r="214">
@@ -4494,11 +5136,14 @@
         <v>0.2708</v>
       </c>
       <c r="D214" s="1" t="n">
-        <v>0.2708</v>
+        <v>0.2701</v>
       </c>
       <c r="E214" s="1" t="n">
         <v>0.2708</v>
       </c>
+      <c r="F214" s="1" t="n">
+        <v>0.2701</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4513,10 +5158,13 @@
         <v>0.02171</v>
       </c>
       <c r="D215" s="1" t="n">
+        <v>0.02158</v>
+      </c>
+      <c r="E215" s="1" t="n">
         <v>0.02171</v>
       </c>
-      <c r="E215" s="1" t="n">
-        <v>0.0217</v>
+      <c r="F215" s="1" t="n">
+        <v>0.02158</v>
       </c>
     </row>
     <row r="216">
@@ -4532,9 +5180,12 @@
         <v>0.01492</v>
       </c>
       <c r="D216" s="1" t="n">
+        <v>0.01485</v>
+      </c>
+      <c r="E216" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="E216" s="1" t="n">
+      <c r="F216" s="1" t="n">
         <v>0.01475</v>
       </c>
     </row>
@@ -4551,9 +5202,12 @@
         <v>0.2538</v>
       </c>
       <c r="D217" s="1" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="E217" s="1" t="n">
         <v>0.2538</v>
       </c>
-      <c r="E217" s="1" t="n">
+      <c r="F217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -4570,9 +5224,12 @@
         <v>0.3087</v>
       </c>
       <c r="D218" s="1" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="E218" s="1" t="n">
         <v>0.3087</v>
       </c>
-      <c r="E218" s="1" t="n">
+      <c r="F218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -4589,9 +5246,12 @@
         <v>0.1784</v>
       </c>
       <c r="D219" s="1" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="E219" s="1" t="n">
         <v>0.1784</v>
       </c>
-      <c r="E219" s="1" t="n">
+      <c r="F219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -4608,9 +5268,12 @@
         <v>15</v>
       </c>
       <c r="D220" s="1" t="n">
-        <v>15</v>
+        <v>15.02</v>
       </c>
       <c r="E220" s="1" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="F220" s="1" t="n">
         <v>14.97</v>
       </c>
     </row>
@@ -4630,6 +5293,9 @@
         <v>0.01594</v>
       </c>
       <c r="E221" s="1" t="n">
+        <v>0.01594</v>
+      </c>
+      <c r="F221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -4646,9 +5312,12 @@
         <v>66.70999999999999</v>
       </c>
       <c r="D222" s="1" t="n">
+        <v>66.47</v>
+      </c>
+      <c r="E222" s="1" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="E222" s="1" t="n">
+      <c r="F222" s="1" t="n">
         <v>66.17</v>
       </c>
     </row>
@@ -4665,9 +5334,12 @@
         <v>0.09272</v>
       </c>
       <c r="D223" s="1" t="n">
-        <v>0.09272</v>
+        <v>0.09279</v>
       </c>
       <c r="E223" s="1" t="n">
+        <v>0.09279</v>
+      </c>
+      <c r="F223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -4684,9 +5356,12 @@
         <v>0.0393</v>
       </c>
       <c r="D224" s="1" t="n">
+        <v>0.03926</v>
+      </c>
+      <c r="E224" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="E224" s="1" t="n">
+      <c r="F224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -4703,9 +5378,12 @@
         <v>0.5725</v>
       </c>
       <c r="D225" s="1" t="n">
+        <v>0.5723</v>
+      </c>
+      <c r="E225" s="1" t="n">
         <v>0.5725</v>
       </c>
-      <c r="E225" s="1" t="n">
+      <c r="F225" s="1" t="n">
         <v>0.5695</v>
       </c>
     </row>
@@ -4722,11 +5400,14 @@
         <v>0.1167</v>
       </c>
       <c r="D226" s="1" t="n">
-        <v>0.1167</v>
+        <v>0.1166</v>
       </c>
       <c r="E226" s="1" t="n">
         <v>0.1167</v>
       </c>
+      <c r="F226" s="1" t="n">
+        <v>0.1166</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4741,10 +5422,13 @@
         <v>0.3201</v>
       </c>
       <c r="D227" s="1" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="E227" s="1" t="n">
         <v>0.3201</v>
       </c>
-      <c r="E227" s="1" t="n">
-        <v>0.3189</v>
+      <c r="F227" s="1" t="n">
+        <v>0.3187</v>
       </c>
     </row>
     <row r="228">
@@ -4760,9 +5444,12 @@
         <v>6.09</v>
       </c>
       <c r="D228" s="1" t="n">
+        <v>6.067</v>
+      </c>
+      <c r="E228" s="1" t="n">
         <v>6.09</v>
       </c>
-      <c r="E228" s="1" t="n">
+      <c r="F228" s="1" t="n">
         <v>6.066</v>
       </c>
     </row>
@@ -4782,6 +5469,9 @@
         <v>0.0289</v>
       </c>
       <c r="E229" s="1" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="F229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -4798,9 +5488,12 @@
         <v>0.3294</v>
       </c>
       <c r="D230" s="1" t="n">
-        <v>0.3297</v>
+        <v>0.3307</v>
       </c>
       <c r="E230" s="1" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="F230" s="1" t="n">
         <v>0.3294</v>
       </c>
     </row>
@@ -4817,9 +5510,12 @@
         <v>0.12041</v>
       </c>
       <c r="D231" s="1" t="n">
-        <v>0.12041</v>
+        <v>0.12076</v>
       </c>
       <c r="E231" s="1" t="n">
+        <v>0.12076</v>
+      </c>
+      <c r="F231" s="1" t="n">
         <v>0.12024</v>
       </c>
     </row>
@@ -4836,9 +5532,12 @@
         <v>0.1185</v>
       </c>
       <c r="D232" s="1" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="E232" s="1" t="n">
         <v>0.1186</v>
       </c>
-      <c r="E232" s="1" t="n">
+      <c r="F232" s="1" t="n">
         <v>0.1185</v>
       </c>
     </row>
@@ -4855,10 +5554,13 @@
         <v>0.03019</v>
       </c>
       <c r="D233" s="1" t="n">
+        <v>0.03013</v>
+      </c>
+      <c r="E233" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="E233" s="1" t="n">
-        <v>0.03018</v>
+      <c r="F233" s="1" t="n">
+        <v>0.03013</v>
       </c>
     </row>
     <row r="234">
@@ -4874,9 +5576,12 @@
         <v>0.015644</v>
       </c>
       <c r="D234" s="1" t="n">
-        <v>0.015715</v>
+        <v>0.01574</v>
       </c>
       <c r="E234" s="1" t="n">
+        <v>0.01574</v>
+      </c>
+      <c r="F234" s="1" t="n">
         <v>0.015644</v>
       </c>
     </row>
@@ -4893,9 +5598,12 @@
         <v>0.01279</v>
       </c>
       <c r="D235" s="1" t="n">
+        <v>0.01277</v>
+      </c>
+      <c r="E235" s="1" t="n">
         <v>0.01279</v>
       </c>
-      <c r="E235" s="1" t="n">
+      <c r="F235" s="1" t="n">
         <v>0.01275</v>
       </c>
     </row>
@@ -4912,9 +5620,12 @@
         <v>0.01929</v>
       </c>
       <c r="D236" s="1" t="n">
+        <v>0.01926</v>
+      </c>
+      <c r="E236" s="1" t="n">
         <v>0.01929</v>
       </c>
-      <c r="E236" s="1" t="n">
+      <c r="F236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -4931,10 +5642,13 @@
         <v>0.08469</v>
       </c>
       <c r="D237" s="1" t="n">
+        <v>0.08452</v>
+      </c>
+      <c r="E237" s="1" t="n">
         <v>0.08509</v>
       </c>
-      <c r="E237" s="1" t="n">
-        <v>0.08469</v>
+      <c r="F237" s="1" t="n">
+        <v>0.08452</v>
       </c>
     </row>
     <row r="238">
@@ -4950,10 +5664,13 @@
         <v>0.05892</v>
       </c>
       <c r="D238" s="1" t="n">
+        <v>0.05875</v>
+      </c>
+      <c r="E238" s="1" t="n">
         <v>0.05892</v>
       </c>
-      <c r="E238" s="1" t="n">
-        <v>0.05884</v>
+      <c r="F238" s="1" t="n">
+        <v>0.05875</v>
       </c>
     </row>
     <row r="239">
@@ -4969,9 +5686,12 @@
         <v>0.009027</v>
       </c>
       <c r="D239" s="1" t="n">
-        <v>0.009063</v>
+        <v>0.009067</v>
       </c>
       <c r="E239" s="1" t="n">
+        <v>0.009067</v>
+      </c>
+      <c r="F239" s="1" t="n">
         <v>0.009027</v>
       </c>
     </row>
@@ -4988,10 +5708,13 @@
         <v>0.004162</v>
       </c>
       <c r="D240" s="1" t="n">
+        <v>0.004154</v>
+      </c>
+      <c r="E240" s="1" t="n">
         <v>0.004162</v>
       </c>
-      <c r="E240" s="1" t="n">
-        <v>0.004157</v>
+      <c r="F240" s="1" t="n">
+        <v>0.004154</v>
       </c>
     </row>
     <row r="241">
@@ -5007,9 +5730,12 @@
         <v>0.2404</v>
       </c>
       <c r="D241" s="1" t="n">
-        <v>0.2404</v>
+        <v>0.241</v>
       </c>
       <c r="E241" s="1" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="F241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -5026,9 +5752,12 @@
         <v>0.0582</v>
       </c>
       <c r="D242" s="1" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="E242" s="1" t="n">
         <v>0.0582</v>
       </c>
-      <c r="E242" s="1" t="n">
+      <c r="F242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -5045,9 +5774,12 @@
         <v>0.0234</v>
       </c>
       <c r="D243" s="1" t="n">
-        <v>0.0234</v>
+        <v>0.02346</v>
       </c>
       <c r="E243" s="1" t="n">
+        <v>0.02346</v>
+      </c>
+      <c r="F243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -5064,10 +5796,13 @@
         <v>0.05572</v>
       </c>
       <c r="D244" s="1" t="n">
+        <v>0.05547</v>
+      </c>
+      <c r="E244" s="1" t="n">
         <v>0.05623</v>
       </c>
-      <c r="E244" s="1" t="n">
-        <v>0.05572</v>
+      <c r="F244" s="1" t="n">
+        <v>0.05547</v>
       </c>
     </row>
     <row r="245">
@@ -5083,9 +5818,12 @@
         <v>0.03433</v>
       </c>
       <c r="D245" s="1" t="n">
+        <v>0.03425</v>
+      </c>
+      <c r="E245" s="1" t="n">
         <v>0.03433</v>
       </c>
-      <c r="E245" s="1" t="n">
+      <c r="F245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -5102,9 +5840,12 @@
         <v>0.06011</v>
       </c>
       <c r="D246" s="1" t="n">
-        <v>0.06011</v>
+        <v>0.06013</v>
       </c>
       <c r="E246" s="1" t="n">
+        <v>0.06013</v>
+      </c>
+      <c r="F246" s="1" t="n">
         <v>0.06004</v>
       </c>
     </row>
@@ -5124,6 +5865,9 @@
         <v>0.385</v>
       </c>
       <c r="E247" s="1" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F247" s="1" t="n">
         <v>0.384</v>
       </c>
     </row>
@@ -5140,9 +5884,12 @@
         <v>0.519</v>
       </c>
       <c r="D248" s="1" t="n">
+        <v>0.5175</v>
+      </c>
+      <c r="E248" s="1" t="n">
         <v>0.519</v>
       </c>
-      <c r="E248" s="1" t="n">
+      <c r="F248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -5159,9 +5906,12 @@
         <v>0.02797</v>
       </c>
       <c r="D249" s="1" t="n">
-        <v>0.02797</v>
+        <v>0.02804</v>
       </c>
       <c r="E249" s="1" t="n">
+        <v>0.02804</v>
+      </c>
+      <c r="F249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -5178,9 +5928,12 @@
         <v>0.01288</v>
       </c>
       <c r="D250" s="1" t="n">
+        <v>0.01294</v>
+      </c>
+      <c r="E250" s="1" t="n">
         <v>0.01295</v>
       </c>
-      <c r="E250" s="1" t="n">
+      <c r="F250" s="1" t="n">
         <v>0.01288</v>
       </c>
     </row>
@@ -5197,9 +5950,12 @@
         <v>0.1003</v>
       </c>
       <c r="D251" s="1" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="E251" s="1" t="n">
         <v>0.1003</v>
       </c>
-      <c r="E251" s="1" t="n">
+      <c r="F251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5216,9 +5972,12 @@
         <v>0.00719</v>
       </c>
       <c r="D252" s="1" t="n">
+        <v>0.00718</v>
+      </c>
+      <c r="E252" s="1" t="n">
         <v>0.00719</v>
       </c>
-      <c r="E252" s="1" t="n">
+      <c r="F252" s="1" t="n">
         <v>0.00716</v>
       </c>
     </row>
@@ -5235,9 +5994,12 @@
         <v>0.005554</v>
       </c>
       <c r="D253" s="1" t="n">
+        <v>0.005558</v>
+      </c>
+      <c r="E253" s="1" t="n">
         <v>0.005561</v>
       </c>
-      <c r="E253" s="1" t="n">
+      <c r="F253" s="1" t="n">
         <v>0.005554</v>
       </c>
     </row>
@@ -5254,9 +6016,12 @@
         <v>0.0646</v>
       </c>
       <c r="D254" s="1" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="E254" s="1" t="n">
         <v>0.0646</v>
       </c>
-      <c r="E254" s="1" t="n">
+      <c r="F254" s="1" t="n">
         <v>0.06419999999999999</v>
       </c>
     </row>
@@ -5273,9 +6038,12 @@
         <v>0.01434</v>
       </c>
       <c r="D255" s="1" t="n">
+        <v>0.01432</v>
+      </c>
+      <c r="E255" s="1" t="n">
         <v>0.01434</v>
       </c>
-      <c r="E255" s="1" t="n">
+      <c r="F255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -5292,10 +6060,13 @@
         <v>0.999297</v>
       </c>
       <c r="D256" s="1" t="n">
+        <v>0.999285</v>
+      </c>
+      <c r="E256" s="1" t="n">
         <v>0.999297</v>
       </c>
-      <c r="E256" s="1" t="n">
-        <v>0.999296</v>
+      <c r="F256" s="1" t="n">
+        <v>0.999285</v>
       </c>
     </row>
     <row r="257">
@@ -5311,9 +6082,12 @@
         <v>0.02101</v>
       </c>
       <c r="D257" s="1" t="n">
+        <v>0.02096</v>
+      </c>
+      <c r="E257" s="1" t="n">
         <v>0.02101</v>
       </c>
-      <c r="E257" s="1" t="n">
+      <c r="F257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -5333,6 +6107,9 @@
         <v>0.01142</v>
       </c>
       <c r="E258" s="1" t="n">
+        <v>0.01142</v>
+      </c>
+      <c r="F258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -5349,9 +6126,12 @@
         <v>0.5119</v>
       </c>
       <c r="D259" s="1" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="E259" s="1" t="n">
         <v>0.5119</v>
       </c>
-      <c r="E259" s="1" t="n">
+      <c r="F259" s="1" t="n">
         <v>0.5085</v>
       </c>
     </row>
@@ -5368,9 +6148,12 @@
         <v>0.08459</v>
       </c>
       <c r="D260" s="1" t="n">
-        <v>0.08459</v>
+        <v>0.08495999999999999</v>
       </c>
       <c r="E260" s="1" t="n">
+        <v>0.08495999999999999</v>
+      </c>
+      <c r="F260" s="1" t="n">
         <v>0.08436</v>
       </c>
     </row>
@@ -5387,10 +6170,13 @@
         <v>0.04138</v>
       </c>
       <c r="D261" s="1" t="n">
+        <v>0.04127</v>
+      </c>
+      <c r="E261" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="E261" s="1" t="n">
-        <v>0.0413</v>
+      <c r="F261" s="1" t="n">
+        <v>0.04127</v>
       </c>
     </row>
     <row r="262">
@@ -5406,11 +6192,14 @@
         <v>2.288</v>
       </c>
       <c r="D262" s="1" t="n">
-        <v>2.288</v>
+        <v>2.283</v>
       </c>
       <c r="E262" s="1" t="n">
         <v>2.288</v>
       </c>
+      <c r="F262" s="1" t="n">
+        <v>2.283</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5425,9 +6214,12 @@
         <v>18.5</v>
       </c>
       <c r="D263" s="1" t="n">
-        <v>18.5</v>
+        <v>18.51</v>
       </c>
       <c r="E263" s="1" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="F263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -5444,9 +6236,12 @@
         <v>0.008404</v>
       </c>
       <c r="D264" s="1" t="n">
-        <v>0.008404</v>
+        <v>0.008498</v>
       </c>
       <c r="E264" s="1" t="n">
+        <v>0.008498</v>
+      </c>
+      <c r="F264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -5466,6 +6261,9 @@
         <v>0.363</v>
       </c>
       <c r="E265" s="1" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="F265" s="1" t="n">
         <v>0.3628</v>
       </c>
     </row>
@@ -5482,10 +6280,13 @@
         <v>0.054291</v>
       </c>
       <c r="D266" s="1" t="n">
+        <v>0.053765</v>
+      </c>
+      <c r="E266" s="1" t="n">
         <v>0.054291</v>
       </c>
-      <c r="E266" s="1" t="n">
-        <v>0.053924</v>
+      <c r="F266" s="1" t="n">
+        <v>0.053765</v>
       </c>
     </row>
     <row r="267">
@@ -5501,9 +6302,12 @@
         <v>0.1321</v>
       </c>
       <c r="D267" s="1" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="E267" s="1" t="n">
         <v>0.1321</v>
       </c>
-      <c r="E267" s="1" t="n">
+      <c r="F267" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -5520,9 +6324,12 @@
         <v>0.007845</v>
       </c>
       <c r="D268" s="1" t="n">
+        <v>0.007830999999999999</v>
+      </c>
+      <c r="E268" s="1" t="n">
         <v>0.007845</v>
       </c>
-      <c r="E268" s="1" t="n">
+      <c r="F268" s="1" t="n">
         <v>0.007759</v>
       </c>
     </row>
@@ -5539,9 +6346,12 @@
         <v>0.001235</v>
       </c>
       <c r="D269" s="1" t="n">
+        <v>0.001236</v>
+      </c>
+      <c r="E269" s="1" t="n">
         <v>0.00124</v>
       </c>
-      <c r="E269" s="1" t="n">
+      <c r="F269" s="1" t="n">
         <v>0.001235</v>
       </c>
     </row>
@@ -5558,10 +6368,13 @@
         <v>0.28989</v>
       </c>
       <c r="D270" s="1" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="E270" s="1" t="n">
         <v>0.28997</v>
       </c>
-      <c r="E270" s="1" t="n">
-        <v>0.28989</v>
+      <c r="F270" s="1" t="n">
+        <v>0.28865</v>
       </c>
     </row>
     <row r="271">
@@ -5577,9 +6390,12 @@
         <v>0.03899</v>
       </c>
       <c r="D271" s="1" t="n">
-        <v>0.03899</v>
+        <v>0.03906</v>
       </c>
       <c r="E271" s="1" t="n">
+        <v>0.03906</v>
+      </c>
+      <c r="F271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -5596,9 +6412,12 @@
         <v>0.05133</v>
       </c>
       <c r="D272" s="1" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="E272" s="1" t="n">
         <v>0.05133</v>
       </c>
-      <c r="E272" s="1" t="n">
+      <c r="F272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -5615,9 +6434,12 @@
         <v>0.0077</v>
       </c>
       <c r="D273" s="1" t="n">
-        <v>0.0077</v>
+        <v>0.00771</v>
       </c>
       <c r="E273" s="1" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="F273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -5634,9 +6456,12 @@
         <v>0.005745</v>
       </c>
       <c r="D274" s="1" t="n">
+        <v>0.005744</v>
+      </c>
+      <c r="E274" s="1" t="n">
         <v>0.005745</v>
       </c>
-      <c r="E274" s="1" t="n">
+      <c r="F274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -5653,10 +6478,13 @@
         <v>0.0005895</v>
       </c>
       <c r="D275" s="1" t="n">
+        <v>0.0005865999999999999</v>
+      </c>
+      <c r="E275" s="1" t="n">
         <v>0.0005895</v>
       </c>
-      <c r="E275" s="1" t="n">
-        <v>0.0005868</v>
+      <c r="F275" s="1" t="n">
+        <v>0.0005865999999999999</v>
       </c>
     </row>
     <row r="276">
@@ -5672,10 +6500,13 @@
         <v>0.15089</v>
       </c>
       <c r="D276" s="1" t="n">
+        <v>0.15077</v>
+      </c>
+      <c r="E276" s="1" t="n">
         <v>0.15167</v>
       </c>
-      <c r="E276" s="1" t="n">
-        <v>0.15089</v>
+      <c r="F276" s="1" t="n">
+        <v>0.15077</v>
       </c>
     </row>
     <row r="277">
@@ -5691,9 +6522,12 @@
         <v>0.022677</v>
       </c>
       <c r="D277" s="1" t="n">
-        <v>0.022677</v>
+        <v>0.022785</v>
       </c>
       <c r="E277" s="1" t="n">
+        <v>0.022785</v>
+      </c>
+      <c r="F277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -5710,9 +6544,12 @@
         <v>0.04179</v>
       </c>
       <c r="D278" s="1" t="n">
+        <v>0.04197</v>
+      </c>
+      <c r="E278" s="1" t="n">
         <v>0.0421</v>
       </c>
-      <c r="E278" s="1" t="n">
+      <c r="F278" s="1" t="n">
         <v>0.04179</v>
       </c>
     </row>
@@ -5729,9 +6566,12 @@
         <v>0.0003982</v>
       </c>
       <c r="D279" s="1" t="n">
-        <v>0.0003982</v>
+        <v>0.0004006</v>
       </c>
       <c r="E279" s="1" t="n">
+        <v>0.0004006</v>
+      </c>
+      <c r="F279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -5748,9 +6588,12 @@
         <v>0.02216</v>
       </c>
       <c r="D280" s="1" t="n">
-        <v>0.02216</v>
+        <v>0.02218</v>
       </c>
       <c r="E280" s="1" t="n">
+        <v>0.02218</v>
+      </c>
+      <c r="F280" s="1" t="n">
         <v>0.02195</v>
       </c>
     </row>
@@ -5767,9 +6610,12 @@
         <v>0.06936</v>
       </c>
       <c r="D281" s="1" t="n">
+        <v>0.06936</v>
+      </c>
+      <c r="E281" s="1" t="n">
         <v>0.0694</v>
       </c>
-      <c r="E281" s="1" t="n">
+      <c r="F281" s="1" t="n">
         <v>0.06936</v>
       </c>
     </row>
@@ -5786,9 +6632,12 @@
         <v>0.006804</v>
       </c>
       <c r="D282" s="1" t="n">
+        <v>0.006794</v>
+      </c>
+      <c r="E282" s="1" t="n">
         <v>0.006804</v>
       </c>
-      <c r="E282" s="1" t="n">
+      <c r="F282" s="1" t="n">
         <v>0.006758</v>
       </c>
     </row>
@@ -5805,11 +6654,14 @@
         <v>0.12</v>
       </c>
       <c r="D283" s="1" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
       <c r="E283" s="1" t="n">
         <v>0.12</v>
       </c>
+      <c r="F283" s="1" t="n">
+        <v>0.119</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5824,9 +6676,12 @@
         <v>0.005475</v>
       </c>
       <c r="D284" s="1" t="n">
+        <v>0.005474</v>
+      </c>
+      <c r="E284" s="1" t="n">
         <v>0.005475</v>
       </c>
-      <c r="E284" s="1" t="n">
+      <c r="F284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -5846,6 +6701,9 @@
         <v>1.251</v>
       </c>
       <c r="E285" s="1" t="n">
+        <v>1.251</v>
+      </c>
+      <c r="F285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -5862,10 +6720,13 @@
         <v>0.4441</v>
       </c>
       <c r="D286" s="1" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="E286" s="1" t="n">
         <v>0.4441</v>
       </c>
-      <c r="E286" s="1" t="n">
-        <v>0.4437</v>
+      <c r="F286" s="1" t="n">
+        <v>0.4429</v>
       </c>
     </row>
     <row r="287">
@@ -5881,9 +6742,12 @@
         <v>0.007865</v>
       </c>
       <c r="D287" s="1" t="n">
-        <v>0.007865</v>
+        <v>0.007875999999999999</v>
       </c>
       <c r="E287" s="1" t="n">
+        <v>0.007875999999999999</v>
+      </c>
+      <c r="F287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -5900,11 +6764,14 @@
         <v>0.02922</v>
       </c>
       <c r="D288" s="1" t="n">
-        <v>0.02922</v>
+        <v>0.0292</v>
       </c>
       <c r="E288" s="1" t="n">
         <v>0.02922</v>
       </c>
+      <c r="F288" s="1" t="n">
+        <v>0.0292</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5919,9 +6786,12 @@
         <v>0.2811</v>
       </c>
       <c r="D289" s="1" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="E289" s="1" t="n">
         <v>0.2811</v>
       </c>
-      <c r="E289" s="1" t="n">
+      <c r="F289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -5938,11 +6808,14 @@
         <v>2.764</v>
       </c>
       <c r="D290" s="1" t="n">
-        <v>2.764</v>
+        <v>2.758</v>
       </c>
       <c r="E290" s="1" t="n">
         <v>2.764</v>
       </c>
+      <c r="F290" s="1" t="n">
+        <v>2.758</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5957,9 +6830,12 @@
         <v>0.003176</v>
       </c>
       <c r="D291" s="1" t="n">
+        <v>0.003165</v>
+      </c>
+      <c r="E291" s="1" t="n">
         <v>0.003176</v>
       </c>
-      <c r="E291" s="1" t="n">
+      <c r="F291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -5976,9 +6852,12 @@
         <v>0.4488</v>
       </c>
       <c r="D292" s="1" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="E292" s="1" t="n">
         <v>0.4488</v>
       </c>
-      <c r="E292" s="1" t="n">
+      <c r="F292" s="1" t="n">
         <v>0.4475</v>
       </c>
     </row>
@@ -5995,10 +6874,13 @@
         <v>0.08295</v>
       </c>
       <c r="D293" s="1" t="n">
+        <v>0.08217000000000001</v>
+      </c>
+      <c r="E293" s="1" t="n">
         <v>0.08298</v>
       </c>
-      <c r="E293" s="1" t="n">
-        <v>0.08295</v>
+      <c r="F293" s="1" t="n">
+        <v>0.08217000000000001</v>
       </c>
     </row>
     <row r="294">
@@ -6014,9 +6896,12 @@
         <v>0.02784</v>
       </c>
       <c r="D294" s="1" t="n">
+        <v>0.02781</v>
+      </c>
+      <c r="E294" s="1" t="n">
         <v>0.02784</v>
       </c>
-      <c r="E294" s="1" t="n">
+      <c r="F294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -6033,9 +6918,12 @@
         <v>0.958</v>
       </c>
       <c r="D295" s="1" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E295" s="1" t="n">
         <v>0.958</v>
       </c>
-      <c r="E295" s="1" t="n">
+      <c r="F295" s="1" t="n">
         <v>0.953</v>
       </c>
     </row>
@@ -6052,9 +6940,12 @@
         <v>0.006871</v>
       </c>
       <c r="D296" s="1" t="n">
+        <v>0.006857</v>
+      </c>
+      <c r="E296" s="1" t="n">
         <v>0.006871</v>
       </c>
-      <c r="E296" s="1" t="n">
+      <c r="F296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -6071,9 +6962,12 @@
         <v>0.1212</v>
       </c>
       <c r="D297" s="1" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="E297" s="1" t="n">
         <v>0.1212</v>
       </c>
-      <c r="E297" s="1" t="n">
+      <c r="F297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -6090,9 +6984,12 @@
         <v>0.01535</v>
       </c>
       <c r="D298" s="1" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="E298" s="1" t="n">
         <v>0.01535</v>
       </c>
-      <c r="E298" s="1" t="n">
+      <c r="F298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -6109,9 +7006,12 @@
         <v>0.4405</v>
       </c>
       <c r="D299" s="1" t="n">
+        <v>0.4396</v>
+      </c>
+      <c r="E299" s="1" t="n">
         <v>0.4405</v>
       </c>
-      <c r="E299" s="1" t="n">
+      <c r="F299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -6128,10 +7028,13 @@
         <v>0.00924</v>
       </c>
       <c r="D300" s="1" t="n">
+        <v>0.009220000000000001</v>
+      </c>
+      <c r="E300" s="1" t="n">
         <v>0.00924</v>
       </c>
-      <c r="E300" s="1" t="n">
-        <v>0.00923</v>
+      <c r="F300" s="1" t="n">
+        <v>0.009220000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -6150,6 +7053,9 @@
         <v>0.1849</v>
       </c>
       <c r="E301" s="1" t="n">
+        <v>0.1849</v>
+      </c>
+      <c r="F301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -6166,9 +7072,12 @@
         <v>0.00754</v>
       </c>
       <c r="D302" s="1" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="E302" s="1" t="n">
         <v>0.00754</v>
       </c>
-      <c r="E302" s="1" t="n">
+      <c r="F302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -6185,10 +7094,13 @@
         <v>0.0002171</v>
       </c>
       <c r="D303" s="1" t="n">
+        <v>0.0002163</v>
+      </c>
+      <c r="E303" s="1" t="n">
         <v>0.0002171</v>
       </c>
-      <c r="E303" s="1" t="n">
-        <v>0.0002164</v>
+      <c r="F303" s="1" t="n">
+        <v>0.0002163</v>
       </c>
     </row>
     <row r="304">
@@ -6204,9 +7116,12 @@
         <v>0.01549</v>
       </c>
       <c r="D304" s="1" t="n">
+        <v>0.01547</v>
+      </c>
+      <c r="E304" s="1" t="n">
         <v>0.01549</v>
       </c>
-      <c r="E304" s="1" t="n">
+      <c r="F304" s="1" t="n">
         <v>0.01545</v>
       </c>
     </row>
@@ -6223,9 +7138,12 @@
         <v>0.07389</v>
       </c>
       <c r="D305" s="1" t="n">
-        <v>0.07389</v>
+        <v>0.07394000000000001</v>
       </c>
       <c r="E305" s="1" t="n">
+        <v>0.07394000000000001</v>
+      </c>
+      <c r="F305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -6242,9 +7160,12 @@
         <v>0.08275</v>
       </c>
       <c r="D306" s="1" t="n">
-        <v>0.08275</v>
+        <v>0.0828</v>
       </c>
       <c r="E306" s="1" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="F306" s="1" t="n">
         <v>0.08275</v>
       </c>
     </row>
@@ -6261,9 +7182,12 @@
         <v>0.01826</v>
       </c>
       <c r="D307" s="1" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="E307" s="1" t="n">
         <v>0.01826</v>
       </c>
-      <c r="E307" s="1" t="n">
+      <c r="F307" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -6280,9 +7204,12 @@
         <v>0.0006255</v>
       </c>
       <c r="D308" s="1" t="n">
+        <v>0.0006239</v>
+      </c>
+      <c r="E308" s="1" t="n">
         <v>0.0006255</v>
       </c>
-      <c r="E308" s="1" t="n">
+      <c r="F308" s="1" t="n">
         <v>0.0006215</v>
       </c>
     </row>
@@ -6299,10 +7226,13 @@
         <v>0.08294</v>
       </c>
       <c r="D309" s="1" t="n">
+        <v>0.08244</v>
+      </c>
+      <c r="E309" s="1" t="n">
         <v>0.08294</v>
       </c>
-      <c r="E309" s="1" t="n">
-        <v>0.08288</v>
+      <c r="F309" s="1" t="n">
+        <v>0.08244</v>
       </c>
     </row>
     <row r="310">
@@ -6318,9 +7248,12 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="D310" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="E310" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="E310" s="1" t="n">
+      <c r="F310" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -6337,9 +7270,12 @@
         <v>0.2113</v>
       </c>
       <c r="D311" s="1" t="n">
+        <v>0.2112</v>
+      </c>
+      <c r="E311" s="1" t="n">
         <v>0.2113</v>
       </c>
-      <c r="E311" s="1" t="n">
+      <c r="F311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -6356,9 +7292,12 @@
         <v>0.394</v>
       </c>
       <c r="D312" s="1" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="E312" s="1" t="n">
         <v>0.394</v>
       </c>
-      <c r="E312" s="1" t="n">
+      <c r="F312" s="1" t="n">
         <v>0.3878</v>
       </c>
     </row>
@@ -6375,9 +7314,12 @@
         <v>0.10542</v>
       </c>
       <c r="D313" s="1" t="n">
+        <v>0.10509</v>
+      </c>
+      <c r="E313" s="1" t="n">
         <v>0.10542</v>
       </c>
-      <c r="E313" s="1" t="n">
+      <c r="F313" s="1" t="n">
         <v>0.10492</v>
       </c>
     </row>
@@ -6394,9 +7336,12 @@
         <v>0.08518000000000001</v>
       </c>
       <c r="D314" s="1" t="n">
-        <v>0.08518000000000001</v>
+        <v>0.08524</v>
       </c>
       <c r="E314" s="1" t="n">
+        <v>0.08524</v>
+      </c>
+      <c r="F314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -6413,9 +7358,12 @@
         <v>0.1185</v>
       </c>
       <c r="D315" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="E315" s="1" t="n">
         <v>0.1185</v>
       </c>
-      <c r="E315" s="1" t="n">
+      <c r="F315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -6432,9 +7380,12 @@
         <v>0.03681</v>
       </c>
       <c r="D316" s="1" t="n">
+        <v>0.03656</v>
+      </c>
+      <c r="E316" s="1" t="n">
         <v>0.03681</v>
       </c>
-      <c r="E316" s="1" t="n">
+      <c r="F316" s="1" t="n">
         <v>0.03628</v>
       </c>
     </row>
@@ -6451,9 +7402,12 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="D317" s="1" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.08125</v>
       </c>
       <c r="E317" s="1" t="n">
+        <v>0.08125</v>
+      </c>
+      <c r="F317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -6470,9 +7424,12 @@
         <v>0.03747</v>
       </c>
       <c r="D318" s="1" t="n">
-        <v>0.03747</v>
+        <v>0.0375</v>
       </c>
       <c r="E318" s="1" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="F318" s="1" t="n">
         <v>0.03736</v>
       </c>
     </row>
@@ -6489,9 +7446,12 @@
         <v>0.4347</v>
       </c>
       <c r="D319" s="1" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="E319" s="1" t="n">
         <v>0.4347</v>
       </c>
-      <c r="E319" s="1" t="n">
+      <c r="F319" s="1" t="n">
         <v>0.4308</v>
       </c>
     </row>
@@ -6508,10 +7468,13 @@
         <v>0.1614</v>
       </c>
       <c r="D320" s="1" t="n">
+        <v>0.1608</v>
+      </c>
+      <c r="E320" s="1" t="n">
         <v>0.1614</v>
       </c>
-      <c r="E320" s="1" t="n">
-        <v>0.1612</v>
+      <c r="F320" s="1" t="n">
+        <v>0.1608</v>
       </c>
     </row>
     <row r="321">
@@ -6527,11 +7490,14 @@
         <v>5.68</v>
       </c>
       <c r="D321" s="1" t="n">
-        <v>5.68</v>
+        <v>5.677</v>
       </c>
       <c r="E321" s="1" t="n">
         <v>5.68</v>
       </c>
+      <c r="F321" s="1" t="n">
+        <v>5.677</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -6546,9 +7512,12 @@
         <v>0.003735</v>
       </c>
       <c r="D322" s="1" t="n">
-        <v>0.003735</v>
+        <v>0.003738</v>
       </c>
       <c r="E322" s="1" t="n">
+        <v>0.003738</v>
+      </c>
+      <c r="F322" s="1" t="n">
         <v>0.003715</v>
       </c>
     </row>
@@ -6565,9 +7534,12 @@
         <v>0.001751</v>
       </c>
       <c r="D323" s="1" t="n">
-        <v>0.001751</v>
+        <v>0.001755</v>
       </c>
       <c r="E323" s="1" t="n">
+        <v>0.001755</v>
+      </c>
+      <c r="F323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -6589,6 +7561,9 @@
       <c r="E324" s="1" t="n">
         <v>1.2e-05</v>
       </c>
+      <c r="F324" s="1" t="n">
+        <v>1.2e-05</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -6603,10 +7578,13 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="D325" s="1" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="E325" s="1" t="n">
         <v>0.08649999999999999</v>
       </c>
-      <c r="E325" s="1" t="n">
-        <v>0.0864</v>
+      <c r="F325" s="1" t="n">
+        <v>0.0863</v>
       </c>
     </row>
     <row r="326">
@@ -6622,9 +7600,12 @@
         <v>0.01736</v>
       </c>
       <c r="D326" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="E326" s="1" t="n">
         <v>0.01736</v>
       </c>
-      <c r="E326" s="1" t="n">
+      <c r="F326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -6641,9 +7622,12 @@
         <v>0.01689</v>
       </c>
       <c r="D327" s="1" t="n">
+        <v>0.01687</v>
+      </c>
+      <c r="E327" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="E327" s="1" t="n">
+      <c r="F327" s="1" t="n">
         <v>0.01687</v>
       </c>
     </row>
@@ -6660,9 +7644,12 @@
         <v>4.462</v>
       </c>
       <c r="D328" s="1" t="n">
+        <v>4.458</v>
+      </c>
+      <c r="E328" s="1" t="n">
         <v>4.462</v>
       </c>
-      <c r="E328" s="1" t="n">
+      <c r="F328" s="1" t="n">
         <v>4.446</v>
       </c>
     </row>
@@ -6679,10 +7666,13 @@
         <v>0.009861</v>
       </c>
       <c r="D329" s="1" t="n">
+        <v>0.009648</v>
+      </c>
+      <c r="E329" s="1" t="n">
         <v>0.009861</v>
       </c>
-      <c r="E329" s="1" t="n">
-        <v>0.009825</v>
+      <c r="F329" s="1" t="n">
+        <v>0.009648</v>
       </c>
     </row>
     <row r="330">
@@ -6698,9 +7688,12 @@
         <v>5185.8</v>
       </c>
       <c r="D330" s="1" t="n">
+        <v>5186.5</v>
+      </c>
+      <c r="E330" s="1" t="n">
         <v>5192.9</v>
       </c>
-      <c r="E330" s="1" t="n">
+      <c r="F330" s="1" t="n">
         <v>5185.8</v>
       </c>
     </row>
@@ -6717,9 +7710,12 @@
         <v>0.07074</v>
       </c>
       <c r="D331" s="1" t="n">
-        <v>0.07074</v>
+        <v>0.07085</v>
       </c>
       <c r="E331" s="1" t="n">
+        <v>0.07085</v>
+      </c>
+      <c r="F331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -6736,9 +7732,12 @@
         <v>0.06098</v>
       </c>
       <c r="D332" s="1" t="n">
+        <v>0.06091</v>
+      </c>
+      <c r="E332" s="1" t="n">
         <v>0.06098</v>
       </c>
-      <c r="E332" s="1" t="n">
+      <c r="F332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -6755,9 +7754,12 @@
         <v>0.10347</v>
       </c>
       <c r="D333" s="1" t="n">
-        <v>0.10353</v>
+        <v>0.10416</v>
       </c>
       <c r="E333" s="1" t="n">
+        <v>0.10416</v>
+      </c>
+      <c r="F333" s="1" t="n">
         <v>0.10347</v>
       </c>
     </row>
@@ -6774,10 +7776,13 @@
         <v>0.08831</v>
       </c>
       <c r="D334" s="1" t="n">
+        <v>0.08815000000000001</v>
+      </c>
+      <c r="E334" s="1" t="n">
         <v>0.08837</v>
       </c>
-      <c r="E334" s="1" t="n">
-        <v>0.08831</v>
+      <c r="F334" s="1" t="n">
+        <v>0.08815000000000001</v>
       </c>
     </row>
     <row r="335">
@@ -6793,10 +7798,13 @@
         <v>0.016413</v>
       </c>
       <c r="D335" s="1" t="n">
+        <v>0.016391</v>
+      </c>
+      <c r="E335" s="1" t="n">
         <v>0.016413</v>
       </c>
-      <c r="E335" s="1" t="n">
-        <v>0.01641</v>
+      <c r="F335" s="1" t="n">
+        <v>0.016391</v>
       </c>
     </row>
     <row r="336">
@@ -6812,9 +7820,12 @@
         <v>0.04594</v>
       </c>
       <c r="D336" s="1" t="n">
+        <v>0.04587</v>
+      </c>
+      <c r="E336" s="1" t="n">
         <v>0.04594</v>
       </c>
-      <c r="E336" s="1" t="n">
+      <c r="F336" s="1" t="n">
         <v>0.04587</v>
       </c>
     </row>
@@ -6831,9 +7842,12 @@
         <v>0.1838</v>
       </c>
       <c r="D337" s="1" t="n">
+        <v>0.1846</v>
+      </c>
+      <c r="E337" s="1" t="n">
         <v>0.1853</v>
       </c>
-      <c r="E337" s="1" t="n">
+      <c r="F337" s="1" t="n">
         <v>0.1838</v>
       </c>
     </row>
@@ -6850,9 +7864,12 @@
         <v>0.1836</v>
       </c>
       <c r="D338" s="1" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="E338" s="1" t="n">
         <v>0.1836</v>
       </c>
-      <c r="E338" s="1" t="n">
+      <c r="F338" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -6872,6 +7889,9 @@
         <v>0.01837</v>
       </c>
       <c r="E339" s="1" t="n">
+        <v>0.01837</v>
+      </c>
+      <c r="F339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -6891,6 +7911,9 @@
         <v>0.02311</v>
       </c>
       <c r="E340" s="1" t="n">
+        <v>0.02311</v>
+      </c>
+      <c r="F340" s="1" t="n">
         <v>0.02306</v>
       </c>
     </row>
@@ -6907,9 +7930,12 @@
         <v>0.4548</v>
       </c>
       <c r="D341" s="1" t="n">
+        <v>0.4544</v>
+      </c>
+      <c r="E341" s="1" t="n">
         <v>0.4548</v>
       </c>
-      <c r="E341" s="1" t="n">
+      <c r="F341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -6926,9 +7952,12 @@
         <v>0.01339</v>
       </c>
       <c r="D342" s="1" t="n">
-        <v>0.01339</v>
+        <v>0.01344</v>
       </c>
       <c r="E342" s="1" t="n">
+        <v>0.01344</v>
+      </c>
+      <c r="F342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -6945,9 +7974,12 @@
         <v>2.887</v>
       </c>
       <c r="D343" s="1" t="n">
-        <v>2.887</v>
+        <v>2.89</v>
       </c>
       <c r="E343" s="1" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F343" s="1" t="n">
         <v>2.874</v>
       </c>
     </row>
@@ -6964,9 +7996,12 @@
         <v>0.1551</v>
       </c>
       <c r="D344" s="1" t="n">
-        <v>0.1551</v>
+        <v>0.1552</v>
       </c>
       <c r="E344" s="1" t="n">
+        <v>0.1552</v>
+      </c>
+      <c r="F344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -6983,9 +8018,12 @@
         <v>0.005367</v>
       </c>
       <c r="D345" s="1" t="n">
+        <v>0.005342</v>
+      </c>
+      <c r="E345" s="1" t="n">
         <v>0.005367</v>
       </c>
-      <c r="E345" s="1" t="n">
+      <c r="F345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -7002,9 +8040,12 @@
         <v>0.0578</v>
       </c>
       <c r="D346" s="1" t="n">
-        <v>0.0578</v>
+        <v>0.05781</v>
       </c>
       <c r="E346" s="1" t="n">
+        <v>0.05781</v>
+      </c>
+      <c r="F346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -7021,9 +8062,12 @@
         <v>2606</v>
       </c>
       <c r="D347" s="1" t="n">
+        <v>2599</v>
+      </c>
+      <c r="E347" s="1" t="n">
         <v>2606</v>
       </c>
-      <c r="E347" s="1" t="n">
+      <c r="F347" s="1" t="n">
         <v>2597</v>
       </c>
     </row>
@@ -7040,10 +8084,13 @@
         <v>0.04619</v>
       </c>
       <c r="D348" s="1" t="n">
+        <v>0.04602</v>
+      </c>
+      <c r="E348" s="1" t="n">
         <v>0.04621</v>
       </c>
-      <c r="E348" s="1" t="n">
-        <v>0.04619</v>
+      <c r="F348" s="1" t="n">
+        <v>0.04602</v>
       </c>
     </row>
     <row r="349">
@@ -7059,9 +8106,12 @@
         <v>0.005682</v>
       </c>
       <c r="D349" s="1" t="n">
+        <v>0.005706</v>
+      </c>
+      <c r="E349" s="1" t="n">
         <v>0.005707</v>
       </c>
-      <c r="E349" s="1" t="n">
+      <c r="F349" s="1" t="n">
         <v>0.005682</v>
       </c>
     </row>
@@ -7078,10 +8128,13 @@
         <v>195.51</v>
       </c>
       <c r="D350" s="1" t="n">
+        <v>195.23</v>
+      </c>
+      <c r="E350" s="1" t="n">
         <v>195.51</v>
       </c>
-      <c r="E350" s="1" t="n">
-        <v>195.31</v>
+      <c r="F350" s="1" t="n">
+        <v>195.23</v>
       </c>
     </row>
     <row r="351">
@@ -7097,9 +8150,12 @@
         <v>0.08205999999999999</v>
       </c>
       <c r="D351" s="1" t="n">
+        <v>0.08194</v>
+      </c>
+      <c r="E351" s="1" t="n">
         <v>0.08205999999999999</v>
       </c>
-      <c r="E351" s="1" t="n">
+      <c r="F351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -7116,10 +8172,13 @@
         <v>0.007537</v>
       </c>
       <c r="D352" s="1" t="n">
+        <v>0.007487</v>
+      </c>
+      <c r="E352" s="1" t="n">
         <v>0.007571</v>
       </c>
-      <c r="E352" s="1" t="n">
-        <v>0.007537</v>
+      <c r="F352" s="1" t="n">
+        <v>0.007487</v>
       </c>
     </row>
     <row r="353">
@@ -7135,9 +8194,12 @@
         <v>1.4807</v>
       </c>
       <c r="D353" s="1" t="n">
-        <v>1.486</v>
+        <v>1.4887</v>
       </c>
       <c r="E353" s="1" t="n">
+        <v>1.4887</v>
+      </c>
+      <c r="F353" s="1" t="n">
         <v>1.4807</v>
       </c>
     </row>
@@ -7154,9 +8216,12 @@
         <v>0.07643999999999999</v>
       </c>
       <c r="D354" s="1" t="n">
+        <v>0.07625</v>
+      </c>
+      <c r="E354" s="1" t="n">
         <v>0.07643999999999999</v>
       </c>
-      <c r="E354" s="1" t="n">
+      <c r="F354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -7173,9 +8238,12 @@
         <v>0.04913</v>
       </c>
       <c r="D355" s="1" t="n">
+        <v>0.04915</v>
+      </c>
+      <c r="E355" s="1" t="n">
         <v>0.04921</v>
       </c>
-      <c r="E355" s="1" t="n">
+      <c r="F355" s="1" t="n">
         <v>0.04913</v>
       </c>
     </row>
@@ -7195,6 +8263,9 @@
         <v>0.2857</v>
       </c>
       <c r="E356" s="1" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="F356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -7211,9 +8282,12 @@
         <v>0.1467</v>
       </c>
       <c r="D357" s="1" t="n">
+        <v>0.1462</v>
+      </c>
+      <c r="E357" s="1" t="n">
         <v>0.1467</v>
       </c>
-      <c r="E357" s="1" t="n">
+      <c r="F357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -7230,9 +8304,12 @@
         <v>1.355</v>
       </c>
       <c r="D358" s="1" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="E358" s="1" t="n">
         <v>1.355</v>
       </c>
-      <c r="E358" s="1" t="n">
+      <c r="F358" s="1" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -7249,10 +8326,13 @@
         <v>0.6117</v>
       </c>
       <c r="D359" s="1" t="n">
+        <v>0.6097</v>
+      </c>
+      <c r="E359" s="1" t="n">
         <v>0.6117</v>
       </c>
-      <c r="E359" s="1" t="n">
-        <v>0.6116</v>
+      <c r="F359" s="1" t="n">
+        <v>0.6097</v>
       </c>
     </row>
     <row r="360">
@@ -7268,9 +8348,12 @@
         <v>0.1145</v>
       </c>
       <c r="D360" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="E360" s="1" t="n">
         <v>0.1145</v>
       </c>
-      <c r="E360" s="1" t="n">
+      <c r="F360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -7287,9 +8370,12 @@
         <v>0.026</v>
       </c>
       <c r="D361" s="1" t="n">
+        <v>0.02604</v>
+      </c>
+      <c r="E361" s="1" t="n">
         <v>0.02619</v>
       </c>
-      <c r="E361" s="1" t="n">
+      <c r="F361" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -7306,9 +8392,12 @@
         <v>3.04e-05</v>
       </c>
       <c r="D362" s="1" t="n">
+        <v>3.03e-05</v>
+      </c>
+      <c r="E362" s="1" t="n">
         <v>3.04e-05</v>
       </c>
-      <c r="E362" s="1" t="n">
+      <c r="F362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -7325,9 +8414,12 @@
         <v>0.01026</v>
       </c>
       <c r="D363" s="1" t="n">
+        <v>0.01022</v>
+      </c>
+      <c r="E363" s="1" t="n">
         <v>0.01026</v>
       </c>
-      <c r="E363" s="1" t="n">
+      <c r="F363" s="1" t="n">
         <v>0.01018</v>
       </c>
     </row>
@@ -7344,9 +8436,12 @@
         <v>0.06208</v>
       </c>
       <c r="D364" s="1" t="n">
+        <v>0.06204</v>
+      </c>
+      <c r="E364" s="1" t="n">
         <v>0.06208</v>
       </c>
-      <c r="E364" s="1" t="n">
+      <c r="F364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -7363,9 +8458,12 @@
         <v>0.03297</v>
       </c>
       <c r="D365" s="1" t="n">
+        <v>0.03291</v>
+      </c>
+      <c r="E365" s="1" t="n">
         <v>0.03297</v>
       </c>
-      <c r="E365" s="1" t="n">
+      <c r="F365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -7382,9 +8480,12 @@
         <v>0.03296</v>
       </c>
       <c r="D366" s="1" t="n">
+        <v>0.03289</v>
+      </c>
+      <c r="E366" s="1" t="n">
         <v>0.03296</v>
       </c>
-      <c r="E366" s="1" t="n">
+      <c r="F366" s="1" t="n">
         <v>0.03288</v>
       </c>
     </row>
@@ -7401,9 +8502,12 @@
         <v>0.012155</v>
       </c>
       <c r="D367" s="1" t="n">
-        <v>0.012157</v>
+        <v>0.012163</v>
       </c>
       <c r="E367" s="1" t="n">
+        <v>0.012163</v>
+      </c>
+      <c r="F367" s="1" t="n">
         <v>0.012155</v>
       </c>
     </row>
@@ -7423,6 +8527,9 @@
         <v>0.03534</v>
       </c>
       <c r="E368" s="1" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="F368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -7439,9 +8546,12 @@
         <v>0.6183</v>
       </c>
       <c r="D369" s="1" t="n">
-        <v>0.6183</v>
+        <v>0.6193</v>
       </c>
       <c r="E369" s="1" t="n">
+        <v>0.6193</v>
+      </c>
+      <c r="F369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -7458,9 +8568,12 @@
         <v>0.00847</v>
       </c>
       <c r="D370" s="1" t="n">
+        <v>0.008460000000000001</v>
+      </c>
+      <c r="E370" s="1" t="n">
         <v>0.00847</v>
       </c>
-      <c r="E370" s="1" t="n">
+      <c r="F370" s="1" t="n">
         <v>0.00843</v>
       </c>
     </row>
@@ -7477,9 +8590,12 @@
         <v>0.003263</v>
       </c>
       <c r="D371" s="1" t="n">
-        <v>0.003263</v>
+        <v>0.003287</v>
       </c>
       <c r="E371" s="1" t="n">
+        <v>0.003287</v>
+      </c>
+      <c r="F371" s="1" t="n">
         <v>0.003242</v>
       </c>
     </row>
@@ -7496,9 +8612,12 @@
         <v>0.13235</v>
       </c>
       <c r="D372" s="1" t="n">
-        <v>0.13235</v>
+        <v>0.13275</v>
       </c>
       <c r="E372" s="1" t="n">
+        <v>0.13275</v>
+      </c>
+      <c r="F372" s="1" t="n">
         <v>0.13227</v>
       </c>
     </row>
@@ -7515,9 +8634,12 @@
         <v>0.007822000000000001</v>
       </c>
       <c r="D373" s="1" t="n">
+        <v>0.007821</v>
+      </c>
+      <c r="E373" s="1" t="n">
         <v>0.007822000000000001</v>
       </c>
-      <c r="E373" s="1" t="n">
+      <c r="F373" s="1" t="n">
         <v>0.007820000000000001</v>
       </c>
     </row>
@@ -7534,9 +8656,12 @@
         <v>0.01978</v>
       </c>
       <c r="D374" s="1" t="n">
+        <v>0.01973</v>
+      </c>
+      <c r="E374" s="1" t="n">
         <v>0.01978</v>
       </c>
-      <c r="E374" s="1" t="n">
+      <c r="F374" s="1" t="n">
         <v>0.01972</v>
       </c>
     </row>
@@ -7553,9 +8678,12 @@
         <v>0.0005921</v>
       </c>
       <c r="D375" s="1" t="n">
-        <v>0.0005921</v>
+        <v>0.000594</v>
       </c>
       <c r="E375" s="1" t="n">
+        <v>0.000594</v>
+      </c>
+      <c r="F375" s="1" t="n">
         <v>0.0005914</v>
       </c>
     </row>
@@ -7572,9 +8700,12 @@
         <v>0.0362</v>
       </c>
       <c r="D376" s="1" t="n">
-        <v>0.0362</v>
+        <v>0.0363</v>
       </c>
       <c r="E376" s="1" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="F376" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -7591,9 +8722,12 @@
         <v>0.0007909</v>
       </c>
       <c r="D377" s="1" t="n">
-        <v>0.0007909</v>
+        <v>0.000792</v>
       </c>
       <c r="E377" s="1" t="n">
+        <v>0.000792</v>
+      </c>
+      <c r="F377" s="1" t="n">
         <v>0.0007848</v>
       </c>
     </row>
@@ -7610,9 +8744,12 @@
         <v>1.98</v>
       </c>
       <c r="D378" s="1" t="n">
-        <v>1.98</v>
+        <v>1.984</v>
       </c>
       <c r="E378" s="1" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="F378" s="1" t="n">
         <v>1.973</v>
       </c>
     </row>
@@ -7629,9 +8766,12 @@
         <v>0.0005913</v>
       </c>
       <c r="D379" s="1" t="n">
+        <v>0.000589</v>
+      </c>
+      <c r="E379" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="E379" s="1" t="n">
+      <c r="F379" s="1" t="n">
         <v>0.0005888999999999999</v>
       </c>
     </row>
@@ -7648,10 +8788,13 @@
         <v>0.03743</v>
       </c>
       <c r="D380" s="1" t="n">
+        <v>0.03737</v>
+      </c>
+      <c r="E380" s="1" t="n">
         <v>0.03743</v>
       </c>
-      <c r="E380" s="1" t="n">
-        <v>0.03738</v>
+      <c r="F380" s="1" t="n">
+        <v>0.03737</v>
       </c>
     </row>
     <row r="381">
@@ -7667,9 +8810,12 @@
         <v>0.05477</v>
       </c>
       <c r="D381" s="1" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="E381" s="1" t="n">
         <v>0.05477</v>
       </c>
-      <c r="E381" s="1" t="n">
+      <c r="F381" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -7686,9 +8832,12 @@
         <v>0.01207</v>
       </c>
       <c r="D382" s="1" t="n">
+        <v>0.01206</v>
+      </c>
+      <c r="E382" s="1" t="n">
         <v>0.01207</v>
       </c>
-      <c r="E382" s="1" t="n">
+      <c r="F382" s="1" t="n">
         <v>0.01202</v>
       </c>
     </row>
@@ -7705,10 +8854,13 @@
         <v>0.001555</v>
       </c>
       <c r="D383" s="1" t="n">
+        <v>0.001552</v>
+      </c>
+      <c r="E383" s="1" t="n">
         <v>0.001559</v>
       </c>
-      <c r="E383" s="1" t="n">
-        <v>0.001555</v>
+      <c r="F383" s="1" t="n">
+        <v>0.001552</v>
       </c>
     </row>
     <row r="384">
@@ -7724,9 +8876,12 @@
         <v>0.0002157</v>
       </c>
       <c r="D384" s="1" t="n">
+        <v>0.0002154</v>
+      </c>
+      <c r="E384" s="1" t="n">
         <v>0.0002157</v>
       </c>
-      <c r="E384" s="1" t="n">
+      <c r="F384" s="1" t="n">
         <v>0.0002154</v>
       </c>
     </row>
@@ -7743,10 +8898,13 @@
         <v>0.00242</v>
       </c>
       <c r="D385" s="1" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E385" s="1" t="n">
         <v>0.00242</v>
       </c>
-      <c r="E385" s="1" t="n">
-        <v>0.00241</v>
+      <c r="F385" s="1" t="n">
+        <v>0.0024</v>
       </c>
     </row>
     <row r="386">
@@ -7762,9 +8920,12 @@
         <v>3.908</v>
       </c>
       <c r="D386" s="1" t="n">
+        <v>3.902</v>
+      </c>
+      <c r="E386" s="1" t="n">
         <v>3.908</v>
       </c>
-      <c r="E386" s="1" t="n">
+      <c r="F386" s="1" t="n">
         <v>3.892</v>
       </c>
     </row>
@@ -7781,10 +8942,13 @@
         <v>0.0006254</v>
       </c>
       <c r="D387" s="1" t="n">
+        <v>0.0006237</v>
+      </c>
+      <c r="E387" s="1" t="n">
         <v>0.0006254</v>
       </c>
-      <c r="E387" s="1" t="n">
-        <v>0.0006243000000000001</v>
+      <c r="F387" s="1" t="n">
+        <v>0.0006237</v>
       </c>
     </row>
     <row r="388">
@@ -7800,9 +8964,12 @@
         <v>0.00653</v>
       </c>
       <c r="D388" s="1" t="n">
-        <v>0.00654</v>
+        <v>0.00659</v>
       </c>
       <c r="E388" s="1" t="n">
+        <v>0.00659</v>
+      </c>
+      <c r="F388" s="1" t="n">
         <v>0.00653</v>
       </c>
     </row>
@@ -7819,9 +8986,12 @@
         <v>0.1315</v>
       </c>
       <c r="D389" s="1" t="n">
-        <v>0.1315</v>
+        <v>0.1318</v>
       </c>
       <c r="E389" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="F389" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -7838,9 +9008,12 @@
         <v>0.03202</v>
       </c>
       <c r="D390" s="1" t="n">
-        <v>0.03202</v>
+        <v>0.03223</v>
       </c>
       <c r="E390" s="1" t="n">
+        <v>0.03223</v>
+      </c>
+      <c r="F390" s="1" t="n">
         <v>0.03201</v>
       </c>
     </row>
@@ -7857,11 +9030,14 @@
         <v>0.06362</v>
       </c>
       <c r="D391" s="1" t="n">
-        <v>0.06362</v>
+        <v>0.06356000000000001</v>
       </c>
       <c r="E391" s="1" t="n">
         <v>0.06362</v>
       </c>
+      <c r="F391" s="1" t="n">
+        <v>0.06356000000000001</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -7876,10 +9052,13 @@
         <v>27.82</v>
       </c>
       <c r="D392" s="1" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="E392" s="1" t="n">
         <v>27.82</v>
       </c>
-      <c r="E392" s="1" t="n">
-        <v>27.77</v>
+      <c r="F392" s="1" t="n">
+        <v>27.75</v>
       </c>
     </row>
     <row r="393">
@@ -7895,9 +9074,12 @@
         <v>0.000414</v>
       </c>
       <c r="D393" s="1" t="n">
+        <v>0.000412</v>
+      </c>
+      <c r="E393" s="1" t="n">
         <v>0.000414</v>
       </c>
-      <c r="E393" s="1" t="n">
+      <c r="F393" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -7914,9 +9096,12 @@
         <v>0.06962</v>
       </c>
       <c r="D394" s="1" t="n">
-        <v>0.06962</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E394" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F394" s="1" t="n">
         <v>0.06926</v>
       </c>
     </row>
@@ -7933,9 +9118,12 @@
         <v>0.2589</v>
       </c>
       <c r="D395" s="1" t="n">
+        <v>0.2584</v>
+      </c>
+      <c r="E395" s="1" t="n">
         <v>0.2589</v>
       </c>
-      <c r="E395" s="1" t="n">
+      <c r="F395" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -7952,9 +9140,12 @@
         <v>0.004687</v>
       </c>
       <c r="D396" s="1" t="n">
+        <v>0.004681</v>
+      </c>
+      <c r="E396" s="1" t="n">
         <v>0.004687</v>
       </c>
-      <c r="E396" s="1" t="n">
+      <c r="F396" s="1" t="n">
         <v>0.004677</v>
       </c>
     </row>
@@ -7971,9 +9162,12 @@
         <v>0.2345</v>
       </c>
       <c r="D397" s="1" t="n">
+        <v>0.2343</v>
+      </c>
+      <c r="E397" s="1" t="n">
         <v>0.2345</v>
       </c>
-      <c r="E397" s="1" t="n">
+      <c r="F397" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
@@ -7990,10 +9184,13 @@
         <v>0.18131</v>
       </c>
       <c r="D398" s="1" t="n">
+        <v>0.18106</v>
+      </c>
+      <c r="E398" s="1" t="n">
         <v>0.18131</v>
       </c>
-      <c r="E398" s="1" t="n">
-        <v>0.18108</v>
+      <c r="F398" s="1" t="n">
+        <v>0.18106</v>
       </c>
     </row>
     <row r="399">
@@ -8009,9 +9206,12 @@
         <v>0.0412</v>
       </c>
       <c r="D399" s="1" t="n">
-        <v>0.0412</v>
+        <v>0.04121</v>
       </c>
       <c r="E399" s="1" t="n">
+        <v>0.04121</v>
+      </c>
+      <c r="F399" s="1" t="n">
         <v>0.04108</v>
       </c>
     </row>
@@ -8031,6 +9231,9 @@
         <v>0.076</v>
       </c>
       <c r="E400" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="F400" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -8047,9 +9250,12 @@
         <v>0.001743</v>
       </c>
       <c r="D401" s="1" t="n">
-        <v>0.001743</v>
+        <v>0.001751</v>
       </c>
       <c r="E401" s="1" t="n">
+        <v>0.001751</v>
+      </c>
+      <c r="F401" s="1" t="n">
         <v>0.001739</v>
       </c>
     </row>
@@ -8066,9 +9272,12 @@
         <v>0.05391</v>
       </c>
       <c r="D402" s="1" t="n">
+        <v>0.05374</v>
+      </c>
+      <c r="E402" s="1" t="n">
         <v>0.05391</v>
       </c>
-      <c r="E402" s="1" t="n">
+      <c r="F402" s="1" t="n">
         <v>0.05362</v>
       </c>
     </row>
@@ -8085,10 +9294,13 @@
         <v>2031.8</v>
       </c>
       <c r="D403" s="1" t="n">
+        <v>2029.36</v>
+      </c>
+      <c r="E403" s="1" t="n">
         <v>2031.8</v>
       </c>
-      <c r="E403" s="1" t="n">
-        <v>2030.23</v>
+      <c r="F403" s="1" t="n">
+        <v>2029.36</v>
       </c>
     </row>
     <row r="404">
@@ -8104,10 +9316,13 @@
         <v>1.082</v>
       </c>
       <c r="D404" s="1" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E404" s="1" t="n">
         <v>1.082</v>
       </c>
-      <c r="E404" s="1" t="n">
-        <v>1.081</v>
+      <c r="F404" s="1" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="405">
@@ -8123,9 +9338,12 @@
         <v>7.658</v>
       </c>
       <c r="D405" s="1" t="n">
+        <v>7.654</v>
+      </c>
+      <c r="E405" s="1" t="n">
         <v>7.658</v>
       </c>
-      <c r="E405" s="1" t="n">
+      <c r="F405" s="1" t="n">
         <v>7.65</v>
       </c>
     </row>
@@ -8142,9 +9360,12 @@
         <v>3.257</v>
       </c>
       <c r="D406" s="1" t="n">
+        <v>3.247</v>
+      </c>
+      <c r="E406" s="1" t="n">
         <v>3.257</v>
       </c>
-      <c r="E406" s="1" t="n">
+      <c r="F406" s="1" t="n">
         <v>3.238</v>
       </c>
     </row>
@@ -8161,9 +9382,12 @@
         <v>0.1814</v>
       </c>
       <c r="D407" s="1" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="E407" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="E407" s="1" t="n">
+      <c r="F407" s="1" t="n">
         <v>0.1814</v>
       </c>
     </row>
@@ -8180,9 +9404,12 @@
         <v>0.1533</v>
       </c>
       <c r="D408" s="1" t="n">
-        <v>0.1533</v>
+        <v>0.1537</v>
       </c>
       <c r="E408" s="1" t="n">
+        <v>0.1537</v>
+      </c>
+      <c r="F408" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -8199,9 +9426,12 @@
         <v>0.07346999999999999</v>
       </c>
       <c r="D409" s="1" t="n">
+        <v>0.07342</v>
+      </c>
+      <c r="E409" s="1" t="n">
         <v>0.07346999999999999</v>
       </c>
-      <c r="E409" s="1" t="n">
+      <c r="F409" s="1" t="n">
         <v>0.07315000000000001</v>
       </c>
     </row>
@@ -8218,9 +9448,12 @@
         <v>0.0209</v>
       </c>
       <c r="D410" s="1" t="n">
-        <v>0.0209</v>
+        <v>0.02091</v>
       </c>
       <c r="E410" s="1" t="n">
+        <v>0.02091</v>
+      </c>
+      <c r="F410" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -8237,9 +9470,12 @@
         <v>0.2659</v>
       </c>
       <c r="D411" s="1" t="n">
+        <v>0.2658</v>
+      </c>
+      <c r="E411" s="1" t="n">
         <v>0.2659</v>
       </c>
-      <c r="E411" s="1" t="n">
+      <c r="F411" s="1" t="n">
         <v>0.2642</v>
       </c>
     </row>
@@ -8256,9 +9492,12 @@
         <v>0.007369</v>
       </c>
       <c r="D412" s="1" t="n">
+        <v>0.007356</v>
+      </c>
+      <c r="E412" s="1" t="n">
         <v>0.007369</v>
       </c>
-      <c r="E412" s="1" t="n">
+      <c r="F412" s="1" t="n">
         <v>0.007302</v>
       </c>
     </row>
@@ -8275,9 +9514,12 @@
         <v>0.01391</v>
       </c>
       <c r="D413" s="1" t="n">
+        <v>0.01388</v>
+      </c>
+      <c r="E413" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="E413" s="1" t="n">
+      <c r="F413" s="1" t="n">
         <v>0.01385</v>
       </c>
     </row>
@@ -8294,11 +9536,14 @@
         <v>0.093</v>
       </c>
       <c r="D414" s="1" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="E414" s="1" t="n">
         <v>0.093</v>
       </c>
+      <c r="F414" s="1" t="n">
+        <v>0.092</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -8313,9 +9558,12 @@
         <v>0.04007</v>
       </c>
       <c r="D415" s="1" t="n">
-        <v>0.04007</v>
+        <v>0.04009</v>
       </c>
       <c r="E415" s="1" t="n">
+        <v>0.04009</v>
+      </c>
+      <c r="F415" s="1" t="n">
         <v>0.03998</v>
       </c>
     </row>
@@ -8332,10 +9580,13 @@
         <v>0.2854</v>
       </c>
       <c r="D416" s="1" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="E416" s="1" t="n">
         <v>0.2854</v>
       </c>
-      <c r="E416" s="1" t="n">
-        <v>0.2845</v>
+      <c r="F416" s="1" t="n">
+        <v>0.2841</v>
       </c>
     </row>
     <row r="417">
@@ -8351,9 +9602,12 @@
         <v>1.818</v>
       </c>
       <c r="D417" s="1" t="n">
-        <v>1.818</v>
+        <v>1.821</v>
       </c>
       <c r="E417" s="1" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="F417" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -8370,9 +9624,12 @@
         <v>0.06707</v>
       </c>
       <c r="D418" s="1" t="n">
+        <v>0.06675</v>
+      </c>
+      <c r="E418" s="1" t="n">
         <v>0.06707</v>
       </c>
-      <c r="E418" s="1" t="n">
+      <c r="F418" s="1" t="n">
         <v>0.06672</v>
       </c>
     </row>
@@ -8389,10 +9646,13 @@
         <v>207.39</v>
       </c>
       <c r="D419" s="1" t="n">
+        <v>207.35</v>
+      </c>
+      <c r="E419" s="1" t="n">
         <v>207.4</v>
       </c>
-      <c r="E419" s="1" t="n">
-        <v>207.39</v>
+      <c r="F419" s="1" t="n">
+        <v>207.35</v>
       </c>
     </row>
     <row r="420">
@@ -8408,9 +9668,12 @@
         <v>73.15000000000001</v>
       </c>
       <c r="D420" s="1" t="n">
+        <v>73.15000000000001</v>
+      </c>
+      <c r="E420" s="1" t="n">
         <v>73.17</v>
       </c>
-      <c r="E420" s="1" t="n">
+      <c r="F420" s="1" t="n">
         <v>73.15000000000001</v>
       </c>
     </row>
@@ -8427,9 +9690,12 @@
         <v>0.0725</v>
       </c>
       <c r="D421" s="1" t="n">
+        <v>0.07247000000000001</v>
+      </c>
+      <c r="E421" s="1" t="n">
         <v>0.0725</v>
       </c>
-      <c r="E421" s="1" t="n">
+      <c r="F421" s="1" t="n">
         <v>0.07242</v>
       </c>
     </row>
@@ -8449,6 +9715,9 @@
         <v>0.05005</v>
       </c>
       <c r="E422" s="1" t="n">
+        <v>0.05005</v>
+      </c>
+      <c r="F422" s="1" t="n">
         <v>0.04998</v>
       </c>
     </row>
@@ -8465,10 +9734,13 @@
         <v>0.00115</v>
       </c>
       <c r="D423" s="1" t="n">
+        <v>0.001148</v>
+      </c>
+      <c r="E423" s="1" t="n">
         <v>0.00115</v>
       </c>
-      <c r="E423" s="1" t="n">
-        <v>0.001149</v>
+      <c r="F423" s="1" t="n">
+        <v>0.001148</v>
       </c>
     </row>
     <row r="424">
@@ -8484,9 +9756,12 @@
         <v>0.00505</v>
       </c>
       <c r="D424" s="1" t="n">
+        <v>0.00502</v>
+      </c>
+      <c r="E424" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="E424" s="1" t="n">
+      <c r="F424" s="1" t="n">
         <v>0.00502</v>
       </c>
     </row>
@@ -8503,9 +9778,12 @@
         <v>0.1267</v>
       </c>
       <c r="D425" s="1" t="n">
+        <v>0.1266</v>
+      </c>
+      <c r="E425" s="1" t="n">
         <v>0.1267</v>
       </c>
-      <c r="E425" s="1" t="n">
+      <c r="F425" s="1" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -8525,6 +9803,9 @@
         <v>1.299</v>
       </c>
       <c r="E426" s="1" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="F426" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -8541,10 +9822,13 @@
         <v>0.004408</v>
       </c>
       <c r="D427" s="1" t="n">
+        <v>0.004393</v>
+      </c>
+      <c r="E427" s="1" t="n">
         <v>0.004408</v>
       </c>
-      <c r="E427" s="1" t="n">
-        <v>0.004399</v>
+      <c r="F427" s="1" t="n">
+        <v>0.004393</v>
       </c>
     </row>
     <row r="428">
@@ -8560,9 +9844,12 @@
         <v>0.005039</v>
       </c>
       <c r="D428" s="1" t="n">
-        <v>0.005039</v>
+        <v>0.005041</v>
       </c>
       <c r="E428" s="1" t="n">
+        <v>0.005041</v>
+      </c>
+      <c r="F428" s="1" t="n">
         <v>0.005017</v>
       </c>
     </row>
@@ -8579,9 +9866,12 @@
         <v>0.02323</v>
       </c>
       <c r="D429" s="1" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="E429" s="1" t="n">
         <v>0.02323</v>
       </c>
-      <c r="E429" s="1" t="n">
+      <c r="F429" s="1" t="n">
         <v>0.02288</v>
       </c>
     </row>
@@ -8598,9 +9888,12 @@
         <v>0.02511</v>
       </c>
       <c r="D430" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="E430" s="1" t="n">
         <v>0.02511</v>
       </c>
-      <c r="E430" s="1" t="n">
+      <c r="F430" s="1" t="n">
         <v>0.02501</v>
       </c>
     </row>
@@ -8617,9 +9910,12 @@
         <v>0.016</v>
       </c>
       <c r="D431" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="E431" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="E431" s="1" t="n">
+      <c r="F431" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -8636,9 +9932,12 @@
         <v>0.5455</v>
       </c>
       <c r="D432" s="1" t="n">
+        <v>0.5441</v>
+      </c>
+      <c r="E432" s="1" t="n">
         <v>0.5455</v>
       </c>
-      <c r="E432" s="1" t="n">
+      <c r="F432" s="1" t="n">
         <v>0.5439000000000001</v>
       </c>
     </row>
@@ -8655,9 +9954,12 @@
         <v>0.001383</v>
       </c>
       <c r="D433" s="1" t="n">
-        <v>0.001383</v>
+        <v>0.001389</v>
       </c>
       <c r="E433" s="1" t="n">
+        <v>0.001389</v>
+      </c>
+      <c r="F433" s="1" t="n">
         <v>0.001383</v>
       </c>
     </row>
@@ -8674,9 +9976,12 @@
         <v>0.3931</v>
       </c>
       <c r="D434" s="1" t="n">
-        <v>0.3931</v>
+        <v>0.3938</v>
       </c>
       <c r="E434" s="1" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="F434" s="1" t="n">
         <v>0.3925</v>
       </c>
     </row>
@@ -8696,6 +10001,9 @@
         <v>0.001393</v>
       </c>
       <c r="E435" s="1" t="n">
+        <v>0.001393</v>
+      </c>
+      <c r="F435" s="1" t="n">
         <v>0.00139</v>
       </c>
     </row>
@@ -8712,10 +10020,13 @@
         <v>0.00716</v>
       </c>
       <c r="D436" s="1" t="n">
+        <v>0.00714</v>
+      </c>
+      <c r="E436" s="1" t="n">
         <v>0.00716</v>
       </c>
-      <c r="E436" s="1" t="n">
-        <v>0.00715</v>
+      <c r="F436" s="1" t="n">
+        <v>0.00714</v>
       </c>
     </row>
     <row r="437">
@@ -8731,9 +10042,12 @@
         <v>0.001991</v>
       </c>
       <c r="D437" s="1" t="n">
+        <v>0.001984</v>
+      </c>
+      <c r="E437" s="1" t="n">
         <v>0.001991</v>
       </c>
-      <c r="E437" s="1" t="n">
+      <c r="F437" s="1" t="n">
         <v>0.001982</v>
       </c>
     </row>
@@ -8750,9 +10064,12 @@
         <v>0.3143</v>
       </c>
       <c r="D438" s="1" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="E438" s="1" t="n">
         <v>0.3143</v>
       </c>
-      <c r="E438" s="1" t="n">
+      <c r="F438" s="1" t="n">
         <v>0.3122</v>
       </c>
     </row>
@@ -8769,10 +10086,13 @@
         <v>0.04434</v>
       </c>
       <c r="D439" s="1" t="n">
+        <v>0.04429</v>
+      </c>
+      <c r="E439" s="1" t="n">
         <v>0.04435</v>
       </c>
-      <c r="E439" s="1" t="n">
-        <v>0.04434</v>
+      <c r="F439" s="1" t="n">
+        <v>0.04429</v>
       </c>
     </row>
     <row r="440">
@@ -8788,9 +10108,12 @@
         <v>0.907</v>
       </c>
       <c r="D440" s="1" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="E440" s="1" t="n">
         <v>0.907</v>
       </c>
-      <c r="E440" s="1" t="n">
+      <c r="F440" s="1" t="n">
         <v>0.906</v>
       </c>
     </row>
@@ -8807,10 +10130,13 @@
         <v>1550.68</v>
       </c>
       <c r="D441" s="1" t="n">
+        <v>1548.06</v>
+      </c>
+      <c r="E441" s="1" t="n">
         <v>1550.68</v>
       </c>
-      <c r="E441" s="1" t="n">
-        <v>1549.67</v>
+      <c r="F441" s="1" t="n">
+        <v>1548.06</v>
       </c>
     </row>
     <row r="442">
@@ -8826,9 +10152,12 @@
         <v>0.0007951</v>
       </c>
       <c r="D442" s="1" t="n">
+        <v>0.000795</v>
+      </c>
+      <c r="E442" s="1" t="n">
         <v>0.0007951</v>
       </c>
-      <c r="E442" s="1" t="n">
+      <c r="F442" s="1" t="n">
         <v>0.0007877</v>
       </c>
     </row>
@@ -8845,11 +10174,14 @@
         <v>0.003558</v>
       </c>
       <c r="D443" s="1" t="n">
-        <v>0.003558</v>
+        <v>0.003549</v>
       </c>
       <c r="E443" s="1" t="n">
         <v>0.003558</v>
       </c>
+      <c r="F443" s="1" t="n">
+        <v>0.003549</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -8864,10 +10196,13 @@
         <v>1.986</v>
       </c>
       <c r="D444" s="1" t="n">
+        <v>1.979</v>
+      </c>
+      <c r="E444" s="1" t="n">
         <v>1.989</v>
       </c>
-      <c r="E444" s="1" t="n">
-        <v>1.986</v>
+      <c r="F444" s="1" t="n">
+        <v>1.979</v>
       </c>
     </row>
     <row r="445">
@@ -8883,9 +10218,12 @@
         <v>1.31</v>
       </c>
       <c r="D445" s="1" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="E445" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="E445" s="1" t="n">
+      <c r="F445" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -8902,9 +10240,12 @@
         <v>0.06920999999999999</v>
       </c>
       <c r="D446" s="1" t="n">
+        <v>0.06923</v>
+      </c>
+      <c r="E446" s="1" t="n">
         <v>0.06929</v>
       </c>
-      <c r="E446" s="1" t="n">
+      <c r="F446" s="1" t="n">
         <v>0.06920999999999999</v>
       </c>
     </row>
@@ -8924,6 +10265,9 @@
         <v>0.0236</v>
       </c>
       <c r="E447" s="1" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="F447" s="1" t="n">
         <v>0.02347</v>
       </c>
     </row>
@@ -8940,9 +10284,12 @@
         <v>0.01394</v>
       </c>
       <c r="D448" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="E448" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="E448" s="1" t="n">
+      <c r="F448" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -8959,9 +10306,12 @@
         <v>3.734</v>
       </c>
       <c r="D449" s="1" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E449" s="1" t="n">
         <v>3.734</v>
       </c>
-      <c r="E449" s="1" t="n">
+      <c r="F449" s="1" t="n">
         <v>3.726</v>
       </c>
     </row>
@@ -8978,9 +10328,12 @@
         <v>0.0114</v>
       </c>
       <c r="D450" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="E450" s="1" t="n">
         <v>0.0115</v>
       </c>
-      <c r="E450" s="1" t="n">
+      <c r="F450" s="1" t="n">
         <v>0.0114</v>
       </c>
     </row>
@@ -8997,9 +10350,12 @@
         <v>0.01029</v>
       </c>
       <c r="D451" s="1" t="n">
+        <v>0.01028</v>
+      </c>
+      <c r="E451" s="1" t="n">
         <v>0.01029</v>
       </c>
-      <c r="E451" s="1" t="n">
+      <c r="F451" s="1" t="n">
         <v>0.01024</v>
       </c>
     </row>
@@ -9016,9 +10372,12 @@
         <v>0.1525</v>
       </c>
       <c r="D452" s="1" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="E452" s="1" t="n">
         <v>0.1525</v>
       </c>
-      <c r="E452" s="1" t="n">
+      <c r="F452" s="1" t="n">
         <v>0.1522</v>
       </c>
     </row>
@@ -9035,10 +10394,13 @@
         <v>150.98</v>
       </c>
       <c r="D453" s="1" t="n">
+        <v>150.85</v>
+      </c>
+      <c r="E453" s="1" t="n">
         <v>150.98</v>
       </c>
-      <c r="E453" s="1" t="n">
-        <v>150.88</v>
+      <c r="F453" s="1" t="n">
+        <v>150.85</v>
       </c>
     </row>
     <row r="454">
@@ -9054,9 +10416,12 @@
         <v>0.008623</v>
       </c>
       <c r="D454" s="1" t="n">
+        <v>0.008616</v>
+      </c>
+      <c r="E454" s="1" t="n">
         <v>0.008623</v>
       </c>
-      <c r="E454" s="1" t="n">
+      <c r="F454" s="1" t="n">
         <v>0.008593999999999999</v>
       </c>
     </row>
@@ -9073,9 +10438,12 @@
         <v>0.05246</v>
       </c>
       <c r="D455" s="1" t="n">
+        <v>0.05241</v>
+      </c>
+      <c r="E455" s="1" t="n">
         <v>0.05246</v>
       </c>
-      <c r="E455" s="1" t="n">
+      <c r="F455" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -9092,9 +10460,12 @@
         <v>0.30429</v>
       </c>
       <c r="D456" s="1" t="n">
-        <v>0.30429</v>
+        <v>0.30499</v>
       </c>
       <c r="E456" s="1" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="F456" s="1" t="n">
         <v>0.30269</v>
       </c>
     </row>
@@ -9111,9 +10482,12 @@
         <v>0.00546</v>
       </c>
       <c r="D457" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="E457" s="1" t="n">
         <v>0.00546</v>
       </c>
-      <c r="E457" s="1" t="n">
+      <c r="F457" s="1" t="n">
         <v>0.00544</v>
       </c>
     </row>
@@ -9130,9 +10504,12 @@
         <v>0.1007</v>
       </c>
       <c r="D458" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="E458" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="E458" s="1" t="n">
+      <c r="F458" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -9149,9 +10526,12 @@
         <v>0.001828</v>
       </c>
       <c r="D459" s="1" t="n">
-        <v>0.001828</v>
+        <v>0.001835</v>
       </c>
       <c r="E459" s="1" t="n">
+        <v>0.001835</v>
+      </c>
+      <c r="F459" s="1" t="n">
         <v>0.001825</v>
       </c>
     </row>
@@ -9168,10 +10548,13 @@
         <v>0.01829</v>
       </c>
       <c r="D460" s="1" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="E460" s="1" t="n">
         <v>0.01829</v>
       </c>
-      <c r="E460" s="1" t="n">
-        <v>0.01828</v>
+      <c r="F460" s="1" t="n">
+        <v>0.01822</v>
       </c>
     </row>
     <row r="461">
@@ -9187,9 +10570,12 @@
         <v>0.0004874</v>
       </c>
       <c r="D461" s="1" t="n">
+        <v>0.0004875</v>
+      </c>
+      <c r="E461" s="1" t="n">
         <v>0.0004877</v>
       </c>
-      <c r="E461" s="1" t="n">
+      <c r="F461" s="1" t="n">
         <v>0.0004874</v>
       </c>
     </row>
@@ -9206,9 +10592,12 @@
         <v>0.0958</v>
       </c>
       <c r="D462" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="E462" s="1" t="n">
         <v>0.0958</v>
       </c>
-      <c r="E462" s="1" t="n">
+      <c r="F462" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -9225,9 +10614,12 @@
         <v>0.07926</v>
       </c>
       <c r="D463" s="1" t="n">
+        <v>0.07912</v>
+      </c>
+      <c r="E463" s="1" t="n">
         <v>0.07926</v>
       </c>
-      <c r="E463" s="1" t="n">
+      <c r="F463" s="1" t="n">
         <v>0.07888000000000001</v>
       </c>
     </row>
@@ -9244,9 +10636,12 @@
         <v>0.03155</v>
       </c>
       <c r="D464" s="1" t="n">
+        <v>0.03151</v>
+      </c>
+      <c r="E464" s="1" t="n">
         <v>0.03155</v>
       </c>
-      <c r="E464" s="1" t="n">
+      <c r="F464" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -9263,9 +10658,12 @@
         <v>0.01618</v>
       </c>
       <c r="D465" s="1" t="n">
+        <v>0.01617</v>
+      </c>
+      <c r="E465" s="1" t="n">
         <v>0.01618</v>
       </c>
-      <c r="E465" s="1" t="n">
+      <c r="F465" s="1" t="n">
         <v>0.01613</v>
       </c>
     </row>
@@ -9282,10 +10680,13 @@
         <v>0.06781</v>
       </c>
       <c r="D466" s="1" t="n">
+        <v>0.06769</v>
+      </c>
+      <c r="E466" s="1" t="n">
         <v>0.06781</v>
       </c>
-      <c r="E466" s="1" t="n">
-        <v>0.06777</v>
+      <c r="F466" s="1" t="n">
+        <v>0.06769</v>
       </c>
     </row>
     <row r="467">
@@ -9301,9 +10702,12 @@
         <v>0.04332</v>
       </c>
       <c r="D467" s="1" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="E467" s="1" t="n">
         <v>0.04332</v>
       </c>
-      <c r="E467" s="1" t="n">
+      <c r="F467" s="1" t="n">
         <v>0.04322</v>
       </c>
     </row>
@@ -9320,9 +10724,12 @@
         <v>0.05624</v>
       </c>
       <c r="D468" s="1" t="n">
-        <v>0.05624</v>
+        <v>0.05689</v>
       </c>
       <c r="E468" s="1" t="n">
+        <v>0.05689</v>
+      </c>
+      <c r="F468" s="1" t="n">
         <v>0.05587</v>
       </c>
     </row>
@@ -9339,9 +10746,12 @@
         <v>0.2305</v>
       </c>
       <c r="D469" s="1" t="n">
+        <v>0.2301</v>
+      </c>
+      <c r="E469" s="1" t="n">
         <v>0.2305</v>
       </c>
-      <c r="E469" s="1" t="n">
+      <c r="F469" s="1" t="n">
         <v>0.2294</v>
       </c>
     </row>
@@ -9361,6 +10771,9 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="E470" s="1" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="F470" s="1" t="n">
         <v>0.0902</v>
       </c>
     </row>
@@ -9377,10 +10790,13 @@
         <v>0.0669</v>
       </c>
       <c r="D471" s="1" t="n">
+        <v>0.06669</v>
+      </c>
+      <c r="E471" s="1" t="n">
         <v>0.0669</v>
       </c>
-      <c r="E471" s="1" t="n">
-        <v>0.06686</v>
+      <c r="F471" s="1" t="n">
+        <v>0.06669</v>
       </c>
     </row>
     <row r="472">
@@ -9396,9 +10812,12 @@
         <v>6.52</v>
       </c>
       <c r="D472" s="1" t="n">
-        <v>6.52</v>
+        <v>6.525</v>
       </c>
       <c r="E472" s="1" t="n">
+        <v>6.525</v>
+      </c>
+      <c r="F472" s="1" t="n">
         <v>6.486</v>
       </c>
     </row>
@@ -9415,9 +10834,12 @@
         <v>0.01943</v>
       </c>
       <c r="D473" s="1" t="n">
+        <v>0.01941</v>
+      </c>
+      <c r="E473" s="1" t="n">
         <v>0.01943</v>
       </c>
-      <c r="E473" s="1" t="n">
+      <c r="F473" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -9434,10 +10856,13 @@
         <v>1.423</v>
       </c>
       <c r="D474" s="1" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="E474" s="1" t="n">
         <v>1.423</v>
       </c>
-      <c r="E474" s="1" t="n">
-        <v>1.422</v>
+      <c r="F474" s="1" t="n">
+        <v>1.421</v>
       </c>
     </row>
     <row r="475">
@@ -9453,11 +10878,14 @@
         <v>0.0898</v>
       </c>
       <c r="D475" s="1" t="n">
-        <v>0.0898</v>
+        <v>0.08974</v>
       </c>
       <c r="E475" s="1" t="n">
         <v>0.0898</v>
       </c>
+      <c r="F475" s="1" t="n">
+        <v>0.08974</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -9475,6 +10903,9 @@
         <v>0.1062</v>
       </c>
       <c r="E476" s="1" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="F476" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -9491,9 +10922,12 @@
         <v>0.09429</v>
       </c>
       <c r="D477" s="1" t="n">
-        <v>0.09429</v>
+        <v>0.09437</v>
       </c>
       <c r="E477" s="1" t="n">
+        <v>0.09437</v>
+      </c>
+      <c r="F477" s="1" t="n">
         <v>0.09427000000000001</v>
       </c>
     </row>
@@ -9510,9 +10944,12 @@
         <v>0.0001629</v>
       </c>
       <c r="D478" s="1" t="n">
+        <v>0.0001627</v>
+      </c>
+      <c r="E478" s="1" t="n">
         <v>0.0001629</v>
       </c>
-      <c r="E478" s="1" t="n">
+      <c r="F478" s="1" t="n">
         <v>0.0001624</v>
       </c>
     </row>
@@ -9529,9 +10966,12 @@
         <v>0.04017</v>
       </c>
       <c r="D479" s="1" t="n">
-        <v>0.04017</v>
+        <v>0.04023</v>
       </c>
       <c r="E479" s="1" t="n">
+        <v>0.04023</v>
+      </c>
+      <c r="F479" s="1" t="n">
         <v>0.04007</v>
       </c>
     </row>
@@ -9548,9 +10988,12 @@
         <v>0.007422</v>
       </c>
       <c r="D480" s="1" t="n">
+        <v>0.007395</v>
+      </c>
+      <c r="E480" s="1" t="n">
         <v>0.007422</v>
       </c>
-      <c r="E480" s="1" t="n">
+      <c r="F480" s="1" t="n">
         <v>0.007389</v>
       </c>
     </row>
@@ -9570,6 +11013,9 @@
         <v>0.0955</v>
       </c>
       <c r="E481" s="1" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="F481" s="1" t="n">
         <v>0.0954</v>
       </c>
     </row>
@@ -9586,9 +11032,12 @@
         <v>0.05621</v>
       </c>
       <c r="D482" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="E482" s="1" t="n">
         <v>0.05621</v>
       </c>
-      <c r="E482" s="1" t="n">
+      <c r="F482" s="1" t="n">
         <v>0.05595</v>
       </c>
     </row>
@@ -9605,9 +11054,12 @@
         <v>0.006161</v>
       </c>
       <c r="D483" s="1" t="n">
+        <v>0.006172</v>
+      </c>
+      <c r="E483" s="1" t="n">
         <v>0.006194</v>
       </c>
-      <c r="E483" s="1" t="n">
+      <c r="F483" s="1" t="n">
         <v>0.006161</v>
       </c>
     </row>
@@ -9627,6 +11079,9 @@
         <v>0.01492</v>
       </c>
       <c r="E484" s="1" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="F484" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -9643,10 +11098,13 @@
         <v>0.02427</v>
       </c>
       <c r="D485" s="1" t="n">
+        <v>0.02403</v>
+      </c>
+      <c r="E485" s="1" t="n">
         <v>0.02427</v>
       </c>
-      <c r="E485" s="1" t="n">
-        <v>0.02404</v>
+      <c r="F485" s="1" t="n">
+        <v>0.02403</v>
       </c>
     </row>
     <row r="486">
@@ -9662,9 +11120,12 @@
         <v>0.06679</v>
       </c>
       <c r="D486" s="1" t="n">
-        <v>0.06679</v>
+        <v>0.06687</v>
       </c>
       <c r="E486" s="1" t="n">
+        <v>0.06687</v>
+      </c>
+      <c r="F486" s="1" t="n">
         <v>0.0667</v>
       </c>
     </row>
@@ -9681,10 +11142,13 @@
         <v>0.03683</v>
       </c>
       <c r="D487" s="1" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="E487" s="1" t="n">
         <v>0.03705</v>
       </c>
-      <c r="E487" s="1" t="n">
-        <v>0.03683</v>
+      <c r="F487" s="1" t="n">
+        <v>0.0368</v>
       </c>
     </row>
     <row r="488">
@@ -9700,10 +11164,13 @@
         <v>0.01819</v>
       </c>
       <c r="D488" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="E488" s="1" t="n">
         <v>0.0182</v>
       </c>
-      <c r="E488" s="1" t="n">
-        <v>0.01819</v>
+      <c r="F488" s="1" t="n">
+        <v>0.01814</v>
       </c>
     </row>
     <row r="489">
@@ -9719,10 +11186,13 @@
         <v>0.03258</v>
       </c>
       <c r="D489" s="1" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="E489" s="1" t="n">
         <v>0.03278</v>
       </c>
-      <c r="E489" s="1" t="n">
-        <v>0.03258</v>
+      <c r="F489" s="1" t="n">
+        <v>0.0325</v>
       </c>
     </row>
     <row r="490">
@@ -9738,9 +11208,12 @@
         <v>0.01464</v>
       </c>
       <c r="D490" s="1" t="n">
-        <v>0.01464</v>
+        <v>0.01474</v>
       </c>
       <c r="E490" s="1" t="n">
+        <v>0.01474</v>
+      </c>
+      <c r="F490" s="1" t="n">
         <v>0.01458</v>
       </c>
     </row>
@@ -9757,9 +11230,12 @@
         <v>0.01859</v>
       </c>
       <c r="D491" s="1" t="n">
+        <v>0.01858</v>
+      </c>
+      <c r="E491" s="1" t="n">
         <v>0.01859</v>
       </c>
-      <c r="E491" s="1" t="n">
+      <c r="F491" s="1" t="n">
         <v>0.01851</v>
       </c>
     </row>
@@ -9776,10 +11252,13 @@
         <v>0.08935</v>
       </c>
       <c r="D492" s="1" t="n">
+        <v>0.08842</v>
+      </c>
+      <c r="E492" s="1" t="n">
         <v>0.08935</v>
       </c>
-      <c r="E492" s="1" t="n">
-        <v>0.08907</v>
+      <c r="F492" s="1" t="n">
+        <v>0.08842</v>
       </c>
     </row>
     <row r="493">
@@ -9795,9 +11274,12 @@
         <v>0.006514</v>
       </c>
       <c r="D493" s="1" t="n">
+        <v>0.006509</v>
+      </c>
+      <c r="E493" s="1" t="n">
         <v>0.006514</v>
       </c>
-      <c r="E493" s="1" t="n">
+      <c r="F493" s="1" t="n">
         <v>0.006498</v>
       </c>
     </row>
@@ -9814,9 +11296,12 @@
         <v>0.1324</v>
       </c>
       <c r="D494" s="1" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="E494" s="1" t="n">
         <v>0.1324</v>
       </c>
-      <c r="E494" s="1" t="n">
+      <c r="F494" s="1" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -9833,9 +11318,12 @@
         <v>0.2853</v>
       </c>
       <c r="D495" s="1" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="E495" s="1" t="n">
         <v>0.2853</v>
       </c>
-      <c r="E495" s="1" t="n">
+      <c r="F495" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -9852,9 +11340,12 @@
         <v>0.004534</v>
       </c>
       <c r="D496" s="1" t="n">
+        <v>0.00452</v>
+      </c>
+      <c r="E496" s="1" t="n">
         <v>0.004534</v>
       </c>
-      <c r="E496" s="1" t="n">
+      <c r="F496" s="1" t="n">
         <v>0.004516</v>
       </c>
     </row>
@@ -9871,9 +11362,12 @@
         <v>0.1283</v>
       </c>
       <c r="D497" s="1" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="E497" s="1" t="n">
         <v>0.1283</v>
       </c>
-      <c r="E497" s="1" t="n">
+      <c r="F497" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -9890,10 +11384,13 @@
         <v>0.03439</v>
       </c>
       <c r="D498" s="1" t="n">
+        <v>0.03423</v>
+      </c>
+      <c r="E498" s="1" t="n">
         <v>0.03439</v>
       </c>
-      <c r="E498" s="1" t="n">
-        <v>0.03431</v>
+      <c r="F498" s="1" t="n">
+        <v>0.03423</v>
       </c>
     </row>
     <row r="499">
@@ -9909,9 +11406,12 @@
         <v>0.03576</v>
       </c>
       <c r="D499" s="1" t="n">
+        <v>0.03565</v>
+      </c>
+      <c r="E499" s="1" t="n">
         <v>0.03576</v>
       </c>
-      <c r="E499" s="1" t="n">
+      <c r="F499" s="1" t="n">
         <v>0.03557</v>
       </c>
     </row>
@@ -9928,9 +11428,12 @@
         <v>0.003421</v>
       </c>
       <c r="D500" s="1" t="n">
+        <v>0.003418</v>
+      </c>
+      <c r="E500" s="1" t="n">
         <v>0.003421</v>
       </c>
-      <c r="E500" s="1" t="n">
+      <c r="F500" s="1" t="n">
         <v>0.003417</v>
       </c>
     </row>
@@ -9947,9 +11450,12 @@
         <v>0.0003799</v>
       </c>
       <c r="D501" s="1" t="n">
+        <v>0.0003798</v>
+      </c>
+      <c r="E501" s="1" t="n">
         <v>0.0003799</v>
       </c>
-      <c r="E501" s="1" t="n">
+      <c r="F501" s="1" t="n">
         <v>0.0003786</v>
       </c>
     </row>
@@ -9966,9 +11472,12 @@
         <v>0.3003</v>
       </c>
       <c r="D502" s="1" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="E502" s="1" t="n">
         <v>0.3003</v>
       </c>
-      <c r="E502" s="1" t="n">
+      <c r="F502" s="1" t="n">
         <v>0.2986</v>
       </c>
     </row>
@@ -9985,10 +11494,13 @@
         <v>0.06507</v>
       </c>
       <c r="D503" s="1" t="n">
+        <v>0.06497</v>
+      </c>
+      <c r="E503" s="1" t="n">
         <v>0.06507</v>
       </c>
-      <c r="E503" s="1" t="n">
-        <v>0.06501999999999999</v>
+      <c r="F503" s="1" t="n">
+        <v>0.06497</v>
       </c>
     </row>
     <row r="504">
@@ -10004,9 +11516,12 @@
         <v>0.1777</v>
       </c>
       <c r="D504" s="1" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="E504" s="1" t="n">
         <v>0.1777</v>
       </c>
-      <c r="E504" s="1" t="n">
+      <c r="F504" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -10023,9 +11538,12 @@
         <v>0.1512</v>
       </c>
       <c r="D505" s="1" t="n">
-        <v>0.1512</v>
+        <v>0.1513</v>
       </c>
       <c r="E505" s="1" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="F505" s="1" t="n">
         <v>0.1512</v>
       </c>
     </row>
@@ -10042,9 +11560,12 @@
         <v>0.01198</v>
       </c>
       <c r="D506" s="1" t="n">
+        <v>0.01195</v>
+      </c>
+      <c r="E506" s="1" t="n">
         <v>0.01198</v>
       </c>
-      <c r="E506" s="1" t="n">
+      <c r="F506" s="1" t="n">
         <v>0.01193</v>
       </c>
     </row>
@@ -10061,9 +11582,12 @@
         <v>0.2883</v>
       </c>
       <c r="D507" s="1" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="E507" s="1" t="n">
         <v>0.2883</v>
       </c>
-      <c r="E507" s="1" t="n">
+      <c r="F507" s="1" t="n">
         <v>0.2875</v>
       </c>
     </row>
@@ -10080,10 +11604,13 @@
         <v>0.0094</v>
       </c>
       <c r="D508" s="1" t="n">
+        <v>0.009339999999999999</v>
+      </c>
+      <c r="E508" s="1" t="n">
         <v>0.0094</v>
       </c>
-      <c r="E508" s="1" t="n">
-        <v>0.009379999999999999</v>
+      <c r="F508" s="1" t="n">
+        <v>0.009339999999999999</v>
       </c>
     </row>
     <row r="509">
@@ -10099,10 +11626,13 @@
         <v>0.006816</v>
       </c>
       <c r="D509" s="1" t="n">
+        <v>0.006783</v>
+      </c>
+      <c r="E509" s="1" t="n">
         <v>0.006816</v>
       </c>
-      <c r="E509" s="1" t="n">
-        <v>0.006801</v>
+      <c r="F509" s="1" t="n">
+        <v>0.006783</v>
       </c>
     </row>
     <row r="510">
@@ -10118,9 +11648,12 @@
         <v>0.2951</v>
       </c>
       <c r="D510" s="1" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="E510" s="1" t="n">
         <v>0.2951</v>
       </c>
-      <c r="E510" s="1" t="n">
+      <c r="F510" s="1" t="n">
         <v>0.2936</v>
       </c>
     </row>
@@ -10137,9 +11670,12 @@
         <v>0.01471</v>
       </c>
       <c r="D511" s="1" t="n">
+        <v>0.01468</v>
+      </c>
+      <c r="E511" s="1" t="n">
         <v>0.01471</v>
       </c>
-      <c r="E511" s="1" t="n">
+      <c r="F511" s="1" t="n">
         <v>0.01467</v>
       </c>
     </row>
@@ -10156,9 +11692,12 @@
         <v>0.1398</v>
       </c>
       <c r="D512" s="1" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="E512" s="1" t="n">
         <v>0.1398</v>
       </c>
-      <c r="E512" s="1" t="n">
+      <c r="F512" s="1" t="n">
         <v>0.1395</v>
       </c>
     </row>
@@ -10175,9 +11714,12 @@
         <v>0.08144999999999999</v>
       </c>
       <c r="D513" s="1" t="n">
+        <v>0.08128000000000001</v>
+      </c>
+      <c r="E513" s="1" t="n">
         <v>0.08144999999999999</v>
       </c>
-      <c r="E513" s="1" t="n">
+      <c r="F513" s="1" t="n">
         <v>0.08069</v>
       </c>
     </row>
@@ -10194,9 +11736,12 @@
         <v>0.0251</v>
       </c>
       <c r="D514" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E514" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="E514" s="1" t="n">
+      <c r="F514" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -10213,9 +11758,12 @@
         <v>0.06319</v>
       </c>
       <c r="D515" s="1" t="n">
+        <v>0.06311</v>
+      </c>
+      <c r="E515" s="1" t="n">
         <v>0.06319</v>
       </c>
-      <c r="E515" s="1" t="n">
+      <c r="F515" s="1" t="n">
         <v>0.06301</v>
       </c>
     </row>
@@ -10232,9 +11780,12 @@
         <v>0.04723</v>
       </c>
       <c r="D516" s="1" t="n">
+        <v>0.04713</v>
+      </c>
+      <c r="E516" s="1" t="n">
         <v>0.04723</v>
       </c>
-      <c r="E516" s="1" t="n">
+      <c r="F516" s="1" t="n">
         <v>0.04707</v>
       </c>
     </row>
@@ -10251,9 +11802,12 @@
         <v>0.004907</v>
       </c>
       <c r="D517" s="1" t="n">
-        <v>0.004907</v>
+        <v>0.004908</v>
       </c>
       <c r="E517" s="1" t="n">
+        <v>0.004908</v>
+      </c>
+      <c r="F517" s="1" t="n">
         <v>0.004906</v>
       </c>
     </row>
@@ -10270,9 +11824,12 @@
         <v>0.00941</v>
       </c>
       <c r="D518" s="1" t="n">
-        <v>0.009419</v>
+        <v>0.009429999999999999</v>
       </c>
       <c r="E518" s="1" t="n">
+        <v>0.009429999999999999</v>
+      </c>
+      <c r="F518" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -10292,6 +11849,9 @@
         <v>0.01807</v>
       </c>
       <c r="E519" s="1" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="F519" s="1" t="n">
         <v>0.01803</v>
       </c>
     </row>
@@ -10308,9 +11868,12 @@
         <v>0.06666999999999999</v>
       </c>
       <c r="D520" s="1" t="n">
+        <v>0.06648999999999999</v>
+      </c>
+      <c r="E520" s="1" t="n">
         <v>0.06666999999999999</v>
       </c>
-      <c r="E520" s="1" t="n">
+      <c r="F520" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -10327,9 +11890,12 @@
         <v>0.1365</v>
       </c>
       <c r="D521" s="1" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="E521" s="1" t="n">
         <v>0.1365</v>
       </c>
-      <c r="E521" s="1" t="n">
+      <c r="F521" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -10346,9 +11912,12 @@
         <v>0.04746</v>
       </c>
       <c r="D522" s="1" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="E522" s="1" t="n">
         <v>0.04746</v>
       </c>
-      <c r="E522" s="1" t="n">
+      <c r="F522" s="1" t="n">
         <v>0.04718</v>
       </c>
     </row>
@@ -10365,9 +11934,12 @@
         <v>0.06809</v>
       </c>
       <c r="D523" s="1" t="n">
+        <v>0.06798</v>
+      </c>
+      <c r="E523" s="1" t="n">
         <v>0.06809</v>
       </c>
-      <c r="E523" s="1" t="n">
+      <c r="F523" s="1" t="n">
         <v>0.06793</v>
       </c>
     </row>
@@ -10384,10 +11956,13 @@
         <v>0.6982</v>
       </c>
       <c r="D524" s="1" t="n">
+        <v>0.6966</v>
+      </c>
+      <c r="E524" s="1" t="n">
         <v>0.6982</v>
       </c>
-      <c r="E524" s="1" t="n">
-        <v>0.6968</v>
+      <c r="F524" s="1" t="n">
+        <v>0.6966</v>
       </c>
     </row>
     <row r="525">
@@ -10408,6 +11983,9 @@
       <c r="E525" s="1" t="n">
         <v>0.00267</v>
       </c>
+      <c r="F525" s="1" t="n">
+        <v>0.00267</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -10422,9 +12000,12 @@
         <v>0.4868</v>
       </c>
       <c r="D526" s="1" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="E526" s="1" t="n">
         <v>0.4868</v>
       </c>
-      <c r="E526" s="1" t="n">
+      <c r="F526" s="1" t="n">
         <v>0.4856</v>
       </c>
     </row>
@@ -10441,9 +12022,12 @@
         <v>45.81</v>
       </c>
       <c r="D527" s="1" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="E527" s="1" t="n">
         <v>45.81</v>
       </c>
-      <c r="E527" s="1" t="n">
+      <c r="F527" s="1" t="n">
         <v>45.76</v>
       </c>
     </row>
@@ -10460,10 +12044,13 @@
         <v>0.02437</v>
       </c>
       <c r="D528" s="1" t="n">
+        <v>0.02434</v>
+      </c>
+      <c r="E528" s="1" t="n">
         <v>0.02437</v>
       </c>
-      <c r="E528" s="1" t="n">
-        <v>0.02436</v>
+      <c r="F528" s="1" t="n">
+        <v>0.02434</v>
       </c>
     </row>
     <row r="529">
@@ -10479,10 +12066,13 @@
         <v>0.006384</v>
       </c>
       <c r="D529" s="1" t="n">
+        <v>0.00638</v>
+      </c>
+      <c r="E529" s="1" t="n">
         <v>0.006388</v>
       </c>
-      <c r="E529" s="1" t="n">
-        <v>0.006384</v>
+      <c r="F529" s="1" t="n">
+        <v>0.00638</v>
       </c>
     </row>
     <row r="530">
@@ -10498,9 +12088,12 @@
         <v>0.2</v>
       </c>
       <c r="D530" s="1" t="n">
+        <v>0.1998</v>
+      </c>
+      <c r="E530" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="E530" s="1" t="n">
+      <c r="F530" s="1" t="n">
         <v>0.1993</v>
       </c>
     </row>
@@ -10517,9 +12110,12 @@
         <v>0.007657</v>
       </c>
       <c r="D531" s="1" t="n">
+        <v>0.007671</v>
+      </c>
+      <c r="E531" s="1" t="n">
         <v>0.007727</v>
       </c>
-      <c r="E531" s="1" t="n">
+      <c r="F531" s="1" t="n">
         <v>0.007657</v>
       </c>
     </row>
@@ -10536,9 +12132,12 @@
         <v>2.285</v>
       </c>
       <c r="D532" s="1" t="n">
+        <v>2.283</v>
+      </c>
+      <c r="E532" s="1" t="n">
         <v>2.285</v>
       </c>
-      <c r="E532" s="1" t="n">
+      <c r="F532" s="1" t="n">
         <v>2.275</v>
       </c>
     </row>
@@ -10555,9 +12154,12 @@
         <v>0.04138</v>
       </c>
       <c r="D533" s="1" t="n">
+        <v>0.04138</v>
+      </c>
+      <c r="E533" s="1" t="n">
         <v>0.04142</v>
       </c>
-      <c r="E533" s="1" t="n">
+      <c r="F533" s="1" t="n">
         <v>0.04138</v>
       </c>
     </row>
@@ -10574,9 +12176,12 @@
         <v>0.1816</v>
       </c>
       <c r="D534" s="1" t="n">
-        <v>0.1816</v>
+        <v>0.1819</v>
       </c>
       <c r="E534" s="1" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="F534" s="1" t="n">
         <v>0.1811</v>
       </c>
     </row>
@@ -10593,10 +12198,13 @@
         <v>0.04311</v>
       </c>
       <c r="D535" s="1" t="n">
+        <v>0.04291</v>
+      </c>
+      <c r="E535" s="1" t="n">
         <v>0.04311</v>
       </c>
-      <c r="E535" s="1" t="n">
-        <v>0.04303</v>
+      <c r="F535" s="1" t="n">
+        <v>0.04291</v>
       </c>
     </row>
     <row r="536">
@@ -10612,9 +12220,12 @@
         <v>0.05438</v>
       </c>
       <c r="D536" s="1" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="E536" s="1" t="n">
         <v>0.05438</v>
       </c>
-      <c r="E536" s="1" t="n">
+      <c r="F536" s="1" t="n">
         <v>0.0542</v>
       </c>
     </row>
@@ -10631,9 +12242,12 @@
         <v>0.1609</v>
       </c>
       <c r="D537" s="1" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="E537" s="1" t="n">
         <v>0.1609</v>
       </c>
-      <c r="E537" s="1" t="n">
+      <c r="F537" s="1" t="n">
         <v>0.1605</v>
       </c>
     </row>
@@ -10650,10 +12264,13 @@
         <v>0.03683</v>
       </c>
       <c r="D538" s="1" t="n">
+        <v>0.03672</v>
+      </c>
+      <c r="E538" s="1" t="n">
         <v>0.03687</v>
       </c>
-      <c r="E538" s="1" t="n">
-        <v>0.03683</v>
+      <c r="F538" s="1" t="n">
+        <v>0.03672</v>
       </c>
     </row>
     <row r="539">
@@ -10669,9 +12286,12 @@
         <v>0.05772</v>
       </c>
       <c r="D539" s="1" t="n">
-        <v>0.05772</v>
+        <v>0.05775</v>
       </c>
       <c r="E539" s="1" t="n">
+        <v>0.05775</v>
+      </c>
+      <c r="F539" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -10688,10 +12308,13 @@
         <v>0.04267</v>
       </c>
       <c r="D540" s="1" t="n">
+        <v>0.04257</v>
+      </c>
+      <c r="E540" s="1" t="n">
         <v>0.04267</v>
       </c>
-      <c r="E540" s="1" t="n">
-        <v>0.04259</v>
+      <c r="F540" s="1" t="n">
+        <v>0.04257</v>
       </c>
     </row>
     <row r="541">
@@ -10710,6 +12333,9 @@
         <v>0.0173</v>
       </c>
       <c r="E541" s="1" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="F541" s="1" t="n">
         <v>0.0172</v>
       </c>
     </row>
@@ -10726,9 +12352,12 @@
         <v>0.003971</v>
       </c>
       <c r="D542" s="1" t="n">
+        <v>0.003972</v>
+      </c>
+      <c r="E542" s="1" t="n">
         <v>0.003975</v>
       </c>
-      <c r="E542" s="1" t="n">
+      <c r="F542" s="1" t="n">
         <v>0.003971</v>
       </c>
     </row>
@@ -10745,9 +12374,12 @@
         <v>0.05735</v>
       </c>
       <c r="D543" s="1" t="n">
+        <v>0.05749</v>
+      </c>
+      <c r="E543" s="1" t="n">
         <v>0.05817</v>
       </c>
-      <c r="E543" s="1" t="n">
+      <c r="F543" s="1" t="n">
         <v>0.05735</v>
       </c>
     </row>
@@ -10764,9 +12396,12 @@
         <v>0.05042</v>
       </c>
       <c r="D544" s="1" t="n">
+        <v>0.05034</v>
+      </c>
+      <c r="E544" s="1" t="n">
         <v>0.05042</v>
       </c>
-      <c r="E544" s="1" t="n">
+      <c r="F544" s="1" t="n">
         <v>0.05022</v>
       </c>
     </row>
@@ -10783,9 +12418,12 @@
         <v>0.04064</v>
       </c>
       <c r="D545" s="1" t="n">
+        <v>0.04041</v>
+      </c>
+      <c r="E545" s="1" t="n">
         <v>0.04064</v>
       </c>
-      <c r="E545" s="1" t="n">
+      <c r="F545" s="1" t="n">
         <v>0.04038</v>
       </c>
     </row>
@@ -10802,9 +12440,12 @@
         <v>0.007412</v>
       </c>
       <c r="D546" s="1" t="n">
-        <v>0.007412</v>
+        <v>0.00743</v>
       </c>
       <c r="E546" s="1" t="n">
+        <v>0.00743</v>
+      </c>
+      <c r="F546" s="1" t="n">
         <v>0.007402</v>
       </c>
     </row>
@@ -10821,9 +12462,12 @@
         <v>0.0146</v>
       </c>
       <c r="D547" s="1" t="n">
-        <v>0.01461</v>
+        <v>0.01464</v>
       </c>
       <c r="E547" s="1" t="n">
+        <v>0.01464</v>
+      </c>
+      <c r="F547" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -10843,6 +12487,9 @@
         <v>0.01573</v>
       </c>
       <c r="E548" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="F548" s="1" t="n">
         <v>0.01572</v>
       </c>
     </row>
@@ -10859,9 +12506,12 @@
         <v>0.13283</v>
       </c>
       <c r="D549" s="1" t="n">
-        <v>0.13283</v>
+        <v>0.13434</v>
       </c>
       <c r="E549" s="1" t="n">
+        <v>0.13434</v>
+      </c>
+      <c r="F549" s="1" t="n">
         <v>0.13271</v>
       </c>
     </row>
@@ -10878,9 +12528,12 @@
         <v>0.1696</v>
       </c>
       <c r="D550" s="1" t="n">
+        <v>0.1695</v>
+      </c>
+      <c r="E550" s="1" t="n">
         <v>0.1696</v>
       </c>
-      <c r="E550" s="1" t="n">
+      <c r="F550" s="1" t="n">
         <v>0.1695</v>
       </c>
     </row>
@@ -10897,9 +12550,12 @@
         <v>0.003577</v>
       </c>
       <c r="D551" s="1" t="n">
+        <v>0.003579</v>
+      </c>
+      <c r="E551" s="1" t="n">
         <v>0.003583</v>
       </c>
-      <c r="E551" s="1" t="n">
+      <c r="F551" s="1" t="n">
         <v>0.003577</v>
       </c>
     </row>
@@ -10916,9 +12572,12 @@
         <v>0.03032</v>
       </c>
       <c r="D552" s="1" t="n">
-        <v>0.03034</v>
+        <v>0.03038</v>
       </c>
       <c r="E552" s="1" t="n">
+        <v>0.03038</v>
+      </c>
+      <c r="F552" s="1" t="n">
         <v>0.03032</v>
       </c>
     </row>
@@ -10938,6 +12597,9 @@
         <v>0.01325</v>
       </c>
       <c r="E553" s="1" t="n">
+        <v>0.01325</v>
+      </c>
+      <c r="F553" s="1" t="n">
         <v>0.01324</v>
       </c>
     </row>
@@ -10954,10 +12616,13 @@
         <v>0.1046</v>
       </c>
       <c r="D554" s="1" t="n">
+        <v>0.1042</v>
+      </c>
+      <c r="E554" s="1" t="n">
         <v>0.1046</v>
       </c>
-      <c r="E554" s="1" t="n">
-        <v>0.1043</v>
+      <c r="F554" s="1" t="n">
+        <v>0.1042</v>
       </c>
     </row>
     <row r="555">
@@ -10973,9 +12638,12 @@
         <v>0.05319</v>
       </c>
       <c r="D555" s="1" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="E555" s="1" t="n">
         <v>0.05319</v>
       </c>
-      <c r="E555" s="1" t="n">
+      <c r="F555" s="1" t="n">
         <v>0.05291</v>
       </c>
     </row>
@@ -10995,6 +12663,9 @@
         <v>0.01224</v>
       </c>
       <c r="E556" s="1" t="n">
+        <v>0.01224</v>
+      </c>
+      <c r="F556" s="1" t="n">
         <v>0.01223</v>
       </c>
     </row>

--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,15 +416,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F556"/>
+  <dimension ref="A1:G556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -450,10 +451,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>price_00:45</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -475,9 +481,12 @@
         <v>71364.39999999999</v>
       </c>
       <c r="E2" s="1" t="n">
+        <v>71413.2</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>71530</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="G2" s="1" t="n">
         <v>71364.39999999999</v>
       </c>
     </row>
@@ -497,9 +506,12 @@
         <v>2091.71</v>
       </c>
       <c r="E3" s="1" t="n">
+        <v>2092.33</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>2096.9</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="G3" s="1" t="n">
         <v>2091.71</v>
       </c>
     </row>
@@ -519,10 +531,13 @@
         <v>87.68000000000001</v>
       </c>
       <c r="E4" s="1" t="n">
+        <v>87.66</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>87.95</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>87.68000000000001</v>
+      <c r="G4" s="1" t="n">
+        <v>87.66</v>
       </c>
     </row>
     <row r="5">
@@ -541,9 +556,12 @@
         <v>23.5</v>
       </c>
       <c r="E5" s="1" t="n">
+        <v>23.512</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>23.579</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>23.478</v>
       </c>
     </row>
@@ -563,9 +581,12 @@
         <v>0.001831</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.001852</v>
+        <v>0.001892</v>
       </c>
       <c r="F6" s="1" t="n">
+        <v>0.001892</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>0.001827</v>
       </c>
     </row>
@@ -585,10 +606,13 @@
         <v>1.4136</v>
       </c>
       <c r="E7" s="1" t="n">
+        <v>1.4135</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>1.4149</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>1.4136</v>
+      <c r="G7" s="1" t="n">
+        <v>1.4135</v>
       </c>
     </row>
     <row r="8">
@@ -607,10 +631,13 @@
         <v>0.010969</v>
       </c>
       <c r="E8" s="1" t="n">
+        <v>0.010846</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>0.011244</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>0.010969</v>
+      <c r="G8" s="1" t="n">
+        <v>0.010846</v>
       </c>
     </row>
     <row r="9">
@@ -629,9 +656,12 @@
         <v>3.954</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>3.968</v>
+        <v>3.979</v>
       </c>
       <c r="F9" s="1" t="n">
+        <v>3.979</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>3.954</v>
       </c>
     </row>
@@ -651,10 +681,13 @@
         <v>275.37</v>
       </c>
       <c r="E10" s="1" t="n">
+        <v>272.11</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>275.37</v>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>272.62</v>
+      <c r="G10" s="1" t="n">
+        <v>272.11</v>
       </c>
     </row>
     <row r="11">
@@ -673,10 +706,13 @@
         <v>0.07988000000000001</v>
       </c>
       <c r="E11" s="1" t="n">
+        <v>0.07904</v>
+      </c>
+      <c r="F11" s="1" t="n">
         <v>0.08047</v>
       </c>
-      <c r="F11" s="1" t="n">
-        <v>0.07929</v>
+      <c r="G11" s="1" t="n">
+        <v>0.07904</v>
       </c>
     </row>
     <row r="12">
@@ -695,10 +731,13 @@
         <v>226.28</v>
       </c>
       <c r="E12" s="1" t="n">
+        <v>224.51</v>
+      </c>
+      <c r="F12" s="1" t="n">
         <v>227.69</v>
       </c>
-      <c r="F12" s="1" t="n">
-        <v>226.28</v>
+      <c r="G12" s="1" t="n">
+        <v>224.51</v>
       </c>
     </row>
     <row r="13">
@@ -717,9 +756,12 @@
         <v>0.09464</v>
       </c>
       <c r="E13" s="1" t="n">
+        <v>0.0948</v>
+      </c>
+      <c r="F13" s="1" t="n">
         <v>0.09497</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="G13" s="1" t="n">
         <v>0.09464</v>
       </c>
     </row>
@@ -739,10 +781,13 @@
         <v>37.222</v>
       </c>
       <c r="E14" s="1" t="n">
+        <v>37.127</v>
+      </c>
+      <c r="F14" s="1" t="n">
         <v>37.279</v>
       </c>
-      <c r="F14" s="1" t="n">
-        <v>37.222</v>
+      <c r="G14" s="1" t="n">
+        <v>37.127</v>
       </c>
     </row>
     <row r="15">
@@ -761,9 +806,12 @@
         <v>0.09845</v>
       </c>
       <c r="E15" s="1" t="n">
+        <v>0.09589</v>
+      </c>
+      <c r="F15" s="1" t="n">
         <v>0.09845</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="G15" s="1" t="n">
         <v>0.09461</v>
       </c>
     </row>
@@ -783,10 +831,13 @@
         <v>0.2291</v>
       </c>
       <c r="E16" s="1" t="n">
+        <v>0.2256</v>
+      </c>
+      <c r="F16" s="1" t="n">
         <v>0.2339</v>
       </c>
-      <c r="F16" s="1" t="n">
-        <v>0.2291</v>
+      <c r="G16" s="1" t="n">
+        <v>0.2256</v>
       </c>
     </row>
     <row r="17">
@@ -805,10 +856,13 @@
         <v>0.011542</v>
       </c>
       <c r="E17" s="1" t="n">
+        <v>0.011501</v>
+      </c>
+      <c r="F17" s="1" t="n">
         <v>0.011542</v>
       </c>
-      <c r="F17" s="1" t="n">
-        <v>0.011513</v>
+      <c r="G17" s="1" t="n">
+        <v>0.011501</v>
       </c>
     </row>
     <row r="18">
@@ -827,10 +881,13 @@
         <v>659.73</v>
       </c>
       <c r="E18" s="1" t="n">
+        <v>659.5599999999999</v>
+      </c>
+      <c r="F18" s="1" t="n">
         <v>660.72</v>
       </c>
-      <c r="F18" s="1" t="n">
-        <v>659.6799999999999</v>
+      <c r="G18" s="1" t="n">
+        <v>659.5599999999999</v>
       </c>
     </row>
     <row r="19">
@@ -849,9 +906,12 @@
         <v>0.0033295</v>
       </c>
       <c r="E19" s="1" t="n">
+        <v>0.0033321</v>
+      </c>
+      <c r="F19" s="1" t="n">
         <v>0.0033451</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="G19" s="1" t="n">
         <v>0.0033295</v>
       </c>
     </row>
@@ -871,10 +931,13 @@
         <v>0.17941</v>
       </c>
       <c r="E20" s="1" t="n">
+        <v>0.17675</v>
+      </c>
+      <c r="F20" s="1" t="n">
         <v>0.18017</v>
       </c>
-      <c r="F20" s="1" t="n">
-        <v>0.17762</v>
+      <c r="G20" s="1" t="n">
+        <v>0.17675</v>
       </c>
     </row>
     <row r="21">
@@ -893,9 +956,12 @@
         <v>0.010012</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0.010012</v>
+        <v>0.010044</v>
       </c>
       <c r="F21" s="1" t="n">
+        <v>0.010044</v>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -915,9 +981,12 @@
         <v>1.0011</v>
       </c>
       <c r="E22" s="1" t="n">
+        <v>1.0007</v>
+      </c>
+      <c r="F22" s="1" t="n">
         <v>1.0033</v>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="G22" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -937,9 +1006,12 @@
         <v>5003.45</v>
       </c>
       <c r="E23" s="1" t="n">
+        <v>5006.75</v>
+      </c>
+      <c r="F23" s="1" t="n">
         <v>5012.25</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="G23" s="1" t="n">
         <v>5003.45</v>
       </c>
     </row>
@@ -959,10 +1031,13 @@
         <v>0.2633</v>
       </c>
       <c r="E24" s="1" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="F24" s="1" t="n">
         <v>0.2643</v>
       </c>
-      <c r="F24" s="1" t="n">
-        <v>0.2633</v>
+      <c r="G24" s="1" t="n">
+        <v>0.2632</v>
       </c>
     </row>
     <row r="25">
@@ -984,6 +1059,9 @@
         <v>2.917</v>
       </c>
       <c r="F25" s="1" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="G25" s="1" t="n">
         <v>2.899</v>
       </c>
     </row>
@@ -1003,9 +1081,12 @@
         <v>0.4031</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.4035</v>
+        <v>0.4096</v>
       </c>
       <c r="F26" s="1" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>0.3959</v>
       </c>
     </row>
@@ -1025,10 +1106,13 @@
         <v>0.884</v>
       </c>
       <c r="E27" s="1" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="F27" s="1" t="n">
         <v>0.885</v>
       </c>
-      <c r="F27" s="1" t="n">
-        <v>0.884</v>
+      <c r="G27" s="1" t="n">
+        <v>0.883</v>
       </c>
     </row>
     <row r="28">
@@ -1047,9 +1131,12 @@
         <v>1.339</v>
       </c>
       <c r="E28" s="1" t="n">
+        <v>1.338</v>
+      </c>
+      <c r="F28" s="1" t="n">
         <v>1.343</v>
       </c>
-      <c r="F28" s="1" t="n">
+      <c r="G28" s="1" t="n">
         <v>1.336</v>
       </c>
     </row>
@@ -1069,10 +1156,13 @@
         <v>9.148999999999999</v>
       </c>
       <c r="E29" s="1" t="n">
+        <v>9.145</v>
+      </c>
+      <c r="F29" s="1" t="n">
         <v>9.179</v>
       </c>
-      <c r="F29" s="1" t="n">
-        <v>9.148999999999999</v>
+      <c r="G29" s="1" t="n">
+        <v>9.145</v>
       </c>
     </row>
     <row r="30">
@@ -1091,10 +1181,13 @@
         <v>461.31</v>
       </c>
       <c r="E30" s="1" t="n">
+        <v>461.3</v>
+      </c>
+      <c r="F30" s="1" t="n">
         <v>463.35</v>
       </c>
-      <c r="F30" s="1" t="n">
-        <v>461.31</v>
+      <c r="G30" s="1" t="n">
+        <v>461.3</v>
       </c>
     </row>
     <row r="31">
@@ -1113,9 +1206,12 @@
         <v>9.696999999999999</v>
       </c>
       <c r="E31" s="1" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="F31" s="1" t="n">
         <v>9.728999999999999</v>
       </c>
-      <c r="F31" s="1" t="n">
+      <c r="G31" s="1" t="n">
         <v>9.696999999999999</v>
       </c>
     </row>
@@ -1135,10 +1231,13 @@
         <v>0.36306</v>
       </c>
       <c r="E32" s="1" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="F32" s="1" t="n">
         <v>0.36683</v>
       </c>
-      <c r="F32" s="1" t="n">
-        <v>0.36306</v>
+      <c r="G32" s="1" t="n">
+        <v>0.36285</v>
       </c>
     </row>
     <row r="33">
@@ -1157,10 +1256,13 @@
         <v>1.412</v>
       </c>
       <c r="E33" s="1" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="F33" s="1" t="n">
         <v>1.419</v>
       </c>
-      <c r="F33" s="1" t="n">
-        <v>1.412</v>
+      <c r="G33" s="1" t="n">
+        <v>1.411</v>
       </c>
     </row>
     <row r="34">
@@ -1179,9 +1281,12 @@
         <v>0.5926900000000001</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>0.59391</v>
+        <v>0.59693</v>
       </c>
       <c r="F34" s="1" t="n">
+        <v>0.59693</v>
+      </c>
+      <c r="G34" s="1" t="n">
         <v>0.5926900000000001</v>
       </c>
     </row>
@@ -1201,9 +1306,12 @@
         <v>1.2186</v>
       </c>
       <c r="E35" s="1" t="n">
+        <v>1.2205</v>
+      </c>
+      <c r="F35" s="1" t="n">
         <v>1.2228</v>
       </c>
-      <c r="F35" s="1" t="n">
+      <c r="G35" s="1" t="n">
         <v>1.2186</v>
       </c>
     </row>
@@ -1223,9 +1331,12 @@
         <v>80.27</v>
       </c>
       <c r="E36" s="1" t="n">
+        <v>80.37</v>
+      </c>
+      <c r="F36" s="1" t="n">
         <v>80.5</v>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="G36" s="1" t="n">
         <v>80.27</v>
       </c>
     </row>
@@ -1245,9 +1356,12 @@
         <v>0.1986</v>
       </c>
       <c r="E37" s="1" t="n">
+        <v>0.1996</v>
+      </c>
+      <c r="F37" s="1" t="n">
         <v>0.204</v>
       </c>
-      <c r="F37" s="1" t="n">
+      <c r="G37" s="1" t="n">
         <v>0.1977</v>
       </c>
     </row>
@@ -1267,9 +1381,12 @@
         <v>1.853</v>
       </c>
       <c r="E38" s="1" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="F38" s="1" t="n">
         <v>1.865</v>
       </c>
-      <c r="F38" s="1" t="n">
+      <c r="G38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -1289,9 +1406,12 @@
         <v>0.3245</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.3245</v>
+        <v>0.3283</v>
       </c>
       <c r="F39" s="1" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="G39" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -1311,10 +1431,13 @@
         <v>0.9115</v>
       </c>
       <c r="E40" s="1" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="F40" s="1" t="n">
         <v>0.9115</v>
       </c>
-      <c r="F40" s="1" t="n">
-        <v>0.9022</v>
+      <c r="G40" s="1" t="n">
+        <v>0.899</v>
       </c>
     </row>
     <row r="41">
@@ -1333,9 +1456,12 @@
         <v>0.7136</v>
       </c>
       <c r="E41" s="1" t="n">
+        <v>0.7147</v>
+      </c>
+      <c r="F41" s="1" t="n">
         <v>0.7149</v>
       </c>
-      <c r="F41" s="1" t="n">
+      <c r="G41" s="1" t="n">
         <v>0.7136</v>
       </c>
     </row>
@@ -1355,9 +1481,12 @@
         <v>0.0665</v>
       </c>
       <c r="E42" s="1" t="n">
+        <v>0.0665</v>
+      </c>
+      <c r="F42" s="1" t="n">
         <v>0.06769</v>
       </c>
-      <c r="F42" s="1" t="n">
+      <c r="G42" s="1" t="n">
         <v>0.0665</v>
       </c>
     </row>
@@ -1377,9 +1506,12 @@
         <v>113.08</v>
       </c>
       <c r="E43" s="1" t="n">
+        <v>113.06</v>
+      </c>
+      <c r="F43" s="1" t="n">
         <v>113.57</v>
       </c>
-      <c r="F43" s="1" t="n">
+      <c r="G43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -1399,9 +1531,12 @@
         <v>0.6617</v>
       </c>
       <c r="E44" s="1" t="n">
+        <v>0.6593</v>
+      </c>
+      <c r="F44" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="F44" s="1" t="n">
+      <c r="G44" s="1" t="n">
         <v>0.6578000000000001</v>
       </c>
     </row>
@@ -1421,9 +1556,12 @@
         <v>1.215</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>1.215</v>
+        <v>1.216</v>
       </c>
       <c r="F45" s="1" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="G45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -1443,10 +1581,13 @@
         <v>0.02383</v>
       </c>
       <c r="E46" s="1" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="F46" s="1" t="n">
         <v>0.02392</v>
       </c>
-      <c r="F46" s="1" t="n">
-        <v>0.02382</v>
+      <c r="G46" s="1" t="n">
+        <v>0.02376</v>
       </c>
     </row>
     <row r="47">
@@ -1465,10 +1606,13 @@
         <v>55.09</v>
       </c>
       <c r="E47" s="1" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="F47" s="1" t="n">
         <v>55.17</v>
       </c>
-      <c r="F47" s="1" t="n">
-        <v>55.06</v>
+      <c r="G47" s="1" t="n">
+        <v>55.04</v>
       </c>
     </row>
     <row r="48">
@@ -1487,9 +1631,12 @@
         <v>0.05994</v>
       </c>
       <c r="E48" s="1" t="n">
+        <v>0.06021</v>
+      </c>
+      <c r="F48" s="1" t="n">
         <v>0.06081</v>
       </c>
-      <c r="F48" s="1" t="n">
+      <c r="G48" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -1509,10 +1656,13 @@
         <v>0.1079</v>
       </c>
       <c r="E49" s="1" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="F49" s="1" t="n">
         <v>0.1082</v>
       </c>
-      <c r="F49" s="1" t="n">
-        <v>0.1079</v>
+      <c r="G49" s="1" t="n">
+        <v>0.1078</v>
       </c>
     </row>
     <row r="50">
@@ -1531,9 +1681,12 @@
         <v>0.01806</v>
       </c>
       <c r="E50" s="1" t="n">
+        <v>0.01808</v>
+      </c>
+      <c r="F50" s="1" t="n">
         <v>0.01815</v>
       </c>
-      <c r="F50" s="1" t="n">
+      <c r="G50" s="1" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -1553,10 +1706,13 @@
         <v>1.4659</v>
       </c>
       <c r="E51" s="1" t="n">
+        <v>1.4618</v>
+      </c>
+      <c r="F51" s="1" t="n">
         <v>1.4659</v>
       </c>
-      <c r="F51" s="1" t="n">
-        <v>1.4622</v>
+      <c r="G51" s="1" t="n">
+        <v>1.4618</v>
       </c>
     </row>
     <row r="52">
@@ -1575,9 +1731,12 @@
         <v>0.3594</v>
       </c>
       <c r="E52" s="1" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="F52" s="1" t="n">
         <v>0.3603</v>
       </c>
-      <c r="F52" s="1" t="n">
+      <c r="G52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -1597,9 +1756,12 @@
         <v>0.001946</v>
       </c>
       <c r="E53" s="1" t="n">
+        <v>0.001946</v>
+      </c>
+      <c r="F53" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="G53" s="1" t="n">
         <v>0.001946</v>
       </c>
     </row>
@@ -1619,9 +1781,12 @@
         <v>0.09540999999999999</v>
       </c>
       <c r="E54" s="1" t="n">
+        <v>0.09537</v>
+      </c>
+      <c r="F54" s="1" t="n">
         <v>0.09569</v>
       </c>
-      <c r="F54" s="1" t="n">
+      <c r="G54" s="1" t="n">
         <v>0.09524000000000001</v>
       </c>
     </row>
@@ -1641,9 +1806,12 @@
         <v>0.04017</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>0.04071</v>
+        <v>0.04084</v>
       </c>
       <c r="F55" s="1" t="n">
+        <v>0.04084</v>
+      </c>
+      <c r="G55" s="1" t="n">
         <v>0.04003</v>
       </c>
     </row>
@@ -1663,9 +1831,12 @@
         <v>0.29831</v>
       </c>
       <c r="E56" s="1" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="F56" s="1" t="n">
         <v>0.29861</v>
       </c>
-      <c r="F56" s="1" t="n">
+      <c r="G56" s="1" t="n">
         <v>0.29831</v>
       </c>
     </row>
@@ -1685,10 +1856,13 @@
         <v>0.00579</v>
       </c>
       <c r="E57" s="1" t="n">
+        <v>0.005752</v>
+      </c>
+      <c r="F57" s="1" t="n">
         <v>0.005824</v>
       </c>
-      <c r="F57" s="1" t="n">
-        <v>0.00579</v>
+      <c r="G57" s="1" t="n">
+        <v>0.005752</v>
       </c>
     </row>
     <row r="58">
@@ -1707,9 +1881,12 @@
         <v>4991.64</v>
       </c>
       <c r="E58" s="1" t="n">
+        <v>4993.56</v>
+      </c>
+      <c r="F58" s="1" t="n">
         <v>4998.37</v>
       </c>
-      <c r="F58" s="1" t="n">
+      <c r="G58" s="1" t="n">
         <v>4991.64</v>
       </c>
     </row>
@@ -1729,10 +1906,13 @@
         <v>0.4171</v>
       </c>
       <c r="E59" s="1" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="F59" s="1" t="n">
         <v>0.4246</v>
       </c>
-      <c r="F59" s="1" t="n">
-        <v>0.4171</v>
+      <c r="G59" s="1" t="n">
+        <v>0.4126</v>
       </c>
     </row>
     <row r="60">
@@ -1751,9 +1931,12 @@
         <v>0.04683</v>
       </c>
       <c r="E60" s="1" t="n">
+        <v>0.04677</v>
+      </c>
+      <c r="F60" s="1" t="n">
         <v>0.04683</v>
       </c>
-      <c r="F60" s="1" t="n">
+      <c r="G60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -1773,10 +1956,13 @@
         <v>0.21618</v>
       </c>
       <c r="E61" s="1" t="n">
+        <v>0.21568</v>
+      </c>
+      <c r="F61" s="1" t="n">
         <v>0.21708</v>
       </c>
-      <c r="F61" s="1" t="n">
-        <v>0.21618</v>
+      <c r="G61" s="1" t="n">
+        <v>0.21568</v>
       </c>
     </row>
     <row r="62">
@@ -1795,10 +1981,13 @@
         <v>0.1068</v>
       </c>
       <c r="E62" s="1" t="n">
+        <v>0.1065</v>
+      </c>
+      <c r="F62" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="F62" s="1" t="n">
-        <v>0.1068</v>
+      <c r="G62" s="1" t="n">
+        <v>0.1065</v>
       </c>
     </row>
     <row r="63">
@@ -1817,9 +2006,12 @@
         <v>0.7272</v>
       </c>
       <c r="E63" s="1" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="F63" s="1" t="n">
         <v>0.7301</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="G63" s="1" t="n">
         <v>0.7267</v>
       </c>
     </row>
@@ -1839,9 +2031,12 @@
         <v>0.1662</v>
       </c>
       <c r="E64" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="F64" s="1" t="n">
         <v>0.1667</v>
       </c>
-      <c r="F64" s="1" t="n">
+      <c r="G64" s="1" t="n">
         <v>0.166</v>
       </c>
     </row>
@@ -1861,9 +2056,12 @@
         <v>2.65</v>
       </c>
       <c r="E65" s="1" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="F65" s="1" t="n">
         <v>2.661</v>
       </c>
-      <c r="F65" s="1" t="n">
+      <c r="G65" s="1" t="n">
         <v>2.65</v>
       </c>
     </row>
@@ -1883,9 +2081,12 @@
         <v>0.0404</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>0.04048</v>
+        <v>0.04056</v>
       </c>
       <c r="F66" s="1" t="n">
+        <v>0.04056</v>
+      </c>
+      <c r="G66" s="1" t="n">
         <v>0.04018</v>
       </c>
     </row>
@@ -1905,9 +2106,12 @@
         <v>0.04249</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>0.04249</v>
+        <v>0.04254</v>
       </c>
       <c r="F67" s="1" t="n">
+        <v>0.04254</v>
+      </c>
+      <c r="G67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -1927,9 +2131,12 @@
         <v>3.959</v>
       </c>
       <c r="E68" s="1" t="n">
+        <v>3.956</v>
+      </c>
+      <c r="F68" s="1" t="n">
         <v>3.967</v>
       </c>
-      <c r="F68" s="1" t="n">
+      <c r="G68" s="1" t="n">
         <v>3.952</v>
       </c>
     </row>
@@ -1949,9 +2156,12 @@
         <v>0.1257</v>
       </c>
       <c r="E69" s="1" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="F69" s="1" t="n">
         <v>0.1261</v>
       </c>
-      <c r="F69" s="1" t="n">
+      <c r="G69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -1971,9 +2181,12 @@
         <v>6.207</v>
       </c>
       <c r="E70" s="1" t="n">
+        <v>6.204</v>
+      </c>
+      <c r="F70" s="1" t="n">
         <v>6.207</v>
       </c>
-      <c r="F70" s="1" t="n">
+      <c r="G70" s="1" t="n">
         <v>6.114</v>
       </c>
     </row>
@@ -1993,10 +2206,13 @@
         <v>0.04991</v>
       </c>
       <c r="E71" s="1" t="n">
+        <v>0.04989</v>
+      </c>
+      <c r="F71" s="1" t="n">
         <v>0.04999</v>
       </c>
-      <c r="F71" s="1" t="n">
-        <v>0.04991</v>
+      <c r="G71" s="1" t="n">
+        <v>0.04989</v>
       </c>
     </row>
     <row r="72">
@@ -2015,9 +2231,12 @@
         <v>0.004181</v>
       </c>
       <c r="E72" s="1" t="n">
+        <v>0.004163</v>
+      </c>
+      <c r="F72" s="1" t="n">
         <v>0.004181</v>
       </c>
-      <c r="F72" s="1" t="n">
+      <c r="G72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -2037,10 +2256,13 @@
         <v>6.018</v>
       </c>
       <c r="E73" s="1" t="n">
+        <v>5.975</v>
+      </c>
+      <c r="F73" s="1" t="n">
         <v>6.029</v>
       </c>
-      <c r="F73" s="1" t="n">
-        <v>6.001</v>
+      <c r="G73" s="1" t="n">
+        <v>5.975</v>
       </c>
     </row>
     <row r="74">
@@ -2059,10 +2281,13 @@
         <v>0.1629</v>
       </c>
       <c r="E74" s="1" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="F74" s="1" t="n">
         <v>0.1633</v>
       </c>
-      <c r="F74" s="1" t="n">
-        <v>0.1629</v>
+      <c r="G74" s="1" t="n">
+        <v>0.1624</v>
       </c>
     </row>
     <row r="75">
@@ -2081,10 +2306,13 @@
         <v>0.007281</v>
       </c>
       <c r="E75" s="1" t="n">
+        <v>0.007272</v>
+      </c>
+      <c r="F75" s="1" t="n">
         <v>0.007297</v>
       </c>
-      <c r="F75" s="1" t="n">
-        <v>0.007276</v>
+      <c r="G75" s="1" t="n">
+        <v>0.007272</v>
       </c>
     </row>
     <row r="76">
@@ -2103,9 +2331,12 @@
         <v>0.2095</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>0.2095</v>
+        <v>0.2102</v>
       </c>
       <c r="F76" s="1" t="n">
+        <v>0.2102</v>
+      </c>
+      <c r="G76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -2125,9 +2356,12 @@
         <v>0.005799</v>
       </c>
       <c r="E77" s="1" t="n">
+        <v>0.005802</v>
+      </c>
+      <c r="F77" s="1" t="n">
         <v>0.005826</v>
       </c>
-      <c r="F77" s="1" t="n">
+      <c r="G77" s="1" t="n">
         <v>0.005799</v>
       </c>
     </row>
@@ -2147,9 +2381,12 @@
         <v>0.1016</v>
       </c>
       <c r="E78" s="1" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="F78" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="F78" s="1" t="n">
+      <c r="G78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -2169,9 +2406,12 @@
         <v>0.006269</v>
       </c>
       <c r="E79" s="1" t="n">
+        <v>0.006261</v>
+      </c>
+      <c r="F79" s="1" t="n">
         <v>0.006292</v>
       </c>
-      <c r="F79" s="1" t="n">
+      <c r="G79" s="1" t="n">
         <v>0.006256</v>
       </c>
     </row>
@@ -2191,9 +2431,12 @@
         <v>33.47</v>
       </c>
       <c r="E80" s="1" t="n">
+        <v>33.36</v>
+      </c>
+      <c r="F80" s="1" t="n">
         <v>33.51</v>
       </c>
-      <c r="F80" s="1" t="n">
+      <c r="G80" s="1" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -2213,9 +2456,12 @@
         <v>0.04042</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>0.04043</v>
+        <v>0.0405</v>
       </c>
       <c r="F81" s="1" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="G81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -2235,9 +2481,12 @@
         <v>0.16688</v>
       </c>
       <c r="E82" s="1" t="n">
+        <v>0.16746</v>
+      </c>
+      <c r="F82" s="1" t="n">
         <v>0.1675</v>
       </c>
-      <c r="F82" s="1" t="n">
+      <c r="G82" s="1" t="n">
         <v>0.16688</v>
       </c>
     </row>
@@ -2257,9 +2506,12 @@
         <v>0.1032</v>
       </c>
       <c r="E83" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="F83" s="1" t="n">
         <v>0.1035</v>
       </c>
-      <c r="F83" s="1" t="n">
+      <c r="G83" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -2282,6 +2534,9 @@
         <v>0.08848</v>
       </c>
       <c r="F84" s="1" t="n">
+        <v>0.08848</v>
+      </c>
+      <c r="G84" s="1" t="n">
         <v>0.08810999999999999</v>
       </c>
     </row>
@@ -2301,10 +2556,13 @@
         <v>0.02322</v>
       </c>
       <c r="E85" s="1" t="n">
+        <v>0.02311</v>
+      </c>
+      <c r="F85" s="1" t="n">
         <v>0.02331</v>
       </c>
-      <c r="F85" s="1" t="n">
-        <v>0.02322</v>
+      <c r="G85" s="1" t="n">
+        <v>0.02311</v>
       </c>
     </row>
     <row r="86">
@@ -2323,9 +2581,12 @@
         <v>0.238</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>0.238</v>
+        <v>0.239</v>
       </c>
       <c r="F86" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="G86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -2345,9 +2606,12 @@
         <v>357.4</v>
       </c>
       <c r="E87" s="1" t="n">
+        <v>357.39</v>
+      </c>
+      <c r="F87" s="1" t="n">
         <v>357.4</v>
       </c>
-      <c r="F87" s="1" t="n">
+      <c r="G87" s="1" t="n">
         <v>355.75</v>
       </c>
     </row>
@@ -2367,9 +2631,12 @@
         <v>0.00344</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>0.00344</v>
+        <v>0.00345</v>
       </c>
       <c r="F88" s="1" t="n">
+        <v>0.00345</v>
+      </c>
+      <c r="G88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -2389,9 +2656,12 @@
         <v>8.272</v>
       </c>
       <c r="E89" s="1" t="n">
+        <v>8.276999999999999</v>
+      </c>
+      <c r="F89" s="1" t="n">
         <v>8.301</v>
       </c>
-      <c r="F89" s="1" t="n">
+      <c r="G89" s="1" t="n">
         <v>8.272</v>
       </c>
     </row>
@@ -2411,9 +2681,12 @@
         <v>0.00591</v>
       </c>
       <c r="E90" s="1" t="n">
+        <v>0.005916</v>
+      </c>
+      <c r="F90" s="1" t="n">
         <v>0.005945</v>
       </c>
-      <c r="F90" s="1" t="n">
+      <c r="G90" s="1" t="n">
         <v>0.00591</v>
       </c>
     </row>
@@ -2433,10 +2706,13 @@
         <v>0.06891</v>
       </c>
       <c r="E91" s="1" t="n">
+        <v>0.06841999999999999</v>
+      </c>
+      <c r="F91" s="1" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="F91" s="1" t="n">
-        <v>0.06884999999999999</v>
+      <c r="G91" s="1" t="n">
+        <v>0.06841999999999999</v>
       </c>
     </row>
     <row r="92">
@@ -2455,10 +2731,13 @@
         <v>0.02883</v>
       </c>
       <c r="E92" s="1" t="n">
+        <v>0.02869</v>
+      </c>
+      <c r="F92" s="1" t="n">
         <v>0.02894</v>
       </c>
-      <c r="F92" s="1" t="n">
-        <v>0.02879</v>
+      <c r="G92" s="1" t="n">
+        <v>0.02869</v>
       </c>
     </row>
     <row r="93">
@@ -2477,9 +2756,12 @@
         <v>5.159</v>
       </c>
       <c r="E93" s="1" t="n">
+        <v>5.183</v>
+      </c>
+      <c r="F93" s="1" t="n">
         <v>5.202</v>
       </c>
-      <c r="F93" s="1" t="n">
+      <c r="G93" s="1" t="n">
         <v>5.159</v>
       </c>
     </row>
@@ -2502,6 +2784,9 @@
         <v>0.000228</v>
       </c>
       <c r="F94" s="1" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="G94" s="1" t="n">
         <v>0.000226</v>
       </c>
     </row>
@@ -2521,9 +2806,12 @@
         <v>0.9223</v>
       </c>
       <c r="E95" s="1" t="n">
+        <v>0.9211</v>
+      </c>
+      <c r="F95" s="1" t="n">
         <v>0.9241</v>
       </c>
-      <c r="F95" s="1" t="n">
+      <c r="G95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -2543,9 +2831,12 @@
         <v>2.0658</v>
       </c>
       <c r="E96" s="1" t="n">
+        <v>2.0648</v>
+      </c>
+      <c r="F96" s="1" t="n">
         <v>2.0774</v>
       </c>
-      <c r="F96" s="1" t="n">
+      <c r="G96" s="1" t="n">
         <v>2.0598</v>
       </c>
     </row>
@@ -2565,10 +2856,13 @@
         <v>0.3706</v>
       </c>
       <c r="E97" s="1" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="F97" s="1" t="n">
         <v>0.3711</v>
       </c>
-      <c r="F97" s="1" t="n">
-        <v>0.369</v>
+      <c r="G97" s="1" t="n">
+        <v>0.3686</v>
       </c>
     </row>
     <row r="98">
@@ -2587,9 +2881,12 @@
         <v>1.615</v>
       </c>
       <c r="E98" s="1" t="n">
+        <v>1.616</v>
+      </c>
+      <c r="F98" s="1" t="n">
         <v>1.618</v>
       </c>
-      <c r="F98" s="1" t="n">
+      <c r="G98" s="1" t="n">
         <v>1.613</v>
       </c>
     </row>
@@ -2609,9 +2906,12 @@
         <v>0.2366</v>
       </c>
       <c r="E99" s="1" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="F99" s="1" t="n">
         <v>0.2368</v>
       </c>
-      <c r="F99" s="1" t="n">
+      <c r="G99" s="1" t="n">
         <v>0.2351</v>
       </c>
     </row>
@@ -2631,9 +2931,12 @@
         <v>0.13665</v>
       </c>
       <c r="E100" s="1" t="n">
+        <v>0.13655</v>
+      </c>
+      <c r="F100" s="1" t="n">
         <v>0.13665</v>
       </c>
-      <c r="F100" s="1" t="n">
+      <c r="G100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -2653,9 +2956,12 @@
         <v>0.07115</v>
       </c>
       <c r="E101" s="1" t="n">
+        <v>0.07094</v>
+      </c>
+      <c r="F101" s="1" t="n">
         <v>0.07115</v>
       </c>
-      <c r="F101" s="1" t="n">
+      <c r="G101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -2675,9 +2981,12 @@
         <v>0.001085</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>0.001085</v>
+        <v>0.0010875</v>
       </c>
       <c r="F102" s="1" t="n">
+        <v>0.0010875</v>
+      </c>
+      <c r="G102" s="1" t="n">
         <v>0.001084</v>
       </c>
     </row>
@@ -2697,10 +3006,13 @@
         <v>0.003409</v>
       </c>
       <c r="E103" s="1" t="n">
+        <v>0.003404</v>
+      </c>
+      <c r="F103" s="1" t="n">
         <v>0.003424</v>
       </c>
-      <c r="F103" s="1" t="n">
-        <v>0.003409</v>
+      <c r="G103" s="1" t="n">
+        <v>0.003404</v>
       </c>
     </row>
     <row r="104">
@@ -2719,10 +3031,13 @@
         <v>0.27584</v>
       </c>
       <c r="E104" s="1" t="n">
+        <v>0.27548</v>
+      </c>
+      <c r="F104" s="1" t="n">
         <v>0.27751</v>
       </c>
-      <c r="F104" s="1" t="n">
-        <v>0.27584</v>
+      <c r="G104" s="1" t="n">
+        <v>0.27548</v>
       </c>
     </row>
     <row r="105">
@@ -2741,9 +3056,12 @@
         <v>0.01243</v>
       </c>
       <c r="E105" s="1" t="n">
+        <v>0.01254</v>
+      </c>
+      <c r="F105" s="1" t="n">
         <v>0.01257</v>
       </c>
-      <c r="F105" s="1" t="n">
+      <c r="G105" s="1" t="n">
         <v>0.01243</v>
       </c>
     </row>
@@ -2763,10 +3081,13 @@
         <v>0.13413</v>
       </c>
       <c r="E106" s="1" t="n">
+        <v>0.13329</v>
+      </c>
+      <c r="F106" s="1" t="n">
         <v>0.13569</v>
       </c>
-      <c r="F106" s="1" t="n">
-        <v>0.13413</v>
+      <c r="G106" s="1" t="n">
+        <v>0.13329</v>
       </c>
     </row>
     <row r="107">
@@ -2785,9 +3106,12 @@
         <v>0.3493</v>
       </c>
       <c r="E107" s="1" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="F107" s="1" t="n">
         <v>0.3496</v>
       </c>
-      <c r="F107" s="1" t="n">
+      <c r="G107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -2807,9 +3131,12 @@
         <v>0.1429</v>
       </c>
       <c r="E108" s="1" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="F108" s="1" t="n">
         <v>0.1436</v>
       </c>
-      <c r="F108" s="1" t="n">
+      <c r="G108" s="1" t="n">
         <v>0.1426</v>
       </c>
     </row>
@@ -2832,6 +3159,9 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="F109" s="1" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="G109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -2851,10 +3181,13 @@
         <v>0.01624</v>
       </c>
       <c r="E110" s="1" t="n">
+        <v>0.016223</v>
+      </c>
+      <c r="F110" s="1" t="n">
         <v>0.016308</v>
       </c>
-      <c r="F110" s="1" t="n">
-        <v>0.01624</v>
+      <c r="G110" s="1" t="n">
+        <v>0.016223</v>
       </c>
     </row>
     <row r="111">
@@ -2873,9 +3206,12 @@
         <v>0.038015</v>
       </c>
       <c r="E111" s="1" t="n">
+        <v>0.038268</v>
+      </c>
+      <c r="F111" s="1" t="n">
         <v>0.038335</v>
       </c>
-      <c r="F111" s="1" t="n">
+      <c r="G111" s="1" t="n">
         <v>0.03774</v>
       </c>
     </row>
@@ -2895,9 +3231,12 @@
         <v>0.11952</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>0.11959</v>
+        <v>0.12031</v>
       </c>
       <c r="F112" s="1" t="n">
+        <v>0.12031</v>
+      </c>
+      <c r="G112" s="1" t="n">
         <v>0.11926</v>
       </c>
     </row>
@@ -2917,9 +3256,12 @@
         <v>0.0945</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>0.09465</v>
+        <v>0.09517</v>
       </c>
       <c r="F113" s="1" t="n">
+        <v>0.09517</v>
+      </c>
+      <c r="G113" s="1" t="n">
         <v>0.09426</v>
       </c>
     </row>
@@ -2939,9 +3281,12 @@
         <v>0.12895</v>
       </c>
       <c r="E114" s="1" t="n">
+        <v>0.12904</v>
+      </c>
+      <c r="F114" s="1" t="n">
         <v>0.1299</v>
       </c>
-      <c r="F114" s="1" t="n">
+      <c r="G114" s="1" t="n">
         <v>0.12895</v>
       </c>
     </row>
@@ -2961,9 +3306,12 @@
         <v>0.2645</v>
       </c>
       <c r="E115" s="1" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="F115" s="1" t="n">
         <v>0.2656</v>
       </c>
-      <c r="F115" s="1" t="n">
+      <c r="G115" s="1" t="n">
         <v>0.264</v>
       </c>
     </row>
@@ -2983,10 +3331,13 @@
         <v>0.05223</v>
       </c>
       <c r="E116" s="1" t="n">
+        <v>0.04943</v>
+      </c>
+      <c r="F116" s="1" t="n">
         <v>0.0529</v>
       </c>
-      <c r="F116" s="1" t="n">
-        <v>0.05208</v>
+      <c r="G116" s="1" t="n">
+        <v>0.04943</v>
       </c>
     </row>
     <row r="117">
@@ -3005,9 +3356,12 @@
         <v>0.0914</v>
       </c>
       <c r="E117" s="1" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="F117" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="F117" s="1" t="n">
+      <c r="G117" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -3027,9 +3381,12 @@
         <v>0.05509</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>0.05545</v>
+        <v>0.05563</v>
       </c>
       <c r="F118" s="1" t="n">
+        <v>0.05563</v>
+      </c>
+      <c r="G118" s="1" t="n">
         <v>0.05509</v>
       </c>
     </row>
@@ -3049,10 +3406,13 @@
         <v>0.01511</v>
       </c>
       <c r="E119" s="1" t="n">
+        <v>0.01509</v>
+      </c>
+      <c r="F119" s="1" t="n">
         <v>0.01515</v>
       </c>
-      <c r="F119" s="1" t="n">
-        <v>0.01511</v>
+      <c r="G119" s="1" t="n">
+        <v>0.01509</v>
       </c>
     </row>
     <row r="120">
@@ -3071,9 +3431,12 @@
         <v>3.055</v>
       </c>
       <c r="E120" s="1" t="n">
+        <v>3.054</v>
+      </c>
+      <c r="F120" s="1" t="n">
         <v>3.06</v>
       </c>
-      <c r="F120" s="1" t="n">
+      <c r="G120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -3093,9 +3456,12 @@
         <v>1.852</v>
       </c>
       <c r="E121" s="1" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F121" s="1" t="n">
         <v>1.855</v>
       </c>
-      <c r="F121" s="1" t="n">
+      <c r="G121" s="1" t="n">
         <v>1.85</v>
       </c>
     </row>
@@ -3115,9 +3481,12 @@
         <v>1.2934</v>
       </c>
       <c r="E122" s="1" t="n">
+        <v>1.2946</v>
+      </c>
+      <c r="F122" s="1" t="n">
         <v>1.2965</v>
       </c>
-      <c r="F122" s="1" t="n">
+      <c r="G122" s="1" t="n">
         <v>1.2934</v>
       </c>
     </row>
@@ -3137,10 +3506,13 @@
         <v>0.318</v>
       </c>
       <c r="E123" s="1" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="F123" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="F123" s="1" t="n">
-        <v>0.318</v>
+      <c r="G123" s="1" t="n">
+        <v>0.317</v>
       </c>
     </row>
     <row r="124">
@@ -3159,9 +3531,12 @@
         <v>0.12363</v>
       </c>
       <c r="E124" s="1" t="n">
+        <v>0.12346</v>
+      </c>
+      <c r="F124" s="1" t="n">
         <v>0.12506</v>
       </c>
-      <c r="F124" s="1" t="n">
+      <c r="G124" s="1" t="n">
         <v>0.12242</v>
       </c>
     </row>
@@ -3181,9 +3556,12 @@
         <v>0.008263</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>0.008263</v>
+        <v>0.008459</v>
       </c>
       <c r="F125" s="1" t="n">
+        <v>0.008459</v>
+      </c>
+      <c r="G125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -3203,9 +3581,12 @@
         <v>0.01582</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>0.01582</v>
+        <v>0.01587</v>
       </c>
       <c r="F126" s="1" t="n">
+        <v>0.01587</v>
+      </c>
+      <c r="G126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -3225,9 +3606,12 @@
         <v>0.04468</v>
       </c>
       <c r="E127" s="1" t="n">
+        <v>0.04466</v>
+      </c>
+      <c r="F127" s="1" t="n">
         <v>0.04468</v>
       </c>
-      <c r="F127" s="1" t="n">
+      <c r="G127" s="1" t="n">
         <v>0.04402</v>
       </c>
     </row>
@@ -3247,9 +3631,12 @@
         <v>0.04618</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>0.04618</v>
+        <v>0.04645</v>
       </c>
       <c r="F128" s="1" t="n">
+        <v>0.04645</v>
+      </c>
+      <c r="G128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -3269,9 +3656,12 @@
         <v>0.09544999999999999</v>
       </c>
       <c r="E129" s="1" t="n">
+        <v>0.09563000000000001</v>
+      </c>
+      <c r="F129" s="1" t="n">
         <v>0.09635000000000001</v>
       </c>
-      <c r="F129" s="1" t="n">
+      <c r="G129" s="1" t="n">
         <v>0.09544999999999999</v>
       </c>
     </row>
@@ -3291,9 +3681,12 @@
         <v>0.09877</v>
       </c>
       <c r="E130" s="1" t="n">
+        <v>0.09891999999999999</v>
+      </c>
+      <c r="F130" s="1" t="n">
         <v>0.09927</v>
       </c>
-      <c r="F130" s="1" t="n">
+      <c r="G130" s="1" t="n">
         <v>0.09877</v>
       </c>
     </row>
@@ -3313,9 +3706,12 @@
         <v>0.1651</v>
       </c>
       <c r="E131" s="1" t="n">
+        <v>0.16522</v>
+      </c>
+      <c r="F131" s="1" t="n">
         <v>0.16577</v>
       </c>
-      <c r="F131" s="1" t="n">
+      <c r="G131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -3335,9 +3731,12 @@
         <v>0.01693</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>0.01693</v>
+        <v>0.01694</v>
       </c>
       <c r="F132" s="1" t="n">
+        <v>0.01694</v>
+      </c>
+      <c r="G132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -3360,6 +3759,9 @@
         <v>0.06655</v>
       </c>
       <c r="F133" s="1" t="n">
+        <v>0.06655</v>
+      </c>
+      <c r="G133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -3379,9 +3781,12 @@
         <v>0.3014</v>
       </c>
       <c r="E134" s="1" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="F134" s="1" t="n">
         <v>0.3023</v>
       </c>
-      <c r="F134" s="1" t="n">
+      <c r="G134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -3401,10 +3806,13 @@
         <v>0.0451</v>
       </c>
       <c r="E135" s="1" t="n">
+        <v>0.04508</v>
+      </c>
+      <c r="F135" s="1" t="n">
         <v>0.04515</v>
       </c>
-      <c r="F135" s="1" t="n">
-        <v>0.0451</v>
+      <c r="G135" s="1" t="n">
+        <v>0.04508</v>
       </c>
     </row>
     <row r="136">
@@ -3423,9 +3831,12 @@
         <v>0.781</v>
       </c>
       <c r="E136" s="1" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="F136" s="1" t="n">
         <v>0.783</v>
       </c>
-      <c r="F136" s="1" t="n">
+      <c r="G136" s="1" t="n">
         <v>0.781</v>
       </c>
     </row>
@@ -3445,9 +3856,12 @@
         <v>0.1162</v>
       </c>
       <c r="E137" s="1" t="n">
+        <v>0.1162</v>
+      </c>
+      <c r="F137" s="1" t="n">
         <v>0.1168</v>
       </c>
-      <c r="F137" s="1" t="n">
+      <c r="G137" s="1" t="n">
         <v>0.1162</v>
       </c>
     </row>
@@ -3467,9 +3881,12 @@
         <v>0.14571</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>0.146</v>
+        <v>0.14641</v>
       </c>
       <c r="F138" s="1" t="n">
+        <v>0.14641</v>
+      </c>
+      <c r="G138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -3489,10 +3906,13 @@
         <v>0.05713</v>
       </c>
       <c r="E139" s="1" t="n">
+        <v>0.05699</v>
+      </c>
+      <c r="F139" s="1" t="n">
         <v>0.05719</v>
       </c>
-      <c r="F139" s="1" t="n">
-        <v>0.05713</v>
+      <c r="G139" s="1" t="n">
+        <v>0.05699</v>
       </c>
     </row>
     <row r="140">
@@ -3511,10 +3931,13 @@
         <v>0.00728</v>
       </c>
       <c r="E140" s="1" t="n">
+        <v>0.007273</v>
+      </c>
+      <c r="F140" s="1" t="n">
         <v>0.007295</v>
       </c>
-      <c r="F140" s="1" t="n">
-        <v>0.007274</v>
+      <c r="G140" s="1" t="n">
+        <v>0.007273</v>
       </c>
     </row>
     <row r="141">
@@ -3533,10 +3956,13 @@
         <v>0.0958</v>
       </c>
       <c r="E141" s="1" t="n">
+        <v>0.09569</v>
+      </c>
+      <c r="F141" s="1" t="n">
         <v>0.09601</v>
       </c>
-      <c r="F141" s="1" t="n">
-        <v>0.0958</v>
+      <c r="G141" s="1" t="n">
+        <v>0.09569</v>
       </c>
     </row>
     <row r="142">
@@ -3555,9 +3981,12 @@
         <v>0.08323</v>
       </c>
       <c r="E142" s="1" t="n">
+        <v>0.08336</v>
+      </c>
+      <c r="F142" s="1" t="n">
         <v>0.08348</v>
       </c>
-      <c r="F142" s="1" t="n">
+      <c r="G142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -3577,9 +4006,12 @@
         <v>0.00851</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>0.00852</v>
+        <v>0.00856</v>
       </c>
       <c r="F143" s="1" t="n">
+        <v>0.00856</v>
+      </c>
+      <c r="G143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -3599,10 +4031,13 @@
         <v>0.07267999999999999</v>
       </c>
       <c r="E144" s="1" t="n">
+        <v>0.07251000000000001</v>
+      </c>
+      <c r="F144" s="1" t="n">
         <v>0.07288</v>
       </c>
-      <c r="F144" s="1" t="n">
-        <v>0.0726</v>
+      <c r="G144" s="1" t="n">
+        <v>0.07251000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -3621,9 +4056,12 @@
         <v>0.4297</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>0.4303</v>
+        <v>0.4305</v>
       </c>
       <c r="F145" s="1" t="n">
+        <v>0.4305</v>
+      </c>
+      <c r="G145" s="1" t="n">
         <v>0.4297</v>
       </c>
     </row>
@@ -3643,10 +4081,13 @@
         <v>0.03259</v>
       </c>
       <c r="E146" s="1" t="n">
+        <v>0.03246</v>
+      </c>
+      <c r="F146" s="1" t="n">
         <v>0.03276</v>
       </c>
-      <c r="F146" s="1" t="n">
-        <v>0.03252</v>
+      <c r="G146" s="1" t="n">
+        <v>0.03246</v>
       </c>
     </row>
     <row r="147">
@@ -3665,9 +4106,12 @@
         <v>390.43</v>
       </c>
       <c r="E147" s="1" t="n">
+        <v>390.52</v>
+      </c>
+      <c r="F147" s="1" t="n">
         <v>390.55</v>
       </c>
-      <c r="F147" s="1" t="n">
+      <c r="G147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -3687,9 +4131,12 @@
         <v>0.03293</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>0.033</v>
+        <v>0.0333</v>
       </c>
       <c r="F148" s="1" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="G148" s="1" t="n">
         <v>0.0329</v>
       </c>
     </row>
@@ -3709,10 +4156,13 @@
         <v>0.05298</v>
       </c>
       <c r="E149" s="1" t="n">
+        <v>0.05289</v>
+      </c>
+      <c r="F149" s="1" t="n">
         <v>0.05322</v>
       </c>
-      <c r="F149" s="1" t="n">
-        <v>0.05298</v>
+      <c r="G149" s="1" t="n">
+        <v>0.05289</v>
       </c>
     </row>
     <row r="150">
@@ -3731,10 +4181,13 @@
         <v>0.0004407</v>
       </c>
       <c r="E150" s="1" t="n">
+        <v>0.000439</v>
+      </c>
+      <c r="F150" s="1" t="n">
         <v>0.000443</v>
       </c>
-      <c r="F150" s="1" t="n">
-        <v>0.0004396</v>
+      <c r="G150" s="1" t="n">
+        <v>0.000439</v>
       </c>
     </row>
     <row r="151">
@@ -3753,9 +4206,12 @@
         <v>0.02178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>0.02183</v>
+        <v>0.02189</v>
       </c>
       <c r="F151" s="1" t="n">
+        <v>0.02189</v>
+      </c>
+      <c r="G151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -3775,10 +4231,13 @@
         <v>0.001783</v>
       </c>
       <c r="E152" s="1" t="n">
+        <v>0.001774</v>
+      </c>
+      <c r="F152" s="1" t="n">
         <v>0.001783</v>
       </c>
-      <c r="F152" s="1" t="n">
-        <v>0.001781</v>
+      <c r="G152" s="1" t="n">
+        <v>0.001774</v>
       </c>
     </row>
     <row r="153">
@@ -3797,10 +4256,13 @@
         <v>6.2e-06</v>
       </c>
       <c r="E153" s="1" t="n">
+        <v>6.1e-06</v>
+      </c>
+      <c r="F153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
-      <c r="F153" s="1" t="n">
-        <v>6.2e-06</v>
+      <c r="G153" s="1" t="n">
+        <v>6.1e-06</v>
       </c>
     </row>
     <row r="154">
@@ -3819,9 +4281,12 @@
         <v>0.1598</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>0.1598</v>
+        <v>0.16</v>
       </c>
       <c r="F154" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -3841,9 +4306,12 @@
         <v>0.03755</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>0.03765</v>
+        <v>0.03768</v>
       </c>
       <c r="F155" s="1" t="n">
+        <v>0.03768</v>
+      </c>
+      <c r="G155" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -3863,10 +4331,13 @@
         <v>0.005401</v>
       </c>
       <c r="E156" s="1" t="n">
+        <v>0.005368</v>
+      </c>
+      <c r="F156" s="1" t="n">
         <v>0.005402</v>
       </c>
-      <c r="F156" s="1" t="n">
-        <v>0.005379</v>
+      <c r="G156" s="1" t="n">
+        <v>0.005368</v>
       </c>
     </row>
     <row r="157">
@@ -3885,9 +4356,12 @@
         <v>0.02277</v>
       </c>
       <c r="E157" s="1" t="n">
+        <v>0.02281</v>
+      </c>
+      <c r="F157" s="1" t="n">
         <v>0.02284</v>
       </c>
-      <c r="F157" s="1" t="n">
+      <c r="G157" s="1" t="n">
         <v>0.02277</v>
       </c>
     </row>
@@ -3907,9 +4381,12 @@
         <v>1.09</v>
       </c>
       <c r="E158" s="1" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="F158" s="1" t="n">
         <v>1.09</v>
       </c>
-      <c r="F158" s="1" t="n">
+      <c r="G158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -3929,9 +4406,12 @@
         <v>2.554</v>
       </c>
       <c r="E159" s="1" t="n">
+        <v>2.551</v>
+      </c>
+      <c r="F159" s="1" t="n">
         <v>2.558</v>
       </c>
-      <c r="F159" s="1" t="n">
+      <c r="G159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -3951,9 +4431,12 @@
         <v>4.858</v>
       </c>
       <c r="E160" s="1" t="n">
+        <v>4.842</v>
+      </c>
+      <c r="F160" s="1" t="n">
         <v>4.858</v>
       </c>
-      <c r="F160" s="1" t="n">
+      <c r="G160" s="1" t="n">
         <v>4.836</v>
       </c>
     </row>
@@ -3973,9 +4456,12 @@
         <v>0.1596</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>0.1596</v>
+        <v>0.1599</v>
       </c>
       <c r="F161" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="G161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -3995,9 +4481,12 @@
         <v>0.20754</v>
       </c>
       <c r="E162" s="1" t="n">
+        <v>0.20645</v>
+      </c>
+      <c r="F162" s="1" t="n">
         <v>0.20754</v>
       </c>
-      <c r="F162" s="1" t="n">
+      <c r="G162" s="1" t="n">
         <v>0.20584</v>
       </c>
     </row>
@@ -4017,9 +4506,12 @@
         <v>0.03936</v>
       </c>
       <c r="E163" s="1" t="n">
+        <v>0.03931</v>
+      </c>
+      <c r="F163" s="1" t="n">
         <v>0.03939</v>
       </c>
-      <c r="F163" s="1" t="n">
+      <c r="G163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -4042,6 +4534,9 @@
         <v>0.06308999999999999</v>
       </c>
       <c r="F164" s="1" t="n">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="G164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -4061,9 +4556,12 @@
         <v>0.355</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>0.355</v>
+        <v>0.3557</v>
       </c>
       <c r="F165" s="1" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="G165" s="1" t="n">
         <v>0.3525</v>
       </c>
     </row>
@@ -4083,9 +4581,12 @@
         <v>139.1</v>
       </c>
       <c r="E166" s="1" t="n">
+        <v>139.14</v>
+      </c>
+      <c r="F166" s="1" t="n">
         <v>139.27</v>
       </c>
-      <c r="F166" s="1" t="n">
+      <c r="G166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -4105,9 +4606,12 @@
         <v>0.0006431</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>0.0006477</v>
+        <v>0.0006533</v>
       </c>
       <c r="F167" s="1" t="n">
+        <v>0.0006533</v>
+      </c>
+      <c r="G167" s="1" t="n">
         <v>0.0006431</v>
       </c>
     </row>
@@ -4127,10 +4631,13 @@
         <v>0.01678</v>
       </c>
       <c r="E168" s="1" t="n">
+        <v>0.01656</v>
+      </c>
+      <c r="F168" s="1" t="n">
         <v>0.01678</v>
       </c>
-      <c r="F168" s="1" t="n">
-        <v>0.01664</v>
+      <c r="G168" s="1" t="n">
+        <v>0.01656</v>
       </c>
     </row>
     <row r="169">
@@ -4149,9 +4656,12 @@
         <v>0.04793</v>
       </c>
       <c r="E169" s="1" t="n">
+        <v>0.04793</v>
+      </c>
+      <c r="F169" s="1" t="n">
         <v>0.04798</v>
       </c>
-      <c r="F169" s="1" t="n">
+      <c r="G169" s="1" t="n">
         <v>0.04788</v>
       </c>
     </row>
@@ -4171,9 +4681,12 @@
         <v>4.279</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>4.279</v>
+        <v>4.297</v>
       </c>
       <c r="F170" s="1" t="n">
+        <v>4.297</v>
+      </c>
+      <c r="G170" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -4193,9 +4706,12 @@
         <v>0.03874</v>
       </c>
       <c r="E171" s="1" t="n">
+        <v>0.03862</v>
+      </c>
+      <c r="F171" s="1" t="n">
         <v>0.03874</v>
       </c>
-      <c r="F171" s="1" t="n">
+      <c r="G171" s="1" t="n">
         <v>0.03846</v>
       </c>
     </row>
@@ -4215,10 +4731,13 @@
         <v>0.0431</v>
       </c>
       <c r="E172" s="1" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="F172" s="1" t="n">
         <v>0.0431</v>
       </c>
-      <c r="F172" s="1" t="n">
-        <v>0.0427</v>
+      <c r="G172" s="1" t="n">
+        <v>0.0426</v>
       </c>
     </row>
     <row r="173">
@@ -4237,9 +4756,12 @@
         <v>0.024201</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>0.024201</v>
+        <v>0.024277</v>
       </c>
       <c r="F173" s="1" t="n">
+        <v>0.024277</v>
+      </c>
+      <c r="G173" s="1" t="n">
         <v>0.02382</v>
       </c>
     </row>
@@ -4259,9 +4781,12 @@
         <v>1.0708</v>
       </c>
       <c r="E174" s="1" t="n">
+        <v>1.0704</v>
+      </c>
+      <c r="F174" s="1" t="n">
         <v>1.0708</v>
       </c>
-      <c r="F174" s="1" t="n">
+      <c r="G174" s="1" t="n">
         <v>1.0704</v>
       </c>
     </row>
@@ -4281,10 +4806,13 @@
         <v>0.028647</v>
       </c>
       <c r="E175" s="1" t="n">
+        <v>0.028636</v>
+      </c>
+      <c r="F175" s="1" t="n">
         <v>0.028967</v>
       </c>
-      <c r="F175" s="1" t="n">
-        <v>0.028647</v>
+      <c r="G175" s="1" t="n">
+        <v>0.028636</v>
       </c>
     </row>
     <row r="176">
@@ -4303,9 +4831,12 @@
         <v>0.0218</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>0.0218</v>
+        <v>0.02188</v>
       </c>
       <c r="F176" s="1" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="G176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -4328,6 +4859,9 @@
         <v>0.5444</v>
       </c>
       <c r="F177" s="1" t="n">
+        <v>0.5444</v>
+      </c>
+      <c r="G177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -4347,9 +4881,12 @@
         <v>0.08261</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>0.08268</v>
+        <v>0.08276</v>
       </c>
       <c r="F178" s="1" t="n">
+        <v>0.08276</v>
+      </c>
+      <c r="G178" s="1" t="n">
         <v>0.08255999999999999</v>
       </c>
     </row>
@@ -4369,9 +4906,12 @@
         <v>0.02133</v>
       </c>
       <c r="E179" s="1" t="n">
+        <v>0.02132</v>
+      </c>
+      <c r="F179" s="1" t="n">
         <v>0.02133</v>
       </c>
-      <c r="F179" s="1" t="n">
+      <c r="G179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -4391,9 +4931,12 @@
         <v>0.27127</v>
       </c>
       <c r="E180" s="1" t="n">
+        <v>0.27058</v>
+      </c>
+      <c r="F180" s="1" t="n">
         <v>0.27127</v>
       </c>
-      <c r="F180" s="1" t="n">
+      <c r="G180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -4416,6 +4959,9 @@
         <v>0.0042</v>
       </c>
       <c r="F181" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="G181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -4435,9 +4981,12 @@
         <v>0.07981000000000001</v>
       </c>
       <c r="E182" s="1" t="n">
+        <v>0.07976</v>
+      </c>
+      <c r="F182" s="1" t="n">
         <v>0.07981000000000001</v>
       </c>
-      <c r="F182" s="1" t="n">
+      <c r="G182" s="1" t="n">
         <v>0.07931000000000001</v>
       </c>
     </row>
@@ -4457,9 +5006,12 @@
         <v>0.02346</v>
       </c>
       <c r="E183" s="1" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="F183" s="1" t="n">
         <v>0.02357</v>
       </c>
-      <c r="F183" s="1" t="n">
+      <c r="G183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -4479,9 +5031,12 @@
         <v>6.963e-05</v>
       </c>
       <c r="E184" s="1" t="n">
+        <v>6.965e-05</v>
+      </c>
+      <c r="F184" s="1" t="n">
         <v>6.981e-05</v>
       </c>
-      <c r="F184" s="1" t="n">
+      <c r="G184" s="1" t="n">
         <v>6.957e-05</v>
       </c>
     </row>
@@ -4501,9 +5056,12 @@
         <v>0.02127</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>0.02127</v>
+        <v>0.02131</v>
       </c>
       <c r="F185" s="1" t="n">
+        <v>0.02131</v>
+      </c>
+      <c r="G185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -4523,10 +5081,13 @@
         <v>0.01626</v>
       </c>
       <c r="E186" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="F186" s="1" t="n">
         <v>0.01632</v>
       </c>
-      <c r="F186" s="1" t="n">
-        <v>0.01626</v>
+      <c r="G186" s="1" t="n">
+        <v>0.01623</v>
       </c>
     </row>
     <row r="187">
@@ -4545,9 +5106,12 @@
         <v>0.976</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>0.976</v>
+        <v>0.978</v>
       </c>
       <c r="F187" s="1" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="G187" s="1" t="n">
         <v>0.971</v>
       </c>
     </row>
@@ -4570,6 +5134,9 @@
         <v>0.0239</v>
       </c>
       <c r="F188" s="1" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="G188" s="1" t="n">
         <v>0.0237</v>
       </c>
     </row>
@@ -4589,10 +5156,13 @@
         <v>1.863</v>
       </c>
       <c r="E189" s="1" t="n">
+        <v>1.8609</v>
+      </c>
+      <c r="F189" s="1" t="n">
         <v>1.8658</v>
       </c>
-      <c r="F189" s="1" t="n">
-        <v>1.8627</v>
+      <c r="G189" s="1" t="n">
+        <v>1.8609</v>
       </c>
     </row>
     <row r="190">
@@ -4611,10 +5181,13 @@
         <v>1.836</v>
       </c>
       <c r="E190" s="1" t="n">
+        <v>1.832</v>
+      </c>
+      <c r="F190" s="1" t="n">
         <v>1.838</v>
       </c>
-      <c r="F190" s="1" t="n">
-        <v>1.835</v>
+      <c r="G190" s="1" t="n">
+        <v>1.832</v>
       </c>
     </row>
     <row r="191">
@@ -4633,9 +5206,12 @@
         <v>0.02677</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>0.02677</v>
+        <v>0.0268</v>
       </c>
       <c r="F191" s="1" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="G191" s="1" t="n">
         <v>0.02669</v>
       </c>
     </row>
@@ -4655,9 +5231,12 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="E192" s="1" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="F192" s="1" t="n">
         <v>0.0973</v>
       </c>
-      <c r="F192" s="1" t="n">
+      <c r="G192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -4677,9 +5256,12 @@
         <v>0.1682</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>0.1682</v>
+        <v>0.1693</v>
       </c>
       <c r="F193" s="1" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="G193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -4699,9 +5281,12 @@
         <v>16.261</v>
       </c>
       <c r="E194" s="1" t="n">
+        <v>16.264</v>
+      </c>
+      <c r="F194" s="1" t="n">
         <v>16.294</v>
       </c>
-      <c r="F194" s="1" t="n">
+      <c r="G194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -4721,9 +5306,12 @@
         <v>4.094</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>4.096</v>
+        <v>4.098</v>
       </c>
       <c r="F195" s="1" t="n">
+        <v>4.098</v>
+      </c>
+      <c r="G195" s="1" t="n">
         <v>4.093</v>
       </c>
     </row>
@@ -4743,10 +5331,13 @@
         <v>1.2683</v>
       </c>
       <c r="E196" s="1" t="n">
+        <v>1.2671</v>
+      </c>
+      <c r="F196" s="1" t="n">
         <v>1.2794</v>
       </c>
-      <c r="F196" s="1" t="n">
-        <v>1.2683</v>
+      <c r="G196" s="1" t="n">
+        <v>1.2671</v>
       </c>
     </row>
     <row r="197">
@@ -4765,9 +5356,12 @@
         <v>3.07</v>
       </c>
       <c r="E197" s="1" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="F197" s="1" t="n">
         <v>3.092</v>
       </c>
-      <c r="F197" s="1" t="n">
+      <c r="G197" s="1" t="n">
         <v>3.07</v>
       </c>
     </row>
@@ -4787,9 +5381,12 @@
         <v>0.01265</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>0.01265</v>
+        <v>0.01266</v>
       </c>
       <c r="F198" s="1" t="n">
+        <v>0.01266</v>
+      </c>
+      <c r="G198" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -4812,6 +5409,9 @@
         <v>0.0001762</v>
       </c>
       <c r="F199" s="1" t="n">
+        <v>0.0001762</v>
+      </c>
+      <c r="G199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -4831,9 +5431,12 @@
         <v>115.55</v>
       </c>
       <c r="E200" s="1" t="n">
+        <v>115.57</v>
+      </c>
+      <c r="F200" s="1" t="n">
         <v>115.62</v>
       </c>
-      <c r="F200" s="1" t="n">
+      <c r="G200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -4853,9 +5456,12 @@
         <v>0.01028</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>0.01028</v>
+        <v>0.01031</v>
       </c>
       <c r="F201" s="1" t="n">
+        <v>0.01031</v>
+      </c>
+      <c r="G201" s="1" t="n">
         <v>0.01023</v>
       </c>
     </row>
@@ -4875,9 +5481,12 @@
         <v>0.01072</v>
       </c>
       <c r="E202" s="1" t="n">
+        <v>0.01072</v>
+      </c>
+      <c r="F202" s="1" t="n">
         <v>0.01073</v>
       </c>
-      <c r="F202" s="1" t="n">
+      <c r="G202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -4897,9 +5506,12 @@
         <v>0.003149</v>
       </c>
       <c r="E203" s="1" t="n">
+        <v>0.003151</v>
+      </c>
+      <c r="F203" s="1" t="n">
         <v>0.003153</v>
       </c>
-      <c r="F203" s="1" t="n">
+      <c r="G203" s="1" t="n">
         <v>0.003137</v>
       </c>
     </row>
@@ -4919,10 +5531,13 @@
         <v>28.32</v>
       </c>
       <c r="E204" s="1" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="F204" s="1" t="n">
         <v>28.38</v>
       </c>
-      <c r="F204" s="1" t="n">
-        <v>28.32</v>
+      <c r="G204" s="1" t="n">
+        <v>28.28</v>
       </c>
     </row>
     <row r="205">
@@ -4941,9 +5556,12 @@
         <v>0.5608</v>
       </c>
       <c r="E205" s="1" t="n">
+        <v>0.5627</v>
+      </c>
+      <c r="F205" s="1" t="n">
         <v>0.5636</v>
       </c>
-      <c r="F205" s="1" t="n">
+      <c r="G205" s="1" t="n">
         <v>0.5608</v>
       </c>
     </row>
@@ -4963,9 +5581,12 @@
         <v>0.0004387</v>
       </c>
       <c r="E206" s="1" t="n">
+        <v>0.0004387</v>
+      </c>
+      <c r="F206" s="1" t="n">
         <v>0.0004403</v>
       </c>
-      <c r="F206" s="1" t="n">
+      <c r="G206" s="1" t="n">
         <v>0.0004387</v>
       </c>
     </row>
@@ -4985,9 +5606,12 @@
         <v>0.04656</v>
       </c>
       <c r="E207" s="1" t="n">
+        <v>0.04655</v>
+      </c>
+      <c r="F207" s="1" t="n">
         <v>0.04667</v>
       </c>
-      <c r="F207" s="1" t="n">
+      <c r="G207" s="1" t="n">
         <v>0.04651</v>
       </c>
     </row>
@@ -5007,9 +5631,12 @@
         <v>0.09</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>0.09</v>
+        <v>0.091</v>
       </c>
       <c r="F208" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="G208" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -5029,9 +5656,12 @@
         <v>0.02572</v>
       </c>
       <c r="E209" s="1" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="F209" s="1" t="n">
         <v>0.02572</v>
       </c>
-      <c r="F209" s="1" t="n">
+      <c r="G209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -5051,9 +5681,12 @@
         <v>0.012745</v>
       </c>
       <c r="E210" s="1" t="n">
+        <v>0.012735</v>
+      </c>
+      <c r="F210" s="1" t="n">
         <v>0.012745</v>
       </c>
-      <c r="F210" s="1" t="n">
+      <c r="G210" s="1" t="n">
         <v>0.012652</v>
       </c>
     </row>
@@ -5073,9 +5706,12 @@
         <v>0.0915</v>
       </c>
       <c r="E211" s="1" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="F211" s="1" t="n">
         <v>0.09180000000000001</v>
       </c>
-      <c r="F211" s="1" t="n">
+      <c r="G211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -5095,10 +5731,13 @@
         <v>0.007076</v>
       </c>
       <c r="E212" s="1" t="n">
+        <v>0.007049</v>
+      </c>
+      <c r="F212" s="1" t="n">
         <v>0.007076</v>
       </c>
-      <c r="F212" s="1" t="n">
-        <v>0.007053</v>
+      <c r="G212" s="1" t="n">
+        <v>0.007049</v>
       </c>
     </row>
     <row r="213">
@@ -5117,9 +5756,12 @@
         <v>0.02954</v>
       </c>
       <c r="E213" s="1" t="n">
+        <v>0.02956</v>
+      </c>
+      <c r="F213" s="1" t="n">
         <v>0.02966</v>
       </c>
-      <c r="F213" s="1" t="n">
+      <c r="G213" s="1" t="n">
         <v>0.02954</v>
       </c>
     </row>
@@ -5139,10 +5781,13 @@
         <v>0.2701</v>
       </c>
       <c r="E214" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F214" s="1" t="n">
         <v>0.2708</v>
       </c>
-      <c r="F214" s="1" t="n">
-        <v>0.2701</v>
+      <c r="G214" s="1" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="215">
@@ -5161,9 +5806,12 @@
         <v>0.02158</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>0.02171</v>
+        <v>0.02183</v>
       </c>
       <c r="F215" s="1" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="G215" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -5183,9 +5831,12 @@
         <v>0.01485</v>
       </c>
       <c r="E216" s="1" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="F216" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="F216" s="1" t="n">
+      <c r="G216" s="1" t="n">
         <v>0.01475</v>
       </c>
     </row>
@@ -5205,9 +5856,12 @@
         <v>0.2533</v>
       </c>
       <c r="E217" s="1" t="n">
+        <v>0.2537</v>
+      </c>
+      <c r="F217" s="1" t="n">
         <v>0.2538</v>
       </c>
-      <c r="F217" s="1" t="n">
+      <c r="G217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -5227,9 +5881,12 @@
         <v>0.3075</v>
       </c>
       <c r="E218" s="1" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="F218" s="1" t="n">
         <v>0.3087</v>
       </c>
-      <c r="F218" s="1" t="n">
+      <c r="G218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -5249,9 +5906,12 @@
         <v>0.1774</v>
       </c>
       <c r="E219" s="1" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="F219" s="1" t="n">
         <v>0.1784</v>
       </c>
-      <c r="F219" s="1" t="n">
+      <c r="G219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -5271,9 +5931,12 @@
         <v>15.02</v>
       </c>
       <c r="E220" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="F220" s="1" t="n">
         <v>15.02</v>
       </c>
-      <c r="F220" s="1" t="n">
+      <c r="G220" s="1" t="n">
         <v>14.97</v>
       </c>
     </row>
@@ -5293,9 +5956,12 @@
         <v>0.01594</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>0.01594</v>
+        <v>0.01599</v>
       </c>
       <c r="F221" s="1" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="G221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -5315,9 +5981,12 @@
         <v>66.47</v>
       </c>
       <c r="E222" s="1" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="F222" s="1" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="F222" s="1" t="n">
+      <c r="G222" s="1" t="n">
         <v>66.17</v>
       </c>
     </row>
@@ -5337,9 +6006,12 @@
         <v>0.09279</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>0.09279</v>
+        <v>0.09291000000000001</v>
       </c>
       <c r="F223" s="1" t="n">
+        <v>0.09291000000000001</v>
+      </c>
+      <c r="G223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -5359,9 +6031,12 @@
         <v>0.03926</v>
       </c>
       <c r="E224" s="1" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="F224" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="F224" s="1" t="n">
+      <c r="G224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -5381,9 +6056,12 @@
         <v>0.5723</v>
       </c>
       <c r="E225" s="1" t="n">
+        <v>0.5717</v>
+      </c>
+      <c r="F225" s="1" t="n">
         <v>0.5725</v>
       </c>
-      <c r="F225" s="1" t="n">
+      <c r="G225" s="1" t="n">
         <v>0.5695</v>
       </c>
     </row>
@@ -5403,9 +6081,12 @@
         <v>0.1166</v>
       </c>
       <c r="E226" s="1" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="F226" s="1" t="n">
         <v>0.1167</v>
       </c>
-      <c r="F226" s="1" t="n">
+      <c r="G226" s="1" t="n">
         <v>0.1166</v>
       </c>
     </row>
@@ -5425,10 +6106,13 @@
         <v>0.3187</v>
       </c>
       <c r="E227" s="1" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="F227" s="1" t="n">
         <v>0.3201</v>
       </c>
-      <c r="F227" s="1" t="n">
-        <v>0.3187</v>
+      <c r="G227" s="1" t="n">
+        <v>0.3179</v>
       </c>
     </row>
     <row r="228">
@@ -5447,9 +6131,12 @@
         <v>6.067</v>
       </c>
       <c r="E228" s="1" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="F228" s="1" t="n">
         <v>6.09</v>
       </c>
-      <c r="F228" s="1" t="n">
+      <c r="G228" s="1" t="n">
         <v>6.066</v>
       </c>
     </row>
@@ -5469,9 +6156,12 @@
         <v>0.0289</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>0.0289</v>
+        <v>0.029</v>
       </c>
       <c r="F229" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="G229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -5491,9 +6181,12 @@
         <v>0.3307</v>
       </c>
       <c r="E230" s="1" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="F230" s="1" t="n">
         <v>0.3307</v>
       </c>
-      <c r="F230" s="1" t="n">
+      <c r="G230" s="1" t="n">
         <v>0.3294</v>
       </c>
     </row>
@@ -5513,9 +6206,12 @@
         <v>0.12076</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>0.12076</v>
+        <v>0.12089</v>
       </c>
       <c r="F231" s="1" t="n">
+        <v>0.12089</v>
+      </c>
+      <c r="G231" s="1" t="n">
         <v>0.12024</v>
       </c>
     </row>
@@ -5538,6 +6234,9 @@
         <v>0.1186</v>
       </c>
       <c r="F232" s="1" t="n">
+        <v>0.1186</v>
+      </c>
+      <c r="G232" s="1" t="n">
         <v>0.1185</v>
       </c>
     </row>
@@ -5557,10 +6256,13 @@
         <v>0.03013</v>
       </c>
       <c r="E233" s="1" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="F233" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="F233" s="1" t="n">
-        <v>0.03013</v>
+      <c r="G233" s="1" t="n">
+        <v>0.0301</v>
       </c>
     </row>
     <row r="234">
@@ -5579,9 +6281,12 @@
         <v>0.01574</v>
       </c>
       <c r="E234" s="1" t="n">
+        <v>0.015644</v>
+      </c>
+      <c r="F234" s="1" t="n">
         <v>0.01574</v>
       </c>
-      <c r="F234" s="1" t="n">
+      <c r="G234" s="1" t="n">
         <v>0.015644</v>
       </c>
     </row>
@@ -5601,10 +6306,13 @@
         <v>0.01277</v>
       </c>
       <c r="E235" s="1" t="n">
+        <v>0.01272</v>
+      </c>
+      <c r="F235" s="1" t="n">
         <v>0.01279</v>
       </c>
-      <c r="F235" s="1" t="n">
-        <v>0.01275</v>
+      <c r="G235" s="1" t="n">
+        <v>0.01272</v>
       </c>
     </row>
     <row r="236">
@@ -5623,9 +6331,12 @@
         <v>0.01926</v>
       </c>
       <c r="E236" s="1" t="n">
+        <v>0.01926</v>
+      </c>
+      <c r="F236" s="1" t="n">
         <v>0.01929</v>
       </c>
-      <c r="F236" s="1" t="n">
+      <c r="G236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -5645,10 +6356,13 @@
         <v>0.08452</v>
       </c>
       <c r="E237" s="1" t="n">
+        <v>0.08427999999999999</v>
+      </c>
+      <c r="F237" s="1" t="n">
         <v>0.08509</v>
       </c>
-      <c r="F237" s="1" t="n">
-        <v>0.08452</v>
+      <c r="G237" s="1" t="n">
+        <v>0.08427999999999999</v>
       </c>
     </row>
     <row r="238">
@@ -5667,9 +6381,12 @@
         <v>0.05875</v>
       </c>
       <c r="E238" s="1" t="n">
+        <v>0.05877</v>
+      </c>
+      <c r="F238" s="1" t="n">
         <v>0.05892</v>
       </c>
-      <c r="F238" s="1" t="n">
+      <c r="G238" s="1" t="n">
         <v>0.05875</v>
       </c>
     </row>
@@ -5689,9 +6406,12 @@
         <v>0.009067</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>0.009067</v>
+        <v>0.009083000000000001</v>
       </c>
       <c r="F239" s="1" t="n">
+        <v>0.009083000000000001</v>
+      </c>
+      <c r="G239" s="1" t="n">
         <v>0.009027</v>
       </c>
     </row>
@@ -5711,9 +6431,12 @@
         <v>0.004154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>0.004162</v>
+        <v>0.004175</v>
       </c>
       <c r="F240" s="1" t="n">
+        <v>0.004175</v>
+      </c>
+      <c r="G240" s="1" t="n">
         <v>0.004154</v>
       </c>
     </row>
@@ -5733,9 +6456,12 @@
         <v>0.241</v>
       </c>
       <c r="E241" s="1" t="n">
+        <v>0.2407</v>
+      </c>
+      <c r="F241" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="F241" s="1" t="n">
+      <c r="G241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -5758,6 +6484,9 @@
         <v>0.0582</v>
       </c>
       <c r="F242" s="1" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="G242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -5777,9 +6506,12 @@
         <v>0.02346</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>0.02346</v>
+        <v>0.02356</v>
       </c>
       <c r="F243" s="1" t="n">
+        <v>0.02356</v>
+      </c>
+      <c r="G243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -5799,9 +6531,12 @@
         <v>0.05547</v>
       </c>
       <c r="E244" s="1" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="F244" s="1" t="n">
         <v>0.05623</v>
       </c>
-      <c r="F244" s="1" t="n">
+      <c r="G244" s="1" t="n">
         <v>0.05547</v>
       </c>
     </row>
@@ -5821,9 +6556,12 @@
         <v>0.03425</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>0.03433</v>
+        <v>0.03438</v>
       </c>
       <c r="F245" s="1" t="n">
+        <v>0.03438</v>
+      </c>
+      <c r="G245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -5843,10 +6581,13 @@
         <v>0.06013</v>
       </c>
       <c r="E246" s="1" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="F246" s="1" t="n">
         <v>0.06013</v>
       </c>
-      <c r="F246" s="1" t="n">
-        <v>0.06004</v>
+      <c r="G246" s="1" t="n">
+        <v>0.0599</v>
       </c>
     </row>
     <row r="247">
@@ -5865,10 +6606,13 @@
         <v>0.385</v>
       </c>
       <c r="E247" s="1" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="F247" s="1" t="n">
         <v>0.385</v>
       </c>
-      <c r="F247" s="1" t="n">
-        <v>0.384</v>
+      <c r="G247" s="1" t="n">
+        <v>0.383</v>
       </c>
     </row>
     <row r="248">
@@ -5887,9 +6631,12 @@
         <v>0.5175</v>
       </c>
       <c r="E248" s="1" t="n">
+        <v>0.5173</v>
+      </c>
+      <c r="F248" s="1" t="n">
         <v>0.519</v>
       </c>
-      <c r="F248" s="1" t="n">
+      <c r="G248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -5909,9 +6656,12 @@
         <v>0.02804</v>
       </c>
       <c r="E249" s="1" t="n">
+        <v>0.02798</v>
+      </c>
+      <c r="F249" s="1" t="n">
         <v>0.02804</v>
       </c>
-      <c r="F249" s="1" t="n">
+      <c r="G249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -5931,9 +6681,12 @@
         <v>0.01294</v>
       </c>
       <c r="E250" s="1" t="n">
+        <v>0.01292</v>
+      </c>
+      <c r="F250" s="1" t="n">
         <v>0.01295</v>
       </c>
-      <c r="F250" s="1" t="n">
+      <c r="G250" s="1" t="n">
         <v>0.01288</v>
       </c>
     </row>
@@ -5953,9 +6706,12 @@
         <v>0.1001</v>
       </c>
       <c r="E251" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="F251" s="1" t="n">
         <v>0.1003</v>
       </c>
-      <c r="F251" s="1" t="n">
+      <c r="G251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5975,9 +6731,12 @@
         <v>0.00718</v>
       </c>
       <c r="E252" s="1" t="n">
+        <v>0.00718</v>
+      </c>
+      <c r="F252" s="1" t="n">
         <v>0.00719</v>
       </c>
-      <c r="F252" s="1" t="n">
+      <c r="G252" s="1" t="n">
         <v>0.00716</v>
       </c>
     </row>
@@ -5997,9 +6756,12 @@
         <v>0.005558</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>0.005561</v>
+        <v>0.005563</v>
       </c>
       <c r="F253" s="1" t="n">
+        <v>0.005563</v>
+      </c>
+      <c r="G253" s="1" t="n">
         <v>0.005554</v>
       </c>
     </row>
@@ -6019,9 +6781,12 @@
         <v>0.0643</v>
       </c>
       <c r="E254" s="1" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="F254" s="1" t="n">
         <v>0.0646</v>
       </c>
-      <c r="F254" s="1" t="n">
+      <c r="G254" s="1" t="n">
         <v>0.06419999999999999</v>
       </c>
     </row>
@@ -6041,9 +6806,12 @@
         <v>0.01432</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>0.01434</v>
+        <v>0.01436</v>
       </c>
       <c r="F255" s="1" t="n">
+        <v>0.01436</v>
+      </c>
+      <c r="G255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -6063,9 +6831,12 @@
         <v>0.999285</v>
       </c>
       <c r="E256" s="1" t="n">
+        <v>0.999286</v>
+      </c>
+      <c r="F256" s="1" t="n">
         <v>0.999297</v>
       </c>
-      <c r="F256" s="1" t="n">
+      <c r="G256" s="1" t="n">
         <v>0.999285</v>
       </c>
     </row>
@@ -6085,9 +6856,12 @@
         <v>0.02096</v>
       </c>
       <c r="E257" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F257" s="1" t="n">
         <v>0.02101</v>
       </c>
-      <c r="F257" s="1" t="n">
+      <c r="G257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -6107,9 +6881,12 @@
         <v>0.01142</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>0.01142</v>
+        <v>0.01148</v>
       </c>
       <c r="F258" s="1" t="n">
+        <v>0.01148</v>
+      </c>
+      <c r="G258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -6129,9 +6906,12 @@
         <v>0.5103</v>
       </c>
       <c r="E259" s="1" t="n">
+        <v>0.5092</v>
+      </c>
+      <c r="F259" s="1" t="n">
         <v>0.5119</v>
       </c>
-      <c r="F259" s="1" t="n">
+      <c r="G259" s="1" t="n">
         <v>0.5085</v>
       </c>
     </row>
@@ -6151,9 +6931,12 @@
         <v>0.08495999999999999</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>0.08495999999999999</v>
+        <v>0.08537</v>
       </c>
       <c r="F260" s="1" t="n">
+        <v>0.08537</v>
+      </c>
+      <c r="G260" s="1" t="n">
         <v>0.08436</v>
       </c>
     </row>
@@ -6173,10 +6956,13 @@
         <v>0.04127</v>
       </c>
       <c r="E261" s="1" t="n">
+        <v>0.04124</v>
+      </c>
+      <c r="F261" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="F261" s="1" t="n">
-        <v>0.04127</v>
+      <c r="G261" s="1" t="n">
+        <v>0.04124</v>
       </c>
     </row>
     <row r="262">
@@ -6195,10 +6981,13 @@
         <v>2.283</v>
       </c>
       <c r="E262" s="1" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="F262" s="1" t="n">
         <v>2.288</v>
       </c>
-      <c r="F262" s="1" t="n">
-        <v>2.283</v>
+      <c r="G262" s="1" t="n">
+        <v>2.282</v>
       </c>
     </row>
     <row r="263">
@@ -6217,9 +7006,12 @@
         <v>18.51</v>
       </c>
       <c r="E263" s="1" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="F263" s="1" t="n">
         <v>18.51</v>
       </c>
-      <c r="F263" s="1" t="n">
+      <c r="G263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -6239,9 +7031,12 @@
         <v>0.008498</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>0.008498</v>
+        <v>0.008562999999999999</v>
       </c>
       <c r="F264" s="1" t="n">
+        <v>0.008562999999999999</v>
+      </c>
+      <c r="G264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -6261,10 +7056,13 @@
         <v>0.363</v>
       </c>
       <c r="E265" s="1" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="F265" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="F265" s="1" t="n">
-        <v>0.3628</v>
+      <c r="G265" s="1" t="n">
+        <v>0.3627</v>
       </c>
     </row>
     <row r="266">
@@ -6283,9 +7081,12 @@
         <v>0.053765</v>
       </c>
       <c r="E266" s="1" t="n">
+        <v>0.054195</v>
+      </c>
+      <c r="F266" s="1" t="n">
         <v>0.054291</v>
       </c>
-      <c r="F266" s="1" t="n">
+      <c r="G266" s="1" t="n">
         <v>0.053765</v>
       </c>
     </row>
@@ -6305,9 +7106,12 @@
         <v>0.1314</v>
       </c>
       <c r="E267" s="1" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="F267" s="1" t="n">
         <v>0.1321</v>
       </c>
-      <c r="F267" s="1" t="n">
+      <c r="G267" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -6327,9 +7131,12 @@
         <v>0.007830999999999999</v>
       </c>
       <c r="E268" s="1" t="n">
+        <v>0.007795</v>
+      </c>
+      <c r="F268" s="1" t="n">
         <v>0.007845</v>
       </c>
-      <c r="F268" s="1" t="n">
+      <c r="G268" s="1" t="n">
         <v>0.007759</v>
       </c>
     </row>
@@ -6349,9 +7156,12 @@
         <v>0.001236</v>
       </c>
       <c r="E269" s="1" t="n">
+        <v>0.001235</v>
+      </c>
+      <c r="F269" s="1" t="n">
         <v>0.00124</v>
       </c>
-      <c r="F269" s="1" t="n">
+      <c r="G269" s="1" t="n">
         <v>0.001235</v>
       </c>
     </row>
@@ -6371,9 +7181,12 @@
         <v>0.28865</v>
       </c>
       <c r="E270" s="1" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="F270" s="1" t="n">
         <v>0.28997</v>
       </c>
-      <c r="F270" s="1" t="n">
+      <c r="G270" s="1" t="n">
         <v>0.28865</v>
       </c>
     </row>
@@ -6393,9 +7206,12 @@
         <v>0.03906</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>0.03906</v>
+        <v>0.03922</v>
       </c>
       <c r="F271" s="1" t="n">
+        <v>0.03922</v>
+      </c>
+      <c r="G271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -6415,9 +7231,12 @@
         <v>0.0513</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>0.05133</v>
+        <v>0.05137</v>
       </c>
       <c r="F272" s="1" t="n">
+        <v>0.05137</v>
+      </c>
+      <c r="G272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -6440,6 +7259,9 @@
         <v>0.00771</v>
       </c>
       <c r="F273" s="1" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="G273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -6459,9 +7281,12 @@
         <v>0.005744</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>0.005745</v>
+        <v>0.005779</v>
       </c>
       <c r="F274" s="1" t="n">
+        <v>0.005779</v>
+      </c>
+      <c r="G274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -6481,10 +7306,13 @@
         <v>0.0005865999999999999</v>
       </c>
       <c r="E275" s="1" t="n">
+        <v>0.0005863</v>
+      </c>
+      <c r="F275" s="1" t="n">
         <v>0.0005895</v>
       </c>
-      <c r="F275" s="1" t="n">
-        <v>0.0005865999999999999</v>
+      <c r="G275" s="1" t="n">
+        <v>0.0005863</v>
       </c>
     </row>
     <row r="276">
@@ -6503,10 +7331,13 @@
         <v>0.15077</v>
       </c>
       <c r="E276" s="1" t="n">
+        <v>0.15044</v>
+      </c>
+      <c r="F276" s="1" t="n">
         <v>0.15167</v>
       </c>
-      <c r="F276" s="1" t="n">
-        <v>0.15077</v>
+      <c r="G276" s="1" t="n">
+        <v>0.15044</v>
       </c>
     </row>
     <row r="277">
@@ -6525,9 +7356,12 @@
         <v>0.022785</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>0.022785</v>
+        <v>0.022788</v>
       </c>
       <c r="F277" s="1" t="n">
+        <v>0.022788</v>
+      </c>
+      <c r="G277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -6547,9 +7381,12 @@
         <v>0.04197</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>0.0421</v>
+        <v>0.04242</v>
       </c>
       <c r="F278" s="1" t="n">
+        <v>0.04242</v>
+      </c>
+      <c r="G278" s="1" t="n">
         <v>0.04179</v>
       </c>
     </row>
@@ -6569,9 +7406,12 @@
         <v>0.0004006</v>
       </c>
       <c r="E279" s="1" t="n">
+        <v>0.0003994</v>
+      </c>
+      <c r="F279" s="1" t="n">
         <v>0.0004006</v>
       </c>
-      <c r="F279" s="1" t="n">
+      <c r="G279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -6591,9 +7431,12 @@
         <v>0.02218</v>
       </c>
       <c r="E280" s="1" t="n">
+        <v>0.02213</v>
+      </c>
+      <c r="F280" s="1" t="n">
         <v>0.02218</v>
       </c>
-      <c r="F280" s="1" t="n">
+      <c r="G280" s="1" t="n">
         <v>0.02195</v>
       </c>
     </row>
@@ -6613,9 +7456,12 @@
         <v>0.06936</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>0.0694</v>
+        <v>0.06945</v>
       </c>
       <c r="F281" s="1" t="n">
+        <v>0.06945</v>
+      </c>
+      <c r="G281" s="1" t="n">
         <v>0.06936</v>
       </c>
     </row>
@@ -6635,9 +7481,12 @@
         <v>0.006794</v>
       </c>
       <c r="E282" s="1" t="n">
+        <v>0.006787</v>
+      </c>
+      <c r="F282" s="1" t="n">
         <v>0.006804</v>
       </c>
-      <c r="F282" s="1" t="n">
+      <c r="G282" s="1" t="n">
         <v>0.006758</v>
       </c>
     </row>
@@ -6660,6 +7509,9 @@
         <v>0.12</v>
       </c>
       <c r="F283" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G283" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -6682,6 +7534,9 @@
         <v>0.005475</v>
       </c>
       <c r="F284" s="1" t="n">
+        <v>0.005475</v>
+      </c>
+      <c r="G284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -6701,9 +7556,12 @@
         <v>1.251</v>
       </c>
       <c r="E285" s="1" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="F285" s="1" t="n">
         <v>1.251</v>
       </c>
-      <c r="F285" s="1" t="n">
+      <c r="G285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -6723,9 +7581,12 @@
         <v>0.4429</v>
       </c>
       <c r="E286" s="1" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="F286" s="1" t="n">
         <v>0.4441</v>
       </c>
-      <c r="F286" s="1" t="n">
+      <c r="G286" s="1" t="n">
         <v>0.4429</v>
       </c>
     </row>
@@ -6745,9 +7606,12 @@
         <v>0.007875999999999999</v>
       </c>
       <c r="E287" s="1" t="n">
+        <v>0.007868</v>
+      </c>
+      <c r="F287" s="1" t="n">
         <v>0.007875999999999999</v>
       </c>
-      <c r="F287" s="1" t="n">
+      <c r="G287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -6767,10 +7631,13 @@
         <v>0.0292</v>
       </c>
       <c r="E288" s="1" t="n">
+        <v>0.02914</v>
+      </c>
+      <c r="F288" s="1" t="n">
         <v>0.02922</v>
       </c>
-      <c r="F288" s="1" t="n">
-        <v>0.0292</v>
+      <c r="G288" s="1" t="n">
+        <v>0.02914</v>
       </c>
     </row>
     <row r="289">
@@ -6789,9 +7656,12 @@
         <v>0.2809</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>0.2811</v>
+        <v>0.2812</v>
       </c>
       <c r="F289" s="1" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="G289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6811,10 +7681,13 @@
         <v>2.758</v>
       </c>
       <c r="E290" s="1" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F290" s="1" t="n">
         <v>2.764</v>
       </c>
-      <c r="F290" s="1" t="n">
-        <v>2.758</v>
+      <c r="G290" s="1" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="291">
@@ -6833,9 +7706,12 @@
         <v>0.003165</v>
       </c>
       <c r="E291" s="1" t="n">
+        <v>0.003164</v>
+      </c>
+      <c r="F291" s="1" t="n">
         <v>0.003176</v>
       </c>
-      <c r="F291" s="1" t="n">
+      <c r="G291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -6855,9 +7731,12 @@
         <v>0.4478</v>
       </c>
       <c r="E292" s="1" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="F292" s="1" t="n">
         <v>0.4488</v>
       </c>
-      <c r="F292" s="1" t="n">
+      <c r="G292" s="1" t="n">
         <v>0.4475</v>
       </c>
     </row>
@@ -6877,10 +7756,13 @@
         <v>0.08217000000000001</v>
       </c>
       <c r="E293" s="1" t="n">
+        <v>0.08214</v>
+      </c>
+      <c r="F293" s="1" t="n">
         <v>0.08298</v>
       </c>
-      <c r="F293" s="1" t="n">
-        <v>0.08217000000000001</v>
+      <c r="G293" s="1" t="n">
+        <v>0.08214</v>
       </c>
     </row>
     <row r="294">
@@ -6899,9 +7781,12 @@
         <v>0.02781</v>
       </c>
       <c r="E294" s="1" t="n">
+        <v>0.02783</v>
+      </c>
+      <c r="F294" s="1" t="n">
         <v>0.02784</v>
       </c>
-      <c r="F294" s="1" t="n">
+      <c r="G294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -6921,9 +7806,12 @@
         <v>0.955</v>
       </c>
       <c r="E295" s="1" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="F295" s="1" t="n">
         <v>0.958</v>
       </c>
-      <c r="F295" s="1" t="n">
+      <c r="G295" s="1" t="n">
         <v>0.953</v>
       </c>
     </row>
@@ -6943,9 +7831,12 @@
         <v>0.006857</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>0.006871</v>
+        <v>0.006891</v>
       </c>
       <c r="F296" s="1" t="n">
+        <v>0.006891</v>
+      </c>
+      <c r="G296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -6965,9 +7856,12 @@
         <v>0.1206</v>
       </c>
       <c r="E297" s="1" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="F297" s="1" t="n">
         <v>0.1212</v>
       </c>
-      <c r="F297" s="1" t="n">
+      <c r="G297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -6987,9 +7881,12 @@
         <v>0.01533</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>0.01535</v>
+        <v>0.01548</v>
       </c>
       <c r="F298" s="1" t="n">
+        <v>0.01548</v>
+      </c>
+      <c r="G298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -7009,9 +7906,12 @@
         <v>0.4396</v>
       </c>
       <c r="E299" s="1" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="F299" s="1" t="n">
         <v>0.4405</v>
       </c>
-      <c r="F299" s="1" t="n">
+      <c r="G299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -7031,10 +7931,13 @@
         <v>0.009220000000000001</v>
       </c>
       <c r="E300" s="1" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="F300" s="1" t="n">
         <v>0.00924</v>
       </c>
-      <c r="F300" s="1" t="n">
-        <v>0.009220000000000001</v>
+      <c r="G300" s="1" t="n">
+        <v>0.0092</v>
       </c>
     </row>
     <row r="301">
@@ -7053,9 +7956,12 @@
         <v>0.1849</v>
       </c>
       <c r="E301" s="1" t="n">
+        <v>0.1848</v>
+      </c>
+      <c r="F301" s="1" t="n">
         <v>0.1849</v>
       </c>
-      <c r="F301" s="1" t="n">
+      <c r="G301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -7075,9 +7981,12 @@
         <v>0.00753</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>0.00754</v>
+        <v>0.00756</v>
       </c>
       <c r="F302" s="1" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="G302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -7097,9 +8006,12 @@
         <v>0.0002163</v>
       </c>
       <c r="E303" s="1" t="n">
+        <v>0.0002163</v>
+      </c>
+      <c r="F303" s="1" t="n">
         <v>0.0002171</v>
       </c>
-      <c r="F303" s="1" t="n">
+      <c r="G303" s="1" t="n">
         <v>0.0002163</v>
       </c>
     </row>
@@ -7119,10 +8031,13 @@
         <v>0.01547</v>
       </c>
       <c r="E304" s="1" t="n">
+        <v>0.01542</v>
+      </c>
+      <c r="F304" s="1" t="n">
         <v>0.01549</v>
       </c>
-      <c r="F304" s="1" t="n">
-        <v>0.01545</v>
+      <c r="G304" s="1" t="n">
+        <v>0.01542</v>
       </c>
     </row>
     <row r="305">
@@ -7141,9 +8056,12 @@
         <v>0.07394000000000001</v>
       </c>
       <c r="E305" s="1" t="n">
+        <v>0.07386</v>
+      </c>
+      <c r="F305" s="1" t="n">
         <v>0.07394000000000001</v>
       </c>
-      <c r="F305" s="1" t="n">
+      <c r="G305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -7163,9 +8081,12 @@
         <v>0.0828</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>0.0828</v>
+        <v>0.08291</v>
       </c>
       <c r="F306" s="1" t="n">
+        <v>0.08291</v>
+      </c>
+      <c r="G306" s="1" t="n">
         <v>0.08275</v>
       </c>
     </row>
@@ -7185,9 +8106,12 @@
         <v>0.01822</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>0.01826</v>
+        <v>0.01827</v>
       </c>
       <c r="F307" s="1" t="n">
+        <v>0.01827</v>
+      </c>
+      <c r="G307" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -7207,9 +8131,12 @@
         <v>0.0006239</v>
       </c>
       <c r="E308" s="1" t="n">
+        <v>0.0006223999999999999</v>
+      </c>
+      <c r="F308" s="1" t="n">
         <v>0.0006255</v>
       </c>
-      <c r="F308" s="1" t="n">
+      <c r="G308" s="1" t="n">
         <v>0.0006215</v>
       </c>
     </row>
@@ -7229,9 +8156,12 @@
         <v>0.08244</v>
       </c>
       <c r="E309" s="1" t="n">
+        <v>0.08252</v>
+      </c>
+      <c r="F309" s="1" t="n">
         <v>0.08294</v>
       </c>
-      <c r="F309" s="1" t="n">
+      <c r="G309" s="1" t="n">
         <v>0.08244</v>
       </c>
     </row>
@@ -7251,10 +8181,13 @@
         <v>0.0978</v>
       </c>
       <c r="E310" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="F310" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="F310" s="1" t="n">
-        <v>0.09760000000000001</v>
+      <c r="G310" s="1" t="n">
+        <v>0.0974</v>
       </c>
     </row>
     <row r="311">
@@ -7273,9 +8206,12 @@
         <v>0.2112</v>
       </c>
       <c r="E311" s="1" t="n">
+        <v>0.2112</v>
+      </c>
+      <c r="F311" s="1" t="n">
         <v>0.2113</v>
       </c>
-      <c r="F311" s="1" t="n">
+      <c r="G311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -7295,10 +8231,13 @@
         <v>0.3904</v>
       </c>
       <c r="E312" s="1" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="F312" s="1" t="n">
         <v>0.394</v>
       </c>
-      <c r="F312" s="1" t="n">
-        <v>0.3878</v>
+      <c r="G312" s="1" t="n">
+        <v>0.387</v>
       </c>
     </row>
     <row r="313">
@@ -7317,9 +8256,12 @@
         <v>0.10509</v>
       </c>
       <c r="E313" s="1" t="n">
+        <v>0.10518</v>
+      </c>
+      <c r="F313" s="1" t="n">
         <v>0.10542</v>
       </c>
-      <c r="F313" s="1" t="n">
+      <c r="G313" s="1" t="n">
         <v>0.10492</v>
       </c>
     </row>
@@ -7339,9 +8281,12 @@
         <v>0.08524</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>0.08524</v>
+        <v>0.08575000000000001</v>
       </c>
       <c r="F314" s="1" t="n">
+        <v>0.08575000000000001</v>
+      </c>
+      <c r="G314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -7361,9 +8306,12 @@
         <v>0.118</v>
       </c>
       <c r="E315" s="1" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="F315" s="1" t="n">
         <v>0.1185</v>
       </c>
-      <c r="F315" s="1" t="n">
+      <c r="G315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -7383,9 +8331,12 @@
         <v>0.03656</v>
       </c>
       <c r="E316" s="1" t="n">
+        <v>0.03666</v>
+      </c>
+      <c r="F316" s="1" t="n">
         <v>0.03681</v>
       </c>
-      <c r="F316" s="1" t="n">
+      <c r="G316" s="1" t="n">
         <v>0.03628</v>
       </c>
     </row>
@@ -7405,9 +8356,12 @@
         <v>0.08125</v>
       </c>
       <c r="E317" s="1" t="n">
+        <v>0.08087</v>
+      </c>
+      <c r="F317" s="1" t="n">
         <v>0.08125</v>
       </c>
-      <c r="F317" s="1" t="n">
+      <c r="G317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -7427,9 +8381,12 @@
         <v>0.0375</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>0.0375</v>
+        <v>0.03766</v>
       </c>
       <c r="F318" s="1" t="n">
+        <v>0.03766</v>
+      </c>
+      <c r="G318" s="1" t="n">
         <v>0.03736</v>
       </c>
     </row>
@@ -7449,9 +8406,12 @@
         <v>0.4327</v>
       </c>
       <c r="E319" s="1" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="F319" s="1" t="n">
         <v>0.4347</v>
       </c>
-      <c r="F319" s="1" t="n">
+      <c r="G319" s="1" t="n">
         <v>0.4308</v>
       </c>
     </row>
@@ -7471,10 +8431,13 @@
         <v>0.1608</v>
       </c>
       <c r="E320" s="1" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="F320" s="1" t="n">
         <v>0.1614</v>
       </c>
-      <c r="F320" s="1" t="n">
-        <v>0.1608</v>
+      <c r="G320" s="1" t="n">
+        <v>0.1607</v>
       </c>
     </row>
     <row r="321">
@@ -7493,9 +8456,12 @@
         <v>5.677</v>
       </c>
       <c r="E321" s="1" t="n">
+        <v>5.678</v>
+      </c>
+      <c r="F321" s="1" t="n">
         <v>5.68</v>
       </c>
-      <c r="F321" s="1" t="n">
+      <c r="G321" s="1" t="n">
         <v>5.677</v>
       </c>
     </row>
@@ -7515,9 +8481,12 @@
         <v>0.003738</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>0.003738</v>
+        <v>0.003739</v>
       </c>
       <c r="F322" s="1" t="n">
+        <v>0.003739</v>
+      </c>
+      <c r="G322" s="1" t="n">
         <v>0.003715</v>
       </c>
     </row>
@@ -7537,9 +8506,12 @@
         <v>0.001755</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>0.001755</v>
+        <v>0.001757</v>
       </c>
       <c r="F323" s="1" t="n">
+        <v>0.001757</v>
+      </c>
+      <c r="G323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -7559,11 +8531,14 @@
         <v>1.2e-05</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>1.2e-05</v>
+        <v>1.19e-05</v>
       </c>
       <c r="F324" s="1" t="n">
         <v>1.2e-05</v>
       </c>
+      <c r="G324" s="1" t="n">
+        <v>1.19e-05</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7581,10 +8556,13 @@
         <v>0.0863</v>
       </c>
       <c r="E325" s="1" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="F325" s="1" t="n">
         <v>0.08649999999999999</v>
       </c>
-      <c r="F325" s="1" t="n">
-        <v>0.0863</v>
+      <c r="G325" s="1" t="n">
+        <v>0.0862</v>
       </c>
     </row>
     <row r="326">
@@ -7603,9 +8581,12 @@
         <v>0.01732</v>
       </c>
       <c r="E326" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="F326" s="1" t="n">
         <v>0.01736</v>
       </c>
-      <c r="F326" s="1" t="n">
+      <c r="G326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -7625,10 +8606,13 @@
         <v>0.01687</v>
       </c>
       <c r="E327" s="1" t="n">
+        <v>0.01679</v>
+      </c>
+      <c r="F327" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="F327" s="1" t="n">
-        <v>0.01687</v>
+      <c r="G327" s="1" t="n">
+        <v>0.01679</v>
       </c>
     </row>
     <row r="328">
@@ -7647,9 +8631,12 @@
         <v>4.458</v>
       </c>
       <c r="E328" s="1" t="n">
+        <v>4.454</v>
+      </c>
+      <c r="F328" s="1" t="n">
         <v>4.462</v>
       </c>
-      <c r="F328" s="1" t="n">
+      <c r="G328" s="1" t="n">
         <v>4.446</v>
       </c>
     </row>
@@ -7669,10 +8656,13 @@
         <v>0.009648</v>
       </c>
       <c r="E329" s="1" t="n">
+        <v>0.009532000000000001</v>
+      </c>
+      <c r="F329" s="1" t="n">
         <v>0.009861</v>
       </c>
-      <c r="F329" s="1" t="n">
-        <v>0.009648</v>
+      <c r="G329" s="1" t="n">
+        <v>0.009532000000000001</v>
       </c>
     </row>
     <row r="330">
@@ -7691,9 +8681,12 @@
         <v>5186.5</v>
       </c>
       <c r="E330" s="1" t="n">
+        <v>5189</v>
+      </c>
+      <c r="F330" s="1" t="n">
         <v>5192.9</v>
       </c>
-      <c r="F330" s="1" t="n">
+      <c r="G330" s="1" t="n">
         <v>5185.8</v>
       </c>
     </row>
@@ -7713,9 +8706,12 @@
         <v>0.07085</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>0.07085</v>
+        <v>0.07087</v>
       </c>
       <c r="F331" s="1" t="n">
+        <v>0.07087</v>
+      </c>
+      <c r="G331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -7738,6 +8734,9 @@
         <v>0.06098</v>
       </c>
       <c r="F332" s="1" t="n">
+        <v>0.06098</v>
+      </c>
+      <c r="G332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -7757,9 +8756,12 @@
         <v>0.10416</v>
       </c>
       <c r="E333" s="1" t="n">
+        <v>0.10372</v>
+      </c>
+      <c r="F333" s="1" t="n">
         <v>0.10416</v>
       </c>
-      <c r="F333" s="1" t="n">
+      <c r="G333" s="1" t="n">
         <v>0.10347</v>
       </c>
     </row>
@@ -7779,10 +8781,13 @@
         <v>0.08815000000000001</v>
       </c>
       <c r="E334" s="1" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="F334" s="1" t="n">
         <v>0.08837</v>
       </c>
-      <c r="F334" s="1" t="n">
-        <v>0.08815000000000001</v>
+      <c r="G334" s="1" t="n">
+        <v>0.08749999999999999</v>
       </c>
     </row>
     <row r="335">
@@ -7801,9 +8806,12 @@
         <v>0.016391</v>
       </c>
       <c r="E335" s="1" t="n">
+        <v>0.016401</v>
+      </c>
+      <c r="F335" s="1" t="n">
         <v>0.016413</v>
       </c>
-      <c r="F335" s="1" t="n">
+      <c r="G335" s="1" t="n">
         <v>0.016391</v>
       </c>
     </row>
@@ -7823,10 +8831,13 @@
         <v>0.04587</v>
       </c>
       <c r="E336" s="1" t="n">
+        <v>0.04583</v>
+      </c>
+      <c r="F336" s="1" t="n">
         <v>0.04594</v>
       </c>
-      <c r="F336" s="1" t="n">
-        <v>0.04587</v>
+      <c r="G336" s="1" t="n">
+        <v>0.04583</v>
       </c>
     </row>
     <row r="337">
@@ -7845,9 +8856,12 @@
         <v>0.1846</v>
       </c>
       <c r="E337" s="1" t="n">
+        <v>0.1842</v>
+      </c>
+      <c r="F337" s="1" t="n">
         <v>0.1853</v>
       </c>
-      <c r="F337" s="1" t="n">
+      <c r="G337" s="1" t="n">
         <v>0.1838</v>
       </c>
     </row>
@@ -7867,9 +8881,12 @@
         <v>0.1833</v>
       </c>
       <c r="E338" s="1" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="F338" s="1" t="n">
         <v>0.1836</v>
       </c>
-      <c r="F338" s="1" t="n">
+      <c r="G338" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -7889,9 +8906,12 @@
         <v>0.01837</v>
       </c>
       <c r="E339" s="1" t="n">
+        <v>0.01836</v>
+      </c>
+      <c r="F339" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="F339" s="1" t="n">
+      <c r="G339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -7911,9 +8931,12 @@
         <v>0.02311</v>
       </c>
       <c r="E340" s="1" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="F340" s="1" t="n">
         <v>0.02311</v>
       </c>
-      <c r="F340" s="1" t="n">
+      <c r="G340" s="1" t="n">
         <v>0.02306</v>
       </c>
     </row>
@@ -7933,9 +8956,12 @@
         <v>0.4544</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>0.4548</v>
+        <v>0.455</v>
       </c>
       <c r="F341" s="1" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="G341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -7955,9 +8981,12 @@
         <v>0.01344</v>
       </c>
       <c r="E342" s="1" t="n">
+        <v>0.01343</v>
+      </c>
+      <c r="F342" s="1" t="n">
         <v>0.01344</v>
       </c>
-      <c r="F342" s="1" t="n">
+      <c r="G342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -7977,9 +9006,12 @@
         <v>2.89</v>
       </c>
       <c r="E343" s="1" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="F343" s="1" t="n">
         <v>2.89</v>
       </c>
-      <c r="F343" s="1" t="n">
+      <c r="G343" s="1" t="n">
         <v>2.874</v>
       </c>
     </row>
@@ -7999,9 +9031,12 @@
         <v>0.1552</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>0.1552</v>
+        <v>0.1577</v>
       </c>
       <c r="F344" s="1" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="G344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -8021,9 +9056,12 @@
         <v>0.005342</v>
       </c>
       <c r="E345" s="1" t="n">
+        <v>0.005351</v>
+      </c>
+      <c r="F345" s="1" t="n">
         <v>0.005367</v>
       </c>
-      <c r="F345" s="1" t="n">
+      <c r="G345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -8043,9 +9081,12 @@
         <v>0.05781</v>
       </c>
       <c r="E346" s="1" t="n">
+        <v>0.05778</v>
+      </c>
+      <c r="F346" s="1" t="n">
         <v>0.05781</v>
       </c>
-      <c r="F346" s="1" t="n">
+      <c r="G346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -8065,9 +9106,12 @@
         <v>2599</v>
       </c>
       <c r="E347" s="1" t="n">
+        <v>2603</v>
+      </c>
+      <c r="F347" s="1" t="n">
         <v>2606</v>
       </c>
-      <c r="F347" s="1" t="n">
+      <c r="G347" s="1" t="n">
         <v>2597</v>
       </c>
     </row>
@@ -8087,10 +9131,13 @@
         <v>0.04602</v>
       </c>
       <c r="E348" s="1" t="n">
+        <v>0.04595</v>
+      </c>
+      <c r="F348" s="1" t="n">
         <v>0.04621</v>
       </c>
-      <c r="F348" s="1" t="n">
-        <v>0.04602</v>
+      <c r="G348" s="1" t="n">
+        <v>0.04595</v>
       </c>
     </row>
     <row r="349">
@@ -8109,10 +9156,13 @@
         <v>0.005706</v>
       </c>
       <c r="E349" s="1" t="n">
+        <v>0.005676</v>
+      </c>
+      <c r="F349" s="1" t="n">
         <v>0.005707</v>
       </c>
-      <c r="F349" s="1" t="n">
-        <v>0.005682</v>
+      <c r="G349" s="1" t="n">
+        <v>0.005676</v>
       </c>
     </row>
     <row r="350">
@@ -8131,9 +9181,12 @@
         <v>195.23</v>
       </c>
       <c r="E350" s="1" t="n">
+        <v>195.32</v>
+      </c>
+      <c r="F350" s="1" t="n">
         <v>195.51</v>
       </c>
-      <c r="F350" s="1" t="n">
+      <c r="G350" s="1" t="n">
         <v>195.23</v>
       </c>
     </row>
@@ -8153,9 +9206,12 @@
         <v>0.08194</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>0.08205999999999999</v>
+        <v>0.08237999999999999</v>
       </c>
       <c r="F351" s="1" t="n">
+        <v>0.08237999999999999</v>
+      </c>
+      <c r="G351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -8175,10 +9231,13 @@
         <v>0.007487</v>
       </c>
       <c r="E352" s="1" t="n">
+        <v>0.007458</v>
+      </c>
+      <c r="F352" s="1" t="n">
         <v>0.007571</v>
       </c>
-      <c r="F352" s="1" t="n">
-        <v>0.007487</v>
+      <c r="G352" s="1" t="n">
+        <v>0.007458</v>
       </c>
     </row>
     <row r="353">
@@ -8197,9 +9256,12 @@
         <v>1.4887</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>1.4887</v>
+        <v>1.5085</v>
       </c>
       <c r="F353" s="1" t="n">
+        <v>1.5085</v>
+      </c>
+      <c r="G353" s="1" t="n">
         <v>1.4807</v>
       </c>
     </row>
@@ -8219,9 +9281,12 @@
         <v>0.07625</v>
       </c>
       <c r="E354" s="1" t="n">
+        <v>0.07617</v>
+      </c>
+      <c r="F354" s="1" t="n">
         <v>0.07643999999999999</v>
       </c>
-      <c r="F354" s="1" t="n">
+      <c r="G354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -8241,10 +9306,13 @@
         <v>0.04915</v>
       </c>
       <c r="E355" s="1" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="F355" s="1" t="n">
         <v>0.04921</v>
       </c>
-      <c r="F355" s="1" t="n">
-        <v>0.04913</v>
+      <c r="G355" s="1" t="n">
+        <v>0.0489</v>
       </c>
     </row>
     <row r="356">
@@ -8263,9 +9331,12 @@
         <v>0.2857</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>0.2857</v>
+        <v>0.2861</v>
       </c>
       <c r="F356" s="1" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="G356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -8285,9 +9356,12 @@
         <v>0.1462</v>
       </c>
       <c r="E357" s="1" t="n">
+        <v>0.1466</v>
+      </c>
+      <c r="F357" s="1" t="n">
         <v>0.1467</v>
       </c>
-      <c r="F357" s="1" t="n">
+      <c r="G357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -8307,9 +9381,12 @@
         <v>1.354</v>
       </c>
       <c r="E358" s="1" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="F358" s="1" t="n">
         <v>1.355</v>
       </c>
-      <c r="F358" s="1" t="n">
+      <c r="G358" s="1" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -8329,10 +9406,13 @@
         <v>0.6097</v>
       </c>
       <c r="E359" s="1" t="n">
+        <v>0.6091</v>
+      </c>
+      <c r="F359" s="1" t="n">
         <v>0.6117</v>
       </c>
-      <c r="F359" s="1" t="n">
-        <v>0.6097</v>
+      <c r="G359" s="1" t="n">
+        <v>0.6091</v>
       </c>
     </row>
     <row r="360">
@@ -8351,9 +9431,12 @@
         <v>0.1143</v>
       </c>
       <c r="E360" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="F360" s="1" t="n">
         <v>0.1145</v>
       </c>
-      <c r="F360" s="1" t="n">
+      <c r="G360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -8373,9 +9456,12 @@
         <v>0.02604</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>0.02619</v>
+        <v>0.02624</v>
       </c>
       <c r="F361" s="1" t="n">
+        <v>0.02624</v>
+      </c>
+      <c r="G361" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -8398,6 +9484,9 @@
         <v>3.04e-05</v>
       </c>
       <c r="F362" s="1" t="n">
+        <v>3.04e-05</v>
+      </c>
+      <c r="G362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -8417,9 +9506,12 @@
         <v>0.01022</v>
       </c>
       <c r="E363" s="1" t="n">
+        <v>0.01022</v>
+      </c>
+      <c r="F363" s="1" t="n">
         <v>0.01026</v>
       </c>
-      <c r="F363" s="1" t="n">
+      <c r="G363" s="1" t="n">
         <v>0.01018</v>
       </c>
     </row>
@@ -8439,9 +9531,12 @@
         <v>0.06204</v>
       </c>
       <c r="E364" s="1" t="n">
+        <v>0.06207</v>
+      </c>
+      <c r="F364" s="1" t="n">
         <v>0.06208</v>
       </c>
-      <c r="F364" s="1" t="n">
+      <c r="G364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -8461,9 +9556,12 @@
         <v>0.03291</v>
       </c>
       <c r="E365" s="1" t="n">
+        <v>0.03285</v>
+      </c>
+      <c r="F365" s="1" t="n">
         <v>0.03297</v>
       </c>
-      <c r="F365" s="1" t="n">
+      <c r="G365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -8483,9 +9581,12 @@
         <v>0.03289</v>
       </c>
       <c r="E366" s="1" t="n">
+        <v>0.03292</v>
+      </c>
+      <c r="F366" s="1" t="n">
         <v>0.03296</v>
       </c>
-      <c r="F366" s="1" t="n">
+      <c r="G366" s="1" t="n">
         <v>0.03288</v>
       </c>
     </row>
@@ -8505,9 +9606,12 @@
         <v>0.012163</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>0.012163</v>
+        <v>0.012203</v>
       </c>
       <c r="F367" s="1" t="n">
+        <v>0.012203</v>
+      </c>
+      <c r="G367" s="1" t="n">
         <v>0.012155</v>
       </c>
     </row>
@@ -8527,9 +9631,12 @@
         <v>0.03534</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>0.03534</v>
+        <v>0.03559</v>
       </c>
       <c r="F368" s="1" t="n">
+        <v>0.03559</v>
+      </c>
+      <c r="G368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -8549,9 +9656,12 @@
         <v>0.6193</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>0.6193</v>
+        <v>0.6198</v>
       </c>
       <c r="F369" s="1" t="n">
+        <v>0.6198</v>
+      </c>
+      <c r="G369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -8571,9 +9681,12 @@
         <v>0.008460000000000001</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>0.00847</v>
+        <v>0.00856</v>
       </c>
       <c r="F370" s="1" t="n">
+        <v>0.00856</v>
+      </c>
+      <c r="G370" s="1" t="n">
         <v>0.00843</v>
       </c>
     </row>
@@ -8593,9 +9706,12 @@
         <v>0.003287</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>0.003287</v>
+        <v>0.003288</v>
       </c>
       <c r="F371" s="1" t="n">
+        <v>0.003288</v>
+      </c>
+      <c r="G371" s="1" t="n">
         <v>0.003242</v>
       </c>
     </row>
@@ -8615,9 +9731,12 @@
         <v>0.13275</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>0.13275</v>
+        <v>0.13301</v>
       </c>
       <c r="F372" s="1" t="n">
+        <v>0.13301</v>
+      </c>
+      <c r="G372" s="1" t="n">
         <v>0.13227</v>
       </c>
     </row>
@@ -8637,10 +9756,13 @@
         <v>0.007821</v>
       </c>
       <c r="E373" s="1" t="n">
+        <v>0.007806</v>
+      </c>
+      <c r="F373" s="1" t="n">
         <v>0.007822000000000001</v>
       </c>
-      <c r="F373" s="1" t="n">
-        <v>0.007820000000000001</v>
+      <c r="G373" s="1" t="n">
+        <v>0.007806</v>
       </c>
     </row>
     <row r="374">
@@ -8659,10 +9781,13 @@
         <v>0.01973</v>
       </c>
       <c r="E374" s="1" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="F374" s="1" t="n">
         <v>0.01978</v>
       </c>
-      <c r="F374" s="1" t="n">
-        <v>0.01972</v>
+      <c r="G374" s="1" t="n">
+        <v>0.0197</v>
       </c>
     </row>
     <row r="375">
@@ -8681,9 +9806,12 @@
         <v>0.000594</v>
       </c>
       <c r="E375" s="1" t="n">
+        <v>0.0005918</v>
+      </c>
+      <c r="F375" s="1" t="n">
         <v>0.000594</v>
       </c>
-      <c r="F375" s="1" t="n">
+      <c r="G375" s="1" t="n">
         <v>0.0005914</v>
       </c>
     </row>
@@ -8706,6 +9834,9 @@
         <v>0.0363</v>
       </c>
       <c r="F376" s="1" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="G376" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -8725,9 +9856,12 @@
         <v>0.000792</v>
       </c>
       <c r="E377" s="1" t="n">
+        <v>0.0007917</v>
+      </c>
+      <c r="F377" s="1" t="n">
         <v>0.000792</v>
       </c>
-      <c r="F377" s="1" t="n">
+      <c r="G377" s="1" t="n">
         <v>0.0007848</v>
       </c>
     </row>
@@ -8747,9 +9881,12 @@
         <v>1.984</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>1.984</v>
+        <v>1.99</v>
       </c>
       <c r="F378" s="1" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G378" s="1" t="n">
         <v>1.973</v>
       </c>
     </row>
@@ -8769,10 +9906,13 @@
         <v>0.000589</v>
       </c>
       <c r="E379" s="1" t="n">
+        <v>0.0005882</v>
+      </c>
+      <c r="F379" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="F379" s="1" t="n">
-        <v>0.0005888999999999999</v>
+      <c r="G379" s="1" t="n">
+        <v>0.0005882</v>
       </c>
     </row>
     <row r="380">
@@ -8791,9 +9931,12 @@
         <v>0.03737</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>0.03743</v>
+        <v>0.03747</v>
       </c>
       <c r="F380" s="1" t="n">
+        <v>0.03747</v>
+      </c>
+      <c r="G380" s="1" t="n">
         <v>0.03737</v>
       </c>
     </row>
@@ -8813,9 +9956,12 @@
         <v>0.0546</v>
       </c>
       <c r="E381" s="1" t="n">
+        <v>0.05467</v>
+      </c>
+      <c r="F381" s="1" t="n">
         <v>0.05477</v>
       </c>
-      <c r="F381" s="1" t="n">
+      <c r="G381" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -8835,9 +9981,12 @@
         <v>0.01206</v>
       </c>
       <c r="E382" s="1" t="n">
+        <v>0.01205</v>
+      </c>
+      <c r="F382" s="1" t="n">
         <v>0.01207</v>
       </c>
-      <c r="F382" s="1" t="n">
+      <c r="G382" s="1" t="n">
         <v>0.01202</v>
       </c>
     </row>
@@ -8857,9 +10006,12 @@
         <v>0.001552</v>
       </c>
       <c r="E383" s="1" t="n">
+        <v>0.001553</v>
+      </c>
+      <c r="F383" s="1" t="n">
         <v>0.001559</v>
       </c>
-      <c r="F383" s="1" t="n">
+      <c r="G383" s="1" t="n">
         <v>0.001552</v>
       </c>
     </row>
@@ -8882,6 +10034,9 @@
         <v>0.0002157</v>
       </c>
       <c r="F384" s="1" t="n">
+        <v>0.0002157</v>
+      </c>
+      <c r="G384" s="1" t="n">
         <v>0.0002154</v>
       </c>
     </row>
@@ -8901,9 +10056,12 @@
         <v>0.0024</v>
       </c>
       <c r="E385" s="1" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="F385" s="1" t="n">
         <v>0.00242</v>
       </c>
-      <c r="F385" s="1" t="n">
+      <c r="G385" s="1" t="n">
         <v>0.0024</v>
       </c>
     </row>
@@ -8923,9 +10081,12 @@
         <v>3.902</v>
       </c>
       <c r="E386" s="1" t="n">
+        <v>3.906</v>
+      </c>
+      <c r="F386" s="1" t="n">
         <v>3.908</v>
       </c>
-      <c r="F386" s="1" t="n">
+      <c r="G386" s="1" t="n">
         <v>3.892</v>
       </c>
     </row>
@@ -8945,9 +10106,12 @@
         <v>0.0006237</v>
       </c>
       <c r="E387" s="1" t="n">
+        <v>0.0006241</v>
+      </c>
+      <c r="F387" s="1" t="n">
         <v>0.0006254</v>
       </c>
-      <c r="F387" s="1" t="n">
+      <c r="G387" s="1" t="n">
         <v>0.0006237</v>
       </c>
     </row>
@@ -8967,9 +10131,12 @@
         <v>0.00659</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>0.00659</v>
+        <v>0.00664</v>
       </c>
       <c r="F388" s="1" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="G388" s="1" t="n">
         <v>0.00653</v>
       </c>
     </row>
@@ -8992,6 +10159,9 @@
         <v>0.1318</v>
       </c>
       <c r="F389" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="G389" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -9011,9 +10181,12 @@
         <v>0.03223</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>0.03223</v>
+        <v>0.0323</v>
       </c>
       <c r="F390" s="1" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="G390" s="1" t="n">
         <v>0.03201</v>
       </c>
     </row>
@@ -9033,10 +10206,13 @@
         <v>0.06356000000000001</v>
       </c>
       <c r="E391" s="1" t="n">
+        <v>0.06351</v>
+      </c>
+      <c r="F391" s="1" t="n">
         <v>0.06362</v>
       </c>
-      <c r="F391" s="1" t="n">
-        <v>0.06356000000000001</v>
+      <c r="G391" s="1" t="n">
+        <v>0.06351</v>
       </c>
     </row>
     <row r="392">
@@ -9055,10 +10231,13 @@
         <v>27.75</v>
       </c>
       <c r="E392" s="1" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="F392" s="1" t="n">
         <v>27.82</v>
       </c>
-      <c r="F392" s="1" t="n">
-        <v>27.75</v>
+      <c r="G392" s="1" t="n">
+        <v>27.72</v>
       </c>
     </row>
     <row r="393">
@@ -9077,9 +10256,12 @@
         <v>0.000412</v>
       </c>
       <c r="E393" s="1" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="F393" s="1" t="n">
         <v>0.000414</v>
       </c>
-      <c r="F393" s="1" t="n">
+      <c r="G393" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -9099,9 +10281,12 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07005</v>
       </c>
       <c r="F394" s="1" t="n">
+        <v>0.07005</v>
+      </c>
+      <c r="G394" s="1" t="n">
         <v>0.06926</v>
       </c>
     </row>
@@ -9121,9 +10306,12 @@
         <v>0.2584</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>0.2589</v>
+        <v>0.2591</v>
       </c>
       <c r="F395" s="1" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="G395" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -9143,9 +10331,12 @@
         <v>0.004681</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>0.004687</v>
+        <v>0.00469</v>
       </c>
       <c r="F396" s="1" t="n">
+        <v>0.00469</v>
+      </c>
+      <c r="G396" s="1" t="n">
         <v>0.004677</v>
       </c>
     </row>
@@ -9165,9 +10356,12 @@
         <v>0.2343</v>
       </c>
       <c r="E397" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="F397" s="1" t="n">
         <v>0.2345</v>
       </c>
-      <c r="F397" s="1" t="n">
+      <c r="G397" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
@@ -9187,9 +10381,12 @@
         <v>0.18106</v>
       </c>
       <c r="E398" s="1" t="n">
+        <v>0.18128</v>
+      </c>
+      <c r="F398" s="1" t="n">
         <v>0.18131</v>
       </c>
-      <c r="F398" s="1" t="n">
+      <c r="G398" s="1" t="n">
         <v>0.18106</v>
       </c>
     </row>
@@ -9209,9 +10406,12 @@
         <v>0.04121</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>0.04121</v>
+        <v>0.04124</v>
       </c>
       <c r="F399" s="1" t="n">
+        <v>0.04124</v>
+      </c>
+      <c r="G399" s="1" t="n">
         <v>0.04108</v>
       </c>
     </row>
@@ -9231,9 +10431,12 @@
         <v>0.076</v>
       </c>
       <c r="E400" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F400" s="1" t="n">
         <v>0.076</v>
       </c>
-      <c r="F400" s="1" t="n">
+      <c r="G400" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -9253,9 +10456,12 @@
         <v>0.001751</v>
       </c>
       <c r="E401" s="1" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="F401" s="1" t="n">
         <v>0.001751</v>
       </c>
-      <c r="F401" s="1" t="n">
+      <c r="G401" s="1" t="n">
         <v>0.001739</v>
       </c>
     </row>
@@ -9275,9 +10481,12 @@
         <v>0.05374</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>0.05391</v>
+        <v>0.05394</v>
       </c>
       <c r="F402" s="1" t="n">
+        <v>0.05394</v>
+      </c>
+      <c r="G402" s="1" t="n">
         <v>0.05362</v>
       </c>
     </row>
@@ -9297,10 +10506,13 @@
         <v>2029.36</v>
       </c>
       <c r="E403" s="1" t="n">
+        <v>2027.43</v>
+      </c>
+      <c r="F403" s="1" t="n">
         <v>2031.8</v>
       </c>
-      <c r="F403" s="1" t="n">
-        <v>2029.36</v>
+      <c r="G403" s="1" t="n">
+        <v>2027.43</v>
       </c>
     </row>
     <row r="404">
@@ -9319,10 +10531,13 @@
         <v>1.08</v>
       </c>
       <c r="E404" s="1" t="n">
+        <v>1.079</v>
+      </c>
+      <c r="F404" s="1" t="n">
         <v>1.082</v>
       </c>
-      <c r="F404" s="1" t="n">
-        <v>1.08</v>
+      <c r="G404" s="1" t="n">
+        <v>1.079</v>
       </c>
     </row>
     <row r="405">
@@ -9341,9 +10556,12 @@
         <v>7.654</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>7.658</v>
+        <v>7.662</v>
       </c>
       <c r="F405" s="1" t="n">
+        <v>7.662</v>
+      </c>
+      <c r="G405" s="1" t="n">
         <v>7.65</v>
       </c>
     </row>
@@ -9363,9 +10581,12 @@
         <v>3.247</v>
       </c>
       <c r="E406" s="1" t="n">
+        <v>3.246</v>
+      </c>
+      <c r="F406" s="1" t="n">
         <v>3.257</v>
       </c>
-      <c r="F406" s="1" t="n">
+      <c r="G406" s="1" t="n">
         <v>3.238</v>
       </c>
     </row>
@@ -9385,9 +10606,12 @@
         <v>0.1816</v>
       </c>
       <c r="E407" s="1" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="F407" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="F407" s="1" t="n">
+      <c r="G407" s="1" t="n">
         <v>0.1814</v>
       </c>
     </row>
@@ -9407,9 +10631,12 @@
         <v>0.1537</v>
       </c>
       <c r="E408" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="F408" s="1" t="n">
         <v>0.1537</v>
       </c>
-      <c r="F408" s="1" t="n">
+      <c r="G408" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -9429,9 +10656,12 @@
         <v>0.07342</v>
       </c>
       <c r="E409" s="1" t="n">
+        <v>0.07345</v>
+      </c>
+      <c r="F409" s="1" t="n">
         <v>0.07346999999999999</v>
       </c>
-      <c r="F409" s="1" t="n">
+      <c r="G409" s="1" t="n">
         <v>0.07315000000000001</v>
       </c>
     </row>
@@ -9451,9 +10681,12 @@
         <v>0.02091</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>0.02091</v>
+        <v>0.02118</v>
       </c>
       <c r="F410" s="1" t="n">
+        <v>0.02118</v>
+      </c>
+      <c r="G410" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -9473,9 +10706,12 @@
         <v>0.2658</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>0.2659</v>
+        <v>0.2666</v>
       </c>
       <c r="F411" s="1" t="n">
+        <v>0.2666</v>
+      </c>
+      <c r="G411" s="1" t="n">
         <v>0.2642</v>
       </c>
     </row>
@@ -9495,9 +10731,12 @@
         <v>0.007356</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>0.007369</v>
+        <v>0.007383</v>
       </c>
       <c r="F412" s="1" t="n">
+        <v>0.007383</v>
+      </c>
+      <c r="G412" s="1" t="n">
         <v>0.007302</v>
       </c>
     </row>
@@ -9517,9 +10756,12 @@
         <v>0.01388</v>
       </c>
       <c r="E413" s="1" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="F413" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="F413" s="1" t="n">
+      <c r="G413" s="1" t="n">
         <v>0.01385</v>
       </c>
     </row>
@@ -9542,6 +10784,9 @@
         <v>0.093</v>
       </c>
       <c r="F414" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G414" s="1" t="n">
         <v>0.092</v>
       </c>
     </row>
@@ -9561,9 +10806,12 @@
         <v>0.04009</v>
       </c>
       <c r="E415" s="1" t="n">
+        <v>0.04004</v>
+      </c>
+      <c r="F415" s="1" t="n">
         <v>0.04009</v>
       </c>
-      <c r="F415" s="1" t="n">
+      <c r="G415" s="1" t="n">
         <v>0.03998</v>
       </c>
     </row>
@@ -9583,10 +10831,13 @@
         <v>0.2841</v>
       </c>
       <c r="E416" s="1" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="F416" s="1" t="n">
         <v>0.2854</v>
       </c>
-      <c r="F416" s="1" t="n">
-        <v>0.2841</v>
+      <c r="G416" s="1" t="n">
+        <v>0.284</v>
       </c>
     </row>
     <row r="417">
@@ -9605,9 +10856,12 @@
         <v>1.821</v>
       </c>
       <c r="E417" s="1" t="n">
+        <v>1.819</v>
+      </c>
+      <c r="F417" s="1" t="n">
         <v>1.821</v>
       </c>
-      <c r="F417" s="1" t="n">
+      <c r="G417" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -9627,9 +10881,12 @@
         <v>0.06675</v>
       </c>
       <c r="E418" s="1" t="n">
+        <v>0.06686</v>
+      </c>
+      <c r="F418" s="1" t="n">
         <v>0.06707</v>
       </c>
-      <c r="F418" s="1" t="n">
+      <c r="G418" s="1" t="n">
         <v>0.06672</v>
       </c>
     </row>
@@ -9649,9 +10906,12 @@
         <v>207.35</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>207.4</v>
+        <v>207.46</v>
       </c>
       <c r="F419" s="1" t="n">
+        <v>207.46</v>
+      </c>
+      <c r="G419" s="1" t="n">
         <v>207.35</v>
       </c>
     </row>
@@ -9671,9 +10931,12 @@
         <v>73.15000000000001</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>73.17</v>
+        <v>73.27</v>
       </c>
       <c r="F420" s="1" t="n">
+        <v>73.27</v>
+      </c>
+      <c r="G420" s="1" t="n">
         <v>73.15000000000001</v>
       </c>
     </row>
@@ -9693,9 +10956,12 @@
         <v>0.07247000000000001</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>0.0725</v>
+        <v>0.07251000000000001</v>
       </c>
       <c r="F421" s="1" t="n">
+        <v>0.07251000000000001</v>
+      </c>
+      <c r="G421" s="1" t="n">
         <v>0.07242</v>
       </c>
     </row>
@@ -9715,9 +10981,12 @@
         <v>0.05005</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>0.05005</v>
+        <v>0.05017</v>
       </c>
       <c r="F422" s="1" t="n">
+        <v>0.05017</v>
+      </c>
+      <c r="G422" s="1" t="n">
         <v>0.04998</v>
       </c>
     </row>
@@ -9740,6 +11009,9 @@
         <v>0.00115</v>
       </c>
       <c r="F423" s="1" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="G423" s="1" t="n">
         <v>0.001148</v>
       </c>
     </row>
@@ -9759,9 +11031,12 @@
         <v>0.00502</v>
       </c>
       <c r="E424" s="1" t="n">
+        <v>0.00502</v>
+      </c>
+      <c r="F424" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="F424" s="1" t="n">
+      <c r="G424" s="1" t="n">
         <v>0.00502</v>
       </c>
     </row>
@@ -9781,9 +11056,12 @@
         <v>0.1266</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>0.1267</v>
+        <v>0.1269</v>
       </c>
       <c r="F425" s="1" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="G425" s="1" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -9803,9 +11081,12 @@
         <v>1.299</v>
       </c>
       <c r="E426" s="1" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="F426" s="1" t="n">
         <v>1.299</v>
       </c>
-      <c r="F426" s="1" t="n">
+      <c r="G426" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -9825,9 +11106,12 @@
         <v>0.004393</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>0.004408</v>
+        <v>0.004413</v>
       </c>
       <c r="F427" s="1" t="n">
+        <v>0.004413</v>
+      </c>
+      <c r="G427" s="1" t="n">
         <v>0.004393</v>
       </c>
     </row>
@@ -9847,9 +11131,12 @@
         <v>0.005041</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>0.005041</v>
+        <v>0.005042</v>
       </c>
       <c r="F428" s="1" t="n">
+        <v>0.005042</v>
+      </c>
+      <c r="G428" s="1" t="n">
         <v>0.005017</v>
       </c>
     </row>
@@ -9869,9 +11156,12 @@
         <v>0.02318</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>0.02323</v>
+        <v>0.02329</v>
       </c>
       <c r="F429" s="1" t="n">
+        <v>0.02329</v>
+      </c>
+      <c r="G429" s="1" t="n">
         <v>0.02288</v>
       </c>
     </row>
@@ -9894,6 +11184,9 @@
         <v>0.02511</v>
       </c>
       <c r="F430" s="1" t="n">
+        <v>0.02511</v>
+      </c>
+      <c r="G430" s="1" t="n">
         <v>0.02501</v>
       </c>
     </row>
@@ -9916,6 +11209,9 @@
         <v>0.016</v>
       </c>
       <c r="F431" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G431" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -9935,9 +11231,12 @@
         <v>0.5441</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>0.5455</v>
+        <v>0.546</v>
       </c>
       <c r="F432" s="1" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="G432" s="1" t="n">
         <v>0.5439000000000001</v>
       </c>
     </row>
@@ -9960,6 +11259,9 @@
         <v>0.001389</v>
       </c>
       <c r="F433" s="1" t="n">
+        <v>0.001389</v>
+      </c>
+      <c r="G433" s="1" t="n">
         <v>0.001383</v>
       </c>
     </row>
@@ -9979,9 +11281,12 @@
         <v>0.3938</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>0.3938</v>
+        <v>0.3949</v>
       </c>
       <c r="F434" s="1" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="G434" s="1" t="n">
         <v>0.3925</v>
       </c>
     </row>
@@ -10001,9 +11306,12 @@
         <v>0.001393</v>
       </c>
       <c r="E435" s="1" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="F435" s="1" t="n">
         <v>0.001393</v>
       </c>
-      <c r="F435" s="1" t="n">
+      <c r="G435" s="1" t="n">
         <v>0.00139</v>
       </c>
     </row>
@@ -10023,9 +11331,12 @@
         <v>0.00714</v>
       </c>
       <c r="E436" s="1" t="n">
+        <v>0.00715</v>
+      </c>
+      <c r="F436" s="1" t="n">
         <v>0.00716</v>
       </c>
-      <c r="F436" s="1" t="n">
+      <c r="G436" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -10045,9 +11356,12 @@
         <v>0.001984</v>
       </c>
       <c r="E437" s="1" t="n">
+        <v>0.001987</v>
+      </c>
+      <c r="F437" s="1" t="n">
         <v>0.001991</v>
       </c>
-      <c r="F437" s="1" t="n">
+      <c r="G437" s="1" t="n">
         <v>0.001982</v>
       </c>
     </row>
@@ -10067,9 +11381,12 @@
         <v>0.3138</v>
       </c>
       <c r="E438" s="1" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="F438" s="1" t="n">
         <v>0.3143</v>
       </c>
-      <c r="F438" s="1" t="n">
+      <c r="G438" s="1" t="n">
         <v>0.3122</v>
       </c>
     </row>
@@ -10089,10 +11406,13 @@
         <v>0.04429</v>
       </c>
       <c r="E439" s="1" t="n">
+        <v>0.04426</v>
+      </c>
+      <c r="F439" s="1" t="n">
         <v>0.04435</v>
       </c>
-      <c r="F439" s="1" t="n">
-        <v>0.04429</v>
+      <c r="G439" s="1" t="n">
+        <v>0.04426</v>
       </c>
     </row>
     <row r="440">
@@ -10111,9 +11431,12 @@
         <v>0.906</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>0.907</v>
+        <v>0.908</v>
       </c>
       <c r="F440" s="1" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="G440" s="1" t="n">
         <v>0.906</v>
       </c>
     </row>
@@ -10133,9 +11456,12 @@
         <v>1548.06</v>
       </c>
       <c r="E441" s="1" t="n">
+        <v>1550.12</v>
+      </c>
+      <c r="F441" s="1" t="n">
         <v>1550.68</v>
       </c>
-      <c r="F441" s="1" t="n">
+      <c r="G441" s="1" t="n">
         <v>1548.06</v>
       </c>
     </row>
@@ -10155,9 +11481,12 @@
         <v>0.000795</v>
       </c>
       <c r="E442" s="1" t="n">
+        <v>0.0007936</v>
+      </c>
+      <c r="F442" s="1" t="n">
         <v>0.0007951</v>
       </c>
-      <c r="F442" s="1" t="n">
+      <c r="G442" s="1" t="n">
         <v>0.0007877</v>
       </c>
     </row>
@@ -10177,10 +11506,13 @@
         <v>0.003549</v>
       </c>
       <c r="E443" s="1" t="n">
+        <v>0.003543</v>
+      </c>
+      <c r="F443" s="1" t="n">
         <v>0.003558</v>
       </c>
-      <c r="F443" s="1" t="n">
-        <v>0.003549</v>
+      <c r="G443" s="1" t="n">
+        <v>0.003543</v>
       </c>
     </row>
     <row r="444">
@@ -10199,9 +11531,12 @@
         <v>1.979</v>
       </c>
       <c r="E444" s="1" t="n">
+        <v>1.979</v>
+      </c>
+      <c r="F444" s="1" t="n">
         <v>1.989</v>
       </c>
-      <c r="F444" s="1" t="n">
+      <c r="G444" s="1" t="n">
         <v>1.979</v>
       </c>
     </row>
@@ -10221,9 +11556,12 @@
         <v>1.302</v>
       </c>
       <c r="E445" s="1" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="F445" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="F445" s="1" t="n">
+      <c r="G445" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -10243,10 +11581,13 @@
         <v>0.06923</v>
       </c>
       <c r="E446" s="1" t="n">
+        <v>0.06906</v>
+      </c>
+      <c r="F446" s="1" t="n">
         <v>0.06929</v>
       </c>
-      <c r="F446" s="1" t="n">
-        <v>0.06920999999999999</v>
+      <c r="G446" s="1" t="n">
+        <v>0.06906</v>
       </c>
     </row>
     <row r="447">
@@ -10265,9 +11606,12 @@
         <v>0.0236</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>0.0236</v>
+        <v>0.0238</v>
       </c>
       <c r="F447" s="1" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="G447" s="1" t="n">
         <v>0.02347</v>
       </c>
     </row>
@@ -10287,9 +11631,12 @@
         <v>0.01392</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>0.01394</v>
+        <v>0.01397</v>
       </c>
       <c r="F448" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="G448" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -10309,9 +11656,12 @@
         <v>3.73</v>
       </c>
       <c r="E449" s="1" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F449" s="1" t="n">
         <v>3.734</v>
       </c>
-      <c r="F449" s="1" t="n">
+      <c r="G449" s="1" t="n">
         <v>3.726</v>
       </c>
     </row>
@@ -10331,9 +11681,12 @@
         <v>0.0114</v>
       </c>
       <c r="E450" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F450" s="1" t="n">
         <v>0.0115</v>
       </c>
-      <c r="F450" s="1" t="n">
+      <c r="G450" s="1" t="n">
         <v>0.0114</v>
       </c>
     </row>
@@ -10356,6 +11709,9 @@
         <v>0.01029</v>
       </c>
       <c r="F451" s="1" t="n">
+        <v>0.01029</v>
+      </c>
+      <c r="G451" s="1" t="n">
         <v>0.01024</v>
       </c>
     </row>
@@ -10375,9 +11731,12 @@
         <v>0.1523</v>
       </c>
       <c r="E452" s="1" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="F452" s="1" t="n">
         <v>0.1525</v>
       </c>
-      <c r="F452" s="1" t="n">
+      <c r="G452" s="1" t="n">
         <v>0.1522</v>
       </c>
     </row>
@@ -10397,9 +11756,12 @@
         <v>150.85</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>150.98</v>
+        <v>151.04</v>
       </c>
       <c r="F453" s="1" t="n">
+        <v>151.04</v>
+      </c>
+      <c r="G453" s="1" t="n">
         <v>150.85</v>
       </c>
     </row>
@@ -10419,9 +11781,12 @@
         <v>0.008616</v>
       </c>
       <c r="E454" s="1" t="n">
+        <v>0.008617</v>
+      </c>
+      <c r="F454" s="1" t="n">
         <v>0.008623</v>
       </c>
-      <c r="F454" s="1" t="n">
+      <c r="G454" s="1" t="n">
         <v>0.008593999999999999</v>
       </c>
     </row>
@@ -10441,9 +11806,12 @@
         <v>0.05241</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>0.05246</v>
+        <v>0.05248</v>
       </c>
       <c r="F455" s="1" t="n">
+        <v>0.05248</v>
+      </c>
+      <c r="G455" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -10463,9 +11831,12 @@
         <v>0.30499</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>0.30499</v>
+        <v>0.30511</v>
       </c>
       <c r="F456" s="1" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="G456" s="1" t="n">
         <v>0.30269</v>
       </c>
     </row>
@@ -10488,6 +11859,9 @@
         <v>0.00546</v>
       </c>
       <c r="F457" s="1" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="G457" s="1" t="n">
         <v>0.00544</v>
       </c>
     </row>
@@ -10507,9 +11881,12 @@
         <v>0.1003</v>
       </c>
       <c r="E458" s="1" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="F458" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="F458" s="1" t="n">
+      <c r="G458" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -10529,9 +11906,12 @@
         <v>0.001835</v>
       </c>
       <c r="E459" s="1" t="n">
+        <v>0.001832</v>
+      </c>
+      <c r="F459" s="1" t="n">
         <v>0.001835</v>
       </c>
-      <c r="F459" s="1" t="n">
+      <c r="G459" s="1" t="n">
         <v>0.001825</v>
       </c>
     </row>
@@ -10551,9 +11931,12 @@
         <v>0.01822</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>0.01829</v>
+        <v>0.01835</v>
       </c>
       <c r="F460" s="1" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="G460" s="1" t="n">
         <v>0.01822</v>
       </c>
     </row>
@@ -10573,10 +11956,13 @@
         <v>0.0004875</v>
       </c>
       <c r="E461" s="1" t="n">
+        <v>0.0004859</v>
+      </c>
+      <c r="F461" s="1" t="n">
         <v>0.0004877</v>
       </c>
-      <c r="F461" s="1" t="n">
-        <v>0.0004874</v>
+      <c r="G461" s="1" t="n">
+        <v>0.0004859</v>
       </c>
     </row>
     <row r="462">
@@ -10595,9 +11981,12 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>0.0958</v>
+        <v>0.096</v>
       </c>
       <c r="F462" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="G462" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -10617,9 +12006,12 @@
         <v>0.07912</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>0.07926</v>
+        <v>0.07931000000000001</v>
       </c>
       <c r="F463" s="1" t="n">
+        <v>0.07931000000000001</v>
+      </c>
+      <c r="G463" s="1" t="n">
         <v>0.07888000000000001</v>
       </c>
     </row>
@@ -10639,9 +12031,12 @@
         <v>0.03151</v>
       </c>
       <c r="E464" s="1" t="n">
+        <v>0.03151</v>
+      </c>
+      <c r="F464" s="1" t="n">
         <v>0.03155</v>
       </c>
-      <c r="F464" s="1" t="n">
+      <c r="G464" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -10661,9 +12056,12 @@
         <v>0.01617</v>
       </c>
       <c r="E465" s="1" t="n">
+        <v>0.01616</v>
+      </c>
+      <c r="F465" s="1" t="n">
         <v>0.01618</v>
       </c>
-      <c r="F465" s="1" t="n">
+      <c r="G465" s="1" t="n">
         <v>0.01613</v>
       </c>
     </row>
@@ -10683,10 +12081,13 @@
         <v>0.06769</v>
       </c>
       <c r="E466" s="1" t="n">
+        <v>0.06764000000000001</v>
+      </c>
+      <c r="F466" s="1" t="n">
         <v>0.06781</v>
       </c>
-      <c r="F466" s="1" t="n">
-        <v>0.06769</v>
+      <c r="G466" s="1" t="n">
+        <v>0.06764000000000001</v>
       </c>
     </row>
     <row r="467">
@@ -10705,9 +12106,12 @@
         <v>0.04325</v>
       </c>
       <c r="E467" s="1" t="n">
+        <v>0.04331</v>
+      </c>
+      <c r="F467" s="1" t="n">
         <v>0.04332</v>
       </c>
-      <c r="F467" s="1" t="n">
+      <c r="G467" s="1" t="n">
         <v>0.04322</v>
       </c>
     </row>
@@ -10727,9 +12131,12 @@
         <v>0.05689</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>0.05689</v>
+        <v>0.05795</v>
       </c>
       <c r="F468" s="1" t="n">
+        <v>0.05795</v>
+      </c>
+      <c r="G468" s="1" t="n">
         <v>0.05587</v>
       </c>
     </row>
@@ -10749,9 +12156,12 @@
         <v>0.2301</v>
       </c>
       <c r="E469" s="1" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="F469" s="1" t="n">
         <v>0.2305</v>
       </c>
-      <c r="F469" s="1" t="n">
+      <c r="G469" s="1" t="n">
         <v>0.2294</v>
       </c>
     </row>
@@ -10771,9 +12181,12 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0905</v>
       </c>
       <c r="F470" s="1" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="G470" s="1" t="n">
         <v>0.0902</v>
       </c>
     </row>
@@ -10793,9 +12206,12 @@
         <v>0.06669</v>
       </c>
       <c r="E471" s="1" t="n">
+        <v>0.06677</v>
+      </c>
+      <c r="F471" s="1" t="n">
         <v>0.0669</v>
       </c>
-      <c r="F471" s="1" t="n">
+      <c r="G471" s="1" t="n">
         <v>0.06669</v>
       </c>
     </row>
@@ -10815,9 +12231,12 @@
         <v>6.525</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>6.525</v>
+        <v>6.527</v>
       </c>
       <c r="F472" s="1" t="n">
+        <v>6.527</v>
+      </c>
+      <c r="G472" s="1" t="n">
         <v>6.486</v>
       </c>
     </row>
@@ -10837,10 +12256,13 @@
         <v>0.01941</v>
       </c>
       <c r="E473" s="1" t="n">
+        <v>0.01937</v>
+      </c>
+      <c r="F473" s="1" t="n">
         <v>0.01943</v>
       </c>
-      <c r="F473" s="1" t="n">
-        <v>0.01938</v>
+      <c r="G473" s="1" t="n">
+        <v>0.01937</v>
       </c>
     </row>
     <row r="474">
@@ -10859,9 +12281,12 @@
         <v>1.421</v>
       </c>
       <c r="E474" s="1" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="F474" s="1" t="n">
         <v>1.423</v>
       </c>
-      <c r="F474" s="1" t="n">
+      <c r="G474" s="1" t="n">
         <v>1.421</v>
       </c>
     </row>
@@ -10881,9 +12306,12 @@
         <v>0.08974</v>
       </c>
       <c r="E475" s="1" t="n">
+        <v>0.08977</v>
+      </c>
+      <c r="F475" s="1" t="n">
         <v>0.0898</v>
       </c>
-      <c r="F475" s="1" t="n">
+      <c r="G475" s="1" t="n">
         <v>0.08974</v>
       </c>
     </row>
@@ -10903,9 +12331,12 @@
         <v>0.1062</v>
       </c>
       <c r="E476" s="1" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="F476" s="1" t="n">
         <v>0.1062</v>
       </c>
-      <c r="F476" s="1" t="n">
+      <c r="G476" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -10925,9 +12356,12 @@
         <v>0.09437</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>0.09437</v>
+        <v>0.09451</v>
       </c>
       <c r="F477" s="1" t="n">
+        <v>0.09451</v>
+      </c>
+      <c r="G477" s="1" t="n">
         <v>0.09427000000000001</v>
       </c>
     </row>
@@ -10947,9 +12381,12 @@
         <v>0.0001627</v>
       </c>
       <c r="E478" s="1" t="n">
+        <v>0.0001628</v>
+      </c>
+      <c r="F478" s="1" t="n">
         <v>0.0001629</v>
       </c>
-      <c r="F478" s="1" t="n">
+      <c r="G478" s="1" t="n">
         <v>0.0001624</v>
       </c>
     </row>
@@ -10969,9 +12406,12 @@
         <v>0.04023</v>
       </c>
       <c r="E479" s="1" t="n">
+        <v>0.04018</v>
+      </c>
+      <c r="F479" s="1" t="n">
         <v>0.04023</v>
       </c>
-      <c r="F479" s="1" t="n">
+      <c r="G479" s="1" t="n">
         <v>0.04007</v>
       </c>
     </row>
@@ -10991,9 +12431,12 @@
         <v>0.007395</v>
       </c>
       <c r="E480" s="1" t="n">
+        <v>0.007407</v>
+      </c>
+      <c r="F480" s="1" t="n">
         <v>0.007422</v>
       </c>
-      <c r="F480" s="1" t="n">
+      <c r="G480" s="1" t="n">
         <v>0.007389</v>
       </c>
     </row>
@@ -11016,6 +12459,9 @@
         <v>0.0955</v>
       </c>
       <c r="F481" s="1" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="G481" s="1" t="n">
         <v>0.0954</v>
       </c>
     </row>
@@ -11035,10 +12481,13 @@
         <v>0.056</v>
       </c>
       <c r="E482" s="1" t="n">
+        <v>0.05594</v>
+      </c>
+      <c r="F482" s="1" t="n">
         <v>0.05621</v>
       </c>
-      <c r="F482" s="1" t="n">
-        <v>0.05595</v>
+      <c r="G482" s="1" t="n">
+        <v>0.05594</v>
       </c>
     </row>
     <row r="483">
@@ -11057,9 +12506,12 @@
         <v>0.006172</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>0.006194</v>
+        <v>0.006195</v>
       </c>
       <c r="F483" s="1" t="n">
+        <v>0.006195</v>
+      </c>
+      <c r="G483" s="1" t="n">
         <v>0.006161</v>
       </c>
     </row>
@@ -11079,9 +12531,12 @@
         <v>0.01492</v>
       </c>
       <c r="E484" s="1" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="F484" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="F484" s="1" t="n">
+      <c r="G484" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -11101,9 +12556,12 @@
         <v>0.02403</v>
       </c>
       <c r="E485" s="1" t="n">
+        <v>0.02413</v>
+      </c>
+      <c r="F485" s="1" t="n">
         <v>0.02427</v>
       </c>
-      <c r="F485" s="1" t="n">
+      <c r="G485" s="1" t="n">
         <v>0.02403</v>
       </c>
     </row>
@@ -11123,9 +12581,12 @@
         <v>0.06687</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>0.06687</v>
+        <v>0.06702</v>
       </c>
       <c r="F486" s="1" t="n">
+        <v>0.06702</v>
+      </c>
+      <c r="G486" s="1" t="n">
         <v>0.0667</v>
       </c>
     </row>
@@ -11145,9 +12606,12 @@
         <v>0.0368</v>
       </c>
       <c r="E487" s="1" t="n">
+        <v>0.03693</v>
+      </c>
+      <c r="F487" s="1" t="n">
         <v>0.03705</v>
       </c>
-      <c r="F487" s="1" t="n">
+      <c r="G487" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -11167,9 +12631,12 @@
         <v>0.01814</v>
       </c>
       <c r="E488" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="F488" s="1" t="n">
         <v>0.0182</v>
       </c>
-      <c r="F488" s="1" t="n">
+      <c r="G488" s="1" t="n">
         <v>0.01814</v>
       </c>
     </row>
@@ -11189,9 +12656,12 @@
         <v>0.0325</v>
       </c>
       <c r="E489" s="1" t="n">
+        <v>0.03254</v>
+      </c>
+      <c r="F489" s="1" t="n">
         <v>0.03278</v>
       </c>
-      <c r="F489" s="1" t="n">
+      <c r="G489" s="1" t="n">
         <v>0.0325</v>
       </c>
     </row>
@@ -11211,9 +12681,12 @@
         <v>0.01474</v>
       </c>
       <c r="E490" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="F490" s="1" t="n">
         <v>0.01474</v>
       </c>
-      <c r="F490" s="1" t="n">
+      <c r="G490" s="1" t="n">
         <v>0.01458</v>
       </c>
     </row>
@@ -11233,9 +12706,12 @@
         <v>0.01858</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>0.01859</v>
+        <v>0.01861</v>
       </c>
       <c r="F491" s="1" t="n">
+        <v>0.01861</v>
+      </c>
+      <c r="G491" s="1" t="n">
         <v>0.01851</v>
       </c>
     </row>
@@ -11255,9 +12731,12 @@
         <v>0.08842</v>
       </c>
       <c r="E492" s="1" t="n">
+        <v>0.08919000000000001</v>
+      </c>
+      <c r="F492" s="1" t="n">
         <v>0.08935</v>
       </c>
-      <c r="F492" s="1" t="n">
+      <c r="G492" s="1" t="n">
         <v>0.08842</v>
       </c>
     </row>
@@ -11277,9 +12756,12 @@
         <v>0.006509</v>
       </c>
       <c r="E493" s="1" t="n">
+        <v>0.006506</v>
+      </c>
+      <c r="F493" s="1" t="n">
         <v>0.006514</v>
       </c>
-      <c r="F493" s="1" t="n">
+      <c r="G493" s="1" t="n">
         <v>0.006498</v>
       </c>
     </row>
@@ -11299,9 +12781,12 @@
         <v>0.1322</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>0.1324</v>
+        <v>0.1327</v>
       </c>
       <c r="F494" s="1" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="G494" s="1" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -11321,9 +12806,12 @@
         <v>0.2844</v>
       </c>
       <c r="E495" s="1" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="F495" s="1" t="n">
         <v>0.2853</v>
       </c>
-      <c r="F495" s="1" t="n">
+      <c r="G495" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -11343,9 +12831,12 @@
         <v>0.00452</v>
       </c>
       <c r="E496" s="1" t="n">
+        <v>0.004518</v>
+      </c>
+      <c r="F496" s="1" t="n">
         <v>0.004534</v>
       </c>
-      <c r="F496" s="1" t="n">
+      <c r="G496" s="1" t="n">
         <v>0.004516</v>
       </c>
     </row>
@@ -11365,10 +12856,13 @@
         <v>0.1277</v>
       </c>
       <c r="E497" s="1" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="F497" s="1" t="n">
         <v>0.1283</v>
       </c>
-      <c r="F497" s="1" t="n">
-        <v>0.1272</v>
+      <c r="G497" s="1" t="n">
+        <v>0.1265</v>
       </c>
     </row>
     <row r="498">
@@ -11387,9 +12881,12 @@
         <v>0.03423</v>
       </c>
       <c r="E498" s="1" t="n">
+        <v>0.03428</v>
+      </c>
+      <c r="F498" s="1" t="n">
         <v>0.03439</v>
       </c>
-      <c r="F498" s="1" t="n">
+      <c r="G498" s="1" t="n">
         <v>0.03423</v>
       </c>
     </row>
@@ -11409,9 +12906,12 @@
         <v>0.03565</v>
       </c>
       <c r="E499" s="1" t="n">
+        <v>0.03559</v>
+      </c>
+      <c r="F499" s="1" t="n">
         <v>0.03576</v>
       </c>
-      <c r="F499" s="1" t="n">
+      <c r="G499" s="1" t="n">
         <v>0.03557</v>
       </c>
     </row>
@@ -11431,9 +12931,12 @@
         <v>0.003418</v>
       </c>
       <c r="E500" s="1" t="n">
+        <v>0.003417</v>
+      </c>
+      <c r="F500" s="1" t="n">
         <v>0.003421</v>
       </c>
-      <c r="F500" s="1" t="n">
+      <c r="G500" s="1" t="n">
         <v>0.003417</v>
       </c>
     </row>
@@ -11453,9 +12956,12 @@
         <v>0.0003798</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>0.0003799</v>
+        <v>0.0003809</v>
       </c>
       <c r="F501" s="1" t="n">
+        <v>0.0003809</v>
+      </c>
+      <c r="G501" s="1" t="n">
         <v>0.0003786</v>
       </c>
     </row>
@@ -11478,6 +12984,9 @@
         <v>0.3003</v>
       </c>
       <c r="F502" s="1" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="G502" s="1" t="n">
         <v>0.2986</v>
       </c>
     </row>
@@ -11497,10 +13006,13 @@
         <v>0.06497</v>
       </c>
       <c r="E503" s="1" t="n">
+        <v>0.06494999999999999</v>
+      </c>
+      <c r="F503" s="1" t="n">
         <v>0.06507</v>
       </c>
-      <c r="F503" s="1" t="n">
-        <v>0.06497</v>
+      <c r="G503" s="1" t="n">
+        <v>0.06494999999999999</v>
       </c>
     </row>
     <row r="504">
@@ -11522,6 +13034,9 @@
         <v>0.1777</v>
       </c>
       <c r="F504" s="1" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="G504" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -11544,6 +13059,9 @@
         <v>0.1513</v>
       </c>
       <c r="F505" s="1" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="G505" s="1" t="n">
         <v>0.1512</v>
       </c>
     </row>
@@ -11563,9 +13081,12 @@
         <v>0.01195</v>
       </c>
       <c r="E506" s="1" t="n">
+        <v>0.01196</v>
+      </c>
+      <c r="F506" s="1" t="n">
         <v>0.01198</v>
       </c>
-      <c r="F506" s="1" t="n">
+      <c r="G506" s="1" t="n">
         <v>0.01193</v>
       </c>
     </row>
@@ -11585,10 +13106,13 @@
         <v>0.2877</v>
       </c>
       <c r="E507" s="1" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="F507" s="1" t="n">
         <v>0.2883</v>
       </c>
-      <c r="F507" s="1" t="n">
-        <v>0.2875</v>
+      <c r="G507" s="1" t="n">
+        <v>0.2871</v>
       </c>
     </row>
     <row r="508">
@@ -11607,10 +13131,13 @@
         <v>0.009339999999999999</v>
       </c>
       <c r="E508" s="1" t="n">
+        <v>0.00933</v>
+      </c>
+      <c r="F508" s="1" t="n">
         <v>0.0094</v>
       </c>
-      <c r="F508" s="1" t="n">
-        <v>0.009339999999999999</v>
+      <c r="G508" s="1" t="n">
+        <v>0.00933</v>
       </c>
     </row>
     <row r="509">
@@ -11629,9 +13156,12 @@
         <v>0.006783</v>
       </c>
       <c r="E509" s="1" t="n">
+        <v>0.006795</v>
+      </c>
+      <c r="F509" s="1" t="n">
         <v>0.006816</v>
       </c>
-      <c r="F509" s="1" t="n">
+      <c r="G509" s="1" t="n">
         <v>0.006783</v>
       </c>
     </row>
@@ -11651,9 +13181,12 @@
         <v>0.2945</v>
       </c>
       <c r="E510" s="1" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="F510" s="1" t="n">
         <v>0.2951</v>
       </c>
-      <c r="F510" s="1" t="n">
+      <c r="G510" s="1" t="n">
         <v>0.2936</v>
       </c>
     </row>
@@ -11673,10 +13206,13 @@
         <v>0.01468</v>
       </c>
       <c r="E511" s="1" t="n">
+        <v>0.01466</v>
+      </c>
+      <c r="F511" s="1" t="n">
         <v>0.01471</v>
       </c>
-      <c r="F511" s="1" t="n">
-        <v>0.01467</v>
+      <c r="G511" s="1" t="n">
+        <v>0.01466</v>
       </c>
     </row>
     <row r="512">
@@ -11695,9 +13231,12 @@
         <v>0.1395</v>
       </c>
       <c r="E512" s="1" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="F512" s="1" t="n">
         <v>0.1398</v>
       </c>
-      <c r="F512" s="1" t="n">
+      <c r="G512" s="1" t="n">
         <v>0.1395</v>
       </c>
     </row>
@@ -11717,9 +13256,12 @@
         <v>0.08128000000000001</v>
       </c>
       <c r="E513" s="1" t="n">
+        <v>0.08112</v>
+      </c>
+      <c r="F513" s="1" t="n">
         <v>0.08144999999999999</v>
       </c>
-      <c r="F513" s="1" t="n">
+      <c r="G513" s="1" t="n">
         <v>0.08069</v>
       </c>
     </row>
@@ -11739,9 +13281,12 @@
         <v>0.025</v>
       </c>
       <c r="E514" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F514" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="F514" s="1" t="n">
+      <c r="G514" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -11761,9 +13306,12 @@
         <v>0.06311</v>
       </c>
       <c r="E515" s="1" t="n">
+        <v>0.06307</v>
+      </c>
+      <c r="F515" s="1" t="n">
         <v>0.06319</v>
       </c>
-      <c r="F515" s="1" t="n">
+      <c r="G515" s="1" t="n">
         <v>0.06301</v>
       </c>
     </row>
@@ -11783,9 +13331,12 @@
         <v>0.04713</v>
       </c>
       <c r="E516" s="1" t="n">
+        <v>0.04722</v>
+      </c>
+      <c r="F516" s="1" t="n">
         <v>0.04723</v>
       </c>
-      <c r="F516" s="1" t="n">
+      <c r="G516" s="1" t="n">
         <v>0.04707</v>
       </c>
     </row>
@@ -11805,10 +13356,13 @@
         <v>0.004908</v>
       </c>
       <c r="E517" s="1" t="n">
+        <v>0.004904</v>
+      </c>
+      <c r="F517" s="1" t="n">
         <v>0.004908</v>
       </c>
-      <c r="F517" s="1" t="n">
-        <v>0.004906</v>
+      <c r="G517" s="1" t="n">
+        <v>0.004904</v>
       </c>
     </row>
     <row r="518">
@@ -11827,9 +13381,12 @@
         <v>0.009429999999999999</v>
       </c>
       <c r="E518" s="1" t="n">
+        <v>0.009426</v>
+      </c>
+      <c r="F518" s="1" t="n">
         <v>0.009429999999999999</v>
       </c>
-      <c r="F518" s="1" t="n">
+      <c r="G518" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -11849,10 +13406,13 @@
         <v>0.01807</v>
       </c>
       <c r="E519" s="1" t="n">
+        <v>0.01798</v>
+      </c>
+      <c r="F519" s="1" t="n">
         <v>0.01807</v>
       </c>
-      <c r="F519" s="1" t="n">
-        <v>0.01803</v>
+      <c r="G519" s="1" t="n">
+        <v>0.01798</v>
       </c>
     </row>
     <row r="520">
@@ -11871,9 +13431,12 @@
         <v>0.06648999999999999</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>0.06666999999999999</v>
+        <v>0.06684</v>
       </c>
       <c r="F520" s="1" t="n">
+        <v>0.06684</v>
+      </c>
+      <c r="G520" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -11893,9 +13456,12 @@
         <v>0.136</v>
       </c>
       <c r="E521" s="1" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="F521" s="1" t="n">
         <v>0.1365</v>
       </c>
-      <c r="F521" s="1" t="n">
+      <c r="G521" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -11915,9 +13481,12 @@
         <v>0.04736</v>
       </c>
       <c r="E522" s="1" t="n">
+        <v>0.04741</v>
+      </c>
+      <c r="F522" s="1" t="n">
         <v>0.04746</v>
       </c>
-      <c r="F522" s="1" t="n">
+      <c r="G522" s="1" t="n">
         <v>0.04718</v>
       </c>
     </row>
@@ -11937,9 +13506,12 @@
         <v>0.06798</v>
       </c>
       <c r="E523" s="1" t="n">
+        <v>0.06798999999999999</v>
+      </c>
+      <c r="F523" s="1" t="n">
         <v>0.06809</v>
       </c>
-      <c r="F523" s="1" t="n">
+      <c r="G523" s="1" t="n">
         <v>0.06793</v>
       </c>
     </row>
@@ -11959,9 +13531,12 @@
         <v>0.6966</v>
       </c>
       <c r="E524" s="1" t="n">
+        <v>0.6981000000000001</v>
+      </c>
+      <c r="F524" s="1" t="n">
         <v>0.6982</v>
       </c>
-      <c r="F524" s="1" t="n">
+      <c r="G524" s="1" t="n">
         <v>0.6966</v>
       </c>
     </row>
@@ -11986,6 +13561,9 @@
       <c r="F525" s="1" t="n">
         <v>0.00267</v>
       </c>
+      <c r="G525" s="1" t="n">
+        <v>0.00267</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -12003,9 +13581,12 @@
         <v>0.4864</v>
       </c>
       <c r="E526" s="1" t="n">
+        <v>0.4865</v>
+      </c>
+      <c r="F526" s="1" t="n">
         <v>0.4868</v>
       </c>
-      <c r="F526" s="1" t="n">
+      <c r="G526" s="1" t="n">
         <v>0.4856</v>
       </c>
     </row>
@@ -12025,9 +13606,12 @@
         <v>45.8</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>45.81</v>
+        <v>45.82</v>
       </c>
       <c r="F527" s="1" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="G527" s="1" t="n">
         <v>45.76</v>
       </c>
     </row>
@@ -12047,10 +13631,13 @@
         <v>0.02434</v>
       </c>
       <c r="E528" s="1" t="n">
+        <v>0.02431</v>
+      </c>
+      <c r="F528" s="1" t="n">
         <v>0.02437</v>
       </c>
-      <c r="F528" s="1" t="n">
-        <v>0.02434</v>
+      <c r="G528" s="1" t="n">
+        <v>0.02431</v>
       </c>
     </row>
     <row r="529">
@@ -12069,9 +13656,12 @@
         <v>0.00638</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>0.006388</v>
+        <v>0.006392</v>
       </c>
       <c r="F529" s="1" t="n">
+        <v>0.006392</v>
+      </c>
+      <c r="G529" s="1" t="n">
         <v>0.00638</v>
       </c>
     </row>
@@ -12091,9 +13681,12 @@
         <v>0.1998</v>
       </c>
       <c r="E530" s="1" t="n">
+        <v>0.1995</v>
+      </c>
+      <c r="F530" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="F530" s="1" t="n">
+      <c r="G530" s="1" t="n">
         <v>0.1993</v>
       </c>
     </row>
@@ -12113,9 +13706,12 @@
         <v>0.007671</v>
       </c>
       <c r="E531" s="1" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="F531" s="1" t="n">
         <v>0.007727</v>
       </c>
-      <c r="F531" s="1" t="n">
+      <c r="G531" s="1" t="n">
         <v>0.007657</v>
       </c>
     </row>
@@ -12135,9 +13731,12 @@
         <v>2.283</v>
       </c>
       <c r="E532" s="1" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="F532" s="1" t="n">
         <v>2.285</v>
       </c>
-      <c r="F532" s="1" t="n">
+      <c r="G532" s="1" t="n">
         <v>2.275</v>
       </c>
     </row>
@@ -12157,9 +13756,12 @@
         <v>0.04138</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>0.04142</v>
+        <v>0.04148</v>
       </c>
       <c r="F533" s="1" t="n">
+        <v>0.04148</v>
+      </c>
+      <c r="G533" s="1" t="n">
         <v>0.04138</v>
       </c>
     </row>
@@ -12179,9 +13781,12 @@
         <v>0.1819</v>
       </c>
       <c r="E534" s="1" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="F534" s="1" t="n">
         <v>0.1819</v>
       </c>
-      <c r="F534" s="1" t="n">
+      <c r="G534" s="1" t="n">
         <v>0.1811</v>
       </c>
     </row>
@@ -12201,10 +13806,13 @@
         <v>0.04291</v>
       </c>
       <c r="E535" s="1" t="n">
+        <v>0.04287</v>
+      </c>
+      <c r="F535" s="1" t="n">
         <v>0.04311</v>
       </c>
-      <c r="F535" s="1" t="n">
-        <v>0.04291</v>
+      <c r="G535" s="1" t="n">
+        <v>0.04287</v>
       </c>
     </row>
     <row r="536">
@@ -12223,9 +13831,12 @@
         <v>0.0543</v>
       </c>
       <c r="E536" s="1" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="F536" s="1" t="n">
         <v>0.05438</v>
       </c>
-      <c r="F536" s="1" t="n">
+      <c r="G536" s="1" t="n">
         <v>0.0542</v>
       </c>
     </row>
@@ -12245,9 +13856,12 @@
         <v>0.1606</v>
       </c>
       <c r="E537" s="1" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="F537" s="1" t="n">
         <v>0.1609</v>
       </c>
-      <c r="F537" s="1" t="n">
+      <c r="G537" s="1" t="n">
         <v>0.1605</v>
       </c>
     </row>
@@ -12267,9 +13881,12 @@
         <v>0.03672</v>
       </c>
       <c r="E538" s="1" t="n">
+        <v>0.03677</v>
+      </c>
+      <c r="F538" s="1" t="n">
         <v>0.03687</v>
       </c>
-      <c r="F538" s="1" t="n">
+      <c r="G538" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -12289,9 +13906,12 @@
         <v>0.05775</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>0.05775</v>
+        <v>0.05776</v>
       </c>
       <c r="F539" s="1" t="n">
+        <v>0.05776</v>
+      </c>
+      <c r="G539" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -12311,9 +13931,12 @@
         <v>0.04257</v>
       </c>
       <c r="E540" s="1" t="n">
+        <v>0.04258</v>
+      </c>
+      <c r="F540" s="1" t="n">
         <v>0.04267</v>
       </c>
-      <c r="F540" s="1" t="n">
+      <c r="G540" s="1" t="n">
         <v>0.04257</v>
       </c>
     </row>
@@ -12333,9 +13956,12 @@
         <v>0.0173</v>
       </c>
       <c r="E541" s="1" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="F541" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="F541" s="1" t="n">
+      <c r="G541" s="1" t="n">
         <v>0.0172</v>
       </c>
     </row>
@@ -12355,10 +13981,13 @@
         <v>0.003972</v>
       </c>
       <c r="E542" s="1" t="n">
+        <v>0.00397</v>
+      </c>
+      <c r="F542" s="1" t="n">
         <v>0.003975</v>
       </c>
-      <c r="F542" s="1" t="n">
-        <v>0.003971</v>
+      <c r="G542" s="1" t="n">
+        <v>0.00397</v>
       </c>
     </row>
     <row r="543">
@@ -12377,9 +14006,12 @@
         <v>0.05749</v>
       </c>
       <c r="E543" s="1" t="n">
+        <v>0.05781</v>
+      </c>
+      <c r="F543" s="1" t="n">
         <v>0.05817</v>
       </c>
-      <c r="F543" s="1" t="n">
+      <c r="G543" s="1" t="n">
         <v>0.05735</v>
       </c>
     </row>
@@ -12399,10 +14031,13 @@
         <v>0.05034</v>
       </c>
       <c r="E544" s="1" t="n">
+        <v>0.05016</v>
+      </c>
+      <c r="F544" s="1" t="n">
         <v>0.05042</v>
       </c>
-      <c r="F544" s="1" t="n">
-        <v>0.05022</v>
+      <c r="G544" s="1" t="n">
+        <v>0.05016</v>
       </c>
     </row>
     <row r="545">
@@ -12421,9 +14056,12 @@
         <v>0.04041</v>
       </c>
       <c r="E545" s="1" t="n">
+        <v>0.04045</v>
+      </c>
+      <c r="F545" s="1" t="n">
         <v>0.04064</v>
       </c>
-      <c r="F545" s="1" t="n">
+      <c r="G545" s="1" t="n">
         <v>0.04038</v>
       </c>
     </row>
@@ -12443,9 +14081,12 @@
         <v>0.00743</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>0.00743</v>
+        <v>0.007432</v>
       </c>
       <c r="F546" s="1" t="n">
+        <v>0.007432</v>
+      </c>
+      <c r="G546" s="1" t="n">
         <v>0.007402</v>
       </c>
     </row>
@@ -12465,9 +14106,12 @@
         <v>0.01464</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>0.01464</v>
+        <v>0.01466</v>
       </c>
       <c r="F547" s="1" t="n">
+        <v>0.01466</v>
+      </c>
+      <c r="G547" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -12487,9 +14131,12 @@
         <v>0.01573</v>
       </c>
       <c r="E548" s="1" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="F548" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="F548" s="1" t="n">
+      <c r="G548" s="1" t="n">
         <v>0.01572</v>
       </c>
     </row>
@@ -12509,9 +14156,12 @@
         <v>0.13434</v>
       </c>
       <c r="E549" s="1" t="n">
+        <v>0.13429</v>
+      </c>
+      <c r="F549" s="1" t="n">
         <v>0.13434</v>
       </c>
-      <c r="F549" s="1" t="n">
+      <c r="G549" s="1" t="n">
         <v>0.13271</v>
       </c>
     </row>
@@ -12534,6 +14184,9 @@
         <v>0.1696</v>
       </c>
       <c r="F550" s="1" t="n">
+        <v>0.1696</v>
+      </c>
+      <c r="G550" s="1" t="n">
         <v>0.1695</v>
       </c>
     </row>
@@ -12553,9 +14206,12 @@
         <v>0.003579</v>
       </c>
       <c r="E551" s="1" t="n">
+        <v>0.003579</v>
+      </c>
+      <c r="F551" s="1" t="n">
         <v>0.003583</v>
       </c>
-      <c r="F551" s="1" t="n">
+      <c r="G551" s="1" t="n">
         <v>0.003577</v>
       </c>
     </row>
@@ -12575,9 +14231,12 @@
         <v>0.03038</v>
       </c>
       <c r="E552" s="1" t="n">
+        <v>0.03037</v>
+      </c>
+      <c r="F552" s="1" t="n">
         <v>0.03038</v>
       </c>
-      <c r="F552" s="1" t="n">
+      <c r="G552" s="1" t="n">
         <v>0.03032</v>
       </c>
     </row>
@@ -12597,9 +14256,12 @@
         <v>0.01325</v>
       </c>
       <c r="E553" s="1" t="n">
+        <v>0.01324</v>
+      </c>
+      <c r="F553" s="1" t="n">
         <v>0.01325</v>
       </c>
-      <c r="F553" s="1" t="n">
+      <c r="G553" s="1" t="n">
         <v>0.01324</v>
       </c>
     </row>
@@ -12619,10 +14281,13 @@
         <v>0.1042</v>
       </c>
       <c r="E554" s="1" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="F554" s="1" t="n">
         <v>0.1046</v>
       </c>
-      <c r="F554" s="1" t="n">
-        <v>0.1042</v>
+      <c r="G554" s="1" t="n">
+        <v>0.1039</v>
       </c>
     </row>
     <row r="555">
@@ -12641,9 +14306,12 @@
         <v>0.053</v>
       </c>
       <c r="E555" s="1" t="n">
+        <v>0.05304</v>
+      </c>
+      <c r="F555" s="1" t="n">
         <v>0.05319</v>
       </c>
-      <c r="F555" s="1" t="n">
+      <c r="G555" s="1" t="n">
         <v>0.05291</v>
       </c>
     </row>
@@ -12663,10 +14331,13 @@
         <v>0.01224</v>
       </c>
       <c r="E556" s="1" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="F556" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="F556" s="1" t="n">
-        <v>0.01223</v>
+      <c r="G556" s="1" t="n">
+        <v>0.0122</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G556"/>
+  <dimension ref="A1:H556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -424,8 +424,9 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,10 +457,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>price_01:00</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -484,9 +490,12 @@
         <v>71413.2</v>
       </c>
       <c r="F2" s="1" t="n">
+        <v>71390.89999999999</v>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>71530</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="H2" s="1" t="n">
         <v>71364.39999999999</v>
       </c>
     </row>
@@ -509,10 +518,13 @@
         <v>2092.33</v>
       </c>
       <c r="F3" s="1" t="n">
+        <v>2090.41</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>2096.9</v>
       </c>
-      <c r="G3" s="1" t="n">
-        <v>2091.71</v>
+      <c r="H3" s="1" t="n">
+        <v>2090.41</v>
       </c>
     </row>
     <row r="4">
@@ -534,10 +546,13 @@
         <v>87.66</v>
       </c>
       <c r="F4" s="1" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>87.95</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>87.66</v>
+      <c r="H4" s="1" t="n">
+        <v>87.47</v>
       </c>
     </row>
     <row r="5">
@@ -559,10 +574,13 @@
         <v>23.512</v>
       </c>
       <c r="F5" s="1" t="n">
+        <v>23.329</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>23.579</v>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>23.478</v>
+      <c r="H5" s="1" t="n">
+        <v>23.329</v>
       </c>
     </row>
     <row r="6">
@@ -584,9 +602,12 @@
         <v>0.001892</v>
       </c>
       <c r="F6" s="1" t="n">
+        <v>0.001878</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>0.001892</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>0.001827</v>
       </c>
     </row>
@@ -609,10 +630,13 @@
         <v>1.4135</v>
       </c>
       <c r="F7" s="1" t="n">
+        <v>1.4117</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>1.4149</v>
       </c>
-      <c r="G7" s="1" t="n">
-        <v>1.4135</v>
+      <c r="H7" s="1" t="n">
+        <v>1.4117</v>
       </c>
     </row>
     <row r="8">
@@ -634,10 +658,13 @@
         <v>0.010846</v>
       </c>
       <c r="F8" s="1" t="n">
+        <v>0.010738</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>0.011244</v>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>0.010846</v>
+      <c r="H8" s="1" t="n">
+        <v>0.010738</v>
       </c>
     </row>
     <row r="9">
@@ -659,9 +686,12 @@
         <v>3.979</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>3.979</v>
+        <v>4.062</v>
       </c>
       <c r="G9" s="1" t="n">
+        <v>4.062</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <v>3.954</v>
       </c>
     </row>
@@ -684,9 +714,12 @@
         <v>272.11</v>
       </c>
       <c r="F10" s="1" t="n">
+        <v>274.18</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>275.37</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="H10" s="1" t="n">
         <v>272.11</v>
       </c>
     </row>
@@ -709,10 +742,13 @@
         <v>0.07904</v>
       </c>
       <c r="F11" s="1" t="n">
+        <v>0.07854999999999999</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>0.08047</v>
       </c>
-      <c r="G11" s="1" t="n">
-        <v>0.07904</v>
+      <c r="H11" s="1" t="n">
+        <v>0.07854999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +770,13 @@
         <v>224.51</v>
       </c>
       <c r="F12" s="1" t="n">
+        <v>223.76</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>227.69</v>
       </c>
-      <c r="G12" s="1" t="n">
-        <v>224.51</v>
+      <c r="H12" s="1" t="n">
+        <v>223.76</v>
       </c>
     </row>
     <row r="13">
@@ -759,10 +798,13 @@
         <v>0.0948</v>
       </c>
       <c r="F13" s="1" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>0.09497</v>
       </c>
-      <c r="G13" s="1" t="n">
-        <v>0.09464</v>
+      <c r="H13" s="1" t="n">
+        <v>0.0946</v>
       </c>
     </row>
     <row r="14">
@@ -784,10 +826,13 @@
         <v>37.127</v>
       </c>
       <c r="F14" s="1" t="n">
+        <v>37.089</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>37.279</v>
       </c>
-      <c r="G14" s="1" t="n">
-        <v>37.127</v>
+      <c r="H14" s="1" t="n">
+        <v>37.089</v>
       </c>
     </row>
     <row r="15">
@@ -809,9 +854,12 @@
         <v>0.09589</v>
       </c>
       <c r="F15" s="1" t="n">
+        <v>0.09525</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>0.09845</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="H15" s="1" t="n">
         <v>0.09461</v>
       </c>
     </row>
@@ -834,9 +882,12 @@
         <v>0.2256</v>
       </c>
       <c r="F16" s="1" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>0.2339</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="H16" s="1" t="n">
         <v>0.2256</v>
       </c>
     </row>
@@ -859,10 +910,13 @@
         <v>0.011501</v>
       </c>
       <c r="F17" s="1" t="n">
+        <v>0.011493</v>
+      </c>
+      <c r="G17" s="1" t="n">
         <v>0.011542</v>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>0.011501</v>
+      <c r="H17" s="1" t="n">
+        <v>0.011493</v>
       </c>
     </row>
     <row r="18">
@@ -884,10 +938,13 @@
         <v>659.5599999999999</v>
       </c>
       <c r="F18" s="1" t="n">
+        <v>658.89</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <v>660.72</v>
       </c>
-      <c r="G18" s="1" t="n">
-        <v>659.5599999999999</v>
+      <c r="H18" s="1" t="n">
+        <v>658.89</v>
       </c>
     </row>
     <row r="19">
@@ -909,10 +966,13 @@
         <v>0.0033321</v>
       </c>
       <c r="F19" s="1" t="n">
+        <v>0.0033271</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>0.0033451</v>
       </c>
-      <c r="G19" s="1" t="n">
-        <v>0.0033295</v>
+      <c r="H19" s="1" t="n">
+        <v>0.0033271</v>
       </c>
     </row>
     <row r="20">
@@ -934,9 +994,12 @@
         <v>0.17675</v>
       </c>
       <c r="F20" s="1" t="n">
+        <v>0.17839</v>
+      </c>
+      <c r="G20" s="1" t="n">
         <v>0.18017</v>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="H20" s="1" t="n">
         <v>0.17675</v>
       </c>
     </row>
@@ -959,9 +1022,12 @@
         <v>0.010044</v>
       </c>
       <c r="F21" s="1" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>0.010044</v>
       </c>
-      <c r="G21" s="1" t="n">
+      <c r="H21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -984,10 +1050,13 @@
         <v>1.0007</v>
       </c>
       <c r="F22" s="1" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="G22" s="1" t="n">
         <v>1.0033</v>
       </c>
-      <c r="G22" s="1" t="n">
-        <v>1</v>
+      <c r="H22" s="1" t="n">
+        <v>0.9985000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1009,10 +1078,13 @@
         <v>5006.75</v>
       </c>
       <c r="F23" s="1" t="n">
+        <v>5003.05</v>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>5012.25</v>
       </c>
-      <c r="G23" s="1" t="n">
-        <v>5003.45</v>
+      <c r="H23" s="1" t="n">
+        <v>5003.05</v>
       </c>
     </row>
     <row r="24">
@@ -1034,10 +1106,13 @@
         <v>0.2632</v>
       </c>
       <c r="F24" s="1" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>0.2643</v>
       </c>
-      <c r="G24" s="1" t="n">
-        <v>0.2632</v>
+      <c r="H24" s="1" t="n">
+        <v>0.2625</v>
       </c>
     </row>
     <row r="25">
@@ -1059,9 +1134,12 @@
         <v>2.917</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>2.917</v>
+        <v>2.924</v>
       </c>
       <c r="G25" s="1" t="n">
+        <v>2.924</v>
+      </c>
+      <c r="H25" s="1" t="n">
         <v>2.899</v>
       </c>
     </row>
@@ -1084,9 +1162,12 @@
         <v>0.4096</v>
       </c>
       <c r="F26" s="1" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>0.4096</v>
       </c>
-      <c r="G26" s="1" t="n">
+      <c r="H26" s="1" t="n">
         <v>0.3959</v>
       </c>
     </row>
@@ -1109,10 +1190,13 @@
         <v>0.883</v>
       </c>
       <c r="F27" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="G27" s="1" t="n">
         <v>0.885</v>
       </c>
-      <c r="G27" s="1" t="n">
-        <v>0.883</v>
+      <c r="H27" s="1" t="n">
+        <v>0.881</v>
       </c>
     </row>
     <row r="28">
@@ -1134,10 +1218,13 @@
         <v>1.338</v>
       </c>
       <c r="F28" s="1" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>1.343</v>
       </c>
-      <c r="G28" s="1" t="n">
-        <v>1.336</v>
+      <c r="H28" s="1" t="n">
+        <v>1.335</v>
       </c>
     </row>
     <row r="29">
@@ -1159,10 +1246,13 @@
         <v>9.145</v>
       </c>
       <c r="F29" s="1" t="n">
+        <v>9.131</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>9.179</v>
       </c>
-      <c r="G29" s="1" t="n">
-        <v>9.145</v>
+      <c r="H29" s="1" t="n">
+        <v>9.131</v>
       </c>
     </row>
     <row r="30">
@@ -1184,10 +1274,13 @@
         <v>461.3</v>
       </c>
       <c r="F30" s="1" t="n">
+        <v>461.24</v>
+      </c>
+      <c r="G30" s="1" t="n">
         <v>463.35</v>
       </c>
-      <c r="G30" s="1" t="n">
-        <v>461.3</v>
+      <c r="H30" s="1" t="n">
+        <v>461.24</v>
       </c>
     </row>
     <row r="31">
@@ -1209,9 +1302,12 @@
         <v>9.720000000000001</v>
       </c>
       <c r="F31" s="1" t="n">
+        <v>9.699</v>
+      </c>
+      <c r="G31" s="1" t="n">
         <v>9.728999999999999</v>
       </c>
-      <c r="G31" s="1" t="n">
+      <c r="H31" s="1" t="n">
         <v>9.696999999999999</v>
       </c>
     </row>
@@ -1234,10 +1330,13 @@
         <v>0.36285</v>
       </c>
       <c r="F32" s="1" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>0.36683</v>
       </c>
-      <c r="G32" s="1" t="n">
-        <v>0.36285</v>
+      <c r="H32" s="1" t="n">
+        <v>0.36159</v>
       </c>
     </row>
     <row r="33">
@@ -1259,10 +1358,13 @@
         <v>1.411</v>
       </c>
       <c r="F33" s="1" t="n">
+        <v>1.409</v>
+      </c>
+      <c r="G33" s="1" t="n">
         <v>1.419</v>
       </c>
-      <c r="G33" s="1" t="n">
-        <v>1.411</v>
+      <c r="H33" s="1" t="n">
+        <v>1.409</v>
       </c>
     </row>
     <row r="34">
@@ -1284,9 +1386,12 @@
         <v>0.59693</v>
       </c>
       <c r="F34" s="1" t="n">
+        <v>0.59383</v>
+      </c>
+      <c r="G34" s="1" t="n">
         <v>0.59693</v>
       </c>
-      <c r="G34" s="1" t="n">
+      <c r="H34" s="1" t="n">
         <v>0.5926900000000001</v>
       </c>
     </row>
@@ -1309,9 +1414,12 @@
         <v>1.2205</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>1.2228</v>
+        <v>1.2236</v>
       </c>
       <c r="G35" s="1" t="n">
+        <v>1.2236</v>
+      </c>
+      <c r="H35" s="1" t="n">
         <v>1.2186</v>
       </c>
     </row>
@@ -1334,9 +1442,12 @@
         <v>80.37</v>
       </c>
       <c r="F36" s="1" t="n">
+        <v>80.31</v>
+      </c>
+      <c r="G36" s="1" t="n">
         <v>80.5</v>
       </c>
-      <c r="G36" s="1" t="n">
+      <c r="H36" s="1" t="n">
         <v>80.27</v>
       </c>
     </row>
@@ -1359,9 +1470,12 @@
         <v>0.1996</v>
       </c>
       <c r="F37" s="1" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="G37" s="1" t="n">
         <v>0.204</v>
       </c>
-      <c r="G37" s="1" t="n">
+      <c r="H37" s="1" t="n">
         <v>0.1977</v>
       </c>
     </row>
@@ -1384,9 +1498,12 @@
         <v>1.853</v>
       </c>
       <c r="F38" s="1" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="G38" s="1" t="n">
         <v>1.865</v>
       </c>
-      <c r="G38" s="1" t="n">
+      <c r="H38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -1409,9 +1526,12 @@
         <v>0.3283</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.3283</v>
+        <v>0.3338</v>
       </c>
       <c r="G39" s="1" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="H39" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -1434,9 +1554,12 @@
         <v>0.899</v>
       </c>
       <c r="F40" s="1" t="n">
+        <v>0.9011</v>
+      </c>
+      <c r="G40" s="1" t="n">
         <v>0.9115</v>
       </c>
-      <c r="G40" s="1" t="n">
+      <c r="H40" s="1" t="n">
         <v>0.899</v>
       </c>
     </row>
@@ -1459,10 +1582,13 @@
         <v>0.7147</v>
       </c>
       <c r="F41" s="1" t="n">
+        <v>0.7131</v>
+      </c>
+      <c r="G41" s="1" t="n">
         <v>0.7149</v>
       </c>
-      <c r="G41" s="1" t="n">
-        <v>0.7136</v>
+      <c r="H41" s="1" t="n">
+        <v>0.7131</v>
       </c>
     </row>
     <row r="42">
@@ -1484,10 +1610,13 @@
         <v>0.0665</v>
       </c>
       <c r="F42" s="1" t="n">
+        <v>0.06622</v>
+      </c>
+      <c r="G42" s="1" t="n">
         <v>0.06769</v>
       </c>
-      <c r="G42" s="1" t="n">
-        <v>0.0665</v>
+      <c r="H42" s="1" t="n">
+        <v>0.06622</v>
       </c>
     </row>
     <row r="43">
@@ -1509,9 +1638,12 @@
         <v>113.06</v>
       </c>
       <c r="F43" s="1" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="G43" s="1" t="n">
         <v>113.57</v>
       </c>
-      <c r="G43" s="1" t="n">
+      <c r="H43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -1534,9 +1666,12 @@
         <v>0.6593</v>
       </c>
       <c r="F44" s="1" t="n">
+        <v>0.6584</v>
+      </c>
+      <c r="G44" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="G44" s="1" t="n">
+      <c r="H44" s="1" t="n">
         <v>0.6578000000000001</v>
       </c>
     </row>
@@ -1559,9 +1694,12 @@
         <v>1.216</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>1.216</v>
+        <v>1.218</v>
       </c>
       <c r="G45" s="1" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="H45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -1584,9 +1722,12 @@
         <v>0.02376</v>
       </c>
       <c r="F46" s="1" t="n">
+        <v>0.02377</v>
+      </c>
+      <c r="G46" s="1" t="n">
         <v>0.02392</v>
       </c>
-      <c r="G46" s="1" t="n">
+      <c r="H46" s="1" t="n">
         <v>0.02376</v>
       </c>
     </row>
@@ -1609,10 +1750,13 @@
         <v>55.04</v>
       </c>
       <c r="F47" s="1" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="G47" s="1" t="n">
         <v>55.17</v>
       </c>
-      <c r="G47" s="1" t="n">
-        <v>55.04</v>
+      <c r="H47" s="1" t="n">
+        <v>54.99</v>
       </c>
     </row>
     <row r="48">
@@ -1634,9 +1778,12 @@
         <v>0.06021</v>
       </c>
       <c r="F48" s="1" t="n">
+        <v>0.06032</v>
+      </c>
+      <c r="G48" s="1" t="n">
         <v>0.06081</v>
       </c>
-      <c r="G48" s="1" t="n">
+      <c r="H48" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -1659,10 +1806,13 @@
         <v>0.1078</v>
       </c>
       <c r="F49" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="G49" s="1" t="n">
         <v>0.1082</v>
       </c>
-      <c r="G49" s="1" t="n">
-        <v>0.1078</v>
+      <c r="H49" s="1" t="n">
+        <v>0.1076</v>
       </c>
     </row>
     <row r="50">
@@ -1684,9 +1834,12 @@
         <v>0.01808</v>
       </c>
       <c r="F50" s="1" t="n">
+        <v>0.01806</v>
+      </c>
+      <c r="G50" s="1" t="n">
         <v>0.01815</v>
       </c>
-      <c r="G50" s="1" t="n">
+      <c r="H50" s="1" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -1709,9 +1862,12 @@
         <v>1.4618</v>
       </c>
       <c r="F51" s="1" t="n">
+        <v>1.4646</v>
+      </c>
+      <c r="G51" s="1" t="n">
         <v>1.4659</v>
       </c>
-      <c r="G51" s="1" t="n">
+      <c r="H51" s="1" t="n">
         <v>1.4618</v>
       </c>
     </row>
@@ -1734,9 +1890,12 @@
         <v>0.3589</v>
       </c>
       <c r="F52" s="1" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="G52" s="1" t="n">
         <v>0.3603</v>
       </c>
-      <c r="G52" s="1" t="n">
+      <c r="H52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -1759,10 +1918,13 @@
         <v>0.001946</v>
       </c>
       <c r="F53" s="1" t="n">
+        <v>0.001942</v>
+      </c>
+      <c r="G53" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="G53" s="1" t="n">
-        <v>0.001946</v>
+      <c r="H53" s="1" t="n">
+        <v>0.001942</v>
       </c>
     </row>
     <row r="54">
@@ -1784,10 +1946,13 @@
         <v>0.09537</v>
       </c>
       <c r="F54" s="1" t="n">
+        <v>0.09514</v>
+      </c>
+      <c r="G54" s="1" t="n">
         <v>0.09569</v>
       </c>
-      <c r="G54" s="1" t="n">
-        <v>0.09524000000000001</v>
+      <c r="H54" s="1" t="n">
+        <v>0.09514</v>
       </c>
     </row>
     <row r="55">
@@ -1809,9 +1974,12 @@
         <v>0.04084</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.04084</v>
+        <v>0.04087</v>
       </c>
       <c r="G55" s="1" t="n">
+        <v>0.04087</v>
+      </c>
+      <c r="H55" s="1" t="n">
         <v>0.04003</v>
       </c>
     </row>
@@ -1834,9 +2002,12 @@
         <v>0.29831</v>
       </c>
       <c r="F56" s="1" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="G56" s="1" t="n">
         <v>0.29861</v>
       </c>
-      <c r="G56" s="1" t="n">
+      <c r="H56" s="1" t="n">
         <v>0.29831</v>
       </c>
     </row>
@@ -1859,10 +2030,13 @@
         <v>0.005752</v>
       </c>
       <c r="F57" s="1" t="n">
+        <v>0.005716</v>
+      </c>
+      <c r="G57" s="1" t="n">
         <v>0.005824</v>
       </c>
-      <c r="G57" s="1" t="n">
-        <v>0.005752</v>
+      <c r="H57" s="1" t="n">
+        <v>0.005716</v>
       </c>
     </row>
     <row r="58">
@@ -1884,10 +2058,13 @@
         <v>4993.56</v>
       </c>
       <c r="F58" s="1" t="n">
+        <v>4989.99</v>
+      </c>
+      <c r="G58" s="1" t="n">
         <v>4998.37</v>
       </c>
-      <c r="G58" s="1" t="n">
-        <v>4991.64</v>
+      <c r="H58" s="1" t="n">
+        <v>4989.99</v>
       </c>
     </row>
     <row r="59">
@@ -1909,9 +2086,12 @@
         <v>0.4126</v>
       </c>
       <c r="F59" s="1" t="n">
+        <v>0.4137</v>
+      </c>
+      <c r="G59" s="1" t="n">
         <v>0.4246</v>
       </c>
-      <c r="G59" s="1" t="n">
+      <c r="H59" s="1" t="n">
         <v>0.4126</v>
       </c>
     </row>
@@ -1934,9 +2114,12 @@
         <v>0.04677</v>
       </c>
       <c r="F60" s="1" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="G60" s="1" t="n">
         <v>0.04683</v>
       </c>
-      <c r="G60" s="1" t="n">
+      <c r="H60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -1959,10 +2142,13 @@
         <v>0.21568</v>
       </c>
       <c r="F61" s="1" t="n">
+        <v>0.21432</v>
+      </c>
+      <c r="G61" s="1" t="n">
         <v>0.21708</v>
       </c>
-      <c r="G61" s="1" t="n">
-        <v>0.21568</v>
+      <c r="H61" s="1" t="n">
+        <v>0.21432</v>
       </c>
     </row>
     <row r="62">
@@ -1984,9 +2170,12 @@
         <v>0.1065</v>
       </c>
       <c r="F62" s="1" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="G62" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="G62" s="1" t="n">
+      <c r="H62" s="1" t="n">
         <v>0.1065</v>
       </c>
     </row>
@@ -2009,10 +2198,13 @@
         <v>0.727</v>
       </c>
       <c r="F63" s="1" t="n">
+        <v>0.7255</v>
+      </c>
+      <c r="G63" s="1" t="n">
         <v>0.7301</v>
       </c>
-      <c r="G63" s="1" t="n">
-        <v>0.7267</v>
+      <c r="H63" s="1" t="n">
+        <v>0.7255</v>
       </c>
     </row>
     <row r="64">
@@ -2034,10 +2226,13 @@
         <v>0.166</v>
       </c>
       <c r="F64" s="1" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="G64" s="1" t="n">
         <v>0.1667</v>
       </c>
-      <c r="G64" s="1" t="n">
-        <v>0.166</v>
+      <c r="H64" s="1" t="n">
+        <v>0.1658</v>
       </c>
     </row>
     <row r="65">
@@ -2059,9 +2254,12 @@
         <v>2.656</v>
       </c>
       <c r="F65" s="1" t="n">
+        <v>2.651</v>
+      </c>
+      <c r="G65" s="1" t="n">
         <v>2.661</v>
       </c>
-      <c r="G65" s="1" t="n">
+      <c r="H65" s="1" t="n">
         <v>2.65</v>
       </c>
     </row>
@@ -2087,6 +2285,9 @@
         <v>0.04056</v>
       </c>
       <c r="G66" s="1" t="n">
+        <v>0.04056</v>
+      </c>
+      <c r="H66" s="1" t="n">
         <v>0.04018</v>
       </c>
     </row>
@@ -2109,9 +2310,12 @@
         <v>0.04254</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>0.04254</v>
+        <v>0.04261</v>
       </c>
       <c r="G67" s="1" t="n">
+        <v>0.04261</v>
+      </c>
+      <c r="H67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -2134,10 +2338,13 @@
         <v>3.956</v>
       </c>
       <c r="F68" s="1" t="n">
+        <v>3.951</v>
+      </c>
+      <c r="G68" s="1" t="n">
         <v>3.967</v>
       </c>
-      <c r="G68" s="1" t="n">
-        <v>3.952</v>
+      <c r="H68" s="1" t="n">
+        <v>3.951</v>
       </c>
     </row>
     <row r="69">
@@ -2159,9 +2366,12 @@
         <v>0.1257</v>
       </c>
       <c r="F69" s="1" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="G69" s="1" t="n">
         <v>0.1261</v>
       </c>
-      <c r="G69" s="1" t="n">
+      <c r="H69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -2184,9 +2394,12 @@
         <v>6.204</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>6.207</v>
+        <v>6.307</v>
       </c>
       <c r="G70" s="1" t="n">
+        <v>6.307</v>
+      </c>
+      <c r="H70" s="1" t="n">
         <v>6.114</v>
       </c>
     </row>
@@ -2209,10 +2422,13 @@
         <v>0.04989</v>
       </c>
       <c r="F71" s="1" t="n">
+        <v>0.04959</v>
+      </c>
+      <c r="G71" s="1" t="n">
         <v>0.04999</v>
       </c>
-      <c r="G71" s="1" t="n">
-        <v>0.04989</v>
+      <c r="H71" s="1" t="n">
+        <v>0.04959</v>
       </c>
     </row>
     <row r="72">
@@ -2234,9 +2450,12 @@
         <v>0.004163</v>
       </c>
       <c r="F72" s="1" t="n">
+        <v>0.004148</v>
+      </c>
+      <c r="G72" s="1" t="n">
         <v>0.004181</v>
       </c>
-      <c r="G72" s="1" t="n">
+      <c r="H72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -2259,10 +2478,13 @@
         <v>5.975</v>
       </c>
       <c r="F73" s="1" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="G73" s="1" t="n">
         <v>6.029</v>
       </c>
-      <c r="G73" s="1" t="n">
-        <v>5.975</v>
+      <c r="H73" s="1" t="n">
+        <v>5.96</v>
       </c>
     </row>
     <row r="74">
@@ -2284,10 +2506,13 @@
         <v>0.1624</v>
       </c>
       <c r="F74" s="1" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="G74" s="1" t="n">
         <v>0.1633</v>
       </c>
-      <c r="G74" s="1" t="n">
-        <v>0.1624</v>
+      <c r="H74" s="1" t="n">
+        <v>0.1619</v>
       </c>
     </row>
     <row r="75">
@@ -2309,10 +2534,13 @@
         <v>0.007272</v>
       </c>
       <c r="F75" s="1" t="n">
+        <v>0.007261</v>
+      </c>
+      <c r="G75" s="1" t="n">
         <v>0.007297</v>
       </c>
-      <c r="G75" s="1" t="n">
-        <v>0.007272</v>
+      <c r="H75" s="1" t="n">
+        <v>0.007261</v>
       </c>
     </row>
     <row r="76">
@@ -2334,9 +2562,12 @@
         <v>0.2102</v>
       </c>
       <c r="F76" s="1" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="G76" s="1" t="n">
         <v>0.2102</v>
       </c>
-      <c r="G76" s="1" t="n">
+      <c r="H76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -2359,10 +2590,13 @@
         <v>0.005802</v>
       </c>
       <c r="F77" s="1" t="n">
+        <v>0.005796</v>
+      </c>
+      <c r="G77" s="1" t="n">
         <v>0.005826</v>
       </c>
-      <c r="G77" s="1" t="n">
-        <v>0.005799</v>
+      <c r="H77" s="1" t="n">
+        <v>0.005796</v>
       </c>
     </row>
     <row r="78">
@@ -2384,9 +2618,12 @@
         <v>0.1015</v>
       </c>
       <c r="F78" s="1" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="G78" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="G78" s="1" t="n">
+      <c r="H78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -2409,10 +2646,13 @@
         <v>0.006261</v>
       </c>
       <c r="F79" s="1" t="n">
+        <v>0.006237</v>
+      </c>
+      <c r="G79" s="1" t="n">
         <v>0.006292</v>
       </c>
-      <c r="G79" s="1" t="n">
-        <v>0.006256</v>
+      <c r="H79" s="1" t="n">
+        <v>0.006237</v>
       </c>
     </row>
     <row r="80">
@@ -2434,9 +2674,12 @@
         <v>33.36</v>
       </c>
       <c r="F80" s="1" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="G80" s="1" t="n">
         <v>33.51</v>
       </c>
-      <c r="G80" s="1" t="n">
+      <c r="H80" s="1" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -2459,9 +2702,12 @@
         <v>0.0405</v>
       </c>
       <c r="F81" s="1" t="n">
+        <v>0.04038</v>
+      </c>
+      <c r="G81" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="G81" s="1" t="n">
+      <c r="H81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -2484,10 +2730,13 @@
         <v>0.16746</v>
       </c>
       <c r="F82" s="1" t="n">
+        <v>0.16679</v>
+      </c>
+      <c r="G82" s="1" t="n">
         <v>0.1675</v>
       </c>
-      <c r="G82" s="1" t="n">
-        <v>0.16688</v>
+      <c r="H82" s="1" t="n">
+        <v>0.16679</v>
       </c>
     </row>
     <row r="83">
@@ -2509,9 +2758,12 @@
         <v>0.1032</v>
       </c>
       <c r="F83" s="1" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="G83" s="1" t="n">
         <v>0.1035</v>
       </c>
-      <c r="G83" s="1" t="n">
+      <c r="H83" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -2534,10 +2786,13 @@
         <v>0.08848</v>
       </c>
       <c r="F84" s="1" t="n">
+        <v>0.08803999999999999</v>
+      </c>
+      <c r="G84" s="1" t="n">
         <v>0.08848</v>
       </c>
-      <c r="G84" s="1" t="n">
-        <v>0.08810999999999999</v>
+      <c r="H84" s="1" t="n">
+        <v>0.08803999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -2559,9 +2814,12 @@
         <v>0.02311</v>
       </c>
       <c r="F85" s="1" t="n">
+        <v>0.02311</v>
+      </c>
+      <c r="G85" s="1" t="n">
         <v>0.02331</v>
       </c>
-      <c r="G85" s="1" t="n">
+      <c r="H85" s="1" t="n">
         <v>0.02311</v>
       </c>
     </row>
@@ -2584,9 +2842,12 @@
         <v>0.239</v>
       </c>
       <c r="F86" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="G86" s="1" t="n">
         <v>0.239</v>
       </c>
-      <c r="G86" s="1" t="n">
+      <c r="H86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -2609,9 +2870,12 @@
         <v>357.39</v>
       </c>
       <c r="F87" s="1" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="G87" s="1" t="n">
         <v>357.4</v>
       </c>
-      <c r="G87" s="1" t="n">
+      <c r="H87" s="1" t="n">
         <v>355.75</v>
       </c>
     </row>
@@ -2634,9 +2898,12 @@
         <v>0.00345</v>
       </c>
       <c r="F88" s="1" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="G88" s="1" t="n">
         <v>0.00345</v>
       </c>
-      <c r="G88" s="1" t="n">
+      <c r="H88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -2659,10 +2926,13 @@
         <v>8.276999999999999</v>
       </c>
       <c r="F89" s="1" t="n">
+        <v>8.257</v>
+      </c>
+      <c r="G89" s="1" t="n">
         <v>8.301</v>
       </c>
-      <c r="G89" s="1" t="n">
-        <v>8.272</v>
+      <c r="H89" s="1" t="n">
+        <v>8.257</v>
       </c>
     </row>
     <row r="90">
@@ -2684,10 +2954,13 @@
         <v>0.005916</v>
       </c>
       <c r="F90" s="1" t="n">
+        <v>0.005905</v>
+      </c>
+      <c r="G90" s="1" t="n">
         <v>0.005945</v>
       </c>
-      <c r="G90" s="1" t="n">
-        <v>0.00591</v>
+      <c r="H90" s="1" t="n">
+        <v>0.005905</v>
       </c>
     </row>
     <row r="91">
@@ -2709,10 +2982,13 @@
         <v>0.06841999999999999</v>
       </c>
       <c r="F91" s="1" t="n">
+        <v>0.06837</v>
+      </c>
+      <c r="G91" s="1" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="G91" s="1" t="n">
-        <v>0.06841999999999999</v>
+      <c r="H91" s="1" t="n">
+        <v>0.06837</v>
       </c>
     </row>
     <row r="92">
@@ -2734,9 +3010,12 @@
         <v>0.02869</v>
       </c>
       <c r="F92" s="1" t="n">
+        <v>0.02885</v>
+      </c>
+      <c r="G92" s="1" t="n">
         <v>0.02894</v>
       </c>
-      <c r="G92" s="1" t="n">
+      <c r="H92" s="1" t="n">
         <v>0.02869</v>
       </c>
     </row>
@@ -2759,9 +3038,12 @@
         <v>5.183</v>
       </c>
       <c r="F93" s="1" t="n">
+        <v>5.169</v>
+      </c>
+      <c r="G93" s="1" t="n">
         <v>5.202</v>
       </c>
-      <c r="G93" s="1" t="n">
+      <c r="H93" s="1" t="n">
         <v>5.159</v>
       </c>
     </row>
@@ -2787,6 +3069,9 @@
         <v>0.000228</v>
       </c>
       <c r="G94" s="1" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="H94" s="1" t="n">
         <v>0.000226</v>
       </c>
     </row>
@@ -2809,9 +3094,12 @@
         <v>0.9211</v>
       </c>
       <c r="F95" s="1" t="n">
+        <v>0.9195</v>
+      </c>
+      <c r="G95" s="1" t="n">
         <v>0.9241</v>
       </c>
-      <c r="G95" s="1" t="n">
+      <c r="H95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -2834,9 +3122,12 @@
         <v>2.0648</v>
       </c>
       <c r="F96" s="1" t="n">
+        <v>2.0731</v>
+      </c>
+      <c r="G96" s="1" t="n">
         <v>2.0774</v>
       </c>
-      <c r="G96" s="1" t="n">
+      <c r="H96" s="1" t="n">
         <v>2.0598</v>
       </c>
     </row>
@@ -2859,9 +3150,12 @@
         <v>0.3686</v>
       </c>
       <c r="F97" s="1" t="n">
-        <v>0.3711</v>
+        <v>0.3722</v>
       </c>
       <c r="G97" s="1" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="H97" s="1" t="n">
         <v>0.3686</v>
       </c>
     </row>
@@ -2884,9 +3178,12 @@
         <v>1.616</v>
       </c>
       <c r="F98" s="1" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="G98" s="1" t="n">
         <v>1.618</v>
       </c>
-      <c r="G98" s="1" t="n">
+      <c r="H98" s="1" t="n">
         <v>1.613</v>
       </c>
     </row>
@@ -2909,9 +3206,12 @@
         <v>0.2363</v>
       </c>
       <c r="F99" s="1" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="G99" s="1" t="n">
         <v>0.2368</v>
       </c>
-      <c r="G99" s="1" t="n">
+      <c r="H99" s="1" t="n">
         <v>0.2351</v>
       </c>
     </row>
@@ -2934,9 +3234,12 @@
         <v>0.13655</v>
       </c>
       <c r="F100" s="1" t="n">
+        <v>0.13549</v>
+      </c>
+      <c r="G100" s="1" t="n">
         <v>0.13665</v>
       </c>
-      <c r="G100" s="1" t="n">
+      <c r="H100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -2959,9 +3262,12 @@
         <v>0.07094</v>
       </c>
       <c r="F101" s="1" t="n">
+        <v>0.07045</v>
+      </c>
+      <c r="G101" s="1" t="n">
         <v>0.07115</v>
       </c>
-      <c r="G101" s="1" t="n">
+      <c r="H101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -2984,10 +3290,13 @@
         <v>0.0010875</v>
       </c>
       <c r="F102" s="1" t="n">
+        <v>0.0010832</v>
+      </c>
+      <c r="G102" s="1" t="n">
         <v>0.0010875</v>
       </c>
-      <c r="G102" s="1" t="n">
-        <v>0.001084</v>
+      <c r="H102" s="1" t="n">
+        <v>0.0010832</v>
       </c>
     </row>
     <row r="103">
@@ -3009,10 +3318,13 @@
         <v>0.003404</v>
       </c>
       <c r="F103" s="1" t="n">
+        <v>0.003403</v>
+      </c>
+      <c r="G103" s="1" t="n">
         <v>0.003424</v>
       </c>
-      <c r="G103" s="1" t="n">
-        <v>0.003404</v>
+      <c r="H103" s="1" t="n">
+        <v>0.003403</v>
       </c>
     </row>
     <row r="104">
@@ -3034,10 +3346,13 @@
         <v>0.27548</v>
       </c>
       <c r="F104" s="1" t="n">
+        <v>0.27534</v>
+      </c>
+      <c r="G104" s="1" t="n">
         <v>0.27751</v>
       </c>
-      <c r="G104" s="1" t="n">
-        <v>0.27548</v>
+      <c r="H104" s="1" t="n">
+        <v>0.27534</v>
       </c>
     </row>
     <row r="105">
@@ -3059,9 +3374,12 @@
         <v>0.01254</v>
       </c>
       <c r="F105" s="1" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="G105" s="1" t="n">
         <v>0.01257</v>
       </c>
-      <c r="G105" s="1" t="n">
+      <c r="H105" s="1" t="n">
         <v>0.01243</v>
       </c>
     </row>
@@ -3084,9 +3402,12 @@
         <v>0.13329</v>
       </c>
       <c r="F106" s="1" t="n">
+        <v>0.13453</v>
+      </c>
+      <c r="G106" s="1" t="n">
         <v>0.13569</v>
       </c>
-      <c r="G106" s="1" t="n">
+      <c r="H106" s="1" t="n">
         <v>0.13329</v>
       </c>
     </row>
@@ -3109,9 +3430,12 @@
         <v>0.3482</v>
       </c>
       <c r="F107" s="1" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="G107" s="1" t="n">
         <v>0.3496</v>
       </c>
-      <c r="G107" s="1" t="n">
+      <c r="H107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -3134,9 +3458,12 @@
         <v>0.1434</v>
       </c>
       <c r="F108" s="1" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="G108" s="1" t="n">
         <v>0.1436</v>
       </c>
-      <c r="G108" s="1" t="n">
+      <c r="H108" s="1" t="n">
         <v>0.1426</v>
       </c>
     </row>
@@ -3162,6 +3489,9 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="G109" s="1" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="H109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -3184,10 +3514,13 @@
         <v>0.016223</v>
       </c>
       <c r="F110" s="1" t="n">
+        <v>0.016195</v>
+      </c>
+      <c r="G110" s="1" t="n">
         <v>0.016308</v>
       </c>
-      <c r="G110" s="1" t="n">
-        <v>0.016223</v>
+      <c r="H110" s="1" t="n">
+        <v>0.016195</v>
       </c>
     </row>
     <row r="111">
@@ -3209,9 +3542,12 @@
         <v>0.038268</v>
       </c>
       <c r="F111" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="G111" s="1" t="n">
         <v>0.038335</v>
       </c>
-      <c r="G111" s="1" t="n">
+      <c r="H111" s="1" t="n">
         <v>0.03774</v>
       </c>
     </row>
@@ -3234,9 +3570,12 @@
         <v>0.12031</v>
       </c>
       <c r="F112" s="1" t="n">
+        <v>0.11991</v>
+      </c>
+      <c r="G112" s="1" t="n">
         <v>0.12031</v>
       </c>
-      <c r="G112" s="1" t="n">
+      <c r="H112" s="1" t="n">
         <v>0.11926</v>
       </c>
     </row>
@@ -3259,9 +3598,12 @@
         <v>0.09517</v>
       </c>
       <c r="F113" s="1" t="n">
-        <v>0.09517</v>
+        <v>0.09555</v>
       </c>
       <c r="G113" s="1" t="n">
+        <v>0.09555</v>
+      </c>
+      <c r="H113" s="1" t="n">
         <v>0.09426</v>
       </c>
     </row>
@@ -3284,9 +3626,12 @@
         <v>0.12904</v>
       </c>
       <c r="F114" s="1" t="n">
-        <v>0.1299</v>
+        <v>0.13002</v>
       </c>
       <c r="G114" s="1" t="n">
+        <v>0.13002</v>
+      </c>
+      <c r="H114" s="1" t="n">
         <v>0.12895</v>
       </c>
     </row>
@@ -3309,10 +3654,13 @@
         <v>0.2644</v>
       </c>
       <c r="F115" s="1" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="G115" s="1" t="n">
         <v>0.2656</v>
       </c>
-      <c r="G115" s="1" t="n">
-        <v>0.264</v>
+      <c r="H115" s="1" t="n">
+        <v>0.2638</v>
       </c>
     </row>
     <row r="116">
@@ -3334,10 +3682,13 @@
         <v>0.04943</v>
       </c>
       <c r="F116" s="1" t="n">
+        <v>0.04891</v>
+      </c>
+      <c r="G116" s="1" t="n">
         <v>0.0529</v>
       </c>
-      <c r="G116" s="1" t="n">
-        <v>0.04943</v>
+      <c r="H116" s="1" t="n">
+        <v>0.04891</v>
       </c>
     </row>
     <row r="117">
@@ -3359,10 +3710,13 @@
         <v>0.0914</v>
       </c>
       <c r="F117" s="1" t="n">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="G117" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="G117" s="1" t="n">
-        <v>0.0914</v>
+      <c r="H117" s="1" t="n">
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="118">
@@ -3384,9 +3738,12 @@
         <v>0.05563</v>
       </c>
       <c r="F118" s="1" t="n">
+        <v>0.05517</v>
+      </c>
+      <c r="G118" s="1" t="n">
         <v>0.05563</v>
       </c>
-      <c r="G118" s="1" t="n">
+      <c r="H118" s="1" t="n">
         <v>0.05509</v>
       </c>
     </row>
@@ -3409,10 +3766,13 @@
         <v>0.01509</v>
       </c>
       <c r="F119" s="1" t="n">
+        <v>0.01505</v>
+      </c>
+      <c r="G119" s="1" t="n">
         <v>0.01515</v>
       </c>
-      <c r="G119" s="1" t="n">
-        <v>0.01509</v>
+      <c r="H119" s="1" t="n">
+        <v>0.01505</v>
       </c>
     </row>
     <row r="120">
@@ -3434,9 +3794,12 @@
         <v>3.054</v>
       </c>
       <c r="F120" s="1" t="n">
+        <v>3.051</v>
+      </c>
+      <c r="G120" s="1" t="n">
         <v>3.06</v>
       </c>
-      <c r="G120" s="1" t="n">
+      <c r="H120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -3459,10 +3822,13 @@
         <v>1.85</v>
       </c>
       <c r="F121" s="1" t="n">
+        <v>1.849</v>
+      </c>
+      <c r="G121" s="1" t="n">
         <v>1.855</v>
       </c>
-      <c r="G121" s="1" t="n">
-        <v>1.85</v>
+      <c r="H121" s="1" t="n">
+        <v>1.849</v>
       </c>
     </row>
     <row r="122">
@@ -3484,9 +3850,12 @@
         <v>1.2946</v>
       </c>
       <c r="F122" s="1" t="n">
+        <v>1.2942</v>
+      </c>
+      <c r="G122" s="1" t="n">
         <v>1.2965</v>
       </c>
-      <c r="G122" s="1" t="n">
+      <c r="H122" s="1" t="n">
         <v>1.2934</v>
       </c>
     </row>
@@ -3509,10 +3878,13 @@
         <v>0.317</v>
       </c>
       <c r="F123" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="G123" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="G123" s="1" t="n">
-        <v>0.317</v>
+      <c r="H123" s="1" t="n">
+        <v>0.316</v>
       </c>
     </row>
     <row r="124">
@@ -3534,9 +3906,12 @@
         <v>0.12346</v>
       </c>
       <c r="F124" s="1" t="n">
+        <v>0.12344</v>
+      </c>
+      <c r="G124" s="1" t="n">
         <v>0.12506</v>
       </c>
-      <c r="G124" s="1" t="n">
+      <c r="H124" s="1" t="n">
         <v>0.12242</v>
       </c>
     </row>
@@ -3559,9 +3934,12 @@
         <v>0.008459</v>
       </c>
       <c r="F125" s="1" t="n">
+        <v>0.008304000000000001</v>
+      </c>
+      <c r="G125" s="1" t="n">
         <v>0.008459</v>
       </c>
-      <c r="G125" s="1" t="n">
+      <c r="H125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -3584,9 +3962,12 @@
         <v>0.01587</v>
       </c>
       <c r="F126" s="1" t="n">
+        <v>0.01586</v>
+      </c>
+      <c r="G126" s="1" t="n">
         <v>0.01587</v>
       </c>
-      <c r="G126" s="1" t="n">
+      <c r="H126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -3609,9 +3990,12 @@
         <v>0.04466</v>
       </c>
       <c r="F127" s="1" t="n">
+        <v>0.04448</v>
+      </c>
+      <c r="G127" s="1" t="n">
         <v>0.04468</v>
       </c>
-      <c r="G127" s="1" t="n">
+      <c r="H127" s="1" t="n">
         <v>0.04402</v>
       </c>
     </row>
@@ -3634,9 +4018,12 @@
         <v>0.04645</v>
       </c>
       <c r="F128" s="1" t="n">
-        <v>0.04645</v>
+        <v>0.04706</v>
       </c>
       <c r="G128" s="1" t="n">
+        <v>0.04706</v>
+      </c>
+      <c r="H128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -3659,9 +4046,12 @@
         <v>0.09563000000000001</v>
       </c>
       <c r="F129" s="1" t="n">
+        <v>0.09585</v>
+      </c>
+      <c r="G129" s="1" t="n">
         <v>0.09635000000000001</v>
       </c>
-      <c r="G129" s="1" t="n">
+      <c r="H129" s="1" t="n">
         <v>0.09544999999999999</v>
       </c>
     </row>
@@ -3684,9 +4074,12 @@
         <v>0.09891999999999999</v>
       </c>
       <c r="F130" s="1" t="n">
+        <v>0.09902</v>
+      </c>
+      <c r="G130" s="1" t="n">
         <v>0.09927</v>
       </c>
-      <c r="G130" s="1" t="n">
+      <c r="H130" s="1" t="n">
         <v>0.09877</v>
       </c>
     </row>
@@ -3709,9 +4102,12 @@
         <v>0.16522</v>
       </c>
       <c r="F131" s="1" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="G131" s="1" t="n">
         <v>0.16577</v>
       </c>
-      <c r="G131" s="1" t="n">
+      <c r="H131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -3734,9 +4130,12 @@
         <v>0.01694</v>
       </c>
       <c r="F132" s="1" t="n">
-        <v>0.01694</v>
+        <v>0.01696</v>
       </c>
       <c r="G132" s="1" t="n">
+        <v>0.01696</v>
+      </c>
+      <c r="H132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -3759,9 +4158,12 @@
         <v>0.06655</v>
       </c>
       <c r="F133" s="1" t="n">
+        <v>0.06645</v>
+      </c>
+      <c r="G133" s="1" t="n">
         <v>0.06655</v>
       </c>
-      <c r="G133" s="1" t="n">
+      <c r="H133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -3784,9 +4186,12 @@
         <v>0.3014</v>
       </c>
       <c r="F134" s="1" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="G134" s="1" t="n">
         <v>0.3023</v>
       </c>
-      <c r="G134" s="1" t="n">
+      <c r="H134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -3809,9 +4214,12 @@
         <v>0.04508</v>
       </c>
       <c r="F135" s="1" t="n">
-        <v>0.04515</v>
+        <v>0.04518</v>
       </c>
       <c r="G135" s="1" t="n">
+        <v>0.04518</v>
+      </c>
+      <c r="H135" s="1" t="n">
         <v>0.04508</v>
       </c>
     </row>
@@ -3834,9 +4242,12 @@
         <v>0.782</v>
       </c>
       <c r="F136" s="1" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="G136" s="1" t="n">
         <v>0.783</v>
       </c>
-      <c r="G136" s="1" t="n">
+      <c r="H136" s="1" t="n">
         <v>0.781</v>
       </c>
     </row>
@@ -3859,9 +4270,12 @@
         <v>0.1162</v>
       </c>
       <c r="F137" s="1" t="n">
+        <v>0.1165</v>
+      </c>
+      <c r="G137" s="1" t="n">
         <v>0.1168</v>
       </c>
-      <c r="G137" s="1" t="n">
+      <c r="H137" s="1" t="n">
         <v>0.1162</v>
       </c>
     </row>
@@ -3884,9 +4298,12 @@
         <v>0.14641</v>
       </c>
       <c r="F138" s="1" t="n">
-        <v>0.14641</v>
+        <v>0.14685</v>
       </c>
       <c r="G138" s="1" t="n">
+        <v>0.14685</v>
+      </c>
+      <c r="H138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -3909,9 +4326,12 @@
         <v>0.05699</v>
       </c>
       <c r="F139" s="1" t="n">
-        <v>0.05719</v>
+        <v>0.05727</v>
       </c>
       <c r="G139" s="1" t="n">
+        <v>0.05727</v>
+      </c>
+      <c r="H139" s="1" t="n">
         <v>0.05699</v>
       </c>
     </row>
@@ -3934,10 +4354,13 @@
         <v>0.007273</v>
       </c>
       <c r="F140" s="1" t="n">
+        <v>0.007267</v>
+      </c>
+      <c r="G140" s="1" t="n">
         <v>0.007295</v>
       </c>
-      <c r="G140" s="1" t="n">
-        <v>0.007273</v>
+      <c r="H140" s="1" t="n">
+        <v>0.007267</v>
       </c>
     </row>
     <row r="141">
@@ -3959,9 +4382,12 @@
         <v>0.09569</v>
       </c>
       <c r="F141" s="1" t="n">
+        <v>0.09572</v>
+      </c>
+      <c r="G141" s="1" t="n">
         <v>0.09601</v>
       </c>
-      <c r="G141" s="1" t="n">
+      <c r="H141" s="1" t="n">
         <v>0.09569</v>
       </c>
     </row>
@@ -3984,9 +4410,12 @@
         <v>0.08336</v>
       </c>
       <c r="F142" s="1" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="G142" s="1" t="n">
         <v>0.08348</v>
       </c>
-      <c r="G142" s="1" t="n">
+      <c r="H142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -4009,9 +4438,12 @@
         <v>0.00856</v>
       </c>
       <c r="F143" s="1" t="n">
-        <v>0.00856</v>
+        <v>0.0086</v>
       </c>
       <c r="G143" s="1" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="H143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -4034,10 +4466,13 @@
         <v>0.07251000000000001</v>
       </c>
       <c r="F144" s="1" t="n">
+        <v>0.07240000000000001</v>
+      </c>
+      <c r="G144" s="1" t="n">
         <v>0.07288</v>
       </c>
-      <c r="G144" s="1" t="n">
-        <v>0.07251000000000001</v>
+      <c r="H144" s="1" t="n">
+        <v>0.07240000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -4059,10 +4494,13 @@
         <v>0.4305</v>
       </c>
       <c r="F145" s="1" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="G145" s="1" t="n">
         <v>0.4305</v>
       </c>
-      <c r="G145" s="1" t="n">
-        <v>0.4297</v>
+      <c r="H145" s="1" t="n">
+        <v>0.4271</v>
       </c>
     </row>
     <row r="146">
@@ -4084,10 +4522,13 @@
         <v>0.03246</v>
       </c>
       <c r="F146" s="1" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="G146" s="1" t="n">
         <v>0.03276</v>
       </c>
-      <c r="G146" s="1" t="n">
-        <v>0.03246</v>
+      <c r="H146" s="1" t="n">
+        <v>0.0322</v>
       </c>
     </row>
     <row r="147">
@@ -4109,9 +4550,12 @@
         <v>390.52</v>
       </c>
       <c r="F147" s="1" t="n">
+        <v>390.42</v>
+      </c>
+      <c r="G147" s="1" t="n">
         <v>390.55</v>
       </c>
-      <c r="G147" s="1" t="n">
+      <c r="H147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -4134,9 +4578,12 @@
         <v>0.0333</v>
       </c>
       <c r="F148" s="1" t="n">
+        <v>0.03301</v>
+      </c>
+      <c r="G148" s="1" t="n">
         <v>0.0333</v>
       </c>
-      <c r="G148" s="1" t="n">
+      <c r="H148" s="1" t="n">
         <v>0.0329</v>
       </c>
     </row>
@@ -4159,9 +4606,12 @@
         <v>0.05289</v>
       </c>
       <c r="F149" s="1" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="G149" s="1" t="n">
         <v>0.05322</v>
       </c>
-      <c r="G149" s="1" t="n">
+      <c r="H149" s="1" t="n">
         <v>0.05289</v>
       </c>
     </row>
@@ -4184,9 +4634,12 @@
         <v>0.000439</v>
       </c>
       <c r="F150" s="1" t="n">
+        <v>0.0004396</v>
+      </c>
+      <c r="G150" s="1" t="n">
         <v>0.000443</v>
       </c>
-      <c r="G150" s="1" t="n">
+      <c r="H150" s="1" t="n">
         <v>0.000439</v>
       </c>
     </row>
@@ -4209,9 +4662,12 @@
         <v>0.02189</v>
       </c>
       <c r="F151" s="1" t="n">
+        <v>0.02173</v>
+      </c>
+      <c r="G151" s="1" t="n">
         <v>0.02189</v>
       </c>
-      <c r="G151" s="1" t="n">
+      <c r="H151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -4234,10 +4690,13 @@
         <v>0.001774</v>
       </c>
       <c r="F152" s="1" t="n">
+        <v>0.001768</v>
+      </c>
+      <c r="G152" s="1" t="n">
         <v>0.001783</v>
       </c>
-      <c r="G152" s="1" t="n">
-        <v>0.001774</v>
+      <c r="H152" s="1" t="n">
+        <v>0.001768</v>
       </c>
     </row>
     <row r="153">
@@ -4259,10 +4718,13 @@
         <v>6.1e-06</v>
       </c>
       <c r="F153" s="1" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="G153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
-      <c r="G153" s="1" t="n">
-        <v>6.1e-06</v>
+      <c r="H153" s="1" t="n">
+        <v>6e-06</v>
       </c>
     </row>
     <row r="154">
@@ -4284,9 +4746,12 @@
         <v>0.16</v>
       </c>
       <c r="F154" s="1" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="G154" s="1" t="n">
         <v>0.16</v>
       </c>
-      <c r="G154" s="1" t="n">
+      <c r="H154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -4309,9 +4774,12 @@
         <v>0.03768</v>
       </c>
       <c r="F155" s="1" t="n">
+        <v>0.03763</v>
+      </c>
+      <c r="G155" s="1" t="n">
         <v>0.03768</v>
       </c>
-      <c r="G155" s="1" t="n">
+      <c r="H155" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -4334,10 +4802,13 @@
         <v>0.005368</v>
       </c>
       <c r="F156" s="1" t="n">
+        <v>0.005364</v>
+      </c>
+      <c r="G156" s="1" t="n">
         <v>0.005402</v>
       </c>
-      <c r="G156" s="1" t="n">
-        <v>0.005368</v>
+      <c r="H156" s="1" t="n">
+        <v>0.005364</v>
       </c>
     </row>
     <row r="157">
@@ -4359,9 +4830,12 @@
         <v>0.02281</v>
       </c>
       <c r="F157" s="1" t="n">
+        <v>0.02277</v>
+      </c>
+      <c r="G157" s="1" t="n">
         <v>0.02284</v>
       </c>
-      <c r="G157" s="1" t="n">
+      <c r="H157" s="1" t="n">
         <v>0.02277</v>
       </c>
     </row>
@@ -4384,9 +4858,12 @@
         <v>1.088</v>
       </c>
       <c r="F158" s="1" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="G158" s="1" t="n">
         <v>1.09</v>
       </c>
-      <c r="G158" s="1" t="n">
+      <c r="H158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -4409,9 +4886,12 @@
         <v>2.551</v>
       </c>
       <c r="F159" s="1" t="n">
+        <v>2.549</v>
+      </c>
+      <c r="G159" s="1" t="n">
         <v>2.558</v>
       </c>
-      <c r="G159" s="1" t="n">
+      <c r="H159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -4434,9 +4914,12 @@
         <v>4.842</v>
       </c>
       <c r="F160" s="1" t="n">
+        <v>4.839</v>
+      </c>
+      <c r="G160" s="1" t="n">
         <v>4.858</v>
       </c>
-      <c r="G160" s="1" t="n">
+      <c r="H160" s="1" t="n">
         <v>4.836</v>
       </c>
     </row>
@@ -4462,6 +4945,9 @@
         <v>0.1599</v>
       </c>
       <c r="G161" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="H161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -4484,9 +4970,12 @@
         <v>0.20645</v>
       </c>
       <c r="F162" s="1" t="n">
+        <v>0.2073</v>
+      </c>
+      <c r="G162" s="1" t="n">
         <v>0.20754</v>
       </c>
-      <c r="G162" s="1" t="n">
+      <c r="H162" s="1" t="n">
         <v>0.20584</v>
       </c>
     </row>
@@ -4509,9 +4998,12 @@
         <v>0.03931</v>
       </c>
       <c r="F163" s="1" t="n">
+        <v>0.03933</v>
+      </c>
+      <c r="G163" s="1" t="n">
         <v>0.03939</v>
       </c>
-      <c r="G163" s="1" t="n">
+      <c r="H163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -4534,9 +5026,12 @@
         <v>0.06308999999999999</v>
       </c>
       <c r="F164" s="1" t="n">
-        <v>0.06308999999999999</v>
+        <v>0.06326</v>
       </c>
       <c r="G164" s="1" t="n">
+        <v>0.06326</v>
+      </c>
+      <c r="H164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -4559,9 +5054,12 @@
         <v>0.3557</v>
       </c>
       <c r="F165" s="1" t="n">
-        <v>0.3557</v>
+        <v>0.3601</v>
       </c>
       <c r="G165" s="1" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="H165" s="1" t="n">
         <v>0.3525</v>
       </c>
     </row>
@@ -4584,9 +5082,12 @@
         <v>139.14</v>
       </c>
       <c r="F166" s="1" t="n">
+        <v>139.12</v>
+      </c>
+      <c r="G166" s="1" t="n">
         <v>139.27</v>
       </c>
-      <c r="G166" s="1" t="n">
+      <c r="H166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -4609,9 +5110,12 @@
         <v>0.0006533</v>
       </c>
       <c r="F167" s="1" t="n">
+        <v>0.0006507</v>
+      </c>
+      <c r="G167" s="1" t="n">
         <v>0.0006533</v>
       </c>
-      <c r="G167" s="1" t="n">
+      <c r="H167" s="1" t="n">
         <v>0.0006431</v>
       </c>
     </row>
@@ -4634,10 +5138,13 @@
         <v>0.01656</v>
       </c>
       <c r="F168" s="1" t="n">
+        <v>0.01629</v>
+      </c>
+      <c r="G168" s="1" t="n">
         <v>0.01678</v>
       </c>
-      <c r="G168" s="1" t="n">
-        <v>0.01656</v>
+      <c r="H168" s="1" t="n">
+        <v>0.01629</v>
       </c>
     </row>
     <row r="169">
@@ -4659,10 +5166,13 @@
         <v>0.04793</v>
       </c>
       <c r="F169" s="1" t="n">
+        <v>0.04785</v>
+      </c>
+      <c r="G169" s="1" t="n">
         <v>0.04798</v>
       </c>
-      <c r="G169" s="1" t="n">
-        <v>0.04788</v>
+      <c r="H169" s="1" t="n">
+        <v>0.04785</v>
       </c>
     </row>
     <row r="170">
@@ -4684,9 +5194,12 @@
         <v>4.297</v>
       </c>
       <c r="F170" s="1" t="n">
-        <v>4.297</v>
+        <v>4.298</v>
       </c>
       <c r="G170" s="1" t="n">
+        <v>4.298</v>
+      </c>
+      <c r="H170" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -4709,10 +5222,13 @@
         <v>0.03862</v>
       </c>
       <c r="F171" s="1" t="n">
+        <v>0.03836</v>
+      </c>
+      <c r="G171" s="1" t="n">
         <v>0.03874</v>
       </c>
-      <c r="G171" s="1" t="n">
-        <v>0.03846</v>
+      <c r="H171" s="1" t="n">
+        <v>0.03836</v>
       </c>
     </row>
     <row r="172">
@@ -4734,10 +5250,13 @@
         <v>0.0426</v>
       </c>
       <c r="F172" s="1" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="G172" s="1" t="n">
         <v>0.0431</v>
       </c>
-      <c r="G172" s="1" t="n">
-        <v>0.0426</v>
+      <c r="H172" s="1" t="n">
+        <v>0.0425</v>
       </c>
     </row>
     <row r="173">
@@ -4759,9 +5278,12 @@
         <v>0.024277</v>
       </c>
       <c r="F173" s="1" t="n">
-        <v>0.024277</v>
+        <v>0.024294</v>
       </c>
       <c r="G173" s="1" t="n">
+        <v>0.024294</v>
+      </c>
+      <c r="H173" s="1" t="n">
         <v>0.02382</v>
       </c>
     </row>
@@ -4784,9 +5306,12 @@
         <v>1.0704</v>
       </c>
       <c r="F174" s="1" t="n">
-        <v>1.0708</v>
+        <v>1.0768</v>
       </c>
       <c r="G174" s="1" t="n">
+        <v>1.0768</v>
+      </c>
+      <c r="H174" s="1" t="n">
         <v>1.0704</v>
       </c>
     </row>
@@ -4809,10 +5334,13 @@
         <v>0.028636</v>
       </c>
       <c r="F175" s="1" t="n">
+        <v>0.028551</v>
+      </c>
+      <c r="G175" s="1" t="n">
         <v>0.028967</v>
       </c>
-      <c r="G175" s="1" t="n">
-        <v>0.028636</v>
+      <c r="H175" s="1" t="n">
+        <v>0.028551</v>
       </c>
     </row>
     <row r="176">
@@ -4834,9 +5362,12 @@
         <v>0.02188</v>
       </c>
       <c r="F176" s="1" t="n">
-        <v>0.02188</v>
+        <v>0.02193</v>
       </c>
       <c r="G176" s="1" t="n">
+        <v>0.02193</v>
+      </c>
+      <c r="H176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -4859,9 +5390,12 @@
         <v>0.5444</v>
       </c>
       <c r="F177" s="1" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="G177" s="1" t="n">
         <v>0.5444</v>
       </c>
-      <c r="G177" s="1" t="n">
+      <c r="H177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -4884,10 +5418,13 @@
         <v>0.08276</v>
       </c>
       <c r="F178" s="1" t="n">
+        <v>0.08248999999999999</v>
+      </c>
+      <c r="G178" s="1" t="n">
         <v>0.08276</v>
       </c>
-      <c r="G178" s="1" t="n">
-        <v>0.08255999999999999</v>
+      <c r="H178" s="1" t="n">
+        <v>0.08248999999999999</v>
       </c>
     </row>
     <row r="179">
@@ -4909,9 +5446,12 @@
         <v>0.02132</v>
       </c>
       <c r="F179" s="1" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="G179" s="1" t="n">
         <v>0.02133</v>
       </c>
-      <c r="G179" s="1" t="n">
+      <c r="H179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -4934,9 +5474,12 @@
         <v>0.27058</v>
       </c>
       <c r="F180" s="1" t="n">
+        <v>0.27047</v>
+      </c>
+      <c r="G180" s="1" t="n">
         <v>0.27127</v>
       </c>
-      <c r="G180" s="1" t="n">
+      <c r="H180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -4959,9 +5502,12 @@
         <v>0.0042</v>
       </c>
       <c r="F181" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="G181" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="G181" s="1" t="n">
+      <c r="H181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -4984,9 +5530,12 @@
         <v>0.07976</v>
       </c>
       <c r="F182" s="1" t="n">
+        <v>0.07973</v>
+      </c>
+      <c r="G182" s="1" t="n">
         <v>0.07981000000000001</v>
       </c>
-      <c r="G182" s="1" t="n">
+      <c r="H182" s="1" t="n">
         <v>0.07931000000000001</v>
       </c>
     </row>
@@ -5009,9 +5558,12 @@
         <v>0.02347</v>
       </c>
       <c r="F183" s="1" t="n">
+        <v>0.02345</v>
+      </c>
+      <c r="G183" s="1" t="n">
         <v>0.02357</v>
       </c>
-      <c r="G183" s="1" t="n">
+      <c r="H183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -5034,9 +5586,12 @@
         <v>6.965e-05</v>
       </c>
       <c r="F184" s="1" t="n">
+        <v>6.957999999999999e-05</v>
+      </c>
+      <c r="G184" s="1" t="n">
         <v>6.981e-05</v>
       </c>
-      <c r="G184" s="1" t="n">
+      <c r="H184" s="1" t="n">
         <v>6.957e-05</v>
       </c>
     </row>
@@ -5062,6 +5617,9 @@
         <v>0.02131</v>
       </c>
       <c r="G185" s="1" t="n">
+        <v>0.02131</v>
+      </c>
+      <c r="H185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -5084,9 +5642,12 @@
         <v>0.01623</v>
       </c>
       <c r="F186" s="1" t="n">
+        <v>0.01627</v>
+      </c>
+      <c r="G186" s="1" t="n">
         <v>0.01632</v>
       </c>
-      <c r="G186" s="1" t="n">
+      <c r="H186" s="1" t="n">
         <v>0.01623</v>
       </c>
     </row>
@@ -5109,9 +5670,12 @@
         <v>0.978</v>
       </c>
       <c r="F187" s="1" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="G187" s="1" t="n">
         <v>0.978</v>
       </c>
-      <c r="G187" s="1" t="n">
+      <c r="H187" s="1" t="n">
         <v>0.971</v>
       </c>
     </row>
@@ -5134,9 +5698,12 @@
         <v>0.0239</v>
       </c>
       <c r="F188" s="1" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="G188" s="1" t="n">
         <v>0.0239</v>
       </c>
-      <c r="G188" s="1" t="n">
+      <c r="H188" s="1" t="n">
         <v>0.0237</v>
       </c>
     </row>
@@ -5159,9 +5726,12 @@
         <v>1.8609</v>
       </c>
       <c r="F189" s="1" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="G189" s="1" t="n">
         <v>1.8658</v>
       </c>
-      <c r="G189" s="1" t="n">
+      <c r="H189" s="1" t="n">
         <v>1.8609</v>
       </c>
     </row>
@@ -5184,10 +5754,13 @@
         <v>1.832</v>
       </c>
       <c r="F190" s="1" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="G190" s="1" t="n">
         <v>1.838</v>
       </c>
-      <c r="G190" s="1" t="n">
-        <v>1.832</v>
+      <c r="H190" s="1" t="n">
+        <v>1.826</v>
       </c>
     </row>
     <row r="191">
@@ -5209,9 +5782,12 @@
         <v>0.0268</v>
       </c>
       <c r="F191" s="1" t="n">
+        <v>0.02671</v>
+      </c>
+      <c r="G191" s="1" t="n">
         <v>0.0268</v>
       </c>
-      <c r="G191" s="1" t="n">
+      <c r="H191" s="1" t="n">
         <v>0.02669</v>
       </c>
     </row>
@@ -5234,9 +5810,12 @@
         <v>0.0968</v>
       </c>
       <c r="F192" s="1" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="G192" s="1" t="n">
         <v>0.0973</v>
       </c>
-      <c r="G192" s="1" t="n">
+      <c r="H192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -5259,9 +5838,12 @@
         <v>0.1693</v>
       </c>
       <c r="F193" s="1" t="n">
-        <v>0.1693</v>
+        <v>0.1701</v>
       </c>
       <c r="G193" s="1" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="H193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -5284,9 +5866,12 @@
         <v>16.264</v>
       </c>
       <c r="F194" s="1" t="n">
+        <v>16.246</v>
+      </c>
+      <c r="G194" s="1" t="n">
         <v>16.294</v>
       </c>
-      <c r="G194" s="1" t="n">
+      <c r="H194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -5309,10 +5894,13 @@
         <v>4.098</v>
       </c>
       <c r="F195" s="1" t="n">
+        <v>4.087</v>
+      </c>
+      <c r="G195" s="1" t="n">
         <v>4.098</v>
       </c>
-      <c r="G195" s="1" t="n">
-        <v>4.093</v>
+      <c r="H195" s="1" t="n">
+        <v>4.087</v>
       </c>
     </row>
     <row r="196">
@@ -5334,10 +5922,13 @@
         <v>1.2671</v>
       </c>
       <c r="F196" s="1" t="n">
+        <v>1.2663</v>
+      </c>
+      <c r="G196" s="1" t="n">
         <v>1.2794</v>
       </c>
-      <c r="G196" s="1" t="n">
-        <v>1.2671</v>
+      <c r="H196" s="1" t="n">
+        <v>1.2663</v>
       </c>
     </row>
     <row r="197">
@@ -5359,10 +5950,13 @@
         <v>3.07</v>
       </c>
       <c r="F197" s="1" t="n">
+        <v>3.066</v>
+      </c>
+      <c r="G197" s="1" t="n">
         <v>3.092</v>
       </c>
-      <c r="G197" s="1" t="n">
-        <v>3.07</v>
+      <c r="H197" s="1" t="n">
+        <v>3.066</v>
       </c>
     </row>
     <row r="198">
@@ -5384,9 +5978,12 @@
         <v>0.01266</v>
       </c>
       <c r="F198" s="1" t="n">
+        <v>0.01263</v>
+      </c>
+      <c r="G198" s="1" t="n">
         <v>0.01266</v>
       </c>
-      <c r="G198" s="1" t="n">
+      <c r="H198" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -5409,9 +6006,12 @@
         <v>0.0001762</v>
       </c>
       <c r="F199" s="1" t="n">
+        <v>0.0001758</v>
+      </c>
+      <c r="G199" s="1" t="n">
         <v>0.0001762</v>
       </c>
-      <c r="G199" s="1" t="n">
+      <c r="H199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -5434,9 +6034,12 @@
         <v>115.57</v>
       </c>
       <c r="F200" s="1" t="n">
+        <v>115.48</v>
+      </c>
+      <c r="G200" s="1" t="n">
         <v>115.62</v>
       </c>
-      <c r="G200" s="1" t="n">
+      <c r="H200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -5459,9 +6062,12 @@
         <v>0.01031</v>
       </c>
       <c r="F201" s="1" t="n">
+        <v>0.01025</v>
+      </c>
+      <c r="G201" s="1" t="n">
         <v>0.01031</v>
       </c>
-      <c r="G201" s="1" t="n">
+      <c r="H201" s="1" t="n">
         <v>0.01023</v>
       </c>
     </row>
@@ -5484,9 +6090,12 @@
         <v>0.01072</v>
       </c>
       <c r="F202" s="1" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="G202" s="1" t="n">
         <v>0.01073</v>
       </c>
-      <c r="G202" s="1" t="n">
+      <c r="H202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -5509,10 +6118,13 @@
         <v>0.003151</v>
       </c>
       <c r="F203" s="1" t="n">
+        <v>0.003136</v>
+      </c>
+      <c r="G203" s="1" t="n">
         <v>0.003153</v>
       </c>
-      <c r="G203" s="1" t="n">
-        <v>0.003137</v>
+      <c r="H203" s="1" t="n">
+        <v>0.003136</v>
       </c>
     </row>
     <row r="204">
@@ -5534,10 +6146,13 @@
         <v>28.28</v>
       </c>
       <c r="F204" s="1" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="G204" s="1" t="n">
         <v>28.38</v>
       </c>
-      <c r="G204" s="1" t="n">
-        <v>28.28</v>
+      <c r="H204" s="1" t="n">
+        <v>28.23</v>
       </c>
     </row>
     <row r="205">
@@ -5559,9 +6174,12 @@
         <v>0.5627</v>
       </c>
       <c r="F205" s="1" t="n">
+        <v>0.5613</v>
+      </c>
+      <c r="G205" s="1" t="n">
         <v>0.5636</v>
       </c>
-      <c r="G205" s="1" t="n">
+      <c r="H205" s="1" t="n">
         <v>0.5608</v>
       </c>
     </row>
@@ -5584,9 +6202,12 @@
         <v>0.0004387</v>
       </c>
       <c r="F206" s="1" t="n">
+        <v>0.0004389</v>
+      </c>
+      <c r="G206" s="1" t="n">
         <v>0.0004403</v>
       </c>
-      <c r="G206" s="1" t="n">
+      <c r="H206" s="1" t="n">
         <v>0.0004387</v>
       </c>
     </row>
@@ -5609,10 +6230,13 @@
         <v>0.04655</v>
       </c>
       <c r="F207" s="1" t="n">
+        <v>0.04648</v>
+      </c>
+      <c r="G207" s="1" t="n">
         <v>0.04667</v>
       </c>
-      <c r="G207" s="1" t="n">
-        <v>0.04651</v>
+      <c r="H207" s="1" t="n">
+        <v>0.04648</v>
       </c>
     </row>
     <row r="208">
@@ -5634,9 +6258,12 @@
         <v>0.091</v>
       </c>
       <c r="F208" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G208" s="1" t="n">
         <v>0.091</v>
       </c>
-      <c r="G208" s="1" t="n">
+      <c r="H208" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -5659,9 +6286,12 @@
         <v>0.02562</v>
       </c>
       <c r="F209" s="1" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="G209" s="1" t="n">
         <v>0.02572</v>
       </c>
-      <c r="G209" s="1" t="n">
+      <c r="H209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -5684,9 +6314,12 @@
         <v>0.012735</v>
       </c>
       <c r="F210" s="1" t="n">
+        <v>0.012729</v>
+      </c>
+      <c r="G210" s="1" t="n">
         <v>0.012745</v>
       </c>
-      <c r="G210" s="1" t="n">
+      <c r="H210" s="1" t="n">
         <v>0.012652</v>
       </c>
     </row>
@@ -5709,9 +6342,12 @@
         <v>0.0915</v>
       </c>
       <c r="F211" s="1" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="G211" s="1" t="n">
         <v>0.09180000000000001</v>
       </c>
-      <c r="G211" s="1" t="n">
+      <c r="H211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -5734,10 +6370,13 @@
         <v>0.007049</v>
       </c>
       <c r="F212" s="1" t="n">
+        <v>0.007044</v>
+      </c>
+      <c r="G212" s="1" t="n">
         <v>0.007076</v>
       </c>
-      <c r="G212" s="1" t="n">
-        <v>0.007049</v>
+      <c r="H212" s="1" t="n">
+        <v>0.007044</v>
       </c>
     </row>
     <row r="213">
@@ -5759,10 +6398,13 @@
         <v>0.02956</v>
       </c>
       <c r="F213" s="1" t="n">
+        <v>0.02949</v>
+      </c>
+      <c r="G213" s="1" t="n">
         <v>0.02966</v>
       </c>
-      <c r="G213" s="1" t="n">
-        <v>0.02954</v>
+      <c r="H213" s="1" t="n">
+        <v>0.02949</v>
       </c>
     </row>
     <row r="214">
@@ -5784,10 +6426,13 @@
         <v>0.27</v>
       </c>
       <c r="F214" s="1" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="G214" s="1" t="n">
         <v>0.2708</v>
       </c>
-      <c r="G214" s="1" t="n">
-        <v>0.27</v>
+      <c r="H214" s="1" t="n">
+        <v>0.2698</v>
       </c>
     </row>
     <row r="215">
@@ -5812,6 +6457,9 @@
         <v>0.02183</v>
       </c>
       <c r="G215" s="1" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="H215" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -5834,10 +6482,13 @@
         <v>0.01483</v>
       </c>
       <c r="F216" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="G216" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="G216" s="1" t="n">
-        <v>0.01475</v>
+      <c r="H216" s="1" t="n">
+        <v>0.0147</v>
       </c>
     </row>
     <row r="217">
@@ -5859,9 +6510,12 @@
         <v>0.2537</v>
       </c>
       <c r="F217" s="1" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="G217" s="1" t="n">
         <v>0.2538</v>
       </c>
-      <c r="G217" s="1" t="n">
+      <c r="H217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -5884,9 +6538,12 @@
         <v>0.3076</v>
       </c>
       <c r="F218" s="1" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="G218" s="1" t="n">
         <v>0.3087</v>
       </c>
-      <c r="G218" s="1" t="n">
+      <c r="H218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -5909,9 +6566,12 @@
         <v>0.1774</v>
       </c>
       <c r="F219" s="1" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="G219" s="1" t="n">
         <v>0.1784</v>
       </c>
-      <c r="G219" s="1" t="n">
+      <c r="H219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -5934,9 +6594,12 @@
         <v>15</v>
       </c>
       <c r="F220" s="1" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="G220" s="1" t="n">
         <v>15.02</v>
       </c>
-      <c r="G220" s="1" t="n">
+      <c r="H220" s="1" t="n">
         <v>14.97</v>
       </c>
     </row>
@@ -5962,6 +6625,9 @@
         <v>0.01599</v>
       </c>
       <c r="G221" s="1" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="H221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -5984,9 +6650,12 @@
         <v>66.3</v>
       </c>
       <c r="F222" s="1" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G222" s="1" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="G222" s="1" t="n">
+      <c r="H222" s="1" t="n">
         <v>66.17</v>
       </c>
     </row>
@@ -6009,9 +6678,12 @@
         <v>0.09291000000000001</v>
       </c>
       <c r="F223" s="1" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="G223" s="1" t="n">
         <v>0.09291000000000001</v>
       </c>
-      <c r="G223" s="1" t="n">
+      <c r="H223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -6034,9 +6706,12 @@
         <v>0.03927</v>
       </c>
       <c r="F224" s="1" t="n">
-        <v>0.0393</v>
+        <v>0.03931</v>
       </c>
       <c r="G224" s="1" t="n">
+        <v>0.03931</v>
+      </c>
+      <c r="H224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -6059,9 +6734,12 @@
         <v>0.5717</v>
       </c>
       <c r="F225" s="1" t="n">
+        <v>0.5706</v>
+      </c>
+      <c r="G225" s="1" t="n">
         <v>0.5725</v>
       </c>
-      <c r="G225" s="1" t="n">
+      <c r="H225" s="1" t="n">
         <v>0.5695</v>
       </c>
     </row>
@@ -6084,9 +6762,12 @@
         <v>0.1166</v>
       </c>
       <c r="F226" s="1" t="n">
-        <v>0.1167</v>
+        <v>0.1184</v>
       </c>
       <c r="G226" s="1" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="H226" s="1" t="n">
         <v>0.1166</v>
       </c>
     </row>
@@ -6109,10 +6790,13 @@
         <v>0.3179</v>
       </c>
       <c r="F227" s="1" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="G227" s="1" t="n">
         <v>0.3201</v>
       </c>
-      <c r="G227" s="1" t="n">
-        <v>0.3179</v>
+      <c r="H227" s="1" t="n">
+        <v>0.3167</v>
       </c>
     </row>
     <row r="228">
@@ -6134,10 +6818,13 @@
         <v>6.07</v>
       </c>
       <c r="F228" s="1" t="n">
+        <v>6.062</v>
+      </c>
+      <c r="G228" s="1" t="n">
         <v>6.09</v>
       </c>
-      <c r="G228" s="1" t="n">
-        <v>6.066</v>
+      <c r="H228" s="1" t="n">
+        <v>6.062</v>
       </c>
     </row>
     <row r="229">
@@ -6159,9 +6846,12 @@
         <v>0.029</v>
       </c>
       <c r="F229" s="1" t="n">
-        <v>0.029</v>
+        <v>0.0291</v>
       </c>
       <c r="G229" s="1" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="H229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -6184,10 +6874,13 @@
         <v>0.3304</v>
       </c>
       <c r="F230" s="1" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="G230" s="1" t="n">
         <v>0.3307</v>
       </c>
-      <c r="G230" s="1" t="n">
-        <v>0.3294</v>
+      <c r="H230" s="1" t="n">
+        <v>0.3288</v>
       </c>
     </row>
     <row r="231">
@@ -6209,10 +6902,13 @@
         <v>0.12089</v>
       </c>
       <c r="F231" s="1" t="n">
+        <v>0.11994</v>
+      </c>
+      <c r="G231" s="1" t="n">
         <v>0.12089</v>
       </c>
-      <c r="G231" s="1" t="n">
-        <v>0.12024</v>
+      <c r="H231" s="1" t="n">
+        <v>0.11994</v>
       </c>
     </row>
     <row r="232">
@@ -6234,9 +6930,12 @@
         <v>0.1186</v>
       </c>
       <c r="F232" s="1" t="n">
-        <v>0.1186</v>
+        <v>0.1187</v>
       </c>
       <c r="G232" s="1" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="H232" s="1" t="n">
         <v>0.1185</v>
       </c>
     </row>
@@ -6259,9 +6958,12 @@
         <v>0.0301</v>
       </c>
       <c r="F233" s="1" t="n">
+        <v>0.03011</v>
+      </c>
+      <c r="G233" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="G233" s="1" t="n">
+      <c r="H233" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -6284,10 +6986,13 @@
         <v>0.015644</v>
       </c>
       <c r="F234" s="1" t="n">
+        <v>0.015628</v>
+      </c>
+      <c r="G234" s="1" t="n">
         <v>0.01574</v>
       </c>
-      <c r="G234" s="1" t="n">
-        <v>0.015644</v>
+      <c r="H234" s="1" t="n">
+        <v>0.015628</v>
       </c>
     </row>
     <row r="235">
@@ -6309,9 +7014,12 @@
         <v>0.01272</v>
       </c>
       <c r="F235" s="1" t="n">
+        <v>0.01274</v>
+      </c>
+      <c r="G235" s="1" t="n">
         <v>0.01279</v>
       </c>
-      <c r="G235" s="1" t="n">
+      <c r="H235" s="1" t="n">
         <v>0.01272</v>
       </c>
     </row>
@@ -6334,9 +7042,12 @@
         <v>0.01926</v>
       </c>
       <c r="F236" s="1" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="G236" s="1" t="n">
         <v>0.01929</v>
       </c>
-      <c r="G236" s="1" t="n">
+      <c r="H236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -6359,9 +7070,12 @@
         <v>0.08427999999999999</v>
       </c>
       <c r="F237" s="1" t="n">
+        <v>0.08477</v>
+      </c>
+      <c r="G237" s="1" t="n">
         <v>0.08509</v>
       </c>
-      <c r="G237" s="1" t="n">
+      <c r="H237" s="1" t="n">
         <v>0.08427999999999999</v>
       </c>
     </row>
@@ -6384,10 +7098,13 @@
         <v>0.05877</v>
       </c>
       <c r="F238" s="1" t="n">
+        <v>0.05857</v>
+      </c>
+      <c r="G238" s="1" t="n">
         <v>0.05892</v>
       </c>
-      <c r="G238" s="1" t="n">
-        <v>0.05875</v>
+      <c r="H238" s="1" t="n">
+        <v>0.05857</v>
       </c>
     </row>
     <row r="239">
@@ -6409,9 +7126,12 @@
         <v>0.009083000000000001</v>
       </c>
       <c r="F239" s="1" t="n">
+        <v>0.00908</v>
+      </c>
+      <c r="G239" s="1" t="n">
         <v>0.009083000000000001</v>
       </c>
-      <c r="G239" s="1" t="n">
+      <c r="H239" s="1" t="n">
         <v>0.009027</v>
       </c>
     </row>
@@ -6434,9 +7154,12 @@
         <v>0.004175</v>
       </c>
       <c r="F240" s="1" t="n">
+        <v>0.004163</v>
+      </c>
+      <c r="G240" s="1" t="n">
         <v>0.004175</v>
       </c>
-      <c r="G240" s="1" t="n">
+      <c r="H240" s="1" t="n">
         <v>0.004154</v>
       </c>
     </row>
@@ -6459,9 +7182,12 @@
         <v>0.2407</v>
       </c>
       <c r="F241" s="1" t="n">
+        <v>0.2404</v>
+      </c>
+      <c r="G241" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="G241" s="1" t="n">
+      <c r="H241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -6487,6 +7213,9 @@
         <v>0.0582</v>
       </c>
       <c r="G242" s="1" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="H242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -6509,9 +7238,12 @@
         <v>0.02356</v>
       </c>
       <c r="F243" s="1" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="G243" s="1" t="n">
         <v>0.02356</v>
       </c>
-      <c r="G243" s="1" t="n">
+      <c r="H243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -6534,9 +7266,12 @@
         <v>0.0556</v>
       </c>
       <c r="F244" s="1" t="n">
+        <v>0.05559</v>
+      </c>
+      <c r="G244" s="1" t="n">
         <v>0.05623</v>
       </c>
-      <c r="G244" s="1" t="n">
+      <c r="H244" s="1" t="n">
         <v>0.05547</v>
       </c>
     </row>
@@ -6559,9 +7294,12 @@
         <v>0.03438</v>
       </c>
       <c r="F245" s="1" t="n">
+        <v>0.03431</v>
+      </c>
+      <c r="G245" s="1" t="n">
         <v>0.03438</v>
       </c>
-      <c r="G245" s="1" t="n">
+      <c r="H245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -6584,9 +7322,12 @@
         <v>0.0599</v>
       </c>
       <c r="F246" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G246" s="1" t="n">
         <v>0.06013</v>
       </c>
-      <c r="G246" s="1" t="n">
+      <c r="H246" s="1" t="n">
         <v>0.0599</v>
       </c>
     </row>
@@ -6609,9 +7350,12 @@
         <v>0.383</v>
       </c>
       <c r="F247" s="1" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="G247" s="1" t="n">
         <v>0.385</v>
       </c>
-      <c r="G247" s="1" t="n">
+      <c r="H247" s="1" t="n">
         <v>0.383</v>
       </c>
     </row>
@@ -6634,9 +7378,12 @@
         <v>0.5173</v>
       </c>
       <c r="F248" s="1" t="n">
+        <v>0.5173</v>
+      </c>
+      <c r="G248" s="1" t="n">
         <v>0.519</v>
       </c>
-      <c r="G248" s="1" t="n">
+      <c r="H248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -6659,9 +7406,12 @@
         <v>0.02798</v>
       </c>
       <c r="F249" s="1" t="n">
+        <v>0.02801</v>
+      </c>
+      <c r="G249" s="1" t="n">
         <v>0.02804</v>
       </c>
-      <c r="G249" s="1" t="n">
+      <c r="H249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -6684,9 +7434,12 @@
         <v>0.01292</v>
       </c>
       <c r="F250" s="1" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="G250" s="1" t="n">
         <v>0.01295</v>
       </c>
-      <c r="G250" s="1" t="n">
+      <c r="H250" s="1" t="n">
         <v>0.01288</v>
       </c>
     </row>
@@ -6709,9 +7462,12 @@
         <v>0.1002</v>
       </c>
       <c r="F251" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="G251" s="1" t="n">
         <v>0.1003</v>
       </c>
-      <c r="G251" s="1" t="n">
+      <c r="H251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -6734,9 +7490,12 @@
         <v>0.00718</v>
       </c>
       <c r="F252" s="1" t="n">
+        <v>0.00716</v>
+      </c>
+      <c r="G252" s="1" t="n">
         <v>0.00719</v>
       </c>
-      <c r="G252" s="1" t="n">
+      <c r="H252" s="1" t="n">
         <v>0.00716</v>
       </c>
     </row>
@@ -6759,9 +7518,12 @@
         <v>0.005563</v>
       </c>
       <c r="F253" s="1" t="n">
+        <v>0.005559</v>
+      </c>
+      <c r="G253" s="1" t="n">
         <v>0.005563</v>
       </c>
-      <c r="G253" s="1" t="n">
+      <c r="H253" s="1" t="n">
         <v>0.005554</v>
       </c>
     </row>
@@ -6784,10 +7546,13 @@
         <v>0.0643</v>
       </c>
       <c r="F254" s="1" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="G254" s="1" t="n">
         <v>0.0646</v>
       </c>
-      <c r="G254" s="1" t="n">
-        <v>0.06419999999999999</v>
+      <c r="H254" s="1" t="n">
+        <v>0.0641</v>
       </c>
     </row>
     <row r="255">
@@ -6809,9 +7574,12 @@
         <v>0.01436</v>
       </c>
       <c r="F255" s="1" t="n">
-        <v>0.01436</v>
+        <v>0.01441</v>
       </c>
       <c r="G255" s="1" t="n">
+        <v>0.01441</v>
+      </c>
+      <c r="H255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -6834,9 +7602,12 @@
         <v>0.999286</v>
       </c>
       <c r="F256" s="1" t="n">
+        <v>0.999286</v>
+      </c>
+      <c r="G256" s="1" t="n">
         <v>0.999297</v>
       </c>
-      <c r="G256" s="1" t="n">
+      <c r="H256" s="1" t="n">
         <v>0.999285</v>
       </c>
     </row>
@@ -6862,6 +7633,9 @@
         <v>0.02101</v>
       </c>
       <c r="G257" s="1" t="n">
+        <v>0.02101</v>
+      </c>
+      <c r="H257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -6884,9 +7658,12 @@
         <v>0.01148</v>
       </c>
       <c r="F258" s="1" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="G258" s="1" t="n">
         <v>0.01148</v>
       </c>
-      <c r="G258" s="1" t="n">
+      <c r="H258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -6909,10 +7686,13 @@
         <v>0.5092</v>
       </c>
       <c r="F259" s="1" t="n">
+        <v>0.5071</v>
+      </c>
+      <c r="G259" s="1" t="n">
         <v>0.5119</v>
       </c>
-      <c r="G259" s="1" t="n">
-        <v>0.5085</v>
+      <c r="H259" s="1" t="n">
+        <v>0.5071</v>
       </c>
     </row>
     <row r="260">
@@ -6934,9 +7714,12 @@
         <v>0.08537</v>
       </c>
       <c r="F260" s="1" t="n">
+        <v>0.08501</v>
+      </c>
+      <c r="G260" s="1" t="n">
         <v>0.08537</v>
       </c>
-      <c r="G260" s="1" t="n">
+      <c r="H260" s="1" t="n">
         <v>0.08436</v>
       </c>
     </row>
@@ -6959,10 +7742,13 @@
         <v>0.04124</v>
       </c>
       <c r="F261" s="1" t="n">
+        <v>0.04123</v>
+      </c>
+      <c r="G261" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="G261" s="1" t="n">
-        <v>0.04124</v>
+      <c r="H261" s="1" t="n">
+        <v>0.04123</v>
       </c>
     </row>
     <row r="262">
@@ -6984,10 +7770,13 @@
         <v>2.282</v>
       </c>
       <c r="F262" s="1" t="n">
+        <v>2.279</v>
+      </c>
+      <c r="G262" s="1" t="n">
         <v>2.288</v>
       </c>
-      <c r="G262" s="1" t="n">
-        <v>2.282</v>
+      <c r="H262" s="1" t="n">
+        <v>2.279</v>
       </c>
     </row>
     <row r="263">
@@ -7009,9 +7798,12 @@
         <v>18.48</v>
       </c>
       <c r="F263" s="1" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="G263" s="1" t="n">
         <v>18.51</v>
       </c>
-      <c r="G263" s="1" t="n">
+      <c r="H263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -7034,9 +7826,12 @@
         <v>0.008562999999999999</v>
       </c>
       <c r="F264" s="1" t="n">
+        <v>0.008555</v>
+      </c>
+      <c r="G264" s="1" t="n">
         <v>0.008562999999999999</v>
       </c>
-      <c r="G264" s="1" t="n">
+      <c r="H264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -7059,9 +7854,12 @@
         <v>0.3627</v>
       </c>
       <c r="F265" s="1" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="G265" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="G265" s="1" t="n">
+      <c r="H265" s="1" t="n">
         <v>0.3627</v>
       </c>
     </row>
@@ -7084,9 +7882,12 @@
         <v>0.054195</v>
       </c>
       <c r="F266" s="1" t="n">
+        <v>0.05428</v>
+      </c>
+      <c r="G266" s="1" t="n">
         <v>0.054291</v>
       </c>
-      <c r="G266" s="1" t="n">
+      <c r="H266" s="1" t="n">
         <v>0.053765</v>
       </c>
     </row>
@@ -7109,9 +7910,12 @@
         <v>0.1316</v>
       </c>
       <c r="F267" s="1" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="G267" s="1" t="n">
         <v>0.1321</v>
       </c>
-      <c r="G267" s="1" t="n">
+      <c r="H267" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -7134,9 +7938,12 @@
         <v>0.007795</v>
       </c>
       <c r="F268" s="1" t="n">
+        <v>0.007789</v>
+      </c>
+      <c r="G268" s="1" t="n">
         <v>0.007845</v>
       </c>
-      <c r="G268" s="1" t="n">
+      <c r="H268" s="1" t="n">
         <v>0.007759</v>
       </c>
     </row>
@@ -7159,10 +7966,13 @@
         <v>0.001235</v>
       </c>
       <c r="F269" s="1" t="n">
+        <v>0.001233</v>
+      </c>
+      <c r="G269" s="1" t="n">
         <v>0.00124</v>
       </c>
-      <c r="G269" s="1" t="n">
-        <v>0.001235</v>
+      <c r="H269" s="1" t="n">
+        <v>0.001233</v>
       </c>
     </row>
     <row r="270">
@@ -7184,9 +7994,12 @@
         <v>0.28905</v>
       </c>
       <c r="F270" s="1" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="G270" s="1" t="n">
         <v>0.28997</v>
       </c>
-      <c r="G270" s="1" t="n">
+      <c r="H270" s="1" t="n">
         <v>0.28865</v>
       </c>
     </row>
@@ -7209,9 +8022,12 @@
         <v>0.03922</v>
       </c>
       <c r="F271" s="1" t="n">
+        <v>0.03887</v>
+      </c>
+      <c r="G271" s="1" t="n">
         <v>0.03922</v>
       </c>
-      <c r="G271" s="1" t="n">
+      <c r="H271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -7234,9 +8050,12 @@
         <v>0.05137</v>
       </c>
       <c r="F272" s="1" t="n">
+        <v>0.05129</v>
+      </c>
+      <c r="G272" s="1" t="n">
         <v>0.05137</v>
       </c>
-      <c r="G272" s="1" t="n">
+      <c r="H272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -7259,9 +8078,12 @@
         <v>0.00771</v>
       </c>
       <c r="F273" s="1" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="G273" s="1" t="n">
         <v>0.00771</v>
       </c>
-      <c r="G273" s="1" t="n">
+      <c r="H273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -7284,9 +8106,12 @@
         <v>0.005779</v>
       </c>
       <c r="F274" s="1" t="n">
+        <v>0.005769</v>
+      </c>
+      <c r="G274" s="1" t="n">
         <v>0.005779</v>
       </c>
-      <c r="G274" s="1" t="n">
+      <c r="H274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -7309,9 +8134,12 @@
         <v>0.0005863</v>
       </c>
       <c r="F275" s="1" t="n">
+        <v>0.0005872</v>
+      </c>
+      <c r="G275" s="1" t="n">
         <v>0.0005895</v>
       </c>
-      <c r="G275" s="1" t="n">
+      <c r="H275" s="1" t="n">
         <v>0.0005863</v>
       </c>
     </row>
@@ -7334,10 +8162,13 @@
         <v>0.15044</v>
       </c>
       <c r="F276" s="1" t="n">
+        <v>0.15007</v>
+      </c>
+      <c r="G276" s="1" t="n">
         <v>0.15167</v>
       </c>
-      <c r="G276" s="1" t="n">
-        <v>0.15044</v>
+      <c r="H276" s="1" t="n">
+        <v>0.15007</v>
       </c>
     </row>
     <row r="277">
@@ -7359,9 +8190,12 @@
         <v>0.022788</v>
       </c>
       <c r="F277" s="1" t="n">
-        <v>0.022788</v>
+        <v>0.022828</v>
       </c>
       <c r="G277" s="1" t="n">
+        <v>0.022828</v>
+      </c>
+      <c r="H277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -7384,9 +8218,12 @@
         <v>0.04242</v>
       </c>
       <c r="F278" s="1" t="n">
+        <v>0.04219</v>
+      </c>
+      <c r="G278" s="1" t="n">
         <v>0.04242</v>
       </c>
-      <c r="G278" s="1" t="n">
+      <c r="H278" s="1" t="n">
         <v>0.04179</v>
       </c>
     </row>
@@ -7409,9 +8246,12 @@
         <v>0.0003994</v>
       </c>
       <c r="F279" s="1" t="n">
+        <v>0.0003996</v>
+      </c>
+      <c r="G279" s="1" t="n">
         <v>0.0004006</v>
       </c>
-      <c r="G279" s="1" t="n">
+      <c r="H279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -7434,9 +8274,12 @@
         <v>0.02213</v>
       </c>
       <c r="F280" s="1" t="n">
+        <v>0.02214</v>
+      </c>
+      <c r="G280" s="1" t="n">
         <v>0.02218</v>
       </c>
-      <c r="G280" s="1" t="n">
+      <c r="H280" s="1" t="n">
         <v>0.02195</v>
       </c>
     </row>
@@ -7459,9 +8302,12 @@
         <v>0.06945</v>
       </c>
       <c r="F281" s="1" t="n">
+        <v>0.06938999999999999</v>
+      </c>
+      <c r="G281" s="1" t="n">
         <v>0.06945</v>
       </c>
-      <c r="G281" s="1" t="n">
+      <c r="H281" s="1" t="n">
         <v>0.06936</v>
       </c>
     </row>
@@ -7484,10 +8330,13 @@
         <v>0.006787</v>
       </c>
       <c r="F282" s="1" t="n">
+        <v>0.006732</v>
+      </c>
+      <c r="G282" s="1" t="n">
         <v>0.006804</v>
       </c>
-      <c r="G282" s="1" t="n">
-        <v>0.006758</v>
+      <c r="H282" s="1" t="n">
+        <v>0.006732</v>
       </c>
     </row>
     <row r="283">
@@ -7512,6 +8361,9 @@
         <v>0.12</v>
       </c>
       <c r="G283" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H283" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -7534,9 +8386,12 @@
         <v>0.005475</v>
       </c>
       <c r="F284" s="1" t="n">
+        <v>0.005467</v>
+      </c>
+      <c r="G284" s="1" t="n">
         <v>0.005475</v>
       </c>
-      <c r="G284" s="1" t="n">
+      <c r="H284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -7559,9 +8414,12 @@
         <v>1.248</v>
       </c>
       <c r="F285" s="1" t="n">
-        <v>1.251</v>
+        <v>1.255</v>
       </c>
       <c r="G285" s="1" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="H285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -7584,10 +8442,13 @@
         <v>0.4431</v>
       </c>
       <c r="F286" s="1" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="G286" s="1" t="n">
         <v>0.4441</v>
       </c>
-      <c r="G286" s="1" t="n">
-        <v>0.4429</v>
+      <c r="H286" s="1" t="n">
+        <v>0.4423</v>
       </c>
     </row>
     <row r="287">
@@ -7609,9 +8470,12 @@
         <v>0.007868</v>
       </c>
       <c r="F287" s="1" t="n">
+        <v>0.007866</v>
+      </c>
+      <c r="G287" s="1" t="n">
         <v>0.007875999999999999</v>
       </c>
-      <c r="G287" s="1" t="n">
+      <c r="H287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -7634,9 +8498,12 @@
         <v>0.02914</v>
       </c>
       <c r="F288" s="1" t="n">
-        <v>0.02922</v>
+        <v>0.02928</v>
       </c>
       <c r="G288" s="1" t="n">
+        <v>0.02928</v>
+      </c>
+      <c r="H288" s="1" t="n">
         <v>0.02914</v>
       </c>
     </row>
@@ -7662,6 +8529,9 @@
         <v>0.2812</v>
       </c>
       <c r="G289" s="1" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="H289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -7684,9 +8554,12 @@
         <v>2.75</v>
       </c>
       <c r="F290" s="1" t="n">
+        <v>2.753</v>
+      </c>
+      <c r="G290" s="1" t="n">
         <v>2.764</v>
       </c>
-      <c r="G290" s="1" t="n">
+      <c r="H290" s="1" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -7709,9 +8582,12 @@
         <v>0.003164</v>
       </c>
       <c r="F291" s="1" t="n">
+        <v>0.003167</v>
+      </c>
+      <c r="G291" s="1" t="n">
         <v>0.003176</v>
       </c>
-      <c r="G291" s="1" t="n">
+      <c r="H291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -7734,9 +8610,12 @@
         <v>0.448</v>
       </c>
       <c r="F292" s="1" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="G292" s="1" t="n">
         <v>0.4488</v>
       </c>
-      <c r="G292" s="1" t="n">
+      <c r="H292" s="1" t="n">
         <v>0.4475</v>
       </c>
     </row>
@@ -7759,9 +8638,12 @@
         <v>0.08214</v>
       </c>
       <c r="F293" s="1" t="n">
+        <v>0.08218</v>
+      </c>
+      <c r="G293" s="1" t="n">
         <v>0.08298</v>
       </c>
-      <c r="G293" s="1" t="n">
+      <c r="H293" s="1" t="n">
         <v>0.08214</v>
       </c>
     </row>
@@ -7784,9 +8666,12 @@
         <v>0.02783</v>
       </c>
       <c r="F294" s="1" t="n">
+        <v>0.02782</v>
+      </c>
+      <c r="G294" s="1" t="n">
         <v>0.02784</v>
       </c>
-      <c r="G294" s="1" t="n">
+      <c r="H294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -7809,9 +8694,12 @@
         <v>0.957</v>
       </c>
       <c r="F295" s="1" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="G295" s="1" t="n">
         <v>0.958</v>
       </c>
-      <c r="G295" s="1" t="n">
+      <c r="H295" s="1" t="n">
         <v>0.953</v>
       </c>
     </row>
@@ -7834,9 +8722,12 @@
         <v>0.006891</v>
       </c>
       <c r="F296" s="1" t="n">
+        <v>0.00689</v>
+      </c>
+      <c r="G296" s="1" t="n">
         <v>0.006891</v>
       </c>
-      <c r="G296" s="1" t="n">
+      <c r="H296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -7859,9 +8750,12 @@
         <v>0.1206</v>
       </c>
       <c r="F297" s="1" t="n">
+        <v>0.1209</v>
+      </c>
+      <c r="G297" s="1" t="n">
         <v>0.1212</v>
       </c>
-      <c r="G297" s="1" t="n">
+      <c r="H297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -7884,9 +8778,12 @@
         <v>0.01548</v>
       </c>
       <c r="F298" s="1" t="n">
+        <v>0.01543</v>
+      </c>
+      <c r="G298" s="1" t="n">
         <v>0.01548</v>
       </c>
-      <c r="G298" s="1" t="n">
+      <c r="H298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -7909,9 +8806,12 @@
         <v>0.4401</v>
       </c>
       <c r="F299" s="1" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="G299" s="1" t="n">
         <v>0.4405</v>
       </c>
-      <c r="G299" s="1" t="n">
+      <c r="H299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -7934,10 +8834,13 @@
         <v>0.0092</v>
       </c>
       <c r="F300" s="1" t="n">
+        <v>0.00916</v>
+      </c>
+      <c r="G300" s="1" t="n">
         <v>0.00924</v>
       </c>
-      <c r="G300" s="1" t="n">
-        <v>0.0092</v>
+      <c r="H300" s="1" t="n">
+        <v>0.00916</v>
       </c>
     </row>
     <row r="301">
@@ -7959,9 +8862,12 @@
         <v>0.1848</v>
       </c>
       <c r="F301" s="1" t="n">
-        <v>0.1849</v>
+        <v>0.1852</v>
       </c>
       <c r="G301" s="1" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="H301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -7984,9 +8890,12 @@
         <v>0.00756</v>
       </c>
       <c r="F302" s="1" t="n">
-        <v>0.00756</v>
+        <v>0.0076</v>
       </c>
       <c r="G302" s="1" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="H302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -8009,10 +8918,13 @@
         <v>0.0002163</v>
       </c>
       <c r="F303" s="1" t="n">
+        <v>0.0002159</v>
+      </c>
+      <c r="G303" s="1" t="n">
         <v>0.0002171</v>
       </c>
-      <c r="G303" s="1" t="n">
-        <v>0.0002163</v>
+      <c r="H303" s="1" t="n">
+        <v>0.0002159</v>
       </c>
     </row>
     <row r="304">
@@ -8034,9 +8946,12 @@
         <v>0.01542</v>
       </c>
       <c r="F304" s="1" t="n">
+        <v>0.01542</v>
+      </c>
+      <c r="G304" s="1" t="n">
         <v>0.01549</v>
       </c>
-      <c r="G304" s="1" t="n">
+      <c r="H304" s="1" t="n">
         <v>0.01542</v>
       </c>
     </row>
@@ -8059,9 +8974,12 @@
         <v>0.07386</v>
       </c>
       <c r="F305" s="1" t="n">
+        <v>0.07384</v>
+      </c>
+      <c r="G305" s="1" t="n">
         <v>0.07394000000000001</v>
       </c>
-      <c r="G305" s="1" t="n">
+      <c r="H305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -8084,9 +9002,12 @@
         <v>0.08291</v>
       </c>
       <c r="F306" s="1" t="n">
-        <v>0.08291</v>
+        <v>0.08291999999999999</v>
       </c>
       <c r="G306" s="1" t="n">
+        <v>0.08291999999999999</v>
+      </c>
+      <c r="H306" s="1" t="n">
         <v>0.08275</v>
       </c>
     </row>
@@ -8109,10 +9030,13 @@
         <v>0.01827</v>
       </c>
       <c r="F307" s="1" t="n">
+        <v>0.01808</v>
+      </c>
+      <c r="G307" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="G307" s="1" t="n">
-        <v>0.01812</v>
+      <c r="H307" s="1" t="n">
+        <v>0.01808</v>
       </c>
     </row>
     <row r="308">
@@ -8134,10 +9058,13 @@
         <v>0.0006223999999999999</v>
       </c>
       <c r="F308" s="1" t="n">
+        <v>0.0006212</v>
+      </c>
+      <c r="G308" s="1" t="n">
         <v>0.0006255</v>
       </c>
-      <c r="G308" s="1" t="n">
-        <v>0.0006215</v>
+      <c r="H308" s="1" t="n">
+        <v>0.0006212</v>
       </c>
     </row>
     <row r="309">
@@ -8159,10 +9086,13 @@
         <v>0.08252</v>
       </c>
       <c r="F309" s="1" t="n">
+        <v>0.08243</v>
+      </c>
+      <c r="G309" s="1" t="n">
         <v>0.08294</v>
       </c>
-      <c r="G309" s="1" t="n">
-        <v>0.08244</v>
+      <c r="H309" s="1" t="n">
+        <v>0.08243</v>
       </c>
     </row>
     <row r="310">
@@ -8184,10 +9114,13 @@
         <v>0.0974</v>
       </c>
       <c r="F310" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="G310" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="G310" s="1" t="n">
-        <v>0.0974</v>
+      <c r="H310" s="1" t="n">
+        <v>0.0973</v>
       </c>
     </row>
     <row r="311">
@@ -8209,9 +9142,12 @@
         <v>0.2112</v>
       </c>
       <c r="F311" s="1" t="n">
+        <v>0.2109</v>
+      </c>
+      <c r="G311" s="1" t="n">
         <v>0.2113</v>
       </c>
-      <c r="G311" s="1" t="n">
+      <c r="H311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -8234,9 +9170,12 @@
         <v>0.387</v>
       </c>
       <c r="F312" s="1" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="G312" s="1" t="n">
         <v>0.394</v>
       </c>
-      <c r="G312" s="1" t="n">
+      <c r="H312" s="1" t="n">
         <v>0.387</v>
       </c>
     </row>
@@ -8259,9 +9198,12 @@
         <v>0.10518</v>
       </c>
       <c r="F313" s="1" t="n">
+        <v>0.10537</v>
+      </c>
+      <c r="G313" s="1" t="n">
         <v>0.10542</v>
       </c>
-      <c r="G313" s="1" t="n">
+      <c r="H313" s="1" t="n">
         <v>0.10492</v>
       </c>
     </row>
@@ -8284,9 +9226,12 @@
         <v>0.08575000000000001</v>
       </c>
       <c r="F314" s="1" t="n">
+        <v>0.08554</v>
+      </c>
+      <c r="G314" s="1" t="n">
         <v>0.08575000000000001</v>
       </c>
-      <c r="G314" s="1" t="n">
+      <c r="H314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -8309,9 +9254,12 @@
         <v>0.1179</v>
       </c>
       <c r="F315" s="1" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="G315" s="1" t="n">
         <v>0.1185</v>
       </c>
-      <c r="G315" s="1" t="n">
+      <c r="H315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -8334,9 +9282,12 @@
         <v>0.03666</v>
       </c>
       <c r="F316" s="1" t="n">
+        <v>0.03632</v>
+      </c>
+      <c r="G316" s="1" t="n">
         <v>0.03681</v>
       </c>
-      <c r="G316" s="1" t="n">
+      <c r="H316" s="1" t="n">
         <v>0.03628</v>
       </c>
     </row>
@@ -8359,9 +9310,12 @@
         <v>0.08087</v>
       </c>
       <c r="F317" s="1" t="n">
+        <v>0.08085000000000001</v>
+      </c>
+      <c r="G317" s="1" t="n">
         <v>0.08125</v>
       </c>
-      <c r="G317" s="1" t="n">
+      <c r="H317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -8384,9 +9338,12 @@
         <v>0.03766</v>
       </c>
       <c r="F318" s="1" t="n">
+        <v>0.03761</v>
+      </c>
+      <c r="G318" s="1" t="n">
         <v>0.03766</v>
       </c>
-      <c r="G318" s="1" t="n">
+      <c r="H318" s="1" t="n">
         <v>0.03736</v>
       </c>
     </row>
@@ -8409,9 +9366,12 @@
         <v>0.4341</v>
       </c>
       <c r="F319" s="1" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="G319" s="1" t="n">
         <v>0.4347</v>
       </c>
-      <c r="G319" s="1" t="n">
+      <c r="H319" s="1" t="n">
         <v>0.4308</v>
       </c>
     </row>
@@ -8434,10 +9394,13 @@
         <v>0.1607</v>
       </c>
       <c r="F320" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G320" s="1" t="n">
         <v>0.1614</v>
       </c>
-      <c r="G320" s="1" t="n">
-        <v>0.1607</v>
+      <c r="H320" s="1" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="321">
@@ -8459,9 +9422,12 @@
         <v>5.678</v>
       </c>
       <c r="F321" s="1" t="n">
-        <v>5.68</v>
+        <v>5.681</v>
       </c>
       <c r="G321" s="1" t="n">
+        <v>5.681</v>
+      </c>
+      <c r="H321" s="1" t="n">
         <v>5.677</v>
       </c>
     </row>
@@ -8484,9 +9450,12 @@
         <v>0.003739</v>
       </c>
       <c r="F322" s="1" t="n">
-        <v>0.003739</v>
+        <v>0.003746</v>
       </c>
       <c r="G322" s="1" t="n">
+        <v>0.003746</v>
+      </c>
+      <c r="H322" s="1" t="n">
         <v>0.003715</v>
       </c>
     </row>
@@ -8509,9 +9478,12 @@
         <v>0.001757</v>
       </c>
       <c r="F323" s="1" t="n">
+        <v>0.001754</v>
+      </c>
+      <c r="G323" s="1" t="n">
         <v>0.001757</v>
       </c>
-      <c r="G323" s="1" t="n">
+      <c r="H323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -8534,9 +9506,12 @@
         <v>1.19e-05</v>
       </c>
       <c r="F324" s="1" t="n">
+        <v>1.19e-05</v>
+      </c>
+      <c r="G324" s="1" t="n">
         <v>1.2e-05</v>
       </c>
-      <c r="G324" s="1" t="n">
+      <c r="H324" s="1" t="n">
         <v>1.19e-05</v>
       </c>
     </row>
@@ -8559,10 +9534,13 @@
         <v>0.0862</v>
       </c>
       <c r="F325" s="1" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="G325" s="1" t="n">
         <v>0.08649999999999999</v>
       </c>
-      <c r="G325" s="1" t="n">
-        <v>0.0862</v>
+      <c r="H325" s="1" t="n">
+        <v>0.0857</v>
       </c>
     </row>
     <row r="326">
@@ -8584,9 +9562,12 @@
         <v>0.01732</v>
       </c>
       <c r="F326" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="G326" s="1" t="n">
         <v>0.01736</v>
       </c>
-      <c r="G326" s="1" t="n">
+      <c r="H326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -8609,9 +9590,12 @@
         <v>0.01679</v>
       </c>
       <c r="F327" s="1" t="n">
+        <v>0.01682</v>
+      </c>
+      <c r="G327" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="G327" s="1" t="n">
+      <c r="H327" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -8634,9 +9618,12 @@
         <v>4.454</v>
       </c>
       <c r="F328" s="1" t="n">
+        <v>4.448</v>
+      </c>
+      <c r="G328" s="1" t="n">
         <v>4.462</v>
       </c>
-      <c r="G328" s="1" t="n">
+      <c r="H328" s="1" t="n">
         <v>4.446</v>
       </c>
     </row>
@@ -8659,9 +9646,12 @@
         <v>0.009532000000000001</v>
       </c>
       <c r="F329" s="1" t="n">
+        <v>0.009573999999999999</v>
+      </c>
+      <c r="G329" s="1" t="n">
         <v>0.009861</v>
       </c>
-      <c r="G329" s="1" t="n">
+      <c r="H329" s="1" t="n">
         <v>0.009532000000000001</v>
       </c>
     </row>
@@ -8684,9 +9674,12 @@
         <v>5189</v>
       </c>
       <c r="F330" s="1" t="n">
+        <v>5192.7</v>
+      </c>
+      <c r="G330" s="1" t="n">
         <v>5192.9</v>
       </c>
-      <c r="G330" s="1" t="n">
+      <c r="H330" s="1" t="n">
         <v>5185.8</v>
       </c>
     </row>
@@ -8709,9 +9702,12 @@
         <v>0.07087</v>
       </c>
       <c r="F331" s="1" t="n">
+        <v>0.07048</v>
+      </c>
+      <c r="G331" s="1" t="n">
         <v>0.07087</v>
       </c>
-      <c r="G331" s="1" t="n">
+      <c r="H331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -8734,9 +9730,12 @@
         <v>0.06098</v>
       </c>
       <c r="F332" s="1" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="G332" s="1" t="n">
         <v>0.06098</v>
       </c>
-      <c r="G332" s="1" t="n">
+      <c r="H332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -8759,10 +9758,13 @@
         <v>0.10372</v>
       </c>
       <c r="F333" s="1" t="n">
+        <v>0.10344</v>
+      </c>
+      <c r="G333" s="1" t="n">
         <v>0.10416</v>
       </c>
-      <c r="G333" s="1" t="n">
-        <v>0.10347</v>
+      <c r="H333" s="1" t="n">
+        <v>0.10344</v>
       </c>
     </row>
     <row r="334">
@@ -8784,10 +9786,13 @@
         <v>0.08749999999999999</v>
       </c>
       <c r="F334" s="1" t="n">
+        <v>0.08734</v>
+      </c>
+      <c r="G334" s="1" t="n">
         <v>0.08837</v>
       </c>
-      <c r="G334" s="1" t="n">
-        <v>0.08749999999999999</v>
+      <c r="H334" s="1" t="n">
+        <v>0.08734</v>
       </c>
     </row>
     <row r="335">
@@ -8812,6 +9817,9 @@
         <v>0.016413</v>
       </c>
       <c r="G335" s="1" t="n">
+        <v>0.016413</v>
+      </c>
+      <c r="H335" s="1" t="n">
         <v>0.016391</v>
       </c>
     </row>
@@ -8834,9 +9842,12 @@
         <v>0.04583</v>
       </c>
       <c r="F336" s="1" t="n">
+        <v>0.04588</v>
+      </c>
+      <c r="G336" s="1" t="n">
         <v>0.04594</v>
       </c>
-      <c r="G336" s="1" t="n">
+      <c r="H336" s="1" t="n">
         <v>0.04583</v>
       </c>
     </row>
@@ -8859,9 +9870,12 @@
         <v>0.1842</v>
       </c>
       <c r="F337" s="1" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="G337" s="1" t="n">
         <v>0.1853</v>
       </c>
-      <c r="G337" s="1" t="n">
+      <c r="H337" s="1" t="n">
         <v>0.1838</v>
       </c>
     </row>
@@ -8884,9 +9898,12 @@
         <v>0.1833</v>
       </c>
       <c r="F338" s="1" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="G338" s="1" t="n">
         <v>0.1836</v>
       </c>
-      <c r="G338" s="1" t="n">
+      <c r="H338" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -8909,9 +9926,12 @@
         <v>0.01836</v>
       </c>
       <c r="F339" s="1" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="G339" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="G339" s="1" t="n">
+      <c r="H339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -8934,10 +9954,13 @@
         <v>0.02307</v>
       </c>
       <c r="F340" s="1" t="n">
+        <v>0.02305</v>
+      </c>
+      <c r="G340" s="1" t="n">
         <v>0.02311</v>
       </c>
-      <c r="G340" s="1" t="n">
-        <v>0.02306</v>
+      <c r="H340" s="1" t="n">
+        <v>0.02305</v>
       </c>
     </row>
     <row r="341">
@@ -8959,9 +9982,12 @@
         <v>0.455</v>
       </c>
       <c r="F341" s="1" t="n">
+        <v>0.4541</v>
+      </c>
+      <c r="G341" s="1" t="n">
         <v>0.455</v>
       </c>
-      <c r="G341" s="1" t="n">
+      <c r="H341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -8984,9 +10010,12 @@
         <v>0.01343</v>
       </c>
       <c r="F342" s="1" t="n">
+        <v>0.01341</v>
+      </c>
+      <c r="G342" s="1" t="n">
         <v>0.01344</v>
       </c>
-      <c r="G342" s="1" t="n">
+      <c r="H342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -9009,9 +10038,12 @@
         <v>2.885</v>
       </c>
       <c r="F343" s="1" t="n">
+        <v>2.886</v>
+      </c>
+      <c r="G343" s="1" t="n">
         <v>2.89</v>
       </c>
-      <c r="G343" s="1" t="n">
+      <c r="H343" s="1" t="n">
         <v>2.874</v>
       </c>
     </row>
@@ -9034,9 +10066,12 @@
         <v>0.1577</v>
       </c>
       <c r="F344" s="1" t="n">
+        <v>0.1534</v>
+      </c>
+      <c r="G344" s="1" t="n">
         <v>0.1577</v>
       </c>
-      <c r="G344" s="1" t="n">
+      <c r="H344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -9059,9 +10094,12 @@
         <v>0.005351</v>
       </c>
       <c r="F345" s="1" t="n">
+        <v>0.005344</v>
+      </c>
+      <c r="G345" s="1" t="n">
         <v>0.005367</v>
       </c>
-      <c r="G345" s="1" t="n">
+      <c r="H345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -9084,9 +10122,12 @@
         <v>0.05778</v>
       </c>
       <c r="F346" s="1" t="n">
+        <v>0.05768</v>
+      </c>
+      <c r="G346" s="1" t="n">
         <v>0.05781</v>
       </c>
-      <c r="G346" s="1" t="n">
+      <c r="H346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -9109,9 +10150,12 @@
         <v>2603</v>
       </c>
       <c r="F347" s="1" t="n">
+        <v>2601</v>
+      </c>
+      <c r="G347" s="1" t="n">
         <v>2606</v>
       </c>
-      <c r="G347" s="1" t="n">
+      <c r="H347" s="1" t="n">
         <v>2597</v>
       </c>
     </row>
@@ -9134,9 +10178,12 @@
         <v>0.04595</v>
       </c>
       <c r="F348" s="1" t="n">
+        <v>0.04596</v>
+      </c>
+      <c r="G348" s="1" t="n">
         <v>0.04621</v>
       </c>
-      <c r="G348" s="1" t="n">
+      <c r="H348" s="1" t="n">
         <v>0.04595</v>
       </c>
     </row>
@@ -9159,9 +10206,12 @@
         <v>0.005676</v>
       </c>
       <c r="F349" s="1" t="n">
-        <v>0.005707</v>
+        <v>0.005714</v>
       </c>
       <c r="G349" s="1" t="n">
+        <v>0.005714</v>
+      </c>
+      <c r="H349" s="1" t="n">
         <v>0.005676</v>
       </c>
     </row>
@@ -9184,9 +10234,12 @@
         <v>195.32</v>
       </c>
       <c r="F350" s="1" t="n">
+        <v>195.26</v>
+      </c>
+      <c r="G350" s="1" t="n">
         <v>195.51</v>
       </c>
-      <c r="G350" s="1" t="n">
+      <c r="H350" s="1" t="n">
         <v>195.23</v>
       </c>
     </row>
@@ -9209,9 +10262,12 @@
         <v>0.08237999999999999</v>
       </c>
       <c r="F351" s="1" t="n">
+        <v>0.08207</v>
+      </c>
+      <c r="G351" s="1" t="n">
         <v>0.08237999999999999</v>
       </c>
-      <c r="G351" s="1" t="n">
+      <c r="H351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -9234,9 +10290,12 @@
         <v>0.007458</v>
       </c>
       <c r="F352" s="1" t="n">
+        <v>0.00746</v>
+      </c>
+      <c r="G352" s="1" t="n">
         <v>0.007571</v>
       </c>
-      <c r="G352" s="1" t="n">
+      <c r="H352" s="1" t="n">
         <v>0.007458</v>
       </c>
     </row>
@@ -9259,9 +10318,12 @@
         <v>1.5085</v>
       </c>
       <c r="F353" s="1" t="n">
-        <v>1.5085</v>
+        <v>1.5087</v>
       </c>
       <c r="G353" s="1" t="n">
+        <v>1.5087</v>
+      </c>
+      <c r="H353" s="1" t="n">
         <v>1.4807</v>
       </c>
     </row>
@@ -9284,9 +10346,12 @@
         <v>0.07617</v>
       </c>
       <c r="F354" s="1" t="n">
+        <v>0.07629</v>
+      </c>
+      <c r="G354" s="1" t="n">
         <v>0.07643999999999999</v>
       </c>
-      <c r="G354" s="1" t="n">
+      <c r="H354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -9309,10 +10374,13 @@
         <v>0.0489</v>
       </c>
       <c r="F355" s="1" t="n">
+        <v>0.04874</v>
+      </c>
+      <c r="G355" s="1" t="n">
         <v>0.04921</v>
       </c>
-      <c r="G355" s="1" t="n">
-        <v>0.0489</v>
+      <c r="H355" s="1" t="n">
+        <v>0.04874</v>
       </c>
     </row>
     <row r="356">
@@ -9334,9 +10402,12 @@
         <v>0.2861</v>
       </c>
       <c r="F356" s="1" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="G356" s="1" t="n">
         <v>0.2861</v>
       </c>
-      <c r="G356" s="1" t="n">
+      <c r="H356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -9359,9 +10430,12 @@
         <v>0.1466</v>
       </c>
       <c r="F357" s="1" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="G357" s="1" t="n">
         <v>0.1467</v>
       </c>
-      <c r="G357" s="1" t="n">
+      <c r="H357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -9384,9 +10458,12 @@
         <v>1.353</v>
       </c>
       <c r="F358" s="1" t="n">
+        <v>1.352</v>
+      </c>
+      <c r="G358" s="1" t="n">
         <v>1.355</v>
       </c>
-      <c r="G358" s="1" t="n">
+      <c r="H358" s="1" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -9409,10 +10486,13 @@
         <v>0.6091</v>
       </c>
       <c r="F359" s="1" t="n">
+        <v>0.6081</v>
+      </c>
+      <c r="G359" s="1" t="n">
         <v>0.6117</v>
       </c>
-      <c r="G359" s="1" t="n">
-        <v>0.6091</v>
+      <c r="H359" s="1" t="n">
+        <v>0.6081</v>
       </c>
     </row>
     <row r="360">
@@ -9434,9 +10514,12 @@
         <v>0.1144</v>
       </c>
       <c r="F360" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="G360" s="1" t="n">
         <v>0.1145</v>
       </c>
-      <c r="G360" s="1" t="n">
+      <c r="H360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -9459,9 +10542,12 @@
         <v>0.02624</v>
       </c>
       <c r="F361" s="1" t="n">
-        <v>0.02624</v>
+        <v>0.02631</v>
       </c>
       <c r="G361" s="1" t="n">
+        <v>0.02631</v>
+      </c>
+      <c r="H361" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -9484,9 +10570,12 @@
         <v>3.04e-05</v>
       </c>
       <c r="F362" s="1" t="n">
+        <v>3.03e-05</v>
+      </c>
+      <c r="G362" s="1" t="n">
         <v>3.04e-05</v>
       </c>
-      <c r="G362" s="1" t="n">
+      <c r="H362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -9509,9 +10598,12 @@
         <v>0.01022</v>
       </c>
       <c r="F363" s="1" t="n">
+        <v>0.01022</v>
+      </c>
+      <c r="G363" s="1" t="n">
         <v>0.01026</v>
       </c>
-      <c r="G363" s="1" t="n">
+      <c r="H363" s="1" t="n">
         <v>0.01018</v>
       </c>
     </row>
@@ -9534,9 +10626,12 @@
         <v>0.06207</v>
       </c>
       <c r="F364" s="1" t="n">
+        <v>0.06206</v>
+      </c>
+      <c r="G364" s="1" t="n">
         <v>0.06208</v>
       </c>
-      <c r="G364" s="1" t="n">
+      <c r="H364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -9559,9 +10654,12 @@
         <v>0.03285</v>
       </c>
       <c r="F365" s="1" t="n">
+        <v>0.03295</v>
+      </c>
+      <c r="G365" s="1" t="n">
         <v>0.03297</v>
       </c>
-      <c r="G365" s="1" t="n">
+      <c r="H365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -9584,10 +10682,13 @@
         <v>0.03292</v>
       </c>
       <c r="F366" s="1" t="n">
+        <v>0.03283</v>
+      </c>
+      <c r="G366" s="1" t="n">
         <v>0.03296</v>
       </c>
-      <c r="G366" s="1" t="n">
-        <v>0.03288</v>
+      <c r="H366" s="1" t="n">
+        <v>0.03283</v>
       </c>
     </row>
     <row r="367">
@@ -9609,9 +10710,12 @@
         <v>0.012203</v>
       </c>
       <c r="F367" s="1" t="n">
-        <v>0.012203</v>
+        <v>0.012215</v>
       </c>
       <c r="G367" s="1" t="n">
+        <v>0.012215</v>
+      </c>
+      <c r="H367" s="1" t="n">
         <v>0.012155</v>
       </c>
     </row>
@@ -9634,9 +10738,12 @@
         <v>0.03559</v>
       </c>
       <c r="F368" s="1" t="n">
+        <v>0.03547</v>
+      </c>
+      <c r="G368" s="1" t="n">
         <v>0.03559</v>
       </c>
-      <c r="G368" s="1" t="n">
+      <c r="H368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -9659,9 +10766,12 @@
         <v>0.6198</v>
       </c>
       <c r="F369" s="1" t="n">
-        <v>0.6198</v>
+        <v>0.6261</v>
       </c>
       <c r="G369" s="1" t="n">
+        <v>0.6261</v>
+      </c>
+      <c r="H369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -9684,9 +10794,12 @@
         <v>0.00856</v>
       </c>
       <c r="F370" s="1" t="n">
-        <v>0.00856</v>
+        <v>0.008630000000000001</v>
       </c>
       <c r="G370" s="1" t="n">
+        <v>0.008630000000000001</v>
+      </c>
+      <c r="H370" s="1" t="n">
         <v>0.00843</v>
       </c>
     </row>
@@ -9709,9 +10822,12 @@
         <v>0.003288</v>
       </c>
       <c r="F371" s="1" t="n">
+        <v>0.00328</v>
+      </c>
+      <c r="G371" s="1" t="n">
         <v>0.003288</v>
       </c>
-      <c r="G371" s="1" t="n">
+      <c r="H371" s="1" t="n">
         <v>0.003242</v>
       </c>
     </row>
@@ -9734,9 +10850,12 @@
         <v>0.13301</v>
       </c>
       <c r="F372" s="1" t="n">
+        <v>0.13278</v>
+      </c>
+      <c r="G372" s="1" t="n">
         <v>0.13301</v>
       </c>
-      <c r="G372" s="1" t="n">
+      <c r="H372" s="1" t="n">
         <v>0.13227</v>
       </c>
     </row>
@@ -9759,10 +10878,13 @@
         <v>0.007806</v>
       </c>
       <c r="F373" s="1" t="n">
+        <v>0.007771</v>
+      </c>
+      <c r="G373" s="1" t="n">
         <v>0.007822000000000001</v>
       </c>
-      <c r="G373" s="1" t="n">
-        <v>0.007806</v>
+      <c r="H373" s="1" t="n">
+        <v>0.007771</v>
       </c>
     </row>
     <row r="374">
@@ -9784,10 +10906,13 @@
         <v>0.0197</v>
       </c>
       <c r="F374" s="1" t="n">
+        <v>0.01969</v>
+      </c>
+      <c r="G374" s="1" t="n">
         <v>0.01978</v>
       </c>
-      <c r="G374" s="1" t="n">
-        <v>0.0197</v>
+      <c r="H374" s="1" t="n">
+        <v>0.01969</v>
       </c>
     </row>
     <row r="375">
@@ -9809,10 +10934,13 @@
         <v>0.0005918</v>
       </c>
       <c r="F375" s="1" t="n">
+        <v>0.0005910000000000001</v>
+      </c>
+      <c r="G375" s="1" t="n">
         <v>0.000594</v>
       </c>
-      <c r="G375" s="1" t="n">
-        <v>0.0005914</v>
+      <c r="H375" s="1" t="n">
+        <v>0.0005910000000000001</v>
       </c>
     </row>
     <row r="376">
@@ -9837,6 +10965,9 @@
         <v>0.0363</v>
       </c>
       <c r="G376" s="1" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="H376" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -9859,9 +10990,12 @@
         <v>0.0007917</v>
       </c>
       <c r="F377" s="1" t="n">
+        <v>0.0007906</v>
+      </c>
+      <c r="G377" s="1" t="n">
         <v>0.000792</v>
       </c>
-      <c r="G377" s="1" t="n">
+      <c r="H377" s="1" t="n">
         <v>0.0007848</v>
       </c>
     </row>
@@ -9884,9 +11018,12 @@
         <v>1.99</v>
       </c>
       <c r="F378" s="1" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="G378" s="1" t="n">
         <v>1.99</v>
       </c>
-      <c r="G378" s="1" t="n">
+      <c r="H378" s="1" t="n">
         <v>1.973</v>
       </c>
     </row>
@@ -9909,10 +11046,13 @@
         <v>0.0005882</v>
       </c>
       <c r="F379" s="1" t="n">
+        <v>0.0005881</v>
+      </c>
+      <c r="G379" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="G379" s="1" t="n">
-        <v>0.0005882</v>
+      <c r="H379" s="1" t="n">
+        <v>0.0005881</v>
       </c>
     </row>
     <row r="380">
@@ -9934,9 +11074,12 @@
         <v>0.03747</v>
       </c>
       <c r="F380" s="1" t="n">
-        <v>0.03747</v>
+        <v>0.03751</v>
       </c>
       <c r="G380" s="1" t="n">
+        <v>0.03751</v>
+      </c>
+      <c r="H380" s="1" t="n">
         <v>0.03737</v>
       </c>
     </row>
@@ -9959,9 +11102,12 @@
         <v>0.05467</v>
       </c>
       <c r="F381" s="1" t="n">
+        <v>0.05462</v>
+      </c>
+      <c r="G381" s="1" t="n">
         <v>0.05477</v>
       </c>
-      <c r="G381" s="1" t="n">
+      <c r="H381" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -9984,9 +11130,12 @@
         <v>0.01205</v>
       </c>
       <c r="F382" s="1" t="n">
+        <v>0.01204</v>
+      </c>
+      <c r="G382" s="1" t="n">
         <v>0.01207</v>
       </c>
-      <c r="G382" s="1" t="n">
+      <c r="H382" s="1" t="n">
         <v>0.01202</v>
       </c>
     </row>
@@ -10009,10 +11158,13 @@
         <v>0.001553</v>
       </c>
       <c r="F383" s="1" t="n">
+        <v>0.001551</v>
+      </c>
+      <c r="G383" s="1" t="n">
         <v>0.001559</v>
       </c>
-      <c r="G383" s="1" t="n">
-        <v>0.001552</v>
+      <c r="H383" s="1" t="n">
+        <v>0.001551</v>
       </c>
     </row>
     <row r="384">
@@ -10034,9 +11186,12 @@
         <v>0.0002157</v>
       </c>
       <c r="F384" s="1" t="n">
-        <v>0.0002157</v>
+        <v>0.0002158</v>
       </c>
       <c r="G384" s="1" t="n">
+        <v>0.0002158</v>
+      </c>
+      <c r="H384" s="1" t="n">
         <v>0.0002154</v>
       </c>
     </row>
@@ -10059,9 +11214,12 @@
         <v>0.0024</v>
       </c>
       <c r="F385" s="1" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="G385" s="1" t="n">
         <v>0.00242</v>
       </c>
-      <c r="G385" s="1" t="n">
+      <c r="H385" s="1" t="n">
         <v>0.0024</v>
       </c>
     </row>
@@ -10084,9 +11242,12 @@
         <v>3.906</v>
       </c>
       <c r="F386" s="1" t="n">
+        <v>3.906</v>
+      </c>
+      <c r="G386" s="1" t="n">
         <v>3.908</v>
       </c>
-      <c r="G386" s="1" t="n">
+      <c r="H386" s="1" t="n">
         <v>3.892</v>
       </c>
     </row>
@@ -10109,10 +11270,13 @@
         <v>0.0006241</v>
       </c>
       <c r="F387" s="1" t="n">
+        <v>0.0006236</v>
+      </c>
+      <c r="G387" s="1" t="n">
         <v>0.0006254</v>
       </c>
-      <c r="G387" s="1" t="n">
-        <v>0.0006237</v>
+      <c r="H387" s="1" t="n">
+        <v>0.0006236</v>
       </c>
     </row>
     <row r="388">
@@ -10134,9 +11298,12 @@
         <v>0.00664</v>
       </c>
       <c r="F388" s="1" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="G388" s="1" t="n">
         <v>0.00664</v>
       </c>
-      <c r="G388" s="1" t="n">
+      <c r="H388" s="1" t="n">
         <v>0.00653</v>
       </c>
     </row>
@@ -10159,9 +11326,12 @@
         <v>0.1318</v>
       </c>
       <c r="F389" s="1" t="n">
-        <v>0.1318</v>
+        <v>0.1319</v>
       </c>
       <c r="G389" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="H389" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -10184,9 +11354,12 @@
         <v>0.0323</v>
       </c>
       <c r="F390" s="1" t="n">
-        <v>0.0323</v>
+        <v>0.0324</v>
       </c>
       <c r="G390" s="1" t="n">
+        <v>0.0324</v>
+      </c>
+      <c r="H390" s="1" t="n">
         <v>0.03201</v>
       </c>
     </row>
@@ -10209,10 +11382,13 @@
         <v>0.06351</v>
       </c>
       <c r="F391" s="1" t="n">
+        <v>0.06344</v>
+      </c>
+      <c r="G391" s="1" t="n">
         <v>0.06362</v>
       </c>
-      <c r="G391" s="1" t="n">
-        <v>0.06351</v>
+      <c r="H391" s="1" t="n">
+        <v>0.06344</v>
       </c>
     </row>
     <row r="392">
@@ -10234,10 +11410,13 @@
         <v>27.72</v>
       </c>
       <c r="F392" s="1" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="G392" s="1" t="n">
         <v>27.82</v>
       </c>
-      <c r="G392" s="1" t="n">
-        <v>27.72</v>
+      <c r="H392" s="1" t="n">
+        <v>27.57</v>
       </c>
     </row>
     <row r="393">
@@ -10259,9 +11438,12 @@
         <v>0.000413</v>
       </c>
       <c r="F393" s="1" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="G393" s="1" t="n">
         <v>0.000414</v>
       </c>
-      <c r="G393" s="1" t="n">
+      <c r="H393" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -10284,9 +11466,12 @@
         <v>0.07005</v>
       </c>
       <c r="F394" s="1" t="n">
+        <v>0.06961000000000001</v>
+      </c>
+      <c r="G394" s="1" t="n">
         <v>0.07005</v>
       </c>
-      <c r="G394" s="1" t="n">
+      <c r="H394" s="1" t="n">
         <v>0.06926</v>
       </c>
     </row>
@@ -10309,9 +11494,12 @@
         <v>0.2591</v>
       </c>
       <c r="F395" s="1" t="n">
-        <v>0.2591</v>
+        <v>0.2592</v>
       </c>
       <c r="G395" s="1" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="H395" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -10334,9 +11522,12 @@
         <v>0.00469</v>
       </c>
       <c r="F396" s="1" t="n">
+        <v>0.004678</v>
+      </c>
+      <c r="G396" s="1" t="n">
         <v>0.00469</v>
       </c>
-      <c r="G396" s="1" t="n">
+      <c r="H396" s="1" t="n">
         <v>0.004677</v>
       </c>
     </row>
@@ -10359,9 +11550,12 @@
         <v>0.234</v>
       </c>
       <c r="F397" s="1" t="n">
-        <v>0.2345</v>
+        <v>0.2352</v>
       </c>
       <c r="G397" s="1" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="H397" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
@@ -10384,9 +11578,12 @@
         <v>0.18128</v>
       </c>
       <c r="F398" s="1" t="n">
+        <v>0.18123</v>
+      </c>
+      <c r="G398" s="1" t="n">
         <v>0.18131</v>
       </c>
-      <c r="G398" s="1" t="n">
+      <c r="H398" s="1" t="n">
         <v>0.18106</v>
       </c>
     </row>
@@ -10409,9 +11606,12 @@
         <v>0.04124</v>
       </c>
       <c r="F399" s="1" t="n">
+        <v>0.04119</v>
+      </c>
+      <c r="G399" s="1" t="n">
         <v>0.04124</v>
       </c>
-      <c r="G399" s="1" t="n">
+      <c r="H399" s="1" t="n">
         <v>0.04108</v>
       </c>
     </row>
@@ -10434,9 +11634,12 @@
         <v>0.075</v>
       </c>
       <c r="F400" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G400" s="1" t="n">
         <v>0.076</v>
       </c>
-      <c r="G400" s="1" t="n">
+      <c r="H400" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -10459,9 +11662,12 @@
         <v>0.00175</v>
       </c>
       <c r="F401" s="1" t="n">
+        <v>0.001743</v>
+      </c>
+      <c r="G401" s="1" t="n">
         <v>0.001751</v>
       </c>
-      <c r="G401" s="1" t="n">
+      <c r="H401" s="1" t="n">
         <v>0.001739</v>
       </c>
     </row>
@@ -10487,6 +11693,9 @@
         <v>0.05394</v>
       </c>
       <c r="G402" s="1" t="n">
+        <v>0.05394</v>
+      </c>
+      <c r="H402" s="1" t="n">
         <v>0.05362</v>
       </c>
     </row>
@@ -10509,9 +11718,12 @@
         <v>2027.43</v>
       </c>
       <c r="F403" s="1" t="n">
+        <v>2028.07</v>
+      </c>
+      <c r="G403" s="1" t="n">
         <v>2031.8</v>
       </c>
-      <c r="G403" s="1" t="n">
+      <c r="H403" s="1" t="n">
         <v>2027.43</v>
       </c>
     </row>
@@ -10534,10 +11746,13 @@
         <v>1.079</v>
       </c>
       <c r="F404" s="1" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="G404" s="1" t="n">
         <v>1.082</v>
       </c>
-      <c r="G404" s="1" t="n">
-        <v>1.079</v>
+      <c r="H404" s="1" t="n">
+        <v>1.078</v>
       </c>
     </row>
     <row r="405">
@@ -10559,10 +11774,13 @@
         <v>7.662</v>
       </c>
       <c r="F405" s="1" t="n">
+        <v>7.649</v>
+      </c>
+      <c r="G405" s="1" t="n">
         <v>7.662</v>
       </c>
-      <c r="G405" s="1" t="n">
-        <v>7.65</v>
+      <c r="H405" s="1" t="n">
+        <v>7.649</v>
       </c>
     </row>
     <row r="406">
@@ -10584,9 +11802,12 @@
         <v>3.246</v>
       </c>
       <c r="F406" s="1" t="n">
+        <v>3.253</v>
+      </c>
+      <c r="G406" s="1" t="n">
         <v>3.257</v>
       </c>
-      <c r="G406" s="1" t="n">
+      <c r="H406" s="1" t="n">
         <v>3.238</v>
       </c>
     </row>
@@ -10609,9 +11830,12 @@
         <v>0.1817</v>
       </c>
       <c r="F407" s="1" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="G407" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="G407" s="1" t="n">
+      <c r="H407" s="1" t="n">
         <v>0.1814</v>
       </c>
     </row>
@@ -10634,9 +11858,12 @@
         <v>0.153</v>
       </c>
       <c r="F408" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="G408" s="1" t="n">
         <v>0.1537</v>
       </c>
-      <c r="G408" s="1" t="n">
+      <c r="H408" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -10659,9 +11886,12 @@
         <v>0.07345</v>
       </c>
       <c r="F409" s="1" t="n">
+        <v>0.07335999999999999</v>
+      </c>
+      <c r="G409" s="1" t="n">
         <v>0.07346999999999999</v>
       </c>
-      <c r="G409" s="1" t="n">
+      <c r="H409" s="1" t="n">
         <v>0.07315000000000001</v>
       </c>
     </row>
@@ -10684,9 +11914,12 @@
         <v>0.02118</v>
       </c>
       <c r="F410" s="1" t="n">
+        <v>0.02104</v>
+      </c>
+      <c r="G410" s="1" t="n">
         <v>0.02118</v>
       </c>
-      <c r="G410" s="1" t="n">
+      <c r="H410" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -10709,9 +11942,12 @@
         <v>0.2666</v>
       </c>
       <c r="F411" s="1" t="n">
-        <v>0.2666</v>
+        <v>0.2669</v>
       </c>
       <c r="G411" s="1" t="n">
+        <v>0.2669</v>
+      </c>
+      <c r="H411" s="1" t="n">
         <v>0.2642</v>
       </c>
     </row>
@@ -10734,9 +11970,12 @@
         <v>0.007383</v>
       </c>
       <c r="F412" s="1" t="n">
+        <v>0.00735</v>
+      </c>
+      <c r="G412" s="1" t="n">
         <v>0.007383</v>
       </c>
-      <c r="G412" s="1" t="n">
+      <c r="H412" s="1" t="n">
         <v>0.007302</v>
       </c>
     </row>
@@ -10759,10 +11998,13 @@
         <v>0.01386</v>
       </c>
       <c r="F413" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="G413" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="G413" s="1" t="n">
-        <v>0.01385</v>
+      <c r="H413" s="1" t="n">
+        <v>0.01384</v>
       </c>
     </row>
     <row r="414">
@@ -10787,6 +12029,9 @@
         <v>0.093</v>
       </c>
       <c r="G414" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="H414" s="1" t="n">
         <v>0.092</v>
       </c>
     </row>
@@ -10809,9 +12054,12 @@
         <v>0.04004</v>
       </c>
       <c r="F415" s="1" t="n">
-        <v>0.04009</v>
+        <v>0.04012</v>
       </c>
       <c r="G415" s="1" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="H415" s="1" t="n">
         <v>0.03998</v>
       </c>
     </row>
@@ -10834,9 +12082,12 @@
         <v>0.284</v>
       </c>
       <c r="F416" s="1" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="G416" s="1" t="n">
         <v>0.2854</v>
       </c>
-      <c r="G416" s="1" t="n">
+      <c r="H416" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -10859,9 +12110,12 @@
         <v>1.819</v>
       </c>
       <c r="F417" s="1" t="n">
-        <v>1.821</v>
+        <v>1.826</v>
       </c>
       <c r="G417" s="1" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="H417" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -10884,10 +12138,13 @@
         <v>0.06686</v>
       </c>
       <c r="F418" s="1" t="n">
+        <v>0.06668</v>
+      </c>
+      <c r="G418" s="1" t="n">
         <v>0.06707</v>
       </c>
-      <c r="G418" s="1" t="n">
-        <v>0.06672</v>
+      <c r="H418" s="1" t="n">
+        <v>0.06668</v>
       </c>
     </row>
     <row r="419">
@@ -10909,9 +12166,12 @@
         <v>207.46</v>
       </c>
       <c r="F419" s="1" t="n">
+        <v>207.39</v>
+      </c>
+      <c r="G419" s="1" t="n">
         <v>207.46</v>
       </c>
-      <c r="G419" s="1" t="n">
+      <c r="H419" s="1" t="n">
         <v>207.35</v>
       </c>
     </row>
@@ -10934,9 +12194,12 @@
         <v>73.27</v>
       </c>
       <c r="F420" s="1" t="n">
-        <v>73.27</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="G420" s="1" t="n">
+        <v>73.31999999999999</v>
+      </c>
+      <c r="H420" s="1" t="n">
         <v>73.15000000000001</v>
       </c>
     </row>
@@ -10959,10 +12222,13 @@
         <v>0.07251000000000001</v>
       </c>
       <c r="F421" s="1" t="n">
+        <v>0.07226</v>
+      </c>
+      <c r="G421" s="1" t="n">
         <v>0.07251000000000001</v>
       </c>
-      <c r="G421" s="1" t="n">
-        <v>0.07242</v>
+      <c r="H421" s="1" t="n">
+        <v>0.07226</v>
       </c>
     </row>
     <row r="422">
@@ -10984,9 +12250,12 @@
         <v>0.05017</v>
       </c>
       <c r="F422" s="1" t="n">
-        <v>0.05017</v>
+        <v>0.05041</v>
       </c>
       <c r="G422" s="1" t="n">
+        <v>0.05041</v>
+      </c>
+      <c r="H422" s="1" t="n">
         <v>0.04998</v>
       </c>
     </row>
@@ -11012,6 +12281,9 @@
         <v>0.00115</v>
       </c>
       <c r="G423" s="1" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="H423" s="1" t="n">
         <v>0.001148</v>
       </c>
     </row>
@@ -11034,10 +12306,13 @@
         <v>0.00502</v>
       </c>
       <c r="F424" s="1" t="n">
+        <v>0.00501</v>
+      </c>
+      <c r="G424" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="G424" s="1" t="n">
-        <v>0.00502</v>
+      <c r="H424" s="1" t="n">
+        <v>0.00501</v>
       </c>
     </row>
     <row r="425">
@@ -11062,6 +12337,9 @@
         <v>0.1269</v>
       </c>
       <c r="G425" s="1" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="H425" s="1" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -11084,9 +12362,12 @@
         <v>1.295</v>
       </c>
       <c r="F426" s="1" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="G426" s="1" t="n">
         <v>1.299</v>
       </c>
-      <c r="G426" s="1" t="n">
+      <c r="H426" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -11109,9 +12390,12 @@
         <v>0.004413</v>
       </c>
       <c r="F427" s="1" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="G427" s="1" t="n">
         <v>0.004413</v>
       </c>
-      <c r="G427" s="1" t="n">
+      <c r="H427" s="1" t="n">
         <v>0.004393</v>
       </c>
     </row>
@@ -11134,9 +12418,12 @@
         <v>0.005042</v>
       </c>
       <c r="F428" s="1" t="n">
+        <v>0.005038</v>
+      </c>
+      <c r="G428" s="1" t="n">
         <v>0.005042</v>
       </c>
-      <c r="G428" s="1" t="n">
+      <c r="H428" s="1" t="n">
         <v>0.005017</v>
       </c>
     </row>
@@ -11159,9 +12446,12 @@
         <v>0.02329</v>
       </c>
       <c r="F429" s="1" t="n">
+        <v>0.02327</v>
+      </c>
+      <c r="G429" s="1" t="n">
         <v>0.02329</v>
       </c>
-      <c r="G429" s="1" t="n">
+      <c r="H429" s="1" t="n">
         <v>0.02288</v>
       </c>
     </row>
@@ -11184,9 +12474,12 @@
         <v>0.02511</v>
       </c>
       <c r="F430" s="1" t="n">
-        <v>0.02511</v>
+        <v>0.02516</v>
       </c>
       <c r="G430" s="1" t="n">
+        <v>0.02516</v>
+      </c>
+      <c r="H430" s="1" t="n">
         <v>0.02501</v>
       </c>
     </row>
@@ -11209,9 +12502,12 @@
         <v>0.016</v>
       </c>
       <c r="F431" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="G431" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="G431" s="1" t="n">
+      <c r="H431" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -11234,9 +12530,12 @@
         <v>0.546</v>
       </c>
       <c r="F432" s="1" t="n">
+        <v>0.5444</v>
+      </c>
+      <c r="G432" s="1" t="n">
         <v>0.546</v>
       </c>
-      <c r="G432" s="1" t="n">
+      <c r="H432" s="1" t="n">
         <v>0.5439000000000001</v>
       </c>
     </row>
@@ -11259,9 +12558,12 @@
         <v>0.001389</v>
       </c>
       <c r="F433" s="1" t="n">
+        <v>0.001387</v>
+      </c>
+      <c r="G433" s="1" t="n">
         <v>0.001389</v>
       </c>
-      <c r="G433" s="1" t="n">
+      <c r="H433" s="1" t="n">
         <v>0.001383</v>
       </c>
     </row>
@@ -11284,9 +12586,12 @@
         <v>0.3949</v>
       </c>
       <c r="F434" s="1" t="n">
-        <v>0.3949</v>
+        <v>0.3952</v>
       </c>
       <c r="G434" s="1" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="H434" s="1" t="n">
         <v>0.3925</v>
       </c>
     </row>
@@ -11309,9 +12614,12 @@
         <v>0.00139</v>
       </c>
       <c r="F435" s="1" t="n">
+        <v>0.001391</v>
+      </c>
+      <c r="G435" s="1" t="n">
         <v>0.001393</v>
       </c>
-      <c r="G435" s="1" t="n">
+      <c r="H435" s="1" t="n">
         <v>0.00139</v>
       </c>
     </row>
@@ -11334,9 +12642,12 @@
         <v>0.00715</v>
       </c>
       <c r="F436" s="1" t="n">
+        <v>0.00715</v>
+      </c>
+      <c r="G436" s="1" t="n">
         <v>0.00716</v>
       </c>
-      <c r="G436" s="1" t="n">
+      <c r="H436" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -11359,9 +12670,12 @@
         <v>0.001987</v>
       </c>
       <c r="F437" s="1" t="n">
+        <v>0.001988</v>
+      </c>
+      <c r="G437" s="1" t="n">
         <v>0.001991</v>
       </c>
-      <c r="G437" s="1" t="n">
+      <c r="H437" s="1" t="n">
         <v>0.001982</v>
       </c>
     </row>
@@ -11384,9 +12698,12 @@
         <v>0.3142</v>
       </c>
       <c r="F438" s="1" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="G438" s="1" t="n">
         <v>0.3143</v>
       </c>
-      <c r="G438" s="1" t="n">
+      <c r="H438" s="1" t="n">
         <v>0.3122</v>
       </c>
     </row>
@@ -11409,9 +12726,12 @@
         <v>0.04426</v>
       </c>
       <c r="F439" s="1" t="n">
+        <v>0.04429</v>
+      </c>
+      <c r="G439" s="1" t="n">
         <v>0.04435</v>
       </c>
-      <c r="G439" s="1" t="n">
+      <c r="H439" s="1" t="n">
         <v>0.04426</v>
       </c>
     </row>
@@ -11434,9 +12754,12 @@
         <v>0.908</v>
       </c>
       <c r="F440" s="1" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="G440" s="1" t="n">
         <v>0.908</v>
       </c>
-      <c r="G440" s="1" t="n">
+      <c r="H440" s="1" t="n">
         <v>0.906</v>
       </c>
     </row>
@@ -11459,9 +12782,12 @@
         <v>1550.12</v>
       </c>
       <c r="F441" s="1" t="n">
+        <v>1548.99</v>
+      </c>
+      <c r="G441" s="1" t="n">
         <v>1550.68</v>
       </c>
-      <c r="G441" s="1" t="n">
+      <c r="H441" s="1" t="n">
         <v>1548.06</v>
       </c>
     </row>
@@ -11484,9 +12810,12 @@
         <v>0.0007936</v>
       </c>
       <c r="F442" s="1" t="n">
+        <v>0.0007915</v>
+      </c>
+      <c r="G442" s="1" t="n">
         <v>0.0007951</v>
       </c>
-      <c r="G442" s="1" t="n">
+      <c r="H442" s="1" t="n">
         <v>0.0007877</v>
       </c>
     </row>
@@ -11509,9 +12838,12 @@
         <v>0.003543</v>
       </c>
       <c r="F443" s="1" t="n">
+        <v>0.003544</v>
+      </c>
+      <c r="G443" s="1" t="n">
         <v>0.003558</v>
       </c>
-      <c r="G443" s="1" t="n">
+      <c r="H443" s="1" t="n">
         <v>0.003543</v>
       </c>
     </row>
@@ -11534,10 +12866,13 @@
         <v>1.979</v>
       </c>
       <c r="F444" s="1" t="n">
+        <v>1.977</v>
+      </c>
+      <c r="G444" s="1" t="n">
         <v>1.989</v>
       </c>
-      <c r="G444" s="1" t="n">
-        <v>1.979</v>
+      <c r="H444" s="1" t="n">
+        <v>1.977</v>
       </c>
     </row>
     <row r="445">
@@ -11559,9 +12894,12 @@
         <v>1.305</v>
       </c>
       <c r="F445" s="1" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="G445" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="G445" s="1" t="n">
+      <c r="H445" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -11584,10 +12922,13 @@
         <v>0.06906</v>
       </c>
       <c r="F446" s="1" t="n">
+        <v>0.06894</v>
+      </c>
+      <c r="G446" s="1" t="n">
         <v>0.06929</v>
       </c>
-      <c r="G446" s="1" t="n">
-        <v>0.06906</v>
+      <c r="H446" s="1" t="n">
+        <v>0.06894</v>
       </c>
     </row>
     <row r="447">
@@ -11609,9 +12950,12 @@
         <v>0.0238</v>
       </c>
       <c r="F447" s="1" t="n">
-        <v>0.0238</v>
+        <v>0.02381</v>
       </c>
       <c r="G447" s="1" t="n">
+        <v>0.02381</v>
+      </c>
+      <c r="H447" s="1" t="n">
         <v>0.02347</v>
       </c>
     </row>
@@ -11634,9 +12978,12 @@
         <v>0.01397</v>
       </c>
       <c r="F448" s="1" t="n">
-        <v>0.01397</v>
+        <v>0.014</v>
       </c>
       <c r="G448" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H448" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -11659,9 +13006,12 @@
         <v>3.733</v>
       </c>
       <c r="F449" s="1" t="n">
+        <v>3.731</v>
+      </c>
+      <c r="G449" s="1" t="n">
         <v>3.734</v>
       </c>
-      <c r="G449" s="1" t="n">
+      <c r="H449" s="1" t="n">
         <v>3.726</v>
       </c>
     </row>
@@ -11684,9 +13034,12 @@
         <v>0.0114</v>
       </c>
       <c r="F450" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="G450" s="1" t="n">
         <v>0.0115</v>
       </c>
-      <c r="G450" s="1" t="n">
+      <c r="H450" s="1" t="n">
         <v>0.0114</v>
       </c>
     </row>
@@ -11709,9 +13062,12 @@
         <v>0.01029</v>
       </c>
       <c r="F451" s="1" t="n">
+        <v>0.01028</v>
+      </c>
+      <c r="G451" s="1" t="n">
         <v>0.01029</v>
       </c>
-      <c r="G451" s="1" t="n">
+      <c r="H451" s="1" t="n">
         <v>0.01024</v>
       </c>
     </row>
@@ -11734,9 +13090,12 @@
         <v>0.1524</v>
       </c>
       <c r="F452" s="1" t="n">
-        <v>0.1525</v>
+        <v>0.1526</v>
       </c>
       <c r="G452" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="H452" s="1" t="n">
         <v>0.1522</v>
       </c>
     </row>
@@ -11759,9 +13118,12 @@
         <v>151.04</v>
       </c>
       <c r="F453" s="1" t="n">
-        <v>151.04</v>
+        <v>151.12</v>
       </c>
       <c r="G453" s="1" t="n">
+        <v>151.12</v>
+      </c>
+      <c r="H453" s="1" t="n">
         <v>150.85</v>
       </c>
     </row>
@@ -11784,9 +13146,12 @@
         <v>0.008617</v>
       </c>
       <c r="F454" s="1" t="n">
+        <v>0.008607999999999999</v>
+      </c>
+      <c r="G454" s="1" t="n">
         <v>0.008623</v>
       </c>
-      <c r="G454" s="1" t="n">
+      <c r="H454" s="1" t="n">
         <v>0.008593999999999999</v>
       </c>
     </row>
@@ -11809,9 +13174,12 @@
         <v>0.05248</v>
       </c>
       <c r="F455" s="1" t="n">
+        <v>0.05243</v>
+      </c>
+      <c r="G455" s="1" t="n">
         <v>0.05248</v>
       </c>
-      <c r="G455" s="1" t="n">
+      <c r="H455" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -11834,9 +13202,12 @@
         <v>0.30511</v>
       </c>
       <c r="F456" s="1" t="n">
-        <v>0.30511</v>
+        <v>0.30535</v>
       </c>
       <c r="G456" s="1" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="H456" s="1" t="n">
         <v>0.30269</v>
       </c>
     </row>
@@ -11859,9 +13230,12 @@
         <v>0.00546</v>
       </c>
       <c r="F457" s="1" t="n">
+        <v>0.00544</v>
+      </c>
+      <c r="G457" s="1" t="n">
         <v>0.00546</v>
       </c>
-      <c r="G457" s="1" t="n">
+      <c r="H457" s="1" t="n">
         <v>0.00544</v>
       </c>
     </row>
@@ -11884,9 +13258,12 @@
         <v>0.1004</v>
       </c>
       <c r="F458" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="G458" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="G458" s="1" t="n">
+      <c r="H458" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -11909,9 +13286,12 @@
         <v>0.001832</v>
       </c>
       <c r="F459" s="1" t="n">
+        <v>0.001832</v>
+      </c>
+      <c r="G459" s="1" t="n">
         <v>0.001835</v>
       </c>
-      <c r="G459" s="1" t="n">
+      <c r="H459" s="1" t="n">
         <v>0.001825</v>
       </c>
     </row>
@@ -11934,9 +13314,12 @@
         <v>0.01835</v>
       </c>
       <c r="F460" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="G460" s="1" t="n">
         <v>0.01835</v>
       </c>
-      <c r="G460" s="1" t="n">
+      <c r="H460" s="1" t="n">
         <v>0.01822</v>
       </c>
     </row>
@@ -11959,10 +13342,13 @@
         <v>0.0004859</v>
       </c>
       <c r="F461" s="1" t="n">
+        <v>0.0004844</v>
+      </c>
+      <c r="G461" s="1" t="n">
         <v>0.0004877</v>
       </c>
-      <c r="G461" s="1" t="n">
-        <v>0.0004859</v>
+      <c r="H461" s="1" t="n">
+        <v>0.0004844</v>
       </c>
     </row>
     <row r="462">
@@ -11984,9 +13370,12 @@
         <v>0.096</v>
       </c>
       <c r="F462" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="G462" s="1" t="n">
         <v>0.096</v>
       </c>
-      <c r="G462" s="1" t="n">
+      <c r="H462" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -12009,9 +13398,12 @@
         <v>0.07931000000000001</v>
       </c>
       <c r="F463" s="1" t="n">
+        <v>0.07914</v>
+      </c>
+      <c r="G463" s="1" t="n">
         <v>0.07931000000000001</v>
       </c>
-      <c r="G463" s="1" t="n">
+      <c r="H463" s="1" t="n">
         <v>0.07888000000000001</v>
       </c>
     </row>
@@ -12034,9 +13426,12 @@
         <v>0.03151</v>
       </c>
       <c r="F464" s="1" t="n">
+        <v>0.03148</v>
+      </c>
+      <c r="G464" s="1" t="n">
         <v>0.03155</v>
       </c>
-      <c r="G464" s="1" t="n">
+      <c r="H464" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -12059,9 +13454,12 @@
         <v>0.01616</v>
       </c>
       <c r="F465" s="1" t="n">
+        <v>0.01614</v>
+      </c>
+      <c r="G465" s="1" t="n">
         <v>0.01618</v>
       </c>
-      <c r="G465" s="1" t="n">
+      <c r="H465" s="1" t="n">
         <v>0.01613</v>
       </c>
     </row>
@@ -12084,10 +13482,13 @@
         <v>0.06764000000000001</v>
       </c>
       <c r="F466" s="1" t="n">
+        <v>0.06763</v>
+      </c>
+      <c r="G466" s="1" t="n">
         <v>0.06781</v>
       </c>
-      <c r="G466" s="1" t="n">
-        <v>0.06764000000000001</v>
+      <c r="H466" s="1" t="n">
+        <v>0.06763</v>
       </c>
     </row>
     <row r="467">
@@ -12109,9 +13510,12 @@
         <v>0.04331</v>
       </c>
       <c r="F467" s="1" t="n">
+        <v>0.04323</v>
+      </c>
+      <c r="G467" s="1" t="n">
         <v>0.04332</v>
       </c>
-      <c r="G467" s="1" t="n">
+      <c r="H467" s="1" t="n">
         <v>0.04322</v>
       </c>
     </row>
@@ -12134,9 +13538,12 @@
         <v>0.05795</v>
       </c>
       <c r="F468" s="1" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="G468" s="1" t="n">
         <v>0.05795</v>
       </c>
-      <c r="G468" s="1" t="n">
+      <c r="H468" s="1" t="n">
         <v>0.05587</v>
       </c>
     </row>
@@ -12159,9 +13566,12 @@
         <v>0.2304</v>
       </c>
       <c r="F469" s="1" t="n">
+        <v>0.2301</v>
+      </c>
+      <c r="G469" s="1" t="n">
         <v>0.2305</v>
       </c>
-      <c r="G469" s="1" t="n">
+      <c r="H469" s="1" t="n">
         <v>0.2294</v>
       </c>
     </row>
@@ -12184,9 +13594,12 @@
         <v>0.0905</v>
       </c>
       <c r="F470" s="1" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="G470" s="1" t="n">
         <v>0.0905</v>
       </c>
-      <c r="G470" s="1" t="n">
+      <c r="H470" s="1" t="n">
         <v>0.0902</v>
       </c>
     </row>
@@ -12209,9 +13622,12 @@
         <v>0.06677</v>
       </c>
       <c r="F471" s="1" t="n">
+        <v>0.06673</v>
+      </c>
+      <c r="G471" s="1" t="n">
         <v>0.0669</v>
       </c>
-      <c r="G471" s="1" t="n">
+      <c r="H471" s="1" t="n">
         <v>0.06669</v>
       </c>
     </row>
@@ -12234,9 +13650,12 @@
         <v>6.527</v>
       </c>
       <c r="F472" s="1" t="n">
-        <v>6.527</v>
+        <v>6.552</v>
       </c>
       <c r="G472" s="1" t="n">
+        <v>6.552</v>
+      </c>
+      <c r="H472" s="1" t="n">
         <v>6.486</v>
       </c>
     </row>
@@ -12259,9 +13678,12 @@
         <v>0.01937</v>
       </c>
       <c r="F473" s="1" t="n">
+        <v>0.01937</v>
+      </c>
+      <c r="G473" s="1" t="n">
         <v>0.01943</v>
       </c>
-      <c r="G473" s="1" t="n">
+      <c r="H473" s="1" t="n">
         <v>0.01937</v>
       </c>
     </row>
@@ -12284,10 +13706,13 @@
         <v>1.422</v>
       </c>
       <c r="F474" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G474" s="1" t="n">
         <v>1.423</v>
       </c>
-      <c r="G474" s="1" t="n">
-        <v>1.421</v>
+      <c r="H474" s="1" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="475">
@@ -12309,9 +13734,12 @@
         <v>0.08977</v>
       </c>
       <c r="F475" s="1" t="n">
-        <v>0.0898</v>
+        <v>0.08981</v>
       </c>
       <c r="G475" s="1" t="n">
+        <v>0.08981</v>
+      </c>
+      <c r="H475" s="1" t="n">
         <v>0.08974</v>
       </c>
     </row>
@@ -12334,9 +13762,12 @@
         <v>0.1058</v>
       </c>
       <c r="F476" s="1" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="G476" s="1" t="n">
         <v>0.1062</v>
       </c>
-      <c r="G476" s="1" t="n">
+      <c r="H476" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -12359,10 +13790,13 @@
         <v>0.09451</v>
       </c>
       <c r="F477" s="1" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="G477" s="1" t="n">
         <v>0.09451</v>
       </c>
-      <c r="G477" s="1" t="n">
-        <v>0.09427000000000001</v>
+      <c r="H477" s="1" t="n">
+        <v>0.0941</v>
       </c>
     </row>
     <row r="478">
@@ -12384,9 +13818,12 @@
         <v>0.0001628</v>
       </c>
       <c r="F478" s="1" t="n">
+        <v>0.0001626</v>
+      </c>
+      <c r="G478" s="1" t="n">
         <v>0.0001629</v>
       </c>
-      <c r="G478" s="1" t="n">
+      <c r="H478" s="1" t="n">
         <v>0.0001624</v>
       </c>
     </row>
@@ -12409,9 +13846,12 @@
         <v>0.04018</v>
       </c>
       <c r="F479" s="1" t="n">
+        <v>0.04016</v>
+      </c>
+      <c r="G479" s="1" t="n">
         <v>0.04023</v>
       </c>
-      <c r="G479" s="1" t="n">
+      <c r="H479" s="1" t="n">
         <v>0.04007</v>
       </c>
     </row>
@@ -12434,9 +13874,12 @@
         <v>0.007407</v>
       </c>
       <c r="F480" s="1" t="n">
+        <v>0.007394</v>
+      </c>
+      <c r="G480" s="1" t="n">
         <v>0.007422</v>
       </c>
-      <c r="G480" s="1" t="n">
+      <c r="H480" s="1" t="n">
         <v>0.007389</v>
       </c>
     </row>
@@ -12459,9 +13902,12 @@
         <v>0.0955</v>
       </c>
       <c r="F481" s="1" t="n">
+        <v>0.0954</v>
+      </c>
+      <c r="G481" s="1" t="n">
         <v>0.0955</v>
       </c>
-      <c r="G481" s="1" t="n">
+      <c r="H481" s="1" t="n">
         <v>0.0954</v>
       </c>
     </row>
@@ -12484,10 +13930,13 @@
         <v>0.05594</v>
       </c>
       <c r="F482" s="1" t="n">
+        <v>0.05569</v>
+      </c>
+      <c r="G482" s="1" t="n">
         <v>0.05621</v>
       </c>
-      <c r="G482" s="1" t="n">
-        <v>0.05594</v>
+      <c r="H482" s="1" t="n">
+        <v>0.05569</v>
       </c>
     </row>
     <row r="483">
@@ -12509,9 +13958,12 @@
         <v>0.006195</v>
       </c>
       <c r="F483" s="1" t="n">
+        <v>0.006167</v>
+      </c>
+      <c r="G483" s="1" t="n">
         <v>0.006195</v>
       </c>
-      <c r="G483" s="1" t="n">
+      <c r="H483" s="1" t="n">
         <v>0.006161</v>
       </c>
     </row>
@@ -12534,9 +13986,12 @@
         <v>0.0149</v>
       </c>
       <c r="F484" s="1" t="n">
+        <v>0.01488</v>
+      </c>
+      <c r="G484" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="G484" s="1" t="n">
+      <c r="H484" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -12559,9 +14014,12 @@
         <v>0.02413</v>
       </c>
       <c r="F485" s="1" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="G485" s="1" t="n">
         <v>0.02427</v>
       </c>
-      <c r="G485" s="1" t="n">
+      <c r="H485" s="1" t="n">
         <v>0.02403</v>
       </c>
     </row>
@@ -12584,9 +14042,12 @@
         <v>0.06702</v>
       </c>
       <c r="F486" s="1" t="n">
+        <v>0.06687</v>
+      </c>
+      <c r="G486" s="1" t="n">
         <v>0.06702</v>
       </c>
-      <c r="G486" s="1" t="n">
+      <c r="H486" s="1" t="n">
         <v>0.0667</v>
       </c>
     </row>
@@ -12609,9 +14070,12 @@
         <v>0.03693</v>
       </c>
       <c r="F487" s="1" t="n">
+        <v>0.03687</v>
+      </c>
+      <c r="G487" s="1" t="n">
         <v>0.03705</v>
       </c>
-      <c r="G487" s="1" t="n">
+      <c r="H487" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -12634,9 +14098,12 @@
         <v>0.01814</v>
       </c>
       <c r="F488" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="G488" s="1" t="n">
         <v>0.0182</v>
       </c>
-      <c r="G488" s="1" t="n">
+      <c r="H488" s="1" t="n">
         <v>0.01814</v>
       </c>
     </row>
@@ -12659,10 +14126,13 @@
         <v>0.03254</v>
       </c>
       <c r="F489" s="1" t="n">
+        <v>0.03244</v>
+      </c>
+      <c r="G489" s="1" t="n">
         <v>0.03278</v>
       </c>
-      <c r="G489" s="1" t="n">
-        <v>0.0325</v>
+      <c r="H489" s="1" t="n">
+        <v>0.03244</v>
       </c>
     </row>
     <row r="490">
@@ -12684,9 +14154,12 @@
         <v>0.0147</v>
       </c>
       <c r="F490" s="1" t="n">
+        <v>0.01466</v>
+      </c>
+      <c r="G490" s="1" t="n">
         <v>0.01474</v>
       </c>
-      <c r="G490" s="1" t="n">
+      <c r="H490" s="1" t="n">
         <v>0.01458</v>
       </c>
     </row>
@@ -12709,9 +14182,12 @@
         <v>0.01861</v>
       </c>
       <c r="F491" s="1" t="n">
+        <v>0.01858</v>
+      </c>
+      <c r="G491" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="G491" s="1" t="n">
+      <c r="H491" s="1" t="n">
         <v>0.01851</v>
       </c>
     </row>
@@ -12734,10 +14210,13 @@
         <v>0.08919000000000001</v>
       </c>
       <c r="F492" s="1" t="n">
+        <v>0.08810999999999999</v>
+      </c>
+      <c r="G492" s="1" t="n">
         <v>0.08935</v>
       </c>
-      <c r="G492" s="1" t="n">
-        <v>0.08842</v>
+      <c r="H492" s="1" t="n">
+        <v>0.08810999999999999</v>
       </c>
     </row>
     <row r="493">
@@ -12759,10 +14238,13 @@
         <v>0.006506</v>
       </c>
       <c r="F493" s="1" t="n">
+        <v>0.006497</v>
+      </c>
+      <c r="G493" s="1" t="n">
         <v>0.006514</v>
       </c>
-      <c r="G493" s="1" t="n">
-        <v>0.006498</v>
+      <c r="H493" s="1" t="n">
+        <v>0.006497</v>
       </c>
     </row>
     <row r="494">
@@ -12784,9 +14266,12 @@
         <v>0.1327</v>
       </c>
       <c r="F494" s="1" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="G494" s="1" t="n">
         <v>0.1327</v>
       </c>
-      <c r="G494" s="1" t="n">
+      <c r="H494" s="1" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -12809,9 +14294,12 @@
         <v>0.2847</v>
       </c>
       <c r="F495" s="1" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="G495" s="1" t="n">
         <v>0.2853</v>
       </c>
-      <c r="G495" s="1" t="n">
+      <c r="H495" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -12834,9 +14322,12 @@
         <v>0.004518</v>
       </c>
       <c r="F496" s="1" t="n">
+        <v>0.004523</v>
+      </c>
+      <c r="G496" s="1" t="n">
         <v>0.004534</v>
       </c>
-      <c r="G496" s="1" t="n">
+      <c r="H496" s="1" t="n">
         <v>0.004516</v>
       </c>
     </row>
@@ -12859,9 +14350,12 @@
         <v>0.1265</v>
       </c>
       <c r="F497" s="1" t="n">
+        <v>0.1268</v>
+      </c>
+      <c r="G497" s="1" t="n">
         <v>0.1283</v>
       </c>
-      <c r="G497" s="1" t="n">
+      <c r="H497" s="1" t="n">
         <v>0.1265</v>
       </c>
     </row>
@@ -12884,9 +14378,12 @@
         <v>0.03428</v>
       </c>
       <c r="F498" s="1" t="n">
+        <v>0.03429</v>
+      </c>
+      <c r="G498" s="1" t="n">
         <v>0.03439</v>
       </c>
-      <c r="G498" s="1" t="n">
+      <c r="H498" s="1" t="n">
         <v>0.03423</v>
       </c>
     </row>
@@ -12909,9 +14406,12 @@
         <v>0.03559</v>
       </c>
       <c r="F499" s="1" t="n">
+        <v>0.03557</v>
+      </c>
+      <c r="G499" s="1" t="n">
         <v>0.03576</v>
       </c>
-      <c r="G499" s="1" t="n">
+      <c r="H499" s="1" t="n">
         <v>0.03557</v>
       </c>
     </row>
@@ -12934,10 +14434,13 @@
         <v>0.003417</v>
       </c>
       <c r="F500" s="1" t="n">
+        <v>0.003413</v>
+      </c>
+      <c r="G500" s="1" t="n">
         <v>0.003421</v>
       </c>
-      <c r="G500" s="1" t="n">
-        <v>0.003417</v>
+      <c r="H500" s="1" t="n">
+        <v>0.003413</v>
       </c>
     </row>
     <row r="501">
@@ -12959,9 +14462,12 @@
         <v>0.0003809</v>
       </c>
       <c r="F501" s="1" t="n">
-        <v>0.0003809</v>
+        <v>0.0003824</v>
       </c>
       <c r="G501" s="1" t="n">
+        <v>0.0003824</v>
+      </c>
+      <c r="H501" s="1" t="n">
         <v>0.0003786</v>
       </c>
     </row>
@@ -12984,9 +14490,12 @@
         <v>0.3003</v>
       </c>
       <c r="F502" s="1" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="G502" s="1" t="n">
         <v>0.3003</v>
       </c>
-      <c r="G502" s="1" t="n">
+      <c r="H502" s="1" t="n">
         <v>0.2986</v>
       </c>
     </row>
@@ -13009,10 +14518,13 @@
         <v>0.06494999999999999</v>
       </c>
       <c r="F503" s="1" t="n">
+        <v>0.06485</v>
+      </c>
+      <c r="G503" s="1" t="n">
         <v>0.06507</v>
       </c>
-      <c r="G503" s="1" t="n">
-        <v>0.06494999999999999</v>
+      <c r="H503" s="1" t="n">
+        <v>0.06485</v>
       </c>
     </row>
     <row r="504">
@@ -13034,9 +14546,12 @@
         <v>0.1777</v>
       </c>
       <c r="F504" s="1" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="G504" s="1" t="n">
         <v>0.1777</v>
       </c>
-      <c r="G504" s="1" t="n">
+      <c r="H504" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -13059,9 +14574,12 @@
         <v>0.1513</v>
       </c>
       <c r="F505" s="1" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="G505" s="1" t="n">
         <v>0.1513</v>
       </c>
-      <c r="G505" s="1" t="n">
+      <c r="H505" s="1" t="n">
         <v>0.1512</v>
       </c>
     </row>
@@ -13084,9 +14602,12 @@
         <v>0.01196</v>
       </c>
       <c r="F506" s="1" t="n">
-        <v>0.01198</v>
+        <v>0.01199</v>
       </c>
       <c r="G506" s="1" t="n">
+        <v>0.01199</v>
+      </c>
+      <c r="H506" s="1" t="n">
         <v>0.01193</v>
       </c>
     </row>
@@ -13109,9 +14630,12 @@
         <v>0.2871</v>
       </c>
       <c r="F507" s="1" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="G507" s="1" t="n">
         <v>0.2883</v>
       </c>
-      <c r="G507" s="1" t="n">
+      <c r="H507" s="1" t="n">
         <v>0.2871</v>
       </c>
     </row>
@@ -13134,10 +14658,13 @@
         <v>0.00933</v>
       </c>
       <c r="F508" s="1" t="n">
+        <v>0.009310000000000001</v>
+      </c>
+      <c r="G508" s="1" t="n">
         <v>0.0094</v>
       </c>
-      <c r="G508" s="1" t="n">
-        <v>0.00933</v>
+      <c r="H508" s="1" t="n">
+        <v>0.009310000000000001</v>
       </c>
     </row>
     <row r="509">
@@ -13159,9 +14686,12 @@
         <v>0.006795</v>
       </c>
       <c r="F509" s="1" t="n">
+        <v>0.00681</v>
+      </c>
+      <c r="G509" s="1" t="n">
         <v>0.006816</v>
       </c>
-      <c r="G509" s="1" t="n">
+      <c r="H509" s="1" t="n">
         <v>0.006783</v>
       </c>
     </row>
@@ -13184,10 +14714,13 @@
         <v>0.2942</v>
       </c>
       <c r="F510" s="1" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="G510" s="1" t="n">
         <v>0.2951</v>
       </c>
-      <c r="G510" s="1" t="n">
-        <v>0.2936</v>
+      <c r="H510" s="1" t="n">
+        <v>0.2934</v>
       </c>
     </row>
     <row r="511">
@@ -13209,10 +14742,13 @@
         <v>0.01466</v>
       </c>
       <c r="F511" s="1" t="n">
+        <v>0.01465</v>
+      </c>
+      <c r="G511" s="1" t="n">
         <v>0.01471</v>
       </c>
-      <c r="G511" s="1" t="n">
-        <v>0.01466</v>
+      <c r="H511" s="1" t="n">
+        <v>0.01465</v>
       </c>
     </row>
     <row r="512">
@@ -13234,10 +14770,13 @@
         <v>0.1395</v>
       </c>
       <c r="F512" s="1" t="n">
+        <v>0.1394</v>
+      </c>
+      <c r="G512" s="1" t="n">
         <v>0.1398</v>
       </c>
-      <c r="G512" s="1" t="n">
-        <v>0.1395</v>
+      <c r="H512" s="1" t="n">
+        <v>0.1394</v>
       </c>
     </row>
     <row r="513">
@@ -13259,9 +14798,12 @@
         <v>0.08112</v>
       </c>
       <c r="F513" s="1" t="n">
+        <v>0.08103</v>
+      </c>
+      <c r="G513" s="1" t="n">
         <v>0.08144999999999999</v>
       </c>
-      <c r="G513" s="1" t="n">
+      <c r="H513" s="1" t="n">
         <v>0.08069</v>
       </c>
     </row>
@@ -13284,9 +14826,12 @@
         <v>0.025</v>
       </c>
       <c r="F514" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G514" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="G514" s="1" t="n">
+      <c r="H514" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -13309,9 +14854,12 @@
         <v>0.06307</v>
       </c>
       <c r="F515" s="1" t="n">
+        <v>0.06308</v>
+      </c>
+      <c r="G515" s="1" t="n">
         <v>0.06319</v>
       </c>
-      <c r="G515" s="1" t="n">
+      <c r="H515" s="1" t="n">
         <v>0.06301</v>
       </c>
     </row>
@@ -13334,9 +14882,12 @@
         <v>0.04722</v>
       </c>
       <c r="F516" s="1" t="n">
+        <v>0.04717</v>
+      </c>
+      <c r="G516" s="1" t="n">
         <v>0.04723</v>
       </c>
-      <c r="G516" s="1" t="n">
+      <c r="H516" s="1" t="n">
         <v>0.04707</v>
       </c>
     </row>
@@ -13359,10 +14910,13 @@
         <v>0.004904</v>
       </c>
       <c r="F517" s="1" t="n">
+        <v>0.004902</v>
+      </c>
+      <c r="G517" s="1" t="n">
         <v>0.004908</v>
       </c>
-      <c r="G517" s="1" t="n">
-        <v>0.004904</v>
+      <c r="H517" s="1" t="n">
+        <v>0.004902</v>
       </c>
     </row>
     <row r="518">
@@ -13384,9 +14938,12 @@
         <v>0.009426</v>
       </c>
       <c r="F518" s="1" t="n">
-        <v>0.009429999999999999</v>
+        <v>0.009431999999999999</v>
       </c>
       <c r="G518" s="1" t="n">
+        <v>0.009431999999999999</v>
+      </c>
+      <c r="H518" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -13409,9 +14966,12 @@
         <v>0.01798</v>
       </c>
       <c r="F519" s="1" t="n">
+        <v>0.01803</v>
+      </c>
+      <c r="G519" s="1" t="n">
         <v>0.01807</v>
       </c>
-      <c r="G519" s="1" t="n">
+      <c r="H519" s="1" t="n">
         <v>0.01798</v>
       </c>
     </row>
@@ -13434,9 +14994,12 @@
         <v>0.06684</v>
       </c>
       <c r="F520" s="1" t="n">
+        <v>0.06677</v>
+      </c>
+      <c r="G520" s="1" t="n">
         <v>0.06684</v>
       </c>
-      <c r="G520" s="1" t="n">
+      <c r="H520" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -13459,9 +15022,12 @@
         <v>0.1362</v>
       </c>
       <c r="F521" s="1" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="G521" s="1" t="n">
         <v>0.1365</v>
       </c>
-      <c r="G521" s="1" t="n">
+      <c r="H521" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -13484,9 +15050,12 @@
         <v>0.04741</v>
       </c>
       <c r="F522" s="1" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="G522" s="1" t="n">
         <v>0.04746</v>
       </c>
-      <c r="G522" s="1" t="n">
+      <c r="H522" s="1" t="n">
         <v>0.04718</v>
       </c>
     </row>
@@ -13509,10 +15078,13 @@
         <v>0.06798999999999999</v>
       </c>
       <c r="F523" s="1" t="n">
+        <v>0.06784999999999999</v>
+      </c>
+      <c r="G523" s="1" t="n">
         <v>0.06809</v>
       </c>
-      <c r="G523" s="1" t="n">
-        <v>0.06793</v>
+      <c r="H523" s="1" t="n">
+        <v>0.06784999999999999</v>
       </c>
     </row>
     <row r="524">
@@ -13534,9 +15106,12 @@
         <v>0.6981000000000001</v>
       </c>
       <c r="F524" s="1" t="n">
+        <v>0.6966</v>
+      </c>
+      <c r="G524" s="1" t="n">
         <v>0.6982</v>
       </c>
-      <c r="G524" s="1" t="n">
+      <c r="H524" s="1" t="n">
         <v>0.6966</v>
       </c>
     </row>
@@ -13564,6 +15139,9 @@
       <c r="G525" s="1" t="n">
         <v>0.00267</v>
       </c>
+      <c r="H525" s="1" t="n">
+        <v>0.00267</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -13584,9 +15162,12 @@
         <v>0.4865</v>
       </c>
       <c r="F526" s="1" t="n">
+        <v>0.4859</v>
+      </c>
+      <c r="G526" s="1" t="n">
         <v>0.4868</v>
       </c>
-      <c r="G526" s="1" t="n">
+      <c r="H526" s="1" t="n">
         <v>0.4856</v>
       </c>
     </row>
@@ -13612,6 +15193,9 @@
         <v>45.82</v>
       </c>
       <c r="G527" s="1" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="H527" s="1" t="n">
         <v>45.76</v>
       </c>
     </row>
@@ -13634,10 +15218,13 @@
         <v>0.02431</v>
       </c>
       <c r="F528" s="1" t="n">
+        <v>0.02429</v>
+      </c>
+      <c r="G528" s="1" t="n">
         <v>0.02437</v>
       </c>
-      <c r="G528" s="1" t="n">
-        <v>0.02431</v>
+      <c r="H528" s="1" t="n">
+        <v>0.02429</v>
       </c>
     </row>
     <row r="529">
@@ -13659,9 +15246,12 @@
         <v>0.006392</v>
       </c>
       <c r="F529" s="1" t="n">
+        <v>0.006391</v>
+      </c>
+      <c r="G529" s="1" t="n">
         <v>0.006392</v>
       </c>
-      <c r="G529" s="1" t="n">
+      <c r="H529" s="1" t="n">
         <v>0.00638</v>
       </c>
     </row>
@@ -13684,9 +15274,12 @@
         <v>0.1995</v>
       </c>
       <c r="F530" s="1" t="n">
+        <v>0.1993</v>
+      </c>
+      <c r="G530" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="G530" s="1" t="n">
+      <c r="H530" s="1" t="n">
         <v>0.1993</v>
       </c>
     </row>
@@ -13709,9 +15302,12 @@
         <v>0.00768</v>
       </c>
       <c r="F531" s="1" t="n">
+        <v>0.007675</v>
+      </c>
+      <c r="G531" s="1" t="n">
         <v>0.007727</v>
       </c>
-      <c r="G531" s="1" t="n">
+      <c r="H531" s="1" t="n">
         <v>0.007657</v>
       </c>
     </row>
@@ -13734,9 +15330,12 @@
         <v>2.282</v>
       </c>
       <c r="F532" s="1" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="G532" s="1" t="n">
         <v>2.285</v>
       </c>
-      <c r="G532" s="1" t="n">
+      <c r="H532" s="1" t="n">
         <v>2.275</v>
       </c>
     </row>
@@ -13759,9 +15358,12 @@
         <v>0.04148</v>
       </c>
       <c r="F533" s="1" t="n">
-        <v>0.04148</v>
+        <v>0.04153</v>
       </c>
       <c r="G533" s="1" t="n">
+        <v>0.04153</v>
+      </c>
+      <c r="H533" s="1" t="n">
         <v>0.04138</v>
       </c>
     </row>
@@ -13784,9 +15386,12 @@
         <v>0.1816</v>
       </c>
       <c r="F534" s="1" t="n">
-        <v>0.1819</v>
+        <v>0.1824</v>
       </c>
       <c r="G534" s="1" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="H534" s="1" t="n">
         <v>0.1811</v>
       </c>
     </row>
@@ -13809,9 +15414,12 @@
         <v>0.04287</v>
       </c>
       <c r="F535" s="1" t="n">
+        <v>0.04291</v>
+      </c>
+      <c r="G535" s="1" t="n">
         <v>0.04311</v>
       </c>
-      <c r="G535" s="1" t="n">
+      <c r="H535" s="1" t="n">
         <v>0.04287</v>
       </c>
     </row>
@@ -13834,10 +15442,13 @@
         <v>0.0543</v>
       </c>
       <c r="F536" s="1" t="n">
+        <v>0.05417</v>
+      </c>
+      <c r="G536" s="1" t="n">
         <v>0.05438</v>
       </c>
-      <c r="G536" s="1" t="n">
-        <v>0.0542</v>
+      <c r="H536" s="1" t="n">
+        <v>0.05417</v>
       </c>
     </row>
     <row r="537">
@@ -13859,10 +15470,13 @@
         <v>0.1606</v>
       </c>
       <c r="F537" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="G537" s="1" t="n">
         <v>0.1609</v>
       </c>
-      <c r="G537" s="1" t="n">
-        <v>0.1605</v>
+      <c r="H537" s="1" t="n">
+        <v>0.1602</v>
       </c>
     </row>
     <row r="538">
@@ -13884,9 +15498,12 @@
         <v>0.03677</v>
       </c>
       <c r="F538" s="1" t="n">
+        <v>0.03673</v>
+      </c>
+      <c r="G538" s="1" t="n">
         <v>0.03687</v>
       </c>
-      <c r="G538" s="1" t="n">
+      <c r="H538" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -13909,9 +15526,12 @@
         <v>0.05776</v>
       </c>
       <c r="F539" s="1" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="G539" s="1" t="n">
         <v>0.05776</v>
       </c>
-      <c r="G539" s="1" t="n">
+      <c r="H539" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -13934,10 +15554,13 @@
         <v>0.04258</v>
       </c>
       <c r="F540" s="1" t="n">
+        <v>0.04256</v>
+      </c>
+      <c r="G540" s="1" t="n">
         <v>0.04267</v>
       </c>
-      <c r="G540" s="1" t="n">
-        <v>0.04257</v>
+      <c r="H540" s="1" t="n">
+        <v>0.04256</v>
       </c>
     </row>
     <row r="541">
@@ -13959,9 +15582,12 @@
         <v>0.01729</v>
       </c>
       <c r="F541" s="1" t="n">
+        <v>0.01724</v>
+      </c>
+      <c r="G541" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="G541" s="1" t="n">
+      <c r="H541" s="1" t="n">
         <v>0.0172</v>
       </c>
     </row>
@@ -13984,10 +15610,13 @@
         <v>0.00397</v>
       </c>
       <c r="F542" s="1" t="n">
+        <v>0.003963</v>
+      </c>
+      <c r="G542" s="1" t="n">
         <v>0.003975</v>
       </c>
-      <c r="G542" s="1" t="n">
-        <v>0.00397</v>
+      <c r="H542" s="1" t="n">
+        <v>0.003963</v>
       </c>
     </row>
     <row r="543">
@@ -14009,9 +15638,12 @@
         <v>0.05781</v>
       </c>
       <c r="F543" s="1" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="G543" s="1" t="n">
         <v>0.05817</v>
       </c>
-      <c r="G543" s="1" t="n">
+      <c r="H543" s="1" t="n">
         <v>0.05735</v>
       </c>
     </row>
@@ -14034,9 +15666,12 @@
         <v>0.05016</v>
       </c>
       <c r="F544" s="1" t="n">
+        <v>0.05016</v>
+      </c>
+      <c r="G544" s="1" t="n">
         <v>0.05042</v>
       </c>
-      <c r="G544" s="1" t="n">
+      <c r="H544" s="1" t="n">
         <v>0.05016</v>
       </c>
     </row>
@@ -14059,9 +15694,12 @@
         <v>0.04045</v>
       </c>
       <c r="F545" s="1" t="n">
+        <v>0.04053</v>
+      </c>
+      <c r="G545" s="1" t="n">
         <v>0.04064</v>
       </c>
-      <c r="G545" s="1" t="n">
+      <c r="H545" s="1" t="n">
         <v>0.04038</v>
       </c>
     </row>
@@ -14084,9 +15722,12 @@
         <v>0.007432</v>
       </c>
       <c r="F546" s="1" t="n">
+        <v>0.007429</v>
+      </c>
+      <c r="G546" s="1" t="n">
         <v>0.007432</v>
       </c>
-      <c r="G546" s="1" t="n">
+      <c r="H546" s="1" t="n">
         <v>0.007402</v>
       </c>
     </row>
@@ -14109,9 +15750,12 @@
         <v>0.01466</v>
       </c>
       <c r="F547" s="1" t="n">
-        <v>0.01466</v>
+        <v>0.01469</v>
       </c>
       <c r="G547" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="H547" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -14134,10 +15778,13 @@
         <v>0.01572</v>
       </c>
       <c r="F548" s="1" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="G548" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="G548" s="1" t="n">
-        <v>0.01572</v>
+      <c r="H548" s="1" t="n">
+        <v>0.0157</v>
       </c>
     </row>
     <row r="549">
@@ -14159,9 +15806,12 @@
         <v>0.13429</v>
       </c>
       <c r="F549" s="1" t="n">
+        <v>0.13429</v>
+      </c>
+      <c r="G549" s="1" t="n">
         <v>0.13434</v>
       </c>
-      <c r="G549" s="1" t="n">
+      <c r="H549" s="1" t="n">
         <v>0.13271</v>
       </c>
     </row>
@@ -14184,10 +15834,13 @@
         <v>0.1696</v>
       </c>
       <c r="F550" s="1" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="G550" s="1" t="n">
         <v>0.1696</v>
       </c>
-      <c r="G550" s="1" t="n">
-        <v>0.1695</v>
+      <c r="H550" s="1" t="n">
+        <v>0.1693</v>
       </c>
     </row>
     <row r="551">
@@ -14209,9 +15862,12 @@
         <v>0.003579</v>
       </c>
       <c r="F551" s="1" t="n">
+        <v>0.003579</v>
+      </c>
+      <c r="G551" s="1" t="n">
         <v>0.003583</v>
       </c>
-      <c r="G551" s="1" t="n">
+      <c r="H551" s="1" t="n">
         <v>0.003577</v>
       </c>
     </row>
@@ -14234,10 +15890,13 @@
         <v>0.03037</v>
       </c>
       <c r="F552" s="1" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="G552" s="1" t="n">
         <v>0.03038</v>
       </c>
-      <c r="G552" s="1" t="n">
-        <v>0.03032</v>
+      <c r="H552" s="1" t="n">
+        <v>0.0303</v>
       </c>
     </row>
     <row r="553">
@@ -14259,10 +15918,13 @@
         <v>0.01324</v>
       </c>
       <c r="F553" s="1" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="G553" s="1" t="n">
         <v>0.01325</v>
       </c>
-      <c r="G553" s="1" t="n">
-        <v>0.01324</v>
+      <c r="H553" s="1" t="n">
+        <v>0.0132</v>
       </c>
     </row>
     <row r="554">
@@ -14284,9 +15946,12 @@
         <v>0.1039</v>
       </c>
       <c r="F554" s="1" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="G554" s="1" t="n">
         <v>0.1046</v>
       </c>
-      <c r="G554" s="1" t="n">
+      <c r="H554" s="1" t="n">
         <v>0.1039</v>
       </c>
     </row>
@@ -14309,9 +15974,12 @@
         <v>0.05304</v>
       </c>
       <c r="F555" s="1" t="n">
+        <v>0.05297</v>
+      </c>
+      <c r="G555" s="1" t="n">
         <v>0.05319</v>
       </c>
-      <c r="G555" s="1" t="n">
+      <c r="H555" s="1" t="n">
         <v>0.05291</v>
       </c>
     </row>
@@ -14334,10 +16002,13 @@
         <v>0.0122</v>
       </c>
       <c r="F556" s="1" t="n">
+        <v>0.01219</v>
+      </c>
+      <c r="G556" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="G556" s="1" t="n">
-        <v>0.0122</v>
+      <c r="H556" s="1" t="n">
+        <v>0.01219</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H556"/>
+  <dimension ref="A1:I556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -425,8 +425,9 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,10 +463,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>price_01:15</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -493,9 +499,12 @@
         <v>71390.89999999999</v>
       </c>
       <c r="G2" s="1" t="n">
+        <v>71450</v>
+      </c>
+      <c r="H2" s="1" t="n">
         <v>71530</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="I2" s="1" t="n">
         <v>71364.39999999999</v>
       </c>
     </row>
@@ -521,9 +530,12 @@
         <v>2090.41</v>
       </c>
       <c r="G3" s="1" t="n">
+        <v>2093.92</v>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>2096.9</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="I3" s="1" t="n">
         <v>2090.41</v>
       </c>
     </row>
@@ -549,9 +561,12 @@
         <v>87.47</v>
       </c>
       <c r="G4" s="1" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="H4" s="1" t="n">
         <v>87.95</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>87.47</v>
       </c>
     </row>
@@ -577,10 +592,13 @@
         <v>23.329</v>
       </c>
       <c r="G5" s="1" t="n">
+        <v>23.043</v>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>23.579</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>23.329</v>
+      <c r="I5" s="1" t="n">
+        <v>23.043</v>
       </c>
     </row>
     <row r="6">
@@ -605,9 +623,12 @@
         <v>0.001878</v>
       </c>
       <c r="G6" s="1" t="n">
+        <v>0.001845</v>
+      </c>
+      <c r="H6" s="1" t="n">
         <v>0.001892</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>0.001827</v>
       </c>
     </row>
@@ -633,9 +654,12 @@
         <v>1.4117</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>1.4149</v>
+        <v>1.4151</v>
       </c>
       <c r="H7" s="1" t="n">
+        <v>1.4151</v>
+      </c>
+      <c r="I7" s="1" t="n">
         <v>1.4117</v>
       </c>
     </row>
@@ -661,10 +685,13 @@
         <v>0.010738</v>
       </c>
       <c r="G8" s="1" t="n">
+        <v>0.010599</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <v>0.011244</v>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>0.010738</v>
+      <c r="I8" s="1" t="n">
+        <v>0.010599</v>
       </c>
     </row>
     <row r="9">
@@ -689,9 +716,12 @@
         <v>4.062</v>
       </c>
       <c r="G9" s="1" t="n">
+        <v>4.034</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <v>4.062</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="I9" s="1" t="n">
         <v>3.954</v>
       </c>
     </row>
@@ -717,9 +747,12 @@
         <v>274.18</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>275.37</v>
+        <v>278.1</v>
       </c>
       <c r="H10" s="1" t="n">
+        <v>278.1</v>
+      </c>
+      <c r="I10" s="1" t="n">
         <v>272.11</v>
       </c>
     </row>
@@ -745,10 +778,13 @@
         <v>0.07854999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
+        <v>0.07833</v>
+      </c>
+      <c r="H11" s="1" t="n">
         <v>0.08047</v>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>0.07854999999999999</v>
+      <c r="I11" s="1" t="n">
+        <v>0.07833</v>
       </c>
     </row>
     <row r="12">
@@ -773,9 +809,12 @@
         <v>223.76</v>
       </c>
       <c r="G12" s="1" t="n">
+        <v>225.26</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <v>227.69</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="I12" s="1" t="n">
         <v>223.76</v>
       </c>
     </row>
@@ -801,9 +840,12 @@
         <v>0.0946</v>
       </c>
       <c r="G13" s="1" t="n">
+        <v>0.09495000000000001</v>
+      </c>
+      <c r="H13" s="1" t="n">
         <v>0.09497</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="I13" s="1" t="n">
         <v>0.0946</v>
       </c>
     </row>
@@ -829,9 +871,12 @@
         <v>37.089</v>
       </c>
       <c r="G14" s="1" t="n">
+        <v>37.208</v>
+      </c>
+      <c r="H14" s="1" t="n">
         <v>37.279</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="I14" s="1" t="n">
         <v>37.089</v>
       </c>
     </row>
@@ -857,9 +902,12 @@
         <v>0.09525</v>
       </c>
       <c r="G15" s="1" t="n">
+        <v>0.09467</v>
+      </c>
+      <c r="H15" s="1" t="n">
         <v>0.09845</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="I15" s="1" t="n">
         <v>0.09461</v>
       </c>
     </row>
@@ -885,9 +933,12 @@
         <v>0.2283</v>
       </c>
       <c r="G16" s="1" t="n">
+        <v>0.2282</v>
+      </c>
+      <c r="H16" s="1" t="n">
         <v>0.2339</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="I16" s="1" t="n">
         <v>0.2256</v>
       </c>
     </row>
@@ -913,10 +964,13 @@
         <v>0.011493</v>
       </c>
       <c r="G17" s="1" t="n">
+        <v>0.011379</v>
+      </c>
+      <c r="H17" s="1" t="n">
         <v>0.011542</v>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>0.011493</v>
+      <c r="I17" s="1" t="n">
+        <v>0.011379</v>
       </c>
     </row>
     <row r="18">
@@ -941,9 +995,12 @@
         <v>658.89</v>
       </c>
       <c r="G18" s="1" t="n">
+        <v>659.5700000000001</v>
+      </c>
+      <c r="H18" s="1" t="n">
         <v>660.72</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="I18" s="1" t="n">
         <v>658.89</v>
       </c>
     </row>
@@ -969,9 +1026,12 @@
         <v>0.0033271</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>0.0033451</v>
+        <v>0.0033454</v>
       </c>
       <c r="H19" s="1" t="n">
+        <v>0.0033454</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>0.0033271</v>
       </c>
     </row>
@@ -997,9 +1057,12 @@
         <v>0.17839</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.18017</v>
+        <v>0.18066</v>
       </c>
       <c r="H20" s="1" t="n">
+        <v>0.18066</v>
+      </c>
+      <c r="I20" s="1" t="n">
         <v>0.17675</v>
       </c>
     </row>
@@ -1025,9 +1088,12 @@
         <v>0.00996</v>
       </c>
       <c r="G21" s="1" t="n">
+        <v>0.009953</v>
+      </c>
+      <c r="H21" s="1" t="n">
         <v>0.010044</v>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="I21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -1053,9 +1119,12 @@
         <v>0.9985000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
+        <v>1.0008</v>
+      </c>
+      <c r="H22" s="1" t="n">
         <v>1.0033</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="I22" s="1" t="n">
         <v>0.9985000000000001</v>
       </c>
     </row>
@@ -1081,10 +1150,13 @@
         <v>5003.05</v>
       </c>
       <c r="G23" s="1" t="n">
+        <v>5002.67</v>
+      </c>
+      <c r="H23" s="1" t="n">
         <v>5012.25</v>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>5003.05</v>
+      <c r="I23" s="1" t="n">
+        <v>5002.67</v>
       </c>
     </row>
     <row r="24">
@@ -1109,9 +1181,12 @@
         <v>0.2625</v>
       </c>
       <c r="G24" s="1" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="H24" s="1" t="n">
         <v>0.2643</v>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="I24" s="1" t="n">
         <v>0.2625</v>
       </c>
     </row>
@@ -1137,9 +1212,12 @@
         <v>2.924</v>
       </c>
       <c r="G25" s="1" t="n">
+        <v>2.914</v>
+      </c>
+      <c r="H25" s="1" t="n">
         <v>2.924</v>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="I25" s="1" t="n">
         <v>2.899</v>
       </c>
     </row>
@@ -1165,9 +1243,12 @@
         <v>0.4022</v>
       </c>
       <c r="G26" s="1" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="H26" s="1" t="n">
         <v>0.4096</v>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="I26" s="1" t="n">
         <v>0.3959</v>
       </c>
     </row>
@@ -1193,9 +1274,12 @@
         <v>0.881</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
       <c r="H27" s="1" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="I27" s="1" t="n">
         <v>0.881</v>
       </c>
     </row>
@@ -1224,6 +1308,9 @@
         <v>1.343</v>
       </c>
       <c r="H28" s="1" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="I28" s="1" t="n">
         <v>1.335</v>
       </c>
     </row>
@@ -1249,9 +1336,12 @@
         <v>9.131</v>
       </c>
       <c r="G29" s="1" t="n">
+        <v>9.154</v>
+      </c>
+      <c r="H29" s="1" t="n">
         <v>9.179</v>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="I29" s="1" t="n">
         <v>9.131</v>
       </c>
     </row>
@@ -1277,9 +1367,12 @@
         <v>461.24</v>
       </c>
       <c r="G30" s="1" t="n">
+        <v>461.65</v>
+      </c>
+      <c r="H30" s="1" t="n">
         <v>463.35</v>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="I30" s="1" t="n">
         <v>461.24</v>
       </c>
     </row>
@@ -1305,9 +1398,12 @@
         <v>9.699</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>9.728999999999999</v>
+        <v>9.731</v>
       </c>
       <c r="H31" s="1" t="n">
+        <v>9.731</v>
+      </c>
+      <c r="I31" s="1" t="n">
         <v>9.696999999999999</v>
       </c>
     </row>
@@ -1333,9 +1429,12 @@
         <v>0.36159</v>
       </c>
       <c r="G32" s="1" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="H32" s="1" t="n">
         <v>0.36683</v>
       </c>
-      <c r="H32" s="1" t="n">
+      <c r="I32" s="1" t="n">
         <v>0.36159</v>
       </c>
     </row>
@@ -1361,9 +1460,12 @@
         <v>1.409</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>1.419</v>
+        <v>1.421</v>
       </c>
       <c r="H33" s="1" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="I33" s="1" t="n">
         <v>1.409</v>
       </c>
     </row>
@@ -1389,9 +1491,12 @@
         <v>0.59383</v>
       </c>
       <c r="G34" s="1" t="n">
+        <v>0.59314</v>
+      </c>
+      <c r="H34" s="1" t="n">
         <v>0.59693</v>
       </c>
-      <c r="H34" s="1" t="n">
+      <c r="I34" s="1" t="n">
         <v>0.5926900000000001</v>
       </c>
     </row>
@@ -1417,9 +1522,12 @@
         <v>1.2236</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>1.2236</v>
+        <v>1.2283</v>
       </c>
       <c r="H35" s="1" t="n">
+        <v>1.2283</v>
+      </c>
+      <c r="I35" s="1" t="n">
         <v>1.2186</v>
       </c>
     </row>
@@ -1445,9 +1553,12 @@
         <v>80.31</v>
       </c>
       <c r="G36" s="1" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="H36" s="1" t="n">
         <v>80.5</v>
       </c>
-      <c r="H36" s="1" t="n">
+      <c r="I36" s="1" t="n">
         <v>80.27</v>
       </c>
     </row>
@@ -1473,9 +1584,12 @@
         <v>0.199</v>
       </c>
       <c r="G37" s="1" t="n">
+        <v>0.1993</v>
+      </c>
+      <c r="H37" s="1" t="n">
         <v>0.204</v>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="I37" s="1" t="n">
         <v>0.1977</v>
       </c>
     </row>
@@ -1501,9 +1615,12 @@
         <v>1.847</v>
       </c>
       <c r="G38" s="1" t="n">
+        <v>1.851</v>
+      </c>
+      <c r="H38" s="1" t="n">
         <v>1.865</v>
       </c>
-      <c r="H38" s="1" t="n">
+      <c r="I38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -1529,9 +1646,12 @@
         <v>0.3338</v>
       </c>
       <c r="G39" s="1" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="H39" s="1" t="n">
         <v>0.3338</v>
       </c>
-      <c r="H39" s="1" t="n">
+      <c r="I39" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -1557,9 +1677,12 @@
         <v>0.9011</v>
       </c>
       <c r="G40" s="1" t="n">
+        <v>0.8993</v>
+      </c>
+      <c r="H40" s="1" t="n">
         <v>0.9115</v>
       </c>
-      <c r="H40" s="1" t="n">
+      <c r="I40" s="1" t="n">
         <v>0.899</v>
       </c>
     </row>
@@ -1585,10 +1708,13 @@
         <v>0.7131</v>
       </c>
       <c r="G41" s="1" t="n">
+        <v>0.7122000000000001</v>
+      </c>
+      <c r="H41" s="1" t="n">
         <v>0.7149</v>
       </c>
-      <c r="H41" s="1" t="n">
-        <v>0.7131</v>
+      <c r="I41" s="1" t="n">
+        <v>0.7122000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1613,10 +1739,13 @@
         <v>0.06622</v>
       </c>
       <c r="G42" s="1" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="H42" s="1" t="n">
         <v>0.06769</v>
       </c>
-      <c r="H42" s="1" t="n">
-        <v>0.06622</v>
+      <c r="I42" s="1" t="n">
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1641,9 +1770,12 @@
         <v>113.2</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>113.57</v>
+        <v>113.86</v>
       </c>
       <c r="H43" s="1" t="n">
+        <v>113.86</v>
+      </c>
+      <c r="I43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -1669,10 +1801,13 @@
         <v>0.6584</v>
       </c>
       <c r="G44" s="1" t="n">
+        <v>0.6562</v>
+      </c>
+      <c r="H44" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="H44" s="1" t="n">
-        <v>0.6578000000000001</v>
+      <c r="I44" s="1" t="n">
+        <v>0.6562</v>
       </c>
     </row>
     <row r="45">
@@ -1697,9 +1832,12 @@
         <v>1.218</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>1.218</v>
+        <v>1.22</v>
       </c>
       <c r="H45" s="1" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -1725,9 +1863,12 @@
         <v>0.02377</v>
       </c>
       <c r="G46" s="1" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="H46" s="1" t="n">
         <v>0.02392</v>
       </c>
-      <c r="H46" s="1" t="n">
+      <c r="I46" s="1" t="n">
         <v>0.02376</v>
       </c>
     </row>
@@ -1753,9 +1894,12 @@
         <v>54.99</v>
       </c>
       <c r="G47" s="1" t="n">
+        <v>55.05</v>
+      </c>
+      <c r="H47" s="1" t="n">
         <v>55.17</v>
       </c>
-      <c r="H47" s="1" t="n">
+      <c r="I47" s="1" t="n">
         <v>54.99</v>
       </c>
     </row>
@@ -1781,9 +1925,12 @@
         <v>0.06032</v>
       </c>
       <c r="G48" s="1" t="n">
+        <v>0.06068</v>
+      </c>
+      <c r="H48" s="1" t="n">
         <v>0.06081</v>
       </c>
-      <c r="H48" s="1" t="n">
+      <c r="I48" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -1809,9 +1956,12 @@
         <v>0.1076</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.1082</v>
+        <v>0.1083</v>
       </c>
       <c r="H49" s="1" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="I49" s="1" t="n">
         <v>0.1076</v>
       </c>
     </row>
@@ -1837,9 +1987,12 @@
         <v>0.01806</v>
       </c>
       <c r="G50" s="1" t="n">
+        <v>0.01804</v>
+      </c>
+      <c r="H50" s="1" t="n">
         <v>0.01815</v>
       </c>
-      <c r="H50" s="1" t="n">
+      <c r="I50" s="1" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -1865,9 +2018,12 @@
         <v>1.4646</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>1.4659</v>
+        <v>1.4679</v>
       </c>
       <c r="H51" s="1" t="n">
+        <v>1.4679</v>
+      </c>
+      <c r="I51" s="1" t="n">
         <v>1.4618</v>
       </c>
     </row>
@@ -1893,9 +2049,12 @@
         <v>0.3581</v>
       </c>
       <c r="G52" s="1" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="H52" s="1" t="n">
         <v>0.3603</v>
       </c>
-      <c r="H52" s="1" t="n">
+      <c r="I52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -1921,9 +2080,12 @@
         <v>0.001942</v>
       </c>
       <c r="G53" s="1" t="n">
+        <v>0.001946</v>
+      </c>
+      <c r="H53" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="H53" s="1" t="n">
+      <c r="I53" s="1" t="n">
         <v>0.001942</v>
       </c>
     </row>
@@ -1949,9 +2111,12 @@
         <v>0.09514</v>
       </c>
       <c r="G54" s="1" t="n">
+        <v>0.09551999999999999</v>
+      </c>
+      <c r="H54" s="1" t="n">
         <v>0.09569</v>
       </c>
-      <c r="H54" s="1" t="n">
+      <c r="I54" s="1" t="n">
         <v>0.09514</v>
       </c>
     </row>
@@ -1977,9 +2142,12 @@
         <v>0.04087</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.04087</v>
+        <v>0.04097</v>
       </c>
       <c r="H55" s="1" t="n">
+        <v>0.04097</v>
+      </c>
+      <c r="I55" s="1" t="n">
         <v>0.04003</v>
       </c>
     </row>
@@ -2005,9 +2173,12 @@
         <v>0.29832</v>
       </c>
       <c r="G56" s="1" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="H56" s="1" t="n">
         <v>0.29861</v>
       </c>
-      <c r="H56" s="1" t="n">
+      <c r="I56" s="1" t="n">
         <v>0.29831</v>
       </c>
     </row>
@@ -2033,10 +2204,13 @@
         <v>0.005716</v>
       </c>
       <c r="G57" s="1" t="n">
+        <v>0.005633</v>
+      </c>
+      <c r="H57" s="1" t="n">
         <v>0.005824</v>
       </c>
-      <c r="H57" s="1" t="n">
-        <v>0.005716</v>
+      <c r="I57" s="1" t="n">
+        <v>0.005633</v>
       </c>
     </row>
     <row r="58">
@@ -2061,10 +2235,13 @@
         <v>4989.99</v>
       </c>
       <c r="G58" s="1" t="n">
+        <v>4988.64</v>
+      </c>
+      <c r="H58" s="1" t="n">
         <v>4998.37</v>
       </c>
-      <c r="H58" s="1" t="n">
-        <v>4989.99</v>
+      <c r="I58" s="1" t="n">
+        <v>4988.64</v>
       </c>
     </row>
     <row r="59">
@@ -2089,9 +2266,12 @@
         <v>0.4137</v>
       </c>
       <c r="G59" s="1" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="H59" s="1" t="n">
         <v>0.4246</v>
       </c>
-      <c r="H59" s="1" t="n">
+      <c r="I59" s="1" t="n">
         <v>0.4126</v>
       </c>
     </row>
@@ -2117,9 +2297,12 @@
         <v>0.0465</v>
       </c>
       <c r="G60" s="1" t="n">
+        <v>0.04653</v>
+      </c>
+      <c r="H60" s="1" t="n">
         <v>0.04683</v>
       </c>
-      <c r="H60" s="1" t="n">
+      <c r="I60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -2145,10 +2328,13 @@
         <v>0.21432</v>
       </c>
       <c r="G61" s="1" t="n">
+        <v>0.21344</v>
+      </c>
+      <c r="H61" s="1" t="n">
         <v>0.21708</v>
       </c>
-      <c r="H61" s="1" t="n">
-        <v>0.21432</v>
+      <c r="I61" s="1" t="n">
+        <v>0.21344</v>
       </c>
     </row>
     <row r="62">
@@ -2173,9 +2359,12 @@
         <v>0.1067</v>
       </c>
       <c r="G62" s="1" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="H62" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="H62" s="1" t="n">
+      <c r="I62" s="1" t="n">
         <v>0.1065</v>
       </c>
     </row>
@@ -2201,9 +2390,12 @@
         <v>0.7255</v>
       </c>
       <c r="G63" s="1" t="n">
+        <v>0.7299</v>
+      </c>
+      <c r="H63" s="1" t="n">
         <v>0.7301</v>
       </c>
-      <c r="H63" s="1" t="n">
+      <c r="I63" s="1" t="n">
         <v>0.7255</v>
       </c>
     </row>
@@ -2229,9 +2421,12 @@
         <v>0.1658</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>0.1667</v>
+        <v>0.1668</v>
       </c>
       <c r="H64" s="1" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="I64" s="1" t="n">
         <v>0.1658</v>
       </c>
     </row>
@@ -2257,9 +2452,12 @@
         <v>2.651</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>2.661</v>
+        <v>2.665</v>
       </c>
       <c r="H65" s="1" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="I65" s="1" t="n">
         <v>2.65</v>
       </c>
     </row>
@@ -2285,9 +2483,12 @@
         <v>0.04056</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>0.04056</v>
+        <v>0.04072</v>
       </c>
       <c r="H66" s="1" t="n">
+        <v>0.04072</v>
+      </c>
+      <c r="I66" s="1" t="n">
         <v>0.04018</v>
       </c>
     </row>
@@ -2313,9 +2514,12 @@
         <v>0.04261</v>
       </c>
       <c r="G67" s="1" t="n">
+        <v>0.04243</v>
+      </c>
+      <c r="H67" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="H67" s="1" t="n">
+      <c r="I67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -2341,9 +2545,12 @@
         <v>3.951</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>3.967</v>
+        <v>3.971</v>
       </c>
       <c r="H68" s="1" t="n">
+        <v>3.971</v>
+      </c>
+      <c r="I68" s="1" t="n">
         <v>3.951</v>
       </c>
     </row>
@@ -2372,6 +2579,9 @@
         <v>0.1261</v>
       </c>
       <c r="H69" s="1" t="n">
+        <v>0.1261</v>
+      </c>
+      <c r="I69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -2397,9 +2607,12 @@
         <v>6.307</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>6.307</v>
+        <v>6.328</v>
       </c>
       <c r="H70" s="1" t="n">
+        <v>6.328</v>
+      </c>
+      <c r="I70" s="1" t="n">
         <v>6.114</v>
       </c>
     </row>
@@ -2425,9 +2638,12 @@
         <v>0.04959</v>
       </c>
       <c r="G71" s="1" t="n">
+        <v>0.04966</v>
+      </c>
+      <c r="H71" s="1" t="n">
         <v>0.04999</v>
       </c>
-      <c r="H71" s="1" t="n">
+      <c r="I71" s="1" t="n">
         <v>0.04959</v>
       </c>
     </row>
@@ -2453,9 +2669,12 @@
         <v>0.004148</v>
       </c>
       <c r="G72" s="1" t="n">
+        <v>0.004142</v>
+      </c>
+      <c r="H72" s="1" t="n">
         <v>0.004181</v>
       </c>
-      <c r="H72" s="1" t="n">
+      <c r="I72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -2481,9 +2700,12 @@
         <v>5.96</v>
       </c>
       <c r="G73" s="1" t="n">
+        <v>5.985</v>
+      </c>
+      <c r="H73" s="1" t="n">
         <v>6.029</v>
       </c>
-      <c r="H73" s="1" t="n">
+      <c r="I73" s="1" t="n">
         <v>5.96</v>
       </c>
     </row>
@@ -2509,9 +2731,12 @@
         <v>0.1619</v>
       </c>
       <c r="G74" s="1" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="H74" s="1" t="n">
         <v>0.1633</v>
       </c>
-      <c r="H74" s="1" t="n">
+      <c r="I74" s="1" t="n">
         <v>0.1619</v>
       </c>
     </row>
@@ -2537,9 +2762,12 @@
         <v>0.007261</v>
       </c>
       <c r="G75" s="1" t="n">
+        <v>0.007287</v>
+      </c>
+      <c r="H75" s="1" t="n">
         <v>0.007297</v>
       </c>
-      <c r="H75" s="1" t="n">
+      <c r="I75" s="1" t="n">
         <v>0.007261</v>
       </c>
     </row>
@@ -2565,9 +2793,12 @@
         <v>0.2092</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>0.2102</v>
+        <v>0.2128</v>
       </c>
       <c r="H76" s="1" t="n">
+        <v>0.2128</v>
+      </c>
+      <c r="I76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -2593,9 +2824,12 @@
         <v>0.005796</v>
       </c>
       <c r="G77" s="1" t="n">
+        <v>0.005818</v>
+      </c>
+      <c r="H77" s="1" t="n">
         <v>0.005826</v>
       </c>
-      <c r="H77" s="1" t="n">
+      <c r="I77" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -2621,9 +2855,12 @@
         <v>0.1013</v>
       </c>
       <c r="G78" s="1" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="H78" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="H78" s="1" t="n">
+      <c r="I78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -2649,9 +2886,12 @@
         <v>0.006237</v>
       </c>
       <c r="G79" s="1" t="n">
+        <v>0.006265</v>
+      </c>
+      <c r="H79" s="1" t="n">
         <v>0.006292</v>
       </c>
-      <c r="H79" s="1" t="n">
+      <c r="I79" s="1" t="n">
         <v>0.006237</v>
       </c>
     </row>
@@ -2680,6 +2920,9 @@
         <v>33.51</v>
       </c>
       <c r="H80" s="1" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="I80" s="1" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -2705,9 +2948,12 @@
         <v>0.04038</v>
       </c>
       <c r="G81" s="1" t="n">
+        <v>0.04041</v>
+      </c>
+      <c r="H81" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="H81" s="1" t="n">
+      <c r="I81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -2733,9 +2979,12 @@
         <v>0.16679</v>
       </c>
       <c r="G82" s="1" t="n">
+        <v>0.16723</v>
+      </c>
+      <c r="H82" s="1" t="n">
         <v>0.1675</v>
       </c>
-      <c r="H82" s="1" t="n">
+      <c r="I82" s="1" t="n">
         <v>0.16679</v>
       </c>
     </row>
@@ -2761,9 +3010,12 @@
         <v>0.1033</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>0.1035</v>
+        <v>0.1037</v>
       </c>
       <c r="H83" s="1" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="I83" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -2789,9 +3041,12 @@
         <v>0.08803999999999999</v>
       </c>
       <c r="G84" s="1" t="n">
+        <v>0.08825</v>
+      </c>
+      <c r="H84" s="1" t="n">
         <v>0.08848</v>
       </c>
-      <c r="H84" s="1" t="n">
+      <c r="I84" s="1" t="n">
         <v>0.08803999999999999</v>
       </c>
     </row>
@@ -2817,9 +3072,12 @@
         <v>0.02311</v>
       </c>
       <c r="G85" s="1" t="n">
+        <v>0.02317</v>
+      </c>
+      <c r="H85" s="1" t="n">
         <v>0.02331</v>
       </c>
-      <c r="H85" s="1" t="n">
+      <c r="I85" s="1" t="n">
         <v>0.02311</v>
       </c>
     </row>
@@ -2845,9 +3103,12 @@
         <v>0.238</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>0.239</v>
+        <v>0.24</v>
       </c>
       <c r="H86" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -2873,9 +3134,12 @@
         <v>356.11</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>357.4</v>
+        <v>357.71</v>
       </c>
       <c r="H87" s="1" t="n">
+        <v>357.71</v>
+      </c>
+      <c r="I87" s="1" t="n">
         <v>355.75</v>
       </c>
     </row>
@@ -2901,9 +3165,12 @@
         <v>0.00344</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>0.00345</v>
+        <v>0.00347</v>
       </c>
       <c r="H88" s="1" t="n">
+        <v>0.00347</v>
+      </c>
+      <c r="I88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -2929,9 +3196,12 @@
         <v>8.257</v>
       </c>
       <c r="G89" s="1" t="n">
+        <v>8.278</v>
+      </c>
+      <c r="H89" s="1" t="n">
         <v>8.301</v>
       </c>
-      <c r="H89" s="1" t="n">
+      <c r="I89" s="1" t="n">
         <v>8.257</v>
       </c>
     </row>
@@ -2957,9 +3227,12 @@
         <v>0.005905</v>
       </c>
       <c r="G90" s="1" t="n">
+        <v>0.005915</v>
+      </c>
+      <c r="H90" s="1" t="n">
         <v>0.005945</v>
       </c>
-      <c r="H90" s="1" t="n">
+      <c r="I90" s="1" t="n">
         <v>0.005905</v>
       </c>
     </row>
@@ -2985,10 +3258,13 @@
         <v>0.06837</v>
       </c>
       <c r="G91" s="1" t="n">
+        <v>0.06822</v>
+      </c>
+      <c r="H91" s="1" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="H91" s="1" t="n">
-        <v>0.06837</v>
+      <c r="I91" s="1" t="n">
+        <v>0.06822</v>
       </c>
     </row>
     <row r="92">
@@ -3013,9 +3289,12 @@
         <v>0.02885</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>0.02894</v>
+        <v>0.02897</v>
       </c>
       <c r="H92" s="1" t="n">
+        <v>0.02897</v>
+      </c>
+      <c r="I92" s="1" t="n">
         <v>0.02869</v>
       </c>
     </row>
@@ -3041,9 +3320,12 @@
         <v>5.169</v>
       </c>
       <c r="G93" s="1" t="n">
+        <v>5.195</v>
+      </c>
+      <c r="H93" s="1" t="n">
         <v>5.202</v>
       </c>
-      <c r="H93" s="1" t="n">
+      <c r="I93" s="1" t="n">
         <v>5.159</v>
       </c>
     </row>
@@ -3072,6 +3354,9 @@
         <v>0.000228</v>
       </c>
       <c r="H94" s="1" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="I94" s="1" t="n">
         <v>0.000226</v>
       </c>
     </row>
@@ -3097,9 +3382,12 @@
         <v>0.9195</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>0.9241</v>
+        <v>0.9248</v>
       </c>
       <c r="H95" s="1" t="n">
+        <v>0.9248</v>
+      </c>
+      <c r="I95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -3125,9 +3413,12 @@
         <v>2.0731</v>
       </c>
       <c r="G96" s="1" t="n">
-        <v>2.0774</v>
+        <v>2.0874</v>
       </c>
       <c r="H96" s="1" t="n">
+        <v>2.0874</v>
+      </c>
+      <c r="I96" s="1" t="n">
         <v>2.0598</v>
       </c>
     </row>
@@ -3153,9 +3444,12 @@
         <v>0.3722</v>
       </c>
       <c r="G97" s="1" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="H97" s="1" t="n">
         <v>0.3722</v>
       </c>
-      <c r="H97" s="1" t="n">
+      <c r="I97" s="1" t="n">
         <v>0.3686</v>
       </c>
     </row>
@@ -3181,9 +3475,12 @@
         <v>1.614</v>
       </c>
       <c r="G98" s="1" t="n">
-        <v>1.618</v>
+        <v>1.621</v>
       </c>
       <c r="H98" s="1" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="I98" s="1" t="n">
         <v>1.613</v>
       </c>
     </row>
@@ -3209,10 +3506,13 @@
         <v>0.2353</v>
       </c>
       <c r="G99" s="1" t="n">
+        <v>0.2342</v>
+      </c>
+      <c r="H99" s="1" t="n">
         <v>0.2368</v>
       </c>
-      <c r="H99" s="1" t="n">
-        <v>0.2351</v>
+      <c r="I99" s="1" t="n">
+        <v>0.2342</v>
       </c>
     </row>
     <row r="100">
@@ -3237,9 +3537,12 @@
         <v>0.13549</v>
       </c>
       <c r="G100" s="1" t="n">
-        <v>0.13665</v>
+        <v>0.13683</v>
       </c>
       <c r="H100" s="1" t="n">
+        <v>0.13683</v>
+      </c>
+      <c r="I100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -3265,9 +3568,12 @@
         <v>0.07045</v>
       </c>
       <c r="G101" s="1" t="n">
+        <v>0.07051</v>
+      </c>
+      <c r="H101" s="1" t="n">
         <v>0.07115</v>
       </c>
-      <c r="H101" s="1" t="n">
+      <c r="I101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -3293,9 +3599,12 @@
         <v>0.0010832</v>
       </c>
       <c r="G102" s="1" t="n">
+        <v>0.0010855</v>
+      </c>
+      <c r="H102" s="1" t="n">
         <v>0.0010875</v>
       </c>
-      <c r="H102" s="1" t="n">
+      <c r="I102" s="1" t="n">
         <v>0.0010832</v>
       </c>
     </row>
@@ -3321,9 +3630,12 @@
         <v>0.003403</v>
       </c>
       <c r="G103" s="1" t="n">
+        <v>0.003403</v>
+      </c>
+      <c r="H103" s="1" t="n">
         <v>0.003424</v>
       </c>
-      <c r="H103" s="1" t="n">
+      <c r="I103" s="1" t="n">
         <v>0.003403</v>
       </c>
     </row>
@@ -3349,10 +3661,13 @@
         <v>0.27534</v>
       </c>
       <c r="G104" s="1" t="n">
+        <v>0.27472</v>
+      </c>
+      <c r="H104" s="1" t="n">
         <v>0.27751</v>
       </c>
-      <c r="H104" s="1" t="n">
-        <v>0.27534</v>
+      <c r="I104" s="1" t="n">
+        <v>0.27472</v>
       </c>
     </row>
     <row r="105">
@@ -3380,6 +3695,9 @@
         <v>0.01257</v>
       </c>
       <c r="H105" s="1" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="I105" s="1" t="n">
         <v>0.01243</v>
       </c>
     </row>
@@ -3405,9 +3723,12 @@
         <v>0.13453</v>
       </c>
       <c r="G106" s="1" t="n">
+        <v>0.13537</v>
+      </c>
+      <c r="H106" s="1" t="n">
         <v>0.13569</v>
       </c>
-      <c r="H106" s="1" t="n">
+      <c r="I106" s="1" t="n">
         <v>0.13329</v>
       </c>
     </row>
@@ -3433,9 +3754,12 @@
         <v>0.3484</v>
       </c>
       <c r="G107" s="1" t="n">
-        <v>0.3496</v>
+        <v>0.3508</v>
       </c>
       <c r="H107" s="1" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -3461,9 +3785,12 @@
         <v>0.1426</v>
       </c>
       <c r="G108" s="1" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="H108" s="1" t="n">
         <v>0.1436</v>
       </c>
-      <c r="H108" s="1" t="n">
+      <c r="I108" s="1" t="n">
         <v>0.1426</v>
       </c>
     </row>
@@ -3492,6 +3819,9 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="H109" s="1" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="I109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -3517,9 +3847,12 @@
         <v>0.016195</v>
       </c>
       <c r="G110" s="1" t="n">
+        <v>0.016241</v>
+      </c>
+      <c r="H110" s="1" t="n">
         <v>0.016308</v>
       </c>
-      <c r="H110" s="1" t="n">
+      <c r="I110" s="1" t="n">
         <v>0.016195</v>
       </c>
     </row>
@@ -3545,9 +3878,12 @@
         <v>0.038</v>
       </c>
       <c r="G111" s="1" t="n">
+        <v>0.03818</v>
+      </c>
+      <c r="H111" s="1" t="n">
         <v>0.038335</v>
       </c>
-      <c r="H111" s="1" t="n">
+      <c r="I111" s="1" t="n">
         <v>0.03774</v>
       </c>
     </row>
@@ -3573,9 +3909,12 @@
         <v>0.11991</v>
       </c>
       <c r="G112" s="1" t="n">
+        <v>0.12008</v>
+      </c>
+      <c r="H112" s="1" t="n">
         <v>0.12031</v>
       </c>
-      <c r="H112" s="1" t="n">
+      <c r="I112" s="1" t="n">
         <v>0.11926</v>
       </c>
     </row>
@@ -3601,9 +3940,12 @@
         <v>0.09555</v>
       </c>
       <c r="G113" s="1" t="n">
-        <v>0.09555</v>
+        <v>0.09574000000000001</v>
       </c>
       <c r="H113" s="1" t="n">
+        <v>0.09574000000000001</v>
+      </c>
+      <c r="I113" s="1" t="n">
         <v>0.09426</v>
       </c>
     </row>
@@ -3629,9 +3971,12 @@
         <v>0.13002</v>
       </c>
       <c r="G114" s="1" t="n">
-        <v>0.13002</v>
+        <v>0.13063</v>
       </c>
       <c r="H114" s="1" t="n">
+        <v>0.13063</v>
+      </c>
+      <c r="I114" s="1" t="n">
         <v>0.12895</v>
       </c>
     </row>
@@ -3657,9 +4002,12 @@
         <v>0.2638</v>
       </c>
       <c r="G115" s="1" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="H115" s="1" t="n">
         <v>0.2656</v>
       </c>
-      <c r="H115" s="1" t="n">
+      <c r="I115" s="1" t="n">
         <v>0.2638</v>
       </c>
     </row>
@@ -3685,9 +4033,12 @@
         <v>0.04891</v>
       </c>
       <c r="G116" s="1" t="n">
+        <v>0.04911</v>
+      </c>
+      <c r="H116" s="1" t="n">
         <v>0.0529</v>
       </c>
-      <c r="H116" s="1" t="n">
+      <c r="I116" s="1" t="n">
         <v>0.04891</v>
       </c>
     </row>
@@ -3713,9 +4064,12 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="G117" s="1" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="H117" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="H117" s="1" t="n">
+      <c r="I117" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -3741,10 +4095,13 @@
         <v>0.05517</v>
       </c>
       <c r="G118" s="1" t="n">
+        <v>0.05501</v>
+      </c>
+      <c r="H118" s="1" t="n">
         <v>0.05563</v>
       </c>
-      <c r="H118" s="1" t="n">
-        <v>0.05509</v>
+      <c r="I118" s="1" t="n">
+        <v>0.05501</v>
       </c>
     </row>
     <row r="119">
@@ -3769,9 +4126,12 @@
         <v>0.01505</v>
       </c>
       <c r="G119" s="1" t="n">
+        <v>0.01507</v>
+      </c>
+      <c r="H119" s="1" t="n">
         <v>0.01515</v>
       </c>
-      <c r="H119" s="1" t="n">
+      <c r="I119" s="1" t="n">
         <v>0.01505</v>
       </c>
     </row>
@@ -3797,9 +4157,12 @@
         <v>3.051</v>
       </c>
       <c r="G120" s="1" t="n">
-        <v>3.06</v>
+        <v>3.062</v>
       </c>
       <c r="H120" s="1" t="n">
+        <v>3.062</v>
+      </c>
+      <c r="I120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -3825,9 +4188,12 @@
         <v>1.849</v>
       </c>
       <c r="G121" s="1" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H121" s="1" t="n">
         <v>1.855</v>
       </c>
-      <c r="H121" s="1" t="n">
+      <c r="I121" s="1" t="n">
         <v>1.849</v>
       </c>
     </row>
@@ -3853,9 +4219,12 @@
         <v>1.2942</v>
       </c>
       <c r="G122" s="1" t="n">
-        <v>1.2965</v>
+        <v>1.2991</v>
       </c>
       <c r="H122" s="1" t="n">
+        <v>1.2991</v>
+      </c>
+      <c r="I122" s="1" t="n">
         <v>1.2934</v>
       </c>
     </row>
@@ -3881,9 +4250,12 @@
         <v>0.316</v>
       </c>
       <c r="G123" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="H123" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="H123" s="1" t="n">
+      <c r="I123" s="1" t="n">
         <v>0.316</v>
       </c>
     </row>
@@ -3909,10 +4281,13 @@
         <v>0.12344</v>
       </c>
       <c r="G124" s="1" t="n">
+        <v>0.12202</v>
+      </c>
+      <c r="H124" s="1" t="n">
         <v>0.12506</v>
       </c>
-      <c r="H124" s="1" t="n">
-        <v>0.12242</v>
+      <c r="I124" s="1" t="n">
+        <v>0.12202</v>
       </c>
     </row>
     <row r="125">
@@ -3937,9 +4312,12 @@
         <v>0.008304000000000001</v>
       </c>
       <c r="G125" s="1" t="n">
+        <v>0.008389000000000001</v>
+      </c>
+      <c r="H125" s="1" t="n">
         <v>0.008459</v>
       </c>
-      <c r="H125" s="1" t="n">
+      <c r="I125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -3965,9 +4343,12 @@
         <v>0.01586</v>
       </c>
       <c r="G126" s="1" t="n">
-        <v>0.01587</v>
+        <v>0.01599</v>
       </c>
       <c r="H126" s="1" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="I126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -3993,9 +4374,12 @@
         <v>0.04448</v>
       </c>
       <c r="G127" s="1" t="n">
+        <v>0.04436</v>
+      </c>
+      <c r="H127" s="1" t="n">
         <v>0.04468</v>
       </c>
-      <c r="H127" s="1" t="n">
+      <c r="I127" s="1" t="n">
         <v>0.04402</v>
       </c>
     </row>
@@ -4021,9 +4405,12 @@
         <v>0.04706</v>
       </c>
       <c r="G128" s="1" t="n">
-        <v>0.04706</v>
+        <v>0.04717</v>
       </c>
       <c r="H128" s="1" t="n">
+        <v>0.04717</v>
+      </c>
+      <c r="I128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -4049,10 +4436,13 @@
         <v>0.09585</v>
       </c>
       <c r="G129" s="1" t="n">
+        <v>0.09543</v>
+      </c>
+      <c r="H129" s="1" t="n">
         <v>0.09635000000000001</v>
       </c>
-      <c r="H129" s="1" t="n">
-        <v>0.09544999999999999</v>
+      <c r="I129" s="1" t="n">
+        <v>0.09543</v>
       </c>
     </row>
     <row r="130">
@@ -4077,9 +4467,12 @@
         <v>0.09902</v>
       </c>
       <c r="G130" s="1" t="n">
+        <v>0.09891</v>
+      </c>
+      <c r="H130" s="1" t="n">
         <v>0.09927</v>
       </c>
-      <c r="H130" s="1" t="n">
+      <c r="I130" s="1" t="n">
         <v>0.09877</v>
       </c>
     </row>
@@ -4105,9 +4498,12 @@
         <v>0.1652</v>
       </c>
       <c r="G131" s="1" t="n">
-        <v>0.16577</v>
+        <v>0.16612</v>
       </c>
       <c r="H131" s="1" t="n">
+        <v>0.16612</v>
+      </c>
+      <c r="I131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -4133,9 +4529,12 @@
         <v>0.01696</v>
       </c>
       <c r="G132" s="1" t="n">
-        <v>0.01696</v>
+        <v>0.01702</v>
       </c>
       <c r="H132" s="1" t="n">
+        <v>0.01702</v>
+      </c>
+      <c r="I132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -4161,9 +4560,12 @@
         <v>0.06645</v>
       </c>
       <c r="G133" s="1" t="n">
-        <v>0.06655</v>
+        <v>0.06671000000000001</v>
       </c>
       <c r="H133" s="1" t="n">
+        <v>0.06671000000000001</v>
+      </c>
+      <c r="I133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -4189,9 +4591,12 @@
         <v>0.3012</v>
       </c>
       <c r="G134" s="1" t="n">
-        <v>0.3023</v>
+        <v>0.3025</v>
       </c>
       <c r="H134" s="1" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="I134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -4217,9 +4622,12 @@
         <v>0.04518</v>
       </c>
       <c r="G135" s="1" t="n">
-        <v>0.04518</v>
+        <v>0.0452</v>
       </c>
       <c r="H135" s="1" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="I135" s="1" t="n">
         <v>0.04508</v>
       </c>
     </row>
@@ -4245,9 +4653,12 @@
         <v>0.782</v>
       </c>
       <c r="G136" s="1" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="H136" s="1" t="n">
         <v>0.783</v>
       </c>
-      <c r="H136" s="1" t="n">
+      <c r="I136" s="1" t="n">
         <v>0.781</v>
       </c>
     </row>
@@ -4273,9 +4684,12 @@
         <v>0.1165</v>
       </c>
       <c r="G137" s="1" t="n">
+        <v>0.1167</v>
+      </c>
+      <c r="H137" s="1" t="n">
         <v>0.1168</v>
       </c>
-      <c r="H137" s="1" t="n">
+      <c r="I137" s="1" t="n">
         <v>0.1162</v>
       </c>
     </row>
@@ -4301,9 +4715,12 @@
         <v>0.14685</v>
       </c>
       <c r="G138" s="1" t="n">
-        <v>0.14685</v>
+        <v>0.14729</v>
       </c>
       <c r="H138" s="1" t="n">
+        <v>0.14729</v>
+      </c>
+      <c r="I138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -4329,9 +4746,12 @@
         <v>0.05727</v>
       </c>
       <c r="G139" s="1" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="H139" s="1" t="n">
         <v>0.05727</v>
       </c>
-      <c r="H139" s="1" t="n">
+      <c r="I139" s="1" t="n">
         <v>0.05699</v>
       </c>
     </row>
@@ -4357,9 +4777,12 @@
         <v>0.007267</v>
       </c>
       <c r="G140" s="1" t="n">
+        <v>0.007283</v>
+      </c>
+      <c r="H140" s="1" t="n">
         <v>0.007295</v>
       </c>
-      <c r="H140" s="1" t="n">
+      <c r="I140" s="1" t="n">
         <v>0.007267</v>
       </c>
     </row>
@@ -4385,9 +4808,12 @@
         <v>0.09572</v>
       </c>
       <c r="G141" s="1" t="n">
+        <v>0.09587</v>
+      </c>
+      <c r="H141" s="1" t="n">
         <v>0.09601</v>
       </c>
-      <c r="H141" s="1" t="n">
+      <c r="I141" s="1" t="n">
         <v>0.09569</v>
       </c>
     </row>
@@ -4413,9 +4839,12 @@
         <v>0.0832</v>
       </c>
       <c r="G142" s="1" t="n">
-        <v>0.08348</v>
+        <v>0.08363</v>
       </c>
       <c r="H142" s="1" t="n">
+        <v>0.08363</v>
+      </c>
+      <c r="I142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -4441,9 +4870,12 @@
         <v>0.0086</v>
       </c>
       <c r="G143" s="1" t="n">
+        <v>0.00859</v>
+      </c>
+      <c r="H143" s="1" t="n">
         <v>0.0086</v>
       </c>
-      <c r="H143" s="1" t="n">
+      <c r="I143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -4469,9 +4901,12 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="G144" s="1" t="n">
+        <v>0.07242</v>
+      </c>
+      <c r="H144" s="1" t="n">
         <v>0.07288</v>
       </c>
-      <c r="H144" s="1" t="n">
+      <c r="I144" s="1" t="n">
         <v>0.07240000000000001</v>
       </c>
     </row>
@@ -4497,9 +4932,12 @@
         <v>0.4271</v>
       </c>
       <c r="G145" s="1" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="H145" s="1" t="n">
         <v>0.4305</v>
       </c>
-      <c r="H145" s="1" t="n">
+      <c r="I145" s="1" t="n">
         <v>0.4271</v>
       </c>
     </row>
@@ -4525,9 +4963,12 @@
         <v>0.0322</v>
       </c>
       <c r="G146" s="1" t="n">
+        <v>0.03228</v>
+      </c>
+      <c r="H146" s="1" t="n">
         <v>0.03276</v>
       </c>
-      <c r="H146" s="1" t="n">
+      <c r="I146" s="1" t="n">
         <v>0.0322</v>
       </c>
     </row>
@@ -4553,9 +4994,12 @@
         <v>390.42</v>
       </c>
       <c r="G147" s="1" t="n">
+        <v>390.43</v>
+      </c>
+      <c r="H147" s="1" t="n">
         <v>390.55</v>
       </c>
-      <c r="H147" s="1" t="n">
+      <c r="I147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -4581,9 +5025,12 @@
         <v>0.03301</v>
       </c>
       <c r="G148" s="1" t="n">
+        <v>0.03304</v>
+      </c>
+      <c r="H148" s="1" t="n">
         <v>0.0333</v>
       </c>
-      <c r="H148" s="1" t="n">
+      <c r="I148" s="1" t="n">
         <v>0.0329</v>
       </c>
     </row>
@@ -4609,9 +5056,12 @@
         <v>0.0529</v>
       </c>
       <c r="G149" s="1" t="n">
+        <v>0.05314</v>
+      </c>
+      <c r="H149" s="1" t="n">
         <v>0.05322</v>
       </c>
-      <c r="H149" s="1" t="n">
+      <c r="I149" s="1" t="n">
         <v>0.05289</v>
       </c>
     </row>
@@ -4637,9 +5087,12 @@
         <v>0.0004396</v>
       </c>
       <c r="G150" s="1" t="n">
+        <v>0.0004409</v>
+      </c>
+      <c r="H150" s="1" t="n">
         <v>0.000443</v>
       </c>
-      <c r="H150" s="1" t="n">
+      <c r="I150" s="1" t="n">
         <v>0.000439</v>
       </c>
     </row>
@@ -4665,9 +5118,12 @@
         <v>0.02173</v>
       </c>
       <c r="G151" s="1" t="n">
+        <v>0.02184</v>
+      </c>
+      <c r="H151" s="1" t="n">
         <v>0.02189</v>
       </c>
-      <c r="H151" s="1" t="n">
+      <c r="I151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -4693,9 +5149,12 @@
         <v>0.001768</v>
       </c>
       <c r="G152" s="1" t="n">
+        <v>0.001781</v>
+      </c>
+      <c r="H152" s="1" t="n">
         <v>0.001783</v>
       </c>
-      <c r="H152" s="1" t="n">
+      <c r="I152" s="1" t="n">
         <v>0.001768</v>
       </c>
     </row>
@@ -4721,9 +5180,12 @@
         <v>6e-06</v>
       </c>
       <c r="G153" s="1" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="H153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
-      <c r="H153" s="1" t="n">
+      <c r="I153" s="1" t="n">
         <v>6e-06</v>
       </c>
     </row>
@@ -4749,9 +5211,12 @@
         <v>0.1598</v>
       </c>
       <c r="G154" s="1" t="n">
-        <v>0.16</v>
+        <v>0.1602</v>
       </c>
       <c r="H154" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="I154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -4777,9 +5242,12 @@
         <v>0.03763</v>
       </c>
       <c r="G155" s="1" t="n">
+        <v>0.03765</v>
+      </c>
+      <c r="H155" s="1" t="n">
         <v>0.03768</v>
       </c>
-      <c r="H155" s="1" t="n">
+      <c r="I155" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -4805,9 +5273,12 @@
         <v>0.005364</v>
       </c>
       <c r="G156" s="1" t="n">
+        <v>0.005375</v>
+      </c>
+      <c r="H156" s="1" t="n">
         <v>0.005402</v>
       </c>
-      <c r="H156" s="1" t="n">
+      <c r="I156" s="1" t="n">
         <v>0.005364</v>
       </c>
     </row>
@@ -4833,10 +5304,13 @@
         <v>0.02277</v>
       </c>
       <c r="G157" s="1" t="n">
+        <v>0.02276</v>
+      </c>
+      <c r="H157" s="1" t="n">
         <v>0.02284</v>
       </c>
-      <c r="H157" s="1" t="n">
-        <v>0.02277</v>
+      <c r="I157" s="1" t="n">
+        <v>0.02276</v>
       </c>
     </row>
     <row r="158">
@@ -4864,6 +5338,9 @@
         <v>1.09</v>
       </c>
       <c r="H158" s="1" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -4889,9 +5366,12 @@
         <v>2.549</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>2.558</v>
+        <v>2.562</v>
       </c>
       <c r="H159" s="1" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="I159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -4917,9 +5397,12 @@
         <v>4.839</v>
       </c>
       <c r="G160" s="1" t="n">
+        <v>4.843</v>
+      </c>
+      <c r="H160" s="1" t="n">
         <v>4.858</v>
       </c>
-      <c r="H160" s="1" t="n">
+      <c r="I160" s="1" t="n">
         <v>4.836</v>
       </c>
     </row>
@@ -4945,9 +5428,12 @@
         <v>0.1599</v>
       </c>
       <c r="G161" s="1" t="n">
-        <v>0.1599</v>
+        <v>0.1605</v>
       </c>
       <c r="H161" s="1" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="I161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -4973,9 +5459,12 @@
         <v>0.2073</v>
       </c>
       <c r="G162" s="1" t="n">
+        <v>0.20639</v>
+      </c>
+      <c r="H162" s="1" t="n">
         <v>0.20754</v>
       </c>
-      <c r="H162" s="1" t="n">
+      <c r="I162" s="1" t="n">
         <v>0.20584</v>
       </c>
     </row>
@@ -5004,6 +5493,9 @@
         <v>0.03939</v>
       </c>
       <c r="H163" s="1" t="n">
+        <v>0.03939</v>
+      </c>
+      <c r="I163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -5029,9 +5521,12 @@
         <v>0.06326</v>
       </c>
       <c r="G164" s="1" t="n">
-        <v>0.06326</v>
+        <v>0.06339</v>
       </c>
       <c r="H164" s="1" t="n">
+        <v>0.06339</v>
+      </c>
+      <c r="I164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -5057,9 +5552,12 @@
         <v>0.3601</v>
       </c>
       <c r="G165" s="1" t="n">
-        <v>0.3601</v>
+        <v>0.3618</v>
       </c>
       <c r="H165" s="1" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="I165" s="1" t="n">
         <v>0.3525</v>
       </c>
     </row>
@@ -5085,9 +5583,12 @@
         <v>139.12</v>
       </c>
       <c r="G166" s="1" t="n">
+        <v>139.21</v>
+      </c>
+      <c r="H166" s="1" t="n">
         <v>139.27</v>
       </c>
-      <c r="H166" s="1" t="n">
+      <c r="I166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -5113,9 +5614,12 @@
         <v>0.0006507</v>
       </c>
       <c r="G167" s="1" t="n">
+        <v>0.0006464</v>
+      </c>
+      <c r="H167" s="1" t="n">
         <v>0.0006533</v>
       </c>
-      <c r="H167" s="1" t="n">
+      <c r="I167" s="1" t="n">
         <v>0.0006431</v>
       </c>
     </row>
@@ -5141,9 +5645,12 @@
         <v>0.01629</v>
       </c>
       <c r="G168" s="1" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="H168" s="1" t="n">
         <v>0.01678</v>
       </c>
-      <c r="H168" s="1" t="n">
+      <c r="I168" s="1" t="n">
         <v>0.01629</v>
       </c>
     </row>
@@ -5169,9 +5676,12 @@
         <v>0.04785</v>
       </c>
       <c r="G169" s="1" t="n">
-        <v>0.04798</v>
+        <v>0.04806</v>
       </c>
       <c r="H169" s="1" t="n">
+        <v>0.04806</v>
+      </c>
+      <c r="I169" s="1" t="n">
         <v>0.04785</v>
       </c>
     </row>
@@ -5197,9 +5707,12 @@
         <v>4.298</v>
       </c>
       <c r="G170" s="1" t="n">
+        <v>4.289</v>
+      </c>
+      <c r="H170" s="1" t="n">
         <v>4.298</v>
       </c>
-      <c r="H170" s="1" t="n">
+      <c r="I170" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -5225,9 +5738,12 @@
         <v>0.03836</v>
       </c>
       <c r="G171" s="1" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="H171" s="1" t="n">
         <v>0.03874</v>
       </c>
-      <c r="H171" s="1" t="n">
+      <c r="I171" s="1" t="n">
         <v>0.03836</v>
       </c>
     </row>
@@ -5253,9 +5769,12 @@
         <v>0.0425</v>
       </c>
       <c r="G172" s="1" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="H172" s="1" t="n">
         <v>0.0431</v>
       </c>
-      <c r="H172" s="1" t="n">
+      <c r="I172" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -5281,9 +5800,12 @@
         <v>0.024294</v>
       </c>
       <c r="G173" s="1" t="n">
-        <v>0.024294</v>
+        <v>0.024556</v>
       </c>
       <c r="H173" s="1" t="n">
+        <v>0.024556</v>
+      </c>
+      <c r="I173" s="1" t="n">
         <v>0.02382</v>
       </c>
     </row>
@@ -5309,9 +5831,12 @@
         <v>1.0768</v>
       </c>
       <c r="G174" s="1" t="n">
-        <v>1.0768</v>
+        <v>1.0803</v>
       </c>
       <c r="H174" s="1" t="n">
+        <v>1.0803</v>
+      </c>
+      <c r="I174" s="1" t="n">
         <v>1.0704</v>
       </c>
     </row>
@@ -5337,10 +5862,13 @@
         <v>0.028551</v>
       </c>
       <c r="G175" s="1" t="n">
+        <v>0.028452</v>
+      </c>
+      <c r="H175" s="1" t="n">
         <v>0.028967</v>
       </c>
-      <c r="H175" s="1" t="n">
-        <v>0.028551</v>
+      <c r="I175" s="1" t="n">
+        <v>0.028452</v>
       </c>
     </row>
     <row r="176">
@@ -5365,9 +5893,12 @@
         <v>0.02193</v>
       </c>
       <c r="G176" s="1" t="n">
-        <v>0.02193</v>
+        <v>0.02195</v>
       </c>
       <c r="H176" s="1" t="n">
+        <v>0.02195</v>
+      </c>
+      <c r="I176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -5393,9 +5924,12 @@
         <v>0.5442</v>
       </c>
       <c r="G177" s="1" t="n">
-        <v>0.5444</v>
+        <v>0.5453</v>
       </c>
       <c r="H177" s="1" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="I177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -5421,9 +5955,12 @@
         <v>0.08248999999999999</v>
       </c>
       <c r="G178" s="1" t="n">
+        <v>0.08266</v>
+      </c>
+      <c r="H178" s="1" t="n">
         <v>0.08276</v>
       </c>
-      <c r="H178" s="1" t="n">
+      <c r="I178" s="1" t="n">
         <v>0.08248999999999999</v>
       </c>
     </row>
@@ -5449,9 +5986,12 @@
         <v>0.02129</v>
       </c>
       <c r="G179" s="1" t="n">
-        <v>0.02133</v>
+        <v>0.0214</v>
       </c>
       <c r="H179" s="1" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="I179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -5477,9 +6017,12 @@
         <v>0.27047</v>
       </c>
       <c r="G180" s="1" t="n">
-        <v>0.27127</v>
+        <v>0.27157</v>
       </c>
       <c r="H180" s="1" t="n">
+        <v>0.27157</v>
+      </c>
+      <c r="I180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -5508,6 +6051,9 @@
         <v>0.0042</v>
       </c>
       <c r="H181" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="I181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -5533,9 +6079,12 @@
         <v>0.07973</v>
       </c>
       <c r="G182" s="1" t="n">
+        <v>0.07965</v>
+      </c>
+      <c r="H182" s="1" t="n">
         <v>0.07981000000000001</v>
       </c>
-      <c r="H182" s="1" t="n">
+      <c r="I182" s="1" t="n">
         <v>0.07931000000000001</v>
       </c>
     </row>
@@ -5561,9 +6110,12 @@
         <v>0.02345</v>
       </c>
       <c r="G183" s="1" t="n">
+        <v>0.02349</v>
+      </c>
+      <c r="H183" s="1" t="n">
         <v>0.02357</v>
       </c>
-      <c r="H183" s="1" t="n">
+      <c r="I183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -5589,9 +6141,12 @@
         <v>6.957999999999999e-05</v>
       </c>
       <c r="G184" s="1" t="n">
-        <v>6.981e-05</v>
+        <v>7.002e-05</v>
       </c>
       <c r="H184" s="1" t="n">
+        <v>7.002e-05</v>
+      </c>
+      <c r="I184" s="1" t="n">
         <v>6.957e-05</v>
       </c>
     </row>
@@ -5617,9 +6172,12 @@
         <v>0.02131</v>
       </c>
       <c r="G185" s="1" t="n">
-        <v>0.02131</v>
+        <v>0.0214</v>
       </c>
       <c r="H185" s="1" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="I185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -5645,9 +6203,12 @@
         <v>0.01627</v>
       </c>
       <c r="G186" s="1" t="n">
+        <v>0.01627</v>
+      </c>
+      <c r="H186" s="1" t="n">
         <v>0.01632</v>
       </c>
-      <c r="H186" s="1" t="n">
+      <c r="I186" s="1" t="n">
         <v>0.01623</v>
       </c>
     </row>
@@ -5673,9 +6234,12 @@
         <v>0.974</v>
       </c>
       <c r="G187" s="1" t="n">
-        <v>0.978</v>
+        <v>0.981</v>
       </c>
       <c r="H187" s="1" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="I187" s="1" t="n">
         <v>0.971</v>
       </c>
     </row>
@@ -5701,9 +6265,12 @@
         <v>0.0238</v>
       </c>
       <c r="G188" s="1" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="H188" s="1" t="n">
         <v>0.0239</v>
       </c>
-      <c r="H188" s="1" t="n">
+      <c r="I188" s="1" t="n">
         <v>0.0237</v>
       </c>
     </row>
@@ -5729,9 +6296,12 @@
         <v>1.861</v>
       </c>
       <c r="G189" s="1" t="n">
-        <v>1.8658</v>
+        <v>1.8712</v>
       </c>
       <c r="H189" s="1" t="n">
+        <v>1.8712</v>
+      </c>
+      <c r="I189" s="1" t="n">
         <v>1.8609</v>
       </c>
     </row>
@@ -5757,9 +6327,12 @@
         <v>1.826</v>
       </c>
       <c r="G190" s="1" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="H190" s="1" t="n">
         <v>1.838</v>
       </c>
-      <c r="H190" s="1" t="n">
+      <c r="I190" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -5785,9 +6358,12 @@
         <v>0.02671</v>
       </c>
       <c r="G191" s="1" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="H191" s="1" t="n">
         <v>0.0268</v>
       </c>
-      <c r="H191" s="1" t="n">
+      <c r="I191" s="1" t="n">
         <v>0.02669</v>
       </c>
     </row>
@@ -5813,9 +6389,12 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="G192" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="H192" s="1" t="n">
         <v>0.0973</v>
       </c>
-      <c r="H192" s="1" t="n">
+      <c r="I192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -5841,9 +6420,12 @@
         <v>0.1701</v>
       </c>
       <c r="G193" s="1" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H193" s="1" t="n">
         <v>0.1701</v>
       </c>
-      <c r="H193" s="1" t="n">
+      <c r="I193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -5869,9 +6451,12 @@
         <v>16.246</v>
       </c>
       <c r="G194" s="1" t="n">
-        <v>16.294</v>
+        <v>16.315</v>
       </c>
       <c r="H194" s="1" t="n">
+        <v>16.315</v>
+      </c>
+      <c r="I194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -5897,9 +6482,12 @@
         <v>4.087</v>
       </c>
       <c r="G195" s="1" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="H195" s="1" t="n">
         <v>4.098</v>
       </c>
-      <c r="H195" s="1" t="n">
+      <c r="I195" s="1" t="n">
         <v>4.087</v>
       </c>
     </row>
@@ -5925,9 +6513,12 @@
         <v>1.2663</v>
       </c>
       <c r="G196" s="1" t="n">
+        <v>1.2705</v>
+      </c>
+      <c r="H196" s="1" t="n">
         <v>1.2794</v>
       </c>
-      <c r="H196" s="1" t="n">
+      <c r="I196" s="1" t="n">
         <v>1.2663</v>
       </c>
     </row>
@@ -5953,9 +6544,12 @@
         <v>3.066</v>
       </c>
       <c r="G197" s="1" t="n">
+        <v>3.082</v>
+      </c>
+      <c r="H197" s="1" t="n">
         <v>3.092</v>
       </c>
-      <c r="H197" s="1" t="n">
+      <c r="I197" s="1" t="n">
         <v>3.066</v>
       </c>
     </row>
@@ -5981,9 +6575,12 @@
         <v>0.01263</v>
       </c>
       <c r="G198" s="1" t="n">
+        <v>0.01262</v>
+      </c>
+      <c r="H198" s="1" t="n">
         <v>0.01266</v>
       </c>
-      <c r="H198" s="1" t="n">
+      <c r="I198" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -6009,9 +6606,12 @@
         <v>0.0001758</v>
       </c>
       <c r="G199" s="1" t="n">
+        <v>0.0001761</v>
+      </c>
+      <c r="H199" s="1" t="n">
         <v>0.0001762</v>
       </c>
-      <c r="H199" s="1" t="n">
+      <c r="I199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -6037,9 +6637,12 @@
         <v>115.48</v>
       </c>
       <c r="G200" s="1" t="n">
+        <v>115.53</v>
+      </c>
+      <c r="H200" s="1" t="n">
         <v>115.62</v>
       </c>
-      <c r="H200" s="1" t="n">
+      <c r="I200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -6065,9 +6668,12 @@
         <v>0.01025</v>
       </c>
       <c r="G201" s="1" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="H201" s="1" t="n">
         <v>0.01031</v>
       </c>
-      <c r="H201" s="1" t="n">
+      <c r="I201" s="1" t="n">
         <v>0.01023</v>
       </c>
     </row>
@@ -6093,9 +6699,12 @@
         <v>0.0107</v>
       </c>
       <c r="G202" s="1" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="H202" s="1" t="n">
         <v>0.01073</v>
       </c>
-      <c r="H202" s="1" t="n">
+      <c r="I202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -6121,9 +6730,12 @@
         <v>0.003136</v>
       </c>
       <c r="G203" s="1" t="n">
+        <v>0.003137</v>
+      </c>
+      <c r="H203" s="1" t="n">
         <v>0.003153</v>
       </c>
-      <c r="H203" s="1" t="n">
+      <c r="I203" s="1" t="n">
         <v>0.003136</v>
       </c>
     </row>
@@ -6149,9 +6761,12 @@
         <v>28.23</v>
       </c>
       <c r="G204" s="1" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="H204" s="1" t="n">
         <v>28.38</v>
       </c>
-      <c r="H204" s="1" t="n">
+      <c r="I204" s="1" t="n">
         <v>28.23</v>
       </c>
     </row>
@@ -6177,9 +6792,12 @@
         <v>0.5613</v>
       </c>
       <c r="G205" s="1" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="H205" s="1" t="n">
         <v>0.5636</v>
       </c>
-      <c r="H205" s="1" t="n">
+      <c r="I205" s="1" t="n">
         <v>0.5608</v>
       </c>
     </row>
@@ -6205,9 +6823,12 @@
         <v>0.0004389</v>
       </c>
       <c r="G206" s="1" t="n">
-        <v>0.0004403</v>
+        <v>0.0004417</v>
       </c>
       <c r="H206" s="1" t="n">
+        <v>0.0004417</v>
+      </c>
+      <c r="I206" s="1" t="n">
         <v>0.0004387</v>
       </c>
     </row>
@@ -6236,6 +6857,9 @@
         <v>0.04667</v>
       </c>
       <c r="H207" s="1" t="n">
+        <v>0.04667</v>
+      </c>
+      <c r="I207" s="1" t="n">
         <v>0.04648</v>
       </c>
     </row>
@@ -6261,9 +6885,12 @@
         <v>0.09</v>
       </c>
       <c r="G208" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H208" s="1" t="n">
         <v>0.091</v>
       </c>
-      <c r="H208" s="1" t="n">
+      <c r="I208" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -6289,9 +6916,12 @@
         <v>0.02562</v>
       </c>
       <c r="G209" s="1" t="n">
+        <v>0.02566</v>
+      </c>
+      <c r="H209" s="1" t="n">
         <v>0.02572</v>
       </c>
-      <c r="H209" s="1" t="n">
+      <c r="I209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -6317,9 +6947,12 @@
         <v>0.012729</v>
       </c>
       <c r="G210" s="1" t="n">
+        <v>0.012671</v>
+      </c>
+      <c r="H210" s="1" t="n">
         <v>0.012745</v>
       </c>
-      <c r="H210" s="1" t="n">
+      <c r="I210" s="1" t="n">
         <v>0.012652</v>
       </c>
     </row>
@@ -6345,9 +6978,12 @@
         <v>0.0916</v>
       </c>
       <c r="G211" s="1" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0921</v>
       </c>
       <c r="H211" s="1" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="I211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -6373,9 +7009,12 @@
         <v>0.007044</v>
       </c>
       <c r="G212" s="1" t="n">
+        <v>0.007047</v>
+      </c>
+      <c r="H212" s="1" t="n">
         <v>0.007076</v>
       </c>
-      <c r="H212" s="1" t="n">
+      <c r="I212" s="1" t="n">
         <v>0.007044</v>
       </c>
     </row>
@@ -6401,9 +7040,12 @@
         <v>0.02949</v>
       </c>
       <c r="G213" s="1" t="n">
+        <v>0.02962</v>
+      </c>
+      <c r="H213" s="1" t="n">
         <v>0.02966</v>
       </c>
-      <c r="H213" s="1" t="n">
+      <c r="I213" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -6429,9 +7071,12 @@
         <v>0.2698</v>
       </c>
       <c r="G214" s="1" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="H214" s="1" t="n">
         <v>0.2708</v>
       </c>
-      <c r="H214" s="1" t="n">
+      <c r="I214" s="1" t="n">
         <v>0.2698</v>
       </c>
     </row>
@@ -6457,9 +7102,12 @@
         <v>0.02183</v>
       </c>
       <c r="G215" s="1" t="n">
-        <v>0.02183</v>
+        <v>0.02195</v>
       </c>
       <c r="H215" s="1" t="n">
+        <v>0.02195</v>
+      </c>
+      <c r="I215" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -6485,9 +7133,12 @@
         <v>0.0147</v>
       </c>
       <c r="G216" s="1" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="H216" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="H216" s="1" t="n">
+      <c r="I216" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -6513,9 +7164,12 @@
         <v>0.2533</v>
       </c>
       <c r="G217" s="1" t="n">
-        <v>0.2538</v>
+        <v>0.2542</v>
       </c>
       <c r="H217" s="1" t="n">
+        <v>0.2542</v>
+      </c>
+      <c r="I217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -6541,9 +7195,12 @@
         <v>0.3069</v>
       </c>
       <c r="G218" s="1" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="H218" s="1" t="n">
         <v>0.3087</v>
       </c>
-      <c r="H218" s="1" t="n">
+      <c r="I218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -6569,9 +7226,12 @@
         <v>0.1774</v>
       </c>
       <c r="G219" s="1" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="H219" s="1" t="n">
         <v>0.1784</v>
       </c>
-      <c r="H219" s="1" t="n">
+      <c r="I219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -6597,9 +7257,12 @@
         <v>14.99</v>
       </c>
       <c r="G220" s="1" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="H220" s="1" t="n">
         <v>15.02</v>
       </c>
-      <c r="H220" s="1" t="n">
+      <c r="I220" s="1" t="n">
         <v>14.97</v>
       </c>
     </row>
@@ -6625,9 +7288,12 @@
         <v>0.01599</v>
       </c>
       <c r="G221" s="1" t="n">
-        <v>0.01599</v>
+        <v>0.01611</v>
       </c>
       <c r="H221" s="1" t="n">
+        <v>0.01611</v>
+      </c>
+      <c r="I221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -6653,9 +7319,12 @@
         <v>66.2</v>
       </c>
       <c r="G222" s="1" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="H222" s="1" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="H222" s="1" t="n">
+      <c r="I222" s="1" t="n">
         <v>66.17</v>
       </c>
     </row>
@@ -6681,9 +7350,12 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="G223" s="1" t="n">
-        <v>0.09291000000000001</v>
+        <v>0.09308</v>
       </c>
       <c r="H223" s="1" t="n">
+        <v>0.09308</v>
+      </c>
+      <c r="I223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -6709,9 +7381,12 @@
         <v>0.03931</v>
       </c>
       <c r="G224" s="1" t="n">
-        <v>0.03931</v>
+        <v>0.03963</v>
       </c>
       <c r="H224" s="1" t="n">
+        <v>0.03963</v>
+      </c>
+      <c r="I224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -6737,9 +7412,12 @@
         <v>0.5706</v>
       </c>
       <c r="G225" s="1" t="n">
+        <v>0.5713</v>
+      </c>
+      <c r="H225" s="1" t="n">
         <v>0.5725</v>
       </c>
-      <c r="H225" s="1" t="n">
+      <c r="I225" s="1" t="n">
         <v>0.5695</v>
       </c>
     </row>
@@ -6765,9 +7443,12 @@
         <v>0.1184</v>
       </c>
       <c r="G226" s="1" t="n">
+        <v>0.1181</v>
+      </c>
+      <c r="H226" s="1" t="n">
         <v>0.1184</v>
       </c>
-      <c r="H226" s="1" t="n">
+      <c r="I226" s="1" t="n">
         <v>0.1166</v>
       </c>
     </row>
@@ -6793,9 +7474,12 @@
         <v>0.3167</v>
       </c>
       <c r="G227" s="1" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="H227" s="1" t="n">
         <v>0.3201</v>
       </c>
-      <c r="H227" s="1" t="n">
+      <c r="I227" s="1" t="n">
         <v>0.3167</v>
       </c>
     </row>
@@ -6821,9 +7505,12 @@
         <v>6.062</v>
       </c>
       <c r="G228" s="1" t="n">
+        <v>6.079</v>
+      </c>
+      <c r="H228" s="1" t="n">
         <v>6.09</v>
       </c>
-      <c r="H228" s="1" t="n">
+      <c r="I228" s="1" t="n">
         <v>6.062</v>
       </c>
     </row>
@@ -6849,9 +7536,12 @@
         <v>0.0291</v>
       </c>
       <c r="G229" s="1" t="n">
-        <v>0.0291</v>
+        <v>0.0294</v>
       </c>
       <c r="H229" s="1" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="I229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -6877,9 +7567,12 @@
         <v>0.3288</v>
       </c>
       <c r="G230" s="1" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="H230" s="1" t="n">
         <v>0.3307</v>
       </c>
-      <c r="H230" s="1" t="n">
+      <c r="I230" s="1" t="n">
         <v>0.3288</v>
       </c>
     </row>
@@ -6905,9 +7598,12 @@
         <v>0.11994</v>
       </c>
       <c r="G231" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="H231" s="1" t="n">
         <v>0.12089</v>
       </c>
-      <c r="H231" s="1" t="n">
+      <c r="I231" s="1" t="n">
         <v>0.11994</v>
       </c>
     </row>
@@ -6933,10 +7629,13 @@
         <v>0.1187</v>
       </c>
       <c r="G232" s="1" t="n">
+        <v>0.1182</v>
+      </c>
+      <c r="H232" s="1" t="n">
         <v>0.1187</v>
       </c>
-      <c r="H232" s="1" t="n">
-        <v>0.1185</v>
+      <c r="I232" s="1" t="n">
+        <v>0.1182</v>
       </c>
     </row>
     <row r="233">
@@ -6961,9 +7660,12 @@
         <v>0.03011</v>
       </c>
       <c r="G233" s="1" t="n">
+        <v>0.03015</v>
+      </c>
+      <c r="H233" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="H233" s="1" t="n">
+      <c r="I233" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -6989,10 +7691,13 @@
         <v>0.015628</v>
       </c>
       <c r="G234" s="1" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="H234" s="1" t="n">
         <v>0.01574</v>
       </c>
-      <c r="H234" s="1" t="n">
-        <v>0.015628</v>
+      <c r="I234" s="1" t="n">
+        <v>0.0156</v>
       </c>
     </row>
     <row r="235">
@@ -7017,9 +7722,12 @@
         <v>0.01274</v>
       </c>
       <c r="G235" s="1" t="n">
-        <v>0.01279</v>
+        <v>0.01281</v>
       </c>
       <c r="H235" s="1" t="n">
+        <v>0.01281</v>
+      </c>
+      <c r="I235" s="1" t="n">
         <v>0.01272</v>
       </c>
     </row>
@@ -7045,9 +7753,12 @@
         <v>0.01925</v>
       </c>
       <c r="G236" s="1" t="n">
+        <v>0.01927</v>
+      </c>
+      <c r="H236" s="1" t="n">
         <v>0.01929</v>
       </c>
-      <c r="H236" s="1" t="n">
+      <c r="I236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -7073,9 +7784,12 @@
         <v>0.08477</v>
       </c>
       <c r="G237" s="1" t="n">
-        <v>0.08509</v>
+        <v>0.08545999999999999</v>
       </c>
       <c r="H237" s="1" t="n">
+        <v>0.08545999999999999</v>
+      </c>
+      <c r="I237" s="1" t="n">
         <v>0.08427999999999999</v>
       </c>
     </row>
@@ -7101,9 +7815,12 @@
         <v>0.05857</v>
       </c>
       <c r="G238" s="1" t="n">
+        <v>0.05866</v>
+      </c>
+      <c r="H238" s="1" t="n">
         <v>0.05892</v>
       </c>
-      <c r="H238" s="1" t="n">
+      <c r="I238" s="1" t="n">
         <v>0.05857</v>
       </c>
     </row>
@@ -7129,9 +7846,12 @@
         <v>0.00908</v>
       </c>
       <c r="G239" s="1" t="n">
-        <v>0.009083000000000001</v>
+        <v>0.009131999999999999</v>
       </c>
       <c r="H239" s="1" t="n">
+        <v>0.009131999999999999</v>
+      </c>
+      <c r="I239" s="1" t="n">
         <v>0.009027</v>
       </c>
     </row>
@@ -7157,9 +7877,12 @@
         <v>0.004163</v>
       </c>
       <c r="G240" s="1" t="n">
+        <v>0.004156</v>
+      </c>
+      <c r="H240" s="1" t="n">
         <v>0.004175</v>
       </c>
-      <c r="H240" s="1" t="n">
+      <c r="I240" s="1" t="n">
         <v>0.004154</v>
       </c>
     </row>
@@ -7185,9 +7908,12 @@
         <v>0.2404</v>
       </c>
       <c r="G241" s="1" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="H241" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="H241" s="1" t="n">
+      <c r="I241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -7213,9 +7939,12 @@
         <v>0.0582</v>
       </c>
       <c r="G242" s="1" t="n">
-        <v>0.0582</v>
+        <v>0.0584</v>
       </c>
       <c r="H242" s="1" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="I242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -7241,9 +7970,12 @@
         <v>0.02347</v>
       </c>
       <c r="G243" s="1" t="n">
-        <v>0.02356</v>
+        <v>0.02363</v>
       </c>
       <c r="H243" s="1" t="n">
+        <v>0.02363</v>
+      </c>
+      <c r="I243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -7269,9 +8001,12 @@
         <v>0.05559</v>
       </c>
       <c r="G244" s="1" t="n">
+        <v>0.05575</v>
+      </c>
+      <c r="H244" s="1" t="n">
         <v>0.05623</v>
       </c>
-      <c r="H244" s="1" t="n">
+      <c r="I244" s="1" t="n">
         <v>0.05547</v>
       </c>
     </row>
@@ -7297,9 +8032,12 @@
         <v>0.03431</v>
       </c>
       <c r="G245" s="1" t="n">
-        <v>0.03438</v>
+        <v>0.03444</v>
       </c>
       <c r="H245" s="1" t="n">
+        <v>0.03444</v>
+      </c>
+      <c r="I245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -7325,9 +8063,12 @@
         <v>0.06</v>
       </c>
       <c r="G246" s="1" t="n">
-        <v>0.06013</v>
+        <v>0.06027</v>
       </c>
       <c r="H246" s="1" t="n">
+        <v>0.06027</v>
+      </c>
+      <c r="I246" s="1" t="n">
         <v>0.0599</v>
       </c>
     </row>
@@ -7353,10 +8094,13 @@
         <v>0.383</v>
       </c>
       <c r="G247" s="1" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="H247" s="1" t="n">
         <v>0.385</v>
       </c>
-      <c r="H247" s="1" t="n">
-        <v>0.383</v>
+      <c r="I247" s="1" t="n">
+        <v>0.382</v>
       </c>
     </row>
     <row r="248">
@@ -7381,9 +8125,12 @@
         <v>0.5173</v>
       </c>
       <c r="G248" s="1" t="n">
+        <v>0.5188</v>
+      </c>
+      <c r="H248" s="1" t="n">
         <v>0.519</v>
       </c>
-      <c r="H248" s="1" t="n">
+      <c r="I248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -7409,9 +8156,12 @@
         <v>0.02801</v>
       </c>
       <c r="G249" s="1" t="n">
-        <v>0.02804</v>
+        <v>0.02819</v>
       </c>
       <c r="H249" s="1" t="n">
+        <v>0.02819</v>
+      </c>
+      <c r="I249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -7437,9 +8187,12 @@
         <v>0.0129</v>
       </c>
       <c r="G250" s="1" t="n">
-        <v>0.01295</v>
+        <v>0.01299</v>
       </c>
       <c r="H250" s="1" t="n">
+        <v>0.01299</v>
+      </c>
+      <c r="I250" s="1" t="n">
         <v>0.01288</v>
       </c>
     </row>
@@ -7468,6 +8221,9 @@
         <v>0.1003</v>
       </c>
       <c r="H251" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="I251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -7493,10 +8249,13 @@
         <v>0.00716</v>
       </c>
       <c r="G252" s="1" t="n">
+        <v>0.00715</v>
+      </c>
+      <c r="H252" s="1" t="n">
         <v>0.00719</v>
       </c>
-      <c r="H252" s="1" t="n">
-        <v>0.00716</v>
+      <c r="I252" s="1" t="n">
+        <v>0.00715</v>
       </c>
     </row>
     <row r="253">
@@ -7524,6 +8283,9 @@
         <v>0.005563</v>
       </c>
       <c r="H253" s="1" t="n">
+        <v>0.005563</v>
+      </c>
+      <c r="I253" s="1" t="n">
         <v>0.005554</v>
       </c>
     </row>
@@ -7549,9 +8311,12 @@
         <v>0.0641</v>
       </c>
       <c r="G254" s="1" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="H254" s="1" t="n">
         <v>0.0646</v>
       </c>
-      <c r="H254" s="1" t="n">
+      <c r="I254" s="1" t="n">
         <v>0.0641</v>
       </c>
     </row>
@@ -7577,9 +8342,12 @@
         <v>0.01441</v>
       </c>
       <c r="G255" s="1" t="n">
-        <v>0.01441</v>
+        <v>0.01453</v>
       </c>
       <c r="H255" s="1" t="n">
+        <v>0.01453</v>
+      </c>
+      <c r="I255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -7605,9 +8373,12 @@
         <v>0.999286</v>
       </c>
       <c r="G256" s="1" t="n">
+        <v>0.999285</v>
+      </c>
+      <c r="H256" s="1" t="n">
         <v>0.999297</v>
       </c>
-      <c r="H256" s="1" t="n">
+      <c r="I256" s="1" t="n">
         <v>0.999285</v>
       </c>
     </row>
@@ -7633,9 +8404,12 @@
         <v>0.02101</v>
       </c>
       <c r="G257" s="1" t="n">
-        <v>0.02101</v>
+        <v>0.02114</v>
       </c>
       <c r="H257" s="1" t="n">
+        <v>0.02114</v>
+      </c>
+      <c r="I257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -7661,9 +8435,12 @@
         <v>0.01144</v>
       </c>
       <c r="G258" s="1" t="n">
+        <v>0.01145</v>
+      </c>
+      <c r="H258" s="1" t="n">
         <v>0.01148</v>
       </c>
-      <c r="H258" s="1" t="n">
+      <c r="I258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -7689,9 +8466,12 @@
         <v>0.5071</v>
       </c>
       <c r="G259" s="1" t="n">
+        <v>0.5078</v>
+      </c>
+      <c r="H259" s="1" t="n">
         <v>0.5119</v>
       </c>
-      <c r="H259" s="1" t="n">
+      <c r="I259" s="1" t="n">
         <v>0.5071</v>
       </c>
     </row>
@@ -7717,9 +8497,12 @@
         <v>0.08501</v>
       </c>
       <c r="G260" s="1" t="n">
+        <v>0.08495999999999999</v>
+      </c>
+      <c r="H260" s="1" t="n">
         <v>0.08537</v>
       </c>
-      <c r="H260" s="1" t="n">
+      <c r="I260" s="1" t="n">
         <v>0.08436</v>
       </c>
     </row>
@@ -7745,9 +8528,12 @@
         <v>0.04123</v>
       </c>
       <c r="G261" s="1" t="n">
+        <v>0.04124</v>
+      </c>
+      <c r="H261" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="H261" s="1" t="n">
+      <c r="I261" s="1" t="n">
         <v>0.04123</v>
       </c>
     </row>
@@ -7773,9 +8559,12 @@
         <v>2.279</v>
       </c>
       <c r="G262" s="1" t="n">
+        <v>2.283</v>
+      </c>
+      <c r="H262" s="1" t="n">
         <v>2.288</v>
       </c>
-      <c r="H262" s="1" t="n">
+      <c r="I262" s="1" t="n">
         <v>2.279</v>
       </c>
     </row>
@@ -7801,9 +8590,12 @@
         <v>18.44</v>
       </c>
       <c r="G263" s="1" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="H263" s="1" t="n">
         <v>18.51</v>
       </c>
-      <c r="H263" s="1" t="n">
+      <c r="I263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -7832,6 +8624,9 @@
         <v>0.008562999999999999</v>
       </c>
       <c r="H264" s="1" t="n">
+        <v>0.008562999999999999</v>
+      </c>
+      <c r="I264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -7857,9 +8652,12 @@
         <v>0.3627</v>
       </c>
       <c r="G265" s="1" t="n">
-        <v>0.363</v>
+        <v>0.3645</v>
       </c>
       <c r="H265" s="1" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="I265" s="1" t="n">
         <v>0.3627</v>
       </c>
     </row>
@@ -7885,9 +8683,12 @@
         <v>0.05428</v>
       </c>
       <c r="G266" s="1" t="n">
-        <v>0.054291</v>
+        <v>0.054644</v>
       </c>
       <c r="H266" s="1" t="n">
+        <v>0.054644</v>
+      </c>
+      <c r="I266" s="1" t="n">
         <v>0.053765</v>
       </c>
     </row>
@@ -7913,9 +8714,12 @@
         <v>0.1316</v>
       </c>
       <c r="G267" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="H267" s="1" t="n">
         <v>0.1321</v>
       </c>
-      <c r="H267" s="1" t="n">
+      <c r="I267" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -7941,9 +8745,12 @@
         <v>0.007789</v>
       </c>
       <c r="G268" s="1" t="n">
+        <v>0.00777</v>
+      </c>
+      <c r="H268" s="1" t="n">
         <v>0.007845</v>
       </c>
-      <c r="H268" s="1" t="n">
+      <c r="I268" s="1" t="n">
         <v>0.007759</v>
       </c>
     </row>
@@ -7969,10 +8776,13 @@
         <v>0.001233</v>
       </c>
       <c r="G269" s="1" t="n">
+        <v>0.001232</v>
+      </c>
+      <c r="H269" s="1" t="n">
         <v>0.00124</v>
       </c>
-      <c r="H269" s="1" t="n">
-        <v>0.001233</v>
+      <c r="I269" s="1" t="n">
+        <v>0.001232</v>
       </c>
     </row>
     <row r="270">
@@ -7997,9 +8807,12 @@
         <v>0.28984</v>
       </c>
       <c r="G270" s="1" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="H270" s="1" t="n">
         <v>0.28997</v>
       </c>
-      <c r="H270" s="1" t="n">
+      <c r="I270" s="1" t="n">
         <v>0.28865</v>
       </c>
     </row>
@@ -8025,9 +8838,12 @@
         <v>0.03887</v>
       </c>
       <c r="G271" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H271" s="1" t="n">
         <v>0.03922</v>
       </c>
-      <c r="H271" s="1" t="n">
+      <c r="I271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -8053,9 +8869,12 @@
         <v>0.05129</v>
       </c>
       <c r="G272" s="1" t="n">
-        <v>0.05137</v>
+        <v>0.0515</v>
       </c>
       <c r="H272" s="1" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="I272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -8084,6 +8903,9 @@
         <v>0.00771</v>
       </c>
       <c r="H273" s="1" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -8109,9 +8931,12 @@
         <v>0.005769</v>
       </c>
       <c r="G274" s="1" t="n">
-        <v>0.005779</v>
+        <v>0.005797</v>
       </c>
       <c r="H274" s="1" t="n">
+        <v>0.005797</v>
+      </c>
+      <c r="I274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -8137,9 +8962,12 @@
         <v>0.0005872</v>
       </c>
       <c r="G275" s="1" t="n">
+        <v>0.000588</v>
+      </c>
+      <c r="H275" s="1" t="n">
         <v>0.0005895</v>
       </c>
-      <c r="H275" s="1" t="n">
+      <c r="I275" s="1" t="n">
         <v>0.0005863</v>
       </c>
     </row>
@@ -8165,10 +8993,13 @@
         <v>0.15007</v>
       </c>
       <c r="G276" s="1" t="n">
+        <v>0.15004</v>
+      </c>
+      <c r="H276" s="1" t="n">
         <v>0.15167</v>
       </c>
-      <c r="H276" s="1" t="n">
-        <v>0.15007</v>
+      <c r="I276" s="1" t="n">
+        <v>0.15004</v>
       </c>
     </row>
     <row r="277">
@@ -8193,9 +9024,12 @@
         <v>0.022828</v>
       </c>
       <c r="G277" s="1" t="n">
-        <v>0.022828</v>
+        <v>0.022966</v>
       </c>
       <c r="H277" s="1" t="n">
+        <v>0.022966</v>
+      </c>
+      <c r="I277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -8221,9 +9055,12 @@
         <v>0.04219</v>
       </c>
       <c r="G278" s="1" t="n">
+        <v>0.04214</v>
+      </c>
+      <c r="H278" s="1" t="n">
         <v>0.04242</v>
       </c>
-      <c r="H278" s="1" t="n">
+      <c r="I278" s="1" t="n">
         <v>0.04179</v>
       </c>
     </row>
@@ -8249,9 +9086,12 @@
         <v>0.0003996</v>
       </c>
       <c r="G279" s="1" t="n">
+        <v>0.0003993</v>
+      </c>
+      <c r="H279" s="1" t="n">
         <v>0.0004006</v>
       </c>
-      <c r="H279" s="1" t="n">
+      <c r="I279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -8277,9 +9117,12 @@
         <v>0.02214</v>
       </c>
       <c r="G280" s="1" t="n">
+        <v>0.02209</v>
+      </c>
+      <c r="H280" s="1" t="n">
         <v>0.02218</v>
       </c>
-      <c r="H280" s="1" t="n">
+      <c r="I280" s="1" t="n">
         <v>0.02195</v>
       </c>
     </row>
@@ -8305,9 +9148,12 @@
         <v>0.06938999999999999</v>
       </c>
       <c r="G281" s="1" t="n">
-        <v>0.06945</v>
+        <v>0.06991</v>
       </c>
       <c r="H281" s="1" t="n">
+        <v>0.06991</v>
+      </c>
+      <c r="I281" s="1" t="n">
         <v>0.06936</v>
       </c>
     </row>
@@ -8333,10 +9179,13 @@
         <v>0.006732</v>
       </c>
       <c r="G282" s="1" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="H282" s="1" t="n">
         <v>0.006804</v>
       </c>
-      <c r="H282" s="1" t="n">
-        <v>0.006732</v>
+      <c r="I282" s="1" t="n">
+        <v>0.0067</v>
       </c>
     </row>
     <row r="283">
@@ -8364,6 +9213,9 @@
         <v>0.12</v>
       </c>
       <c r="H283" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I283" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -8389,9 +9241,12 @@
         <v>0.005467</v>
       </c>
       <c r="G284" s="1" t="n">
-        <v>0.005475</v>
+        <v>0.005491</v>
       </c>
       <c r="H284" s="1" t="n">
+        <v>0.005491</v>
+      </c>
+      <c r="I284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -8417,9 +9272,12 @@
         <v>1.255</v>
       </c>
       <c r="G285" s="1" t="n">
-        <v>1.255</v>
+        <v>1.263</v>
       </c>
       <c r="H285" s="1" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="I285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -8445,9 +9303,12 @@
         <v>0.4423</v>
       </c>
       <c r="G286" s="1" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="H286" s="1" t="n">
         <v>0.4441</v>
       </c>
-      <c r="H286" s="1" t="n">
+      <c r="I286" s="1" t="n">
         <v>0.4423</v>
       </c>
     </row>
@@ -8473,9 +9334,12 @@
         <v>0.007866</v>
       </c>
       <c r="G287" s="1" t="n">
-        <v>0.007875999999999999</v>
+        <v>0.007924</v>
       </c>
       <c r="H287" s="1" t="n">
+        <v>0.007924</v>
+      </c>
+      <c r="I287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -8501,9 +9365,12 @@
         <v>0.02928</v>
       </c>
       <c r="G288" s="1" t="n">
-        <v>0.02928</v>
+        <v>0.0295</v>
       </c>
       <c r="H288" s="1" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="I288" s="1" t="n">
         <v>0.02914</v>
       </c>
     </row>
@@ -8529,9 +9396,12 @@
         <v>0.2812</v>
       </c>
       <c r="G289" s="1" t="n">
-        <v>0.2812</v>
+        <v>0.2822</v>
       </c>
       <c r="H289" s="1" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="I289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -8557,9 +9427,12 @@
         <v>2.753</v>
       </c>
       <c r="G290" s="1" t="n">
+        <v>2.756</v>
+      </c>
+      <c r="H290" s="1" t="n">
         <v>2.764</v>
       </c>
-      <c r="H290" s="1" t="n">
+      <c r="I290" s="1" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -8585,9 +9458,12 @@
         <v>0.003167</v>
       </c>
       <c r="G291" s="1" t="n">
-        <v>0.003176</v>
+        <v>0.003177</v>
       </c>
       <c r="H291" s="1" t="n">
+        <v>0.003177</v>
+      </c>
+      <c r="I291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -8613,9 +9489,12 @@
         <v>0.4476</v>
       </c>
       <c r="G292" s="1" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="H292" s="1" t="n">
         <v>0.4488</v>
       </c>
-      <c r="H292" s="1" t="n">
+      <c r="I292" s="1" t="n">
         <v>0.4475</v>
       </c>
     </row>
@@ -8641,10 +9520,13 @@
         <v>0.08218</v>
       </c>
       <c r="G293" s="1" t="n">
+        <v>0.08203000000000001</v>
+      </c>
+      <c r="H293" s="1" t="n">
         <v>0.08298</v>
       </c>
-      <c r="H293" s="1" t="n">
-        <v>0.08214</v>
+      <c r="I293" s="1" t="n">
+        <v>0.08203000000000001</v>
       </c>
     </row>
     <row r="294">
@@ -8669,9 +9551,12 @@
         <v>0.02782</v>
       </c>
       <c r="G294" s="1" t="n">
-        <v>0.02784</v>
+        <v>0.02791</v>
       </c>
       <c r="H294" s="1" t="n">
+        <v>0.02791</v>
+      </c>
+      <c r="I294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -8697,9 +9582,12 @@
         <v>0.953</v>
       </c>
       <c r="G295" s="1" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="H295" s="1" t="n">
         <v>0.958</v>
       </c>
-      <c r="H295" s="1" t="n">
+      <c r="I295" s="1" t="n">
         <v>0.953</v>
       </c>
     </row>
@@ -8725,9 +9613,12 @@
         <v>0.00689</v>
       </c>
       <c r="G296" s="1" t="n">
-        <v>0.006891</v>
+        <v>0.007005</v>
       </c>
       <c r="H296" s="1" t="n">
+        <v>0.007005</v>
+      </c>
+      <c r="I296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -8753,9 +9644,12 @@
         <v>0.1209</v>
       </c>
       <c r="G297" s="1" t="n">
-        <v>0.1212</v>
+        <v>0.1213</v>
       </c>
       <c r="H297" s="1" t="n">
+        <v>0.1213</v>
+      </c>
+      <c r="I297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -8781,9 +9675,12 @@
         <v>0.01543</v>
       </c>
       <c r="G298" s="1" t="n">
-        <v>0.01548</v>
+        <v>0.01554</v>
       </c>
       <c r="H298" s="1" t="n">
+        <v>0.01554</v>
+      </c>
+      <c r="I298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -8809,9 +9706,12 @@
         <v>0.4399</v>
       </c>
       <c r="G299" s="1" t="n">
-        <v>0.4405</v>
+        <v>0.4409</v>
       </c>
       <c r="H299" s="1" t="n">
+        <v>0.4409</v>
+      </c>
+      <c r="I299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -8837,10 +9737,13 @@
         <v>0.00916</v>
       </c>
       <c r="G300" s="1" t="n">
+        <v>0.009140000000000001</v>
+      </c>
+      <c r="H300" s="1" t="n">
         <v>0.00924</v>
       </c>
-      <c r="H300" s="1" t="n">
-        <v>0.00916</v>
+      <c r="I300" s="1" t="n">
+        <v>0.009140000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -8865,9 +9768,12 @@
         <v>0.1852</v>
       </c>
       <c r="G301" s="1" t="n">
-        <v>0.1852</v>
+        <v>0.1855</v>
       </c>
       <c r="H301" s="1" t="n">
+        <v>0.1855</v>
+      </c>
+      <c r="I301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -8893,9 +9799,12 @@
         <v>0.0076</v>
       </c>
       <c r="G302" s="1" t="n">
-        <v>0.0076</v>
+        <v>0.00765</v>
       </c>
       <c r="H302" s="1" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -8921,10 +9830,13 @@
         <v>0.0002159</v>
       </c>
       <c r="G303" s="1" t="n">
+        <v>0.0002151</v>
+      </c>
+      <c r="H303" s="1" t="n">
         <v>0.0002171</v>
       </c>
-      <c r="H303" s="1" t="n">
-        <v>0.0002159</v>
+      <c r="I303" s="1" t="n">
+        <v>0.0002151</v>
       </c>
     </row>
     <row r="304">
@@ -8949,9 +9861,12 @@
         <v>0.01542</v>
       </c>
       <c r="G304" s="1" t="n">
-        <v>0.01549</v>
+        <v>0.01553</v>
       </c>
       <c r="H304" s="1" t="n">
+        <v>0.01553</v>
+      </c>
+      <c r="I304" s="1" t="n">
         <v>0.01542</v>
       </c>
     </row>
@@ -8977,9 +9892,12 @@
         <v>0.07384</v>
       </c>
       <c r="G305" s="1" t="n">
+        <v>0.07386</v>
+      </c>
+      <c r="H305" s="1" t="n">
         <v>0.07394000000000001</v>
       </c>
-      <c r="H305" s="1" t="n">
+      <c r="I305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -9005,9 +9923,12 @@
         <v>0.08291999999999999</v>
       </c>
       <c r="G306" s="1" t="n">
-        <v>0.08291999999999999</v>
+        <v>0.08301</v>
       </c>
       <c r="H306" s="1" t="n">
+        <v>0.08301</v>
+      </c>
+      <c r="I306" s="1" t="n">
         <v>0.08275</v>
       </c>
     </row>
@@ -9033,9 +9954,12 @@
         <v>0.01808</v>
       </c>
       <c r="G307" s="1" t="n">
+        <v>0.01809</v>
+      </c>
+      <c r="H307" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="H307" s="1" t="n">
+      <c r="I307" s="1" t="n">
         <v>0.01808</v>
       </c>
     </row>
@@ -9061,9 +9985,12 @@
         <v>0.0006212</v>
       </c>
       <c r="G308" s="1" t="n">
+        <v>0.0006243000000000001</v>
+      </c>
+      <c r="H308" s="1" t="n">
         <v>0.0006255</v>
       </c>
-      <c r="H308" s="1" t="n">
+      <c r="I308" s="1" t="n">
         <v>0.0006212</v>
       </c>
     </row>
@@ -9089,10 +10016,13 @@
         <v>0.08243</v>
       </c>
       <c r="G309" s="1" t="n">
+        <v>0.0824</v>
+      </c>
+      <c r="H309" s="1" t="n">
         <v>0.08294</v>
       </c>
-      <c r="H309" s="1" t="n">
-        <v>0.08243</v>
+      <c r="I309" s="1" t="n">
+        <v>0.0824</v>
       </c>
     </row>
     <row r="310">
@@ -9117,9 +10047,12 @@
         <v>0.0973</v>
       </c>
       <c r="G310" s="1" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="H310" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="H310" s="1" t="n">
+      <c r="I310" s="1" t="n">
         <v>0.0973</v>
       </c>
     </row>
@@ -9145,9 +10078,12 @@
         <v>0.2109</v>
       </c>
       <c r="G311" s="1" t="n">
-        <v>0.2113</v>
+        <v>0.2119</v>
       </c>
       <c r="H311" s="1" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="I311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -9173,9 +10109,12 @@
         <v>0.3895</v>
       </c>
       <c r="G312" s="1" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="H312" s="1" t="n">
         <v>0.394</v>
       </c>
-      <c r="H312" s="1" t="n">
+      <c r="I312" s="1" t="n">
         <v>0.387</v>
       </c>
     </row>
@@ -9201,9 +10140,12 @@
         <v>0.10537</v>
       </c>
       <c r="G313" s="1" t="n">
+        <v>0.10539</v>
+      </c>
+      <c r="H313" s="1" t="n">
         <v>0.10542</v>
       </c>
-      <c r="H313" s="1" t="n">
+      <c r="I313" s="1" t="n">
         <v>0.10492</v>
       </c>
     </row>
@@ -9229,9 +10171,12 @@
         <v>0.08554</v>
       </c>
       <c r="G314" s="1" t="n">
-        <v>0.08575000000000001</v>
+        <v>0.08618000000000001</v>
       </c>
       <c r="H314" s="1" t="n">
+        <v>0.08618000000000001</v>
+      </c>
+      <c r="I314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -9257,9 +10202,12 @@
         <v>0.1179</v>
       </c>
       <c r="G315" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="H315" s="1" t="n">
         <v>0.1185</v>
       </c>
-      <c r="H315" s="1" t="n">
+      <c r="I315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -9285,9 +10233,12 @@
         <v>0.03632</v>
       </c>
       <c r="G316" s="1" t="n">
+        <v>0.03643</v>
+      </c>
+      <c r="H316" s="1" t="n">
         <v>0.03681</v>
       </c>
-      <c r="H316" s="1" t="n">
+      <c r="I316" s="1" t="n">
         <v>0.03628</v>
       </c>
     </row>
@@ -9313,9 +10264,12 @@
         <v>0.08085000000000001</v>
       </c>
       <c r="G317" s="1" t="n">
-        <v>0.08125</v>
+        <v>0.08133</v>
       </c>
       <c r="H317" s="1" t="n">
+        <v>0.08133</v>
+      </c>
+      <c r="I317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -9341,9 +10295,12 @@
         <v>0.03761</v>
       </c>
       <c r="G318" s="1" t="n">
+        <v>0.03759</v>
+      </c>
+      <c r="H318" s="1" t="n">
         <v>0.03766</v>
       </c>
-      <c r="H318" s="1" t="n">
+      <c r="I318" s="1" t="n">
         <v>0.03736</v>
       </c>
     </row>
@@ -9369,10 +10326,13 @@
         <v>0.4308</v>
       </c>
       <c r="G319" s="1" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="H319" s="1" t="n">
         <v>0.4347</v>
       </c>
-      <c r="H319" s="1" t="n">
-        <v>0.4308</v>
+      <c r="I319" s="1" t="n">
+        <v>0.4303</v>
       </c>
     </row>
     <row r="320">
@@ -9397,9 +10357,12 @@
         <v>0.16</v>
       </c>
       <c r="G320" s="1" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="H320" s="1" t="n">
         <v>0.1614</v>
       </c>
-      <c r="H320" s="1" t="n">
+      <c r="I320" s="1" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -9425,9 +10388,12 @@
         <v>5.681</v>
       </c>
       <c r="G321" s="1" t="n">
+        <v>5.679</v>
+      </c>
+      <c r="H321" s="1" t="n">
         <v>5.681</v>
       </c>
-      <c r="H321" s="1" t="n">
+      <c r="I321" s="1" t="n">
         <v>5.677</v>
       </c>
     </row>
@@ -9453,9 +10419,12 @@
         <v>0.003746</v>
       </c>
       <c r="G322" s="1" t="n">
+        <v>0.003727</v>
+      </c>
+      <c r="H322" s="1" t="n">
         <v>0.003746</v>
       </c>
-      <c r="H322" s="1" t="n">
+      <c r="I322" s="1" t="n">
         <v>0.003715</v>
       </c>
     </row>
@@ -9481,9 +10450,12 @@
         <v>0.001754</v>
       </c>
       <c r="G323" s="1" t="n">
-        <v>0.001757</v>
+        <v>0.001761</v>
       </c>
       <c r="H323" s="1" t="n">
+        <v>0.001761</v>
+      </c>
+      <c r="I323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -9509,9 +10481,12 @@
         <v>1.19e-05</v>
       </c>
       <c r="G324" s="1" t="n">
+        <v>1.19e-05</v>
+      </c>
+      <c r="H324" s="1" t="n">
         <v>1.2e-05</v>
       </c>
-      <c r="H324" s="1" t="n">
+      <c r="I324" s="1" t="n">
         <v>1.19e-05</v>
       </c>
     </row>
@@ -9537,9 +10512,12 @@
         <v>0.0857</v>
       </c>
       <c r="G325" s="1" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="H325" s="1" t="n">
         <v>0.08649999999999999</v>
       </c>
-      <c r="H325" s="1" t="n">
+      <c r="I325" s="1" t="n">
         <v>0.0857</v>
       </c>
     </row>
@@ -9565,9 +10543,12 @@
         <v>0.01732</v>
       </c>
       <c r="G326" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="H326" s="1" t="n">
         <v>0.01736</v>
       </c>
-      <c r="H326" s="1" t="n">
+      <c r="I326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -9593,9 +10574,12 @@
         <v>0.01682</v>
       </c>
       <c r="G327" s="1" t="n">
+        <v>0.01686</v>
+      </c>
+      <c r="H327" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="H327" s="1" t="n">
+      <c r="I327" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -9621,9 +10605,12 @@
         <v>4.448</v>
       </c>
       <c r="G328" s="1" t="n">
+        <v>4.459</v>
+      </c>
+      <c r="H328" s="1" t="n">
         <v>4.462</v>
       </c>
-      <c r="H328" s="1" t="n">
+      <c r="I328" s="1" t="n">
         <v>4.446</v>
       </c>
     </row>
@@ -9649,9 +10636,12 @@
         <v>0.009573999999999999</v>
       </c>
       <c r="G329" s="1" t="n">
+        <v>0.009629</v>
+      </c>
+      <c r="H329" s="1" t="n">
         <v>0.009861</v>
       </c>
-      <c r="H329" s="1" t="n">
+      <c r="I329" s="1" t="n">
         <v>0.009532000000000001</v>
       </c>
     </row>
@@ -9677,9 +10667,12 @@
         <v>5192.7</v>
       </c>
       <c r="G330" s="1" t="n">
+        <v>5189</v>
+      </c>
+      <c r="H330" s="1" t="n">
         <v>5192.9</v>
       </c>
-      <c r="H330" s="1" t="n">
+      <c r="I330" s="1" t="n">
         <v>5185.8</v>
       </c>
     </row>
@@ -9705,9 +10698,12 @@
         <v>0.07048</v>
       </c>
       <c r="G331" s="1" t="n">
+        <v>0.07054000000000001</v>
+      </c>
+      <c r="H331" s="1" t="n">
         <v>0.07087</v>
       </c>
-      <c r="H331" s="1" t="n">
+      <c r="I331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -9733,9 +10729,12 @@
         <v>0.0609</v>
       </c>
       <c r="G332" s="1" t="n">
-        <v>0.06098</v>
+        <v>0.06106</v>
       </c>
       <c r="H332" s="1" t="n">
+        <v>0.06106</v>
+      </c>
+      <c r="I332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -9761,9 +10760,12 @@
         <v>0.10344</v>
       </c>
       <c r="G333" s="1" t="n">
+        <v>0.10346</v>
+      </c>
+      <c r="H333" s="1" t="n">
         <v>0.10416</v>
       </c>
-      <c r="H333" s="1" t="n">
+      <c r="I333" s="1" t="n">
         <v>0.10344</v>
       </c>
     </row>
@@ -9789,9 +10791,12 @@
         <v>0.08734</v>
       </c>
       <c r="G334" s="1" t="n">
+        <v>0.08748</v>
+      </c>
+      <c r="H334" s="1" t="n">
         <v>0.08837</v>
       </c>
-      <c r="H334" s="1" t="n">
+      <c r="I334" s="1" t="n">
         <v>0.08734</v>
       </c>
     </row>
@@ -9817,9 +10822,12 @@
         <v>0.016413</v>
       </c>
       <c r="G335" s="1" t="n">
+        <v>0.016401</v>
+      </c>
+      <c r="H335" s="1" t="n">
         <v>0.016413</v>
       </c>
-      <c r="H335" s="1" t="n">
+      <c r="I335" s="1" t="n">
         <v>0.016391</v>
       </c>
     </row>
@@ -9845,9 +10853,12 @@
         <v>0.04588</v>
       </c>
       <c r="G336" s="1" t="n">
-        <v>0.04594</v>
+        <v>0.046</v>
       </c>
       <c r="H336" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="I336" s="1" t="n">
         <v>0.04583</v>
       </c>
     </row>
@@ -9873,9 +10884,12 @@
         <v>0.1845</v>
       </c>
       <c r="G337" s="1" t="n">
-        <v>0.1853</v>
+        <v>0.1858</v>
       </c>
       <c r="H337" s="1" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="I337" s="1" t="n">
         <v>0.1838</v>
       </c>
     </row>
@@ -9901,9 +10915,12 @@
         <v>0.1831</v>
       </c>
       <c r="G338" s="1" t="n">
+        <v>0.1832</v>
+      </c>
+      <c r="H338" s="1" t="n">
         <v>0.1836</v>
       </c>
-      <c r="H338" s="1" t="n">
+      <c r="I338" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -9929,9 +10946,12 @@
         <v>0.01835</v>
       </c>
       <c r="G339" s="1" t="n">
-        <v>0.01837</v>
+        <v>0.01838</v>
       </c>
       <c r="H339" s="1" t="n">
+        <v>0.01838</v>
+      </c>
+      <c r="I339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -9957,9 +10977,12 @@
         <v>0.02305</v>
       </c>
       <c r="G340" s="1" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="H340" s="1" t="n">
         <v>0.02311</v>
       </c>
-      <c r="H340" s="1" t="n">
+      <c r="I340" s="1" t="n">
         <v>0.02305</v>
       </c>
     </row>
@@ -9985,9 +11008,12 @@
         <v>0.4541</v>
       </c>
       <c r="G341" s="1" t="n">
-        <v>0.455</v>
+        <v>0.4562</v>
       </c>
       <c r="H341" s="1" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="I341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -10013,9 +11039,12 @@
         <v>0.01341</v>
       </c>
       <c r="G342" s="1" t="n">
-        <v>0.01344</v>
+        <v>0.01347</v>
       </c>
       <c r="H342" s="1" t="n">
+        <v>0.01347</v>
+      </c>
+      <c r="I342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -10041,10 +11070,13 @@
         <v>2.886</v>
       </c>
       <c r="G343" s="1" t="n">
+        <v>2.872</v>
+      </c>
+      <c r="H343" s="1" t="n">
         <v>2.89</v>
       </c>
-      <c r="H343" s="1" t="n">
-        <v>2.874</v>
+      <c r="I343" s="1" t="n">
+        <v>2.872</v>
       </c>
     </row>
     <row r="344">
@@ -10069,9 +11101,12 @@
         <v>0.1534</v>
       </c>
       <c r="G344" s="1" t="n">
+        <v>0.1552</v>
+      </c>
+      <c r="H344" s="1" t="n">
         <v>0.1577</v>
       </c>
-      <c r="H344" s="1" t="n">
+      <c r="I344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -10097,9 +11132,12 @@
         <v>0.005344</v>
       </c>
       <c r="G345" s="1" t="n">
+        <v>0.005363</v>
+      </c>
+      <c r="H345" s="1" t="n">
         <v>0.005367</v>
       </c>
-      <c r="H345" s="1" t="n">
+      <c r="I345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -10125,9 +11163,12 @@
         <v>0.05768</v>
       </c>
       <c r="G346" s="1" t="n">
-        <v>0.05781</v>
+        <v>0.0579</v>
       </c>
       <c r="H346" s="1" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="I346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -10153,9 +11194,12 @@
         <v>2601</v>
       </c>
       <c r="G347" s="1" t="n">
-        <v>2606</v>
+        <v>2612</v>
       </c>
       <c r="H347" s="1" t="n">
+        <v>2612</v>
+      </c>
+      <c r="I347" s="1" t="n">
         <v>2597</v>
       </c>
     </row>
@@ -10181,9 +11225,12 @@
         <v>0.04596</v>
       </c>
       <c r="G348" s="1" t="n">
+        <v>0.04601</v>
+      </c>
+      <c r="H348" s="1" t="n">
         <v>0.04621</v>
       </c>
-      <c r="H348" s="1" t="n">
+      <c r="I348" s="1" t="n">
         <v>0.04595</v>
       </c>
     </row>
@@ -10209,10 +11256,13 @@
         <v>0.005714</v>
       </c>
       <c r="G349" s="1" t="n">
+        <v>0.005667</v>
+      </c>
+      <c r="H349" s="1" t="n">
         <v>0.005714</v>
       </c>
-      <c r="H349" s="1" t="n">
-        <v>0.005676</v>
+      <c r="I349" s="1" t="n">
+        <v>0.005667</v>
       </c>
     </row>
     <row r="350">
@@ -10237,9 +11287,12 @@
         <v>195.26</v>
       </c>
       <c r="G350" s="1" t="n">
+        <v>195.35</v>
+      </c>
+      <c r="H350" s="1" t="n">
         <v>195.51</v>
       </c>
-      <c r="H350" s="1" t="n">
+      <c r="I350" s="1" t="n">
         <v>195.23</v>
       </c>
     </row>
@@ -10265,9 +11318,12 @@
         <v>0.08207</v>
       </c>
       <c r="G351" s="1" t="n">
-        <v>0.08237999999999999</v>
+        <v>0.08245</v>
       </c>
       <c r="H351" s="1" t="n">
+        <v>0.08245</v>
+      </c>
+      <c r="I351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -10293,9 +11349,12 @@
         <v>0.00746</v>
       </c>
       <c r="G352" s="1" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H352" s="1" t="n">
         <v>0.007571</v>
       </c>
-      <c r="H352" s="1" t="n">
+      <c r="I352" s="1" t="n">
         <v>0.007458</v>
       </c>
     </row>
@@ -10321,9 +11380,12 @@
         <v>1.5087</v>
       </c>
       <c r="G353" s="1" t="n">
-        <v>1.5087</v>
+        <v>1.5217</v>
       </c>
       <c r="H353" s="1" t="n">
+        <v>1.5217</v>
+      </c>
+      <c r="I353" s="1" t="n">
         <v>1.4807</v>
       </c>
     </row>
@@ -10349,9 +11411,12 @@
         <v>0.07629</v>
       </c>
       <c r="G354" s="1" t="n">
-        <v>0.07643999999999999</v>
+        <v>0.07655000000000001</v>
       </c>
       <c r="H354" s="1" t="n">
+        <v>0.07655000000000001</v>
+      </c>
+      <c r="I354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -10377,10 +11442,13 @@
         <v>0.04874</v>
       </c>
       <c r="G355" s="1" t="n">
+        <v>0.04859</v>
+      </c>
+      <c r="H355" s="1" t="n">
         <v>0.04921</v>
       </c>
-      <c r="H355" s="1" t="n">
-        <v>0.04874</v>
+      <c r="I355" s="1" t="n">
+        <v>0.04859</v>
       </c>
     </row>
     <row r="356">
@@ -10405,9 +11473,12 @@
         <v>0.2857</v>
       </c>
       <c r="G356" s="1" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="H356" s="1" t="n">
         <v>0.2861</v>
       </c>
-      <c r="H356" s="1" t="n">
+      <c r="I356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -10433,9 +11504,12 @@
         <v>0.1463</v>
       </c>
       <c r="G357" s="1" t="n">
+        <v>0.1466</v>
+      </c>
+      <c r="H357" s="1" t="n">
         <v>0.1467</v>
       </c>
-      <c r="H357" s="1" t="n">
+      <c r="I357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -10461,9 +11535,12 @@
         <v>1.352</v>
       </c>
       <c r="G358" s="1" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="H358" s="1" t="n">
         <v>1.355</v>
       </c>
-      <c r="H358" s="1" t="n">
+      <c r="I358" s="1" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -10489,9 +11566,12 @@
         <v>0.6081</v>
       </c>
       <c r="G359" s="1" t="n">
+        <v>0.6094000000000001</v>
+      </c>
+      <c r="H359" s="1" t="n">
         <v>0.6117</v>
       </c>
-      <c r="H359" s="1" t="n">
+      <c r="I359" s="1" t="n">
         <v>0.6081</v>
       </c>
     </row>
@@ -10517,9 +11597,12 @@
         <v>0.1144</v>
       </c>
       <c r="G360" s="1" t="n">
-        <v>0.1145</v>
+        <v>0.1146</v>
       </c>
       <c r="H360" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="I360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -10545,9 +11628,12 @@
         <v>0.02631</v>
       </c>
       <c r="G361" s="1" t="n">
-        <v>0.02631</v>
+        <v>0.02632</v>
       </c>
       <c r="H361" s="1" t="n">
+        <v>0.02632</v>
+      </c>
+      <c r="I361" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -10576,6 +11662,9 @@
         <v>3.04e-05</v>
       </c>
       <c r="H362" s="1" t="n">
+        <v>3.04e-05</v>
+      </c>
+      <c r="I362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -10604,6 +11693,9 @@
         <v>0.01026</v>
       </c>
       <c r="H363" s="1" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="I363" s="1" t="n">
         <v>0.01018</v>
       </c>
     </row>
@@ -10629,9 +11721,12 @@
         <v>0.06206</v>
       </c>
       <c r="G364" s="1" t="n">
-        <v>0.06208</v>
+        <v>0.0622</v>
       </c>
       <c r="H364" s="1" t="n">
+        <v>0.0622</v>
+      </c>
+      <c r="I364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -10657,9 +11752,12 @@
         <v>0.03295</v>
       </c>
       <c r="G365" s="1" t="n">
+        <v>0.03287</v>
+      </c>
+      <c r="H365" s="1" t="n">
         <v>0.03297</v>
       </c>
-      <c r="H365" s="1" t="n">
+      <c r="I365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -10685,9 +11783,12 @@
         <v>0.03283</v>
       </c>
       <c r="G366" s="1" t="n">
+        <v>0.03288</v>
+      </c>
+      <c r="H366" s="1" t="n">
         <v>0.03296</v>
       </c>
-      <c r="H366" s="1" t="n">
+      <c r="I366" s="1" t="n">
         <v>0.03283</v>
       </c>
     </row>
@@ -10713,9 +11814,12 @@
         <v>0.012215</v>
       </c>
       <c r="G367" s="1" t="n">
-        <v>0.012215</v>
+        <v>0.012224</v>
       </c>
       <c r="H367" s="1" t="n">
+        <v>0.012224</v>
+      </c>
+      <c r="I367" s="1" t="n">
         <v>0.012155</v>
       </c>
     </row>
@@ -10741,9 +11845,12 @@
         <v>0.03547</v>
       </c>
       <c r="G368" s="1" t="n">
+        <v>0.03539</v>
+      </c>
+      <c r="H368" s="1" t="n">
         <v>0.03559</v>
       </c>
-      <c r="H368" s="1" t="n">
+      <c r="I368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -10769,9 +11876,12 @@
         <v>0.6261</v>
       </c>
       <c r="G369" s="1" t="n">
-        <v>0.6261</v>
+        <v>0.6307</v>
       </c>
       <c r="H369" s="1" t="n">
+        <v>0.6307</v>
+      </c>
+      <c r="I369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -10797,9 +11907,12 @@
         <v>0.008630000000000001</v>
       </c>
       <c r="G370" s="1" t="n">
-        <v>0.008630000000000001</v>
+        <v>0.00876</v>
       </c>
       <c r="H370" s="1" t="n">
+        <v>0.00876</v>
+      </c>
+      <c r="I370" s="1" t="n">
         <v>0.00843</v>
       </c>
     </row>
@@ -10825,9 +11938,12 @@
         <v>0.00328</v>
       </c>
       <c r="G371" s="1" t="n">
-        <v>0.003288</v>
+        <v>0.003289</v>
       </c>
       <c r="H371" s="1" t="n">
+        <v>0.003289</v>
+      </c>
+      <c r="I371" s="1" t="n">
         <v>0.003242</v>
       </c>
     </row>
@@ -10853,9 +11969,12 @@
         <v>0.13278</v>
       </c>
       <c r="G372" s="1" t="n">
-        <v>0.13301</v>
+        <v>0.13361</v>
       </c>
       <c r="H372" s="1" t="n">
+        <v>0.13361</v>
+      </c>
+      <c r="I372" s="1" t="n">
         <v>0.13227</v>
       </c>
     </row>
@@ -10881,9 +12000,12 @@
         <v>0.007771</v>
       </c>
       <c r="G373" s="1" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="H373" s="1" t="n">
         <v>0.007822000000000001</v>
       </c>
-      <c r="H373" s="1" t="n">
+      <c r="I373" s="1" t="n">
         <v>0.007771</v>
       </c>
     </row>
@@ -10909,9 +12031,12 @@
         <v>0.01969</v>
       </c>
       <c r="G374" s="1" t="n">
+        <v>0.01975</v>
+      </c>
+      <c r="H374" s="1" t="n">
         <v>0.01978</v>
       </c>
-      <c r="H374" s="1" t="n">
+      <c r="I374" s="1" t="n">
         <v>0.01969</v>
       </c>
     </row>
@@ -10937,9 +12062,12 @@
         <v>0.0005910000000000001</v>
       </c>
       <c r="G375" s="1" t="n">
+        <v>0.0005925</v>
+      </c>
+      <c r="H375" s="1" t="n">
         <v>0.000594</v>
       </c>
-      <c r="H375" s="1" t="n">
+      <c r="I375" s="1" t="n">
         <v>0.0005910000000000001</v>
       </c>
     </row>
@@ -10965,9 +12093,12 @@
         <v>0.0363</v>
       </c>
       <c r="G376" s="1" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="H376" s="1" t="n">
         <v>0.0363</v>
       </c>
-      <c r="H376" s="1" t="n">
+      <c r="I376" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -10993,9 +12124,12 @@
         <v>0.0007906</v>
       </c>
       <c r="G377" s="1" t="n">
+        <v>0.0007917</v>
+      </c>
+      <c r="H377" s="1" t="n">
         <v>0.000792</v>
       </c>
-      <c r="H377" s="1" t="n">
+      <c r="I377" s="1" t="n">
         <v>0.0007848</v>
       </c>
     </row>
@@ -11021,9 +12155,12 @@
         <v>1.988</v>
       </c>
       <c r="G378" s="1" t="n">
-        <v>1.99</v>
+        <v>2.008</v>
       </c>
       <c r="H378" s="1" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="I378" s="1" t="n">
         <v>1.973</v>
       </c>
     </row>
@@ -11049,9 +12186,12 @@
         <v>0.0005881</v>
       </c>
       <c r="G379" s="1" t="n">
+        <v>0.0005891</v>
+      </c>
+      <c r="H379" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="H379" s="1" t="n">
+      <c r="I379" s="1" t="n">
         <v>0.0005881</v>
       </c>
     </row>
@@ -11077,9 +12217,12 @@
         <v>0.03751</v>
       </c>
       <c r="G380" s="1" t="n">
+        <v>0.03746</v>
+      </c>
+      <c r="H380" s="1" t="n">
         <v>0.03751</v>
       </c>
-      <c r="H380" s="1" t="n">
+      <c r="I380" s="1" t="n">
         <v>0.03737</v>
       </c>
     </row>
@@ -11105,9 +12248,12 @@
         <v>0.05462</v>
       </c>
       <c r="G381" s="1" t="n">
-        <v>0.05477</v>
+        <v>0.05481</v>
       </c>
       <c r="H381" s="1" t="n">
+        <v>0.05481</v>
+      </c>
+      <c r="I381" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -11133,9 +12279,12 @@
         <v>0.01204</v>
       </c>
       <c r="G382" s="1" t="n">
-        <v>0.01207</v>
+        <v>0.01213</v>
       </c>
       <c r="H382" s="1" t="n">
+        <v>0.01213</v>
+      </c>
+      <c r="I382" s="1" t="n">
         <v>0.01202</v>
       </c>
     </row>
@@ -11161,9 +12310,12 @@
         <v>0.001551</v>
       </c>
       <c r="G383" s="1" t="n">
+        <v>0.001554</v>
+      </c>
+      <c r="H383" s="1" t="n">
         <v>0.001559</v>
       </c>
-      <c r="H383" s="1" t="n">
+      <c r="I383" s="1" t="n">
         <v>0.001551</v>
       </c>
     </row>
@@ -11189,9 +12341,12 @@
         <v>0.0002158</v>
       </c>
       <c r="G384" s="1" t="n">
-        <v>0.0002158</v>
+        <v>0.0002164</v>
       </c>
       <c r="H384" s="1" t="n">
+        <v>0.0002164</v>
+      </c>
+      <c r="I384" s="1" t="n">
         <v>0.0002154</v>
       </c>
     </row>
@@ -11217,9 +12372,12 @@
         <v>0.0024</v>
       </c>
       <c r="G385" s="1" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="H385" s="1" t="n">
         <v>0.00242</v>
       </c>
-      <c r="H385" s="1" t="n">
+      <c r="I385" s="1" t="n">
         <v>0.0024</v>
       </c>
     </row>
@@ -11245,9 +12403,12 @@
         <v>3.906</v>
       </c>
       <c r="G386" s="1" t="n">
-        <v>3.908</v>
+        <v>3.933</v>
       </c>
       <c r="H386" s="1" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="I386" s="1" t="n">
         <v>3.892</v>
       </c>
     </row>
@@ -11273,9 +12434,12 @@
         <v>0.0006236</v>
       </c>
       <c r="G387" s="1" t="n">
-        <v>0.0006254</v>
+        <v>0.0006282</v>
       </c>
       <c r="H387" s="1" t="n">
+        <v>0.0006282</v>
+      </c>
+      <c r="I387" s="1" t="n">
         <v>0.0006236</v>
       </c>
     </row>
@@ -11301,9 +12465,12 @@
         <v>0.00663</v>
       </c>
       <c r="G388" s="1" t="n">
-        <v>0.00664</v>
+        <v>0.00673</v>
       </c>
       <c r="H388" s="1" t="n">
+        <v>0.00673</v>
+      </c>
+      <c r="I388" s="1" t="n">
         <v>0.00653</v>
       </c>
     </row>
@@ -11329,9 +12496,12 @@
         <v>0.1319</v>
       </c>
       <c r="G389" s="1" t="n">
-        <v>0.1319</v>
+        <v>0.132</v>
       </c>
       <c r="H389" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="I389" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -11357,9 +12527,12 @@
         <v>0.0324</v>
       </c>
       <c r="G390" s="1" t="n">
+        <v>0.03223</v>
+      </c>
+      <c r="H390" s="1" t="n">
         <v>0.0324</v>
       </c>
-      <c r="H390" s="1" t="n">
+      <c r="I390" s="1" t="n">
         <v>0.03201</v>
       </c>
     </row>
@@ -11385,9 +12558,12 @@
         <v>0.06344</v>
       </c>
       <c r="G391" s="1" t="n">
-        <v>0.06362</v>
+        <v>0.06372</v>
       </c>
       <c r="H391" s="1" t="n">
+        <v>0.06372</v>
+      </c>
+      <c r="I391" s="1" t="n">
         <v>0.06344</v>
       </c>
     </row>
@@ -11413,9 +12589,12 @@
         <v>27.57</v>
       </c>
       <c r="G392" s="1" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="H392" s="1" t="n">
         <v>27.82</v>
       </c>
-      <c r="H392" s="1" t="n">
+      <c r="I392" s="1" t="n">
         <v>27.57</v>
       </c>
     </row>
@@ -11441,9 +12620,12 @@
         <v>0.000413</v>
       </c>
       <c r="G393" s="1" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="H393" s="1" t="n">
         <v>0.000414</v>
       </c>
-      <c r="H393" s="1" t="n">
+      <c r="I393" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -11469,9 +12651,12 @@
         <v>0.06961000000000001</v>
       </c>
       <c r="G394" s="1" t="n">
+        <v>0.06962</v>
+      </c>
+      <c r="H394" s="1" t="n">
         <v>0.07005</v>
       </c>
-      <c r="H394" s="1" t="n">
+      <c r="I394" s="1" t="n">
         <v>0.06926</v>
       </c>
     </row>
@@ -11497,9 +12682,12 @@
         <v>0.2592</v>
       </c>
       <c r="G395" s="1" t="n">
-        <v>0.2592</v>
+        <v>0.2611</v>
       </c>
       <c r="H395" s="1" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="I395" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -11525,9 +12713,12 @@
         <v>0.004678</v>
       </c>
       <c r="G396" s="1" t="n">
+        <v>0.004681</v>
+      </c>
+      <c r="H396" s="1" t="n">
         <v>0.00469</v>
       </c>
-      <c r="H396" s="1" t="n">
+      <c r="I396" s="1" t="n">
         <v>0.004677</v>
       </c>
     </row>
@@ -11553,9 +12744,12 @@
         <v>0.2352</v>
       </c>
       <c r="G397" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="H397" s="1" t="n">
         <v>0.2352</v>
       </c>
-      <c r="H397" s="1" t="n">
+      <c r="I397" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
@@ -11581,9 +12775,12 @@
         <v>0.18123</v>
       </c>
       <c r="G398" s="1" t="n">
+        <v>0.18123</v>
+      </c>
+      <c r="H398" s="1" t="n">
         <v>0.18131</v>
       </c>
-      <c r="H398" s="1" t="n">
+      <c r="I398" s="1" t="n">
         <v>0.18106</v>
       </c>
     </row>
@@ -11609,9 +12806,12 @@
         <v>0.04119</v>
       </c>
       <c r="G399" s="1" t="n">
-        <v>0.04124</v>
+        <v>0.04126</v>
       </c>
       <c r="H399" s="1" t="n">
+        <v>0.04126</v>
+      </c>
+      <c r="I399" s="1" t="n">
         <v>0.04108</v>
       </c>
     </row>
@@ -11637,9 +12837,12 @@
         <v>0.075</v>
       </c>
       <c r="G400" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H400" s="1" t="n">
         <v>0.076</v>
       </c>
-      <c r="H400" s="1" t="n">
+      <c r="I400" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -11665,9 +12868,12 @@
         <v>0.001743</v>
       </c>
       <c r="G401" s="1" t="n">
-        <v>0.001751</v>
+        <v>0.001759</v>
       </c>
       <c r="H401" s="1" t="n">
+        <v>0.001759</v>
+      </c>
+      <c r="I401" s="1" t="n">
         <v>0.001739</v>
       </c>
     </row>
@@ -11693,9 +12899,12 @@
         <v>0.05394</v>
       </c>
       <c r="G402" s="1" t="n">
-        <v>0.05394</v>
+        <v>0.05401</v>
       </c>
       <c r="H402" s="1" t="n">
+        <v>0.05401</v>
+      </c>
+      <c r="I402" s="1" t="n">
         <v>0.05362</v>
       </c>
     </row>
@@ -11721,9 +12930,12 @@
         <v>2028.07</v>
       </c>
       <c r="G403" s="1" t="n">
+        <v>2027.65</v>
+      </c>
+      <c r="H403" s="1" t="n">
         <v>2031.8</v>
       </c>
-      <c r="H403" s="1" t="n">
+      <c r="I403" s="1" t="n">
         <v>2027.43</v>
       </c>
     </row>
@@ -11749,9 +12961,12 @@
         <v>1.078</v>
       </c>
       <c r="G404" s="1" t="n">
+        <v>1.079</v>
+      </c>
+      <c r="H404" s="1" t="n">
         <v>1.082</v>
       </c>
-      <c r="H404" s="1" t="n">
+      <c r="I404" s="1" t="n">
         <v>1.078</v>
       </c>
     </row>
@@ -11777,9 +12992,12 @@
         <v>7.649</v>
       </c>
       <c r="G405" s="1" t="n">
+        <v>7.661</v>
+      </c>
+      <c r="H405" s="1" t="n">
         <v>7.662</v>
       </c>
-      <c r="H405" s="1" t="n">
+      <c r="I405" s="1" t="n">
         <v>7.649</v>
       </c>
     </row>
@@ -11805,9 +13023,12 @@
         <v>3.253</v>
       </c>
       <c r="G406" s="1" t="n">
+        <v>3.253</v>
+      </c>
+      <c r="H406" s="1" t="n">
         <v>3.257</v>
       </c>
-      <c r="H406" s="1" t="n">
+      <c r="I406" s="1" t="n">
         <v>3.238</v>
       </c>
     </row>
@@ -11833,9 +13054,12 @@
         <v>0.1818</v>
       </c>
       <c r="G407" s="1" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="H407" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="H407" s="1" t="n">
+      <c r="I407" s="1" t="n">
         <v>0.1814</v>
       </c>
     </row>
@@ -11861,9 +13085,12 @@
         <v>0.1526</v>
       </c>
       <c r="G408" s="1" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="H408" s="1" t="n">
         <v>0.1537</v>
       </c>
-      <c r="H408" s="1" t="n">
+      <c r="I408" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -11889,9 +13116,12 @@
         <v>0.07335999999999999</v>
       </c>
       <c r="G409" s="1" t="n">
-        <v>0.07346999999999999</v>
+        <v>0.0735</v>
       </c>
       <c r="H409" s="1" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="I409" s="1" t="n">
         <v>0.07315000000000001</v>
       </c>
     </row>
@@ -11917,9 +13147,12 @@
         <v>0.02104</v>
       </c>
       <c r="G410" s="1" t="n">
+        <v>0.02101</v>
+      </c>
+      <c r="H410" s="1" t="n">
         <v>0.02118</v>
       </c>
-      <c r="H410" s="1" t="n">
+      <c r="I410" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -11945,9 +13178,12 @@
         <v>0.2669</v>
       </c>
       <c r="G411" s="1" t="n">
-        <v>0.2669</v>
+        <v>0.2675</v>
       </c>
       <c r="H411" s="1" t="n">
+        <v>0.2675</v>
+      </c>
+      <c r="I411" s="1" t="n">
         <v>0.2642</v>
       </c>
     </row>
@@ -11973,9 +13209,12 @@
         <v>0.00735</v>
       </c>
       <c r="G412" s="1" t="n">
+        <v>0.00737</v>
+      </c>
+      <c r="H412" s="1" t="n">
         <v>0.007383</v>
       </c>
-      <c r="H412" s="1" t="n">
+      <c r="I412" s="1" t="n">
         <v>0.007302</v>
       </c>
     </row>
@@ -12001,9 +13240,12 @@
         <v>0.01384</v>
       </c>
       <c r="G413" s="1" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="H413" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="H413" s="1" t="n">
+      <c r="I413" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -12032,6 +13274,9 @@
         <v>0.093</v>
       </c>
       <c r="H414" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="I414" s="1" t="n">
         <v>0.092</v>
       </c>
     </row>
@@ -12057,10 +13302,13 @@
         <v>0.04012</v>
       </c>
       <c r="G415" s="1" t="n">
+        <v>0.03985</v>
+      </c>
+      <c r="H415" s="1" t="n">
         <v>0.04012</v>
       </c>
-      <c r="H415" s="1" t="n">
-        <v>0.03998</v>
+      <c r="I415" s="1" t="n">
+        <v>0.03985</v>
       </c>
     </row>
     <row r="416">
@@ -12085,9 +13333,12 @@
         <v>0.2841</v>
       </c>
       <c r="G416" s="1" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="H416" s="1" t="n">
         <v>0.2854</v>
       </c>
-      <c r="H416" s="1" t="n">
+      <c r="I416" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -12113,9 +13364,12 @@
         <v>1.826</v>
       </c>
       <c r="G417" s="1" t="n">
-        <v>1.826</v>
+        <v>1.831</v>
       </c>
       <c r="H417" s="1" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="I417" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -12141,9 +13395,12 @@
         <v>0.06668</v>
       </c>
       <c r="G418" s="1" t="n">
+        <v>0.06689000000000001</v>
+      </c>
+      <c r="H418" s="1" t="n">
         <v>0.06707</v>
       </c>
-      <c r="H418" s="1" t="n">
+      <c r="I418" s="1" t="n">
         <v>0.06668</v>
       </c>
     </row>
@@ -12169,9 +13426,12 @@
         <v>207.39</v>
       </c>
       <c r="G419" s="1" t="n">
+        <v>207.38</v>
+      </c>
+      <c r="H419" s="1" t="n">
         <v>207.46</v>
       </c>
-      <c r="H419" s="1" t="n">
+      <c r="I419" s="1" t="n">
         <v>207.35</v>
       </c>
     </row>
@@ -12197,9 +13457,12 @@
         <v>73.31999999999999</v>
       </c>
       <c r="G420" s="1" t="n">
+        <v>73.23</v>
+      </c>
+      <c r="H420" s="1" t="n">
         <v>73.31999999999999</v>
       </c>
-      <c r="H420" s="1" t="n">
+      <c r="I420" s="1" t="n">
         <v>73.15000000000001</v>
       </c>
     </row>
@@ -12225,9 +13488,12 @@
         <v>0.07226</v>
       </c>
       <c r="G421" s="1" t="n">
+        <v>0.07228999999999999</v>
+      </c>
+      <c r="H421" s="1" t="n">
         <v>0.07251000000000001</v>
       </c>
-      <c r="H421" s="1" t="n">
+      <c r="I421" s="1" t="n">
         <v>0.07226</v>
       </c>
     </row>
@@ -12253,9 +13519,12 @@
         <v>0.05041</v>
       </c>
       <c r="G422" s="1" t="n">
-        <v>0.05041</v>
+        <v>0.05076</v>
       </c>
       <c r="H422" s="1" t="n">
+        <v>0.05076</v>
+      </c>
+      <c r="I422" s="1" t="n">
         <v>0.04998</v>
       </c>
     </row>
@@ -12281,9 +13550,12 @@
         <v>0.00115</v>
       </c>
       <c r="G423" s="1" t="n">
-        <v>0.00115</v>
+        <v>0.001152</v>
       </c>
       <c r="H423" s="1" t="n">
+        <v>0.001152</v>
+      </c>
+      <c r="I423" s="1" t="n">
         <v>0.001148</v>
       </c>
     </row>
@@ -12309,9 +13581,12 @@
         <v>0.00501</v>
       </c>
       <c r="G424" s="1" t="n">
+        <v>0.00503</v>
+      </c>
+      <c r="H424" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="H424" s="1" t="n">
+      <c r="I424" s="1" t="n">
         <v>0.00501</v>
       </c>
     </row>
@@ -12337,9 +13612,12 @@
         <v>0.1269</v>
       </c>
       <c r="G425" s="1" t="n">
-        <v>0.1269</v>
+        <v>0.1274</v>
       </c>
       <c r="H425" s="1" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="I425" s="1" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -12365,9 +13643,12 @@
         <v>1.294</v>
       </c>
       <c r="G426" s="1" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="H426" s="1" t="n">
         <v>1.299</v>
       </c>
-      <c r="H426" s="1" t="n">
+      <c r="I426" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -12393,9 +13674,12 @@
         <v>0.0044</v>
       </c>
       <c r="G427" s="1" t="n">
+        <v>0.00441</v>
+      </c>
+      <c r="H427" s="1" t="n">
         <v>0.004413</v>
       </c>
-      <c r="H427" s="1" t="n">
+      <c r="I427" s="1" t="n">
         <v>0.004393</v>
       </c>
     </row>
@@ -12421,9 +13705,12 @@
         <v>0.005038</v>
       </c>
       <c r="G428" s="1" t="n">
-        <v>0.005042</v>
+        <v>0.00505</v>
       </c>
       <c r="H428" s="1" t="n">
+        <v>0.00505</v>
+      </c>
+      <c r="I428" s="1" t="n">
         <v>0.005017</v>
       </c>
     </row>
@@ -12449,9 +13736,12 @@
         <v>0.02327</v>
       </c>
       <c r="G429" s="1" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="H429" s="1" t="n">
         <v>0.02329</v>
       </c>
-      <c r="H429" s="1" t="n">
+      <c r="I429" s="1" t="n">
         <v>0.02288</v>
       </c>
     </row>
@@ -12477,9 +13767,12 @@
         <v>0.02516</v>
       </c>
       <c r="G430" s="1" t="n">
-        <v>0.02516</v>
+        <v>0.02517</v>
       </c>
       <c r="H430" s="1" t="n">
+        <v>0.02517</v>
+      </c>
+      <c r="I430" s="1" t="n">
         <v>0.02501</v>
       </c>
     </row>
@@ -12508,6 +13801,9 @@
         <v>0.016</v>
       </c>
       <c r="H431" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="I431" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -12533,9 +13829,12 @@
         <v>0.5444</v>
       </c>
       <c r="G432" s="1" t="n">
+        <v>0.5447</v>
+      </c>
+      <c r="H432" s="1" t="n">
         <v>0.546</v>
       </c>
-      <c r="H432" s="1" t="n">
+      <c r="I432" s="1" t="n">
         <v>0.5439000000000001</v>
       </c>
     </row>
@@ -12561,9 +13860,12 @@
         <v>0.001387</v>
       </c>
       <c r="G433" s="1" t="n">
+        <v>0.001387</v>
+      </c>
+      <c r="H433" s="1" t="n">
         <v>0.001389</v>
       </c>
-      <c r="H433" s="1" t="n">
+      <c r="I433" s="1" t="n">
         <v>0.001383</v>
       </c>
     </row>
@@ -12589,9 +13891,12 @@
         <v>0.3952</v>
       </c>
       <c r="G434" s="1" t="n">
-        <v>0.3952</v>
+        <v>0.3969</v>
       </c>
       <c r="H434" s="1" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="I434" s="1" t="n">
         <v>0.3925</v>
       </c>
     </row>
@@ -12617,10 +13922,13 @@
         <v>0.001391</v>
       </c>
       <c r="G435" s="1" t="n">
+        <v>0.001389</v>
+      </c>
+      <c r="H435" s="1" t="n">
         <v>0.001393</v>
       </c>
-      <c r="H435" s="1" t="n">
-        <v>0.00139</v>
+      <c r="I435" s="1" t="n">
+        <v>0.001389</v>
       </c>
     </row>
     <row r="436">
@@ -12645,9 +13953,12 @@
         <v>0.00715</v>
       </c>
       <c r="G436" s="1" t="n">
-        <v>0.00716</v>
+        <v>0.00718</v>
       </c>
       <c r="H436" s="1" t="n">
+        <v>0.00718</v>
+      </c>
+      <c r="I436" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -12673,9 +13984,12 @@
         <v>0.001988</v>
       </c>
       <c r="G437" s="1" t="n">
-        <v>0.001991</v>
+        <v>0.001997</v>
       </c>
       <c r="H437" s="1" t="n">
+        <v>0.001997</v>
+      </c>
+      <c r="I437" s="1" t="n">
         <v>0.001982</v>
       </c>
     </row>
@@ -12701,9 +14015,12 @@
         <v>0.3137</v>
       </c>
       <c r="G438" s="1" t="n">
-        <v>0.3143</v>
+        <v>0.3147</v>
       </c>
       <c r="H438" s="1" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="I438" s="1" t="n">
         <v>0.3122</v>
       </c>
     </row>
@@ -12732,6 +14049,9 @@
         <v>0.04435</v>
       </c>
       <c r="H439" s="1" t="n">
+        <v>0.04435</v>
+      </c>
+      <c r="I439" s="1" t="n">
         <v>0.04426</v>
       </c>
     </row>
@@ -12760,6 +14080,9 @@
         <v>0.908</v>
       </c>
       <c r="H440" s="1" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="I440" s="1" t="n">
         <v>0.906</v>
       </c>
     </row>
@@ -12785,9 +14108,12 @@
         <v>1548.99</v>
       </c>
       <c r="G441" s="1" t="n">
-        <v>1550.68</v>
+        <v>1551.5</v>
       </c>
       <c r="H441" s="1" t="n">
+        <v>1551.5</v>
+      </c>
+      <c r="I441" s="1" t="n">
         <v>1548.06</v>
       </c>
     </row>
@@ -12813,9 +14139,12 @@
         <v>0.0007915</v>
       </c>
       <c r="G442" s="1" t="n">
-        <v>0.0007951</v>
+        <v>0.0008032</v>
       </c>
       <c r="H442" s="1" t="n">
+        <v>0.0008032</v>
+      </c>
+      <c r="I442" s="1" t="n">
         <v>0.0007877</v>
       </c>
     </row>
@@ -12841,10 +14170,13 @@
         <v>0.003544</v>
       </c>
       <c r="G443" s="1" t="n">
+        <v>0.003537</v>
+      </c>
+      <c r="H443" s="1" t="n">
         <v>0.003558</v>
       </c>
-      <c r="H443" s="1" t="n">
-        <v>0.003543</v>
+      <c r="I443" s="1" t="n">
+        <v>0.003537</v>
       </c>
     </row>
     <row r="444">
@@ -12869,9 +14201,12 @@
         <v>1.977</v>
       </c>
       <c r="G444" s="1" t="n">
+        <v>1.986</v>
+      </c>
+      <c r="H444" s="1" t="n">
         <v>1.989</v>
       </c>
-      <c r="H444" s="1" t="n">
+      <c r="I444" s="1" t="n">
         <v>1.977</v>
       </c>
     </row>
@@ -12897,9 +14232,12 @@
         <v>1.309</v>
       </c>
       <c r="G445" s="1" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="H445" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="H445" s="1" t="n">
+      <c r="I445" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -12925,10 +14263,13 @@
         <v>0.06894</v>
       </c>
       <c r="G446" s="1" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="H446" s="1" t="n">
         <v>0.06929</v>
       </c>
-      <c r="H446" s="1" t="n">
-        <v>0.06894</v>
+      <c r="I446" s="1" t="n">
+        <v>0.0689</v>
       </c>
     </row>
     <row r="447">
@@ -12953,9 +14294,12 @@
         <v>0.02381</v>
       </c>
       <c r="G447" s="1" t="n">
-        <v>0.02381</v>
+        <v>0.02382</v>
       </c>
       <c r="H447" s="1" t="n">
+        <v>0.02382</v>
+      </c>
+      <c r="I447" s="1" t="n">
         <v>0.02347</v>
       </c>
     </row>
@@ -12981,9 +14325,12 @@
         <v>0.014</v>
       </c>
       <c r="G448" s="1" t="n">
+        <v>0.01399</v>
+      </c>
+      <c r="H448" s="1" t="n">
         <v>0.014</v>
       </c>
-      <c r="H448" s="1" t="n">
+      <c r="I448" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -13009,9 +14356,12 @@
         <v>3.731</v>
       </c>
       <c r="G449" s="1" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="H449" s="1" t="n">
         <v>3.734</v>
       </c>
-      <c r="H449" s="1" t="n">
+      <c r="I449" s="1" t="n">
         <v>3.726</v>
       </c>
     </row>
@@ -13037,9 +14387,12 @@
         <v>0.0114</v>
       </c>
       <c r="G450" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="H450" s="1" t="n">
         <v>0.0115</v>
       </c>
-      <c r="H450" s="1" t="n">
+      <c r="I450" s="1" t="n">
         <v>0.0114</v>
       </c>
     </row>
@@ -13065,9 +14418,12 @@
         <v>0.01028</v>
       </c>
       <c r="G451" s="1" t="n">
-        <v>0.01029</v>
+        <v>0.01034</v>
       </c>
       <c r="H451" s="1" t="n">
+        <v>0.01034</v>
+      </c>
+      <c r="I451" s="1" t="n">
         <v>0.01024</v>
       </c>
     </row>
@@ -13093,9 +14449,12 @@
         <v>0.1526</v>
       </c>
       <c r="G452" s="1" t="n">
-        <v>0.1526</v>
+        <v>0.1532</v>
       </c>
       <c r="H452" s="1" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="I452" s="1" t="n">
         <v>0.1522</v>
       </c>
     </row>
@@ -13121,9 +14480,12 @@
         <v>151.12</v>
       </c>
       <c r="G453" s="1" t="n">
-        <v>151.12</v>
+        <v>151.15</v>
       </c>
       <c r="H453" s="1" t="n">
+        <v>151.15</v>
+      </c>
+      <c r="I453" s="1" t="n">
         <v>150.85</v>
       </c>
     </row>
@@ -13149,9 +14511,12 @@
         <v>0.008607999999999999</v>
       </c>
       <c r="G454" s="1" t="n">
-        <v>0.008623</v>
+        <v>0.008633</v>
       </c>
       <c r="H454" s="1" t="n">
+        <v>0.008633</v>
+      </c>
+      <c r="I454" s="1" t="n">
         <v>0.008593999999999999</v>
       </c>
     </row>
@@ -13177,9 +14542,12 @@
         <v>0.05243</v>
       </c>
       <c r="G455" s="1" t="n">
-        <v>0.05248</v>
+        <v>0.05251</v>
       </c>
       <c r="H455" s="1" t="n">
+        <v>0.05251</v>
+      </c>
+      <c r="I455" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -13205,9 +14573,12 @@
         <v>0.30535</v>
       </c>
       <c r="G456" s="1" t="n">
-        <v>0.30535</v>
+        <v>0.30782</v>
       </c>
       <c r="H456" s="1" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="I456" s="1" t="n">
         <v>0.30269</v>
       </c>
     </row>
@@ -13233,9 +14604,12 @@
         <v>0.00544</v>
       </c>
       <c r="G457" s="1" t="n">
-        <v>0.00546</v>
+        <v>0.00547</v>
       </c>
       <c r="H457" s="1" t="n">
+        <v>0.00547</v>
+      </c>
+      <c r="I457" s="1" t="n">
         <v>0.00544</v>
       </c>
     </row>
@@ -13261,10 +14635,13 @@
         <v>0.1003</v>
       </c>
       <c r="G458" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="H458" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="H458" s="1" t="n">
-        <v>0.1003</v>
+      <c r="I458" s="1" t="n">
+        <v>0.1002</v>
       </c>
     </row>
     <row r="459">
@@ -13292,6 +14669,9 @@
         <v>0.001835</v>
       </c>
       <c r="H459" s="1" t="n">
+        <v>0.001835</v>
+      </c>
+      <c r="I459" s="1" t="n">
         <v>0.001825</v>
       </c>
     </row>
@@ -13317,9 +14697,12 @@
         <v>0.01833</v>
       </c>
       <c r="G460" s="1" t="n">
-        <v>0.01835</v>
+        <v>0.01848</v>
       </c>
       <c r="H460" s="1" t="n">
+        <v>0.01848</v>
+      </c>
+      <c r="I460" s="1" t="n">
         <v>0.01822</v>
       </c>
     </row>
@@ -13345,9 +14728,12 @@
         <v>0.0004844</v>
       </c>
       <c r="G461" s="1" t="n">
+        <v>0.0004858</v>
+      </c>
+      <c r="H461" s="1" t="n">
         <v>0.0004877</v>
       </c>
-      <c r="H461" s="1" t="n">
+      <c r="I461" s="1" t="n">
         <v>0.0004844</v>
       </c>
     </row>
@@ -13373,9 +14759,12 @@
         <v>0.0958</v>
       </c>
       <c r="G462" s="1" t="n">
-        <v>0.096</v>
+        <v>0.0961</v>
       </c>
       <c r="H462" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="I462" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -13401,9 +14790,12 @@
         <v>0.07914</v>
       </c>
       <c r="G463" s="1" t="n">
+        <v>0.07926999999999999</v>
+      </c>
+      <c r="H463" s="1" t="n">
         <v>0.07931000000000001</v>
       </c>
-      <c r="H463" s="1" t="n">
+      <c r="I463" s="1" t="n">
         <v>0.07888000000000001</v>
       </c>
     </row>
@@ -13429,9 +14821,12 @@
         <v>0.03148</v>
       </c>
       <c r="G464" s="1" t="n">
-        <v>0.03155</v>
+        <v>0.03159</v>
       </c>
       <c r="H464" s="1" t="n">
+        <v>0.03159</v>
+      </c>
+      <c r="I464" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -13457,9 +14852,12 @@
         <v>0.01614</v>
       </c>
       <c r="G465" s="1" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="H465" s="1" t="n">
         <v>0.01618</v>
       </c>
-      <c r="H465" s="1" t="n">
+      <c r="I465" s="1" t="n">
         <v>0.01613</v>
       </c>
     </row>
@@ -13485,9 +14883,12 @@
         <v>0.06763</v>
       </c>
       <c r="G466" s="1" t="n">
+        <v>0.06769</v>
+      </c>
+      <c r="H466" s="1" t="n">
         <v>0.06781</v>
       </c>
-      <c r="H466" s="1" t="n">
+      <c r="I466" s="1" t="n">
         <v>0.06763</v>
       </c>
     </row>
@@ -13513,9 +14914,12 @@
         <v>0.04323</v>
       </c>
       <c r="G467" s="1" t="n">
+        <v>0.04324</v>
+      </c>
+      <c r="H467" s="1" t="n">
         <v>0.04332</v>
       </c>
-      <c r="H467" s="1" t="n">
+      <c r="I467" s="1" t="n">
         <v>0.04322</v>
       </c>
     </row>
@@ -13541,9 +14945,12 @@
         <v>0.0568</v>
       </c>
       <c r="G468" s="1" t="n">
+        <v>0.05658</v>
+      </c>
+      <c r="H468" s="1" t="n">
         <v>0.05795</v>
       </c>
-      <c r="H468" s="1" t="n">
+      <c r="I468" s="1" t="n">
         <v>0.05587</v>
       </c>
     </row>
@@ -13569,9 +14976,12 @@
         <v>0.2301</v>
       </c>
       <c r="G469" s="1" t="n">
-        <v>0.2305</v>
+        <v>0.2308</v>
       </c>
       <c r="H469" s="1" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="I469" s="1" t="n">
         <v>0.2294</v>
       </c>
     </row>
@@ -13600,6 +15010,9 @@
         <v>0.0905</v>
       </c>
       <c r="H470" s="1" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="I470" s="1" t="n">
         <v>0.0902</v>
       </c>
     </row>
@@ -13625,10 +15038,13 @@
         <v>0.06673</v>
       </c>
       <c r="G471" s="1" t="n">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="H471" s="1" t="n">
         <v>0.0669</v>
       </c>
-      <c r="H471" s="1" t="n">
-        <v>0.06669</v>
+      <c r="I471" s="1" t="n">
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="472">
@@ -13653,9 +15069,12 @@
         <v>6.552</v>
       </c>
       <c r="G472" s="1" t="n">
-        <v>6.552</v>
+        <v>6.555</v>
       </c>
       <c r="H472" s="1" t="n">
+        <v>6.555</v>
+      </c>
+      <c r="I472" s="1" t="n">
         <v>6.486</v>
       </c>
     </row>
@@ -13681,9 +15100,12 @@
         <v>0.01937</v>
       </c>
       <c r="G473" s="1" t="n">
-        <v>0.01943</v>
+        <v>0.01945</v>
       </c>
       <c r="H473" s="1" t="n">
+        <v>0.01945</v>
+      </c>
+      <c r="I473" s="1" t="n">
         <v>0.01937</v>
       </c>
     </row>
@@ -13709,9 +15131,12 @@
         <v>1.42</v>
       </c>
       <c r="G474" s="1" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="H474" s="1" t="n">
         <v>1.423</v>
       </c>
-      <c r="H474" s="1" t="n">
+      <c r="I474" s="1" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -13737,10 +15162,13 @@
         <v>0.08981</v>
       </c>
       <c r="G475" s="1" t="n">
+        <v>0.08971</v>
+      </c>
+      <c r="H475" s="1" t="n">
         <v>0.08981</v>
       </c>
-      <c r="H475" s="1" t="n">
-        <v>0.08974</v>
+      <c r="I475" s="1" t="n">
+        <v>0.08971</v>
       </c>
     </row>
     <row r="476">
@@ -13765,9 +15193,12 @@
         <v>0.1058</v>
       </c>
       <c r="G476" s="1" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="H476" s="1" t="n">
         <v>0.1062</v>
       </c>
-      <c r="H476" s="1" t="n">
+      <c r="I476" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -13793,9 +15224,12 @@
         <v>0.0941</v>
       </c>
       <c r="G477" s="1" t="n">
+        <v>0.09415</v>
+      </c>
+      <c r="H477" s="1" t="n">
         <v>0.09451</v>
       </c>
-      <c r="H477" s="1" t="n">
+      <c r="I477" s="1" t="n">
         <v>0.0941</v>
       </c>
     </row>
@@ -13821,9 +15255,12 @@
         <v>0.0001626</v>
       </c>
       <c r="G478" s="1" t="n">
+        <v>0.0001628</v>
+      </c>
+      <c r="H478" s="1" t="n">
         <v>0.0001629</v>
       </c>
-      <c r="H478" s="1" t="n">
+      <c r="I478" s="1" t="n">
         <v>0.0001624</v>
       </c>
     </row>
@@ -13849,9 +15286,12 @@
         <v>0.04016</v>
       </c>
       <c r="G479" s="1" t="n">
+        <v>0.04019</v>
+      </c>
+      <c r="H479" s="1" t="n">
         <v>0.04023</v>
       </c>
-      <c r="H479" s="1" t="n">
+      <c r="I479" s="1" t="n">
         <v>0.04007</v>
       </c>
     </row>
@@ -13877,9 +15317,12 @@
         <v>0.007394</v>
       </c>
       <c r="G480" s="1" t="n">
-        <v>0.007422</v>
+        <v>0.007423</v>
       </c>
       <c r="H480" s="1" t="n">
+        <v>0.007423</v>
+      </c>
+      <c r="I480" s="1" t="n">
         <v>0.007389</v>
       </c>
     </row>
@@ -13905,9 +15348,12 @@
         <v>0.0954</v>
       </c>
       <c r="G481" s="1" t="n">
+        <v>0.0954</v>
+      </c>
+      <c r="H481" s="1" t="n">
         <v>0.0955</v>
       </c>
-      <c r="H481" s="1" t="n">
+      <c r="I481" s="1" t="n">
         <v>0.0954</v>
       </c>
     </row>
@@ -13933,9 +15379,12 @@
         <v>0.05569</v>
       </c>
       <c r="G482" s="1" t="n">
+        <v>0.05609</v>
+      </c>
+      <c r="H482" s="1" t="n">
         <v>0.05621</v>
       </c>
-      <c r="H482" s="1" t="n">
+      <c r="I482" s="1" t="n">
         <v>0.05569</v>
       </c>
     </row>
@@ -13961,9 +15410,12 @@
         <v>0.006167</v>
       </c>
       <c r="G483" s="1" t="n">
-        <v>0.006195</v>
+        <v>0.006198</v>
       </c>
       <c r="H483" s="1" t="n">
+        <v>0.006198</v>
+      </c>
+      <c r="I483" s="1" t="n">
         <v>0.006161</v>
       </c>
     </row>
@@ -13989,9 +15441,12 @@
         <v>0.01488</v>
       </c>
       <c r="G484" s="1" t="n">
-        <v>0.01492</v>
+        <v>0.01497</v>
       </c>
       <c r="H484" s="1" t="n">
+        <v>0.01497</v>
+      </c>
+      <c r="I484" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -14017,9 +15472,12 @@
         <v>0.0241</v>
       </c>
       <c r="G485" s="1" t="n">
+        <v>0.02412</v>
+      </c>
+      <c r="H485" s="1" t="n">
         <v>0.02427</v>
       </c>
-      <c r="H485" s="1" t="n">
+      <c r="I485" s="1" t="n">
         <v>0.02403</v>
       </c>
     </row>
@@ -14045,9 +15503,12 @@
         <v>0.06687</v>
       </c>
       <c r="G486" s="1" t="n">
+        <v>0.06696000000000001</v>
+      </c>
+      <c r="H486" s="1" t="n">
         <v>0.06702</v>
       </c>
-      <c r="H486" s="1" t="n">
+      <c r="I486" s="1" t="n">
         <v>0.0667</v>
       </c>
     </row>
@@ -14073,9 +15534,12 @@
         <v>0.03687</v>
       </c>
       <c r="G487" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="H487" s="1" t="n">
         <v>0.03705</v>
       </c>
-      <c r="H487" s="1" t="n">
+      <c r="I487" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -14101,9 +15565,12 @@
         <v>0.01814</v>
       </c>
       <c r="G488" s="1" t="n">
+        <v>0.01818</v>
+      </c>
+      <c r="H488" s="1" t="n">
         <v>0.0182</v>
       </c>
-      <c r="H488" s="1" t="n">
+      <c r="I488" s="1" t="n">
         <v>0.01814</v>
       </c>
     </row>
@@ -14129,10 +15596,13 @@
         <v>0.03244</v>
       </c>
       <c r="G489" s="1" t="n">
+        <v>0.03228</v>
+      </c>
+      <c r="H489" s="1" t="n">
         <v>0.03278</v>
       </c>
-      <c r="H489" s="1" t="n">
-        <v>0.03244</v>
+      <c r="I489" s="1" t="n">
+        <v>0.03228</v>
       </c>
     </row>
     <row r="490">
@@ -14157,9 +15627,12 @@
         <v>0.01466</v>
       </c>
       <c r="G490" s="1" t="n">
+        <v>0.01468</v>
+      </c>
+      <c r="H490" s="1" t="n">
         <v>0.01474</v>
       </c>
-      <c r="H490" s="1" t="n">
+      <c r="I490" s="1" t="n">
         <v>0.01458</v>
       </c>
     </row>
@@ -14185,9 +15658,12 @@
         <v>0.01858</v>
       </c>
       <c r="G491" s="1" t="n">
-        <v>0.01861</v>
+        <v>0.01876</v>
       </c>
       <c r="H491" s="1" t="n">
+        <v>0.01876</v>
+      </c>
+      <c r="I491" s="1" t="n">
         <v>0.01851</v>
       </c>
     </row>
@@ -14213,9 +15689,12 @@
         <v>0.08810999999999999</v>
       </c>
       <c r="G492" s="1" t="n">
+        <v>0.08826000000000001</v>
+      </c>
+      <c r="H492" s="1" t="n">
         <v>0.08935</v>
       </c>
-      <c r="H492" s="1" t="n">
+      <c r="I492" s="1" t="n">
         <v>0.08810999999999999</v>
       </c>
     </row>
@@ -14244,6 +15723,9 @@
         <v>0.006514</v>
       </c>
       <c r="H493" s="1" t="n">
+        <v>0.006514</v>
+      </c>
+      <c r="I493" s="1" t="n">
         <v>0.006497</v>
       </c>
     </row>
@@ -14269,9 +15751,12 @@
         <v>0.1326</v>
       </c>
       <c r="G494" s="1" t="n">
-        <v>0.1327</v>
+        <v>0.1331</v>
       </c>
       <c r="H494" s="1" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="I494" s="1" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -14297,9 +15782,12 @@
         <v>0.2844</v>
       </c>
       <c r="G495" s="1" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="H495" s="1" t="n">
         <v>0.2853</v>
       </c>
-      <c r="H495" s="1" t="n">
+      <c r="I495" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -14325,9 +15813,12 @@
         <v>0.004523</v>
       </c>
       <c r="G496" s="1" t="n">
-        <v>0.004534</v>
+        <v>0.004536</v>
       </c>
       <c r="H496" s="1" t="n">
+        <v>0.004536</v>
+      </c>
+      <c r="I496" s="1" t="n">
         <v>0.004516</v>
       </c>
     </row>
@@ -14353,9 +15844,12 @@
         <v>0.1268</v>
       </c>
       <c r="G497" s="1" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="H497" s="1" t="n">
         <v>0.1283</v>
       </c>
-      <c r="H497" s="1" t="n">
+      <c r="I497" s="1" t="n">
         <v>0.1265</v>
       </c>
     </row>
@@ -14381,9 +15875,12 @@
         <v>0.03429</v>
       </c>
       <c r="G498" s="1" t="n">
-        <v>0.03439</v>
+        <v>0.03445</v>
       </c>
       <c r="H498" s="1" t="n">
+        <v>0.03445</v>
+      </c>
+      <c r="I498" s="1" t="n">
         <v>0.03423</v>
       </c>
     </row>
@@ -14409,9 +15906,12 @@
         <v>0.03557</v>
       </c>
       <c r="G499" s="1" t="n">
+        <v>0.03567</v>
+      </c>
+      <c r="H499" s="1" t="n">
         <v>0.03576</v>
       </c>
-      <c r="H499" s="1" t="n">
+      <c r="I499" s="1" t="n">
         <v>0.03557</v>
       </c>
     </row>
@@ -14437,9 +15937,12 @@
         <v>0.003413</v>
       </c>
       <c r="G500" s="1" t="n">
+        <v>0.003415</v>
+      </c>
+      <c r="H500" s="1" t="n">
         <v>0.003421</v>
       </c>
-      <c r="H500" s="1" t="n">
+      <c r="I500" s="1" t="n">
         <v>0.003413</v>
       </c>
     </row>
@@ -14465,9 +15968,12 @@
         <v>0.0003824</v>
       </c>
       <c r="G501" s="1" t="n">
-        <v>0.0003824</v>
+        <v>0.0003834</v>
       </c>
       <c r="H501" s="1" t="n">
+        <v>0.0003834</v>
+      </c>
+      <c r="I501" s="1" t="n">
         <v>0.0003786</v>
       </c>
     </row>
@@ -14493,9 +15999,12 @@
         <v>0.2994</v>
       </c>
       <c r="G502" s="1" t="n">
-        <v>0.3003</v>
+        <v>0.3004</v>
       </c>
       <c r="H502" s="1" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="I502" s="1" t="n">
         <v>0.2986</v>
       </c>
     </row>
@@ -14521,9 +16030,12 @@
         <v>0.06485</v>
       </c>
       <c r="G503" s="1" t="n">
+        <v>0.06489</v>
+      </c>
+      <c r="H503" s="1" t="n">
         <v>0.06507</v>
       </c>
-      <c r="H503" s="1" t="n">
+      <c r="I503" s="1" t="n">
         <v>0.06485</v>
       </c>
     </row>
@@ -14549,9 +16061,12 @@
         <v>0.1775</v>
       </c>
       <c r="G504" s="1" t="n">
-        <v>0.1777</v>
+        <v>0.178</v>
       </c>
       <c r="H504" s="1" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="I504" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -14577,9 +16092,12 @@
         <v>0.1512</v>
       </c>
       <c r="G505" s="1" t="n">
-        <v>0.1513</v>
+        <v>0.1514</v>
       </c>
       <c r="H505" s="1" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="I505" s="1" t="n">
         <v>0.1512</v>
       </c>
     </row>
@@ -14608,6 +16126,9 @@
         <v>0.01199</v>
       </c>
       <c r="H506" s="1" t="n">
+        <v>0.01199</v>
+      </c>
+      <c r="I506" s="1" t="n">
         <v>0.01193</v>
       </c>
     </row>
@@ -14633,9 +16154,12 @@
         <v>0.2873</v>
       </c>
       <c r="G507" s="1" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="H507" s="1" t="n">
         <v>0.2883</v>
       </c>
-      <c r="H507" s="1" t="n">
+      <c r="I507" s="1" t="n">
         <v>0.2871</v>
       </c>
     </row>
@@ -14661,9 +16185,12 @@
         <v>0.009310000000000001</v>
       </c>
       <c r="G508" s="1" t="n">
+        <v>0.009350000000000001</v>
+      </c>
+      <c r="H508" s="1" t="n">
         <v>0.0094</v>
       </c>
-      <c r="H508" s="1" t="n">
+      <c r="I508" s="1" t="n">
         <v>0.009310000000000001</v>
       </c>
     </row>
@@ -14689,9 +16216,12 @@
         <v>0.00681</v>
       </c>
       <c r="G509" s="1" t="n">
-        <v>0.006816</v>
+        <v>0.006822</v>
       </c>
       <c r="H509" s="1" t="n">
+        <v>0.006822</v>
+      </c>
+      <c r="I509" s="1" t="n">
         <v>0.006783</v>
       </c>
     </row>
@@ -14717,9 +16247,12 @@
         <v>0.2934</v>
       </c>
       <c r="G510" s="1" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="H510" s="1" t="n">
         <v>0.2951</v>
       </c>
-      <c r="H510" s="1" t="n">
+      <c r="I510" s="1" t="n">
         <v>0.2934</v>
       </c>
     </row>
@@ -14745,9 +16278,12 @@
         <v>0.01465</v>
       </c>
       <c r="G511" s="1" t="n">
+        <v>0.01467</v>
+      </c>
+      <c r="H511" s="1" t="n">
         <v>0.01471</v>
       </c>
-      <c r="H511" s="1" t="n">
+      <c r="I511" s="1" t="n">
         <v>0.01465</v>
       </c>
     </row>
@@ -14776,6 +16312,9 @@
         <v>0.1398</v>
       </c>
       <c r="H512" s="1" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="I512" s="1" t="n">
         <v>0.1394</v>
       </c>
     </row>
@@ -14801,9 +16340,12 @@
         <v>0.08103</v>
       </c>
       <c r="G513" s="1" t="n">
+        <v>0.08144</v>
+      </c>
+      <c r="H513" s="1" t="n">
         <v>0.08144999999999999</v>
       </c>
-      <c r="H513" s="1" t="n">
+      <c r="I513" s="1" t="n">
         <v>0.08069</v>
       </c>
     </row>
@@ -14832,6 +16374,9 @@
         <v>0.0251</v>
       </c>
       <c r="H514" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="I514" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -14857,9 +16402,12 @@
         <v>0.06308</v>
       </c>
       <c r="G515" s="1" t="n">
-        <v>0.06319</v>
+        <v>0.06329</v>
       </c>
       <c r="H515" s="1" t="n">
+        <v>0.06329</v>
+      </c>
+      <c r="I515" s="1" t="n">
         <v>0.06301</v>
       </c>
     </row>
@@ -14885,9 +16433,12 @@
         <v>0.04717</v>
       </c>
       <c r="G516" s="1" t="n">
-        <v>0.04723</v>
+        <v>0.04732</v>
       </c>
       <c r="H516" s="1" t="n">
+        <v>0.04732</v>
+      </c>
+      <c r="I516" s="1" t="n">
         <v>0.04707</v>
       </c>
     </row>
@@ -14913,9 +16464,12 @@
         <v>0.004902</v>
       </c>
       <c r="G517" s="1" t="n">
+        <v>0.004904</v>
+      </c>
+      <c r="H517" s="1" t="n">
         <v>0.004908</v>
       </c>
-      <c r="H517" s="1" t="n">
+      <c r="I517" s="1" t="n">
         <v>0.004902</v>
       </c>
     </row>
@@ -14941,9 +16495,12 @@
         <v>0.009431999999999999</v>
       </c>
       <c r="G518" s="1" t="n">
+        <v>0.009424999999999999</v>
+      </c>
+      <c r="H518" s="1" t="n">
         <v>0.009431999999999999</v>
       </c>
-      <c r="H518" s="1" t="n">
+      <c r="I518" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -14969,9 +16526,12 @@
         <v>0.01803</v>
       </c>
       <c r="G519" s="1" t="n">
+        <v>0.01805</v>
+      </c>
+      <c r="H519" s="1" t="n">
         <v>0.01807</v>
       </c>
-      <c r="H519" s="1" t="n">
+      <c r="I519" s="1" t="n">
         <v>0.01798</v>
       </c>
     </row>
@@ -14997,9 +16557,12 @@
         <v>0.06677</v>
       </c>
       <c r="G520" s="1" t="n">
-        <v>0.06684</v>
+        <v>0.06688</v>
       </c>
       <c r="H520" s="1" t="n">
+        <v>0.06688</v>
+      </c>
+      <c r="I520" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -15025,9 +16588,12 @@
         <v>0.136</v>
       </c>
       <c r="G521" s="1" t="n">
-        <v>0.1365</v>
+        <v>0.1368</v>
       </c>
       <c r="H521" s="1" t="n">
+        <v>0.1368</v>
+      </c>
+      <c r="I521" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -15053,9 +16619,12 @@
         <v>0.0474</v>
       </c>
       <c r="G522" s="1" t="n">
+        <v>0.04738</v>
+      </c>
+      <c r="H522" s="1" t="n">
         <v>0.04746</v>
       </c>
-      <c r="H522" s="1" t="n">
+      <c r="I522" s="1" t="n">
         <v>0.04718</v>
       </c>
     </row>
@@ -15081,9 +16650,12 @@
         <v>0.06784999999999999</v>
       </c>
       <c r="G523" s="1" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="H523" s="1" t="n">
         <v>0.06809</v>
       </c>
-      <c r="H523" s="1" t="n">
+      <c r="I523" s="1" t="n">
         <v>0.06784999999999999</v>
       </c>
     </row>
@@ -15109,9 +16681,12 @@
         <v>0.6966</v>
       </c>
       <c r="G524" s="1" t="n">
-        <v>0.6982</v>
+        <v>0.6983</v>
       </c>
       <c r="H524" s="1" t="n">
+        <v>0.6983</v>
+      </c>
+      <c r="I524" s="1" t="n">
         <v>0.6966</v>
       </c>
     </row>
@@ -15137,9 +16712,12 @@
         <v>0.00267</v>
       </c>
       <c r="G525" s="1" t="n">
-        <v>0.00267</v>
+        <v>0.00268</v>
       </c>
       <c r="H525" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="I525" s="1" t="n">
         <v>0.00267</v>
       </c>
     </row>
@@ -15165,9 +16743,12 @@
         <v>0.4859</v>
       </c>
       <c r="G526" s="1" t="n">
+        <v>0.4867</v>
+      </c>
+      <c r="H526" s="1" t="n">
         <v>0.4868</v>
       </c>
-      <c r="H526" s="1" t="n">
+      <c r="I526" s="1" t="n">
         <v>0.4856</v>
       </c>
     </row>
@@ -15193,9 +16774,12 @@
         <v>45.82</v>
       </c>
       <c r="G527" s="1" t="n">
-        <v>45.82</v>
+        <v>45.83</v>
       </c>
       <c r="H527" s="1" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="I527" s="1" t="n">
         <v>45.76</v>
       </c>
     </row>
@@ -15224,6 +16808,9 @@
         <v>0.02437</v>
       </c>
       <c r="H528" s="1" t="n">
+        <v>0.02437</v>
+      </c>
+      <c r="I528" s="1" t="n">
         <v>0.02429</v>
       </c>
     </row>
@@ -15249,9 +16836,12 @@
         <v>0.006391</v>
       </c>
       <c r="G529" s="1" t="n">
-        <v>0.006392</v>
+        <v>0.006403</v>
       </c>
       <c r="H529" s="1" t="n">
+        <v>0.006403</v>
+      </c>
+      <c r="I529" s="1" t="n">
         <v>0.00638</v>
       </c>
     </row>
@@ -15277,9 +16867,12 @@
         <v>0.1993</v>
       </c>
       <c r="G530" s="1" t="n">
-        <v>0.2</v>
+        <v>0.2002</v>
       </c>
       <c r="H530" s="1" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="I530" s="1" t="n">
         <v>0.1993</v>
       </c>
     </row>
@@ -15305,9 +16898,12 @@
         <v>0.007675</v>
       </c>
       <c r="G531" s="1" t="n">
+        <v>0.007685</v>
+      </c>
+      <c r="H531" s="1" t="n">
         <v>0.007727</v>
       </c>
-      <c r="H531" s="1" t="n">
+      <c r="I531" s="1" t="n">
         <v>0.007657</v>
       </c>
     </row>
@@ -15333,9 +16929,12 @@
         <v>2.275</v>
       </c>
       <c r="G532" s="1" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="H532" s="1" t="n">
         <v>2.285</v>
       </c>
-      <c r="H532" s="1" t="n">
+      <c r="I532" s="1" t="n">
         <v>2.275</v>
       </c>
     </row>
@@ -15361,9 +16960,12 @@
         <v>0.04153</v>
       </c>
       <c r="G533" s="1" t="n">
-        <v>0.04153</v>
+        <v>0.04156</v>
       </c>
       <c r="H533" s="1" t="n">
+        <v>0.04156</v>
+      </c>
+      <c r="I533" s="1" t="n">
         <v>0.04138</v>
       </c>
     </row>
@@ -15389,9 +16991,12 @@
         <v>0.1824</v>
       </c>
       <c r="G534" s="1" t="n">
-        <v>0.1824</v>
+        <v>0.1833</v>
       </c>
       <c r="H534" s="1" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="I534" s="1" t="n">
         <v>0.1811</v>
       </c>
     </row>
@@ -15417,9 +17022,12 @@
         <v>0.04291</v>
       </c>
       <c r="G535" s="1" t="n">
+        <v>0.04299</v>
+      </c>
+      <c r="H535" s="1" t="n">
         <v>0.04311</v>
       </c>
-      <c r="H535" s="1" t="n">
+      <c r="I535" s="1" t="n">
         <v>0.04287</v>
       </c>
     </row>
@@ -15445,10 +17053,13 @@
         <v>0.05417</v>
       </c>
       <c r="G536" s="1" t="n">
+        <v>0.05409</v>
+      </c>
+      <c r="H536" s="1" t="n">
         <v>0.05438</v>
       </c>
-      <c r="H536" s="1" t="n">
-        <v>0.05417</v>
+      <c r="I536" s="1" t="n">
+        <v>0.05409</v>
       </c>
     </row>
     <row r="537">
@@ -15473,9 +17084,12 @@
         <v>0.1602</v>
       </c>
       <c r="G537" s="1" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="H537" s="1" t="n">
         <v>0.1609</v>
       </c>
-      <c r="H537" s="1" t="n">
+      <c r="I537" s="1" t="n">
         <v>0.1602</v>
       </c>
     </row>
@@ -15501,9 +17115,12 @@
         <v>0.03673</v>
       </c>
       <c r="G538" s="1" t="n">
+        <v>0.03682</v>
+      </c>
+      <c r="H538" s="1" t="n">
         <v>0.03687</v>
       </c>
-      <c r="H538" s="1" t="n">
+      <c r="I538" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -15529,9 +17146,12 @@
         <v>0.0576</v>
       </c>
       <c r="G539" s="1" t="n">
-        <v>0.05776</v>
+        <v>0.05807</v>
       </c>
       <c r="H539" s="1" t="n">
+        <v>0.05807</v>
+      </c>
+      <c r="I539" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -15557,9 +17177,12 @@
         <v>0.04256</v>
       </c>
       <c r="G540" s="1" t="n">
+        <v>0.04266</v>
+      </c>
+      <c r="H540" s="1" t="n">
         <v>0.04267</v>
       </c>
-      <c r="H540" s="1" t="n">
+      <c r="I540" s="1" t="n">
         <v>0.04256</v>
       </c>
     </row>
@@ -15585,9 +17208,12 @@
         <v>0.01724</v>
       </c>
       <c r="G541" s="1" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="H541" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="H541" s="1" t="n">
+      <c r="I541" s="1" t="n">
         <v>0.0172</v>
       </c>
     </row>
@@ -15613,9 +17239,12 @@
         <v>0.003963</v>
       </c>
       <c r="G542" s="1" t="n">
+        <v>0.00397</v>
+      </c>
+      <c r="H542" s="1" t="n">
         <v>0.003975</v>
       </c>
-      <c r="H542" s="1" t="n">
+      <c r="I542" s="1" t="n">
         <v>0.003963</v>
       </c>
     </row>
@@ -15641,9 +17270,12 @@
         <v>0.0578</v>
       </c>
       <c r="G543" s="1" t="n">
+        <v>0.05768</v>
+      </c>
+      <c r="H543" s="1" t="n">
         <v>0.05817</v>
       </c>
-      <c r="H543" s="1" t="n">
+      <c r="I543" s="1" t="n">
         <v>0.05735</v>
       </c>
     </row>
@@ -15669,9 +17301,12 @@
         <v>0.05016</v>
       </c>
       <c r="G544" s="1" t="n">
+        <v>0.05019</v>
+      </c>
+      <c r="H544" s="1" t="n">
         <v>0.05042</v>
       </c>
-      <c r="H544" s="1" t="n">
+      <c r="I544" s="1" t="n">
         <v>0.05016</v>
       </c>
     </row>
@@ -15697,9 +17332,12 @@
         <v>0.04053</v>
       </c>
       <c r="G545" s="1" t="n">
-        <v>0.04064</v>
+        <v>0.04071</v>
       </c>
       <c r="H545" s="1" t="n">
+        <v>0.04071</v>
+      </c>
+      <c r="I545" s="1" t="n">
         <v>0.04038</v>
       </c>
     </row>
@@ -15725,9 +17363,12 @@
         <v>0.007429</v>
       </c>
       <c r="G546" s="1" t="n">
-        <v>0.007432</v>
+        <v>0.007433</v>
       </c>
       <c r="H546" s="1" t="n">
+        <v>0.007433</v>
+      </c>
+      <c r="I546" s="1" t="n">
         <v>0.007402</v>
       </c>
     </row>
@@ -15753,9 +17394,12 @@
         <v>0.01469</v>
       </c>
       <c r="G547" s="1" t="n">
-        <v>0.01469</v>
+        <v>0.01486</v>
       </c>
       <c r="H547" s="1" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="I547" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -15781,9 +17425,12 @@
         <v>0.0157</v>
       </c>
       <c r="G548" s="1" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="H548" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="H548" s="1" t="n">
+      <c r="I548" s="1" t="n">
         <v>0.0157</v>
       </c>
     </row>
@@ -15809,9 +17456,12 @@
         <v>0.13429</v>
       </c>
       <c r="G549" s="1" t="n">
+        <v>0.13415</v>
+      </c>
+      <c r="H549" s="1" t="n">
         <v>0.13434</v>
       </c>
-      <c r="H549" s="1" t="n">
+      <c r="I549" s="1" t="n">
         <v>0.13271</v>
       </c>
     </row>
@@ -15837,9 +17487,12 @@
         <v>0.1693</v>
       </c>
       <c r="G550" s="1" t="n">
-        <v>0.1696</v>
+        <v>0.1697</v>
       </c>
       <c r="H550" s="1" t="n">
+        <v>0.1697</v>
+      </c>
+      <c r="I550" s="1" t="n">
         <v>0.1693</v>
       </c>
     </row>
@@ -15865,9 +17518,12 @@
         <v>0.003579</v>
       </c>
       <c r="G551" s="1" t="n">
+        <v>0.003579</v>
+      </c>
+      <c r="H551" s="1" t="n">
         <v>0.003583</v>
       </c>
-      <c r="H551" s="1" t="n">
+      <c r="I551" s="1" t="n">
         <v>0.003577</v>
       </c>
     </row>
@@ -15893,9 +17549,12 @@
         <v>0.0303</v>
       </c>
       <c r="G552" s="1" t="n">
-        <v>0.03038</v>
+        <v>0.03039</v>
       </c>
       <c r="H552" s="1" t="n">
+        <v>0.03039</v>
+      </c>
+      <c r="I552" s="1" t="n">
         <v>0.0303</v>
       </c>
     </row>
@@ -15921,10 +17580,13 @@
         <v>0.0132</v>
       </c>
       <c r="G553" s="1" t="n">
+        <v>0.01319</v>
+      </c>
+      <c r="H553" s="1" t="n">
         <v>0.01325</v>
       </c>
-      <c r="H553" s="1" t="n">
-        <v>0.0132</v>
+      <c r="I553" s="1" t="n">
+        <v>0.01319</v>
       </c>
     </row>
     <row r="554">
@@ -15949,9 +17611,12 @@
         <v>0.1041</v>
       </c>
       <c r="G554" s="1" t="n">
+        <v>0.1043</v>
+      </c>
+      <c r="H554" s="1" t="n">
         <v>0.1046</v>
       </c>
-      <c r="H554" s="1" t="n">
+      <c r="I554" s="1" t="n">
         <v>0.1039</v>
       </c>
     </row>
@@ -15977,9 +17642,12 @@
         <v>0.05297</v>
       </c>
       <c r="G555" s="1" t="n">
+        <v>0.05307</v>
+      </c>
+      <c r="H555" s="1" t="n">
         <v>0.05319</v>
       </c>
-      <c r="H555" s="1" t="n">
+      <c r="I555" s="1" t="n">
         <v>0.05291</v>
       </c>
     </row>
@@ -16005,10 +17673,13 @@
         <v>0.01219</v>
       </c>
       <c r="G556" s="1" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="H556" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="H556" s="1" t="n">
-        <v>0.01219</v>
+      <c r="I556" s="1" t="n">
+        <v>0.01218</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I556"/>
+  <dimension ref="A1:J556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -426,8 +426,9 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,10 +469,15 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>price_01:30</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -502,9 +508,12 @@
         <v>71450</v>
       </c>
       <c r="H2" s="1" t="n">
+        <v>71477.10000000001</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>71530</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="J2" s="1" t="n">
         <v>71364.39999999999</v>
       </c>
     </row>
@@ -533,9 +542,12 @@
         <v>2093.92</v>
       </c>
       <c r="H3" s="1" t="n">
+        <v>2094.02</v>
+      </c>
+      <c r="I3" s="1" t="n">
         <v>2096.9</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="J3" s="1" t="n">
         <v>2090.41</v>
       </c>
     </row>
@@ -564,9 +576,12 @@
         <v>87.68000000000001</v>
       </c>
       <c r="H4" s="1" t="n">
+        <v>87.77</v>
+      </c>
+      <c r="I4" s="1" t="n">
         <v>87.95</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="J4" s="1" t="n">
         <v>87.47</v>
       </c>
     </row>
@@ -595,9 +610,12 @@
         <v>23.043</v>
       </c>
       <c r="H5" s="1" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="I5" s="1" t="n">
         <v>23.579</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="J5" s="1" t="n">
         <v>23.043</v>
       </c>
     </row>
@@ -626,9 +644,12 @@
         <v>0.001845</v>
       </c>
       <c r="H6" s="1" t="n">
+        <v>0.001835</v>
+      </c>
+      <c r="I6" s="1" t="n">
         <v>0.001892</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.001827</v>
       </c>
     </row>
@@ -657,9 +678,12 @@
         <v>1.4151</v>
       </c>
       <c r="H7" s="1" t="n">
+        <v>1.4134</v>
+      </c>
+      <c r="I7" s="1" t="n">
         <v>1.4151</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>1.4117</v>
       </c>
     </row>
@@ -688,10 +712,13 @@
         <v>0.010599</v>
       </c>
       <c r="H8" s="1" t="n">
+        <v>0.010407</v>
+      </c>
+      <c r="I8" s="1" t="n">
         <v>0.011244</v>
       </c>
-      <c r="I8" s="1" t="n">
-        <v>0.010599</v>
+      <c r="J8" s="1" t="n">
+        <v>0.010407</v>
       </c>
     </row>
     <row r="9">
@@ -719,9 +746,12 @@
         <v>4.034</v>
       </c>
       <c r="H9" s="1" t="n">
+        <v>4.022</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>4.062</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="J9" s="1" t="n">
         <v>3.954</v>
       </c>
     </row>
@@ -750,9 +780,12 @@
         <v>278.1</v>
       </c>
       <c r="H10" s="1" t="n">
+        <v>273.93</v>
+      </c>
+      <c r="I10" s="1" t="n">
         <v>278.1</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="J10" s="1" t="n">
         <v>272.11</v>
       </c>
     </row>
@@ -781,9 +814,12 @@
         <v>0.07833</v>
       </c>
       <c r="H11" s="1" t="n">
+        <v>0.07843</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <v>0.08047</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="J11" s="1" t="n">
         <v>0.07833</v>
       </c>
     </row>
@@ -812,9 +848,12 @@
         <v>225.26</v>
       </c>
       <c r="H12" s="1" t="n">
+        <v>224.87</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <v>227.69</v>
       </c>
-      <c r="I12" s="1" t="n">
+      <c r="J12" s="1" t="n">
         <v>223.76</v>
       </c>
     </row>
@@ -843,9 +882,12 @@
         <v>0.09495000000000001</v>
       </c>
       <c r="H13" s="1" t="n">
+        <v>0.09490999999999999</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>0.09497</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="J13" s="1" t="n">
         <v>0.0946</v>
       </c>
     </row>
@@ -874,9 +916,12 @@
         <v>37.208</v>
       </c>
       <c r="H14" s="1" t="n">
+        <v>37.19</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>37.279</v>
       </c>
-      <c r="I14" s="1" t="n">
+      <c r="J14" s="1" t="n">
         <v>37.089</v>
       </c>
     </row>
@@ -905,10 +950,13 @@
         <v>0.09467</v>
       </c>
       <c r="H15" s="1" t="n">
+        <v>0.09456000000000001</v>
+      </c>
+      <c r="I15" s="1" t="n">
         <v>0.09845</v>
       </c>
-      <c r="I15" s="1" t="n">
-        <v>0.09461</v>
+      <c r="J15" s="1" t="n">
+        <v>0.09456000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -936,9 +984,12 @@
         <v>0.2282</v>
       </c>
       <c r="H16" s="1" t="n">
+        <v>0.2262</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>0.2339</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="J16" s="1" t="n">
         <v>0.2256</v>
       </c>
     </row>
@@ -967,9 +1018,12 @@
         <v>0.011379</v>
       </c>
       <c r="H17" s="1" t="n">
+        <v>0.011484</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>0.011542</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="J17" s="1" t="n">
         <v>0.011379</v>
       </c>
     </row>
@@ -998,9 +1052,12 @@
         <v>659.5700000000001</v>
       </c>
       <c r="H18" s="1" t="n">
+        <v>659.8099999999999</v>
+      </c>
+      <c r="I18" s="1" t="n">
         <v>660.72</v>
       </c>
-      <c r="I18" s="1" t="n">
+      <c r="J18" s="1" t="n">
         <v>658.89</v>
       </c>
     </row>
@@ -1029,9 +1086,12 @@
         <v>0.0033454</v>
       </c>
       <c r="H19" s="1" t="n">
+        <v>0.003344</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>0.0033454</v>
       </c>
-      <c r="I19" s="1" t="n">
+      <c r="J19" s="1" t="n">
         <v>0.0033271</v>
       </c>
     </row>
@@ -1060,9 +1120,12 @@
         <v>0.18066</v>
       </c>
       <c r="H20" s="1" t="n">
+        <v>0.18023</v>
+      </c>
+      <c r="I20" s="1" t="n">
         <v>0.18066</v>
       </c>
-      <c r="I20" s="1" t="n">
+      <c r="J20" s="1" t="n">
         <v>0.17675</v>
       </c>
     </row>
@@ -1091,9 +1154,12 @@
         <v>0.009953</v>
       </c>
       <c r="H21" s="1" t="n">
+        <v>0.009926000000000001</v>
+      </c>
+      <c r="I21" s="1" t="n">
         <v>0.010044</v>
       </c>
-      <c r="I21" s="1" t="n">
+      <c r="J21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -1122,9 +1188,12 @@
         <v>1.0008</v>
       </c>
       <c r="H22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="n">
         <v>1.0033</v>
       </c>
-      <c r="I22" s="1" t="n">
+      <c r="J22" s="1" t="n">
         <v>0.9985000000000001</v>
       </c>
     </row>
@@ -1153,9 +1222,12 @@
         <v>5002.67</v>
       </c>
       <c r="H23" s="1" t="n">
+        <v>5006.21</v>
+      </c>
+      <c r="I23" s="1" t="n">
         <v>5012.25</v>
       </c>
-      <c r="I23" s="1" t="n">
+      <c r="J23" s="1" t="n">
         <v>5002.67</v>
       </c>
     </row>
@@ -1184,9 +1256,12 @@
         <v>0.2631</v>
       </c>
       <c r="H24" s="1" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="I24" s="1" t="n">
         <v>0.2643</v>
       </c>
-      <c r="I24" s="1" t="n">
+      <c r="J24" s="1" t="n">
         <v>0.2625</v>
       </c>
     </row>
@@ -1215,9 +1290,12 @@
         <v>2.914</v>
       </c>
       <c r="H25" s="1" t="n">
+        <v>2.914</v>
+      </c>
+      <c r="I25" s="1" t="n">
         <v>2.924</v>
       </c>
-      <c r="I25" s="1" t="n">
+      <c r="J25" s="1" t="n">
         <v>2.899</v>
       </c>
     </row>
@@ -1246,9 +1324,12 @@
         <v>0.3991</v>
       </c>
       <c r="H26" s="1" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="I26" s="1" t="n">
         <v>0.4096</v>
       </c>
-      <c r="I26" s="1" t="n">
+      <c r="J26" s="1" t="n">
         <v>0.3959</v>
       </c>
     </row>
@@ -1280,6 +1361,9 @@
         <v>0.886</v>
       </c>
       <c r="I27" s="1" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="J27" s="1" t="n">
         <v>0.881</v>
       </c>
     </row>
@@ -1308,9 +1392,12 @@
         <v>1.343</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>1.343</v>
+        <v>1.346</v>
       </c>
       <c r="I28" s="1" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="J28" s="1" t="n">
         <v>1.335</v>
       </c>
     </row>
@@ -1339,9 +1426,12 @@
         <v>9.154</v>
       </c>
       <c r="H29" s="1" t="n">
+        <v>9.145</v>
+      </c>
+      <c r="I29" s="1" t="n">
         <v>9.179</v>
       </c>
-      <c r="I29" s="1" t="n">
+      <c r="J29" s="1" t="n">
         <v>9.131</v>
       </c>
     </row>
@@ -1370,9 +1460,12 @@
         <v>461.65</v>
       </c>
       <c r="H30" s="1" t="n">
+        <v>461.4</v>
+      </c>
+      <c r="I30" s="1" t="n">
         <v>463.35</v>
       </c>
-      <c r="I30" s="1" t="n">
+      <c r="J30" s="1" t="n">
         <v>461.24</v>
       </c>
     </row>
@@ -1401,9 +1494,12 @@
         <v>9.731</v>
       </c>
       <c r="H31" s="1" t="n">
+        <v>9.722</v>
+      </c>
+      <c r="I31" s="1" t="n">
         <v>9.731</v>
       </c>
-      <c r="I31" s="1" t="n">
+      <c r="J31" s="1" t="n">
         <v>9.696999999999999</v>
       </c>
     </row>
@@ -1432,9 +1528,12 @@
         <v>0.36189</v>
       </c>
       <c r="H32" s="1" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="I32" s="1" t="n">
         <v>0.36683</v>
       </c>
-      <c r="I32" s="1" t="n">
+      <c r="J32" s="1" t="n">
         <v>0.36159</v>
       </c>
     </row>
@@ -1463,9 +1562,12 @@
         <v>1.421</v>
       </c>
       <c r="H33" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I33" s="1" t="n">
         <v>1.421</v>
       </c>
-      <c r="I33" s="1" t="n">
+      <c r="J33" s="1" t="n">
         <v>1.409</v>
       </c>
     </row>
@@ -1494,9 +1596,12 @@
         <v>0.59314</v>
       </c>
       <c r="H34" s="1" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="I34" s="1" t="n">
         <v>0.59693</v>
       </c>
-      <c r="I34" s="1" t="n">
+      <c r="J34" s="1" t="n">
         <v>0.5926900000000001</v>
       </c>
     </row>
@@ -1525,9 +1630,12 @@
         <v>1.2283</v>
       </c>
       <c r="H35" s="1" t="n">
+        <v>1.2232</v>
+      </c>
+      <c r="I35" s="1" t="n">
         <v>1.2283</v>
       </c>
-      <c r="I35" s="1" t="n">
+      <c r="J35" s="1" t="n">
         <v>1.2186</v>
       </c>
     </row>
@@ -1556,9 +1664,12 @@
         <v>80.27</v>
       </c>
       <c r="H36" s="1" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="I36" s="1" t="n">
         <v>80.5</v>
       </c>
-      <c r="I36" s="1" t="n">
+      <c r="J36" s="1" t="n">
         <v>80.27</v>
       </c>
     </row>
@@ -1587,10 +1698,13 @@
         <v>0.1993</v>
       </c>
       <c r="H37" s="1" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="I37" s="1" t="n">
         <v>0.204</v>
       </c>
-      <c r="I37" s="1" t="n">
-        <v>0.1977</v>
+      <c r="J37" s="1" t="n">
+        <v>0.1971</v>
       </c>
     </row>
     <row r="38">
@@ -1618,9 +1732,12 @@
         <v>1.851</v>
       </c>
       <c r="H38" s="1" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I38" s="1" t="n">
         <v>1.865</v>
       </c>
-      <c r="I38" s="1" t="n">
+      <c r="J38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -1649,9 +1766,12 @@
         <v>0.3316</v>
       </c>
       <c r="H39" s="1" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="I39" s="1" t="n">
         <v>0.3338</v>
       </c>
-      <c r="I39" s="1" t="n">
+      <c r="J39" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -1680,9 +1800,12 @@
         <v>0.8993</v>
       </c>
       <c r="H40" s="1" t="n">
+        <v>0.8996</v>
+      </c>
+      <c r="I40" s="1" t="n">
         <v>0.9115</v>
       </c>
-      <c r="I40" s="1" t="n">
+      <c r="J40" s="1" t="n">
         <v>0.899</v>
       </c>
     </row>
@@ -1711,10 +1834,13 @@
         <v>0.7122000000000001</v>
       </c>
       <c r="H41" s="1" t="n">
+        <v>0.7115</v>
+      </c>
+      <c r="I41" s="1" t="n">
         <v>0.7149</v>
       </c>
-      <c r="I41" s="1" t="n">
-        <v>0.7122000000000001</v>
+      <c r="J41" s="1" t="n">
+        <v>0.7115</v>
       </c>
     </row>
     <row r="42">
@@ -1742,9 +1868,12 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="H42" s="1" t="n">
+        <v>0.06630999999999999</v>
+      </c>
+      <c r="I42" s="1" t="n">
         <v>0.06769</v>
       </c>
-      <c r="I42" s="1" t="n">
+      <c r="J42" s="1" t="n">
         <v>0.06619999999999999</v>
       </c>
     </row>
@@ -1773,9 +1902,12 @@
         <v>113.86</v>
       </c>
       <c r="H43" s="1" t="n">
+        <v>113.49</v>
+      </c>
+      <c r="I43" s="1" t="n">
         <v>113.86</v>
       </c>
-      <c r="I43" s="1" t="n">
+      <c r="J43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -1804,9 +1936,12 @@
         <v>0.6562</v>
       </c>
       <c r="H44" s="1" t="n">
+        <v>0.6574</v>
+      </c>
+      <c r="I44" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="I44" s="1" t="n">
+      <c r="J44" s="1" t="n">
         <v>0.6562</v>
       </c>
     </row>
@@ -1835,9 +1970,12 @@
         <v>1.22</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>1.22</v>
+        <v>1.224</v>
       </c>
       <c r="I45" s="1" t="n">
+        <v>1.224</v>
+      </c>
+      <c r="J45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -1866,9 +2004,12 @@
         <v>0.02376</v>
       </c>
       <c r="H46" s="1" t="n">
+        <v>0.02378</v>
+      </c>
+      <c r="I46" s="1" t="n">
         <v>0.02392</v>
       </c>
-      <c r="I46" s="1" t="n">
+      <c r="J46" s="1" t="n">
         <v>0.02376</v>
       </c>
     </row>
@@ -1897,9 +2038,12 @@
         <v>55.05</v>
       </c>
       <c r="H47" s="1" t="n">
+        <v>55.05</v>
+      </c>
+      <c r="I47" s="1" t="n">
         <v>55.17</v>
       </c>
-      <c r="I47" s="1" t="n">
+      <c r="J47" s="1" t="n">
         <v>54.99</v>
       </c>
     </row>
@@ -1928,9 +2072,12 @@
         <v>0.06068</v>
       </c>
       <c r="H48" s="1" t="n">
+        <v>0.06056</v>
+      </c>
+      <c r="I48" s="1" t="n">
         <v>0.06081</v>
       </c>
-      <c r="I48" s="1" t="n">
+      <c r="J48" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -1959,9 +2106,12 @@
         <v>0.1083</v>
       </c>
       <c r="H49" s="1" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="I49" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="I49" s="1" t="n">
+      <c r="J49" s="1" t="n">
         <v>0.1076</v>
       </c>
     </row>
@@ -1990,9 +2140,12 @@
         <v>0.01804</v>
       </c>
       <c r="H50" s="1" t="n">
+        <v>0.01804</v>
+      </c>
+      <c r="I50" s="1" t="n">
         <v>0.01815</v>
       </c>
-      <c r="I50" s="1" t="n">
+      <c r="J50" s="1" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -2021,9 +2174,12 @@
         <v>1.4679</v>
       </c>
       <c r="H51" s="1" t="n">
+        <v>1.466</v>
+      </c>
+      <c r="I51" s="1" t="n">
         <v>1.4679</v>
       </c>
-      <c r="I51" s="1" t="n">
+      <c r="J51" s="1" t="n">
         <v>1.4618</v>
       </c>
     </row>
@@ -2052,9 +2208,12 @@
         <v>0.3596</v>
       </c>
       <c r="H52" s="1" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="I52" s="1" t="n">
         <v>0.3603</v>
       </c>
-      <c r="I52" s="1" t="n">
+      <c r="J52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -2083,9 +2242,12 @@
         <v>0.001946</v>
       </c>
       <c r="H53" s="1" t="n">
+        <v>0.001946</v>
+      </c>
+      <c r="I53" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="I53" s="1" t="n">
+      <c r="J53" s="1" t="n">
         <v>0.001942</v>
       </c>
     </row>
@@ -2114,9 +2276,12 @@
         <v>0.09551999999999999</v>
       </c>
       <c r="H54" s="1" t="n">
+        <v>0.09526</v>
+      </c>
+      <c r="I54" s="1" t="n">
         <v>0.09569</v>
       </c>
-      <c r="I54" s="1" t="n">
+      <c r="J54" s="1" t="n">
         <v>0.09514</v>
       </c>
     </row>
@@ -2145,9 +2310,12 @@
         <v>0.04097</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.04097</v>
+        <v>0.04099</v>
       </c>
       <c r="I55" s="1" t="n">
+        <v>0.04099</v>
+      </c>
+      <c r="J55" s="1" t="n">
         <v>0.04003</v>
       </c>
     </row>
@@ -2176,9 +2344,12 @@
         <v>0.29834</v>
       </c>
       <c r="H56" s="1" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="I56" s="1" t="n">
         <v>0.29861</v>
       </c>
-      <c r="I56" s="1" t="n">
+      <c r="J56" s="1" t="n">
         <v>0.29831</v>
       </c>
     </row>
@@ -2207,9 +2378,12 @@
         <v>0.005633</v>
       </c>
       <c r="H57" s="1" t="n">
+        <v>0.005692</v>
+      </c>
+      <c r="I57" s="1" t="n">
         <v>0.005824</v>
       </c>
-      <c r="I57" s="1" t="n">
+      <c r="J57" s="1" t="n">
         <v>0.005633</v>
       </c>
     </row>
@@ -2238,9 +2412,12 @@
         <v>4988.64</v>
       </c>
       <c r="H58" s="1" t="n">
+        <v>4993.88</v>
+      </c>
+      <c r="I58" s="1" t="n">
         <v>4998.37</v>
       </c>
-      <c r="I58" s="1" t="n">
+      <c r="J58" s="1" t="n">
         <v>4988.64</v>
       </c>
     </row>
@@ -2269,9 +2446,12 @@
         <v>0.4126</v>
       </c>
       <c r="H59" s="1" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="I59" s="1" t="n">
         <v>0.4246</v>
       </c>
-      <c r="I59" s="1" t="n">
+      <c r="J59" s="1" t="n">
         <v>0.4126</v>
       </c>
     </row>
@@ -2300,9 +2480,12 @@
         <v>0.04653</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>0.04683</v>
+        <v>0.04686</v>
       </c>
       <c r="I60" s="1" t="n">
+        <v>0.04686</v>
+      </c>
+      <c r="J60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -2331,9 +2514,12 @@
         <v>0.21344</v>
       </c>
       <c r="H61" s="1" t="n">
+        <v>0.21379</v>
+      </c>
+      <c r="I61" s="1" t="n">
         <v>0.21708</v>
       </c>
-      <c r="I61" s="1" t="n">
+      <c r="J61" s="1" t="n">
         <v>0.21344</v>
       </c>
     </row>
@@ -2362,9 +2548,12 @@
         <v>0.1071</v>
       </c>
       <c r="H62" s="1" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="I62" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="I62" s="1" t="n">
+      <c r="J62" s="1" t="n">
         <v>0.1065</v>
       </c>
     </row>
@@ -2393,9 +2582,12 @@
         <v>0.7299</v>
       </c>
       <c r="H63" s="1" t="n">
+        <v>0.7291</v>
+      </c>
+      <c r="I63" s="1" t="n">
         <v>0.7301</v>
       </c>
-      <c r="I63" s="1" t="n">
+      <c r="J63" s="1" t="n">
         <v>0.7255</v>
       </c>
     </row>
@@ -2424,9 +2616,12 @@
         <v>0.1668</v>
       </c>
       <c r="H64" s="1" t="n">
+        <v>0.1666</v>
+      </c>
+      <c r="I64" s="1" t="n">
         <v>0.1668</v>
       </c>
-      <c r="I64" s="1" t="n">
+      <c r="J64" s="1" t="n">
         <v>0.1658</v>
       </c>
     </row>
@@ -2455,9 +2650,12 @@
         <v>2.665</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>2.665</v>
+        <v>2.668</v>
       </c>
       <c r="I65" s="1" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="J65" s="1" t="n">
         <v>2.65</v>
       </c>
     </row>
@@ -2486,9 +2684,12 @@
         <v>0.04072</v>
       </c>
       <c r="H66" s="1" t="n">
+        <v>0.04057</v>
+      </c>
+      <c r="I66" s="1" t="n">
         <v>0.04072</v>
       </c>
-      <c r="I66" s="1" t="n">
+      <c r="J66" s="1" t="n">
         <v>0.04018</v>
       </c>
     </row>
@@ -2517,9 +2718,12 @@
         <v>0.04243</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>0.04261</v>
+        <v>0.04268</v>
       </c>
       <c r="I67" s="1" t="n">
+        <v>0.04268</v>
+      </c>
+      <c r="J67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -2548,9 +2752,12 @@
         <v>3.971</v>
       </c>
       <c r="H68" s="1" t="n">
+        <v>3.967</v>
+      </c>
+      <c r="I68" s="1" t="n">
         <v>3.971</v>
       </c>
-      <c r="I68" s="1" t="n">
+      <c r="J68" s="1" t="n">
         <v>3.951</v>
       </c>
     </row>
@@ -2579,9 +2786,12 @@
         <v>0.1261</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>0.1261</v>
+        <v>0.1265</v>
       </c>
       <c r="I69" s="1" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="J69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -2610,9 +2820,12 @@
         <v>6.328</v>
       </c>
       <c r="H70" s="1" t="n">
+        <v>6.326</v>
+      </c>
+      <c r="I70" s="1" t="n">
         <v>6.328</v>
       </c>
-      <c r="I70" s="1" t="n">
+      <c r="J70" s="1" t="n">
         <v>6.114</v>
       </c>
     </row>
@@ -2641,9 +2854,12 @@
         <v>0.04966</v>
       </c>
       <c r="H71" s="1" t="n">
+        <v>0.04995</v>
+      </c>
+      <c r="I71" s="1" t="n">
         <v>0.04999</v>
       </c>
-      <c r="I71" s="1" t="n">
+      <c r="J71" s="1" t="n">
         <v>0.04959</v>
       </c>
     </row>
@@ -2672,9 +2888,12 @@
         <v>0.004142</v>
       </c>
       <c r="H72" s="1" t="n">
+        <v>0.004153</v>
+      </c>
+      <c r="I72" s="1" t="n">
         <v>0.004181</v>
       </c>
-      <c r="I72" s="1" t="n">
+      <c r="J72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -2703,9 +2922,12 @@
         <v>5.985</v>
       </c>
       <c r="H73" s="1" t="n">
+        <v>6.009</v>
+      </c>
+      <c r="I73" s="1" t="n">
         <v>6.029</v>
       </c>
-      <c r="I73" s="1" t="n">
+      <c r="J73" s="1" t="n">
         <v>5.96</v>
       </c>
     </row>
@@ -2734,9 +2956,12 @@
         <v>0.163</v>
       </c>
       <c r="H74" s="1" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="I74" s="1" t="n">
         <v>0.1633</v>
       </c>
-      <c r="I74" s="1" t="n">
+      <c r="J74" s="1" t="n">
         <v>0.1619</v>
       </c>
     </row>
@@ -2765,9 +2990,12 @@
         <v>0.007287</v>
       </c>
       <c r="H75" s="1" t="n">
+        <v>0.007292</v>
+      </c>
+      <c r="I75" s="1" t="n">
         <v>0.007297</v>
       </c>
-      <c r="I75" s="1" t="n">
+      <c r="J75" s="1" t="n">
         <v>0.007261</v>
       </c>
     </row>
@@ -2796,9 +3024,12 @@
         <v>0.2128</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>0.2128</v>
+        <v>0.2199</v>
       </c>
       <c r="I76" s="1" t="n">
+        <v>0.2199</v>
+      </c>
+      <c r="J76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -2827,9 +3058,12 @@
         <v>0.005818</v>
       </c>
       <c r="H77" s="1" t="n">
+        <v>0.005813</v>
+      </c>
+      <c r="I77" s="1" t="n">
         <v>0.005826</v>
       </c>
-      <c r="I77" s="1" t="n">
+      <c r="J77" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -2858,9 +3092,12 @@
         <v>0.1017</v>
       </c>
       <c r="H78" s="1" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="I78" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="I78" s="1" t="n">
+      <c r="J78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -2889,9 +3126,12 @@
         <v>0.006265</v>
       </c>
       <c r="H79" s="1" t="n">
+        <v>0.00626</v>
+      </c>
+      <c r="I79" s="1" t="n">
         <v>0.006292</v>
       </c>
-      <c r="I79" s="1" t="n">
+      <c r="J79" s="1" t="n">
         <v>0.006237</v>
       </c>
     </row>
@@ -2920,9 +3160,12 @@
         <v>33.51</v>
       </c>
       <c r="H80" s="1" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="I80" s="1" t="n">
         <v>33.51</v>
       </c>
-      <c r="I80" s="1" t="n">
+      <c r="J80" s="1" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -2951,9 +3194,12 @@
         <v>0.04041</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>0.0405</v>
+        <v>0.04051</v>
       </c>
       <c r="I81" s="1" t="n">
+        <v>0.04051</v>
+      </c>
+      <c r="J81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -2982,9 +3228,12 @@
         <v>0.16723</v>
       </c>
       <c r="H82" s="1" t="n">
+        <v>0.16702</v>
+      </c>
+      <c r="I82" s="1" t="n">
         <v>0.1675</v>
       </c>
-      <c r="I82" s="1" t="n">
+      <c r="J82" s="1" t="n">
         <v>0.16679</v>
       </c>
     </row>
@@ -3016,6 +3265,9 @@
         <v>0.1037</v>
       </c>
       <c r="I83" s="1" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="J83" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -3044,10 +3296,13 @@
         <v>0.08825</v>
       </c>
       <c r="H84" s="1" t="n">
+        <v>0.08756</v>
+      </c>
+      <c r="I84" s="1" t="n">
         <v>0.08848</v>
       </c>
-      <c r="I84" s="1" t="n">
-        <v>0.08803999999999999</v>
+      <c r="J84" s="1" t="n">
+        <v>0.08756</v>
       </c>
     </row>
     <row r="85">
@@ -3075,9 +3330,12 @@
         <v>0.02317</v>
       </c>
       <c r="H85" s="1" t="n">
+        <v>0.02311</v>
+      </c>
+      <c r="I85" s="1" t="n">
         <v>0.02331</v>
       </c>
-      <c r="I85" s="1" t="n">
+      <c r="J85" s="1" t="n">
         <v>0.02311</v>
       </c>
     </row>
@@ -3109,6 +3367,9 @@
         <v>0.24</v>
       </c>
       <c r="I86" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -3137,9 +3398,12 @@
         <v>357.71</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>357.71</v>
+        <v>358.06</v>
       </c>
       <c r="I87" s="1" t="n">
+        <v>358.06</v>
+      </c>
+      <c r="J87" s="1" t="n">
         <v>355.75</v>
       </c>
     </row>
@@ -3168,9 +3432,12 @@
         <v>0.00347</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>0.00347</v>
+        <v>0.00348</v>
       </c>
       <c r="I88" s="1" t="n">
+        <v>0.00348</v>
+      </c>
+      <c r="J88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -3199,9 +3466,12 @@
         <v>8.278</v>
       </c>
       <c r="H89" s="1" t="n">
+        <v>8.285</v>
+      </c>
+      <c r="I89" s="1" t="n">
         <v>8.301</v>
       </c>
-      <c r="I89" s="1" t="n">
+      <c r="J89" s="1" t="n">
         <v>8.257</v>
       </c>
     </row>
@@ -3230,9 +3500,12 @@
         <v>0.005915</v>
       </c>
       <c r="H90" s="1" t="n">
+        <v>0.005917</v>
+      </c>
+      <c r="I90" s="1" t="n">
         <v>0.005945</v>
       </c>
-      <c r="I90" s="1" t="n">
+      <c r="J90" s="1" t="n">
         <v>0.005905</v>
       </c>
     </row>
@@ -3261,9 +3534,12 @@
         <v>0.06822</v>
       </c>
       <c r="H91" s="1" t="n">
+        <v>0.06838</v>
+      </c>
+      <c r="I91" s="1" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="I91" s="1" t="n">
+      <c r="J91" s="1" t="n">
         <v>0.06822</v>
       </c>
     </row>
@@ -3292,10 +3568,13 @@
         <v>0.02897</v>
       </c>
       <c r="H92" s="1" t="n">
+        <v>0.02867</v>
+      </c>
+      <c r="I92" s="1" t="n">
         <v>0.02897</v>
       </c>
-      <c r="I92" s="1" t="n">
-        <v>0.02869</v>
+      <c r="J92" s="1" t="n">
+        <v>0.02867</v>
       </c>
     </row>
     <row r="93">
@@ -3323,9 +3602,12 @@
         <v>5.195</v>
       </c>
       <c r="H93" s="1" t="n">
+        <v>5.165</v>
+      </c>
+      <c r="I93" s="1" t="n">
         <v>5.202</v>
       </c>
-      <c r="I93" s="1" t="n">
+      <c r="J93" s="1" t="n">
         <v>5.159</v>
       </c>
     </row>
@@ -3354,9 +3636,12 @@
         <v>0.000228</v>
       </c>
       <c r="H94" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="I94" s="1" t="n">
         <v>0.000228</v>
       </c>
-      <c r="I94" s="1" t="n">
+      <c r="J94" s="1" t="n">
         <v>0.000226</v>
       </c>
     </row>
@@ -3385,9 +3670,12 @@
         <v>0.9248</v>
       </c>
       <c r="H95" s="1" t="n">
+        <v>0.9238</v>
+      </c>
+      <c r="I95" s="1" t="n">
         <v>0.9248</v>
       </c>
-      <c r="I95" s="1" t="n">
+      <c r="J95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -3416,9 +3704,12 @@
         <v>2.0874</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>2.0874</v>
+        <v>2.0959</v>
       </c>
       <c r="I96" s="1" t="n">
+        <v>2.0959</v>
+      </c>
+      <c r="J96" s="1" t="n">
         <v>2.0598</v>
       </c>
     </row>
@@ -3447,10 +3738,13 @@
         <v>0.3696</v>
       </c>
       <c r="H97" s="1" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I97" s="1" t="n">
         <v>0.3722</v>
       </c>
-      <c r="I97" s="1" t="n">
-        <v>0.3686</v>
+      <c r="J97" s="1" t="n">
+        <v>0.3681</v>
       </c>
     </row>
     <row r="98">
@@ -3478,9 +3772,12 @@
         <v>1.621</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>1.621</v>
+        <v>1.625</v>
       </c>
       <c r="I98" s="1" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="J98" s="1" t="n">
         <v>1.613</v>
       </c>
     </row>
@@ -3509,10 +3806,13 @@
         <v>0.2342</v>
       </c>
       <c r="H99" s="1" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="I99" s="1" t="n">
         <v>0.2368</v>
       </c>
-      <c r="I99" s="1" t="n">
-        <v>0.2342</v>
+      <c r="J99" s="1" t="n">
+        <v>0.2336</v>
       </c>
     </row>
     <row r="100">
@@ -3540,9 +3840,12 @@
         <v>0.13683</v>
       </c>
       <c r="H100" s="1" t="n">
+        <v>0.13608</v>
+      </c>
+      <c r="I100" s="1" t="n">
         <v>0.13683</v>
       </c>
-      <c r="I100" s="1" t="n">
+      <c r="J100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -3571,9 +3874,12 @@
         <v>0.07051</v>
       </c>
       <c r="H101" s="1" t="n">
+        <v>0.07083</v>
+      </c>
+      <c r="I101" s="1" t="n">
         <v>0.07115</v>
       </c>
-      <c r="I101" s="1" t="n">
+      <c r="J101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -3602,9 +3908,12 @@
         <v>0.0010855</v>
       </c>
       <c r="H102" s="1" t="n">
+        <v>0.0010832</v>
+      </c>
+      <c r="I102" s="1" t="n">
         <v>0.0010875</v>
       </c>
-      <c r="I102" s="1" t="n">
+      <c r="J102" s="1" t="n">
         <v>0.0010832</v>
       </c>
     </row>
@@ -3633,9 +3942,12 @@
         <v>0.003403</v>
       </c>
       <c r="H103" s="1" t="n">
+        <v>0.003412</v>
+      </c>
+      <c r="I103" s="1" t="n">
         <v>0.003424</v>
       </c>
-      <c r="I103" s="1" t="n">
+      <c r="J103" s="1" t="n">
         <v>0.003403</v>
       </c>
     </row>
@@ -3664,9 +3976,12 @@
         <v>0.27472</v>
       </c>
       <c r="H104" s="1" t="n">
+        <v>0.27474</v>
+      </c>
+      <c r="I104" s="1" t="n">
         <v>0.27751</v>
       </c>
-      <c r="I104" s="1" t="n">
+      <c r="J104" s="1" t="n">
         <v>0.27472</v>
       </c>
     </row>
@@ -3695,9 +4010,12 @@
         <v>0.01257</v>
       </c>
       <c r="H105" s="1" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="I105" s="1" t="n">
         <v>0.01257</v>
       </c>
-      <c r="I105" s="1" t="n">
+      <c r="J105" s="1" t="n">
         <v>0.01243</v>
       </c>
     </row>
@@ -3726,9 +4044,12 @@
         <v>0.13537</v>
       </c>
       <c r="H106" s="1" t="n">
+        <v>0.13528</v>
+      </c>
+      <c r="I106" s="1" t="n">
         <v>0.13569</v>
       </c>
-      <c r="I106" s="1" t="n">
+      <c r="J106" s="1" t="n">
         <v>0.13329</v>
       </c>
     </row>
@@ -3757,9 +4078,12 @@
         <v>0.3508</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>0.3508</v>
+        <v>0.3516</v>
       </c>
       <c r="I107" s="1" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="J107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -3788,9 +4112,12 @@
         <v>0.1434</v>
       </c>
       <c r="H108" s="1" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="I108" s="1" t="n">
         <v>0.1436</v>
       </c>
-      <c r="I108" s="1" t="n">
+      <c r="J108" s="1" t="n">
         <v>0.1426</v>
       </c>
     </row>
@@ -3819,9 +4146,12 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="I109" s="1" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="J109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -3850,9 +4180,12 @@
         <v>0.016241</v>
       </c>
       <c r="H110" s="1" t="n">
+        <v>0.016234</v>
+      </c>
+      <c r="I110" s="1" t="n">
         <v>0.016308</v>
       </c>
-      <c r="I110" s="1" t="n">
+      <c r="J110" s="1" t="n">
         <v>0.016195</v>
       </c>
     </row>
@@ -3881,9 +4214,12 @@
         <v>0.03818</v>
       </c>
       <c r="H111" s="1" t="n">
+        <v>0.038092</v>
+      </c>
+      <c r="I111" s="1" t="n">
         <v>0.038335</v>
       </c>
-      <c r="I111" s="1" t="n">
+      <c r="J111" s="1" t="n">
         <v>0.03774</v>
       </c>
     </row>
@@ -3912,9 +4248,12 @@
         <v>0.12008</v>
       </c>
       <c r="H112" s="1" t="n">
+        <v>0.11958</v>
+      </c>
+      <c r="I112" s="1" t="n">
         <v>0.12031</v>
       </c>
-      <c r="I112" s="1" t="n">
+      <c r="J112" s="1" t="n">
         <v>0.11926</v>
       </c>
     </row>
@@ -3943,10 +4282,13 @@
         <v>0.09574000000000001</v>
       </c>
       <c r="H113" s="1" t="n">
+        <v>0.09418</v>
+      </c>
+      <c r="I113" s="1" t="n">
         <v>0.09574000000000001</v>
       </c>
-      <c r="I113" s="1" t="n">
-        <v>0.09426</v>
+      <c r="J113" s="1" t="n">
+        <v>0.09418</v>
       </c>
     </row>
     <row r="114">
@@ -3974,9 +4316,12 @@
         <v>0.13063</v>
       </c>
       <c r="H114" s="1" t="n">
+        <v>0.13006</v>
+      </c>
+      <c r="I114" s="1" t="n">
         <v>0.13063</v>
       </c>
-      <c r="I114" s="1" t="n">
+      <c r="J114" s="1" t="n">
         <v>0.12895</v>
       </c>
     </row>
@@ -4005,9 +4350,12 @@
         <v>0.2649</v>
       </c>
       <c r="H115" s="1" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="I115" s="1" t="n">
         <v>0.2656</v>
       </c>
-      <c r="I115" s="1" t="n">
+      <c r="J115" s="1" t="n">
         <v>0.2638</v>
       </c>
     </row>
@@ -4036,9 +4384,12 @@
         <v>0.04911</v>
       </c>
       <c r="H116" s="1" t="n">
+        <v>0.04961</v>
+      </c>
+      <c r="I116" s="1" t="n">
         <v>0.0529</v>
       </c>
-      <c r="I116" s="1" t="n">
+      <c r="J116" s="1" t="n">
         <v>0.04891</v>
       </c>
     </row>
@@ -4067,9 +4418,12 @@
         <v>0.0914</v>
       </c>
       <c r="H117" s="1" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="I117" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="I117" s="1" t="n">
+      <c r="J117" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -4098,9 +4452,12 @@
         <v>0.05501</v>
       </c>
       <c r="H118" s="1" t="n">
+        <v>0.0554</v>
+      </c>
+      <c r="I118" s="1" t="n">
         <v>0.05563</v>
       </c>
-      <c r="I118" s="1" t="n">
+      <c r="J118" s="1" t="n">
         <v>0.05501</v>
       </c>
     </row>
@@ -4129,9 +4486,12 @@
         <v>0.01507</v>
       </c>
       <c r="H119" s="1" t="n">
+        <v>0.01507</v>
+      </c>
+      <c r="I119" s="1" t="n">
         <v>0.01515</v>
       </c>
-      <c r="I119" s="1" t="n">
+      <c r="J119" s="1" t="n">
         <v>0.01505</v>
       </c>
     </row>
@@ -4160,9 +4520,12 @@
         <v>3.062</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>3.062</v>
+        <v>3.065</v>
       </c>
       <c r="I120" s="1" t="n">
+        <v>3.065</v>
+      </c>
+      <c r="J120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -4191,9 +4554,12 @@
         <v>1.85</v>
       </c>
       <c r="H121" s="1" t="n">
+        <v>1.849</v>
+      </c>
+      <c r="I121" s="1" t="n">
         <v>1.855</v>
       </c>
-      <c r="I121" s="1" t="n">
+      <c r="J121" s="1" t="n">
         <v>1.849</v>
       </c>
     </row>
@@ -4222,9 +4588,12 @@
         <v>1.2991</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>1.2991</v>
+        <v>1.3006</v>
       </c>
       <c r="I122" s="1" t="n">
+        <v>1.3006</v>
+      </c>
+      <c r="J122" s="1" t="n">
         <v>1.2934</v>
       </c>
     </row>
@@ -4253,9 +4622,12 @@
         <v>0.316</v>
       </c>
       <c r="H123" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="I123" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="I123" s="1" t="n">
+      <c r="J123" s="1" t="n">
         <v>0.316</v>
       </c>
     </row>
@@ -4284,9 +4656,12 @@
         <v>0.12202</v>
       </c>
       <c r="H124" s="1" t="n">
+        <v>0.12216</v>
+      </c>
+      <c r="I124" s="1" t="n">
         <v>0.12506</v>
       </c>
-      <c r="I124" s="1" t="n">
+      <c r="J124" s="1" t="n">
         <v>0.12202</v>
       </c>
     </row>
@@ -4315,9 +4690,12 @@
         <v>0.008389000000000001</v>
       </c>
       <c r="H125" s="1" t="n">
+        <v>0.008323000000000001</v>
+      </c>
+      <c r="I125" s="1" t="n">
         <v>0.008459</v>
       </c>
-      <c r="I125" s="1" t="n">
+      <c r="J125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -4346,9 +4724,12 @@
         <v>0.01599</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>0.01599</v>
+        <v>0.01602</v>
       </c>
       <c r="I126" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="J126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -4377,9 +4758,12 @@
         <v>0.04436</v>
       </c>
       <c r="H127" s="1" t="n">
+        <v>0.04425</v>
+      </c>
+      <c r="I127" s="1" t="n">
         <v>0.04468</v>
       </c>
-      <c r="I127" s="1" t="n">
+      <c r="J127" s="1" t="n">
         <v>0.04402</v>
       </c>
     </row>
@@ -4408,9 +4792,12 @@
         <v>0.04717</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>0.04717</v>
+        <v>0.04727</v>
       </c>
       <c r="I128" s="1" t="n">
+        <v>0.04727</v>
+      </c>
+      <c r="J128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -4439,9 +4826,12 @@
         <v>0.09543</v>
       </c>
       <c r="H129" s="1" t="n">
+        <v>0.09616</v>
+      </c>
+      <c r="I129" s="1" t="n">
         <v>0.09635000000000001</v>
       </c>
-      <c r="I129" s="1" t="n">
+      <c r="J129" s="1" t="n">
         <v>0.09543</v>
       </c>
     </row>
@@ -4470,10 +4860,13 @@
         <v>0.09891</v>
       </c>
       <c r="H130" s="1" t="n">
+        <v>0.09848</v>
+      </c>
+      <c r="I130" s="1" t="n">
         <v>0.09927</v>
       </c>
-      <c r="I130" s="1" t="n">
-        <v>0.09877</v>
+      <c r="J130" s="1" t="n">
+        <v>0.09848</v>
       </c>
     </row>
     <row r="131">
@@ -4501,9 +4894,12 @@
         <v>0.16612</v>
       </c>
       <c r="H131" s="1" t="n">
+        <v>0.16592</v>
+      </c>
+      <c r="I131" s="1" t="n">
         <v>0.16612</v>
       </c>
-      <c r="I131" s="1" t="n">
+      <c r="J131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -4532,9 +4928,12 @@
         <v>0.01702</v>
       </c>
       <c r="H132" s="1" t="n">
+        <v>0.01697</v>
+      </c>
+      <c r="I132" s="1" t="n">
         <v>0.01702</v>
       </c>
-      <c r="I132" s="1" t="n">
+      <c r="J132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -4563,9 +4962,12 @@
         <v>0.06671000000000001</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>0.06671000000000001</v>
+        <v>0.06683</v>
       </c>
       <c r="I133" s="1" t="n">
+        <v>0.06683</v>
+      </c>
+      <c r="J133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -4594,9 +4996,12 @@
         <v>0.3025</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>0.3025</v>
+        <v>0.3029</v>
       </c>
       <c r="I134" s="1" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="J134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -4625,9 +5030,12 @@
         <v>0.0452</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>0.0452</v>
+        <v>0.04526</v>
       </c>
       <c r="I135" s="1" t="n">
+        <v>0.04526</v>
+      </c>
+      <c r="J135" s="1" t="n">
         <v>0.04508</v>
       </c>
     </row>
@@ -4656,9 +5064,12 @@
         <v>0.782</v>
       </c>
       <c r="H136" s="1" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="I136" s="1" t="n">
         <v>0.783</v>
       </c>
-      <c r="I136" s="1" t="n">
+      <c r="J136" s="1" t="n">
         <v>0.781</v>
       </c>
     </row>
@@ -4687,9 +5098,12 @@
         <v>0.1167</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>0.1168</v>
+        <v>0.1169</v>
       </c>
       <c r="I137" s="1" t="n">
+        <v>0.1169</v>
+      </c>
+      <c r="J137" s="1" t="n">
         <v>0.1162</v>
       </c>
     </row>
@@ -4718,9 +5132,12 @@
         <v>0.14729</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>0.14729</v>
+        <v>0.14739</v>
       </c>
       <c r="I138" s="1" t="n">
+        <v>0.14739</v>
+      </c>
+      <c r="J138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -4749,9 +5166,12 @@
         <v>0.0572</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>0.05727</v>
+        <v>0.0573</v>
       </c>
       <c r="I139" s="1" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="J139" s="1" t="n">
         <v>0.05699</v>
       </c>
     </row>
@@ -4780,9 +5200,12 @@
         <v>0.007283</v>
       </c>
       <c r="H140" s="1" t="n">
+        <v>0.007278</v>
+      </c>
+      <c r="I140" s="1" t="n">
         <v>0.007295</v>
       </c>
-      <c r="I140" s="1" t="n">
+      <c r="J140" s="1" t="n">
         <v>0.007267</v>
       </c>
     </row>
@@ -4811,9 +5234,12 @@
         <v>0.09587</v>
       </c>
       <c r="H141" s="1" t="n">
+        <v>0.09591</v>
+      </c>
+      <c r="I141" s="1" t="n">
         <v>0.09601</v>
       </c>
-      <c r="I141" s="1" t="n">
+      <c r="J141" s="1" t="n">
         <v>0.09569</v>
       </c>
     </row>
@@ -4842,9 +5268,12 @@
         <v>0.08363</v>
       </c>
       <c r="H142" s="1" t="n">
+        <v>0.0835</v>
+      </c>
+      <c r="I142" s="1" t="n">
         <v>0.08363</v>
       </c>
-      <c r="I142" s="1" t="n">
+      <c r="J142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -4873,9 +5302,12 @@
         <v>0.00859</v>
       </c>
       <c r="H143" s="1" t="n">
+        <v>0.008569999999999999</v>
+      </c>
+      <c r="I143" s="1" t="n">
         <v>0.0086</v>
       </c>
-      <c r="I143" s="1" t="n">
+      <c r="J143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -4904,10 +5336,13 @@
         <v>0.07242</v>
       </c>
       <c r="H144" s="1" t="n">
+        <v>0.07235</v>
+      </c>
+      <c r="I144" s="1" t="n">
         <v>0.07288</v>
       </c>
-      <c r="I144" s="1" t="n">
-        <v>0.07240000000000001</v>
+      <c r="J144" s="1" t="n">
+        <v>0.07235</v>
       </c>
     </row>
     <row r="145">
@@ -4935,9 +5370,12 @@
         <v>0.4274</v>
       </c>
       <c r="H145" s="1" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="I145" s="1" t="n">
         <v>0.4305</v>
       </c>
-      <c r="I145" s="1" t="n">
+      <c r="J145" s="1" t="n">
         <v>0.4271</v>
       </c>
     </row>
@@ -4966,9 +5404,12 @@
         <v>0.03228</v>
       </c>
       <c r="H146" s="1" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="I146" s="1" t="n">
         <v>0.03276</v>
       </c>
-      <c r="I146" s="1" t="n">
+      <c r="J146" s="1" t="n">
         <v>0.0322</v>
       </c>
     </row>
@@ -4997,9 +5438,12 @@
         <v>390.43</v>
       </c>
       <c r="H147" s="1" t="n">
+        <v>390.45</v>
+      </c>
+      <c r="I147" s="1" t="n">
         <v>390.55</v>
       </c>
-      <c r="I147" s="1" t="n">
+      <c r="J147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -5028,9 +5472,12 @@
         <v>0.03304</v>
       </c>
       <c r="H148" s="1" t="n">
+        <v>0.03301</v>
+      </c>
+      <c r="I148" s="1" t="n">
         <v>0.0333</v>
       </c>
-      <c r="I148" s="1" t="n">
+      <c r="J148" s="1" t="n">
         <v>0.0329</v>
       </c>
     </row>
@@ -5059,9 +5506,12 @@
         <v>0.05314</v>
       </c>
       <c r="H149" s="1" t="n">
+        <v>0.05298</v>
+      </c>
+      <c r="I149" s="1" t="n">
         <v>0.05322</v>
       </c>
-      <c r="I149" s="1" t="n">
+      <c r="J149" s="1" t="n">
         <v>0.05289</v>
       </c>
     </row>
@@ -5090,9 +5540,12 @@
         <v>0.0004409</v>
       </c>
       <c r="H150" s="1" t="n">
+        <v>0.0004403</v>
+      </c>
+      <c r="I150" s="1" t="n">
         <v>0.000443</v>
       </c>
-      <c r="I150" s="1" t="n">
+      <c r="J150" s="1" t="n">
         <v>0.000439</v>
       </c>
     </row>
@@ -5121,9 +5574,12 @@
         <v>0.02184</v>
       </c>
       <c r="H151" s="1" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="I151" s="1" t="n">
         <v>0.02189</v>
       </c>
-      <c r="I151" s="1" t="n">
+      <c r="J151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -5152,9 +5608,12 @@
         <v>0.001781</v>
       </c>
       <c r="H152" s="1" t="n">
+        <v>0.001782</v>
+      </c>
+      <c r="I152" s="1" t="n">
         <v>0.001783</v>
       </c>
-      <c r="I152" s="1" t="n">
+      <c r="J152" s="1" t="n">
         <v>0.001768</v>
       </c>
     </row>
@@ -5183,9 +5642,12 @@
         <v>6e-06</v>
       </c>
       <c r="H153" s="1" t="n">
+        <v>6.1e-06</v>
+      </c>
+      <c r="I153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
-      <c r="I153" s="1" t="n">
+      <c r="J153" s="1" t="n">
         <v>6e-06</v>
       </c>
     </row>
@@ -5214,9 +5676,12 @@
         <v>0.1602</v>
       </c>
       <c r="H154" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="I154" s="1" t="n">
         <v>0.1602</v>
       </c>
-      <c r="I154" s="1" t="n">
+      <c r="J154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -5245,9 +5710,12 @@
         <v>0.03765</v>
       </c>
       <c r="H155" s="1" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="I155" s="1" t="n">
         <v>0.03768</v>
       </c>
-      <c r="I155" s="1" t="n">
+      <c r="J155" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -5276,9 +5744,12 @@
         <v>0.005375</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>0.005402</v>
+        <v>0.005404</v>
       </c>
       <c r="I156" s="1" t="n">
+        <v>0.005404</v>
+      </c>
+      <c r="J156" s="1" t="n">
         <v>0.005364</v>
       </c>
     </row>
@@ -5307,9 +5778,12 @@
         <v>0.02276</v>
       </c>
       <c r="H157" s="1" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="I157" s="1" t="n">
         <v>0.02284</v>
       </c>
-      <c r="I157" s="1" t="n">
+      <c r="J157" s="1" t="n">
         <v>0.02276</v>
       </c>
     </row>
@@ -5338,9 +5812,12 @@
         <v>1.09</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>1.09</v>
+        <v>1.096</v>
       </c>
       <c r="I158" s="1" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="J158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -5369,9 +5846,12 @@
         <v>2.562</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>2.562</v>
+        <v>2.565</v>
       </c>
       <c r="I159" s="1" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="J159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -5400,9 +5880,12 @@
         <v>4.843</v>
       </c>
       <c r="H160" s="1" t="n">
+        <v>4.842</v>
+      </c>
+      <c r="I160" s="1" t="n">
         <v>4.858</v>
       </c>
-      <c r="I160" s="1" t="n">
+      <c r="J160" s="1" t="n">
         <v>4.836</v>
       </c>
     </row>
@@ -5431,9 +5914,12 @@
         <v>0.1605</v>
       </c>
       <c r="H161" s="1" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="I161" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="I161" s="1" t="n">
+      <c r="J161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -5462,9 +5948,12 @@
         <v>0.20639</v>
       </c>
       <c r="H162" s="1" t="n">
+        <v>0.20614</v>
+      </c>
+      <c r="I162" s="1" t="n">
         <v>0.20754</v>
       </c>
-      <c r="I162" s="1" t="n">
+      <c r="J162" s="1" t="n">
         <v>0.20584</v>
       </c>
     </row>
@@ -5493,9 +5982,12 @@
         <v>0.03939</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>0.03939</v>
+        <v>0.03941</v>
       </c>
       <c r="I163" s="1" t="n">
+        <v>0.03941</v>
+      </c>
+      <c r="J163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -5524,9 +6016,12 @@
         <v>0.06339</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>0.06339</v>
+        <v>0.0635</v>
       </c>
       <c r="I164" s="1" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="J164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -5555,9 +6050,12 @@
         <v>0.3618</v>
       </c>
       <c r="H165" s="1" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="I165" s="1" t="n">
         <v>0.3618</v>
       </c>
-      <c r="I165" s="1" t="n">
+      <c r="J165" s="1" t="n">
         <v>0.3525</v>
       </c>
     </row>
@@ -5586,9 +6084,12 @@
         <v>139.21</v>
       </c>
       <c r="H166" s="1" t="n">
+        <v>139.2</v>
+      </c>
+      <c r="I166" s="1" t="n">
         <v>139.27</v>
       </c>
-      <c r="I166" s="1" t="n">
+      <c r="J166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -5617,9 +6118,12 @@
         <v>0.0006464</v>
       </c>
       <c r="H167" s="1" t="n">
+        <v>0.0006431</v>
+      </c>
+      <c r="I167" s="1" t="n">
         <v>0.0006533</v>
       </c>
-      <c r="I167" s="1" t="n">
+      <c r="J167" s="1" t="n">
         <v>0.0006431</v>
       </c>
     </row>
@@ -5648,9 +6152,12 @@
         <v>0.01647</v>
       </c>
       <c r="H168" s="1" t="n">
+        <v>0.01653</v>
+      </c>
+      <c r="I168" s="1" t="n">
         <v>0.01678</v>
       </c>
-      <c r="I168" s="1" t="n">
+      <c r="J168" s="1" t="n">
         <v>0.01629</v>
       </c>
     </row>
@@ -5679,9 +6186,12 @@
         <v>0.04806</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>0.04806</v>
+        <v>0.04807</v>
       </c>
       <c r="I169" s="1" t="n">
+        <v>0.04807</v>
+      </c>
+      <c r="J169" s="1" t="n">
         <v>0.04785</v>
       </c>
     </row>
@@ -5710,9 +6220,12 @@
         <v>4.289</v>
       </c>
       <c r="H170" s="1" t="n">
+        <v>4.292</v>
+      </c>
+      <c r="I170" s="1" t="n">
         <v>4.298</v>
       </c>
-      <c r="I170" s="1" t="n">
+      <c r="J170" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -5741,10 +6254,13 @@
         <v>0.03866</v>
       </c>
       <c r="H171" s="1" t="n">
+        <v>0.03831</v>
+      </c>
+      <c r="I171" s="1" t="n">
         <v>0.03874</v>
       </c>
-      <c r="I171" s="1" t="n">
-        <v>0.03836</v>
+      <c r="J171" s="1" t="n">
+        <v>0.03831</v>
       </c>
     </row>
     <row r="172">
@@ -5772,9 +6288,12 @@
         <v>0.0427</v>
       </c>
       <c r="H172" s="1" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="I172" s="1" t="n">
         <v>0.0431</v>
       </c>
-      <c r="I172" s="1" t="n">
+      <c r="J172" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -5803,10 +6322,13 @@
         <v>0.024556</v>
       </c>
       <c r="H173" s="1" t="n">
+        <v>0.023799</v>
+      </c>
+      <c r="I173" s="1" t="n">
         <v>0.024556</v>
       </c>
-      <c r="I173" s="1" t="n">
-        <v>0.02382</v>
+      <c r="J173" s="1" t="n">
+        <v>0.023799</v>
       </c>
     </row>
     <row r="174">
@@ -5834,9 +6356,12 @@
         <v>1.0803</v>
       </c>
       <c r="H174" s="1" t="n">
+        <v>1.0802</v>
+      </c>
+      <c r="I174" s="1" t="n">
         <v>1.0803</v>
       </c>
-      <c r="I174" s="1" t="n">
+      <c r="J174" s="1" t="n">
         <v>1.0704</v>
       </c>
     </row>
@@ -5865,10 +6390,13 @@
         <v>0.028452</v>
       </c>
       <c r="H175" s="1" t="n">
+        <v>0.028121</v>
+      </c>
+      <c r="I175" s="1" t="n">
         <v>0.028967</v>
       </c>
-      <c r="I175" s="1" t="n">
-        <v>0.028452</v>
+      <c r="J175" s="1" t="n">
+        <v>0.028121</v>
       </c>
     </row>
     <row r="176">
@@ -5896,9 +6424,12 @@
         <v>0.02195</v>
       </c>
       <c r="H176" s="1" t="n">
+        <v>0.02192</v>
+      </c>
+      <c r="I176" s="1" t="n">
         <v>0.02195</v>
       </c>
-      <c r="I176" s="1" t="n">
+      <c r="J176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -5927,9 +6458,12 @@
         <v>0.5453</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>0.5453</v>
+        <v>0.5501</v>
       </c>
       <c r="I177" s="1" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="J177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -5958,9 +6492,12 @@
         <v>0.08266</v>
       </c>
       <c r="H178" s="1" t="n">
+        <v>0.08254</v>
+      </c>
+      <c r="I178" s="1" t="n">
         <v>0.08276</v>
       </c>
-      <c r="I178" s="1" t="n">
+      <c r="J178" s="1" t="n">
         <v>0.08248999999999999</v>
       </c>
     </row>
@@ -5989,9 +6526,12 @@
         <v>0.0214</v>
       </c>
       <c r="H179" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="I179" s="1" t="n">
         <v>0.0214</v>
       </c>
-      <c r="I179" s="1" t="n">
+      <c r="J179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -6020,9 +6560,12 @@
         <v>0.27157</v>
       </c>
       <c r="H180" s="1" t="n">
+        <v>0.27151</v>
+      </c>
+      <c r="I180" s="1" t="n">
         <v>0.27157</v>
       </c>
-      <c r="I180" s="1" t="n">
+      <c r="J180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -6054,6 +6597,9 @@
         <v>0.0042</v>
       </c>
       <c r="I181" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="J181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -6082,10 +6628,13 @@
         <v>0.07965</v>
       </c>
       <c r="H182" s="1" t="n">
+        <v>0.07902000000000001</v>
+      </c>
+      <c r="I182" s="1" t="n">
         <v>0.07981000000000001</v>
       </c>
-      <c r="I182" s="1" t="n">
-        <v>0.07931000000000001</v>
+      <c r="J182" s="1" t="n">
+        <v>0.07902000000000001</v>
       </c>
     </row>
     <row r="183">
@@ -6113,9 +6662,12 @@
         <v>0.02349</v>
       </c>
       <c r="H183" s="1" t="n">
+        <v>0.02351</v>
+      </c>
+      <c r="I183" s="1" t="n">
         <v>0.02357</v>
       </c>
-      <c r="I183" s="1" t="n">
+      <c r="J183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -6144,9 +6696,12 @@
         <v>7.002e-05</v>
       </c>
       <c r="H184" s="1" t="n">
+        <v>6.993e-05</v>
+      </c>
+      <c r="I184" s="1" t="n">
         <v>7.002e-05</v>
       </c>
-      <c r="I184" s="1" t="n">
+      <c r="J184" s="1" t="n">
         <v>6.957e-05</v>
       </c>
     </row>
@@ -6175,9 +6730,12 @@
         <v>0.0214</v>
       </c>
       <c r="H185" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="I185" s="1" t="n">
         <v>0.0214</v>
       </c>
-      <c r="I185" s="1" t="n">
+      <c r="J185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -6206,9 +6764,12 @@
         <v>0.01627</v>
       </c>
       <c r="H186" s="1" t="n">
+        <v>0.01627</v>
+      </c>
+      <c r="I186" s="1" t="n">
         <v>0.01632</v>
       </c>
-      <c r="I186" s="1" t="n">
+      <c r="J186" s="1" t="n">
         <v>0.01623</v>
       </c>
     </row>
@@ -6240,6 +6801,9 @@
         <v>0.981</v>
       </c>
       <c r="I187" s="1" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="J187" s="1" t="n">
         <v>0.971</v>
       </c>
     </row>
@@ -6268,9 +6832,12 @@
         <v>0.0238</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>0.0239</v>
+        <v>0.024</v>
       </c>
       <c r="I188" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="J188" s="1" t="n">
         <v>0.0237</v>
       </c>
     </row>
@@ -6299,9 +6866,12 @@
         <v>1.8712</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>1.8712</v>
+        <v>1.8739</v>
       </c>
       <c r="I189" s="1" t="n">
+        <v>1.8739</v>
+      </c>
+      <c r="J189" s="1" t="n">
         <v>1.8609</v>
       </c>
     </row>
@@ -6330,9 +6900,12 @@
         <v>1.833</v>
       </c>
       <c r="H190" s="1" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I190" s="1" t="n">
         <v>1.838</v>
       </c>
-      <c r="I190" s="1" t="n">
+      <c r="J190" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -6361,10 +6934,13 @@
         <v>0.0267</v>
       </c>
       <c r="H191" s="1" t="n">
+        <v>0.02666</v>
+      </c>
+      <c r="I191" s="1" t="n">
         <v>0.0268</v>
       </c>
-      <c r="I191" s="1" t="n">
-        <v>0.02669</v>
+      <c r="J191" s="1" t="n">
+        <v>0.02666</v>
       </c>
     </row>
     <row r="192">
@@ -6392,9 +6968,12 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="H192" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="I192" s="1" t="n">
         <v>0.0973</v>
       </c>
-      <c r="I192" s="1" t="n">
+      <c r="J192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -6423,9 +7002,12 @@
         <v>0.17</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>0.1701</v>
+        <v>0.1718</v>
       </c>
       <c r="I193" s="1" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="J193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -6454,9 +7036,12 @@
         <v>16.315</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>16.315</v>
+        <v>16.318</v>
       </c>
       <c r="I194" s="1" t="n">
+        <v>16.318</v>
+      </c>
+      <c r="J194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -6485,9 +7070,12 @@
         <v>4.093</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>4.098</v>
+        <v>4.1</v>
       </c>
       <c r="I195" s="1" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J195" s="1" t="n">
         <v>4.087</v>
       </c>
     </row>
@@ -6516,9 +7104,12 @@
         <v>1.2705</v>
       </c>
       <c r="H196" s="1" t="n">
+        <v>1.2702</v>
+      </c>
+      <c r="I196" s="1" t="n">
         <v>1.2794</v>
       </c>
-      <c r="I196" s="1" t="n">
+      <c r="J196" s="1" t="n">
         <v>1.2663</v>
       </c>
     </row>
@@ -6547,9 +7138,12 @@
         <v>3.082</v>
       </c>
       <c r="H197" s="1" t="n">
+        <v>3.082</v>
+      </c>
+      <c r="I197" s="1" t="n">
         <v>3.092</v>
       </c>
-      <c r="I197" s="1" t="n">
+      <c r="J197" s="1" t="n">
         <v>3.066</v>
       </c>
     </row>
@@ -6578,9 +7172,12 @@
         <v>0.01262</v>
       </c>
       <c r="H198" s="1" t="n">
+        <v>0.01263</v>
+      </c>
+      <c r="I198" s="1" t="n">
         <v>0.01266</v>
       </c>
-      <c r="I198" s="1" t="n">
+      <c r="J198" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -6609,9 +7206,12 @@
         <v>0.0001761</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>0.0001762</v>
+        <v>0.0001767</v>
       </c>
       <c r="I199" s="1" t="n">
+        <v>0.0001767</v>
+      </c>
+      <c r="J199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -6640,9 +7240,12 @@
         <v>115.53</v>
       </c>
       <c r="H200" s="1" t="n">
+        <v>115.57</v>
+      </c>
+      <c r="I200" s="1" t="n">
         <v>115.62</v>
       </c>
-      <c r="I200" s="1" t="n">
+      <c r="J200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -6671,9 +7274,12 @@
         <v>0.01026</v>
       </c>
       <c r="H201" s="1" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="I201" s="1" t="n">
         <v>0.01031</v>
       </c>
-      <c r="I201" s="1" t="n">
+      <c r="J201" s="1" t="n">
         <v>0.01023</v>
       </c>
     </row>
@@ -6702,9 +7308,12 @@
         <v>0.0107</v>
       </c>
       <c r="H202" s="1" t="n">
+        <v>0.01069</v>
+      </c>
+      <c r="I202" s="1" t="n">
         <v>0.01073</v>
       </c>
-      <c r="I202" s="1" t="n">
+      <c r="J202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -6733,9 +7342,12 @@
         <v>0.003137</v>
       </c>
       <c r="H203" s="1" t="n">
+        <v>0.003138</v>
+      </c>
+      <c r="I203" s="1" t="n">
         <v>0.003153</v>
       </c>
-      <c r="I203" s="1" t="n">
+      <c r="J203" s="1" t="n">
         <v>0.003136</v>
       </c>
     </row>
@@ -6764,9 +7376,12 @@
         <v>28.32</v>
       </c>
       <c r="H204" s="1" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="I204" s="1" t="n">
         <v>28.38</v>
       </c>
-      <c r="I204" s="1" t="n">
+      <c r="J204" s="1" t="n">
         <v>28.23</v>
       </c>
     </row>
@@ -6795,9 +7410,12 @@
         <v>0.5621</v>
       </c>
       <c r="H205" s="1" t="n">
+        <v>0.5622</v>
+      </c>
+      <c r="I205" s="1" t="n">
         <v>0.5636</v>
       </c>
-      <c r="I205" s="1" t="n">
+      <c r="J205" s="1" t="n">
         <v>0.5608</v>
       </c>
     </row>
@@ -6826,9 +7444,12 @@
         <v>0.0004417</v>
       </c>
       <c r="H206" s="1" t="n">
+        <v>0.0004414</v>
+      </c>
+      <c r="I206" s="1" t="n">
         <v>0.0004417</v>
       </c>
-      <c r="I206" s="1" t="n">
+      <c r="J206" s="1" t="n">
         <v>0.0004387</v>
       </c>
     </row>
@@ -6857,9 +7478,12 @@
         <v>0.04667</v>
       </c>
       <c r="H207" s="1" t="n">
+        <v>0.04665</v>
+      </c>
+      <c r="I207" s="1" t="n">
         <v>0.04667</v>
       </c>
-      <c r="I207" s="1" t="n">
+      <c r="J207" s="1" t="n">
         <v>0.04648</v>
       </c>
     </row>
@@ -6888,9 +7512,12 @@
         <v>0.09</v>
       </c>
       <c r="H208" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I208" s="1" t="n">
         <v>0.091</v>
       </c>
-      <c r="I208" s="1" t="n">
+      <c r="J208" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -6919,9 +7546,12 @@
         <v>0.02566</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>0.02572</v>
+        <v>0.02574</v>
       </c>
       <c r="I209" s="1" t="n">
+        <v>0.02574</v>
+      </c>
+      <c r="J209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -6950,9 +7580,12 @@
         <v>0.012671</v>
       </c>
       <c r="H210" s="1" t="n">
+        <v>0.012678</v>
+      </c>
+      <c r="I210" s="1" t="n">
         <v>0.012745</v>
       </c>
-      <c r="I210" s="1" t="n">
+      <c r="J210" s="1" t="n">
         <v>0.012652</v>
       </c>
     </row>
@@ -6981,9 +7614,12 @@
         <v>0.0921</v>
       </c>
       <c r="H211" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="I211" s="1" t="n">
         <v>0.0921</v>
       </c>
-      <c r="I211" s="1" t="n">
+      <c r="J211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -7012,9 +7648,12 @@
         <v>0.007047</v>
       </c>
       <c r="H212" s="1" t="n">
+        <v>0.007061</v>
+      </c>
+      <c r="I212" s="1" t="n">
         <v>0.007076</v>
       </c>
-      <c r="I212" s="1" t="n">
+      <c r="J212" s="1" t="n">
         <v>0.007044</v>
       </c>
     </row>
@@ -7043,9 +7682,12 @@
         <v>0.02962</v>
       </c>
       <c r="H213" s="1" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="I213" s="1" t="n">
         <v>0.02966</v>
       </c>
-      <c r="I213" s="1" t="n">
+      <c r="J213" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -7074,9 +7716,12 @@
         <v>0.2702</v>
       </c>
       <c r="H214" s="1" t="n">
+        <v>0.2705</v>
+      </c>
+      <c r="I214" s="1" t="n">
         <v>0.2708</v>
       </c>
-      <c r="I214" s="1" t="n">
+      <c r="J214" s="1" t="n">
         <v>0.2698</v>
       </c>
     </row>
@@ -7105,9 +7750,12 @@
         <v>0.02195</v>
       </c>
       <c r="H215" s="1" t="n">
-        <v>0.02195</v>
+        <v>0.02205</v>
       </c>
       <c r="I215" s="1" t="n">
+        <v>0.02205</v>
+      </c>
+      <c r="J215" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -7136,10 +7784,13 @@
         <v>0.01475</v>
       </c>
       <c r="H216" s="1" t="n">
+        <v>0.01467</v>
+      </c>
+      <c r="I216" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="I216" s="1" t="n">
-        <v>0.0147</v>
+      <c r="J216" s="1" t="n">
+        <v>0.01467</v>
       </c>
     </row>
     <row r="217">
@@ -7167,9 +7818,12 @@
         <v>0.2542</v>
       </c>
       <c r="H217" s="1" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="I217" s="1" t="n">
         <v>0.2542</v>
       </c>
-      <c r="I217" s="1" t="n">
+      <c r="J217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -7198,9 +7852,12 @@
         <v>0.3084</v>
       </c>
       <c r="H218" s="1" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="I218" s="1" t="n">
         <v>0.3087</v>
       </c>
-      <c r="I218" s="1" t="n">
+      <c r="J218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -7229,9 +7886,12 @@
         <v>0.1783</v>
       </c>
       <c r="H219" s="1" t="n">
-        <v>0.1784</v>
+        <v>0.1786</v>
       </c>
       <c r="I219" s="1" t="n">
+        <v>0.1786</v>
+      </c>
+      <c r="J219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -7260,10 +7920,13 @@
         <v>14.99</v>
       </c>
       <c r="H220" s="1" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="I220" s="1" t="n">
         <v>15.02</v>
       </c>
-      <c r="I220" s="1" t="n">
-        <v>14.97</v>
+      <c r="J220" s="1" t="n">
+        <v>14.96</v>
       </c>
     </row>
     <row r="221">
@@ -7291,9 +7954,12 @@
         <v>0.01611</v>
       </c>
       <c r="H221" s="1" t="n">
+        <v>0.01605</v>
+      </c>
+      <c r="I221" s="1" t="n">
         <v>0.01611</v>
       </c>
-      <c r="I221" s="1" t="n">
+      <c r="J221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -7322,9 +7988,12 @@
         <v>66.25</v>
       </c>
       <c r="H222" s="1" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="I222" s="1" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="I222" s="1" t="n">
+      <c r="J222" s="1" t="n">
         <v>66.17</v>
       </c>
     </row>
@@ -7353,9 +8022,12 @@
         <v>0.09308</v>
       </c>
       <c r="H223" s="1" t="n">
+        <v>0.09271</v>
+      </c>
+      <c r="I223" s="1" t="n">
         <v>0.09308</v>
       </c>
-      <c r="I223" s="1" t="n">
+      <c r="J223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -7384,9 +8056,12 @@
         <v>0.03963</v>
       </c>
       <c r="H224" s="1" t="n">
+        <v>0.03945</v>
+      </c>
+      <c r="I224" s="1" t="n">
         <v>0.03963</v>
       </c>
-      <c r="I224" s="1" t="n">
+      <c r="J224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -7415,9 +8090,12 @@
         <v>0.5713</v>
       </c>
       <c r="H225" s="1" t="n">
+        <v>0.5703</v>
+      </c>
+      <c r="I225" s="1" t="n">
         <v>0.5725</v>
       </c>
-      <c r="I225" s="1" t="n">
+      <c r="J225" s="1" t="n">
         <v>0.5695</v>
       </c>
     </row>
@@ -7446,9 +8124,12 @@
         <v>0.1181</v>
       </c>
       <c r="H226" s="1" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="I226" s="1" t="n">
         <v>0.1184</v>
       </c>
-      <c r="I226" s="1" t="n">
+      <c r="J226" s="1" t="n">
         <v>0.1166</v>
       </c>
     </row>
@@ -7477,9 +8158,12 @@
         <v>0.3174</v>
       </c>
       <c r="H227" s="1" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="I227" s="1" t="n">
         <v>0.3201</v>
       </c>
-      <c r="I227" s="1" t="n">
+      <c r="J227" s="1" t="n">
         <v>0.3167</v>
       </c>
     </row>
@@ -7508,9 +8192,12 @@
         <v>6.079</v>
       </c>
       <c r="H228" s="1" t="n">
+        <v>6.078</v>
+      </c>
+      <c r="I228" s="1" t="n">
         <v>6.09</v>
       </c>
-      <c r="I228" s="1" t="n">
+      <c r="J228" s="1" t="n">
         <v>6.062</v>
       </c>
     </row>
@@ -7542,6 +8229,9 @@
         <v>0.0294</v>
       </c>
       <c r="I229" s="1" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="J229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -7570,9 +8260,12 @@
         <v>0.3297</v>
       </c>
       <c r="H230" s="1" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="I230" s="1" t="n">
         <v>0.3307</v>
       </c>
-      <c r="I230" s="1" t="n">
+      <c r="J230" s="1" t="n">
         <v>0.3288</v>
       </c>
     </row>
@@ -7601,9 +8294,12 @@
         <v>0.1205</v>
       </c>
       <c r="H231" s="1" t="n">
+        <v>0.12011</v>
+      </c>
+      <c r="I231" s="1" t="n">
         <v>0.12089</v>
       </c>
-      <c r="I231" s="1" t="n">
+      <c r="J231" s="1" t="n">
         <v>0.11994</v>
       </c>
     </row>
@@ -7632,9 +8328,12 @@
         <v>0.1182</v>
       </c>
       <c r="H232" s="1" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="I232" s="1" t="n">
         <v>0.1187</v>
       </c>
-      <c r="I232" s="1" t="n">
+      <c r="J232" s="1" t="n">
         <v>0.1182</v>
       </c>
     </row>
@@ -7663,9 +8362,12 @@
         <v>0.03015</v>
       </c>
       <c r="H233" s="1" t="n">
+        <v>0.03017</v>
+      </c>
+      <c r="I233" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="I233" s="1" t="n">
+      <c r="J233" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -7694,9 +8396,12 @@
         <v>0.0156</v>
       </c>
       <c r="H234" s="1" t="n">
-        <v>0.01574</v>
+        <v>0.015906</v>
       </c>
       <c r="I234" s="1" t="n">
+        <v>0.015906</v>
+      </c>
+      <c r="J234" s="1" t="n">
         <v>0.0156</v>
       </c>
     </row>
@@ -7725,9 +8430,12 @@
         <v>0.01281</v>
       </c>
       <c r="H235" s="1" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="I235" s="1" t="n">
         <v>0.01281</v>
       </c>
-      <c r="I235" s="1" t="n">
+      <c r="J235" s="1" t="n">
         <v>0.01272</v>
       </c>
     </row>
@@ -7756,9 +8464,12 @@
         <v>0.01927</v>
       </c>
       <c r="H236" s="1" t="n">
-        <v>0.01929</v>
+        <v>0.0193</v>
       </c>
       <c r="I236" s="1" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="J236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -7787,9 +8498,12 @@
         <v>0.08545999999999999</v>
       </c>
       <c r="H237" s="1" t="n">
+        <v>0.08527</v>
+      </c>
+      <c r="I237" s="1" t="n">
         <v>0.08545999999999999</v>
       </c>
-      <c r="I237" s="1" t="n">
+      <c r="J237" s="1" t="n">
         <v>0.08427999999999999</v>
       </c>
     </row>
@@ -7818,10 +8532,13 @@
         <v>0.05866</v>
       </c>
       <c r="H238" s="1" t="n">
+        <v>0.05852</v>
+      </c>
+      <c r="I238" s="1" t="n">
         <v>0.05892</v>
       </c>
-      <c r="I238" s="1" t="n">
-        <v>0.05857</v>
+      <c r="J238" s="1" t="n">
+        <v>0.05852</v>
       </c>
     </row>
     <row r="239">
@@ -7849,10 +8566,13 @@
         <v>0.009131999999999999</v>
       </c>
       <c r="H239" s="1" t="n">
+        <v>0.008973</v>
+      </c>
+      <c r="I239" s="1" t="n">
         <v>0.009131999999999999</v>
       </c>
-      <c r="I239" s="1" t="n">
-        <v>0.009027</v>
+      <c r="J239" s="1" t="n">
+        <v>0.008973</v>
       </c>
     </row>
     <row r="240">
@@ -7880,9 +8600,12 @@
         <v>0.004156</v>
       </c>
       <c r="H240" s="1" t="n">
+        <v>0.004159</v>
+      </c>
+      <c r="I240" s="1" t="n">
         <v>0.004175</v>
       </c>
-      <c r="I240" s="1" t="n">
+      <c r="J240" s="1" t="n">
         <v>0.004154</v>
       </c>
     </row>
@@ -7911,9 +8634,12 @@
         <v>0.2403</v>
       </c>
       <c r="H241" s="1" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="I241" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="I241" s="1" t="n">
+      <c r="J241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -7942,9 +8668,12 @@
         <v>0.0584</v>
       </c>
       <c r="H242" s="1" t="n">
-        <v>0.0584</v>
+        <v>0.0589</v>
       </c>
       <c r="I242" s="1" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="J242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -7973,9 +8702,12 @@
         <v>0.02363</v>
       </c>
       <c r="H243" s="1" t="n">
+        <v>0.02362</v>
+      </c>
+      <c r="I243" s="1" t="n">
         <v>0.02363</v>
       </c>
-      <c r="I243" s="1" t="n">
+      <c r="J243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -8004,9 +8736,12 @@
         <v>0.05575</v>
       </c>
       <c r="H244" s="1" t="n">
+        <v>0.05579</v>
+      </c>
+      <c r="I244" s="1" t="n">
         <v>0.05623</v>
       </c>
-      <c r="I244" s="1" t="n">
+      <c r="J244" s="1" t="n">
         <v>0.05547</v>
       </c>
     </row>
@@ -8035,9 +8770,12 @@
         <v>0.03444</v>
       </c>
       <c r="H245" s="1" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="I245" s="1" t="n">
         <v>0.03444</v>
       </c>
-      <c r="I245" s="1" t="n">
+      <c r="J245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -8066,9 +8804,12 @@
         <v>0.06027</v>
       </c>
       <c r="H246" s="1" t="n">
+        <v>0.06022</v>
+      </c>
+      <c r="I246" s="1" t="n">
         <v>0.06027</v>
       </c>
-      <c r="I246" s="1" t="n">
+      <c r="J246" s="1" t="n">
         <v>0.0599</v>
       </c>
     </row>
@@ -8097,9 +8838,12 @@
         <v>0.382</v>
       </c>
       <c r="H247" s="1" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="I247" s="1" t="n">
         <v>0.385</v>
       </c>
-      <c r="I247" s="1" t="n">
+      <c r="J247" s="1" t="n">
         <v>0.382</v>
       </c>
     </row>
@@ -8128,9 +8872,12 @@
         <v>0.5188</v>
       </c>
       <c r="H248" s="1" t="n">
-        <v>0.519</v>
+        <v>0.5191</v>
       </c>
       <c r="I248" s="1" t="n">
+        <v>0.5191</v>
+      </c>
+      <c r="J248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -8159,9 +8906,12 @@
         <v>0.02819</v>
       </c>
       <c r="H249" s="1" t="n">
-        <v>0.02819</v>
+        <v>0.02833</v>
       </c>
       <c r="I249" s="1" t="n">
+        <v>0.02833</v>
+      </c>
+      <c r="J249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -8193,6 +8943,9 @@
         <v>0.01299</v>
       </c>
       <c r="I250" s="1" t="n">
+        <v>0.01299</v>
+      </c>
+      <c r="J250" s="1" t="n">
         <v>0.01288</v>
       </c>
     </row>
@@ -8224,6 +8977,9 @@
         <v>0.1003</v>
       </c>
       <c r="I251" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="J251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -8252,10 +9008,13 @@
         <v>0.00715</v>
       </c>
       <c r="H252" s="1" t="n">
+        <v>0.00714</v>
+      </c>
+      <c r="I252" s="1" t="n">
         <v>0.00719</v>
       </c>
-      <c r="I252" s="1" t="n">
-        <v>0.00715</v>
+      <c r="J252" s="1" t="n">
+        <v>0.00714</v>
       </c>
     </row>
     <row r="253">
@@ -8283,9 +9042,12 @@
         <v>0.005563</v>
       </c>
       <c r="H253" s="1" t="n">
+        <v>0.005561</v>
+      </c>
+      <c r="I253" s="1" t="n">
         <v>0.005563</v>
       </c>
-      <c r="I253" s="1" t="n">
+      <c r="J253" s="1" t="n">
         <v>0.005554</v>
       </c>
     </row>
@@ -8314,9 +9076,12 @@
         <v>0.0643</v>
       </c>
       <c r="H254" s="1" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="I254" s="1" t="n">
         <v>0.0646</v>
       </c>
-      <c r="I254" s="1" t="n">
+      <c r="J254" s="1" t="n">
         <v>0.0641</v>
       </c>
     </row>
@@ -8345,9 +9110,12 @@
         <v>0.01453</v>
       </c>
       <c r="H255" s="1" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="I255" s="1" t="n">
         <v>0.01453</v>
       </c>
-      <c r="I255" s="1" t="n">
+      <c r="J255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -8376,9 +9144,12 @@
         <v>0.999285</v>
       </c>
       <c r="H256" s="1" t="n">
+        <v>0.999286</v>
+      </c>
+      <c r="I256" s="1" t="n">
         <v>0.999297</v>
       </c>
-      <c r="I256" s="1" t="n">
+      <c r="J256" s="1" t="n">
         <v>0.999285</v>
       </c>
     </row>
@@ -8407,9 +9178,12 @@
         <v>0.02114</v>
       </c>
       <c r="H257" s="1" t="n">
-        <v>0.02114</v>
+        <v>0.02115</v>
       </c>
       <c r="I257" s="1" t="n">
+        <v>0.02115</v>
+      </c>
+      <c r="J257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -8438,9 +9212,12 @@
         <v>0.01145</v>
       </c>
       <c r="H258" s="1" t="n">
+        <v>0.01147</v>
+      </c>
+      <c r="I258" s="1" t="n">
         <v>0.01148</v>
       </c>
-      <c r="I258" s="1" t="n">
+      <c r="J258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -8469,9 +9246,12 @@
         <v>0.5078</v>
       </c>
       <c r="H259" s="1" t="n">
+        <v>0.5085</v>
+      </c>
+      <c r="I259" s="1" t="n">
         <v>0.5119</v>
       </c>
-      <c r="I259" s="1" t="n">
+      <c r="J259" s="1" t="n">
         <v>0.5071</v>
       </c>
     </row>
@@ -8500,9 +9280,12 @@
         <v>0.08495999999999999</v>
       </c>
       <c r="H260" s="1" t="n">
+        <v>0.08454</v>
+      </c>
+      <c r="I260" s="1" t="n">
         <v>0.08537</v>
       </c>
-      <c r="I260" s="1" t="n">
+      <c r="J260" s="1" t="n">
         <v>0.08436</v>
       </c>
     </row>
@@ -8531,9 +9314,12 @@
         <v>0.04124</v>
       </c>
       <c r="H261" s="1" t="n">
+        <v>0.04125</v>
+      </c>
+      <c r="I261" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="I261" s="1" t="n">
+      <c r="J261" s="1" t="n">
         <v>0.04123</v>
       </c>
     </row>
@@ -8562,9 +9348,12 @@
         <v>2.283</v>
       </c>
       <c r="H262" s="1" t="n">
+        <v>2.283</v>
+      </c>
+      <c r="I262" s="1" t="n">
         <v>2.288</v>
       </c>
-      <c r="I262" s="1" t="n">
+      <c r="J262" s="1" t="n">
         <v>2.279</v>
       </c>
     </row>
@@ -8593,9 +9382,12 @@
         <v>18.47</v>
       </c>
       <c r="H263" s="1" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="I263" s="1" t="n">
         <v>18.51</v>
       </c>
-      <c r="I263" s="1" t="n">
+      <c r="J263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -8624,9 +9416,12 @@
         <v>0.008562999999999999</v>
       </c>
       <c r="H264" s="1" t="n">
+        <v>0.008534</v>
+      </c>
+      <c r="I264" s="1" t="n">
         <v>0.008562999999999999</v>
       </c>
-      <c r="I264" s="1" t="n">
+      <c r="J264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -8655,9 +9450,12 @@
         <v>0.3645</v>
       </c>
       <c r="H265" s="1" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="I265" s="1" t="n">
         <v>0.3645</v>
       </c>
-      <c r="I265" s="1" t="n">
+      <c r="J265" s="1" t="n">
         <v>0.3627</v>
       </c>
     </row>
@@ -8686,9 +9484,12 @@
         <v>0.054644</v>
       </c>
       <c r="H266" s="1" t="n">
-        <v>0.054644</v>
+        <v>0.05489</v>
       </c>
       <c r="I266" s="1" t="n">
+        <v>0.05489</v>
+      </c>
+      <c r="J266" s="1" t="n">
         <v>0.053765</v>
       </c>
     </row>
@@ -8717,9 +9518,12 @@
         <v>0.1313</v>
       </c>
       <c r="H267" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="I267" s="1" t="n">
         <v>0.1321</v>
       </c>
-      <c r="I267" s="1" t="n">
+      <c r="J267" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -8748,10 +9552,13 @@
         <v>0.00777</v>
       </c>
       <c r="H268" s="1" t="n">
+        <v>0.00775</v>
+      </c>
+      <c r="I268" s="1" t="n">
         <v>0.007845</v>
       </c>
-      <c r="I268" s="1" t="n">
-        <v>0.007759</v>
+      <c r="J268" s="1" t="n">
+        <v>0.00775</v>
       </c>
     </row>
     <row r="269">
@@ -8779,9 +9586,12 @@
         <v>0.001232</v>
       </c>
       <c r="H269" s="1" t="n">
+        <v>0.001233</v>
+      </c>
+      <c r="I269" s="1" t="n">
         <v>0.00124</v>
       </c>
-      <c r="I269" s="1" t="n">
+      <c r="J269" s="1" t="n">
         <v>0.001232</v>
       </c>
     </row>
@@ -8810,9 +9620,12 @@
         <v>0.28955</v>
       </c>
       <c r="H270" s="1" t="n">
-        <v>0.28997</v>
+        <v>0.28999</v>
       </c>
       <c r="I270" s="1" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="J270" s="1" t="n">
         <v>0.28865</v>
       </c>
     </row>
@@ -8841,9 +9654,12 @@
         <v>0.039</v>
       </c>
       <c r="H271" s="1" t="n">
+        <v>0.03912</v>
+      </c>
+      <c r="I271" s="1" t="n">
         <v>0.03922</v>
       </c>
-      <c r="I271" s="1" t="n">
+      <c r="J271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -8872,9 +9688,12 @@
         <v>0.0515</v>
       </c>
       <c r="H272" s="1" t="n">
-        <v>0.0515</v>
+        <v>0.05151</v>
       </c>
       <c r="I272" s="1" t="n">
+        <v>0.05151</v>
+      </c>
+      <c r="J272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -8903,9 +9722,12 @@
         <v>0.00771</v>
       </c>
       <c r="H273" s="1" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="I273" s="1" t="n">
         <v>0.00771</v>
       </c>
-      <c r="I273" s="1" t="n">
+      <c r="J273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -8934,9 +9756,12 @@
         <v>0.005797</v>
       </c>
       <c r="H274" s="1" t="n">
+        <v>0.005794</v>
+      </c>
+      <c r="I274" s="1" t="n">
         <v>0.005797</v>
       </c>
-      <c r="I274" s="1" t="n">
+      <c r="J274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -8965,9 +9790,12 @@
         <v>0.000588</v>
       </c>
       <c r="H275" s="1" t="n">
+        <v>0.0005888</v>
+      </c>
+      <c r="I275" s="1" t="n">
         <v>0.0005895</v>
       </c>
-      <c r="I275" s="1" t="n">
+      <c r="J275" s="1" t="n">
         <v>0.0005863</v>
       </c>
     </row>
@@ -8996,9 +9824,12 @@
         <v>0.15004</v>
       </c>
       <c r="H276" s="1" t="n">
+        <v>0.15011</v>
+      </c>
+      <c r="I276" s="1" t="n">
         <v>0.15167</v>
       </c>
-      <c r="I276" s="1" t="n">
+      <c r="J276" s="1" t="n">
         <v>0.15004</v>
       </c>
     </row>
@@ -9027,9 +9858,12 @@
         <v>0.022966</v>
       </c>
       <c r="H277" s="1" t="n">
+        <v>0.022956</v>
+      </c>
+      <c r="I277" s="1" t="n">
         <v>0.022966</v>
       </c>
-      <c r="I277" s="1" t="n">
+      <c r="J277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -9058,9 +9892,12 @@
         <v>0.04214</v>
       </c>
       <c r="H278" s="1" t="n">
+        <v>0.04232</v>
+      </c>
+      <c r="I278" s="1" t="n">
         <v>0.04242</v>
       </c>
-      <c r="I278" s="1" t="n">
+      <c r="J278" s="1" t="n">
         <v>0.04179</v>
       </c>
     </row>
@@ -9089,9 +9926,12 @@
         <v>0.0003993</v>
       </c>
       <c r="H279" s="1" t="n">
+        <v>0.0004002</v>
+      </c>
+      <c r="I279" s="1" t="n">
         <v>0.0004006</v>
       </c>
-      <c r="I279" s="1" t="n">
+      <c r="J279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -9120,10 +9960,13 @@
         <v>0.02209</v>
       </c>
       <c r="H280" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="I280" s="1" t="n">
         <v>0.02218</v>
       </c>
-      <c r="I280" s="1" t="n">
-        <v>0.02195</v>
+      <c r="J280" s="1" t="n">
+        <v>0.0219</v>
       </c>
     </row>
     <row r="281">
@@ -9151,9 +9994,12 @@
         <v>0.06991</v>
       </c>
       <c r="H281" s="1" t="n">
-        <v>0.06991</v>
+        <v>0.07036000000000001</v>
       </c>
       <c r="I281" s="1" t="n">
+        <v>0.07036000000000001</v>
+      </c>
+      <c r="J281" s="1" t="n">
         <v>0.06936</v>
       </c>
     </row>
@@ -9182,10 +10028,13 @@
         <v>0.0067</v>
       </c>
       <c r="H282" s="1" t="n">
+        <v>0.006697</v>
+      </c>
+      <c r="I282" s="1" t="n">
         <v>0.006804</v>
       </c>
-      <c r="I282" s="1" t="n">
-        <v>0.0067</v>
+      <c r="J282" s="1" t="n">
+        <v>0.006697</v>
       </c>
     </row>
     <row r="283">
@@ -9216,6 +10065,9 @@
         <v>0.12</v>
       </c>
       <c r="I283" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J283" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -9244,9 +10096,12 @@
         <v>0.005491</v>
       </c>
       <c r="H284" s="1" t="n">
+        <v>0.00549</v>
+      </c>
+      <c r="I284" s="1" t="n">
         <v>0.005491</v>
       </c>
-      <c r="I284" s="1" t="n">
+      <c r="J284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -9278,6 +10133,9 @@
         <v>1.263</v>
       </c>
       <c r="I285" s="1" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="J285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -9306,9 +10164,12 @@
         <v>0.4428</v>
       </c>
       <c r="H286" s="1" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="I286" s="1" t="n">
         <v>0.4441</v>
       </c>
-      <c r="I286" s="1" t="n">
+      <c r="J286" s="1" t="n">
         <v>0.4423</v>
       </c>
     </row>
@@ -9337,9 +10198,12 @@
         <v>0.007924</v>
       </c>
       <c r="H287" s="1" t="n">
-        <v>0.007924</v>
+        <v>0.007932</v>
       </c>
       <c r="I287" s="1" t="n">
+        <v>0.007932</v>
+      </c>
+      <c r="J287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -9368,9 +10232,12 @@
         <v>0.0295</v>
       </c>
       <c r="H288" s="1" t="n">
+        <v>0.02935</v>
+      </c>
+      <c r="I288" s="1" t="n">
         <v>0.0295</v>
       </c>
-      <c r="I288" s="1" t="n">
+      <c r="J288" s="1" t="n">
         <v>0.02914</v>
       </c>
     </row>
@@ -9399,9 +10266,12 @@
         <v>0.2822</v>
       </c>
       <c r="H289" s="1" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="I289" s="1" t="n">
         <v>0.2822</v>
       </c>
-      <c r="I289" s="1" t="n">
+      <c r="J289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -9430,9 +10300,12 @@
         <v>2.756</v>
       </c>
       <c r="H290" s="1" t="n">
+        <v>2.762</v>
+      </c>
+      <c r="I290" s="1" t="n">
         <v>2.764</v>
       </c>
-      <c r="I290" s="1" t="n">
+      <c r="J290" s="1" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -9461,9 +10334,12 @@
         <v>0.003177</v>
       </c>
       <c r="H291" s="1" t="n">
+        <v>0.003176</v>
+      </c>
+      <c r="I291" s="1" t="n">
         <v>0.003177</v>
       </c>
-      <c r="I291" s="1" t="n">
+      <c r="J291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -9492,9 +10368,12 @@
         <v>0.4479</v>
       </c>
       <c r="H292" s="1" t="n">
+        <v>0.4481</v>
+      </c>
+      <c r="I292" s="1" t="n">
         <v>0.4488</v>
       </c>
-      <c r="I292" s="1" t="n">
+      <c r="J292" s="1" t="n">
         <v>0.4475</v>
       </c>
     </row>
@@ -9523,10 +10402,13 @@
         <v>0.08203000000000001</v>
       </c>
       <c r="H293" s="1" t="n">
+        <v>0.08171</v>
+      </c>
+      <c r="I293" s="1" t="n">
         <v>0.08298</v>
       </c>
-      <c r="I293" s="1" t="n">
-        <v>0.08203000000000001</v>
+      <c r="J293" s="1" t="n">
+        <v>0.08171</v>
       </c>
     </row>
     <row r="294">
@@ -9554,9 +10436,12 @@
         <v>0.02791</v>
       </c>
       <c r="H294" s="1" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="I294" s="1" t="n">
         <v>0.02791</v>
       </c>
-      <c r="I294" s="1" t="n">
+      <c r="J294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -9585,9 +10470,12 @@
         <v>0.955</v>
       </c>
       <c r="H295" s="1" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="I295" s="1" t="n">
         <v>0.958</v>
       </c>
-      <c r="I295" s="1" t="n">
+      <c r="J295" s="1" t="n">
         <v>0.953</v>
       </c>
     </row>
@@ -9616,9 +10504,12 @@
         <v>0.007005</v>
       </c>
       <c r="H296" s="1" t="n">
-        <v>0.007005</v>
+        <v>0.007008</v>
       </c>
       <c r="I296" s="1" t="n">
+        <v>0.007008</v>
+      </c>
+      <c r="J296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -9647,9 +10538,12 @@
         <v>0.1213</v>
       </c>
       <c r="H297" s="1" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="I297" s="1" t="n">
         <v>0.1213</v>
       </c>
-      <c r="I297" s="1" t="n">
+      <c r="J297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -9678,9 +10572,12 @@
         <v>0.01554</v>
       </c>
       <c r="H298" s="1" t="n">
-        <v>0.01554</v>
+        <v>0.01558</v>
       </c>
       <c r="I298" s="1" t="n">
+        <v>0.01558</v>
+      </c>
+      <c r="J298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -9709,9 +10606,12 @@
         <v>0.4409</v>
       </c>
       <c r="H299" s="1" t="n">
-        <v>0.4409</v>
+        <v>0.4422</v>
       </c>
       <c r="I299" s="1" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="J299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -9740,9 +10640,12 @@
         <v>0.009140000000000001</v>
       </c>
       <c r="H300" s="1" t="n">
+        <v>0.00916</v>
+      </c>
+      <c r="I300" s="1" t="n">
         <v>0.00924</v>
       </c>
-      <c r="I300" s="1" t="n">
+      <c r="J300" s="1" t="n">
         <v>0.009140000000000001</v>
       </c>
     </row>
@@ -9771,9 +10674,12 @@
         <v>0.1855</v>
       </c>
       <c r="H301" s="1" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="I301" s="1" t="n">
         <v>0.1855</v>
       </c>
-      <c r="I301" s="1" t="n">
+      <c r="J301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -9802,9 +10708,12 @@
         <v>0.00765</v>
       </c>
       <c r="H302" s="1" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I302" s="1" t="n">
         <v>0.00765</v>
       </c>
-      <c r="I302" s="1" t="n">
+      <c r="J302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -9833,9 +10742,12 @@
         <v>0.0002151</v>
       </c>
       <c r="H303" s="1" t="n">
+        <v>0.0002151</v>
+      </c>
+      <c r="I303" s="1" t="n">
         <v>0.0002171</v>
       </c>
-      <c r="I303" s="1" t="n">
+      <c r="J303" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -9864,9 +10776,12 @@
         <v>0.01553</v>
       </c>
       <c r="H304" s="1" t="n">
+        <v>0.01549</v>
+      </c>
+      <c r="I304" s="1" t="n">
         <v>0.01553</v>
       </c>
-      <c r="I304" s="1" t="n">
+      <c r="J304" s="1" t="n">
         <v>0.01542</v>
       </c>
     </row>
@@ -9895,9 +10810,12 @@
         <v>0.07386</v>
       </c>
       <c r="H305" s="1" t="n">
+        <v>0.07386</v>
+      </c>
+      <c r="I305" s="1" t="n">
         <v>0.07394000000000001</v>
       </c>
-      <c r="I305" s="1" t="n">
+      <c r="J305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -9926,9 +10844,12 @@
         <v>0.08301</v>
       </c>
       <c r="H306" s="1" t="n">
-        <v>0.08301</v>
+        <v>0.0832</v>
       </c>
       <c r="I306" s="1" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="J306" s="1" t="n">
         <v>0.08275</v>
       </c>
     </row>
@@ -9957,10 +10878,13 @@
         <v>0.01809</v>
       </c>
       <c r="H307" s="1" t="n">
+        <v>0.01804</v>
+      </c>
+      <c r="I307" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="I307" s="1" t="n">
-        <v>0.01808</v>
+      <c r="J307" s="1" t="n">
+        <v>0.01804</v>
       </c>
     </row>
     <row r="308">
@@ -9988,9 +10912,12 @@
         <v>0.0006243000000000001</v>
       </c>
       <c r="H308" s="1" t="n">
+        <v>0.0006232</v>
+      </c>
+      <c r="I308" s="1" t="n">
         <v>0.0006255</v>
       </c>
-      <c r="I308" s="1" t="n">
+      <c r="J308" s="1" t="n">
         <v>0.0006212</v>
       </c>
     </row>
@@ -10019,10 +10946,13 @@
         <v>0.0824</v>
       </c>
       <c r="H309" s="1" t="n">
+        <v>0.0822</v>
+      </c>
+      <c r="I309" s="1" t="n">
         <v>0.08294</v>
       </c>
-      <c r="I309" s="1" t="n">
-        <v>0.0824</v>
+      <c r="J309" s="1" t="n">
+        <v>0.0822</v>
       </c>
     </row>
     <row r="310">
@@ -10050,9 +10980,12 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="H310" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="I310" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="I310" s="1" t="n">
+      <c r="J310" s="1" t="n">
         <v>0.0973</v>
       </c>
     </row>
@@ -10081,9 +11014,12 @@
         <v>0.2119</v>
       </c>
       <c r="H311" s="1" t="n">
+        <v>0.2116</v>
+      </c>
+      <c r="I311" s="1" t="n">
         <v>0.2119</v>
       </c>
-      <c r="I311" s="1" t="n">
+      <c r="J311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -10112,9 +11048,12 @@
         <v>0.3899</v>
       </c>
       <c r="H312" s="1" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="I312" s="1" t="n">
         <v>0.394</v>
       </c>
-      <c r="I312" s="1" t="n">
+      <c r="J312" s="1" t="n">
         <v>0.387</v>
       </c>
     </row>
@@ -10143,9 +11082,12 @@
         <v>0.10539</v>
       </c>
       <c r="H313" s="1" t="n">
+        <v>0.10497</v>
+      </c>
+      <c r="I313" s="1" t="n">
         <v>0.10542</v>
       </c>
-      <c r="I313" s="1" t="n">
+      <c r="J313" s="1" t="n">
         <v>0.10492</v>
       </c>
     </row>
@@ -10174,9 +11116,12 @@
         <v>0.08618000000000001</v>
       </c>
       <c r="H314" s="1" t="n">
-        <v>0.08618000000000001</v>
+        <v>0.08628</v>
       </c>
       <c r="I314" s="1" t="n">
+        <v>0.08628</v>
+      </c>
+      <c r="J314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -10205,9 +11150,12 @@
         <v>0.118</v>
       </c>
       <c r="H315" s="1" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="I315" s="1" t="n">
         <v>0.1185</v>
       </c>
-      <c r="I315" s="1" t="n">
+      <c r="J315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -10236,9 +11184,12 @@
         <v>0.03643</v>
       </c>
       <c r="H316" s="1" t="n">
+        <v>0.03638</v>
+      </c>
+      <c r="I316" s="1" t="n">
         <v>0.03681</v>
       </c>
-      <c r="I316" s="1" t="n">
+      <c r="J316" s="1" t="n">
         <v>0.03628</v>
       </c>
     </row>
@@ -10267,9 +11218,12 @@
         <v>0.08133</v>
       </c>
       <c r="H317" s="1" t="n">
-        <v>0.08133</v>
+        <v>0.08164</v>
       </c>
       <c r="I317" s="1" t="n">
+        <v>0.08164</v>
+      </c>
+      <c r="J317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -10298,9 +11252,12 @@
         <v>0.03759</v>
       </c>
       <c r="H318" s="1" t="n">
+        <v>0.03746</v>
+      </c>
+      <c r="I318" s="1" t="n">
         <v>0.03766</v>
       </c>
-      <c r="I318" s="1" t="n">
+      <c r="J318" s="1" t="n">
         <v>0.03736</v>
       </c>
     </row>
@@ -10329,10 +11286,13 @@
         <v>0.4303</v>
       </c>
       <c r="H319" s="1" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="I319" s="1" t="n">
         <v>0.4347</v>
       </c>
-      <c r="I319" s="1" t="n">
-        <v>0.4303</v>
+      <c r="J319" s="1" t="n">
+        <v>0.4296</v>
       </c>
     </row>
     <row r="320">
@@ -10360,9 +11320,12 @@
         <v>0.1604</v>
       </c>
       <c r="H320" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="I320" s="1" t="n">
         <v>0.1614</v>
       </c>
-      <c r="I320" s="1" t="n">
+      <c r="J320" s="1" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -10394,6 +11357,9 @@
         <v>5.681</v>
       </c>
       <c r="I321" s="1" t="n">
+        <v>5.681</v>
+      </c>
+      <c r="J321" s="1" t="n">
         <v>5.677</v>
       </c>
     </row>
@@ -10422,9 +11388,12 @@
         <v>0.003727</v>
       </c>
       <c r="H322" s="1" t="n">
+        <v>0.00373</v>
+      </c>
+      <c r="I322" s="1" t="n">
         <v>0.003746</v>
       </c>
-      <c r="I322" s="1" t="n">
+      <c r="J322" s="1" t="n">
         <v>0.003715</v>
       </c>
     </row>
@@ -10453,9 +11422,12 @@
         <v>0.001761</v>
       </c>
       <c r="H323" s="1" t="n">
+        <v>0.001759</v>
+      </c>
+      <c r="I323" s="1" t="n">
         <v>0.001761</v>
       </c>
-      <c r="I323" s="1" t="n">
+      <c r="J323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -10487,6 +11459,9 @@
         <v>1.2e-05</v>
       </c>
       <c r="I324" s="1" t="n">
+        <v>1.2e-05</v>
+      </c>
+      <c r="J324" s="1" t="n">
         <v>1.19e-05</v>
       </c>
     </row>
@@ -10515,9 +11490,12 @@
         <v>0.0863</v>
       </c>
       <c r="H325" s="1" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="I325" s="1" t="n">
         <v>0.08649999999999999</v>
       </c>
-      <c r="I325" s="1" t="n">
+      <c r="J325" s="1" t="n">
         <v>0.0857</v>
       </c>
     </row>
@@ -10546,9 +11524,12 @@
         <v>0.01732</v>
       </c>
       <c r="H326" s="1" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="I326" s="1" t="n">
         <v>0.01736</v>
       </c>
-      <c r="I326" s="1" t="n">
+      <c r="J326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -10577,9 +11558,12 @@
         <v>0.01686</v>
       </c>
       <c r="H327" s="1" t="n">
+        <v>0.01685</v>
+      </c>
+      <c r="I327" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="I327" s="1" t="n">
+      <c r="J327" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -10608,9 +11592,12 @@
         <v>4.459</v>
       </c>
       <c r="H328" s="1" t="n">
+        <v>4.457</v>
+      </c>
+      <c r="I328" s="1" t="n">
         <v>4.462</v>
       </c>
-      <c r="I328" s="1" t="n">
+      <c r="J328" s="1" t="n">
         <v>4.446</v>
       </c>
     </row>
@@ -10639,9 +11626,12 @@
         <v>0.009629</v>
       </c>
       <c r="H329" s="1" t="n">
+        <v>0.009671000000000001</v>
+      </c>
+      <c r="I329" s="1" t="n">
         <v>0.009861</v>
       </c>
-      <c r="I329" s="1" t="n">
+      <c r="J329" s="1" t="n">
         <v>0.009532000000000001</v>
       </c>
     </row>
@@ -10670,9 +11660,12 @@
         <v>5189</v>
       </c>
       <c r="H330" s="1" t="n">
+        <v>5189.9</v>
+      </c>
+      <c r="I330" s="1" t="n">
         <v>5192.9</v>
       </c>
-      <c r="I330" s="1" t="n">
+      <c r="J330" s="1" t="n">
         <v>5185.8</v>
       </c>
     </row>
@@ -10701,9 +11694,12 @@
         <v>0.07054000000000001</v>
       </c>
       <c r="H331" s="1" t="n">
+        <v>0.07054000000000001</v>
+      </c>
+      <c r="I331" s="1" t="n">
         <v>0.07087</v>
       </c>
-      <c r="I331" s="1" t="n">
+      <c r="J331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -10732,9 +11728,12 @@
         <v>0.06106</v>
       </c>
       <c r="H332" s="1" t="n">
+        <v>0.06098</v>
+      </c>
+      <c r="I332" s="1" t="n">
         <v>0.06106</v>
       </c>
-      <c r="I332" s="1" t="n">
+      <c r="J332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -10763,10 +11762,13 @@
         <v>0.10346</v>
       </c>
       <c r="H333" s="1" t="n">
+        <v>0.10341</v>
+      </c>
+      <c r="I333" s="1" t="n">
         <v>0.10416</v>
       </c>
-      <c r="I333" s="1" t="n">
-        <v>0.10344</v>
+      <c r="J333" s="1" t="n">
+        <v>0.10341</v>
       </c>
     </row>
     <row r="334">
@@ -10794,9 +11796,12 @@
         <v>0.08748</v>
       </c>
       <c r="H334" s="1" t="n">
+        <v>0.08735</v>
+      </c>
+      <c r="I334" s="1" t="n">
         <v>0.08837</v>
       </c>
-      <c r="I334" s="1" t="n">
+      <c r="J334" s="1" t="n">
         <v>0.08734</v>
       </c>
     </row>
@@ -10825,9 +11830,12 @@
         <v>0.016401</v>
       </c>
       <c r="H335" s="1" t="n">
+        <v>0.016404</v>
+      </c>
+      <c r="I335" s="1" t="n">
         <v>0.016413</v>
       </c>
-      <c r="I335" s="1" t="n">
+      <c r="J335" s="1" t="n">
         <v>0.016391</v>
       </c>
     </row>
@@ -10856,9 +11864,12 @@
         <v>0.046</v>
       </c>
       <c r="H336" s="1" t="n">
+        <v>0.04597</v>
+      </c>
+      <c r="I336" s="1" t="n">
         <v>0.046</v>
       </c>
-      <c r="I336" s="1" t="n">
+      <c r="J336" s="1" t="n">
         <v>0.04583</v>
       </c>
     </row>
@@ -10887,9 +11898,12 @@
         <v>0.1858</v>
       </c>
       <c r="H337" s="1" t="n">
-        <v>0.1858</v>
+        <v>0.1865</v>
       </c>
       <c r="I337" s="1" t="n">
+        <v>0.1865</v>
+      </c>
+      <c r="J337" s="1" t="n">
         <v>0.1838</v>
       </c>
     </row>
@@ -10918,9 +11932,12 @@
         <v>0.1832</v>
       </c>
       <c r="H338" s="1" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="I338" s="1" t="n">
         <v>0.1836</v>
       </c>
-      <c r="I338" s="1" t="n">
+      <c r="J338" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -10952,6 +11969,9 @@
         <v>0.01838</v>
       </c>
       <c r="I339" s="1" t="n">
+        <v>0.01838</v>
+      </c>
+      <c r="J339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -10980,9 +12000,12 @@
         <v>0.0231</v>
       </c>
       <c r="H340" s="1" t="n">
-        <v>0.02311</v>
+        <v>0.02313</v>
       </c>
       <c r="I340" s="1" t="n">
+        <v>0.02313</v>
+      </c>
+      <c r="J340" s="1" t="n">
         <v>0.02305</v>
       </c>
     </row>
@@ -11011,9 +12034,12 @@
         <v>0.4562</v>
       </c>
       <c r="H341" s="1" t="n">
-        <v>0.4562</v>
+        <v>0.4577</v>
       </c>
       <c r="I341" s="1" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="J341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -11042,9 +12068,12 @@
         <v>0.01347</v>
       </c>
       <c r="H342" s="1" t="n">
-        <v>0.01347</v>
+        <v>0.01349</v>
       </c>
       <c r="I342" s="1" t="n">
+        <v>0.01349</v>
+      </c>
+      <c r="J342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -11073,9 +12102,12 @@
         <v>2.872</v>
       </c>
       <c r="H343" s="1" t="n">
+        <v>2.874</v>
+      </c>
+      <c r="I343" s="1" t="n">
         <v>2.89</v>
       </c>
-      <c r="I343" s="1" t="n">
+      <c r="J343" s="1" t="n">
         <v>2.872</v>
       </c>
     </row>
@@ -11104,9 +12136,12 @@
         <v>0.1552</v>
       </c>
       <c r="H344" s="1" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="I344" s="1" t="n">
         <v>0.1577</v>
       </c>
-      <c r="I344" s="1" t="n">
+      <c r="J344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -11135,9 +12170,12 @@
         <v>0.005363</v>
       </c>
       <c r="H345" s="1" t="n">
+        <v>0.005361</v>
+      </c>
+      <c r="I345" s="1" t="n">
         <v>0.005367</v>
       </c>
-      <c r="I345" s="1" t="n">
+      <c r="J345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -11166,9 +12204,12 @@
         <v>0.0579</v>
       </c>
       <c r="H346" s="1" t="n">
+        <v>0.05786</v>
+      </c>
+      <c r="I346" s="1" t="n">
         <v>0.0579</v>
       </c>
-      <c r="I346" s="1" t="n">
+      <c r="J346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -11197,9 +12238,12 @@
         <v>2612</v>
       </c>
       <c r="H347" s="1" t="n">
+        <v>2609</v>
+      </c>
+      <c r="I347" s="1" t="n">
         <v>2612</v>
       </c>
-      <c r="I347" s="1" t="n">
+      <c r="J347" s="1" t="n">
         <v>2597</v>
       </c>
     </row>
@@ -11228,9 +12272,12 @@
         <v>0.04601</v>
       </c>
       <c r="H348" s="1" t="n">
+        <v>0.04595</v>
+      </c>
+      <c r="I348" s="1" t="n">
         <v>0.04621</v>
       </c>
-      <c r="I348" s="1" t="n">
+      <c r="J348" s="1" t="n">
         <v>0.04595</v>
       </c>
     </row>
@@ -11259,9 +12306,12 @@
         <v>0.005667</v>
       </c>
       <c r="H349" s="1" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="I349" s="1" t="n">
         <v>0.005714</v>
       </c>
-      <c r="I349" s="1" t="n">
+      <c r="J349" s="1" t="n">
         <v>0.005667</v>
       </c>
     </row>
@@ -11290,9 +12340,12 @@
         <v>195.35</v>
       </c>
       <c r="H350" s="1" t="n">
+        <v>195.39</v>
+      </c>
+      <c r="I350" s="1" t="n">
         <v>195.51</v>
       </c>
-      <c r="I350" s="1" t="n">
+      <c r="J350" s="1" t="n">
         <v>195.23</v>
       </c>
     </row>
@@ -11321,9 +12374,12 @@
         <v>0.08245</v>
       </c>
       <c r="H351" s="1" t="n">
+        <v>0.08236</v>
+      </c>
+      <c r="I351" s="1" t="n">
         <v>0.08245</v>
       </c>
-      <c r="I351" s="1" t="n">
+      <c r="J351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -11352,9 +12408,12 @@
         <v>0.0075</v>
       </c>
       <c r="H352" s="1" t="n">
+        <v>0.007498</v>
+      </c>
+      <c r="I352" s="1" t="n">
         <v>0.007571</v>
       </c>
-      <c r="I352" s="1" t="n">
+      <c r="J352" s="1" t="n">
         <v>0.007458</v>
       </c>
     </row>
@@ -11383,9 +12442,12 @@
         <v>1.5217</v>
       </c>
       <c r="H353" s="1" t="n">
-        <v>1.5217</v>
+        <v>1.526</v>
       </c>
       <c r="I353" s="1" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="J353" s="1" t="n">
         <v>1.4807</v>
       </c>
     </row>
@@ -11414,9 +12476,12 @@
         <v>0.07655000000000001</v>
       </c>
       <c r="H354" s="1" t="n">
-        <v>0.07655000000000001</v>
+        <v>0.07671</v>
       </c>
       <c r="I354" s="1" t="n">
+        <v>0.07671</v>
+      </c>
+      <c r="J354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -11445,9 +12510,12 @@
         <v>0.04859</v>
       </c>
       <c r="H355" s="1" t="n">
+        <v>0.04866</v>
+      </c>
+      <c r="I355" s="1" t="n">
         <v>0.04921</v>
       </c>
-      <c r="I355" s="1" t="n">
+      <c r="J355" s="1" t="n">
         <v>0.04859</v>
       </c>
     </row>
@@ -11479,6 +12547,9 @@
         <v>0.2861</v>
       </c>
       <c r="I356" s="1" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="J356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -11507,9 +12578,12 @@
         <v>0.1466</v>
       </c>
       <c r="H357" s="1" t="n">
-        <v>0.1467</v>
+        <v>0.1468</v>
       </c>
       <c r="I357" s="1" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="J357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -11538,9 +12612,12 @@
         <v>1.353</v>
       </c>
       <c r="H358" s="1" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="I358" s="1" t="n">
         <v>1.355</v>
       </c>
-      <c r="I358" s="1" t="n">
+      <c r="J358" s="1" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -11569,9 +12646,12 @@
         <v>0.6094000000000001</v>
       </c>
       <c r="H359" s="1" t="n">
+        <v>0.6097</v>
+      </c>
+      <c r="I359" s="1" t="n">
         <v>0.6117</v>
       </c>
-      <c r="I359" s="1" t="n">
+      <c r="J359" s="1" t="n">
         <v>0.6081</v>
       </c>
     </row>
@@ -11603,6 +12683,9 @@
         <v>0.1146</v>
       </c>
       <c r="I360" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="J360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -11631,9 +12714,12 @@
         <v>0.02632</v>
       </c>
       <c r="H361" s="1" t="n">
-        <v>0.02632</v>
+        <v>0.02641</v>
       </c>
       <c r="I361" s="1" t="n">
+        <v>0.02641</v>
+      </c>
+      <c r="J361" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -11665,6 +12751,9 @@
         <v>3.04e-05</v>
       </c>
       <c r="I362" s="1" t="n">
+        <v>3.04e-05</v>
+      </c>
+      <c r="J362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -11693,9 +12782,12 @@
         <v>0.01026</v>
       </c>
       <c r="H363" s="1" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="I363" s="1" t="n">
         <v>0.01026</v>
       </c>
-      <c r="I363" s="1" t="n">
+      <c r="J363" s="1" t="n">
         <v>0.01018</v>
       </c>
     </row>
@@ -11724,9 +12816,12 @@
         <v>0.0622</v>
       </c>
       <c r="H364" s="1" t="n">
+        <v>0.06206</v>
+      </c>
+      <c r="I364" s="1" t="n">
         <v>0.0622</v>
       </c>
-      <c r="I364" s="1" t="n">
+      <c r="J364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -11755,9 +12850,12 @@
         <v>0.03287</v>
       </c>
       <c r="H365" s="1" t="n">
-        <v>0.03297</v>
+        <v>0.03299</v>
       </c>
       <c r="I365" s="1" t="n">
+        <v>0.03299</v>
+      </c>
+      <c r="J365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -11786,9 +12884,12 @@
         <v>0.03288</v>
       </c>
       <c r="H366" s="1" t="n">
+        <v>0.03293</v>
+      </c>
+      <c r="I366" s="1" t="n">
         <v>0.03296</v>
       </c>
-      <c r="I366" s="1" t="n">
+      <c r="J366" s="1" t="n">
         <v>0.03283</v>
       </c>
     </row>
@@ -11817,9 +12918,12 @@
         <v>0.012224</v>
       </c>
       <c r="H367" s="1" t="n">
-        <v>0.012224</v>
+        <v>0.012269</v>
       </c>
       <c r="I367" s="1" t="n">
+        <v>0.012269</v>
+      </c>
+      <c r="J367" s="1" t="n">
         <v>0.012155</v>
       </c>
     </row>
@@ -11848,9 +12952,12 @@
         <v>0.03539</v>
       </c>
       <c r="H368" s="1" t="n">
+        <v>0.03553</v>
+      </c>
+      <c r="I368" s="1" t="n">
         <v>0.03559</v>
       </c>
-      <c r="I368" s="1" t="n">
+      <c r="J368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -11879,9 +12986,12 @@
         <v>0.6307</v>
       </c>
       <c r="H369" s="1" t="n">
+        <v>0.6302</v>
+      </c>
+      <c r="I369" s="1" t="n">
         <v>0.6307</v>
       </c>
-      <c r="I369" s="1" t="n">
+      <c r="J369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -11910,9 +13020,12 @@
         <v>0.00876</v>
       </c>
       <c r="H370" s="1" t="n">
-        <v>0.00876</v>
+        <v>0.00882</v>
       </c>
       <c r="I370" s="1" t="n">
+        <v>0.00882</v>
+      </c>
+      <c r="J370" s="1" t="n">
         <v>0.00843</v>
       </c>
     </row>
@@ -11941,9 +13054,12 @@
         <v>0.003289</v>
       </c>
       <c r="H371" s="1" t="n">
-        <v>0.003289</v>
+        <v>0.003331</v>
       </c>
       <c r="I371" s="1" t="n">
+        <v>0.003331</v>
+      </c>
+      <c r="J371" s="1" t="n">
         <v>0.003242</v>
       </c>
     </row>
@@ -11972,9 +13088,12 @@
         <v>0.13361</v>
       </c>
       <c r="H372" s="1" t="n">
-        <v>0.13361</v>
+        <v>0.13391</v>
       </c>
       <c r="I372" s="1" t="n">
+        <v>0.13391</v>
+      </c>
+      <c r="J372" s="1" t="n">
         <v>0.13227</v>
       </c>
     </row>
@@ -12003,9 +13122,12 @@
         <v>0.00781</v>
       </c>
       <c r="H373" s="1" t="n">
+        <v>0.007795</v>
+      </c>
+      <c r="I373" s="1" t="n">
         <v>0.007822000000000001</v>
       </c>
-      <c r="I373" s="1" t="n">
+      <c r="J373" s="1" t="n">
         <v>0.007771</v>
       </c>
     </row>
@@ -12037,6 +13159,9 @@
         <v>0.01978</v>
       </c>
       <c r="I374" s="1" t="n">
+        <v>0.01978</v>
+      </c>
+      <c r="J374" s="1" t="n">
         <v>0.01969</v>
       </c>
     </row>
@@ -12065,9 +13190,12 @@
         <v>0.0005925</v>
       </c>
       <c r="H375" s="1" t="n">
+        <v>0.0005924</v>
+      </c>
+      <c r="I375" s="1" t="n">
         <v>0.000594</v>
       </c>
-      <c r="I375" s="1" t="n">
+      <c r="J375" s="1" t="n">
         <v>0.0005910000000000001</v>
       </c>
     </row>
@@ -12099,6 +13227,9 @@
         <v>0.0363</v>
       </c>
       <c r="I376" s="1" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="J376" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -12127,9 +13258,12 @@
         <v>0.0007917</v>
       </c>
       <c r="H377" s="1" t="n">
+        <v>0.0007906</v>
+      </c>
+      <c r="I377" s="1" t="n">
         <v>0.000792</v>
       </c>
-      <c r="I377" s="1" t="n">
+      <c r="J377" s="1" t="n">
         <v>0.0007848</v>
       </c>
     </row>
@@ -12158,9 +13292,12 @@
         <v>2.008</v>
       </c>
       <c r="H378" s="1" t="n">
-        <v>2.008</v>
+        <v>2.022</v>
       </c>
       <c r="I378" s="1" t="n">
+        <v>2.022</v>
+      </c>
+      <c r="J378" s="1" t="n">
         <v>1.973</v>
       </c>
     </row>
@@ -12189,9 +13326,12 @@
         <v>0.0005891</v>
       </c>
       <c r="H379" s="1" t="n">
+        <v>0.00059</v>
+      </c>
+      <c r="I379" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="I379" s="1" t="n">
+      <c r="J379" s="1" t="n">
         <v>0.0005881</v>
       </c>
     </row>
@@ -12220,9 +13360,12 @@
         <v>0.03746</v>
       </c>
       <c r="H380" s="1" t="n">
+        <v>0.03745</v>
+      </c>
+      <c r="I380" s="1" t="n">
         <v>0.03751</v>
       </c>
-      <c r="I380" s="1" t="n">
+      <c r="J380" s="1" t="n">
         <v>0.03737</v>
       </c>
     </row>
@@ -12251,9 +13394,12 @@
         <v>0.05481</v>
       </c>
       <c r="H381" s="1" t="n">
+        <v>0.05476</v>
+      </c>
+      <c r="I381" s="1" t="n">
         <v>0.05481</v>
       </c>
-      <c r="I381" s="1" t="n">
+      <c r="J381" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -12282,9 +13428,12 @@
         <v>0.01213</v>
       </c>
       <c r="H382" s="1" t="n">
+        <v>0.01209</v>
+      </c>
+      <c r="I382" s="1" t="n">
         <v>0.01213</v>
       </c>
-      <c r="I382" s="1" t="n">
+      <c r="J382" s="1" t="n">
         <v>0.01202</v>
       </c>
     </row>
@@ -12313,9 +13462,12 @@
         <v>0.001554</v>
       </c>
       <c r="H383" s="1" t="n">
+        <v>0.001553</v>
+      </c>
+      <c r="I383" s="1" t="n">
         <v>0.001559</v>
       </c>
-      <c r="I383" s="1" t="n">
+      <c r="J383" s="1" t="n">
         <v>0.001551</v>
       </c>
     </row>
@@ -12344,9 +13496,12 @@
         <v>0.0002164</v>
       </c>
       <c r="H384" s="1" t="n">
+        <v>0.0002162</v>
+      </c>
+      <c r="I384" s="1" t="n">
         <v>0.0002164</v>
       </c>
-      <c r="I384" s="1" t="n">
+      <c r="J384" s="1" t="n">
         <v>0.0002154</v>
       </c>
     </row>
@@ -12378,6 +13533,9 @@
         <v>0.00242</v>
       </c>
       <c r="I385" s="1" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="J385" s="1" t="n">
         <v>0.0024</v>
       </c>
     </row>
@@ -12406,9 +13564,12 @@
         <v>3.933</v>
       </c>
       <c r="H386" s="1" t="n">
+        <v>3.929</v>
+      </c>
+      <c r="I386" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="I386" s="1" t="n">
+      <c r="J386" s="1" t="n">
         <v>3.892</v>
       </c>
     </row>
@@ -12437,9 +13598,12 @@
         <v>0.0006282</v>
       </c>
       <c r="H387" s="1" t="n">
+        <v>0.0006275</v>
+      </c>
+      <c r="I387" s="1" t="n">
         <v>0.0006282</v>
       </c>
-      <c r="I387" s="1" t="n">
+      <c r="J387" s="1" t="n">
         <v>0.0006236</v>
       </c>
     </row>
@@ -12468,9 +13632,12 @@
         <v>0.00673</v>
       </c>
       <c r="H388" s="1" t="n">
+        <v>0.00667</v>
+      </c>
+      <c r="I388" s="1" t="n">
         <v>0.00673</v>
       </c>
-      <c r="I388" s="1" t="n">
+      <c r="J388" s="1" t="n">
         <v>0.00653</v>
       </c>
     </row>
@@ -12502,6 +13669,9 @@
         <v>0.132</v>
       </c>
       <c r="I389" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="J389" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -12530,9 +13700,12 @@
         <v>0.03223</v>
       </c>
       <c r="H390" s="1" t="n">
+        <v>0.03222</v>
+      </c>
+      <c r="I390" s="1" t="n">
         <v>0.0324</v>
       </c>
-      <c r="I390" s="1" t="n">
+      <c r="J390" s="1" t="n">
         <v>0.03201</v>
       </c>
     </row>
@@ -12561,9 +13734,12 @@
         <v>0.06372</v>
       </c>
       <c r="H391" s="1" t="n">
+        <v>0.06364</v>
+      </c>
+      <c r="I391" s="1" t="n">
         <v>0.06372</v>
       </c>
-      <c r="I391" s="1" t="n">
+      <c r="J391" s="1" t="n">
         <v>0.06344</v>
       </c>
     </row>
@@ -12592,9 +13768,12 @@
         <v>27.69</v>
       </c>
       <c r="H392" s="1" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I392" s="1" t="n">
         <v>27.82</v>
       </c>
-      <c r="I392" s="1" t="n">
+      <c r="J392" s="1" t="n">
         <v>27.57</v>
       </c>
     </row>
@@ -12623,9 +13802,12 @@
         <v>0.000413</v>
       </c>
       <c r="H393" s="1" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="I393" s="1" t="n">
         <v>0.000414</v>
       </c>
-      <c r="I393" s="1" t="n">
+      <c r="J393" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -12654,9 +13836,12 @@
         <v>0.06962</v>
       </c>
       <c r="H394" s="1" t="n">
+        <v>0.06952999999999999</v>
+      </c>
+      <c r="I394" s="1" t="n">
         <v>0.07005</v>
       </c>
-      <c r="I394" s="1" t="n">
+      <c r="J394" s="1" t="n">
         <v>0.06926</v>
       </c>
     </row>
@@ -12685,9 +13870,12 @@
         <v>0.2611</v>
       </c>
       <c r="H395" s="1" t="n">
-        <v>0.2611</v>
+        <v>0.2614</v>
       </c>
       <c r="I395" s="1" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="J395" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -12716,9 +13904,12 @@
         <v>0.004681</v>
       </c>
       <c r="H396" s="1" t="n">
+        <v>0.004683</v>
+      </c>
+      <c r="I396" s="1" t="n">
         <v>0.00469</v>
       </c>
-      <c r="I396" s="1" t="n">
+      <c r="J396" s="1" t="n">
         <v>0.004677</v>
       </c>
     </row>
@@ -12747,9 +13938,12 @@
         <v>0.235</v>
       </c>
       <c r="H397" s="1" t="n">
+        <v>0.2351</v>
+      </c>
+      <c r="I397" s="1" t="n">
         <v>0.2352</v>
       </c>
-      <c r="I397" s="1" t="n">
+      <c r="J397" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
@@ -12778,9 +13972,12 @@
         <v>0.18123</v>
       </c>
       <c r="H398" s="1" t="n">
+        <v>0.18128</v>
+      </c>
+      <c r="I398" s="1" t="n">
         <v>0.18131</v>
       </c>
-      <c r="I398" s="1" t="n">
+      <c r="J398" s="1" t="n">
         <v>0.18106</v>
       </c>
     </row>
@@ -12809,9 +14006,12 @@
         <v>0.04126</v>
       </c>
       <c r="H399" s="1" t="n">
+        <v>0.04125</v>
+      </c>
+      <c r="I399" s="1" t="n">
         <v>0.04126</v>
       </c>
-      <c r="I399" s="1" t="n">
+      <c r="J399" s="1" t="n">
         <v>0.04108</v>
       </c>
     </row>
@@ -12840,9 +14040,12 @@
         <v>0.075</v>
       </c>
       <c r="H400" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="I400" s="1" t="n">
         <v>0.076</v>
       </c>
-      <c r="I400" s="1" t="n">
+      <c r="J400" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -12871,9 +14074,12 @@
         <v>0.001759</v>
       </c>
       <c r="H401" s="1" t="n">
-        <v>0.001759</v>
+        <v>0.001766</v>
       </c>
       <c r="I401" s="1" t="n">
+        <v>0.001766</v>
+      </c>
+      <c r="J401" s="1" t="n">
         <v>0.001739</v>
       </c>
     </row>
@@ -12902,9 +14108,12 @@
         <v>0.05401</v>
       </c>
       <c r="H402" s="1" t="n">
+        <v>0.05398</v>
+      </c>
+      <c r="I402" s="1" t="n">
         <v>0.05401</v>
       </c>
-      <c r="I402" s="1" t="n">
+      <c r="J402" s="1" t="n">
         <v>0.05362</v>
       </c>
     </row>
@@ -12933,10 +14142,13 @@
         <v>2027.65</v>
       </c>
       <c r="H403" s="1" t="n">
+        <v>2026.65</v>
+      </c>
+      <c r="I403" s="1" t="n">
         <v>2031.8</v>
       </c>
-      <c r="I403" s="1" t="n">
-        <v>2027.43</v>
+      <c r="J403" s="1" t="n">
+        <v>2026.65</v>
       </c>
     </row>
     <row r="404">
@@ -12967,6 +14179,9 @@
         <v>1.082</v>
       </c>
       <c r="I404" s="1" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="J404" s="1" t="n">
         <v>1.078</v>
       </c>
     </row>
@@ -12998,6 +14213,9 @@
         <v>7.662</v>
       </c>
       <c r="I405" s="1" t="n">
+        <v>7.662</v>
+      </c>
+      <c r="J405" s="1" t="n">
         <v>7.649</v>
       </c>
     </row>
@@ -13026,9 +14244,12 @@
         <v>3.253</v>
       </c>
       <c r="H406" s="1" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I406" s="1" t="n">
         <v>3.257</v>
       </c>
-      <c r="I406" s="1" t="n">
+      <c r="J406" s="1" t="n">
         <v>3.238</v>
       </c>
     </row>
@@ -13057,9 +14278,12 @@
         <v>0.1819</v>
       </c>
       <c r="H407" s="1" t="n">
-        <v>0.1821</v>
+        <v>0.1823</v>
       </c>
       <c r="I407" s="1" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="J407" s="1" t="n">
         <v>0.1814</v>
       </c>
     </row>
@@ -13088,9 +14312,12 @@
         <v>0.1532</v>
       </c>
       <c r="H408" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="I408" s="1" t="n">
         <v>0.1537</v>
       </c>
-      <c r="I408" s="1" t="n">
+      <c r="J408" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -13119,9 +14346,12 @@
         <v>0.0735</v>
       </c>
       <c r="H409" s="1" t="n">
+        <v>0.07349</v>
+      </c>
+      <c r="I409" s="1" t="n">
         <v>0.0735</v>
       </c>
-      <c r="I409" s="1" t="n">
+      <c r="J409" s="1" t="n">
         <v>0.07315000000000001</v>
       </c>
     </row>
@@ -13150,9 +14380,12 @@
         <v>0.02101</v>
       </c>
       <c r="H410" s="1" t="n">
+        <v>0.02101</v>
+      </c>
+      <c r="I410" s="1" t="n">
         <v>0.02118</v>
       </c>
-      <c r="I410" s="1" t="n">
+      <c r="J410" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -13184,6 +14417,9 @@
         <v>0.2675</v>
       </c>
       <c r="I411" s="1" t="n">
+        <v>0.2675</v>
+      </c>
+      <c r="J411" s="1" t="n">
         <v>0.2642</v>
       </c>
     </row>
@@ -13212,9 +14448,12 @@
         <v>0.00737</v>
       </c>
       <c r="H412" s="1" t="n">
+        <v>0.00737</v>
+      </c>
+      <c r="I412" s="1" t="n">
         <v>0.007383</v>
       </c>
-      <c r="I412" s="1" t="n">
+      <c r="J412" s="1" t="n">
         <v>0.007302</v>
       </c>
     </row>
@@ -13243,9 +14482,12 @@
         <v>0.01387</v>
       </c>
       <c r="H413" s="1" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="I413" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="I413" s="1" t="n">
+      <c r="J413" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -13277,6 +14519,9 @@
         <v>0.093</v>
       </c>
       <c r="I414" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="J414" s="1" t="n">
         <v>0.092</v>
       </c>
     </row>
@@ -13305,9 +14550,12 @@
         <v>0.03985</v>
       </c>
       <c r="H415" s="1" t="n">
+        <v>0.03992</v>
+      </c>
+      <c r="I415" s="1" t="n">
         <v>0.04012</v>
       </c>
-      <c r="I415" s="1" t="n">
+      <c r="J415" s="1" t="n">
         <v>0.03985</v>
       </c>
     </row>
@@ -13336,9 +14584,12 @@
         <v>0.2844</v>
       </c>
       <c r="H416" s="1" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="I416" s="1" t="n">
         <v>0.2854</v>
       </c>
-      <c r="I416" s="1" t="n">
+      <c r="J416" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -13367,9 +14618,12 @@
         <v>1.831</v>
       </c>
       <c r="H417" s="1" t="n">
+        <v>1.828</v>
+      </c>
+      <c r="I417" s="1" t="n">
         <v>1.831</v>
       </c>
-      <c r="I417" s="1" t="n">
+      <c r="J417" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -13398,9 +14652,12 @@
         <v>0.06689000000000001</v>
       </c>
       <c r="H418" s="1" t="n">
+        <v>0.06697</v>
+      </c>
+      <c r="I418" s="1" t="n">
         <v>0.06707</v>
       </c>
-      <c r="I418" s="1" t="n">
+      <c r="J418" s="1" t="n">
         <v>0.06668</v>
       </c>
     </row>
@@ -13429,9 +14686,12 @@
         <v>207.38</v>
       </c>
       <c r="H419" s="1" t="n">
+        <v>207.36</v>
+      </c>
+      <c r="I419" s="1" t="n">
         <v>207.46</v>
       </c>
-      <c r="I419" s="1" t="n">
+      <c r="J419" s="1" t="n">
         <v>207.35</v>
       </c>
     </row>
@@ -13460,9 +14720,12 @@
         <v>73.23</v>
       </c>
       <c r="H420" s="1" t="n">
+        <v>73.27</v>
+      </c>
+      <c r="I420" s="1" t="n">
         <v>73.31999999999999</v>
       </c>
-      <c r="I420" s="1" t="n">
+      <c r="J420" s="1" t="n">
         <v>73.15000000000001</v>
       </c>
     </row>
@@ -13491,9 +14754,12 @@
         <v>0.07228999999999999</v>
       </c>
       <c r="H421" s="1" t="n">
+        <v>0.07231</v>
+      </c>
+      <c r="I421" s="1" t="n">
         <v>0.07251000000000001</v>
       </c>
-      <c r="I421" s="1" t="n">
+      <c r="J421" s="1" t="n">
         <v>0.07226</v>
       </c>
     </row>
@@ -13522,9 +14788,12 @@
         <v>0.05076</v>
       </c>
       <c r="H422" s="1" t="n">
+        <v>0.05071</v>
+      </c>
+      <c r="I422" s="1" t="n">
         <v>0.05076</v>
       </c>
-      <c r="I422" s="1" t="n">
+      <c r="J422" s="1" t="n">
         <v>0.04998</v>
       </c>
     </row>
@@ -13556,6 +14825,9 @@
         <v>0.001152</v>
       </c>
       <c r="I423" s="1" t="n">
+        <v>0.001152</v>
+      </c>
+      <c r="J423" s="1" t="n">
         <v>0.001148</v>
       </c>
     </row>
@@ -13584,9 +14856,12 @@
         <v>0.00503</v>
       </c>
       <c r="H424" s="1" t="n">
+        <v>0.00502</v>
+      </c>
+      <c r="I424" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="I424" s="1" t="n">
+      <c r="J424" s="1" t="n">
         <v>0.00501</v>
       </c>
     </row>
@@ -13615,9 +14890,12 @@
         <v>0.1274</v>
       </c>
       <c r="H425" s="1" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="I425" s="1" t="n">
         <v>0.1274</v>
       </c>
-      <c r="I425" s="1" t="n">
+      <c r="J425" s="1" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -13646,9 +14924,12 @@
         <v>1.296</v>
       </c>
       <c r="H426" s="1" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="I426" s="1" t="n">
         <v>1.299</v>
       </c>
-      <c r="I426" s="1" t="n">
+      <c r="J426" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -13677,9 +14958,12 @@
         <v>0.00441</v>
       </c>
       <c r="H427" s="1" t="n">
+        <v>0.004402</v>
+      </c>
+      <c r="I427" s="1" t="n">
         <v>0.004413</v>
       </c>
-      <c r="I427" s="1" t="n">
+      <c r="J427" s="1" t="n">
         <v>0.004393</v>
       </c>
     </row>
@@ -13708,9 +14992,12 @@
         <v>0.00505</v>
       </c>
       <c r="H428" s="1" t="n">
+        <v>0.005044</v>
+      </c>
+      <c r="I428" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="I428" s="1" t="n">
+      <c r="J428" s="1" t="n">
         <v>0.005017</v>
       </c>
     </row>
@@ -13739,9 +15026,12 @@
         <v>0.02318</v>
       </c>
       <c r="H429" s="1" t="n">
+        <v>0.02313</v>
+      </c>
+      <c r="I429" s="1" t="n">
         <v>0.02329</v>
       </c>
-      <c r="I429" s="1" t="n">
+      <c r="J429" s="1" t="n">
         <v>0.02288</v>
       </c>
     </row>
@@ -13770,9 +15060,12 @@
         <v>0.02517</v>
       </c>
       <c r="H430" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="I430" s="1" t="n">
         <v>0.02517</v>
       </c>
-      <c r="I430" s="1" t="n">
+      <c r="J430" s="1" t="n">
         <v>0.02501</v>
       </c>
     </row>
@@ -13801,9 +15094,12 @@
         <v>0.016</v>
       </c>
       <c r="H431" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="I431" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="I431" s="1" t="n">
+      <c r="J431" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -13832,9 +15128,12 @@
         <v>0.5447</v>
       </c>
       <c r="H432" s="1" t="n">
+        <v>0.5447</v>
+      </c>
+      <c r="I432" s="1" t="n">
         <v>0.546</v>
       </c>
-      <c r="I432" s="1" t="n">
+      <c r="J432" s="1" t="n">
         <v>0.5439000000000001</v>
       </c>
     </row>
@@ -13866,6 +15165,9 @@
         <v>0.001389</v>
       </c>
       <c r="I433" s="1" t="n">
+        <v>0.001389</v>
+      </c>
+      <c r="J433" s="1" t="n">
         <v>0.001383</v>
       </c>
     </row>
@@ -13894,9 +15196,12 @@
         <v>0.3969</v>
       </c>
       <c r="H434" s="1" t="n">
-        <v>0.3969</v>
+        <v>0.397</v>
       </c>
       <c r="I434" s="1" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="J434" s="1" t="n">
         <v>0.3925</v>
       </c>
     </row>
@@ -13925,9 +15230,12 @@
         <v>0.001389</v>
       </c>
       <c r="H435" s="1" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="I435" s="1" t="n">
         <v>0.001393</v>
       </c>
-      <c r="I435" s="1" t="n">
+      <c r="J435" s="1" t="n">
         <v>0.001389</v>
       </c>
     </row>
@@ -13956,9 +15264,12 @@
         <v>0.00718</v>
       </c>
       <c r="H436" s="1" t="n">
+        <v>0.00717</v>
+      </c>
+      <c r="I436" s="1" t="n">
         <v>0.00718</v>
       </c>
-      <c r="I436" s="1" t="n">
+      <c r="J436" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -13987,9 +15298,12 @@
         <v>0.001997</v>
       </c>
       <c r="H437" s="1" t="n">
+        <v>0.001994</v>
+      </c>
+      <c r="I437" s="1" t="n">
         <v>0.001997</v>
       </c>
-      <c r="I437" s="1" t="n">
+      <c r="J437" s="1" t="n">
         <v>0.001982</v>
       </c>
     </row>
@@ -14018,9 +15332,12 @@
         <v>0.3147</v>
       </c>
       <c r="H438" s="1" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="I438" s="1" t="n">
         <v>0.3147</v>
       </c>
-      <c r="I438" s="1" t="n">
+      <c r="J438" s="1" t="n">
         <v>0.3122</v>
       </c>
     </row>
@@ -14049,9 +15366,12 @@
         <v>0.04435</v>
       </c>
       <c r="H439" s="1" t="n">
-        <v>0.04435</v>
+        <v>0.04438</v>
       </c>
       <c r="I439" s="1" t="n">
+        <v>0.04438</v>
+      </c>
+      <c r="J439" s="1" t="n">
         <v>0.04426</v>
       </c>
     </row>
@@ -14080,9 +15400,12 @@
         <v>0.908</v>
       </c>
       <c r="H440" s="1" t="n">
-        <v>0.908</v>
+        <v>0.911</v>
       </c>
       <c r="I440" s="1" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="J440" s="1" t="n">
         <v>0.906</v>
       </c>
     </row>
@@ -14111,9 +15434,12 @@
         <v>1551.5</v>
       </c>
       <c r="H441" s="1" t="n">
-        <v>1551.5</v>
+        <v>1552.1</v>
       </c>
       <c r="I441" s="1" t="n">
+        <v>1552.1</v>
+      </c>
+      <c r="J441" s="1" t="n">
         <v>1548.06</v>
       </c>
     </row>
@@ -14142,9 +15468,12 @@
         <v>0.0008032</v>
       </c>
       <c r="H442" s="1" t="n">
+        <v>0.0007972</v>
+      </c>
+      <c r="I442" s="1" t="n">
         <v>0.0008032</v>
       </c>
-      <c r="I442" s="1" t="n">
+      <c r="J442" s="1" t="n">
         <v>0.0007877</v>
       </c>
     </row>
@@ -14173,10 +15502,13 @@
         <v>0.003537</v>
       </c>
       <c r="H443" s="1" t="n">
+        <v>0.003515</v>
+      </c>
+      <c r="I443" s="1" t="n">
         <v>0.003558</v>
       </c>
-      <c r="I443" s="1" t="n">
-        <v>0.003537</v>
+      <c r="J443" s="1" t="n">
+        <v>0.003515</v>
       </c>
     </row>
     <row r="444">
@@ -14204,9 +15536,12 @@
         <v>1.986</v>
       </c>
       <c r="H444" s="1" t="n">
+        <v>1.982</v>
+      </c>
+      <c r="I444" s="1" t="n">
         <v>1.989</v>
       </c>
-      <c r="I444" s="1" t="n">
+      <c r="J444" s="1" t="n">
         <v>1.977</v>
       </c>
     </row>
@@ -14235,9 +15570,12 @@
         <v>1.307</v>
       </c>
       <c r="H445" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="I445" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="I445" s="1" t="n">
+      <c r="J445" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -14266,9 +15604,12 @@
         <v>0.0689</v>
       </c>
       <c r="H446" s="1" t="n">
+        <v>0.06905</v>
+      </c>
+      <c r="I446" s="1" t="n">
         <v>0.06929</v>
       </c>
-      <c r="I446" s="1" t="n">
+      <c r="J446" s="1" t="n">
         <v>0.0689</v>
       </c>
     </row>
@@ -14297,9 +15638,12 @@
         <v>0.02382</v>
       </c>
       <c r="H447" s="1" t="n">
-        <v>0.02382</v>
+        <v>0.02403</v>
       </c>
       <c r="I447" s="1" t="n">
+        <v>0.02403</v>
+      </c>
+      <c r="J447" s="1" t="n">
         <v>0.02347</v>
       </c>
     </row>
@@ -14328,9 +15672,12 @@
         <v>0.01399</v>
       </c>
       <c r="H448" s="1" t="n">
+        <v>0.01399</v>
+      </c>
+      <c r="I448" s="1" t="n">
         <v>0.014</v>
       </c>
-      <c r="I448" s="1" t="n">
+      <c r="J448" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -14359,9 +15706,12 @@
         <v>3.73</v>
       </c>
       <c r="H449" s="1" t="n">
+        <v>3.732</v>
+      </c>
+      <c r="I449" s="1" t="n">
         <v>3.734</v>
       </c>
-      <c r="I449" s="1" t="n">
+      <c r="J449" s="1" t="n">
         <v>3.726</v>
       </c>
     </row>
@@ -14390,9 +15740,12 @@
         <v>0.0114</v>
       </c>
       <c r="H450" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="I450" s="1" t="n">
         <v>0.0115</v>
       </c>
-      <c r="I450" s="1" t="n">
+      <c r="J450" s="1" t="n">
         <v>0.0114</v>
       </c>
     </row>
@@ -14421,9 +15774,12 @@
         <v>0.01034</v>
       </c>
       <c r="H451" s="1" t="n">
+        <v>0.01032</v>
+      </c>
+      <c r="I451" s="1" t="n">
         <v>0.01034</v>
       </c>
-      <c r="I451" s="1" t="n">
+      <c r="J451" s="1" t="n">
         <v>0.01024</v>
       </c>
     </row>
@@ -14452,9 +15808,12 @@
         <v>0.1532</v>
       </c>
       <c r="H452" s="1" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="I452" s="1" t="n">
         <v>0.1532</v>
       </c>
-      <c r="I452" s="1" t="n">
+      <c r="J452" s="1" t="n">
         <v>0.1522</v>
       </c>
     </row>
@@ -14483,9 +15842,12 @@
         <v>151.15</v>
       </c>
       <c r="H453" s="1" t="n">
-        <v>151.15</v>
+        <v>151.19</v>
       </c>
       <c r="I453" s="1" t="n">
+        <v>151.19</v>
+      </c>
+      <c r="J453" s="1" t="n">
         <v>150.85</v>
       </c>
     </row>
@@ -14514,9 +15876,12 @@
         <v>0.008633</v>
       </c>
       <c r="H454" s="1" t="n">
+        <v>0.008626</v>
+      </c>
+      <c r="I454" s="1" t="n">
         <v>0.008633</v>
       </c>
-      <c r="I454" s="1" t="n">
+      <c r="J454" s="1" t="n">
         <v>0.008593999999999999</v>
       </c>
     </row>
@@ -14545,9 +15910,12 @@
         <v>0.05251</v>
       </c>
       <c r="H455" s="1" t="n">
-        <v>0.05251</v>
+        <v>0.05255</v>
       </c>
       <c r="I455" s="1" t="n">
+        <v>0.05255</v>
+      </c>
+      <c r="J455" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -14576,9 +15944,12 @@
         <v>0.30782</v>
       </c>
       <c r="H456" s="1" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="I456" s="1" t="n">
         <v>0.30782</v>
       </c>
-      <c r="I456" s="1" t="n">
+      <c r="J456" s="1" t="n">
         <v>0.30269</v>
       </c>
     </row>
@@ -14610,6 +15981,9 @@
         <v>0.00547</v>
       </c>
       <c r="I457" s="1" t="n">
+        <v>0.00547</v>
+      </c>
+      <c r="J457" s="1" t="n">
         <v>0.00544</v>
       </c>
     </row>
@@ -14638,9 +16012,12 @@
         <v>0.1002</v>
       </c>
       <c r="H458" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="I458" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="I458" s="1" t="n">
+      <c r="J458" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -14669,9 +16046,12 @@
         <v>0.001835</v>
       </c>
       <c r="H459" s="1" t="n">
+        <v>0.001832</v>
+      </c>
+      <c r="I459" s="1" t="n">
         <v>0.001835</v>
       </c>
-      <c r="I459" s="1" t="n">
+      <c r="J459" s="1" t="n">
         <v>0.001825</v>
       </c>
     </row>
@@ -14700,9 +16080,12 @@
         <v>0.01848</v>
       </c>
       <c r="H460" s="1" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="I460" s="1" t="n">
         <v>0.01848</v>
       </c>
-      <c r="I460" s="1" t="n">
+      <c r="J460" s="1" t="n">
         <v>0.01822</v>
       </c>
     </row>
@@ -14731,10 +16114,13 @@
         <v>0.0004858</v>
       </c>
       <c r="H461" s="1" t="n">
+        <v>0.0004842</v>
+      </c>
+      <c r="I461" s="1" t="n">
         <v>0.0004877</v>
       </c>
-      <c r="I461" s="1" t="n">
-        <v>0.0004844</v>
+      <c r="J461" s="1" t="n">
+        <v>0.0004842</v>
       </c>
     </row>
     <row r="462">
@@ -14765,6 +16151,9 @@
         <v>0.0961</v>
       </c>
       <c r="I462" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="J462" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -14793,9 +16182,12 @@
         <v>0.07926999999999999</v>
       </c>
       <c r="H463" s="1" t="n">
+        <v>0.07922999999999999</v>
+      </c>
+      <c r="I463" s="1" t="n">
         <v>0.07931000000000001</v>
       </c>
-      <c r="I463" s="1" t="n">
+      <c r="J463" s="1" t="n">
         <v>0.07888000000000001</v>
       </c>
     </row>
@@ -14824,9 +16216,12 @@
         <v>0.03159</v>
       </c>
       <c r="H464" s="1" t="n">
-        <v>0.03159</v>
+        <v>0.03207</v>
       </c>
       <c r="I464" s="1" t="n">
+        <v>0.03207</v>
+      </c>
+      <c r="J464" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -14855,9 +16250,12 @@
         <v>0.01615</v>
       </c>
       <c r="H465" s="1" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="I465" s="1" t="n">
         <v>0.01618</v>
       </c>
-      <c r="I465" s="1" t="n">
+      <c r="J465" s="1" t="n">
         <v>0.01613</v>
       </c>
     </row>
@@ -14886,9 +16284,12 @@
         <v>0.06769</v>
       </c>
       <c r="H466" s="1" t="n">
+        <v>0.06777</v>
+      </c>
+      <c r="I466" s="1" t="n">
         <v>0.06781</v>
       </c>
-      <c r="I466" s="1" t="n">
+      <c r="J466" s="1" t="n">
         <v>0.06763</v>
       </c>
     </row>
@@ -14917,9 +16318,12 @@
         <v>0.04324</v>
       </c>
       <c r="H467" s="1" t="n">
+        <v>0.04323</v>
+      </c>
+      <c r="I467" s="1" t="n">
         <v>0.04332</v>
       </c>
-      <c r="I467" s="1" t="n">
+      <c r="J467" s="1" t="n">
         <v>0.04322</v>
       </c>
     </row>
@@ -14948,9 +16352,12 @@
         <v>0.05658</v>
       </c>
       <c r="H468" s="1" t="n">
+        <v>0.05595</v>
+      </c>
+      <c r="I468" s="1" t="n">
         <v>0.05795</v>
       </c>
-      <c r="I468" s="1" t="n">
+      <c r="J468" s="1" t="n">
         <v>0.05587</v>
       </c>
     </row>
@@ -14979,9 +16386,12 @@
         <v>0.2308</v>
       </c>
       <c r="H469" s="1" t="n">
-        <v>0.2308</v>
+        <v>0.2309</v>
       </c>
       <c r="I469" s="1" t="n">
+        <v>0.2309</v>
+      </c>
+      <c r="J469" s="1" t="n">
         <v>0.2294</v>
       </c>
     </row>
@@ -15013,6 +16423,9 @@
         <v>0.0905</v>
       </c>
       <c r="I470" s="1" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="J470" s="1" t="n">
         <v>0.0902</v>
       </c>
     </row>
@@ -15041,9 +16454,12 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="H471" s="1" t="n">
+        <v>0.06665</v>
+      </c>
+      <c r="I471" s="1" t="n">
         <v>0.0669</v>
       </c>
-      <c r="I471" s="1" t="n">
+      <c r="J471" s="1" t="n">
         <v>0.06660000000000001</v>
       </c>
     </row>
@@ -15072,9 +16488,12 @@
         <v>6.555</v>
       </c>
       <c r="H472" s="1" t="n">
-        <v>6.555</v>
+        <v>6.563</v>
       </c>
       <c r="I472" s="1" t="n">
+        <v>6.563</v>
+      </c>
+      <c r="J472" s="1" t="n">
         <v>6.486</v>
       </c>
     </row>
@@ -15103,9 +16522,12 @@
         <v>0.01945</v>
       </c>
       <c r="H473" s="1" t="n">
+        <v>0.01944</v>
+      </c>
+      <c r="I473" s="1" t="n">
         <v>0.01945</v>
       </c>
-      <c r="I473" s="1" t="n">
+      <c r="J473" s="1" t="n">
         <v>0.01937</v>
       </c>
     </row>
@@ -15137,6 +16559,9 @@
         <v>1.423</v>
       </c>
       <c r="I474" s="1" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="J474" s="1" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -15165,10 +16590,13 @@
         <v>0.08971</v>
       </c>
       <c r="H475" s="1" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="I475" s="1" t="n">
         <v>0.08981</v>
       </c>
-      <c r="I475" s="1" t="n">
-        <v>0.08971</v>
+      <c r="J475" s="1" t="n">
+        <v>0.0896</v>
       </c>
     </row>
     <row r="476">
@@ -15199,6 +16627,9 @@
         <v>0.1062</v>
       </c>
       <c r="I476" s="1" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="J476" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -15227,9 +16658,12 @@
         <v>0.09415</v>
       </c>
       <c r="H477" s="1" t="n">
+        <v>0.09421</v>
+      </c>
+      <c r="I477" s="1" t="n">
         <v>0.09451</v>
       </c>
-      <c r="I477" s="1" t="n">
+      <c r="J477" s="1" t="n">
         <v>0.0941</v>
       </c>
     </row>
@@ -15258,9 +16692,12 @@
         <v>0.0001628</v>
       </c>
       <c r="H478" s="1" t="n">
-        <v>0.0001629</v>
+        <v>0.000163</v>
       </c>
       <c r="I478" s="1" t="n">
+        <v>0.000163</v>
+      </c>
+      <c r="J478" s="1" t="n">
         <v>0.0001624</v>
       </c>
     </row>
@@ -15289,9 +16726,12 @@
         <v>0.04019</v>
       </c>
       <c r="H479" s="1" t="n">
+        <v>0.04021</v>
+      </c>
+      <c r="I479" s="1" t="n">
         <v>0.04023</v>
       </c>
-      <c r="I479" s="1" t="n">
+      <c r="J479" s="1" t="n">
         <v>0.04007</v>
       </c>
     </row>
@@ -15320,9 +16760,12 @@
         <v>0.007423</v>
       </c>
       <c r="H480" s="1" t="n">
-        <v>0.007423</v>
+        <v>0.007425</v>
       </c>
       <c r="I480" s="1" t="n">
+        <v>0.007425</v>
+      </c>
+      <c r="J480" s="1" t="n">
         <v>0.007389</v>
       </c>
     </row>
@@ -15351,9 +16794,12 @@
         <v>0.0954</v>
       </c>
       <c r="H481" s="1" t="n">
+        <v>0.0954</v>
+      </c>
+      <c r="I481" s="1" t="n">
         <v>0.0955</v>
       </c>
-      <c r="I481" s="1" t="n">
+      <c r="J481" s="1" t="n">
         <v>0.0954</v>
       </c>
     </row>
@@ -15382,9 +16828,12 @@
         <v>0.05609</v>
       </c>
       <c r="H482" s="1" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="I482" s="1" t="n">
         <v>0.05621</v>
       </c>
-      <c r="I482" s="1" t="n">
+      <c r="J482" s="1" t="n">
         <v>0.05569</v>
       </c>
     </row>
@@ -15413,9 +16862,12 @@
         <v>0.006198</v>
       </c>
       <c r="H483" s="1" t="n">
+        <v>0.006189</v>
+      </c>
+      <c r="I483" s="1" t="n">
         <v>0.006198</v>
       </c>
-      <c r="I483" s="1" t="n">
+      <c r="J483" s="1" t="n">
         <v>0.006161</v>
       </c>
     </row>
@@ -15444,9 +16896,12 @@
         <v>0.01497</v>
       </c>
       <c r="H484" s="1" t="n">
+        <v>0.01494</v>
+      </c>
+      <c r="I484" s="1" t="n">
         <v>0.01497</v>
       </c>
-      <c r="I484" s="1" t="n">
+      <c r="J484" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -15475,9 +16930,12 @@
         <v>0.02412</v>
       </c>
       <c r="H485" s="1" t="n">
+        <v>0.02412</v>
+      </c>
+      <c r="I485" s="1" t="n">
         <v>0.02427</v>
       </c>
-      <c r="I485" s="1" t="n">
+      <c r="J485" s="1" t="n">
         <v>0.02403</v>
       </c>
     </row>
@@ -15506,9 +16964,12 @@
         <v>0.06696000000000001</v>
       </c>
       <c r="H486" s="1" t="n">
+        <v>0.06688</v>
+      </c>
+      <c r="I486" s="1" t="n">
         <v>0.06702</v>
       </c>
-      <c r="I486" s="1" t="n">
+      <c r="J486" s="1" t="n">
         <v>0.0667</v>
       </c>
     </row>
@@ -15537,9 +16998,12 @@
         <v>0.0369</v>
       </c>
       <c r="H487" s="1" t="n">
+        <v>0.03692</v>
+      </c>
+      <c r="I487" s="1" t="n">
         <v>0.03705</v>
       </c>
-      <c r="I487" s="1" t="n">
+      <c r="J487" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -15568,9 +17032,12 @@
         <v>0.01818</v>
       </c>
       <c r="H488" s="1" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="I488" s="1" t="n">
         <v>0.0182</v>
       </c>
-      <c r="I488" s="1" t="n">
+      <c r="J488" s="1" t="n">
         <v>0.01814</v>
       </c>
     </row>
@@ -15599,9 +17066,12 @@
         <v>0.03228</v>
       </c>
       <c r="H489" s="1" t="n">
+        <v>0.03253</v>
+      </c>
+      <c r="I489" s="1" t="n">
         <v>0.03278</v>
       </c>
-      <c r="I489" s="1" t="n">
+      <c r="J489" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -15630,9 +17100,12 @@
         <v>0.01468</v>
       </c>
       <c r="H490" s="1" t="n">
+        <v>0.01467</v>
+      </c>
+      <c r="I490" s="1" t="n">
         <v>0.01474</v>
       </c>
-      <c r="I490" s="1" t="n">
+      <c r="J490" s="1" t="n">
         <v>0.01458</v>
       </c>
     </row>
@@ -15661,9 +17134,12 @@
         <v>0.01876</v>
       </c>
       <c r="H491" s="1" t="n">
+        <v>0.01871</v>
+      </c>
+      <c r="I491" s="1" t="n">
         <v>0.01876</v>
       </c>
-      <c r="I491" s="1" t="n">
+      <c r="J491" s="1" t="n">
         <v>0.01851</v>
       </c>
     </row>
@@ -15692,9 +17168,12 @@
         <v>0.08826000000000001</v>
       </c>
       <c r="H492" s="1" t="n">
+        <v>0.08832</v>
+      </c>
+      <c r="I492" s="1" t="n">
         <v>0.08935</v>
       </c>
-      <c r="I492" s="1" t="n">
+      <c r="J492" s="1" t="n">
         <v>0.08810999999999999</v>
       </c>
     </row>
@@ -15723,9 +17202,12 @@
         <v>0.006514</v>
       </c>
       <c r="H493" s="1" t="n">
+        <v>0.006508</v>
+      </c>
+      <c r="I493" s="1" t="n">
         <v>0.006514</v>
       </c>
-      <c r="I493" s="1" t="n">
+      <c r="J493" s="1" t="n">
         <v>0.006497</v>
       </c>
     </row>
@@ -15757,6 +17239,9 @@
         <v>0.1331</v>
       </c>
       <c r="I494" s="1" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="J494" s="1" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -15785,9 +17270,12 @@
         <v>0.2844</v>
       </c>
       <c r="H495" s="1" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="I495" s="1" t="n">
         <v>0.2853</v>
       </c>
-      <c r="I495" s="1" t="n">
+      <c r="J495" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -15816,9 +17304,12 @@
         <v>0.004536</v>
       </c>
       <c r="H496" s="1" t="n">
-        <v>0.004536</v>
+        <v>0.004537</v>
       </c>
       <c r="I496" s="1" t="n">
+        <v>0.004537</v>
+      </c>
+      <c r="J496" s="1" t="n">
         <v>0.004516</v>
       </c>
     </row>
@@ -15847,9 +17338,12 @@
         <v>0.1269</v>
       </c>
       <c r="H497" s="1" t="n">
+        <v>0.1267</v>
+      </c>
+      <c r="I497" s="1" t="n">
         <v>0.1283</v>
       </c>
-      <c r="I497" s="1" t="n">
+      <c r="J497" s="1" t="n">
         <v>0.1265</v>
       </c>
     </row>
@@ -15878,9 +17372,12 @@
         <v>0.03445</v>
       </c>
       <c r="H498" s="1" t="n">
+        <v>0.03441</v>
+      </c>
+      <c r="I498" s="1" t="n">
         <v>0.03445</v>
       </c>
-      <c r="I498" s="1" t="n">
+      <c r="J498" s="1" t="n">
         <v>0.03423</v>
       </c>
     </row>
@@ -15909,9 +17406,12 @@
         <v>0.03567</v>
       </c>
       <c r="H499" s="1" t="n">
+        <v>0.03569</v>
+      </c>
+      <c r="I499" s="1" t="n">
         <v>0.03576</v>
       </c>
-      <c r="I499" s="1" t="n">
+      <c r="J499" s="1" t="n">
         <v>0.03557</v>
       </c>
     </row>
@@ -15940,9 +17440,12 @@
         <v>0.003415</v>
       </c>
       <c r="H500" s="1" t="n">
+        <v>0.003417</v>
+      </c>
+      <c r="I500" s="1" t="n">
         <v>0.003421</v>
       </c>
-      <c r="I500" s="1" t="n">
+      <c r="J500" s="1" t="n">
         <v>0.003413</v>
       </c>
     </row>
@@ -15971,9 +17474,12 @@
         <v>0.0003834</v>
       </c>
       <c r="H501" s="1" t="n">
+        <v>0.0003829</v>
+      </c>
+      <c r="I501" s="1" t="n">
         <v>0.0003834</v>
       </c>
-      <c r="I501" s="1" t="n">
+      <c r="J501" s="1" t="n">
         <v>0.0003786</v>
       </c>
     </row>
@@ -16002,9 +17508,12 @@
         <v>0.3004</v>
       </c>
       <c r="H502" s="1" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="I502" s="1" t="n">
         <v>0.3004</v>
       </c>
-      <c r="I502" s="1" t="n">
+      <c r="J502" s="1" t="n">
         <v>0.2986</v>
       </c>
     </row>
@@ -16033,9 +17542,12 @@
         <v>0.06489</v>
       </c>
       <c r="H503" s="1" t="n">
+        <v>0.06496</v>
+      </c>
+      <c r="I503" s="1" t="n">
         <v>0.06507</v>
       </c>
-      <c r="I503" s="1" t="n">
+      <c r="J503" s="1" t="n">
         <v>0.06485</v>
       </c>
     </row>
@@ -16067,6 +17579,9 @@
         <v>0.178</v>
       </c>
       <c r="I504" s="1" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="J504" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -16095,9 +17610,12 @@
         <v>0.1514</v>
       </c>
       <c r="H505" s="1" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="I505" s="1" t="n">
         <v>0.1514</v>
       </c>
-      <c r="I505" s="1" t="n">
+      <c r="J505" s="1" t="n">
         <v>0.1512</v>
       </c>
     </row>
@@ -16129,6 +17647,9 @@
         <v>0.01199</v>
       </c>
       <c r="I506" s="1" t="n">
+        <v>0.01199</v>
+      </c>
+      <c r="J506" s="1" t="n">
         <v>0.01193</v>
       </c>
     </row>
@@ -16157,9 +17678,12 @@
         <v>0.2873</v>
       </c>
       <c r="H507" s="1" t="n">
-        <v>0.2883</v>
+        <v>0.2893</v>
       </c>
       <c r="I507" s="1" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="J507" s="1" t="n">
         <v>0.2871</v>
       </c>
     </row>
@@ -16188,9 +17712,12 @@
         <v>0.009350000000000001</v>
       </c>
       <c r="H508" s="1" t="n">
+        <v>0.00933</v>
+      </c>
+      <c r="I508" s="1" t="n">
         <v>0.0094</v>
       </c>
-      <c r="I508" s="1" t="n">
+      <c r="J508" s="1" t="n">
         <v>0.009310000000000001</v>
       </c>
     </row>
@@ -16219,9 +17746,12 @@
         <v>0.006822</v>
       </c>
       <c r="H509" s="1" t="n">
-        <v>0.006822</v>
+        <v>0.006833</v>
       </c>
       <c r="I509" s="1" t="n">
+        <v>0.006833</v>
+      </c>
+      <c r="J509" s="1" t="n">
         <v>0.006783</v>
       </c>
     </row>
@@ -16250,9 +17780,12 @@
         <v>0.2942</v>
       </c>
       <c r="H510" s="1" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="I510" s="1" t="n">
         <v>0.2951</v>
       </c>
-      <c r="I510" s="1" t="n">
+      <c r="J510" s="1" t="n">
         <v>0.2934</v>
       </c>
     </row>
@@ -16281,9 +17814,12 @@
         <v>0.01467</v>
       </c>
       <c r="H511" s="1" t="n">
+        <v>0.01467</v>
+      </c>
+      <c r="I511" s="1" t="n">
         <v>0.01471</v>
       </c>
-      <c r="I511" s="1" t="n">
+      <c r="J511" s="1" t="n">
         <v>0.01465</v>
       </c>
     </row>
@@ -16312,9 +17848,12 @@
         <v>0.1398</v>
       </c>
       <c r="H512" s="1" t="n">
+        <v>0.1396</v>
+      </c>
+      <c r="I512" s="1" t="n">
         <v>0.1398</v>
       </c>
-      <c r="I512" s="1" t="n">
+      <c r="J512" s="1" t="n">
         <v>0.1394</v>
       </c>
     </row>
@@ -16346,6 +17885,9 @@
         <v>0.08144999999999999</v>
       </c>
       <c r="I513" s="1" t="n">
+        <v>0.08144999999999999</v>
+      </c>
+      <c r="J513" s="1" t="n">
         <v>0.08069</v>
       </c>
     </row>
@@ -16377,6 +17919,9 @@
         <v>0.0251</v>
       </c>
       <c r="I514" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="J514" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -16405,9 +17950,12 @@
         <v>0.06329</v>
       </c>
       <c r="H515" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="I515" s="1" t="n">
         <v>0.06329</v>
       </c>
-      <c r="I515" s="1" t="n">
+      <c r="J515" s="1" t="n">
         <v>0.06301</v>
       </c>
     </row>
@@ -16436,9 +17984,12 @@
         <v>0.04732</v>
       </c>
       <c r="H516" s="1" t="n">
-        <v>0.04732</v>
+        <v>0.04735</v>
       </c>
       <c r="I516" s="1" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="J516" s="1" t="n">
         <v>0.04707</v>
       </c>
     </row>
@@ -16467,9 +18018,12 @@
         <v>0.004904</v>
       </c>
       <c r="H517" s="1" t="n">
-        <v>0.004908</v>
+        <v>0.004909</v>
       </c>
       <c r="I517" s="1" t="n">
+        <v>0.004909</v>
+      </c>
+      <c r="J517" s="1" t="n">
         <v>0.004902</v>
       </c>
     </row>
@@ -16498,9 +18052,12 @@
         <v>0.009424999999999999</v>
       </c>
       <c r="H518" s="1" t="n">
+        <v>0.009422</v>
+      </c>
+      <c r="I518" s="1" t="n">
         <v>0.009431999999999999</v>
       </c>
-      <c r="I518" s="1" t="n">
+      <c r="J518" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -16529,9 +18086,12 @@
         <v>0.01805</v>
       </c>
       <c r="H519" s="1" t="n">
+        <v>0.01805</v>
+      </c>
+      <c r="I519" s="1" t="n">
         <v>0.01807</v>
       </c>
-      <c r="I519" s="1" t="n">
+      <c r="J519" s="1" t="n">
         <v>0.01798</v>
       </c>
     </row>
@@ -16560,9 +18120,12 @@
         <v>0.06688</v>
       </c>
       <c r="H520" s="1" t="n">
+        <v>0.06642000000000001</v>
+      </c>
+      <c r="I520" s="1" t="n">
         <v>0.06688</v>
       </c>
-      <c r="I520" s="1" t="n">
+      <c r="J520" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -16591,9 +18154,12 @@
         <v>0.1368</v>
       </c>
       <c r="H521" s="1" t="n">
-        <v>0.1368</v>
+        <v>0.137</v>
       </c>
       <c r="I521" s="1" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="J521" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -16622,9 +18188,12 @@
         <v>0.04738</v>
       </c>
       <c r="H522" s="1" t="n">
+        <v>0.04726</v>
+      </c>
+      <c r="I522" s="1" t="n">
         <v>0.04746</v>
       </c>
-      <c r="I522" s="1" t="n">
+      <c r="J522" s="1" t="n">
         <v>0.04718</v>
       </c>
     </row>
@@ -16653,9 +18222,12 @@
         <v>0.068</v>
       </c>
       <c r="H523" s="1" t="n">
+        <v>0.06805</v>
+      </c>
+      <c r="I523" s="1" t="n">
         <v>0.06809</v>
       </c>
-      <c r="I523" s="1" t="n">
+      <c r="J523" s="1" t="n">
         <v>0.06784999999999999</v>
       </c>
     </row>
@@ -16684,9 +18256,12 @@
         <v>0.6983</v>
       </c>
       <c r="H524" s="1" t="n">
+        <v>0.6982</v>
+      </c>
+      <c r="I524" s="1" t="n">
         <v>0.6983</v>
       </c>
-      <c r="I524" s="1" t="n">
+      <c r="J524" s="1" t="n">
         <v>0.6966</v>
       </c>
     </row>
@@ -16718,6 +18293,9 @@
         <v>0.00268</v>
       </c>
       <c r="I525" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="J525" s="1" t="n">
         <v>0.00267</v>
       </c>
     </row>
@@ -16746,9 +18324,12 @@
         <v>0.4867</v>
       </c>
       <c r="H526" s="1" t="n">
-        <v>0.4868</v>
+        <v>0.487</v>
       </c>
       <c r="I526" s="1" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="J526" s="1" t="n">
         <v>0.4856</v>
       </c>
     </row>
@@ -16780,6 +18361,9 @@
         <v>45.83</v>
       </c>
       <c r="I527" s="1" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="J527" s="1" t="n">
         <v>45.76</v>
       </c>
     </row>
@@ -16808,9 +18392,12 @@
         <v>0.02437</v>
       </c>
       <c r="H528" s="1" t="n">
-        <v>0.02437</v>
+        <v>0.02443</v>
       </c>
       <c r="I528" s="1" t="n">
+        <v>0.02443</v>
+      </c>
+      <c r="J528" s="1" t="n">
         <v>0.02429</v>
       </c>
     </row>
@@ -16839,9 +18426,12 @@
         <v>0.006403</v>
       </c>
       <c r="H529" s="1" t="n">
-        <v>0.006403</v>
+        <v>0.006406</v>
       </c>
       <c r="I529" s="1" t="n">
+        <v>0.006406</v>
+      </c>
+      <c r="J529" s="1" t="n">
         <v>0.00638</v>
       </c>
     </row>
@@ -16873,6 +18463,9 @@
         <v>0.2002</v>
       </c>
       <c r="I530" s="1" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="J530" s="1" t="n">
         <v>0.1993</v>
       </c>
     </row>
@@ -16901,9 +18494,12 @@
         <v>0.007685</v>
       </c>
       <c r="H531" s="1" t="n">
+        <v>0.007679</v>
+      </c>
+      <c r="I531" s="1" t="n">
         <v>0.007727</v>
       </c>
-      <c r="I531" s="1" t="n">
+      <c r="J531" s="1" t="n">
         <v>0.007657</v>
       </c>
     </row>
@@ -16932,9 +18528,12 @@
         <v>2.282</v>
       </c>
       <c r="H532" s="1" t="n">
+        <v>2.284</v>
+      </c>
+      <c r="I532" s="1" t="n">
         <v>2.285</v>
       </c>
-      <c r="I532" s="1" t="n">
+      <c r="J532" s="1" t="n">
         <v>2.275</v>
       </c>
     </row>
@@ -16963,9 +18562,12 @@
         <v>0.04156</v>
       </c>
       <c r="H533" s="1" t="n">
+        <v>0.04148</v>
+      </c>
+      <c r="I533" s="1" t="n">
         <v>0.04156</v>
       </c>
-      <c r="I533" s="1" t="n">
+      <c r="J533" s="1" t="n">
         <v>0.04138</v>
       </c>
     </row>
@@ -16994,9 +18596,12 @@
         <v>0.1833</v>
       </c>
       <c r="H534" s="1" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="I534" s="1" t="n">
         <v>0.1833</v>
       </c>
-      <c r="I534" s="1" t="n">
+      <c r="J534" s="1" t="n">
         <v>0.1811</v>
       </c>
     </row>
@@ -17025,9 +18630,12 @@
         <v>0.04299</v>
       </c>
       <c r="H535" s="1" t="n">
+        <v>0.04298</v>
+      </c>
+      <c r="I535" s="1" t="n">
         <v>0.04311</v>
       </c>
-      <c r="I535" s="1" t="n">
+      <c r="J535" s="1" t="n">
         <v>0.04287</v>
       </c>
     </row>
@@ -17056,9 +18664,12 @@
         <v>0.05409</v>
       </c>
       <c r="H536" s="1" t="n">
+        <v>0.0541</v>
+      </c>
+      <c r="I536" s="1" t="n">
         <v>0.05438</v>
       </c>
-      <c r="I536" s="1" t="n">
+      <c r="J536" s="1" t="n">
         <v>0.05409</v>
       </c>
     </row>
@@ -17087,9 +18698,12 @@
         <v>0.1605</v>
       </c>
       <c r="H537" s="1" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="I537" s="1" t="n">
         <v>0.1609</v>
       </c>
-      <c r="I537" s="1" t="n">
+      <c r="J537" s="1" t="n">
         <v>0.1602</v>
       </c>
     </row>
@@ -17118,9 +18732,12 @@
         <v>0.03682</v>
       </c>
       <c r="H538" s="1" t="n">
+        <v>0.03681</v>
+      </c>
+      <c r="I538" s="1" t="n">
         <v>0.03687</v>
       </c>
-      <c r="I538" s="1" t="n">
+      <c r="J538" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -17149,9 +18766,12 @@
         <v>0.05807</v>
       </c>
       <c r="H539" s="1" t="n">
-        <v>0.05807</v>
+        <v>0.05844</v>
       </c>
       <c r="I539" s="1" t="n">
+        <v>0.05844</v>
+      </c>
+      <c r="J539" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -17180,9 +18800,12 @@
         <v>0.04266</v>
       </c>
       <c r="H540" s="1" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="I540" s="1" t="n">
         <v>0.04267</v>
       </c>
-      <c r="I540" s="1" t="n">
+      <c r="J540" s="1" t="n">
         <v>0.04256</v>
       </c>
     </row>
@@ -17211,9 +18834,12 @@
         <v>0.01729</v>
       </c>
       <c r="H541" s="1" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="I541" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="I541" s="1" t="n">
+      <c r="J541" s="1" t="n">
         <v>0.0172</v>
       </c>
     </row>
@@ -17242,9 +18868,12 @@
         <v>0.00397</v>
       </c>
       <c r="H542" s="1" t="n">
+        <v>0.003969</v>
+      </c>
+      <c r="I542" s="1" t="n">
         <v>0.003975</v>
       </c>
-      <c r="I542" s="1" t="n">
+      <c r="J542" s="1" t="n">
         <v>0.003963</v>
       </c>
     </row>
@@ -17273,9 +18902,12 @@
         <v>0.05768</v>
       </c>
       <c r="H543" s="1" t="n">
+        <v>0.05785</v>
+      </c>
+      <c r="I543" s="1" t="n">
         <v>0.05817</v>
       </c>
-      <c r="I543" s="1" t="n">
+      <c r="J543" s="1" t="n">
         <v>0.05735</v>
       </c>
     </row>
@@ -17304,9 +18936,12 @@
         <v>0.05019</v>
       </c>
       <c r="H544" s="1" t="n">
+        <v>0.05023</v>
+      </c>
+      <c r="I544" s="1" t="n">
         <v>0.05042</v>
       </c>
-      <c r="I544" s="1" t="n">
+      <c r="J544" s="1" t="n">
         <v>0.05016</v>
       </c>
     </row>
@@ -17335,9 +18970,12 @@
         <v>0.04071</v>
       </c>
       <c r="H545" s="1" t="n">
+        <v>0.04066</v>
+      </c>
+      <c r="I545" s="1" t="n">
         <v>0.04071</v>
       </c>
-      <c r="I545" s="1" t="n">
+      <c r="J545" s="1" t="n">
         <v>0.04038</v>
       </c>
     </row>
@@ -17366,9 +19004,12 @@
         <v>0.007433</v>
       </c>
       <c r="H546" s="1" t="n">
+        <v>0.007413</v>
+      </c>
+      <c r="I546" s="1" t="n">
         <v>0.007433</v>
       </c>
-      <c r="I546" s="1" t="n">
+      <c r="J546" s="1" t="n">
         <v>0.007402</v>
       </c>
     </row>
@@ -17397,9 +19038,12 @@
         <v>0.01486</v>
       </c>
       <c r="H547" s="1" t="n">
+        <v>0.01474</v>
+      </c>
+      <c r="I547" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="I547" s="1" t="n">
+      <c r="J547" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -17428,9 +19072,12 @@
         <v>0.0157</v>
       </c>
       <c r="H548" s="1" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="I548" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="I548" s="1" t="n">
+      <c r="J548" s="1" t="n">
         <v>0.0157</v>
       </c>
     </row>
@@ -17459,9 +19106,12 @@
         <v>0.13415</v>
       </c>
       <c r="H549" s="1" t="n">
-        <v>0.13434</v>
+        <v>0.13452</v>
       </c>
       <c r="I549" s="1" t="n">
+        <v>0.13452</v>
+      </c>
+      <c r="J549" s="1" t="n">
         <v>0.13271</v>
       </c>
     </row>
@@ -17490,9 +19140,12 @@
         <v>0.1697</v>
       </c>
       <c r="H550" s="1" t="n">
-        <v>0.1697</v>
+        <v>0.1699</v>
       </c>
       <c r="I550" s="1" t="n">
+        <v>0.1699</v>
+      </c>
+      <c r="J550" s="1" t="n">
         <v>0.1693</v>
       </c>
     </row>
@@ -17521,9 +19174,12 @@
         <v>0.003579</v>
       </c>
       <c r="H551" s="1" t="n">
-        <v>0.003583</v>
+        <v>0.003584</v>
       </c>
       <c r="I551" s="1" t="n">
+        <v>0.003584</v>
+      </c>
+      <c r="J551" s="1" t="n">
         <v>0.003577</v>
       </c>
     </row>
@@ -17552,9 +19208,12 @@
         <v>0.03039</v>
       </c>
       <c r="H552" s="1" t="n">
-        <v>0.03039</v>
+        <v>0.03042</v>
       </c>
       <c r="I552" s="1" t="n">
+        <v>0.03042</v>
+      </c>
+      <c r="J552" s="1" t="n">
         <v>0.0303</v>
       </c>
     </row>
@@ -17583,9 +19242,12 @@
         <v>0.01319</v>
       </c>
       <c r="H553" s="1" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="I553" s="1" t="n">
         <v>0.01325</v>
       </c>
-      <c r="I553" s="1" t="n">
+      <c r="J553" s="1" t="n">
         <v>0.01319</v>
       </c>
     </row>
@@ -17614,9 +19276,12 @@
         <v>0.1043</v>
       </c>
       <c r="H554" s="1" t="n">
+        <v>0.1045</v>
+      </c>
+      <c r="I554" s="1" t="n">
         <v>0.1046</v>
       </c>
-      <c r="I554" s="1" t="n">
+      <c r="J554" s="1" t="n">
         <v>0.1039</v>
       </c>
     </row>
@@ -17645,9 +19310,12 @@
         <v>0.05307</v>
       </c>
       <c r="H555" s="1" t="n">
+        <v>0.05302</v>
+      </c>
+      <c r="I555" s="1" t="n">
         <v>0.05319</v>
       </c>
-      <c r="I555" s="1" t="n">
+      <c r="J555" s="1" t="n">
         <v>0.05291</v>
       </c>
     </row>
@@ -17676,9 +19344,12 @@
         <v>0.01218</v>
       </c>
       <c r="H556" s="1" t="n">
+        <v>0.01223</v>
+      </c>
+      <c r="I556" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="I556" s="1" t="n">
+      <c r="J556" s="1" t="n">
         <v>0.01218</v>
       </c>
     </row>

--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J556"/>
+  <dimension ref="A1:K556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -427,8 +427,9 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,10 +475,15 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>price_01:45</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -511,9 +517,12 @@
         <v>71477.10000000001</v>
       </c>
       <c r="I2" s="1" t="n">
+        <v>71493.8</v>
+      </c>
+      <c r="J2" s="1" t="n">
         <v>71530</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="K2" s="1" t="n">
         <v>71364.39999999999</v>
       </c>
     </row>
@@ -545,9 +554,12 @@
         <v>2094.02</v>
       </c>
       <c r="I3" s="1" t="n">
+        <v>2095.85</v>
+      </c>
+      <c r="J3" s="1" t="n">
         <v>2096.9</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="K3" s="1" t="n">
         <v>2090.41</v>
       </c>
     </row>
@@ -579,9 +591,12 @@
         <v>87.77</v>
       </c>
       <c r="I4" s="1" t="n">
+        <v>87.89</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>87.95</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>87.47</v>
       </c>
     </row>
@@ -613,9 +628,12 @@
         <v>23.12</v>
       </c>
       <c r="I5" s="1" t="n">
+        <v>23.159</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>23.579</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>23.043</v>
       </c>
     </row>
@@ -647,10 +665,13 @@
         <v>0.001835</v>
       </c>
       <c r="I6" s="1" t="n">
+        <v>0.001826</v>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>0.001892</v>
       </c>
-      <c r="J6" s="1" t="n">
-        <v>0.001827</v>
+      <c r="K6" s="1" t="n">
+        <v>0.001826</v>
       </c>
     </row>
     <row r="7">
@@ -681,9 +702,12 @@
         <v>1.4134</v>
       </c>
       <c r="I7" s="1" t="n">
+        <v>1.4136</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <v>1.4151</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="K7" s="1" t="n">
         <v>1.4117</v>
       </c>
     </row>
@@ -715,9 +739,12 @@
         <v>0.010407</v>
       </c>
       <c r="I8" s="1" t="n">
+        <v>0.010411</v>
+      </c>
+      <c r="J8" s="1" t="n">
         <v>0.011244</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="K8" s="1" t="n">
         <v>0.010407</v>
       </c>
     </row>
@@ -749,9 +776,12 @@
         <v>4.022</v>
       </c>
       <c r="I9" s="1" t="n">
+        <v>4.021</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <v>4.062</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="K9" s="1" t="n">
         <v>3.954</v>
       </c>
     </row>
@@ -783,9 +813,12 @@
         <v>273.93</v>
       </c>
       <c r="I10" s="1" t="n">
+        <v>276.67</v>
+      </c>
+      <c r="J10" s="1" t="n">
         <v>278.1</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="K10" s="1" t="n">
         <v>272.11</v>
       </c>
     </row>
@@ -817,10 +850,13 @@
         <v>0.07843</v>
       </c>
       <c r="I11" s="1" t="n">
+        <v>0.07815</v>
+      </c>
+      <c r="J11" s="1" t="n">
         <v>0.08047</v>
       </c>
-      <c r="J11" s="1" t="n">
-        <v>0.07833</v>
+      <c r="K11" s="1" t="n">
+        <v>0.07815</v>
       </c>
     </row>
     <row r="12">
@@ -851,9 +887,12 @@
         <v>224.87</v>
       </c>
       <c r="I12" s="1" t="n">
+        <v>224.61</v>
+      </c>
+      <c r="J12" s="1" t="n">
         <v>227.69</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="K12" s="1" t="n">
         <v>223.76</v>
       </c>
     </row>
@@ -885,9 +924,12 @@
         <v>0.09490999999999999</v>
       </c>
       <c r="I13" s="1" t="n">
+        <v>0.09488000000000001</v>
+      </c>
+      <c r="J13" s="1" t="n">
         <v>0.09497</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="K13" s="1" t="n">
         <v>0.0946</v>
       </c>
     </row>
@@ -919,9 +961,12 @@
         <v>37.19</v>
       </c>
       <c r="I14" s="1" t="n">
+        <v>37.247</v>
+      </c>
+      <c r="J14" s="1" t="n">
         <v>37.279</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="K14" s="1" t="n">
         <v>37.089</v>
       </c>
     </row>
@@ -953,10 +998,13 @@
         <v>0.09456000000000001</v>
       </c>
       <c r="I15" s="1" t="n">
+        <v>0.09272</v>
+      </c>
+      <c r="J15" s="1" t="n">
         <v>0.09845</v>
       </c>
-      <c r="J15" s="1" t="n">
-        <v>0.09456000000000001</v>
+      <c r="K15" s="1" t="n">
+        <v>0.09272</v>
       </c>
     </row>
     <row r="16">
@@ -987,9 +1035,12 @@
         <v>0.2262</v>
       </c>
       <c r="I16" s="1" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="J16" s="1" t="n">
         <v>0.2339</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="K16" s="1" t="n">
         <v>0.2256</v>
       </c>
     </row>
@@ -1021,9 +1072,12 @@
         <v>0.011484</v>
       </c>
       <c r="I17" s="1" t="n">
+        <v>0.011413</v>
+      </c>
+      <c r="J17" s="1" t="n">
         <v>0.011542</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="K17" s="1" t="n">
         <v>0.011379</v>
       </c>
     </row>
@@ -1055,9 +1109,12 @@
         <v>659.8099999999999</v>
       </c>
       <c r="I18" s="1" t="n">
+        <v>660.22</v>
+      </c>
+      <c r="J18" s="1" t="n">
         <v>660.72</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="K18" s="1" t="n">
         <v>658.89</v>
       </c>
     </row>
@@ -1089,9 +1146,12 @@
         <v>0.003344</v>
       </c>
       <c r="I19" s="1" t="n">
+        <v>0.0033418</v>
+      </c>
+      <c r="J19" s="1" t="n">
         <v>0.0033454</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="K19" s="1" t="n">
         <v>0.0033271</v>
       </c>
     </row>
@@ -1123,9 +1183,12 @@
         <v>0.18023</v>
       </c>
       <c r="I20" s="1" t="n">
+        <v>0.17936</v>
+      </c>
+      <c r="J20" s="1" t="n">
         <v>0.18066</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="K20" s="1" t="n">
         <v>0.17675</v>
       </c>
     </row>
@@ -1157,9 +1220,12 @@
         <v>0.009926000000000001</v>
       </c>
       <c r="I21" s="1" t="n">
+        <v>0.009887999999999999</v>
+      </c>
+      <c r="J21" s="1" t="n">
         <v>0.010044</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="K21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -1191,9 +1257,12 @@
         <v>1</v>
       </c>
       <c r="I22" s="1" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="J22" s="1" t="n">
         <v>1.0033</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="K22" s="1" t="n">
         <v>0.9985000000000001</v>
       </c>
     </row>
@@ -1225,9 +1294,12 @@
         <v>5006.21</v>
       </c>
       <c r="I23" s="1" t="n">
+        <v>5005.29</v>
+      </c>
+      <c r="J23" s="1" t="n">
         <v>5012.25</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="K23" s="1" t="n">
         <v>5002.67</v>
       </c>
     </row>
@@ -1259,9 +1331,12 @@
         <v>0.2629</v>
       </c>
       <c r="I24" s="1" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="J24" s="1" t="n">
         <v>0.2643</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="K24" s="1" t="n">
         <v>0.2625</v>
       </c>
     </row>
@@ -1293,10 +1368,13 @@
         <v>2.914</v>
       </c>
       <c r="I25" s="1" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="J25" s="1" t="n">
         <v>2.924</v>
       </c>
-      <c r="J25" s="1" t="n">
-        <v>2.899</v>
+      <c r="K25" s="1" t="n">
+        <v>2.885</v>
       </c>
     </row>
     <row r="26">
@@ -1327,9 +1405,12 @@
         <v>0.4073</v>
       </c>
       <c r="I26" s="1" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="J26" s="1" t="n">
         <v>0.4096</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="K26" s="1" t="n">
         <v>0.3959</v>
       </c>
     </row>
@@ -1361,9 +1442,12 @@
         <v>0.886</v>
       </c>
       <c r="I27" s="1" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="J27" s="1" t="n">
         <v>0.886</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="K27" s="1" t="n">
         <v>0.881</v>
       </c>
     </row>
@@ -1395,9 +1479,12 @@
         <v>1.346</v>
       </c>
       <c r="I28" s="1" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="J28" s="1" t="n">
         <v>1.346</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="K28" s="1" t="n">
         <v>1.335</v>
       </c>
     </row>
@@ -1429,9 +1516,12 @@
         <v>9.145</v>
       </c>
       <c r="I29" s="1" t="n">
+        <v>9.151</v>
+      </c>
+      <c r="J29" s="1" t="n">
         <v>9.179</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="K29" s="1" t="n">
         <v>9.131</v>
       </c>
     </row>
@@ -1463,9 +1553,12 @@
         <v>461.4</v>
       </c>
       <c r="I30" s="1" t="n">
+        <v>461.93</v>
+      </c>
+      <c r="J30" s="1" t="n">
         <v>463.35</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="K30" s="1" t="n">
         <v>461.24</v>
       </c>
     </row>
@@ -1497,9 +1590,12 @@
         <v>9.722</v>
       </c>
       <c r="I31" s="1" t="n">
+        <v>9.704000000000001</v>
+      </c>
+      <c r="J31" s="1" t="n">
         <v>9.731</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="K31" s="1" t="n">
         <v>9.696999999999999</v>
       </c>
     </row>
@@ -1531,9 +1627,12 @@
         <v>0.36223</v>
       </c>
       <c r="I32" s="1" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="J32" s="1" t="n">
         <v>0.36683</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="K32" s="1" t="n">
         <v>0.36159</v>
       </c>
     </row>
@@ -1565,9 +1664,12 @@
         <v>1.42</v>
       </c>
       <c r="I33" s="1" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="J33" s="1" t="n">
         <v>1.421</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="K33" s="1" t="n">
         <v>1.409</v>
       </c>
     </row>
@@ -1599,9 +1701,12 @@
         <v>0.593</v>
       </c>
       <c r="I34" s="1" t="n">
+        <v>0.59414</v>
+      </c>
+      <c r="J34" s="1" t="n">
         <v>0.59693</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="K34" s="1" t="n">
         <v>0.5926900000000001</v>
       </c>
     </row>
@@ -1633,9 +1738,12 @@
         <v>1.2232</v>
       </c>
       <c r="I35" s="1" t="n">
+        <v>1.2234</v>
+      </c>
+      <c r="J35" s="1" t="n">
         <v>1.2283</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="K35" s="1" t="n">
         <v>1.2186</v>
       </c>
     </row>
@@ -1667,9 +1775,12 @@
         <v>80.3</v>
       </c>
       <c r="I36" s="1" t="n">
+        <v>80.28</v>
+      </c>
+      <c r="J36" s="1" t="n">
         <v>80.5</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="K36" s="1" t="n">
         <v>80.27</v>
       </c>
     </row>
@@ -1701,10 +1812,13 @@
         <v>0.1971</v>
       </c>
       <c r="I37" s="1" t="n">
+        <v>0.1967</v>
+      </c>
+      <c r="J37" s="1" t="n">
         <v>0.204</v>
       </c>
-      <c r="J37" s="1" t="n">
-        <v>0.1971</v>
+      <c r="K37" s="1" t="n">
+        <v>0.1967</v>
       </c>
     </row>
     <row r="38">
@@ -1735,9 +1849,12 @@
         <v>1.85</v>
       </c>
       <c r="I38" s="1" t="n">
+        <v>1.849</v>
+      </c>
+      <c r="J38" s="1" t="n">
         <v>1.865</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="K38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -1769,9 +1886,12 @@
         <v>0.3305</v>
       </c>
       <c r="I39" s="1" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="J39" s="1" t="n">
         <v>0.3338</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="K39" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -1803,10 +1923,13 @@
         <v>0.8996</v>
       </c>
       <c r="I40" s="1" t="n">
+        <v>0.8931</v>
+      </c>
+      <c r="J40" s="1" t="n">
         <v>0.9115</v>
       </c>
-      <c r="J40" s="1" t="n">
-        <v>0.899</v>
+      <c r="K40" s="1" t="n">
+        <v>0.8931</v>
       </c>
     </row>
     <row r="41">
@@ -1837,9 +1960,12 @@
         <v>0.7115</v>
       </c>
       <c r="I41" s="1" t="n">
+        <v>0.7119</v>
+      </c>
+      <c r="J41" s="1" t="n">
         <v>0.7149</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="K41" s="1" t="n">
         <v>0.7115</v>
       </c>
     </row>
@@ -1871,10 +1997,13 @@
         <v>0.06630999999999999</v>
       </c>
       <c r="I42" s="1" t="n">
+        <v>0.06616</v>
+      </c>
+      <c r="J42" s="1" t="n">
         <v>0.06769</v>
       </c>
-      <c r="J42" s="1" t="n">
-        <v>0.06619999999999999</v>
+      <c r="K42" s="1" t="n">
+        <v>0.06616</v>
       </c>
     </row>
     <row r="43">
@@ -1905,9 +2034,12 @@
         <v>113.49</v>
       </c>
       <c r="I43" s="1" t="n">
+        <v>113.62</v>
+      </c>
+      <c r="J43" s="1" t="n">
         <v>113.86</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="K43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -1939,10 +2071,13 @@
         <v>0.6574</v>
       </c>
       <c r="I44" s="1" t="n">
+        <v>0.6536999999999999</v>
+      </c>
+      <c r="J44" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="J44" s="1" t="n">
-        <v>0.6562</v>
+      <c r="K44" s="1" t="n">
+        <v>0.6536999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1973,9 +2108,12 @@
         <v>1.224</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>1.224</v>
+        <v>1.225</v>
       </c>
       <c r="J45" s="1" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="K45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -2007,9 +2145,12 @@
         <v>0.02378</v>
       </c>
       <c r="I46" s="1" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="J46" s="1" t="n">
         <v>0.02392</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="K46" s="1" t="n">
         <v>0.02376</v>
       </c>
     </row>
@@ -2041,9 +2182,12 @@
         <v>55.05</v>
       </c>
       <c r="I47" s="1" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="J47" s="1" t="n">
         <v>55.17</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="K47" s="1" t="n">
         <v>54.99</v>
       </c>
     </row>
@@ -2075,9 +2219,12 @@
         <v>0.06056</v>
       </c>
       <c r="I48" s="1" t="n">
+        <v>0.06046</v>
+      </c>
+      <c r="J48" s="1" t="n">
         <v>0.06081</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="K48" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -2109,9 +2256,12 @@
         <v>0.1081</v>
       </c>
       <c r="I49" s="1" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="J49" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="K49" s="1" t="n">
         <v>0.1076</v>
       </c>
     </row>
@@ -2143,10 +2293,13 @@
         <v>0.01804</v>
       </c>
       <c r="I50" s="1" t="n">
+        <v>0.01795</v>
+      </c>
+      <c r="J50" s="1" t="n">
         <v>0.01815</v>
       </c>
-      <c r="J50" s="1" t="n">
-        <v>0.018</v>
+      <c r="K50" s="1" t="n">
+        <v>0.01795</v>
       </c>
     </row>
     <row r="51">
@@ -2177,9 +2330,12 @@
         <v>1.466</v>
       </c>
       <c r="I51" s="1" t="n">
+        <v>1.4672</v>
+      </c>
+      <c r="J51" s="1" t="n">
         <v>1.4679</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="K51" s="1" t="n">
         <v>1.4618</v>
       </c>
     </row>
@@ -2211,9 +2367,12 @@
         <v>0.3593</v>
       </c>
       <c r="I52" s="1" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="J52" s="1" t="n">
         <v>0.3603</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="K52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -2245,10 +2404,13 @@
         <v>0.001946</v>
       </c>
       <c r="I53" s="1" t="n">
+        <v>0.001939</v>
+      </c>
+      <c r="J53" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="J53" s="1" t="n">
-        <v>0.001942</v>
+      <c r="K53" s="1" t="n">
+        <v>0.001939</v>
       </c>
     </row>
     <row r="54">
@@ -2279,9 +2441,12 @@
         <v>0.09526</v>
       </c>
       <c r="I54" s="1" t="n">
+        <v>0.09518</v>
+      </c>
+      <c r="J54" s="1" t="n">
         <v>0.09569</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="K54" s="1" t="n">
         <v>0.09514</v>
       </c>
     </row>
@@ -2313,9 +2478,12 @@
         <v>0.04099</v>
       </c>
       <c r="I55" s="1" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="J55" s="1" t="n">
         <v>0.04099</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="K55" s="1" t="n">
         <v>0.04003</v>
       </c>
     </row>
@@ -2347,9 +2515,12 @@
         <v>0.29833</v>
       </c>
       <c r="I56" s="1" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="J56" s="1" t="n">
         <v>0.29861</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="K56" s="1" t="n">
         <v>0.29831</v>
       </c>
     </row>
@@ -2381,9 +2552,12 @@
         <v>0.005692</v>
       </c>
       <c r="I57" s="1" t="n">
+        <v>0.005664</v>
+      </c>
+      <c r="J57" s="1" t="n">
         <v>0.005824</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="K57" s="1" t="n">
         <v>0.005633</v>
       </c>
     </row>
@@ -2415,9 +2589,12 @@
         <v>4993.88</v>
       </c>
       <c r="I58" s="1" t="n">
+        <v>4992.04</v>
+      </c>
+      <c r="J58" s="1" t="n">
         <v>4998.37</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="K58" s="1" t="n">
         <v>4988.64</v>
       </c>
     </row>
@@ -2449,10 +2626,13 @@
         <v>0.4131</v>
       </c>
       <c r="I59" s="1" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="J59" s="1" t="n">
         <v>0.4246</v>
       </c>
-      <c r="J59" s="1" t="n">
-        <v>0.4126</v>
+      <c r="K59" s="1" t="n">
+        <v>0.4105</v>
       </c>
     </row>
     <row r="60">
@@ -2483,9 +2663,12 @@
         <v>0.04686</v>
       </c>
       <c r="I60" s="1" t="n">
+        <v>0.04644</v>
+      </c>
+      <c r="J60" s="1" t="n">
         <v>0.04686</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="K60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -2517,10 +2700,13 @@
         <v>0.21379</v>
       </c>
       <c r="I61" s="1" t="n">
+        <v>0.21338</v>
+      </c>
+      <c r="J61" s="1" t="n">
         <v>0.21708</v>
       </c>
-      <c r="J61" s="1" t="n">
-        <v>0.21344</v>
+      <c r="K61" s="1" t="n">
+        <v>0.21338</v>
       </c>
     </row>
     <row r="62">
@@ -2551,9 +2737,12 @@
         <v>0.1072</v>
       </c>
       <c r="I62" s="1" t="n">
+        <v>0.1069</v>
+      </c>
+      <c r="J62" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="K62" s="1" t="n">
         <v>0.1065</v>
       </c>
     </row>
@@ -2585,9 +2774,12 @@
         <v>0.7291</v>
       </c>
       <c r="I63" s="1" t="n">
+        <v>0.7272</v>
+      </c>
+      <c r="J63" s="1" t="n">
         <v>0.7301</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="K63" s="1" t="n">
         <v>0.7255</v>
       </c>
     </row>
@@ -2619,9 +2811,12 @@
         <v>0.1666</v>
       </c>
       <c r="I64" s="1" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="J64" s="1" t="n">
         <v>0.1668</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="K64" s="1" t="n">
         <v>0.1658</v>
       </c>
     </row>
@@ -2653,9 +2848,12 @@
         <v>2.668</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>2.668</v>
+        <v>2.669</v>
       </c>
       <c r="J65" s="1" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="K65" s="1" t="n">
         <v>2.65</v>
       </c>
     </row>
@@ -2687,9 +2885,12 @@
         <v>0.04057</v>
       </c>
       <c r="I66" s="1" t="n">
+        <v>0.04051</v>
+      </c>
+      <c r="J66" s="1" t="n">
         <v>0.04072</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="K66" s="1" t="n">
         <v>0.04018</v>
       </c>
     </row>
@@ -2721,9 +2922,12 @@
         <v>0.04268</v>
       </c>
       <c r="I67" s="1" t="n">
+        <v>0.04265</v>
+      </c>
+      <c r="J67" s="1" t="n">
         <v>0.04268</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="K67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -2755,9 +2959,12 @@
         <v>3.967</v>
       </c>
       <c r="I68" s="1" t="n">
+        <v>3.966</v>
+      </c>
+      <c r="J68" s="1" t="n">
         <v>3.971</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="K68" s="1" t="n">
         <v>3.951</v>
       </c>
     </row>
@@ -2789,9 +2996,12 @@
         <v>0.1265</v>
       </c>
       <c r="I69" s="1" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="J69" s="1" t="n">
         <v>0.1265</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="K69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -2823,9 +3033,12 @@
         <v>6.326</v>
       </c>
       <c r="I70" s="1" t="n">
+        <v>6.263</v>
+      </c>
+      <c r="J70" s="1" t="n">
         <v>6.328</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="K70" s="1" t="n">
         <v>6.114</v>
       </c>
     </row>
@@ -2857,9 +3070,12 @@
         <v>0.04995</v>
       </c>
       <c r="I71" s="1" t="n">
-        <v>0.04999</v>
+        <v>0.0501</v>
       </c>
       <c r="J71" s="1" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="K71" s="1" t="n">
         <v>0.04959</v>
       </c>
     </row>
@@ -2891,9 +3107,12 @@
         <v>0.004153</v>
       </c>
       <c r="I72" s="1" t="n">
+        <v>0.004133</v>
+      </c>
+      <c r="J72" s="1" t="n">
         <v>0.004181</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="K72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -2925,9 +3144,12 @@
         <v>6.009</v>
       </c>
       <c r="I73" s="1" t="n">
+        <v>6.009</v>
+      </c>
+      <c r="J73" s="1" t="n">
         <v>6.029</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="K73" s="1" t="n">
         <v>5.96</v>
       </c>
     </row>
@@ -2959,9 +3181,12 @@
         <v>0.1629</v>
       </c>
       <c r="I74" s="1" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="J74" s="1" t="n">
         <v>0.1633</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="K74" s="1" t="n">
         <v>0.1619</v>
       </c>
     </row>
@@ -2993,9 +3218,12 @@
         <v>0.007292</v>
       </c>
       <c r="I75" s="1" t="n">
+        <v>0.007285</v>
+      </c>
+      <c r="J75" s="1" t="n">
         <v>0.007297</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="K75" s="1" t="n">
         <v>0.007261</v>
       </c>
     </row>
@@ -3027,9 +3255,12 @@
         <v>0.2199</v>
       </c>
       <c r="I76" s="1" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="J76" s="1" t="n">
         <v>0.2199</v>
       </c>
-      <c r="J76" s="1" t="n">
+      <c r="K76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -3061,9 +3292,12 @@
         <v>0.005813</v>
       </c>
       <c r="I77" s="1" t="n">
+        <v>0.00582</v>
+      </c>
+      <c r="J77" s="1" t="n">
         <v>0.005826</v>
       </c>
-      <c r="J77" s="1" t="n">
+      <c r="K77" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -3095,9 +3329,12 @@
         <v>0.1018</v>
       </c>
       <c r="I78" s="1" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="J78" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="J78" s="1" t="n">
+      <c r="K78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -3129,9 +3366,12 @@
         <v>0.00626</v>
       </c>
       <c r="I79" s="1" t="n">
+        <v>0.00628</v>
+      </c>
+      <c r="J79" s="1" t="n">
         <v>0.006292</v>
       </c>
-      <c r="J79" s="1" t="n">
+      <c r="K79" s="1" t="n">
         <v>0.006237</v>
       </c>
     </row>
@@ -3163,9 +3403,12 @@
         <v>33.46</v>
       </c>
       <c r="I80" s="1" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="J80" s="1" t="n">
         <v>33.51</v>
       </c>
-      <c r="J80" s="1" t="n">
+      <c r="K80" s="1" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -3197,9 +3440,12 @@
         <v>0.04051</v>
       </c>
       <c r="I81" s="1" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="J81" s="1" t="n">
         <v>0.04051</v>
       </c>
-      <c r="J81" s="1" t="n">
+      <c r="K81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -3231,9 +3477,12 @@
         <v>0.16702</v>
       </c>
       <c r="I82" s="1" t="n">
+        <v>0.16682</v>
+      </c>
+      <c r="J82" s="1" t="n">
         <v>0.1675</v>
       </c>
-      <c r="J82" s="1" t="n">
+      <c r="K82" s="1" t="n">
         <v>0.16679</v>
       </c>
     </row>
@@ -3265,9 +3514,12 @@
         <v>0.1037</v>
       </c>
       <c r="I83" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="J83" s="1" t="n">
         <v>0.1037</v>
       </c>
-      <c r="J83" s="1" t="n">
+      <c r="K83" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -3299,9 +3551,12 @@
         <v>0.08756</v>
       </c>
       <c r="I84" s="1" t="n">
+        <v>0.08757</v>
+      </c>
+      <c r="J84" s="1" t="n">
         <v>0.08848</v>
       </c>
-      <c r="J84" s="1" t="n">
+      <c r="K84" s="1" t="n">
         <v>0.08756</v>
       </c>
     </row>
@@ -3333,10 +3588,13 @@
         <v>0.02311</v>
       </c>
       <c r="I85" s="1" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="J85" s="1" t="n">
         <v>0.02331</v>
       </c>
-      <c r="J85" s="1" t="n">
-        <v>0.02311</v>
+      <c r="K85" s="1" t="n">
+        <v>0.0231</v>
       </c>
     </row>
     <row r="86">
@@ -3370,6 +3628,9 @@
         <v>0.24</v>
       </c>
       <c r="J86" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -3401,9 +3662,12 @@
         <v>358.06</v>
       </c>
       <c r="I87" s="1" t="n">
-        <v>358.06</v>
+        <v>358.65</v>
       </c>
       <c r="J87" s="1" t="n">
+        <v>358.65</v>
+      </c>
+      <c r="K87" s="1" t="n">
         <v>355.75</v>
       </c>
     </row>
@@ -3435,9 +3699,12 @@
         <v>0.00348</v>
       </c>
       <c r="I88" s="1" t="n">
+        <v>0.00347</v>
+      </c>
+      <c r="J88" s="1" t="n">
         <v>0.00348</v>
       </c>
-      <c r="J88" s="1" t="n">
+      <c r="K88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -3469,9 +3736,12 @@
         <v>8.285</v>
       </c>
       <c r="I89" s="1" t="n">
+        <v>8.276999999999999</v>
+      </c>
+      <c r="J89" s="1" t="n">
         <v>8.301</v>
       </c>
-      <c r="J89" s="1" t="n">
+      <c r="K89" s="1" t="n">
         <v>8.257</v>
       </c>
     </row>
@@ -3503,9 +3773,12 @@
         <v>0.005917</v>
       </c>
       <c r="I90" s="1" t="n">
+        <v>0.005911</v>
+      </c>
+      <c r="J90" s="1" t="n">
         <v>0.005945</v>
       </c>
-      <c r="J90" s="1" t="n">
+      <c r="K90" s="1" t="n">
         <v>0.005905</v>
       </c>
     </row>
@@ -3537,9 +3810,12 @@
         <v>0.06838</v>
       </c>
       <c r="I91" s="1" t="n">
+        <v>0.06834</v>
+      </c>
+      <c r="J91" s="1" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="J91" s="1" t="n">
+      <c r="K91" s="1" t="n">
         <v>0.06822</v>
       </c>
     </row>
@@ -3571,9 +3847,12 @@
         <v>0.02867</v>
       </c>
       <c r="I92" s="1" t="n">
-        <v>0.02897</v>
+        <v>0.02905</v>
       </c>
       <c r="J92" s="1" t="n">
+        <v>0.02905</v>
+      </c>
+      <c r="K92" s="1" t="n">
         <v>0.02867</v>
       </c>
     </row>
@@ -3605,9 +3884,12 @@
         <v>5.165</v>
       </c>
       <c r="I93" s="1" t="n">
+        <v>5.188</v>
+      </c>
+      <c r="J93" s="1" t="n">
         <v>5.202</v>
       </c>
-      <c r="J93" s="1" t="n">
+      <c r="K93" s="1" t="n">
         <v>5.159</v>
       </c>
     </row>
@@ -3639,9 +3921,12 @@
         <v>0.000226</v>
       </c>
       <c r="I94" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="J94" s="1" t="n">
         <v>0.000228</v>
       </c>
-      <c r="J94" s="1" t="n">
+      <c r="K94" s="1" t="n">
         <v>0.000226</v>
       </c>
     </row>
@@ -3673,9 +3958,12 @@
         <v>0.9238</v>
       </c>
       <c r="I95" s="1" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+      <c r="J95" s="1" t="n">
         <v>0.9248</v>
       </c>
-      <c r="J95" s="1" t="n">
+      <c r="K95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -3707,9 +3995,12 @@
         <v>2.0959</v>
       </c>
       <c r="I96" s="1" t="n">
-        <v>2.0959</v>
+        <v>2.1066</v>
       </c>
       <c r="J96" s="1" t="n">
+        <v>2.1066</v>
+      </c>
+      <c r="K96" s="1" t="n">
         <v>2.0598</v>
       </c>
     </row>
@@ -3741,9 +4032,12 @@
         <v>0.3681</v>
       </c>
       <c r="I97" s="1" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="J97" s="1" t="n">
         <v>0.3722</v>
       </c>
-      <c r="J97" s="1" t="n">
+      <c r="K97" s="1" t="n">
         <v>0.3681</v>
       </c>
     </row>
@@ -3775,9 +4069,12 @@
         <v>1.625</v>
       </c>
       <c r="I98" s="1" t="n">
+        <v>1.619</v>
+      </c>
+      <c r="J98" s="1" t="n">
         <v>1.625</v>
       </c>
-      <c r="J98" s="1" t="n">
+      <c r="K98" s="1" t="n">
         <v>1.613</v>
       </c>
     </row>
@@ -3809,10 +4106,13 @@
         <v>0.2336</v>
       </c>
       <c r="I99" s="1" t="n">
+        <v>0.2332</v>
+      </c>
+      <c r="J99" s="1" t="n">
         <v>0.2368</v>
       </c>
-      <c r="J99" s="1" t="n">
-        <v>0.2336</v>
+      <c r="K99" s="1" t="n">
+        <v>0.2332</v>
       </c>
     </row>
     <row r="100">
@@ -3843,9 +4143,12 @@
         <v>0.13608</v>
       </c>
       <c r="I100" s="1" t="n">
-        <v>0.13683</v>
+        <v>0.13694</v>
       </c>
       <c r="J100" s="1" t="n">
+        <v>0.13694</v>
+      </c>
+      <c r="K100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -3877,9 +4180,12 @@
         <v>0.07083</v>
       </c>
       <c r="I101" s="1" t="n">
+        <v>0.07025000000000001</v>
+      </c>
+      <c r="J101" s="1" t="n">
         <v>0.07115</v>
       </c>
-      <c r="J101" s="1" t="n">
+      <c r="K101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -3911,10 +4217,13 @@
         <v>0.0010832</v>
       </c>
       <c r="I102" s="1" t="n">
+        <v>0.0010822</v>
+      </c>
+      <c r="J102" s="1" t="n">
         <v>0.0010875</v>
       </c>
-      <c r="J102" s="1" t="n">
-        <v>0.0010832</v>
+      <c r="K102" s="1" t="n">
+        <v>0.0010822</v>
       </c>
     </row>
     <row r="103">
@@ -3945,9 +4254,12 @@
         <v>0.003412</v>
       </c>
       <c r="I103" s="1" t="n">
+        <v>0.003413</v>
+      </c>
+      <c r="J103" s="1" t="n">
         <v>0.003424</v>
       </c>
-      <c r="J103" s="1" t="n">
+      <c r="K103" s="1" t="n">
         <v>0.003403</v>
       </c>
     </row>
@@ -3979,9 +4291,12 @@
         <v>0.27474</v>
       </c>
       <c r="I104" s="1" t="n">
+        <v>0.27488</v>
+      </c>
+      <c r="J104" s="1" t="n">
         <v>0.27751</v>
       </c>
-      <c r="J104" s="1" t="n">
+      <c r="K104" s="1" t="n">
         <v>0.27472</v>
       </c>
     </row>
@@ -4013,9 +4328,12 @@
         <v>0.01249</v>
       </c>
       <c r="I105" s="1" t="n">
+        <v>0.01254</v>
+      </c>
+      <c r="J105" s="1" t="n">
         <v>0.01257</v>
       </c>
-      <c r="J105" s="1" t="n">
+      <c r="K105" s="1" t="n">
         <v>0.01243</v>
       </c>
     </row>
@@ -4047,9 +4365,12 @@
         <v>0.13528</v>
       </c>
       <c r="I106" s="1" t="n">
-        <v>0.13569</v>
+        <v>0.1358</v>
       </c>
       <c r="J106" s="1" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="K106" s="1" t="n">
         <v>0.13329</v>
       </c>
     </row>
@@ -4081,9 +4402,12 @@
         <v>0.3516</v>
       </c>
       <c r="I107" s="1" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="J107" s="1" t="n">
         <v>0.3516</v>
       </c>
-      <c r="J107" s="1" t="n">
+      <c r="K107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -4115,9 +4439,12 @@
         <v>0.1429</v>
       </c>
       <c r="I108" s="1" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="J108" s="1" t="n">
         <v>0.1436</v>
       </c>
-      <c r="J108" s="1" t="n">
+      <c r="K108" s="1" t="n">
         <v>0.1426</v>
       </c>
     </row>
@@ -4149,9 +4476,12 @@
         <v>0.9340000000000001</v>
       </c>
       <c r="I109" s="1" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="J109" s="1" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="K109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -4183,9 +4513,12 @@
         <v>0.016234</v>
       </c>
       <c r="I110" s="1" t="n">
+        <v>0.016256</v>
+      </c>
+      <c r="J110" s="1" t="n">
         <v>0.016308</v>
       </c>
-      <c r="J110" s="1" t="n">
+      <c r="K110" s="1" t="n">
         <v>0.016195</v>
       </c>
     </row>
@@ -4217,9 +4550,12 @@
         <v>0.038092</v>
       </c>
       <c r="I111" s="1" t="n">
+        <v>0.03812</v>
+      </c>
+      <c r="J111" s="1" t="n">
         <v>0.038335</v>
       </c>
-      <c r="J111" s="1" t="n">
+      <c r="K111" s="1" t="n">
         <v>0.03774</v>
       </c>
     </row>
@@ -4251,9 +4587,12 @@
         <v>0.11958</v>
       </c>
       <c r="I112" s="1" t="n">
+        <v>0.11974</v>
+      </c>
+      <c r="J112" s="1" t="n">
         <v>0.12031</v>
       </c>
-      <c r="J112" s="1" t="n">
+      <c r="K112" s="1" t="n">
         <v>0.11926</v>
       </c>
     </row>
@@ -4285,10 +4624,13 @@
         <v>0.09418</v>
       </c>
       <c r="I113" s="1" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="J113" s="1" t="n">
         <v>0.09574000000000001</v>
       </c>
-      <c r="J113" s="1" t="n">
-        <v>0.09418</v>
+      <c r="K113" s="1" t="n">
+        <v>0.0941</v>
       </c>
     </row>
     <row r="114">
@@ -4319,9 +4661,12 @@
         <v>0.13006</v>
       </c>
       <c r="I114" s="1" t="n">
+        <v>0.13002</v>
+      </c>
+      <c r="J114" s="1" t="n">
         <v>0.13063</v>
       </c>
-      <c r="J114" s="1" t="n">
+      <c r="K114" s="1" t="n">
         <v>0.12895</v>
       </c>
     </row>
@@ -4353,9 +4698,12 @@
         <v>0.2647</v>
       </c>
       <c r="I115" s="1" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="J115" s="1" t="n">
         <v>0.2656</v>
       </c>
-      <c r="J115" s="1" t="n">
+      <c r="K115" s="1" t="n">
         <v>0.2638</v>
       </c>
     </row>
@@ -4387,10 +4735,13 @@
         <v>0.04961</v>
       </c>
       <c r="I116" s="1" t="n">
+        <v>0.04805</v>
+      </c>
+      <c r="J116" s="1" t="n">
         <v>0.0529</v>
       </c>
-      <c r="J116" s="1" t="n">
-        <v>0.04891</v>
+      <c r="K116" s="1" t="n">
+        <v>0.04805</v>
       </c>
     </row>
     <row r="117">
@@ -4421,9 +4772,12 @@
         <v>0.0914</v>
       </c>
       <c r="I117" s="1" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="J117" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="J117" s="1" t="n">
+      <c r="K117" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -4455,9 +4809,12 @@
         <v>0.0554</v>
       </c>
       <c r="I118" s="1" t="n">
+        <v>0.05559</v>
+      </c>
+      <c r="J118" s="1" t="n">
         <v>0.05563</v>
       </c>
-      <c r="J118" s="1" t="n">
+      <c r="K118" s="1" t="n">
         <v>0.05501</v>
       </c>
     </row>
@@ -4489,9 +4846,12 @@
         <v>0.01507</v>
       </c>
       <c r="I119" s="1" t="n">
+        <v>0.01507</v>
+      </c>
+      <c r="J119" s="1" t="n">
         <v>0.01515</v>
       </c>
-      <c r="J119" s="1" t="n">
+      <c r="K119" s="1" t="n">
         <v>0.01505</v>
       </c>
     </row>
@@ -4523,9 +4883,12 @@
         <v>3.065</v>
       </c>
       <c r="I120" s="1" t="n">
+        <v>3.064</v>
+      </c>
+      <c r="J120" s="1" t="n">
         <v>3.065</v>
       </c>
-      <c r="J120" s="1" t="n">
+      <c r="K120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -4557,10 +4920,13 @@
         <v>1.849</v>
       </c>
       <c r="I121" s="1" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="J121" s="1" t="n">
         <v>1.855</v>
       </c>
-      <c r="J121" s="1" t="n">
-        <v>1.849</v>
+      <c r="K121" s="1" t="n">
+        <v>1.848</v>
       </c>
     </row>
     <row r="122">
@@ -4591,9 +4957,12 @@
         <v>1.3006</v>
       </c>
       <c r="I122" s="1" t="n">
-        <v>1.3006</v>
+        <v>1.3012</v>
       </c>
       <c r="J122" s="1" t="n">
+        <v>1.3012</v>
+      </c>
+      <c r="K122" s="1" t="n">
         <v>1.2934</v>
       </c>
     </row>
@@ -4625,10 +4994,13 @@
         <v>0.316</v>
       </c>
       <c r="I123" s="1" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="J123" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="J123" s="1" t="n">
-        <v>0.316</v>
+      <c r="K123" s="1" t="n">
+        <v>0.315</v>
       </c>
     </row>
     <row r="124">
@@ -4659,9 +5031,12 @@
         <v>0.12216</v>
       </c>
       <c r="I124" s="1" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="J124" s="1" t="n">
         <v>0.12506</v>
       </c>
-      <c r="J124" s="1" t="n">
+      <c r="K124" s="1" t="n">
         <v>0.12202</v>
       </c>
     </row>
@@ -4693,9 +5068,12 @@
         <v>0.008323000000000001</v>
       </c>
       <c r="I125" s="1" t="n">
+        <v>0.008352999999999999</v>
+      </c>
+      <c r="J125" s="1" t="n">
         <v>0.008459</v>
       </c>
-      <c r="J125" s="1" t="n">
+      <c r="K125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -4727,9 +5105,12 @@
         <v>0.01602</v>
       </c>
       <c r="I126" s="1" t="n">
-        <v>0.01602</v>
+        <v>0.01606</v>
       </c>
       <c r="J126" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="K126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -4761,10 +5142,13 @@
         <v>0.04425</v>
       </c>
       <c r="I127" s="1" t="n">
+        <v>0.04394</v>
+      </c>
+      <c r="J127" s="1" t="n">
         <v>0.04468</v>
       </c>
-      <c r="J127" s="1" t="n">
-        <v>0.04402</v>
+      <c r="K127" s="1" t="n">
+        <v>0.04394</v>
       </c>
     </row>
     <row r="128">
@@ -4795,9 +5179,12 @@
         <v>0.04727</v>
       </c>
       <c r="I128" s="1" t="n">
+        <v>0.04679</v>
+      </c>
+      <c r="J128" s="1" t="n">
         <v>0.04727</v>
       </c>
-      <c r="J128" s="1" t="n">
+      <c r="K128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -4829,9 +5216,12 @@
         <v>0.09616</v>
       </c>
       <c r="I129" s="1" t="n">
-        <v>0.09635000000000001</v>
+        <v>0.09654</v>
       </c>
       <c r="J129" s="1" t="n">
+        <v>0.09654</v>
+      </c>
+      <c r="K129" s="1" t="n">
         <v>0.09543</v>
       </c>
     </row>
@@ -4863,9 +5253,12 @@
         <v>0.09848</v>
       </c>
       <c r="I130" s="1" t="n">
+        <v>0.09853000000000001</v>
+      </c>
+      <c r="J130" s="1" t="n">
         <v>0.09927</v>
       </c>
-      <c r="J130" s="1" t="n">
+      <c r="K130" s="1" t="n">
         <v>0.09848</v>
       </c>
     </row>
@@ -4897,9 +5290,12 @@
         <v>0.16592</v>
       </c>
       <c r="I131" s="1" t="n">
-        <v>0.16612</v>
+        <v>0.16637</v>
       </c>
       <c r="J131" s="1" t="n">
+        <v>0.16637</v>
+      </c>
+      <c r="K131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -4931,9 +5327,12 @@
         <v>0.01697</v>
       </c>
       <c r="I132" s="1" t="n">
+        <v>0.01694</v>
+      </c>
+      <c r="J132" s="1" t="n">
         <v>0.01702</v>
       </c>
-      <c r="J132" s="1" t="n">
+      <c r="K132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -4965,9 +5364,12 @@
         <v>0.06683</v>
       </c>
       <c r="I133" s="1" t="n">
+        <v>0.06675</v>
+      </c>
+      <c r="J133" s="1" t="n">
         <v>0.06683</v>
       </c>
-      <c r="J133" s="1" t="n">
+      <c r="K133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -4999,9 +5401,12 @@
         <v>0.3029</v>
       </c>
       <c r="I134" s="1" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="J134" s="1" t="n">
         <v>0.3029</v>
       </c>
-      <c r="J134" s="1" t="n">
+      <c r="K134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -5033,9 +5438,12 @@
         <v>0.04526</v>
       </c>
       <c r="I135" s="1" t="n">
-        <v>0.04526</v>
+        <v>0.04563</v>
       </c>
       <c r="J135" s="1" t="n">
+        <v>0.04563</v>
+      </c>
+      <c r="K135" s="1" t="n">
         <v>0.04508</v>
       </c>
     </row>
@@ -5067,9 +5475,12 @@
         <v>0.782</v>
       </c>
       <c r="I136" s="1" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="J136" s="1" t="n">
         <v>0.783</v>
       </c>
-      <c r="J136" s="1" t="n">
+      <c r="K136" s="1" t="n">
         <v>0.781</v>
       </c>
     </row>
@@ -5101,9 +5512,12 @@
         <v>0.1169</v>
       </c>
       <c r="I137" s="1" t="n">
-        <v>0.1169</v>
+        <v>0.1171</v>
       </c>
       <c r="J137" s="1" t="n">
+        <v>0.1171</v>
+      </c>
+      <c r="K137" s="1" t="n">
         <v>0.1162</v>
       </c>
     </row>
@@ -5135,9 +5549,12 @@
         <v>0.14739</v>
       </c>
       <c r="I138" s="1" t="n">
-        <v>0.14739</v>
+        <v>0.14759</v>
       </c>
       <c r="J138" s="1" t="n">
+        <v>0.14759</v>
+      </c>
+      <c r="K138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -5169,9 +5586,12 @@
         <v>0.0573</v>
       </c>
       <c r="I139" s="1" t="n">
-        <v>0.0573</v>
+        <v>0.05735</v>
       </c>
       <c r="J139" s="1" t="n">
+        <v>0.05735</v>
+      </c>
+      <c r="K139" s="1" t="n">
         <v>0.05699</v>
       </c>
     </row>
@@ -5203,10 +5623,13 @@
         <v>0.007278</v>
       </c>
       <c r="I140" s="1" t="n">
+        <v>0.00726</v>
+      </c>
+      <c r="J140" s="1" t="n">
         <v>0.007295</v>
       </c>
-      <c r="J140" s="1" t="n">
-        <v>0.007267</v>
+      <c r="K140" s="1" t="n">
+        <v>0.00726</v>
       </c>
     </row>
     <row r="141">
@@ -5237,9 +5660,12 @@
         <v>0.09591</v>
       </c>
       <c r="I141" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="J141" s="1" t="n">
         <v>0.09601</v>
       </c>
-      <c r="J141" s="1" t="n">
+      <c r="K141" s="1" t="n">
         <v>0.09569</v>
       </c>
     </row>
@@ -5271,9 +5697,12 @@
         <v>0.0835</v>
       </c>
       <c r="I142" s="1" t="n">
+        <v>0.08337</v>
+      </c>
+      <c r="J142" s="1" t="n">
         <v>0.08363</v>
       </c>
-      <c r="J142" s="1" t="n">
+      <c r="K142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -5305,9 +5734,12 @@
         <v>0.008569999999999999</v>
       </c>
       <c r="I143" s="1" t="n">
+        <v>0.00856</v>
+      </c>
+      <c r="J143" s="1" t="n">
         <v>0.0086</v>
       </c>
-      <c r="J143" s="1" t="n">
+      <c r="K143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -5339,10 +5771,13 @@
         <v>0.07235</v>
       </c>
       <c r="I144" s="1" t="n">
+        <v>0.07224999999999999</v>
+      </c>
+      <c r="J144" s="1" t="n">
         <v>0.07288</v>
       </c>
-      <c r="J144" s="1" t="n">
-        <v>0.07235</v>
+      <c r="K144" s="1" t="n">
+        <v>0.07224999999999999</v>
       </c>
     </row>
     <row r="145">
@@ -5373,10 +5808,13 @@
         <v>0.4271</v>
       </c>
       <c r="I145" s="1" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="J145" s="1" t="n">
         <v>0.4305</v>
       </c>
-      <c r="J145" s="1" t="n">
-        <v>0.4271</v>
+      <c r="K145" s="1" t="n">
+        <v>0.427</v>
       </c>
     </row>
     <row r="146">
@@ -5407,9 +5845,12 @@
         <v>0.0322</v>
       </c>
       <c r="I146" s="1" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="J146" s="1" t="n">
         <v>0.03276</v>
       </c>
-      <c r="J146" s="1" t="n">
+      <c r="K146" s="1" t="n">
         <v>0.0322</v>
       </c>
     </row>
@@ -5441,9 +5882,12 @@
         <v>390.45</v>
       </c>
       <c r="I147" s="1" t="n">
+        <v>390.45</v>
+      </c>
+      <c r="J147" s="1" t="n">
         <v>390.55</v>
       </c>
-      <c r="J147" s="1" t="n">
+      <c r="K147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -5475,9 +5919,12 @@
         <v>0.03301</v>
       </c>
       <c r="I148" s="1" t="n">
+        <v>0.03299</v>
+      </c>
+      <c r="J148" s="1" t="n">
         <v>0.0333</v>
       </c>
-      <c r="J148" s="1" t="n">
+      <c r="K148" s="1" t="n">
         <v>0.0329</v>
       </c>
     </row>
@@ -5509,9 +5956,12 @@
         <v>0.05298</v>
       </c>
       <c r="I149" s="1" t="n">
+        <v>0.05294</v>
+      </c>
+      <c r="J149" s="1" t="n">
         <v>0.05322</v>
       </c>
-      <c r="J149" s="1" t="n">
+      <c r="K149" s="1" t="n">
         <v>0.05289</v>
       </c>
     </row>
@@ -5543,9 +5993,12 @@
         <v>0.0004403</v>
       </c>
       <c r="I150" s="1" t="n">
+        <v>0.0004399</v>
+      </c>
+      <c r="J150" s="1" t="n">
         <v>0.000443</v>
       </c>
-      <c r="J150" s="1" t="n">
+      <c r="K150" s="1" t="n">
         <v>0.000439</v>
       </c>
     </row>
@@ -5577,9 +6030,12 @@
         <v>0.02183</v>
       </c>
       <c r="I151" s="1" t="n">
+        <v>0.02182</v>
+      </c>
+      <c r="J151" s="1" t="n">
         <v>0.02189</v>
       </c>
-      <c r="J151" s="1" t="n">
+      <c r="K151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -5611,9 +6067,12 @@
         <v>0.001782</v>
       </c>
       <c r="I152" s="1" t="n">
+        <v>0.00178</v>
+      </c>
+      <c r="J152" s="1" t="n">
         <v>0.001783</v>
       </c>
-      <c r="J152" s="1" t="n">
+      <c r="K152" s="1" t="n">
         <v>0.001768</v>
       </c>
     </row>
@@ -5645,9 +6104,12 @@
         <v>6.1e-06</v>
       </c>
       <c r="I153" s="1" t="n">
+        <v>6.1e-06</v>
+      </c>
+      <c r="J153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
-      <c r="J153" s="1" t="n">
+      <c r="K153" s="1" t="n">
         <v>6e-06</v>
       </c>
     </row>
@@ -5679,9 +6141,12 @@
         <v>0.1601</v>
       </c>
       <c r="I154" s="1" t="n">
-        <v>0.1602</v>
+        <v>0.1603</v>
       </c>
       <c r="J154" s="1" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="K154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -5713,9 +6178,12 @@
         <v>0.0376</v>
       </c>
       <c r="I155" s="1" t="n">
+        <v>0.03766</v>
+      </c>
+      <c r="J155" s="1" t="n">
         <v>0.03768</v>
       </c>
-      <c r="J155" s="1" t="n">
+      <c r="K155" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -5747,9 +6215,12 @@
         <v>0.005404</v>
       </c>
       <c r="I156" s="1" t="n">
+        <v>0.005397</v>
+      </c>
+      <c r="J156" s="1" t="n">
         <v>0.005404</v>
       </c>
-      <c r="J156" s="1" t="n">
+      <c r="K156" s="1" t="n">
         <v>0.005364</v>
       </c>
     </row>
@@ -5781,10 +6252,13 @@
         <v>0.02278</v>
       </c>
       <c r="I157" s="1" t="n">
+        <v>0.02263</v>
+      </c>
+      <c r="J157" s="1" t="n">
         <v>0.02284</v>
       </c>
-      <c r="J157" s="1" t="n">
-        <v>0.02276</v>
+      <c r="K157" s="1" t="n">
+        <v>0.02263</v>
       </c>
     </row>
     <row r="158">
@@ -5815,9 +6289,12 @@
         <v>1.096</v>
       </c>
       <c r="I158" s="1" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="J158" s="1" t="n">
         <v>1.096</v>
       </c>
-      <c r="J158" s="1" t="n">
+      <c r="K158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -5849,9 +6326,12 @@
         <v>2.565</v>
       </c>
       <c r="I159" s="1" t="n">
+        <v>2.564</v>
+      </c>
+      <c r="J159" s="1" t="n">
         <v>2.565</v>
       </c>
-      <c r="J159" s="1" t="n">
+      <c r="K159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -5883,9 +6363,12 @@
         <v>4.842</v>
       </c>
       <c r="I160" s="1" t="n">
+        <v>4.843</v>
+      </c>
+      <c r="J160" s="1" t="n">
         <v>4.858</v>
       </c>
-      <c r="J160" s="1" t="n">
+      <c r="K160" s="1" t="n">
         <v>4.836</v>
       </c>
     </row>
@@ -5917,9 +6400,12 @@
         <v>0.1604</v>
       </c>
       <c r="I161" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="J161" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="J161" s="1" t="n">
+      <c r="K161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -5951,9 +6437,12 @@
         <v>0.20614</v>
       </c>
       <c r="I162" s="1" t="n">
+        <v>0.20616</v>
+      </c>
+      <c r="J162" s="1" t="n">
         <v>0.20754</v>
       </c>
-      <c r="J162" s="1" t="n">
+      <c r="K162" s="1" t="n">
         <v>0.20584</v>
       </c>
     </row>
@@ -5985,9 +6474,12 @@
         <v>0.03941</v>
       </c>
       <c r="I163" s="1" t="n">
+        <v>0.03939</v>
+      </c>
+      <c r="J163" s="1" t="n">
         <v>0.03941</v>
       </c>
-      <c r="J163" s="1" t="n">
+      <c r="K163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -6019,9 +6511,12 @@
         <v>0.0635</v>
       </c>
       <c r="I164" s="1" t="n">
-        <v>0.0635</v>
+        <v>0.0636</v>
       </c>
       <c r="J164" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="K164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -6053,9 +6548,12 @@
         <v>0.3597</v>
       </c>
       <c r="I165" s="1" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="J165" s="1" t="n">
         <v>0.3618</v>
       </c>
-      <c r="J165" s="1" t="n">
+      <c r="K165" s="1" t="n">
         <v>0.3525</v>
       </c>
     </row>
@@ -6087,9 +6585,12 @@
         <v>139.2</v>
       </c>
       <c r="I166" s="1" t="n">
+        <v>139.19</v>
+      </c>
+      <c r="J166" s="1" t="n">
         <v>139.27</v>
       </c>
-      <c r="J166" s="1" t="n">
+      <c r="K166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -6121,9 +6622,12 @@
         <v>0.0006431</v>
       </c>
       <c r="I167" s="1" t="n">
+        <v>0.0006434</v>
+      </c>
+      <c r="J167" s="1" t="n">
         <v>0.0006533</v>
       </c>
-      <c r="J167" s="1" t="n">
+      <c r="K167" s="1" t="n">
         <v>0.0006431</v>
       </c>
     </row>
@@ -6155,9 +6659,12 @@
         <v>0.01653</v>
       </c>
       <c r="I168" s="1" t="n">
+        <v>0.01657</v>
+      </c>
+      <c r="J168" s="1" t="n">
         <v>0.01678</v>
       </c>
-      <c r="J168" s="1" t="n">
+      <c r="K168" s="1" t="n">
         <v>0.01629</v>
       </c>
     </row>
@@ -6189,9 +6696,12 @@
         <v>0.04807</v>
       </c>
       <c r="I169" s="1" t="n">
+        <v>0.04798</v>
+      </c>
+      <c r="J169" s="1" t="n">
         <v>0.04807</v>
       </c>
-      <c r="J169" s="1" t="n">
+      <c r="K169" s="1" t="n">
         <v>0.04785</v>
       </c>
     </row>
@@ -6223,9 +6733,12 @@
         <v>4.292</v>
       </c>
       <c r="I170" s="1" t="n">
+        <v>4.282</v>
+      </c>
+      <c r="J170" s="1" t="n">
         <v>4.298</v>
       </c>
-      <c r="J170" s="1" t="n">
+      <c r="K170" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -6257,10 +6770,13 @@
         <v>0.03831</v>
       </c>
       <c r="I171" s="1" t="n">
+        <v>0.03825</v>
+      </c>
+      <c r="J171" s="1" t="n">
         <v>0.03874</v>
       </c>
-      <c r="J171" s="1" t="n">
-        <v>0.03831</v>
+      <c r="K171" s="1" t="n">
+        <v>0.03825</v>
       </c>
     </row>
     <row r="172">
@@ -6291,9 +6807,12 @@
         <v>0.0428</v>
       </c>
       <c r="I172" s="1" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="J172" s="1" t="n">
         <v>0.0431</v>
       </c>
-      <c r="J172" s="1" t="n">
+      <c r="K172" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -6325,9 +6844,12 @@
         <v>0.023799</v>
       </c>
       <c r="I173" s="1" t="n">
+        <v>0.02406</v>
+      </c>
+      <c r="J173" s="1" t="n">
         <v>0.024556</v>
       </c>
-      <c r="J173" s="1" t="n">
+      <c r="K173" s="1" t="n">
         <v>0.023799</v>
       </c>
     </row>
@@ -6359,9 +6881,12 @@
         <v>1.0802</v>
       </c>
       <c r="I174" s="1" t="n">
-        <v>1.0803</v>
+        <v>1.0809</v>
       </c>
       <c r="J174" s="1" t="n">
+        <v>1.0809</v>
+      </c>
+      <c r="K174" s="1" t="n">
         <v>1.0704</v>
       </c>
     </row>
@@ -6393,9 +6918,12 @@
         <v>0.028121</v>
       </c>
       <c r="I175" s="1" t="n">
+        <v>0.028195</v>
+      </c>
+      <c r="J175" s="1" t="n">
         <v>0.028967</v>
       </c>
-      <c r="J175" s="1" t="n">
+      <c r="K175" s="1" t="n">
         <v>0.028121</v>
       </c>
     </row>
@@ -6427,9 +6955,12 @@
         <v>0.02192</v>
       </c>
       <c r="I176" s="1" t="n">
-        <v>0.02195</v>
+        <v>0.02198</v>
       </c>
       <c r="J176" s="1" t="n">
+        <v>0.02198</v>
+      </c>
+      <c r="K176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -6461,9 +6992,12 @@
         <v>0.5501</v>
       </c>
       <c r="I177" s="1" t="n">
+        <v>0.5484</v>
+      </c>
+      <c r="J177" s="1" t="n">
         <v>0.5501</v>
       </c>
-      <c r="J177" s="1" t="n">
+      <c r="K177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -6495,10 +7029,13 @@
         <v>0.08254</v>
       </c>
       <c r="I178" s="1" t="n">
+        <v>0.08214</v>
+      </c>
+      <c r="J178" s="1" t="n">
         <v>0.08276</v>
       </c>
-      <c r="J178" s="1" t="n">
-        <v>0.08248999999999999</v>
+      <c r="K178" s="1" t="n">
+        <v>0.08214</v>
       </c>
     </row>
     <row r="179">
@@ -6529,9 +7066,12 @@
         <v>0.02135</v>
       </c>
       <c r="I179" s="1" t="n">
+        <v>0.02134</v>
+      </c>
+      <c r="J179" s="1" t="n">
         <v>0.0214</v>
       </c>
-      <c r="J179" s="1" t="n">
+      <c r="K179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -6563,9 +7103,12 @@
         <v>0.27151</v>
       </c>
       <c r="I180" s="1" t="n">
-        <v>0.27157</v>
+        <v>0.27259</v>
       </c>
       <c r="J180" s="1" t="n">
+        <v>0.27259</v>
+      </c>
+      <c r="K180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -6597,9 +7140,12 @@
         <v>0.0042</v>
       </c>
       <c r="I181" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="J181" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="J181" s="1" t="n">
+      <c r="K181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -6631,9 +7177,12 @@
         <v>0.07902000000000001</v>
       </c>
       <c r="I182" s="1" t="n">
+        <v>0.07918</v>
+      </c>
+      <c r="J182" s="1" t="n">
         <v>0.07981000000000001</v>
       </c>
-      <c r="J182" s="1" t="n">
+      <c r="K182" s="1" t="n">
         <v>0.07902000000000001</v>
       </c>
     </row>
@@ -6665,9 +7214,12 @@
         <v>0.02351</v>
       </c>
       <c r="I183" s="1" t="n">
+        <v>0.02355</v>
+      </c>
+      <c r="J183" s="1" t="n">
         <v>0.02357</v>
       </c>
-      <c r="J183" s="1" t="n">
+      <c r="K183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -6699,9 +7251,12 @@
         <v>6.993e-05</v>
       </c>
       <c r="I184" s="1" t="n">
+        <v>6.978999999999999e-05</v>
+      </c>
+      <c r="J184" s="1" t="n">
         <v>7.002e-05</v>
       </c>
-      <c r="J184" s="1" t="n">
+      <c r="K184" s="1" t="n">
         <v>6.957e-05</v>
       </c>
     </row>
@@ -6733,9 +7288,12 @@
         <v>0.02135</v>
       </c>
       <c r="I185" s="1" t="n">
+        <v>0.02134</v>
+      </c>
+      <c r="J185" s="1" t="n">
         <v>0.0214</v>
       </c>
-      <c r="J185" s="1" t="n">
+      <c r="K185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -6767,9 +7325,12 @@
         <v>0.01627</v>
       </c>
       <c r="I186" s="1" t="n">
-        <v>0.01632</v>
+        <v>0.01637</v>
       </c>
       <c r="J186" s="1" t="n">
+        <v>0.01637</v>
+      </c>
+      <c r="K186" s="1" t="n">
         <v>0.01623</v>
       </c>
     </row>
@@ -6801,9 +7362,12 @@
         <v>0.981</v>
       </c>
       <c r="I187" s="1" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="J187" s="1" t="n">
         <v>0.981</v>
       </c>
-      <c r="J187" s="1" t="n">
+      <c r="K187" s="1" t="n">
         <v>0.971</v>
       </c>
     </row>
@@ -6835,9 +7399,12 @@
         <v>0.024</v>
       </c>
       <c r="I188" s="1" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="J188" s="1" t="n">
         <v>0.024</v>
       </c>
-      <c r="J188" s="1" t="n">
+      <c r="K188" s="1" t="n">
         <v>0.0237</v>
       </c>
     </row>
@@ -6869,9 +7436,12 @@
         <v>1.8739</v>
       </c>
       <c r="I189" s="1" t="n">
+        <v>1.8723</v>
+      </c>
+      <c r="J189" s="1" t="n">
         <v>1.8739</v>
       </c>
-      <c r="J189" s="1" t="n">
+      <c r="K189" s="1" t="n">
         <v>1.8609</v>
       </c>
     </row>
@@ -6903,9 +7473,12 @@
         <v>1.83</v>
       </c>
       <c r="I190" s="1" t="n">
+        <v>1.832</v>
+      </c>
+      <c r="J190" s="1" t="n">
         <v>1.838</v>
       </c>
-      <c r="J190" s="1" t="n">
+      <c r="K190" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -6937,10 +7510,13 @@
         <v>0.02666</v>
       </c>
       <c r="I191" s="1" t="n">
+        <v>0.02662</v>
+      </c>
+      <c r="J191" s="1" t="n">
         <v>0.0268</v>
       </c>
-      <c r="J191" s="1" t="n">
-        <v>0.02666</v>
+      <c r="K191" s="1" t="n">
+        <v>0.02662</v>
       </c>
     </row>
     <row r="192">
@@ -6971,9 +7547,12 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="I192" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="J192" s="1" t="n">
         <v>0.0973</v>
       </c>
-      <c r="J192" s="1" t="n">
+      <c r="K192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -7005,9 +7584,12 @@
         <v>0.1718</v>
       </c>
       <c r="I193" s="1" t="n">
-        <v>0.1718</v>
+        <v>0.1722</v>
       </c>
       <c r="J193" s="1" t="n">
+        <v>0.1722</v>
+      </c>
+      <c r="K193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -7039,9 +7621,12 @@
         <v>16.318</v>
       </c>
       <c r="I194" s="1" t="n">
+        <v>16.314</v>
+      </c>
+      <c r="J194" s="1" t="n">
         <v>16.318</v>
       </c>
-      <c r="J194" s="1" t="n">
+      <c r="K194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -7073,9 +7658,12 @@
         <v>4.1</v>
       </c>
       <c r="I195" s="1" t="n">
-        <v>4.1</v>
+        <v>4.113</v>
       </c>
       <c r="J195" s="1" t="n">
+        <v>4.113</v>
+      </c>
+      <c r="K195" s="1" t="n">
         <v>4.087</v>
       </c>
     </row>
@@ -7107,9 +7695,12 @@
         <v>1.2702</v>
       </c>
       <c r="I196" s="1" t="n">
+        <v>1.2701</v>
+      </c>
+      <c r="J196" s="1" t="n">
         <v>1.2794</v>
       </c>
-      <c r="J196" s="1" t="n">
+      <c r="K196" s="1" t="n">
         <v>1.2663</v>
       </c>
     </row>
@@ -7141,10 +7732,13 @@
         <v>3.082</v>
       </c>
       <c r="I197" s="1" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="J197" s="1" t="n">
         <v>3.092</v>
       </c>
-      <c r="J197" s="1" t="n">
-        <v>3.066</v>
+      <c r="K197" s="1" t="n">
+        <v>3.063</v>
       </c>
     </row>
     <row r="198">
@@ -7175,9 +7769,12 @@
         <v>0.01263</v>
       </c>
       <c r="I198" s="1" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="J198" s="1" t="n">
         <v>0.01266</v>
       </c>
-      <c r="J198" s="1" t="n">
+      <c r="K198" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -7212,6 +7809,9 @@
         <v>0.0001767</v>
       </c>
       <c r="J199" s="1" t="n">
+        <v>0.0001767</v>
+      </c>
+      <c r="K199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -7243,9 +7843,12 @@
         <v>115.57</v>
       </c>
       <c r="I200" s="1" t="n">
+        <v>115.57</v>
+      </c>
+      <c r="J200" s="1" t="n">
         <v>115.62</v>
       </c>
-      <c r="J200" s="1" t="n">
+      <c r="K200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -7277,10 +7880,13 @@
         <v>0.01024</v>
       </c>
       <c r="I201" s="1" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="J201" s="1" t="n">
         <v>0.01031</v>
       </c>
-      <c r="J201" s="1" t="n">
-        <v>0.01023</v>
+      <c r="K201" s="1" t="n">
+        <v>0.01021</v>
       </c>
     </row>
     <row r="202">
@@ -7311,9 +7917,12 @@
         <v>0.01069</v>
       </c>
       <c r="I202" s="1" t="n">
+        <v>0.01069</v>
+      </c>
+      <c r="J202" s="1" t="n">
         <v>0.01073</v>
       </c>
-      <c r="J202" s="1" t="n">
+      <c r="K202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -7345,10 +7954,13 @@
         <v>0.003138</v>
       </c>
       <c r="I203" s="1" t="n">
+        <v>0.003131</v>
+      </c>
+      <c r="J203" s="1" t="n">
         <v>0.003153</v>
       </c>
-      <c r="J203" s="1" t="n">
-        <v>0.003136</v>
+      <c r="K203" s="1" t="n">
+        <v>0.003131</v>
       </c>
     </row>
     <row r="204">
@@ -7379,9 +7991,12 @@
         <v>28.28</v>
       </c>
       <c r="I204" s="1" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="J204" s="1" t="n">
         <v>28.38</v>
       </c>
-      <c r="J204" s="1" t="n">
+      <c r="K204" s="1" t="n">
         <v>28.23</v>
       </c>
     </row>
@@ -7413,9 +8028,12 @@
         <v>0.5622</v>
       </c>
       <c r="I205" s="1" t="n">
+        <v>0.5629</v>
+      </c>
+      <c r="J205" s="1" t="n">
         <v>0.5636</v>
       </c>
-      <c r="J205" s="1" t="n">
+      <c r="K205" s="1" t="n">
         <v>0.5608</v>
       </c>
     </row>
@@ -7447,9 +8065,12 @@
         <v>0.0004414</v>
       </c>
       <c r="I206" s="1" t="n">
+        <v>0.0004404</v>
+      </c>
+      <c r="J206" s="1" t="n">
         <v>0.0004417</v>
       </c>
-      <c r="J206" s="1" t="n">
+      <c r="K206" s="1" t="n">
         <v>0.0004387</v>
       </c>
     </row>
@@ -7481,9 +8102,12 @@
         <v>0.04665</v>
       </c>
       <c r="I207" s="1" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="J207" s="1" t="n">
         <v>0.04667</v>
       </c>
-      <c r="J207" s="1" t="n">
+      <c r="K207" s="1" t="n">
         <v>0.04648</v>
       </c>
     </row>
@@ -7518,6 +8142,9 @@
         <v>0.091</v>
       </c>
       <c r="J208" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="K208" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -7549,9 +8176,12 @@
         <v>0.02574</v>
       </c>
       <c r="I209" s="1" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="J209" s="1" t="n">
         <v>0.02574</v>
       </c>
-      <c r="J209" s="1" t="n">
+      <c r="K209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -7583,9 +8213,12 @@
         <v>0.012678</v>
       </c>
       <c r="I210" s="1" t="n">
+        <v>0.01268</v>
+      </c>
+      <c r="J210" s="1" t="n">
         <v>0.012745</v>
       </c>
-      <c r="J210" s="1" t="n">
+      <c r="K210" s="1" t="n">
         <v>0.012652</v>
       </c>
     </row>
@@ -7617,9 +8250,12 @@
         <v>0.092</v>
       </c>
       <c r="I211" s="1" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="J211" s="1" t="n">
         <v>0.0921</v>
       </c>
-      <c r="J211" s="1" t="n">
+      <c r="K211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -7651,9 +8287,12 @@
         <v>0.007061</v>
       </c>
       <c r="I212" s="1" t="n">
+        <v>0.00706</v>
+      </c>
+      <c r="J212" s="1" t="n">
         <v>0.007076</v>
       </c>
-      <c r="J212" s="1" t="n">
+      <c r="K212" s="1" t="n">
         <v>0.007044</v>
       </c>
     </row>
@@ -7685,9 +8324,12 @@
         <v>0.0296</v>
       </c>
       <c r="I213" s="1" t="n">
+        <v>0.02961</v>
+      </c>
+      <c r="J213" s="1" t="n">
         <v>0.02966</v>
       </c>
-      <c r="J213" s="1" t="n">
+      <c r="K213" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -7719,9 +8361,12 @@
         <v>0.2705</v>
       </c>
       <c r="I214" s="1" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="J214" s="1" t="n">
         <v>0.2708</v>
       </c>
-      <c r="J214" s="1" t="n">
+      <c r="K214" s="1" t="n">
         <v>0.2698</v>
       </c>
     </row>
@@ -7753,9 +8398,12 @@
         <v>0.02205</v>
       </c>
       <c r="I215" s="1" t="n">
-        <v>0.02205</v>
+        <v>0.02227</v>
       </c>
       <c r="J215" s="1" t="n">
+        <v>0.02227</v>
+      </c>
+      <c r="K215" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -7787,10 +8435,13 @@
         <v>0.01467</v>
       </c>
       <c r="I216" s="1" t="n">
+        <v>0.01463</v>
+      </c>
+      <c r="J216" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="J216" s="1" t="n">
-        <v>0.01467</v>
+      <c r="K216" s="1" t="n">
+        <v>0.01463</v>
       </c>
     </row>
     <row r="217">
@@ -7821,9 +8472,12 @@
         <v>0.2539</v>
       </c>
       <c r="I217" s="1" t="n">
+        <v>0.2534</v>
+      </c>
+      <c r="J217" s="1" t="n">
         <v>0.2542</v>
       </c>
-      <c r="J217" s="1" t="n">
+      <c r="K217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -7855,9 +8509,12 @@
         <v>0.3076</v>
       </c>
       <c r="I218" s="1" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="J218" s="1" t="n">
         <v>0.3087</v>
       </c>
-      <c r="J218" s="1" t="n">
+      <c r="K218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -7889,9 +8546,12 @@
         <v>0.1786</v>
       </c>
       <c r="I219" s="1" t="n">
+        <v>0.1784</v>
+      </c>
+      <c r="J219" s="1" t="n">
         <v>0.1786</v>
       </c>
-      <c r="J219" s="1" t="n">
+      <c r="K219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -7923,10 +8583,13 @@
         <v>14.96</v>
       </c>
       <c r="I220" s="1" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="J220" s="1" t="n">
         <v>15.02</v>
       </c>
-      <c r="J220" s="1" t="n">
-        <v>14.96</v>
+      <c r="K220" s="1" t="n">
+        <v>14.95</v>
       </c>
     </row>
     <row r="221">
@@ -7957,9 +8620,12 @@
         <v>0.01605</v>
       </c>
       <c r="I221" s="1" t="n">
+        <v>0.01607</v>
+      </c>
+      <c r="J221" s="1" t="n">
         <v>0.01611</v>
       </c>
-      <c r="J221" s="1" t="n">
+      <c r="K221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -7991,9 +8657,12 @@
         <v>66.34999999999999</v>
       </c>
       <c r="I222" s="1" t="n">
+        <v>66.42</v>
+      </c>
+      <c r="J222" s="1" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="J222" s="1" t="n">
+      <c r="K222" s="1" t="n">
         <v>66.17</v>
       </c>
     </row>
@@ -8025,9 +8694,12 @@
         <v>0.09271</v>
       </c>
       <c r="I223" s="1" t="n">
-        <v>0.09308</v>
+        <v>0.09352000000000001</v>
       </c>
       <c r="J223" s="1" t="n">
+        <v>0.09352000000000001</v>
+      </c>
+      <c r="K223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -8059,9 +8731,12 @@
         <v>0.03945</v>
       </c>
       <c r="I224" s="1" t="n">
+        <v>0.03951</v>
+      </c>
+      <c r="J224" s="1" t="n">
         <v>0.03963</v>
       </c>
-      <c r="J224" s="1" t="n">
+      <c r="K224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -8093,9 +8768,12 @@
         <v>0.5703</v>
       </c>
       <c r="I225" s="1" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="J225" s="1" t="n">
         <v>0.5725</v>
       </c>
-      <c r="J225" s="1" t="n">
+      <c r="K225" s="1" t="n">
         <v>0.5695</v>
       </c>
     </row>
@@ -8127,9 +8805,12 @@
         <v>0.1176</v>
       </c>
       <c r="I226" s="1" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="J226" s="1" t="n">
         <v>0.1184</v>
       </c>
-      <c r="J226" s="1" t="n">
+      <c r="K226" s="1" t="n">
         <v>0.1166</v>
       </c>
     </row>
@@ -8161,10 +8842,13 @@
         <v>0.317</v>
       </c>
       <c r="I227" s="1" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="J227" s="1" t="n">
         <v>0.3201</v>
       </c>
-      <c r="J227" s="1" t="n">
-        <v>0.3167</v>
+      <c r="K227" s="1" t="n">
+        <v>0.3165</v>
       </c>
     </row>
     <row r="228">
@@ -8195,9 +8879,12 @@
         <v>6.078</v>
       </c>
       <c r="I228" s="1" t="n">
+        <v>6.074</v>
+      </c>
+      <c r="J228" s="1" t="n">
         <v>6.09</v>
       </c>
-      <c r="J228" s="1" t="n">
+      <c r="K228" s="1" t="n">
         <v>6.062</v>
       </c>
     </row>
@@ -8229,9 +8916,12 @@
         <v>0.0294</v>
       </c>
       <c r="I229" s="1" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="J229" s="1" t="n">
         <v>0.0294</v>
       </c>
-      <c r="J229" s="1" t="n">
+      <c r="K229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -8263,9 +8953,12 @@
         <v>0.3302</v>
       </c>
       <c r="I230" s="1" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="J230" s="1" t="n">
         <v>0.3307</v>
       </c>
-      <c r="J230" s="1" t="n">
+      <c r="K230" s="1" t="n">
         <v>0.3288</v>
       </c>
     </row>
@@ -8297,9 +8990,12 @@
         <v>0.12011</v>
       </c>
       <c r="I231" s="1" t="n">
+        <v>0.12008</v>
+      </c>
+      <c r="J231" s="1" t="n">
         <v>0.12089</v>
       </c>
-      <c r="J231" s="1" t="n">
+      <c r="K231" s="1" t="n">
         <v>0.11994</v>
       </c>
     </row>
@@ -8331,9 +9027,12 @@
         <v>0.1185</v>
       </c>
       <c r="I232" s="1" t="n">
+        <v>0.1183</v>
+      </c>
+      <c r="J232" s="1" t="n">
         <v>0.1187</v>
       </c>
-      <c r="J232" s="1" t="n">
+      <c r="K232" s="1" t="n">
         <v>0.1182</v>
       </c>
     </row>
@@ -8365,9 +9064,12 @@
         <v>0.03017</v>
       </c>
       <c r="I233" s="1" t="n">
+        <v>0.03017</v>
+      </c>
+      <c r="J233" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="J233" s="1" t="n">
+      <c r="K233" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -8399,9 +9101,12 @@
         <v>0.015906</v>
       </c>
       <c r="I234" s="1" t="n">
+        <v>0.015871</v>
+      </c>
+      <c r="J234" s="1" t="n">
         <v>0.015906</v>
       </c>
-      <c r="J234" s="1" t="n">
+      <c r="K234" s="1" t="n">
         <v>0.0156</v>
       </c>
     </row>
@@ -8433,10 +9138,13 @@
         <v>0.0128</v>
       </c>
       <c r="I235" s="1" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="J235" s="1" t="n">
         <v>0.01281</v>
       </c>
-      <c r="J235" s="1" t="n">
-        <v>0.01272</v>
+      <c r="K235" s="1" t="n">
+        <v>0.0127</v>
       </c>
     </row>
     <row r="236">
@@ -8467,9 +9175,12 @@
         <v>0.0193</v>
       </c>
       <c r="I236" s="1" t="n">
-        <v>0.0193</v>
+        <v>0.01933</v>
       </c>
       <c r="J236" s="1" t="n">
+        <v>0.01933</v>
+      </c>
+      <c r="K236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -8501,9 +9212,12 @@
         <v>0.08527</v>
       </c>
       <c r="I237" s="1" t="n">
+        <v>0.0852</v>
+      </c>
+      <c r="J237" s="1" t="n">
         <v>0.08545999999999999</v>
       </c>
-      <c r="J237" s="1" t="n">
+      <c r="K237" s="1" t="n">
         <v>0.08427999999999999</v>
       </c>
     </row>
@@ -8535,9 +9249,12 @@
         <v>0.05852</v>
       </c>
       <c r="I238" s="1" t="n">
+        <v>0.05862</v>
+      </c>
+      <c r="J238" s="1" t="n">
         <v>0.05892</v>
       </c>
-      <c r="J238" s="1" t="n">
+      <c r="K238" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>
@@ -8569,10 +9286,13 @@
         <v>0.008973</v>
       </c>
       <c r="I239" s="1" t="n">
+        <v>0.008954</v>
+      </c>
+      <c r="J239" s="1" t="n">
         <v>0.009131999999999999</v>
       </c>
-      <c r="J239" s="1" t="n">
-        <v>0.008973</v>
+      <c r="K239" s="1" t="n">
+        <v>0.008954</v>
       </c>
     </row>
     <row r="240">
@@ -8603,9 +9323,12 @@
         <v>0.004159</v>
       </c>
       <c r="I240" s="1" t="n">
+        <v>0.004161</v>
+      </c>
+      <c r="J240" s="1" t="n">
         <v>0.004175</v>
       </c>
-      <c r="J240" s="1" t="n">
+      <c r="K240" s="1" t="n">
         <v>0.004154</v>
       </c>
     </row>
@@ -8637,9 +9360,12 @@
         <v>0.2403</v>
       </c>
       <c r="I241" s="1" t="n">
+        <v>0.2406</v>
+      </c>
+      <c r="J241" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="J241" s="1" t="n">
+      <c r="K241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -8671,9 +9397,12 @@
         <v>0.0589</v>
       </c>
       <c r="I242" s="1" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="J242" s="1" t="n">
         <v>0.0589</v>
       </c>
-      <c r="J242" s="1" t="n">
+      <c r="K242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -8705,9 +9434,12 @@
         <v>0.02362</v>
       </c>
       <c r="I243" s="1" t="n">
+        <v>0.02362</v>
+      </c>
+      <c r="J243" s="1" t="n">
         <v>0.02363</v>
       </c>
-      <c r="J243" s="1" t="n">
+      <c r="K243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -8739,9 +9471,12 @@
         <v>0.05579</v>
       </c>
       <c r="I244" s="1" t="n">
+        <v>0.0558</v>
+      </c>
+      <c r="J244" s="1" t="n">
         <v>0.05623</v>
       </c>
-      <c r="J244" s="1" t="n">
+      <c r="K244" s="1" t="n">
         <v>0.05547</v>
       </c>
     </row>
@@ -8773,9 +9508,12 @@
         <v>0.03442</v>
       </c>
       <c r="I245" s="1" t="n">
-        <v>0.03444</v>
+        <v>0.03449</v>
       </c>
       <c r="J245" s="1" t="n">
+        <v>0.03449</v>
+      </c>
+      <c r="K245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -8807,9 +9545,12 @@
         <v>0.06022</v>
       </c>
       <c r="I246" s="1" t="n">
-        <v>0.06027</v>
+        <v>0.06035</v>
       </c>
       <c r="J246" s="1" t="n">
+        <v>0.06035</v>
+      </c>
+      <c r="K246" s="1" t="n">
         <v>0.0599</v>
       </c>
     </row>
@@ -8841,9 +9582,12 @@
         <v>0.382</v>
       </c>
       <c r="I247" s="1" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="J247" s="1" t="n">
         <v>0.385</v>
       </c>
-      <c r="J247" s="1" t="n">
+      <c r="K247" s="1" t="n">
         <v>0.382</v>
       </c>
     </row>
@@ -8875,9 +9619,12 @@
         <v>0.5191</v>
       </c>
       <c r="I248" s="1" t="n">
+        <v>0.5183</v>
+      </c>
+      <c r="J248" s="1" t="n">
         <v>0.5191</v>
       </c>
-      <c r="J248" s="1" t="n">
+      <c r="K248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -8909,9 +9656,12 @@
         <v>0.02833</v>
       </c>
       <c r="I249" s="1" t="n">
-        <v>0.02833</v>
+        <v>0.0288</v>
       </c>
       <c r="J249" s="1" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="K249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -8943,9 +9693,12 @@
         <v>0.01299</v>
       </c>
       <c r="I250" s="1" t="n">
-        <v>0.01299</v>
+        <v>0.01307</v>
       </c>
       <c r="J250" s="1" t="n">
+        <v>0.01307</v>
+      </c>
+      <c r="K250" s="1" t="n">
         <v>0.01288</v>
       </c>
     </row>
@@ -8980,6 +9733,9 @@
         <v>0.1003</v>
       </c>
       <c r="J251" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="K251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -9011,9 +9767,12 @@
         <v>0.00714</v>
       </c>
       <c r="I252" s="1" t="n">
+        <v>0.00717</v>
+      </c>
+      <c r="J252" s="1" t="n">
         <v>0.00719</v>
       </c>
-      <c r="J252" s="1" t="n">
+      <c r="K252" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -9045,9 +9804,12 @@
         <v>0.005561</v>
       </c>
       <c r="I253" s="1" t="n">
-        <v>0.005563</v>
+        <v>0.005571</v>
       </c>
       <c r="J253" s="1" t="n">
+        <v>0.005571</v>
+      </c>
+      <c r="K253" s="1" t="n">
         <v>0.005554</v>
       </c>
     </row>
@@ -9079,9 +9841,12 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="I254" s="1" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="J254" s="1" t="n">
         <v>0.0646</v>
       </c>
-      <c r="J254" s="1" t="n">
+      <c r="K254" s="1" t="n">
         <v>0.0641</v>
       </c>
     </row>
@@ -9113,9 +9878,12 @@
         <v>0.01451</v>
       </c>
       <c r="I255" s="1" t="n">
+        <v>0.01449</v>
+      </c>
+      <c r="J255" s="1" t="n">
         <v>0.01453</v>
       </c>
-      <c r="J255" s="1" t="n">
+      <c r="K255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -9147,10 +9915,13 @@
         <v>0.999286</v>
       </c>
       <c r="I256" s="1" t="n">
+        <v>0.9992760000000001</v>
+      </c>
+      <c r="J256" s="1" t="n">
         <v>0.999297</v>
       </c>
-      <c r="J256" s="1" t="n">
-        <v>0.999285</v>
+      <c r="K256" s="1" t="n">
+        <v>0.9992760000000001</v>
       </c>
     </row>
     <row r="257">
@@ -9181,9 +9952,12 @@
         <v>0.02115</v>
       </c>
       <c r="I257" s="1" t="n">
-        <v>0.02115</v>
+        <v>0.02116</v>
       </c>
       <c r="J257" s="1" t="n">
+        <v>0.02116</v>
+      </c>
+      <c r="K257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -9215,9 +9989,12 @@
         <v>0.01147</v>
       </c>
       <c r="I258" s="1" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="J258" s="1" t="n">
         <v>0.01148</v>
       </c>
-      <c r="J258" s="1" t="n">
+      <c r="K258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -9249,9 +10026,12 @@
         <v>0.5085</v>
       </c>
       <c r="I259" s="1" t="n">
+        <v>0.5104</v>
+      </c>
+      <c r="J259" s="1" t="n">
         <v>0.5119</v>
       </c>
-      <c r="J259" s="1" t="n">
+      <c r="K259" s="1" t="n">
         <v>0.5071</v>
       </c>
     </row>
@@ -9283,9 +10063,12 @@
         <v>0.08454</v>
       </c>
       <c r="I260" s="1" t="n">
+        <v>0.08468000000000001</v>
+      </c>
+      <c r="J260" s="1" t="n">
         <v>0.08537</v>
       </c>
-      <c r="J260" s="1" t="n">
+      <c r="K260" s="1" t="n">
         <v>0.08436</v>
       </c>
     </row>
@@ -9317,10 +10100,13 @@
         <v>0.04125</v>
       </c>
       <c r="I261" s="1" t="n">
+        <v>0.04121</v>
+      </c>
+      <c r="J261" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="J261" s="1" t="n">
-        <v>0.04123</v>
+      <c r="K261" s="1" t="n">
+        <v>0.04121</v>
       </c>
     </row>
     <row r="262">
@@ -9351,9 +10137,12 @@
         <v>2.283</v>
       </c>
       <c r="I262" s="1" t="n">
+        <v>2.283</v>
+      </c>
+      <c r="J262" s="1" t="n">
         <v>2.288</v>
       </c>
-      <c r="J262" s="1" t="n">
+      <c r="K262" s="1" t="n">
         <v>2.279</v>
       </c>
     </row>
@@ -9385,9 +10174,12 @@
         <v>18.49</v>
       </c>
       <c r="I263" s="1" t="n">
-        <v>18.51</v>
+        <v>18.55</v>
       </c>
       <c r="J263" s="1" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="K263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -9419,9 +10211,12 @@
         <v>0.008534</v>
       </c>
       <c r="I264" s="1" t="n">
+        <v>0.008534999999999999</v>
+      </c>
+      <c r="J264" s="1" t="n">
         <v>0.008562999999999999</v>
       </c>
-      <c r="J264" s="1" t="n">
+      <c r="K264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -9453,9 +10248,12 @@
         <v>0.363</v>
       </c>
       <c r="I265" s="1" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="J265" s="1" t="n">
         <v>0.3645</v>
       </c>
-      <c r="J265" s="1" t="n">
+      <c r="K265" s="1" t="n">
         <v>0.3627</v>
       </c>
     </row>
@@ -9487,9 +10285,12 @@
         <v>0.05489</v>
       </c>
       <c r="I266" s="1" t="n">
-        <v>0.05489</v>
+        <v>0.054943</v>
       </c>
       <c r="J266" s="1" t="n">
+        <v>0.054943</v>
+      </c>
+      <c r="K266" s="1" t="n">
         <v>0.053765</v>
       </c>
     </row>
@@ -9521,9 +10322,12 @@
         <v>0.1315</v>
       </c>
       <c r="I267" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="J267" s="1" t="n">
         <v>0.1321</v>
       </c>
-      <c r="J267" s="1" t="n">
+      <c r="K267" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -9555,9 +10359,12 @@
         <v>0.00775</v>
       </c>
       <c r="I268" s="1" t="n">
+        <v>0.007763</v>
+      </c>
+      <c r="J268" s="1" t="n">
         <v>0.007845</v>
       </c>
-      <c r="J268" s="1" t="n">
+      <c r="K268" s="1" t="n">
         <v>0.00775</v>
       </c>
     </row>
@@ -9589,9 +10396,12 @@
         <v>0.001233</v>
       </c>
       <c r="I269" s="1" t="n">
+        <v>0.001232</v>
+      </c>
+      <c r="J269" s="1" t="n">
         <v>0.00124</v>
       </c>
-      <c r="J269" s="1" t="n">
+      <c r="K269" s="1" t="n">
         <v>0.001232</v>
       </c>
     </row>
@@ -9623,9 +10433,12 @@
         <v>0.28999</v>
       </c>
       <c r="I270" s="1" t="n">
+        <v>0.28962</v>
+      </c>
+      <c r="J270" s="1" t="n">
         <v>0.28999</v>
       </c>
-      <c r="J270" s="1" t="n">
+      <c r="K270" s="1" t="n">
         <v>0.28865</v>
       </c>
     </row>
@@ -9657,9 +10470,12 @@
         <v>0.03912</v>
       </c>
       <c r="I271" s="1" t="n">
+        <v>0.03894</v>
+      </c>
+      <c r="J271" s="1" t="n">
         <v>0.03922</v>
       </c>
-      <c r="J271" s="1" t="n">
+      <c r="K271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -9691,9 +10507,12 @@
         <v>0.05151</v>
       </c>
       <c r="I272" s="1" t="n">
-        <v>0.05151</v>
+        <v>0.05181</v>
       </c>
       <c r="J272" s="1" t="n">
+        <v>0.05181</v>
+      </c>
+      <c r="K272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -9728,6 +10547,9 @@
         <v>0.00771</v>
       </c>
       <c r="J273" s="1" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="K273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -9759,9 +10581,12 @@
         <v>0.005794</v>
       </c>
       <c r="I274" s="1" t="n">
+        <v>0.005794</v>
+      </c>
+      <c r="J274" s="1" t="n">
         <v>0.005797</v>
       </c>
-      <c r="J274" s="1" t="n">
+      <c r="K274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -9793,9 +10618,12 @@
         <v>0.0005888</v>
       </c>
       <c r="I275" s="1" t="n">
+        <v>0.0005885</v>
+      </c>
+      <c r="J275" s="1" t="n">
         <v>0.0005895</v>
       </c>
-      <c r="J275" s="1" t="n">
+      <c r="K275" s="1" t="n">
         <v>0.0005863</v>
       </c>
     </row>
@@ -9827,9 +10655,12 @@
         <v>0.15011</v>
       </c>
       <c r="I276" s="1" t="n">
+        <v>0.15077</v>
+      </c>
+      <c r="J276" s="1" t="n">
         <v>0.15167</v>
       </c>
-      <c r="J276" s="1" t="n">
+      <c r="K276" s="1" t="n">
         <v>0.15004</v>
       </c>
     </row>
@@ -9861,9 +10692,12 @@
         <v>0.022956</v>
       </c>
       <c r="I277" s="1" t="n">
-        <v>0.022966</v>
+        <v>0.022981</v>
       </c>
       <c r="J277" s="1" t="n">
+        <v>0.022981</v>
+      </c>
+      <c r="K277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -9895,9 +10729,12 @@
         <v>0.04232</v>
       </c>
       <c r="I278" s="1" t="n">
+        <v>0.04197</v>
+      </c>
+      <c r="J278" s="1" t="n">
         <v>0.04242</v>
       </c>
-      <c r="J278" s="1" t="n">
+      <c r="K278" s="1" t="n">
         <v>0.04179</v>
       </c>
     </row>
@@ -9929,9 +10766,12 @@
         <v>0.0004002</v>
       </c>
       <c r="I279" s="1" t="n">
+        <v>0.0003986</v>
+      </c>
+      <c r="J279" s="1" t="n">
         <v>0.0004006</v>
       </c>
-      <c r="J279" s="1" t="n">
+      <c r="K279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -9963,9 +10803,12 @@
         <v>0.0219</v>
       </c>
       <c r="I280" s="1" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="J280" s="1" t="n">
         <v>0.02218</v>
       </c>
-      <c r="J280" s="1" t="n">
+      <c r="K280" s="1" t="n">
         <v>0.0219</v>
       </c>
     </row>
@@ -9997,9 +10840,12 @@
         <v>0.07036000000000001</v>
       </c>
       <c r="I281" s="1" t="n">
-        <v>0.07036000000000001</v>
+        <v>0.07065</v>
       </c>
       <c r="J281" s="1" t="n">
+        <v>0.07065</v>
+      </c>
+      <c r="K281" s="1" t="n">
         <v>0.06936</v>
       </c>
     </row>
@@ -10031,10 +10877,13 @@
         <v>0.006697</v>
       </c>
       <c r="I282" s="1" t="n">
+        <v>0.006688</v>
+      </c>
+      <c r="J282" s="1" t="n">
         <v>0.006804</v>
       </c>
-      <c r="J282" s="1" t="n">
-        <v>0.006697</v>
+      <c r="K282" s="1" t="n">
+        <v>0.006688</v>
       </c>
     </row>
     <row r="283">
@@ -10068,6 +10917,9 @@
         <v>0.12</v>
       </c>
       <c r="J283" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K283" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -10099,9 +10951,12 @@
         <v>0.00549</v>
       </c>
       <c r="I284" s="1" t="n">
-        <v>0.005491</v>
+        <v>0.005492</v>
       </c>
       <c r="J284" s="1" t="n">
+        <v>0.005492</v>
+      </c>
+      <c r="K284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -10133,9 +10988,12 @@
         <v>1.263</v>
       </c>
       <c r="I285" s="1" t="n">
-        <v>1.263</v>
+        <v>1.272</v>
       </c>
       <c r="J285" s="1" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="K285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -10167,9 +11025,12 @@
         <v>0.4432</v>
       </c>
       <c r="I286" s="1" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="J286" s="1" t="n">
         <v>0.4441</v>
       </c>
-      <c r="J286" s="1" t="n">
+      <c r="K286" s="1" t="n">
         <v>0.4423</v>
       </c>
     </row>
@@ -10201,9 +11062,12 @@
         <v>0.007932</v>
       </c>
       <c r="I287" s="1" t="n">
+        <v>0.007927999999999999</v>
+      </c>
+      <c r="J287" s="1" t="n">
         <v>0.007932</v>
       </c>
-      <c r="J287" s="1" t="n">
+      <c r="K287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -10235,9 +11099,12 @@
         <v>0.02935</v>
       </c>
       <c r="I288" s="1" t="n">
+        <v>0.02936</v>
+      </c>
+      <c r="J288" s="1" t="n">
         <v>0.0295</v>
       </c>
-      <c r="J288" s="1" t="n">
+      <c r="K288" s="1" t="n">
         <v>0.02914</v>
       </c>
     </row>
@@ -10269,9 +11136,12 @@
         <v>0.2819</v>
       </c>
       <c r="I289" s="1" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="J289" s="1" t="n">
         <v>0.2822</v>
       </c>
-      <c r="J289" s="1" t="n">
+      <c r="K289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -10303,9 +11173,12 @@
         <v>2.762</v>
       </c>
       <c r="I290" s="1" t="n">
+        <v>2.758</v>
+      </c>
+      <c r="J290" s="1" t="n">
         <v>2.764</v>
       </c>
-      <c r="J290" s="1" t="n">
+      <c r="K290" s="1" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -10337,9 +11210,12 @@
         <v>0.003176</v>
       </c>
       <c r="I291" s="1" t="n">
-        <v>0.003177</v>
+        <v>0.003181</v>
       </c>
       <c r="J291" s="1" t="n">
+        <v>0.003181</v>
+      </c>
+      <c r="K291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -10371,9 +11247,12 @@
         <v>0.4481</v>
       </c>
       <c r="I292" s="1" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="J292" s="1" t="n">
         <v>0.4488</v>
       </c>
-      <c r="J292" s="1" t="n">
+      <c r="K292" s="1" t="n">
         <v>0.4475</v>
       </c>
     </row>
@@ -10405,10 +11284,13 @@
         <v>0.08171</v>
       </c>
       <c r="I293" s="1" t="n">
+        <v>0.08136</v>
+      </c>
+      <c r="J293" s="1" t="n">
         <v>0.08298</v>
       </c>
-      <c r="J293" s="1" t="n">
-        <v>0.08171</v>
+      <c r="K293" s="1" t="n">
+        <v>0.08136</v>
       </c>
     </row>
     <row r="294">
@@ -10439,9 +11321,12 @@
         <v>0.0279</v>
       </c>
       <c r="I294" s="1" t="n">
+        <v>0.02789</v>
+      </c>
+      <c r="J294" s="1" t="n">
         <v>0.02791</v>
       </c>
-      <c r="J294" s="1" t="n">
+      <c r="K294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -10473,10 +11358,13 @@
         <v>0.953</v>
       </c>
       <c r="I295" s="1" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="J295" s="1" t="n">
         <v>0.958</v>
       </c>
-      <c r="J295" s="1" t="n">
-        <v>0.953</v>
+      <c r="K295" s="1" t="n">
+        <v>0.952</v>
       </c>
     </row>
     <row r="296">
@@ -10507,9 +11395,12 @@
         <v>0.007008</v>
       </c>
       <c r="I296" s="1" t="n">
+        <v>0.006979</v>
+      </c>
+      <c r="J296" s="1" t="n">
         <v>0.007008</v>
       </c>
-      <c r="J296" s="1" t="n">
+      <c r="K296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -10541,9 +11432,12 @@
         <v>0.1212</v>
       </c>
       <c r="I297" s="1" t="n">
+        <v>0.1211</v>
+      </c>
+      <c r="J297" s="1" t="n">
         <v>0.1213</v>
       </c>
-      <c r="J297" s="1" t="n">
+      <c r="K297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -10575,9 +11469,12 @@
         <v>0.01558</v>
       </c>
       <c r="I298" s="1" t="n">
+        <v>0.01554</v>
+      </c>
+      <c r="J298" s="1" t="n">
         <v>0.01558</v>
       </c>
-      <c r="J298" s="1" t="n">
+      <c r="K298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -10609,9 +11506,12 @@
         <v>0.4422</v>
       </c>
       <c r="I299" s="1" t="n">
+        <v>0.4418</v>
+      </c>
+      <c r="J299" s="1" t="n">
         <v>0.4422</v>
       </c>
-      <c r="J299" s="1" t="n">
+      <c r="K299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -10643,9 +11543,12 @@
         <v>0.00916</v>
       </c>
       <c r="I300" s="1" t="n">
+        <v>0.009140000000000001</v>
+      </c>
+      <c r="J300" s="1" t="n">
         <v>0.00924</v>
       </c>
-      <c r="J300" s="1" t="n">
+      <c r="K300" s="1" t="n">
         <v>0.009140000000000001</v>
       </c>
     </row>
@@ -10677,9 +11580,12 @@
         <v>0.1854</v>
       </c>
       <c r="I301" s="1" t="n">
-        <v>0.1855</v>
+        <v>0.1856</v>
       </c>
       <c r="J301" s="1" t="n">
+        <v>0.1856</v>
+      </c>
+      <c r="K301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -10711,9 +11617,12 @@
         <v>0.00754</v>
       </c>
       <c r="I302" s="1" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="J302" s="1" t="n">
         <v>0.00765</v>
       </c>
-      <c r="J302" s="1" t="n">
+      <c r="K302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -10745,9 +11654,12 @@
         <v>0.0002151</v>
       </c>
       <c r="I303" s="1" t="n">
+        <v>0.0002157</v>
+      </c>
+      <c r="J303" s="1" t="n">
         <v>0.0002171</v>
       </c>
-      <c r="J303" s="1" t="n">
+      <c r="K303" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -10779,9 +11691,12 @@
         <v>0.01549</v>
       </c>
       <c r="I304" s="1" t="n">
+        <v>0.01544</v>
+      </c>
+      <c r="J304" s="1" t="n">
         <v>0.01553</v>
       </c>
-      <c r="J304" s="1" t="n">
+      <c r="K304" s="1" t="n">
         <v>0.01542</v>
       </c>
     </row>
@@ -10813,9 +11728,12 @@
         <v>0.07386</v>
       </c>
       <c r="I305" s="1" t="n">
+        <v>0.07382</v>
+      </c>
+      <c r="J305" s="1" t="n">
         <v>0.07394000000000001</v>
       </c>
-      <c r="J305" s="1" t="n">
+      <c r="K305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -10847,9 +11765,12 @@
         <v>0.0832</v>
       </c>
       <c r="I306" s="1" t="n">
+        <v>0.08303000000000001</v>
+      </c>
+      <c r="J306" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="J306" s="1" t="n">
+      <c r="K306" s="1" t="n">
         <v>0.08275</v>
       </c>
     </row>
@@ -10881,10 +11802,13 @@
         <v>0.01804</v>
       </c>
       <c r="I307" s="1" t="n">
+        <v>0.01803</v>
+      </c>
+      <c r="J307" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="J307" s="1" t="n">
-        <v>0.01804</v>
+      <c r="K307" s="1" t="n">
+        <v>0.01803</v>
       </c>
     </row>
     <row r="308">
@@ -10915,9 +11839,12 @@
         <v>0.0006232</v>
       </c>
       <c r="I308" s="1" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="J308" s="1" t="n">
         <v>0.0006255</v>
       </c>
-      <c r="J308" s="1" t="n">
+      <c r="K308" s="1" t="n">
         <v>0.0006212</v>
       </c>
     </row>
@@ -10949,9 +11876,12 @@
         <v>0.0822</v>
       </c>
       <c r="I309" s="1" t="n">
+        <v>0.0822</v>
+      </c>
+      <c r="J309" s="1" t="n">
         <v>0.08294</v>
       </c>
-      <c r="J309" s="1" t="n">
+      <c r="K309" s="1" t="n">
         <v>0.0822</v>
       </c>
     </row>
@@ -10983,9 +11913,12 @@
         <v>0.0974</v>
       </c>
       <c r="I310" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="J310" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="J310" s="1" t="n">
+      <c r="K310" s="1" t="n">
         <v>0.0973</v>
       </c>
     </row>
@@ -11017,9 +11950,12 @@
         <v>0.2116</v>
       </c>
       <c r="I311" s="1" t="n">
+        <v>0.2112</v>
+      </c>
+      <c r="J311" s="1" t="n">
         <v>0.2119</v>
       </c>
-      <c r="J311" s="1" t="n">
+      <c r="K311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -11051,9 +11987,12 @@
         <v>0.3887</v>
       </c>
       <c r="I312" s="1" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="J312" s="1" t="n">
         <v>0.394</v>
       </c>
-      <c r="J312" s="1" t="n">
+      <c r="K312" s="1" t="n">
         <v>0.387</v>
       </c>
     </row>
@@ -11085,9 +12024,12 @@
         <v>0.10497</v>
       </c>
       <c r="I313" s="1" t="n">
+        <v>0.10495</v>
+      </c>
+      <c r="J313" s="1" t="n">
         <v>0.10542</v>
       </c>
-      <c r="J313" s="1" t="n">
+      <c r="K313" s="1" t="n">
         <v>0.10492</v>
       </c>
     </row>
@@ -11119,9 +12061,12 @@
         <v>0.08628</v>
       </c>
       <c r="I314" s="1" t="n">
-        <v>0.08628</v>
+        <v>0.08654000000000001</v>
       </c>
       <c r="J314" s="1" t="n">
+        <v>0.08654000000000001</v>
+      </c>
+      <c r="K314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -11153,9 +12098,12 @@
         <v>0.1179</v>
       </c>
       <c r="I315" s="1" t="n">
+        <v>0.1181</v>
+      </c>
+      <c r="J315" s="1" t="n">
         <v>0.1185</v>
       </c>
-      <c r="J315" s="1" t="n">
+      <c r="K315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -11187,10 +12135,13 @@
         <v>0.03638</v>
       </c>
       <c r="I316" s="1" t="n">
+        <v>0.03627</v>
+      </c>
+      <c r="J316" s="1" t="n">
         <v>0.03681</v>
       </c>
-      <c r="J316" s="1" t="n">
-        <v>0.03628</v>
+      <c r="K316" s="1" t="n">
+        <v>0.03627</v>
       </c>
     </row>
     <row r="317">
@@ -11221,9 +12172,12 @@
         <v>0.08164</v>
       </c>
       <c r="I317" s="1" t="n">
+        <v>0.08157</v>
+      </c>
+      <c r="J317" s="1" t="n">
         <v>0.08164</v>
       </c>
-      <c r="J317" s="1" t="n">
+      <c r="K317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -11255,9 +12209,12 @@
         <v>0.03746</v>
       </c>
       <c r="I318" s="1" t="n">
+        <v>0.03743</v>
+      </c>
+      <c r="J318" s="1" t="n">
         <v>0.03766</v>
       </c>
-      <c r="J318" s="1" t="n">
+      <c r="K318" s="1" t="n">
         <v>0.03736</v>
       </c>
     </row>
@@ -11289,9 +12246,12 @@
         <v>0.4296</v>
       </c>
       <c r="I319" s="1" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="J319" s="1" t="n">
         <v>0.4347</v>
       </c>
-      <c r="J319" s="1" t="n">
+      <c r="K319" s="1" t="n">
         <v>0.4296</v>
       </c>
     </row>
@@ -11323,10 +12283,13 @@
         <v>0.1601</v>
       </c>
       <c r="I320" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="J320" s="1" t="n">
         <v>0.1614</v>
       </c>
-      <c r="J320" s="1" t="n">
-        <v>0.16</v>
+      <c r="K320" s="1" t="n">
+        <v>0.1599</v>
       </c>
     </row>
     <row r="321">
@@ -11357,9 +12320,12 @@
         <v>5.681</v>
       </c>
       <c r="I321" s="1" t="n">
+        <v>5.679</v>
+      </c>
+      <c r="J321" s="1" t="n">
         <v>5.681</v>
       </c>
-      <c r="J321" s="1" t="n">
+      <c r="K321" s="1" t="n">
         <v>5.677</v>
       </c>
     </row>
@@ -11391,10 +12357,13 @@
         <v>0.00373</v>
       </c>
       <c r="I322" s="1" t="n">
+        <v>0.003714</v>
+      </c>
+      <c r="J322" s="1" t="n">
         <v>0.003746</v>
       </c>
-      <c r="J322" s="1" t="n">
-        <v>0.003715</v>
+      <c r="K322" s="1" t="n">
+        <v>0.003714</v>
       </c>
     </row>
     <row r="323">
@@ -11425,9 +12394,12 @@
         <v>0.001759</v>
       </c>
       <c r="I323" s="1" t="n">
+        <v>0.001759</v>
+      </c>
+      <c r="J323" s="1" t="n">
         <v>0.001761</v>
       </c>
-      <c r="J323" s="1" t="n">
+      <c r="K323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -11459,9 +12431,12 @@
         <v>1.2e-05</v>
       </c>
       <c r="I324" s="1" t="n">
+        <v>1.19e-05</v>
+      </c>
+      <c r="J324" s="1" t="n">
         <v>1.2e-05</v>
       </c>
-      <c r="J324" s="1" t="n">
+      <c r="K324" s="1" t="n">
         <v>1.19e-05</v>
       </c>
     </row>
@@ -11496,6 +12471,9 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="J325" s="1" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="K325" s="1" t="n">
         <v>0.0857</v>
       </c>
     </row>
@@ -11527,9 +12505,12 @@
         <v>0.01729</v>
       </c>
       <c r="I326" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="J326" s="1" t="n">
         <v>0.01736</v>
       </c>
-      <c r="J326" s="1" t="n">
+      <c r="K326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -11561,9 +12542,12 @@
         <v>0.01685</v>
       </c>
       <c r="I327" s="1" t="n">
+        <v>0.01683</v>
+      </c>
+      <c r="J327" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="J327" s="1" t="n">
+      <c r="K327" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -11595,9 +12579,12 @@
         <v>4.457</v>
       </c>
       <c r="I328" s="1" t="n">
+        <v>4.446</v>
+      </c>
+      <c r="J328" s="1" t="n">
         <v>4.462</v>
       </c>
-      <c r="J328" s="1" t="n">
+      <c r="K328" s="1" t="n">
         <v>4.446</v>
       </c>
     </row>
@@ -11629,9 +12616,12 @@
         <v>0.009671000000000001</v>
       </c>
       <c r="I329" s="1" t="n">
+        <v>0.009611</v>
+      </c>
+      <c r="J329" s="1" t="n">
         <v>0.009861</v>
       </c>
-      <c r="J329" s="1" t="n">
+      <c r="K329" s="1" t="n">
         <v>0.009532000000000001</v>
       </c>
     </row>
@@ -11663,9 +12653,12 @@
         <v>5189.9</v>
       </c>
       <c r="I330" s="1" t="n">
+        <v>5191.7</v>
+      </c>
+      <c r="J330" s="1" t="n">
         <v>5192.9</v>
       </c>
-      <c r="J330" s="1" t="n">
+      <c r="K330" s="1" t="n">
         <v>5185.8</v>
       </c>
     </row>
@@ -11697,9 +12690,12 @@
         <v>0.07054000000000001</v>
       </c>
       <c r="I331" s="1" t="n">
+        <v>0.07063999999999999</v>
+      </c>
+      <c r="J331" s="1" t="n">
         <v>0.07087</v>
       </c>
-      <c r="J331" s="1" t="n">
+      <c r="K331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -11731,9 +12727,12 @@
         <v>0.06098</v>
       </c>
       <c r="I332" s="1" t="n">
+        <v>0.06081</v>
+      </c>
+      <c r="J332" s="1" t="n">
         <v>0.06106</v>
       </c>
-      <c r="J332" s="1" t="n">
+      <c r="K332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -11765,9 +12764,12 @@
         <v>0.10341</v>
       </c>
       <c r="I333" s="1" t="n">
-        <v>0.10416</v>
+        <v>0.10499</v>
       </c>
       <c r="J333" s="1" t="n">
+        <v>0.10499</v>
+      </c>
+      <c r="K333" s="1" t="n">
         <v>0.10341</v>
       </c>
     </row>
@@ -11799,9 +12801,12 @@
         <v>0.08735</v>
       </c>
       <c r="I334" s="1" t="n">
+        <v>0.08758000000000001</v>
+      </c>
+      <c r="J334" s="1" t="n">
         <v>0.08837</v>
       </c>
-      <c r="J334" s="1" t="n">
+      <c r="K334" s="1" t="n">
         <v>0.08734</v>
       </c>
     </row>
@@ -11833,9 +12838,12 @@
         <v>0.016404</v>
       </c>
       <c r="I335" s="1" t="n">
-        <v>0.016413</v>
+        <v>0.01643</v>
       </c>
       <c r="J335" s="1" t="n">
+        <v>0.01643</v>
+      </c>
+      <c r="K335" s="1" t="n">
         <v>0.016391</v>
       </c>
     </row>
@@ -11867,9 +12875,12 @@
         <v>0.04597</v>
       </c>
       <c r="I336" s="1" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="J336" s="1" t="n">
         <v>0.046</v>
       </c>
-      <c r="J336" s="1" t="n">
+      <c r="K336" s="1" t="n">
         <v>0.04583</v>
       </c>
     </row>
@@ -11901,9 +12912,12 @@
         <v>0.1865</v>
       </c>
       <c r="I337" s="1" t="n">
-        <v>0.1865</v>
+        <v>0.187</v>
       </c>
       <c r="J337" s="1" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="K337" s="1" t="n">
         <v>0.1838</v>
       </c>
     </row>
@@ -11938,6 +12952,9 @@
         <v>0.1836</v>
       </c>
       <c r="J338" s="1" t="n">
+        <v>0.1836</v>
+      </c>
+      <c r="K338" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -11969,9 +12986,12 @@
         <v>0.01838</v>
       </c>
       <c r="I339" s="1" t="n">
+        <v>0.01836</v>
+      </c>
+      <c r="J339" s="1" t="n">
         <v>0.01838</v>
       </c>
-      <c r="J339" s="1" t="n">
+      <c r="K339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -12003,9 +13023,12 @@
         <v>0.02313</v>
       </c>
       <c r="I340" s="1" t="n">
-        <v>0.02313</v>
+        <v>0.02314</v>
       </c>
       <c r="J340" s="1" t="n">
+        <v>0.02314</v>
+      </c>
+      <c r="K340" s="1" t="n">
         <v>0.02305</v>
       </c>
     </row>
@@ -12037,9 +13060,12 @@
         <v>0.4577</v>
       </c>
       <c r="I341" s="1" t="n">
+        <v>0.4563</v>
+      </c>
+      <c r="J341" s="1" t="n">
         <v>0.4577</v>
       </c>
-      <c r="J341" s="1" t="n">
+      <c r="K341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -12071,9 +13097,12 @@
         <v>0.01349</v>
       </c>
       <c r="I342" s="1" t="n">
+        <v>0.01346</v>
+      </c>
+      <c r="J342" s="1" t="n">
         <v>0.01349</v>
       </c>
-      <c r="J342" s="1" t="n">
+      <c r="K342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -12105,9 +13134,12 @@
         <v>2.874</v>
       </c>
       <c r="I343" s="1" t="n">
+        <v>2.874</v>
+      </c>
+      <c r="J343" s="1" t="n">
         <v>2.89</v>
       </c>
-      <c r="J343" s="1" t="n">
+      <c r="K343" s="1" t="n">
         <v>2.872</v>
       </c>
     </row>
@@ -12139,9 +13171,12 @@
         <v>0.1538</v>
       </c>
       <c r="I344" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="J344" s="1" t="n">
         <v>0.1577</v>
       </c>
-      <c r="J344" s="1" t="n">
+      <c r="K344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -12173,9 +13208,12 @@
         <v>0.005361</v>
       </c>
       <c r="I345" s="1" t="n">
+        <v>0.005344</v>
+      </c>
+      <c r="J345" s="1" t="n">
         <v>0.005367</v>
       </c>
-      <c r="J345" s="1" t="n">
+      <c r="K345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -12207,9 +13245,12 @@
         <v>0.05786</v>
       </c>
       <c r="I346" s="1" t="n">
+        <v>0.05782</v>
+      </c>
+      <c r="J346" s="1" t="n">
         <v>0.0579</v>
       </c>
-      <c r="J346" s="1" t="n">
+      <c r="K346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -12241,9 +13282,12 @@
         <v>2609</v>
       </c>
       <c r="I347" s="1" t="n">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="J347" s="1" t="n">
+        <v>2613</v>
+      </c>
+      <c r="K347" s="1" t="n">
         <v>2597</v>
       </c>
     </row>
@@ -12275,9 +13319,12 @@
         <v>0.04595</v>
       </c>
       <c r="I348" s="1" t="n">
+        <v>0.04596</v>
+      </c>
+      <c r="J348" s="1" t="n">
         <v>0.04621</v>
       </c>
-      <c r="J348" s="1" t="n">
+      <c r="K348" s="1" t="n">
         <v>0.04595</v>
       </c>
     </row>
@@ -12309,10 +13356,13 @@
         <v>0.0057</v>
       </c>
       <c r="I349" s="1" t="n">
+        <v>0.00565</v>
+      </c>
+      <c r="J349" s="1" t="n">
         <v>0.005714</v>
       </c>
-      <c r="J349" s="1" t="n">
-        <v>0.005667</v>
+      <c r="K349" s="1" t="n">
+        <v>0.00565</v>
       </c>
     </row>
     <row r="350">
@@ -12343,9 +13393,12 @@
         <v>195.39</v>
       </c>
       <c r="I350" s="1" t="n">
+        <v>195.39</v>
+      </c>
+      <c r="J350" s="1" t="n">
         <v>195.51</v>
       </c>
-      <c r="J350" s="1" t="n">
+      <c r="K350" s="1" t="n">
         <v>195.23</v>
       </c>
     </row>
@@ -12377,9 +13430,12 @@
         <v>0.08236</v>
       </c>
       <c r="I351" s="1" t="n">
+        <v>0.08225</v>
+      </c>
+      <c r="J351" s="1" t="n">
         <v>0.08245</v>
       </c>
-      <c r="J351" s="1" t="n">
+      <c r="K351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -12411,9 +13467,12 @@
         <v>0.007498</v>
       </c>
       <c r="I352" s="1" t="n">
+        <v>0.007494</v>
+      </c>
+      <c r="J352" s="1" t="n">
         <v>0.007571</v>
       </c>
-      <c r="J352" s="1" t="n">
+      <c r="K352" s="1" t="n">
         <v>0.007458</v>
       </c>
     </row>
@@ -12445,9 +13504,12 @@
         <v>1.526</v>
       </c>
       <c r="I353" s="1" t="n">
+        <v>1.5093</v>
+      </c>
+      <c r="J353" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="J353" s="1" t="n">
+      <c r="K353" s="1" t="n">
         <v>1.4807</v>
       </c>
     </row>
@@ -12479,9 +13541,12 @@
         <v>0.07671</v>
       </c>
       <c r="I354" s="1" t="n">
+        <v>0.07664</v>
+      </c>
+      <c r="J354" s="1" t="n">
         <v>0.07671</v>
       </c>
-      <c r="J354" s="1" t="n">
+      <c r="K354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -12513,9 +13578,12 @@
         <v>0.04866</v>
       </c>
       <c r="I355" s="1" t="n">
+        <v>0.04889</v>
+      </c>
+      <c r="J355" s="1" t="n">
         <v>0.04921</v>
       </c>
-      <c r="J355" s="1" t="n">
+      <c r="K355" s="1" t="n">
         <v>0.04859</v>
       </c>
     </row>
@@ -12547,9 +13615,12 @@
         <v>0.2861</v>
       </c>
       <c r="I356" s="1" t="n">
-        <v>0.2861</v>
+        <v>0.2862</v>
       </c>
       <c r="J356" s="1" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="K356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -12581,9 +13652,12 @@
         <v>0.1468</v>
       </c>
       <c r="I357" s="1" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="J357" s="1" t="n">
         <v>0.1468</v>
       </c>
-      <c r="J357" s="1" t="n">
+      <c r="K357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -12615,9 +13689,12 @@
         <v>1.351</v>
       </c>
       <c r="I358" s="1" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="J358" s="1" t="n">
         <v>1.355</v>
       </c>
-      <c r="J358" s="1" t="n">
+      <c r="K358" s="1" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -12649,9 +13726,12 @@
         <v>0.6097</v>
       </c>
       <c r="I359" s="1" t="n">
+        <v>0.6096</v>
+      </c>
+      <c r="J359" s="1" t="n">
         <v>0.6117</v>
       </c>
-      <c r="J359" s="1" t="n">
+      <c r="K359" s="1" t="n">
         <v>0.6081</v>
       </c>
     </row>
@@ -12686,6 +13766,9 @@
         <v>0.1146</v>
       </c>
       <c r="J360" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="K360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -12717,9 +13800,12 @@
         <v>0.02641</v>
       </c>
       <c r="I361" s="1" t="n">
-        <v>0.02641</v>
+        <v>0.02648</v>
       </c>
       <c r="J361" s="1" t="n">
+        <v>0.02648</v>
+      </c>
+      <c r="K361" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -12751,9 +13837,12 @@
         <v>3.04e-05</v>
       </c>
       <c r="I362" s="1" t="n">
+        <v>3.03e-05</v>
+      </c>
+      <c r="J362" s="1" t="n">
         <v>3.04e-05</v>
       </c>
-      <c r="J362" s="1" t="n">
+      <c r="K362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -12785,9 +13874,12 @@
         <v>0.01024</v>
       </c>
       <c r="I363" s="1" t="n">
-        <v>0.01026</v>
+        <v>0.01047</v>
       </c>
       <c r="J363" s="1" t="n">
+        <v>0.01047</v>
+      </c>
+      <c r="K363" s="1" t="n">
         <v>0.01018</v>
       </c>
     </row>
@@ -12819,9 +13911,12 @@
         <v>0.06206</v>
       </c>
       <c r="I364" s="1" t="n">
+        <v>0.06211</v>
+      </c>
+      <c r="J364" s="1" t="n">
         <v>0.0622</v>
       </c>
-      <c r="J364" s="1" t="n">
+      <c r="K364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -12853,9 +13948,12 @@
         <v>0.03299</v>
       </c>
       <c r="I365" s="1" t="n">
+        <v>0.03291</v>
+      </c>
+      <c r="J365" s="1" t="n">
         <v>0.03299</v>
       </c>
-      <c r="J365" s="1" t="n">
+      <c r="K365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -12887,9 +13985,12 @@
         <v>0.03293</v>
       </c>
       <c r="I366" s="1" t="n">
-        <v>0.03296</v>
+        <v>0.03312</v>
       </c>
       <c r="J366" s="1" t="n">
+        <v>0.03312</v>
+      </c>
+      <c r="K366" s="1" t="n">
         <v>0.03283</v>
       </c>
     </row>
@@ -12921,9 +14022,12 @@
         <v>0.012269</v>
       </c>
       <c r="I367" s="1" t="n">
-        <v>0.012269</v>
+        <v>0.01231</v>
       </c>
       <c r="J367" s="1" t="n">
+        <v>0.01231</v>
+      </c>
+      <c r="K367" s="1" t="n">
         <v>0.012155</v>
       </c>
     </row>
@@ -12955,9 +14059,12 @@
         <v>0.03553</v>
       </c>
       <c r="I368" s="1" t="n">
-        <v>0.03559</v>
+        <v>0.03561</v>
       </c>
       <c r="J368" s="1" t="n">
+        <v>0.03561</v>
+      </c>
+      <c r="K368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -12989,9 +14096,12 @@
         <v>0.6302</v>
       </c>
       <c r="I369" s="1" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="J369" s="1" t="n">
         <v>0.6307</v>
       </c>
-      <c r="J369" s="1" t="n">
+      <c r="K369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -13023,9 +14133,12 @@
         <v>0.00882</v>
       </c>
       <c r="I370" s="1" t="n">
-        <v>0.00882</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J370" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="K370" s="1" t="n">
         <v>0.00843</v>
       </c>
     </row>
@@ -13057,9 +14170,12 @@
         <v>0.003331</v>
       </c>
       <c r="I371" s="1" t="n">
-        <v>0.003331</v>
+        <v>0.003918</v>
       </c>
       <c r="J371" s="1" t="n">
+        <v>0.003918</v>
+      </c>
+      <c r="K371" s="1" t="n">
         <v>0.003242</v>
       </c>
     </row>
@@ -13091,9 +14207,12 @@
         <v>0.13391</v>
       </c>
       <c r="I372" s="1" t="n">
+        <v>0.13358</v>
+      </c>
+      <c r="J372" s="1" t="n">
         <v>0.13391</v>
       </c>
-      <c r="J372" s="1" t="n">
+      <c r="K372" s="1" t="n">
         <v>0.13227</v>
       </c>
     </row>
@@ -13125,9 +14244,12 @@
         <v>0.007795</v>
       </c>
       <c r="I373" s="1" t="n">
+        <v>0.007786</v>
+      </c>
+      <c r="J373" s="1" t="n">
         <v>0.007822000000000001</v>
       </c>
-      <c r="J373" s="1" t="n">
+      <c r="K373" s="1" t="n">
         <v>0.007771</v>
       </c>
     </row>
@@ -13159,9 +14281,12 @@
         <v>0.01978</v>
       </c>
       <c r="I374" s="1" t="n">
-        <v>0.01978</v>
+        <v>0.01982</v>
       </c>
       <c r="J374" s="1" t="n">
+        <v>0.01982</v>
+      </c>
+      <c r="K374" s="1" t="n">
         <v>0.01969</v>
       </c>
     </row>
@@ -13193,9 +14318,12 @@
         <v>0.0005924</v>
       </c>
       <c r="I375" s="1" t="n">
+        <v>0.0005918</v>
+      </c>
+      <c r="J375" s="1" t="n">
         <v>0.000594</v>
       </c>
-      <c r="J375" s="1" t="n">
+      <c r="K375" s="1" t="n">
         <v>0.0005910000000000001</v>
       </c>
     </row>
@@ -13227,9 +14355,12 @@
         <v>0.0363</v>
       </c>
       <c r="I376" s="1" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="J376" s="1" t="n">
         <v>0.0363</v>
       </c>
-      <c r="J376" s="1" t="n">
+      <c r="K376" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -13261,9 +14392,12 @@
         <v>0.0007906</v>
       </c>
       <c r="I377" s="1" t="n">
-        <v>0.000792</v>
+        <v>0.0007921</v>
       </c>
       <c r="J377" s="1" t="n">
+        <v>0.0007921</v>
+      </c>
+      <c r="K377" s="1" t="n">
         <v>0.0007848</v>
       </c>
     </row>
@@ -13295,9 +14429,12 @@
         <v>2.022</v>
       </c>
       <c r="I378" s="1" t="n">
-        <v>2.022</v>
+        <v>2.034</v>
       </c>
       <c r="J378" s="1" t="n">
+        <v>2.034</v>
+      </c>
+      <c r="K378" s="1" t="n">
         <v>1.973</v>
       </c>
     </row>
@@ -13329,9 +14466,12 @@
         <v>0.00059</v>
       </c>
       <c r="I379" s="1" t="n">
+        <v>0.0005903</v>
+      </c>
+      <c r="J379" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="J379" s="1" t="n">
+      <c r="K379" s="1" t="n">
         <v>0.0005881</v>
       </c>
     </row>
@@ -13363,9 +14503,12 @@
         <v>0.03745</v>
       </c>
       <c r="I380" s="1" t="n">
+        <v>0.03749</v>
+      </c>
+      <c r="J380" s="1" t="n">
         <v>0.03751</v>
       </c>
-      <c r="J380" s="1" t="n">
+      <c r="K380" s="1" t="n">
         <v>0.03737</v>
       </c>
     </row>
@@ -13397,9 +14540,12 @@
         <v>0.05476</v>
       </c>
       <c r="I381" s="1" t="n">
+        <v>0.05474</v>
+      </c>
+      <c r="J381" s="1" t="n">
         <v>0.05481</v>
       </c>
-      <c r="J381" s="1" t="n">
+      <c r="K381" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -13431,9 +14577,12 @@
         <v>0.01209</v>
       </c>
       <c r="I382" s="1" t="n">
+        <v>0.01209</v>
+      </c>
+      <c r="J382" s="1" t="n">
         <v>0.01213</v>
       </c>
-      <c r="J382" s="1" t="n">
+      <c r="K382" s="1" t="n">
         <v>0.01202</v>
       </c>
     </row>
@@ -13465,10 +14614,13 @@
         <v>0.001553</v>
       </c>
       <c r="I383" s="1" t="n">
+        <v>0.001549</v>
+      </c>
+      <c r="J383" s="1" t="n">
         <v>0.001559</v>
       </c>
-      <c r="J383" s="1" t="n">
-        <v>0.001551</v>
+      <c r="K383" s="1" t="n">
+        <v>0.001549</v>
       </c>
     </row>
     <row r="384">
@@ -13502,6 +14654,9 @@
         <v>0.0002164</v>
       </c>
       <c r="J384" s="1" t="n">
+        <v>0.0002164</v>
+      </c>
+      <c r="K384" s="1" t="n">
         <v>0.0002154</v>
       </c>
     </row>
@@ -13533,9 +14688,12 @@
         <v>0.00242</v>
       </c>
       <c r="I385" s="1" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="J385" s="1" t="n">
         <v>0.00242</v>
       </c>
-      <c r="J385" s="1" t="n">
+      <c r="K385" s="1" t="n">
         <v>0.0024</v>
       </c>
     </row>
@@ -13567,9 +14725,12 @@
         <v>3.929</v>
       </c>
       <c r="I386" s="1" t="n">
+        <v>3.928</v>
+      </c>
+      <c r="J386" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="J386" s="1" t="n">
+      <c r="K386" s="1" t="n">
         <v>3.892</v>
       </c>
     </row>
@@ -13601,9 +14762,12 @@
         <v>0.0006275</v>
       </c>
       <c r="I387" s="1" t="n">
+        <v>0.0006281</v>
+      </c>
+      <c r="J387" s="1" t="n">
         <v>0.0006282</v>
       </c>
-      <c r="J387" s="1" t="n">
+      <c r="K387" s="1" t="n">
         <v>0.0006236</v>
       </c>
     </row>
@@ -13635,9 +14799,12 @@
         <v>0.00667</v>
       </c>
       <c r="I388" s="1" t="n">
+        <v>0.00655</v>
+      </c>
+      <c r="J388" s="1" t="n">
         <v>0.00673</v>
       </c>
-      <c r="J388" s="1" t="n">
+      <c r="K388" s="1" t="n">
         <v>0.00653</v>
       </c>
     </row>
@@ -13669,9 +14836,12 @@
         <v>0.132</v>
       </c>
       <c r="I389" s="1" t="n">
-        <v>0.132</v>
+        <v>0.1321</v>
       </c>
       <c r="J389" s="1" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="K389" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -13703,9 +14873,12 @@
         <v>0.03222</v>
       </c>
       <c r="I390" s="1" t="n">
-        <v>0.0324</v>
+        <v>0.03248</v>
       </c>
       <c r="J390" s="1" t="n">
+        <v>0.03248</v>
+      </c>
+      <c r="K390" s="1" t="n">
         <v>0.03201</v>
       </c>
     </row>
@@ -13737,9 +14910,12 @@
         <v>0.06364</v>
       </c>
       <c r="I391" s="1" t="n">
-        <v>0.06372</v>
+        <v>0.06375</v>
       </c>
       <c r="J391" s="1" t="n">
+        <v>0.06375</v>
+      </c>
+      <c r="K391" s="1" t="n">
         <v>0.06344</v>
       </c>
     </row>
@@ -13771,9 +14947,12 @@
         <v>27.7</v>
       </c>
       <c r="I392" s="1" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="J392" s="1" t="n">
         <v>27.82</v>
       </c>
-      <c r="J392" s="1" t="n">
+      <c r="K392" s="1" t="n">
         <v>27.57</v>
       </c>
     </row>
@@ -13808,6 +14987,9 @@
         <v>0.000414</v>
       </c>
       <c r="J393" s="1" t="n">
+        <v>0.000414</v>
+      </c>
+      <c r="K393" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -13839,9 +15021,12 @@
         <v>0.06952999999999999</v>
       </c>
       <c r="I394" s="1" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="J394" s="1" t="n">
         <v>0.07005</v>
       </c>
-      <c r="J394" s="1" t="n">
+      <c r="K394" s="1" t="n">
         <v>0.06926</v>
       </c>
     </row>
@@ -13876,6 +15061,9 @@
         <v>0.2614</v>
       </c>
       <c r="J395" s="1" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="K395" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -13907,9 +15095,12 @@
         <v>0.004683</v>
       </c>
       <c r="I396" s="1" t="n">
+        <v>0.004682</v>
+      </c>
+      <c r="J396" s="1" t="n">
         <v>0.00469</v>
       </c>
-      <c r="J396" s="1" t="n">
+      <c r="K396" s="1" t="n">
         <v>0.004677</v>
       </c>
     </row>
@@ -13941,9 +15132,12 @@
         <v>0.2351</v>
       </c>
       <c r="I397" s="1" t="n">
-        <v>0.2352</v>
+        <v>0.2356</v>
       </c>
       <c r="J397" s="1" t="n">
+        <v>0.2356</v>
+      </c>
+      <c r="K397" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
@@ -13975,9 +15169,12 @@
         <v>0.18128</v>
       </c>
       <c r="I398" s="1" t="n">
-        <v>0.18131</v>
+        <v>0.18172</v>
       </c>
       <c r="J398" s="1" t="n">
+        <v>0.18172</v>
+      </c>
+      <c r="K398" s="1" t="n">
         <v>0.18106</v>
       </c>
     </row>
@@ -14009,9 +15206,12 @@
         <v>0.04125</v>
       </c>
       <c r="I399" s="1" t="n">
-        <v>0.04126</v>
+        <v>0.0414</v>
       </c>
       <c r="J399" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="K399" s="1" t="n">
         <v>0.04108</v>
       </c>
     </row>
@@ -14043,9 +15243,12 @@
         <v>0.075</v>
       </c>
       <c r="I400" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J400" s="1" t="n">
         <v>0.076</v>
       </c>
-      <c r="J400" s="1" t="n">
+      <c r="K400" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -14077,9 +15280,12 @@
         <v>0.001766</v>
       </c>
       <c r="I401" s="1" t="n">
+        <v>0.001763</v>
+      </c>
+      <c r="J401" s="1" t="n">
         <v>0.001766</v>
       </c>
-      <c r="J401" s="1" t="n">
+      <c r="K401" s="1" t="n">
         <v>0.001739</v>
       </c>
     </row>
@@ -14111,9 +15317,12 @@
         <v>0.05398</v>
       </c>
       <c r="I402" s="1" t="n">
+        <v>0.05391</v>
+      </c>
+      <c r="J402" s="1" t="n">
         <v>0.05401</v>
       </c>
-      <c r="J402" s="1" t="n">
+      <c r="K402" s="1" t="n">
         <v>0.05362</v>
       </c>
     </row>
@@ -14145,9 +15354,12 @@
         <v>2026.65</v>
       </c>
       <c r="I403" s="1" t="n">
+        <v>2028.66</v>
+      </c>
+      <c r="J403" s="1" t="n">
         <v>2031.8</v>
       </c>
-      <c r="J403" s="1" t="n">
+      <c r="K403" s="1" t="n">
         <v>2026.65</v>
       </c>
     </row>
@@ -14179,9 +15391,12 @@
         <v>1.082</v>
       </c>
       <c r="I404" s="1" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J404" s="1" t="n">
         <v>1.082</v>
       </c>
-      <c r="J404" s="1" t="n">
+      <c r="K404" s="1" t="n">
         <v>1.078</v>
       </c>
     </row>
@@ -14213,9 +15428,12 @@
         <v>7.662</v>
       </c>
       <c r="I405" s="1" t="n">
-        <v>7.662</v>
+        <v>7.673</v>
       </c>
       <c r="J405" s="1" t="n">
+        <v>7.673</v>
+      </c>
+      <c r="K405" s="1" t="n">
         <v>7.649</v>
       </c>
     </row>
@@ -14247,9 +15465,12 @@
         <v>3.25</v>
       </c>
       <c r="I406" s="1" t="n">
+        <v>3.254</v>
+      </c>
+      <c r="J406" s="1" t="n">
         <v>3.257</v>
       </c>
-      <c r="J406" s="1" t="n">
+      <c r="K406" s="1" t="n">
         <v>3.238</v>
       </c>
     </row>
@@ -14281,9 +15502,12 @@
         <v>0.1823</v>
       </c>
       <c r="I407" s="1" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="J407" s="1" t="n">
         <v>0.1823</v>
       </c>
-      <c r="J407" s="1" t="n">
+      <c r="K407" s="1" t="n">
         <v>0.1814</v>
       </c>
     </row>
@@ -14315,9 +15539,12 @@
         <v>0.1526</v>
       </c>
       <c r="I408" s="1" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="J408" s="1" t="n">
         <v>0.1537</v>
       </c>
-      <c r="J408" s="1" t="n">
+      <c r="K408" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -14349,9 +15576,12 @@
         <v>0.07349</v>
       </c>
       <c r="I409" s="1" t="n">
-        <v>0.0735</v>
+        <v>0.07369000000000001</v>
       </c>
       <c r="J409" s="1" t="n">
+        <v>0.07369000000000001</v>
+      </c>
+      <c r="K409" s="1" t="n">
         <v>0.07315000000000001</v>
       </c>
     </row>
@@ -14383,9 +15613,12 @@
         <v>0.02101</v>
       </c>
       <c r="I410" s="1" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="J410" s="1" t="n">
         <v>0.02118</v>
       </c>
-      <c r="J410" s="1" t="n">
+      <c r="K410" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -14417,9 +15650,12 @@
         <v>0.2675</v>
       </c>
       <c r="I411" s="1" t="n">
-        <v>0.2675</v>
+        <v>0.2683</v>
       </c>
       <c r="J411" s="1" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="K411" s="1" t="n">
         <v>0.2642</v>
       </c>
     </row>
@@ -14451,9 +15687,12 @@
         <v>0.00737</v>
       </c>
       <c r="I412" s="1" t="n">
+        <v>0.007358</v>
+      </c>
+      <c r="J412" s="1" t="n">
         <v>0.007383</v>
       </c>
-      <c r="J412" s="1" t="n">
+      <c r="K412" s="1" t="n">
         <v>0.007302</v>
       </c>
     </row>
@@ -14485,9 +15724,12 @@
         <v>0.01389</v>
       </c>
       <c r="I413" s="1" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="J413" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="J413" s="1" t="n">
+      <c r="K413" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -14522,6 +15764,9 @@
         <v>0.093</v>
       </c>
       <c r="J414" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K414" s="1" t="n">
         <v>0.092</v>
       </c>
     </row>
@@ -14553,9 +15798,12 @@
         <v>0.03992</v>
       </c>
       <c r="I415" s="1" t="n">
+        <v>0.04009</v>
+      </c>
+      <c r="J415" s="1" t="n">
         <v>0.04012</v>
       </c>
-      <c r="J415" s="1" t="n">
+      <c r="K415" s="1" t="n">
         <v>0.03985</v>
       </c>
     </row>
@@ -14587,10 +15835,13 @@
         <v>0.284</v>
       </c>
       <c r="I416" s="1" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="J416" s="1" t="n">
         <v>0.2854</v>
       </c>
-      <c r="J416" s="1" t="n">
-        <v>0.284</v>
+      <c r="K416" s="1" t="n">
+        <v>0.2839</v>
       </c>
     </row>
     <row r="417">
@@ -14621,9 +15872,12 @@
         <v>1.828</v>
       </c>
       <c r="I417" s="1" t="n">
+        <v>1.828</v>
+      </c>
+      <c r="J417" s="1" t="n">
         <v>1.831</v>
       </c>
-      <c r="J417" s="1" t="n">
+      <c r="K417" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -14655,9 +15909,12 @@
         <v>0.06697</v>
       </c>
       <c r="I418" s="1" t="n">
+        <v>0.06704</v>
+      </c>
+      <c r="J418" s="1" t="n">
         <v>0.06707</v>
       </c>
-      <c r="J418" s="1" t="n">
+      <c r="K418" s="1" t="n">
         <v>0.06668</v>
       </c>
     </row>
@@ -14689,9 +15946,12 @@
         <v>207.36</v>
       </c>
       <c r="I419" s="1" t="n">
+        <v>207.39</v>
+      </c>
+      <c r="J419" s="1" t="n">
         <v>207.46</v>
       </c>
-      <c r="J419" s="1" t="n">
+      <c r="K419" s="1" t="n">
         <v>207.35</v>
       </c>
     </row>
@@ -14723,9 +15983,12 @@
         <v>73.27</v>
       </c>
       <c r="I420" s="1" t="n">
+        <v>73.27</v>
+      </c>
+      <c r="J420" s="1" t="n">
         <v>73.31999999999999</v>
       </c>
-      <c r="J420" s="1" t="n">
+      <c r="K420" s="1" t="n">
         <v>73.15000000000001</v>
       </c>
     </row>
@@ -14757,9 +16020,12 @@
         <v>0.07231</v>
       </c>
       <c r="I421" s="1" t="n">
+        <v>0.07232</v>
+      </c>
+      <c r="J421" s="1" t="n">
         <v>0.07251000000000001</v>
       </c>
-      <c r="J421" s="1" t="n">
+      <c r="K421" s="1" t="n">
         <v>0.07226</v>
       </c>
     </row>
@@ -14791,9 +16057,12 @@
         <v>0.05071</v>
       </c>
       <c r="I422" s="1" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="J422" s="1" t="n">
         <v>0.05076</v>
       </c>
-      <c r="J422" s="1" t="n">
+      <c r="K422" s="1" t="n">
         <v>0.04998</v>
       </c>
     </row>
@@ -14825,9 +16094,12 @@
         <v>0.001152</v>
       </c>
       <c r="I423" s="1" t="n">
+        <v>0.001151</v>
+      </c>
+      <c r="J423" s="1" t="n">
         <v>0.001152</v>
       </c>
-      <c r="J423" s="1" t="n">
+      <c r="K423" s="1" t="n">
         <v>0.001148</v>
       </c>
     </row>
@@ -14859,9 +16131,12 @@
         <v>0.00502</v>
       </c>
       <c r="I424" s="1" t="n">
+        <v>0.00502</v>
+      </c>
+      <c r="J424" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="J424" s="1" t="n">
+      <c r="K424" s="1" t="n">
         <v>0.00501</v>
       </c>
     </row>
@@ -14893,9 +16168,12 @@
         <v>0.1273</v>
       </c>
       <c r="I425" s="1" t="n">
+        <v>0.1272</v>
+      </c>
+      <c r="J425" s="1" t="n">
         <v>0.1274</v>
       </c>
-      <c r="J425" s="1" t="n">
+      <c r="K425" s="1" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -14927,9 +16205,12 @@
         <v>1.295</v>
       </c>
       <c r="I426" s="1" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="J426" s="1" t="n">
         <v>1.299</v>
       </c>
-      <c r="J426" s="1" t="n">
+      <c r="K426" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -14961,9 +16242,12 @@
         <v>0.004402</v>
       </c>
       <c r="I427" s="1" t="n">
+        <v>0.004408</v>
+      </c>
+      <c r="J427" s="1" t="n">
         <v>0.004413</v>
       </c>
-      <c r="J427" s="1" t="n">
+      <c r="K427" s="1" t="n">
         <v>0.004393</v>
       </c>
     </row>
@@ -14995,9 +16279,12 @@
         <v>0.005044</v>
       </c>
       <c r="I428" s="1" t="n">
+        <v>0.005045</v>
+      </c>
+      <c r="J428" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="J428" s="1" t="n">
+      <c r="K428" s="1" t="n">
         <v>0.005017</v>
       </c>
     </row>
@@ -15029,9 +16316,12 @@
         <v>0.02313</v>
       </c>
       <c r="I429" s="1" t="n">
+        <v>0.02316</v>
+      </c>
+      <c r="J429" s="1" t="n">
         <v>0.02329</v>
       </c>
-      <c r="J429" s="1" t="n">
+      <c r="K429" s="1" t="n">
         <v>0.02288</v>
       </c>
     </row>
@@ -15063,10 +16353,13 @@
         <v>0.0251</v>
       </c>
       <c r="I430" s="1" t="n">
+        <v>0.02499</v>
+      </c>
+      <c r="J430" s="1" t="n">
         <v>0.02517</v>
       </c>
-      <c r="J430" s="1" t="n">
-        <v>0.02501</v>
+      <c r="K430" s="1" t="n">
+        <v>0.02499</v>
       </c>
     </row>
     <row r="431">
@@ -15100,6 +16393,9 @@
         <v>0.016</v>
       </c>
       <c r="J431" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="K431" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -15131,9 +16427,12 @@
         <v>0.5447</v>
       </c>
       <c r="I432" s="1" t="n">
+        <v>0.5443</v>
+      </c>
+      <c r="J432" s="1" t="n">
         <v>0.546</v>
       </c>
-      <c r="J432" s="1" t="n">
+      <c r="K432" s="1" t="n">
         <v>0.5439000000000001</v>
       </c>
     </row>
@@ -15165,9 +16464,12 @@
         <v>0.001389</v>
       </c>
       <c r="I433" s="1" t="n">
+        <v>0.001385</v>
+      </c>
+      <c r="J433" s="1" t="n">
         <v>0.001389</v>
       </c>
-      <c r="J433" s="1" t="n">
+      <c r="K433" s="1" t="n">
         <v>0.001383</v>
       </c>
     </row>
@@ -15199,9 +16501,12 @@
         <v>0.397</v>
       </c>
       <c r="I434" s="1" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="J434" s="1" t="n">
         <v>0.397</v>
       </c>
-      <c r="J434" s="1" t="n">
+      <c r="K434" s="1" t="n">
         <v>0.3925</v>
       </c>
     </row>
@@ -15233,10 +16538,13 @@
         <v>0.00139</v>
       </c>
       <c r="I435" s="1" t="n">
+        <v>0.001388</v>
+      </c>
+      <c r="J435" s="1" t="n">
         <v>0.001393</v>
       </c>
-      <c r="J435" s="1" t="n">
-        <v>0.001389</v>
+      <c r="K435" s="1" t="n">
+        <v>0.001388</v>
       </c>
     </row>
     <row r="436">
@@ -15267,9 +16575,12 @@
         <v>0.00717</v>
       </c>
       <c r="I436" s="1" t="n">
+        <v>0.00717</v>
+      </c>
+      <c r="J436" s="1" t="n">
         <v>0.00718</v>
       </c>
-      <c r="J436" s="1" t="n">
+      <c r="K436" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -15301,9 +16612,12 @@
         <v>0.001994</v>
       </c>
       <c r="I437" s="1" t="n">
-        <v>0.001997</v>
+        <v>0.002003</v>
       </c>
       <c r="J437" s="1" t="n">
+        <v>0.002003</v>
+      </c>
+      <c r="K437" s="1" t="n">
         <v>0.001982</v>
       </c>
     </row>
@@ -15335,9 +16649,12 @@
         <v>0.3137</v>
       </c>
       <c r="I438" s="1" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="J438" s="1" t="n">
         <v>0.3147</v>
       </c>
-      <c r="J438" s="1" t="n">
+      <c r="K438" s="1" t="n">
         <v>0.3122</v>
       </c>
     </row>
@@ -15369,9 +16686,12 @@
         <v>0.04438</v>
       </c>
       <c r="I439" s="1" t="n">
+        <v>0.04429</v>
+      </c>
+      <c r="J439" s="1" t="n">
         <v>0.04438</v>
       </c>
-      <c r="J439" s="1" t="n">
+      <c r="K439" s="1" t="n">
         <v>0.04426</v>
       </c>
     </row>
@@ -15406,6 +16726,9 @@
         <v>0.911</v>
       </c>
       <c r="J440" s="1" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="K440" s="1" t="n">
         <v>0.906</v>
       </c>
     </row>
@@ -15437,9 +16760,12 @@
         <v>1552.1</v>
       </c>
       <c r="I441" s="1" t="n">
-        <v>1552.1</v>
+        <v>1552.4</v>
       </c>
       <c r="J441" s="1" t="n">
+        <v>1552.4</v>
+      </c>
+      <c r="K441" s="1" t="n">
         <v>1548.06</v>
       </c>
     </row>
@@ -15471,9 +16797,12 @@
         <v>0.0007972</v>
       </c>
       <c r="I442" s="1" t="n">
+        <v>0.0007976</v>
+      </c>
+      <c r="J442" s="1" t="n">
         <v>0.0008032</v>
       </c>
-      <c r="J442" s="1" t="n">
+      <c r="K442" s="1" t="n">
         <v>0.0007877</v>
       </c>
     </row>
@@ -15505,9 +16834,12 @@
         <v>0.003515</v>
       </c>
       <c r="I443" s="1" t="n">
+        <v>0.003518</v>
+      </c>
+      <c r="J443" s="1" t="n">
         <v>0.003558</v>
       </c>
-      <c r="J443" s="1" t="n">
+      <c r="K443" s="1" t="n">
         <v>0.003515</v>
       </c>
     </row>
@@ -15539,9 +16871,12 @@
         <v>1.982</v>
       </c>
       <c r="I444" s="1" t="n">
+        <v>1.986</v>
+      </c>
+      <c r="J444" s="1" t="n">
         <v>1.989</v>
       </c>
-      <c r="J444" s="1" t="n">
+      <c r="K444" s="1" t="n">
         <v>1.977</v>
       </c>
     </row>
@@ -15573,9 +16908,12 @@
         <v>1.308</v>
       </c>
       <c r="I445" s="1" t="n">
-        <v>1.31</v>
+        <v>1.311</v>
       </c>
       <c r="J445" s="1" t="n">
+        <v>1.311</v>
+      </c>
+      <c r="K445" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -15607,9 +16945,12 @@
         <v>0.06905</v>
       </c>
       <c r="I446" s="1" t="n">
+        <v>0.06907000000000001</v>
+      </c>
+      <c r="J446" s="1" t="n">
         <v>0.06929</v>
       </c>
-      <c r="J446" s="1" t="n">
+      <c r="K446" s="1" t="n">
         <v>0.0689</v>
       </c>
     </row>
@@ -15641,9 +16982,12 @@
         <v>0.02403</v>
       </c>
       <c r="I447" s="1" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="J447" s="1" t="n">
         <v>0.02403</v>
       </c>
-      <c r="J447" s="1" t="n">
+      <c r="K447" s="1" t="n">
         <v>0.02347</v>
       </c>
     </row>
@@ -15675,9 +17019,12 @@
         <v>0.01399</v>
       </c>
       <c r="I448" s="1" t="n">
-        <v>0.014</v>
+        <v>0.01403</v>
       </c>
       <c r="J448" s="1" t="n">
+        <v>0.01403</v>
+      </c>
+      <c r="K448" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -15709,9 +17056,12 @@
         <v>3.732</v>
       </c>
       <c r="I449" s="1" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="J449" s="1" t="n">
         <v>3.734</v>
       </c>
-      <c r="J449" s="1" t="n">
+      <c r="K449" s="1" t="n">
         <v>3.726</v>
       </c>
     </row>
@@ -15743,10 +17093,13 @@
         <v>0.0114</v>
       </c>
       <c r="I450" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="J450" s="1" t="n">
         <v>0.0115</v>
       </c>
-      <c r="J450" s="1" t="n">
-        <v>0.0114</v>
+      <c r="K450" s="1" t="n">
+        <v>0.0113</v>
       </c>
     </row>
     <row r="451">
@@ -15780,6 +17133,9 @@
         <v>0.01034</v>
       </c>
       <c r="J451" s="1" t="n">
+        <v>0.01034</v>
+      </c>
+      <c r="K451" s="1" t="n">
         <v>0.01024</v>
       </c>
     </row>
@@ -15811,9 +17167,12 @@
         <v>0.1525</v>
       </c>
       <c r="I452" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="J452" s="1" t="n">
         <v>0.1532</v>
       </c>
-      <c r="J452" s="1" t="n">
+      <c r="K452" s="1" t="n">
         <v>0.1522</v>
       </c>
     </row>
@@ -15845,9 +17204,12 @@
         <v>151.19</v>
       </c>
       <c r="I453" s="1" t="n">
+        <v>151.15</v>
+      </c>
+      <c r="J453" s="1" t="n">
         <v>151.19</v>
       </c>
-      <c r="J453" s="1" t="n">
+      <c r="K453" s="1" t="n">
         <v>150.85</v>
       </c>
     </row>
@@ -15879,9 +17241,12 @@
         <v>0.008626</v>
       </c>
       <c r="I454" s="1" t="n">
+        <v>0.008630000000000001</v>
+      </c>
+      <c r="J454" s="1" t="n">
         <v>0.008633</v>
       </c>
-      <c r="J454" s="1" t="n">
+      <c r="K454" s="1" t="n">
         <v>0.008593999999999999</v>
       </c>
     </row>
@@ -15916,6 +17281,9 @@
         <v>0.05255</v>
       </c>
       <c r="J455" s="1" t="n">
+        <v>0.05255</v>
+      </c>
+      <c r="K455" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -15947,9 +17315,12 @@
         <v>0.30623</v>
       </c>
       <c r="I456" s="1" t="n">
-        <v>0.30782</v>
+        <v>0.30925</v>
       </c>
       <c r="J456" s="1" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="K456" s="1" t="n">
         <v>0.30269</v>
       </c>
     </row>
@@ -15984,6 +17355,9 @@
         <v>0.00547</v>
       </c>
       <c r="J457" s="1" t="n">
+        <v>0.00547</v>
+      </c>
+      <c r="K457" s="1" t="n">
         <v>0.00544</v>
       </c>
     </row>
@@ -16015,9 +17389,12 @@
         <v>0.1003</v>
       </c>
       <c r="I458" s="1" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="J458" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="J458" s="1" t="n">
+      <c r="K458" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -16052,6 +17429,9 @@
         <v>0.001835</v>
       </c>
       <c r="J459" s="1" t="n">
+        <v>0.001835</v>
+      </c>
+      <c r="K459" s="1" t="n">
         <v>0.001825</v>
       </c>
     </row>
@@ -16083,9 +17463,12 @@
         <v>0.01845</v>
       </c>
       <c r="I460" s="1" t="n">
+        <v>0.01839</v>
+      </c>
+      <c r="J460" s="1" t="n">
         <v>0.01848</v>
       </c>
-      <c r="J460" s="1" t="n">
+      <c r="K460" s="1" t="n">
         <v>0.01822</v>
       </c>
     </row>
@@ -16117,9 +17500,12 @@
         <v>0.0004842</v>
       </c>
       <c r="I461" s="1" t="n">
+        <v>0.0004859</v>
+      </c>
+      <c r="J461" s="1" t="n">
         <v>0.0004877</v>
       </c>
-      <c r="J461" s="1" t="n">
+      <c r="K461" s="1" t="n">
         <v>0.0004842</v>
       </c>
     </row>
@@ -16151,9 +17537,12 @@
         <v>0.0961</v>
       </c>
       <c r="I462" s="1" t="n">
-        <v>0.0961</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="J462" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="K462" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -16185,9 +17574,12 @@
         <v>0.07922999999999999</v>
       </c>
       <c r="I463" s="1" t="n">
+        <v>0.07915</v>
+      </c>
+      <c r="J463" s="1" t="n">
         <v>0.07931000000000001</v>
       </c>
-      <c r="J463" s="1" t="n">
+      <c r="K463" s="1" t="n">
         <v>0.07888000000000001</v>
       </c>
     </row>
@@ -16219,9 +17611,12 @@
         <v>0.03207</v>
       </c>
       <c r="I464" s="1" t="n">
+        <v>0.03198</v>
+      </c>
+      <c r="J464" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="J464" s="1" t="n">
+      <c r="K464" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -16253,9 +17648,12 @@
         <v>0.01615</v>
       </c>
       <c r="I465" s="1" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="J465" s="1" t="n">
         <v>0.01618</v>
       </c>
-      <c r="J465" s="1" t="n">
+      <c r="K465" s="1" t="n">
         <v>0.01613</v>
       </c>
     </row>
@@ -16287,9 +17685,12 @@
         <v>0.06777</v>
       </c>
       <c r="I466" s="1" t="n">
-        <v>0.06781</v>
+        <v>0.06786</v>
       </c>
       <c r="J466" s="1" t="n">
+        <v>0.06786</v>
+      </c>
+      <c r="K466" s="1" t="n">
         <v>0.06763</v>
       </c>
     </row>
@@ -16324,6 +17725,9 @@
         <v>0.04332</v>
       </c>
       <c r="J467" s="1" t="n">
+        <v>0.04332</v>
+      </c>
+      <c r="K467" s="1" t="n">
         <v>0.04322</v>
       </c>
     </row>
@@ -16355,9 +17759,12 @@
         <v>0.05595</v>
       </c>
       <c r="I468" s="1" t="n">
+        <v>0.05617</v>
+      </c>
+      <c r="J468" s="1" t="n">
         <v>0.05795</v>
       </c>
-      <c r="J468" s="1" t="n">
+      <c r="K468" s="1" t="n">
         <v>0.05587</v>
       </c>
     </row>
@@ -16392,6 +17799,9 @@
         <v>0.2309</v>
       </c>
       <c r="J469" s="1" t="n">
+        <v>0.2309</v>
+      </c>
+      <c r="K469" s="1" t="n">
         <v>0.2294</v>
       </c>
     </row>
@@ -16423,9 +17833,12 @@
         <v>0.0905</v>
       </c>
       <c r="I470" s="1" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="J470" s="1" t="n">
         <v>0.0905</v>
       </c>
-      <c r="J470" s="1" t="n">
+      <c r="K470" s="1" t="n">
         <v>0.0902</v>
       </c>
     </row>
@@ -16457,9 +17870,12 @@
         <v>0.06665</v>
       </c>
       <c r="I471" s="1" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="J471" s="1" t="n">
         <v>0.0669</v>
       </c>
-      <c r="J471" s="1" t="n">
+      <c r="K471" s="1" t="n">
         <v>0.06660000000000001</v>
       </c>
     </row>
@@ -16491,9 +17907,12 @@
         <v>6.563</v>
       </c>
       <c r="I472" s="1" t="n">
-        <v>6.563</v>
+        <v>6.593</v>
       </c>
       <c r="J472" s="1" t="n">
+        <v>6.593</v>
+      </c>
+      <c r="K472" s="1" t="n">
         <v>6.486</v>
       </c>
     </row>
@@ -16525,9 +17944,12 @@
         <v>0.01944</v>
       </c>
       <c r="I473" s="1" t="n">
+        <v>0.01942</v>
+      </c>
+      <c r="J473" s="1" t="n">
         <v>0.01945</v>
       </c>
-      <c r="J473" s="1" t="n">
+      <c r="K473" s="1" t="n">
         <v>0.01937</v>
       </c>
     </row>
@@ -16559,9 +17981,12 @@
         <v>1.423</v>
       </c>
       <c r="I474" s="1" t="n">
-        <v>1.423</v>
+        <v>1.426</v>
       </c>
       <c r="J474" s="1" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="K474" s="1" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -16596,6 +18021,9 @@
         <v>0.08981</v>
       </c>
       <c r="J475" s="1" t="n">
+        <v>0.08981</v>
+      </c>
+      <c r="K475" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -16627,9 +18055,12 @@
         <v>0.1062</v>
       </c>
       <c r="I476" s="1" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="J476" s="1" t="n">
         <v>0.1062</v>
       </c>
-      <c r="J476" s="1" t="n">
+      <c r="K476" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -16661,9 +18092,12 @@
         <v>0.09421</v>
       </c>
       <c r="I477" s="1" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="J477" s="1" t="n">
         <v>0.09451</v>
       </c>
-      <c r="J477" s="1" t="n">
+      <c r="K477" s="1" t="n">
         <v>0.0941</v>
       </c>
     </row>
@@ -16695,9 +18129,12 @@
         <v>0.000163</v>
       </c>
       <c r="I478" s="1" t="n">
-        <v>0.000163</v>
+        <v>0.0001633</v>
       </c>
       <c r="J478" s="1" t="n">
+        <v>0.0001633</v>
+      </c>
+      <c r="K478" s="1" t="n">
         <v>0.0001624</v>
       </c>
     </row>
@@ -16732,6 +18169,9 @@
         <v>0.04023</v>
       </c>
       <c r="J479" s="1" t="n">
+        <v>0.04023</v>
+      </c>
+      <c r="K479" s="1" t="n">
         <v>0.04007</v>
       </c>
     </row>
@@ -16763,9 +18203,12 @@
         <v>0.007425</v>
       </c>
       <c r="I480" s="1" t="n">
+        <v>0.007422</v>
+      </c>
+      <c r="J480" s="1" t="n">
         <v>0.007425</v>
       </c>
-      <c r="J480" s="1" t="n">
+      <c r="K480" s="1" t="n">
         <v>0.007389</v>
       </c>
     </row>
@@ -16797,10 +18240,13 @@
         <v>0.0954</v>
       </c>
       <c r="I481" s="1" t="n">
+        <v>0.0953</v>
+      </c>
+      <c r="J481" s="1" t="n">
         <v>0.0955</v>
       </c>
-      <c r="J481" s="1" t="n">
-        <v>0.0954</v>
+      <c r="K481" s="1" t="n">
+        <v>0.0953</v>
       </c>
     </row>
     <row r="482">
@@ -16831,9 +18277,12 @@
         <v>0.0561</v>
       </c>
       <c r="I482" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="J482" s="1" t="n">
         <v>0.05621</v>
       </c>
-      <c r="J482" s="1" t="n">
+      <c r="K482" s="1" t="n">
         <v>0.05569</v>
       </c>
     </row>
@@ -16865,9 +18314,12 @@
         <v>0.006189</v>
       </c>
       <c r="I483" s="1" t="n">
+        <v>0.006173</v>
+      </c>
+      <c r="J483" s="1" t="n">
         <v>0.006198</v>
       </c>
-      <c r="J483" s="1" t="n">
+      <c r="K483" s="1" t="n">
         <v>0.006161</v>
       </c>
     </row>
@@ -16899,9 +18351,12 @@
         <v>0.01494</v>
       </c>
       <c r="I484" s="1" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="J484" s="1" t="n">
         <v>0.01497</v>
       </c>
-      <c r="J484" s="1" t="n">
+      <c r="K484" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -16933,9 +18388,12 @@
         <v>0.02412</v>
       </c>
       <c r="I485" s="1" t="n">
+        <v>0.02408</v>
+      </c>
+      <c r="J485" s="1" t="n">
         <v>0.02427</v>
       </c>
-      <c r="J485" s="1" t="n">
+      <c r="K485" s="1" t="n">
         <v>0.02403</v>
       </c>
     </row>
@@ -16967,9 +18425,12 @@
         <v>0.06688</v>
       </c>
       <c r="I486" s="1" t="n">
+        <v>0.06696000000000001</v>
+      </c>
+      <c r="J486" s="1" t="n">
         <v>0.06702</v>
       </c>
-      <c r="J486" s="1" t="n">
+      <c r="K486" s="1" t="n">
         <v>0.0667</v>
       </c>
     </row>
@@ -17001,9 +18462,12 @@
         <v>0.03692</v>
       </c>
       <c r="I487" s="1" t="n">
+        <v>0.03692</v>
+      </c>
+      <c r="J487" s="1" t="n">
         <v>0.03705</v>
       </c>
-      <c r="J487" s="1" t="n">
+      <c r="K487" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -17035,9 +18499,12 @@
         <v>0.01817</v>
       </c>
       <c r="I488" s="1" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="J488" s="1" t="n">
         <v>0.0182</v>
       </c>
-      <c r="J488" s="1" t="n">
+      <c r="K488" s="1" t="n">
         <v>0.01814</v>
       </c>
     </row>
@@ -17069,9 +18536,12 @@
         <v>0.03253</v>
       </c>
       <c r="I489" s="1" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="J489" s="1" t="n">
         <v>0.03278</v>
       </c>
-      <c r="J489" s="1" t="n">
+      <c r="K489" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -17103,9 +18573,12 @@
         <v>0.01467</v>
       </c>
       <c r="I490" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="J490" s="1" t="n">
         <v>0.01474</v>
       </c>
-      <c r="J490" s="1" t="n">
+      <c r="K490" s="1" t="n">
         <v>0.01458</v>
       </c>
     </row>
@@ -17137,9 +18610,12 @@
         <v>0.01871</v>
       </c>
       <c r="I491" s="1" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="J491" s="1" t="n">
         <v>0.01876</v>
       </c>
-      <c r="J491" s="1" t="n">
+      <c r="K491" s="1" t="n">
         <v>0.01851</v>
       </c>
     </row>
@@ -17171,10 +18647,13 @@
         <v>0.08832</v>
       </c>
       <c r="I492" s="1" t="n">
+        <v>0.08784</v>
+      </c>
+      <c r="J492" s="1" t="n">
         <v>0.08935</v>
       </c>
-      <c r="J492" s="1" t="n">
-        <v>0.08810999999999999</v>
+      <c r="K492" s="1" t="n">
+        <v>0.08784</v>
       </c>
     </row>
     <row r="493">
@@ -17205,9 +18684,12 @@
         <v>0.006508</v>
       </c>
       <c r="I493" s="1" t="n">
+        <v>0.006503</v>
+      </c>
+      <c r="J493" s="1" t="n">
         <v>0.006514</v>
       </c>
-      <c r="J493" s="1" t="n">
+      <c r="K493" s="1" t="n">
         <v>0.006497</v>
       </c>
     </row>
@@ -17239,9 +18721,12 @@
         <v>0.1331</v>
       </c>
       <c r="I494" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="J494" s="1" t="n">
         <v>0.1331</v>
       </c>
-      <c r="J494" s="1" t="n">
+      <c r="K494" s="1" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -17273,9 +18758,12 @@
         <v>0.2844</v>
       </c>
       <c r="I495" s="1" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="J495" s="1" t="n">
         <v>0.2853</v>
       </c>
-      <c r="J495" s="1" t="n">
+      <c r="K495" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -17307,9 +18795,12 @@
         <v>0.004537</v>
       </c>
       <c r="I496" s="1" t="n">
-        <v>0.004537</v>
+        <v>0.004544</v>
       </c>
       <c r="J496" s="1" t="n">
+        <v>0.004544</v>
+      </c>
+      <c r="K496" s="1" t="n">
         <v>0.004516</v>
       </c>
     </row>
@@ -17341,10 +18832,13 @@
         <v>0.1267</v>
       </c>
       <c r="I497" s="1" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="J497" s="1" t="n">
         <v>0.1283</v>
       </c>
-      <c r="J497" s="1" t="n">
-        <v>0.1265</v>
+      <c r="K497" s="1" t="n">
+        <v>0.1264</v>
       </c>
     </row>
     <row r="498">
@@ -17378,6 +18872,9 @@
         <v>0.03445</v>
       </c>
       <c r="J498" s="1" t="n">
+        <v>0.03445</v>
+      </c>
+      <c r="K498" s="1" t="n">
         <v>0.03423</v>
       </c>
     </row>
@@ -17409,9 +18906,12 @@
         <v>0.03569</v>
       </c>
       <c r="I499" s="1" t="n">
+        <v>0.03563</v>
+      </c>
+      <c r="J499" s="1" t="n">
         <v>0.03576</v>
       </c>
-      <c r="J499" s="1" t="n">
+      <c r="K499" s="1" t="n">
         <v>0.03557</v>
       </c>
     </row>
@@ -17443,9 +18943,12 @@
         <v>0.003417</v>
       </c>
       <c r="I500" s="1" t="n">
+        <v>0.003413</v>
+      </c>
+      <c r="J500" s="1" t="n">
         <v>0.003421</v>
       </c>
-      <c r="J500" s="1" t="n">
+      <c r="K500" s="1" t="n">
         <v>0.003413</v>
       </c>
     </row>
@@ -17477,9 +18980,12 @@
         <v>0.0003829</v>
       </c>
       <c r="I501" s="1" t="n">
+        <v>0.0003821</v>
+      </c>
+      <c r="J501" s="1" t="n">
         <v>0.0003834</v>
       </c>
-      <c r="J501" s="1" t="n">
+      <c r="K501" s="1" t="n">
         <v>0.0003786</v>
       </c>
     </row>
@@ -17511,9 +19017,12 @@
         <v>0.3003</v>
       </c>
       <c r="I502" s="1" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="J502" s="1" t="n">
         <v>0.3004</v>
       </c>
-      <c r="J502" s="1" t="n">
+      <c r="K502" s="1" t="n">
         <v>0.2986</v>
       </c>
     </row>
@@ -17545,9 +19054,12 @@
         <v>0.06496</v>
       </c>
       <c r="I503" s="1" t="n">
+        <v>0.06485</v>
+      </c>
+      <c r="J503" s="1" t="n">
         <v>0.06507</v>
       </c>
-      <c r="J503" s="1" t="n">
+      <c r="K503" s="1" t="n">
         <v>0.06485</v>
       </c>
     </row>
@@ -17579,9 +19091,12 @@
         <v>0.178</v>
       </c>
       <c r="I504" s="1" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="J504" s="1" t="n">
         <v>0.178</v>
       </c>
-      <c r="J504" s="1" t="n">
+      <c r="K504" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -17613,10 +19128,13 @@
         <v>0.1512</v>
       </c>
       <c r="I505" s="1" t="n">
+        <v>0.1511</v>
+      </c>
+      <c r="J505" s="1" t="n">
         <v>0.1514</v>
       </c>
-      <c r="J505" s="1" t="n">
-        <v>0.1512</v>
+      <c r="K505" s="1" t="n">
+        <v>0.1511</v>
       </c>
     </row>
     <row r="506">
@@ -17647,9 +19165,12 @@
         <v>0.01199</v>
       </c>
       <c r="I506" s="1" t="n">
+        <v>0.01198</v>
+      </c>
+      <c r="J506" s="1" t="n">
         <v>0.01199</v>
       </c>
-      <c r="J506" s="1" t="n">
+      <c r="K506" s="1" t="n">
         <v>0.01193</v>
       </c>
     </row>
@@ -17681,9 +19202,12 @@
         <v>0.2893</v>
       </c>
       <c r="I507" s="1" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="J507" s="1" t="n">
         <v>0.2893</v>
       </c>
-      <c r="J507" s="1" t="n">
+      <c r="K507" s="1" t="n">
         <v>0.2871</v>
       </c>
     </row>
@@ -17715,9 +19239,12 @@
         <v>0.00933</v>
       </c>
       <c r="I508" s="1" t="n">
+        <v>0.009339999999999999</v>
+      </c>
+      <c r="J508" s="1" t="n">
         <v>0.0094</v>
       </c>
-      <c r="J508" s="1" t="n">
+      <c r="K508" s="1" t="n">
         <v>0.009310000000000001</v>
       </c>
     </row>
@@ -17749,9 +19276,12 @@
         <v>0.006833</v>
       </c>
       <c r="I509" s="1" t="n">
+        <v>0.006829</v>
+      </c>
+      <c r="J509" s="1" t="n">
         <v>0.006833</v>
       </c>
-      <c r="J509" s="1" t="n">
+      <c r="K509" s="1" t="n">
         <v>0.006783</v>
       </c>
     </row>
@@ -17783,9 +19313,12 @@
         <v>0.2944</v>
       </c>
       <c r="I510" s="1" t="n">
-        <v>0.2951</v>
+        <v>0.2954</v>
       </c>
       <c r="J510" s="1" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="K510" s="1" t="n">
         <v>0.2934</v>
       </c>
     </row>
@@ -17817,9 +19350,12 @@
         <v>0.01467</v>
       </c>
       <c r="I511" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="J511" s="1" t="n">
         <v>0.01471</v>
       </c>
-      <c r="J511" s="1" t="n">
+      <c r="K511" s="1" t="n">
         <v>0.01465</v>
       </c>
     </row>
@@ -17854,6 +19390,9 @@
         <v>0.1398</v>
       </c>
       <c r="J512" s="1" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="K512" s="1" t="n">
         <v>0.1394</v>
       </c>
     </row>
@@ -17885,9 +19424,12 @@
         <v>0.08144999999999999</v>
       </c>
       <c r="I513" s="1" t="n">
+        <v>0.08128000000000001</v>
+      </c>
+      <c r="J513" s="1" t="n">
         <v>0.08144999999999999</v>
       </c>
-      <c r="J513" s="1" t="n">
+      <c r="K513" s="1" t="n">
         <v>0.08069</v>
       </c>
     </row>
@@ -17922,6 +19464,9 @@
         <v>0.0251</v>
       </c>
       <c r="J514" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="K514" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -17953,9 +19498,12 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="I515" s="1" t="n">
+        <v>0.06314</v>
+      </c>
+      <c r="J515" s="1" t="n">
         <v>0.06329</v>
       </c>
-      <c r="J515" s="1" t="n">
+      <c r="K515" s="1" t="n">
         <v>0.06301</v>
       </c>
     </row>
@@ -17987,9 +19535,12 @@
         <v>0.04735</v>
       </c>
       <c r="I516" s="1" t="n">
+        <v>0.04732</v>
+      </c>
+      <c r="J516" s="1" t="n">
         <v>0.04735</v>
       </c>
-      <c r="J516" s="1" t="n">
+      <c r="K516" s="1" t="n">
         <v>0.04707</v>
       </c>
     </row>
@@ -18021,9 +19572,12 @@
         <v>0.004909</v>
       </c>
       <c r="I517" s="1" t="n">
+        <v>0.004902</v>
+      </c>
+      <c r="J517" s="1" t="n">
         <v>0.004909</v>
       </c>
-      <c r="J517" s="1" t="n">
+      <c r="K517" s="1" t="n">
         <v>0.004902</v>
       </c>
     </row>
@@ -18055,9 +19609,12 @@
         <v>0.009422</v>
       </c>
       <c r="I518" s="1" t="n">
-        <v>0.009431999999999999</v>
+        <v>0.00944</v>
       </c>
       <c r="J518" s="1" t="n">
+        <v>0.00944</v>
+      </c>
+      <c r="K518" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -18089,9 +19646,12 @@
         <v>0.01805</v>
       </c>
       <c r="I519" s="1" t="n">
+        <v>0.01803</v>
+      </c>
+      <c r="J519" s="1" t="n">
         <v>0.01807</v>
       </c>
-      <c r="J519" s="1" t="n">
+      <c r="K519" s="1" t="n">
         <v>0.01798</v>
       </c>
     </row>
@@ -18123,9 +19683,12 @@
         <v>0.06642000000000001</v>
       </c>
       <c r="I520" s="1" t="n">
-        <v>0.06688</v>
+        <v>0.06689000000000001</v>
       </c>
       <c r="J520" s="1" t="n">
+        <v>0.06689000000000001</v>
+      </c>
+      <c r="K520" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -18157,9 +19720,12 @@
         <v>0.137</v>
       </c>
       <c r="I521" s="1" t="n">
+        <v>0.1368</v>
+      </c>
+      <c r="J521" s="1" t="n">
         <v>0.137</v>
       </c>
-      <c r="J521" s="1" t="n">
+      <c r="K521" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -18191,9 +19757,12 @@
         <v>0.04726</v>
       </c>
       <c r="I522" s="1" t="n">
+        <v>0.04726</v>
+      </c>
+      <c r="J522" s="1" t="n">
         <v>0.04746</v>
       </c>
-      <c r="J522" s="1" t="n">
+      <c r="K522" s="1" t="n">
         <v>0.04718</v>
       </c>
     </row>
@@ -18225,9 +19794,12 @@
         <v>0.06805</v>
       </c>
       <c r="I523" s="1" t="n">
+        <v>0.06798</v>
+      </c>
+      <c r="J523" s="1" t="n">
         <v>0.06809</v>
       </c>
-      <c r="J523" s="1" t="n">
+      <c r="K523" s="1" t="n">
         <v>0.06784999999999999</v>
       </c>
     </row>
@@ -18259,9 +19831,12 @@
         <v>0.6982</v>
       </c>
       <c r="I524" s="1" t="n">
-        <v>0.6983</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="J524" s="1" t="n">
+        <v>0.6991000000000001</v>
+      </c>
+      <c r="K524" s="1" t="n">
         <v>0.6966</v>
       </c>
     </row>
@@ -18293,9 +19868,12 @@
         <v>0.00268</v>
       </c>
       <c r="I525" s="1" t="n">
-        <v>0.00268</v>
+        <v>0.00269</v>
       </c>
       <c r="J525" s="1" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="K525" s="1" t="n">
         <v>0.00267</v>
       </c>
     </row>
@@ -18327,9 +19905,12 @@
         <v>0.487</v>
       </c>
       <c r="I526" s="1" t="n">
-        <v>0.487</v>
+        <v>0.4872</v>
       </c>
       <c r="J526" s="1" t="n">
+        <v>0.4872</v>
+      </c>
+      <c r="K526" s="1" t="n">
         <v>0.4856</v>
       </c>
     </row>
@@ -18364,6 +19945,9 @@
         <v>45.83</v>
       </c>
       <c r="J527" s="1" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="K527" s="1" t="n">
         <v>45.76</v>
       </c>
     </row>
@@ -18395,9 +19979,12 @@
         <v>0.02443</v>
       </c>
       <c r="I528" s="1" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="J528" s="1" t="n">
         <v>0.02443</v>
       </c>
-      <c r="J528" s="1" t="n">
+      <c r="K528" s="1" t="n">
         <v>0.02429</v>
       </c>
     </row>
@@ -18429,9 +20016,12 @@
         <v>0.006406</v>
       </c>
       <c r="I529" s="1" t="n">
-        <v>0.006406</v>
+        <v>0.00641</v>
       </c>
       <c r="J529" s="1" t="n">
+        <v>0.00641</v>
+      </c>
+      <c r="K529" s="1" t="n">
         <v>0.00638</v>
       </c>
     </row>
@@ -18466,6 +20056,9 @@
         <v>0.2002</v>
       </c>
       <c r="J530" s="1" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="K530" s="1" t="n">
         <v>0.1993</v>
       </c>
     </row>
@@ -18497,9 +20090,12 @@
         <v>0.007679</v>
       </c>
       <c r="I531" s="1" t="n">
+        <v>0.007684</v>
+      </c>
+      <c r="J531" s="1" t="n">
         <v>0.007727</v>
       </c>
-      <c r="J531" s="1" t="n">
+      <c r="K531" s="1" t="n">
         <v>0.007657</v>
       </c>
     </row>
@@ -18531,9 +20127,12 @@
         <v>2.284</v>
       </c>
       <c r="I532" s="1" t="n">
+        <v>2.281</v>
+      </c>
+      <c r="J532" s="1" t="n">
         <v>2.285</v>
       </c>
-      <c r="J532" s="1" t="n">
+      <c r="K532" s="1" t="n">
         <v>2.275</v>
       </c>
     </row>
@@ -18565,9 +20164,12 @@
         <v>0.04148</v>
       </c>
       <c r="I533" s="1" t="n">
-        <v>0.04156</v>
+        <v>0.04164</v>
       </c>
       <c r="J533" s="1" t="n">
+        <v>0.04164</v>
+      </c>
+      <c r="K533" s="1" t="n">
         <v>0.04138</v>
       </c>
     </row>
@@ -18599,9 +20201,12 @@
         <v>0.183</v>
       </c>
       <c r="I534" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="J534" s="1" t="n">
         <v>0.1833</v>
       </c>
-      <c r="J534" s="1" t="n">
+      <c r="K534" s="1" t="n">
         <v>0.1811</v>
       </c>
     </row>
@@ -18633,9 +20238,12 @@
         <v>0.04298</v>
       </c>
       <c r="I535" s="1" t="n">
-        <v>0.04311</v>
+        <v>0.04328</v>
       </c>
       <c r="J535" s="1" t="n">
+        <v>0.04328</v>
+      </c>
+      <c r="K535" s="1" t="n">
         <v>0.04287</v>
       </c>
     </row>
@@ -18667,9 +20275,12 @@
         <v>0.0541</v>
       </c>
       <c r="I536" s="1" t="n">
+        <v>0.05409</v>
+      </c>
+      <c r="J536" s="1" t="n">
         <v>0.05438</v>
       </c>
-      <c r="J536" s="1" t="n">
+      <c r="K536" s="1" t="n">
         <v>0.05409</v>
       </c>
     </row>
@@ -18701,9 +20312,12 @@
         <v>0.1605</v>
       </c>
       <c r="I537" s="1" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="J537" s="1" t="n">
         <v>0.1609</v>
       </c>
-      <c r="J537" s="1" t="n">
+      <c r="K537" s="1" t="n">
         <v>0.1602</v>
       </c>
     </row>
@@ -18735,9 +20349,12 @@
         <v>0.03681</v>
       </c>
       <c r="I538" s="1" t="n">
+        <v>0.03677</v>
+      </c>
+      <c r="J538" s="1" t="n">
         <v>0.03687</v>
       </c>
-      <c r="J538" s="1" t="n">
+      <c r="K538" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -18769,9 +20386,12 @@
         <v>0.05844</v>
       </c>
       <c r="I539" s="1" t="n">
-        <v>0.05844</v>
+        <v>0.05858</v>
       </c>
       <c r="J539" s="1" t="n">
+        <v>0.05858</v>
+      </c>
+      <c r="K539" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -18803,9 +20423,12 @@
         <v>0.04263</v>
       </c>
       <c r="I540" s="1" t="n">
-        <v>0.04267</v>
+        <v>0.04273</v>
       </c>
       <c r="J540" s="1" t="n">
+        <v>0.04273</v>
+      </c>
+      <c r="K540" s="1" t="n">
         <v>0.04256</v>
       </c>
     </row>
@@ -18837,9 +20460,12 @@
         <v>0.01729</v>
       </c>
       <c r="I541" s="1" t="n">
+        <v>0.01725</v>
+      </c>
+      <c r="J541" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="J541" s="1" t="n">
+      <c r="K541" s="1" t="n">
         <v>0.0172</v>
       </c>
     </row>
@@ -18871,9 +20497,12 @@
         <v>0.003969</v>
       </c>
       <c r="I542" s="1" t="n">
+        <v>0.003967</v>
+      </c>
+      <c r="J542" s="1" t="n">
         <v>0.003975</v>
       </c>
-      <c r="J542" s="1" t="n">
+      <c r="K542" s="1" t="n">
         <v>0.003963</v>
       </c>
     </row>
@@ -18905,9 +20534,12 @@
         <v>0.05785</v>
       </c>
       <c r="I543" s="1" t="n">
-        <v>0.05817</v>
+        <v>0.05835</v>
       </c>
       <c r="J543" s="1" t="n">
+        <v>0.05835</v>
+      </c>
+      <c r="K543" s="1" t="n">
         <v>0.05735</v>
       </c>
     </row>
@@ -18939,9 +20571,12 @@
         <v>0.05023</v>
       </c>
       <c r="I544" s="1" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="J544" s="1" t="n">
         <v>0.05042</v>
       </c>
-      <c r="J544" s="1" t="n">
+      <c r="K544" s="1" t="n">
         <v>0.05016</v>
       </c>
     </row>
@@ -18973,9 +20608,12 @@
         <v>0.04066</v>
       </c>
       <c r="I545" s="1" t="n">
+        <v>0.04069</v>
+      </c>
+      <c r="J545" s="1" t="n">
         <v>0.04071</v>
       </c>
-      <c r="J545" s="1" t="n">
+      <c r="K545" s="1" t="n">
         <v>0.04038</v>
       </c>
     </row>
@@ -19007,9 +20645,12 @@
         <v>0.007413</v>
       </c>
       <c r="I546" s="1" t="n">
+        <v>0.007411</v>
+      </c>
+      <c r="J546" s="1" t="n">
         <v>0.007433</v>
       </c>
-      <c r="J546" s="1" t="n">
+      <c r="K546" s="1" t="n">
         <v>0.007402</v>
       </c>
     </row>
@@ -19041,9 +20682,12 @@
         <v>0.01474</v>
       </c>
       <c r="I547" s="1" t="n">
+        <v>0.01472</v>
+      </c>
+      <c r="J547" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="J547" s="1" t="n">
+      <c r="K547" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -19075,9 +20719,12 @@
         <v>0.01572</v>
       </c>
       <c r="I548" s="1" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="J548" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="J548" s="1" t="n">
+      <c r="K548" s="1" t="n">
         <v>0.0157</v>
       </c>
     </row>
@@ -19109,9 +20756,12 @@
         <v>0.13452</v>
       </c>
       <c r="I549" s="1" t="n">
-        <v>0.13452</v>
+        <v>0.13556</v>
       </c>
       <c r="J549" s="1" t="n">
+        <v>0.13556</v>
+      </c>
+      <c r="K549" s="1" t="n">
         <v>0.13271</v>
       </c>
     </row>
@@ -19146,6 +20796,9 @@
         <v>0.1699</v>
       </c>
       <c r="J550" s="1" t="n">
+        <v>0.1699</v>
+      </c>
+      <c r="K550" s="1" t="n">
         <v>0.1693</v>
       </c>
     </row>
@@ -19177,9 +20830,12 @@
         <v>0.003584</v>
       </c>
       <c r="I551" s="1" t="n">
-        <v>0.003584</v>
+        <v>0.003586</v>
       </c>
       <c r="J551" s="1" t="n">
+        <v>0.003586</v>
+      </c>
+      <c r="K551" s="1" t="n">
         <v>0.003577</v>
       </c>
     </row>
@@ -19211,9 +20867,12 @@
         <v>0.03042</v>
       </c>
       <c r="I552" s="1" t="n">
-        <v>0.03042</v>
+        <v>0.03044</v>
       </c>
       <c r="J552" s="1" t="n">
+        <v>0.03044</v>
+      </c>
+      <c r="K552" s="1" t="n">
         <v>0.0303</v>
       </c>
     </row>
@@ -19245,9 +20904,12 @@
         <v>0.0132</v>
       </c>
       <c r="I553" s="1" t="n">
+        <v>0.01322</v>
+      </c>
+      <c r="J553" s="1" t="n">
         <v>0.01325</v>
       </c>
-      <c r="J553" s="1" t="n">
+      <c r="K553" s="1" t="n">
         <v>0.01319</v>
       </c>
     </row>
@@ -19279,9 +20941,12 @@
         <v>0.1045</v>
       </c>
       <c r="I554" s="1" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="J554" s="1" t="n">
         <v>0.1046</v>
       </c>
-      <c r="J554" s="1" t="n">
+      <c r="K554" s="1" t="n">
         <v>0.1039</v>
       </c>
     </row>
@@ -19313,9 +20978,12 @@
         <v>0.05302</v>
       </c>
       <c r="I555" s="1" t="n">
+        <v>0.05303</v>
+      </c>
+      <c r="J555" s="1" t="n">
         <v>0.05319</v>
       </c>
-      <c r="J555" s="1" t="n">
+      <c r="K555" s="1" t="n">
         <v>0.05291</v>
       </c>
     </row>
@@ -19347,9 +21015,12 @@
         <v>0.01223</v>
       </c>
       <c r="I556" s="1" t="n">
+        <v>0.01223</v>
+      </c>
+      <c r="J556" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="J556" s="1" t="n">
+      <c r="K556" s="1" t="n">
         <v>0.01218</v>
       </c>
     </row>

--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K556"/>
+  <dimension ref="A1:L556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -428,8 +428,9 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,10 +481,15 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>price_02:00</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -520,9 +526,12 @@
         <v>71493.8</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>71530</v>
+        <v>71788</v>
       </c>
       <c r="K2" s="1" t="n">
+        <v>71788</v>
+      </c>
+      <c r="L2" s="1" t="n">
         <v>71364.39999999999</v>
       </c>
     </row>
@@ -557,9 +566,12 @@
         <v>2095.85</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>2096.9</v>
+        <v>2109.75</v>
       </c>
       <c r="K3" s="1" t="n">
+        <v>2109.75</v>
+      </c>
+      <c r="L3" s="1" t="n">
         <v>2090.41</v>
       </c>
     </row>
@@ -594,9 +606,12 @@
         <v>87.89</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>87.95</v>
+        <v>88.38</v>
       </c>
       <c r="K4" s="1" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="L4" s="1" t="n">
         <v>87.47</v>
       </c>
     </row>
@@ -631,9 +646,12 @@
         <v>23.159</v>
       </c>
       <c r="J5" s="1" t="n">
+        <v>23.388</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>23.579</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" s="1" t="n">
         <v>23.043</v>
       </c>
     </row>
@@ -668,10 +686,13 @@
         <v>0.001826</v>
       </c>
       <c r="J6" s="1" t="n">
+        <v>0.001811</v>
+      </c>
+      <c r="K6" s="1" t="n">
         <v>0.001892</v>
       </c>
-      <c r="K6" s="1" t="n">
-        <v>0.001826</v>
+      <c r="L6" s="1" t="n">
+        <v>0.001811</v>
       </c>
     </row>
     <row r="7">
@@ -705,9 +726,12 @@
         <v>1.4136</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>1.4151</v>
+        <v>1.4184</v>
       </c>
       <c r="K7" s="1" t="n">
+        <v>1.4184</v>
+      </c>
+      <c r="L7" s="1" t="n">
         <v>1.4117</v>
       </c>
     </row>
@@ -742,9 +766,12 @@
         <v>0.010411</v>
       </c>
       <c r="J8" s="1" t="n">
+        <v>0.010642</v>
+      </c>
+      <c r="K8" s="1" t="n">
         <v>0.011244</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="L8" s="1" t="n">
         <v>0.010407</v>
       </c>
     </row>
@@ -779,9 +806,12 @@
         <v>4.021</v>
       </c>
       <c r="J9" s="1" t="n">
+        <v>4.035</v>
+      </c>
+      <c r="K9" s="1" t="n">
         <v>4.062</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="L9" s="1" t="n">
         <v>3.954</v>
       </c>
     </row>
@@ -816,9 +846,12 @@
         <v>276.67</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>278.1</v>
+        <v>279.92</v>
       </c>
       <c r="K10" s="1" t="n">
+        <v>279.92</v>
+      </c>
+      <c r="L10" s="1" t="n">
         <v>272.11</v>
       </c>
     </row>
@@ -853,10 +886,13 @@
         <v>0.07815</v>
       </c>
       <c r="J11" s="1" t="n">
+        <v>0.07804</v>
+      </c>
+      <c r="K11" s="1" t="n">
         <v>0.08047</v>
       </c>
-      <c r="K11" s="1" t="n">
-        <v>0.07815</v>
+      <c r="L11" s="1" t="n">
+        <v>0.07804</v>
       </c>
     </row>
     <row r="12">
@@ -890,9 +926,12 @@
         <v>224.61</v>
       </c>
       <c r="J12" s="1" t="n">
+        <v>226.41</v>
+      </c>
+      <c r="K12" s="1" t="n">
         <v>227.69</v>
       </c>
-      <c r="K12" s="1" t="n">
+      <c r="L12" s="1" t="n">
         <v>223.76</v>
       </c>
     </row>
@@ -927,9 +966,12 @@
         <v>0.09488000000000001</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.09497</v>
+        <v>0.09543</v>
       </c>
       <c r="K13" s="1" t="n">
+        <v>0.09543</v>
+      </c>
+      <c r="L13" s="1" t="n">
         <v>0.0946</v>
       </c>
     </row>
@@ -964,9 +1006,12 @@
         <v>37.247</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>37.279</v>
+        <v>37.361</v>
       </c>
       <c r="K14" s="1" t="n">
+        <v>37.361</v>
+      </c>
+      <c r="L14" s="1" t="n">
         <v>37.089</v>
       </c>
     </row>
@@ -1001,10 +1046,13 @@
         <v>0.09272</v>
       </c>
       <c r="J15" s="1" t="n">
+        <v>0.09271</v>
+      </c>
+      <c r="K15" s="1" t="n">
         <v>0.09845</v>
       </c>
-      <c r="K15" s="1" t="n">
-        <v>0.09272</v>
+      <c r="L15" s="1" t="n">
+        <v>0.09271</v>
       </c>
     </row>
     <row r="16">
@@ -1038,9 +1086,12 @@
         <v>0.2261</v>
       </c>
       <c r="J16" s="1" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="K16" s="1" t="n">
         <v>0.2339</v>
       </c>
-      <c r="K16" s="1" t="n">
+      <c r="L16" s="1" t="n">
         <v>0.2256</v>
       </c>
     </row>
@@ -1075,9 +1126,12 @@
         <v>0.011413</v>
       </c>
       <c r="J17" s="1" t="n">
+        <v>0.011455</v>
+      </c>
+      <c r="K17" s="1" t="n">
         <v>0.011542</v>
       </c>
-      <c r="K17" s="1" t="n">
+      <c r="L17" s="1" t="n">
         <v>0.011379</v>
       </c>
     </row>
@@ -1112,9 +1166,12 @@
         <v>660.22</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>660.72</v>
+        <v>661.9</v>
       </c>
       <c r="K18" s="1" t="n">
+        <v>661.9</v>
+      </c>
+      <c r="L18" s="1" t="n">
         <v>658.89</v>
       </c>
     </row>
@@ -1149,9 +1206,12 @@
         <v>0.0033418</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0.0033454</v>
+        <v>0.0033672</v>
       </c>
       <c r="K19" s="1" t="n">
+        <v>0.0033672</v>
+      </c>
+      <c r="L19" s="1" t="n">
         <v>0.0033271</v>
       </c>
     </row>
@@ -1186,9 +1246,12 @@
         <v>0.17936</v>
       </c>
       <c r="J20" s="1" t="n">
+        <v>0.17759</v>
+      </c>
+      <c r="K20" s="1" t="n">
         <v>0.18066</v>
       </c>
-      <c r="K20" s="1" t="n">
+      <c r="L20" s="1" t="n">
         <v>0.17675</v>
       </c>
     </row>
@@ -1223,9 +1286,12 @@
         <v>0.009887999999999999</v>
       </c>
       <c r="J21" s="1" t="n">
+        <v>0.009918</v>
+      </c>
+      <c r="K21" s="1" t="n">
         <v>0.010044</v>
       </c>
-      <c r="K21" s="1" t="n">
+      <c r="L21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -1260,9 +1326,12 @@
         <v>0.9992</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>1.0033</v>
+        <v>1.009</v>
       </c>
       <c r="K22" s="1" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="L22" s="1" t="n">
         <v>0.9985000000000001</v>
       </c>
     </row>
@@ -1297,9 +1366,12 @@
         <v>5005.29</v>
       </c>
       <c r="J23" s="1" t="n">
+        <v>5006.11</v>
+      </c>
+      <c r="K23" s="1" t="n">
         <v>5012.25</v>
       </c>
-      <c r="K23" s="1" t="n">
+      <c r="L23" s="1" t="n">
         <v>5002.67</v>
       </c>
     </row>
@@ -1334,9 +1406,12 @@
         <v>0.2628</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.2643</v>
+        <v>0.2645</v>
       </c>
       <c r="K24" s="1" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="L24" s="1" t="n">
         <v>0.2625</v>
       </c>
     </row>
@@ -1371,10 +1446,13 @@
         <v>2.885</v>
       </c>
       <c r="J25" s="1" t="n">
+        <v>2.877</v>
+      </c>
+      <c r="K25" s="1" t="n">
         <v>2.924</v>
       </c>
-      <c r="K25" s="1" t="n">
-        <v>2.885</v>
+      <c r="L25" s="1" t="n">
+        <v>2.877</v>
       </c>
     </row>
     <row r="26">
@@ -1408,10 +1486,13 @@
         <v>0.3988</v>
       </c>
       <c r="J26" s="1" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="K26" s="1" t="n">
         <v>0.4096</v>
       </c>
-      <c r="K26" s="1" t="n">
-        <v>0.3959</v>
+      <c r="L26" s="1" t="n">
+        <v>0.3825</v>
       </c>
     </row>
     <row r="27">
@@ -1445,9 +1526,12 @@
         <v>0.885</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.886</v>
+        <v>0.889</v>
       </c>
       <c r="K27" s="1" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="L27" s="1" t="n">
         <v>0.881</v>
       </c>
     </row>
@@ -1482,9 +1566,12 @@
         <v>1.342</v>
       </c>
       <c r="J28" s="1" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="K28" s="1" t="n">
         <v>1.346</v>
       </c>
-      <c r="K28" s="1" t="n">
+      <c r="L28" s="1" t="n">
         <v>1.335</v>
       </c>
     </row>
@@ -1519,9 +1606,12 @@
         <v>9.151</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>9.179</v>
+        <v>9.205</v>
       </c>
       <c r="K29" s="1" t="n">
+        <v>9.205</v>
+      </c>
+      <c r="L29" s="1" t="n">
         <v>9.131</v>
       </c>
     </row>
@@ -1556,9 +1646,12 @@
         <v>461.93</v>
       </c>
       <c r="J30" s="1" t="n">
+        <v>463.29</v>
+      </c>
+      <c r="K30" s="1" t="n">
         <v>463.35</v>
       </c>
-      <c r="K30" s="1" t="n">
+      <c r="L30" s="1" t="n">
         <v>461.24</v>
       </c>
     </row>
@@ -1593,9 +1686,12 @@
         <v>9.704000000000001</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>9.731</v>
+        <v>9.765000000000001</v>
       </c>
       <c r="K31" s="1" t="n">
+        <v>9.765000000000001</v>
+      </c>
+      <c r="L31" s="1" t="n">
         <v>9.696999999999999</v>
       </c>
     </row>
@@ -1630,10 +1726,13 @@
         <v>0.36251</v>
       </c>
       <c r="J32" s="1" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="K32" s="1" t="n">
         <v>0.36683</v>
       </c>
-      <c r="K32" s="1" t="n">
-        <v>0.36159</v>
+      <c r="L32" s="1" t="n">
+        <v>0.35998</v>
       </c>
     </row>
     <row r="33">
@@ -1670,6 +1769,9 @@
         <v>1.421</v>
       </c>
       <c r="K33" s="1" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="L33" s="1" t="n">
         <v>1.409</v>
       </c>
     </row>
@@ -1704,10 +1806,13 @@
         <v>0.59414</v>
       </c>
       <c r="J34" s="1" t="n">
+        <v>0.58969</v>
+      </c>
+      <c r="K34" s="1" t="n">
         <v>0.59693</v>
       </c>
-      <c r="K34" s="1" t="n">
-        <v>0.5926900000000001</v>
+      <c r="L34" s="1" t="n">
+        <v>0.58969</v>
       </c>
     </row>
     <row r="35">
@@ -1741,9 +1846,12 @@
         <v>1.2234</v>
       </c>
       <c r="J35" s="1" t="n">
+        <v>1.2251</v>
+      </c>
+      <c r="K35" s="1" t="n">
         <v>1.2283</v>
       </c>
-      <c r="K35" s="1" t="n">
+      <c r="L35" s="1" t="n">
         <v>1.2186</v>
       </c>
     </row>
@@ -1778,9 +1886,12 @@
         <v>80.28</v>
       </c>
       <c r="J36" s="1" t="n">
+        <v>80.33</v>
+      </c>
+      <c r="K36" s="1" t="n">
         <v>80.5</v>
       </c>
-      <c r="K36" s="1" t="n">
+      <c r="L36" s="1" t="n">
         <v>80.27</v>
       </c>
     </row>
@@ -1815,9 +1926,12 @@
         <v>0.1967</v>
       </c>
       <c r="J37" s="1" t="n">
+        <v>0.1978</v>
+      </c>
+      <c r="K37" s="1" t="n">
         <v>0.204</v>
       </c>
-      <c r="K37" s="1" t="n">
+      <c r="L37" s="1" t="n">
         <v>0.1967</v>
       </c>
     </row>
@@ -1852,9 +1966,12 @@
         <v>1.849</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.865</v>
+        <v>1.866</v>
       </c>
       <c r="K38" s="1" t="n">
+        <v>1.866</v>
+      </c>
+      <c r="L38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -1889,9 +2006,12 @@
         <v>0.3318</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.3338</v>
+        <v>0.3382</v>
       </c>
       <c r="K39" s="1" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="L39" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -1926,10 +2046,13 @@
         <v>0.8931</v>
       </c>
       <c r="J40" s="1" t="n">
+        <v>0.8895999999999999</v>
+      </c>
+      <c r="K40" s="1" t="n">
         <v>0.9115</v>
       </c>
-      <c r="K40" s="1" t="n">
-        <v>0.8931</v>
+      <c r="L40" s="1" t="n">
+        <v>0.8895999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1963,9 +2086,12 @@
         <v>0.7119</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.7149</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="K41" s="1" t="n">
+        <v>0.7151999999999999</v>
+      </c>
+      <c r="L41" s="1" t="n">
         <v>0.7115</v>
       </c>
     </row>
@@ -2000,10 +2126,13 @@
         <v>0.06616</v>
       </c>
       <c r="J42" s="1" t="n">
+        <v>0.06551999999999999</v>
+      </c>
+      <c r="K42" s="1" t="n">
         <v>0.06769</v>
       </c>
-      <c r="K42" s="1" t="n">
-        <v>0.06616</v>
+      <c r="L42" s="1" t="n">
+        <v>0.06551999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -2037,9 +2166,12 @@
         <v>113.62</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>113.86</v>
+        <v>114.65</v>
       </c>
       <c r="K43" s="1" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="L43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -2074,9 +2206,12 @@
         <v>0.6536999999999999</v>
       </c>
       <c r="J44" s="1" t="n">
+        <v>0.6539</v>
+      </c>
+      <c r="K44" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="K44" s="1" t="n">
+      <c r="L44" s="1" t="n">
         <v>0.6536999999999999</v>
       </c>
     </row>
@@ -2111,9 +2246,12 @@
         <v>1.225</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>1.225</v>
+        <v>1.227</v>
       </c>
       <c r="K45" s="1" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="L45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -2148,9 +2286,12 @@
         <v>0.02376</v>
       </c>
       <c r="J46" s="1" t="n">
+        <v>0.02378</v>
+      </c>
+      <c r="K46" s="1" t="n">
         <v>0.02392</v>
       </c>
-      <c r="K46" s="1" t="n">
+      <c r="L46" s="1" t="n">
         <v>0.02376</v>
       </c>
     </row>
@@ -2185,9 +2326,12 @@
         <v>55.03</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>55.17</v>
+        <v>55.19</v>
       </c>
       <c r="K47" s="1" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="L47" s="1" t="n">
         <v>54.99</v>
       </c>
     </row>
@@ -2222,9 +2366,12 @@
         <v>0.06046</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.06081</v>
+        <v>0.061</v>
       </c>
       <c r="K48" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="L48" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -2259,9 +2406,12 @@
         <v>0.108</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.1083</v>
+        <v>0.1086</v>
       </c>
       <c r="K49" s="1" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="L49" s="1" t="n">
         <v>0.1076</v>
       </c>
     </row>
@@ -2296,9 +2446,12 @@
         <v>0.01795</v>
       </c>
       <c r="J50" s="1" t="n">
+        <v>0.01803</v>
+      </c>
+      <c r="K50" s="1" t="n">
         <v>0.01815</v>
       </c>
-      <c r="K50" s="1" t="n">
+      <c r="L50" s="1" t="n">
         <v>0.01795</v>
       </c>
     </row>
@@ -2333,9 +2486,12 @@
         <v>1.4672</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>1.4679</v>
+        <v>1.4817</v>
       </c>
       <c r="K51" s="1" t="n">
+        <v>1.4817</v>
+      </c>
+      <c r="L51" s="1" t="n">
         <v>1.4618</v>
       </c>
     </row>
@@ -2370,9 +2526,12 @@
         <v>0.359</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>0.3603</v>
+        <v>0.3612</v>
       </c>
       <c r="K52" s="1" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="L52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -2407,9 +2566,12 @@
         <v>0.001939</v>
       </c>
       <c r="J53" s="1" t="n">
+        <v>0.001948</v>
+      </c>
+      <c r="K53" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="K53" s="1" t="n">
+      <c r="L53" s="1" t="n">
         <v>0.001939</v>
       </c>
     </row>
@@ -2444,9 +2606,12 @@
         <v>0.09518</v>
       </c>
       <c r="J54" s="1" t="n">
+        <v>0.09565</v>
+      </c>
+      <c r="K54" s="1" t="n">
         <v>0.09569</v>
       </c>
-      <c r="K54" s="1" t="n">
+      <c r="L54" s="1" t="n">
         <v>0.09514</v>
       </c>
     </row>
@@ -2484,6 +2649,9 @@
         <v>0.04099</v>
       </c>
       <c r="K55" s="1" t="n">
+        <v>0.04099</v>
+      </c>
+      <c r="L55" s="1" t="n">
         <v>0.04003</v>
       </c>
     </row>
@@ -2518,9 +2686,12 @@
         <v>0.29839</v>
       </c>
       <c r="J56" s="1" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="K56" s="1" t="n">
         <v>0.29861</v>
       </c>
-      <c r="K56" s="1" t="n">
+      <c r="L56" s="1" t="n">
         <v>0.29831</v>
       </c>
     </row>
@@ -2555,9 +2726,12 @@
         <v>0.005664</v>
       </c>
       <c r="J57" s="1" t="n">
+        <v>0.00569</v>
+      </c>
+      <c r="K57" s="1" t="n">
         <v>0.005824</v>
       </c>
-      <c r="K57" s="1" t="n">
+      <c r="L57" s="1" t="n">
         <v>0.005633</v>
       </c>
     </row>
@@ -2592,9 +2766,12 @@
         <v>4992.04</v>
       </c>
       <c r="J58" s="1" t="n">
+        <v>4993.59</v>
+      </c>
+      <c r="K58" s="1" t="n">
         <v>4998.37</v>
       </c>
-      <c r="K58" s="1" t="n">
+      <c r="L58" s="1" t="n">
         <v>4988.64</v>
       </c>
     </row>
@@ -2629,10 +2806,13 @@
         <v>0.4105</v>
       </c>
       <c r="J59" s="1" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="K59" s="1" t="n">
         <v>0.4246</v>
       </c>
-      <c r="K59" s="1" t="n">
-        <v>0.4105</v>
+      <c r="L59" s="1" t="n">
+        <v>0.4093</v>
       </c>
     </row>
     <row r="60">
@@ -2666,9 +2846,12 @@
         <v>0.04644</v>
       </c>
       <c r="J60" s="1" t="n">
+        <v>0.04647</v>
+      </c>
+      <c r="K60" s="1" t="n">
         <v>0.04686</v>
       </c>
-      <c r="K60" s="1" t="n">
+      <c r="L60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -2703,10 +2886,13 @@
         <v>0.21338</v>
       </c>
       <c r="J61" s="1" t="n">
+        <v>0.21309</v>
+      </c>
+      <c r="K61" s="1" t="n">
         <v>0.21708</v>
       </c>
-      <c r="K61" s="1" t="n">
-        <v>0.21338</v>
+      <c r="L61" s="1" t="n">
+        <v>0.21309</v>
       </c>
     </row>
     <row r="62">
@@ -2740,9 +2926,12 @@
         <v>0.1069</v>
       </c>
       <c r="J62" s="1" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="K62" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="K62" s="1" t="n">
+      <c r="L62" s="1" t="n">
         <v>0.1065</v>
       </c>
     </row>
@@ -2777,9 +2966,12 @@
         <v>0.7272</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>0.7301</v>
+        <v>0.7335</v>
       </c>
       <c r="K63" s="1" t="n">
+        <v>0.7335</v>
+      </c>
+      <c r="L63" s="1" t="n">
         <v>0.7255</v>
       </c>
     </row>
@@ -2814,9 +3006,12 @@
         <v>0.1664</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>0.1668</v>
+        <v>0.1671</v>
       </c>
       <c r="K64" s="1" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="L64" s="1" t="n">
         <v>0.1658</v>
       </c>
     </row>
@@ -2851,9 +3046,12 @@
         <v>2.669</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>2.669</v>
+        <v>2.677</v>
       </c>
       <c r="K65" s="1" t="n">
+        <v>2.677</v>
+      </c>
+      <c r="L65" s="1" t="n">
         <v>2.65</v>
       </c>
     </row>
@@ -2888,9 +3086,12 @@
         <v>0.04051</v>
       </c>
       <c r="J66" s="1" t="n">
+        <v>0.04054</v>
+      </c>
+      <c r="K66" s="1" t="n">
         <v>0.04072</v>
       </c>
-      <c r="K66" s="1" t="n">
+      <c r="L66" s="1" t="n">
         <v>0.04018</v>
       </c>
     </row>
@@ -2925,9 +3126,12 @@
         <v>0.04265</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>0.04268</v>
+        <v>0.04314</v>
       </c>
       <c r="K67" s="1" t="n">
+        <v>0.04314</v>
+      </c>
+      <c r="L67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -2962,9 +3166,12 @@
         <v>3.966</v>
       </c>
       <c r="J68" s="1" t="n">
-        <v>3.971</v>
+        <v>3.992</v>
       </c>
       <c r="K68" s="1" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="L68" s="1" t="n">
         <v>3.951</v>
       </c>
     </row>
@@ -2999,9 +3206,12 @@
         <v>0.1263</v>
       </c>
       <c r="J69" s="1" t="n">
-        <v>0.1265</v>
+        <v>0.1273</v>
       </c>
       <c r="K69" s="1" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="L69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -3036,9 +3246,12 @@
         <v>6.263</v>
       </c>
       <c r="J70" s="1" t="n">
-        <v>6.328</v>
+        <v>6.338</v>
       </c>
       <c r="K70" s="1" t="n">
+        <v>6.338</v>
+      </c>
+      <c r="L70" s="1" t="n">
         <v>6.114</v>
       </c>
     </row>
@@ -3073,9 +3286,12 @@
         <v>0.0501</v>
       </c>
       <c r="J71" s="1" t="n">
+        <v>0.05007</v>
+      </c>
+      <c r="K71" s="1" t="n">
         <v>0.0501</v>
       </c>
-      <c r="K71" s="1" t="n">
+      <c r="L71" s="1" t="n">
         <v>0.04959</v>
       </c>
     </row>
@@ -3110,9 +3326,12 @@
         <v>0.004133</v>
       </c>
       <c r="J72" s="1" t="n">
+        <v>0.00413</v>
+      </c>
+      <c r="K72" s="1" t="n">
         <v>0.004181</v>
       </c>
-      <c r="K72" s="1" t="n">
+      <c r="L72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -3147,9 +3366,12 @@
         <v>6.009</v>
       </c>
       <c r="J73" s="1" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="K73" s="1" t="n">
         <v>6.029</v>
       </c>
-      <c r="K73" s="1" t="n">
+      <c r="L73" s="1" t="n">
         <v>5.96</v>
       </c>
     </row>
@@ -3184,9 +3406,12 @@
         <v>0.1628</v>
       </c>
       <c r="J74" s="1" t="n">
-        <v>0.1633</v>
+        <v>0.1645</v>
       </c>
       <c r="K74" s="1" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="L74" s="1" t="n">
         <v>0.1619</v>
       </c>
     </row>
@@ -3221,9 +3446,12 @@
         <v>0.007285</v>
       </c>
       <c r="J75" s="1" t="n">
-        <v>0.007297</v>
+        <v>0.007355</v>
       </c>
       <c r="K75" s="1" t="n">
+        <v>0.007355</v>
+      </c>
+      <c r="L75" s="1" t="n">
         <v>0.007261</v>
       </c>
     </row>
@@ -3258,9 +3486,12 @@
         <v>0.212</v>
       </c>
       <c r="J76" s="1" t="n">
+        <v>0.2128</v>
+      </c>
+      <c r="K76" s="1" t="n">
         <v>0.2199</v>
       </c>
-      <c r="K76" s="1" t="n">
+      <c r="L76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -3295,9 +3526,12 @@
         <v>0.00582</v>
       </c>
       <c r="J77" s="1" t="n">
-        <v>0.005826</v>
+        <v>0.005844</v>
       </c>
       <c r="K77" s="1" t="n">
+        <v>0.005844</v>
+      </c>
+      <c r="L77" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -3332,9 +3566,12 @@
         <v>0.1017</v>
       </c>
       <c r="J78" s="1" t="n">
-        <v>0.1019</v>
+        <v>0.1023</v>
       </c>
       <c r="K78" s="1" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="L78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -3369,9 +3606,12 @@
         <v>0.00628</v>
       </c>
       <c r="J79" s="1" t="n">
-        <v>0.006292</v>
+        <v>0.006315</v>
       </c>
       <c r="K79" s="1" t="n">
+        <v>0.006315</v>
+      </c>
+      <c r="L79" s="1" t="n">
         <v>0.006237</v>
       </c>
     </row>
@@ -3406,9 +3646,12 @@
         <v>33.45</v>
       </c>
       <c r="J80" s="1" t="n">
-        <v>33.51</v>
+        <v>33.66</v>
       </c>
       <c r="K80" s="1" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="L80" s="1" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -3443,9 +3686,12 @@
         <v>0.0405</v>
       </c>
       <c r="J81" s="1" t="n">
-        <v>0.04051</v>
+        <v>0.04063</v>
       </c>
       <c r="K81" s="1" t="n">
+        <v>0.04063</v>
+      </c>
+      <c r="L81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -3480,9 +3726,12 @@
         <v>0.16682</v>
       </c>
       <c r="J82" s="1" t="n">
-        <v>0.1675</v>
+        <v>0.16759</v>
       </c>
       <c r="K82" s="1" t="n">
+        <v>0.16759</v>
+      </c>
+      <c r="L82" s="1" t="n">
         <v>0.16679</v>
       </c>
     </row>
@@ -3517,9 +3766,12 @@
         <v>0.1034</v>
       </c>
       <c r="J83" s="1" t="n">
-        <v>0.1037</v>
+        <v>0.1038</v>
       </c>
       <c r="K83" s="1" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="L83" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -3554,9 +3806,12 @@
         <v>0.08757</v>
       </c>
       <c r="J84" s="1" t="n">
+        <v>0.08758000000000001</v>
+      </c>
+      <c r="K84" s="1" t="n">
         <v>0.08848</v>
       </c>
-      <c r="K84" s="1" t="n">
+      <c r="L84" s="1" t="n">
         <v>0.08756</v>
       </c>
     </row>
@@ -3591,10 +3846,13 @@
         <v>0.0231</v>
       </c>
       <c r="J85" s="1" t="n">
+        <v>0.02305</v>
+      </c>
+      <c r="K85" s="1" t="n">
         <v>0.02331</v>
       </c>
-      <c r="K85" s="1" t="n">
-        <v>0.0231</v>
+      <c r="L85" s="1" t="n">
+        <v>0.02305</v>
       </c>
     </row>
     <row r="86">
@@ -3628,9 +3886,12 @@
         <v>0.24</v>
       </c>
       <c r="J86" s="1" t="n">
-        <v>0.24</v>
+        <v>0.244</v>
       </c>
       <c r="K86" s="1" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="L86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -3665,9 +3926,12 @@
         <v>358.65</v>
       </c>
       <c r="J87" s="1" t="n">
+        <v>358.47</v>
+      </c>
+      <c r="K87" s="1" t="n">
         <v>358.65</v>
       </c>
-      <c r="K87" s="1" t="n">
+      <c r="L87" s="1" t="n">
         <v>355.75</v>
       </c>
     </row>
@@ -3702,9 +3966,12 @@
         <v>0.00347</v>
       </c>
       <c r="J88" s="1" t="n">
-        <v>0.00348</v>
+        <v>0.0035</v>
       </c>
       <c r="K88" s="1" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="L88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -3739,9 +4006,12 @@
         <v>8.276999999999999</v>
       </c>
       <c r="J89" s="1" t="n">
-        <v>8.301</v>
+        <v>8.323</v>
       </c>
       <c r="K89" s="1" t="n">
+        <v>8.323</v>
+      </c>
+      <c r="L89" s="1" t="n">
         <v>8.257</v>
       </c>
     </row>
@@ -3776,9 +4046,12 @@
         <v>0.005911</v>
       </c>
       <c r="J90" s="1" t="n">
-        <v>0.005945</v>
+        <v>0.005952</v>
       </c>
       <c r="K90" s="1" t="n">
+        <v>0.005952</v>
+      </c>
+      <c r="L90" s="1" t="n">
         <v>0.005905</v>
       </c>
     </row>
@@ -3813,10 +4086,13 @@
         <v>0.06834</v>
       </c>
       <c r="J91" s="1" t="n">
+        <v>0.06812</v>
+      </c>
+      <c r="K91" s="1" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="K91" s="1" t="n">
-        <v>0.06822</v>
+      <c r="L91" s="1" t="n">
+        <v>0.06812</v>
       </c>
     </row>
     <row r="92">
@@ -3850,10 +4126,13 @@
         <v>0.02905</v>
       </c>
       <c r="J92" s="1" t="n">
+        <v>0.02866</v>
+      </c>
+      <c r="K92" s="1" t="n">
         <v>0.02905</v>
       </c>
-      <c r="K92" s="1" t="n">
-        <v>0.02867</v>
+      <c r="L92" s="1" t="n">
+        <v>0.02866</v>
       </c>
     </row>
     <row r="93">
@@ -3887,9 +4166,12 @@
         <v>5.188</v>
       </c>
       <c r="J93" s="1" t="n">
-        <v>5.202</v>
+        <v>5.228</v>
       </c>
       <c r="K93" s="1" t="n">
+        <v>5.228</v>
+      </c>
+      <c r="L93" s="1" t="n">
         <v>5.159</v>
       </c>
     </row>
@@ -3924,9 +4206,12 @@
         <v>0.000226</v>
       </c>
       <c r="J94" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="K94" s="1" t="n">
         <v>0.000228</v>
       </c>
-      <c r="K94" s="1" t="n">
+      <c r="L94" s="1" t="n">
         <v>0.000226</v>
       </c>
     </row>
@@ -3961,9 +4246,12 @@
         <v>0.9229000000000001</v>
       </c>
       <c r="J95" s="1" t="n">
-        <v>0.9248</v>
+        <v>0.9264</v>
       </c>
       <c r="K95" s="1" t="n">
+        <v>0.9264</v>
+      </c>
+      <c r="L95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -3998,9 +4286,12 @@
         <v>2.1066</v>
       </c>
       <c r="J96" s="1" t="n">
-        <v>2.1066</v>
+        <v>2.1278</v>
       </c>
       <c r="K96" s="1" t="n">
+        <v>2.1278</v>
+      </c>
+      <c r="L96" s="1" t="n">
         <v>2.0598</v>
       </c>
     </row>
@@ -4035,9 +4326,12 @@
         <v>0.3693</v>
       </c>
       <c r="J97" s="1" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="K97" s="1" t="n">
         <v>0.3722</v>
       </c>
-      <c r="K97" s="1" t="n">
+      <c r="L97" s="1" t="n">
         <v>0.3681</v>
       </c>
     </row>
@@ -4072,9 +4366,12 @@
         <v>1.619</v>
       </c>
       <c r="J98" s="1" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="K98" s="1" t="n">
         <v>1.625</v>
       </c>
-      <c r="K98" s="1" t="n">
+      <c r="L98" s="1" t="n">
         <v>1.613</v>
       </c>
     </row>
@@ -4109,10 +4406,13 @@
         <v>0.2332</v>
       </c>
       <c r="J99" s="1" t="n">
+        <v>0.2328</v>
+      </c>
+      <c r="K99" s="1" t="n">
         <v>0.2368</v>
       </c>
-      <c r="K99" s="1" t="n">
-        <v>0.2332</v>
+      <c r="L99" s="1" t="n">
+        <v>0.2328</v>
       </c>
     </row>
     <row r="100">
@@ -4146,9 +4446,12 @@
         <v>0.13694</v>
       </c>
       <c r="J100" s="1" t="n">
-        <v>0.13694</v>
+        <v>0.13745</v>
       </c>
       <c r="K100" s="1" t="n">
+        <v>0.13745</v>
+      </c>
+      <c r="L100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -4183,9 +4486,12 @@
         <v>0.07025000000000001</v>
       </c>
       <c r="J101" s="1" t="n">
+        <v>0.06988999999999999</v>
+      </c>
+      <c r="K101" s="1" t="n">
         <v>0.07115</v>
       </c>
-      <c r="K101" s="1" t="n">
+      <c r="L101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -4220,9 +4526,12 @@
         <v>0.0010822</v>
       </c>
       <c r="J102" s="1" t="n">
-        <v>0.0010875</v>
+        <v>0.0010886</v>
       </c>
       <c r="K102" s="1" t="n">
+        <v>0.0010886</v>
+      </c>
+      <c r="L102" s="1" t="n">
         <v>0.0010822</v>
       </c>
     </row>
@@ -4257,9 +4566,12 @@
         <v>0.003413</v>
       </c>
       <c r="J103" s="1" t="n">
-        <v>0.003424</v>
+        <v>0.003427</v>
       </c>
       <c r="K103" s="1" t="n">
+        <v>0.003427</v>
+      </c>
+      <c r="L103" s="1" t="n">
         <v>0.003403</v>
       </c>
     </row>
@@ -4294,10 +4606,13 @@
         <v>0.27488</v>
       </c>
       <c r="J104" s="1" t="n">
+        <v>0.27312</v>
+      </c>
+      <c r="K104" s="1" t="n">
         <v>0.27751</v>
       </c>
-      <c r="K104" s="1" t="n">
-        <v>0.27472</v>
+      <c r="L104" s="1" t="n">
+        <v>0.27312</v>
       </c>
     </row>
     <row r="105">
@@ -4331,9 +4646,12 @@
         <v>0.01254</v>
       </c>
       <c r="J105" s="1" t="n">
+        <v>0.01251</v>
+      </c>
+      <c r="K105" s="1" t="n">
         <v>0.01257</v>
       </c>
-      <c r="K105" s="1" t="n">
+      <c r="L105" s="1" t="n">
         <v>0.01243</v>
       </c>
     </row>
@@ -4368,9 +4686,12 @@
         <v>0.1358</v>
       </c>
       <c r="J106" s="1" t="n">
+        <v>0.13478</v>
+      </c>
+      <c r="K106" s="1" t="n">
         <v>0.1358</v>
       </c>
-      <c r="K106" s="1" t="n">
+      <c r="L106" s="1" t="n">
         <v>0.13329</v>
       </c>
     </row>
@@ -4405,9 +4726,12 @@
         <v>0.3504</v>
       </c>
       <c r="J107" s="1" t="n">
-        <v>0.3516</v>
+        <v>0.3522</v>
       </c>
       <c r="K107" s="1" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="L107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -4442,10 +4766,13 @@
         <v>0.1426</v>
       </c>
       <c r="J108" s="1" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="K108" s="1" t="n">
         <v>0.1436</v>
       </c>
-      <c r="K108" s="1" t="n">
-        <v>0.1426</v>
+      <c r="L108" s="1" t="n">
+        <v>0.1418</v>
       </c>
     </row>
     <row r="109">
@@ -4479,9 +4806,12 @@
         <v>0.9360000000000001</v>
       </c>
       <c r="J109" s="1" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="K109" s="1" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="K109" s="1" t="n">
+      <c r="L109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -4516,9 +4846,12 @@
         <v>0.016256</v>
       </c>
       <c r="J110" s="1" t="n">
+        <v>0.016294</v>
+      </c>
+      <c r="K110" s="1" t="n">
         <v>0.016308</v>
       </c>
-      <c r="K110" s="1" t="n">
+      <c r="L110" s="1" t="n">
         <v>0.016195</v>
       </c>
     </row>
@@ -4553,9 +4886,12 @@
         <v>0.03812</v>
       </c>
       <c r="J111" s="1" t="n">
-        <v>0.038335</v>
+        <v>0.038462</v>
       </c>
       <c r="K111" s="1" t="n">
+        <v>0.038462</v>
+      </c>
+      <c r="L111" s="1" t="n">
         <v>0.03774</v>
       </c>
     </row>
@@ -4590,9 +4926,12 @@
         <v>0.11974</v>
       </c>
       <c r="J112" s="1" t="n">
+        <v>0.11976</v>
+      </c>
+      <c r="K112" s="1" t="n">
         <v>0.12031</v>
       </c>
-      <c r="K112" s="1" t="n">
+      <c r="L112" s="1" t="n">
         <v>0.11926</v>
       </c>
     </row>
@@ -4627,10 +4966,13 @@
         <v>0.0941</v>
       </c>
       <c r="J113" s="1" t="n">
+        <v>0.09381</v>
+      </c>
+      <c r="K113" s="1" t="n">
         <v>0.09574000000000001</v>
       </c>
-      <c r="K113" s="1" t="n">
-        <v>0.0941</v>
+      <c r="L113" s="1" t="n">
+        <v>0.09381</v>
       </c>
     </row>
     <row r="114">
@@ -4664,9 +5006,12 @@
         <v>0.13002</v>
       </c>
       <c r="J114" s="1" t="n">
+        <v>0.13021</v>
+      </c>
+      <c r="K114" s="1" t="n">
         <v>0.13063</v>
       </c>
-      <c r="K114" s="1" t="n">
+      <c r="L114" s="1" t="n">
         <v>0.12895</v>
       </c>
     </row>
@@ -4701,9 +5046,12 @@
         <v>0.2645</v>
       </c>
       <c r="J115" s="1" t="n">
-        <v>0.2656</v>
+        <v>0.2663</v>
       </c>
       <c r="K115" s="1" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="L115" s="1" t="n">
         <v>0.2638</v>
       </c>
     </row>
@@ -4738,9 +5086,12 @@
         <v>0.04805</v>
       </c>
       <c r="J116" s="1" t="n">
+        <v>0.04859</v>
+      </c>
+      <c r="K116" s="1" t="n">
         <v>0.0529</v>
       </c>
-      <c r="K116" s="1" t="n">
+      <c r="L116" s="1" t="n">
         <v>0.04805</v>
       </c>
     </row>
@@ -4778,6 +5129,9 @@
         <v>0.0916</v>
       </c>
       <c r="K117" s="1" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="L117" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -4812,9 +5166,12 @@
         <v>0.05559</v>
       </c>
       <c r="J118" s="1" t="n">
+        <v>0.05538</v>
+      </c>
+      <c r="K118" s="1" t="n">
         <v>0.05563</v>
       </c>
-      <c r="K118" s="1" t="n">
+      <c r="L118" s="1" t="n">
         <v>0.05501</v>
       </c>
     </row>
@@ -4849,9 +5206,12 @@
         <v>0.01507</v>
       </c>
       <c r="J119" s="1" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="K119" s="1" t="n">
         <v>0.01515</v>
       </c>
-      <c r="K119" s="1" t="n">
+      <c r="L119" s="1" t="n">
         <v>0.01505</v>
       </c>
     </row>
@@ -4886,9 +5246,12 @@
         <v>3.064</v>
       </c>
       <c r="J120" s="1" t="n">
-        <v>3.065</v>
+        <v>3.079</v>
       </c>
       <c r="K120" s="1" t="n">
+        <v>3.079</v>
+      </c>
+      <c r="L120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -4923,9 +5286,12 @@
         <v>1.848</v>
       </c>
       <c r="J121" s="1" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="K121" s="1" t="n">
         <v>1.855</v>
       </c>
-      <c r="K121" s="1" t="n">
+      <c r="L121" s="1" t="n">
         <v>1.848</v>
       </c>
     </row>
@@ -4960,9 +5326,12 @@
         <v>1.3012</v>
       </c>
       <c r="J122" s="1" t="n">
-        <v>1.3012</v>
+        <v>1.3028</v>
       </c>
       <c r="K122" s="1" t="n">
+        <v>1.3028</v>
+      </c>
+      <c r="L122" s="1" t="n">
         <v>1.2934</v>
       </c>
     </row>
@@ -4997,9 +5366,12 @@
         <v>0.315</v>
       </c>
       <c r="J123" s="1" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="K123" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="K123" s="1" t="n">
+      <c r="L123" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -5034,9 +5406,12 @@
         <v>0.1233</v>
       </c>
       <c r="J124" s="1" t="n">
+        <v>0.12275</v>
+      </c>
+      <c r="K124" s="1" t="n">
         <v>0.12506</v>
       </c>
-      <c r="K124" s="1" t="n">
+      <c r="L124" s="1" t="n">
         <v>0.12202</v>
       </c>
     </row>
@@ -5071,9 +5446,12 @@
         <v>0.008352999999999999</v>
       </c>
       <c r="J125" s="1" t="n">
-        <v>0.008459</v>
+        <v>0.008626999999999999</v>
       </c>
       <c r="K125" s="1" t="n">
+        <v>0.008626999999999999</v>
+      </c>
+      <c r="L125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -5108,9 +5486,12 @@
         <v>0.01606</v>
       </c>
       <c r="J126" s="1" t="n">
-        <v>0.01606</v>
+        <v>0.01621</v>
       </c>
       <c r="K126" s="1" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="L126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -5145,9 +5526,12 @@
         <v>0.04394</v>
       </c>
       <c r="J127" s="1" t="n">
+        <v>0.04424</v>
+      </c>
+      <c r="K127" s="1" t="n">
         <v>0.04468</v>
       </c>
-      <c r="K127" s="1" t="n">
+      <c r="L127" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -5182,9 +5566,12 @@
         <v>0.04679</v>
       </c>
       <c r="J128" s="1" t="n">
+        <v>0.04693</v>
+      </c>
+      <c r="K128" s="1" t="n">
         <v>0.04727</v>
       </c>
-      <c r="K128" s="1" t="n">
+      <c r="L128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -5219,9 +5606,12 @@
         <v>0.09654</v>
       </c>
       <c r="J129" s="1" t="n">
-        <v>0.09654</v>
+        <v>0.09656000000000001</v>
       </c>
       <c r="K129" s="1" t="n">
+        <v>0.09656000000000001</v>
+      </c>
+      <c r="L129" s="1" t="n">
         <v>0.09543</v>
       </c>
     </row>
@@ -5256,9 +5646,12 @@
         <v>0.09853000000000001</v>
       </c>
       <c r="J130" s="1" t="n">
+        <v>0.09855</v>
+      </c>
+      <c r="K130" s="1" t="n">
         <v>0.09927</v>
       </c>
-      <c r="K130" s="1" t="n">
+      <c r="L130" s="1" t="n">
         <v>0.09848</v>
       </c>
     </row>
@@ -5293,9 +5686,12 @@
         <v>0.16637</v>
       </c>
       <c r="J131" s="1" t="n">
-        <v>0.16637</v>
+        <v>0.16695</v>
       </c>
       <c r="K131" s="1" t="n">
+        <v>0.16695</v>
+      </c>
+      <c r="L131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -5330,9 +5726,12 @@
         <v>0.01694</v>
       </c>
       <c r="J132" s="1" t="n">
+        <v>0.01696</v>
+      </c>
+      <c r="K132" s="1" t="n">
         <v>0.01702</v>
       </c>
-      <c r="K132" s="1" t="n">
+      <c r="L132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -5367,9 +5766,12 @@
         <v>0.06675</v>
       </c>
       <c r="J133" s="1" t="n">
-        <v>0.06683</v>
+        <v>0.06707</v>
       </c>
       <c r="K133" s="1" t="n">
+        <v>0.06707</v>
+      </c>
+      <c r="L133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -5404,9 +5806,12 @@
         <v>0.3022</v>
       </c>
       <c r="J134" s="1" t="n">
-        <v>0.3029</v>
+        <v>0.3042</v>
       </c>
       <c r="K134" s="1" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="L134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -5441,10 +5846,13 @@
         <v>0.04563</v>
       </c>
       <c r="J135" s="1" t="n">
+        <v>0.04502</v>
+      </c>
+      <c r="K135" s="1" t="n">
         <v>0.04563</v>
       </c>
-      <c r="K135" s="1" t="n">
-        <v>0.04508</v>
+      <c r="L135" s="1" t="n">
+        <v>0.04502</v>
       </c>
     </row>
     <row r="136">
@@ -5478,9 +5886,12 @@
         <v>0.781</v>
       </c>
       <c r="J136" s="1" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="K136" s="1" t="n">
         <v>0.783</v>
       </c>
-      <c r="K136" s="1" t="n">
+      <c r="L136" s="1" t="n">
         <v>0.781</v>
       </c>
     </row>
@@ -5515,9 +5926,12 @@
         <v>0.1171</v>
       </c>
       <c r="J137" s="1" t="n">
-        <v>0.1171</v>
+        <v>0.1178</v>
       </c>
       <c r="K137" s="1" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="L137" s="1" t="n">
         <v>0.1162</v>
       </c>
     </row>
@@ -5552,9 +5966,12 @@
         <v>0.14759</v>
       </c>
       <c r="J138" s="1" t="n">
+        <v>0.14723</v>
+      </c>
+      <c r="K138" s="1" t="n">
         <v>0.14759</v>
       </c>
-      <c r="K138" s="1" t="n">
+      <c r="L138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -5589,9 +6006,12 @@
         <v>0.05735</v>
       </c>
       <c r="J139" s="1" t="n">
-        <v>0.05735</v>
+        <v>0.05766</v>
       </c>
       <c r="K139" s="1" t="n">
+        <v>0.05766</v>
+      </c>
+      <c r="L139" s="1" t="n">
         <v>0.05699</v>
       </c>
     </row>
@@ -5626,9 +6046,12 @@
         <v>0.00726</v>
       </c>
       <c r="J140" s="1" t="n">
-        <v>0.007295</v>
+        <v>0.007302</v>
       </c>
       <c r="K140" s="1" t="n">
+        <v>0.007302</v>
+      </c>
+      <c r="L140" s="1" t="n">
         <v>0.00726</v>
       </c>
     </row>
@@ -5663,9 +6086,12 @@
         <v>0.096</v>
       </c>
       <c r="J141" s="1" t="n">
-        <v>0.09601</v>
+        <v>0.09637</v>
       </c>
       <c r="K141" s="1" t="n">
+        <v>0.09637</v>
+      </c>
+      <c r="L141" s="1" t="n">
         <v>0.09569</v>
       </c>
     </row>
@@ -5700,9 +6126,12 @@
         <v>0.08337</v>
       </c>
       <c r="J142" s="1" t="n">
-        <v>0.08363</v>
+        <v>0.08388</v>
       </c>
       <c r="K142" s="1" t="n">
+        <v>0.08388</v>
+      </c>
+      <c r="L142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -5737,9 +6166,12 @@
         <v>0.00856</v>
       </c>
       <c r="J143" s="1" t="n">
-        <v>0.0086</v>
+        <v>0.00861</v>
       </c>
       <c r="K143" s="1" t="n">
+        <v>0.00861</v>
+      </c>
+      <c r="L143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -5774,9 +6206,12 @@
         <v>0.07224999999999999</v>
       </c>
       <c r="J144" s="1" t="n">
+        <v>0.07267999999999999</v>
+      </c>
+      <c r="K144" s="1" t="n">
         <v>0.07288</v>
       </c>
-      <c r="K144" s="1" t="n">
+      <c r="L144" s="1" t="n">
         <v>0.07224999999999999</v>
       </c>
     </row>
@@ -5811,9 +6246,12 @@
         <v>0.427</v>
       </c>
       <c r="J145" s="1" t="n">
+        <v>0.4287</v>
+      </c>
+      <c r="K145" s="1" t="n">
         <v>0.4305</v>
       </c>
-      <c r="K145" s="1" t="n">
+      <c r="L145" s="1" t="n">
         <v>0.427</v>
       </c>
     </row>
@@ -5848,9 +6286,12 @@
         <v>0.0322</v>
       </c>
       <c r="J146" s="1" t="n">
+        <v>0.03227</v>
+      </c>
+      <c r="K146" s="1" t="n">
         <v>0.03276</v>
       </c>
-      <c r="K146" s="1" t="n">
+      <c r="L146" s="1" t="n">
         <v>0.0322</v>
       </c>
     </row>
@@ -5885,9 +6326,12 @@
         <v>390.45</v>
       </c>
       <c r="J147" s="1" t="n">
+        <v>390.54</v>
+      </c>
+      <c r="K147" s="1" t="n">
         <v>390.55</v>
       </c>
-      <c r="K147" s="1" t="n">
+      <c r="L147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -5922,9 +6366,12 @@
         <v>0.03299</v>
       </c>
       <c r="J148" s="1" t="n">
+        <v>0.03306</v>
+      </c>
+      <c r="K148" s="1" t="n">
         <v>0.0333</v>
       </c>
-      <c r="K148" s="1" t="n">
+      <c r="L148" s="1" t="n">
         <v>0.0329</v>
       </c>
     </row>
@@ -5959,9 +6406,12 @@
         <v>0.05294</v>
       </c>
       <c r="J149" s="1" t="n">
+        <v>0.05319</v>
+      </c>
+      <c r="K149" s="1" t="n">
         <v>0.05322</v>
       </c>
-      <c r="K149" s="1" t="n">
+      <c r="L149" s="1" t="n">
         <v>0.05289</v>
       </c>
     </row>
@@ -5996,9 +6446,12 @@
         <v>0.0004399</v>
       </c>
       <c r="J150" s="1" t="n">
+        <v>0.0004415</v>
+      </c>
+      <c r="K150" s="1" t="n">
         <v>0.000443</v>
       </c>
-      <c r="K150" s="1" t="n">
+      <c r="L150" s="1" t="n">
         <v>0.000439</v>
       </c>
     </row>
@@ -6033,9 +6486,12 @@
         <v>0.02182</v>
       </c>
       <c r="J151" s="1" t="n">
-        <v>0.02189</v>
+        <v>0.02194</v>
       </c>
       <c r="K151" s="1" t="n">
+        <v>0.02194</v>
+      </c>
+      <c r="L151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -6070,9 +6526,12 @@
         <v>0.00178</v>
       </c>
       <c r="J152" s="1" t="n">
-        <v>0.001783</v>
+        <v>0.001788</v>
       </c>
       <c r="K152" s="1" t="n">
+        <v>0.001788</v>
+      </c>
+      <c r="L152" s="1" t="n">
         <v>0.001768</v>
       </c>
     </row>
@@ -6107,9 +6566,12 @@
         <v>6.1e-06</v>
       </c>
       <c r="J153" s="1" t="n">
+        <v>6.1e-06</v>
+      </c>
+      <c r="K153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
-      <c r="K153" s="1" t="n">
+      <c r="L153" s="1" t="n">
         <v>6e-06</v>
       </c>
     </row>
@@ -6144,9 +6606,12 @@
         <v>0.1603</v>
       </c>
       <c r="J154" s="1" t="n">
-        <v>0.1603</v>
+        <v>0.1609</v>
       </c>
       <c r="K154" s="1" t="n">
+        <v>0.1609</v>
+      </c>
+      <c r="L154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -6181,9 +6646,12 @@
         <v>0.03766</v>
       </c>
       <c r="J155" s="1" t="n">
-        <v>0.03768</v>
+        <v>0.03781</v>
       </c>
       <c r="K155" s="1" t="n">
+        <v>0.03781</v>
+      </c>
+      <c r="L155" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -6218,9 +6686,12 @@
         <v>0.005397</v>
       </c>
       <c r="J156" s="1" t="n">
+        <v>0.005403</v>
+      </c>
+      <c r="K156" s="1" t="n">
         <v>0.005404</v>
       </c>
-      <c r="K156" s="1" t="n">
+      <c r="L156" s="1" t="n">
         <v>0.005364</v>
       </c>
     </row>
@@ -6255,9 +6726,12 @@
         <v>0.02263</v>
       </c>
       <c r="J157" s="1" t="n">
+        <v>0.02279</v>
+      </c>
+      <c r="K157" s="1" t="n">
         <v>0.02284</v>
       </c>
-      <c r="K157" s="1" t="n">
+      <c r="L157" s="1" t="n">
         <v>0.02263</v>
       </c>
     </row>
@@ -6292,9 +6766,12 @@
         <v>1.094</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>1.096</v>
+        <v>1.099</v>
       </c>
       <c r="K158" s="1" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="L158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -6329,9 +6806,12 @@
         <v>2.564</v>
       </c>
       <c r="J159" s="1" t="n">
-        <v>2.565</v>
+        <v>2.577</v>
       </c>
       <c r="K159" s="1" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="L159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -6366,9 +6846,12 @@
         <v>4.843</v>
       </c>
       <c r="J160" s="1" t="n">
+        <v>4.855</v>
+      </c>
+      <c r="K160" s="1" t="n">
         <v>4.858</v>
       </c>
-      <c r="K160" s="1" t="n">
+      <c r="L160" s="1" t="n">
         <v>4.836</v>
       </c>
     </row>
@@ -6403,9 +6886,12 @@
         <v>0.1601</v>
       </c>
       <c r="J161" s="1" t="n">
-        <v>0.1605</v>
+        <v>0.1607</v>
       </c>
       <c r="K161" s="1" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="L161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -6440,10 +6926,13 @@
         <v>0.20616</v>
       </c>
       <c r="J162" s="1" t="n">
+        <v>0.20425</v>
+      </c>
+      <c r="K162" s="1" t="n">
         <v>0.20754</v>
       </c>
-      <c r="K162" s="1" t="n">
-        <v>0.20584</v>
+      <c r="L162" s="1" t="n">
+        <v>0.20425</v>
       </c>
     </row>
     <row r="163">
@@ -6477,9 +6966,12 @@
         <v>0.03939</v>
       </c>
       <c r="J163" s="1" t="n">
-        <v>0.03941</v>
+        <v>0.03954</v>
       </c>
       <c r="K163" s="1" t="n">
+        <v>0.03954</v>
+      </c>
+      <c r="L163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -6514,9 +7006,12 @@
         <v>0.0636</v>
       </c>
       <c r="J164" s="1" t="n">
+        <v>0.06324</v>
+      </c>
+      <c r="K164" s="1" t="n">
         <v>0.0636</v>
       </c>
-      <c r="K164" s="1" t="n">
+      <c r="L164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -6551,9 +7046,12 @@
         <v>0.3601</v>
       </c>
       <c r="J165" s="1" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="K165" s="1" t="n">
         <v>0.3618</v>
       </c>
-      <c r="K165" s="1" t="n">
+      <c r="L165" s="1" t="n">
         <v>0.3525</v>
       </c>
     </row>
@@ -6588,9 +7086,12 @@
         <v>139.19</v>
       </c>
       <c r="J166" s="1" t="n">
-        <v>139.27</v>
+        <v>139.63</v>
       </c>
       <c r="K166" s="1" t="n">
+        <v>139.63</v>
+      </c>
+      <c r="L166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -6625,9 +7126,12 @@
         <v>0.0006434</v>
       </c>
       <c r="J167" s="1" t="n">
+        <v>0.0006491</v>
+      </c>
+      <c r="K167" s="1" t="n">
         <v>0.0006533</v>
       </c>
-      <c r="K167" s="1" t="n">
+      <c r="L167" s="1" t="n">
         <v>0.0006431</v>
       </c>
     </row>
@@ -6662,9 +7166,12 @@
         <v>0.01657</v>
       </c>
       <c r="J168" s="1" t="n">
+        <v>0.01655</v>
+      </c>
+      <c r="K168" s="1" t="n">
         <v>0.01678</v>
       </c>
-      <c r="K168" s="1" t="n">
+      <c r="L168" s="1" t="n">
         <v>0.01629</v>
       </c>
     </row>
@@ -6699,9 +7206,12 @@
         <v>0.04798</v>
       </c>
       <c r="J169" s="1" t="n">
-        <v>0.04807</v>
+        <v>0.04818</v>
       </c>
       <c r="K169" s="1" t="n">
+        <v>0.04818</v>
+      </c>
+      <c r="L169" s="1" t="n">
         <v>0.04785</v>
       </c>
     </row>
@@ -6736,9 +7246,12 @@
         <v>4.282</v>
       </c>
       <c r="J170" s="1" t="n">
+        <v>4.282</v>
+      </c>
+      <c r="K170" s="1" t="n">
         <v>4.298</v>
       </c>
-      <c r="K170" s="1" t="n">
+      <c r="L170" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -6773,9 +7286,12 @@
         <v>0.03825</v>
       </c>
       <c r="J171" s="1" t="n">
-        <v>0.03874</v>
+        <v>0.03875</v>
       </c>
       <c r="K171" s="1" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="L171" s="1" t="n">
         <v>0.03825</v>
       </c>
     </row>
@@ -6810,9 +7326,12 @@
         <v>0.0427</v>
       </c>
       <c r="J172" s="1" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="K172" s="1" t="n">
         <v>0.0431</v>
       </c>
-      <c r="K172" s="1" t="n">
+      <c r="L172" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -6847,10 +7366,13 @@
         <v>0.02406</v>
       </c>
       <c r="J173" s="1" t="n">
+        <v>0.023745</v>
+      </c>
+      <c r="K173" s="1" t="n">
         <v>0.024556</v>
       </c>
-      <c r="K173" s="1" t="n">
-        <v>0.023799</v>
+      <c r="L173" s="1" t="n">
+        <v>0.023745</v>
       </c>
     </row>
     <row r="174">
@@ -6884,9 +7406,12 @@
         <v>1.0809</v>
       </c>
       <c r="J174" s="1" t="n">
+        <v>1.0782</v>
+      </c>
+      <c r="K174" s="1" t="n">
         <v>1.0809</v>
       </c>
-      <c r="K174" s="1" t="n">
+      <c r="L174" s="1" t="n">
         <v>1.0704</v>
       </c>
     </row>
@@ -6921,10 +7446,13 @@
         <v>0.028195</v>
       </c>
       <c r="J175" s="1" t="n">
+        <v>0.028034</v>
+      </c>
+      <c r="K175" s="1" t="n">
         <v>0.028967</v>
       </c>
-      <c r="K175" s="1" t="n">
-        <v>0.028121</v>
+      <c r="L175" s="1" t="n">
+        <v>0.028034</v>
       </c>
     </row>
     <row r="176">
@@ -6958,9 +7486,12 @@
         <v>0.02198</v>
       </c>
       <c r="J176" s="1" t="n">
-        <v>0.02198</v>
+        <v>0.02207</v>
       </c>
       <c r="K176" s="1" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="L176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -6995,9 +7526,12 @@
         <v>0.5484</v>
       </c>
       <c r="J177" s="1" t="n">
+        <v>0.5492</v>
+      </c>
+      <c r="K177" s="1" t="n">
         <v>0.5501</v>
       </c>
-      <c r="K177" s="1" t="n">
+      <c r="L177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -7032,9 +7566,12 @@
         <v>0.08214</v>
       </c>
       <c r="J178" s="1" t="n">
+        <v>0.08248</v>
+      </c>
+      <c r="K178" s="1" t="n">
         <v>0.08276</v>
       </c>
-      <c r="K178" s="1" t="n">
+      <c r="L178" s="1" t="n">
         <v>0.08214</v>
       </c>
     </row>
@@ -7069,9 +7606,12 @@
         <v>0.02134</v>
       </c>
       <c r="J179" s="1" t="n">
-        <v>0.0214</v>
+        <v>0.02142</v>
       </c>
       <c r="K179" s="1" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="L179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -7106,9 +7646,12 @@
         <v>0.27259</v>
       </c>
       <c r="J180" s="1" t="n">
-        <v>0.27259</v>
+        <v>0.27417</v>
       </c>
       <c r="K180" s="1" t="n">
+        <v>0.27417</v>
+      </c>
+      <c r="L180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -7143,9 +7686,12 @@
         <v>0.00418</v>
       </c>
       <c r="J181" s="1" t="n">
-        <v>0.0042</v>
+        <v>0.00421</v>
       </c>
       <c r="K181" s="1" t="n">
+        <v>0.00421</v>
+      </c>
+      <c r="L181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -7180,9 +7726,12 @@
         <v>0.07918</v>
       </c>
       <c r="J182" s="1" t="n">
+        <v>0.07904</v>
+      </c>
+      <c r="K182" s="1" t="n">
         <v>0.07981000000000001</v>
       </c>
-      <c r="K182" s="1" t="n">
+      <c r="L182" s="1" t="n">
         <v>0.07902000000000001</v>
       </c>
     </row>
@@ -7217,9 +7766,12 @@
         <v>0.02355</v>
       </c>
       <c r="J183" s="1" t="n">
-        <v>0.02357</v>
+        <v>0.02364</v>
       </c>
       <c r="K183" s="1" t="n">
+        <v>0.02364</v>
+      </c>
+      <c r="L183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -7254,9 +7806,12 @@
         <v>6.978999999999999e-05</v>
       </c>
       <c r="J184" s="1" t="n">
-        <v>7.002e-05</v>
+        <v>7.016000000000001e-05</v>
       </c>
       <c r="K184" s="1" t="n">
+        <v>7.016000000000001e-05</v>
+      </c>
+      <c r="L184" s="1" t="n">
         <v>6.957e-05</v>
       </c>
     </row>
@@ -7291,9 +7846,12 @@
         <v>0.02134</v>
       </c>
       <c r="J185" s="1" t="n">
+        <v>0.02138</v>
+      </c>
+      <c r="K185" s="1" t="n">
         <v>0.0214</v>
       </c>
-      <c r="K185" s="1" t="n">
+      <c r="L185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -7328,9 +7886,12 @@
         <v>0.01637</v>
       </c>
       <c r="J186" s="1" t="n">
-        <v>0.01637</v>
+        <v>0.01643</v>
       </c>
       <c r="K186" s="1" t="n">
+        <v>0.01643</v>
+      </c>
+      <c r="L186" s="1" t="n">
         <v>0.01623</v>
       </c>
     </row>
@@ -7365,9 +7926,12 @@
         <v>0.977</v>
       </c>
       <c r="J187" s="1" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="K187" s="1" t="n">
         <v>0.981</v>
       </c>
-      <c r="K187" s="1" t="n">
+      <c r="L187" s="1" t="n">
         <v>0.971</v>
       </c>
     </row>
@@ -7402,9 +7966,12 @@
         <v>0.0239</v>
       </c>
       <c r="J188" s="1" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="K188" s="1" t="n">
         <v>0.024</v>
       </c>
-      <c r="K188" s="1" t="n">
+      <c r="L188" s="1" t="n">
         <v>0.0237</v>
       </c>
     </row>
@@ -7439,9 +8006,12 @@
         <v>1.8723</v>
       </c>
       <c r="J189" s="1" t="n">
-        <v>1.8739</v>
+        <v>1.8888</v>
       </c>
       <c r="K189" s="1" t="n">
+        <v>1.8888</v>
+      </c>
+      <c r="L189" s="1" t="n">
         <v>1.8609</v>
       </c>
     </row>
@@ -7476,9 +8046,12 @@
         <v>1.832</v>
       </c>
       <c r="J190" s="1" t="n">
-        <v>1.838</v>
+        <v>1.843</v>
       </c>
       <c r="K190" s="1" t="n">
+        <v>1.843</v>
+      </c>
+      <c r="L190" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -7513,9 +8086,12 @@
         <v>0.02662</v>
       </c>
       <c r="J191" s="1" t="n">
-        <v>0.0268</v>
+        <v>0.02685</v>
       </c>
       <c r="K191" s="1" t="n">
+        <v>0.02685</v>
+      </c>
+      <c r="L191" s="1" t="n">
         <v>0.02662</v>
       </c>
     </row>
@@ -7550,9 +8126,12 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="J192" s="1" t="n">
-        <v>0.0973</v>
+        <v>0.0975</v>
       </c>
       <c r="K192" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="L192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -7587,9 +8166,12 @@
         <v>0.1722</v>
       </c>
       <c r="J193" s="1" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="K193" s="1" t="n">
         <v>0.1722</v>
       </c>
-      <c r="K193" s="1" t="n">
+      <c r="L193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -7624,9 +8206,12 @@
         <v>16.314</v>
       </c>
       <c r="J194" s="1" t="n">
-        <v>16.318</v>
+        <v>16.407</v>
       </c>
       <c r="K194" s="1" t="n">
+        <v>16.407</v>
+      </c>
+      <c r="L194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -7661,9 +8246,12 @@
         <v>4.113</v>
       </c>
       <c r="J195" s="1" t="n">
-        <v>4.113</v>
+        <v>4.136</v>
       </c>
       <c r="K195" s="1" t="n">
+        <v>4.136</v>
+      </c>
+      <c r="L195" s="1" t="n">
         <v>4.087</v>
       </c>
     </row>
@@ -7698,9 +8286,12 @@
         <v>1.2701</v>
       </c>
       <c r="J196" s="1" t="n">
+        <v>1.2753</v>
+      </c>
+      <c r="K196" s="1" t="n">
         <v>1.2794</v>
       </c>
-      <c r="K196" s="1" t="n">
+      <c r="L196" s="1" t="n">
         <v>1.2663</v>
       </c>
     </row>
@@ -7735,9 +8326,12 @@
         <v>3.063</v>
       </c>
       <c r="J197" s="1" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="K197" s="1" t="n">
         <v>3.092</v>
       </c>
-      <c r="K197" s="1" t="n">
+      <c r="L197" s="1" t="n">
         <v>3.063</v>
       </c>
     </row>
@@ -7772,9 +8366,12 @@
         <v>0.01257</v>
       </c>
       <c r="J198" s="1" t="n">
+        <v>0.01261</v>
+      </c>
+      <c r="K198" s="1" t="n">
         <v>0.01266</v>
       </c>
-      <c r="K198" s="1" t="n">
+      <c r="L198" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -7809,9 +8406,12 @@
         <v>0.0001767</v>
       </c>
       <c r="J199" s="1" t="n">
-        <v>0.0001767</v>
+        <v>0.000177</v>
       </c>
       <c r="K199" s="1" t="n">
+        <v>0.000177</v>
+      </c>
+      <c r="L199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -7846,9 +8446,12 @@
         <v>115.57</v>
       </c>
       <c r="J200" s="1" t="n">
-        <v>115.62</v>
+        <v>115.81</v>
       </c>
       <c r="K200" s="1" t="n">
+        <v>115.81</v>
+      </c>
+      <c r="L200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -7883,9 +8486,12 @@
         <v>0.01021</v>
       </c>
       <c r="J201" s="1" t="n">
+        <v>0.01022</v>
+      </c>
+      <c r="K201" s="1" t="n">
         <v>0.01031</v>
       </c>
-      <c r="K201" s="1" t="n">
+      <c r="L201" s="1" t="n">
         <v>0.01021</v>
       </c>
     </row>
@@ -7920,9 +8526,12 @@
         <v>0.01069</v>
       </c>
       <c r="J202" s="1" t="n">
+        <v>0.01067</v>
+      </c>
+      <c r="K202" s="1" t="n">
         <v>0.01073</v>
       </c>
-      <c r="K202" s="1" t="n">
+      <c r="L202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -7957,9 +8566,12 @@
         <v>0.003131</v>
       </c>
       <c r="J203" s="1" t="n">
+        <v>0.00314</v>
+      </c>
+      <c r="K203" s="1" t="n">
         <v>0.003153</v>
       </c>
-      <c r="K203" s="1" t="n">
+      <c r="L203" s="1" t="n">
         <v>0.003131</v>
       </c>
     </row>
@@ -7994,9 +8606,12 @@
         <v>28.28</v>
       </c>
       <c r="J204" s="1" t="n">
-        <v>28.38</v>
+        <v>28.39</v>
       </c>
       <c r="K204" s="1" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="L204" s="1" t="n">
         <v>28.23</v>
       </c>
     </row>
@@ -8031,10 +8646,13 @@
         <v>0.5629</v>
       </c>
       <c r="J205" s="1" t="n">
+        <v>0.5592</v>
+      </c>
+      <c r="K205" s="1" t="n">
         <v>0.5636</v>
       </c>
-      <c r="K205" s="1" t="n">
-        <v>0.5608</v>
+      <c r="L205" s="1" t="n">
+        <v>0.5592</v>
       </c>
     </row>
     <row r="206">
@@ -8068,9 +8686,12 @@
         <v>0.0004404</v>
       </c>
       <c r="J206" s="1" t="n">
-        <v>0.0004417</v>
+        <v>0.0004434</v>
       </c>
       <c r="K206" s="1" t="n">
+        <v>0.0004434</v>
+      </c>
+      <c r="L206" s="1" t="n">
         <v>0.0004387</v>
       </c>
     </row>
@@ -8105,9 +8726,12 @@
         <v>0.04658</v>
       </c>
       <c r="J207" s="1" t="n">
-        <v>0.04667</v>
+        <v>0.04689</v>
       </c>
       <c r="K207" s="1" t="n">
+        <v>0.04689</v>
+      </c>
+      <c r="L207" s="1" t="n">
         <v>0.04648</v>
       </c>
     </row>
@@ -8142,9 +8766,12 @@
         <v>0.091</v>
       </c>
       <c r="J208" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K208" s="1" t="n">
         <v>0.091</v>
       </c>
-      <c r="K208" s="1" t="n">
+      <c r="L208" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -8179,9 +8806,12 @@
         <v>0.02572</v>
       </c>
       <c r="J209" s="1" t="n">
-        <v>0.02574</v>
+        <v>0.02584</v>
       </c>
       <c r="K209" s="1" t="n">
+        <v>0.02584</v>
+      </c>
+      <c r="L209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -8216,10 +8846,13 @@
         <v>0.01268</v>
       </c>
       <c r="J210" s="1" t="n">
+        <v>0.012645</v>
+      </c>
+      <c r="K210" s="1" t="n">
         <v>0.012745</v>
       </c>
-      <c r="K210" s="1" t="n">
-        <v>0.012652</v>
+      <c r="L210" s="1" t="n">
+        <v>0.012645</v>
       </c>
     </row>
     <row r="211">
@@ -8256,6 +8889,9 @@
         <v>0.0921</v>
       </c>
       <c r="K211" s="1" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="L211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -8290,9 +8926,12 @@
         <v>0.00706</v>
       </c>
       <c r="J212" s="1" t="n">
+        <v>0.00707</v>
+      </c>
+      <c r="K212" s="1" t="n">
         <v>0.007076</v>
       </c>
-      <c r="K212" s="1" t="n">
+      <c r="L212" s="1" t="n">
         <v>0.007044</v>
       </c>
     </row>
@@ -8327,9 +8966,12 @@
         <v>0.02961</v>
       </c>
       <c r="J213" s="1" t="n">
-        <v>0.02966</v>
+        <v>0.02975</v>
       </c>
       <c r="K213" s="1" t="n">
+        <v>0.02975</v>
+      </c>
+      <c r="L213" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -8364,9 +9006,12 @@
         <v>0.2698</v>
       </c>
       <c r="J214" s="1" t="n">
-        <v>0.2708</v>
+        <v>0.271</v>
       </c>
       <c r="K214" s="1" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="L214" s="1" t="n">
         <v>0.2698</v>
       </c>
     </row>
@@ -8401,9 +9046,12 @@
         <v>0.02227</v>
       </c>
       <c r="J215" s="1" t="n">
-        <v>0.02227</v>
+        <v>0.02256</v>
       </c>
       <c r="K215" s="1" t="n">
+        <v>0.02256</v>
+      </c>
+      <c r="L215" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -8438,9 +9086,12 @@
         <v>0.01463</v>
       </c>
       <c r="J216" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="K216" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="K216" s="1" t="n">
+      <c r="L216" s="1" t="n">
         <v>0.01463</v>
       </c>
     </row>
@@ -8475,9 +9126,12 @@
         <v>0.2534</v>
       </c>
       <c r="J217" s="1" t="n">
-        <v>0.2542</v>
+        <v>0.255</v>
       </c>
       <c r="K217" s="1" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="L217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -8512,9 +9166,12 @@
         <v>0.3074</v>
       </c>
       <c r="J218" s="1" t="n">
-        <v>0.3087</v>
+        <v>0.3114</v>
       </c>
       <c r="K218" s="1" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="L218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -8549,9 +9206,12 @@
         <v>0.1784</v>
       </c>
       <c r="J219" s="1" t="n">
-        <v>0.1786</v>
+        <v>0.1788</v>
       </c>
       <c r="K219" s="1" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="L219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -8586,9 +9246,12 @@
         <v>14.95</v>
       </c>
       <c r="J220" s="1" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="K220" s="1" t="n">
         <v>15.02</v>
       </c>
-      <c r="K220" s="1" t="n">
+      <c r="L220" s="1" t="n">
         <v>14.95</v>
       </c>
     </row>
@@ -8623,9 +9286,12 @@
         <v>0.01607</v>
       </c>
       <c r="J221" s="1" t="n">
-        <v>0.01611</v>
+        <v>0.01614</v>
       </c>
       <c r="K221" s="1" t="n">
+        <v>0.01614</v>
+      </c>
+      <c r="L221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -8660,9 +9326,12 @@
         <v>66.42</v>
       </c>
       <c r="J222" s="1" t="n">
+        <v>66.61</v>
+      </c>
+      <c r="K222" s="1" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="K222" s="1" t="n">
+      <c r="L222" s="1" t="n">
         <v>66.17</v>
       </c>
     </row>
@@ -8697,9 +9366,12 @@
         <v>0.09352000000000001</v>
       </c>
       <c r="J223" s="1" t="n">
+        <v>0.09316000000000001</v>
+      </c>
+      <c r="K223" s="1" t="n">
         <v>0.09352000000000001</v>
       </c>
-      <c r="K223" s="1" t="n">
+      <c r="L223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -8734,9 +9406,12 @@
         <v>0.03951</v>
       </c>
       <c r="J224" s="1" t="n">
-        <v>0.03963</v>
+        <v>0.03974</v>
       </c>
       <c r="K224" s="1" t="n">
+        <v>0.03974</v>
+      </c>
+      <c r="L224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -8771,9 +9446,12 @@
         <v>0.5701000000000001</v>
       </c>
       <c r="J225" s="1" t="n">
+        <v>0.5718</v>
+      </c>
+      <c r="K225" s="1" t="n">
         <v>0.5725</v>
       </c>
-      <c r="K225" s="1" t="n">
+      <c r="L225" s="1" t="n">
         <v>0.5695</v>
       </c>
     </row>
@@ -8808,9 +9486,12 @@
         <v>0.1179</v>
       </c>
       <c r="J226" s="1" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="K226" s="1" t="n">
         <v>0.1184</v>
       </c>
-      <c r="K226" s="1" t="n">
+      <c r="L226" s="1" t="n">
         <v>0.1166</v>
       </c>
     </row>
@@ -8845,9 +9526,12 @@
         <v>0.3165</v>
       </c>
       <c r="J227" s="1" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="K227" s="1" t="n">
         <v>0.3201</v>
       </c>
-      <c r="K227" s="1" t="n">
+      <c r="L227" s="1" t="n">
         <v>0.3165</v>
       </c>
     </row>
@@ -8882,9 +9566,12 @@
         <v>6.074</v>
       </c>
       <c r="J228" s="1" t="n">
-        <v>6.09</v>
+        <v>6.108</v>
       </c>
       <c r="K228" s="1" t="n">
+        <v>6.108</v>
+      </c>
+      <c r="L228" s="1" t="n">
         <v>6.062</v>
       </c>
     </row>
@@ -8919,9 +9606,12 @@
         <v>0.0293</v>
       </c>
       <c r="J229" s="1" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="K229" s="1" t="n">
         <v>0.0294</v>
       </c>
-      <c r="K229" s="1" t="n">
+      <c r="L229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -8956,9 +9646,12 @@
         <v>0.3297</v>
       </c>
       <c r="J230" s="1" t="n">
-        <v>0.3307</v>
+        <v>0.3325</v>
       </c>
       <c r="K230" s="1" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="L230" s="1" t="n">
         <v>0.3288</v>
       </c>
     </row>
@@ -8993,10 +9686,13 @@
         <v>0.12008</v>
       </c>
       <c r="J231" s="1" t="n">
+        <v>0.11986</v>
+      </c>
+      <c r="K231" s="1" t="n">
         <v>0.12089</v>
       </c>
-      <c r="K231" s="1" t="n">
-        <v>0.11994</v>
+      <c r="L231" s="1" t="n">
+        <v>0.11986</v>
       </c>
     </row>
     <row r="232">
@@ -9033,6 +9729,9 @@
         <v>0.1187</v>
       </c>
       <c r="K232" s="1" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="L232" s="1" t="n">
         <v>0.1182</v>
       </c>
     </row>
@@ -9067,9 +9766,12 @@
         <v>0.03017</v>
       </c>
       <c r="J233" s="1" t="n">
-        <v>0.03019</v>
+        <v>0.03039</v>
       </c>
       <c r="K233" s="1" t="n">
+        <v>0.03039</v>
+      </c>
+      <c r="L233" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -9104,9 +9806,12 @@
         <v>0.015871</v>
       </c>
       <c r="J234" s="1" t="n">
-        <v>0.015906</v>
+        <v>0.016171</v>
       </c>
       <c r="K234" s="1" t="n">
+        <v>0.016171</v>
+      </c>
+      <c r="L234" s="1" t="n">
         <v>0.0156</v>
       </c>
     </row>
@@ -9141,10 +9846,13 @@
         <v>0.0127</v>
       </c>
       <c r="J235" s="1" t="n">
+        <v>0.01268</v>
+      </c>
+      <c r="K235" s="1" t="n">
         <v>0.01281</v>
       </c>
-      <c r="K235" s="1" t="n">
-        <v>0.0127</v>
+      <c r="L235" s="1" t="n">
+        <v>0.01268</v>
       </c>
     </row>
     <row r="236">
@@ -9178,9 +9886,12 @@
         <v>0.01933</v>
       </c>
       <c r="J236" s="1" t="n">
-        <v>0.01933</v>
+        <v>0.01937</v>
       </c>
       <c r="K236" s="1" t="n">
+        <v>0.01937</v>
+      </c>
+      <c r="L236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -9215,9 +9926,12 @@
         <v>0.0852</v>
       </c>
       <c r="J237" s="1" t="n">
+        <v>0.08527</v>
+      </c>
+      <c r="K237" s="1" t="n">
         <v>0.08545999999999999</v>
       </c>
-      <c r="K237" s="1" t="n">
+      <c r="L237" s="1" t="n">
         <v>0.08427999999999999</v>
       </c>
     </row>
@@ -9255,6 +9969,9 @@
         <v>0.05892</v>
       </c>
       <c r="K238" s="1" t="n">
+        <v>0.05892</v>
+      </c>
+      <c r="L238" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>
@@ -9289,9 +10006,12 @@
         <v>0.008954</v>
       </c>
       <c r="J239" s="1" t="n">
+        <v>0.008999</v>
+      </c>
+      <c r="K239" s="1" t="n">
         <v>0.009131999999999999</v>
       </c>
-      <c r="K239" s="1" t="n">
+      <c r="L239" s="1" t="n">
         <v>0.008954</v>
       </c>
     </row>
@@ -9326,9 +10046,12 @@
         <v>0.004161</v>
       </c>
       <c r="J240" s="1" t="n">
-        <v>0.004175</v>
+        <v>0.004185</v>
       </c>
       <c r="K240" s="1" t="n">
+        <v>0.004185</v>
+      </c>
+      <c r="L240" s="1" t="n">
         <v>0.004154</v>
       </c>
     </row>
@@ -9363,9 +10086,12 @@
         <v>0.2406</v>
       </c>
       <c r="J241" s="1" t="n">
-        <v>0.241</v>
+        <v>0.2418</v>
       </c>
       <c r="K241" s="1" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="L241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -9400,9 +10126,12 @@
         <v>0.0586</v>
       </c>
       <c r="J242" s="1" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="K242" s="1" t="n">
         <v>0.0589</v>
       </c>
-      <c r="K242" s="1" t="n">
+      <c r="L242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -9437,9 +10166,12 @@
         <v>0.02362</v>
       </c>
       <c r="J243" s="1" t="n">
+        <v>0.02357</v>
+      </c>
+      <c r="K243" s="1" t="n">
         <v>0.02363</v>
       </c>
-      <c r="K243" s="1" t="n">
+      <c r="L243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -9474,9 +10206,12 @@
         <v>0.0558</v>
       </c>
       <c r="J244" s="1" t="n">
-        <v>0.05623</v>
+        <v>0.05671</v>
       </c>
       <c r="K244" s="1" t="n">
+        <v>0.05671</v>
+      </c>
+      <c r="L244" s="1" t="n">
         <v>0.05547</v>
       </c>
     </row>
@@ -9511,9 +10246,12 @@
         <v>0.03449</v>
       </c>
       <c r="J245" s="1" t="n">
-        <v>0.03449</v>
+        <v>0.03493</v>
       </c>
       <c r="K245" s="1" t="n">
+        <v>0.03493</v>
+      </c>
+      <c r="L245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -9548,9 +10286,12 @@
         <v>0.06035</v>
       </c>
       <c r="J246" s="1" t="n">
-        <v>0.06035</v>
+        <v>0.0604</v>
       </c>
       <c r="K246" s="1" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="L246" s="1" t="n">
         <v>0.0599</v>
       </c>
     </row>
@@ -9585,9 +10326,12 @@
         <v>0.382</v>
       </c>
       <c r="J247" s="1" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="K247" s="1" t="n">
         <v>0.385</v>
       </c>
-      <c r="K247" s="1" t="n">
+      <c r="L247" s="1" t="n">
         <v>0.382</v>
       </c>
     </row>
@@ -9622,9 +10366,12 @@
         <v>0.5183</v>
       </c>
       <c r="J248" s="1" t="n">
-        <v>0.5191</v>
+        <v>0.5223</v>
       </c>
       <c r="K248" s="1" t="n">
+        <v>0.5223</v>
+      </c>
+      <c r="L248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -9659,9 +10406,12 @@
         <v>0.0288</v>
       </c>
       <c r="J249" s="1" t="n">
+        <v>0.02878</v>
+      </c>
+      <c r="K249" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="K249" s="1" t="n">
+      <c r="L249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -9696,9 +10446,12 @@
         <v>0.01307</v>
       </c>
       <c r="J250" s="1" t="n">
-        <v>0.01307</v>
+        <v>0.01317</v>
       </c>
       <c r="K250" s="1" t="n">
+        <v>0.01317</v>
+      </c>
+      <c r="L250" s="1" t="n">
         <v>0.01288</v>
       </c>
     </row>
@@ -9733,9 +10486,12 @@
         <v>0.1003</v>
       </c>
       <c r="J251" s="1" t="n">
-        <v>0.1003</v>
+        <v>0.1004</v>
       </c>
       <c r="K251" s="1" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="L251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -9770,9 +10526,12 @@
         <v>0.00717</v>
       </c>
       <c r="J252" s="1" t="n">
+        <v>0.00718</v>
+      </c>
+      <c r="K252" s="1" t="n">
         <v>0.00719</v>
       </c>
-      <c r="K252" s="1" t="n">
+      <c r="L252" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -9807,9 +10566,12 @@
         <v>0.005571</v>
       </c>
       <c r="J253" s="1" t="n">
+        <v>0.005568</v>
+      </c>
+      <c r="K253" s="1" t="n">
         <v>0.005571</v>
       </c>
-      <c r="K253" s="1" t="n">
+      <c r="L253" s="1" t="n">
         <v>0.005554</v>
       </c>
     </row>
@@ -9844,9 +10606,12 @@
         <v>0.0641</v>
       </c>
       <c r="J254" s="1" t="n">
+        <v>0.0644</v>
+      </c>
+      <c r="K254" s="1" t="n">
         <v>0.0646</v>
       </c>
-      <c r="K254" s="1" t="n">
+      <c r="L254" s="1" t="n">
         <v>0.0641</v>
       </c>
     </row>
@@ -9881,9 +10646,12 @@
         <v>0.01449</v>
       </c>
       <c r="J255" s="1" t="n">
-        <v>0.01453</v>
+        <v>0.01454</v>
       </c>
       <c r="K255" s="1" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="L255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -9918,10 +10686,13 @@
         <v>0.9992760000000001</v>
       </c>
       <c r="J256" s="1" t="n">
+        <v>0.999275</v>
+      </c>
+      <c r="K256" s="1" t="n">
         <v>0.999297</v>
       </c>
-      <c r="K256" s="1" t="n">
-        <v>0.9992760000000001</v>
+      <c r="L256" s="1" t="n">
+        <v>0.999275</v>
       </c>
     </row>
     <row r="257">
@@ -9955,9 +10726,12 @@
         <v>0.02116</v>
       </c>
       <c r="J257" s="1" t="n">
-        <v>0.02116</v>
+        <v>0.02118</v>
       </c>
       <c r="K257" s="1" t="n">
+        <v>0.02118</v>
+      </c>
+      <c r="L257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -9992,9 +10766,12 @@
         <v>0.01144</v>
       </c>
       <c r="J258" s="1" t="n">
+        <v>0.01145</v>
+      </c>
+      <c r="K258" s="1" t="n">
         <v>0.01148</v>
       </c>
-      <c r="K258" s="1" t="n">
+      <c r="L258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -10029,9 +10806,12 @@
         <v>0.5104</v>
       </c>
       <c r="J259" s="1" t="n">
+        <v>0.5108</v>
+      </c>
+      <c r="K259" s="1" t="n">
         <v>0.5119</v>
       </c>
-      <c r="K259" s="1" t="n">
+      <c r="L259" s="1" t="n">
         <v>0.5071</v>
       </c>
     </row>
@@ -10066,9 +10846,12 @@
         <v>0.08468000000000001</v>
       </c>
       <c r="J260" s="1" t="n">
+        <v>0.08491</v>
+      </c>
+      <c r="K260" s="1" t="n">
         <v>0.08537</v>
       </c>
-      <c r="K260" s="1" t="n">
+      <c r="L260" s="1" t="n">
         <v>0.08436</v>
       </c>
     </row>
@@ -10103,9 +10886,12 @@
         <v>0.04121</v>
       </c>
       <c r="J261" s="1" t="n">
+        <v>0.04134</v>
+      </c>
+      <c r="K261" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="K261" s="1" t="n">
+      <c r="L261" s="1" t="n">
         <v>0.04121</v>
       </c>
     </row>
@@ -10140,9 +10926,12 @@
         <v>2.283</v>
       </c>
       <c r="J262" s="1" t="n">
-        <v>2.288</v>
+        <v>2.297</v>
       </c>
       <c r="K262" s="1" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="L262" s="1" t="n">
         <v>2.279</v>
       </c>
     </row>
@@ -10177,9 +10966,12 @@
         <v>18.55</v>
       </c>
       <c r="J263" s="1" t="n">
-        <v>18.55</v>
+        <v>18.64</v>
       </c>
       <c r="K263" s="1" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="L263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -10214,9 +11006,12 @@
         <v>0.008534999999999999</v>
       </c>
       <c r="J264" s="1" t="n">
+        <v>0.00852</v>
+      </c>
+      <c r="K264" s="1" t="n">
         <v>0.008562999999999999</v>
       </c>
-      <c r="K264" s="1" t="n">
+      <c r="L264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -10251,9 +11046,12 @@
         <v>0.3634</v>
       </c>
       <c r="J265" s="1" t="n">
-        <v>0.3645</v>
+        <v>0.3651</v>
       </c>
       <c r="K265" s="1" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="L265" s="1" t="n">
         <v>0.3627</v>
       </c>
     </row>
@@ -10288,9 +11086,12 @@
         <v>0.054943</v>
       </c>
       <c r="J266" s="1" t="n">
-        <v>0.054943</v>
+        <v>0.055369</v>
       </c>
       <c r="K266" s="1" t="n">
+        <v>0.055369</v>
+      </c>
+      <c r="L266" s="1" t="n">
         <v>0.053765</v>
       </c>
     </row>
@@ -10325,9 +11126,12 @@
         <v>0.1315</v>
       </c>
       <c r="J267" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="K267" s="1" t="n">
         <v>0.1321</v>
       </c>
-      <c r="K267" s="1" t="n">
+      <c r="L267" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -10362,9 +11166,12 @@
         <v>0.007763</v>
       </c>
       <c r="J268" s="1" t="n">
+        <v>0.007813000000000001</v>
+      </c>
+      <c r="K268" s="1" t="n">
         <v>0.007845</v>
       </c>
-      <c r="K268" s="1" t="n">
+      <c r="L268" s="1" t="n">
         <v>0.00775</v>
       </c>
     </row>
@@ -10399,9 +11206,12 @@
         <v>0.001232</v>
       </c>
       <c r="J269" s="1" t="n">
+        <v>0.001232</v>
+      </c>
+      <c r="K269" s="1" t="n">
         <v>0.00124</v>
       </c>
-      <c r="K269" s="1" t="n">
+      <c r="L269" s="1" t="n">
         <v>0.001232</v>
       </c>
     </row>
@@ -10436,9 +11246,12 @@
         <v>0.28962</v>
       </c>
       <c r="J270" s="1" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="K270" s="1" t="n">
         <v>0.28999</v>
       </c>
-      <c r="K270" s="1" t="n">
+      <c r="L270" s="1" t="n">
         <v>0.28865</v>
       </c>
     </row>
@@ -10473,9 +11286,12 @@
         <v>0.03894</v>
       </c>
       <c r="J271" s="1" t="n">
+        <v>0.03914</v>
+      </c>
+      <c r="K271" s="1" t="n">
         <v>0.03922</v>
       </c>
-      <c r="K271" s="1" t="n">
+      <c r="L271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -10510,9 +11326,12 @@
         <v>0.05181</v>
       </c>
       <c r="J272" s="1" t="n">
+        <v>0.05173</v>
+      </c>
+      <c r="K272" s="1" t="n">
         <v>0.05181</v>
       </c>
-      <c r="K272" s="1" t="n">
+      <c r="L272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -10547,9 +11366,12 @@
         <v>0.00771</v>
       </c>
       <c r="J273" s="1" t="n">
-        <v>0.00771</v>
+        <v>0.00773</v>
       </c>
       <c r="K273" s="1" t="n">
+        <v>0.00773</v>
+      </c>
+      <c r="L273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -10584,9 +11406,12 @@
         <v>0.005794</v>
       </c>
       <c r="J274" s="1" t="n">
-        <v>0.005797</v>
+        <v>0.005813</v>
       </c>
       <c r="K274" s="1" t="n">
+        <v>0.005813</v>
+      </c>
+      <c r="L274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -10621,9 +11446,12 @@
         <v>0.0005885</v>
       </c>
       <c r="J275" s="1" t="n">
+        <v>0.0005885</v>
+      </c>
+      <c r="K275" s="1" t="n">
         <v>0.0005895</v>
       </c>
-      <c r="K275" s="1" t="n">
+      <c r="L275" s="1" t="n">
         <v>0.0005863</v>
       </c>
     </row>
@@ -10658,9 +11486,12 @@
         <v>0.15077</v>
       </c>
       <c r="J276" s="1" t="n">
+        <v>0.15074</v>
+      </c>
+      <c r="K276" s="1" t="n">
         <v>0.15167</v>
       </c>
-      <c r="K276" s="1" t="n">
+      <c r="L276" s="1" t="n">
         <v>0.15004</v>
       </c>
     </row>
@@ -10695,9 +11526,12 @@
         <v>0.022981</v>
       </c>
       <c r="J277" s="1" t="n">
-        <v>0.022981</v>
+        <v>0.023073</v>
       </c>
       <c r="K277" s="1" t="n">
+        <v>0.023073</v>
+      </c>
+      <c r="L277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -10732,9 +11566,12 @@
         <v>0.04197</v>
       </c>
       <c r="J278" s="1" t="n">
+        <v>0.04188</v>
+      </c>
+      <c r="K278" s="1" t="n">
         <v>0.04242</v>
       </c>
-      <c r="K278" s="1" t="n">
+      <c r="L278" s="1" t="n">
         <v>0.04179</v>
       </c>
     </row>
@@ -10769,9 +11606,12 @@
         <v>0.0003986</v>
       </c>
       <c r="J279" s="1" t="n">
+        <v>0.0003987</v>
+      </c>
+      <c r="K279" s="1" t="n">
         <v>0.0004006</v>
       </c>
-      <c r="K279" s="1" t="n">
+      <c r="L279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -10806,9 +11646,12 @@
         <v>0.02191</v>
       </c>
       <c r="J280" s="1" t="n">
+        <v>0.02206</v>
+      </c>
+      <c r="K280" s="1" t="n">
         <v>0.02218</v>
       </c>
-      <c r="K280" s="1" t="n">
+      <c r="L280" s="1" t="n">
         <v>0.0219</v>
       </c>
     </row>
@@ -10843,9 +11686,12 @@
         <v>0.07065</v>
       </c>
       <c r="J281" s="1" t="n">
-        <v>0.07065</v>
+        <v>0.07093000000000001</v>
       </c>
       <c r="K281" s="1" t="n">
+        <v>0.07093000000000001</v>
+      </c>
+      <c r="L281" s="1" t="n">
         <v>0.06936</v>
       </c>
     </row>
@@ -10880,9 +11726,12 @@
         <v>0.006688</v>
       </c>
       <c r="J282" s="1" t="n">
+        <v>0.006751</v>
+      </c>
+      <c r="K282" s="1" t="n">
         <v>0.006804</v>
       </c>
-      <c r="K282" s="1" t="n">
+      <c r="L282" s="1" t="n">
         <v>0.006688</v>
       </c>
     </row>
@@ -10920,6 +11769,9 @@
         <v>0.12</v>
       </c>
       <c r="K283" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L283" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -10954,9 +11806,12 @@
         <v>0.005492</v>
       </c>
       <c r="J284" s="1" t="n">
-        <v>0.005492</v>
+        <v>0.005499</v>
       </c>
       <c r="K284" s="1" t="n">
+        <v>0.005499</v>
+      </c>
+      <c r="L284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -10994,6 +11849,9 @@
         <v>1.272</v>
       </c>
       <c r="K285" s="1" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="L285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -11028,9 +11886,12 @@
         <v>0.4433</v>
       </c>
       <c r="J286" s="1" t="n">
-        <v>0.4441</v>
+        <v>0.4458</v>
       </c>
       <c r="K286" s="1" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="L286" s="1" t="n">
         <v>0.4423</v>
       </c>
     </row>
@@ -11065,9 +11926,12 @@
         <v>0.007927999999999999</v>
       </c>
       <c r="J287" s="1" t="n">
-        <v>0.007932</v>
+        <v>0.007998999999999999</v>
       </c>
       <c r="K287" s="1" t="n">
+        <v>0.007998999999999999</v>
+      </c>
+      <c r="L287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -11102,9 +11966,12 @@
         <v>0.02936</v>
       </c>
       <c r="J288" s="1" t="n">
+        <v>0.02948</v>
+      </c>
+      <c r="K288" s="1" t="n">
         <v>0.0295</v>
       </c>
-      <c r="K288" s="1" t="n">
+      <c r="L288" s="1" t="n">
         <v>0.02914</v>
       </c>
     </row>
@@ -11139,9 +12006,12 @@
         <v>0.2818</v>
       </c>
       <c r="J289" s="1" t="n">
-        <v>0.2822</v>
+        <v>0.2824</v>
       </c>
       <c r="K289" s="1" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="L289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -11176,9 +12046,12 @@
         <v>2.758</v>
       </c>
       <c r="J290" s="1" t="n">
-        <v>2.764</v>
+        <v>2.783</v>
       </c>
       <c r="K290" s="1" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="L290" s="1" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -11213,9 +12086,12 @@
         <v>0.003181</v>
       </c>
       <c r="J291" s="1" t="n">
-        <v>0.003181</v>
+        <v>0.003187</v>
       </c>
       <c r="K291" s="1" t="n">
+        <v>0.003187</v>
+      </c>
+      <c r="L291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -11250,9 +12126,12 @@
         <v>0.4478</v>
       </c>
       <c r="J292" s="1" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="K292" s="1" t="n">
         <v>0.4488</v>
       </c>
-      <c r="K292" s="1" t="n">
+      <c r="L292" s="1" t="n">
         <v>0.4475</v>
       </c>
     </row>
@@ -11287,9 +12166,12 @@
         <v>0.08136</v>
       </c>
       <c r="J293" s="1" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="K293" s="1" t="n">
         <v>0.08298</v>
       </c>
-      <c r="K293" s="1" t="n">
+      <c r="L293" s="1" t="n">
         <v>0.08136</v>
       </c>
     </row>
@@ -11324,9 +12206,12 @@
         <v>0.02789</v>
       </c>
       <c r="J294" s="1" t="n">
-        <v>0.02791</v>
+        <v>0.02801</v>
       </c>
       <c r="K294" s="1" t="n">
+        <v>0.02801</v>
+      </c>
+      <c r="L294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -11361,9 +12246,12 @@
         <v>0.952</v>
       </c>
       <c r="J295" s="1" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="K295" s="1" t="n">
         <v>0.958</v>
       </c>
-      <c r="K295" s="1" t="n">
+      <c r="L295" s="1" t="n">
         <v>0.952</v>
       </c>
     </row>
@@ -11398,9 +12286,12 @@
         <v>0.006979</v>
       </c>
       <c r="J296" s="1" t="n">
+        <v>0.006975</v>
+      </c>
+      <c r="K296" s="1" t="n">
         <v>0.007008</v>
       </c>
-      <c r="K296" s="1" t="n">
+      <c r="L296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -11435,9 +12326,12 @@
         <v>0.1211</v>
       </c>
       <c r="J297" s="1" t="n">
-        <v>0.1213</v>
+        <v>0.1214</v>
       </c>
       <c r="K297" s="1" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="L297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -11472,9 +12366,12 @@
         <v>0.01554</v>
       </c>
       <c r="J298" s="1" t="n">
-        <v>0.01558</v>
+        <v>0.01563</v>
       </c>
       <c r="K298" s="1" t="n">
+        <v>0.01563</v>
+      </c>
+      <c r="L298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -11509,9 +12406,12 @@
         <v>0.4418</v>
       </c>
       <c r="J299" s="1" t="n">
-        <v>0.4422</v>
+        <v>0.4431</v>
       </c>
       <c r="K299" s="1" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="L299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -11546,9 +12446,12 @@
         <v>0.009140000000000001</v>
       </c>
       <c r="J300" s="1" t="n">
+        <v>0.00916</v>
+      </c>
+      <c r="K300" s="1" t="n">
         <v>0.00924</v>
       </c>
-      <c r="K300" s="1" t="n">
+      <c r="L300" s="1" t="n">
         <v>0.009140000000000001</v>
       </c>
     </row>
@@ -11583,9 +12486,12 @@
         <v>0.1856</v>
       </c>
       <c r="J301" s="1" t="n">
-        <v>0.1856</v>
+        <v>0.1864</v>
       </c>
       <c r="K301" s="1" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="L301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -11620,9 +12526,12 @@
         <v>0.00758</v>
       </c>
       <c r="J302" s="1" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="K302" s="1" t="n">
         <v>0.00765</v>
       </c>
-      <c r="K302" s="1" t="n">
+      <c r="L302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -11657,9 +12566,12 @@
         <v>0.0002157</v>
       </c>
       <c r="J303" s="1" t="n">
+        <v>0.0002164</v>
+      </c>
+      <c r="K303" s="1" t="n">
         <v>0.0002171</v>
       </c>
-      <c r="K303" s="1" t="n">
+      <c r="L303" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -11694,9 +12606,12 @@
         <v>0.01544</v>
       </c>
       <c r="J304" s="1" t="n">
+        <v>0.01551</v>
+      </c>
+      <c r="K304" s="1" t="n">
         <v>0.01553</v>
       </c>
-      <c r="K304" s="1" t="n">
+      <c r="L304" s="1" t="n">
         <v>0.01542</v>
       </c>
     </row>
@@ -11731,9 +12646,12 @@
         <v>0.07382</v>
       </c>
       <c r="J305" s="1" t="n">
-        <v>0.07394000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="K305" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="L305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -11768,9 +12686,12 @@
         <v>0.08303000000000001</v>
       </c>
       <c r="J306" s="1" t="n">
-        <v>0.0832</v>
+        <v>0.08346000000000001</v>
       </c>
       <c r="K306" s="1" t="n">
+        <v>0.08346000000000001</v>
+      </c>
+      <c r="L306" s="1" t="n">
         <v>0.08275</v>
       </c>
     </row>
@@ -11805,9 +12726,12 @@
         <v>0.01803</v>
       </c>
       <c r="J307" s="1" t="n">
+        <v>0.01809</v>
+      </c>
+      <c r="K307" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="K307" s="1" t="n">
+      <c r="L307" s="1" t="n">
         <v>0.01803</v>
       </c>
     </row>
@@ -11842,9 +12766,12 @@
         <v>0.000625</v>
       </c>
       <c r="J308" s="1" t="n">
-        <v>0.0006255</v>
+        <v>0.0006271</v>
       </c>
       <c r="K308" s="1" t="n">
+        <v>0.0006271</v>
+      </c>
+      <c r="L308" s="1" t="n">
         <v>0.0006212</v>
       </c>
     </row>
@@ -11879,9 +12806,12 @@
         <v>0.0822</v>
       </c>
       <c r="J309" s="1" t="n">
+        <v>0.08269</v>
+      </c>
+      <c r="K309" s="1" t="n">
         <v>0.08294</v>
       </c>
-      <c r="K309" s="1" t="n">
+      <c r="L309" s="1" t="n">
         <v>0.0822</v>
       </c>
     </row>
@@ -11919,6 +12849,9 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="K310" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="L310" s="1" t="n">
         <v>0.0973</v>
       </c>
     </row>
@@ -11953,9 +12886,12 @@
         <v>0.2112</v>
       </c>
       <c r="J311" s="1" t="n">
-        <v>0.2119</v>
+        <v>0.2126</v>
       </c>
       <c r="K311" s="1" t="n">
+        <v>0.2126</v>
+      </c>
+      <c r="L311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -11990,9 +12926,12 @@
         <v>0.389</v>
       </c>
       <c r="J312" s="1" t="n">
-        <v>0.394</v>
+        <v>0.3957</v>
       </c>
       <c r="K312" s="1" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="L312" s="1" t="n">
         <v>0.387</v>
       </c>
     </row>
@@ -12027,10 +12966,13 @@
         <v>0.10495</v>
       </c>
       <c r="J313" s="1" t="n">
+        <v>0.10455</v>
+      </c>
+      <c r="K313" s="1" t="n">
         <v>0.10542</v>
       </c>
-      <c r="K313" s="1" t="n">
-        <v>0.10492</v>
+      <c r="L313" s="1" t="n">
+        <v>0.10455</v>
       </c>
     </row>
     <row r="314">
@@ -12064,9 +13006,12 @@
         <v>0.08654000000000001</v>
       </c>
       <c r="J314" s="1" t="n">
-        <v>0.08654000000000001</v>
+        <v>0.08673</v>
       </c>
       <c r="K314" s="1" t="n">
+        <v>0.08673</v>
+      </c>
+      <c r="L314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -12101,9 +13046,12 @@
         <v>0.1181</v>
       </c>
       <c r="J315" s="1" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="K315" s="1" t="n">
         <v>0.1185</v>
       </c>
-      <c r="K315" s="1" t="n">
+      <c r="L315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -12138,10 +13086,13 @@
         <v>0.03627</v>
       </c>
       <c r="J316" s="1" t="n">
+        <v>0.03619</v>
+      </c>
+      <c r="K316" s="1" t="n">
         <v>0.03681</v>
       </c>
-      <c r="K316" s="1" t="n">
-        <v>0.03627</v>
+      <c r="L316" s="1" t="n">
+        <v>0.03619</v>
       </c>
     </row>
     <row r="317">
@@ -12175,9 +13126,12 @@
         <v>0.08157</v>
       </c>
       <c r="J317" s="1" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="K317" s="1" t="n">
         <v>0.08164</v>
       </c>
-      <c r="K317" s="1" t="n">
+      <c r="L317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -12212,9 +13166,12 @@
         <v>0.03743</v>
       </c>
       <c r="J318" s="1" t="n">
+        <v>0.03745</v>
+      </c>
+      <c r="K318" s="1" t="n">
         <v>0.03766</v>
       </c>
-      <c r="K318" s="1" t="n">
+      <c r="L318" s="1" t="n">
         <v>0.03736</v>
       </c>
     </row>
@@ -12249,9 +13206,12 @@
         <v>0.4299</v>
       </c>
       <c r="J319" s="1" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="K319" s="1" t="n">
         <v>0.4347</v>
       </c>
-      <c r="K319" s="1" t="n">
+      <c r="L319" s="1" t="n">
         <v>0.4296</v>
       </c>
     </row>
@@ -12286,9 +13246,12 @@
         <v>0.1599</v>
       </c>
       <c r="J320" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="K320" s="1" t="n">
         <v>0.1614</v>
       </c>
-      <c r="K320" s="1" t="n">
+      <c r="L320" s="1" t="n">
         <v>0.1599</v>
       </c>
     </row>
@@ -12323,9 +13286,12 @@
         <v>5.679</v>
       </c>
       <c r="J321" s="1" t="n">
-        <v>5.681</v>
+        <v>5.685</v>
       </c>
       <c r="K321" s="1" t="n">
+        <v>5.685</v>
+      </c>
+      <c r="L321" s="1" t="n">
         <v>5.677</v>
       </c>
     </row>
@@ -12360,9 +13326,12 @@
         <v>0.003714</v>
       </c>
       <c r="J322" s="1" t="n">
-        <v>0.003746</v>
+        <v>0.003754</v>
       </c>
       <c r="K322" s="1" t="n">
+        <v>0.003754</v>
+      </c>
+      <c r="L322" s="1" t="n">
         <v>0.003714</v>
       </c>
     </row>
@@ -12397,9 +13366,12 @@
         <v>0.001759</v>
       </c>
       <c r="J323" s="1" t="n">
+        <v>0.001758</v>
+      </c>
+      <c r="K323" s="1" t="n">
         <v>0.001761</v>
       </c>
-      <c r="K323" s="1" t="n">
+      <c r="L323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -12437,6 +13409,9 @@
         <v>1.2e-05</v>
       </c>
       <c r="K324" s="1" t="n">
+        <v>1.2e-05</v>
+      </c>
+      <c r="L324" s="1" t="n">
         <v>1.19e-05</v>
       </c>
     </row>
@@ -12474,6 +13449,9 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="K325" s="1" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="L325" s="1" t="n">
         <v>0.0857</v>
       </c>
     </row>
@@ -12511,6 +13489,9 @@
         <v>0.01736</v>
       </c>
       <c r="K326" s="1" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="L326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -12545,9 +13526,12 @@
         <v>0.01683</v>
       </c>
       <c r="J327" s="1" t="n">
+        <v>0.01687</v>
+      </c>
+      <c r="K327" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="K327" s="1" t="n">
+      <c r="L327" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -12582,9 +13566,12 @@
         <v>4.446</v>
       </c>
       <c r="J328" s="1" t="n">
+        <v>4.454</v>
+      </c>
+      <c r="K328" s="1" t="n">
         <v>4.462</v>
       </c>
-      <c r="K328" s="1" t="n">
+      <c r="L328" s="1" t="n">
         <v>4.446</v>
       </c>
     </row>
@@ -12619,9 +13606,12 @@
         <v>0.009611</v>
       </c>
       <c r="J329" s="1" t="n">
+        <v>0.009717999999999999</v>
+      </c>
+      <c r="K329" s="1" t="n">
         <v>0.009861</v>
       </c>
-      <c r="K329" s="1" t="n">
+      <c r="L329" s="1" t="n">
         <v>0.009532000000000001</v>
       </c>
     </row>
@@ -12656,9 +13646,12 @@
         <v>5191.7</v>
       </c>
       <c r="J330" s="1" t="n">
+        <v>5189.1</v>
+      </c>
+      <c r="K330" s="1" t="n">
         <v>5192.9</v>
       </c>
-      <c r="K330" s="1" t="n">
+      <c r="L330" s="1" t="n">
         <v>5185.8</v>
       </c>
     </row>
@@ -12693,9 +13686,12 @@
         <v>0.07063999999999999</v>
       </c>
       <c r="J331" s="1" t="n">
+        <v>0.07079000000000001</v>
+      </c>
+      <c r="K331" s="1" t="n">
         <v>0.07087</v>
       </c>
-      <c r="K331" s="1" t="n">
+      <c r="L331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -12730,9 +13726,12 @@
         <v>0.06081</v>
       </c>
       <c r="J332" s="1" t="n">
+        <v>0.06092</v>
+      </c>
+      <c r="K332" s="1" t="n">
         <v>0.06106</v>
       </c>
-      <c r="K332" s="1" t="n">
+      <c r="L332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -12767,9 +13766,12 @@
         <v>0.10499</v>
       </c>
       <c r="J333" s="1" t="n">
-        <v>0.10499</v>
+        <v>0.10558</v>
       </c>
       <c r="K333" s="1" t="n">
+        <v>0.10558</v>
+      </c>
+      <c r="L333" s="1" t="n">
         <v>0.10341</v>
       </c>
     </row>
@@ -12804,9 +13806,12 @@
         <v>0.08758000000000001</v>
       </c>
       <c r="J334" s="1" t="n">
+        <v>0.08773</v>
+      </c>
+      <c r="K334" s="1" t="n">
         <v>0.08837</v>
       </c>
-      <c r="K334" s="1" t="n">
+      <c r="L334" s="1" t="n">
         <v>0.08734</v>
       </c>
     </row>
@@ -12841,9 +13846,12 @@
         <v>0.01643</v>
       </c>
       <c r="J335" s="1" t="n">
-        <v>0.01643</v>
+        <v>0.016445</v>
       </c>
       <c r="K335" s="1" t="n">
+        <v>0.016445</v>
+      </c>
+      <c r="L335" s="1" t="n">
         <v>0.016391</v>
       </c>
     </row>
@@ -12878,9 +13886,12 @@
         <v>0.0459</v>
       </c>
       <c r="J336" s="1" t="n">
-        <v>0.046</v>
+        <v>0.04619</v>
       </c>
       <c r="K336" s="1" t="n">
+        <v>0.04619</v>
+      </c>
+      <c r="L336" s="1" t="n">
         <v>0.04583</v>
       </c>
     </row>
@@ -12915,9 +13926,12 @@
         <v>0.187</v>
       </c>
       <c r="J337" s="1" t="n">
-        <v>0.187</v>
+        <v>0.1891</v>
       </c>
       <c r="K337" s="1" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="L337" s="1" t="n">
         <v>0.1838</v>
       </c>
     </row>
@@ -12952,9 +13966,12 @@
         <v>0.1836</v>
       </c>
       <c r="J338" s="1" t="n">
-        <v>0.1836</v>
+        <v>0.1843</v>
       </c>
       <c r="K338" s="1" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="L338" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -12989,9 +14006,12 @@
         <v>0.01836</v>
       </c>
       <c r="J339" s="1" t="n">
-        <v>0.01838</v>
+        <v>0.01843</v>
       </c>
       <c r="K339" s="1" t="n">
+        <v>0.01843</v>
+      </c>
+      <c r="L339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -13026,9 +14046,12 @@
         <v>0.02314</v>
       </c>
       <c r="J340" s="1" t="n">
-        <v>0.02314</v>
+        <v>0.02325</v>
       </c>
       <c r="K340" s="1" t="n">
+        <v>0.02325</v>
+      </c>
+      <c r="L340" s="1" t="n">
         <v>0.02305</v>
       </c>
     </row>
@@ -13063,9 +14086,12 @@
         <v>0.4563</v>
       </c>
       <c r="J341" s="1" t="n">
+        <v>0.4573</v>
+      </c>
+      <c r="K341" s="1" t="n">
         <v>0.4577</v>
       </c>
-      <c r="K341" s="1" t="n">
+      <c r="L341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -13100,9 +14126,12 @@
         <v>0.01346</v>
       </c>
       <c r="J342" s="1" t="n">
-        <v>0.01349</v>
+        <v>0.0135</v>
       </c>
       <c r="K342" s="1" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="L342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -13137,9 +14166,12 @@
         <v>2.874</v>
       </c>
       <c r="J343" s="1" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K343" s="1" t="n">
         <v>2.89</v>
       </c>
-      <c r="K343" s="1" t="n">
+      <c r="L343" s="1" t="n">
         <v>2.872</v>
       </c>
     </row>
@@ -13174,9 +14206,12 @@
         <v>0.1517</v>
       </c>
       <c r="J344" s="1" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="K344" s="1" t="n">
         <v>0.1577</v>
       </c>
-      <c r="K344" s="1" t="n">
+      <c r="L344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -13211,9 +14246,12 @@
         <v>0.005344</v>
       </c>
       <c r="J345" s="1" t="n">
+        <v>0.005366</v>
+      </c>
+      <c r="K345" s="1" t="n">
         <v>0.005367</v>
       </c>
-      <c r="K345" s="1" t="n">
+      <c r="L345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -13248,9 +14286,12 @@
         <v>0.05782</v>
       </c>
       <c r="J346" s="1" t="n">
+        <v>0.05784</v>
+      </c>
+      <c r="K346" s="1" t="n">
         <v>0.0579</v>
       </c>
-      <c r="K346" s="1" t="n">
+      <c r="L346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -13285,9 +14326,12 @@
         <v>2613</v>
       </c>
       <c r="J347" s="1" t="n">
+        <v>2606</v>
+      </c>
+      <c r="K347" s="1" t="n">
         <v>2613</v>
       </c>
-      <c r="K347" s="1" t="n">
+      <c r="L347" s="1" t="n">
         <v>2597</v>
       </c>
     </row>
@@ -13322,9 +14366,12 @@
         <v>0.04596</v>
       </c>
       <c r="J348" s="1" t="n">
-        <v>0.04621</v>
+        <v>0.04642</v>
       </c>
       <c r="K348" s="1" t="n">
+        <v>0.04642</v>
+      </c>
+      <c r="L348" s="1" t="n">
         <v>0.04595</v>
       </c>
     </row>
@@ -13359,9 +14406,12 @@
         <v>0.00565</v>
       </c>
       <c r="J349" s="1" t="n">
+        <v>0.00565</v>
+      </c>
+      <c r="K349" s="1" t="n">
         <v>0.005714</v>
       </c>
-      <c r="K349" s="1" t="n">
+      <c r="L349" s="1" t="n">
         <v>0.00565</v>
       </c>
     </row>
@@ -13396,9 +14446,12 @@
         <v>195.39</v>
       </c>
       <c r="J350" s="1" t="n">
-        <v>195.51</v>
+        <v>195.95</v>
       </c>
       <c r="K350" s="1" t="n">
+        <v>195.95</v>
+      </c>
+      <c r="L350" s="1" t="n">
         <v>195.23</v>
       </c>
     </row>
@@ -13433,9 +14486,12 @@
         <v>0.08225</v>
       </c>
       <c r="J351" s="1" t="n">
+        <v>0.08235000000000001</v>
+      </c>
+      <c r="K351" s="1" t="n">
         <v>0.08245</v>
       </c>
-      <c r="K351" s="1" t="n">
+      <c r="L351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -13470,10 +14526,13 @@
         <v>0.007494</v>
       </c>
       <c r="J352" s="1" t="n">
+        <v>0.007436</v>
+      </c>
+      <c r="K352" s="1" t="n">
         <v>0.007571</v>
       </c>
-      <c r="K352" s="1" t="n">
-        <v>0.007458</v>
+      <c r="L352" s="1" t="n">
+        <v>0.007436</v>
       </c>
     </row>
     <row r="353">
@@ -13507,9 +14566,12 @@
         <v>1.5093</v>
       </c>
       <c r="J353" s="1" t="n">
+        <v>1.5028</v>
+      </c>
+      <c r="K353" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="K353" s="1" t="n">
+      <c r="L353" s="1" t="n">
         <v>1.4807</v>
       </c>
     </row>
@@ -13544,9 +14606,12 @@
         <v>0.07664</v>
       </c>
       <c r="J354" s="1" t="n">
-        <v>0.07671</v>
+        <v>0.07677</v>
       </c>
       <c r="K354" s="1" t="n">
+        <v>0.07677</v>
+      </c>
+      <c r="L354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -13581,10 +14646,13 @@
         <v>0.04889</v>
       </c>
       <c r="J355" s="1" t="n">
+        <v>0.04855</v>
+      </c>
+      <c r="K355" s="1" t="n">
         <v>0.04921</v>
       </c>
-      <c r="K355" s="1" t="n">
-        <v>0.04859</v>
+      <c r="L355" s="1" t="n">
+        <v>0.04855</v>
       </c>
     </row>
     <row r="356">
@@ -13621,6 +14689,9 @@
         <v>0.2862</v>
       </c>
       <c r="K356" s="1" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="L356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -13655,9 +14726,12 @@
         <v>0.1467</v>
       </c>
       <c r="J357" s="1" t="n">
-        <v>0.1468</v>
+        <v>0.1472</v>
       </c>
       <c r="K357" s="1" t="n">
+        <v>0.1472</v>
+      </c>
+      <c r="L357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -13692,10 +14766,13 @@
         <v>1.351</v>
       </c>
       <c r="J358" s="1" t="n">
+        <v>1.349</v>
+      </c>
+      <c r="K358" s="1" t="n">
         <v>1.355</v>
       </c>
-      <c r="K358" s="1" t="n">
-        <v>1.35</v>
+      <c r="L358" s="1" t="n">
+        <v>1.349</v>
       </c>
     </row>
     <row r="359">
@@ -13729,9 +14806,12 @@
         <v>0.6096</v>
       </c>
       <c r="J359" s="1" t="n">
-        <v>0.6117</v>
+        <v>0.6135</v>
       </c>
       <c r="K359" s="1" t="n">
+        <v>0.6135</v>
+      </c>
+      <c r="L359" s="1" t="n">
         <v>0.6081</v>
       </c>
     </row>
@@ -13766,9 +14846,12 @@
         <v>0.1146</v>
       </c>
       <c r="J360" s="1" t="n">
-        <v>0.1146</v>
+        <v>0.1149</v>
       </c>
       <c r="K360" s="1" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="L360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -13803,9 +14886,12 @@
         <v>0.02648</v>
       </c>
       <c r="J361" s="1" t="n">
-        <v>0.02648</v>
+        <v>0.02678</v>
       </c>
       <c r="K361" s="1" t="n">
+        <v>0.02678</v>
+      </c>
+      <c r="L361" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -13840,9 +14926,12 @@
         <v>3.03e-05</v>
       </c>
       <c r="J362" s="1" t="n">
-        <v>3.04e-05</v>
+        <v>3.05e-05</v>
       </c>
       <c r="K362" s="1" t="n">
+        <v>3.05e-05</v>
+      </c>
+      <c r="L362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -13877,9 +14966,12 @@
         <v>0.01047</v>
       </c>
       <c r="J363" s="1" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="K363" s="1" t="n">
         <v>0.01047</v>
       </c>
-      <c r="K363" s="1" t="n">
+      <c r="L363" s="1" t="n">
         <v>0.01018</v>
       </c>
     </row>
@@ -13914,9 +15006,12 @@
         <v>0.06211</v>
       </c>
       <c r="J364" s="1" t="n">
-        <v>0.0622</v>
+        <v>0.06233</v>
       </c>
       <c r="K364" s="1" t="n">
+        <v>0.06233</v>
+      </c>
+      <c r="L364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -13951,9 +15046,12 @@
         <v>0.03291</v>
       </c>
       <c r="J365" s="1" t="n">
+        <v>0.03285</v>
+      </c>
+      <c r="K365" s="1" t="n">
         <v>0.03299</v>
       </c>
-      <c r="K365" s="1" t="n">
+      <c r="L365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -13988,9 +15086,12 @@
         <v>0.03312</v>
       </c>
       <c r="J366" s="1" t="n">
-        <v>0.03312</v>
+        <v>0.0333</v>
       </c>
       <c r="K366" s="1" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="L366" s="1" t="n">
         <v>0.03283</v>
       </c>
     </row>
@@ -14025,9 +15126,12 @@
         <v>0.01231</v>
       </c>
       <c r="J367" s="1" t="n">
-        <v>0.01231</v>
+        <v>0.012321</v>
       </c>
       <c r="K367" s="1" t="n">
+        <v>0.012321</v>
+      </c>
+      <c r="L367" s="1" t="n">
         <v>0.012155</v>
       </c>
     </row>
@@ -14062,9 +15166,12 @@
         <v>0.03561</v>
       </c>
       <c r="J368" s="1" t="n">
-        <v>0.03561</v>
+        <v>0.03574</v>
       </c>
       <c r="K368" s="1" t="n">
+        <v>0.03574</v>
+      </c>
+      <c r="L368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -14099,9 +15206,12 @@
         <v>0.6296</v>
       </c>
       <c r="J369" s="1" t="n">
+        <v>0.6283</v>
+      </c>
+      <c r="K369" s="1" t="n">
         <v>0.6307</v>
       </c>
-      <c r="K369" s="1" t="n">
+      <c r="L369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -14136,9 +15246,12 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="J370" s="1" t="n">
+        <v>0.00848</v>
+      </c>
+      <c r="K370" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="K370" s="1" t="n">
+      <c r="L370" s="1" t="n">
         <v>0.00843</v>
       </c>
     </row>
@@ -14173,9 +15286,12 @@
         <v>0.003918</v>
       </c>
       <c r="J371" s="1" t="n">
-        <v>0.003918</v>
+        <v>0.004026</v>
       </c>
       <c r="K371" s="1" t="n">
+        <v>0.004026</v>
+      </c>
+      <c r="L371" s="1" t="n">
         <v>0.003242</v>
       </c>
     </row>
@@ -14210,9 +15326,12 @@
         <v>0.13358</v>
       </c>
       <c r="J372" s="1" t="n">
+        <v>0.13366</v>
+      </c>
+      <c r="K372" s="1" t="n">
         <v>0.13391</v>
       </c>
-      <c r="K372" s="1" t="n">
+      <c r="L372" s="1" t="n">
         <v>0.13227</v>
       </c>
     </row>
@@ -14247,9 +15366,12 @@
         <v>0.007786</v>
       </c>
       <c r="J373" s="1" t="n">
+        <v>0.007807</v>
+      </c>
+      <c r="K373" s="1" t="n">
         <v>0.007822000000000001</v>
       </c>
-      <c r="K373" s="1" t="n">
+      <c r="L373" s="1" t="n">
         <v>0.007771</v>
       </c>
     </row>
@@ -14284,9 +15406,12 @@
         <v>0.01982</v>
       </c>
       <c r="J374" s="1" t="n">
+        <v>0.01981</v>
+      </c>
+      <c r="K374" s="1" t="n">
         <v>0.01982</v>
       </c>
-      <c r="K374" s="1" t="n">
+      <c r="L374" s="1" t="n">
         <v>0.01969</v>
       </c>
     </row>
@@ -14321,9 +15446,12 @@
         <v>0.0005918</v>
       </c>
       <c r="J375" s="1" t="n">
+        <v>0.0005921</v>
+      </c>
+      <c r="K375" s="1" t="n">
         <v>0.000594</v>
       </c>
-      <c r="K375" s="1" t="n">
+      <c r="L375" s="1" t="n">
         <v>0.0005910000000000001</v>
       </c>
     </row>
@@ -14358,9 +15486,12 @@
         <v>0.0362</v>
       </c>
       <c r="J376" s="1" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="K376" s="1" t="n">
         <v>0.0363</v>
       </c>
-      <c r="K376" s="1" t="n">
+      <c r="L376" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -14395,9 +15526,12 @@
         <v>0.0007921</v>
       </c>
       <c r="J377" s="1" t="n">
-        <v>0.0007921</v>
+        <v>0.0007956</v>
       </c>
       <c r="K377" s="1" t="n">
+        <v>0.0007956</v>
+      </c>
+      <c r="L377" s="1" t="n">
         <v>0.0007848</v>
       </c>
     </row>
@@ -14432,9 +15566,12 @@
         <v>2.034</v>
       </c>
       <c r="J378" s="1" t="n">
-        <v>2.034</v>
+        <v>2.044</v>
       </c>
       <c r="K378" s="1" t="n">
+        <v>2.044</v>
+      </c>
+      <c r="L378" s="1" t="n">
         <v>1.973</v>
       </c>
     </row>
@@ -14469,9 +15606,12 @@
         <v>0.0005903</v>
       </c>
       <c r="J379" s="1" t="n">
-        <v>0.0005913</v>
+        <v>0.000593</v>
       </c>
       <c r="K379" s="1" t="n">
+        <v>0.000593</v>
+      </c>
+      <c r="L379" s="1" t="n">
         <v>0.0005881</v>
       </c>
     </row>
@@ -14506,9 +15646,12 @@
         <v>0.03749</v>
       </c>
       <c r="J380" s="1" t="n">
-        <v>0.03751</v>
+        <v>0.03756</v>
       </c>
       <c r="K380" s="1" t="n">
+        <v>0.03756</v>
+      </c>
+      <c r="L380" s="1" t="n">
         <v>0.03737</v>
       </c>
     </row>
@@ -14543,9 +15686,12 @@
         <v>0.05474</v>
       </c>
       <c r="J381" s="1" t="n">
-        <v>0.05481</v>
+        <v>0.05486</v>
       </c>
       <c r="K381" s="1" t="n">
+        <v>0.05486</v>
+      </c>
+      <c r="L381" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -14580,9 +15726,12 @@
         <v>0.01209</v>
       </c>
       <c r="J382" s="1" t="n">
-        <v>0.01213</v>
+        <v>0.01214</v>
       </c>
       <c r="K382" s="1" t="n">
+        <v>0.01214</v>
+      </c>
+      <c r="L382" s="1" t="n">
         <v>0.01202</v>
       </c>
     </row>
@@ -14617,9 +15766,12 @@
         <v>0.001549</v>
       </c>
       <c r="J383" s="1" t="n">
+        <v>0.001553</v>
+      </c>
+      <c r="K383" s="1" t="n">
         <v>0.001559</v>
       </c>
-      <c r="K383" s="1" t="n">
+      <c r="L383" s="1" t="n">
         <v>0.001549</v>
       </c>
     </row>
@@ -14654,9 +15806,12 @@
         <v>0.0002164</v>
       </c>
       <c r="J384" s="1" t="n">
-        <v>0.0002164</v>
+        <v>0.0002167</v>
       </c>
       <c r="K384" s="1" t="n">
+        <v>0.0002167</v>
+      </c>
+      <c r="L384" s="1" t="n">
         <v>0.0002154</v>
       </c>
     </row>
@@ -14694,6 +15849,9 @@
         <v>0.00242</v>
       </c>
       <c r="K385" s="1" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="L385" s="1" t="n">
         <v>0.0024</v>
       </c>
     </row>
@@ -14728,9 +15886,12 @@
         <v>3.928</v>
       </c>
       <c r="J386" s="1" t="n">
-        <v>3.933</v>
+        <v>3.951</v>
       </c>
       <c r="K386" s="1" t="n">
+        <v>3.951</v>
+      </c>
+      <c r="L386" s="1" t="n">
         <v>3.892</v>
       </c>
     </row>
@@ -14765,9 +15926,12 @@
         <v>0.0006281</v>
       </c>
       <c r="J387" s="1" t="n">
-        <v>0.0006282</v>
+        <v>0.0006316</v>
       </c>
       <c r="K387" s="1" t="n">
+        <v>0.0006316</v>
+      </c>
+      <c r="L387" s="1" t="n">
         <v>0.0006236</v>
       </c>
     </row>
@@ -14802,9 +15966,12 @@
         <v>0.00655</v>
       </c>
       <c r="J388" s="1" t="n">
+        <v>0.00659</v>
+      </c>
+      <c r="K388" s="1" t="n">
         <v>0.00673</v>
       </c>
-      <c r="K388" s="1" t="n">
+      <c r="L388" s="1" t="n">
         <v>0.00653</v>
       </c>
     </row>
@@ -14839,9 +16006,12 @@
         <v>0.1321</v>
       </c>
       <c r="J389" s="1" t="n">
-        <v>0.1321</v>
+        <v>0.1324</v>
       </c>
       <c r="K389" s="1" t="n">
+        <v>0.1324</v>
+      </c>
+      <c r="L389" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -14876,9 +16046,12 @@
         <v>0.03248</v>
       </c>
       <c r="J390" s="1" t="n">
+        <v>0.03242</v>
+      </c>
+      <c r="K390" s="1" t="n">
         <v>0.03248</v>
       </c>
-      <c r="K390" s="1" t="n">
+      <c r="L390" s="1" t="n">
         <v>0.03201</v>
       </c>
     </row>
@@ -14913,9 +16086,12 @@
         <v>0.06375</v>
       </c>
       <c r="J391" s="1" t="n">
-        <v>0.06375</v>
+        <v>0.06393</v>
       </c>
       <c r="K391" s="1" t="n">
+        <v>0.06393</v>
+      </c>
+      <c r="L391" s="1" t="n">
         <v>0.06344</v>
       </c>
     </row>
@@ -14950,9 +16126,12 @@
         <v>27.69</v>
       </c>
       <c r="J392" s="1" t="n">
-        <v>27.82</v>
+        <v>27.88</v>
       </c>
       <c r="K392" s="1" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="L392" s="1" t="n">
         <v>27.57</v>
       </c>
     </row>
@@ -14990,6 +16169,9 @@
         <v>0.000414</v>
       </c>
       <c r="K393" s="1" t="n">
+        <v>0.000414</v>
+      </c>
+      <c r="L393" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -15024,9 +16206,12 @@
         <v>0.0696</v>
       </c>
       <c r="J394" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K394" s="1" t="n">
         <v>0.07005</v>
       </c>
-      <c r="K394" s="1" t="n">
+      <c r="L394" s="1" t="n">
         <v>0.06926</v>
       </c>
     </row>
@@ -15064,6 +16249,9 @@
         <v>0.2614</v>
       </c>
       <c r="K395" s="1" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="L395" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -15098,9 +16286,12 @@
         <v>0.004682</v>
       </c>
       <c r="J396" s="1" t="n">
-        <v>0.00469</v>
+        <v>0.004693</v>
       </c>
       <c r="K396" s="1" t="n">
+        <v>0.004693</v>
+      </c>
+      <c r="L396" s="1" t="n">
         <v>0.004677</v>
       </c>
     </row>
@@ -15135,9 +16326,12 @@
         <v>0.2356</v>
       </c>
       <c r="J397" s="1" t="n">
-        <v>0.2356</v>
+        <v>0.2367</v>
       </c>
       <c r="K397" s="1" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="L397" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
@@ -15172,9 +16366,12 @@
         <v>0.18172</v>
       </c>
       <c r="J398" s="1" t="n">
-        <v>0.18172</v>
+        <v>0.18235</v>
       </c>
       <c r="K398" s="1" t="n">
+        <v>0.18235</v>
+      </c>
+      <c r="L398" s="1" t="n">
         <v>0.18106</v>
       </c>
     </row>
@@ -15209,9 +16406,12 @@
         <v>0.0414</v>
       </c>
       <c r="J399" s="1" t="n">
-        <v>0.0414</v>
+        <v>0.0415</v>
       </c>
       <c r="K399" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="L399" s="1" t="n">
         <v>0.04108</v>
       </c>
     </row>
@@ -15249,6 +16449,9 @@
         <v>0.076</v>
       </c>
       <c r="K400" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="L400" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -15283,9 +16486,12 @@
         <v>0.001763</v>
       </c>
       <c r="J401" s="1" t="n">
+        <v>0.001759</v>
+      </c>
+      <c r="K401" s="1" t="n">
         <v>0.001766</v>
       </c>
-      <c r="K401" s="1" t="n">
+      <c r="L401" s="1" t="n">
         <v>0.001739</v>
       </c>
     </row>
@@ -15320,9 +16526,12 @@
         <v>0.05391</v>
       </c>
       <c r="J402" s="1" t="n">
-        <v>0.05401</v>
+        <v>0.05402</v>
       </c>
       <c r="K402" s="1" t="n">
+        <v>0.05402</v>
+      </c>
+      <c r="L402" s="1" t="n">
         <v>0.05362</v>
       </c>
     </row>
@@ -15357,9 +16566,12 @@
         <v>2028.66</v>
       </c>
       <c r="J403" s="1" t="n">
+        <v>2030.26</v>
+      </c>
+      <c r="K403" s="1" t="n">
         <v>2031.8</v>
       </c>
-      <c r="K403" s="1" t="n">
+      <c r="L403" s="1" t="n">
         <v>2026.65</v>
       </c>
     </row>
@@ -15394,9 +16606,12 @@
         <v>1.08</v>
       </c>
       <c r="J404" s="1" t="n">
+        <v>1.079</v>
+      </c>
+      <c r="K404" s="1" t="n">
         <v>1.082</v>
       </c>
-      <c r="K404" s="1" t="n">
+      <c r="L404" s="1" t="n">
         <v>1.078</v>
       </c>
     </row>
@@ -15431,10 +16646,13 @@
         <v>7.673</v>
       </c>
       <c r="J405" s="1" t="n">
+        <v>7.647</v>
+      </c>
+      <c r="K405" s="1" t="n">
         <v>7.673</v>
       </c>
-      <c r="K405" s="1" t="n">
-        <v>7.649</v>
+      <c r="L405" s="1" t="n">
+        <v>7.647</v>
       </c>
     </row>
     <row r="406">
@@ -15468,9 +16686,12 @@
         <v>3.254</v>
       </c>
       <c r="J406" s="1" t="n">
-        <v>3.257</v>
+        <v>3.274</v>
       </c>
       <c r="K406" s="1" t="n">
+        <v>3.274</v>
+      </c>
+      <c r="L406" s="1" t="n">
         <v>3.238</v>
       </c>
     </row>
@@ -15508,6 +16729,9 @@
         <v>0.1823</v>
       </c>
       <c r="K407" s="1" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="L407" s="1" t="n">
         <v>0.1814</v>
       </c>
     </row>
@@ -15542,9 +16766,12 @@
         <v>0.1527</v>
       </c>
       <c r="J408" s="1" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="K408" s="1" t="n">
         <v>0.1537</v>
       </c>
-      <c r="K408" s="1" t="n">
+      <c r="L408" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -15579,9 +16806,12 @@
         <v>0.07369000000000001</v>
       </c>
       <c r="J409" s="1" t="n">
-        <v>0.07369000000000001</v>
+        <v>0.07385</v>
       </c>
       <c r="K409" s="1" t="n">
+        <v>0.07385</v>
+      </c>
+      <c r="L409" s="1" t="n">
         <v>0.07315000000000001</v>
       </c>
     </row>
@@ -15616,9 +16846,12 @@
         <v>0.0211</v>
       </c>
       <c r="J410" s="1" t="n">
+        <v>0.02112</v>
+      </c>
+      <c r="K410" s="1" t="n">
         <v>0.02118</v>
       </c>
-      <c r="K410" s="1" t="n">
+      <c r="L410" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -15653,9 +16886,12 @@
         <v>0.2683</v>
       </c>
       <c r="J411" s="1" t="n">
+        <v>0.2675</v>
+      </c>
+      <c r="K411" s="1" t="n">
         <v>0.2683</v>
       </c>
-      <c r="K411" s="1" t="n">
+      <c r="L411" s="1" t="n">
         <v>0.2642</v>
       </c>
     </row>
@@ -15690,9 +16926,12 @@
         <v>0.007358</v>
       </c>
       <c r="J412" s="1" t="n">
-        <v>0.007383</v>
+        <v>0.007396</v>
       </c>
       <c r="K412" s="1" t="n">
+        <v>0.007396</v>
+      </c>
+      <c r="L412" s="1" t="n">
         <v>0.007302</v>
       </c>
     </row>
@@ -15727,9 +16966,12 @@
         <v>0.01387</v>
       </c>
       <c r="J413" s="1" t="n">
-        <v>0.01391</v>
+        <v>0.01392</v>
       </c>
       <c r="K413" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="L413" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -15764,9 +17006,12 @@
         <v>0.093</v>
       </c>
       <c r="J414" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="K414" s="1" t="n">
         <v>0.093</v>
       </c>
-      <c r="K414" s="1" t="n">
+      <c r="L414" s="1" t="n">
         <v>0.092</v>
       </c>
     </row>
@@ -15801,9 +17046,12 @@
         <v>0.04009</v>
       </c>
       <c r="J415" s="1" t="n">
-        <v>0.04012</v>
+        <v>0.04015</v>
       </c>
       <c r="K415" s="1" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="L415" s="1" t="n">
         <v>0.03985</v>
       </c>
     </row>
@@ -15838,9 +17086,12 @@
         <v>0.2839</v>
       </c>
       <c r="J416" s="1" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="K416" s="1" t="n">
         <v>0.2854</v>
       </c>
-      <c r="K416" s="1" t="n">
+      <c r="L416" s="1" t="n">
         <v>0.2839</v>
       </c>
     </row>
@@ -15875,9 +17126,12 @@
         <v>1.828</v>
       </c>
       <c r="J417" s="1" t="n">
+        <v>1.822</v>
+      </c>
+      <c r="K417" s="1" t="n">
         <v>1.831</v>
       </c>
-      <c r="K417" s="1" t="n">
+      <c r="L417" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -15912,9 +17166,12 @@
         <v>0.06704</v>
       </c>
       <c r="J418" s="1" t="n">
-        <v>0.06707</v>
+        <v>0.06718</v>
       </c>
       <c r="K418" s="1" t="n">
+        <v>0.06718</v>
+      </c>
+      <c r="L418" s="1" t="n">
         <v>0.06668</v>
       </c>
     </row>
@@ -15949,9 +17206,12 @@
         <v>207.39</v>
       </c>
       <c r="J419" s="1" t="n">
-        <v>207.46</v>
+        <v>207.47</v>
       </c>
       <c r="K419" s="1" t="n">
+        <v>207.47</v>
+      </c>
+      <c r="L419" s="1" t="n">
         <v>207.35</v>
       </c>
     </row>
@@ -15986,9 +17246,12 @@
         <v>73.27</v>
       </c>
       <c r="J420" s="1" t="n">
-        <v>73.31999999999999</v>
+        <v>73.37</v>
       </c>
       <c r="K420" s="1" t="n">
+        <v>73.37</v>
+      </c>
+      <c r="L420" s="1" t="n">
         <v>73.15000000000001</v>
       </c>
     </row>
@@ -16023,9 +17286,12 @@
         <v>0.07232</v>
       </c>
       <c r="J421" s="1" t="n">
+        <v>0.07241</v>
+      </c>
+      <c r="K421" s="1" t="n">
         <v>0.07251000000000001</v>
       </c>
-      <c r="K421" s="1" t="n">
+      <c r="L421" s="1" t="n">
         <v>0.07226</v>
       </c>
     </row>
@@ -16060,9 +17326,12 @@
         <v>0.05033</v>
       </c>
       <c r="J422" s="1" t="n">
+        <v>0.05015</v>
+      </c>
+      <c r="K422" s="1" t="n">
         <v>0.05076</v>
       </c>
-      <c r="K422" s="1" t="n">
+      <c r="L422" s="1" t="n">
         <v>0.04998</v>
       </c>
     </row>
@@ -16097,9 +17366,12 @@
         <v>0.001151</v>
       </c>
       <c r="J423" s="1" t="n">
-        <v>0.001152</v>
+        <v>0.001153</v>
       </c>
       <c r="K423" s="1" t="n">
+        <v>0.001153</v>
+      </c>
+      <c r="L423" s="1" t="n">
         <v>0.001148</v>
       </c>
     </row>
@@ -16134,9 +17406,12 @@
         <v>0.00502</v>
       </c>
       <c r="J424" s="1" t="n">
+        <v>0.00503</v>
+      </c>
+      <c r="K424" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="K424" s="1" t="n">
+      <c r="L424" s="1" t="n">
         <v>0.00501</v>
       </c>
     </row>
@@ -16171,9 +17446,12 @@
         <v>0.1272</v>
       </c>
       <c r="J425" s="1" t="n">
-        <v>0.1274</v>
+        <v>0.1281</v>
       </c>
       <c r="K425" s="1" t="n">
+        <v>0.1281</v>
+      </c>
+      <c r="L425" s="1" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -16208,9 +17486,12 @@
         <v>1.298</v>
       </c>
       <c r="J426" s="1" t="n">
-        <v>1.299</v>
+        <v>1.301</v>
       </c>
       <c r="K426" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="L426" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -16245,9 +17526,12 @@
         <v>0.004408</v>
       </c>
       <c r="J427" s="1" t="n">
-        <v>0.004413</v>
+        <v>0.00442</v>
       </c>
       <c r="K427" s="1" t="n">
+        <v>0.00442</v>
+      </c>
+      <c r="L427" s="1" t="n">
         <v>0.004393</v>
       </c>
     </row>
@@ -16282,9 +17566,12 @@
         <v>0.005045</v>
       </c>
       <c r="J428" s="1" t="n">
-        <v>0.00505</v>
+        <v>0.005072</v>
       </c>
       <c r="K428" s="1" t="n">
+        <v>0.005072</v>
+      </c>
+      <c r="L428" s="1" t="n">
         <v>0.005017</v>
       </c>
     </row>
@@ -16319,9 +17606,12 @@
         <v>0.02316</v>
       </c>
       <c r="J429" s="1" t="n">
+        <v>0.02327</v>
+      </c>
+      <c r="K429" s="1" t="n">
         <v>0.02329</v>
       </c>
-      <c r="K429" s="1" t="n">
+      <c r="L429" s="1" t="n">
         <v>0.02288</v>
       </c>
     </row>
@@ -16356,9 +17646,12 @@
         <v>0.02499</v>
       </c>
       <c r="J430" s="1" t="n">
+        <v>0.02499</v>
+      </c>
+      <c r="K430" s="1" t="n">
         <v>0.02517</v>
       </c>
-      <c r="K430" s="1" t="n">
+      <c r="L430" s="1" t="n">
         <v>0.02499</v>
       </c>
     </row>
@@ -16396,6 +17689,9 @@
         <v>0.016</v>
       </c>
       <c r="K431" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="L431" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -16430,9 +17726,12 @@
         <v>0.5443</v>
       </c>
       <c r="J432" s="1" t="n">
+        <v>0.5447</v>
+      </c>
+      <c r="K432" s="1" t="n">
         <v>0.546</v>
       </c>
-      <c r="K432" s="1" t="n">
+      <c r="L432" s="1" t="n">
         <v>0.5439000000000001</v>
       </c>
     </row>
@@ -16467,9 +17766,12 @@
         <v>0.001385</v>
       </c>
       <c r="J433" s="1" t="n">
+        <v>0.001386</v>
+      </c>
+      <c r="K433" s="1" t="n">
         <v>0.001389</v>
       </c>
-      <c r="K433" s="1" t="n">
+      <c r="L433" s="1" t="n">
         <v>0.001383</v>
       </c>
     </row>
@@ -16504,9 +17806,12 @@
         <v>0.3959</v>
       </c>
       <c r="J434" s="1" t="n">
-        <v>0.397</v>
+        <v>0.3972</v>
       </c>
       <c r="K434" s="1" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="L434" s="1" t="n">
         <v>0.3925</v>
       </c>
     </row>
@@ -16541,9 +17846,12 @@
         <v>0.001388</v>
       </c>
       <c r="J435" s="1" t="n">
+        <v>0.001392</v>
+      </c>
+      <c r="K435" s="1" t="n">
         <v>0.001393</v>
       </c>
-      <c r="K435" s="1" t="n">
+      <c r="L435" s="1" t="n">
         <v>0.001388</v>
       </c>
     </row>
@@ -16581,6 +17889,9 @@
         <v>0.00718</v>
       </c>
       <c r="K436" s="1" t="n">
+        <v>0.00718</v>
+      </c>
+      <c r="L436" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -16615,9 +17926,12 @@
         <v>0.002003</v>
       </c>
       <c r="J437" s="1" t="n">
-        <v>0.002003</v>
+        <v>0.002012</v>
       </c>
       <c r="K437" s="1" t="n">
+        <v>0.002012</v>
+      </c>
+      <c r="L437" s="1" t="n">
         <v>0.001982</v>
       </c>
     </row>
@@ -16652,9 +17966,12 @@
         <v>0.3133</v>
       </c>
       <c r="J438" s="1" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="K438" s="1" t="n">
         <v>0.3147</v>
       </c>
-      <c r="K438" s="1" t="n">
+      <c r="L438" s="1" t="n">
         <v>0.3122</v>
       </c>
     </row>
@@ -16689,9 +18006,12 @@
         <v>0.04429</v>
       </c>
       <c r="J439" s="1" t="n">
+        <v>0.04436</v>
+      </c>
+      <c r="K439" s="1" t="n">
         <v>0.04438</v>
       </c>
-      <c r="K439" s="1" t="n">
+      <c r="L439" s="1" t="n">
         <v>0.04426</v>
       </c>
     </row>
@@ -16726,9 +18046,12 @@
         <v>0.911</v>
       </c>
       <c r="J440" s="1" t="n">
-        <v>0.911</v>
+        <v>0.913</v>
       </c>
       <c r="K440" s="1" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="L440" s="1" t="n">
         <v>0.906</v>
       </c>
     </row>
@@ -16763,9 +18086,12 @@
         <v>1552.4</v>
       </c>
       <c r="J441" s="1" t="n">
+        <v>1552.18</v>
+      </c>
+      <c r="K441" s="1" t="n">
         <v>1552.4</v>
       </c>
-      <c r="K441" s="1" t="n">
+      <c r="L441" s="1" t="n">
         <v>1548.06</v>
       </c>
     </row>
@@ -16800,9 +18126,12 @@
         <v>0.0007976</v>
       </c>
       <c r="J442" s="1" t="n">
-        <v>0.0008032</v>
+        <v>0.0008061</v>
       </c>
       <c r="K442" s="1" t="n">
+        <v>0.0008061</v>
+      </c>
+      <c r="L442" s="1" t="n">
         <v>0.0007877</v>
       </c>
     </row>
@@ -16837,9 +18166,12 @@
         <v>0.003518</v>
       </c>
       <c r="J443" s="1" t="n">
+        <v>0.003533</v>
+      </c>
+      <c r="K443" s="1" t="n">
         <v>0.003558</v>
       </c>
-      <c r="K443" s="1" t="n">
+      <c r="L443" s="1" t="n">
         <v>0.003515</v>
       </c>
     </row>
@@ -16874,9 +18206,12 @@
         <v>1.986</v>
       </c>
       <c r="J444" s="1" t="n">
-        <v>1.989</v>
+        <v>1.994</v>
       </c>
       <c r="K444" s="1" t="n">
+        <v>1.994</v>
+      </c>
+      <c r="L444" s="1" t="n">
         <v>1.977</v>
       </c>
     </row>
@@ -16911,9 +18246,12 @@
         <v>1.311</v>
       </c>
       <c r="J445" s="1" t="n">
-        <v>1.311</v>
+        <v>1.319</v>
       </c>
       <c r="K445" s="1" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="L445" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -16948,9 +18286,12 @@
         <v>0.06907000000000001</v>
       </c>
       <c r="J446" s="1" t="n">
+        <v>0.06908</v>
+      </c>
+      <c r="K446" s="1" t="n">
         <v>0.06929</v>
       </c>
-      <c r="K446" s="1" t="n">
+      <c r="L446" s="1" t="n">
         <v>0.0689</v>
       </c>
     </row>
@@ -16985,9 +18326,12 @@
         <v>0.02375</v>
       </c>
       <c r="J447" s="1" t="n">
+        <v>0.02381</v>
+      </c>
+      <c r="K447" s="1" t="n">
         <v>0.02403</v>
       </c>
-      <c r="K447" s="1" t="n">
+      <c r="L447" s="1" t="n">
         <v>0.02347</v>
       </c>
     </row>
@@ -17022,9 +18366,12 @@
         <v>0.01403</v>
       </c>
       <c r="J448" s="1" t="n">
-        <v>0.01403</v>
+        <v>0.0141</v>
       </c>
       <c r="K448" s="1" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="L448" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -17059,9 +18406,12 @@
         <v>3.733</v>
       </c>
       <c r="J449" s="1" t="n">
-        <v>3.734</v>
+        <v>3.748</v>
       </c>
       <c r="K449" s="1" t="n">
+        <v>3.748</v>
+      </c>
+      <c r="L449" s="1" t="n">
         <v>3.726</v>
       </c>
     </row>
@@ -17096,9 +18446,12 @@
         <v>0.0113</v>
       </c>
       <c r="J450" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="K450" s="1" t="n">
         <v>0.0115</v>
       </c>
-      <c r="K450" s="1" t="n">
+      <c r="L450" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -17133,9 +18486,12 @@
         <v>0.01034</v>
       </c>
       <c r="J451" s="1" t="n">
-        <v>0.01034</v>
+        <v>0.01038</v>
       </c>
       <c r="K451" s="1" t="n">
+        <v>0.01038</v>
+      </c>
+      <c r="L451" s="1" t="n">
         <v>0.01024</v>
       </c>
     </row>
@@ -17170,9 +18526,12 @@
         <v>0.153</v>
       </c>
       <c r="J452" s="1" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="K452" s="1" t="n">
         <v>0.1532</v>
       </c>
-      <c r="K452" s="1" t="n">
+      <c r="L452" s="1" t="n">
         <v>0.1522</v>
       </c>
     </row>
@@ -17207,9 +18566,12 @@
         <v>151.15</v>
       </c>
       <c r="J453" s="1" t="n">
-        <v>151.19</v>
+        <v>151.29</v>
       </c>
       <c r="K453" s="1" t="n">
+        <v>151.29</v>
+      </c>
+      <c r="L453" s="1" t="n">
         <v>150.85</v>
       </c>
     </row>
@@ -17244,9 +18606,12 @@
         <v>0.008630000000000001</v>
       </c>
       <c r="J454" s="1" t="n">
-        <v>0.008633</v>
+        <v>0.008639000000000001</v>
       </c>
       <c r="K454" s="1" t="n">
+        <v>0.008639000000000001</v>
+      </c>
+      <c r="L454" s="1" t="n">
         <v>0.008593999999999999</v>
       </c>
     </row>
@@ -17281,9 +18646,12 @@
         <v>0.05255</v>
       </c>
       <c r="J455" s="1" t="n">
-        <v>0.05255</v>
+        <v>0.05258</v>
       </c>
       <c r="K455" s="1" t="n">
+        <v>0.05258</v>
+      </c>
+      <c r="L455" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -17318,9 +18686,12 @@
         <v>0.30925</v>
       </c>
       <c r="J456" s="1" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="K456" s="1" t="n">
         <v>0.30925</v>
       </c>
-      <c r="K456" s="1" t="n">
+      <c r="L456" s="1" t="n">
         <v>0.30269</v>
       </c>
     </row>
@@ -17355,9 +18726,12 @@
         <v>0.00547</v>
       </c>
       <c r="J457" s="1" t="n">
-        <v>0.00547</v>
+        <v>0.00549</v>
       </c>
       <c r="K457" s="1" t="n">
+        <v>0.00549</v>
+      </c>
+      <c r="L457" s="1" t="n">
         <v>0.00544</v>
       </c>
     </row>
@@ -17392,9 +18766,12 @@
         <v>0.1004</v>
       </c>
       <c r="J458" s="1" t="n">
-        <v>0.1007</v>
+        <v>0.1008</v>
       </c>
       <c r="K458" s="1" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="L458" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -17429,9 +18806,12 @@
         <v>0.001835</v>
       </c>
       <c r="J459" s="1" t="n">
-        <v>0.001835</v>
+        <v>0.001844</v>
       </c>
       <c r="K459" s="1" t="n">
+        <v>0.001844</v>
+      </c>
+      <c r="L459" s="1" t="n">
         <v>0.001825</v>
       </c>
     </row>
@@ -17466,9 +18846,12 @@
         <v>0.01839</v>
       </c>
       <c r="J460" s="1" t="n">
+        <v>0.01842</v>
+      </c>
+      <c r="K460" s="1" t="n">
         <v>0.01848</v>
       </c>
-      <c r="K460" s="1" t="n">
+      <c r="L460" s="1" t="n">
         <v>0.01822</v>
       </c>
     </row>
@@ -17503,9 +18886,12 @@
         <v>0.0004859</v>
       </c>
       <c r="J461" s="1" t="n">
-        <v>0.0004877</v>
+        <v>0.0004883</v>
       </c>
       <c r="K461" s="1" t="n">
+        <v>0.0004883</v>
+      </c>
+      <c r="L461" s="1" t="n">
         <v>0.0004842</v>
       </c>
     </row>
@@ -17540,9 +18926,12 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="J462" s="1" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="K462" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="L462" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -17577,9 +18966,12 @@
         <v>0.07915</v>
       </c>
       <c r="J463" s="1" t="n">
-        <v>0.07931000000000001</v>
+        <v>0.07954</v>
       </c>
       <c r="K463" s="1" t="n">
+        <v>0.07954</v>
+      </c>
+      <c r="L463" s="1" t="n">
         <v>0.07888000000000001</v>
       </c>
     </row>
@@ -17614,9 +19006,12 @@
         <v>0.03198</v>
       </c>
       <c r="J464" s="1" t="n">
+        <v>0.03191</v>
+      </c>
+      <c r="K464" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="K464" s="1" t="n">
+      <c r="L464" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -17651,9 +19046,12 @@
         <v>0.01615</v>
       </c>
       <c r="J465" s="1" t="n">
-        <v>0.01618</v>
+        <v>0.01623</v>
       </c>
       <c r="K465" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="L465" s="1" t="n">
         <v>0.01613</v>
       </c>
     </row>
@@ -17688,9 +19086,12 @@
         <v>0.06786</v>
       </c>
       <c r="J466" s="1" t="n">
-        <v>0.06786</v>
+        <v>0.06794</v>
       </c>
       <c r="K466" s="1" t="n">
+        <v>0.06794</v>
+      </c>
+      <c r="L466" s="1" t="n">
         <v>0.06763</v>
       </c>
     </row>
@@ -17725,9 +19126,12 @@
         <v>0.04332</v>
       </c>
       <c r="J467" s="1" t="n">
-        <v>0.04332</v>
+        <v>0.04344</v>
       </c>
       <c r="K467" s="1" t="n">
+        <v>0.04344</v>
+      </c>
+      <c r="L467" s="1" t="n">
         <v>0.04322</v>
       </c>
     </row>
@@ -17762,9 +19166,12 @@
         <v>0.05617</v>
       </c>
       <c r="J468" s="1" t="n">
+        <v>0.05639</v>
+      </c>
+      <c r="K468" s="1" t="n">
         <v>0.05795</v>
       </c>
-      <c r="K468" s="1" t="n">
+      <c r="L468" s="1" t="n">
         <v>0.05587</v>
       </c>
     </row>
@@ -17799,9 +19206,12 @@
         <v>0.2309</v>
       </c>
       <c r="J469" s="1" t="n">
-        <v>0.2309</v>
+        <v>0.2317</v>
       </c>
       <c r="K469" s="1" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="L469" s="1" t="n">
         <v>0.2294</v>
       </c>
     </row>
@@ -17836,9 +19246,12 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="J470" s="1" t="n">
-        <v>0.0905</v>
+        <v>0.0906</v>
       </c>
       <c r="K470" s="1" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="L470" s="1" t="n">
         <v>0.0902</v>
       </c>
     </row>
@@ -17873,9 +19286,12 @@
         <v>0.0667</v>
       </c>
       <c r="J471" s="1" t="n">
-        <v>0.0669</v>
+        <v>0.06693</v>
       </c>
       <c r="K471" s="1" t="n">
+        <v>0.06693</v>
+      </c>
+      <c r="L471" s="1" t="n">
         <v>0.06660000000000001</v>
       </c>
     </row>
@@ -17910,9 +19326,12 @@
         <v>6.593</v>
       </c>
       <c r="J472" s="1" t="n">
-        <v>6.593</v>
+        <v>6.595</v>
       </c>
       <c r="K472" s="1" t="n">
+        <v>6.595</v>
+      </c>
+      <c r="L472" s="1" t="n">
         <v>6.486</v>
       </c>
     </row>
@@ -17947,9 +19366,12 @@
         <v>0.01942</v>
       </c>
       <c r="J473" s="1" t="n">
-        <v>0.01945</v>
+        <v>0.01949</v>
       </c>
       <c r="K473" s="1" t="n">
+        <v>0.01949</v>
+      </c>
+      <c r="L473" s="1" t="n">
         <v>0.01937</v>
       </c>
     </row>
@@ -17984,9 +19406,12 @@
         <v>1.426</v>
       </c>
       <c r="J474" s="1" t="n">
-        <v>1.426</v>
+        <v>1.431</v>
       </c>
       <c r="K474" s="1" t="n">
+        <v>1.431</v>
+      </c>
+      <c r="L474" s="1" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -18021,9 +19446,12 @@
         <v>0.08981</v>
       </c>
       <c r="J475" s="1" t="n">
-        <v>0.08981</v>
+        <v>0.09</v>
       </c>
       <c r="K475" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L475" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -18058,9 +19486,12 @@
         <v>0.1061</v>
       </c>
       <c r="J476" s="1" t="n">
-        <v>0.1062</v>
+        <v>0.1066</v>
       </c>
       <c r="K476" s="1" t="n">
+        <v>0.1066</v>
+      </c>
+      <c r="L476" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -18095,10 +19526,13 @@
         <v>0.0941</v>
       </c>
       <c r="J477" s="1" t="n">
+        <v>0.09402000000000001</v>
+      </c>
+      <c r="K477" s="1" t="n">
         <v>0.09451</v>
       </c>
-      <c r="K477" s="1" t="n">
-        <v>0.0941</v>
+      <c r="L477" s="1" t="n">
+        <v>0.09402000000000001</v>
       </c>
     </row>
     <row r="478">
@@ -18132,9 +19566,12 @@
         <v>0.0001633</v>
       </c>
       <c r="J478" s="1" t="n">
-        <v>0.0001633</v>
+        <v>0.0001636</v>
       </c>
       <c r="K478" s="1" t="n">
+        <v>0.0001636</v>
+      </c>
+      <c r="L478" s="1" t="n">
         <v>0.0001624</v>
       </c>
     </row>
@@ -18169,9 +19606,12 @@
         <v>0.04023</v>
       </c>
       <c r="J479" s="1" t="n">
-        <v>0.04023</v>
+        <v>0.04034</v>
       </c>
       <c r="K479" s="1" t="n">
+        <v>0.04034</v>
+      </c>
+      <c r="L479" s="1" t="n">
         <v>0.04007</v>
       </c>
     </row>
@@ -18206,9 +19646,12 @@
         <v>0.007422</v>
       </c>
       <c r="J480" s="1" t="n">
-        <v>0.007425</v>
+        <v>0.007442</v>
       </c>
       <c r="K480" s="1" t="n">
+        <v>0.007442</v>
+      </c>
+      <c r="L480" s="1" t="n">
         <v>0.007389</v>
       </c>
     </row>
@@ -18243,9 +19686,12 @@
         <v>0.0953</v>
       </c>
       <c r="J481" s="1" t="n">
-        <v>0.0955</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="K481" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="L481" s="1" t="n">
         <v>0.0953</v>
       </c>
     </row>
@@ -18280,9 +19726,12 @@
         <v>0.056</v>
       </c>
       <c r="J482" s="1" t="n">
+        <v>0.05603</v>
+      </c>
+      <c r="K482" s="1" t="n">
         <v>0.05621</v>
       </c>
-      <c r="K482" s="1" t="n">
+      <c r="L482" s="1" t="n">
         <v>0.05569</v>
       </c>
     </row>
@@ -18317,9 +19766,12 @@
         <v>0.006173</v>
       </c>
       <c r="J483" s="1" t="n">
-        <v>0.006198</v>
+        <v>0.006209</v>
       </c>
       <c r="K483" s="1" t="n">
+        <v>0.006209</v>
+      </c>
+      <c r="L483" s="1" t="n">
         <v>0.006161</v>
       </c>
     </row>
@@ -18354,9 +19806,12 @@
         <v>0.01493</v>
       </c>
       <c r="J484" s="1" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="K484" s="1" t="n">
         <v>0.01497</v>
       </c>
-      <c r="K484" s="1" t="n">
+      <c r="L484" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -18391,9 +19846,12 @@
         <v>0.02408</v>
       </c>
       <c r="J485" s="1" t="n">
+        <v>0.02415</v>
+      </c>
+      <c r="K485" s="1" t="n">
         <v>0.02427</v>
       </c>
-      <c r="K485" s="1" t="n">
+      <c r="L485" s="1" t="n">
         <v>0.02403</v>
       </c>
     </row>
@@ -18428,9 +19886,12 @@
         <v>0.06696000000000001</v>
       </c>
       <c r="J486" s="1" t="n">
+        <v>0.06698999999999999</v>
+      </c>
+      <c r="K486" s="1" t="n">
         <v>0.06702</v>
       </c>
-      <c r="K486" s="1" t="n">
+      <c r="L486" s="1" t="n">
         <v>0.0667</v>
       </c>
     </row>
@@ -18465,9 +19926,12 @@
         <v>0.03692</v>
       </c>
       <c r="J487" s="1" t="n">
-        <v>0.03705</v>
+        <v>0.03709</v>
       </c>
       <c r="K487" s="1" t="n">
+        <v>0.03709</v>
+      </c>
+      <c r="L487" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -18502,9 +19966,12 @@
         <v>0.01817</v>
       </c>
       <c r="J488" s="1" t="n">
-        <v>0.0182</v>
+        <v>0.01826</v>
       </c>
       <c r="K488" s="1" t="n">
+        <v>0.01826</v>
+      </c>
+      <c r="L488" s="1" t="n">
         <v>0.01814</v>
       </c>
     </row>
@@ -18539,9 +20006,12 @@
         <v>0.0326</v>
       </c>
       <c r="J489" s="1" t="n">
-        <v>0.03278</v>
+        <v>0.03299</v>
       </c>
       <c r="K489" s="1" t="n">
+        <v>0.03299</v>
+      </c>
+      <c r="L489" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -18576,9 +20046,12 @@
         <v>0.01473</v>
       </c>
       <c r="J490" s="1" t="n">
-        <v>0.01474</v>
+        <v>0.01481</v>
       </c>
       <c r="K490" s="1" t="n">
+        <v>0.01481</v>
+      </c>
+      <c r="L490" s="1" t="n">
         <v>0.01458</v>
       </c>
     </row>
@@ -18613,9 +20086,12 @@
         <v>0.01875</v>
       </c>
       <c r="J491" s="1" t="n">
-        <v>0.01876</v>
+        <v>0.01884</v>
       </c>
       <c r="K491" s="1" t="n">
+        <v>0.01884</v>
+      </c>
+      <c r="L491" s="1" t="n">
         <v>0.01851</v>
       </c>
     </row>
@@ -18650,9 +20126,12 @@
         <v>0.08784</v>
       </c>
       <c r="J492" s="1" t="n">
+        <v>0.08792999999999999</v>
+      </c>
+      <c r="K492" s="1" t="n">
         <v>0.08935</v>
       </c>
-      <c r="K492" s="1" t="n">
+      <c r="L492" s="1" t="n">
         <v>0.08784</v>
       </c>
     </row>
@@ -18687,9 +20166,12 @@
         <v>0.006503</v>
       </c>
       <c r="J493" s="1" t="n">
-        <v>0.006514</v>
+        <v>0.006521</v>
       </c>
       <c r="K493" s="1" t="n">
+        <v>0.006521</v>
+      </c>
+      <c r="L493" s="1" t="n">
         <v>0.006497</v>
       </c>
     </row>
@@ -18724,9 +20206,12 @@
         <v>0.133</v>
       </c>
       <c r="J494" s="1" t="n">
-        <v>0.1331</v>
+        <v>0.1332</v>
       </c>
       <c r="K494" s="1" t="n">
+        <v>0.1332</v>
+      </c>
+      <c r="L494" s="1" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -18761,9 +20246,12 @@
         <v>0.2849</v>
       </c>
       <c r="J495" s="1" t="n">
-        <v>0.2853</v>
+        <v>0.2859</v>
       </c>
       <c r="K495" s="1" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="L495" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -18798,9 +20286,12 @@
         <v>0.004544</v>
       </c>
       <c r="J496" s="1" t="n">
-        <v>0.004544</v>
+        <v>0.004554</v>
       </c>
       <c r="K496" s="1" t="n">
+        <v>0.004554</v>
+      </c>
+      <c r="L496" s="1" t="n">
         <v>0.004516</v>
       </c>
     </row>
@@ -18835,9 +20326,12 @@
         <v>0.1264</v>
       </c>
       <c r="J497" s="1" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="K497" s="1" t="n">
         <v>0.1283</v>
       </c>
-      <c r="K497" s="1" t="n">
+      <c r="L497" s="1" t="n">
         <v>0.1264</v>
       </c>
     </row>
@@ -18872,9 +20366,12 @@
         <v>0.03445</v>
       </c>
       <c r="J498" s="1" t="n">
-        <v>0.03445</v>
+        <v>0.0345</v>
       </c>
       <c r="K498" s="1" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="L498" s="1" t="n">
         <v>0.03423</v>
       </c>
     </row>
@@ -18909,9 +20406,12 @@
         <v>0.03563</v>
       </c>
       <c r="J499" s="1" t="n">
+        <v>0.03566</v>
+      </c>
+      <c r="K499" s="1" t="n">
         <v>0.03576</v>
       </c>
-      <c r="K499" s="1" t="n">
+      <c r="L499" s="1" t="n">
         <v>0.03557</v>
       </c>
     </row>
@@ -18946,9 +20446,12 @@
         <v>0.003413</v>
       </c>
       <c r="J500" s="1" t="n">
+        <v>0.003416</v>
+      </c>
+      <c r="K500" s="1" t="n">
         <v>0.003421</v>
       </c>
-      <c r="K500" s="1" t="n">
+      <c r="L500" s="1" t="n">
         <v>0.003413</v>
       </c>
     </row>
@@ -18983,9 +20486,12 @@
         <v>0.0003821</v>
       </c>
       <c r="J501" s="1" t="n">
-        <v>0.0003834</v>
+        <v>0.0003837</v>
       </c>
       <c r="K501" s="1" t="n">
+        <v>0.0003837</v>
+      </c>
+      <c r="L501" s="1" t="n">
         <v>0.0003786</v>
       </c>
     </row>
@@ -19020,9 +20526,12 @@
         <v>0.3002</v>
       </c>
       <c r="J502" s="1" t="n">
-        <v>0.3004</v>
+        <v>0.3011</v>
       </c>
       <c r="K502" s="1" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="L502" s="1" t="n">
         <v>0.2986</v>
       </c>
     </row>
@@ -19057,9 +20566,12 @@
         <v>0.06485</v>
       </c>
       <c r="J503" s="1" t="n">
+        <v>0.06506000000000001</v>
+      </c>
+      <c r="K503" s="1" t="n">
         <v>0.06507</v>
       </c>
-      <c r="K503" s="1" t="n">
+      <c r="L503" s="1" t="n">
         <v>0.06485</v>
       </c>
     </row>
@@ -19094,9 +20606,12 @@
         <v>0.1779</v>
       </c>
       <c r="J504" s="1" t="n">
-        <v>0.178</v>
+        <v>0.1782</v>
       </c>
       <c r="K504" s="1" t="n">
+        <v>0.1782</v>
+      </c>
+      <c r="L504" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -19131,9 +20646,12 @@
         <v>0.1511</v>
       </c>
       <c r="J505" s="1" t="n">
-        <v>0.1514</v>
+        <v>0.1519</v>
       </c>
       <c r="K505" s="1" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="L505" s="1" t="n">
         <v>0.1511</v>
       </c>
     </row>
@@ -19168,9 +20686,12 @@
         <v>0.01198</v>
       </c>
       <c r="J506" s="1" t="n">
-        <v>0.01199</v>
+        <v>0.01202</v>
       </c>
       <c r="K506" s="1" t="n">
+        <v>0.01202</v>
+      </c>
+      <c r="L506" s="1" t="n">
         <v>0.01193</v>
       </c>
     </row>
@@ -19205,9 +20726,12 @@
         <v>0.2884</v>
       </c>
       <c r="J507" s="1" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="K507" s="1" t="n">
         <v>0.2893</v>
       </c>
-      <c r="K507" s="1" t="n">
+      <c r="L507" s="1" t="n">
         <v>0.2871</v>
       </c>
     </row>
@@ -19242,9 +20766,12 @@
         <v>0.009339999999999999</v>
       </c>
       <c r="J508" s="1" t="n">
-        <v>0.0094</v>
+        <v>0.00942</v>
       </c>
       <c r="K508" s="1" t="n">
+        <v>0.00942</v>
+      </c>
+      <c r="L508" s="1" t="n">
         <v>0.009310000000000001</v>
       </c>
     </row>
@@ -19279,9 +20806,12 @@
         <v>0.006829</v>
       </c>
       <c r="J509" s="1" t="n">
-        <v>0.006833</v>
+        <v>0.006851</v>
       </c>
       <c r="K509" s="1" t="n">
+        <v>0.006851</v>
+      </c>
+      <c r="L509" s="1" t="n">
         <v>0.006783</v>
       </c>
     </row>
@@ -19316,9 +20846,12 @@
         <v>0.2954</v>
       </c>
       <c r="J510" s="1" t="n">
-        <v>0.2954</v>
+        <v>0.2986</v>
       </c>
       <c r="K510" s="1" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="L510" s="1" t="n">
         <v>0.2934</v>
       </c>
     </row>
@@ -19353,9 +20886,12 @@
         <v>0.0147</v>
       </c>
       <c r="J511" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="K511" s="1" t="n">
         <v>0.01471</v>
       </c>
-      <c r="K511" s="1" t="n">
+      <c r="L511" s="1" t="n">
         <v>0.01465</v>
       </c>
     </row>
@@ -19390,9 +20926,12 @@
         <v>0.1398</v>
       </c>
       <c r="J512" s="1" t="n">
-        <v>0.1398</v>
+        <v>0.1402</v>
       </c>
       <c r="K512" s="1" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="L512" s="1" t="n">
         <v>0.1394</v>
       </c>
     </row>
@@ -19427,9 +20966,12 @@
         <v>0.08128000000000001</v>
       </c>
       <c r="J513" s="1" t="n">
+        <v>0.08112</v>
+      </c>
+      <c r="K513" s="1" t="n">
         <v>0.08144999999999999</v>
       </c>
-      <c r="K513" s="1" t="n">
+      <c r="L513" s="1" t="n">
         <v>0.08069</v>
       </c>
     </row>
@@ -19467,6 +21009,9 @@
         <v>0.0251</v>
       </c>
       <c r="K514" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="L514" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -19501,9 +21046,12 @@
         <v>0.06314</v>
       </c>
       <c r="J515" s="1" t="n">
+        <v>0.06318</v>
+      </c>
+      <c r="K515" s="1" t="n">
         <v>0.06329</v>
       </c>
-      <c r="K515" s="1" t="n">
+      <c r="L515" s="1" t="n">
         <v>0.06301</v>
       </c>
     </row>
@@ -19538,9 +21086,12 @@
         <v>0.04732</v>
       </c>
       <c r="J516" s="1" t="n">
-        <v>0.04735</v>
+        <v>0.04752</v>
       </c>
       <c r="K516" s="1" t="n">
+        <v>0.04752</v>
+      </c>
+      <c r="L516" s="1" t="n">
         <v>0.04707</v>
       </c>
     </row>
@@ -19575,9 +21126,12 @@
         <v>0.004902</v>
       </c>
       <c r="J517" s="1" t="n">
-        <v>0.004909</v>
+        <v>0.00493</v>
       </c>
       <c r="K517" s="1" t="n">
+        <v>0.00493</v>
+      </c>
+      <c r="L517" s="1" t="n">
         <v>0.004902</v>
       </c>
     </row>
@@ -19612,9 +21166,12 @@
         <v>0.00944</v>
       </c>
       <c r="J518" s="1" t="n">
-        <v>0.00944</v>
+        <v>0.009441</v>
       </c>
       <c r="K518" s="1" t="n">
+        <v>0.009441</v>
+      </c>
+      <c r="L518" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -19649,9 +21206,12 @@
         <v>0.01803</v>
       </c>
       <c r="J519" s="1" t="n">
+        <v>0.01805</v>
+      </c>
+      <c r="K519" s="1" t="n">
         <v>0.01807</v>
       </c>
-      <c r="K519" s="1" t="n">
+      <c r="L519" s="1" t="n">
         <v>0.01798</v>
       </c>
     </row>
@@ -19686,9 +21246,12 @@
         <v>0.06689000000000001</v>
       </c>
       <c r="J520" s="1" t="n">
-        <v>0.06689000000000001</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="K520" s="1" t="n">
+        <v>0.06696000000000001</v>
+      </c>
+      <c r="L520" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -19723,9 +21286,12 @@
         <v>0.1368</v>
       </c>
       <c r="J521" s="1" t="n">
-        <v>0.137</v>
+        <v>0.1372</v>
       </c>
       <c r="K521" s="1" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="L521" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -19760,9 +21326,12 @@
         <v>0.04726</v>
       </c>
       <c r="J522" s="1" t="n">
-        <v>0.04746</v>
+        <v>0.04761</v>
       </c>
       <c r="K522" s="1" t="n">
+        <v>0.04761</v>
+      </c>
+      <c r="L522" s="1" t="n">
         <v>0.04718</v>
       </c>
     </row>
@@ -19797,9 +21366,12 @@
         <v>0.06798</v>
       </c>
       <c r="J523" s="1" t="n">
-        <v>0.06809</v>
+        <v>0.06827</v>
       </c>
       <c r="K523" s="1" t="n">
+        <v>0.06827</v>
+      </c>
+      <c r="L523" s="1" t="n">
         <v>0.06784999999999999</v>
       </c>
     </row>
@@ -19834,9 +21406,12 @@
         <v>0.6991000000000001</v>
       </c>
       <c r="J524" s="1" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.6999</v>
       </c>
       <c r="K524" s="1" t="n">
+        <v>0.6999</v>
+      </c>
+      <c r="L524" s="1" t="n">
         <v>0.6966</v>
       </c>
     </row>
@@ -19874,6 +21449,9 @@
         <v>0.00269</v>
       </c>
       <c r="K525" s="1" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="L525" s="1" t="n">
         <v>0.00267</v>
       </c>
     </row>
@@ -19908,9 +21486,12 @@
         <v>0.4872</v>
       </c>
       <c r="J526" s="1" t="n">
-        <v>0.4872</v>
+        <v>0.488</v>
       </c>
       <c r="K526" s="1" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="L526" s="1" t="n">
         <v>0.4856</v>
       </c>
     </row>
@@ -19945,9 +21526,12 @@
         <v>45.83</v>
       </c>
       <c r="J527" s="1" t="n">
-        <v>45.83</v>
+        <v>45.84</v>
       </c>
       <c r="K527" s="1" t="n">
+        <v>45.84</v>
+      </c>
+      <c r="L527" s="1" t="n">
         <v>45.76</v>
       </c>
     </row>
@@ -19982,9 +21566,12 @@
         <v>0.0244</v>
       </c>
       <c r="J528" s="1" t="n">
-        <v>0.02443</v>
+        <v>0.02447</v>
       </c>
       <c r="K528" s="1" t="n">
+        <v>0.02447</v>
+      </c>
+      <c r="L528" s="1" t="n">
         <v>0.02429</v>
       </c>
     </row>
@@ -20019,9 +21606,12 @@
         <v>0.00641</v>
       </c>
       <c r="J529" s="1" t="n">
-        <v>0.00641</v>
+        <v>0.006422</v>
       </c>
       <c r="K529" s="1" t="n">
+        <v>0.006422</v>
+      </c>
+      <c r="L529" s="1" t="n">
         <v>0.00638</v>
       </c>
     </row>
@@ -20056,9 +21646,12 @@
         <v>0.2002</v>
       </c>
       <c r="J530" s="1" t="n">
-        <v>0.2002</v>
+        <v>0.2007</v>
       </c>
       <c r="K530" s="1" t="n">
+        <v>0.2007</v>
+      </c>
+      <c r="L530" s="1" t="n">
         <v>0.1993</v>
       </c>
     </row>
@@ -20093,9 +21686,12 @@
         <v>0.007684</v>
       </c>
       <c r="J531" s="1" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="K531" s="1" t="n">
         <v>0.007727</v>
       </c>
-      <c r="K531" s="1" t="n">
+      <c r="L531" s="1" t="n">
         <v>0.007657</v>
       </c>
     </row>
@@ -20130,9 +21726,12 @@
         <v>2.281</v>
       </c>
       <c r="J532" s="1" t="n">
-        <v>2.285</v>
+        <v>2.302</v>
       </c>
       <c r="K532" s="1" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="L532" s="1" t="n">
         <v>2.275</v>
       </c>
     </row>
@@ -20167,9 +21766,12 @@
         <v>0.04164</v>
       </c>
       <c r="J533" s="1" t="n">
-        <v>0.04164</v>
+        <v>0.04186</v>
       </c>
       <c r="K533" s="1" t="n">
+        <v>0.04186</v>
+      </c>
+      <c r="L533" s="1" t="n">
         <v>0.04138</v>
       </c>
     </row>
@@ -20204,9 +21806,12 @@
         <v>0.1829</v>
       </c>
       <c r="J534" s="1" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="K534" s="1" t="n">
         <v>0.1833</v>
       </c>
-      <c r="K534" s="1" t="n">
+      <c r="L534" s="1" t="n">
         <v>0.1811</v>
       </c>
     </row>
@@ -20241,9 +21846,12 @@
         <v>0.04328</v>
       </c>
       <c r="J535" s="1" t="n">
-        <v>0.04328</v>
+        <v>0.04372</v>
       </c>
       <c r="K535" s="1" t="n">
+        <v>0.04372</v>
+      </c>
+      <c r="L535" s="1" t="n">
         <v>0.04287</v>
       </c>
     </row>
@@ -20278,9 +21886,12 @@
         <v>0.05409</v>
       </c>
       <c r="J536" s="1" t="n">
+        <v>0.05428</v>
+      </c>
+      <c r="K536" s="1" t="n">
         <v>0.05438</v>
       </c>
-      <c r="K536" s="1" t="n">
+      <c r="L536" s="1" t="n">
         <v>0.05409</v>
       </c>
     </row>
@@ -20315,9 +21926,12 @@
         <v>0.1605</v>
       </c>
       <c r="J537" s="1" t="n">
-        <v>0.1609</v>
+        <v>0.1611</v>
       </c>
       <c r="K537" s="1" t="n">
+        <v>0.1611</v>
+      </c>
+      <c r="L537" s="1" t="n">
         <v>0.1602</v>
       </c>
     </row>
@@ -20355,6 +21969,9 @@
         <v>0.03687</v>
       </c>
       <c r="K538" s="1" t="n">
+        <v>0.03687</v>
+      </c>
+      <c r="L538" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -20389,9 +22006,12 @@
         <v>0.05858</v>
       </c>
       <c r="J539" s="1" t="n">
-        <v>0.05858</v>
+        <v>0.0587</v>
       </c>
       <c r="K539" s="1" t="n">
+        <v>0.0587</v>
+      </c>
+      <c r="L539" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -20426,9 +22046,12 @@
         <v>0.04273</v>
       </c>
       <c r="J540" s="1" t="n">
-        <v>0.04273</v>
+        <v>0.04282</v>
       </c>
       <c r="K540" s="1" t="n">
+        <v>0.04282</v>
+      </c>
+      <c r="L540" s="1" t="n">
         <v>0.04256</v>
       </c>
     </row>
@@ -20463,9 +22086,12 @@
         <v>0.01725</v>
       </c>
       <c r="J541" s="1" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="K541" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="K541" s="1" t="n">
+      <c r="L541" s="1" t="n">
         <v>0.0172</v>
       </c>
     </row>
@@ -20500,9 +22126,12 @@
         <v>0.003967</v>
       </c>
       <c r="J542" s="1" t="n">
+        <v>0.003973</v>
+      </c>
+      <c r="K542" s="1" t="n">
         <v>0.003975</v>
       </c>
-      <c r="K542" s="1" t="n">
+      <c r="L542" s="1" t="n">
         <v>0.003963</v>
       </c>
     </row>
@@ -20537,9 +22166,12 @@
         <v>0.05835</v>
       </c>
       <c r="J543" s="1" t="n">
+        <v>0.05789</v>
+      </c>
+      <c r="K543" s="1" t="n">
         <v>0.05835</v>
       </c>
-      <c r="K543" s="1" t="n">
+      <c r="L543" s="1" t="n">
         <v>0.05735</v>
       </c>
     </row>
@@ -20574,9 +22206,12 @@
         <v>0.0502</v>
       </c>
       <c r="J544" s="1" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="K544" s="1" t="n">
         <v>0.05042</v>
       </c>
-      <c r="K544" s="1" t="n">
+      <c r="L544" s="1" t="n">
         <v>0.05016</v>
       </c>
     </row>
@@ -20611,9 +22246,12 @@
         <v>0.04069</v>
       </c>
       <c r="J545" s="1" t="n">
-        <v>0.04071</v>
+        <v>0.04082</v>
       </c>
       <c r="K545" s="1" t="n">
+        <v>0.04082</v>
+      </c>
+      <c r="L545" s="1" t="n">
         <v>0.04038</v>
       </c>
     </row>
@@ -20648,9 +22286,12 @@
         <v>0.007411</v>
       </c>
       <c r="J546" s="1" t="n">
-        <v>0.007433</v>
+        <v>0.007436</v>
       </c>
       <c r="K546" s="1" t="n">
+        <v>0.007436</v>
+      </c>
+      <c r="L546" s="1" t="n">
         <v>0.007402</v>
       </c>
     </row>
@@ -20685,9 +22326,12 @@
         <v>0.01472</v>
       </c>
       <c r="J547" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="K547" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="K547" s="1" t="n">
+      <c r="L547" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -20722,9 +22366,12 @@
         <v>0.0157</v>
       </c>
       <c r="J548" s="1" t="n">
-        <v>0.01573</v>
+        <v>0.01576</v>
       </c>
       <c r="K548" s="1" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="L548" s="1" t="n">
         <v>0.0157</v>
       </c>
     </row>
@@ -20759,9 +22406,12 @@
         <v>0.13556</v>
       </c>
       <c r="J549" s="1" t="n">
-        <v>0.13556</v>
+        <v>0.13562</v>
       </c>
       <c r="K549" s="1" t="n">
+        <v>0.13562</v>
+      </c>
+      <c r="L549" s="1" t="n">
         <v>0.13271</v>
       </c>
     </row>
@@ -20796,9 +22446,12 @@
         <v>0.1699</v>
       </c>
       <c r="J550" s="1" t="n">
-        <v>0.1699</v>
+        <v>0.1706</v>
       </c>
       <c r="K550" s="1" t="n">
+        <v>0.1706</v>
+      </c>
+      <c r="L550" s="1" t="n">
         <v>0.1693</v>
       </c>
     </row>
@@ -20833,9 +22486,12 @@
         <v>0.003586</v>
       </c>
       <c r="J551" s="1" t="n">
-        <v>0.003586</v>
+        <v>0.003593</v>
       </c>
       <c r="K551" s="1" t="n">
+        <v>0.003593</v>
+      </c>
+      <c r="L551" s="1" t="n">
         <v>0.003577</v>
       </c>
     </row>
@@ -20870,9 +22526,12 @@
         <v>0.03044</v>
       </c>
       <c r="J552" s="1" t="n">
-        <v>0.03044</v>
+        <v>0.03046</v>
       </c>
       <c r="K552" s="1" t="n">
+        <v>0.03046</v>
+      </c>
+      <c r="L552" s="1" t="n">
         <v>0.0303</v>
       </c>
     </row>
@@ -20907,9 +22566,12 @@
         <v>0.01322</v>
       </c>
       <c r="J553" s="1" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="K553" s="1" t="n">
         <v>0.01325</v>
       </c>
-      <c r="K553" s="1" t="n">
+      <c r="L553" s="1" t="n">
         <v>0.01319</v>
       </c>
     </row>
@@ -20944,9 +22606,12 @@
         <v>0.1041</v>
       </c>
       <c r="J554" s="1" t="n">
+        <v>0.1044</v>
+      </c>
+      <c r="K554" s="1" t="n">
         <v>0.1046</v>
       </c>
-      <c r="K554" s="1" t="n">
+      <c r="L554" s="1" t="n">
         <v>0.1039</v>
       </c>
     </row>
@@ -20981,9 +22646,12 @@
         <v>0.05303</v>
       </c>
       <c r="J555" s="1" t="n">
+        <v>0.05316</v>
+      </c>
+      <c r="K555" s="1" t="n">
         <v>0.05319</v>
       </c>
-      <c r="K555" s="1" t="n">
+      <c r="L555" s="1" t="n">
         <v>0.05291</v>
       </c>
     </row>
@@ -21018,9 +22686,12 @@
         <v>0.01223</v>
       </c>
       <c r="J556" s="1" t="n">
-        <v>0.01224</v>
+        <v>0.01234</v>
       </c>
       <c r="K556" s="1" t="n">
+        <v>0.01234</v>
+      </c>
+      <c r="L556" s="1" t="n">
         <v>0.01218</v>
       </c>
     </row>

--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L556"/>
+  <dimension ref="A1:M556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -429,8 +429,9 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,10 +487,15 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>price_02:15</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -529,9 +535,12 @@
         <v>71788</v>
       </c>
       <c r="K2" s="1" t="n">
+        <v>71686.89999999999</v>
+      </c>
+      <c r="L2" s="1" t="n">
         <v>71788</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="M2" s="1" t="n">
         <v>71364.39999999999</v>
       </c>
     </row>
@@ -569,9 +578,12 @@
         <v>2109.75</v>
       </c>
       <c r="K3" s="1" t="n">
+        <v>2107.59</v>
+      </c>
+      <c r="L3" s="1" t="n">
         <v>2109.75</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="M3" s="1" t="n">
         <v>2090.41</v>
       </c>
     </row>
@@ -609,9 +621,12 @@
         <v>88.38</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>88.38</v>
+        <v>88.5</v>
       </c>
       <c r="L4" s="1" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="M4" s="1" t="n">
         <v>87.47</v>
       </c>
     </row>
@@ -649,9 +664,12 @@
         <v>23.388</v>
       </c>
       <c r="K5" s="1" t="n">
+        <v>23.262</v>
+      </c>
+      <c r="L5" s="1" t="n">
         <v>23.579</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="M5" s="1" t="n">
         <v>23.043</v>
       </c>
     </row>
@@ -689,9 +707,12 @@
         <v>0.001811</v>
       </c>
       <c r="K6" s="1" t="n">
+        <v>0.001815</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>0.001892</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.001811</v>
       </c>
     </row>
@@ -729,9 +750,12 @@
         <v>1.4184</v>
       </c>
       <c r="K7" s="1" t="n">
+        <v>1.4179</v>
+      </c>
+      <c r="L7" s="1" t="n">
         <v>1.4184</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>1.4117</v>
       </c>
     </row>
@@ -769,9 +793,12 @@
         <v>0.010642</v>
       </c>
       <c r="K8" s="1" t="n">
+        <v>0.010714</v>
+      </c>
+      <c r="L8" s="1" t="n">
         <v>0.011244</v>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.010407</v>
       </c>
     </row>
@@ -809,9 +836,12 @@
         <v>4.035</v>
       </c>
       <c r="K9" s="1" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L9" s="1" t="n">
         <v>4.062</v>
       </c>
-      <c r="L9" s="1" t="n">
+      <c r="M9" s="1" t="n">
         <v>3.954</v>
       </c>
     </row>
@@ -849,9 +879,12 @@
         <v>279.92</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>279.92</v>
+        <v>282.64</v>
       </c>
       <c r="L10" s="1" t="n">
+        <v>282.64</v>
+      </c>
+      <c r="M10" s="1" t="n">
         <v>272.11</v>
       </c>
     </row>
@@ -889,10 +922,13 @@
         <v>0.07804</v>
       </c>
       <c r="K11" s="1" t="n">
+        <v>0.07764</v>
+      </c>
+      <c r="L11" s="1" t="n">
         <v>0.08047</v>
       </c>
-      <c r="L11" s="1" t="n">
-        <v>0.07804</v>
+      <c r="M11" s="1" t="n">
+        <v>0.07764</v>
       </c>
     </row>
     <row r="12">
@@ -929,9 +965,12 @@
         <v>226.41</v>
       </c>
       <c r="K12" s="1" t="n">
+        <v>227.18</v>
+      </c>
+      <c r="L12" s="1" t="n">
         <v>227.69</v>
       </c>
-      <c r="L12" s="1" t="n">
+      <c r="M12" s="1" t="n">
         <v>223.76</v>
       </c>
     </row>
@@ -969,9 +1008,12 @@
         <v>0.09543</v>
       </c>
       <c r="K13" s="1" t="n">
+        <v>0.09525</v>
+      </c>
+      <c r="L13" s="1" t="n">
         <v>0.09543</v>
       </c>
-      <c r="L13" s="1" t="n">
+      <c r="M13" s="1" t="n">
         <v>0.0946</v>
       </c>
     </row>
@@ -1009,9 +1051,12 @@
         <v>37.361</v>
       </c>
       <c r="K14" s="1" t="n">
+        <v>37.274</v>
+      </c>
+      <c r="L14" s="1" t="n">
         <v>37.361</v>
       </c>
-      <c r="L14" s="1" t="n">
+      <c r="M14" s="1" t="n">
         <v>37.089</v>
       </c>
     </row>
@@ -1049,10 +1094,13 @@
         <v>0.09271</v>
       </c>
       <c r="K15" s="1" t="n">
+        <v>0.08938</v>
+      </c>
+      <c r="L15" s="1" t="n">
         <v>0.09845</v>
       </c>
-      <c r="L15" s="1" t="n">
-        <v>0.09271</v>
+      <c r="M15" s="1" t="n">
+        <v>0.08938</v>
       </c>
     </row>
     <row r="16">
@@ -1089,9 +1137,12 @@
         <v>0.2286</v>
       </c>
       <c r="K16" s="1" t="n">
+        <v>0.2266</v>
+      </c>
+      <c r="L16" s="1" t="n">
         <v>0.2339</v>
       </c>
-      <c r="L16" s="1" t="n">
+      <c r="M16" s="1" t="n">
         <v>0.2256</v>
       </c>
     </row>
@@ -1129,9 +1180,12 @@
         <v>0.011455</v>
       </c>
       <c r="K17" s="1" t="n">
+        <v>0.011518</v>
+      </c>
+      <c r="L17" s="1" t="n">
         <v>0.011542</v>
       </c>
-      <c r="L17" s="1" t="n">
+      <c r="M17" s="1" t="n">
         <v>0.011379</v>
       </c>
     </row>
@@ -1169,9 +1223,12 @@
         <v>661.9</v>
       </c>
       <c r="K18" s="1" t="n">
+        <v>661.45</v>
+      </c>
+      <c r="L18" s="1" t="n">
         <v>661.9</v>
       </c>
-      <c r="L18" s="1" t="n">
+      <c r="M18" s="1" t="n">
         <v>658.89</v>
       </c>
     </row>
@@ -1209,9 +1266,12 @@
         <v>0.0033672</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.0033672</v>
+        <v>0.003368</v>
       </c>
       <c r="L19" s="1" t="n">
+        <v>0.003368</v>
+      </c>
+      <c r="M19" s="1" t="n">
         <v>0.0033271</v>
       </c>
     </row>
@@ -1249,10 +1309,13 @@
         <v>0.17759</v>
       </c>
       <c r="K20" s="1" t="n">
+        <v>0.17643</v>
+      </c>
+      <c r="L20" s="1" t="n">
         <v>0.18066</v>
       </c>
-      <c r="L20" s="1" t="n">
-        <v>0.17675</v>
+      <c r="M20" s="1" t="n">
+        <v>0.17643</v>
       </c>
     </row>
     <row r="21">
@@ -1289,9 +1352,12 @@
         <v>0.009918</v>
       </c>
       <c r="K21" s="1" t="n">
+        <v>0.009849</v>
+      </c>
+      <c r="L21" s="1" t="n">
         <v>0.010044</v>
       </c>
-      <c r="L21" s="1" t="n">
+      <c r="M21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -1329,9 +1395,12 @@
         <v>1.009</v>
       </c>
       <c r="K22" s="1" t="n">
+        <v>1.0086</v>
+      </c>
+      <c r="L22" s="1" t="n">
         <v>1.009</v>
       </c>
-      <c r="L22" s="1" t="n">
+      <c r="M22" s="1" t="n">
         <v>0.9985000000000001</v>
       </c>
     </row>
@@ -1369,9 +1438,12 @@
         <v>5006.11</v>
       </c>
       <c r="K23" s="1" t="n">
+        <v>5005.7</v>
+      </c>
+      <c r="L23" s="1" t="n">
         <v>5012.25</v>
       </c>
-      <c r="L23" s="1" t="n">
+      <c r="M23" s="1" t="n">
         <v>5002.67</v>
       </c>
     </row>
@@ -1409,9 +1481,12 @@
         <v>0.2645</v>
       </c>
       <c r="K24" s="1" t="n">
+        <v>0.2643</v>
+      </c>
+      <c r="L24" s="1" t="n">
         <v>0.2645</v>
       </c>
-      <c r="L24" s="1" t="n">
+      <c r="M24" s="1" t="n">
         <v>0.2625</v>
       </c>
     </row>
@@ -1449,10 +1524,13 @@
         <v>2.877</v>
       </c>
       <c r="K25" s="1" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="L25" s="1" t="n">
         <v>2.924</v>
       </c>
-      <c r="L25" s="1" t="n">
-        <v>2.877</v>
+      <c r="M25" s="1" t="n">
+        <v>2.875</v>
       </c>
     </row>
     <row r="26">
@@ -1489,9 +1567,12 @@
         <v>0.3825</v>
       </c>
       <c r="K26" s="1" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="L26" s="1" t="n">
         <v>0.4096</v>
       </c>
-      <c r="L26" s="1" t="n">
+      <c r="M26" s="1" t="n">
         <v>0.3825</v>
       </c>
     </row>
@@ -1532,6 +1613,9 @@
         <v>0.889</v>
       </c>
       <c r="L27" s="1" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="M27" s="1" t="n">
         <v>0.881</v>
       </c>
     </row>
@@ -1569,9 +1653,12 @@
         <v>1.345</v>
       </c>
       <c r="K28" s="1" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="L28" s="1" t="n">
         <v>1.346</v>
       </c>
-      <c r="L28" s="1" t="n">
+      <c r="M28" s="1" t="n">
         <v>1.335</v>
       </c>
     </row>
@@ -1609,9 +1696,12 @@
         <v>9.205</v>
       </c>
       <c r="K29" s="1" t="n">
+        <v>9.198</v>
+      </c>
+      <c r="L29" s="1" t="n">
         <v>9.205</v>
       </c>
-      <c r="L29" s="1" t="n">
+      <c r="M29" s="1" t="n">
         <v>9.131</v>
       </c>
     </row>
@@ -1649,9 +1739,12 @@
         <v>463.29</v>
       </c>
       <c r="K30" s="1" t="n">
+        <v>462.58</v>
+      </c>
+      <c r="L30" s="1" t="n">
         <v>463.35</v>
       </c>
-      <c r="L30" s="1" t="n">
+      <c r="M30" s="1" t="n">
         <v>461.24</v>
       </c>
     </row>
@@ -1689,9 +1782,12 @@
         <v>9.765000000000001</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>9.765000000000001</v>
+        <v>9.771000000000001</v>
       </c>
       <c r="L31" s="1" t="n">
+        <v>9.771000000000001</v>
+      </c>
+      <c r="M31" s="1" t="n">
         <v>9.696999999999999</v>
       </c>
     </row>
@@ -1729,9 +1825,12 @@
         <v>0.35998</v>
       </c>
       <c r="K32" s="1" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="L32" s="1" t="n">
         <v>0.36683</v>
       </c>
-      <c r="L32" s="1" t="n">
+      <c r="M32" s="1" t="n">
         <v>0.35998</v>
       </c>
     </row>
@@ -1769,9 +1868,12 @@
         <v>1.421</v>
       </c>
       <c r="K33" s="1" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="L33" s="1" t="n">
         <v>1.421</v>
       </c>
-      <c r="L33" s="1" t="n">
+      <c r="M33" s="1" t="n">
         <v>1.409</v>
       </c>
     </row>
@@ -1809,10 +1911,13 @@
         <v>0.58969</v>
       </c>
       <c r="K34" s="1" t="n">
+        <v>0.58086</v>
+      </c>
+      <c r="L34" s="1" t="n">
         <v>0.59693</v>
       </c>
-      <c r="L34" s="1" t="n">
-        <v>0.58969</v>
+      <c r="M34" s="1" t="n">
+        <v>0.58086</v>
       </c>
     </row>
     <row r="35">
@@ -1849,9 +1954,12 @@
         <v>1.2251</v>
       </c>
       <c r="K35" s="1" t="n">
+        <v>1.223</v>
+      </c>
+      <c r="L35" s="1" t="n">
         <v>1.2283</v>
       </c>
-      <c r="L35" s="1" t="n">
+      <c r="M35" s="1" t="n">
         <v>1.2186</v>
       </c>
     </row>
@@ -1889,9 +1997,12 @@
         <v>80.33</v>
       </c>
       <c r="K36" s="1" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="L36" s="1" t="n">
         <v>80.5</v>
       </c>
-      <c r="L36" s="1" t="n">
+      <c r="M36" s="1" t="n">
         <v>80.27</v>
       </c>
     </row>
@@ -1929,9 +2040,12 @@
         <v>0.1978</v>
       </c>
       <c r="K37" s="1" t="n">
+        <v>0.1991</v>
+      </c>
+      <c r="L37" s="1" t="n">
         <v>0.204</v>
       </c>
-      <c r="L37" s="1" t="n">
+      <c r="M37" s="1" t="n">
         <v>0.1967</v>
       </c>
     </row>
@@ -1969,9 +2083,12 @@
         <v>1.866</v>
       </c>
       <c r="K38" s="1" t="n">
+        <v>1.863</v>
+      </c>
+      <c r="L38" s="1" t="n">
         <v>1.866</v>
       </c>
-      <c r="L38" s="1" t="n">
+      <c r="M38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -2009,9 +2126,12 @@
         <v>0.3382</v>
       </c>
       <c r="K39" s="1" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="L39" s="1" t="n">
         <v>0.3382</v>
       </c>
-      <c r="L39" s="1" t="n">
+      <c r="M39" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -2049,9 +2169,12 @@
         <v>0.8895999999999999</v>
       </c>
       <c r="K40" s="1" t="n">
+        <v>0.8929</v>
+      </c>
+      <c r="L40" s="1" t="n">
         <v>0.9115</v>
       </c>
-      <c r="L40" s="1" t="n">
+      <c r="M40" s="1" t="n">
         <v>0.8895999999999999</v>
       </c>
     </row>
@@ -2089,9 +2212,12 @@
         <v>0.7151999999999999</v>
       </c>
       <c r="K41" s="1" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="L41" s="1" t="n">
         <v>0.7151999999999999</v>
       </c>
-      <c r="L41" s="1" t="n">
+      <c r="M41" s="1" t="n">
         <v>0.7115</v>
       </c>
     </row>
@@ -2129,9 +2255,12 @@
         <v>0.06551999999999999</v>
       </c>
       <c r="K42" s="1" t="n">
+        <v>0.06567000000000001</v>
+      </c>
+      <c r="L42" s="1" t="n">
         <v>0.06769</v>
       </c>
-      <c r="L42" s="1" t="n">
+      <c r="M42" s="1" t="n">
         <v>0.06551999999999999</v>
       </c>
     </row>
@@ -2169,9 +2298,12 @@
         <v>114.65</v>
       </c>
       <c r="K43" s="1" t="n">
+        <v>114.61</v>
+      </c>
+      <c r="L43" s="1" t="n">
         <v>114.65</v>
       </c>
-      <c r="L43" s="1" t="n">
+      <c r="M43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -2209,9 +2341,12 @@
         <v>0.6539</v>
       </c>
       <c r="K44" s="1" t="n">
+        <v>0.6561</v>
+      </c>
+      <c r="L44" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="L44" s="1" t="n">
+      <c r="M44" s="1" t="n">
         <v>0.6536999999999999</v>
       </c>
     </row>
@@ -2249,9 +2384,12 @@
         <v>1.227</v>
       </c>
       <c r="K45" s="1" t="n">
+        <v>1.224</v>
+      </c>
+      <c r="L45" s="1" t="n">
         <v>1.227</v>
       </c>
-      <c r="L45" s="1" t="n">
+      <c r="M45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -2289,10 +2427,13 @@
         <v>0.02378</v>
       </c>
       <c r="K46" s="1" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="L46" s="1" t="n">
         <v>0.02392</v>
       </c>
-      <c r="L46" s="1" t="n">
-        <v>0.02376</v>
+      <c r="M46" s="1" t="n">
+        <v>0.02375</v>
       </c>
     </row>
     <row r="47">
@@ -2329,9 +2470,12 @@
         <v>55.19</v>
       </c>
       <c r="K47" s="1" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="L47" s="1" t="n">
         <v>55.19</v>
       </c>
-      <c r="L47" s="1" t="n">
+      <c r="M47" s="1" t="n">
         <v>54.99</v>
       </c>
     </row>
@@ -2369,9 +2513,12 @@
         <v>0.061</v>
       </c>
       <c r="K48" s="1" t="n">
+        <v>0.06046</v>
+      </c>
+      <c r="L48" s="1" t="n">
         <v>0.061</v>
       </c>
-      <c r="L48" s="1" t="n">
+      <c r="M48" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -2409,9 +2556,12 @@
         <v>0.1086</v>
       </c>
       <c r="K49" s="1" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="L49" s="1" t="n">
         <v>0.1086</v>
       </c>
-      <c r="L49" s="1" t="n">
+      <c r="M49" s="1" t="n">
         <v>0.1076</v>
       </c>
     </row>
@@ -2449,9 +2599,12 @@
         <v>0.01803</v>
       </c>
       <c r="K50" s="1" t="n">
+        <v>0.01804</v>
+      </c>
+      <c r="L50" s="1" t="n">
         <v>0.01815</v>
       </c>
-      <c r="L50" s="1" t="n">
+      <c r="M50" s="1" t="n">
         <v>0.01795</v>
       </c>
     </row>
@@ -2489,9 +2642,12 @@
         <v>1.4817</v>
       </c>
       <c r="K51" s="1" t="n">
+        <v>1.4805</v>
+      </c>
+      <c r="L51" s="1" t="n">
         <v>1.4817</v>
       </c>
-      <c r="L51" s="1" t="n">
+      <c r="M51" s="1" t="n">
         <v>1.4618</v>
       </c>
     </row>
@@ -2529,9 +2685,12 @@
         <v>0.3612</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>0.3612</v>
+        <v>0.3617</v>
       </c>
       <c r="L52" s="1" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="M52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -2569,9 +2728,12 @@
         <v>0.001948</v>
       </c>
       <c r="K53" s="1" t="n">
+        <v>0.001944</v>
+      </c>
+      <c r="L53" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="L53" s="1" t="n">
+      <c r="M53" s="1" t="n">
         <v>0.001939</v>
       </c>
     </row>
@@ -2609,9 +2771,12 @@
         <v>0.09565</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.09569</v>
+        <v>0.09574000000000001</v>
       </c>
       <c r="L54" s="1" t="n">
+        <v>0.09574000000000001</v>
+      </c>
+      <c r="M54" s="1" t="n">
         <v>0.09514</v>
       </c>
     </row>
@@ -2649,9 +2814,12 @@
         <v>0.04099</v>
       </c>
       <c r="K55" s="1" t="n">
+        <v>0.04093</v>
+      </c>
+      <c r="L55" s="1" t="n">
         <v>0.04099</v>
       </c>
-      <c r="L55" s="1" t="n">
+      <c r="M55" s="1" t="n">
         <v>0.04003</v>
       </c>
     </row>
@@ -2689,9 +2857,12 @@
         <v>0.29857</v>
       </c>
       <c r="K56" s="1" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="L56" s="1" t="n">
         <v>0.29861</v>
       </c>
-      <c r="L56" s="1" t="n">
+      <c r="M56" s="1" t="n">
         <v>0.29831</v>
       </c>
     </row>
@@ -2729,9 +2900,12 @@
         <v>0.00569</v>
       </c>
       <c r="K57" s="1" t="n">
+        <v>0.005684</v>
+      </c>
+      <c r="L57" s="1" t="n">
         <v>0.005824</v>
       </c>
-      <c r="L57" s="1" t="n">
+      <c r="M57" s="1" t="n">
         <v>0.005633</v>
       </c>
     </row>
@@ -2769,9 +2943,12 @@
         <v>4993.59</v>
       </c>
       <c r="K58" s="1" t="n">
+        <v>4990.71</v>
+      </c>
+      <c r="L58" s="1" t="n">
         <v>4998.37</v>
       </c>
-      <c r="L58" s="1" t="n">
+      <c r="M58" s="1" t="n">
         <v>4988.64</v>
       </c>
     </row>
@@ -2809,10 +2986,13 @@
         <v>0.4093</v>
       </c>
       <c r="K59" s="1" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="L59" s="1" t="n">
         <v>0.4246</v>
       </c>
-      <c r="L59" s="1" t="n">
-        <v>0.4093</v>
+      <c r="M59" s="1" t="n">
+        <v>0.4073</v>
       </c>
     </row>
     <row r="60">
@@ -2849,9 +3029,12 @@
         <v>0.04647</v>
       </c>
       <c r="K60" s="1" t="n">
+        <v>0.04648</v>
+      </c>
+      <c r="L60" s="1" t="n">
         <v>0.04686</v>
       </c>
-      <c r="L60" s="1" t="n">
+      <c r="M60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -2889,9 +3072,12 @@
         <v>0.21309</v>
       </c>
       <c r="K61" s="1" t="n">
+        <v>0.21336</v>
+      </c>
+      <c r="L61" s="1" t="n">
         <v>0.21708</v>
       </c>
-      <c r="L61" s="1" t="n">
+      <c r="M61" s="1" t="n">
         <v>0.21309</v>
       </c>
     </row>
@@ -2929,9 +3115,12 @@
         <v>0.1074</v>
       </c>
       <c r="K62" s="1" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="L62" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="L62" s="1" t="n">
+      <c r="M62" s="1" t="n">
         <v>0.1065</v>
       </c>
     </row>
@@ -2969,9 +3158,12 @@
         <v>0.7335</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>0.7335</v>
+        <v>0.7341</v>
       </c>
       <c r="L63" s="1" t="n">
+        <v>0.7341</v>
+      </c>
+      <c r="M63" s="1" t="n">
         <v>0.7255</v>
       </c>
     </row>
@@ -3009,9 +3201,12 @@
         <v>0.1671</v>
       </c>
       <c r="K64" s="1" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="L64" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="L64" s="1" t="n">
+      <c r="M64" s="1" t="n">
         <v>0.1658</v>
       </c>
     </row>
@@ -3049,9 +3244,12 @@
         <v>2.677</v>
       </c>
       <c r="K65" s="1" t="n">
+        <v>2.676</v>
+      </c>
+      <c r="L65" s="1" t="n">
         <v>2.677</v>
       </c>
-      <c r="L65" s="1" t="n">
+      <c r="M65" s="1" t="n">
         <v>2.65</v>
       </c>
     </row>
@@ -3089,9 +3287,12 @@
         <v>0.04054</v>
       </c>
       <c r="K66" s="1" t="n">
+        <v>0.04031</v>
+      </c>
+      <c r="L66" s="1" t="n">
         <v>0.04072</v>
       </c>
-      <c r="L66" s="1" t="n">
+      <c r="M66" s="1" t="n">
         <v>0.04018</v>
       </c>
     </row>
@@ -3129,9 +3330,12 @@
         <v>0.04314</v>
       </c>
       <c r="K67" s="1" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="L67" s="1" t="n">
         <v>0.04314</v>
       </c>
-      <c r="L67" s="1" t="n">
+      <c r="M67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -3169,9 +3373,12 @@
         <v>3.992</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>3.992</v>
+        <v>3.993</v>
       </c>
       <c r="L68" s="1" t="n">
+        <v>3.993</v>
+      </c>
+      <c r="M68" s="1" t="n">
         <v>3.951</v>
       </c>
     </row>
@@ -3209,9 +3416,12 @@
         <v>0.1273</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>0.1273</v>
+        <v>0.1274</v>
       </c>
       <c r="L69" s="1" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="M69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -3249,9 +3459,12 @@
         <v>6.338</v>
       </c>
       <c r="K70" s="1" t="n">
+        <v>6.308</v>
+      </c>
+      <c r="L70" s="1" t="n">
         <v>6.338</v>
       </c>
-      <c r="L70" s="1" t="n">
+      <c r="M70" s="1" t="n">
         <v>6.114</v>
       </c>
     </row>
@@ -3289,9 +3502,12 @@
         <v>0.05007</v>
       </c>
       <c r="K71" s="1" t="n">
+        <v>0.05009</v>
+      </c>
+      <c r="L71" s="1" t="n">
         <v>0.0501</v>
       </c>
-      <c r="L71" s="1" t="n">
+      <c r="M71" s="1" t="n">
         <v>0.04959</v>
       </c>
     </row>
@@ -3329,9 +3545,12 @@
         <v>0.00413</v>
       </c>
       <c r="K72" s="1" t="n">
+        <v>0.004131</v>
+      </c>
+      <c r="L72" s="1" t="n">
         <v>0.004181</v>
       </c>
-      <c r="L72" s="1" t="n">
+      <c r="M72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -3369,9 +3588,12 @@
         <v>6.02</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>6.029</v>
+        <v>6.032</v>
       </c>
       <c r="L73" s="1" t="n">
+        <v>6.032</v>
+      </c>
+      <c r="M73" s="1" t="n">
         <v>5.96</v>
       </c>
     </row>
@@ -3409,9 +3631,12 @@
         <v>0.1645</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>0.1645</v>
+        <v>0.1655</v>
       </c>
       <c r="L74" s="1" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="M74" s="1" t="n">
         <v>0.1619</v>
       </c>
     </row>
@@ -3449,9 +3674,12 @@
         <v>0.007355</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>0.007355</v>
+        <v>0.007365</v>
       </c>
       <c r="L75" s="1" t="n">
+        <v>0.007365</v>
+      </c>
+      <c r="M75" s="1" t="n">
         <v>0.007261</v>
       </c>
     </row>
@@ -3489,9 +3717,12 @@
         <v>0.2128</v>
       </c>
       <c r="K76" s="1" t="n">
+        <v>0.2171</v>
+      </c>
+      <c r="L76" s="1" t="n">
         <v>0.2199</v>
       </c>
-      <c r="L76" s="1" t="n">
+      <c r="M76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -3529,9 +3760,12 @@
         <v>0.005844</v>
       </c>
       <c r="K77" s="1" t="n">
+        <v>0.005836</v>
+      </c>
+      <c r="L77" s="1" t="n">
         <v>0.005844</v>
       </c>
-      <c r="L77" s="1" t="n">
+      <c r="M77" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -3569,9 +3803,12 @@
         <v>0.1023</v>
       </c>
       <c r="K78" s="1" t="n">
+        <v>0.1022</v>
+      </c>
+      <c r="L78" s="1" t="n">
         <v>0.1023</v>
       </c>
-      <c r="L78" s="1" t="n">
+      <c r="M78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -3609,9 +3846,12 @@
         <v>0.006315</v>
       </c>
       <c r="K79" s="1" t="n">
+        <v>0.00631</v>
+      </c>
+      <c r="L79" s="1" t="n">
         <v>0.006315</v>
       </c>
-      <c r="L79" s="1" t="n">
+      <c r="M79" s="1" t="n">
         <v>0.006237</v>
       </c>
     </row>
@@ -3649,9 +3889,12 @@
         <v>33.66</v>
       </c>
       <c r="K80" s="1" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="L80" s="1" t="n">
         <v>33.66</v>
       </c>
-      <c r="L80" s="1" t="n">
+      <c r="M80" s="1" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -3689,9 +3932,12 @@
         <v>0.04063</v>
       </c>
       <c r="K81" s="1" t="n">
+        <v>0.04055</v>
+      </c>
+      <c r="L81" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="L81" s="1" t="n">
+      <c r="M81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -3729,9 +3975,12 @@
         <v>0.16759</v>
       </c>
       <c r="K82" s="1" t="n">
+        <v>0.16753</v>
+      </c>
+      <c r="L82" s="1" t="n">
         <v>0.16759</v>
       </c>
-      <c r="L82" s="1" t="n">
+      <c r="M82" s="1" t="n">
         <v>0.16679</v>
       </c>
     </row>
@@ -3769,9 +4018,12 @@
         <v>0.1038</v>
       </c>
       <c r="K83" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="L83" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="L83" s="1" t="n">
+      <c r="M83" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -3809,9 +4061,12 @@
         <v>0.08758000000000001</v>
       </c>
       <c r="K84" s="1" t="n">
+        <v>0.08756</v>
+      </c>
+      <c r="L84" s="1" t="n">
         <v>0.08848</v>
       </c>
-      <c r="L84" s="1" t="n">
+      <c r="M84" s="1" t="n">
         <v>0.08756</v>
       </c>
     </row>
@@ -3849,10 +4104,13 @@
         <v>0.02305</v>
       </c>
       <c r="K85" s="1" t="n">
+        <v>0.02298</v>
+      </c>
+      <c r="L85" s="1" t="n">
         <v>0.02331</v>
       </c>
-      <c r="L85" s="1" t="n">
-        <v>0.02305</v>
+      <c r="M85" s="1" t="n">
+        <v>0.02298</v>
       </c>
     </row>
     <row r="86">
@@ -3892,6 +4150,9 @@
         <v>0.244</v>
       </c>
       <c r="L86" s="1" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="M86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -3929,9 +4190,12 @@
         <v>358.47</v>
       </c>
       <c r="K87" s="1" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="L87" s="1" t="n">
         <v>358.65</v>
       </c>
-      <c r="L87" s="1" t="n">
+      <c r="M87" s="1" t="n">
         <v>355.75</v>
       </c>
     </row>
@@ -3969,9 +4233,12 @@
         <v>0.0035</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>0.0035</v>
+        <v>0.00352</v>
       </c>
       <c r="L88" s="1" t="n">
+        <v>0.00352</v>
+      </c>
+      <c r="M88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -4009,9 +4276,12 @@
         <v>8.323</v>
       </c>
       <c r="K89" s="1" t="n">
+        <v>8.321</v>
+      </c>
+      <c r="L89" s="1" t="n">
         <v>8.323</v>
       </c>
-      <c r="L89" s="1" t="n">
+      <c r="M89" s="1" t="n">
         <v>8.257</v>
       </c>
     </row>
@@ -4049,9 +4319,12 @@
         <v>0.005952</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>0.005952</v>
+        <v>0.005958</v>
       </c>
       <c r="L90" s="1" t="n">
+        <v>0.005958</v>
+      </c>
+      <c r="M90" s="1" t="n">
         <v>0.005905</v>
       </c>
     </row>
@@ -4089,9 +4362,12 @@
         <v>0.06812</v>
       </c>
       <c r="K91" s="1" t="n">
+        <v>0.06908</v>
+      </c>
+      <c r="L91" s="1" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="L91" s="1" t="n">
+      <c r="M91" s="1" t="n">
         <v>0.06812</v>
       </c>
     </row>
@@ -4129,9 +4405,12 @@
         <v>0.02866</v>
       </c>
       <c r="K92" s="1" t="n">
+        <v>0.02869</v>
+      </c>
+      <c r="L92" s="1" t="n">
         <v>0.02905</v>
       </c>
-      <c r="L92" s="1" t="n">
+      <c r="M92" s="1" t="n">
         <v>0.02866</v>
       </c>
     </row>
@@ -4169,9 +4448,12 @@
         <v>5.228</v>
       </c>
       <c r="K93" s="1" t="n">
+        <v>5.188</v>
+      </c>
+      <c r="L93" s="1" t="n">
         <v>5.228</v>
       </c>
-      <c r="L93" s="1" t="n">
+      <c r="M93" s="1" t="n">
         <v>5.159</v>
       </c>
     </row>
@@ -4209,10 +4491,13 @@
         <v>0.000226</v>
       </c>
       <c r="K94" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="L94" s="1" t="n">
         <v>0.000228</v>
       </c>
-      <c r="L94" s="1" t="n">
-        <v>0.000226</v>
+      <c r="M94" s="1" t="n">
+        <v>0.000225</v>
       </c>
     </row>
     <row r="95">
@@ -4249,9 +4534,12 @@
         <v>0.9264</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>0.9264</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="L95" s="1" t="n">
+        <v>0.9278999999999999</v>
+      </c>
+      <c r="M95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -4289,9 +4577,12 @@
         <v>2.1278</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>2.1278</v>
+        <v>2.145</v>
       </c>
       <c r="L96" s="1" t="n">
+        <v>2.145</v>
+      </c>
+      <c r="M96" s="1" t="n">
         <v>2.0598</v>
       </c>
     </row>
@@ -4329,9 +4620,12 @@
         <v>0.3694</v>
       </c>
       <c r="K97" s="1" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L97" s="1" t="n">
         <v>0.3722</v>
       </c>
-      <c r="L97" s="1" t="n">
+      <c r="M97" s="1" t="n">
         <v>0.3681</v>
       </c>
     </row>
@@ -4369,9 +4663,12 @@
         <v>1.621</v>
       </c>
       <c r="K98" s="1" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="L98" s="1" t="n">
         <v>1.625</v>
       </c>
-      <c r="L98" s="1" t="n">
+      <c r="M98" s="1" t="n">
         <v>1.613</v>
       </c>
     </row>
@@ -4409,10 +4706,13 @@
         <v>0.2328</v>
       </c>
       <c r="K99" s="1" t="n">
+        <v>0.2316</v>
+      </c>
+      <c r="L99" s="1" t="n">
         <v>0.2368</v>
       </c>
-      <c r="L99" s="1" t="n">
-        <v>0.2328</v>
+      <c r="M99" s="1" t="n">
+        <v>0.2316</v>
       </c>
     </row>
     <row r="100">
@@ -4449,9 +4749,12 @@
         <v>0.13745</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>0.13745</v>
+        <v>0.13748</v>
       </c>
       <c r="L100" s="1" t="n">
+        <v>0.13748</v>
+      </c>
+      <c r="M100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -4489,9 +4792,12 @@
         <v>0.06988999999999999</v>
       </c>
       <c r="K101" s="1" t="n">
+        <v>0.06927</v>
+      </c>
+      <c r="L101" s="1" t="n">
         <v>0.07115</v>
       </c>
-      <c r="L101" s="1" t="n">
+      <c r="M101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -4529,9 +4835,12 @@
         <v>0.0010886</v>
       </c>
       <c r="K102" s="1" t="n">
+        <v>0.0010859</v>
+      </c>
+      <c r="L102" s="1" t="n">
         <v>0.0010886</v>
       </c>
-      <c r="L102" s="1" t="n">
+      <c r="M102" s="1" t="n">
         <v>0.0010822</v>
       </c>
     </row>
@@ -4569,9 +4878,12 @@
         <v>0.003427</v>
       </c>
       <c r="K103" s="1" t="n">
+        <v>0.003422</v>
+      </c>
+      <c r="L103" s="1" t="n">
         <v>0.003427</v>
       </c>
-      <c r="L103" s="1" t="n">
+      <c r="M103" s="1" t="n">
         <v>0.003403</v>
       </c>
     </row>
@@ -4609,9 +4921,12 @@
         <v>0.27312</v>
       </c>
       <c r="K104" s="1" t="n">
+        <v>0.27345</v>
+      </c>
+      <c r="L104" s="1" t="n">
         <v>0.27751</v>
       </c>
-      <c r="L104" s="1" t="n">
+      <c r="M104" s="1" t="n">
         <v>0.27312</v>
       </c>
     </row>
@@ -4649,9 +4964,12 @@
         <v>0.01251</v>
       </c>
       <c r="K105" s="1" t="n">
+        <v>0.01254</v>
+      </c>
+      <c r="L105" s="1" t="n">
         <v>0.01257</v>
       </c>
-      <c r="L105" s="1" t="n">
+      <c r="M105" s="1" t="n">
         <v>0.01243</v>
       </c>
     </row>
@@ -4689,9 +5007,12 @@
         <v>0.13478</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>0.1358</v>
+        <v>0.13586</v>
       </c>
       <c r="L106" s="1" t="n">
+        <v>0.13586</v>
+      </c>
+      <c r="M106" s="1" t="n">
         <v>0.13329</v>
       </c>
     </row>
@@ -4729,9 +5050,12 @@
         <v>0.3522</v>
       </c>
       <c r="K107" s="1" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="L107" s="1" t="n">
         <v>0.3522</v>
       </c>
-      <c r="L107" s="1" t="n">
+      <c r="M107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -4769,10 +5093,13 @@
         <v>0.1418</v>
       </c>
       <c r="K108" s="1" t="n">
+        <v>0.1413</v>
+      </c>
+      <c r="L108" s="1" t="n">
         <v>0.1436</v>
       </c>
-      <c r="L108" s="1" t="n">
-        <v>0.1418</v>
+      <c r="M108" s="1" t="n">
+        <v>0.1413</v>
       </c>
     </row>
     <row r="109">
@@ -4809,9 +5136,12 @@
         <v>0.9340000000000001</v>
       </c>
       <c r="K109" s="1" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="L109" s="1" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="L109" s="1" t="n">
+      <c r="M109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -4849,9 +5179,12 @@
         <v>0.016294</v>
       </c>
       <c r="K110" s="1" t="n">
+        <v>0.016242</v>
+      </c>
+      <c r="L110" s="1" t="n">
         <v>0.016308</v>
       </c>
-      <c r="L110" s="1" t="n">
+      <c r="M110" s="1" t="n">
         <v>0.016195</v>
       </c>
     </row>
@@ -4889,9 +5222,12 @@
         <v>0.038462</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>0.038462</v>
+        <v>0.038821</v>
       </c>
       <c r="L111" s="1" t="n">
+        <v>0.038821</v>
+      </c>
+      <c r="M111" s="1" t="n">
         <v>0.03774</v>
       </c>
     </row>
@@ -4929,9 +5265,12 @@
         <v>0.11976</v>
       </c>
       <c r="K112" s="1" t="n">
+        <v>0.11994</v>
+      </c>
+      <c r="L112" s="1" t="n">
         <v>0.12031</v>
       </c>
-      <c r="L112" s="1" t="n">
+      <c r="M112" s="1" t="n">
         <v>0.11926</v>
       </c>
     </row>
@@ -4969,10 +5308,13 @@
         <v>0.09381</v>
       </c>
       <c r="K113" s="1" t="n">
+        <v>0.09342</v>
+      </c>
+      <c r="L113" s="1" t="n">
         <v>0.09574000000000001</v>
       </c>
-      <c r="L113" s="1" t="n">
-        <v>0.09381</v>
+      <c r="M113" s="1" t="n">
+        <v>0.09342</v>
       </c>
     </row>
     <row r="114">
@@ -5009,9 +5351,12 @@
         <v>0.13021</v>
       </c>
       <c r="K114" s="1" t="n">
+        <v>0.13016</v>
+      </c>
+      <c r="L114" s="1" t="n">
         <v>0.13063</v>
       </c>
-      <c r="L114" s="1" t="n">
+      <c r="M114" s="1" t="n">
         <v>0.12895</v>
       </c>
     </row>
@@ -5049,9 +5394,12 @@
         <v>0.2663</v>
       </c>
       <c r="K115" s="1" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="L115" s="1" t="n">
         <v>0.2663</v>
       </c>
-      <c r="L115" s="1" t="n">
+      <c r="M115" s="1" t="n">
         <v>0.2638</v>
       </c>
     </row>
@@ -5089,9 +5437,12 @@
         <v>0.04859</v>
       </c>
       <c r="K116" s="1" t="n">
+        <v>0.04855</v>
+      </c>
+      <c r="L116" s="1" t="n">
         <v>0.0529</v>
       </c>
-      <c r="L116" s="1" t="n">
+      <c r="M116" s="1" t="n">
         <v>0.04805</v>
       </c>
     </row>
@@ -5129,9 +5480,12 @@
         <v>0.0916</v>
       </c>
       <c r="K117" s="1" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="L117" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="L117" s="1" t="n">
+      <c r="M117" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -5169,9 +5523,12 @@
         <v>0.05538</v>
       </c>
       <c r="K118" s="1" t="n">
-        <v>0.05563</v>
+        <v>0.05566</v>
       </c>
       <c r="L118" s="1" t="n">
+        <v>0.05566</v>
+      </c>
+      <c r="M118" s="1" t="n">
         <v>0.05501</v>
       </c>
     </row>
@@ -5209,9 +5566,12 @@
         <v>0.01513</v>
       </c>
       <c r="K119" s="1" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="L119" s="1" t="n">
         <v>0.01515</v>
       </c>
-      <c r="L119" s="1" t="n">
+      <c r="M119" s="1" t="n">
         <v>0.01505</v>
       </c>
     </row>
@@ -5249,9 +5609,12 @@
         <v>3.079</v>
       </c>
       <c r="K120" s="1" t="n">
+        <v>3.078</v>
+      </c>
+      <c r="L120" s="1" t="n">
         <v>3.079</v>
       </c>
-      <c r="L120" s="1" t="n">
+      <c r="M120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -5289,9 +5652,12 @@
         <v>1.853</v>
       </c>
       <c r="K121" s="1" t="n">
+        <v>1.851</v>
+      </c>
+      <c r="L121" s="1" t="n">
         <v>1.855</v>
       </c>
-      <c r="L121" s="1" t="n">
+      <c r="M121" s="1" t="n">
         <v>1.848</v>
       </c>
     </row>
@@ -5329,9 +5695,12 @@
         <v>1.3028</v>
       </c>
       <c r="K122" s="1" t="n">
+        <v>1.3019</v>
+      </c>
+      <c r="L122" s="1" t="n">
         <v>1.3028</v>
       </c>
-      <c r="L122" s="1" t="n">
+      <c r="M122" s="1" t="n">
         <v>1.2934</v>
       </c>
     </row>
@@ -5369,9 +5738,12 @@
         <v>0.318</v>
       </c>
       <c r="K123" s="1" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="L123" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="L123" s="1" t="n">
+      <c r="M123" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -5409,9 +5781,12 @@
         <v>0.12275</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>0.12506</v>
+        <v>0.12601</v>
       </c>
       <c r="L124" s="1" t="n">
+        <v>0.12601</v>
+      </c>
+      <c r="M124" s="1" t="n">
         <v>0.12202</v>
       </c>
     </row>
@@ -5449,9 +5824,12 @@
         <v>0.008626999999999999</v>
       </c>
       <c r="K125" s="1" t="n">
+        <v>0.008567999999999999</v>
+      </c>
+      <c r="L125" s="1" t="n">
         <v>0.008626999999999999</v>
       </c>
-      <c r="L125" s="1" t="n">
+      <c r="M125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -5489,9 +5867,12 @@
         <v>0.01621</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>0.01621</v>
+        <v>0.01622</v>
       </c>
       <c r="L126" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="M126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -5529,9 +5910,12 @@
         <v>0.04424</v>
       </c>
       <c r="K127" s="1" t="n">
+        <v>0.04425</v>
+      </c>
+      <c r="L127" s="1" t="n">
         <v>0.04468</v>
       </c>
-      <c r="L127" s="1" t="n">
+      <c r="M127" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -5569,9 +5953,12 @@
         <v>0.04693</v>
       </c>
       <c r="K128" s="1" t="n">
+        <v>0.04674</v>
+      </c>
+      <c r="L128" s="1" t="n">
         <v>0.04727</v>
       </c>
-      <c r="L128" s="1" t="n">
+      <c r="M128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -5609,9 +5996,12 @@
         <v>0.09656000000000001</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>0.09656000000000001</v>
+        <v>0.09673</v>
       </c>
       <c r="L129" s="1" t="n">
+        <v>0.09673</v>
+      </c>
+      <c r="M129" s="1" t="n">
         <v>0.09543</v>
       </c>
     </row>
@@ -5649,9 +6039,12 @@
         <v>0.09855</v>
       </c>
       <c r="K130" s="1" t="n">
+        <v>0.09875</v>
+      </c>
+      <c r="L130" s="1" t="n">
         <v>0.09927</v>
       </c>
-      <c r="L130" s="1" t="n">
+      <c r="M130" s="1" t="n">
         <v>0.09848</v>
       </c>
     </row>
@@ -5689,9 +6082,12 @@
         <v>0.16695</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>0.16695</v>
+        <v>0.16707</v>
       </c>
       <c r="L131" s="1" t="n">
+        <v>0.16707</v>
+      </c>
+      <c r="M131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -5729,9 +6125,12 @@
         <v>0.01696</v>
       </c>
       <c r="K132" s="1" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="L132" s="1" t="n">
         <v>0.01702</v>
       </c>
-      <c r="L132" s="1" t="n">
+      <c r="M132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -5769,9 +6168,12 @@
         <v>0.06707</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>0.06707</v>
+        <v>0.06714000000000001</v>
       </c>
       <c r="L133" s="1" t="n">
+        <v>0.06714000000000001</v>
+      </c>
+      <c r="M133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -5809,9 +6211,12 @@
         <v>0.3042</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>0.3042</v>
+        <v>0.3043</v>
       </c>
       <c r="L134" s="1" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="M134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -5849,9 +6254,12 @@
         <v>0.04502</v>
       </c>
       <c r="K135" s="1" t="n">
+        <v>0.04537</v>
+      </c>
+      <c r="L135" s="1" t="n">
         <v>0.04563</v>
       </c>
-      <c r="L135" s="1" t="n">
+      <c r="M135" s="1" t="n">
         <v>0.04502</v>
       </c>
     </row>
@@ -5889,9 +6297,12 @@
         <v>0.782</v>
       </c>
       <c r="K136" s="1" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="L136" s="1" t="n">
         <v>0.783</v>
       </c>
-      <c r="L136" s="1" t="n">
+      <c r="M136" s="1" t="n">
         <v>0.781</v>
       </c>
     </row>
@@ -5929,9 +6340,12 @@
         <v>0.1178</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>0.1178</v>
+        <v>0.1181</v>
       </c>
       <c r="L137" s="1" t="n">
+        <v>0.1181</v>
+      </c>
+      <c r="M137" s="1" t="n">
         <v>0.1162</v>
       </c>
     </row>
@@ -5969,9 +6383,12 @@
         <v>0.14723</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>0.14759</v>
+        <v>0.14787</v>
       </c>
       <c r="L138" s="1" t="n">
+        <v>0.14787</v>
+      </c>
+      <c r="M138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -6009,9 +6426,12 @@
         <v>0.05766</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>0.05766</v>
+        <v>0.05776</v>
       </c>
       <c r="L139" s="1" t="n">
+        <v>0.05776</v>
+      </c>
+      <c r="M139" s="1" t="n">
         <v>0.05699</v>
       </c>
     </row>
@@ -6049,9 +6469,12 @@
         <v>0.007302</v>
       </c>
       <c r="K140" s="1" t="n">
+        <v>0.007293</v>
+      </c>
+      <c r="L140" s="1" t="n">
         <v>0.007302</v>
       </c>
-      <c r="L140" s="1" t="n">
+      <c r="M140" s="1" t="n">
         <v>0.00726</v>
       </c>
     </row>
@@ -6089,9 +6512,12 @@
         <v>0.09637</v>
       </c>
       <c r="K141" s="1" t="n">
+        <v>0.09624000000000001</v>
+      </c>
+      <c r="L141" s="1" t="n">
         <v>0.09637</v>
       </c>
-      <c r="L141" s="1" t="n">
+      <c r="M141" s="1" t="n">
         <v>0.09569</v>
       </c>
     </row>
@@ -6129,9 +6555,12 @@
         <v>0.08388</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>0.08388</v>
+        <v>0.0839</v>
       </c>
       <c r="L142" s="1" t="n">
+        <v>0.0839</v>
+      </c>
+      <c r="M142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -6169,9 +6598,12 @@
         <v>0.00861</v>
       </c>
       <c r="K143" s="1" t="n">
+        <v>0.008529999999999999</v>
+      </c>
+      <c r="L143" s="1" t="n">
         <v>0.00861</v>
       </c>
-      <c r="L143" s="1" t="n">
+      <c r="M143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -6209,9 +6641,12 @@
         <v>0.07267999999999999</v>
       </c>
       <c r="K144" s="1" t="n">
+        <v>0.07260999999999999</v>
+      </c>
+      <c r="L144" s="1" t="n">
         <v>0.07288</v>
       </c>
-      <c r="L144" s="1" t="n">
+      <c r="M144" s="1" t="n">
         <v>0.07224999999999999</v>
       </c>
     </row>
@@ -6249,10 +6684,13 @@
         <v>0.4287</v>
       </c>
       <c r="K145" s="1" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="L145" s="1" t="n">
         <v>0.4305</v>
       </c>
-      <c r="L145" s="1" t="n">
-        <v>0.427</v>
+      <c r="M145" s="1" t="n">
+        <v>0.4258</v>
       </c>
     </row>
     <row r="146">
@@ -6289,9 +6727,12 @@
         <v>0.03227</v>
       </c>
       <c r="K146" s="1" t="n">
+        <v>0.03237</v>
+      </c>
+      <c r="L146" s="1" t="n">
         <v>0.03276</v>
       </c>
-      <c r="L146" s="1" t="n">
+      <c r="M146" s="1" t="n">
         <v>0.0322</v>
       </c>
     </row>
@@ -6332,6 +6773,9 @@
         <v>390.55</v>
       </c>
       <c r="L147" s="1" t="n">
+        <v>390.55</v>
+      </c>
+      <c r="M147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -6369,9 +6813,12 @@
         <v>0.03306</v>
       </c>
       <c r="K148" s="1" t="n">
+        <v>0.03291</v>
+      </c>
+      <c r="L148" s="1" t="n">
         <v>0.0333</v>
       </c>
-      <c r="L148" s="1" t="n">
+      <c r="M148" s="1" t="n">
         <v>0.0329</v>
       </c>
     </row>
@@ -6409,9 +6856,12 @@
         <v>0.05319</v>
       </c>
       <c r="K149" s="1" t="n">
+        <v>0.05316</v>
+      </c>
+      <c r="L149" s="1" t="n">
         <v>0.05322</v>
       </c>
-      <c r="L149" s="1" t="n">
+      <c r="M149" s="1" t="n">
         <v>0.05289</v>
       </c>
     </row>
@@ -6449,9 +6899,12 @@
         <v>0.0004415</v>
       </c>
       <c r="K150" s="1" t="n">
+        <v>0.0004398</v>
+      </c>
+      <c r="L150" s="1" t="n">
         <v>0.000443</v>
       </c>
-      <c r="L150" s="1" t="n">
+      <c r="M150" s="1" t="n">
         <v>0.000439</v>
       </c>
     </row>
@@ -6489,9 +6942,12 @@
         <v>0.02194</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>0.02194</v>
+        <v>0.02197</v>
       </c>
       <c r="L151" s="1" t="n">
+        <v>0.02197</v>
+      </c>
+      <c r="M151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -6529,9 +6985,12 @@
         <v>0.001788</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>0.001788</v>
+        <v>0.001793</v>
       </c>
       <c r="L152" s="1" t="n">
+        <v>0.001793</v>
+      </c>
+      <c r="M152" s="1" t="n">
         <v>0.001768</v>
       </c>
     </row>
@@ -6569,9 +7028,12 @@
         <v>6.1e-06</v>
       </c>
       <c r="K153" s="1" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="L153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
-      <c r="L153" s="1" t="n">
+      <c r="M153" s="1" t="n">
         <v>6e-06</v>
       </c>
     </row>
@@ -6609,9 +7071,12 @@
         <v>0.1609</v>
       </c>
       <c r="K154" s="1" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="L154" s="1" t="n">
         <v>0.1609</v>
       </c>
-      <c r="L154" s="1" t="n">
+      <c r="M154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -6649,9 +7114,12 @@
         <v>0.03781</v>
       </c>
       <c r="K155" s="1" t="n">
+        <v>0.03778</v>
+      </c>
+      <c r="L155" s="1" t="n">
         <v>0.03781</v>
       </c>
-      <c r="L155" s="1" t="n">
+      <c r="M155" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -6689,9 +7157,12 @@
         <v>0.005403</v>
       </c>
       <c r="K156" s="1" t="n">
+        <v>0.005402</v>
+      </c>
+      <c r="L156" s="1" t="n">
         <v>0.005404</v>
       </c>
-      <c r="L156" s="1" t="n">
+      <c r="M156" s="1" t="n">
         <v>0.005364</v>
       </c>
     </row>
@@ -6732,6 +7203,9 @@
         <v>0.02284</v>
       </c>
       <c r="L157" s="1" t="n">
+        <v>0.02284</v>
+      </c>
+      <c r="M157" s="1" t="n">
         <v>0.02263</v>
       </c>
     </row>
@@ -6772,6 +7246,9 @@
         <v>1.099</v>
       </c>
       <c r="L158" s="1" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="M158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -6809,9 +7286,12 @@
         <v>2.577</v>
       </c>
       <c r="K159" s="1" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="L159" s="1" t="n">
         <v>2.577</v>
       </c>
-      <c r="L159" s="1" t="n">
+      <c r="M159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -6849,9 +7329,12 @@
         <v>4.855</v>
       </c>
       <c r="K160" s="1" t="n">
+        <v>4.847</v>
+      </c>
+      <c r="L160" s="1" t="n">
         <v>4.858</v>
       </c>
-      <c r="L160" s="1" t="n">
+      <c r="M160" s="1" t="n">
         <v>4.836</v>
       </c>
     </row>
@@ -6889,9 +7372,12 @@
         <v>0.1607</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>0.1607</v>
+        <v>0.1608</v>
       </c>
       <c r="L161" s="1" t="n">
+        <v>0.1608</v>
+      </c>
+      <c r="M161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -6929,9 +7415,12 @@
         <v>0.20425</v>
       </c>
       <c r="K162" s="1" t="n">
+        <v>0.20494</v>
+      </c>
+      <c r="L162" s="1" t="n">
         <v>0.20754</v>
       </c>
-      <c r="L162" s="1" t="n">
+      <c r="M162" s="1" t="n">
         <v>0.20425</v>
       </c>
     </row>
@@ -6969,9 +7458,12 @@
         <v>0.03954</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>0.03954</v>
+        <v>0.03955</v>
       </c>
       <c r="L163" s="1" t="n">
+        <v>0.03955</v>
+      </c>
+      <c r="M163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -7009,9 +7501,12 @@
         <v>0.06324</v>
       </c>
       <c r="K164" s="1" t="n">
+        <v>0.06317</v>
+      </c>
+      <c r="L164" s="1" t="n">
         <v>0.0636</v>
       </c>
-      <c r="L164" s="1" t="n">
+      <c r="M164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -7049,9 +7544,12 @@
         <v>0.3601</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>0.3618</v>
+        <v>0.3658</v>
       </c>
       <c r="L165" s="1" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="M165" s="1" t="n">
         <v>0.3525</v>
       </c>
     </row>
@@ -7089,9 +7587,12 @@
         <v>139.63</v>
       </c>
       <c r="K166" s="1" t="n">
+        <v>139.47</v>
+      </c>
+      <c r="L166" s="1" t="n">
         <v>139.63</v>
       </c>
-      <c r="L166" s="1" t="n">
+      <c r="M166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -7129,10 +7630,13 @@
         <v>0.0006491</v>
       </c>
       <c r="K167" s="1" t="n">
+        <v>0.0006419</v>
+      </c>
+      <c r="L167" s="1" t="n">
         <v>0.0006533</v>
       </c>
-      <c r="L167" s="1" t="n">
-        <v>0.0006431</v>
+      <c r="M167" s="1" t="n">
+        <v>0.0006419</v>
       </c>
     </row>
     <row r="168">
@@ -7169,9 +7673,12 @@
         <v>0.01655</v>
       </c>
       <c r="K168" s="1" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="L168" s="1" t="n">
         <v>0.01678</v>
       </c>
-      <c r="L168" s="1" t="n">
+      <c r="M168" s="1" t="n">
         <v>0.01629</v>
       </c>
     </row>
@@ -7209,9 +7716,12 @@
         <v>0.04818</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>0.04818</v>
+        <v>0.04823</v>
       </c>
       <c r="L169" s="1" t="n">
+        <v>0.04823</v>
+      </c>
+      <c r="M169" s="1" t="n">
         <v>0.04785</v>
       </c>
     </row>
@@ -7249,9 +7759,12 @@
         <v>4.282</v>
       </c>
       <c r="K170" s="1" t="n">
+        <v>4.278</v>
+      </c>
+      <c r="L170" s="1" t="n">
         <v>4.298</v>
       </c>
-      <c r="L170" s="1" t="n">
+      <c r="M170" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -7289,9 +7802,12 @@
         <v>0.03875</v>
       </c>
       <c r="K171" s="1" t="n">
+        <v>0.03874</v>
+      </c>
+      <c r="L171" s="1" t="n">
         <v>0.03875</v>
       </c>
-      <c r="L171" s="1" t="n">
+      <c r="M171" s="1" t="n">
         <v>0.03825</v>
       </c>
     </row>
@@ -7329,9 +7845,12 @@
         <v>0.0429</v>
       </c>
       <c r="K172" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="L172" s="1" t="n">
         <v>0.0431</v>
       </c>
-      <c r="L172" s="1" t="n">
+      <c r="M172" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -7369,10 +7888,13 @@
         <v>0.023745</v>
       </c>
       <c r="K173" s="1" t="n">
+        <v>0.023721</v>
+      </c>
+      <c r="L173" s="1" t="n">
         <v>0.024556</v>
       </c>
-      <c r="L173" s="1" t="n">
-        <v>0.023745</v>
+      <c r="M173" s="1" t="n">
+        <v>0.023721</v>
       </c>
     </row>
     <row r="174">
@@ -7409,9 +7931,12 @@
         <v>1.0782</v>
       </c>
       <c r="K174" s="1" t="n">
+        <v>1.0788</v>
+      </c>
+      <c r="L174" s="1" t="n">
         <v>1.0809</v>
       </c>
-      <c r="L174" s="1" t="n">
+      <c r="M174" s="1" t="n">
         <v>1.0704</v>
       </c>
     </row>
@@ -7449,9 +7974,12 @@
         <v>0.028034</v>
       </c>
       <c r="K175" s="1" t="n">
+        <v>0.028071</v>
+      </c>
+      <c r="L175" s="1" t="n">
         <v>0.028967</v>
       </c>
-      <c r="L175" s="1" t="n">
+      <c r="M175" s="1" t="n">
         <v>0.028034</v>
       </c>
     </row>
@@ -7489,9 +8017,12 @@
         <v>0.02207</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>0.02207</v>
+        <v>0.02215</v>
       </c>
       <c r="L176" s="1" t="n">
+        <v>0.02215</v>
+      </c>
+      <c r="M176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -7529,9 +8060,12 @@
         <v>0.5492</v>
       </c>
       <c r="K177" s="1" t="n">
+        <v>0.5488</v>
+      </c>
+      <c r="L177" s="1" t="n">
         <v>0.5501</v>
       </c>
-      <c r="L177" s="1" t="n">
+      <c r="M177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -7569,9 +8103,12 @@
         <v>0.08248</v>
       </c>
       <c r="K178" s="1" t="n">
+        <v>0.08219</v>
+      </c>
+      <c r="L178" s="1" t="n">
         <v>0.08276</v>
       </c>
-      <c r="L178" s="1" t="n">
+      <c r="M178" s="1" t="n">
         <v>0.08214</v>
       </c>
     </row>
@@ -7609,9 +8146,12 @@
         <v>0.02142</v>
       </c>
       <c r="K179" s="1" t="n">
+        <v>0.02141</v>
+      </c>
+      <c r="L179" s="1" t="n">
         <v>0.02142</v>
       </c>
-      <c r="L179" s="1" t="n">
+      <c r="M179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -7649,9 +8189,12 @@
         <v>0.27417</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>0.27417</v>
+        <v>0.27438</v>
       </c>
       <c r="L180" s="1" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="M180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -7692,6 +8235,9 @@
         <v>0.00421</v>
       </c>
       <c r="L181" s="1" t="n">
+        <v>0.00421</v>
+      </c>
+      <c r="M181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -7729,10 +8275,13 @@
         <v>0.07904</v>
       </c>
       <c r="K182" s="1" t="n">
+        <v>0.07901</v>
+      </c>
+      <c r="L182" s="1" t="n">
         <v>0.07981000000000001</v>
       </c>
-      <c r="L182" s="1" t="n">
-        <v>0.07902000000000001</v>
+      <c r="M182" s="1" t="n">
+        <v>0.07901</v>
       </c>
     </row>
     <row r="183">
@@ -7769,9 +8318,12 @@
         <v>0.02364</v>
       </c>
       <c r="K183" s="1" t="n">
+        <v>0.02361</v>
+      </c>
+      <c r="L183" s="1" t="n">
         <v>0.02364</v>
       </c>
-      <c r="L183" s="1" t="n">
+      <c r="M183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -7809,9 +8361,12 @@
         <v>7.016000000000001e-05</v>
       </c>
       <c r="K184" s="1" t="n">
+        <v>7.015e-05</v>
+      </c>
+      <c r="L184" s="1" t="n">
         <v>7.016000000000001e-05</v>
       </c>
-      <c r="L184" s="1" t="n">
+      <c r="M184" s="1" t="n">
         <v>6.957e-05</v>
       </c>
     </row>
@@ -7849,9 +8404,12 @@
         <v>0.02138</v>
       </c>
       <c r="K185" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="L185" s="1" t="n">
         <v>0.0214</v>
       </c>
-      <c r="L185" s="1" t="n">
+      <c r="M185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -7889,9 +8447,12 @@
         <v>0.01643</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>0.01643</v>
+        <v>0.01644</v>
       </c>
       <c r="L186" s="1" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="M186" s="1" t="n">
         <v>0.01623</v>
       </c>
     </row>
@@ -7929,9 +8490,12 @@
         <v>0.979</v>
       </c>
       <c r="K187" s="1" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="L187" s="1" t="n">
         <v>0.981</v>
       </c>
-      <c r="L187" s="1" t="n">
+      <c r="M187" s="1" t="n">
         <v>0.971</v>
       </c>
     </row>
@@ -7969,9 +8533,12 @@
         <v>0.0239</v>
       </c>
       <c r="K188" s="1" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="L188" s="1" t="n">
         <v>0.024</v>
       </c>
-      <c r="L188" s="1" t="n">
+      <c r="M188" s="1" t="n">
         <v>0.0237</v>
       </c>
     </row>
@@ -8009,9 +8576,12 @@
         <v>1.8888</v>
       </c>
       <c r="K189" s="1" t="n">
+        <v>1.886</v>
+      </c>
+      <c r="L189" s="1" t="n">
         <v>1.8888</v>
       </c>
-      <c r="L189" s="1" t="n">
+      <c r="M189" s="1" t="n">
         <v>1.8609</v>
       </c>
     </row>
@@ -8049,9 +8619,12 @@
         <v>1.843</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>1.843</v>
+        <v>1.844</v>
       </c>
       <c r="L190" s="1" t="n">
+        <v>1.844</v>
+      </c>
+      <c r="M190" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -8089,9 +8662,12 @@
         <v>0.02685</v>
       </c>
       <c r="K191" s="1" t="n">
+        <v>0.02678</v>
+      </c>
+      <c r="L191" s="1" t="n">
         <v>0.02685</v>
       </c>
-      <c r="L191" s="1" t="n">
+      <c r="M191" s="1" t="n">
         <v>0.02662</v>
       </c>
     </row>
@@ -8129,9 +8705,12 @@
         <v>0.0975</v>
       </c>
       <c r="K192" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="L192" s="1" t="n">
         <v>0.0975</v>
       </c>
-      <c r="L192" s="1" t="n">
+      <c r="M192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -8169,9 +8748,12 @@
         <v>0.1718</v>
       </c>
       <c r="K193" s="1" t="n">
+        <v>0.1717</v>
+      </c>
+      <c r="L193" s="1" t="n">
         <v>0.1722</v>
       </c>
-      <c r="L193" s="1" t="n">
+      <c r="M193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -8209,9 +8791,12 @@
         <v>16.407</v>
       </c>
       <c r="K194" s="1" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="L194" s="1" t="n">
         <v>16.407</v>
       </c>
-      <c r="L194" s="1" t="n">
+      <c r="M194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -8249,9 +8834,12 @@
         <v>4.136</v>
       </c>
       <c r="K195" s="1" t="n">
+        <v>4.123</v>
+      </c>
+      <c r="L195" s="1" t="n">
         <v>4.136</v>
       </c>
-      <c r="L195" s="1" t="n">
+      <c r="M195" s="1" t="n">
         <v>4.087</v>
       </c>
     </row>
@@ -8289,9 +8877,12 @@
         <v>1.2753</v>
       </c>
       <c r="K196" s="1" t="n">
+        <v>1.2747</v>
+      </c>
+      <c r="L196" s="1" t="n">
         <v>1.2794</v>
       </c>
-      <c r="L196" s="1" t="n">
+      <c r="M196" s="1" t="n">
         <v>1.2663</v>
       </c>
     </row>
@@ -8329,9 +8920,12 @@
         <v>3.063</v>
       </c>
       <c r="K197" s="1" t="n">
+        <v>3.091</v>
+      </c>
+      <c r="L197" s="1" t="n">
         <v>3.092</v>
       </c>
-      <c r="L197" s="1" t="n">
+      <c r="M197" s="1" t="n">
         <v>3.063</v>
       </c>
     </row>
@@ -8369,9 +8963,12 @@
         <v>0.01261</v>
       </c>
       <c r="K198" s="1" t="n">
+        <v>0.01261</v>
+      </c>
+      <c r="L198" s="1" t="n">
         <v>0.01266</v>
       </c>
-      <c r="L198" s="1" t="n">
+      <c r="M198" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -8409,9 +9006,12 @@
         <v>0.000177</v>
       </c>
       <c r="K199" s="1" t="n">
+        <v>0.0001768</v>
+      </c>
+      <c r="L199" s="1" t="n">
         <v>0.000177</v>
       </c>
-      <c r="L199" s="1" t="n">
+      <c r="M199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -8449,9 +9049,12 @@
         <v>115.81</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>115.81</v>
+        <v>115.82</v>
       </c>
       <c r="L200" s="1" t="n">
+        <v>115.82</v>
+      </c>
+      <c r="M200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -8489,10 +9092,13 @@
         <v>0.01022</v>
       </c>
       <c r="K201" s="1" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="L201" s="1" t="n">
         <v>0.01031</v>
       </c>
-      <c r="L201" s="1" t="n">
-        <v>0.01021</v>
+      <c r="M201" s="1" t="n">
+        <v>0.0102</v>
       </c>
     </row>
     <row r="202">
@@ -8529,9 +9135,12 @@
         <v>0.01067</v>
       </c>
       <c r="K202" s="1" t="n">
+        <v>0.01069</v>
+      </c>
+      <c r="L202" s="1" t="n">
         <v>0.01073</v>
       </c>
-      <c r="L202" s="1" t="n">
+      <c r="M202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -8569,9 +9178,12 @@
         <v>0.00314</v>
       </c>
       <c r="K203" s="1" t="n">
+        <v>0.003141</v>
+      </c>
+      <c r="L203" s="1" t="n">
         <v>0.003153</v>
       </c>
-      <c r="L203" s="1" t="n">
+      <c r="M203" s="1" t="n">
         <v>0.003131</v>
       </c>
     </row>
@@ -8609,9 +9221,12 @@
         <v>28.39</v>
       </c>
       <c r="K204" s="1" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="L204" s="1" t="n">
         <v>28.39</v>
       </c>
-      <c r="L204" s="1" t="n">
+      <c r="M204" s="1" t="n">
         <v>28.23</v>
       </c>
     </row>
@@ -8649,10 +9264,13 @@
         <v>0.5592</v>
       </c>
       <c r="K205" s="1" t="n">
+        <v>0.5578</v>
+      </c>
+      <c r="L205" s="1" t="n">
         <v>0.5636</v>
       </c>
-      <c r="L205" s="1" t="n">
-        <v>0.5592</v>
+      <c r="M205" s="1" t="n">
+        <v>0.5578</v>
       </c>
     </row>
     <row r="206">
@@ -8689,9 +9307,12 @@
         <v>0.0004434</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>0.0004434</v>
+        <v>0.0004438</v>
       </c>
       <c r="L206" s="1" t="n">
+        <v>0.0004438</v>
+      </c>
+      <c r="M206" s="1" t="n">
         <v>0.0004387</v>
       </c>
     </row>
@@ -8729,9 +9350,12 @@
         <v>0.04689</v>
       </c>
       <c r="K207" s="1" t="n">
+        <v>0.04684</v>
+      </c>
+      <c r="L207" s="1" t="n">
         <v>0.04689</v>
       </c>
-      <c r="L207" s="1" t="n">
+      <c r="M207" s="1" t="n">
         <v>0.04648</v>
       </c>
     </row>
@@ -8769,9 +9393,12 @@
         <v>0.09</v>
       </c>
       <c r="K208" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L208" s="1" t="n">
         <v>0.091</v>
       </c>
-      <c r="L208" s="1" t="n">
+      <c r="M208" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -8809,9 +9436,12 @@
         <v>0.02584</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>0.02584</v>
+        <v>0.0259</v>
       </c>
       <c r="L209" s="1" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="M209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -8849,9 +9479,12 @@
         <v>0.012645</v>
       </c>
       <c r="K210" s="1" t="n">
+        <v>0.01266</v>
+      </c>
+      <c r="L210" s="1" t="n">
         <v>0.012745</v>
       </c>
-      <c r="L210" s="1" t="n">
+      <c r="M210" s="1" t="n">
         <v>0.012645</v>
       </c>
     </row>
@@ -8892,6 +9525,9 @@
         <v>0.0921</v>
       </c>
       <c r="L211" s="1" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="M211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -8929,10 +9565,13 @@
         <v>0.00707</v>
       </c>
       <c r="K212" s="1" t="n">
+        <v>0.007038</v>
+      </c>
+      <c r="L212" s="1" t="n">
         <v>0.007076</v>
       </c>
-      <c r="L212" s="1" t="n">
-        <v>0.007044</v>
+      <c r="M212" s="1" t="n">
+        <v>0.007038</v>
       </c>
     </row>
     <row r="213">
@@ -8969,9 +9608,12 @@
         <v>0.02975</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>0.02975</v>
+        <v>0.02978</v>
       </c>
       <c r="L213" s="1" t="n">
+        <v>0.02978</v>
+      </c>
+      <c r="M213" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -9009,9 +9651,12 @@
         <v>0.271</v>
       </c>
       <c r="K214" s="1" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="L214" s="1" t="n">
         <v>0.271</v>
       </c>
-      <c r="L214" s="1" t="n">
+      <c r="M214" s="1" t="n">
         <v>0.2698</v>
       </c>
     </row>
@@ -9049,9 +9694,12 @@
         <v>0.02256</v>
       </c>
       <c r="K215" s="1" t="n">
+        <v>0.02229</v>
+      </c>
+      <c r="L215" s="1" t="n">
         <v>0.02256</v>
       </c>
-      <c r="L215" s="1" t="n">
+      <c r="M215" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -9089,9 +9737,12 @@
         <v>0.0147</v>
       </c>
       <c r="K216" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="L216" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="L216" s="1" t="n">
+      <c r="M216" s="1" t="n">
         <v>0.01463</v>
       </c>
     </row>
@@ -9132,6 +9783,9 @@
         <v>0.255</v>
       </c>
       <c r="L217" s="1" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="M217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -9169,9 +9823,12 @@
         <v>0.3114</v>
       </c>
       <c r="K218" s="1" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="L218" s="1" t="n">
         <v>0.3114</v>
       </c>
-      <c r="L218" s="1" t="n">
+      <c r="M218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -9209,9 +9866,12 @@
         <v>0.1788</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>0.1788</v>
+        <v>0.179</v>
       </c>
       <c r="L219" s="1" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="M219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -9249,9 +9909,12 @@
         <v>14.98</v>
       </c>
       <c r="K220" s="1" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="L220" s="1" t="n">
         <v>15.02</v>
       </c>
-      <c r="L220" s="1" t="n">
+      <c r="M220" s="1" t="n">
         <v>14.95</v>
       </c>
     </row>
@@ -9289,9 +9952,12 @@
         <v>0.01614</v>
       </c>
       <c r="K221" s="1" t="n">
+        <v>0.01611</v>
+      </c>
+      <c r="L221" s="1" t="n">
         <v>0.01614</v>
       </c>
-      <c r="L221" s="1" t="n">
+      <c r="M221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -9329,9 +9995,12 @@
         <v>66.61</v>
       </c>
       <c r="K222" s="1" t="n">
+        <v>66.44</v>
+      </c>
+      <c r="L222" s="1" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="L222" s="1" t="n">
+      <c r="M222" s="1" t="n">
         <v>66.17</v>
       </c>
     </row>
@@ -9369,9 +10038,12 @@
         <v>0.09316000000000001</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>0.09352000000000001</v>
+        <v>0.09379</v>
       </c>
       <c r="L223" s="1" t="n">
+        <v>0.09379</v>
+      </c>
+      <c r="M223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -9409,9 +10081,12 @@
         <v>0.03974</v>
       </c>
       <c r="K224" s="1" t="n">
+        <v>0.03962</v>
+      </c>
+      <c r="L224" s="1" t="n">
         <v>0.03974</v>
       </c>
-      <c r="L224" s="1" t="n">
+      <c r="M224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -9449,9 +10124,12 @@
         <v>0.5718</v>
       </c>
       <c r="K225" s="1" t="n">
+        <v>0.5712</v>
+      </c>
+      <c r="L225" s="1" t="n">
         <v>0.5725</v>
       </c>
-      <c r="L225" s="1" t="n">
+      <c r="M225" s="1" t="n">
         <v>0.5695</v>
       </c>
     </row>
@@ -9489,9 +10167,12 @@
         <v>0.1178</v>
       </c>
       <c r="K226" s="1" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="L226" s="1" t="n">
         <v>0.1184</v>
       </c>
-      <c r="L226" s="1" t="n">
+      <c r="M226" s="1" t="n">
         <v>0.1166</v>
       </c>
     </row>
@@ -9529,9 +10210,12 @@
         <v>0.3178</v>
       </c>
       <c r="K227" s="1" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="L227" s="1" t="n">
         <v>0.3201</v>
       </c>
-      <c r="L227" s="1" t="n">
+      <c r="M227" s="1" t="n">
         <v>0.3165</v>
       </c>
     </row>
@@ -9569,9 +10253,12 @@
         <v>6.108</v>
       </c>
       <c r="K228" s="1" t="n">
+        <v>6.106</v>
+      </c>
+      <c r="L228" s="1" t="n">
         <v>6.108</v>
       </c>
-      <c r="L228" s="1" t="n">
+      <c r="M228" s="1" t="n">
         <v>6.062</v>
       </c>
     </row>
@@ -9609,9 +10296,12 @@
         <v>0.0293</v>
       </c>
       <c r="K229" s="1" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="L229" s="1" t="n">
         <v>0.0294</v>
       </c>
-      <c r="L229" s="1" t="n">
+      <c r="M229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -9649,9 +10339,12 @@
         <v>0.3325</v>
       </c>
       <c r="K230" s="1" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="L230" s="1" t="n">
         <v>0.3325</v>
       </c>
-      <c r="L230" s="1" t="n">
+      <c r="M230" s="1" t="n">
         <v>0.3288</v>
       </c>
     </row>
@@ -9689,9 +10382,12 @@
         <v>0.11986</v>
       </c>
       <c r="K231" s="1" t="n">
+        <v>0.11997</v>
+      </c>
+      <c r="L231" s="1" t="n">
         <v>0.12089</v>
       </c>
-      <c r="L231" s="1" t="n">
+      <c r="M231" s="1" t="n">
         <v>0.11986</v>
       </c>
     </row>
@@ -9729,9 +10425,12 @@
         <v>0.1187</v>
       </c>
       <c r="K232" s="1" t="n">
-        <v>0.1187</v>
+        <v>0.1195</v>
       </c>
       <c r="L232" s="1" t="n">
+        <v>0.1195</v>
+      </c>
+      <c r="M232" s="1" t="n">
         <v>0.1182</v>
       </c>
     </row>
@@ -9769,9 +10468,12 @@
         <v>0.03039</v>
       </c>
       <c r="K233" s="1" t="n">
+        <v>0.03036</v>
+      </c>
+      <c r="L233" s="1" t="n">
         <v>0.03039</v>
       </c>
-      <c r="L233" s="1" t="n">
+      <c r="M233" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -9809,9 +10511,12 @@
         <v>0.016171</v>
       </c>
       <c r="K234" s="1" t="n">
+        <v>0.015925</v>
+      </c>
+      <c r="L234" s="1" t="n">
         <v>0.016171</v>
       </c>
-      <c r="L234" s="1" t="n">
+      <c r="M234" s="1" t="n">
         <v>0.0156</v>
       </c>
     </row>
@@ -9849,10 +10554,13 @@
         <v>0.01268</v>
       </c>
       <c r="K235" s="1" t="n">
+        <v>0.01263</v>
+      </c>
+      <c r="L235" s="1" t="n">
         <v>0.01281</v>
       </c>
-      <c r="L235" s="1" t="n">
-        <v>0.01268</v>
+      <c r="M235" s="1" t="n">
+        <v>0.01263</v>
       </c>
     </row>
     <row r="236">
@@ -9892,6 +10600,9 @@
         <v>0.01937</v>
       </c>
       <c r="L236" s="1" t="n">
+        <v>0.01937</v>
+      </c>
+      <c r="M236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -9929,9 +10640,12 @@
         <v>0.08527</v>
       </c>
       <c r="K237" s="1" t="n">
+        <v>0.08511000000000001</v>
+      </c>
+      <c r="L237" s="1" t="n">
         <v>0.08545999999999999</v>
       </c>
-      <c r="L237" s="1" t="n">
+      <c r="M237" s="1" t="n">
         <v>0.08427999999999999</v>
       </c>
     </row>
@@ -9969,9 +10683,12 @@
         <v>0.05892</v>
       </c>
       <c r="K238" s="1" t="n">
+        <v>0.05883</v>
+      </c>
+      <c r="L238" s="1" t="n">
         <v>0.05892</v>
       </c>
-      <c r="L238" s="1" t="n">
+      <c r="M238" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>
@@ -10009,9 +10726,12 @@
         <v>0.008999</v>
       </c>
       <c r="K239" s="1" t="n">
+        <v>0.009027</v>
+      </c>
+      <c r="L239" s="1" t="n">
         <v>0.009131999999999999</v>
       </c>
-      <c r="L239" s="1" t="n">
+      <c r="M239" s="1" t="n">
         <v>0.008954</v>
       </c>
     </row>
@@ -10049,9 +10769,12 @@
         <v>0.004185</v>
       </c>
       <c r="K240" s="1" t="n">
-        <v>0.004185</v>
+        <v>0.004189</v>
       </c>
       <c r="L240" s="1" t="n">
+        <v>0.004189</v>
+      </c>
+      <c r="M240" s="1" t="n">
         <v>0.004154</v>
       </c>
     </row>
@@ -10089,9 +10812,12 @@
         <v>0.2418</v>
       </c>
       <c r="K241" s="1" t="n">
-        <v>0.2418</v>
+        <v>0.2424</v>
       </c>
       <c r="L241" s="1" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="M241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -10129,9 +10855,12 @@
         <v>0.0586</v>
       </c>
       <c r="K242" s="1" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="L242" s="1" t="n">
         <v>0.0589</v>
       </c>
-      <c r="L242" s="1" t="n">
+      <c r="M242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -10169,9 +10898,12 @@
         <v>0.02357</v>
       </c>
       <c r="K243" s="1" t="n">
+        <v>0.02353</v>
+      </c>
+      <c r="L243" s="1" t="n">
         <v>0.02363</v>
       </c>
-      <c r="L243" s="1" t="n">
+      <c r="M243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -10209,9 +10941,12 @@
         <v>0.05671</v>
       </c>
       <c r="K244" s="1" t="n">
+        <v>0.05623</v>
+      </c>
+      <c r="L244" s="1" t="n">
         <v>0.05671</v>
       </c>
-      <c r="L244" s="1" t="n">
+      <c r="M244" s="1" t="n">
         <v>0.05547</v>
       </c>
     </row>
@@ -10249,9 +10984,12 @@
         <v>0.03493</v>
       </c>
       <c r="K245" s="1" t="n">
-        <v>0.03493</v>
+        <v>0.03499</v>
       </c>
       <c r="L245" s="1" t="n">
+        <v>0.03499</v>
+      </c>
+      <c r="M245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -10289,9 +11027,12 @@
         <v>0.0604</v>
       </c>
       <c r="K246" s="1" t="n">
+        <v>0.06021</v>
+      </c>
+      <c r="L246" s="1" t="n">
         <v>0.0604</v>
       </c>
-      <c r="L246" s="1" t="n">
+      <c r="M246" s="1" t="n">
         <v>0.0599</v>
       </c>
     </row>
@@ -10329,9 +11070,12 @@
         <v>0.382</v>
       </c>
       <c r="K247" s="1" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="L247" s="1" t="n">
         <v>0.385</v>
       </c>
-      <c r="L247" s="1" t="n">
+      <c r="M247" s="1" t="n">
         <v>0.382</v>
       </c>
     </row>
@@ -10369,9 +11113,12 @@
         <v>0.5223</v>
       </c>
       <c r="K248" s="1" t="n">
+        <v>0.5218</v>
+      </c>
+      <c r="L248" s="1" t="n">
         <v>0.5223</v>
       </c>
-      <c r="L248" s="1" t="n">
+      <c r="M248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -10409,9 +11156,12 @@
         <v>0.02878</v>
       </c>
       <c r="K249" s="1" t="n">
-        <v>0.0288</v>
+        <v>0.02884</v>
       </c>
       <c r="L249" s="1" t="n">
+        <v>0.02884</v>
+      </c>
+      <c r="M249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -10449,9 +11199,12 @@
         <v>0.01317</v>
       </c>
       <c r="K250" s="1" t="n">
+        <v>0.01297</v>
+      </c>
+      <c r="L250" s="1" t="n">
         <v>0.01317</v>
       </c>
-      <c r="L250" s="1" t="n">
+      <c r="M250" s="1" t="n">
         <v>0.01288</v>
       </c>
     </row>
@@ -10489,9 +11242,12 @@
         <v>0.1004</v>
       </c>
       <c r="K251" s="1" t="n">
-        <v>0.1004</v>
+        <v>0.1006</v>
       </c>
       <c r="L251" s="1" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="M251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -10529,9 +11285,12 @@
         <v>0.00718</v>
       </c>
       <c r="K252" s="1" t="n">
+        <v>0.00718</v>
+      </c>
+      <c r="L252" s="1" t="n">
         <v>0.00719</v>
       </c>
-      <c r="L252" s="1" t="n">
+      <c r="M252" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -10569,10 +11328,13 @@
         <v>0.005568</v>
       </c>
       <c r="K253" s="1" t="n">
+        <v>0.005552</v>
+      </c>
+      <c r="L253" s="1" t="n">
         <v>0.005571</v>
       </c>
-      <c r="L253" s="1" t="n">
-        <v>0.005554</v>
+      <c r="M253" s="1" t="n">
+        <v>0.005552</v>
       </c>
     </row>
     <row r="254">
@@ -10609,9 +11371,12 @@
         <v>0.0644</v>
       </c>
       <c r="K254" s="1" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="L254" s="1" t="n">
         <v>0.0646</v>
       </c>
-      <c r="L254" s="1" t="n">
+      <c r="M254" s="1" t="n">
         <v>0.0641</v>
       </c>
     </row>
@@ -10649,9 +11414,12 @@
         <v>0.01454</v>
       </c>
       <c r="K255" s="1" t="n">
+        <v>0.01438</v>
+      </c>
+      <c r="L255" s="1" t="n">
         <v>0.01454</v>
       </c>
-      <c r="L255" s="1" t="n">
+      <c r="M255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -10689,9 +11457,12 @@
         <v>0.999275</v>
       </c>
       <c r="K256" s="1" t="n">
+        <v>0.999275</v>
+      </c>
+      <c r="L256" s="1" t="n">
         <v>0.999297</v>
       </c>
-      <c r="L256" s="1" t="n">
+      <c r="M256" s="1" t="n">
         <v>0.999275</v>
       </c>
     </row>
@@ -10729,9 +11500,12 @@
         <v>0.02118</v>
       </c>
       <c r="K257" s="1" t="n">
+        <v>0.02113</v>
+      </c>
+      <c r="L257" s="1" t="n">
         <v>0.02118</v>
       </c>
-      <c r="L257" s="1" t="n">
+      <c r="M257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -10769,9 +11543,12 @@
         <v>0.01145</v>
       </c>
       <c r="K258" s="1" t="n">
-        <v>0.01148</v>
+        <v>0.01149</v>
       </c>
       <c r="L258" s="1" t="n">
+        <v>0.01149</v>
+      </c>
+      <c r="M258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -10809,9 +11586,12 @@
         <v>0.5108</v>
       </c>
       <c r="K259" s="1" t="n">
+        <v>0.5074</v>
+      </c>
+      <c r="L259" s="1" t="n">
         <v>0.5119</v>
       </c>
-      <c r="L259" s="1" t="n">
+      <c r="M259" s="1" t="n">
         <v>0.5071</v>
       </c>
     </row>
@@ -10849,9 +11629,12 @@
         <v>0.08491</v>
       </c>
       <c r="K260" s="1" t="n">
+        <v>0.08484999999999999</v>
+      </c>
+      <c r="L260" s="1" t="n">
         <v>0.08537</v>
       </c>
-      <c r="L260" s="1" t="n">
+      <c r="M260" s="1" t="n">
         <v>0.08436</v>
       </c>
     </row>
@@ -10889,9 +11672,12 @@
         <v>0.04134</v>
       </c>
       <c r="K261" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="L261" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="L261" s="1" t="n">
+      <c r="M261" s="1" t="n">
         <v>0.04121</v>
       </c>
     </row>
@@ -10929,9 +11715,12 @@
         <v>2.297</v>
       </c>
       <c r="K262" s="1" t="n">
+        <v>2.293</v>
+      </c>
+      <c r="L262" s="1" t="n">
         <v>2.297</v>
       </c>
-      <c r="L262" s="1" t="n">
+      <c r="M262" s="1" t="n">
         <v>2.279</v>
       </c>
     </row>
@@ -10969,9 +11758,12 @@
         <v>18.64</v>
       </c>
       <c r="K263" s="1" t="n">
-        <v>18.64</v>
+        <v>18.65</v>
       </c>
       <c r="L263" s="1" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="M263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -11009,9 +11801,12 @@
         <v>0.00852</v>
       </c>
       <c r="K264" s="1" t="n">
+        <v>0.008514000000000001</v>
+      </c>
+      <c r="L264" s="1" t="n">
         <v>0.008562999999999999</v>
       </c>
-      <c r="L264" s="1" t="n">
+      <c r="M264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -11049,9 +11844,12 @@
         <v>0.3651</v>
       </c>
       <c r="K265" s="1" t="n">
-        <v>0.3651</v>
+        <v>0.3659</v>
       </c>
       <c r="L265" s="1" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="M265" s="1" t="n">
         <v>0.3627</v>
       </c>
     </row>
@@ -11089,9 +11887,12 @@
         <v>0.055369</v>
       </c>
       <c r="K266" s="1" t="n">
+        <v>0.05515</v>
+      </c>
+      <c r="L266" s="1" t="n">
         <v>0.055369</v>
       </c>
-      <c r="L266" s="1" t="n">
+      <c r="M266" s="1" t="n">
         <v>0.053765</v>
       </c>
     </row>
@@ -11129,9 +11930,12 @@
         <v>0.1318</v>
       </c>
       <c r="K267" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="L267" s="1" t="n">
         <v>0.1321</v>
       </c>
-      <c r="L267" s="1" t="n">
+      <c r="M267" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -11169,9 +11973,12 @@
         <v>0.007813000000000001</v>
       </c>
       <c r="K268" s="1" t="n">
-        <v>0.007845</v>
+        <v>0.007873</v>
       </c>
       <c r="L268" s="1" t="n">
+        <v>0.007873</v>
+      </c>
+      <c r="M268" s="1" t="n">
         <v>0.00775</v>
       </c>
     </row>
@@ -11209,9 +12016,12 @@
         <v>0.001232</v>
       </c>
       <c r="K269" s="1" t="n">
-        <v>0.00124</v>
+        <v>0.001249</v>
       </c>
       <c r="L269" s="1" t="n">
+        <v>0.001249</v>
+      </c>
+      <c r="M269" s="1" t="n">
         <v>0.001232</v>
       </c>
     </row>
@@ -11249,9 +12059,12 @@
         <v>0.28925</v>
       </c>
       <c r="K270" s="1" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="L270" s="1" t="n">
         <v>0.28999</v>
       </c>
-      <c r="L270" s="1" t="n">
+      <c r="M270" s="1" t="n">
         <v>0.28865</v>
       </c>
     </row>
@@ -11289,9 +12102,12 @@
         <v>0.03914</v>
       </c>
       <c r="K271" s="1" t="n">
+        <v>0.03901</v>
+      </c>
+      <c r="L271" s="1" t="n">
         <v>0.03922</v>
       </c>
-      <c r="L271" s="1" t="n">
+      <c r="M271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -11329,9 +12145,12 @@
         <v>0.05173</v>
       </c>
       <c r="K272" s="1" t="n">
+        <v>0.0518</v>
+      </c>
+      <c r="L272" s="1" t="n">
         <v>0.05181</v>
       </c>
-      <c r="L272" s="1" t="n">
+      <c r="M272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -11369,9 +12188,12 @@
         <v>0.00773</v>
       </c>
       <c r="K273" s="1" t="n">
-        <v>0.00773</v>
+        <v>0.00776</v>
       </c>
       <c r="L273" s="1" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="M273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -11409,9 +12231,12 @@
         <v>0.005813</v>
       </c>
       <c r="K274" s="1" t="n">
+        <v>0.005799</v>
+      </c>
+      <c r="L274" s="1" t="n">
         <v>0.005813</v>
       </c>
-      <c r="L274" s="1" t="n">
+      <c r="M274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -11449,9 +12274,12 @@
         <v>0.0005885</v>
       </c>
       <c r="K275" s="1" t="n">
+        <v>0.0005874</v>
+      </c>
+      <c r="L275" s="1" t="n">
         <v>0.0005895</v>
       </c>
-      <c r="L275" s="1" t="n">
+      <c r="M275" s="1" t="n">
         <v>0.0005863</v>
       </c>
     </row>
@@ -11489,9 +12317,12 @@
         <v>0.15074</v>
       </c>
       <c r="K276" s="1" t="n">
+        <v>0.15042</v>
+      </c>
+      <c r="L276" s="1" t="n">
         <v>0.15167</v>
       </c>
-      <c r="L276" s="1" t="n">
+      <c r="M276" s="1" t="n">
         <v>0.15004</v>
       </c>
     </row>
@@ -11529,9 +12360,12 @@
         <v>0.023073</v>
       </c>
       <c r="K277" s="1" t="n">
+        <v>0.023035</v>
+      </c>
+      <c r="L277" s="1" t="n">
         <v>0.023073</v>
       </c>
-      <c r="L277" s="1" t="n">
+      <c r="M277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -11569,9 +12403,12 @@
         <v>0.04188</v>
       </c>
       <c r="K278" s="1" t="n">
+        <v>0.04206</v>
+      </c>
+      <c r="L278" s="1" t="n">
         <v>0.04242</v>
       </c>
-      <c r="L278" s="1" t="n">
+      <c r="M278" s="1" t="n">
         <v>0.04179</v>
       </c>
     </row>
@@ -11609,9 +12446,12 @@
         <v>0.0003987</v>
       </c>
       <c r="K279" s="1" t="n">
+        <v>0.0003993</v>
+      </c>
+      <c r="L279" s="1" t="n">
         <v>0.0004006</v>
       </c>
-      <c r="L279" s="1" t="n">
+      <c r="M279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -11649,9 +12489,12 @@
         <v>0.02206</v>
       </c>
       <c r="K280" s="1" t="n">
+        <v>0.02195</v>
+      </c>
+      <c r="L280" s="1" t="n">
         <v>0.02218</v>
       </c>
-      <c r="L280" s="1" t="n">
+      <c r="M280" s="1" t="n">
         <v>0.0219</v>
       </c>
     </row>
@@ -11689,9 +12532,12 @@
         <v>0.07093000000000001</v>
       </c>
       <c r="K281" s="1" t="n">
-        <v>0.07093000000000001</v>
+        <v>0.07128</v>
       </c>
       <c r="L281" s="1" t="n">
+        <v>0.07128</v>
+      </c>
+      <c r="M281" s="1" t="n">
         <v>0.06936</v>
       </c>
     </row>
@@ -11729,9 +12575,12 @@
         <v>0.006751</v>
       </c>
       <c r="K282" s="1" t="n">
+        <v>0.006717</v>
+      </c>
+      <c r="L282" s="1" t="n">
         <v>0.006804</v>
       </c>
-      <c r="L282" s="1" t="n">
+      <c r="M282" s="1" t="n">
         <v>0.006688</v>
       </c>
     </row>
@@ -11769,9 +12618,12 @@
         <v>0.12</v>
       </c>
       <c r="K283" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="L283" s="1" t="n">
         <v>0.12</v>
       </c>
-      <c r="L283" s="1" t="n">
+      <c r="M283" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -11809,9 +12661,12 @@
         <v>0.005499</v>
       </c>
       <c r="K284" s="1" t="n">
+        <v>0.005493</v>
+      </c>
+      <c r="L284" s="1" t="n">
         <v>0.005499</v>
       </c>
-      <c r="L284" s="1" t="n">
+      <c r="M284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -11849,9 +12704,12 @@
         <v>1.272</v>
       </c>
       <c r="K285" s="1" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="L285" s="1" t="n">
         <v>1.272</v>
       </c>
-      <c r="L285" s="1" t="n">
+      <c r="M285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -11889,9 +12747,12 @@
         <v>0.4458</v>
       </c>
       <c r="K286" s="1" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="L286" s="1" t="n">
         <v>0.4458</v>
       </c>
-      <c r="L286" s="1" t="n">
+      <c r="M286" s="1" t="n">
         <v>0.4423</v>
       </c>
     </row>
@@ -11929,9 +12790,12 @@
         <v>0.007998999999999999</v>
       </c>
       <c r="K287" s="1" t="n">
+        <v>0.007977</v>
+      </c>
+      <c r="L287" s="1" t="n">
         <v>0.007998999999999999</v>
       </c>
-      <c r="L287" s="1" t="n">
+      <c r="M287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -11969,9 +12833,12 @@
         <v>0.02948</v>
       </c>
       <c r="K288" s="1" t="n">
+        <v>0.02941</v>
+      </c>
+      <c r="L288" s="1" t="n">
         <v>0.0295</v>
       </c>
-      <c r="L288" s="1" t="n">
+      <c r="M288" s="1" t="n">
         <v>0.02914</v>
       </c>
     </row>
@@ -12009,9 +12876,12 @@
         <v>0.2824</v>
       </c>
       <c r="K289" s="1" t="n">
-        <v>0.2824</v>
+        <v>0.2827</v>
       </c>
       <c r="L289" s="1" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="M289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -12049,9 +12919,12 @@
         <v>2.783</v>
       </c>
       <c r="K290" s="1" t="n">
+        <v>2.766</v>
+      </c>
+      <c r="L290" s="1" t="n">
         <v>2.783</v>
       </c>
-      <c r="L290" s="1" t="n">
+      <c r="M290" s="1" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -12089,9 +12962,12 @@
         <v>0.003187</v>
       </c>
       <c r="K291" s="1" t="n">
-        <v>0.003187</v>
+        <v>0.003191</v>
       </c>
       <c r="L291" s="1" t="n">
+        <v>0.003191</v>
+      </c>
+      <c r="M291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -12129,9 +13005,12 @@
         <v>0.448</v>
       </c>
       <c r="K292" s="1" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="L292" s="1" t="n">
         <v>0.4488</v>
       </c>
-      <c r="L292" s="1" t="n">
+      <c r="M292" s="1" t="n">
         <v>0.4475</v>
       </c>
     </row>
@@ -12169,9 +13048,12 @@
         <v>0.0819</v>
       </c>
       <c r="K293" s="1" t="n">
+        <v>0.08237999999999999</v>
+      </c>
+      <c r="L293" s="1" t="n">
         <v>0.08298</v>
       </c>
-      <c r="L293" s="1" t="n">
+      <c r="M293" s="1" t="n">
         <v>0.08136</v>
       </c>
     </row>
@@ -12209,9 +13091,12 @@
         <v>0.02801</v>
       </c>
       <c r="K294" s="1" t="n">
+        <v>0.02792</v>
+      </c>
+      <c r="L294" s="1" t="n">
         <v>0.02801</v>
       </c>
-      <c r="L294" s="1" t="n">
+      <c r="M294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -12249,9 +13134,12 @@
         <v>0.954</v>
       </c>
       <c r="K295" s="1" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="L295" s="1" t="n">
         <v>0.958</v>
       </c>
-      <c r="L295" s="1" t="n">
+      <c r="M295" s="1" t="n">
         <v>0.952</v>
       </c>
     </row>
@@ -12289,9 +13177,12 @@
         <v>0.006975</v>
       </c>
       <c r="K296" s="1" t="n">
+        <v>0.006963</v>
+      </c>
+      <c r="L296" s="1" t="n">
         <v>0.007008</v>
       </c>
-      <c r="L296" s="1" t="n">
+      <c r="M296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -12329,9 +13220,12 @@
         <v>0.1214</v>
       </c>
       <c r="K297" s="1" t="n">
-        <v>0.1214</v>
+        <v>0.1215</v>
       </c>
       <c r="L297" s="1" t="n">
+        <v>0.1215</v>
+      </c>
+      <c r="M297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -12369,9 +13263,12 @@
         <v>0.01563</v>
       </c>
       <c r="K298" s="1" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="L298" s="1" t="n">
         <v>0.01563</v>
       </c>
-      <c r="L298" s="1" t="n">
+      <c r="M298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -12409,9 +13306,12 @@
         <v>0.4431</v>
       </c>
       <c r="K299" s="1" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="L299" s="1" t="n">
         <v>0.4431</v>
       </c>
-      <c r="L299" s="1" t="n">
+      <c r="M299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -12449,9 +13349,12 @@
         <v>0.00916</v>
       </c>
       <c r="K300" s="1" t="n">
+        <v>0.009140000000000001</v>
+      </c>
+      <c r="L300" s="1" t="n">
         <v>0.00924</v>
       </c>
-      <c r="L300" s="1" t="n">
+      <c r="M300" s="1" t="n">
         <v>0.009140000000000001</v>
       </c>
     </row>
@@ -12489,9 +13392,12 @@
         <v>0.1864</v>
       </c>
       <c r="K301" s="1" t="n">
-        <v>0.1864</v>
+        <v>0.1905</v>
       </c>
       <c r="L301" s="1" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="M301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -12529,9 +13435,12 @@
         <v>0.00757</v>
       </c>
       <c r="K302" s="1" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="L302" s="1" t="n">
         <v>0.00765</v>
       </c>
-      <c r="L302" s="1" t="n">
+      <c r="M302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -12569,9 +13478,12 @@
         <v>0.0002164</v>
       </c>
       <c r="K303" s="1" t="n">
+        <v>0.000217</v>
+      </c>
+      <c r="L303" s="1" t="n">
         <v>0.0002171</v>
       </c>
-      <c r="L303" s="1" t="n">
+      <c r="M303" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -12609,9 +13521,12 @@
         <v>0.01551</v>
       </c>
       <c r="K304" s="1" t="n">
-        <v>0.01553</v>
+        <v>0.01555</v>
       </c>
       <c r="L304" s="1" t="n">
+        <v>0.01555</v>
+      </c>
+      <c r="M304" s="1" t="n">
         <v>0.01542</v>
       </c>
     </row>
@@ -12649,9 +13564,12 @@
         <v>0.074</v>
       </c>
       <c r="K305" s="1" t="n">
+        <v>0.07399</v>
+      </c>
+      <c r="L305" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="L305" s="1" t="n">
+      <c r="M305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -12689,9 +13607,12 @@
         <v>0.08346000000000001</v>
       </c>
       <c r="K306" s="1" t="n">
-        <v>0.08346000000000001</v>
+        <v>0.08347</v>
       </c>
       <c r="L306" s="1" t="n">
+        <v>0.08347</v>
+      </c>
+      <c r="M306" s="1" t="n">
         <v>0.08275</v>
       </c>
     </row>
@@ -12729,9 +13650,12 @@
         <v>0.01809</v>
       </c>
       <c r="K307" s="1" t="n">
+        <v>0.01806</v>
+      </c>
+      <c r="L307" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="L307" s="1" t="n">
+      <c r="M307" s="1" t="n">
         <v>0.01803</v>
       </c>
     </row>
@@ -12769,9 +13693,12 @@
         <v>0.0006271</v>
       </c>
       <c r="K308" s="1" t="n">
-        <v>0.0006271</v>
+        <v>0.0006274</v>
       </c>
       <c r="L308" s="1" t="n">
+        <v>0.0006274</v>
+      </c>
+      <c r="M308" s="1" t="n">
         <v>0.0006212</v>
       </c>
     </row>
@@ -12809,9 +13736,12 @@
         <v>0.08269</v>
       </c>
       <c r="K309" s="1" t="n">
+        <v>0.08244</v>
+      </c>
+      <c r="L309" s="1" t="n">
         <v>0.08294</v>
       </c>
-      <c r="L309" s="1" t="n">
+      <c r="M309" s="1" t="n">
         <v>0.0822</v>
       </c>
     </row>
@@ -12849,9 +13779,12 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="K310" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="L310" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="L310" s="1" t="n">
+      <c r="M310" s="1" t="n">
         <v>0.0973</v>
       </c>
     </row>
@@ -12892,6 +13825,9 @@
         <v>0.2126</v>
       </c>
       <c r="L311" s="1" t="n">
+        <v>0.2126</v>
+      </c>
+      <c r="M311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -12929,9 +13865,12 @@
         <v>0.3957</v>
       </c>
       <c r="K312" s="1" t="n">
-        <v>0.3957</v>
+        <v>0.3958</v>
       </c>
       <c r="L312" s="1" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="M312" s="1" t="n">
         <v>0.387</v>
       </c>
     </row>
@@ -12969,9 +13908,12 @@
         <v>0.10455</v>
       </c>
       <c r="K313" s="1" t="n">
+        <v>0.10462</v>
+      </c>
+      <c r="L313" s="1" t="n">
         <v>0.10542</v>
       </c>
-      <c r="L313" s="1" t="n">
+      <c r="M313" s="1" t="n">
         <v>0.10455</v>
       </c>
     </row>
@@ -13009,9 +13951,12 @@
         <v>0.08673</v>
       </c>
       <c r="K314" s="1" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="L314" s="1" t="n">
         <v>0.08673</v>
       </c>
-      <c r="L314" s="1" t="n">
+      <c r="M314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -13052,6 +13997,9 @@
         <v>0.1185</v>
       </c>
       <c r="L315" s="1" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="M315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -13089,10 +14037,13 @@
         <v>0.03619</v>
       </c>
       <c r="K316" s="1" t="n">
+        <v>0.03615</v>
+      </c>
+      <c r="L316" s="1" t="n">
         <v>0.03681</v>
       </c>
-      <c r="L316" s="1" t="n">
-        <v>0.03619</v>
+      <c r="M316" s="1" t="n">
+        <v>0.03615</v>
       </c>
     </row>
     <row r="317">
@@ -13129,9 +14080,12 @@
         <v>0.0815</v>
       </c>
       <c r="K317" s="1" t="n">
+        <v>0.08119</v>
+      </c>
+      <c r="L317" s="1" t="n">
         <v>0.08164</v>
       </c>
-      <c r="L317" s="1" t="n">
+      <c r="M317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -13169,9 +14123,12 @@
         <v>0.03745</v>
       </c>
       <c r="K318" s="1" t="n">
+        <v>0.03747</v>
+      </c>
+      <c r="L318" s="1" t="n">
         <v>0.03766</v>
       </c>
-      <c r="L318" s="1" t="n">
+      <c r="M318" s="1" t="n">
         <v>0.03736</v>
       </c>
     </row>
@@ -13209,9 +14166,12 @@
         <v>0.4307</v>
       </c>
       <c r="K319" s="1" t="n">
+        <v>0.4309</v>
+      </c>
+      <c r="L319" s="1" t="n">
         <v>0.4347</v>
       </c>
-      <c r="L319" s="1" t="n">
+      <c r="M319" s="1" t="n">
         <v>0.4296</v>
       </c>
     </row>
@@ -13249,10 +14209,13 @@
         <v>0.1601</v>
       </c>
       <c r="K320" s="1" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="L320" s="1" t="n">
         <v>0.1614</v>
       </c>
-      <c r="L320" s="1" t="n">
-        <v>0.1599</v>
+      <c r="M320" s="1" t="n">
+        <v>0.1598</v>
       </c>
     </row>
     <row r="321">
@@ -13289,9 +14252,12 @@
         <v>5.685</v>
       </c>
       <c r="K321" s="1" t="n">
-        <v>5.685</v>
+        <v>5.688</v>
       </c>
       <c r="L321" s="1" t="n">
+        <v>5.688</v>
+      </c>
+      <c r="M321" s="1" t="n">
         <v>5.677</v>
       </c>
     </row>
@@ -13329,9 +14295,12 @@
         <v>0.003754</v>
       </c>
       <c r="K322" s="1" t="n">
+        <v>0.003752</v>
+      </c>
+      <c r="L322" s="1" t="n">
         <v>0.003754</v>
       </c>
-      <c r="L322" s="1" t="n">
+      <c r="M322" s="1" t="n">
         <v>0.003714</v>
       </c>
     </row>
@@ -13369,9 +14338,12 @@
         <v>0.001758</v>
       </c>
       <c r="K323" s="1" t="n">
-        <v>0.001761</v>
+        <v>0.001762</v>
       </c>
       <c r="L323" s="1" t="n">
+        <v>0.001762</v>
+      </c>
+      <c r="M323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -13409,9 +14381,12 @@
         <v>1.2e-05</v>
       </c>
       <c r="K324" s="1" t="n">
+        <v>1.19e-05</v>
+      </c>
+      <c r="L324" s="1" t="n">
         <v>1.2e-05</v>
       </c>
-      <c r="L324" s="1" t="n">
+      <c r="M324" s="1" t="n">
         <v>1.19e-05</v>
       </c>
     </row>
@@ -13449,9 +14424,12 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="K325" s="1" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="L325" s="1" t="n">
         <v>0.08649999999999999</v>
       </c>
-      <c r="L325" s="1" t="n">
+      <c r="M325" s="1" t="n">
         <v>0.0857</v>
       </c>
     </row>
@@ -13489,9 +14467,12 @@
         <v>0.01736</v>
       </c>
       <c r="K326" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="L326" s="1" t="n">
         <v>0.01736</v>
       </c>
-      <c r="L326" s="1" t="n">
+      <c r="M326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -13529,9 +14510,12 @@
         <v>0.01687</v>
       </c>
       <c r="K327" s="1" t="n">
+        <v>0.01684</v>
+      </c>
+      <c r="L327" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="L327" s="1" t="n">
+      <c r="M327" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -13569,9 +14553,12 @@
         <v>4.454</v>
       </c>
       <c r="K328" s="1" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L328" s="1" t="n">
         <v>4.462</v>
       </c>
-      <c r="L328" s="1" t="n">
+      <c r="M328" s="1" t="n">
         <v>4.446</v>
       </c>
     </row>
@@ -13609,9 +14596,12 @@
         <v>0.009717999999999999</v>
       </c>
       <c r="K329" s="1" t="n">
+        <v>0.009693999999999999</v>
+      </c>
+      <c r="L329" s="1" t="n">
         <v>0.009861</v>
       </c>
-      <c r="L329" s="1" t="n">
+      <c r="M329" s="1" t="n">
         <v>0.009532000000000001</v>
       </c>
     </row>
@@ -13649,10 +14639,13 @@
         <v>5189.1</v>
       </c>
       <c r="K330" s="1" t="n">
+        <v>5180</v>
+      </c>
+      <c r="L330" s="1" t="n">
         <v>5192.9</v>
       </c>
-      <c r="L330" s="1" t="n">
-        <v>5185.8</v>
+      <c r="M330" s="1" t="n">
+        <v>5180</v>
       </c>
     </row>
     <row r="331">
@@ -13689,9 +14682,12 @@
         <v>0.07079000000000001</v>
       </c>
       <c r="K331" s="1" t="n">
+        <v>0.07081</v>
+      </c>
+      <c r="L331" s="1" t="n">
         <v>0.07087</v>
       </c>
-      <c r="L331" s="1" t="n">
+      <c r="M331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -13729,9 +14725,12 @@
         <v>0.06092</v>
       </c>
       <c r="K332" s="1" t="n">
+        <v>0.06092</v>
+      </c>
+      <c r="L332" s="1" t="n">
         <v>0.06106</v>
       </c>
-      <c r="L332" s="1" t="n">
+      <c r="M332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -13769,9 +14768,12 @@
         <v>0.10558</v>
       </c>
       <c r="K333" s="1" t="n">
+        <v>0.10545</v>
+      </c>
+      <c r="L333" s="1" t="n">
         <v>0.10558</v>
       </c>
-      <c r="L333" s="1" t="n">
+      <c r="M333" s="1" t="n">
         <v>0.10341</v>
       </c>
     </row>
@@ -13809,9 +14811,12 @@
         <v>0.08773</v>
       </c>
       <c r="K334" s="1" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="L334" s="1" t="n">
         <v>0.08837</v>
       </c>
-      <c r="L334" s="1" t="n">
+      <c r="M334" s="1" t="n">
         <v>0.08734</v>
       </c>
     </row>
@@ -13849,9 +14854,12 @@
         <v>0.016445</v>
       </c>
       <c r="K335" s="1" t="n">
-        <v>0.016445</v>
+        <v>0.016468</v>
       </c>
       <c r="L335" s="1" t="n">
+        <v>0.016468</v>
+      </c>
+      <c r="M335" s="1" t="n">
         <v>0.016391</v>
       </c>
     </row>
@@ -13889,9 +14897,12 @@
         <v>0.04619</v>
       </c>
       <c r="K336" s="1" t="n">
+        <v>0.04608</v>
+      </c>
+      <c r="L336" s="1" t="n">
         <v>0.04619</v>
       </c>
-      <c r="L336" s="1" t="n">
+      <c r="M336" s="1" t="n">
         <v>0.04583</v>
       </c>
     </row>
@@ -13929,9 +14940,12 @@
         <v>0.1891</v>
       </c>
       <c r="K337" s="1" t="n">
-        <v>0.1891</v>
+        <v>0.1904</v>
       </c>
       <c r="L337" s="1" t="n">
+        <v>0.1904</v>
+      </c>
+      <c r="M337" s="1" t="n">
         <v>0.1838</v>
       </c>
     </row>
@@ -13969,9 +14983,12 @@
         <v>0.1843</v>
       </c>
       <c r="K338" s="1" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="L338" s="1" t="n">
         <v>0.1843</v>
       </c>
-      <c r="L338" s="1" t="n">
+      <c r="M338" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -14012,6 +15029,9 @@
         <v>0.01843</v>
       </c>
       <c r="L339" s="1" t="n">
+        <v>0.01843</v>
+      </c>
+      <c r="M339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -14052,6 +15072,9 @@
         <v>0.02325</v>
       </c>
       <c r="L340" s="1" t="n">
+        <v>0.02325</v>
+      </c>
+      <c r="M340" s="1" t="n">
         <v>0.02305</v>
       </c>
     </row>
@@ -14089,9 +15112,12 @@
         <v>0.4573</v>
       </c>
       <c r="K341" s="1" t="n">
+        <v>0.4559</v>
+      </c>
+      <c r="L341" s="1" t="n">
         <v>0.4577</v>
       </c>
-      <c r="L341" s="1" t="n">
+      <c r="M341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -14129,9 +15155,12 @@
         <v>0.0135</v>
       </c>
       <c r="K342" s="1" t="n">
-        <v>0.0135</v>
+        <v>0.01352</v>
       </c>
       <c r="L342" s="1" t="n">
+        <v>0.01352</v>
+      </c>
+      <c r="M342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -14169,9 +15198,12 @@
         <v>2.88</v>
       </c>
       <c r="K343" s="1" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="L343" s="1" t="n">
         <v>2.89</v>
       </c>
-      <c r="L343" s="1" t="n">
+      <c r="M343" s="1" t="n">
         <v>2.872</v>
       </c>
     </row>
@@ -14209,9 +15241,12 @@
         <v>0.1523</v>
       </c>
       <c r="K344" s="1" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="L344" s="1" t="n">
         <v>0.1577</v>
       </c>
-      <c r="L344" s="1" t="n">
+      <c r="M344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -14249,9 +15284,12 @@
         <v>0.005366</v>
       </c>
       <c r="K345" s="1" t="n">
-        <v>0.005367</v>
+        <v>0.005407</v>
       </c>
       <c r="L345" s="1" t="n">
+        <v>0.005407</v>
+      </c>
+      <c r="M345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -14289,9 +15327,12 @@
         <v>0.05784</v>
       </c>
       <c r="K346" s="1" t="n">
+        <v>0.05777</v>
+      </c>
+      <c r="L346" s="1" t="n">
         <v>0.0579</v>
       </c>
-      <c r="L346" s="1" t="n">
+      <c r="M346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -14329,9 +15370,12 @@
         <v>2606</v>
       </c>
       <c r="K347" s="1" t="n">
+        <v>2605</v>
+      </c>
+      <c r="L347" s="1" t="n">
         <v>2613</v>
       </c>
-      <c r="L347" s="1" t="n">
+      <c r="M347" s="1" t="n">
         <v>2597</v>
       </c>
     </row>
@@ -14369,9 +15413,12 @@
         <v>0.04642</v>
       </c>
       <c r="K348" s="1" t="n">
+        <v>0.04635</v>
+      </c>
+      <c r="L348" s="1" t="n">
         <v>0.04642</v>
       </c>
-      <c r="L348" s="1" t="n">
+      <c r="M348" s="1" t="n">
         <v>0.04595</v>
       </c>
     </row>
@@ -14409,10 +15456,13 @@
         <v>0.00565</v>
       </c>
       <c r="K349" s="1" t="n">
+        <v>0.005625</v>
+      </c>
+      <c r="L349" s="1" t="n">
         <v>0.005714</v>
       </c>
-      <c r="L349" s="1" t="n">
-        <v>0.00565</v>
+      <c r="M349" s="1" t="n">
+        <v>0.005625</v>
       </c>
     </row>
     <row r="350">
@@ -14449,9 +15499,12 @@
         <v>195.95</v>
       </c>
       <c r="K350" s="1" t="n">
+        <v>195.78</v>
+      </c>
+      <c r="L350" s="1" t="n">
         <v>195.95</v>
       </c>
-      <c r="L350" s="1" t="n">
+      <c r="M350" s="1" t="n">
         <v>195.23</v>
       </c>
     </row>
@@ -14489,9 +15542,12 @@
         <v>0.08235000000000001</v>
       </c>
       <c r="K351" s="1" t="n">
+        <v>0.08241999999999999</v>
+      </c>
+      <c r="L351" s="1" t="n">
         <v>0.08245</v>
       </c>
-      <c r="L351" s="1" t="n">
+      <c r="M351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -14529,9 +15585,12 @@
         <v>0.007436</v>
       </c>
       <c r="K352" s="1" t="n">
+        <v>0.007455</v>
+      </c>
+      <c r="L352" s="1" t="n">
         <v>0.007571</v>
       </c>
-      <c r="L352" s="1" t="n">
+      <c r="M352" s="1" t="n">
         <v>0.007436</v>
       </c>
     </row>
@@ -14569,9 +15628,12 @@
         <v>1.5028</v>
       </c>
       <c r="K353" s="1" t="n">
+        <v>1.4823</v>
+      </c>
+      <c r="L353" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="L353" s="1" t="n">
+      <c r="M353" s="1" t="n">
         <v>1.4807</v>
       </c>
     </row>
@@ -14609,9 +15671,12 @@
         <v>0.07677</v>
       </c>
       <c r="K354" s="1" t="n">
+        <v>0.07675999999999999</v>
+      </c>
+      <c r="L354" s="1" t="n">
         <v>0.07677</v>
       </c>
-      <c r="L354" s="1" t="n">
+      <c r="M354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -14649,9 +15714,12 @@
         <v>0.04855</v>
       </c>
       <c r="K355" s="1" t="n">
+        <v>0.04861</v>
+      </c>
+      <c r="L355" s="1" t="n">
         <v>0.04921</v>
       </c>
-      <c r="L355" s="1" t="n">
+      <c r="M355" s="1" t="n">
         <v>0.04855</v>
       </c>
     </row>
@@ -14689,9 +15757,12 @@
         <v>0.2862</v>
       </c>
       <c r="K356" s="1" t="n">
-        <v>0.2862</v>
+        <v>0.2871</v>
       </c>
       <c r="L356" s="1" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="M356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -14729,9 +15800,12 @@
         <v>0.1472</v>
       </c>
       <c r="K357" s="1" t="n">
-        <v>0.1472</v>
+        <v>0.1473</v>
       </c>
       <c r="L357" s="1" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="M357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -14769,9 +15843,12 @@
         <v>1.349</v>
       </c>
       <c r="K358" s="1" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="L358" s="1" t="n">
         <v>1.355</v>
       </c>
-      <c r="L358" s="1" t="n">
+      <c r="M358" s="1" t="n">
         <v>1.349</v>
       </c>
     </row>
@@ -14809,9 +15886,12 @@
         <v>0.6135</v>
       </c>
       <c r="K359" s="1" t="n">
-        <v>0.6135</v>
+        <v>0.6136</v>
       </c>
       <c r="L359" s="1" t="n">
+        <v>0.6136</v>
+      </c>
+      <c r="M359" s="1" t="n">
         <v>0.6081</v>
       </c>
     </row>
@@ -14852,6 +15932,9 @@
         <v>0.1149</v>
       </c>
       <c r="L360" s="1" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="M360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -14889,9 +15972,12 @@
         <v>0.02678</v>
       </c>
       <c r="K361" s="1" t="n">
+        <v>0.02656</v>
+      </c>
+      <c r="L361" s="1" t="n">
         <v>0.02678</v>
       </c>
-      <c r="L361" s="1" t="n">
+      <c r="M361" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -14929,9 +16015,12 @@
         <v>3.05e-05</v>
       </c>
       <c r="K362" s="1" t="n">
+        <v>3.04e-05</v>
+      </c>
+      <c r="L362" s="1" t="n">
         <v>3.05e-05</v>
       </c>
-      <c r="L362" s="1" t="n">
+      <c r="M362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -14969,9 +16058,12 @@
         <v>0.01041</v>
       </c>
       <c r="K363" s="1" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="L363" s="1" t="n">
         <v>0.01047</v>
       </c>
-      <c r="L363" s="1" t="n">
+      <c r="M363" s="1" t="n">
         <v>0.01018</v>
       </c>
     </row>
@@ -15009,9 +16101,12 @@
         <v>0.06233</v>
       </c>
       <c r="K364" s="1" t="n">
+        <v>0.06227</v>
+      </c>
+      <c r="L364" s="1" t="n">
         <v>0.06233</v>
       </c>
-      <c r="L364" s="1" t="n">
+      <c r="M364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -15049,9 +16144,12 @@
         <v>0.03285</v>
       </c>
       <c r="K365" s="1" t="n">
+        <v>0.03285</v>
+      </c>
+      <c r="L365" s="1" t="n">
         <v>0.03299</v>
       </c>
-      <c r="L365" s="1" t="n">
+      <c r="M365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -15089,9 +16187,12 @@
         <v>0.0333</v>
       </c>
       <c r="K366" s="1" t="n">
+        <v>0.03325</v>
+      </c>
+      <c r="L366" s="1" t="n">
         <v>0.0333</v>
       </c>
-      <c r="L366" s="1" t="n">
+      <c r="M366" s="1" t="n">
         <v>0.03283</v>
       </c>
     </row>
@@ -15129,9 +16230,12 @@
         <v>0.012321</v>
       </c>
       <c r="K367" s="1" t="n">
-        <v>0.012321</v>
+        <v>0.012357</v>
       </c>
       <c r="L367" s="1" t="n">
+        <v>0.012357</v>
+      </c>
+      <c r="M367" s="1" t="n">
         <v>0.012155</v>
       </c>
     </row>
@@ -15169,9 +16273,12 @@
         <v>0.03574</v>
       </c>
       <c r="K368" s="1" t="n">
+        <v>0.03569</v>
+      </c>
+      <c r="L368" s="1" t="n">
         <v>0.03574</v>
       </c>
-      <c r="L368" s="1" t="n">
+      <c r="M368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -15209,9 +16316,12 @@
         <v>0.6283</v>
       </c>
       <c r="K369" s="1" t="n">
+        <v>0.6283</v>
+      </c>
+      <c r="L369" s="1" t="n">
         <v>0.6307</v>
       </c>
-      <c r="L369" s="1" t="n">
+      <c r="M369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -15249,10 +16359,13 @@
         <v>0.00848</v>
       </c>
       <c r="K370" s="1" t="n">
+        <v>0.008359999999999999</v>
+      </c>
+      <c r="L370" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="L370" s="1" t="n">
-        <v>0.00843</v>
+      <c r="M370" s="1" t="n">
+        <v>0.008359999999999999</v>
       </c>
     </row>
     <row r="371">
@@ -15289,9 +16402,12 @@
         <v>0.004026</v>
       </c>
       <c r="K371" s="1" t="n">
-        <v>0.004026</v>
+        <v>0.004166</v>
       </c>
       <c r="L371" s="1" t="n">
+        <v>0.004166</v>
+      </c>
+      <c r="M371" s="1" t="n">
         <v>0.003242</v>
       </c>
     </row>
@@ -15329,9 +16445,12 @@
         <v>0.13366</v>
       </c>
       <c r="K372" s="1" t="n">
+        <v>0.13378</v>
+      </c>
+      <c r="L372" s="1" t="n">
         <v>0.13391</v>
       </c>
-      <c r="L372" s="1" t="n">
+      <c r="M372" s="1" t="n">
         <v>0.13227</v>
       </c>
     </row>
@@ -15369,9 +16488,12 @@
         <v>0.007807</v>
       </c>
       <c r="K373" s="1" t="n">
+        <v>0.007772</v>
+      </c>
+      <c r="L373" s="1" t="n">
         <v>0.007822000000000001</v>
       </c>
-      <c r="L373" s="1" t="n">
+      <c r="M373" s="1" t="n">
         <v>0.007771</v>
       </c>
     </row>
@@ -15409,9 +16531,12 @@
         <v>0.01981</v>
       </c>
       <c r="K374" s="1" t="n">
-        <v>0.01982</v>
+        <v>0.02003</v>
       </c>
       <c r="L374" s="1" t="n">
+        <v>0.02003</v>
+      </c>
+      <c r="M374" s="1" t="n">
         <v>0.01969</v>
       </c>
     </row>
@@ -15449,9 +16574,12 @@
         <v>0.0005921</v>
       </c>
       <c r="K375" s="1" t="n">
+        <v>0.000592</v>
+      </c>
+      <c r="L375" s="1" t="n">
         <v>0.000594</v>
       </c>
-      <c r="L375" s="1" t="n">
+      <c r="M375" s="1" t="n">
         <v>0.0005910000000000001</v>
       </c>
     </row>
@@ -15492,6 +16620,9 @@
         <v>0.0363</v>
       </c>
       <c r="L376" s="1" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="M376" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -15529,9 +16660,12 @@
         <v>0.0007956</v>
       </c>
       <c r="K377" s="1" t="n">
+        <v>0.0007947</v>
+      </c>
+      <c r="L377" s="1" t="n">
         <v>0.0007956</v>
       </c>
-      <c r="L377" s="1" t="n">
+      <c r="M377" s="1" t="n">
         <v>0.0007848</v>
       </c>
     </row>
@@ -15569,9 +16703,12 @@
         <v>2.044</v>
       </c>
       <c r="K378" s="1" t="n">
+        <v>2.038</v>
+      </c>
+      <c r="L378" s="1" t="n">
         <v>2.044</v>
       </c>
-      <c r="L378" s="1" t="n">
+      <c r="M378" s="1" t="n">
         <v>1.973</v>
       </c>
     </row>
@@ -15609,9 +16746,12 @@
         <v>0.000593</v>
       </c>
       <c r="K379" s="1" t="n">
-        <v>0.000593</v>
+        <v>0.0005932</v>
       </c>
       <c r="L379" s="1" t="n">
+        <v>0.0005932</v>
+      </c>
+      <c r="M379" s="1" t="n">
         <v>0.0005881</v>
       </c>
     </row>
@@ -15649,9 +16789,12 @@
         <v>0.03756</v>
       </c>
       <c r="K380" s="1" t="n">
+        <v>0.03753</v>
+      </c>
+      <c r="L380" s="1" t="n">
         <v>0.03756</v>
       </c>
-      <c r="L380" s="1" t="n">
+      <c r="M380" s="1" t="n">
         <v>0.03737</v>
       </c>
     </row>
@@ -15689,9 +16832,12 @@
         <v>0.05486</v>
       </c>
       <c r="K381" s="1" t="n">
+        <v>0.05476</v>
+      </c>
+      <c r="L381" s="1" t="n">
         <v>0.05486</v>
       </c>
-      <c r="L381" s="1" t="n">
+      <c r="M381" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -15732,6 +16878,9 @@
         <v>0.01214</v>
       </c>
       <c r="L382" s="1" t="n">
+        <v>0.01214</v>
+      </c>
+      <c r="M382" s="1" t="n">
         <v>0.01202</v>
       </c>
     </row>
@@ -15769,9 +16918,12 @@
         <v>0.001553</v>
       </c>
       <c r="K383" s="1" t="n">
+        <v>0.001554</v>
+      </c>
+      <c r="L383" s="1" t="n">
         <v>0.001559</v>
       </c>
-      <c r="L383" s="1" t="n">
+      <c r="M383" s="1" t="n">
         <v>0.001549</v>
       </c>
     </row>
@@ -15812,6 +16964,9 @@
         <v>0.0002167</v>
       </c>
       <c r="L384" s="1" t="n">
+        <v>0.0002167</v>
+      </c>
+      <c r="M384" s="1" t="n">
         <v>0.0002154</v>
       </c>
     </row>
@@ -15849,9 +17004,12 @@
         <v>0.00242</v>
       </c>
       <c r="K385" s="1" t="n">
-        <v>0.00242</v>
+        <v>0.00243</v>
       </c>
       <c r="L385" s="1" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="M385" s="1" t="n">
         <v>0.0024</v>
       </c>
     </row>
@@ -15889,9 +17047,12 @@
         <v>3.951</v>
       </c>
       <c r="K386" s="1" t="n">
-        <v>3.951</v>
+        <v>3.954</v>
       </c>
       <c r="L386" s="1" t="n">
+        <v>3.954</v>
+      </c>
+      <c r="M386" s="1" t="n">
         <v>3.892</v>
       </c>
     </row>
@@ -15929,9 +17090,12 @@
         <v>0.0006316</v>
       </c>
       <c r="K387" s="1" t="n">
+        <v>0.0006308</v>
+      </c>
+      <c r="L387" s="1" t="n">
         <v>0.0006316</v>
       </c>
-      <c r="L387" s="1" t="n">
+      <c r="M387" s="1" t="n">
         <v>0.0006236</v>
       </c>
     </row>
@@ -15969,9 +17133,12 @@
         <v>0.00659</v>
       </c>
       <c r="K388" s="1" t="n">
+        <v>0.00656</v>
+      </c>
+      <c r="L388" s="1" t="n">
         <v>0.00673</v>
       </c>
-      <c r="L388" s="1" t="n">
+      <c r="M388" s="1" t="n">
         <v>0.00653</v>
       </c>
     </row>
@@ -16009,9 +17176,12 @@
         <v>0.1324</v>
       </c>
       <c r="K389" s="1" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="L389" s="1" t="n">
         <v>0.1324</v>
       </c>
-      <c r="L389" s="1" t="n">
+      <c r="M389" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -16049,9 +17219,12 @@
         <v>0.03242</v>
       </c>
       <c r="K390" s="1" t="n">
+        <v>0.03234</v>
+      </c>
+      <c r="L390" s="1" t="n">
         <v>0.03248</v>
       </c>
-      <c r="L390" s="1" t="n">
+      <c r="M390" s="1" t="n">
         <v>0.03201</v>
       </c>
     </row>
@@ -16089,9 +17262,12 @@
         <v>0.06393</v>
       </c>
       <c r="K391" s="1" t="n">
-        <v>0.06393</v>
+        <v>0.06401999999999999</v>
       </c>
       <c r="L391" s="1" t="n">
+        <v>0.06401999999999999</v>
+      </c>
+      <c r="M391" s="1" t="n">
         <v>0.06344</v>
       </c>
     </row>
@@ -16129,9 +17305,12 @@
         <v>27.88</v>
       </c>
       <c r="K392" s="1" t="n">
-        <v>27.88</v>
+        <v>27.95</v>
       </c>
       <c r="L392" s="1" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="M392" s="1" t="n">
         <v>27.57</v>
       </c>
     </row>
@@ -16169,9 +17348,12 @@
         <v>0.000414</v>
       </c>
       <c r="K393" s="1" t="n">
-        <v>0.000414</v>
+        <v>0.000416</v>
       </c>
       <c r="L393" s="1" t="n">
+        <v>0.000416</v>
+      </c>
+      <c r="M393" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -16209,9 +17391,12 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K394" s="1" t="n">
+        <v>0.06993000000000001</v>
+      </c>
+      <c r="L394" s="1" t="n">
         <v>0.07005</v>
       </c>
-      <c r="L394" s="1" t="n">
+      <c r="M394" s="1" t="n">
         <v>0.06926</v>
       </c>
     </row>
@@ -16249,9 +17434,12 @@
         <v>0.2614</v>
       </c>
       <c r="K395" s="1" t="n">
+        <v>0.2613</v>
+      </c>
+      <c r="L395" s="1" t="n">
         <v>0.2614</v>
       </c>
-      <c r="L395" s="1" t="n">
+      <c r="M395" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -16289,9 +17477,12 @@
         <v>0.004693</v>
       </c>
       <c r="K396" s="1" t="n">
+        <v>0.004691</v>
+      </c>
+      <c r="L396" s="1" t="n">
         <v>0.004693</v>
       </c>
-      <c r="L396" s="1" t="n">
+      <c r="M396" s="1" t="n">
         <v>0.004677</v>
       </c>
     </row>
@@ -16329,9 +17520,12 @@
         <v>0.2367</v>
       </c>
       <c r="K397" s="1" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="L397" s="1" t="n">
         <v>0.2367</v>
       </c>
-      <c r="L397" s="1" t="n">
+      <c r="M397" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
@@ -16369,9 +17563,12 @@
         <v>0.18235</v>
       </c>
       <c r="K398" s="1" t="n">
+        <v>0.18222</v>
+      </c>
+      <c r="L398" s="1" t="n">
         <v>0.18235</v>
       </c>
-      <c r="L398" s="1" t="n">
+      <c r="M398" s="1" t="n">
         <v>0.18106</v>
       </c>
     </row>
@@ -16409,9 +17606,12 @@
         <v>0.0415</v>
       </c>
       <c r="K399" s="1" t="n">
+        <v>0.04147</v>
+      </c>
+      <c r="L399" s="1" t="n">
         <v>0.0415</v>
       </c>
-      <c r="L399" s="1" t="n">
+      <c r="M399" s="1" t="n">
         <v>0.04108</v>
       </c>
     </row>
@@ -16452,6 +17652,9 @@
         <v>0.076</v>
       </c>
       <c r="L400" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="M400" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -16489,9 +17692,12 @@
         <v>0.001759</v>
       </c>
       <c r="K401" s="1" t="n">
+        <v>0.001752</v>
+      </c>
+      <c r="L401" s="1" t="n">
         <v>0.001766</v>
       </c>
-      <c r="L401" s="1" t="n">
+      <c r="M401" s="1" t="n">
         <v>0.001739</v>
       </c>
     </row>
@@ -16529,9 +17735,12 @@
         <v>0.05402</v>
       </c>
       <c r="K402" s="1" t="n">
+        <v>0.05399</v>
+      </c>
+      <c r="L402" s="1" t="n">
         <v>0.05402</v>
       </c>
-      <c r="L402" s="1" t="n">
+      <c r="M402" s="1" t="n">
         <v>0.05362</v>
       </c>
     </row>
@@ -16569,9 +17778,12 @@
         <v>2030.26</v>
       </c>
       <c r="K403" s="1" t="n">
+        <v>2026.92</v>
+      </c>
+      <c r="L403" s="1" t="n">
         <v>2031.8</v>
       </c>
-      <c r="L403" s="1" t="n">
+      <c r="M403" s="1" t="n">
         <v>2026.65</v>
       </c>
     </row>
@@ -16609,9 +17821,12 @@
         <v>1.079</v>
       </c>
       <c r="K404" s="1" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="L404" s="1" t="n">
         <v>1.082</v>
       </c>
-      <c r="L404" s="1" t="n">
+      <c r="M404" s="1" t="n">
         <v>1.078</v>
       </c>
     </row>
@@ -16649,9 +17864,12 @@
         <v>7.647</v>
       </c>
       <c r="K405" s="1" t="n">
+        <v>7.647</v>
+      </c>
+      <c r="L405" s="1" t="n">
         <v>7.673</v>
       </c>
-      <c r="L405" s="1" t="n">
+      <c r="M405" s="1" t="n">
         <v>7.647</v>
       </c>
     </row>
@@ -16689,9 +17907,12 @@
         <v>3.274</v>
       </c>
       <c r="K406" s="1" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="L406" s="1" t="n">
         <v>3.274</v>
       </c>
-      <c r="L406" s="1" t="n">
+      <c r="M406" s="1" t="n">
         <v>3.238</v>
       </c>
     </row>
@@ -16729,9 +17950,12 @@
         <v>0.1823</v>
       </c>
       <c r="K407" s="1" t="n">
-        <v>0.1823</v>
+        <v>0.1825</v>
       </c>
       <c r="L407" s="1" t="n">
+        <v>0.1825</v>
+      </c>
+      <c r="M407" s="1" t="n">
         <v>0.1814</v>
       </c>
     </row>
@@ -16769,10 +17993,13 @@
         <v>0.1528</v>
       </c>
       <c r="K408" s="1" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="L408" s="1" t="n">
         <v>0.1537</v>
       </c>
-      <c r="L408" s="1" t="n">
-        <v>0.1526</v>
+      <c r="M408" s="1" t="n">
+        <v>0.1525</v>
       </c>
     </row>
     <row r="409">
@@ -16809,9 +18036,12 @@
         <v>0.07385</v>
       </c>
       <c r="K409" s="1" t="n">
+        <v>0.07376000000000001</v>
+      </c>
+      <c r="L409" s="1" t="n">
         <v>0.07385</v>
       </c>
-      <c r="L409" s="1" t="n">
+      <c r="M409" s="1" t="n">
         <v>0.07315000000000001</v>
       </c>
     </row>
@@ -16849,9 +18079,12 @@
         <v>0.02112</v>
       </c>
       <c r="K410" s="1" t="n">
-        <v>0.02118</v>
+        <v>0.02124</v>
       </c>
       <c r="L410" s="1" t="n">
+        <v>0.02124</v>
+      </c>
+      <c r="M410" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -16889,9 +18122,12 @@
         <v>0.2675</v>
       </c>
       <c r="K411" s="1" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="L411" s="1" t="n">
         <v>0.2683</v>
       </c>
-      <c r="L411" s="1" t="n">
+      <c r="M411" s="1" t="n">
         <v>0.2642</v>
       </c>
     </row>
@@ -16929,9 +18165,12 @@
         <v>0.007396</v>
       </c>
       <c r="K412" s="1" t="n">
-        <v>0.007396</v>
+        <v>0.007404</v>
       </c>
       <c r="L412" s="1" t="n">
+        <v>0.007404</v>
+      </c>
+      <c r="M412" s="1" t="n">
         <v>0.007302</v>
       </c>
     </row>
@@ -16972,6 +18211,9 @@
         <v>0.01392</v>
       </c>
       <c r="L413" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="M413" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -17012,6 +18254,9 @@
         <v>0.093</v>
       </c>
       <c r="L414" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="M414" s="1" t="n">
         <v>0.092</v>
       </c>
     </row>
@@ -17049,9 +18294,12 @@
         <v>0.04015</v>
       </c>
       <c r="K415" s="1" t="n">
+        <v>0.04007</v>
+      </c>
+      <c r="L415" s="1" t="n">
         <v>0.04015</v>
       </c>
-      <c r="L415" s="1" t="n">
+      <c r="M415" s="1" t="n">
         <v>0.03985</v>
       </c>
     </row>
@@ -17089,9 +18337,12 @@
         <v>0.2845</v>
       </c>
       <c r="K416" s="1" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="L416" s="1" t="n">
         <v>0.2854</v>
       </c>
-      <c r="L416" s="1" t="n">
+      <c r="M416" s="1" t="n">
         <v>0.2839</v>
       </c>
     </row>
@@ -17129,9 +18380,12 @@
         <v>1.822</v>
       </c>
       <c r="K417" s="1" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="L417" s="1" t="n">
         <v>1.831</v>
       </c>
-      <c r="L417" s="1" t="n">
+      <c r="M417" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -17169,9 +18423,12 @@
         <v>0.06718</v>
       </c>
       <c r="K418" s="1" t="n">
+        <v>0.06704</v>
+      </c>
+      <c r="L418" s="1" t="n">
         <v>0.06718</v>
       </c>
-      <c r="L418" s="1" t="n">
+      <c r="M418" s="1" t="n">
         <v>0.06668</v>
       </c>
     </row>
@@ -17209,9 +18466,12 @@
         <v>207.47</v>
       </c>
       <c r="K419" s="1" t="n">
+        <v>207.38</v>
+      </c>
+      <c r="L419" s="1" t="n">
         <v>207.47</v>
       </c>
-      <c r="L419" s="1" t="n">
+      <c r="M419" s="1" t="n">
         <v>207.35</v>
       </c>
     </row>
@@ -17249,9 +18509,12 @@
         <v>73.37</v>
       </c>
       <c r="K420" s="1" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="L420" s="1" t="n">
         <v>73.37</v>
       </c>
-      <c r="L420" s="1" t="n">
+      <c r="M420" s="1" t="n">
         <v>73.15000000000001</v>
       </c>
     </row>
@@ -17289,9 +18552,12 @@
         <v>0.07241</v>
       </c>
       <c r="K421" s="1" t="n">
+        <v>0.07235</v>
+      </c>
+      <c r="L421" s="1" t="n">
         <v>0.07251000000000001</v>
       </c>
-      <c r="L421" s="1" t="n">
+      <c r="M421" s="1" t="n">
         <v>0.07226</v>
       </c>
     </row>
@@ -17329,9 +18595,12 @@
         <v>0.05015</v>
       </c>
       <c r="K422" s="1" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="L422" s="1" t="n">
         <v>0.05076</v>
       </c>
-      <c r="L422" s="1" t="n">
+      <c r="M422" s="1" t="n">
         <v>0.04998</v>
       </c>
     </row>
@@ -17372,6 +18641,9 @@
         <v>0.001153</v>
       </c>
       <c r="L423" s="1" t="n">
+        <v>0.001153</v>
+      </c>
+      <c r="M423" s="1" t="n">
         <v>0.001148</v>
       </c>
     </row>
@@ -17409,9 +18681,12 @@
         <v>0.00503</v>
       </c>
       <c r="K424" s="1" t="n">
+        <v>0.00503</v>
+      </c>
+      <c r="L424" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="L424" s="1" t="n">
+      <c r="M424" s="1" t="n">
         <v>0.00501</v>
       </c>
     </row>
@@ -17449,9 +18724,12 @@
         <v>0.1281</v>
       </c>
       <c r="K425" s="1" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="L425" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="L425" s="1" t="n">
+      <c r="M425" s="1" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -17492,6 +18770,9 @@
         <v>1.301</v>
       </c>
       <c r="L426" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="M426" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -17529,9 +18810,12 @@
         <v>0.00442</v>
       </c>
       <c r="K427" s="1" t="n">
-        <v>0.00442</v>
+        <v>0.004421</v>
       </c>
       <c r="L427" s="1" t="n">
+        <v>0.004421</v>
+      </c>
+      <c r="M427" s="1" t="n">
         <v>0.004393</v>
       </c>
     </row>
@@ -17569,9 +18853,12 @@
         <v>0.005072</v>
       </c>
       <c r="K428" s="1" t="n">
+        <v>0.005063</v>
+      </c>
+      <c r="L428" s="1" t="n">
         <v>0.005072</v>
       </c>
-      <c r="L428" s="1" t="n">
+      <c r="M428" s="1" t="n">
         <v>0.005017</v>
       </c>
     </row>
@@ -17609,9 +18896,12 @@
         <v>0.02327</v>
       </c>
       <c r="K429" s="1" t="n">
+        <v>0.02323</v>
+      </c>
+      <c r="L429" s="1" t="n">
         <v>0.02329</v>
       </c>
-      <c r="L429" s="1" t="n">
+      <c r="M429" s="1" t="n">
         <v>0.02288</v>
       </c>
     </row>
@@ -17649,9 +18939,12 @@
         <v>0.02499</v>
       </c>
       <c r="K430" s="1" t="n">
+        <v>0.02509</v>
+      </c>
+      <c r="L430" s="1" t="n">
         <v>0.02517</v>
       </c>
-      <c r="L430" s="1" t="n">
+      <c r="M430" s="1" t="n">
         <v>0.02499</v>
       </c>
     </row>
@@ -17692,6 +18985,9 @@
         <v>0.016</v>
       </c>
       <c r="L431" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="M431" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -17729,10 +19025,13 @@
         <v>0.5447</v>
       </c>
       <c r="K432" s="1" t="n">
+        <v>0.5432</v>
+      </c>
+      <c r="L432" s="1" t="n">
         <v>0.546</v>
       </c>
-      <c r="L432" s="1" t="n">
-        <v>0.5439000000000001</v>
+      <c r="M432" s="1" t="n">
+        <v>0.5432</v>
       </c>
     </row>
     <row r="433">
@@ -17769,9 +19068,12 @@
         <v>0.001386</v>
       </c>
       <c r="K433" s="1" t="n">
-        <v>0.001389</v>
+        <v>0.00139</v>
       </c>
       <c r="L433" s="1" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="M433" s="1" t="n">
         <v>0.001383</v>
       </c>
     </row>
@@ -17809,9 +19111,12 @@
         <v>0.3972</v>
       </c>
       <c r="K434" s="1" t="n">
-        <v>0.3972</v>
+        <v>0.3975</v>
       </c>
       <c r="L434" s="1" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="M434" s="1" t="n">
         <v>0.3925</v>
       </c>
     </row>
@@ -17849,9 +19154,12 @@
         <v>0.001392</v>
       </c>
       <c r="K435" s="1" t="n">
+        <v>0.001391</v>
+      </c>
+      <c r="L435" s="1" t="n">
         <v>0.001393</v>
       </c>
-      <c r="L435" s="1" t="n">
+      <c r="M435" s="1" t="n">
         <v>0.001388</v>
       </c>
     </row>
@@ -17892,6 +19200,9 @@
         <v>0.00718</v>
       </c>
       <c r="L436" s="1" t="n">
+        <v>0.00718</v>
+      </c>
+      <c r="M436" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -17929,9 +19240,12 @@
         <v>0.002012</v>
       </c>
       <c r="K437" s="1" t="n">
+        <v>0.00201</v>
+      </c>
+      <c r="L437" s="1" t="n">
         <v>0.002012</v>
       </c>
-      <c r="L437" s="1" t="n">
+      <c r="M437" s="1" t="n">
         <v>0.001982</v>
       </c>
     </row>
@@ -17969,9 +19283,12 @@
         <v>0.3136</v>
       </c>
       <c r="K438" s="1" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="L438" s="1" t="n">
         <v>0.3147</v>
       </c>
-      <c r="L438" s="1" t="n">
+      <c r="M438" s="1" t="n">
         <v>0.3122</v>
       </c>
     </row>
@@ -18009,9 +19326,12 @@
         <v>0.04436</v>
       </c>
       <c r="K439" s="1" t="n">
-        <v>0.04438</v>
+        <v>0.04448</v>
       </c>
       <c r="L439" s="1" t="n">
+        <v>0.04448</v>
+      </c>
+      <c r="M439" s="1" t="n">
         <v>0.04426</v>
       </c>
     </row>
@@ -18052,6 +19372,9 @@
         <v>0.913</v>
       </c>
       <c r="L440" s="1" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="M440" s="1" t="n">
         <v>0.906</v>
       </c>
     </row>
@@ -18089,9 +19412,12 @@
         <v>1552.18</v>
       </c>
       <c r="K441" s="1" t="n">
+        <v>1550.86</v>
+      </c>
+      <c r="L441" s="1" t="n">
         <v>1552.4</v>
       </c>
-      <c r="L441" s="1" t="n">
+      <c r="M441" s="1" t="n">
         <v>1548.06</v>
       </c>
     </row>
@@ -18129,9 +19455,12 @@
         <v>0.0008061</v>
       </c>
       <c r="K442" s="1" t="n">
+        <v>0.0008023</v>
+      </c>
+      <c r="L442" s="1" t="n">
         <v>0.0008061</v>
       </c>
-      <c r="L442" s="1" t="n">
+      <c r="M442" s="1" t="n">
         <v>0.0007877</v>
       </c>
     </row>
@@ -18169,9 +19498,12 @@
         <v>0.003533</v>
       </c>
       <c r="K443" s="1" t="n">
+        <v>0.003524</v>
+      </c>
+      <c r="L443" s="1" t="n">
         <v>0.003558</v>
       </c>
-      <c r="L443" s="1" t="n">
+      <c r="M443" s="1" t="n">
         <v>0.003515</v>
       </c>
     </row>
@@ -18209,9 +19541,12 @@
         <v>1.994</v>
       </c>
       <c r="K444" s="1" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="L444" s="1" t="n">
         <v>1.994</v>
       </c>
-      <c r="L444" s="1" t="n">
+      <c r="M444" s="1" t="n">
         <v>1.977</v>
       </c>
     </row>
@@ -18249,9 +19584,12 @@
         <v>1.319</v>
       </c>
       <c r="K445" s="1" t="n">
-        <v>1.319</v>
+        <v>1.321</v>
       </c>
       <c r="L445" s="1" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="M445" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -18289,9 +19627,12 @@
         <v>0.06908</v>
       </c>
       <c r="K446" s="1" t="n">
+        <v>0.06902999999999999</v>
+      </c>
+      <c r="L446" s="1" t="n">
         <v>0.06929</v>
       </c>
-      <c r="L446" s="1" t="n">
+      <c r="M446" s="1" t="n">
         <v>0.0689</v>
       </c>
     </row>
@@ -18329,9 +19670,12 @@
         <v>0.02381</v>
       </c>
       <c r="K447" s="1" t="n">
+        <v>0.02391</v>
+      </c>
+      <c r="L447" s="1" t="n">
         <v>0.02403</v>
       </c>
-      <c r="L447" s="1" t="n">
+      <c r="M447" s="1" t="n">
         <v>0.02347</v>
       </c>
     </row>
@@ -18369,9 +19713,12 @@
         <v>0.0141</v>
       </c>
       <c r="K448" s="1" t="n">
+        <v>0.01403</v>
+      </c>
+      <c r="L448" s="1" t="n">
         <v>0.0141</v>
       </c>
-      <c r="L448" s="1" t="n">
+      <c r="M448" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -18409,9 +19756,12 @@
         <v>3.748</v>
       </c>
       <c r="K449" s="1" t="n">
+        <v>3.744</v>
+      </c>
+      <c r="L449" s="1" t="n">
         <v>3.748</v>
       </c>
-      <c r="L449" s="1" t="n">
+      <c r="M449" s="1" t="n">
         <v>3.726</v>
       </c>
     </row>
@@ -18449,9 +19799,12 @@
         <v>0.0113</v>
       </c>
       <c r="K450" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="L450" s="1" t="n">
         <v>0.0115</v>
       </c>
-      <c r="L450" s="1" t="n">
+      <c r="M450" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -18489,9 +19842,12 @@
         <v>0.01038</v>
       </c>
       <c r="K451" s="1" t="n">
-        <v>0.01038</v>
+        <v>0.01039</v>
       </c>
       <c r="L451" s="1" t="n">
+        <v>0.01039</v>
+      </c>
+      <c r="M451" s="1" t="n">
         <v>0.01024</v>
       </c>
     </row>
@@ -18529,9 +19885,12 @@
         <v>0.1531</v>
       </c>
       <c r="K452" s="1" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="L452" s="1" t="n">
         <v>0.1532</v>
       </c>
-      <c r="L452" s="1" t="n">
+      <c r="M452" s="1" t="n">
         <v>0.1522</v>
       </c>
     </row>
@@ -18569,9 +19928,12 @@
         <v>151.29</v>
       </c>
       <c r="K453" s="1" t="n">
+        <v>151.28</v>
+      </c>
+      <c r="L453" s="1" t="n">
         <v>151.29</v>
       </c>
-      <c r="L453" s="1" t="n">
+      <c r="M453" s="1" t="n">
         <v>150.85</v>
       </c>
     </row>
@@ -18609,9 +19971,12 @@
         <v>0.008639000000000001</v>
       </c>
       <c r="K454" s="1" t="n">
+        <v>0.008637000000000001</v>
+      </c>
+      <c r="L454" s="1" t="n">
         <v>0.008639000000000001</v>
       </c>
-      <c r="L454" s="1" t="n">
+      <c r="M454" s="1" t="n">
         <v>0.008593999999999999</v>
       </c>
     </row>
@@ -18649,9 +20014,12 @@
         <v>0.05258</v>
       </c>
       <c r="K455" s="1" t="n">
-        <v>0.05258</v>
+        <v>0.0526</v>
       </c>
       <c r="L455" s="1" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="M455" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -18689,9 +20057,12 @@
         <v>0.30828</v>
       </c>
       <c r="K456" s="1" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="L456" s="1" t="n">
         <v>0.30925</v>
       </c>
-      <c r="L456" s="1" t="n">
+      <c r="M456" s="1" t="n">
         <v>0.30269</v>
       </c>
     </row>
@@ -18729,9 +20100,12 @@
         <v>0.00549</v>
       </c>
       <c r="K457" s="1" t="n">
-        <v>0.00549</v>
+        <v>0.0055</v>
       </c>
       <c r="L457" s="1" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="M457" s="1" t="n">
         <v>0.00544</v>
       </c>
     </row>
@@ -18769,9 +20143,12 @@
         <v>0.1008</v>
       </c>
       <c r="K458" s="1" t="n">
+        <v>0.1007</v>
+      </c>
+      <c r="L458" s="1" t="n">
         <v>0.1008</v>
       </c>
-      <c r="L458" s="1" t="n">
+      <c r="M458" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -18812,6 +20189,9 @@
         <v>0.001844</v>
       </c>
       <c r="L459" s="1" t="n">
+        <v>0.001844</v>
+      </c>
+      <c r="M459" s="1" t="n">
         <v>0.001825</v>
       </c>
     </row>
@@ -18849,9 +20229,12 @@
         <v>0.01842</v>
       </c>
       <c r="K460" s="1" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="L460" s="1" t="n">
         <v>0.01848</v>
       </c>
-      <c r="L460" s="1" t="n">
+      <c r="M460" s="1" t="n">
         <v>0.01822</v>
       </c>
     </row>
@@ -18889,9 +20272,12 @@
         <v>0.0004883</v>
       </c>
       <c r="K461" s="1" t="n">
-        <v>0.0004883</v>
+        <v>0.0004888</v>
       </c>
       <c r="L461" s="1" t="n">
+        <v>0.0004888</v>
+      </c>
+      <c r="M461" s="1" t="n">
         <v>0.0004842</v>
       </c>
     </row>
@@ -18929,9 +20315,12 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="K462" s="1" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0968</v>
       </c>
       <c r="L462" s="1" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="M462" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -18969,9 +20358,12 @@
         <v>0.07954</v>
       </c>
       <c r="K463" s="1" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="L463" s="1" t="n">
         <v>0.07954</v>
       </c>
-      <c r="L463" s="1" t="n">
+      <c r="M463" s="1" t="n">
         <v>0.07888000000000001</v>
       </c>
     </row>
@@ -19009,9 +20401,12 @@
         <v>0.03191</v>
       </c>
       <c r="K464" s="1" t="n">
-        <v>0.03207</v>
+        <v>0.03235</v>
       </c>
       <c r="L464" s="1" t="n">
+        <v>0.03235</v>
+      </c>
+      <c r="M464" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -19052,6 +20447,9 @@
         <v>0.01623</v>
       </c>
       <c r="L465" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="M465" s="1" t="n">
         <v>0.01613</v>
       </c>
     </row>
@@ -19089,9 +20487,12 @@
         <v>0.06794</v>
       </c>
       <c r="K466" s="1" t="n">
+        <v>0.06787</v>
+      </c>
+      <c r="L466" s="1" t="n">
         <v>0.06794</v>
       </c>
-      <c r="L466" s="1" t="n">
+      <c r="M466" s="1" t="n">
         <v>0.06763</v>
       </c>
     </row>
@@ -19129,9 +20530,12 @@
         <v>0.04344</v>
       </c>
       <c r="K467" s="1" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="L467" s="1" t="n">
         <v>0.04344</v>
       </c>
-      <c r="L467" s="1" t="n">
+      <c r="M467" s="1" t="n">
         <v>0.04322</v>
       </c>
     </row>
@@ -19169,9 +20573,12 @@
         <v>0.05639</v>
       </c>
       <c r="K468" s="1" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="L468" s="1" t="n">
         <v>0.05795</v>
       </c>
-      <c r="L468" s="1" t="n">
+      <c r="M468" s="1" t="n">
         <v>0.05587</v>
       </c>
     </row>
@@ -19209,9 +20616,12 @@
         <v>0.2317</v>
       </c>
       <c r="K469" s="1" t="n">
-        <v>0.2317</v>
+        <v>0.232</v>
       </c>
       <c r="L469" s="1" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="M469" s="1" t="n">
         <v>0.2294</v>
       </c>
     </row>
@@ -19249,9 +20659,12 @@
         <v>0.0906</v>
       </c>
       <c r="K470" s="1" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="L470" s="1" t="n">
         <v>0.0906</v>
       </c>
-      <c r="L470" s="1" t="n">
+      <c r="M470" s="1" t="n">
         <v>0.0902</v>
       </c>
     </row>
@@ -19289,9 +20702,12 @@
         <v>0.06693</v>
       </c>
       <c r="K471" s="1" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="L471" s="1" t="n">
         <v>0.06693</v>
       </c>
-      <c r="L471" s="1" t="n">
+      <c r="M471" s="1" t="n">
         <v>0.06660000000000001</v>
       </c>
     </row>
@@ -19329,9 +20745,12 @@
         <v>6.595</v>
       </c>
       <c r="K472" s="1" t="n">
+        <v>6.586</v>
+      </c>
+      <c r="L472" s="1" t="n">
         <v>6.595</v>
       </c>
-      <c r="L472" s="1" t="n">
+      <c r="M472" s="1" t="n">
         <v>6.486</v>
       </c>
     </row>
@@ -19369,9 +20788,12 @@
         <v>0.01949</v>
       </c>
       <c r="K473" s="1" t="n">
+        <v>0.01948</v>
+      </c>
+      <c r="L473" s="1" t="n">
         <v>0.01949</v>
       </c>
-      <c r="L473" s="1" t="n">
+      <c r="M473" s="1" t="n">
         <v>0.01937</v>
       </c>
     </row>
@@ -19409,9 +20831,12 @@
         <v>1.431</v>
       </c>
       <c r="K474" s="1" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L474" s="1" t="n">
         <v>1.431</v>
       </c>
-      <c r="L474" s="1" t="n">
+      <c r="M474" s="1" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -19449,9 +20874,12 @@
         <v>0.09</v>
       </c>
       <c r="K475" s="1" t="n">
-        <v>0.09</v>
+        <v>0.09001000000000001</v>
       </c>
       <c r="L475" s="1" t="n">
+        <v>0.09001000000000001</v>
+      </c>
+      <c r="M475" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -19489,9 +20917,12 @@
         <v>0.1066</v>
       </c>
       <c r="K476" s="1" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="L476" s="1" t="n">
         <v>0.1066</v>
       </c>
-      <c r="L476" s="1" t="n">
+      <c r="M476" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -19529,10 +20960,13 @@
         <v>0.09402000000000001</v>
       </c>
       <c r="K477" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="L477" s="1" t="n">
         <v>0.09451</v>
       </c>
-      <c r="L477" s="1" t="n">
-        <v>0.09402000000000001</v>
+      <c r="M477" s="1" t="n">
+        <v>0.094</v>
       </c>
     </row>
     <row r="478">
@@ -19569,9 +21003,12 @@
         <v>0.0001636</v>
       </c>
       <c r="K478" s="1" t="n">
-        <v>0.0001636</v>
+        <v>0.0001637</v>
       </c>
       <c r="L478" s="1" t="n">
+        <v>0.0001637</v>
+      </c>
+      <c r="M478" s="1" t="n">
         <v>0.0001624</v>
       </c>
     </row>
@@ -19609,9 +21046,12 @@
         <v>0.04034</v>
       </c>
       <c r="K479" s="1" t="n">
+        <v>0.04031</v>
+      </c>
+      <c r="L479" s="1" t="n">
         <v>0.04034</v>
       </c>
-      <c r="L479" s="1" t="n">
+      <c r="M479" s="1" t="n">
         <v>0.04007</v>
       </c>
     </row>
@@ -19649,9 +21089,12 @@
         <v>0.007442</v>
       </c>
       <c r="K480" s="1" t="n">
+        <v>0.007426</v>
+      </c>
+      <c r="L480" s="1" t="n">
         <v>0.007442</v>
       </c>
-      <c r="L480" s="1" t="n">
+      <c r="M480" s="1" t="n">
         <v>0.007389</v>
       </c>
     </row>
@@ -19692,6 +21135,9 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="L481" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="M481" s="1" t="n">
         <v>0.0953</v>
       </c>
     </row>
@@ -19729,9 +21175,12 @@
         <v>0.05603</v>
       </c>
       <c r="K482" s="1" t="n">
+        <v>0.05614</v>
+      </c>
+      <c r="L482" s="1" t="n">
         <v>0.05621</v>
       </c>
-      <c r="L482" s="1" t="n">
+      <c r="M482" s="1" t="n">
         <v>0.05569</v>
       </c>
     </row>
@@ -19769,9 +21218,12 @@
         <v>0.006209</v>
       </c>
       <c r="K483" s="1" t="n">
+        <v>0.006187</v>
+      </c>
+      <c r="L483" s="1" t="n">
         <v>0.006209</v>
       </c>
-      <c r="L483" s="1" t="n">
+      <c r="M483" s="1" t="n">
         <v>0.006161</v>
       </c>
     </row>
@@ -19809,9 +21261,12 @@
         <v>0.01492</v>
       </c>
       <c r="K484" s="1" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="L484" s="1" t="n">
         <v>0.01497</v>
       </c>
-      <c r="L484" s="1" t="n">
+      <c r="M484" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -19849,9 +21304,12 @@
         <v>0.02415</v>
       </c>
       <c r="K485" s="1" t="n">
+        <v>0.02417</v>
+      </c>
+      <c r="L485" s="1" t="n">
         <v>0.02427</v>
       </c>
-      <c r="L485" s="1" t="n">
+      <c r="M485" s="1" t="n">
         <v>0.02403</v>
       </c>
     </row>
@@ -19889,9 +21347,12 @@
         <v>0.06698999999999999</v>
       </c>
       <c r="K486" s="1" t="n">
-        <v>0.06702</v>
+        <v>0.06707</v>
       </c>
       <c r="L486" s="1" t="n">
+        <v>0.06707</v>
+      </c>
+      <c r="M486" s="1" t="n">
         <v>0.0667</v>
       </c>
     </row>
@@ -19929,9 +21390,12 @@
         <v>0.03709</v>
       </c>
       <c r="K487" s="1" t="n">
+        <v>0.03692</v>
+      </c>
+      <c r="L487" s="1" t="n">
         <v>0.03709</v>
       </c>
-      <c r="L487" s="1" t="n">
+      <c r="M487" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -19969,9 +21433,12 @@
         <v>0.01826</v>
       </c>
       <c r="K488" s="1" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="L488" s="1" t="n">
         <v>0.01826</v>
       </c>
-      <c r="L488" s="1" t="n">
+      <c r="M488" s="1" t="n">
         <v>0.01814</v>
       </c>
     </row>
@@ -20009,9 +21476,12 @@
         <v>0.03299</v>
       </c>
       <c r="K489" s="1" t="n">
+        <v>0.03285</v>
+      </c>
+      <c r="L489" s="1" t="n">
         <v>0.03299</v>
       </c>
-      <c r="L489" s="1" t="n">
+      <c r="M489" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -20049,9 +21519,12 @@
         <v>0.01481</v>
       </c>
       <c r="K490" s="1" t="n">
-        <v>0.01481</v>
+        <v>0.0151</v>
       </c>
       <c r="L490" s="1" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="M490" s="1" t="n">
         <v>0.01458</v>
       </c>
     </row>
@@ -20089,9 +21562,12 @@
         <v>0.01884</v>
       </c>
       <c r="K491" s="1" t="n">
-        <v>0.01884</v>
+        <v>0.019</v>
       </c>
       <c r="L491" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="M491" s="1" t="n">
         <v>0.01851</v>
       </c>
     </row>
@@ -20129,9 +21605,12 @@
         <v>0.08792999999999999</v>
       </c>
       <c r="K492" s="1" t="n">
+        <v>0.08789</v>
+      </c>
+      <c r="L492" s="1" t="n">
         <v>0.08935</v>
       </c>
-      <c r="L492" s="1" t="n">
+      <c r="M492" s="1" t="n">
         <v>0.08784</v>
       </c>
     </row>
@@ -20169,9 +21648,12 @@
         <v>0.006521</v>
       </c>
       <c r="K493" s="1" t="n">
+        <v>0.006513</v>
+      </c>
+      <c r="L493" s="1" t="n">
         <v>0.006521</v>
       </c>
-      <c r="L493" s="1" t="n">
+      <c r="M493" s="1" t="n">
         <v>0.006497</v>
       </c>
     </row>
@@ -20209,9 +21691,12 @@
         <v>0.1332</v>
       </c>
       <c r="K494" s="1" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="L494" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="L494" s="1" t="n">
+      <c r="M494" s="1" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -20249,9 +21734,12 @@
         <v>0.2859</v>
       </c>
       <c r="K495" s="1" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="L495" s="1" t="n">
         <v>0.2859</v>
       </c>
-      <c r="L495" s="1" t="n">
+      <c r="M495" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -20289,9 +21777,12 @@
         <v>0.004554</v>
       </c>
       <c r="K496" s="1" t="n">
-        <v>0.004554</v>
+        <v>0.004562</v>
       </c>
       <c r="L496" s="1" t="n">
+        <v>0.004562</v>
+      </c>
+      <c r="M496" s="1" t="n">
         <v>0.004516</v>
       </c>
     </row>
@@ -20329,9 +21820,12 @@
         <v>0.1265</v>
       </c>
       <c r="K497" s="1" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="L497" s="1" t="n">
         <v>0.1283</v>
       </c>
-      <c r="L497" s="1" t="n">
+      <c r="M497" s="1" t="n">
         <v>0.1264</v>
       </c>
     </row>
@@ -20369,9 +21863,12 @@
         <v>0.0345</v>
       </c>
       <c r="K498" s="1" t="n">
-        <v>0.0345</v>
+        <v>0.03461</v>
       </c>
       <c r="L498" s="1" t="n">
+        <v>0.03461</v>
+      </c>
+      <c r="M498" s="1" t="n">
         <v>0.03423</v>
       </c>
     </row>
@@ -20409,9 +21906,12 @@
         <v>0.03566</v>
       </c>
       <c r="K499" s="1" t="n">
+        <v>0.03559</v>
+      </c>
+      <c r="L499" s="1" t="n">
         <v>0.03576</v>
       </c>
-      <c r="L499" s="1" t="n">
+      <c r="M499" s="1" t="n">
         <v>0.03557</v>
       </c>
     </row>
@@ -20449,9 +21949,12 @@
         <v>0.003416</v>
       </c>
       <c r="K500" s="1" t="n">
-        <v>0.003421</v>
+        <v>0.003422</v>
       </c>
       <c r="L500" s="1" t="n">
+        <v>0.003422</v>
+      </c>
+      <c r="M500" s="1" t="n">
         <v>0.003413</v>
       </c>
     </row>
@@ -20489,9 +21992,12 @@
         <v>0.0003837</v>
       </c>
       <c r="K501" s="1" t="n">
-        <v>0.0003837</v>
+        <v>0.0003854</v>
       </c>
       <c r="L501" s="1" t="n">
+        <v>0.0003854</v>
+      </c>
+      <c r="M501" s="1" t="n">
         <v>0.0003786</v>
       </c>
     </row>
@@ -20529,9 +22035,12 @@
         <v>0.3011</v>
       </c>
       <c r="K502" s="1" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="L502" s="1" t="n">
         <v>0.3011</v>
       </c>
-      <c r="L502" s="1" t="n">
+      <c r="M502" s="1" t="n">
         <v>0.2986</v>
       </c>
     </row>
@@ -20569,9 +22078,12 @@
         <v>0.06506000000000001</v>
       </c>
       <c r="K503" s="1" t="n">
+        <v>0.06497</v>
+      </c>
+      <c r="L503" s="1" t="n">
         <v>0.06507</v>
       </c>
-      <c r="L503" s="1" t="n">
+      <c r="M503" s="1" t="n">
         <v>0.06485</v>
       </c>
     </row>
@@ -20609,9 +22121,12 @@
         <v>0.1782</v>
       </c>
       <c r="K504" s="1" t="n">
-        <v>0.1782</v>
+        <v>0.1784</v>
       </c>
       <c r="L504" s="1" t="n">
+        <v>0.1784</v>
+      </c>
+      <c r="M504" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -20649,9 +22164,12 @@
         <v>0.1519</v>
       </c>
       <c r="K505" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="L505" s="1" t="n">
         <v>0.1519</v>
       </c>
-      <c r="L505" s="1" t="n">
+      <c r="M505" s="1" t="n">
         <v>0.1511</v>
       </c>
     </row>
@@ -20689,9 +22207,12 @@
         <v>0.01202</v>
       </c>
       <c r="K506" s="1" t="n">
-        <v>0.01202</v>
+        <v>0.01205</v>
       </c>
       <c r="L506" s="1" t="n">
+        <v>0.01205</v>
+      </c>
+      <c r="M506" s="1" t="n">
         <v>0.01193</v>
       </c>
     </row>
@@ -20729,9 +22250,12 @@
         <v>0.2878</v>
       </c>
       <c r="K507" s="1" t="n">
-        <v>0.2893</v>
+        <v>0.2899</v>
       </c>
       <c r="L507" s="1" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="M507" s="1" t="n">
         <v>0.2871</v>
       </c>
     </row>
@@ -20769,9 +22293,12 @@
         <v>0.00942</v>
       </c>
       <c r="K508" s="1" t="n">
+        <v>0.009390000000000001</v>
+      </c>
+      <c r="L508" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="L508" s="1" t="n">
+      <c r="M508" s="1" t="n">
         <v>0.009310000000000001</v>
       </c>
     </row>
@@ -20809,9 +22336,12 @@
         <v>0.006851</v>
       </c>
       <c r="K509" s="1" t="n">
+        <v>0.006845</v>
+      </c>
+      <c r="L509" s="1" t="n">
         <v>0.006851</v>
       </c>
-      <c r="L509" s="1" t="n">
+      <c r="M509" s="1" t="n">
         <v>0.006783</v>
       </c>
     </row>
@@ -20849,9 +22379,12 @@
         <v>0.2986</v>
       </c>
       <c r="K510" s="1" t="n">
-        <v>0.2986</v>
+        <v>0.2989</v>
       </c>
       <c r="L510" s="1" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="M510" s="1" t="n">
         <v>0.2934</v>
       </c>
     </row>
@@ -20892,6 +22425,9 @@
         <v>0.01471</v>
       </c>
       <c r="L511" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="M511" s="1" t="n">
         <v>0.01465</v>
       </c>
     </row>
@@ -20932,6 +22468,9 @@
         <v>0.1402</v>
       </c>
       <c r="L512" s="1" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="M512" s="1" t="n">
         <v>0.1394</v>
       </c>
     </row>
@@ -20969,9 +22508,12 @@
         <v>0.08112</v>
       </c>
       <c r="K513" s="1" t="n">
+        <v>0.08103</v>
+      </c>
+      <c r="L513" s="1" t="n">
         <v>0.08144999999999999</v>
       </c>
-      <c r="L513" s="1" t="n">
+      <c r="M513" s="1" t="n">
         <v>0.08069</v>
       </c>
     </row>
@@ -21012,6 +22554,9 @@
         <v>0.0251</v>
       </c>
       <c r="L514" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="M514" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -21049,9 +22594,12 @@
         <v>0.06318</v>
       </c>
       <c r="K515" s="1" t="n">
+        <v>0.06313000000000001</v>
+      </c>
+      <c r="L515" s="1" t="n">
         <v>0.06329</v>
       </c>
-      <c r="L515" s="1" t="n">
+      <c r="M515" s="1" t="n">
         <v>0.06301</v>
       </c>
     </row>
@@ -21089,9 +22637,12 @@
         <v>0.04752</v>
       </c>
       <c r="K516" s="1" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="L516" s="1" t="n">
         <v>0.04752</v>
       </c>
-      <c r="L516" s="1" t="n">
+      <c r="M516" s="1" t="n">
         <v>0.04707</v>
       </c>
     </row>
@@ -21129,9 +22680,12 @@
         <v>0.00493</v>
       </c>
       <c r="K517" s="1" t="n">
-        <v>0.00493</v>
+        <v>0.004935</v>
       </c>
       <c r="L517" s="1" t="n">
+        <v>0.004935</v>
+      </c>
+      <c r="M517" s="1" t="n">
         <v>0.004902</v>
       </c>
     </row>
@@ -21169,9 +22723,12 @@
         <v>0.009441</v>
       </c>
       <c r="K518" s="1" t="n">
-        <v>0.009441</v>
+        <v>0.009504</v>
       </c>
       <c r="L518" s="1" t="n">
+        <v>0.009504</v>
+      </c>
+      <c r="M518" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -21209,9 +22766,12 @@
         <v>0.01805</v>
       </c>
       <c r="K519" s="1" t="n">
+        <v>0.01804</v>
+      </c>
+      <c r="L519" s="1" t="n">
         <v>0.01807</v>
       </c>
-      <c r="L519" s="1" t="n">
+      <c r="M519" s="1" t="n">
         <v>0.01798</v>
       </c>
     </row>
@@ -21249,9 +22809,12 @@
         <v>0.06696000000000001</v>
       </c>
       <c r="K520" s="1" t="n">
-        <v>0.06696000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="L520" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="M520" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -21289,9 +22852,12 @@
         <v>0.1372</v>
       </c>
       <c r="K521" s="1" t="n">
-        <v>0.1372</v>
+        <v>0.1373</v>
       </c>
       <c r="L521" s="1" t="n">
+        <v>0.1373</v>
+      </c>
+      <c r="M521" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -21329,9 +22895,12 @@
         <v>0.04761</v>
       </c>
       <c r="K522" s="1" t="n">
-        <v>0.04761</v>
+        <v>0.04768</v>
       </c>
       <c r="L522" s="1" t="n">
+        <v>0.04768</v>
+      </c>
+      <c r="M522" s="1" t="n">
         <v>0.04718</v>
       </c>
     </row>
@@ -21369,9 +22938,12 @@
         <v>0.06827</v>
       </c>
       <c r="K523" s="1" t="n">
+        <v>0.06822</v>
+      </c>
+      <c r="L523" s="1" t="n">
         <v>0.06827</v>
       </c>
-      <c r="L523" s="1" t="n">
+      <c r="M523" s="1" t="n">
         <v>0.06784999999999999</v>
       </c>
     </row>
@@ -21409,9 +22981,12 @@
         <v>0.6999</v>
       </c>
       <c r="K524" s="1" t="n">
-        <v>0.6999</v>
+        <v>0.7019</v>
       </c>
       <c r="L524" s="1" t="n">
+        <v>0.7019</v>
+      </c>
+      <c r="M524" s="1" t="n">
         <v>0.6966</v>
       </c>
     </row>
@@ -21452,6 +23027,9 @@
         <v>0.00269</v>
       </c>
       <c r="L525" s="1" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="M525" s="1" t="n">
         <v>0.00267</v>
       </c>
     </row>
@@ -21489,9 +23067,12 @@
         <v>0.488</v>
       </c>
       <c r="K526" s="1" t="n">
+        <v>0.4877</v>
+      </c>
+      <c r="L526" s="1" t="n">
         <v>0.488</v>
       </c>
-      <c r="L526" s="1" t="n">
+      <c r="M526" s="1" t="n">
         <v>0.4856</v>
       </c>
     </row>
@@ -21529,9 +23110,12 @@
         <v>45.84</v>
       </c>
       <c r="K527" s="1" t="n">
-        <v>45.84</v>
+        <v>45.85</v>
       </c>
       <c r="L527" s="1" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="M527" s="1" t="n">
         <v>45.76</v>
       </c>
     </row>
@@ -21569,9 +23153,12 @@
         <v>0.02447</v>
       </c>
       <c r="K528" s="1" t="n">
+        <v>0.02443</v>
+      </c>
+      <c r="L528" s="1" t="n">
         <v>0.02447</v>
       </c>
-      <c r="L528" s="1" t="n">
+      <c r="M528" s="1" t="n">
         <v>0.02429</v>
       </c>
     </row>
@@ -21609,9 +23196,12 @@
         <v>0.006422</v>
       </c>
       <c r="K529" s="1" t="n">
-        <v>0.006422</v>
+        <v>0.006427</v>
       </c>
       <c r="L529" s="1" t="n">
+        <v>0.006427</v>
+      </c>
+      <c r="M529" s="1" t="n">
         <v>0.00638</v>
       </c>
     </row>
@@ -21649,9 +23239,12 @@
         <v>0.2007</v>
       </c>
       <c r="K530" s="1" t="n">
-        <v>0.2007</v>
+        <v>0.2011</v>
       </c>
       <c r="L530" s="1" t="n">
+        <v>0.2011</v>
+      </c>
+      <c r="M530" s="1" t="n">
         <v>0.1993</v>
       </c>
     </row>
@@ -21689,9 +23282,12 @@
         <v>0.00769</v>
       </c>
       <c r="K531" s="1" t="n">
+        <v>0.007695</v>
+      </c>
+      <c r="L531" s="1" t="n">
         <v>0.007727</v>
       </c>
-      <c r="L531" s="1" t="n">
+      <c r="M531" s="1" t="n">
         <v>0.007657</v>
       </c>
     </row>
@@ -21729,9 +23325,12 @@
         <v>2.302</v>
       </c>
       <c r="K532" s="1" t="n">
+        <v>2.292</v>
+      </c>
+      <c r="L532" s="1" t="n">
         <v>2.302</v>
       </c>
-      <c r="L532" s="1" t="n">
+      <c r="M532" s="1" t="n">
         <v>2.275</v>
       </c>
     </row>
@@ -21769,9 +23368,12 @@
         <v>0.04186</v>
       </c>
       <c r="K533" s="1" t="n">
+        <v>0.04175</v>
+      </c>
+      <c r="L533" s="1" t="n">
         <v>0.04186</v>
       </c>
-      <c r="L533" s="1" t="n">
+      <c r="M533" s="1" t="n">
         <v>0.04138</v>
       </c>
     </row>
@@ -21809,9 +23411,12 @@
         <v>0.1828</v>
       </c>
       <c r="K534" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="L534" s="1" t="n">
         <v>0.1833</v>
       </c>
-      <c r="L534" s="1" t="n">
+      <c r="M534" s="1" t="n">
         <v>0.1811</v>
       </c>
     </row>
@@ -21849,9 +23454,12 @@
         <v>0.04372</v>
       </c>
       <c r="K535" s="1" t="n">
+        <v>0.04368</v>
+      </c>
+      <c r="L535" s="1" t="n">
         <v>0.04372</v>
       </c>
-      <c r="L535" s="1" t="n">
+      <c r="M535" s="1" t="n">
         <v>0.04287</v>
       </c>
     </row>
@@ -21889,9 +23497,12 @@
         <v>0.05428</v>
       </c>
       <c r="K536" s="1" t="n">
+        <v>0.05427</v>
+      </c>
+      <c r="L536" s="1" t="n">
         <v>0.05438</v>
       </c>
-      <c r="L536" s="1" t="n">
+      <c r="M536" s="1" t="n">
         <v>0.05409</v>
       </c>
     </row>
@@ -21929,9 +23540,12 @@
         <v>0.1611</v>
       </c>
       <c r="K537" s="1" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="L537" s="1" t="n">
         <v>0.1611</v>
       </c>
-      <c r="L537" s="1" t="n">
+      <c r="M537" s="1" t="n">
         <v>0.1602</v>
       </c>
     </row>
@@ -21969,9 +23583,12 @@
         <v>0.03687</v>
       </c>
       <c r="K538" s="1" t="n">
+        <v>0.03684</v>
+      </c>
+      <c r="L538" s="1" t="n">
         <v>0.03687</v>
       </c>
-      <c r="L538" s="1" t="n">
+      <c r="M538" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -22009,9 +23626,12 @@
         <v>0.0587</v>
       </c>
       <c r="K539" s="1" t="n">
+        <v>0.05864</v>
+      </c>
+      <c r="L539" s="1" t="n">
         <v>0.0587</v>
       </c>
-      <c r="L539" s="1" t="n">
+      <c r="M539" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -22049,9 +23669,12 @@
         <v>0.04282</v>
       </c>
       <c r="K540" s="1" t="n">
-        <v>0.04282</v>
+        <v>0.04286</v>
       </c>
       <c r="L540" s="1" t="n">
+        <v>0.04286</v>
+      </c>
+      <c r="M540" s="1" t="n">
         <v>0.04256</v>
       </c>
     </row>
@@ -22089,9 +23712,12 @@
         <v>0.01729</v>
       </c>
       <c r="K541" s="1" t="n">
+        <v>0.01727</v>
+      </c>
+      <c r="L541" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="L541" s="1" t="n">
+      <c r="M541" s="1" t="n">
         <v>0.0172</v>
       </c>
     </row>
@@ -22129,9 +23755,12 @@
         <v>0.003973</v>
       </c>
       <c r="K542" s="1" t="n">
+        <v>0.003965</v>
+      </c>
+      <c r="L542" s="1" t="n">
         <v>0.003975</v>
       </c>
-      <c r="L542" s="1" t="n">
+      <c r="M542" s="1" t="n">
         <v>0.003963</v>
       </c>
     </row>
@@ -22169,9 +23798,12 @@
         <v>0.05789</v>
       </c>
       <c r="K543" s="1" t="n">
+        <v>0.05798</v>
+      </c>
+      <c r="L543" s="1" t="n">
         <v>0.05835</v>
       </c>
-      <c r="L543" s="1" t="n">
+      <c r="M543" s="1" t="n">
         <v>0.05735</v>
       </c>
     </row>
@@ -22209,9 +23841,12 @@
         <v>0.05032</v>
       </c>
       <c r="K544" s="1" t="n">
+        <v>0.05026</v>
+      </c>
+      <c r="L544" s="1" t="n">
         <v>0.05042</v>
       </c>
-      <c r="L544" s="1" t="n">
+      <c r="M544" s="1" t="n">
         <v>0.05016</v>
       </c>
     </row>
@@ -22249,9 +23884,12 @@
         <v>0.04082</v>
       </c>
       <c r="K545" s="1" t="n">
-        <v>0.04082</v>
+        <v>0.04089</v>
       </c>
       <c r="L545" s="1" t="n">
+        <v>0.04089</v>
+      </c>
+      <c r="M545" s="1" t="n">
         <v>0.04038</v>
       </c>
     </row>
@@ -22289,9 +23927,12 @@
         <v>0.007436</v>
       </c>
       <c r="K546" s="1" t="n">
+        <v>0.007429</v>
+      </c>
+      <c r="L546" s="1" t="n">
         <v>0.007436</v>
       </c>
-      <c r="L546" s="1" t="n">
+      <c r="M546" s="1" t="n">
         <v>0.007402</v>
       </c>
     </row>
@@ -22329,9 +23970,12 @@
         <v>0.0148</v>
       </c>
       <c r="K547" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="L547" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="L547" s="1" t="n">
+      <c r="M547" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -22369,9 +24013,12 @@
         <v>0.01576</v>
       </c>
       <c r="K548" s="1" t="n">
+        <v>0.01574</v>
+      </c>
+      <c r="L548" s="1" t="n">
         <v>0.01576</v>
       </c>
-      <c r="L548" s="1" t="n">
+      <c r="M548" s="1" t="n">
         <v>0.0157</v>
       </c>
     </row>
@@ -22409,9 +24056,12 @@
         <v>0.13562</v>
       </c>
       <c r="K549" s="1" t="n">
+        <v>0.13553</v>
+      </c>
+      <c r="L549" s="1" t="n">
         <v>0.13562</v>
       </c>
-      <c r="L549" s="1" t="n">
+      <c r="M549" s="1" t="n">
         <v>0.13271</v>
       </c>
     </row>
@@ -22449,9 +24099,12 @@
         <v>0.1706</v>
       </c>
       <c r="K550" s="1" t="n">
+        <v>0.1704</v>
+      </c>
+      <c r="L550" s="1" t="n">
         <v>0.1706</v>
       </c>
-      <c r="L550" s="1" t="n">
+      <c r="M550" s="1" t="n">
         <v>0.1693</v>
       </c>
     </row>
@@ -22489,10 +24142,13 @@
         <v>0.003593</v>
       </c>
       <c r="K551" s="1" t="n">
+        <v>0.003576</v>
+      </c>
+      <c r="L551" s="1" t="n">
         <v>0.003593</v>
       </c>
-      <c r="L551" s="1" t="n">
-        <v>0.003577</v>
+      <c r="M551" s="1" t="n">
+        <v>0.003576</v>
       </c>
     </row>
     <row r="552">
@@ -22529,9 +24185,12 @@
         <v>0.03046</v>
       </c>
       <c r="K552" s="1" t="n">
-        <v>0.03046</v>
+        <v>0.03055</v>
       </c>
       <c r="L552" s="1" t="n">
+        <v>0.03055</v>
+      </c>
+      <c r="M552" s="1" t="n">
         <v>0.0303</v>
       </c>
     </row>
@@ -22569,9 +24228,12 @@
         <v>0.0132</v>
       </c>
       <c r="K553" s="1" t="n">
+        <v>0.01321</v>
+      </c>
+      <c r="L553" s="1" t="n">
         <v>0.01325</v>
       </c>
-      <c r="L553" s="1" t="n">
+      <c r="M553" s="1" t="n">
         <v>0.01319</v>
       </c>
     </row>
@@ -22609,9 +24271,12 @@
         <v>0.1044</v>
       </c>
       <c r="K554" s="1" t="n">
+        <v>0.1044</v>
+      </c>
+      <c r="L554" s="1" t="n">
         <v>0.1046</v>
       </c>
-      <c r="L554" s="1" t="n">
+      <c r="M554" s="1" t="n">
         <v>0.1039</v>
       </c>
     </row>
@@ -22649,9 +24314,12 @@
         <v>0.05316</v>
       </c>
       <c r="K555" s="1" t="n">
+        <v>0.05314</v>
+      </c>
+      <c r="L555" s="1" t="n">
         <v>0.05319</v>
       </c>
-      <c r="L555" s="1" t="n">
+      <c r="M555" s="1" t="n">
         <v>0.05291</v>
       </c>
     </row>
@@ -22689,9 +24357,12 @@
         <v>0.01234</v>
       </c>
       <c r="K556" s="1" t="n">
+        <v>0.01224</v>
+      </c>
+      <c r="L556" s="1" t="n">
         <v>0.01234</v>
       </c>
-      <c r="L556" s="1" t="n">
+      <c r="M556" s="1" t="n">
         <v>0.01218</v>
       </c>
     </row>

--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M556"/>
+  <dimension ref="A1:N556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -430,8 +430,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,10 +493,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>price_02:30</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -538,9 +544,12 @@
         <v>71686.89999999999</v>
       </c>
       <c r="L2" s="1" t="n">
+        <v>71696.5</v>
+      </c>
+      <c r="M2" s="1" t="n">
         <v>71788</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="N2" s="1" t="n">
         <v>71364.39999999999</v>
       </c>
     </row>
@@ -581,9 +590,12 @@
         <v>2107.59</v>
       </c>
       <c r="L3" s="1" t="n">
+        <v>2107.36</v>
+      </c>
+      <c r="M3" s="1" t="n">
         <v>2109.75</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="N3" s="1" t="n">
         <v>2090.41</v>
       </c>
     </row>
@@ -624,9 +636,12 @@
         <v>88.5</v>
       </c>
       <c r="L4" s="1" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="M4" s="1" t="n">
         <v>88.5</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="N4" s="1" t="n">
         <v>87.47</v>
       </c>
     </row>
@@ -667,9 +682,12 @@
         <v>23.262</v>
       </c>
       <c r="L5" s="1" t="n">
+        <v>23.179</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>23.579</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="N5" s="1" t="n">
         <v>23.043</v>
       </c>
     </row>
@@ -710,9 +728,12 @@
         <v>0.001815</v>
       </c>
       <c r="L6" s="1" t="n">
+        <v>0.001826</v>
+      </c>
+      <c r="M6" s="1" t="n">
         <v>0.001892</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.001811</v>
       </c>
     </row>
@@ -753,9 +774,12 @@
         <v>1.4179</v>
       </c>
       <c r="L7" s="1" t="n">
+        <v>1.4168</v>
+      </c>
+      <c r="M7" s="1" t="n">
         <v>1.4184</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="N7" s="1" t="n">
         <v>1.4117</v>
       </c>
     </row>
@@ -796,9 +820,12 @@
         <v>0.010714</v>
       </c>
       <c r="L8" s="1" t="n">
+        <v>0.010642</v>
+      </c>
+      <c r="M8" s="1" t="n">
         <v>0.011244</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="N8" s="1" t="n">
         <v>0.010407</v>
       </c>
     </row>
@@ -839,9 +866,12 @@
         <v>4.03</v>
       </c>
       <c r="L9" s="1" t="n">
+        <v>4.059</v>
+      </c>
+      <c r="M9" s="1" t="n">
         <v>4.062</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="N9" s="1" t="n">
         <v>3.954</v>
       </c>
     </row>
@@ -882,9 +912,12 @@
         <v>282.64</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>282.64</v>
+        <v>284.04</v>
       </c>
       <c r="M10" s="1" t="n">
+        <v>284.04</v>
+      </c>
+      <c r="N10" s="1" t="n">
         <v>272.11</v>
       </c>
     </row>
@@ -925,9 +958,12 @@
         <v>0.07764</v>
       </c>
       <c r="L11" s="1" t="n">
+        <v>0.07778</v>
+      </c>
+      <c r="M11" s="1" t="n">
         <v>0.08047</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="N11" s="1" t="n">
         <v>0.07764</v>
       </c>
     </row>
@@ -968,9 +1004,12 @@
         <v>227.18</v>
       </c>
       <c r="L12" s="1" t="n">
+        <v>227.37</v>
+      </c>
+      <c r="M12" s="1" t="n">
         <v>227.69</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="N12" s="1" t="n">
         <v>223.76</v>
       </c>
     </row>
@@ -1011,9 +1050,12 @@
         <v>0.09525</v>
       </c>
       <c r="L13" s="1" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="M13" s="1" t="n">
         <v>0.09543</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="N13" s="1" t="n">
         <v>0.0946</v>
       </c>
     </row>
@@ -1054,10 +1096,13 @@
         <v>37.274</v>
       </c>
       <c r="L14" s="1" t="n">
+        <v>37.059</v>
+      </c>
+      <c r="M14" s="1" t="n">
         <v>37.361</v>
       </c>
-      <c r="M14" s="1" t="n">
-        <v>37.089</v>
+      <c r="N14" s="1" t="n">
+        <v>37.059</v>
       </c>
     </row>
     <row r="15">
@@ -1097,9 +1142,12 @@
         <v>0.08938</v>
       </c>
       <c r="L15" s="1" t="n">
+        <v>0.09046</v>
+      </c>
+      <c r="M15" s="1" t="n">
         <v>0.09845</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="N15" s="1" t="n">
         <v>0.08938</v>
       </c>
     </row>
@@ -1140,9 +1188,12 @@
         <v>0.2266</v>
       </c>
       <c r="L16" s="1" t="n">
+        <v>0.2258</v>
+      </c>
+      <c r="M16" s="1" t="n">
         <v>0.2339</v>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="N16" s="1" t="n">
         <v>0.2256</v>
       </c>
     </row>
@@ -1183,9 +1234,12 @@
         <v>0.011518</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>0.011542</v>
+        <v>0.011575</v>
       </c>
       <c r="M17" s="1" t="n">
+        <v>0.011575</v>
+      </c>
+      <c r="N17" s="1" t="n">
         <v>0.011379</v>
       </c>
     </row>
@@ -1226,9 +1280,12 @@
         <v>661.45</v>
       </c>
       <c r="L18" s="1" t="n">
+        <v>661.3</v>
+      </c>
+      <c r="M18" s="1" t="n">
         <v>661.9</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="N18" s="1" t="n">
         <v>658.89</v>
       </c>
     </row>
@@ -1269,9 +1326,12 @@
         <v>0.003368</v>
       </c>
       <c r="L19" s="1" t="n">
+        <v>0.003361</v>
+      </c>
+      <c r="M19" s="1" t="n">
         <v>0.003368</v>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="N19" s="1" t="n">
         <v>0.0033271</v>
       </c>
     </row>
@@ -1312,10 +1372,13 @@
         <v>0.17643</v>
       </c>
       <c r="L20" s="1" t="n">
+        <v>0.17367</v>
+      </c>
+      <c r="M20" s="1" t="n">
         <v>0.18066</v>
       </c>
-      <c r="M20" s="1" t="n">
-        <v>0.17643</v>
+      <c r="N20" s="1" t="n">
+        <v>0.17367</v>
       </c>
     </row>
     <row r="21">
@@ -1355,9 +1418,12 @@
         <v>0.009849</v>
       </c>
       <c r="L21" s="1" t="n">
+        <v>0.009929</v>
+      </c>
+      <c r="M21" s="1" t="n">
         <v>0.010044</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="N21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -1398,9 +1464,12 @@
         <v>1.0086</v>
       </c>
       <c r="L22" s="1" t="n">
+        <v>1.0063</v>
+      </c>
+      <c r="M22" s="1" t="n">
         <v>1.009</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="N22" s="1" t="n">
         <v>0.9985000000000001</v>
       </c>
     </row>
@@ -1441,9 +1510,12 @@
         <v>5005.7</v>
       </c>
       <c r="L23" s="1" t="n">
+        <v>5007.37</v>
+      </c>
+      <c r="M23" s="1" t="n">
         <v>5012.25</v>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="N23" s="1" t="n">
         <v>5002.67</v>
       </c>
     </row>
@@ -1484,9 +1556,12 @@
         <v>0.2643</v>
       </c>
       <c r="L24" s="1" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="M24" s="1" t="n">
         <v>0.2645</v>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="N24" s="1" t="n">
         <v>0.2625</v>
       </c>
     </row>
@@ -1527,10 +1602,13 @@
         <v>2.875</v>
       </c>
       <c r="L25" s="1" t="n">
+        <v>2.873</v>
+      </c>
+      <c r="M25" s="1" t="n">
         <v>2.924</v>
       </c>
-      <c r="M25" s="1" t="n">
-        <v>2.875</v>
+      <c r="N25" s="1" t="n">
+        <v>2.873</v>
       </c>
     </row>
     <row r="26">
@@ -1570,9 +1648,12 @@
         <v>0.3854</v>
       </c>
       <c r="L26" s="1" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="M26" s="1" t="n">
         <v>0.4096</v>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="N26" s="1" t="n">
         <v>0.3825</v>
       </c>
     </row>
@@ -1613,9 +1694,12 @@
         <v>0.889</v>
       </c>
       <c r="L27" s="1" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="M27" s="1" t="n">
         <v>0.889</v>
       </c>
-      <c r="M27" s="1" t="n">
+      <c r="N27" s="1" t="n">
         <v>0.881</v>
       </c>
     </row>
@@ -1656,9 +1740,12 @@
         <v>1.343</v>
       </c>
       <c r="L28" s="1" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="M28" s="1" t="n">
         <v>1.346</v>
       </c>
-      <c r="M28" s="1" t="n">
+      <c r="N28" s="1" t="n">
         <v>1.335</v>
       </c>
     </row>
@@ -1699,9 +1786,12 @@
         <v>9.198</v>
       </c>
       <c r="L29" s="1" t="n">
+        <v>9.192</v>
+      </c>
+      <c r="M29" s="1" t="n">
         <v>9.205</v>
       </c>
-      <c r="M29" s="1" t="n">
+      <c r="N29" s="1" t="n">
         <v>9.131</v>
       </c>
     </row>
@@ -1742,9 +1832,12 @@
         <v>462.58</v>
       </c>
       <c r="L30" s="1" t="n">
+        <v>462.21</v>
+      </c>
+      <c r="M30" s="1" t="n">
         <v>463.35</v>
       </c>
-      <c r="M30" s="1" t="n">
+      <c r="N30" s="1" t="n">
         <v>461.24</v>
       </c>
     </row>
@@ -1785,9 +1878,12 @@
         <v>9.771000000000001</v>
       </c>
       <c r="L31" s="1" t="n">
+        <v>9.763999999999999</v>
+      </c>
+      <c r="M31" s="1" t="n">
         <v>9.771000000000001</v>
       </c>
-      <c r="M31" s="1" t="n">
+      <c r="N31" s="1" t="n">
         <v>9.696999999999999</v>
       </c>
     </row>
@@ -1828,9 +1924,12 @@
         <v>0.36051</v>
       </c>
       <c r="L32" s="1" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="M32" s="1" t="n">
         <v>0.36683</v>
       </c>
-      <c r="M32" s="1" t="n">
+      <c r="N32" s="1" t="n">
         <v>0.35998</v>
       </c>
     </row>
@@ -1871,9 +1970,12 @@
         <v>1.418</v>
       </c>
       <c r="L33" s="1" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="M33" s="1" t="n">
         <v>1.421</v>
       </c>
-      <c r="M33" s="1" t="n">
+      <c r="N33" s="1" t="n">
         <v>1.409</v>
       </c>
     </row>
@@ -1914,9 +2016,12 @@
         <v>0.58086</v>
       </c>
       <c r="L34" s="1" t="n">
+        <v>0.59069</v>
+      </c>
+      <c r="M34" s="1" t="n">
         <v>0.59693</v>
       </c>
-      <c r="M34" s="1" t="n">
+      <c r="N34" s="1" t="n">
         <v>0.58086</v>
       </c>
     </row>
@@ -1957,9 +2062,12 @@
         <v>1.223</v>
       </c>
       <c r="L35" s="1" t="n">
+        <v>1.2242</v>
+      </c>
+      <c r="M35" s="1" t="n">
         <v>1.2283</v>
       </c>
-      <c r="M35" s="1" t="n">
+      <c r="N35" s="1" t="n">
         <v>1.2186</v>
       </c>
     </row>
@@ -2000,9 +2108,12 @@
         <v>80.36</v>
       </c>
       <c r="L36" s="1" t="n">
+        <v>80.38</v>
+      </c>
+      <c r="M36" s="1" t="n">
         <v>80.5</v>
       </c>
-      <c r="M36" s="1" t="n">
+      <c r="N36" s="1" t="n">
         <v>80.27</v>
       </c>
     </row>
@@ -2043,9 +2154,12 @@
         <v>0.1991</v>
       </c>
       <c r="L37" s="1" t="n">
+        <v>0.1991</v>
+      </c>
+      <c r="M37" s="1" t="n">
         <v>0.204</v>
       </c>
-      <c r="M37" s="1" t="n">
+      <c r="N37" s="1" t="n">
         <v>0.1967</v>
       </c>
     </row>
@@ -2086,9 +2200,12 @@
         <v>1.863</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>1.866</v>
+        <v>1.867</v>
       </c>
       <c r="M38" s="1" t="n">
+        <v>1.867</v>
+      </c>
+      <c r="N38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -2129,9 +2246,12 @@
         <v>0.3363</v>
       </c>
       <c r="L39" s="1" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="M39" s="1" t="n">
         <v>0.3382</v>
       </c>
-      <c r="M39" s="1" t="n">
+      <c r="N39" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -2172,10 +2292,13 @@
         <v>0.8929</v>
       </c>
       <c r="L40" s="1" t="n">
+        <v>0.8846000000000001</v>
+      </c>
+      <c r="M40" s="1" t="n">
         <v>0.9115</v>
       </c>
-      <c r="M40" s="1" t="n">
-        <v>0.8895999999999999</v>
+      <c r="N40" s="1" t="n">
+        <v>0.8846000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2215,9 +2338,12 @@
         <v>0.713</v>
       </c>
       <c r="L41" s="1" t="n">
+        <v>0.7121</v>
+      </c>
+      <c r="M41" s="1" t="n">
         <v>0.7151999999999999</v>
       </c>
-      <c r="M41" s="1" t="n">
+      <c r="N41" s="1" t="n">
         <v>0.7115</v>
       </c>
     </row>
@@ -2258,9 +2384,12 @@
         <v>0.06567000000000001</v>
       </c>
       <c r="L42" s="1" t="n">
+        <v>0.06562999999999999</v>
+      </c>
+      <c r="M42" s="1" t="n">
         <v>0.06769</v>
       </c>
-      <c r="M42" s="1" t="n">
+      <c r="N42" s="1" t="n">
         <v>0.06551999999999999</v>
       </c>
     </row>
@@ -2301,9 +2430,12 @@
         <v>114.61</v>
       </c>
       <c r="L43" s="1" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="M43" s="1" t="n">
         <v>114.65</v>
       </c>
-      <c r="M43" s="1" t="n">
+      <c r="N43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -2344,9 +2476,12 @@
         <v>0.6561</v>
       </c>
       <c r="L44" s="1" t="n">
+        <v>0.6552</v>
+      </c>
+      <c r="M44" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="M44" s="1" t="n">
+      <c r="N44" s="1" t="n">
         <v>0.6536999999999999</v>
       </c>
     </row>
@@ -2390,6 +2525,9 @@
         <v>1.227</v>
       </c>
       <c r="M45" s="1" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="N45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -2430,9 +2568,12 @@
         <v>0.02375</v>
       </c>
       <c r="L46" s="1" t="n">
+        <v>0.02387</v>
+      </c>
+      <c r="M46" s="1" t="n">
         <v>0.02392</v>
       </c>
-      <c r="M46" s="1" t="n">
+      <c r="N46" s="1" t="n">
         <v>0.02375</v>
       </c>
     </row>
@@ -2473,9 +2614,12 @@
         <v>55.17</v>
       </c>
       <c r="L47" s="1" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="M47" s="1" t="n">
         <v>55.19</v>
       </c>
-      <c r="M47" s="1" t="n">
+      <c r="N47" s="1" t="n">
         <v>54.99</v>
       </c>
     </row>
@@ -2516,9 +2660,12 @@
         <v>0.06046</v>
       </c>
       <c r="L48" s="1" t="n">
+        <v>0.06074</v>
+      </c>
+      <c r="M48" s="1" t="n">
         <v>0.061</v>
       </c>
-      <c r="M48" s="1" t="n">
+      <c r="N48" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -2559,9 +2706,12 @@
         <v>0.1085</v>
       </c>
       <c r="L49" s="1" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="M49" s="1" t="n">
         <v>0.1086</v>
       </c>
-      <c r="M49" s="1" t="n">
+      <c r="N49" s="1" t="n">
         <v>0.1076</v>
       </c>
     </row>
@@ -2602,9 +2752,12 @@
         <v>0.01804</v>
       </c>
       <c r="L50" s="1" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="M50" s="1" t="n">
         <v>0.01815</v>
       </c>
-      <c r="M50" s="1" t="n">
+      <c r="N50" s="1" t="n">
         <v>0.01795</v>
       </c>
     </row>
@@ -2645,9 +2798,12 @@
         <v>1.4805</v>
       </c>
       <c r="L51" s="1" t="n">
+        <v>1.4787</v>
+      </c>
+      <c r="M51" s="1" t="n">
         <v>1.4817</v>
       </c>
-      <c r="M51" s="1" t="n">
+      <c r="N51" s="1" t="n">
         <v>1.4618</v>
       </c>
     </row>
@@ -2688,9 +2844,12 @@
         <v>0.3617</v>
       </c>
       <c r="L52" s="1" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="M52" s="1" t="n">
         <v>0.3617</v>
       </c>
-      <c r="M52" s="1" t="n">
+      <c r="N52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -2731,9 +2890,12 @@
         <v>0.001944</v>
       </c>
       <c r="L53" s="1" t="n">
+        <v>0.001943</v>
+      </c>
+      <c r="M53" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="M53" s="1" t="n">
+      <c r="N53" s="1" t="n">
         <v>0.001939</v>
       </c>
     </row>
@@ -2774,9 +2936,12 @@
         <v>0.09574000000000001</v>
       </c>
       <c r="L54" s="1" t="n">
+        <v>0.09572</v>
+      </c>
+      <c r="M54" s="1" t="n">
         <v>0.09574000000000001</v>
       </c>
-      <c r="M54" s="1" t="n">
+      <c r="N54" s="1" t="n">
         <v>0.09514</v>
       </c>
     </row>
@@ -2817,9 +2982,12 @@
         <v>0.04093</v>
       </c>
       <c r="L55" s="1" t="n">
+        <v>0.04092</v>
+      </c>
+      <c r="M55" s="1" t="n">
         <v>0.04099</v>
       </c>
-      <c r="M55" s="1" t="n">
+      <c r="N55" s="1" t="n">
         <v>0.04003</v>
       </c>
     </row>
@@ -2860,10 +3028,13 @@
         <v>0.29836</v>
       </c>
       <c r="L56" s="1" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="M56" s="1" t="n">
         <v>0.29861</v>
       </c>
-      <c r="M56" s="1" t="n">
-        <v>0.29831</v>
+      <c r="N56" s="1" t="n">
+        <v>0.29821</v>
       </c>
     </row>
     <row r="57">
@@ -2903,9 +3074,12 @@
         <v>0.005684</v>
       </c>
       <c r="L57" s="1" t="n">
+        <v>0.005676</v>
+      </c>
+      <c r="M57" s="1" t="n">
         <v>0.005824</v>
       </c>
-      <c r="M57" s="1" t="n">
+      <c r="N57" s="1" t="n">
         <v>0.005633</v>
       </c>
     </row>
@@ -2946,9 +3120,12 @@
         <v>4990.71</v>
       </c>
       <c r="L58" s="1" t="n">
+        <v>4992.33</v>
+      </c>
+      <c r="M58" s="1" t="n">
         <v>4998.37</v>
       </c>
-      <c r="M58" s="1" t="n">
+      <c r="N58" s="1" t="n">
         <v>4988.64</v>
       </c>
     </row>
@@ -2989,10 +3166,13 @@
         <v>0.4073</v>
       </c>
       <c r="L59" s="1" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="M59" s="1" t="n">
         <v>0.4246</v>
       </c>
-      <c r="M59" s="1" t="n">
-        <v>0.4073</v>
+      <c r="N59" s="1" t="n">
+        <v>0.4067</v>
       </c>
     </row>
     <row r="60">
@@ -3032,9 +3212,12 @@
         <v>0.04648</v>
       </c>
       <c r="L60" s="1" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="M60" s="1" t="n">
         <v>0.04686</v>
       </c>
-      <c r="M60" s="1" t="n">
+      <c r="N60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -3075,9 +3258,12 @@
         <v>0.21336</v>
       </c>
       <c r="L61" s="1" t="n">
+        <v>0.21418</v>
+      </c>
+      <c r="M61" s="1" t="n">
         <v>0.21708</v>
       </c>
-      <c r="M61" s="1" t="n">
+      <c r="N61" s="1" t="n">
         <v>0.21309</v>
       </c>
     </row>
@@ -3118,9 +3304,12 @@
         <v>0.1074</v>
       </c>
       <c r="L62" s="1" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="M62" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="M62" s="1" t="n">
+      <c r="N62" s="1" t="n">
         <v>0.1065</v>
       </c>
     </row>
@@ -3161,9 +3350,12 @@
         <v>0.7341</v>
       </c>
       <c r="L63" s="1" t="n">
+        <v>0.7324000000000001</v>
+      </c>
+      <c r="M63" s="1" t="n">
         <v>0.7341</v>
       </c>
-      <c r="M63" s="1" t="n">
+      <c r="N63" s="1" t="n">
         <v>0.7255</v>
       </c>
     </row>
@@ -3204,9 +3396,12 @@
         <v>0.1669</v>
       </c>
       <c r="L64" s="1" t="n">
+        <v>0.1666</v>
+      </c>
+      <c r="M64" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="M64" s="1" t="n">
+      <c r="N64" s="1" t="n">
         <v>0.1658</v>
       </c>
     </row>
@@ -3247,9 +3442,12 @@
         <v>2.676</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>2.677</v>
+        <v>2.679</v>
       </c>
       <c r="M65" s="1" t="n">
+        <v>2.679</v>
+      </c>
+      <c r="N65" s="1" t="n">
         <v>2.65</v>
       </c>
     </row>
@@ -3290,9 +3488,12 @@
         <v>0.04031</v>
       </c>
       <c r="L66" s="1" t="n">
+        <v>0.04035</v>
+      </c>
+      <c r="M66" s="1" t="n">
         <v>0.04072</v>
       </c>
-      <c r="M66" s="1" t="n">
+      <c r="N66" s="1" t="n">
         <v>0.04018</v>
       </c>
     </row>
@@ -3333,9 +3534,12 @@
         <v>0.0431</v>
       </c>
       <c r="L67" s="1" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="M67" s="1" t="n">
         <v>0.04314</v>
       </c>
-      <c r="M67" s="1" t="n">
+      <c r="N67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -3376,9 +3580,12 @@
         <v>3.993</v>
       </c>
       <c r="L68" s="1" t="n">
+        <v>3.991</v>
+      </c>
+      <c r="M68" s="1" t="n">
         <v>3.993</v>
       </c>
-      <c r="M68" s="1" t="n">
+      <c r="N68" s="1" t="n">
         <v>3.951</v>
       </c>
     </row>
@@ -3419,9 +3626,12 @@
         <v>0.1274</v>
       </c>
       <c r="L69" s="1" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="M69" s="1" t="n">
         <v>0.1274</v>
       </c>
-      <c r="M69" s="1" t="n">
+      <c r="N69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -3462,9 +3672,12 @@
         <v>6.308</v>
       </c>
       <c r="L70" s="1" t="n">
+        <v>6.299</v>
+      </c>
+      <c r="M70" s="1" t="n">
         <v>6.338</v>
       </c>
-      <c r="M70" s="1" t="n">
+      <c r="N70" s="1" t="n">
         <v>6.114</v>
       </c>
     </row>
@@ -3505,9 +3718,12 @@
         <v>0.05009</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>0.0501</v>
+        <v>0.05015</v>
       </c>
       <c r="M71" s="1" t="n">
+        <v>0.05015</v>
+      </c>
+      <c r="N71" s="1" t="n">
         <v>0.04959</v>
       </c>
     </row>
@@ -3548,9 +3764,12 @@
         <v>0.004131</v>
       </c>
       <c r="L72" s="1" t="n">
+        <v>0.004134</v>
+      </c>
+      <c r="M72" s="1" t="n">
         <v>0.004181</v>
       </c>
-      <c r="M72" s="1" t="n">
+      <c r="N72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -3591,9 +3810,12 @@
         <v>6.032</v>
       </c>
       <c r="L73" s="1" t="n">
+        <v>6.024</v>
+      </c>
+      <c r="M73" s="1" t="n">
         <v>6.032</v>
       </c>
-      <c r="M73" s="1" t="n">
+      <c r="N73" s="1" t="n">
         <v>5.96</v>
       </c>
     </row>
@@ -3634,9 +3856,12 @@
         <v>0.1655</v>
       </c>
       <c r="L74" s="1" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="M74" s="1" t="n">
         <v>0.1655</v>
       </c>
-      <c r="M74" s="1" t="n">
+      <c r="N74" s="1" t="n">
         <v>0.1619</v>
       </c>
     </row>
@@ -3677,9 +3902,12 @@
         <v>0.007365</v>
       </c>
       <c r="L75" s="1" t="n">
+        <v>0.007343</v>
+      </c>
+      <c r="M75" s="1" t="n">
         <v>0.007365</v>
       </c>
-      <c r="M75" s="1" t="n">
+      <c r="N75" s="1" t="n">
         <v>0.007261</v>
       </c>
     </row>
@@ -3720,9 +3948,12 @@
         <v>0.2171</v>
       </c>
       <c r="L76" s="1" t="n">
+        <v>0.2153</v>
+      </c>
+      <c r="M76" s="1" t="n">
         <v>0.2199</v>
       </c>
-      <c r="M76" s="1" t="n">
+      <c r="N76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -3763,9 +3994,12 @@
         <v>0.005836</v>
       </c>
       <c r="L77" s="1" t="n">
+        <v>0.005819</v>
+      </c>
+      <c r="M77" s="1" t="n">
         <v>0.005844</v>
       </c>
-      <c r="M77" s="1" t="n">
+      <c r="N77" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -3806,9 +4040,12 @@
         <v>0.1022</v>
       </c>
       <c r="L78" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="M78" s="1" t="n">
         <v>0.1023</v>
       </c>
-      <c r="M78" s="1" t="n">
+      <c r="N78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -3849,9 +4086,12 @@
         <v>0.00631</v>
       </c>
       <c r="L79" s="1" t="n">
+        <v>0.006308</v>
+      </c>
+      <c r="M79" s="1" t="n">
         <v>0.006315</v>
       </c>
-      <c r="M79" s="1" t="n">
+      <c r="N79" s="1" t="n">
         <v>0.006237</v>
       </c>
     </row>
@@ -3892,9 +4132,12 @@
         <v>33.61</v>
       </c>
       <c r="L80" s="1" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="M80" s="1" t="n">
         <v>33.66</v>
       </c>
-      <c r="M80" s="1" t="n">
+      <c r="N80" s="1" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -3935,9 +4178,12 @@
         <v>0.04055</v>
       </c>
       <c r="L81" s="1" t="n">
+        <v>0.04053</v>
+      </c>
+      <c r="M81" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="M81" s="1" t="n">
+      <c r="N81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -3978,9 +4224,12 @@
         <v>0.16753</v>
       </c>
       <c r="L82" s="1" t="n">
+        <v>0.16719</v>
+      </c>
+      <c r="M82" s="1" t="n">
         <v>0.16759</v>
       </c>
-      <c r="M82" s="1" t="n">
+      <c r="N82" s="1" t="n">
         <v>0.16679</v>
       </c>
     </row>
@@ -4021,9 +4270,12 @@
         <v>0.1035</v>
       </c>
       <c r="L83" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="M83" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="M83" s="1" t="n">
+      <c r="N83" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -4064,10 +4316,13 @@
         <v>0.08756</v>
       </c>
       <c r="L84" s="1" t="n">
+        <v>0.0873</v>
+      </c>
+      <c r="M84" s="1" t="n">
         <v>0.08848</v>
       </c>
-      <c r="M84" s="1" t="n">
-        <v>0.08756</v>
+      <c r="N84" s="1" t="n">
+        <v>0.0873</v>
       </c>
     </row>
     <row r="85">
@@ -4107,10 +4362,13 @@
         <v>0.02298</v>
       </c>
       <c r="L85" s="1" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="M85" s="1" t="n">
         <v>0.02331</v>
       </c>
-      <c r="M85" s="1" t="n">
-        <v>0.02298</v>
+      <c r="N85" s="1" t="n">
+        <v>0.0229</v>
       </c>
     </row>
     <row r="86">
@@ -4150,9 +4408,12 @@
         <v>0.244</v>
       </c>
       <c r="L86" s="1" t="n">
-        <v>0.244</v>
+        <v>0.245</v>
       </c>
       <c r="M86" s="1" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="N86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -4193,9 +4454,12 @@
         <v>358.15</v>
       </c>
       <c r="L87" s="1" t="n">
+        <v>357.03</v>
+      </c>
+      <c r="M87" s="1" t="n">
         <v>358.65</v>
       </c>
-      <c r="M87" s="1" t="n">
+      <c r="N87" s="1" t="n">
         <v>355.75</v>
       </c>
     </row>
@@ -4236,9 +4500,12 @@
         <v>0.00352</v>
       </c>
       <c r="L88" s="1" t="n">
+        <v>0.00349</v>
+      </c>
+      <c r="M88" s="1" t="n">
         <v>0.00352</v>
       </c>
-      <c r="M88" s="1" t="n">
+      <c r="N88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -4279,9 +4546,12 @@
         <v>8.321</v>
       </c>
       <c r="L89" s="1" t="n">
+        <v>8.316000000000001</v>
+      </c>
+      <c r="M89" s="1" t="n">
         <v>8.323</v>
       </c>
-      <c r="M89" s="1" t="n">
+      <c r="N89" s="1" t="n">
         <v>8.257</v>
       </c>
     </row>
@@ -4322,9 +4592,12 @@
         <v>0.005958</v>
       </c>
       <c r="L90" s="1" t="n">
+        <v>0.00594</v>
+      </c>
+      <c r="M90" s="1" t="n">
         <v>0.005958</v>
       </c>
-      <c r="M90" s="1" t="n">
+      <c r="N90" s="1" t="n">
         <v>0.005905</v>
       </c>
     </row>
@@ -4365,9 +4638,12 @@
         <v>0.06908</v>
       </c>
       <c r="L91" s="1" t="n">
+        <v>0.06845999999999999</v>
+      </c>
+      <c r="M91" s="1" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="M91" s="1" t="n">
+      <c r="N91" s="1" t="n">
         <v>0.06812</v>
       </c>
     </row>
@@ -4408,10 +4684,13 @@
         <v>0.02869</v>
       </c>
       <c r="L92" s="1" t="n">
+        <v>0.02851</v>
+      </c>
+      <c r="M92" s="1" t="n">
         <v>0.02905</v>
       </c>
-      <c r="M92" s="1" t="n">
-        <v>0.02866</v>
+      <c r="N92" s="1" t="n">
+        <v>0.02851</v>
       </c>
     </row>
     <row r="93">
@@ -4451,9 +4730,12 @@
         <v>5.188</v>
       </c>
       <c r="L93" s="1" t="n">
+        <v>5.173</v>
+      </c>
+      <c r="M93" s="1" t="n">
         <v>5.228</v>
       </c>
-      <c r="M93" s="1" t="n">
+      <c r="N93" s="1" t="n">
         <v>5.159</v>
       </c>
     </row>
@@ -4494,9 +4776,12 @@
         <v>0.000225</v>
       </c>
       <c r="L94" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="M94" s="1" t="n">
         <v>0.000228</v>
       </c>
-      <c r="M94" s="1" t="n">
+      <c r="N94" s="1" t="n">
         <v>0.000225</v>
       </c>
     </row>
@@ -4537,9 +4822,12 @@
         <v>0.9278999999999999</v>
       </c>
       <c r="L95" s="1" t="n">
+        <v>0.9248</v>
+      </c>
+      <c r="M95" s="1" t="n">
         <v>0.9278999999999999</v>
       </c>
-      <c r="M95" s="1" t="n">
+      <c r="N95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -4580,9 +4868,12 @@
         <v>2.145</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>2.145</v>
+        <v>2.1985</v>
       </c>
       <c r="M96" s="1" t="n">
+        <v>2.1985</v>
+      </c>
+      <c r="N96" s="1" t="n">
         <v>2.0598</v>
       </c>
     </row>
@@ -4623,10 +4914,13 @@
         <v>0.37</v>
       </c>
       <c r="L97" s="1" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="M97" s="1" t="n">
         <v>0.3722</v>
       </c>
-      <c r="M97" s="1" t="n">
-        <v>0.3681</v>
+      <c r="N97" s="1" t="n">
+        <v>0.3675</v>
       </c>
     </row>
     <row r="98">
@@ -4666,9 +4960,12 @@
         <v>1.617</v>
       </c>
       <c r="L98" s="1" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="M98" s="1" t="n">
         <v>1.625</v>
       </c>
-      <c r="M98" s="1" t="n">
+      <c r="N98" s="1" t="n">
         <v>1.613</v>
       </c>
     </row>
@@ -4709,10 +5006,13 @@
         <v>0.2316</v>
       </c>
       <c r="L99" s="1" t="n">
+        <v>0.2314</v>
+      </c>
+      <c r="M99" s="1" t="n">
         <v>0.2368</v>
       </c>
-      <c r="M99" s="1" t="n">
-        <v>0.2316</v>
+      <c r="N99" s="1" t="n">
+        <v>0.2314</v>
       </c>
     </row>
     <row r="100">
@@ -4752,9 +5052,12 @@
         <v>0.13748</v>
       </c>
       <c r="L100" s="1" t="n">
+        <v>0.1367</v>
+      </c>
+      <c r="M100" s="1" t="n">
         <v>0.13748</v>
       </c>
-      <c r="M100" s="1" t="n">
+      <c r="N100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -4795,9 +5098,12 @@
         <v>0.06927</v>
       </c>
       <c r="L101" s="1" t="n">
+        <v>0.06920999999999999</v>
+      </c>
+      <c r="M101" s="1" t="n">
         <v>0.07115</v>
       </c>
-      <c r="M101" s="1" t="n">
+      <c r="N101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -4838,9 +5144,12 @@
         <v>0.0010859</v>
       </c>
       <c r="L102" s="1" t="n">
+        <v>0.0010838</v>
+      </c>
+      <c r="M102" s="1" t="n">
         <v>0.0010886</v>
       </c>
-      <c r="M102" s="1" t="n">
+      <c r="N102" s="1" t="n">
         <v>0.0010822</v>
       </c>
     </row>
@@ -4881,9 +5190,12 @@
         <v>0.003422</v>
       </c>
       <c r="L103" s="1" t="n">
+        <v>0.003419</v>
+      </c>
+      <c r="M103" s="1" t="n">
         <v>0.003427</v>
       </c>
-      <c r="M103" s="1" t="n">
+      <c r="N103" s="1" t="n">
         <v>0.003403</v>
       </c>
     </row>
@@ -4924,9 +5236,12 @@
         <v>0.27345</v>
       </c>
       <c r="L104" s="1" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="M104" s="1" t="n">
         <v>0.27751</v>
       </c>
-      <c r="M104" s="1" t="n">
+      <c r="N104" s="1" t="n">
         <v>0.27312</v>
       </c>
     </row>
@@ -4967,9 +5282,12 @@
         <v>0.01254</v>
       </c>
       <c r="L105" s="1" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="M105" s="1" t="n">
         <v>0.01257</v>
       </c>
-      <c r="M105" s="1" t="n">
+      <c r="N105" s="1" t="n">
         <v>0.01243</v>
       </c>
     </row>
@@ -5010,9 +5328,12 @@
         <v>0.13586</v>
       </c>
       <c r="L106" s="1" t="n">
-        <v>0.13586</v>
+        <v>0.13615</v>
       </c>
       <c r="M106" s="1" t="n">
+        <v>0.13615</v>
+      </c>
+      <c r="N106" s="1" t="n">
         <v>0.13329</v>
       </c>
     </row>
@@ -5053,9 +5374,12 @@
         <v>0.3521</v>
       </c>
       <c r="L107" s="1" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="M107" s="1" t="n">
         <v>0.3522</v>
       </c>
-      <c r="M107" s="1" t="n">
+      <c r="N107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -5096,9 +5420,12 @@
         <v>0.1413</v>
       </c>
       <c r="L108" s="1" t="n">
+        <v>0.1413</v>
+      </c>
+      <c r="M108" s="1" t="n">
         <v>0.1436</v>
       </c>
-      <c r="M108" s="1" t="n">
+      <c r="N108" s="1" t="n">
         <v>0.1413</v>
       </c>
     </row>
@@ -5142,6 +5469,9 @@
         <v>0.9360000000000001</v>
       </c>
       <c r="M109" s="1" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="N109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -5182,9 +5512,12 @@
         <v>0.016242</v>
       </c>
       <c r="L110" s="1" t="n">
+        <v>0.016207</v>
+      </c>
+      <c r="M110" s="1" t="n">
         <v>0.016308</v>
       </c>
-      <c r="M110" s="1" t="n">
+      <c r="N110" s="1" t="n">
         <v>0.016195</v>
       </c>
     </row>
@@ -5225,9 +5558,12 @@
         <v>0.038821</v>
       </c>
       <c r="L111" s="1" t="n">
-        <v>0.038821</v>
+        <v>0.038973</v>
       </c>
       <c r="M111" s="1" t="n">
+        <v>0.038973</v>
+      </c>
+      <c r="N111" s="1" t="n">
         <v>0.03774</v>
       </c>
     </row>
@@ -5268,9 +5604,12 @@
         <v>0.11994</v>
       </c>
       <c r="L112" s="1" t="n">
+        <v>0.11996</v>
+      </c>
+      <c r="M112" s="1" t="n">
         <v>0.12031</v>
       </c>
-      <c r="M112" s="1" t="n">
+      <c r="N112" s="1" t="n">
         <v>0.11926</v>
       </c>
     </row>
@@ -5311,9 +5650,12 @@
         <v>0.09342</v>
       </c>
       <c r="L113" s="1" t="n">
+        <v>0.09352000000000001</v>
+      </c>
+      <c r="M113" s="1" t="n">
         <v>0.09574000000000001</v>
       </c>
-      <c r="M113" s="1" t="n">
+      <c r="N113" s="1" t="n">
         <v>0.09342</v>
       </c>
     </row>
@@ -5354,9 +5696,12 @@
         <v>0.13016</v>
       </c>
       <c r="L114" s="1" t="n">
+        <v>0.12997</v>
+      </c>
+      <c r="M114" s="1" t="n">
         <v>0.13063</v>
       </c>
-      <c r="M114" s="1" t="n">
+      <c r="N114" s="1" t="n">
         <v>0.12895</v>
       </c>
     </row>
@@ -5397,9 +5742,12 @@
         <v>0.2661</v>
       </c>
       <c r="L115" s="1" t="n">
+        <v>0.2656</v>
+      </c>
+      <c r="M115" s="1" t="n">
         <v>0.2663</v>
       </c>
-      <c r="M115" s="1" t="n">
+      <c r="N115" s="1" t="n">
         <v>0.2638</v>
       </c>
     </row>
@@ -5440,9 +5788,12 @@
         <v>0.04855</v>
       </c>
       <c r="L116" s="1" t="n">
+        <v>0.04814</v>
+      </c>
+      <c r="M116" s="1" t="n">
         <v>0.0529</v>
       </c>
-      <c r="M116" s="1" t="n">
+      <c r="N116" s="1" t="n">
         <v>0.04805</v>
       </c>
     </row>
@@ -5483,9 +5834,12 @@
         <v>0.0915</v>
       </c>
       <c r="L117" s="1" t="n">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="M117" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="M117" s="1" t="n">
+      <c r="N117" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -5526,9 +5880,12 @@
         <v>0.05566</v>
       </c>
       <c r="L118" s="1" t="n">
-        <v>0.05566</v>
+        <v>0.05573</v>
       </c>
       <c r="M118" s="1" t="n">
+        <v>0.05573</v>
+      </c>
+      <c r="N118" s="1" t="n">
         <v>0.05501</v>
       </c>
     </row>
@@ -5569,9 +5926,12 @@
         <v>0.01513</v>
       </c>
       <c r="L119" s="1" t="n">
+        <v>0.01509</v>
+      </c>
+      <c r="M119" s="1" t="n">
         <v>0.01515</v>
       </c>
-      <c r="M119" s="1" t="n">
+      <c r="N119" s="1" t="n">
         <v>0.01505</v>
       </c>
     </row>
@@ -5612,9 +5972,12 @@
         <v>3.078</v>
       </c>
       <c r="L120" s="1" t="n">
+        <v>3.072</v>
+      </c>
+      <c r="M120" s="1" t="n">
         <v>3.079</v>
       </c>
-      <c r="M120" s="1" t="n">
+      <c r="N120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -5655,9 +6018,12 @@
         <v>1.851</v>
       </c>
       <c r="L121" s="1" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M121" s="1" t="n">
         <v>1.855</v>
       </c>
-      <c r="M121" s="1" t="n">
+      <c r="N121" s="1" t="n">
         <v>1.848</v>
       </c>
     </row>
@@ -5698,9 +6064,12 @@
         <v>1.3019</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>1.3028</v>
+        <v>1.3042</v>
       </c>
       <c r="M122" s="1" t="n">
+        <v>1.3042</v>
+      </c>
+      <c r="N122" s="1" t="n">
         <v>1.2934</v>
       </c>
     </row>
@@ -5741,9 +6110,12 @@
         <v>0.318</v>
       </c>
       <c r="L123" s="1" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="M123" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="M123" s="1" t="n">
+      <c r="N123" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -5784,9 +6156,12 @@
         <v>0.12601</v>
       </c>
       <c r="L124" s="1" t="n">
+        <v>0.12501</v>
+      </c>
+      <c r="M124" s="1" t="n">
         <v>0.12601</v>
       </c>
-      <c r="M124" s="1" t="n">
+      <c r="N124" s="1" t="n">
         <v>0.12202</v>
       </c>
     </row>
@@ -5827,9 +6202,12 @@
         <v>0.008567999999999999</v>
       </c>
       <c r="L125" s="1" t="n">
+        <v>0.008540000000000001</v>
+      </c>
+      <c r="M125" s="1" t="n">
         <v>0.008626999999999999</v>
       </c>
-      <c r="M125" s="1" t="n">
+      <c r="N125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -5873,6 +6251,9 @@
         <v>0.01622</v>
       </c>
       <c r="M126" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="N126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -5913,9 +6294,12 @@
         <v>0.04425</v>
       </c>
       <c r="L127" s="1" t="n">
+        <v>0.04414</v>
+      </c>
+      <c r="M127" s="1" t="n">
         <v>0.04468</v>
       </c>
-      <c r="M127" s="1" t="n">
+      <c r="N127" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -5956,9 +6340,12 @@
         <v>0.04674</v>
       </c>
       <c r="L128" s="1" t="n">
+        <v>0.04689</v>
+      </c>
+      <c r="M128" s="1" t="n">
         <v>0.04727</v>
       </c>
-      <c r="M128" s="1" t="n">
+      <c r="N128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -5999,9 +6386,12 @@
         <v>0.09673</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>0.09673</v>
+        <v>0.09680999999999999</v>
       </c>
       <c r="M129" s="1" t="n">
+        <v>0.09680999999999999</v>
+      </c>
+      <c r="N129" s="1" t="n">
         <v>0.09543</v>
       </c>
     </row>
@@ -6042,9 +6432,12 @@
         <v>0.09875</v>
       </c>
       <c r="L130" s="1" t="n">
+        <v>0.09915</v>
+      </c>
+      <c r="M130" s="1" t="n">
         <v>0.09927</v>
       </c>
-      <c r="M130" s="1" t="n">
+      <c r="N130" s="1" t="n">
         <v>0.09848</v>
       </c>
     </row>
@@ -6085,9 +6478,12 @@
         <v>0.16707</v>
       </c>
       <c r="L131" s="1" t="n">
+        <v>0.16705</v>
+      </c>
+      <c r="M131" s="1" t="n">
         <v>0.16707</v>
       </c>
-      <c r="M131" s="1" t="n">
+      <c r="N131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -6128,9 +6524,12 @@
         <v>0.01698</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>0.01702</v>
+        <v>0.01708</v>
       </c>
       <c r="M132" s="1" t="n">
+        <v>0.01708</v>
+      </c>
+      <c r="N132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -6171,9 +6570,12 @@
         <v>0.06714000000000001</v>
       </c>
       <c r="L133" s="1" t="n">
+        <v>0.06707</v>
+      </c>
+      <c r="M133" s="1" t="n">
         <v>0.06714000000000001</v>
       </c>
-      <c r="M133" s="1" t="n">
+      <c r="N133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -6214,9 +6616,12 @@
         <v>0.3043</v>
       </c>
       <c r="L134" s="1" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="M134" s="1" t="n">
         <v>0.3043</v>
       </c>
-      <c r="M134" s="1" t="n">
+      <c r="N134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -6257,9 +6662,12 @@
         <v>0.04537</v>
       </c>
       <c r="L135" s="1" t="n">
+        <v>0.04533</v>
+      </c>
+      <c r="M135" s="1" t="n">
         <v>0.04563</v>
       </c>
-      <c r="M135" s="1" t="n">
+      <c r="N135" s="1" t="n">
         <v>0.04502</v>
       </c>
     </row>
@@ -6303,6 +6711,9 @@
         <v>0.783</v>
       </c>
       <c r="M136" s="1" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="N136" s="1" t="n">
         <v>0.781</v>
       </c>
     </row>
@@ -6343,9 +6754,12 @@
         <v>0.1181</v>
       </c>
       <c r="L137" s="1" t="n">
+        <v>0.1174</v>
+      </c>
+      <c r="M137" s="1" t="n">
         <v>0.1181</v>
       </c>
-      <c r="M137" s="1" t="n">
+      <c r="N137" s="1" t="n">
         <v>0.1162</v>
       </c>
     </row>
@@ -6386,9 +6800,12 @@
         <v>0.14787</v>
       </c>
       <c r="L138" s="1" t="n">
+        <v>0.14776</v>
+      </c>
+      <c r="M138" s="1" t="n">
         <v>0.14787</v>
       </c>
-      <c r="M138" s="1" t="n">
+      <c r="N138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -6429,9 +6846,12 @@
         <v>0.05776</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>0.05776</v>
+        <v>0.05781</v>
       </c>
       <c r="M139" s="1" t="n">
+        <v>0.05781</v>
+      </c>
+      <c r="N139" s="1" t="n">
         <v>0.05699</v>
       </c>
     </row>
@@ -6472,9 +6892,12 @@
         <v>0.007293</v>
       </c>
       <c r="L140" s="1" t="n">
+        <v>0.007283</v>
+      </c>
+      <c r="M140" s="1" t="n">
         <v>0.007302</v>
       </c>
-      <c r="M140" s="1" t="n">
+      <c r="N140" s="1" t="n">
         <v>0.00726</v>
       </c>
     </row>
@@ -6515,9 +6938,12 @@
         <v>0.09624000000000001</v>
       </c>
       <c r="L141" s="1" t="n">
+        <v>0.09625</v>
+      </c>
+      <c r="M141" s="1" t="n">
         <v>0.09637</v>
       </c>
-      <c r="M141" s="1" t="n">
+      <c r="N141" s="1" t="n">
         <v>0.09569</v>
       </c>
     </row>
@@ -6558,9 +6984,12 @@
         <v>0.0839</v>
       </c>
       <c r="L142" s="1" t="n">
+        <v>0.08384999999999999</v>
+      </c>
+      <c r="M142" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="M142" s="1" t="n">
+      <c r="N142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -6601,9 +7030,12 @@
         <v>0.008529999999999999</v>
       </c>
       <c r="L143" s="1" t="n">
+        <v>0.00848</v>
+      </c>
+      <c r="M143" s="1" t="n">
         <v>0.00861</v>
       </c>
-      <c r="M143" s="1" t="n">
+      <c r="N143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -6644,9 +7076,12 @@
         <v>0.07260999999999999</v>
       </c>
       <c r="L144" s="1" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="M144" s="1" t="n">
         <v>0.07288</v>
       </c>
-      <c r="M144" s="1" t="n">
+      <c r="N144" s="1" t="n">
         <v>0.07224999999999999</v>
       </c>
     </row>
@@ -6687,10 +7122,13 @@
         <v>0.4258</v>
       </c>
       <c r="L145" s="1" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="M145" s="1" t="n">
         <v>0.4305</v>
       </c>
-      <c r="M145" s="1" t="n">
-        <v>0.4258</v>
+      <c r="N145" s="1" t="n">
+        <v>0.425</v>
       </c>
     </row>
     <row r="146">
@@ -6730,9 +7168,12 @@
         <v>0.03237</v>
       </c>
       <c r="L146" s="1" t="n">
+        <v>0.03235</v>
+      </c>
+      <c r="M146" s="1" t="n">
         <v>0.03276</v>
       </c>
-      <c r="M146" s="1" t="n">
+      <c r="N146" s="1" t="n">
         <v>0.0322</v>
       </c>
     </row>
@@ -6773,9 +7214,12 @@
         <v>390.55</v>
       </c>
       <c r="L147" s="1" t="n">
+        <v>390.54</v>
+      </c>
+      <c r="M147" s="1" t="n">
         <v>390.55</v>
       </c>
-      <c r="M147" s="1" t="n">
+      <c r="N147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -6816,9 +7260,12 @@
         <v>0.03291</v>
       </c>
       <c r="L148" s="1" t="n">
+        <v>0.03292</v>
+      </c>
+      <c r="M148" s="1" t="n">
         <v>0.0333</v>
       </c>
-      <c r="M148" s="1" t="n">
+      <c r="N148" s="1" t="n">
         <v>0.0329</v>
       </c>
     </row>
@@ -6859,9 +7306,12 @@
         <v>0.05316</v>
       </c>
       <c r="L149" s="1" t="n">
+        <v>0.05294</v>
+      </c>
+      <c r="M149" s="1" t="n">
         <v>0.05322</v>
       </c>
-      <c r="M149" s="1" t="n">
+      <c r="N149" s="1" t="n">
         <v>0.05289</v>
       </c>
     </row>
@@ -6902,10 +7352,13 @@
         <v>0.0004398</v>
       </c>
       <c r="L150" s="1" t="n">
+        <v>0.0004383</v>
+      </c>
+      <c r="M150" s="1" t="n">
         <v>0.000443</v>
       </c>
-      <c r="M150" s="1" t="n">
-        <v>0.000439</v>
+      <c r="N150" s="1" t="n">
+        <v>0.0004383</v>
       </c>
     </row>
     <row r="151">
@@ -6945,9 +7398,12 @@
         <v>0.02197</v>
       </c>
       <c r="L151" s="1" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="M151" s="1" t="n">
         <v>0.02197</v>
       </c>
-      <c r="M151" s="1" t="n">
+      <c r="N151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -6988,9 +7444,12 @@
         <v>0.001793</v>
       </c>
       <c r="L152" s="1" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="M152" s="1" t="n">
         <v>0.001793</v>
       </c>
-      <c r="M152" s="1" t="n">
+      <c r="N152" s="1" t="n">
         <v>0.001768</v>
       </c>
     </row>
@@ -7031,9 +7490,12 @@
         <v>6e-06</v>
       </c>
       <c r="L153" s="1" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="M153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
-      <c r="M153" s="1" t="n">
+      <c r="N153" s="1" t="n">
         <v>6e-06</v>
       </c>
     </row>
@@ -7074,9 +7536,12 @@
         <v>0.1607</v>
       </c>
       <c r="L154" s="1" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="M154" s="1" t="n">
         <v>0.1609</v>
       </c>
-      <c r="M154" s="1" t="n">
+      <c r="N154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -7117,9 +7582,12 @@
         <v>0.03778</v>
       </c>
       <c r="L155" s="1" t="n">
+        <v>0.03777</v>
+      </c>
+      <c r="M155" s="1" t="n">
         <v>0.03781</v>
       </c>
-      <c r="M155" s="1" t="n">
+      <c r="N155" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -7160,9 +7628,12 @@
         <v>0.005402</v>
       </c>
       <c r="L156" s="1" t="n">
+        <v>0.005399</v>
+      </c>
+      <c r="M156" s="1" t="n">
         <v>0.005404</v>
       </c>
-      <c r="M156" s="1" t="n">
+      <c r="N156" s="1" t="n">
         <v>0.005364</v>
       </c>
     </row>
@@ -7203,9 +7674,12 @@
         <v>0.02284</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>0.02284</v>
+        <v>0.02294</v>
       </c>
       <c r="M157" s="1" t="n">
+        <v>0.02294</v>
+      </c>
+      <c r="N157" s="1" t="n">
         <v>0.02263</v>
       </c>
     </row>
@@ -7249,6 +7723,9 @@
         <v>1.099</v>
       </c>
       <c r="M158" s="1" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="N158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -7289,9 +7766,12 @@
         <v>2.574</v>
       </c>
       <c r="L159" s="1" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M159" s="1" t="n">
         <v>2.577</v>
       </c>
-      <c r="M159" s="1" t="n">
+      <c r="N159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -7332,9 +7812,12 @@
         <v>4.847</v>
       </c>
       <c r="L160" s="1" t="n">
+        <v>4.845</v>
+      </c>
+      <c r="M160" s="1" t="n">
         <v>4.858</v>
       </c>
-      <c r="M160" s="1" t="n">
+      <c r="N160" s="1" t="n">
         <v>4.836</v>
       </c>
     </row>
@@ -7375,9 +7858,12 @@
         <v>0.1608</v>
       </c>
       <c r="L161" s="1" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="M161" s="1" t="n">
         <v>0.1608</v>
       </c>
-      <c r="M161" s="1" t="n">
+      <c r="N161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -7418,9 +7904,12 @@
         <v>0.20494</v>
       </c>
       <c r="L162" s="1" t="n">
+        <v>0.2045</v>
+      </c>
+      <c r="M162" s="1" t="n">
         <v>0.20754</v>
       </c>
-      <c r="M162" s="1" t="n">
+      <c r="N162" s="1" t="n">
         <v>0.20425</v>
       </c>
     </row>
@@ -7461,9 +7950,12 @@
         <v>0.03955</v>
       </c>
       <c r="L163" s="1" t="n">
+        <v>0.03948</v>
+      </c>
+      <c r="M163" s="1" t="n">
         <v>0.03955</v>
       </c>
-      <c r="M163" s="1" t="n">
+      <c r="N163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -7504,9 +7996,12 @@
         <v>0.06317</v>
       </c>
       <c r="L164" s="1" t="n">
+        <v>0.06336</v>
+      </c>
+      <c r="M164" s="1" t="n">
         <v>0.0636</v>
       </c>
-      <c r="M164" s="1" t="n">
+      <c r="N164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -7547,9 +8042,12 @@
         <v>0.3658</v>
       </c>
       <c r="L165" s="1" t="n">
-        <v>0.3658</v>
+        <v>0.3667</v>
       </c>
       <c r="M165" s="1" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="N165" s="1" t="n">
         <v>0.3525</v>
       </c>
     </row>
@@ -7590,9 +8088,12 @@
         <v>139.47</v>
       </c>
       <c r="L166" s="1" t="n">
+        <v>139.47</v>
+      </c>
+      <c r="M166" s="1" t="n">
         <v>139.63</v>
       </c>
-      <c r="M166" s="1" t="n">
+      <c r="N166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -7633,9 +8134,12 @@
         <v>0.0006419</v>
       </c>
       <c r="L167" s="1" t="n">
+        <v>0.0006454</v>
+      </c>
+      <c r="M167" s="1" t="n">
         <v>0.0006533</v>
       </c>
-      <c r="M167" s="1" t="n">
+      <c r="N167" s="1" t="n">
         <v>0.0006419</v>
       </c>
     </row>
@@ -7676,9 +8180,12 @@
         <v>0.0167</v>
       </c>
       <c r="L168" s="1" t="n">
+        <v>0.01664</v>
+      </c>
+      <c r="M168" s="1" t="n">
         <v>0.01678</v>
       </c>
-      <c r="M168" s="1" t="n">
+      <c r="N168" s="1" t="n">
         <v>0.01629</v>
       </c>
     </row>
@@ -7719,9 +8226,12 @@
         <v>0.04823</v>
       </c>
       <c r="L169" s="1" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="M169" s="1" t="n">
         <v>0.04823</v>
       </c>
-      <c r="M169" s="1" t="n">
+      <c r="N169" s="1" t="n">
         <v>0.04785</v>
       </c>
     </row>
@@ -7762,9 +8272,12 @@
         <v>4.278</v>
       </c>
       <c r="L170" s="1" t="n">
+        <v>4.274</v>
+      </c>
+      <c r="M170" s="1" t="n">
         <v>4.298</v>
       </c>
-      <c r="M170" s="1" t="n">
+      <c r="N170" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -7805,9 +8318,12 @@
         <v>0.03874</v>
       </c>
       <c r="L171" s="1" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="M171" s="1" t="n">
         <v>0.03875</v>
       </c>
-      <c r="M171" s="1" t="n">
+      <c r="N171" s="1" t="n">
         <v>0.03825</v>
       </c>
     </row>
@@ -7848,9 +8364,12 @@
         <v>0.043</v>
       </c>
       <c r="L172" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="M172" s="1" t="n">
         <v>0.0431</v>
       </c>
-      <c r="M172" s="1" t="n">
+      <c r="N172" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -7891,10 +8410,13 @@
         <v>0.023721</v>
       </c>
       <c r="L173" s="1" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="M173" s="1" t="n">
         <v>0.024556</v>
       </c>
-      <c r="M173" s="1" t="n">
-        <v>0.023721</v>
+      <c r="N173" s="1" t="n">
+        <v>0.02354</v>
       </c>
     </row>
     <row r="174">
@@ -7934,9 +8456,12 @@
         <v>1.0788</v>
       </c>
       <c r="L174" s="1" t="n">
+        <v>1.0804</v>
+      </c>
+      <c r="M174" s="1" t="n">
         <v>1.0809</v>
       </c>
-      <c r="M174" s="1" t="n">
+      <c r="N174" s="1" t="n">
         <v>1.0704</v>
       </c>
     </row>
@@ -7977,10 +8502,13 @@
         <v>0.028071</v>
       </c>
       <c r="L175" s="1" t="n">
+        <v>0.028008</v>
+      </c>
+      <c r="M175" s="1" t="n">
         <v>0.028967</v>
       </c>
-      <c r="M175" s="1" t="n">
-        <v>0.028034</v>
+      <c r="N175" s="1" t="n">
+        <v>0.028008</v>
       </c>
     </row>
     <row r="176">
@@ -8020,9 +8548,12 @@
         <v>0.02215</v>
       </c>
       <c r="L176" s="1" t="n">
+        <v>0.02214</v>
+      </c>
+      <c r="M176" s="1" t="n">
         <v>0.02215</v>
       </c>
-      <c r="M176" s="1" t="n">
+      <c r="N176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -8063,9 +8594,12 @@
         <v>0.5488</v>
       </c>
       <c r="L177" s="1" t="n">
-        <v>0.5501</v>
+        <v>0.5502</v>
       </c>
       <c r="M177" s="1" t="n">
+        <v>0.5502</v>
+      </c>
+      <c r="N177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -8106,10 +8640,13 @@
         <v>0.08219</v>
       </c>
       <c r="L178" s="1" t="n">
+        <v>0.08202</v>
+      </c>
+      <c r="M178" s="1" t="n">
         <v>0.08276</v>
       </c>
-      <c r="M178" s="1" t="n">
-        <v>0.08214</v>
+      <c r="N178" s="1" t="n">
+        <v>0.08202</v>
       </c>
     </row>
     <row r="179">
@@ -8149,9 +8686,12 @@
         <v>0.02141</v>
       </c>
       <c r="L179" s="1" t="n">
+        <v>0.02139</v>
+      </c>
+      <c r="M179" s="1" t="n">
         <v>0.02142</v>
       </c>
-      <c r="M179" s="1" t="n">
+      <c r="N179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -8192,9 +8732,12 @@
         <v>0.27438</v>
       </c>
       <c r="L180" s="1" t="n">
-        <v>0.27438</v>
+        <v>0.27464</v>
       </c>
       <c r="M180" s="1" t="n">
+        <v>0.27464</v>
+      </c>
+      <c r="N180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -8235,9 +8778,12 @@
         <v>0.00421</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>0.00421</v>
+        <v>0.00422</v>
       </c>
       <c r="M181" s="1" t="n">
+        <v>0.00422</v>
+      </c>
+      <c r="N181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -8278,9 +8824,12 @@
         <v>0.07901</v>
       </c>
       <c r="L182" s="1" t="n">
+        <v>0.07906000000000001</v>
+      </c>
+      <c r="M182" s="1" t="n">
         <v>0.07981000000000001</v>
       </c>
-      <c r="M182" s="1" t="n">
+      <c r="N182" s="1" t="n">
         <v>0.07901</v>
       </c>
     </row>
@@ -8321,9 +8870,12 @@
         <v>0.02361</v>
       </c>
       <c r="L183" s="1" t="n">
-        <v>0.02364</v>
+        <v>0.02369</v>
       </c>
       <c r="M183" s="1" t="n">
+        <v>0.02369</v>
+      </c>
+      <c r="N183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -8364,9 +8916,12 @@
         <v>7.015e-05</v>
       </c>
       <c r="L184" s="1" t="n">
+        <v>6.989e-05</v>
+      </c>
+      <c r="M184" s="1" t="n">
         <v>7.016000000000001e-05</v>
       </c>
-      <c r="M184" s="1" t="n">
+      <c r="N184" s="1" t="n">
         <v>6.957e-05</v>
       </c>
     </row>
@@ -8407,9 +8962,12 @@
         <v>0.02135</v>
       </c>
       <c r="L185" s="1" t="n">
+        <v>0.02136</v>
+      </c>
+      <c r="M185" s="1" t="n">
         <v>0.0214</v>
       </c>
-      <c r="M185" s="1" t="n">
+      <c r="N185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -8450,9 +9008,12 @@
         <v>0.01644</v>
       </c>
       <c r="L186" s="1" t="n">
+        <v>0.01642</v>
+      </c>
+      <c r="M186" s="1" t="n">
         <v>0.01644</v>
       </c>
-      <c r="M186" s="1" t="n">
+      <c r="N186" s="1" t="n">
         <v>0.01623</v>
       </c>
     </row>
@@ -8493,9 +9054,12 @@
         <v>0.978</v>
       </c>
       <c r="L187" s="1" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="M187" s="1" t="n">
         <v>0.981</v>
       </c>
-      <c r="M187" s="1" t="n">
+      <c r="N187" s="1" t="n">
         <v>0.971</v>
       </c>
     </row>
@@ -8536,9 +9100,12 @@
         <v>0.0239</v>
       </c>
       <c r="L188" s="1" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="M188" s="1" t="n">
         <v>0.024</v>
       </c>
-      <c r="M188" s="1" t="n">
+      <c r="N188" s="1" t="n">
         <v>0.0237</v>
       </c>
     </row>
@@ -8579,9 +9146,12 @@
         <v>1.886</v>
       </c>
       <c r="L189" s="1" t="n">
+        <v>1.8863</v>
+      </c>
+      <c r="M189" s="1" t="n">
         <v>1.8888</v>
       </c>
-      <c r="M189" s="1" t="n">
+      <c r="N189" s="1" t="n">
         <v>1.8609</v>
       </c>
     </row>
@@ -8622,9 +9192,12 @@
         <v>1.844</v>
       </c>
       <c r="L190" s="1" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M190" s="1" t="n">
         <v>1.844</v>
       </c>
-      <c r="M190" s="1" t="n">
+      <c r="N190" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -8665,9 +9238,12 @@
         <v>0.02678</v>
       </c>
       <c r="L191" s="1" t="n">
+        <v>0.02677</v>
+      </c>
+      <c r="M191" s="1" t="n">
         <v>0.02685</v>
       </c>
-      <c r="M191" s="1" t="n">
+      <c r="N191" s="1" t="n">
         <v>0.02662</v>
       </c>
     </row>
@@ -8708,9 +9284,12 @@
         <v>0.0974</v>
       </c>
       <c r="L192" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="M192" s="1" t="n">
         <v>0.0975</v>
       </c>
-      <c r="M192" s="1" t="n">
+      <c r="N192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -8751,9 +9330,12 @@
         <v>0.1717</v>
       </c>
       <c r="L193" s="1" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="M193" s="1" t="n">
         <v>0.1722</v>
       </c>
-      <c r="M193" s="1" t="n">
+      <c r="N193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -8794,9 +9376,12 @@
         <v>16.37</v>
       </c>
       <c r="L194" s="1" t="n">
+        <v>16.352</v>
+      </c>
+      <c r="M194" s="1" t="n">
         <v>16.407</v>
       </c>
-      <c r="M194" s="1" t="n">
+      <c r="N194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -8837,9 +9422,12 @@
         <v>4.123</v>
       </c>
       <c r="L195" s="1" t="n">
+        <v>4.109</v>
+      </c>
+      <c r="M195" s="1" t="n">
         <v>4.136</v>
       </c>
-      <c r="M195" s="1" t="n">
+      <c r="N195" s="1" t="n">
         <v>4.087</v>
       </c>
     </row>
@@ -8880,9 +9468,12 @@
         <v>1.2747</v>
       </c>
       <c r="L196" s="1" t="n">
+        <v>1.2751</v>
+      </c>
+      <c r="M196" s="1" t="n">
         <v>1.2794</v>
       </c>
-      <c r="M196" s="1" t="n">
+      <c r="N196" s="1" t="n">
         <v>1.2663</v>
       </c>
     </row>
@@ -8923,9 +9514,12 @@
         <v>3.091</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>3.092</v>
+        <v>3.108</v>
       </c>
       <c r="M197" s="1" t="n">
+        <v>3.108</v>
+      </c>
+      <c r="N197" s="1" t="n">
         <v>3.063</v>
       </c>
     </row>
@@ -8966,9 +9560,12 @@
         <v>0.01261</v>
       </c>
       <c r="L198" s="1" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="M198" s="1" t="n">
         <v>0.01266</v>
       </c>
-      <c r="M198" s="1" t="n">
+      <c r="N198" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -9009,9 +9606,12 @@
         <v>0.0001768</v>
       </c>
       <c r="L199" s="1" t="n">
+        <v>0.0001766</v>
+      </c>
+      <c r="M199" s="1" t="n">
         <v>0.000177</v>
       </c>
-      <c r="M199" s="1" t="n">
+      <c r="N199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -9052,9 +9652,12 @@
         <v>115.82</v>
       </c>
       <c r="L200" s="1" t="n">
-        <v>115.82</v>
+        <v>115.85</v>
       </c>
       <c r="M200" s="1" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="N200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -9095,9 +9698,12 @@
         <v>0.0102</v>
       </c>
       <c r="L201" s="1" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="M201" s="1" t="n">
         <v>0.01031</v>
       </c>
-      <c r="M201" s="1" t="n">
+      <c r="N201" s="1" t="n">
         <v>0.0102</v>
       </c>
     </row>
@@ -9138,9 +9744,12 @@
         <v>0.01069</v>
       </c>
       <c r="L202" s="1" t="n">
+        <v>0.01067</v>
+      </c>
+      <c r="M202" s="1" t="n">
         <v>0.01073</v>
       </c>
-      <c r="M202" s="1" t="n">
+      <c r="N202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -9181,9 +9790,12 @@
         <v>0.003141</v>
       </c>
       <c r="L203" s="1" t="n">
+        <v>0.003138</v>
+      </c>
+      <c r="M203" s="1" t="n">
         <v>0.003153</v>
       </c>
-      <c r="M203" s="1" t="n">
+      <c r="N203" s="1" t="n">
         <v>0.003131</v>
       </c>
     </row>
@@ -9224,9 +9836,12 @@
         <v>28.33</v>
       </c>
       <c r="L204" s="1" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="M204" s="1" t="n">
         <v>28.39</v>
       </c>
-      <c r="M204" s="1" t="n">
+      <c r="N204" s="1" t="n">
         <v>28.23</v>
       </c>
     </row>
@@ -9267,9 +9882,12 @@
         <v>0.5578</v>
       </c>
       <c r="L205" s="1" t="n">
+        <v>0.5582</v>
+      </c>
+      <c r="M205" s="1" t="n">
         <v>0.5636</v>
       </c>
-      <c r="M205" s="1" t="n">
+      <c r="N205" s="1" t="n">
         <v>0.5578</v>
       </c>
     </row>
@@ -9310,9 +9928,12 @@
         <v>0.0004438</v>
       </c>
       <c r="L206" s="1" t="n">
+        <v>0.0004424</v>
+      </c>
+      <c r="M206" s="1" t="n">
         <v>0.0004438</v>
       </c>
-      <c r="M206" s="1" t="n">
+      <c r="N206" s="1" t="n">
         <v>0.0004387</v>
       </c>
     </row>
@@ -9353,9 +9974,12 @@
         <v>0.04684</v>
       </c>
       <c r="L207" s="1" t="n">
+        <v>0.04675</v>
+      </c>
+      <c r="M207" s="1" t="n">
         <v>0.04689</v>
       </c>
-      <c r="M207" s="1" t="n">
+      <c r="N207" s="1" t="n">
         <v>0.04648</v>
       </c>
     </row>
@@ -9399,6 +10023,9 @@
         <v>0.091</v>
       </c>
       <c r="M208" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="N208" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -9439,9 +10066,12 @@
         <v>0.0259</v>
       </c>
       <c r="L209" s="1" t="n">
+        <v>0.02586</v>
+      </c>
+      <c r="M209" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="M209" s="1" t="n">
+      <c r="N209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -9482,9 +10112,12 @@
         <v>0.01266</v>
       </c>
       <c r="L210" s="1" t="n">
+        <v>0.012678</v>
+      </c>
+      <c r="M210" s="1" t="n">
         <v>0.012745</v>
       </c>
-      <c r="M210" s="1" t="n">
+      <c r="N210" s="1" t="n">
         <v>0.012645</v>
       </c>
     </row>
@@ -9528,6 +10161,9 @@
         <v>0.0921</v>
       </c>
       <c r="M211" s="1" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="N211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -9568,9 +10204,12 @@
         <v>0.007038</v>
       </c>
       <c r="L212" s="1" t="n">
+        <v>0.007069</v>
+      </c>
+      <c r="M212" s="1" t="n">
         <v>0.007076</v>
       </c>
-      <c r="M212" s="1" t="n">
+      <c r="N212" s="1" t="n">
         <v>0.007038</v>
       </c>
     </row>
@@ -9611,9 +10250,12 @@
         <v>0.02978</v>
       </c>
       <c r="L213" s="1" t="n">
+        <v>0.02969</v>
+      </c>
+      <c r="M213" s="1" t="n">
         <v>0.02978</v>
       </c>
-      <c r="M213" s="1" t="n">
+      <c r="N213" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -9654,9 +10296,12 @@
         <v>0.2704</v>
       </c>
       <c r="L214" s="1" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="M214" s="1" t="n">
         <v>0.271</v>
       </c>
-      <c r="M214" s="1" t="n">
+      <c r="N214" s="1" t="n">
         <v>0.2698</v>
       </c>
     </row>
@@ -9697,9 +10342,12 @@
         <v>0.02229</v>
       </c>
       <c r="L215" s="1" t="n">
+        <v>0.02225</v>
+      </c>
+      <c r="M215" s="1" t="n">
         <v>0.02256</v>
       </c>
-      <c r="M215" s="1" t="n">
+      <c r="N215" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -9740,9 +10388,12 @@
         <v>0.01469</v>
       </c>
       <c r="L216" s="1" t="n">
+        <v>0.01463</v>
+      </c>
+      <c r="M216" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="M216" s="1" t="n">
+      <c r="N216" s="1" t="n">
         <v>0.01463</v>
       </c>
     </row>
@@ -9783,9 +10434,12 @@
         <v>0.255</v>
       </c>
       <c r="L217" s="1" t="n">
+        <v>0.2547</v>
+      </c>
+      <c r="M217" s="1" t="n">
         <v>0.255</v>
       </c>
-      <c r="M217" s="1" t="n">
+      <c r="N217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -9826,9 +10480,12 @@
         <v>0.3111</v>
       </c>
       <c r="L218" s="1" t="n">
-        <v>0.3114</v>
+        <v>0.3116</v>
       </c>
       <c r="M218" s="1" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="N218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -9869,9 +10526,12 @@
         <v>0.179</v>
       </c>
       <c r="L219" s="1" t="n">
+        <v>0.1786</v>
+      </c>
+      <c r="M219" s="1" t="n">
         <v>0.179</v>
       </c>
-      <c r="M219" s="1" t="n">
+      <c r="N219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -9912,9 +10572,12 @@
         <v>14.99</v>
       </c>
       <c r="L220" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M220" s="1" t="n">
         <v>15.02</v>
       </c>
-      <c r="M220" s="1" t="n">
+      <c r="N220" s="1" t="n">
         <v>14.95</v>
       </c>
     </row>
@@ -9955,9 +10618,12 @@
         <v>0.01611</v>
       </c>
       <c r="L221" s="1" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="M221" s="1" t="n">
         <v>0.01614</v>
       </c>
-      <c r="M221" s="1" t="n">
+      <c r="N221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -9998,9 +10664,12 @@
         <v>66.44</v>
       </c>
       <c r="L222" s="1" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="M222" s="1" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="M222" s="1" t="n">
+      <c r="N222" s="1" t="n">
         <v>66.17</v>
       </c>
     </row>
@@ -10041,9 +10710,12 @@
         <v>0.09379</v>
       </c>
       <c r="L223" s="1" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="M223" s="1" t="n">
         <v>0.09379</v>
       </c>
-      <c r="M223" s="1" t="n">
+      <c r="N223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -10084,9 +10756,12 @@
         <v>0.03962</v>
       </c>
       <c r="L224" s="1" t="n">
-        <v>0.03974</v>
+        <v>0.03993</v>
       </c>
       <c r="M224" s="1" t="n">
+        <v>0.03993</v>
+      </c>
+      <c r="N224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -10127,9 +10802,12 @@
         <v>0.5712</v>
       </c>
       <c r="L225" s="1" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="M225" s="1" t="n">
         <v>0.5725</v>
       </c>
-      <c r="M225" s="1" t="n">
+      <c r="N225" s="1" t="n">
         <v>0.5695</v>
       </c>
     </row>
@@ -10170,9 +10848,12 @@
         <v>0.1177</v>
       </c>
       <c r="L226" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="M226" s="1" t="n">
         <v>0.1184</v>
       </c>
-      <c r="M226" s="1" t="n">
+      <c r="N226" s="1" t="n">
         <v>0.1166</v>
       </c>
     </row>
@@ -10213,9 +10894,12 @@
         <v>0.3177</v>
       </c>
       <c r="L227" s="1" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="M227" s="1" t="n">
         <v>0.3201</v>
       </c>
-      <c r="M227" s="1" t="n">
+      <c r="N227" s="1" t="n">
         <v>0.3165</v>
       </c>
     </row>
@@ -10256,9 +10940,12 @@
         <v>6.106</v>
       </c>
       <c r="L228" s="1" t="n">
+        <v>6.105</v>
+      </c>
+      <c r="M228" s="1" t="n">
         <v>6.108</v>
       </c>
-      <c r="M228" s="1" t="n">
+      <c r="N228" s="1" t="n">
         <v>6.062</v>
       </c>
     </row>
@@ -10299,9 +10986,12 @@
         <v>0.0293</v>
       </c>
       <c r="L229" s="1" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="M229" s="1" t="n">
         <v>0.0294</v>
       </c>
-      <c r="M229" s="1" t="n">
+      <c r="N229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -10342,9 +11032,12 @@
         <v>0.3319</v>
       </c>
       <c r="L230" s="1" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="M230" s="1" t="n">
         <v>0.3325</v>
       </c>
-      <c r="M230" s="1" t="n">
+      <c r="N230" s="1" t="n">
         <v>0.3288</v>
       </c>
     </row>
@@ -10385,9 +11078,12 @@
         <v>0.11997</v>
       </c>
       <c r="L231" s="1" t="n">
+        <v>0.12015</v>
+      </c>
+      <c r="M231" s="1" t="n">
         <v>0.12089</v>
       </c>
-      <c r="M231" s="1" t="n">
+      <c r="N231" s="1" t="n">
         <v>0.11986</v>
       </c>
     </row>
@@ -10428,9 +11124,12 @@
         <v>0.1195</v>
       </c>
       <c r="L232" s="1" t="n">
-        <v>0.1195</v>
+        <v>0.1204</v>
       </c>
       <c r="M232" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="N232" s="1" t="n">
         <v>0.1182</v>
       </c>
     </row>
@@ -10471,9 +11170,12 @@
         <v>0.03036</v>
       </c>
       <c r="L233" s="1" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="M233" s="1" t="n">
         <v>0.03039</v>
       </c>
-      <c r="M233" s="1" t="n">
+      <c r="N233" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -10514,9 +11216,12 @@
         <v>0.015925</v>
       </c>
       <c r="L234" s="1" t="n">
+        <v>0.015748</v>
+      </c>
+      <c r="M234" s="1" t="n">
         <v>0.016171</v>
       </c>
-      <c r="M234" s="1" t="n">
+      <c r="N234" s="1" t="n">
         <v>0.0156</v>
       </c>
     </row>
@@ -10557,9 +11262,12 @@
         <v>0.01263</v>
       </c>
       <c r="L235" s="1" t="n">
+        <v>0.01264</v>
+      </c>
+      <c r="M235" s="1" t="n">
         <v>0.01281</v>
       </c>
-      <c r="M235" s="1" t="n">
+      <c r="N235" s="1" t="n">
         <v>0.01263</v>
       </c>
     </row>
@@ -10600,9 +11308,12 @@
         <v>0.01937</v>
       </c>
       <c r="L236" s="1" t="n">
-        <v>0.01937</v>
+        <v>0.0194</v>
       </c>
       <c r="M236" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="N236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -10643,9 +11354,12 @@
         <v>0.08511000000000001</v>
       </c>
       <c r="L237" s="1" t="n">
-        <v>0.08545999999999999</v>
+        <v>0.08551</v>
       </c>
       <c r="M237" s="1" t="n">
+        <v>0.08551</v>
+      </c>
+      <c r="N237" s="1" t="n">
         <v>0.08427999999999999</v>
       </c>
     </row>
@@ -10686,9 +11400,12 @@
         <v>0.05883</v>
       </c>
       <c r="L238" s="1" t="n">
+        <v>0.05879</v>
+      </c>
+      <c r="M238" s="1" t="n">
         <v>0.05892</v>
       </c>
-      <c r="M238" s="1" t="n">
+      <c r="N238" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>
@@ -10729,9 +11446,12 @@
         <v>0.009027</v>
       </c>
       <c r="L239" s="1" t="n">
+        <v>0.009018</v>
+      </c>
+      <c r="M239" s="1" t="n">
         <v>0.009131999999999999</v>
       </c>
-      <c r="M239" s="1" t="n">
+      <c r="N239" s="1" t="n">
         <v>0.008954</v>
       </c>
     </row>
@@ -10772,9 +11492,12 @@
         <v>0.004189</v>
       </c>
       <c r="L240" s="1" t="n">
-        <v>0.004189</v>
+        <v>0.00419</v>
       </c>
       <c r="M240" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="N240" s="1" t="n">
         <v>0.004154</v>
       </c>
     </row>
@@ -10815,9 +11538,12 @@
         <v>0.2424</v>
       </c>
       <c r="L241" s="1" t="n">
-        <v>0.2424</v>
+        <v>0.2435</v>
       </c>
       <c r="M241" s="1" t="n">
+        <v>0.2435</v>
+      </c>
+      <c r="N241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -10858,9 +11584,12 @@
         <v>0.0585</v>
       </c>
       <c r="L242" s="1" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="M242" s="1" t="n">
         <v>0.0589</v>
       </c>
-      <c r="M242" s="1" t="n">
+      <c r="N242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -10901,9 +11630,12 @@
         <v>0.02353</v>
       </c>
       <c r="L243" s="1" t="n">
+        <v>0.02355</v>
+      </c>
+      <c r="M243" s="1" t="n">
         <v>0.02363</v>
       </c>
-      <c r="M243" s="1" t="n">
+      <c r="N243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -10944,9 +11676,12 @@
         <v>0.05623</v>
       </c>
       <c r="L244" s="1" t="n">
+        <v>0.05591</v>
+      </c>
+      <c r="M244" s="1" t="n">
         <v>0.05671</v>
       </c>
-      <c r="M244" s="1" t="n">
+      <c r="N244" s="1" t="n">
         <v>0.05547</v>
       </c>
     </row>
@@ -10987,9 +11722,12 @@
         <v>0.03499</v>
       </c>
       <c r="L245" s="1" t="n">
+        <v>0.03496</v>
+      </c>
+      <c r="M245" s="1" t="n">
         <v>0.03499</v>
       </c>
-      <c r="M245" s="1" t="n">
+      <c r="N245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -11030,9 +11768,12 @@
         <v>0.06021</v>
       </c>
       <c r="L246" s="1" t="n">
+        <v>0.06018</v>
+      </c>
+      <c r="M246" s="1" t="n">
         <v>0.0604</v>
       </c>
-      <c r="M246" s="1" t="n">
+      <c r="N246" s="1" t="n">
         <v>0.0599</v>
       </c>
     </row>
@@ -11073,9 +11814,12 @@
         <v>0.383</v>
       </c>
       <c r="L247" s="1" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="M247" s="1" t="n">
         <v>0.385</v>
       </c>
-      <c r="M247" s="1" t="n">
+      <c r="N247" s="1" t="n">
         <v>0.382</v>
       </c>
     </row>
@@ -11116,9 +11860,12 @@
         <v>0.5218</v>
       </c>
       <c r="L248" s="1" t="n">
-        <v>0.5223</v>
+        <v>0.5233</v>
       </c>
       <c r="M248" s="1" t="n">
+        <v>0.5233</v>
+      </c>
+      <c r="N248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -11159,9 +11906,12 @@
         <v>0.02884</v>
       </c>
       <c r="L249" s="1" t="n">
+        <v>0.02861</v>
+      </c>
+      <c r="M249" s="1" t="n">
         <v>0.02884</v>
       </c>
-      <c r="M249" s="1" t="n">
+      <c r="N249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -11202,9 +11952,12 @@
         <v>0.01297</v>
       </c>
       <c r="L250" s="1" t="n">
+        <v>0.01298</v>
+      </c>
+      <c r="M250" s="1" t="n">
         <v>0.01317</v>
       </c>
-      <c r="M250" s="1" t="n">
+      <c r="N250" s="1" t="n">
         <v>0.01288</v>
       </c>
     </row>
@@ -11245,9 +11998,12 @@
         <v>0.1006</v>
       </c>
       <c r="L251" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="M251" s="1" t="n">
         <v>0.1006</v>
       </c>
-      <c r="M251" s="1" t="n">
+      <c r="N251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -11288,9 +12044,12 @@
         <v>0.00718</v>
       </c>
       <c r="L252" s="1" t="n">
+        <v>0.00716</v>
+      </c>
+      <c r="M252" s="1" t="n">
         <v>0.00719</v>
       </c>
-      <c r="M252" s="1" t="n">
+      <c r="N252" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -11331,9 +12090,12 @@
         <v>0.005552</v>
       </c>
       <c r="L253" s="1" t="n">
+        <v>0.005553</v>
+      </c>
+      <c r="M253" s="1" t="n">
         <v>0.005571</v>
       </c>
-      <c r="M253" s="1" t="n">
+      <c r="N253" s="1" t="n">
         <v>0.005552</v>
       </c>
     </row>
@@ -11374,9 +12136,12 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="L254" s="1" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="M254" s="1" t="n">
         <v>0.0646</v>
       </c>
-      <c r="M254" s="1" t="n">
+      <c r="N254" s="1" t="n">
         <v>0.0641</v>
       </c>
     </row>
@@ -11417,9 +12182,12 @@
         <v>0.01438</v>
       </c>
       <c r="L255" s="1" t="n">
+        <v>0.01438</v>
+      </c>
+      <c r="M255" s="1" t="n">
         <v>0.01454</v>
       </c>
-      <c r="M255" s="1" t="n">
+      <c r="N255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -11460,9 +12228,12 @@
         <v>0.999275</v>
       </c>
       <c r="L256" s="1" t="n">
+        <v>0.9992760000000001</v>
+      </c>
+      <c r="M256" s="1" t="n">
         <v>0.999297</v>
       </c>
-      <c r="M256" s="1" t="n">
+      <c r="N256" s="1" t="n">
         <v>0.999275</v>
       </c>
     </row>
@@ -11503,9 +12274,12 @@
         <v>0.02113</v>
       </c>
       <c r="L257" s="1" t="n">
+        <v>0.02111</v>
+      </c>
+      <c r="M257" s="1" t="n">
         <v>0.02118</v>
       </c>
-      <c r="M257" s="1" t="n">
+      <c r="N257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -11546,9 +12320,12 @@
         <v>0.01149</v>
       </c>
       <c r="L258" s="1" t="n">
-        <v>0.01149</v>
+        <v>0.01152</v>
       </c>
       <c r="M258" s="1" t="n">
+        <v>0.01152</v>
+      </c>
+      <c r="N258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -11589,10 +12366,13 @@
         <v>0.5074</v>
       </c>
       <c r="L259" s="1" t="n">
+        <v>0.5062</v>
+      </c>
+      <c r="M259" s="1" t="n">
         <v>0.5119</v>
       </c>
-      <c r="M259" s="1" t="n">
-        <v>0.5071</v>
+      <c r="N259" s="1" t="n">
+        <v>0.5062</v>
       </c>
     </row>
     <row r="260">
@@ -11632,9 +12412,12 @@
         <v>0.08484999999999999</v>
       </c>
       <c r="L260" s="1" t="n">
+        <v>0.08444</v>
+      </c>
+      <c r="M260" s="1" t="n">
         <v>0.08537</v>
       </c>
-      <c r="M260" s="1" t="n">
+      <c r="N260" s="1" t="n">
         <v>0.08436</v>
       </c>
     </row>
@@ -11675,9 +12458,12 @@
         <v>0.04131</v>
       </c>
       <c r="L261" s="1" t="n">
+        <v>0.04136</v>
+      </c>
+      <c r="M261" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="M261" s="1" t="n">
+      <c r="N261" s="1" t="n">
         <v>0.04121</v>
       </c>
     </row>
@@ -11718,9 +12504,12 @@
         <v>2.293</v>
       </c>
       <c r="L262" s="1" t="n">
+        <v>2.294</v>
+      </c>
+      <c r="M262" s="1" t="n">
         <v>2.297</v>
       </c>
-      <c r="M262" s="1" t="n">
+      <c r="N262" s="1" t="n">
         <v>2.279</v>
       </c>
     </row>
@@ -11761,9 +12550,12 @@
         <v>18.65</v>
       </c>
       <c r="L263" s="1" t="n">
-        <v>18.65</v>
+        <v>18.73</v>
       </c>
       <c r="M263" s="1" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="N263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -11804,9 +12596,12 @@
         <v>0.008514000000000001</v>
       </c>
       <c r="L264" s="1" t="n">
+        <v>0.008510999999999999</v>
+      </c>
+      <c r="M264" s="1" t="n">
         <v>0.008562999999999999</v>
       </c>
-      <c r="M264" s="1" t="n">
+      <c r="N264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -11847,9 +12642,12 @@
         <v>0.3659</v>
       </c>
       <c r="L265" s="1" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="M265" s="1" t="n">
         <v>0.3659</v>
       </c>
-      <c r="M265" s="1" t="n">
+      <c r="N265" s="1" t="n">
         <v>0.3627</v>
       </c>
     </row>
@@ -11890,9 +12688,12 @@
         <v>0.05515</v>
       </c>
       <c r="L266" s="1" t="n">
+        <v>0.055235</v>
+      </c>
+      <c r="M266" s="1" t="n">
         <v>0.055369</v>
       </c>
-      <c r="M266" s="1" t="n">
+      <c r="N266" s="1" t="n">
         <v>0.053765</v>
       </c>
     </row>
@@ -11933,9 +12734,12 @@
         <v>0.1318</v>
       </c>
       <c r="L267" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="M267" s="1" t="n">
         <v>0.1321</v>
       </c>
-      <c r="M267" s="1" t="n">
+      <c r="N267" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -11976,9 +12780,12 @@
         <v>0.007873</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>0.007873</v>
+        <v>0.007990000000000001</v>
       </c>
       <c r="M268" s="1" t="n">
+        <v>0.007990000000000001</v>
+      </c>
+      <c r="N268" s="1" t="n">
         <v>0.00775</v>
       </c>
     </row>
@@ -12019,9 +12826,12 @@
         <v>0.001249</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>0.001249</v>
+        <v>0.001264</v>
       </c>
       <c r="M269" s="1" t="n">
+        <v>0.001264</v>
+      </c>
+      <c r="N269" s="1" t="n">
         <v>0.001232</v>
       </c>
     </row>
@@ -12062,9 +12872,12 @@
         <v>0.28945</v>
       </c>
       <c r="L270" s="1" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="M270" s="1" t="n">
         <v>0.28999</v>
       </c>
-      <c r="M270" s="1" t="n">
+      <c r="N270" s="1" t="n">
         <v>0.28865</v>
       </c>
     </row>
@@ -12105,9 +12918,12 @@
         <v>0.03901</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>0.03922</v>
+        <v>0.03924</v>
       </c>
       <c r="M271" s="1" t="n">
+        <v>0.03924</v>
+      </c>
+      <c r="N271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -12148,9 +12964,12 @@
         <v>0.0518</v>
       </c>
       <c r="L272" s="1" t="n">
-        <v>0.05181</v>
+        <v>0.05182</v>
       </c>
       <c r="M272" s="1" t="n">
+        <v>0.05182</v>
+      </c>
+      <c r="N272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -12194,6 +13013,9 @@
         <v>0.00776</v>
       </c>
       <c r="M273" s="1" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="N273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -12234,9 +13056,12 @@
         <v>0.005799</v>
       </c>
       <c r="L274" s="1" t="n">
+        <v>0.005786</v>
+      </c>
+      <c r="M274" s="1" t="n">
         <v>0.005813</v>
       </c>
-      <c r="M274" s="1" t="n">
+      <c r="N274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -12277,9 +13102,12 @@
         <v>0.0005874</v>
       </c>
       <c r="L275" s="1" t="n">
+        <v>0.0005865999999999999</v>
+      </c>
+      <c r="M275" s="1" t="n">
         <v>0.0005895</v>
       </c>
-      <c r="M275" s="1" t="n">
+      <c r="N275" s="1" t="n">
         <v>0.0005863</v>
       </c>
     </row>
@@ -12320,9 +13148,12 @@
         <v>0.15042</v>
       </c>
       <c r="L276" s="1" t="n">
+        <v>0.15013</v>
+      </c>
+      <c r="M276" s="1" t="n">
         <v>0.15167</v>
       </c>
-      <c r="M276" s="1" t="n">
+      <c r="N276" s="1" t="n">
         <v>0.15004</v>
       </c>
     </row>
@@ -12363,9 +13194,12 @@
         <v>0.023035</v>
       </c>
       <c r="L277" s="1" t="n">
-        <v>0.023073</v>
+        <v>0.023083</v>
       </c>
       <c r="M277" s="1" t="n">
+        <v>0.023083</v>
+      </c>
+      <c r="N277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -12406,9 +13240,12 @@
         <v>0.04206</v>
       </c>
       <c r="L278" s="1" t="n">
+        <v>0.04199</v>
+      </c>
+      <c r="M278" s="1" t="n">
         <v>0.04242</v>
       </c>
-      <c r="M278" s="1" t="n">
+      <c r="N278" s="1" t="n">
         <v>0.04179</v>
       </c>
     </row>
@@ -12449,9 +13286,12 @@
         <v>0.0003993</v>
       </c>
       <c r="L279" s="1" t="n">
+        <v>0.0003985</v>
+      </c>
+      <c r="M279" s="1" t="n">
         <v>0.0004006</v>
       </c>
-      <c r="M279" s="1" t="n">
+      <c r="N279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -12492,9 +13332,12 @@
         <v>0.02195</v>
       </c>
       <c r="L280" s="1" t="n">
+        <v>0.02202</v>
+      </c>
+      <c r="M280" s="1" t="n">
         <v>0.02218</v>
       </c>
-      <c r="M280" s="1" t="n">
+      <c r="N280" s="1" t="n">
         <v>0.0219</v>
       </c>
     </row>
@@ -12535,9 +13378,12 @@
         <v>0.07128</v>
       </c>
       <c r="L281" s="1" t="n">
+        <v>0.07084</v>
+      </c>
+      <c r="M281" s="1" t="n">
         <v>0.07128</v>
       </c>
-      <c r="M281" s="1" t="n">
+      <c r="N281" s="1" t="n">
         <v>0.06936</v>
       </c>
     </row>
@@ -12578,9 +13424,12 @@
         <v>0.006717</v>
       </c>
       <c r="L282" s="1" t="n">
+        <v>0.006737</v>
+      </c>
+      <c r="M282" s="1" t="n">
         <v>0.006804</v>
       </c>
-      <c r="M282" s="1" t="n">
+      <c r="N282" s="1" t="n">
         <v>0.006688</v>
       </c>
     </row>
@@ -12621,9 +13470,12 @@
         <v>0.119</v>
       </c>
       <c r="L283" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="M283" s="1" t="n">
         <v>0.12</v>
       </c>
-      <c r="M283" s="1" t="n">
+      <c r="N283" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -12664,9 +13516,12 @@
         <v>0.005493</v>
       </c>
       <c r="L284" s="1" t="n">
+        <v>0.005489</v>
+      </c>
+      <c r="M284" s="1" t="n">
         <v>0.005499</v>
       </c>
-      <c r="M284" s="1" t="n">
+      <c r="N284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -12707,9 +13562,12 @@
         <v>1.261</v>
       </c>
       <c r="L285" s="1" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="M285" s="1" t="n">
         <v>1.272</v>
       </c>
-      <c r="M285" s="1" t="n">
+      <c r="N285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -12750,9 +13608,12 @@
         <v>0.4454</v>
       </c>
       <c r="L286" s="1" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="M286" s="1" t="n">
         <v>0.4458</v>
       </c>
-      <c r="M286" s="1" t="n">
+      <c r="N286" s="1" t="n">
         <v>0.4423</v>
       </c>
     </row>
@@ -12793,9 +13654,12 @@
         <v>0.007977</v>
       </c>
       <c r="L287" s="1" t="n">
+        <v>0.007962</v>
+      </c>
+      <c r="M287" s="1" t="n">
         <v>0.007998999999999999</v>
       </c>
-      <c r="M287" s="1" t="n">
+      <c r="N287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -12836,9 +13700,12 @@
         <v>0.02941</v>
       </c>
       <c r="L288" s="1" t="n">
+        <v>0.02933</v>
+      </c>
+      <c r="M288" s="1" t="n">
         <v>0.0295</v>
       </c>
-      <c r="M288" s="1" t="n">
+      <c r="N288" s="1" t="n">
         <v>0.02914</v>
       </c>
     </row>
@@ -12879,9 +13746,12 @@
         <v>0.2827</v>
       </c>
       <c r="L289" s="1" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="M289" s="1" t="n">
         <v>0.2827</v>
       </c>
-      <c r="M289" s="1" t="n">
+      <c r="N289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -12922,9 +13792,12 @@
         <v>2.766</v>
       </c>
       <c r="L290" s="1" t="n">
+        <v>2.759</v>
+      </c>
+      <c r="M290" s="1" t="n">
         <v>2.783</v>
       </c>
-      <c r="M290" s="1" t="n">
+      <c r="N290" s="1" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -12965,9 +13838,12 @@
         <v>0.003191</v>
       </c>
       <c r="L291" s="1" t="n">
+        <v>0.00319</v>
+      </c>
+      <c r="M291" s="1" t="n">
         <v>0.003191</v>
       </c>
-      <c r="M291" s="1" t="n">
+      <c r="N291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -13008,10 +13884,13 @@
         <v>0.4478</v>
       </c>
       <c r="L292" s="1" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="M292" s="1" t="n">
         <v>0.4488</v>
       </c>
-      <c r="M292" s="1" t="n">
-        <v>0.4475</v>
+      <c r="N292" s="1" t="n">
+        <v>0.447</v>
       </c>
     </row>
     <row r="293">
@@ -13051,9 +13930,12 @@
         <v>0.08237999999999999</v>
       </c>
       <c r="L293" s="1" t="n">
+        <v>0.08278000000000001</v>
+      </c>
+      <c r="M293" s="1" t="n">
         <v>0.08298</v>
       </c>
-      <c r="M293" s="1" t="n">
+      <c r="N293" s="1" t="n">
         <v>0.08136</v>
       </c>
     </row>
@@ -13094,9 +13976,12 @@
         <v>0.02792</v>
       </c>
       <c r="L294" s="1" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="M294" s="1" t="n">
         <v>0.02801</v>
       </c>
-      <c r="M294" s="1" t="n">
+      <c r="N294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -13137,10 +14022,13 @@
         <v>0.953</v>
       </c>
       <c r="L295" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M295" s="1" t="n">
         <v>0.958</v>
       </c>
-      <c r="M295" s="1" t="n">
-        <v>0.952</v>
+      <c r="N295" s="1" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="296">
@@ -13180,9 +14068,12 @@
         <v>0.006963</v>
       </c>
       <c r="L296" s="1" t="n">
+        <v>0.006976</v>
+      </c>
+      <c r="M296" s="1" t="n">
         <v>0.007008</v>
       </c>
-      <c r="M296" s="1" t="n">
+      <c r="N296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -13223,9 +14114,12 @@
         <v>0.1215</v>
       </c>
       <c r="L297" s="1" t="n">
+        <v>0.1213</v>
+      </c>
+      <c r="M297" s="1" t="n">
         <v>0.1215</v>
       </c>
-      <c r="M297" s="1" t="n">
+      <c r="N297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -13266,9 +14160,12 @@
         <v>0.0156</v>
       </c>
       <c r="L298" s="1" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="M298" s="1" t="n">
         <v>0.01563</v>
       </c>
-      <c r="M298" s="1" t="n">
+      <c r="N298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -13309,9 +14206,12 @@
         <v>0.4427</v>
       </c>
       <c r="L299" s="1" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="M299" s="1" t="n">
         <v>0.4431</v>
       </c>
-      <c r="M299" s="1" t="n">
+      <c r="N299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -13352,10 +14252,13 @@
         <v>0.009140000000000001</v>
       </c>
       <c r="L300" s="1" t="n">
+        <v>0.009129999999999999</v>
+      </c>
+      <c r="M300" s="1" t="n">
         <v>0.00924</v>
       </c>
-      <c r="M300" s="1" t="n">
-        <v>0.009140000000000001</v>
+      <c r="N300" s="1" t="n">
+        <v>0.009129999999999999</v>
       </c>
     </row>
     <row r="301">
@@ -13395,9 +14298,12 @@
         <v>0.1905</v>
       </c>
       <c r="L301" s="1" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="M301" s="1" t="n">
         <v>0.1905</v>
       </c>
-      <c r="M301" s="1" t="n">
+      <c r="N301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -13438,9 +14344,12 @@
         <v>0.00758</v>
       </c>
       <c r="L302" s="1" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="M302" s="1" t="n">
         <v>0.00765</v>
       </c>
-      <c r="M302" s="1" t="n">
+      <c r="N302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -13481,10 +14390,13 @@
         <v>0.000217</v>
       </c>
       <c r="L303" s="1" t="n">
+        <v>0.0002147</v>
+      </c>
+      <c r="M303" s="1" t="n">
         <v>0.0002171</v>
       </c>
-      <c r="M303" s="1" t="n">
-        <v>0.0002151</v>
+      <c r="N303" s="1" t="n">
+        <v>0.0002147</v>
       </c>
     </row>
     <row r="304">
@@ -13524,9 +14436,12 @@
         <v>0.01555</v>
       </c>
       <c r="L304" s="1" t="n">
+        <v>0.01545</v>
+      </c>
+      <c r="M304" s="1" t="n">
         <v>0.01555</v>
       </c>
-      <c r="M304" s="1" t="n">
+      <c r="N304" s="1" t="n">
         <v>0.01542</v>
       </c>
     </row>
@@ -13567,9 +14482,12 @@
         <v>0.07399</v>
       </c>
       <c r="L305" s="1" t="n">
-        <v>0.074</v>
+        <v>0.07401000000000001</v>
       </c>
       <c r="M305" s="1" t="n">
+        <v>0.07401000000000001</v>
+      </c>
+      <c r="N305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -13610,9 +14528,12 @@
         <v>0.08347</v>
       </c>
       <c r="L306" s="1" t="n">
+        <v>0.08344</v>
+      </c>
+      <c r="M306" s="1" t="n">
         <v>0.08347</v>
       </c>
-      <c r="M306" s="1" t="n">
+      <c r="N306" s="1" t="n">
         <v>0.08275</v>
       </c>
     </row>
@@ -13653,10 +14574,13 @@
         <v>0.01806</v>
       </c>
       <c r="L307" s="1" t="n">
+        <v>0.01801</v>
+      </c>
+      <c r="M307" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="M307" s="1" t="n">
-        <v>0.01803</v>
+      <c r="N307" s="1" t="n">
+        <v>0.01801</v>
       </c>
     </row>
     <row r="308">
@@ -13696,9 +14620,12 @@
         <v>0.0006274</v>
       </c>
       <c r="L308" s="1" t="n">
+        <v>0.0006261</v>
+      </c>
+      <c r="M308" s="1" t="n">
         <v>0.0006274</v>
       </c>
-      <c r="M308" s="1" t="n">
+      <c r="N308" s="1" t="n">
         <v>0.0006212</v>
       </c>
     </row>
@@ -13739,9 +14666,12 @@
         <v>0.08244</v>
       </c>
       <c r="L309" s="1" t="n">
+        <v>0.08223</v>
+      </c>
+      <c r="M309" s="1" t="n">
         <v>0.08294</v>
       </c>
-      <c r="M309" s="1" t="n">
+      <c r="N309" s="1" t="n">
         <v>0.0822</v>
       </c>
     </row>
@@ -13785,6 +14715,9 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="M310" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="N310" s="1" t="n">
         <v>0.0973</v>
       </c>
     </row>
@@ -13825,9 +14758,12 @@
         <v>0.2126</v>
       </c>
       <c r="L311" s="1" t="n">
+        <v>0.2123</v>
+      </c>
+      <c r="M311" s="1" t="n">
         <v>0.2126</v>
       </c>
-      <c r="M311" s="1" t="n">
+      <c r="N311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -13868,9 +14804,12 @@
         <v>0.3958</v>
       </c>
       <c r="L312" s="1" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="M312" s="1" t="n">
         <v>0.3958</v>
       </c>
-      <c r="M312" s="1" t="n">
+      <c r="N312" s="1" t="n">
         <v>0.387</v>
       </c>
     </row>
@@ -13911,9 +14850,12 @@
         <v>0.10462</v>
       </c>
       <c r="L313" s="1" t="n">
+        <v>0.10458</v>
+      </c>
+      <c r="M313" s="1" t="n">
         <v>0.10542</v>
       </c>
-      <c r="M313" s="1" t="n">
+      <c r="N313" s="1" t="n">
         <v>0.10455</v>
       </c>
     </row>
@@ -13954,9 +14896,12 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="L314" s="1" t="n">
-        <v>0.08673</v>
+        <v>0.08711000000000001</v>
       </c>
       <c r="M314" s="1" t="n">
+        <v>0.08711000000000001</v>
+      </c>
+      <c r="N314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -13997,9 +14942,12 @@
         <v>0.1185</v>
       </c>
       <c r="L315" s="1" t="n">
-        <v>0.1185</v>
+        <v>0.1187</v>
       </c>
       <c r="M315" s="1" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="N315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -14040,10 +14988,13 @@
         <v>0.03615</v>
       </c>
       <c r="L316" s="1" t="n">
+        <v>0.03602</v>
+      </c>
+      <c r="M316" s="1" t="n">
         <v>0.03681</v>
       </c>
-      <c r="M316" s="1" t="n">
-        <v>0.03615</v>
+      <c r="N316" s="1" t="n">
+        <v>0.03602</v>
       </c>
     </row>
     <row r="317">
@@ -14083,9 +15034,12 @@
         <v>0.08119</v>
       </c>
       <c r="L317" s="1" t="n">
+        <v>0.08137999999999999</v>
+      </c>
+      <c r="M317" s="1" t="n">
         <v>0.08164</v>
       </c>
-      <c r="M317" s="1" t="n">
+      <c r="N317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -14126,9 +15080,12 @@
         <v>0.03747</v>
       </c>
       <c r="L318" s="1" t="n">
+        <v>0.03746</v>
+      </c>
+      <c r="M318" s="1" t="n">
         <v>0.03766</v>
       </c>
-      <c r="M318" s="1" t="n">
+      <c r="N318" s="1" t="n">
         <v>0.03736</v>
       </c>
     </row>
@@ -14169,9 +15126,12 @@
         <v>0.4309</v>
       </c>
       <c r="L319" s="1" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="M319" s="1" t="n">
         <v>0.4347</v>
       </c>
-      <c r="M319" s="1" t="n">
+      <c r="N319" s="1" t="n">
         <v>0.4296</v>
       </c>
     </row>
@@ -14212,9 +15172,12 @@
         <v>0.1598</v>
       </c>
       <c r="L320" s="1" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="M320" s="1" t="n">
         <v>0.1614</v>
       </c>
-      <c r="M320" s="1" t="n">
+      <c r="N320" s="1" t="n">
         <v>0.1598</v>
       </c>
     </row>
@@ -14255,9 +15218,12 @@
         <v>5.688</v>
       </c>
       <c r="L321" s="1" t="n">
+        <v>5.681</v>
+      </c>
+      <c r="M321" s="1" t="n">
         <v>5.688</v>
       </c>
-      <c r="M321" s="1" t="n">
+      <c r="N321" s="1" t="n">
         <v>5.677</v>
       </c>
     </row>
@@ -14298,9 +15264,12 @@
         <v>0.003752</v>
       </c>
       <c r="L322" s="1" t="n">
+        <v>0.003742</v>
+      </c>
+      <c r="M322" s="1" t="n">
         <v>0.003754</v>
       </c>
-      <c r="M322" s="1" t="n">
+      <c r="N322" s="1" t="n">
         <v>0.003714</v>
       </c>
     </row>
@@ -14341,9 +15310,12 @@
         <v>0.001762</v>
       </c>
       <c r="L323" s="1" t="n">
+        <v>0.001758</v>
+      </c>
+      <c r="M323" s="1" t="n">
         <v>0.001762</v>
       </c>
-      <c r="M323" s="1" t="n">
+      <c r="N323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -14387,6 +15359,9 @@
         <v>1.2e-05</v>
       </c>
       <c r="M324" s="1" t="n">
+        <v>1.2e-05</v>
+      </c>
+      <c r="N324" s="1" t="n">
         <v>1.19e-05</v>
       </c>
     </row>
@@ -14430,6 +15405,9 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="M325" s="1" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="N325" s="1" t="n">
         <v>0.0857</v>
       </c>
     </row>
@@ -14470,9 +15448,12 @@
         <v>0.01732</v>
       </c>
       <c r="L326" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="M326" s="1" t="n">
         <v>0.01736</v>
       </c>
-      <c r="M326" s="1" t="n">
+      <c r="N326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -14513,9 +15494,12 @@
         <v>0.01684</v>
       </c>
       <c r="L327" s="1" t="n">
+        <v>0.01684</v>
+      </c>
+      <c r="M327" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="M327" s="1" t="n">
+      <c r="N327" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -14556,9 +15540,12 @@
         <v>4.45</v>
       </c>
       <c r="L328" s="1" t="n">
+        <v>4.449</v>
+      </c>
+      <c r="M328" s="1" t="n">
         <v>4.462</v>
       </c>
-      <c r="M328" s="1" t="n">
+      <c r="N328" s="1" t="n">
         <v>4.446</v>
       </c>
     </row>
@@ -14599,9 +15586,12 @@
         <v>0.009693999999999999</v>
       </c>
       <c r="L329" s="1" t="n">
+        <v>0.009730000000000001</v>
+      </c>
+      <c r="M329" s="1" t="n">
         <v>0.009861</v>
       </c>
-      <c r="M329" s="1" t="n">
+      <c r="N329" s="1" t="n">
         <v>0.009532000000000001</v>
       </c>
     </row>
@@ -14642,9 +15632,12 @@
         <v>5180</v>
       </c>
       <c r="L330" s="1" t="n">
+        <v>5181.1</v>
+      </c>
+      <c r="M330" s="1" t="n">
         <v>5192.9</v>
       </c>
-      <c r="M330" s="1" t="n">
+      <c r="N330" s="1" t="n">
         <v>5180</v>
       </c>
     </row>
@@ -14685,9 +15678,12 @@
         <v>0.07081</v>
       </c>
       <c r="L331" s="1" t="n">
-        <v>0.07087</v>
+        <v>0.07092</v>
       </c>
       <c r="M331" s="1" t="n">
+        <v>0.07092</v>
+      </c>
+      <c r="N331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -14728,9 +15724,12 @@
         <v>0.06092</v>
       </c>
       <c r="L332" s="1" t="n">
+        <v>0.06084</v>
+      </c>
+      <c r="M332" s="1" t="n">
         <v>0.06106</v>
       </c>
-      <c r="M332" s="1" t="n">
+      <c r="N332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -14771,9 +15770,12 @@
         <v>0.10545</v>
       </c>
       <c r="L333" s="1" t="n">
+        <v>0.10531</v>
+      </c>
+      <c r="M333" s="1" t="n">
         <v>0.10558</v>
       </c>
-      <c r="M333" s="1" t="n">
+      <c r="N333" s="1" t="n">
         <v>0.10341</v>
       </c>
     </row>
@@ -14814,9 +15816,12 @@
         <v>0.0877</v>
       </c>
       <c r="L334" s="1" t="n">
+        <v>0.08755</v>
+      </c>
+      <c r="M334" s="1" t="n">
         <v>0.08837</v>
       </c>
-      <c r="M334" s="1" t="n">
+      <c r="N334" s="1" t="n">
         <v>0.08734</v>
       </c>
     </row>
@@ -14857,9 +15862,12 @@
         <v>0.016468</v>
       </c>
       <c r="L335" s="1" t="n">
-        <v>0.016468</v>
+        <v>0.016489</v>
       </c>
       <c r="M335" s="1" t="n">
+        <v>0.016489</v>
+      </c>
+      <c r="N335" s="1" t="n">
         <v>0.016391</v>
       </c>
     </row>
@@ -14900,9 +15908,12 @@
         <v>0.04608</v>
       </c>
       <c r="L336" s="1" t="n">
+        <v>0.04618</v>
+      </c>
+      <c r="M336" s="1" t="n">
         <v>0.04619</v>
       </c>
-      <c r="M336" s="1" t="n">
+      <c r="N336" s="1" t="n">
         <v>0.04583</v>
       </c>
     </row>
@@ -14943,9 +15954,12 @@
         <v>0.1904</v>
       </c>
       <c r="L337" s="1" t="n">
-        <v>0.1904</v>
+        <v>0.1942</v>
       </c>
       <c r="M337" s="1" t="n">
+        <v>0.1942</v>
+      </c>
+      <c r="N337" s="1" t="n">
         <v>0.1838</v>
       </c>
     </row>
@@ -14986,9 +16000,12 @@
         <v>0.1839</v>
       </c>
       <c r="L338" s="1" t="n">
+        <v>0.1837</v>
+      </c>
+      <c r="M338" s="1" t="n">
         <v>0.1843</v>
       </c>
-      <c r="M338" s="1" t="n">
+      <c r="N338" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -15029,9 +16046,12 @@
         <v>0.01843</v>
       </c>
       <c r="L339" s="1" t="n">
+        <v>0.01842</v>
+      </c>
+      <c r="M339" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="M339" s="1" t="n">
+      <c r="N339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -15072,9 +16092,12 @@
         <v>0.02325</v>
       </c>
       <c r="L340" s="1" t="n">
-        <v>0.02325</v>
+        <v>0.02326</v>
       </c>
       <c r="M340" s="1" t="n">
+        <v>0.02326</v>
+      </c>
+      <c r="N340" s="1" t="n">
         <v>0.02305</v>
       </c>
     </row>
@@ -15115,9 +16138,12 @@
         <v>0.4559</v>
       </c>
       <c r="L341" s="1" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="M341" s="1" t="n">
         <v>0.4577</v>
       </c>
-      <c r="M341" s="1" t="n">
+      <c r="N341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -15158,9 +16184,12 @@
         <v>0.01352</v>
       </c>
       <c r="L342" s="1" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="M342" s="1" t="n">
         <v>0.01352</v>
       </c>
-      <c r="M342" s="1" t="n">
+      <c r="N342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -15201,9 +16230,12 @@
         <v>2.885</v>
       </c>
       <c r="L343" s="1" t="n">
+        <v>2.884</v>
+      </c>
+      <c r="M343" s="1" t="n">
         <v>2.89</v>
       </c>
-      <c r="M343" s="1" t="n">
+      <c r="N343" s="1" t="n">
         <v>2.872</v>
       </c>
     </row>
@@ -15244,9 +16276,12 @@
         <v>0.1525</v>
       </c>
       <c r="L344" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="M344" s="1" t="n">
         <v>0.1577</v>
       </c>
-      <c r="M344" s="1" t="n">
+      <c r="N344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -15287,9 +16322,12 @@
         <v>0.005407</v>
       </c>
       <c r="L345" s="1" t="n">
+        <v>0.005394</v>
+      </c>
+      <c r="M345" s="1" t="n">
         <v>0.005407</v>
       </c>
-      <c r="M345" s="1" t="n">
+      <c r="N345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -15330,9 +16368,12 @@
         <v>0.05777</v>
       </c>
       <c r="L346" s="1" t="n">
+        <v>0.05776</v>
+      </c>
+      <c r="M346" s="1" t="n">
         <v>0.0579</v>
       </c>
-      <c r="M346" s="1" t="n">
+      <c r="N346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -15373,9 +16414,12 @@
         <v>2605</v>
       </c>
       <c r="L347" s="1" t="n">
+        <v>2600</v>
+      </c>
+      <c r="M347" s="1" t="n">
         <v>2613</v>
       </c>
-      <c r="M347" s="1" t="n">
+      <c r="N347" s="1" t="n">
         <v>2597</v>
       </c>
     </row>
@@ -15416,9 +16460,12 @@
         <v>0.04635</v>
       </c>
       <c r="L348" s="1" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="M348" s="1" t="n">
         <v>0.04642</v>
       </c>
-      <c r="M348" s="1" t="n">
+      <c r="N348" s="1" t="n">
         <v>0.04595</v>
       </c>
     </row>
@@ -15459,9 +16506,12 @@
         <v>0.005625</v>
       </c>
       <c r="L349" s="1" t="n">
+        <v>0.005661</v>
+      </c>
+      <c r="M349" s="1" t="n">
         <v>0.005714</v>
       </c>
-      <c r="M349" s="1" t="n">
+      <c r="N349" s="1" t="n">
         <v>0.005625</v>
       </c>
     </row>
@@ -15502,9 +16552,12 @@
         <v>195.78</v>
       </c>
       <c r="L350" s="1" t="n">
+        <v>195.79</v>
+      </c>
+      <c r="M350" s="1" t="n">
         <v>195.95</v>
       </c>
-      <c r="M350" s="1" t="n">
+      <c r="N350" s="1" t="n">
         <v>195.23</v>
       </c>
     </row>
@@ -15545,9 +16598,12 @@
         <v>0.08241999999999999</v>
       </c>
       <c r="L351" s="1" t="n">
+        <v>0.08235000000000001</v>
+      </c>
+      <c r="M351" s="1" t="n">
         <v>0.08245</v>
       </c>
-      <c r="M351" s="1" t="n">
+      <c r="N351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -15588,10 +16644,13 @@
         <v>0.007455</v>
       </c>
       <c r="L352" s="1" t="n">
+        <v>0.00741</v>
+      </c>
+      <c r="M352" s="1" t="n">
         <v>0.007571</v>
       </c>
-      <c r="M352" s="1" t="n">
-        <v>0.007436</v>
+      <c r="N352" s="1" t="n">
+        <v>0.00741</v>
       </c>
     </row>
     <row r="353">
@@ -15631,9 +16690,12 @@
         <v>1.4823</v>
       </c>
       <c r="L353" s="1" t="n">
+        <v>1.4827</v>
+      </c>
+      <c r="M353" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="M353" s="1" t="n">
+      <c r="N353" s="1" t="n">
         <v>1.4807</v>
       </c>
     </row>
@@ -15674,9 +16736,12 @@
         <v>0.07675999999999999</v>
       </c>
       <c r="L354" s="1" t="n">
+        <v>0.07656</v>
+      </c>
+      <c r="M354" s="1" t="n">
         <v>0.07677</v>
       </c>
-      <c r="M354" s="1" t="n">
+      <c r="N354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -15717,10 +16782,13 @@
         <v>0.04861</v>
       </c>
       <c r="L355" s="1" t="n">
+        <v>0.04839</v>
+      </c>
+      <c r="M355" s="1" t="n">
         <v>0.04921</v>
       </c>
-      <c r="M355" s="1" t="n">
-        <v>0.04855</v>
+      <c r="N355" s="1" t="n">
+        <v>0.04839</v>
       </c>
     </row>
     <row r="356">
@@ -15760,9 +16828,12 @@
         <v>0.2871</v>
       </c>
       <c r="L356" s="1" t="n">
-        <v>0.2871</v>
+        <v>0.2872</v>
       </c>
       <c r="M356" s="1" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="N356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -15803,9 +16874,12 @@
         <v>0.1473</v>
       </c>
       <c r="L357" s="1" t="n">
+        <v>0.1472</v>
+      </c>
+      <c r="M357" s="1" t="n">
         <v>0.1473</v>
       </c>
-      <c r="M357" s="1" t="n">
+      <c r="N357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -15846,10 +16920,13 @@
         <v>1.353</v>
       </c>
       <c r="L358" s="1" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="M358" s="1" t="n">
         <v>1.355</v>
       </c>
-      <c r="M358" s="1" t="n">
-        <v>1.349</v>
+      <c r="N358" s="1" t="n">
+        <v>1.348</v>
       </c>
     </row>
     <row r="359">
@@ -15892,6 +16969,9 @@
         <v>0.6136</v>
       </c>
       <c r="M359" s="1" t="n">
+        <v>0.6136</v>
+      </c>
+      <c r="N359" s="1" t="n">
         <v>0.6081</v>
       </c>
     </row>
@@ -15932,9 +17012,12 @@
         <v>0.1149</v>
       </c>
       <c r="L360" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="M360" s="1" t="n">
         <v>0.1149</v>
       </c>
-      <c r="M360" s="1" t="n">
+      <c r="N360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -15975,9 +17058,12 @@
         <v>0.02656</v>
       </c>
       <c r="L361" s="1" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="M361" s="1" t="n">
         <v>0.02678</v>
       </c>
-      <c r="M361" s="1" t="n">
+      <c r="N361" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -16021,6 +17107,9 @@
         <v>3.05e-05</v>
       </c>
       <c r="M362" s="1" t="n">
+        <v>3.05e-05</v>
+      </c>
+      <c r="N362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -16061,9 +17150,12 @@
         <v>0.0104</v>
       </c>
       <c r="L363" s="1" t="n">
+        <v>0.01025</v>
+      </c>
+      <c r="M363" s="1" t="n">
         <v>0.01047</v>
       </c>
-      <c r="M363" s="1" t="n">
+      <c r="N363" s="1" t="n">
         <v>0.01018</v>
       </c>
     </row>
@@ -16104,9 +17196,12 @@
         <v>0.06227</v>
       </c>
       <c r="L364" s="1" t="n">
+        <v>0.06227</v>
+      </c>
+      <c r="M364" s="1" t="n">
         <v>0.06233</v>
       </c>
-      <c r="M364" s="1" t="n">
+      <c r="N364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -16147,9 +17242,12 @@
         <v>0.03285</v>
       </c>
       <c r="L365" s="1" t="n">
+        <v>0.03275</v>
+      </c>
+      <c r="M365" s="1" t="n">
         <v>0.03299</v>
       </c>
-      <c r="M365" s="1" t="n">
+      <c r="N365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -16190,9 +17288,12 @@
         <v>0.03325</v>
       </c>
       <c r="L366" s="1" t="n">
-        <v>0.0333</v>
+        <v>0.0334</v>
       </c>
       <c r="M366" s="1" t="n">
+        <v>0.0334</v>
+      </c>
+      <c r="N366" s="1" t="n">
         <v>0.03283</v>
       </c>
     </row>
@@ -16233,9 +17334,12 @@
         <v>0.012357</v>
       </c>
       <c r="L367" s="1" t="n">
+        <v>0.012295</v>
+      </c>
+      <c r="M367" s="1" t="n">
         <v>0.012357</v>
       </c>
-      <c r="M367" s="1" t="n">
+      <c r="N367" s="1" t="n">
         <v>0.012155</v>
       </c>
     </row>
@@ -16276,9 +17380,12 @@
         <v>0.03569</v>
       </c>
       <c r="L368" s="1" t="n">
+        <v>0.03571</v>
+      </c>
+      <c r="M368" s="1" t="n">
         <v>0.03574</v>
       </c>
-      <c r="M368" s="1" t="n">
+      <c r="N368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -16319,9 +17426,12 @@
         <v>0.6283</v>
       </c>
       <c r="L369" s="1" t="n">
+        <v>0.6279</v>
+      </c>
+      <c r="M369" s="1" t="n">
         <v>0.6307</v>
       </c>
-      <c r="M369" s="1" t="n">
+      <c r="N369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -16362,10 +17472,13 @@
         <v>0.008359999999999999</v>
       </c>
       <c r="L370" s="1" t="n">
+        <v>0.008149999999999999</v>
+      </c>
+      <c r="M370" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="M370" s="1" t="n">
-        <v>0.008359999999999999</v>
+      <c r="N370" s="1" t="n">
+        <v>0.008149999999999999</v>
       </c>
     </row>
     <row r="371">
@@ -16405,9 +17518,12 @@
         <v>0.004166</v>
       </c>
       <c r="L371" s="1" t="n">
+        <v>0.004139</v>
+      </c>
+      <c r="M371" s="1" t="n">
         <v>0.004166</v>
       </c>
-      <c r="M371" s="1" t="n">
+      <c r="N371" s="1" t="n">
         <v>0.003242</v>
       </c>
     </row>
@@ -16448,9 +17564,12 @@
         <v>0.13378</v>
       </c>
       <c r="L372" s="1" t="n">
+        <v>0.13362</v>
+      </c>
+      <c r="M372" s="1" t="n">
         <v>0.13391</v>
       </c>
-      <c r="M372" s="1" t="n">
+      <c r="N372" s="1" t="n">
         <v>0.13227</v>
       </c>
     </row>
@@ -16491,10 +17610,13 @@
         <v>0.007772</v>
       </c>
       <c r="L373" s="1" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="M373" s="1" t="n">
         <v>0.007822000000000001</v>
       </c>
-      <c r="M373" s="1" t="n">
-        <v>0.007771</v>
+      <c r="N373" s="1" t="n">
+        <v>0.00776</v>
       </c>
     </row>
     <row r="374">
@@ -16534,9 +17656,12 @@
         <v>0.02003</v>
       </c>
       <c r="L374" s="1" t="n">
+        <v>0.01994</v>
+      </c>
+      <c r="M374" s="1" t="n">
         <v>0.02003</v>
       </c>
-      <c r="M374" s="1" t="n">
+      <c r="N374" s="1" t="n">
         <v>0.01969</v>
       </c>
     </row>
@@ -16577,9 +17702,12 @@
         <v>0.000592</v>
       </c>
       <c r="L375" s="1" t="n">
+        <v>0.0005922</v>
+      </c>
+      <c r="M375" s="1" t="n">
         <v>0.000594</v>
       </c>
-      <c r="M375" s="1" t="n">
+      <c r="N375" s="1" t="n">
         <v>0.0005910000000000001</v>
       </c>
     </row>
@@ -16623,6 +17751,9 @@
         <v>0.0363</v>
       </c>
       <c r="M376" s="1" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="N376" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -16663,9 +17794,12 @@
         <v>0.0007947</v>
       </c>
       <c r="L377" s="1" t="n">
-        <v>0.0007956</v>
+        <v>0.000796</v>
       </c>
       <c r="M377" s="1" t="n">
+        <v>0.000796</v>
+      </c>
+      <c r="N377" s="1" t="n">
         <v>0.0007848</v>
       </c>
     </row>
@@ -16706,9 +17840,12 @@
         <v>2.038</v>
       </c>
       <c r="L378" s="1" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M378" s="1" t="n">
         <v>2.044</v>
       </c>
-      <c r="M378" s="1" t="n">
+      <c r="N378" s="1" t="n">
         <v>1.973</v>
       </c>
     </row>
@@ -16749,9 +17886,12 @@
         <v>0.0005932</v>
       </c>
       <c r="L379" s="1" t="n">
+        <v>0.0005928</v>
+      </c>
+      <c r="M379" s="1" t="n">
         <v>0.0005932</v>
       </c>
-      <c r="M379" s="1" t="n">
+      <c r="N379" s="1" t="n">
         <v>0.0005881</v>
       </c>
     </row>
@@ -16792,9 +17932,12 @@
         <v>0.03753</v>
       </c>
       <c r="L380" s="1" t="n">
-        <v>0.03756</v>
+        <v>0.03764</v>
       </c>
       <c r="M380" s="1" t="n">
+        <v>0.03764</v>
+      </c>
+      <c r="N380" s="1" t="n">
         <v>0.03737</v>
       </c>
     </row>
@@ -16835,9 +17978,12 @@
         <v>0.05476</v>
       </c>
       <c r="L381" s="1" t="n">
+        <v>0.05473</v>
+      </c>
+      <c r="M381" s="1" t="n">
         <v>0.05486</v>
       </c>
-      <c r="M381" s="1" t="n">
+      <c r="N381" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -16878,9 +18024,12 @@
         <v>0.01214</v>
       </c>
       <c r="L382" s="1" t="n">
+        <v>0.01213</v>
+      </c>
+      <c r="M382" s="1" t="n">
         <v>0.01214</v>
       </c>
-      <c r="M382" s="1" t="n">
+      <c r="N382" s="1" t="n">
         <v>0.01202</v>
       </c>
     </row>
@@ -16921,9 +18070,12 @@
         <v>0.001554</v>
       </c>
       <c r="L383" s="1" t="n">
+        <v>0.001553</v>
+      </c>
+      <c r="M383" s="1" t="n">
         <v>0.001559</v>
       </c>
-      <c r="M383" s="1" t="n">
+      <c r="N383" s="1" t="n">
         <v>0.001549</v>
       </c>
     </row>
@@ -16964,9 +18116,12 @@
         <v>0.0002167</v>
       </c>
       <c r="L384" s="1" t="n">
+        <v>0.0002166</v>
+      </c>
+      <c r="M384" s="1" t="n">
         <v>0.0002167</v>
       </c>
-      <c r="M384" s="1" t="n">
+      <c r="N384" s="1" t="n">
         <v>0.0002154</v>
       </c>
     </row>
@@ -17010,6 +18165,9 @@
         <v>0.00243</v>
       </c>
       <c r="M385" s="1" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="N385" s="1" t="n">
         <v>0.0024</v>
       </c>
     </row>
@@ -17050,9 +18208,12 @@
         <v>3.954</v>
       </c>
       <c r="L386" s="1" t="n">
-        <v>3.954</v>
+        <v>3.955</v>
       </c>
       <c r="M386" s="1" t="n">
+        <v>3.955</v>
+      </c>
+      <c r="N386" s="1" t="n">
         <v>3.892</v>
       </c>
     </row>
@@ -17093,9 +18254,12 @@
         <v>0.0006308</v>
       </c>
       <c r="L387" s="1" t="n">
+        <v>0.0006299</v>
+      </c>
+      <c r="M387" s="1" t="n">
         <v>0.0006316</v>
       </c>
-      <c r="M387" s="1" t="n">
+      <c r="N387" s="1" t="n">
         <v>0.0006236</v>
       </c>
     </row>
@@ -17136,9 +18300,12 @@
         <v>0.00656</v>
       </c>
       <c r="L388" s="1" t="n">
+        <v>0.00656</v>
+      </c>
+      <c r="M388" s="1" t="n">
         <v>0.00673</v>
       </c>
-      <c r="M388" s="1" t="n">
+      <c r="N388" s="1" t="n">
         <v>0.00653</v>
       </c>
     </row>
@@ -17179,9 +18346,12 @@
         <v>0.1323</v>
       </c>
       <c r="L389" s="1" t="n">
-        <v>0.1324</v>
+        <v>0.1325</v>
       </c>
       <c r="M389" s="1" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="N389" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -17222,9 +18392,12 @@
         <v>0.03234</v>
       </c>
       <c r="L390" s="1" t="n">
+        <v>0.03229</v>
+      </c>
+      <c r="M390" s="1" t="n">
         <v>0.03248</v>
       </c>
-      <c r="M390" s="1" t="n">
+      <c r="N390" s="1" t="n">
         <v>0.03201</v>
       </c>
     </row>
@@ -17265,9 +18438,12 @@
         <v>0.06401999999999999</v>
       </c>
       <c r="L391" s="1" t="n">
+        <v>0.06393</v>
+      </c>
+      <c r="M391" s="1" t="n">
         <v>0.06401999999999999</v>
       </c>
-      <c r="M391" s="1" t="n">
+      <c r="N391" s="1" t="n">
         <v>0.06344</v>
       </c>
     </row>
@@ -17308,9 +18484,12 @@
         <v>27.95</v>
       </c>
       <c r="L392" s="1" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="M392" s="1" t="n">
         <v>27.95</v>
       </c>
-      <c r="M392" s="1" t="n">
+      <c r="N392" s="1" t="n">
         <v>27.57</v>
       </c>
     </row>
@@ -17354,6 +18533,9 @@
         <v>0.000416</v>
       </c>
       <c r="M393" s="1" t="n">
+        <v>0.000416</v>
+      </c>
+      <c r="N393" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -17394,9 +18576,12 @@
         <v>0.06993000000000001</v>
       </c>
       <c r="L394" s="1" t="n">
+        <v>0.06970999999999999</v>
+      </c>
+      <c r="M394" s="1" t="n">
         <v>0.07005</v>
       </c>
-      <c r="M394" s="1" t="n">
+      <c r="N394" s="1" t="n">
         <v>0.06926</v>
       </c>
     </row>
@@ -17437,9 +18622,12 @@
         <v>0.2613</v>
       </c>
       <c r="L395" s="1" t="n">
+        <v>0.2612</v>
+      </c>
+      <c r="M395" s="1" t="n">
         <v>0.2614</v>
       </c>
-      <c r="M395" s="1" t="n">
+      <c r="N395" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -17480,9 +18668,12 @@
         <v>0.004691</v>
       </c>
       <c r="L396" s="1" t="n">
+        <v>0.004688</v>
+      </c>
+      <c r="M396" s="1" t="n">
         <v>0.004693</v>
       </c>
-      <c r="M396" s="1" t="n">
+      <c r="N396" s="1" t="n">
         <v>0.004677</v>
       </c>
     </row>
@@ -17523,9 +18714,12 @@
         <v>0.2353</v>
       </c>
       <c r="L397" s="1" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="M397" s="1" t="n">
         <v>0.2367</v>
       </c>
-      <c r="M397" s="1" t="n">
+      <c r="N397" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
@@ -17566,9 +18760,12 @@
         <v>0.18222</v>
       </c>
       <c r="L398" s="1" t="n">
+        <v>0.18218</v>
+      </c>
+      <c r="M398" s="1" t="n">
         <v>0.18235</v>
       </c>
-      <c r="M398" s="1" t="n">
+      <c r="N398" s="1" t="n">
         <v>0.18106</v>
       </c>
     </row>
@@ -17609,9 +18806,12 @@
         <v>0.04147</v>
       </c>
       <c r="L399" s="1" t="n">
-        <v>0.0415</v>
+        <v>0.04151</v>
       </c>
       <c r="M399" s="1" t="n">
+        <v>0.04151</v>
+      </c>
+      <c r="N399" s="1" t="n">
         <v>0.04108</v>
       </c>
     </row>
@@ -17655,6 +18855,9 @@
         <v>0.076</v>
       </c>
       <c r="M400" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="N400" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -17695,9 +18898,12 @@
         <v>0.001752</v>
       </c>
       <c r="L401" s="1" t="n">
+        <v>0.001752</v>
+      </c>
+      <c r="M401" s="1" t="n">
         <v>0.001766</v>
       </c>
-      <c r="M401" s="1" t="n">
+      <c r="N401" s="1" t="n">
         <v>0.001739</v>
       </c>
     </row>
@@ -17738,9 +18944,12 @@
         <v>0.05399</v>
       </c>
       <c r="L402" s="1" t="n">
-        <v>0.05402</v>
+        <v>0.05403</v>
       </c>
       <c r="M402" s="1" t="n">
+        <v>0.05403</v>
+      </c>
+      <c r="N402" s="1" t="n">
         <v>0.05362</v>
       </c>
     </row>
@@ -17781,9 +18990,12 @@
         <v>2026.92</v>
       </c>
       <c r="L403" s="1" t="n">
+        <v>2027.2</v>
+      </c>
+      <c r="M403" s="1" t="n">
         <v>2031.8</v>
       </c>
-      <c r="M403" s="1" t="n">
+      <c r="N403" s="1" t="n">
         <v>2026.65</v>
       </c>
     </row>
@@ -17824,9 +19036,12 @@
         <v>1.081</v>
       </c>
       <c r="L404" s="1" t="n">
+        <v>1.079</v>
+      </c>
+      <c r="M404" s="1" t="n">
         <v>1.082</v>
       </c>
-      <c r="M404" s="1" t="n">
+      <c r="N404" s="1" t="n">
         <v>1.078</v>
       </c>
     </row>
@@ -17867,10 +19082,13 @@
         <v>7.647</v>
       </c>
       <c r="L405" s="1" t="n">
+        <v>7.645</v>
+      </c>
+      <c r="M405" s="1" t="n">
         <v>7.673</v>
       </c>
-      <c r="M405" s="1" t="n">
-        <v>7.647</v>
+      <c r="N405" s="1" t="n">
+        <v>7.645</v>
       </c>
     </row>
     <row r="406">
@@ -17910,9 +19128,12 @@
         <v>3.263</v>
       </c>
       <c r="L406" s="1" t="n">
+        <v>3.259</v>
+      </c>
+      <c r="M406" s="1" t="n">
         <v>3.274</v>
       </c>
-      <c r="M406" s="1" t="n">
+      <c r="N406" s="1" t="n">
         <v>3.238</v>
       </c>
     </row>
@@ -17953,9 +19174,12 @@
         <v>0.1825</v>
       </c>
       <c r="L407" s="1" t="n">
+        <v>0.1822</v>
+      </c>
+      <c r="M407" s="1" t="n">
         <v>0.1825</v>
       </c>
-      <c r="M407" s="1" t="n">
+      <c r="N407" s="1" t="n">
         <v>0.1814</v>
       </c>
     </row>
@@ -17996,9 +19220,12 @@
         <v>0.1525</v>
       </c>
       <c r="L408" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="M408" s="1" t="n">
         <v>0.1537</v>
       </c>
-      <c r="M408" s="1" t="n">
+      <c r="N408" s="1" t="n">
         <v>0.1525</v>
       </c>
     </row>
@@ -18039,9 +19266,12 @@
         <v>0.07376000000000001</v>
       </c>
       <c r="L409" s="1" t="n">
+        <v>0.07382</v>
+      </c>
+      <c r="M409" s="1" t="n">
         <v>0.07385</v>
       </c>
-      <c r="M409" s="1" t="n">
+      <c r="N409" s="1" t="n">
         <v>0.07315000000000001</v>
       </c>
     </row>
@@ -18082,9 +19312,12 @@
         <v>0.02124</v>
       </c>
       <c r="L410" s="1" t="n">
+        <v>0.02118</v>
+      </c>
+      <c r="M410" s="1" t="n">
         <v>0.02124</v>
       </c>
-      <c r="M410" s="1" t="n">
+      <c r="N410" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -18125,9 +19358,12 @@
         <v>0.268</v>
       </c>
       <c r="L411" s="1" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="M411" s="1" t="n">
         <v>0.2683</v>
       </c>
-      <c r="M411" s="1" t="n">
+      <c r="N411" s="1" t="n">
         <v>0.2642</v>
       </c>
     </row>
@@ -18168,9 +19404,12 @@
         <v>0.007404</v>
       </c>
       <c r="L412" s="1" t="n">
+        <v>0.007401</v>
+      </c>
+      <c r="M412" s="1" t="n">
         <v>0.007404</v>
       </c>
-      <c r="M412" s="1" t="n">
+      <c r="N412" s="1" t="n">
         <v>0.007302</v>
       </c>
     </row>
@@ -18211,9 +19450,12 @@
         <v>0.01392</v>
       </c>
       <c r="L413" s="1" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="M413" s="1" t="n">
         <v>0.01392</v>
       </c>
-      <c r="M413" s="1" t="n">
+      <c r="N413" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -18257,6 +19499,9 @@
         <v>0.093</v>
       </c>
       <c r="M414" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="N414" s="1" t="n">
         <v>0.092</v>
       </c>
     </row>
@@ -18297,9 +19542,12 @@
         <v>0.04007</v>
       </c>
       <c r="L415" s="1" t="n">
+        <v>0.04009</v>
+      </c>
+      <c r="M415" s="1" t="n">
         <v>0.04015</v>
       </c>
-      <c r="M415" s="1" t="n">
+      <c r="N415" s="1" t="n">
         <v>0.03985</v>
       </c>
     </row>
@@ -18340,9 +19588,12 @@
         <v>0.2841</v>
       </c>
       <c r="L416" s="1" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="M416" s="1" t="n">
         <v>0.2854</v>
       </c>
-      <c r="M416" s="1" t="n">
+      <c r="N416" s="1" t="n">
         <v>0.2839</v>
       </c>
     </row>
@@ -18383,9 +19634,12 @@
         <v>1.825</v>
       </c>
       <c r="L417" s="1" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="M417" s="1" t="n">
         <v>1.831</v>
       </c>
-      <c r="M417" s="1" t="n">
+      <c r="N417" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -18426,9 +19680,12 @@
         <v>0.06704</v>
       </c>
       <c r="L418" s="1" t="n">
+        <v>0.06712</v>
+      </c>
+      <c r="M418" s="1" t="n">
         <v>0.06718</v>
       </c>
-      <c r="M418" s="1" t="n">
+      <c r="N418" s="1" t="n">
         <v>0.06668</v>
       </c>
     </row>
@@ -18469,9 +19726,12 @@
         <v>207.38</v>
       </c>
       <c r="L419" s="1" t="n">
-        <v>207.47</v>
+        <v>207.59</v>
       </c>
       <c r="M419" s="1" t="n">
+        <v>207.59</v>
+      </c>
+      <c r="N419" s="1" t="n">
         <v>207.35</v>
       </c>
     </row>
@@ -18512,9 +19772,12 @@
         <v>73.34999999999999</v>
       </c>
       <c r="L420" s="1" t="n">
+        <v>73.34</v>
+      </c>
+      <c r="M420" s="1" t="n">
         <v>73.37</v>
       </c>
-      <c r="M420" s="1" t="n">
+      <c r="N420" s="1" t="n">
         <v>73.15000000000001</v>
       </c>
     </row>
@@ -18555,9 +19818,12 @@
         <v>0.07235</v>
       </c>
       <c r="L421" s="1" t="n">
+        <v>0.07227</v>
+      </c>
+      <c r="M421" s="1" t="n">
         <v>0.07251000000000001</v>
       </c>
-      <c r="M421" s="1" t="n">
+      <c r="N421" s="1" t="n">
         <v>0.07226</v>
       </c>
     </row>
@@ -18598,9 +19864,12 @@
         <v>0.0502</v>
       </c>
       <c r="L422" s="1" t="n">
+        <v>0.05031</v>
+      </c>
+      <c r="M422" s="1" t="n">
         <v>0.05076</v>
       </c>
-      <c r="M422" s="1" t="n">
+      <c r="N422" s="1" t="n">
         <v>0.04998</v>
       </c>
     </row>
@@ -18641,9 +19910,12 @@
         <v>0.001153</v>
       </c>
       <c r="L423" s="1" t="n">
+        <v>0.001152</v>
+      </c>
+      <c r="M423" s="1" t="n">
         <v>0.001153</v>
       </c>
-      <c r="M423" s="1" t="n">
+      <c r="N423" s="1" t="n">
         <v>0.001148</v>
       </c>
     </row>
@@ -18684,9 +19956,12 @@
         <v>0.00503</v>
       </c>
       <c r="L424" s="1" t="n">
+        <v>0.00504</v>
+      </c>
+      <c r="M424" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="M424" s="1" t="n">
+      <c r="N424" s="1" t="n">
         <v>0.00501</v>
       </c>
     </row>
@@ -18727,9 +20002,12 @@
         <v>0.1279</v>
       </c>
       <c r="L425" s="1" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="M425" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="M425" s="1" t="n">
+      <c r="N425" s="1" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -18773,6 +20051,9 @@
         <v>1.301</v>
       </c>
       <c r="M426" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="N426" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -18813,9 +20094,12 @@
         <v>0.004421</v>
       </c>
       <c r="L427" s="1" t="n">
+        <v>0.00442</v>
+      </c>
+      <c r="M427" s="1" t="n">
         <v>0.004421</v>
       </c>
-      <c r="M427" s="1" t="n">
+      <c r="N427" s="1" t="n">
         <v>0.004393</v>
       </c>
     </row>
@@ -18856,9 +20140,12 @@
         <v>0.005063</v>
       </c>
       <c r="L428" s="1" t="n">
+        <v>0.005071</v>
+      </c>
+      <c r="M428" s="1" t="n">
         <v>0.005072</v>
       </c>
-      <c r="M428" s="1" t="n">
+      <c r="N428" s="1" t="n">
         <v>0.005017</v>
       </c>
     </row>
@@ -18899,9 +20186,12 @@
         <v>0.02323</v>
       </c>
       <c r="L429" s="1" t="n">
+        <v>0.02322</v>
+      </c>
+      <c r="M429" s="1" t="n">
         <v>0.02329</v>
       </c>
-      <c r="M429" s="1" t="n">
+      <c r="N429" s="1" t="n">
         <v>0.02288</v>
       </c>
     </row>
@@ -18942,9 +20232,12 @@
         <v>0.02509</v>
       </c>
       <c r="L430" s="1" t="n">
+        <v>0.02509</v>
+      </c>
+      <c r="M430" s="1" t="n">
         <v>0.02517</v>
       </c>
-      <c r="M430" s="1" t="n">
+      <c r="N430" s="1" t="n">
         <v>0.02499</v>
       </c>
     </row>
@@ -18985,9 +20278,12 @@
         <v>0.016</v>
       </c>
       <c r="L431" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="M431" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="M431" s="1" t="n">
+      <c r="N431" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -19028,10 +20324,13 @@
         <v>0.5432</v>
       </c>
       <c r="L432" s="1" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M432" s="1" t="n">
         <v>0.546</v>
       </c>
-      <c r="M432" s="1" t="n">
-        <v>0.5432</v>
+      <c r="N432" s="1" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="433">
@@ -19071,9 +20370,12 @@
         <v>0.00139</v>
       </c>
       <c r="L433" s="1" t="n">
+        <v>0.001388</v>
+      </c>
+      <c r="M433" s="1" t="n">
         <v>0.00139</v>
       </c>
-      <c r="M433" s="1" t="n">
+      <c r="N433" s="1" t="n">
         <v>0.001383</v>
       </c>
     </row>
@@ -19114,9 +20416,12 @@
         <v>0.3975</v>
       </c>
       <c r="L434" s="1" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="M434" s="1" t="n">
         <v>0.3975</v>
       </c>
-      <c r="M434" s="1" t="n">
+      <c r="N434" s="1" t="n">
         <v>0.3925</v>
       </c>
     </row>
@@ -19160,6 +20465,9 @@
         <v>0.001393</v>
       </c>
       <c r="M435" s="1" t="n">
+        <v>0.001393</v>
+      </c>
+      <c r="N435" s="1" t="n">
         <v>0.001388</v>
       </c>
     </row>
@@ -19203,6 +20511,9 @@
         <v>0.00718</v>
       </c>
       <c r="M436" s="1" t="n">
+        <v>0.00718</v>
+      </c>
+      <c r="N436" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -19243,9 +20554,12 @@
         <v>0.00201</v>
       </c>
       <c r="L437" s="1" t="n">
+        <v>0.002006</v>
+      </c>
+      <c r="M437" s="1" t="n">
         <v>0.002012</v>
       </c>
-      <c r="M437" s="1" t="n">
+      <c r="N437" s="1" t="n">
         <v>0.001982</v>
       </c>
     </row>
@@ -19289,6 +20603,9 @@
         <v>0.3147</v>
       </c>
       <c r="M438" s="1" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="N438" s="1" t="n">
         <v>0.3122</v>
       </c>
     </row>
@@ -19329,9 +20646,12 @@
         <v>0.04448</v>
       </c>
       <c r="L439" s="1" t="n">
+        <v>0.04447</v>
+      </c>
+      <c r="M439" s="1" t="n">
         <v>0.04448</v>
       </c>
-      <c r="M439" s="1" t="n">
+      <c r="N439" s="1" t="n">
         <v>0.04426</v>
       </c>
     </row>
@@ -19372,9 +20692,12 @@
         <v>0.913</v>
       </c>
       <c r="L440" s="1" t="n">
-        <v>0.913</v>
+        <v>0.914</v>
       </c>
       <c r="M440" s="1" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="N440" s="1" t="n">
         <v>0.906</v>
       </c>
     </row>
@@ -19415,9 +20738,12 @@
         <v>1550.86</v>
       </c>
       <c r="L441" s="1" t="n">
+        <v>1551.41</v>
+      </c>
+      <c r="M441" s="1" t="n">
         <v>1552.4</v>
       </c>
-      <c r="M441" s="1" t="n">
+      <c r="N441" s="1" t="n">
         <v>1548.06</v>
       </c>
     </row>
@@ -19458,9 +20784,12 @@
         <v>0.0008023</v>
       </c>
       <c r="L442" s="1" t="n">
+        <v>0.0008050000000000001</v>
+      </c>
+      <c r="M442" s="1" t="n">
         <v>0.0008061</v>
       </c>
-      <c r="M442" s="1" t="n">
+      <c r="N442" s="1" t="n">
         <v>0.0007877</v>
       </c>
     </row>
@@ -19501,9 +20830,12 @@
         <v>0.003524</v>
       </c>
       <c r="L443" s="1" t="n">
+        <v>0.003523</v>
+      </c>
+      <c r="M443" s="1" t="n">
         <v>0.003558</v>
       </c>
-      <c r="M443" s="1" t="n">
+      <c r="N443" s="1" t="n">
         <v>0.003515</v>
       </c>
     </row>
@@ -19544,9 +20876,12 @@
         <v>1.99</v>
       </c>
       <c r="L444" s="1" t="n">
+        <v>1.991</v>
+      </c>
+      <c r="M444" s="1" t="n">
         <v>1.994</v>
       </c>
-      <c r="M444" s="1" t="n">
+      <c r="N444" s="1" t="n">
         <v>1.977</v>
       </c>
     </row>
@@ -19587,9 +20922,12 @@
         <v>1.321</v>
       </c>
       <c r="L445" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M445" s="1" t="n">
         <v>1.321</v>
       </c>
-      <c r="M445" s="1" t="n">
+      <c r="N445" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -19630,9 +20968,12 @@
         <v>0.06902999999999999</v>
       </c>
       <c r="L446" s="1" t="n">
+        <v>0.06902</v>
+      </c>
+      <c r="M446" s="1" t="n">
         <v>0.06929</v>
       </c>
-      <c r="M446" s="1" t="n">
+      <c r="N446" s="1" t="n">
         <v>0.0689</v>
       </c>
     </row>
@@ -19673,9 +21014,12 @@
         <v>0.02391</v>
       </c>
       <c r="L447" s="1" t="n">
-        <v>0.02403</v>
+        <v>0.02412</v>
       </c>
       <c r="M447" s="1" t="n">
+        <v>0.02412</v>
+      </c>
+      <c r="N447" s="1" t="n">
         <v>0.02347</v>
       </c>
     </row>
@@ -19716,9 +21060,12 @@
         <v>0.01403</v>
       </c>
       <c r="L448" s="1" t="n">
+        <v>0.01403</v>
+      </c>
+      <c r="M448" s="1" t="n">
         <v>0.0141</v>
       </c>
-      <c r="M448" s="1" t="n">
+      <c r="N448" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -19759,9 +21106,12 @@
         <v>3.744</v>
       </c>
       <c r="L449" s="1" t="n">
+        <v>3.737</v>
+      </c>
+      <c r="M449" s="1" t="n">
         <v>3.748</v>
       </c>
-      <c r="M449" s="1" t="n">
+      <c r="N449" s="1" t="n">
         <v>3.726</v>
       </c>
     </row>
@@ -19802,9 +21152,12 @@
         <v>0.0114</v>
       </c>
       <c r="L450" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="M450" s="1" t="n">
         <v>0.0115</v>
       </c>
-      <c r="M450" s="1" t="n">
+      <c r="N450" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -19845,9 +21198,12 @@
         <v>0.01039</v>
       </c>
       <c r="L451" s="1" t="n">
-        <v>0.01039</v>
+        <v>0.01041</v>
       </c>
       <c r="M451" s="1" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="N451" s="1" t="n">
         <v>0.01024</v>
       </c>
     </row>
@@ -19891,6 +21247,9 @@
         <v>0.1532</v>
       </c>
       <c r="M452" s="1" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="N452" s="1" t="n">
         <v>0.1522</v>
       </c>
     </row>
@@ -19931,9 +21290,12 @@
         <v>151.28</v>
       </c>
       <c r="L453" s="1" t="n">
-        <v>151.29</v>
+        <v>151.3</v>
       </c>
       <c r="M453" s="1" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="N453" s="1" t="n">
         <v>150.85</v>
       </c>
     </row>
@@ -19974,9 +21336,12 @@
         <v>0.008637000000000001</v>
       </c>
       <c r="L454" s="1" t="n">
+        <v>0.008629</v>
+      </c>
+      <c r="M454" s="1" t="n">
         <v>0.008639000000000001</v>
       </c>
-      <c r="M454" s="1" t="n">
+      <c r="N454" s="1" t="n">
         <v>0.008593999999999999</v>
       </c>
     </row>
@@ -20020,6 +21385,9 @@
         <v>0.0526</v>
       </c>
       <c r="M455" s="1" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="N455" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -20060,9 +21428,12 @@
         <v>0.30886</v>
       </c>
       <c r="L456" s="1" t="n">
-        <v>0.30925</v>
+        <v>0.3095</v>
       </c>
       <c r="M456" s="1" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="N456" s="1" t="n">
         <v>0.30269</v>
       </c>
     </row>
@@ -20103,9 +21474,12 @@
         <v>0.0055</v>
       </c>
       <c r="L457" s="1" t="n">
-        <v>0.0055</v>
+        <v>0.00552</v>
       </c>
       <c r="M457" s="1" t="n">
+        <v>0.00552</v>
+      </c>
+      <c r="N457" s="1" t="n">
         <v>0.00544</v>
       </c>
     </row>
@@ -20146,9 +21520,12 @@
         <v>0.1007</v>
       </c>
       <c r="L458" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="M458" s="1" t="n">
         <v>0.1008</v>
       </c>
-      <c r="M458" s="1" t="n">
+      <c r="N458" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -20189,9 +21566,12 @@
         <v>0.001844</v>
       </c>
       <c r="L459" s="1" t="n">
-        <v>0.001844</v>
+        <v>0.001846</v>
       </c>
       <c r="M459" s="1" t="n">
+        <v>0.001846</v>
+      </c>
+      <c r="N459" s="1" t="n">
         <v>0.001825</v>
       </c>
     </row>
@@ -20232,9 +21612,12 @@
         <v>0.01845</v>
       </c>
       <c r="L460" s="1" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="M460" s="1" t="n">
         <v>0.01848</v>
       </c>
-      <c r="M460" s="1" t="n">
+      <c r="N460" s="1" t="n">
         <v>0.01822</v>
       </c>
     </row>
@@ -20275,9 +21658,12 @@
         <v>0.0004888</v>
       </c>
       <c r="L461" s="1" t="n">
+        <v>0.0004882</v>
+      </c>
+      <c r="M461" s="1" t="n">
         <v>0.0004888</v>
       </c>
-      <c r="M461" s="1" t="n">
+      <c r="N461" s="1" t="n">
         <v>0.0004842</v>
       </c>
     </row>
@@ -20318,9 +21704,12 @@
         <v>0.0968</v>
       </c>
       <c r="L462" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="M462" s="1" t="n">
         <v>0.0968</v>
       </c>
-      <c r="M462" s="1" t="n">
+      <c r="N462" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -20361,9 +21750,12 @@
         <v>0.0794</v>
       </c>
       <c r="L463" s="1" t="n">
+        <v>0.07933999999999999</v>
+      </c>
+      <c r="M463" s="1" t="n">
         <v>0.07954</v>
       </c>
-      <c r="M463" s="1" t="n">
+      <c r="N463" s="1" t="n">
         <v>0.07888000000000001</v>
       </c>
     </row>
@@ -20404,9 +21796,12 @@
         <v>0.03235</v>
       </c>
       <c r="L464" s="1" t="n">
+        <v>0.03212</v>
+      </c>
+      <c r="M464" s="1" t="n">
         <v>0.03235</v>
       </c>
-      <c r="M464" s="1" t="n">
+      <c r="N464" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -20447,9 +21842,12 @@
         <v>0.01623</v>
       </c>
       <c r="L465" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="M465" s="1" t="n">
         <v>0.01623</v>
       </c>
-      <c r="M465" s="1" t="n">
+      <c r="N465" s="1" t="n">
         <v>0.01613</v>
       </c>
     </row>
@@ -20490,9 +21888,12 @@
         <v>0.06787</v>
       </c>
       <c r="L466" s="1" t="n">
+        <v>0.06788</v>
+      </c>
+      <c r="M466" s="1" t="n">
         <v>0.06794</v>
       </c>
-      <c r="M466" s="1" t="n">
+      <c r="N466" s="1" t="n">
         <v>0.06763</v>
       </c>
     </row>
@@ -20533,9 +21934,12 @@
         <v>0.04337</v>
       </c>
       <c r="L467" s="1" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="M467" s="1" t="n">
         <v>0.04344</v>
       </c>
-      <c r="M467" s="1" t="n">
+      <c r="N467" s="1" t="n">
         <v>0.04322</v>
       </c>
     </row>
@@ -20576,9 +21980,12 @@
         <v>0.0564</v>
       </c>
       <c r="L468" s="1" t="n">
+        <v>0.05693</v>
+      </c>
+      <c r="M468" s="1" t="n">
         <v>0.05795</v>
       </c>
-      <c r="M468" s="1" t="n">
+      <c r="N468" s="1" t="n">
         <v>0.05587</v>
       </c>
     </row>
@@ -20619,9 +22026,12 @@
         <v>0.232</v>
       </c>
       <c r="L469" s="1" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="M469" s="1" t="n">
         <v>0.232</v>
       </c>
-      <c r="M469" s="1" t="n">
+      <c r="N469" s="1" t="n">
         <v>0.2294</v>
       </c>
     </row>
@@ -20662,9 +22072,12 @@
         <v>0.0905</v>
       </c>
       <c r="L470" s="1" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="M470" s="1" t="n">
         <v>0.0906</v>
       </c>
-      <c r="M470" s="1" t="n">
+      <c r="N470" s="1" t="n">
         <v>0.0902</v>
       </c>
     </row>
@@ -20705,9 +22118,12 @@
         <v>0.0669</v>
       </c>
       <c r="L471" s="1" t="n">
+        <v>0.06682</v>
+      </c>
+      <c r="M471" s="1" t="n">
         <v>0.06693</v>
       </c>
-      <c r="M471" s="1" t="n">
+      <c r="N471" s="1" t="n">
         <v>0.06660000000000001</v>
       </c>
     </row>
@@ -20748,9 +22164,12 @@
         <v>6.586</v>
       </c>
       <c r="L472" s="1" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="M472" s="1" t="n">
         <v>6.595</v>
       </c>
-      <c r="M472" s="1" t="n">
+      <c r="N472" s="1" t="n">
         <v>6.486</v>
       </c>
     </row>
@@ -20791,9 +22210,12 @@
         <v>0.01948</v>
       </c>
       <c r="L473" s="1" t="n">
+        <v>0.01948</v>
+      </c>
+      <c r="M473" s="1" t="n">
         <v>0.01949</v>
       </c>
-      <c r="M473" s="1" t="n">
+      <c r="N473" s="1" t="n">
         <v>0.01937</v>
       </c>
     </row>
@@ -20834,9 +22256,12 @@
         <v>1.43</v>
       </c>
       <c r="L474" s="1" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M474" s="1" t="n">
         <v>1.431</v>
       </c>
-      <c r="M474" s="1" t="n">
+      <c r="N474" s="1" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -20877,9 +22302,12 @@
         <v>0.09001000000000001</v>
       </c>
       <c r="L475" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="M475" s="1" t="n">
         <v>0.09001000000000001</v>
       </c>
-      <c r="M475" s="1" t="n">
+      <c r="N475" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -20920,9 +22348,12 @@
         <v>0.1064</v>
       </c>
       <c r="L476" s="1" t="n">
-        <v>0.1066</v>
+        <v>0.1067</v>
       </c>
       <c r="M476" s="1" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="N476" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -20963,9 +22394,12 @@
         <v>0.094</v>
       </c>
       <c r="L477" s="1" t="n">
+        <v>0.09407</v>
+      </c>
+      <c r="M477" s="1" t="n">
         <v>0.09451</v>
       </c>
-      <c r="M477" s="1" t="n">
+      <c r="N477" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -21006,9 +22440,12 @@
         <v>0.0001637</v>
       </c>
       <c r="L478" s="1" t="n">
-        <v>0.0001637</v>
+        <v>0.0001641</v>
       </c>
       <c r="M478" s="1" t="n">
+        <v>0.0001641</v>
+      </c>
+      <c r="N478" s="1" t="n">
         <v>0.0001624</v>
       </c>
     </row>
@@ -21049,9 +22486,12 @@
         <v>0.04031</v>
       </c>
       <c r="L479" s="1" t="n">
+        <v>0.04032</v>
+      </c>
+      <c r="M479" s="1" t="n">
         <v>0.04034</v>
       </c>
-      <c r="M479" s="1" t="n">
+      <c r="N479" s="1" t="n">
         <v>0.04007</v>
       </c>
     </row>
@@ -21092,9 +22532,12 @@
         <v>0.007426</v>
       </c>
       <c r="L480" s="1" t="n">
+        <v>0.007422</v>
+      </c>
+      <c r="M480" s="1" t="n">
         <v>0.007442</v>
       </c>
-      <c r="M480" s="1" t="n">
+      <c r="N480" s="1" t="n">
         <v>0.007389</v>
       </c>
     </row>
@@ -21135,9 +22578,12 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="L481" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="M481" s="1" t="n">
         <v>0.09569999999999999</v>
       </c>
-      <c r="M481" s="1" t="n">
+      <c r="N481" s="1" t="n">
         <v>0.0953</v>
       </c>
     </row>
@@ -21178,9 +22624,12 @@
         <v>0.05614</v>
       </c>
       <c r="L482" s="1" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="M482" s="1" t="n">
         <v>0.05621</v>
       </c>
-      <c r="M482" s="1" t="n">
+      <c r="N482" s="1" t="n">
         <v>0.05569</v>
       </c>
     </row>
@@ -21221,9 +22670,12 @@
         <v>0.006187</v>
       </c>
       <c r="L483" s="1" t="n">
+        <v>0.006194</v>
+      </c>
+      <c r="M483" s="1" t="n">
         <v>0.006209</v>
       </c>
-      <c r="M483" s="1" t="n">
+      <c r="N483" s="1" t="n">
         <v>0.006161</v>
       </c>
     </row>
@@ -21264,9 +22716,12 @@
         <v>0.01493</v>
       </c>
       <c r="L484" s="1" t="n">
+        <v>0.01495</v>
+      </c>
+      <c r="M484" s="1" t="n">
         <v>0.01497</v>
       </c>
-      <c r="M484" s="1" t="n">
+      <c r="N484" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -21307,9 +22762,12 @@
         <v>0.02417</v>
       </c>
       <c r="L485" s="1" t="n">
+        <v>0.02406</v>
+      </c>
+      <c r="M485" s="1" t="n">
         <v>0.02427</v>
       </c>
-      <c r="M485" s="1" t="n">
+      <c r="N485" s="1" t="n">
         <v>0.02403</v>
       </c>
     </row>
@@ -21350,9 +22808,12 @@
         <v>0.06707</v>
       </c>
       <c r="L486" s="1" t="n">
-        <v>0.06707</v>
+        <v>0.06713</v>
       </c>
       <c r="M486" s="1" t="n">
+        <v>0.06713</v>
+      </c>
+      <c r="N486" s="1" t="n">
         <v>0.0667</v>
       </c>
     </row>
@@ -21393,9 +22854,12 @@
         <v>0.03692</v>
       </c>
       <c r="L487" s="1" t="n">
+        <v>0.03693</v>
+      </c>
+      <c r="M487" s="1" t="n">
         <v>0.03709</v>
       </c>
-      <c r="M487" s="1" t="n">
+      <c r="N487" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -21436,9 +22900,12 @@
         <v>0.01824</v>
       </c>
       <c r="L488" s="1" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="M488" s="1" t="n">
         <v>0.01826</v>
       </c>
-      <c r="M488" s="1" t="n">
+      <c r="N488" s="1" t="n">
         <v>0.01814</v>
       </c>
     </row>
@@ -21479,9 +22946,12 @@
         <v>0.03285</v>
       </c>
       <c r="L489" s="1" t="n">
+        <v>0.03292</v>
+      </c>
+      <c r="M489" s="1" t="n">
         <v>0.03299</v>
       </c>
-      <c r="M489" s="1" t="n">
+      <c r="N489" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -21522,9 +22992,12 @@
         <v>0.0151</v>
       </c>
       <c r="L490" s="1" t="n">
-        <v>0.0151</v>
+        <v>0.01517</v>
       </c>
       <c r="M490" s="1" t="n">
+        <v>0.01517</v>
+      </c>
+      <c r="N490" s="1" t="n">
         <v>0.01458</v>
       </c>
     </row>
@@ -21565,9 +23038,12 @@
         <v>0.019</v>
       </c>
       <c r="L491" s="1" t="n">
+        <v>0.01885</v>
+      </c>
+      <c r="M491" s="1" t="n">
         <v>0.019</v>
       </c>
-      <c r="M491" s="1" t="n">
+      <c r="N491" s="1" t="n">
         <v>0.01851</v>
       </c>
     </row>
@@ -21608,9 +23084,12 @@
         <v>0.08789</v>
       </c>
       <c r="L492" s="1" t="n">
+        <v>0.08817</v>
+      </c>
+      <c r="M492" s="1" t="n">
         <v>0.08935</v>
       </c>
-      <c r="M492" s="1" t="n">
+      <c r="N492" s="1" t="n">
         <v>0.08784</v>
       </c>
     </row>
@@ -21651,9 +23130,12 @@
         <v>0.006513</v>
       </c>
       <c r="L493" s="1" t="n">
+        <v>0.006502</v>
+      </c>
+      <c r="M493" s="1" t="n">
         <v>0.006521</v>
       </c>
-      <c r="M493" s="1" t="n">
+      <c r="N493" s="1" t="n">
         <v>0.006497</v>
       </c>
     </row>
@@ -21694,9 +23176,12 @@
         <v>0.1331</v>
       </c>
       <c r="L494" s="1" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="M494" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="M494" s="1" t="n">
+      <c r="N494" s="1" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -21737,9 +23222,12 @@
         <v>0.2856</v>
       </c>
       <c r="L495" s="1" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="M495" s="1" t="n">
         <v>0.2859</v>
       </c>
-      <c r="M495" s="1" t="n">
+      <c r="N495" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -21780,9 +23268,12 @@
         <v>0.004562</v>
       </c>
       <c r="L496" s="1" t="n">
+        <v>0.004547</v>
+      </c>
+      <c r="M496" s="1" t="n">
         <v>0.004562</v>
       </c>
-      <c r="M496" s="1" t="n">
+      <c r="N496" s="1" t="n">
         <v>0.004516</v>
       </c>
     </row>
@@ -21823,9 +23314,12 @@
         <v>0.1265</v>
       </c>
       <c r="L497" s="1" t="n">
+        <v>0.1268</v>
+      </c>
+      <c r="M497" s="1" t="n">
         <v>0.1283</v>
       </c>
-      <c r="M497" s="1" t="n">
+      <c r="N497" s="1" t="n">
         <v>0.1264</v>
       </c>
     </row>
@@ -21866,9 +23360,12 @@
         <v>0.03461</v>
       </c>
       <c r="L498" s="1" t="n">
-        <v>0.03461</v>
+        <v>0.03464</v>
       </c>
       <c r="M498" s="1" t="n">
+        <v>0.03464</v>
+      </c>
+      <c r="N498" s="1" t="n">
         <v>0.03423</v>
       </c>
     </row>
@@ -21909,10 +23406,13 @@
         <v>0.03559</v>
       </c>
       <c r="L499" s="1" t="n">
+        <v>0.03551</v>
+      </c>
+      <c r="M499" s="1" t="n">
         <v>0.03576</v>
       </c>
-      <c r="M499" s="1" t="n">
-        <v>0.03557</v>
+      <c r="N499" s="1" t="n">
+        <v>0.03551</v>
       </c>
     </row>
     <row r="500">
@@ -21955,6 +23455,9 @@
         <v>0.003422</v>
       </c>
       <c r="M500" s="1" t="n">
+        <v>0.003422</v>
+      </c>
+      <c r="N500" s="1" t="n">
         <v>0.003413</v>
       </c>
     </row>
@@ -21995,9 +23498,12 @@
         <v>0.0003854</v>
       </c>
       <c r="L501" s="1" t="n">
-        <v>0.0003854</v>
+        <v>0.0003867</v>
       </c>
       <c r="M501" s="1" t="n">
+        <v>0.0003867</v>
+      </c>
+      <c r="N501" s="1" t="n">
         <v>0.0003786</v>
       </c>
     </row>
@@ -22038,9 +23544,12 @@
         <v>0.3005</v>
       </c>
       <c r="L502" s="1" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="M502" s="1" t="n">
         <v>0.3011</v>
       </c>
-      <c r="M502" s="1" t="n">
+      <c r="N502" s="1" t="n">
         <v>0.2986</v>
       </c>
     </row>
@@ -22081,9 +23590,12 @@
         <v>0.06497</v>
       </c>
       <c r="L503" s="1" t="n">
+        <v>0.06494</v>
+      </c>
+      <c r="M503" s="1" t="n">
         <v>0.06507</v>
       </c>
-      <c r="M503" s="1" t="n">
+      <c r="N503" s="1" t="n">
         <v>0.06485</v>
       </c>
     </row>
@@ -22124,9 +23636,12 @@
         <v>0.1784</v>
       </c>
       <c r="L504" s="1" t="n">
-        <v>0.1784</v>
+        <v>0.1787</v>
       </c>
       <c r="M504" s="1" t="n">
+        <v>0.1787</v>
+      </c>
+      <c r="N504" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -22167,9 +23682,12 @@
         <v>0.1517</v>
       </c>
       <c r="L505" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="M505" s="1" t="n">
         <v>0.1519</v>
       </c>
-      <c r="M505" s="1" t="n">
+      <c r="N505" s="1" t="n">
         <v>0.1511</v>
       </c>
     </row>
@@ -22210,9 +23728,12 @@
         <v>0.01205</v>
       </c>
       <c r="L506" s="1" t="n">
+        <v>0.01204</v>
+      </c>
+      <c r="M506" s="1" t="n">
         <v>0.01205</v>
       </c>
-      <c r="M506" s="1" t="n">
+      <c r="N506" s="1" t="n">
         <v>0.01193</v>
       </c>
     </row>
@@ -22253,9 +23774,12 @@
         <v>0.2899</v>
       </c>
       <c r="L507" s="1" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="M507" s="1" t="n">
         <v>0.2899</v>
       </c>
-      <c r="M507" s="1" t="n">
+      <c r="N507" s="1" t="n">
         <v>0.2871</v>
       </c>
     </row>
@@ -22296,9 +23820,12 @@
         <v>0.009390000000000001</v>
       </c>
       <c r="L508" s="1" t="n">
+        <v>0.009379999999999999</v>
+      </c>
+      <c r="M508" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="M508" s="1" t="n">
+      <c r="N508" s="1" t="n">
         <v>0.009310000000000001</v>
       </c>
     </row>
@@ -22339,9 +23866,12 @@
         <v>0.006845</v>
       </c>
       <c r="L509" s="1" t="n">
+        <v>0.006838</v>
+      </c>
+      <c r="M509" s="1" t="n">
         <v>0.006851</v>
       </c>
-      <c r="M509" s="1" t="n">
+      <c r="N509" s="1" t="n">
         <v>0.006783</v>
       </c>
     </row>
@@ -22382,9 +23912,12 @@
         <v>0.2989</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>0.2989</v>
+        <v>0.3019</v>
       </c>
       <c r="M510" s="1" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="N510" s="1" t="n">
         <v>0.2934</v>
       </c>
     </row>
@@ -22425,9 +23958,12 @@
         <v>0.01471</v>
       </c>
       <c r="L511" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="M511" s="1" t="n">
         <v>0.01471</v>
       </c>
-      <c r="M511" s="1" t="n">
+      <c r="N511" s="1" t="n">
         <v>0.01465</v>
       </c>
     </row>
@@ -22468,9 +24004,12 @@
         <v>0.1402</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>0.1402</v>
+        <v>0.1403</v>
       </c>
       <c r="M512" s="1" t="n">
+        <v>0.1403</v>
+      </c>
+      <c r="N512" s="1" t="n">
         <v>0.1394</v>
       </c>
     </row>
@@ -22511,9 +24050,12 @@
         <v>0.08103</v>
       </c>
       <c r="L513" s="1" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="M513" s="1" t="n">
         <v>0.08144999999999999</v>
       </c>
-      <c r="M513" s="1" t="n">
+      <c r="N513" s="1" t="n">
         <v>0.08069</v>
       </c>
     </row>
@@ -22557,6 +24099,9 @@
         <v>0.0251</v>
       </c>
       <c r="M514" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="N514" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -22597,9 +24142,12 @@
         <v>0.06313000000000001</v>
       </c>
       <c r="L515" s="1" t="n">
+        <v>0.06314</v>
+      </c>
+      <c r="M515" s="1" t="n">
         <v>0.06329</v>
       </c>
-      <c r="M515" s="1" t="n">
+      <c r="N515" s="1" t="n">
         <v>0.06301</v>
       </c>
     </row>
@@ -22640,9 +24188,12 @@
         <v>0.0474</v>
       </c>
       <c r="L516" s="1" t="n">
+        <v>0.04728</v>
+      </c>
+      <c r="M516" s="1" t="n">
         <v>0.04752</v>
       </c>
-      <c r="M516" s="1" t="n">
+      <c r="N516" s="1" t="n">
         <v>0.04707</v>
       </c>
     </row>
@@ -22683,9 +24234,12 @@
         <v>0.004935</v>
       </c>
       <c r="L517" s="1" t="n">
-        <v>0.004935</v>
+        <v>0.004942</v>
       </c>
       <c r="M517" s="1" t="n">
+        <v>0.004942</v>
+      </c>
+      <c r="N517" s="1" t="n">
         <v>0.004902</v>
       </c>
     </row>
@@ -22726,9 +24280,12 @@
         <v>0.009504</v>
       </c>
       <c r="L518" s="1" t="n">
+        <v>0.00945</v>
+      </c>
+      <c r="M518" s="1" t="n">
         <v>0.009504</v>
       </c>
-      <c r="M518" s="1" t="n">
+      <c r="N518" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -22769,9 +24326,12 @@
         <v>0.01804</v>
       </c>
       <c r="L519" s="1" t="n">
-        <v>0.01807</v>
+        <v>0.01811</v>
       </c>
       <c r="M519" s="1" t="n">
+        <v>0.01811</v>
+      </c>
+      <c r="N519" s="1" t="n">
         <v>0.01798</v>
       </c>
     </row>
@@ -22812,9 +24372,12 @@
         <v>0.067</v>
       </c>
       <c r="L520" s="1" t="n">
-        <v>0.067</v>
+        <v>0.06723</v>
       </c>
       <c r="M520" s="1" t="n">
+        <v>0.06723</v>
+      </c>
+      <c r="N520" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -22855,9 +24418,12 @@
         <v>0.1373</v>
       </c>
       <c r="L521" s="1" t="n">
-        <v>0.1373</v>
+        <v>0.1374</v>
       </c>
       <c r="M521" s="1" t="n">
+        <v>0.1374</v>
+      </c>
+      <c r="N521" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -22898,9 +24464,12 @@
         <v>0.04768</v>
       </c>
       <c r="L522" s="1" t="n">
-        <v>0.04768</v>
+        <v>0.04772</v>
       </c>
       <c r="M522" s="1" t="n">
+        <v>0.04772</v>
+      </c>
+      <c r="N522" s="1" t="n">
         <v>0.04718</v>
       </c>
     </row>
@@ -22941,9 +24510,12 @@
         <v>0.06822</v>
       </c>
       <c r="L523" s="1" t="n">
+        <v>0.06819</v>
+      </c>
+      <c r="M523" s="1" t="n">
         <v>0.06827</v>
       </c>
-      <c r="M523" s="1" t="n">
+      <c r="N523" s="1" t="n">
         <v>0.06784999999999999</v>
       </c>
     </row>
@@ -22984,9 +24556,12 @@
         <v>0.7019</v>
       </c>
       <c r="L524" s="1" t="n">
-        <v>0.7019</v>
+        <v>0.7055</v>
       </c>
       <c r="M524" s="1" t="n">
+        <v>0.7055</v>
+      </c>
+      <c r="N524" s="1" t="n">
         <v>0.6966</v>
       </c>
     </row>
@@ -23030,6 +24605,9 @@
         <v>0.00269</v>
       </c>
       <c r="M525" s="1" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="N525" s="1" t="n">
         <v>0.00267</v>
       </c>
     </row>
@@ -23070,9 +24648,12 @@
         <v>0.4877</v>
       </c>
       <c r="L526" s="1" t="n">
+        <v>0.4877</v>
+      </c>
+      <c r="M526" s="1" t="n">
         <v>0.488</v>
       </c>
-      <c r="M526" s="1" t="n">
+      <c r="N526" s="1" t="n">
         <v>0.4856</v>
       </c>
     </row>
@@ -23113,9 +24694,12 @@
         <v>45.85</v>
       </c>
       <c r="L527" s="1" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="M527" s="1" t="n">
         <v>45.85</v>
       </c>
-      <c r="M527" s="1" t="n">
+      <c r="N527" s="1" t="n">
         <v>45.76</v>
       </c>
     </row>
@@ -23156,9 +24740,12 @@
         <v>0.02443</v>
       </c>
       <c r="L528" s="1" t="n">
+        <v>0.02439</v>
+      </c>
+      <c r="M528" s="1" t="n">
         <v>0.02447</v>
       </c>
-      <c r="M528" s="1" t="n">
+      <c r="N528" s="1" t="n">
         <v>0.02429</v>
       </c>
     </row>
@@ -23202,6 +24789,9 @@
         <v>0.006427</v>
       </c>
       <c r="M529" s="1" t="n">
+        <v>0.006427</v>
+      </c>
+      <c r="N529" s="1" t="n">
         <v>0.00638</v>
       </c>
     </row>
@@ -23245,6 +24835,9 @@
         <v>0.2011</v>
       </c>
       <c r="M530" s="1" t="n">
+        <v>0.2011</v>
+      </c>
+      <c r="N530" s="1" t="n">
         <v>0.1993</v>
       </c>
     </row>
@@ -23285,9 +24878,12 @@
         <v>0.007695</v>
       </c>
       <c r="L531" s="1" t="n">
+        <v>0.007676</v>
+      </c>
+      <c r="M531" s="1" t="n">
         <v>0.007727</v>
       </c>
-      <c r="M531" s="1" t="n">
+      <c r="N531" s="1" t="n">
         <v>0.007657</v>
       </c>
     </row>
@@ -23328,9 +24924,12 @@
         <v>2.292</v>
       </c>
       <c r="L532" s="1" t="n">
+        <v>2.291</v>
+      </c>
+      <c r="M532" s="1" t="n">
         <v>2.302</v>
       </c>
-      <c r="M532" s="1" t="n">
+      <c r="N532" s="1" t="n">
         <v>2.275</v>
       </c>
     </row>
@@ -23371,9 +24970,12 @@
         <v>0.04175</v>
       </c>
       <c r="L533" s="1" t="n">
+        <v>0.04177</v>
+      </c>
+      <c r="M533" s="1" t="n">
         <v>0.04186</v>
       </c>
-      <c r="M533" s="1" t="n">
+      <c r="N533" s="1" t="n">
         <v>0.04138</v>
       </c>
     </row>
@@ -23414,9 +25016,12 @@
         <v>0.1829</v>
       </c>
       <c r="L534" s="1" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="M534" s="1" t="n">
         <v>0.1833</v>
       </c>
-      <c r="M534" s="1" t="n">
+      <c r="N534" s="1" t="n">
         <v>0.1811</v>
       </c>
     </row>
@@ -23457,9 +25062,12 @@
         <v>0.04368</v>
       </c>
       <c r="L535" s="1" t="n">
-        <v>0.04372</v>
+        <v>0.04373</v>
       </c>
       <c r="M535" s="1" t="n">
+        <v>0.04373</v>
+      </c>
+      <c r="N535" s="1" t="n">
         <v>0.04287</v>
       </c>
     </row>
@@ -23500,9 +25108,12 @@
         <v>0.05427</v>
       </c>
       <c r="L536" s="1" t="n">
+        <v>0.05421</v>
+      </c>
+      <c r="M536" s="1" t="n">
         <v>0.05438</v>
       </c>
-      <c r="M536" s="1" t="n">
+      <c r="N536" s="1" t="n">
         <v>0.05409</v>
       </c>
     </row>
@@ -23543,9 +25154,12 @@
         <v>0.1603</v>
       </c>
       <c r="L537" s="1" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="M537" s="1" t="n">
         <v>0.1611</v>
       </c>
-      <c r="M537" s="1" t="n">
+      <c r="N537" s="1" t="n">
         <v>0.1602</v>
       </c>
     </row>
@@ -23586,9 +25200,12 @@
         <v>0.03684</v>
       </c>
       <c r="L538" s="1" t="n">
+        <v>0.03673</v>
+      </c>
+      <c r="M538" s="1" t="n">
         <v>0.03687</v>
       </c>
-      <c r="M538" s="1" t="n">
+      <c r="N538" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -23629,9 +25246,12 @@
         <v>0.05864</v>
       </c>
       <c r="L539" s="1" t="n">
+        <v>0.05839</v>
+      </c>
+      <c r="M539" s="1" t="n">
         <v>0.0587</v>
       </c>
-      <c r="M539" s="1" t="n">
+      <c r="N539" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -23672,9 +25292,12 @@
         <v>0.04286</v>
       </c>
       <c r="L540" s="1" t="n">
+        <v>0.04281</v>
+      </c>
+      <c r="M540" s="1" t="n">
         <v>0.04286</v>
       </c>
-      <c r="M540" s="1" t="n">
+      <c r="N540" s="1" t="n">
         <v>0.04256</v>
       </c>
     </row>
@@ -23715,9 +25338,12 @@
         <v>0.01727</v>
       </c>
       <c r="L541" s="1" t="n">
+        <v>0.01728</v>
+      </c>
+      <c r="M541" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="M541" s="1" t="n">
+      <c r="N541" s="1" t="n">
         <v>0.0172</v>
       </c>
     </row>
@@ -23758,9 +25384,12 @@
         <v>0.003965</v>
       </c>
       <c r="L542" s="1" t="n">
+        <v>0.003968</v>
+      </c>
+      <c r="M542" s="1" t="n">
         <v>0.003975</v>
       </c>
-      <c r="M542" s="1" t="n">
+      <c r="N542" s="1" t="n">
         <v>0.003963</v>
       </c>
     </row>
@@ -23801,9 +25430,12 @@
         <v>0.05798</v>
       </c>
       <c r="L543" s="1" t="n">
+        <v>0.05773</v>
+      </c>
+      <c r="M543" s="1" t="n">
         <v>0.05835</v>
       </c>
-      <c r="M543" s="1" t="n">
+      <c r="N543" s="1" t="n">
         <v>0.05735</v>
       </c>
     </row>
@@ -23844,9 +25476,12 @@
         <v>0.05026</v>
       </c>
       <c r="L544" s="1" t="n">
+        <v>0.05024</v>
+      </c>
+      <c r="M544" s="1" t="n">
         <v>0.05042</v>
       </c>
-      <c r="M544" s="1" t="n">
+      <c r="N544" s="1" t="n">
         <v>0.05016</v>
       </c>
     </row>
@@ -23887,9 +25522,12 @@
         <v>0.04089</v>
       </c>
       <c r="L545" s="1" t="n">
+        <v>0.04079</v>
+      </c>
+      <c r="M545" s="1" t="n">
         <v>0.04089</v>
       </c>
-      <c r="M545" s="1" t="n">
+      <c r="N545" s="1" t="n">
         <v>0.04038</v>
       </c>
     </row>
@@ -23930,9 +25568,12 @@
         <v>0.007429</v>
       </c>
       <c r="L546" s="1" t="n">
+        <v>0.007426</v>
+      </c>
+      <c r="M546" s="1" t="n">
         <v>0.007436</v>
       </c>
-      <c r="M546" s="1" t="n">
+      <c r="N546" s="1" t="n">
         <v>0.007402</v>
       </c>
     </row>
@@ -23973,9 +25614,12 @@
         <v>0.01482</v>
       </c>
       <c r="L547" s="1" t="n">
+        <v>0.01484</v>
+      </c>
+      <c r="M547" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="M547" s="1" t="n">
+      <c r="N547" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -24016,9 +25660,12 @@
         <v>0.01574</v>
       </c>
       <c r="L548" s="1" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="M548" s="1" t="n">
         <v>0.01576</v>
       </c>
-      <c r="M548" s="1" t="n">
+      <c r="N548" s="1" t="n">
         <v>0.0157</v>
       </c>
     </row>
@@ -24059,9 +25706,12 @@
         <v>0.13553</v>
       </c>
       <c r="L549" s="1" t="n">
-        <v>0.13562</v>
+        <v>0.13569</v>
       </c>
       <c r="M549" s="1" t="n">
+        <v>0.13569</v>
+      </c>
+      <c r="N549" s="1" t="n">
         <v>0.13271</v>
       </c>
     </row>
@@ -24102,9 +25752,12 @@
         <v>0.1704</v>
       </c>
       <c r="L550" s="1" t="n">
+        <v>0.1703</v>
+      </c>
+      <c r="M550" s="1" t="n">
         <v>0.1706</v>
       </c>
-      <c r="M550" s="1" t="n">
+      <c r="N550" s="1" t="n">
         <v>0.1693</v>
       </c>
     </row>
@@ -24145,9 +25798,12 @@
         <v>0.003576</v>
       </c>
       <c r="L551" s="1" t="n">
+        <v>0.003581</v>
+      </c>
+      <c r="M551" s="1" t="n">
         <v>0.003593</v>
       </c>
-      <c r="M551" s="1" t="n">
+      <c r="N551" s="1" t="n">
         <v>0.003576</v>
       </c>
     </row>
@@ -24188,9 +25844,12 @@
         <v>0.03055</v>
       </c>
       <c r="L552" s="1" t="n">
+        <v>0.03053</v>
+      </c>
+      <c r="M552" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="M552" s="1" t="n">
+      <c r="N552" s="1" t="n">
         <v>0.0303</v>
       </c>
     </row>
@@ -24231,10 +25890,13 @@
         <v>0.01321</v>
       </c>
       <c r="L553" s="1" t="n">
+        <v>0.01316</v>
+      </c>
+      <c r="M553" s="1" t="n">
         <v>0.01325</v>
       </c>
-      <c r="M553" s="1" t="n">
-        <v>0.01319</v>
+      <c r="N553" s="1" t="n">
+        <v>0.01316</v>
       </c>
     </row>
     <row r="554">
@@ -24274,9 +25936,12 @@
         <v>0.1044</v>
       </c>
       <c r="L554" s="1" t="n">
+        <v>0.1044</v>
+      </c>
+      <c r="M554" s="1" t="n">
         <v>0.1046</v>
       </c>
-      <c r="M554" s="1" t="n">
+      <c r="N554" s="1" t="n">
         <v>0.1039</v>
       </c>
     </row>
@@ -24317,9 +25982,12 @@
         <v>0.05314</v>
       </c>
       <c r="L555" s="1" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="M555" s="1" t="n">
         <v>0.05319</v>
       </c>
-      <c r="M555" s="1" t="n">
+      <c r="N555" s="1" t="n">
         <v>0.05291</v>
       </c>
     </row>
@@ -24360,9 +26028,12 @@
         <v>0.01224</v>
       </c>
       <c r="L556" s="1" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="M556" s="1" t="n">
         <v>0.01234</v>
       </c>
-      <c r="M556" s="1" t="n">
+      <c r="N556" s="1" t="n">
         <v>0.01218</v>
       </c>
     </row>

--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N556"/>
+  <dimension ref="A1:O556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -431,8 +431,9 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,10 +499,15 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>price_02:45</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -547,9 +553,12 @@
         <v>71696.5</v>
       </c>
       <c r="M2" s="1" t="n">
+        <v>71655.39999999999</v>
+      </c>
+      <c r="N2" s="1" t="n">
         <v>71788</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="O2" s="1" t="n">
         <v>71364.39999999999</v>
       </c>
     </row>
@@ -593,9 +602,12 @@
         <v>2107.36</v>
       </c>
       <c r="M3" s="1" t="n">
+        <v>2108.53</v>
+      </c>
+      <c r="N3" s="1" t="n">
         <v>2109.75</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="O3" s="1" t="n">
         <v>2090.41</v>
       </c>
     </row>
@@ -639,9 +651,12 @@
         <v>88.48999999999999</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>88.5</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="N4" s="1" t="n">
+        <v>88.51000000000001</v>
+      </c>
+      <c r="O4" s="1" t="n">
         <v>87.47</v>
       </c>
     </row>
@@ -685,9 +700,12 @@
         <v>23.179</v>
       </c>
       <c r="M5" s="1" t="n">
+        <v>23.052</v>
+      </c>
+      <c r="N5" s="1" t="n">
         <v>23.579</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="O5" s="1" t="n">
         <v>23.043</v>
       </c>
     </row>
@@ -731,9 +749,12 @@
         <v>0.001826</v>
       </c>
       <c r="M6" s="1" t="n">
+        <v>0.001817</v>
+      </c>
+      <c r="N6" s="1" t="n">
         <v>0.001892</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.001811</v>
       </c>
     </row>
@@ -777,9 +798,12 @@
         <v>1.4168</v>
       </c>
       <c r="M7" s="1" t="n">
+        <v>1.4175</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <v>1.4184</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="O7" s="1" t="n">
         <v>1.4117</v>
       </c>
     </row>
@@ -823,9 +847,12 @@
         <v>0.010642</v>
       </c>
       <c r="M8" s="1" t="n">
+        <v>0.010498</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <v>0.011244</v>
       </c>
-      <c r="N8" s="1" t="n">
+      <c r="O8" s="1" t="n">
         <v>0.010407</v>
       </c>
     </row>
@@ -869,9 +896,12 @@
         <v>4.059</v>
       </c>
       <c r="M9" s="1" t="n">
+        <v>4.017</v>
+      </c>
+      <c r="N9" s="1" t="n">
         <v>4.062</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="O9" s="1" t="n">
         <v>3.954</v>
       </c>
     </row>
@@ -915,9 +945,12 @@
         <v>284.04</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>284.04</v>
+        <v>288.82</v>
       </c>
       <c r="N10" s="1" t="n">
+        <v>288.82</v>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>272.11</v>
       </c>
     </row>
@@ -961,10 +994,13 @@
         <v>0.07778</v>
       </c>
       <c r="M11" s="1" t="n">
+        <v>0.07757</v>
+      </c>
+      <c r="N11" s="1" t="n">
         <v>0.08047</v>
       </c>
-      <c r="N11" s="1" t="n">
-        <v>0.07764</v>
+      <c r="O11" s="1" t="n">
+        <v>0.07757</v>
       </c>
     </row>
     <row r="12">
@@ -1007,9 +1043,12 @@
         <v>227.37</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>227.69</v>
+        <v>227.74</v>
       </c>
       <c r="N12" s="1" t="n">
+        <v>227.74</v>
+      </c>
+      <c r="O12" s="1" t="n">
         <v>223.76</v>
       </c>
     </row>
@@ -1053,9 +1092,12 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="M13" s="1" t="n">
+        <v>0.09524000000000001</v>
+      </c>
+      <c r="N13" s="1" t="n">
         <v>0.09543</v>
       </c>
-      <c r="N13" s="1" t="n">
+      <c r="O13" s="1" t="n">
         <v>0.0946</v>
       </c>
     </row>
@@ -1099,9 +1141,12 @@
         <v>37.059</v>
       </c>
       <c r="M14" s="1" t="n">
+        <v>37.103</v>
+      </c>
+      <c r="N14" s="1" t="n">
         <v>37.361</v>
       </c>
-      <c r="N14" s="1" t="n">
+      <c r="O14" s="1" t="n">
         <v>37.059</v>
       </c>
     </row>
@@ -1145,10 +1190,13 @@
         <v>0.09046</v>
       </c>
       <c r="M15" s="1" t="n">
+        <v>0.08894000000000001</v>
+      </c>
+      <c r="N15" s="1" t="n">
         <v>0.09845</v>
       </c>
-      <c r="N15" s="1" t="n">
-        <v>0.08938</v>
+      <c r="O15" s="1" t="n">
+        <v>0.08894000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1191,9 +1239,12 @@
         <v>0.2258</v>
       </c>
       <c r="M16" s="1" t="n">
+        <v>0.2267</v>
+      </c>
+      <c r="N16" s="1" t="n">
         <v>0.2339</v>
       </c>
-      <c r="N16" s="1" t="n">
+      <c r="O16" s="1" t="n">
         <v>0.2256</v>
       </c>
     </row>
@@ -1237,9 +1288,12 @@
         <v>0.011575</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0.011575</v>
+        <v>0.011627</v>
       </c>
       <c r="N17" s="1" t="n">
+        <v>0.011627</v>
+      </c>
+      <c r="O17" s="1" t="n">
         <v>0.011379</v>
       </c>
     </row>
@@ -1283,9 +1337,12 @@
         <v>661.3</v>
       </c>
       <c r="M18" s="1" t="n">
+        <v>661.25</v>
+      </c>
+      <c r="N18" s="1" t="n">
         <v>661.9</v>
       </c>
-      <c r="N18" s="1" t="n">
+      <c r="O18" s="1" t="n">
         <v>658.89</v>
       </c>
     </row>
@@ -1329,9 +1386,12 @@
         <v>0.003361</v>
       </c>
       <c r="M19" s="1" t="n">
+        <v>0.003363</v>
+      </c>
+      <c r="N19" s="1" t="n">
         <v>0.003368</v>
       </c>
-      <c r="N19" s="1" t="n">
+      <c r="O19" s="1" t="n">
         <v>0.0033271</v>
       </c>
     </row>
@@ -1375,10 +1435,13 @@
         <v>0.17367</v>
       </c>
       <c r="M20" s="1" t="n">
+        <v>0.17083</v>
+      </c>
+      <c r="N20" s="1" t="n">
         <v>0.18066</v>
       </c>
-      <c r="N20" s="1" t="n">
-        <v>0.17367</v>
+      <c r="O20" s="1" t="n">
+        <v>0.17083</v>
       </c>
     </row>
     <row r="21">
@@ -1421,9 +1484,12 @@
         <v>0.009929</v>
       </c>
       <c r="M21" s="1" t="n">
+        <v>0.009871</v>
+      </c>
+      <c r="N21" s="1" t="n">
         <v>0.010044</v>
       </c>
-      <c r="N21" s="1" t="n">
+      <c r="O21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -1467,9 +1533,12 @@
         <v>1.0063</v>
       </c>
       <c r="M22" s="1" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="N22" s="1" t="n">
         <v>1.009</v>
       </c>
-      <c r="N22" s="1" t="n">
+      <c r="O22" s="1" t="n">
         <v>0.9985000000000001</v>
       </c>
     </row>
@@ -1513,9 +1582,12 @@
         <v>5007.37</v>
       </c>
       <c r="M23" s="1" t="n">
+        <v>5005.92</v>
+      </c>
+      <c r="N23" s="1" t="n">
         <v>5012.25</v>
       </c>
-      <c r="N23" s="1" t="n">
+      <c r="O23" s="1" t="n">
         <v>5002.67</v>
       </c>
     </row>
@@ -1559,9 +1631,12 @@
         <v>0.2639</v>
       </c>
       <c r="M24" s="1" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="N24" s="1" t="n">
         <v>0.2645</v>
       </c>
-      <c r="N24" s="1" t="n">
+      <c r="O24" s="1" t="n">
         <v>0.2625</v>
       </c>
     </row>
@@ -1605,9 +1680,12 @@
         <v>2.873</v>
       </c>
       <c r="M25" s="1" t="n">
+        <v>2.881</v>
+      </c>
+      <c r="N25" s="1" t="n">
         <v>2.924</v>
       </c>
-      <c r="N25" s="1" t="n">
+      <c r="O25" s="1" t="n">
         <v>2.873</v>
       </c>
     </row>
@@ -1651,9 +1729,12 @@
         <v>0.3879</v>
       </c>
       <c r="M26" s="1" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="N26" s="1" t="n">
         <v>0.4096</v>
       </c>
-      <c r="N26" s="1" t="n">
+      <c r="O26" s="1" t="n">
         <v>0.3825</v>
       </c>
     </row>
@@ -1697,9 +1778,12 @@
         <v>0.886</v>
       </c>
       <c r="M27" s="1" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="N27" s="1" t="n">
         <v>0.889</v>
       </c>
-      <c r="N27" s="1" t="n">
+      <c r="O27" s="1" t="n">
         <v>0.881</v>
       </c>
     </row>
@@ -1743,9 +1827,12 @@
         <v>1.342</v>
       </c>
       <c r="M28" s="1" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="N28" s="1" t="n">
         <v>1.346</v>
       </c>
-      <c r="N28" s="1" t="n">
+      <c r="O28" s="1" t="n">
         <v>1.335</v>
       </c>
     </row>
@@ -1789,9 +1876,12 @@
         <v>9.192</v>
       </c>
       <c r="M29" s="1" t="n">
+        <v>9.196</v>
+      </c>
+      <c r="N29" s="1" t="n">
         <v>9.205</v>
       </c>
-      <c r="N29" s="1" t="n">
+      <c r="O29" s="1" t="n">
         <v>9.131</v>
       </c>
     </row>
@@ -1835,9 +1925,12 @@
         <v>462.21</v>
       </c>
       <c r="M30" s="1" t="n">
+        <v>462.45</v>
+      </c>
+      <c r="N30" s="1" t="n">
         <v>463.35</v>
       </c>
-      <c r="N30" s="1" t="n">
+      <c r="O30" s="1" t="n">
         <v>461.24</v>
       </c>
     </row>
@@ -1881,9 +1974,12 @@
         <v>9.763999999999999</v>
       </c>
       <c r="M31" s="1" t="n">
+        <v>9.763999999999999</v>
+      </c>
+      <c r="N31" s="1" t="n">
         <v>9.771000000000001</v>
       </c>
-      <c r="N31" s="1" t="n">
+      <c r="O31" s="1" t="n">
         <v>9.696999999999999</v>
       </c>
     </row>
@@ -1927,9 +2023,12 @@
         <v>0.36048</v>
       </c>
       <c r="M32" s="1" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="N32" s="1" t="n">
         <v>0.36683</v>
       </c>
-      <c r="N32" s="1" t="n">
+      <c r="O32" s="1" t="n">
         <v>0.35998</v>
       </c>
     </row>
@@ -1973,9 +2072,12 @@
         <v>1.417</v>
       </c>
       <c r="M33" s="1" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N33" s="1" t="n">
         <v>1.421</v>
       </c>
-      <c r="N33" s="1" t="n">
+      <c r="O33" s="1" t="n">
         <v>1.409</v>
       </c>
     </row>
@@ -2019,9 +2121,12 @@
         <v>0.59069</v>
       </c>
       <c r="M34" s="1" t="n">
+        <v>0.59116</v>
+      </c>
+      <c r="N34" s="1" t="n">
         <v>0.59693</v>
       </c>
-      <c r="N34" s="1" t="n">
+      <c r="O34" s="1" t="n">
         <v>0.58086</v>
       </c>
     </row>
@@ -2065,9 +2170,12 @@
         <v>1.2242</v>
       </c>
       <c r="M35" s="1" t="n">
+        <v>1.2261</v>
+      </c>
+      <c r="N35" s="1" t="n">
         <v>1.2283</v>
       </c>
-      <c r="N35" s="1" t="n">
+      <c r="O35" s="1" t="n">
         <v>1.2186</v>
       </c>
     </row>
@@ -2111,9 +2219,12 @@
         <v>80.38</v>
       </c>
       <c r="M36" s="1" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="N36" s="1" t="n">
         <v>80.5</v>
       </c>
-      <c r="N36" s="1" t="n">
+      <c r="O36" s="1" t="n">
         <v>80.27</v>
       </c>
     </row>
@@ -2157,9 +2268,12 @@
         <v>0.1991</v>
       </c>
       <c r="M37" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N37" s="1" t="n">
         <v>0.204</v>
       </c>
-      <c r="N37" s="1" t="n">
+      <c r="O37" s="1" t="n">
         <v>0.1967</v>
       </c>
     </row>
@@ -2203,9 +2317,12 @@
         <v>1.867</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>1.867</v>
+        <v>1.897</v>
       </c>
       <c r="N38" s="1" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="O38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -2249,9 +2366,12 @@
         <v>0.3337</v>
       </c>
       <c r="M39" s="1" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="N39" s="1" t="n">
         <v>0.3382</v>
       </c>
-      <c r="N39" s="1" t="n">
+      <c r="O39" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -2295,10 +2415,13 @@
         <v>0.8846000000000001</v>
       </c>
       <c r="M40" s="1" t="n">
+        <v>0.8845</v>
+      </c>
+      <c r="N40" s="1" t="n">
         <v>0.9115</v>
       </c>
-      <c r="N40" s="1" t="n">
-        <v>0.8846000000000001</v>
+      <c r="O40" s="1" t="n">
+        <v>0.8845</v>
       </c>
     </row>
     <row r="41">
@@ -2341,9 +2464,12 @@
         <v>0.7121</v>
       </c>
       <c r="M41" s="1" t="n">
+        <v>0.7117</v>
+      </c>
+      <c r="N41" s="1" t="n">
         <v>0.7151999999999999</v>
       </c>
-      <c r="N41" s="1" t="n">
+      <c r="O41" s="1" t="n">
         <v>0.7115</v>
       </c>
     </row>
@@ -2387,10 +2513,13 @@
         <v>0.06562999999999999</v>
       </c>
       <c r="M42" s="1" t="n">
+        <v>0.06544</v>
+      </c>
+      <c r="N42" s="1" t="n">
         <v>0.06769</v>
       </c>
-      <c r="N42" s="1" t="n">
-        <v>0.06551999999999999</v>
+      <c r="O42" s="1" t="n">
+        <v>0.06544</v>
       </c>
     </row>
     <row r="43">
@@ -2433,9 +2562,12 @@
         <v>114.5</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>114.65</v>
+        <v>115.35</v>
       </c>
       <c r="N43" s="1" t="n">
+        <v>115.35</v>
+      </c>
+      <c r="O43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -2479,9 +2611,12 @@
         <v>0.6552</v>
       </c>
       <c r="M44" s="1" t="n">
+        <v>0.6572</v>
+      </c>
+      <c r="N44" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="N44" s="1" t="n">
+      <c r="O44" s="1" t="n">
         <v>0.6536999999999999</v>
       </c>
     </row>
@@ -2528,6 +2663,9 @@
         <v>1.227</v>
       </c>
       <c r="N45" s="1" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="O45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -2571,9 +2709,12 @@
         <v>0.02387</v>
       </c>
       <c r="M46" s="1" t="n">
+        <v>0.02385</v>
+      </c>
+      <c r="N46" s="1" t="n">
         <v>0.02392</v>
       </c>
-      <c r="N46" s="1" t="n">
+      <c r="O46" s="1" t="n">
         <v>0.02375</v>
       </c>
     </row>
@@ -2617,9 +2758,12 @@
         <v>55.13</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>55.19</v>
+        <v>55.23</v>
       </c>
       <c r="N47" s="1" t="n">
+        <v>55.23</v>
+      </c>
+      <c r="O47" s="1" t="n">
         <v>54.99</v>
       </c>
     </row>
@@ -2663,9 +2807,12 @@
         <v>0.06074</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.061</v>
+        <v>0.06112</v>
       </c>
       <c r="N48" s="1" t="n">
+        <v>0.06112</v>
+      </c>
+      <c r="O48" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -2709,9 +2856,12 @@
         <v>0.1082</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.1086</v>
+        <v>0.1088</v>
       </c>
       <c r="N49" s="1" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="O49" s="1" t="n">
         <v>0.1076</v>
       </c>
     </row>
@@ -2755,9 +2905,12 @@
         <v>0.01807</v>
       </c>
       <c r="M50" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="N50" s="1" t="n">
         <v>0.01815</v>
       </c>
-      <c r="N50" s="1" t="n">
+      <c r="O50" s="1" t="n">
         <v>0.01795</v>
       </c>
     </row>
@@ -2801,9 +2954,12 @@
         <v>1.4787</v>
       </c>
       <c r="M51" s="1" t="n">
+        <v>1.4748</v>
+      </c>
+      <c r="N51" s="1" t="n">
         <v>1.4817</v>
       </c>
-      <c r="N51" s="1" t="n">
+      <c r="O51" s="1" t="n">
         <v>1.4618</v>
       </c>
     </row>
@@ -2850,6 +3006,9 @@
         <v>0.3617</v>
       </c>
       <c r="N52" s="1" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="O52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -2893,9 +3052,12 @@
         <v>0.001943</v>
       </c>
       <c r="M53" s="1" t="n">
+        <v>0.001943</v>
+      </c>
+      <c r="N53" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="N53" s="1" t="n">
+      <c r="O53" s="1" t="n">
         <v>0.001939</v>
       </c>
     </row>
@@ -2939,9 +3101,12 @@
         <v>0.09572</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>0.09574000000000001</v>
+        <v>0.09594999999999999</v>
       </c>
       <c r="N54" s="1" t="n">
+        <v>0.09594999999999999</v>
+      </c>
+      <c r="O54" s="1" t="n">
         <v>0.09514</v>
       </c>
     </row>
@@ -2985,9 +3150,12 @@
         <v>0.04092</v>
       </c>
       <c r="M55" s="1" t="n">
+        <v>0.04081</v>
+      </c>
+      <c r="N55" s="1" t="n">
         <v>0.04099</v>
       </c>
-      <c r="N55" s="1" t="n">
+      <c r="O55" s="1" t="n">
         <v>0.04003</v>
       </c>
     </row>
@@ -3031,10 +3199,13 @@
         <v>0.29821</v>
       </c>
       <c r="M56" s="1" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="N56" s="1" t="n">
         <v>0.29861</v>
       </c>
-      <c r="N56" s="1" t="n">
-        <v>0.29821</v>
+      <c r="O56" s="1" t="n">
+        <v>0.29817</v>
       </c>
     </row>
     <row r="57">
@@ -3077,9 +3248,12 @@
         <v>0.005676</v>
       </c>
       <c r="M57" s="1" t="n">
+        <v>0.005692</v>
+      </c>
+      <c r="N57" s="1" t="n">
         <v>0.005824</v>
       </c>
-      <c r="N57" s="1" t="n">
+      <c r="O57" s="1" t="n">
         <v>0.005633</v>
       </c>
     </row>
@@ -3123,9 +3297,12 @@
         <v>4992.33</v>
       </c>
       <c r="M58" s="1" t="n">
+        <v>4990.01</v>
+      </c>
+      <c r="N58" s="1" t="n">
         <v>4998.37</v>
       </c>
-      <c r="N58" s="1" t="n">
+      <c r="O58" s="1" t="n">
         <v>4988.64</v>
       </c>
     </row>
@@ -3169,9 +3346,12 @@
         <v>0.4067</v>
       </c>
       <c r="M59" s="1" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="N59" s="1" t="n">
         <v>0.4246</v>
       </c>
-      <c r="N59" s="1" t="n">
+      <c r="O59" s="1" t="n">
         <v>0.4067</v>
       </c>
     </row>
@@ -3215,9 +3395,12 @@
         <v>0.0463</v>
       </c>
       <c r="M60" s="1" t="n">
+        <v>0.04655</v>
+      </c>
+      <c r="N60" s="1" t="n">
         <v>0.04686</v>
       </c>
-      <c r="N60" s="1" t="n">
+      <c r="O60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -3261,9 +3444,12 @@
         <v>0.21418</v>
       </c>
       <c r="M61" s="1" t="n">
+        <v>0.21338</v>
+      </c>
+      <c r="N61" s="1" t="n">
         <v>0.21708</v>
       </c>
-      <c r="N61" s="1" t="n">
+      <c r="O61" s="1" t="n">
         <v>0.21309</v>
       </c>
     </row>
@@ -3307,9 +3493,12 @@
         <v>0.1072</v>
       </c>
       <c r="M62" s="1" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="N62" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="N62" s="1" t="n">
+      <c r="O62" s="1" t="n">
         <v>0.1065</v>
       </c>
     </row>
@@ -3353,9 +3542,12 @@
         <v>0.7324000000000001</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>0.7341</v>
+        <v>0.7376</v>
       </c>
       <c r="N63" s="1" t="n">
+        <v>0.7376</v>
+      </c>
+      <c r="O63" s="1" t="n">
         <v>0.7255</v>
       </c>
     </row>
@@ -3399,9 +3591,12 @@
         <v>0.1666</v>
       </c>
       <c r="M64" s="1" t="n">
+        <v>0.1665</v>
+      </c>
+      <c r="N64" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="N64" s="1" t="n">
+      <c r="O64" s="1" t="n">
         <v>0.1658</v>
       </c>
     </row>
@@ -3445,9 +3640,12 @@
         <v>2.679</v>
       </c>
       <c r="M65" s="1" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="N65" s="1" t="n">
         <v>2.679</v>
       </c>
-      <c r="N65" s="1" t="n">
+      <c r="O65" s="1" t="n">
         <v>2.65</v>
       </c>
     </row>
@@ -3491,9 +3689,12 @@
         <v>0.04035</v>
       </c>
       <c r="M66" s="1" t="n">
+        <v>0.04029</v>
+      </c>
+      <c r="N66" s="1" t="n">
         <v>0.04072</v>
       </c>
-      <c r="N66" s="1" t="n">
+      <c r="O66" s="1" t="n">
         <v>0.04018</v>
       </c>
     </row>
@@ -3537,9 +3738,12 @@
         <v>0.04304</v>
       </c>
       <c r="M67" s="1" t="n">
+        <v>0.04279</v>
+      </c>
+      <c r="N67" s="1" t="n">
         <v>0.04314</v>
       </c>
-      <c r="N67" s="1" t="n">
+      <c r="O67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -3583,9 +3787,12 @@
         <v>3.991</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>3.993</v>
+        <v>4.001</v>
       </c>
       <c r="N68" s="1" t="n">
+        <v>4.001</v>
+      </c>
+      <c r="O68" s="1" t="n">
         <v>3.951</v>
       </c>
     </row>
@@ -3632,6 +3839,9 @@
         <v>0.1274</v>
       </c>
       <c r="N69" s="1" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="O69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -3675,9 +3885,12 @@
         <v>6.299</v>
       </c>
       <c r="M70" s="1" t="n">
+        <v>6.318</v>
+      </c>
+      <c r="N70" s="1" t="n">
         <v>6.338</v>
       </c>
-      <c r="N70" s="1" t="n">
+      <c r="O70" s="1" t="n">
         <v>6.114</v>
       </c>
     </row>
@@ -3721,9 +3934,12 @@
         <v>0.05015</v>
       </c>
       <c r="M71" s="1" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="N71" s="1" t="n">
         <v>0.05015</v>
       </c>
-      <c r="N71" s="1" t="n">
+      <c r="O71" s="1" t="n">
         <v>0.04959</v>
       </c>
     </row>
@@ -3767,9 +3983,12 @@
         <v>0.004134</v>
       </c>
       <c r="M72" s="1" t="n">
+        <v>0.004122</v>
+      </c>
+      <c r="N72" s="1" t="n">
         <v>0.004181</v>
       </c>
-      <c r="N72" s="1" t="n">
+      <c r="O72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -3813,9 +4032,12 @@
         <v>6.024</v>
       </c>
       <c r="M73" s="1" t="n">
-        <v>6.032</v>
+        <v>6.056</v>
       </c>
       <c r="N73" s="1" t="n">
+        <v>6.056</v>
+      </c>
+      <c r="O73" s="1" t="n">
         <v>5.96</v>
       </c>
     </row>
@@ -3859,9 +4081,12 @@
         <v>0.1648</v>
       </c>
       <c r="M74" s="1" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="N74" s="1" t="n">
         <v>0.1655</v>
       </c>
-      <c r="N74" s="1" t="n">
+      <c r="O74" s="1" t="n">
         <v>0.1619</v>
       </c>
     </row>
@@ -3905,9 +4130,12 @@
         <v>0.007343</v>
       </c>
       <c r="M75" s="1" t="n">
+        <v>0.007362</v>
+      </c>
+      <c r="N75" s="1" t="n">
         <v>0.007365</v>
       </c>
-      <c r="N75" s="1" t="n">
+      <c r="O75" s="1" t="n">
         <v>0.007261</v>
       </c>
     </row>
@@ -3951,9 +4179,12 @@
         <v>0.2153</v>
       </c>
       <c r="M76" s="1" t="n">
+        <v>0.2151</v>
+      </c>
+      <c r="N76" s="1" t="n">
         <v>0.2199</v>
       </c>
-      <c r="N76" s="1" t="n">
+      <c r="O76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -3997,9 +4228,12 @@
         <v>0.005819</v>
       </c>
       <c r="M77" s="1" t="n">
+        <v>0.005827</v>
+      </c>
+      <c r="N77" s="1" t="n">
         <v>0.005844</v>
       </c>
-      <c r="N77" s="1" t="n">
+      <c r="O77" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -4043,9 +4277,12 @@
         <v>0.102</v>
       </c>
       <c r="M78" s="1" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="N78" s="1" t="n">
         <v>0.1023</v>
       </c>
-      <c r="N78" s="1" t="n">
+      <c r="O78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -4089,9 +4326,12 @@
         <v>0.006308</v>
       </c>
       <c r="M79" s="1" t="n">
+        <v>0.006304</v>
+      </c>
+      <c r="N79" s="1" t="n">
         <v>0.006315</v>
       </c>
-      <c r="N79" s="1" t="n">
+      <c r="O79" s="1" t="n">
         <v>0.006237</v>
       </c>
     </row>
@@ -4135,9 +4375,12 @@
         <v>33.56</v>
       </c>
       <c r="M80" s="1" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="N80" s="1" t="n">
         <v>33.66</v>
       </c>
-      <c r="N80" s="1" t="n">
+      <c r="O80" s="1" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -4181,9 +4424,12 @@
         <v>0.04053</v>
       </c>
       <c r="M81" s="1" t="n">
+        <v>0.04058</v>
+      </c>
+      <c r="N81" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="N81" s="1" t="n">
+      <c r="O81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -4227,9 +4473,12 @@
         <v>0.16719</v>
       </c>
       <c r="M82" s="1" t="n">
+        <v>0.16741</v>
+      </c>
+      <c r="N82" s="1" t="n">
         <v>0.16759</v>
       </c>
-      <c r="N82" s="1" t="n">
+      <c r="O82" s="1" t="n">
         <v>0.16679</v>
       </c>
     </row>
@@ -4273,9 +4522,12 @@
         <v>0.1035</v>
       </c>
       <c r="M83" s="1" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="N83" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="N83" s="1" t="n">
+      <c r="O83" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -4319,10 +4571,13 @@
         <v>0.0873</v>
       </c>
       <c r="M84" s="1" t="n">
+        <v>0.08722000000000001</v>
+      </c>
+      <c r="N84" s="1" t="n">
         <v>0.08848</v>
       </c>
-      <c r="N84" s="1" t="n">
-        <v>0.0873</v>
+      <c r="O84" s="1" t="n">
+        <v>0.08722000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -4365,10 +4620,13 @@
         <v>0.0229</v>
       </c>
       <c r="M85" s="1" t="n">
+        <v>0.02288</v>
+      </c>
+      <c r="N85" s="1" t="n">
         <v>0.02331</v>
       </c>
-      <c r="N85" s="1" t="n">
-        <v>0.0229</v>
+      <c r="O85" s="1" t="n">
+        <v>0.02288</v>
       </c>
     </row>
     <row r="86">
@@ -4411,9 +4669,12 @@
         <v>0.245</v>
       </c>
       <c r="M86" s="1" t="n">
-        <v>0.245</v>
+        <v>0.247</v>
       </c>
       <c r="N86" s="1" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="O86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -4457,9 +4718,12 @@
         <v>357.03</v>
       </c>
       <c r="M87" s="1" t="n">
+        <v>356.65</v>
+      </c>
+      <c r="N87" s="1" t="n">
         <v>358.65</v>
       </c>
-      <c r="N87" s="1" t="n">
+      <c r="O87" s="1" t="n">
         <v>355.75</v>
       </c>
     </row>
@@ -4503,9 +4767,12 @@
         <v>0.00349</v>
       </c>
       <c r="M88" s="1" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="N88" s="1" t="n">
         <v>0.00352</v>
       </c>
-      <c r="N88" s="1" t="n">
+      <c r="O88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -4549,9 +4816,12 @@
         <v>8.316000000000001</v>
       </c>
       <c r="M89" s="1" t="n">
-        <v>8.323</v>
+        <v>8.327</v>
       </c>
       <c r="N89" s="1" t="n">
+        <v>8.327</v>
+      </c>
+      <c r="O89" s="1" t="n">
         <v>8.257</v>
       </c>
     </row>
@@ -4595,9 +4865,12 @@
         <v>0.00594</v>
       </c>
       <c r="M90" s="1" t="n">
+        <v>0.005935</v>
+      </c>
+      <c r="N90" s="1" t="n">
         <v>0.005958</v>
       </c>
-      <c r="N90" s="1" t="n">
+      <c r="O90" s="1" t="n">
         <v>0.005905</v>
       </c>
     </row>
@@ -4641,9 +4914,12 @@
         <v>0.06845999999999999</v>
       </c>
       <c r="M91" s="1" t="n">
+        <v>0.06863</v>
+      </c>
+      <c r="N91" s="1" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="N91" s="1" t="n">
+      <c r="O91" s="1" t="n">
         <v>0.06812</v>
       </c>
     </row>
@@ -4687,9 +4963,12 @@
         <v>0.02851</v>
       </c>
       <c r="M92" s="1" t="n">
+        <v>0.02858</v>
+      </c>
+      <c r="N92" s="1" t="n">
         <v>0.02905</v>
       </c>
-      <c r="N92" s="1" t="n">
+      <c r="O92" s="1" t="n">
         <v>0.02851</v>
       </c>
     </row>
@@ -4733,9 +5012,12 @@
         <v>5.173</v>
       </c>
       <c r="M93" s="1" t="n">
+        <v>5.182</v>
+      </c>
+      <c r="N93" s="1" t="n">
         <v>5.228</v>
       </c>
-      <c r="N93" s="1" t="n">
+      <c r="O93" s="1" t="n">
         <v>5.159</v>
       </c>
     </row>
@@ -4779,9 +5061,12 @@
         <v>0.000226</v>
       </c>
       <c r="M94" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="N94" s="1" t="n">
         <v>0.000228</v>
       </c>
-      <c r="N94" s="1" t="n">
+      <c r="O94" s="1" t="n">
         <v>0.000225</v>
       </c>
     </row>
@@ -4825,9 +5110,12 @@
         <v>0.9248</v>
       </c>
       <c r="M95" s="1" t="n">
+        <v>0.9267</v>
+      </c>
+      <c r="N95" s="1" t="n">
         <v>0.9278999999999999</v>
       </c>
-      <c r="N95" s="1" t="n">
+      <c r="O95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -4871,9 +5159,12 @@
         <v>2.1985</v>
       </c>
       <c r="M96" s="1" t="n">
+        <v>2.1792</v>
+      </c>
+      <c r="N96" s="1" t="n">
         <v>2.1985</v>
       </c>
-      <c r="N96" s="1" t="n">
+      <c r="O96" s="1" t="n">
         <v>2.0598</v>
       </c>
     </row>
@@ -4917,10 +5208,13 @@
         <v>0.3675</v>
       </c>
       <c r="M97" s="1" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="N97" s="1" t="n">
         <v>0.3722</v>
       </c>
-      <c r="N97" s="1" t="n">
-        <v>0.3675</v>
+      <c r="O97" s="1" t="n">
+        <v>0.3673</v>
       </c>
     </row>
     <row r="98">
@@ -4963,9 +5257,12 @@
         <v>1.622</v>
       </c>
       <c r="M98" s="1" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="N98" s="1" t="n">
         <v>1.625</v>
       </c>
-      <c r="N98" s="1" t="n">
+      <c r="O98" s="1" t="n">
         <v>1.613</v>
       </c>
     </row>
@@ -5009,9 +5306,12 @@
         <v>0.2314</v>
       </c>
       <c r="M99" s="1" t="n">
+        <v>0.2314</v>
+      </c>
+      <c r="N99" s="1" t="n">
         <v>0.2368</v>
       </c>
-      <c r="N99" s="1" t="n">
+      <c r="O99" s="1" t="n">
         <v>0.2314</v>
       </c>
     </row>
@@ -5055,9 +5355,12 @@
         <v>0.1367</v>
       </c>
       <c r="M100" s="1" t="n">
+        <v>0.13647</v>
+      </c>
+      <c r="N100" s="1" t="n">
         <v>0.13748</v>
       </c>
-      <c r="N100" s="1" t="n">
+      <c r="O100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -5101,9 +5404,12 @@
         <v>0.06920999999999999</v>
       </c>
       <c r="M101" s="1" t="n">
+        <v>0.07020999999999999</v>
+      </c>
+      <c r="N101" s="1" t="n">
         <v>0.07115</v>
       </c>
-      <c r="N101" s="1" t="n">
+      <c r="O101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -5147,9 +5453,12 @@
         <v>0.0010838</v>
       </c>
       <c r="M102" s="1" t="n">
+        <v>0.0010831</v>
+      </c>
+      <c r="N102" s="1" t="n">
         <v>0.0010886</v>
       </c>
-      <c r="N102" s="1" t="n">
+      <c r="O102" s="1" t="n">
         <v>0.0010822</v>
       </c>
     </row>
@@ -5193,9 +5502,12 @@
         <v>0.003419</v>
       </c>
       <c r="M103" s="1" t="n">
+        <v>0.003413</v>
+      </c>
+      <c r="N103" s="1" t="n">
         <v>0.003427</v>
       </c>
-      <c r="N103" s="1" t="n">
+      <c r="O103" s="1" t="n">
         <v>0.003403</v>
       </c>
     </row>
@@ -5239,10 +5551,13 @@
         <v>0.27344</v>
       </c>
       <c r="M104" s="1" t="n">
+        <v>0.27209</v>
+      </c>
+      <c r="N104" s="1" t="n">
         <v>0.27751</v>
       </c>
-      <c r="N104" s="1" t="n">
-        <v>0.27312</v>
+      <c r="O104" s="1" t="n">
+        <v>0.27209</v>
       </c>
     </row>
     <row r="105">
@@ -5285,9 +5600,12 @@
         <v>0.01256</v>
       </c>
       <c r="M105" s="1" t="n">
+        <v>0.01254</v>
+      </c>
+      <c r="N105" s="1" t="n">
         <v>0.01257</v>
       </c>
-      <c r="N105" s="1" t="n">
+      <c r="O105" s="1" t="n">
         <v>0.01243</v>
       </c>
     </row>
@@ -5331,9 +5649,12 @@
         <v>0.13615</v>
       </c>
       <c r="M106" s="1" t="n">
+        <v>0.13568</v>
+      </c>
+      <c r="N106" s="1" t="n">
         <v>0.13615</v>
       </c>
-      <c r="N106" s="1" t="n">
+      <c r="O106" s="1" t="n">
         <v>0.13329</v>
       </c>
     </row>
@@ -5377,9 +5698,12 @@
         <v>0.3519</v>
       </c>
       <c r="M107" s="1" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="N107" s="1" t="n">
         <v>0.3522</v>
       </c>
-      <c r="N107" s="1" t="n">
+      <c r="O107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -5423,9 +5747,12 @@
         <v>0.1413</v>
       </c>
       <c r="M108" s="1" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="N108" s="1" t="n">
         <v>0.1436</v>
       </c>
-      <c r="N108" s="1" t="n">
+      <c r="O108" s="1" t="n">
         <v>0.1413</v>
       </c>
     </row>
@@ -5469,9 +5796,12 @@
         <v>0.9360000000000001</v>
       </c>
       <c r="M109" s="1" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="N109" s="1" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="O109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -5515,9 +5845,12 @@
         <v>0.016207</v>
       </c>
       <c r="M110" s="1" t="n">
+        <v>0.016195</v>
+      </c>
+      <c r="N110" s="1" t="n">
         <v>0.016308</v>
       </c>
-      <c r="N110" s="1" t="n">
+      <c r="O110" s="1" t="n">
         <v>0.016195</v>
       </c>
     </row>
@@ -5561,9 +5894,12 @@
         <v>0.038973</v>
       </c>
       <c r="M111" s="1" t="n">
-        <v>0.038973</v>
+        <v>0.039116</v>
       </c>
       <c r="N111" s="1" t="n">
+        <v>0.039116</v>
+      </c>
+      <c r="O111" s="1" t="n">
         <v>0.03774</v>
       </c>
     </row>
@@ -5607,10 +5943,13 @@
         <v>0.11996</v>
       </c>
       <c r="M112" s="1" t="n">
+        <v>0.11917</v>
+      </c>
+      <c r="N112" s="1" t="n">
         <v>0.12031</v>
       </c>
-      <c r="N112" s="1" t="n">
-        <v>0.11926</v>
+      <c r="O112" s="1" t="n">
+        <v>0.11917</v>
       </c>
     </row>
     <row r="113">
@@ -5653,9 +5992,12 @@
         <v>0.09352000000000001</v>
       </c>
       <c r="M113" s="1" t="n">
+        <v>0.09383</v>
+      </c>
+      <c r="N113" s="1" t="n">
         <v>0.09574000000000001</v>
       </c>
-      <c r="N113" s="1" t="n">
+      <c r="O113" s="1" t="n">
         <v>0.09342</v>
       </c>
     </row>
@@ -5699,9 +6041,12 @@
         <v>0.12997</v>
       </c>
       <c r="M114" s="1" t="n">
+        <v>0.13047</v>
+      </c>
+      <c r="N114" s="1" t="n">
         <v>0.13063</v>
       </c>
-      <c r="N114" s="1" t="n">
+      <c r="O114" s="1" t="n">
         <v>0.12895</v>
       </c>
     </row>
@@ -5748,6 +6093,9 @@
         <v>0.2663</v>
       </c>
       <c r="N115" s="1" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="O115" s="1" t="n">
         <v>0.2638</v>
       </c>
     </row>
@@ -5791,10 +6139,13 @@
         <v>0.04814</v>
       </c>
       <c r="M116" s="1" t="n">
+        <v>0.04779</v>
+      </c>
+      <c r="N116" s="1" t="n">
         <v>0.0529</v>
       </c>
-      <c r="N116" s="1" t="n">
-        <v>0.04805</v>
+      <c r="O116" s="1" t="n">
+        <v>0.04779</v>
       </c>
     </row>
     <row r="117">
@@ -5837,9 +6188,12 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="M117" s="1" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="N117" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="N117" s="1" t="n">
+      <c r="O117" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -5883,9 +6237,12 @@
         <v>0.05573</v>
       </c>
       <c r="M118" s="1" t="n">
+        <v>0.05523</v>
+      </c>
+      <c r="N118" s="1" t="n">
         <v>0.05573</v>
       </c>
-      <c r="N118" s="1" t="n">
+      <c r="O118" s="1" t="n">
         <v>0.05501</v>
       </c>
     </row>
@@ -5929,9 +6286,12 @@
         <v>0.01509</v>
       </c>
       <c r="M119" s="1" t="n">
+        <v>0.01511</v>
+      </c>
+      <c r="N119" s="1" t="n">
         <v>0.01515</v>
       </c>
-      <c r="N119" s="1" t="n">
+      <c r="O119" s="1" t="n">
         <v>0.01505</v>
       </c>
     </row>
@@ -5978,6 +6338,9 @@
         <v>3.079</v>
       </c>
       <c r="N120" s="1" t="n">
+        <v>3.079</v>
+      </c>
+      <c r="O120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -6021,9 +6384,12 @@
         <v>1.85</v>
       </c>
       <c r="M121" s="1" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N121" s="1" t="n">
         <v>1.855</v>
       </c>
-      <c r="N121" s="1" t="n">
+      <c r="O121" s="1" t="n">
         <v>1.848</v>
       </c>
     </row>
@@ -6067,9 +6433,12 @@
         <v>1.3042</v>
       </c>
       <c r="M122" s="1" t="n">
-        <v>1.3042</v>
+        <v>1.307</v>
       </c>
       <c r="N122" s="1" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="O122" s="1" t="n">
         <v>1.2934</v>
       </c>
     </row>
@@ -6113,9 +6482,12 @@
         <v>0.318</v>
       </c>
       <c r="M123" s="1" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="N123" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="N123" s="1" t="n">
+      <c r="O123" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -6159,9 +6531,12 @@
         <v>0.12501</v>
       </c>
       <c r="M124" s="1" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="N124" s="1" t="n">
         <v>0.12601</v>
       </c>
-      <c r="N124" s="1" t="n">
+      <c r="O124" s="1" t="n">
         <v>0.12202</v>
       </c>
     </row>
@@ -6205,9 +6580,12 @@
         <v>0.008540000000000001</v>
       </c>
       <c r="M125" s="1" t="n">
+        <v>0.008576</v>
+      </c>
+      <c r="N125" s="1" t="n">
         <v>0.008626999999999999</v>
       </c>
-      <c r="N125" s="1" t="n">
+      <c r="O125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -6251,9 +6629,12 @@
         <v>0.01622</v>
       </c>
       <c r="M126" s="1" t="n">
-        <v>0.01622</v>
+        <v>0.01628</v>
       </c>
       <c r="N126" s="1" t="n">
+        <v>0.01628</v>
+      </c>
+      <c r="O126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -6297,9 +6678,12 @@
         <v>0.04414</v>
       </c>
       <c r="M127" s="1" t="n">
+        <v>0.04402</v>
+      </c>
+      <c r="N127" s="1" t="n">
         <v>0.04468</v>
       </c>
-      <c r="N127" s="1" t="n">
+      <c r="O127" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -6343,9 +6727,12 @@
         <v>0.04689</v>
       </c>
       <c r="M128" s="1" t="n">
+        <v>0.04656</v>
+      </c>
+      <c r="N128" s="1" t="n">
         <v>0.04727</v>
       </c>
-      <c r="N128" s="1" t="n">
+      <c r="O128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -6389,9 +6776,12 @@
         <v>0.09680999999999999</v>
       </c>
       <c r="M129" s="1" t="n">
+        <v>0.09678</v>
+      </c>
+      <c r="N129" s="1" t="n">
         <v>0.09680999999999999</v>
       </c>
-      <c r="N129" s="1" t="n">
+      <c r="O129" s="1" t="n">
         <v>0.09543</v>
       </c>
     </row>
@@ -6435,9 +6825,12 @@
         <v>0.09915</v>
       </c>
       <c r="M130" s="1" t="n">
+        <v>0.09903000000000001</v>
+      </c>
+      <c r="N130" s="1" t="n">
         <v>0.09927</v>
       </c>
-      <c r="N130" s="1" t="n">
+      <c r="O130" s="1" t="n">
         <v>0.09848</v>
       </c>
     </row>
@@ -6481,9 +6874,12 @@
         <v>0.16705</v>
       </c>
       <c r="M131" s="1" t="n">
+        <v>0.16644</v>
+      </c>
+      <c r="N131" s="1" t="n">
         <v>0.16707</v>
       </c>
-      <c r="N131" s="1" t="n">
+      <c r="O131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -6527,9 +6923,12 @@
         <v>0.01708</v>
       </c>
       <c r="M132" s="1" t="n">
+        <v>0.01706</v>
+      </c>
+      <c r="N132" s="1" t="n">
         <v>0.01708</v>
       </c>
-      <c r="N132" s="1" t="n">
+      <c r="O132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -6573,9 +6972,12 @@
         <v>0.06707</v>
       </c>
       <c r="M133" s="1" t="n">
-        <v>0.06714000000000001</v>
+        <v>0.06721000000000001</v>
       </c>
       <c r="N133" s="1" t="n">
+        <v>0.06721000000000001</v>
+      </c>
+      <c r="O133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -6619,9 +7021,12 @@
         <v>0.3036</v>
       </c>
       <c r="M134" s="1" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="N134" s="1" t="n">
         <v>0.3043</v>
       </c>
-      <c r="N134" s="1" t="n">
+      <c r="O134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -6665,9 +7070,12 @@
         <v>0.04533</v>
       </c>
       <c r="M135" s="1" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="N135" s="1" t="n">
         <v>0.04563</v>
       </c>
-      <c r="N135" s="1" t="n">
+      <c r="O135" s="1" t="n">
         <v>0.04502</v>
       </c>
     </row>
@@ -6714,6 +7122,9 @@
         <v>0.783</v>
       </c>
       <c r="N136" s="1" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="O136" s="1" t="n">
         <v>0.781</v>
       </c>
     </row>
@@ -6757,9 +7168,12 @@
         <v>0.1174</v>
       </c>
       <c r="M137" s="1" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="N137" s="1" t="n">
         <v>0.1181</v>
       </c>
-      <c r="N137" s="1" t="n">
+      <c r="O137" s="1" t="n">
         <v>0.1162</v>
       </c>
     </row>
@@ -6803,9 +7217,12 @@
         <v>0.14776</v>
       </c>
       <c r="M138" s="1" t="n">
-        <v>0.14787</v>
+        <v>0.14817</v>
       </c>
       <c r="N138" s="1" t="n">
+        <v>0.14817</v>
+      </c>
+      <c r="O138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -6849,9 +7266,12 @@
         <v>0.05781</v>
       </c>
       <c r="M139" s="1" t="n">
-        <v>0.05781</v>
+        <v>0.05787</v>
       </c>
       <c r="N139" s="1" t="n">
+        <v>0.05787</v>
+      </c>
+      <c r="O139" s="1" t="n">
         <v>0.05699</v>
       </c>
     </row>
@@ -6895,9 +7315,12 @@
         <v>0.007283</v>
       </c>
       <c r="M140" s="1" t="n">
+        <v>0.007282</v>
+      </c>
+      <c r="N140" s="1" t="n">
         <v>0.007302</v>
       </c>
-      <c r="N140" s="1" t="n">
+      <c r="O140" s="1" t="n">
         <v>0.00726</v>
       </c>
     </row>
@@ -6941,9 +7364,12 @@
         <v>0.09625</v>
       </c>
       <c r="M141" s="1" t="n">
+        <v>0.09622</v>
+      </c>
+      <c r="N141" s="1" t="n">
         <v>0.09637</v>
       </c>
-      <c r="N141" s="1" t="n">
+      <c r="O141" s="1" t="n">
         <v>0.09569</v>
       </c>
     </row>
@@ -6987,9 +7413,12 @@
         <v>0.08384999999999999</v>
       </c>
       <c r="M142" s="1" t="n">
-        <v>0.0839</v>
+        <v>0.08393</v>
       </c>
       <c r="N142" s="1" t="n">
+        <v>0.08393</v>
+      </c>
+      <c r="O142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -7033,9 +7462,12 @@
         <v>0.00848</v>
       </c>
       <c r="M143" s="1" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="N143" s="1" t="n">
         <v>0.00861</v>
       </c>
-      <c r="N143" s="1" t="n">
+      <c r="O143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -7079,9 +7511,12 @@
         <v>0.0725</v>
       </c>
       <c r="M144" s="1" t="n">
+        <v>0.07231</v>
+      </c>
+      <c r="N144" s="1" t="n">
         <v>0.07288</v>
       </c>
-      <c r="N144" s="1" t="n">
+      <c r="O144" s="1" t="n">
         <v>0.07224999999999999</v>
       </c>
     </row>
@@ -7125,9 +7560,12 @@
         <v>0.425</v>
       </c>
       <c r="M145" s="1" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="N145" s="1" t="n">
         <v>0.4305</v>
       </c>
-      <c r="N145" s="1" t="n">
+      <c r="O145" s="1" t="n">
         <v>0.425</v>
       </c>
     </row>
@@ -7171,9 +7609,12 @@
         <v>0.03235</v>
       </c>
       <c r="M146" s="1" t="n">
+        <v>0.03238</v>
+      </c>
+      <c r="N146" s="1" t="n">
         <v>0.03276</v>
       </c>
-      <c r="N146" s="1" t="n">
+      <c r="O146" s="1" t="n">
         <v>0.0322</v>
       </c>
     </row>
@@ -7217,9 +7658,12 @@
         <v>390.54</v>
       </c>
       <c r="M147" s="1" t="n">
-        <v>390.55</v>
+        <v>390.58</v>
       </c>
       <c r="N147" s="1" t="n">
+        <v>390.58</v>
+      </c>
+      <c r="O147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -7263,10 +7707,13 @@
         <v>0.03292</v>
       </c>
       <c r="M148" s="1" t="n">
+        <v>0.03268</v>
+      </c>
+      <c r="N148" s="1" t="n">
         <v>0.0333</v>
       </c>
-      <c r="N148" s="1" t="n">
-        <v>0.0329</v>
+      <c r="O148" s="1" t="n">
+        <v>0.03268</v>
       </c>
     </row>
     <row r="149">
@@ -7309,9 +7756,12 @@
         <v>0.05294</v>
       </c>
       <c r="M149" s="1" t="n">
+        <v>0.05295</v>
+      </c>
+      <c r="N149" s="1" t="n">
         <v>0.05322</v>
       </c>
-      <c r="N149" s="1" t="n">
+      <c r="O149" s="1" t="n">
         <v>0.05289</v>
       </c>
     </row>
@@ -7355,10 +7805,13 @@
         <v>0.0004383</v>
       </c>
       <c r="M150" s="1" t="n">
+        <v>0.0004377</v>
+      </c>
+      <c r="N150" s="1" t="n">
         <v>0.000443</v>
       </c>
-      <c r="N150" s="1" t="n">
-        <v>0.0004383</v>
+      <c r="O150" s="1" t="n">
+        <v>0.0004377</v>
       </c>
     </row>
     <row r="151">
@@ -7401,9 +7854,12 @@
         <v>0.02188</v>
       </c>
       <c r="M151" s="1" t="n">
+        <v>0.02193</v>
+      </c>
+      <c r="N151" s="1" t="n">
         <v>0.02197</v>
       </c>
-      <c r="N151" s="1" t="n">
+      <c r="O151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -7447,9 +7903,12 @@
         <v>0.001785</v>
       </c>
       <c r="M152" s="1" t="n">
+        <v>0.00178</v>
+      </c>
+      <c r="N152" s="1" t="n">
         <v>0.001793</v>
       </c>
-      <c r="N152" s="1" t="n">
+      <c r="O152" s="1" t="n">
         <v>0.001768</v>
       </c>
     </row>
@@ -7493,9 +7952,12 @@
         <v>6e-06</v>
       </c>
       <c r="M153" s="1" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="N153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
-      <c r="N153" s="1" t="n">
+      <c r="O153" s="1" t="n">
         <v>6e-06</v>
       </c>
     </row>
@@ -7539,9 +8001,12 @@
         <v>0.1603</v>
       </c>
       <c r="M154" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="N154" s="1" t="n">
         <v>0.1609</v>
       </c>
-      <c r="N154" s="1" t="n">
+      <c r="O154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -7588,6 +8053,9 @@
         <v>0.03781</v>
       </c>
       <c r="N155" s="1" t="n">
+        <v>0.03781</v>
+      </c>
+      <c r="O155" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -7631,9 +8099,12 @@
         <v>0.005399</v>
       </c>
       <c r="M156" s="1" t="n">
+        <v>0.005384</v>
+      </c>
+      <c r="N156" s="1" t="n">
         <v>0.005404</v>
       </c>
-      <c r="N156" s="1" t="n">
+      <c r="O156" s="1" t="n">
         <v>0.005364</v>
       </c>
     </row>
@@ -7677,9 +8148,12 @@
         <v>0.02294</v>
       </c>
       <c r="M157" s="1" t="n">
+        <v>0.02289</v>
+      </c>
+      <c r="N157" s="1" t="n">
         <v>0.02294</v>
       </c>
-      <c r="N157" s="1" t="n">
+      <c r="O157" s="1" t="n">
         <v>0.02263</v>
       </c>
     </row>
@@ -7723,9 +8197,12 @@
         <v>1.099</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>1.099</v>
+        <v>1.101</v>
       </c>
       <c r="N158" s="1" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="O158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -7769,9 +8246,12 @@
         <v>2.57</v>
       </c>
       <c r="M159" s="1" t="n">
+        <v>2.572</v>
+      </c>
+      <c r="N159" s="1" t="n">
         <v>2.577</v>
       </c>
-      <c r="N159" s="1" t="n">
+      <c r="O159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -7815,9 +8295,12 @@
         <v>4.845</v>
       </c>
       <c r="M160" s="1" t="n">
+        <v>4.846</v>
+      </c>
+      <c r="N160" s="1" t="n">
         <v>4.858</v>
       </c>
-      <c r="N160" s="1" t="n">
+      <c r="O160" s="1" t="n">
         <v>4.836</v>
       </c>
     </row>
@@ -7864,6 +8347,9 @@
         <v>0.1608</v>
       </c>
       <c r="N161" s="1" t="n">
+        <v>0.1608</v>
+      </c>
+      <c r="O161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -7907,10 +8393,13 @@
         <v>0.2045</v>
       </c>
       <c r="M162" s="1" t="n">
+        <v>0.20382</v>
+      </c>
+      <c r="N162" s="1" t="n">
         <v>0.20754</v>
       </c>
-      <c r="N162" s="1" t="n">
-        <v>0.20425</v>
+      <c r="O162" s="1" t="n">
+        <v>0.20382</v>
       </c>
     </row>
     <row r="163">
@@ -7953,9 +8442,12 @@
         <v>0.03948</v>
       </c>
       <c r="M163" s="1" t="n">
+        <v>0.03948</v>
+      </c>
+      <c r="N163" s="1" t="n">
         <v>0.03955</v>
       </c>
-      <c r="N163" s="1" t="n">
+      <c r="O163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -7999,9 +8491,12 @@
         <v>0.06336</v>
       </c>
       <c r="M164" s="1" t="n">
+        <v>0.06325</v>
+      </c>
+      <c r="N164" s="1" t="n">
         <v>0.0636</v>
       </c>
-      <c r="N164" s="1" t="n">
+      <c r="O164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -8045,9 +8540,12 @@
         <v>0.3667</v>
       </c>
       <c r="M165" s="1" t="n">
-        <v>0.3667</v>
+        <v>0.3674</v>
       </c>
       <c r="N165" s="1" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="O165" s="1" t="n">
         <v>0.3525</v>
       </c>
     </row>
@@ -8091,9 +8589,12 @@
         <v>139.47</v>
       </c>
       <c r="M166" s="1" t="n">
+        <v>139.48</v>
+      </c>
+      <c r="N166" s="1" t="n">
         <v>139.63</v>
       </c>
-      <c r="N166" s="1" t="n">
+      <c r="O166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -8137,10 +8638,13 @@
         <v>0.0006454</v>
       </c>
       <c r="M167" s="1" t="n">
+        <v>0.0006414</v>
+      </c>
+      <c r="N167" s="1" t="n">
         <v>0.0006533</v>
       </c>
-      <c r="N167" s="1" t="n">
-        <v>0.0006419</v>
+      <c r="O167" s="1" t="n">
+        <v>0.0006414</v>
       </c>
     </row>
     <row r="168">
@@ -8183,9 +8687,12 @@
         <v>0.01664</v>
       </c>
       <c r="M168" s="1" t="n">
+        <v>0.01648</v>
+      </c>
+      <c r="N168" s="1" t="n">
         <v>0.01678</v>
       </c>
-      <c r="N168" s="1" t="n">
+      <c r="O168" s="1" t="n">
         <v>0.01629</v>
       </c>
     </row>
@@ -8229,9 +8736,12 @@
         <v>0.0482</v>
       </c>
       <c r="M169" s="1" t="n">
-        <v>0.04823</v>
+        <v>0.04824</v>
       </c>
       <c r="N169" s="1" t="n">
+        <v>0.04824</v>
+      </c>
+      <c r="O169" s="1" t="n">
         <v>0.04785</v>
       </c>
     </row>
@@ -8275,9 +8785,12 @@
         <v>4.274</v>
       </c>
       <c r="M170" s="1" t="n">
+        <v>4.272</v>
+      </c>
+      <c r="N170" s="1" t="n">
         <v>4.298</v>
       </c>
-      <c r="N170" s="1" t="n">
+      <c r="O170" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -8321,9 +8834,12 @@
         <v>0.0387</v>
       </c>
       <c r="M171" s="1" t="n">
+        <v>0.03862</v>
+      </c>
+      <c r="N171" s="1" t="n">
         <v>0.03875</v>
       </c>
-      <c r="N171" s="1" t="n">
+      <c r="O171" s="1" t="n">
         <v>0.03825</v>
       </c>
     </row>
@@ -8367,9 +8883,12 @@
         <v>0.043</v>
       </c>
       <c r="M172" s="1" t="n">
-        <v>0.0431</v>
+        <v>0.0432</v>
       </c>
       <c r="N172" s="1" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="O172" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -8413,9 +8932,12 @@
         <v>0.02354</v>
       </c>
       <c r="M173" s="1" t="n">
+        <v>0.023863</v>
+      </c>
+      <c r="N173" s="1" t="n">
         <v>0.024556</v>
       </c>
-      <c r="N173" s="1" t="n">
+      <c r="O173" s="1" t="n">
         <v>0.02354</v>
       </c>
     </row>
@@ -8459,9 +8981,12 @@
         <v>1.0804</v>
       </c>
       <c r="M174" s="1" t="n">
+        <v>1.0794</v>
+      </c>
+      <c r="N174" s="1" t="n">
         <v>1.0809</v>
       </c>
-      <c r="N174" s="1" t="n">
+      <c r="O174" s="1" t="n">
         <v>1.0704</v>
       </c>
     </row>
@@ -8505,9 +9030,12 @@
         <v>0.028008</v>
       </c>
       <c r="M175" s="1" t="n">
+        <v>0.028024</v>
+      </c>
+      <c r="N175" s="1" t="n">
         <v>0.028967</v>
       </c>
-      <c r="N175" s="1" t="n">
+      <c r="O175" s="1" t="n">
         <v>0.028008</v>
       </c>
     </row>
@@ -8551,9 +9079,12 @@
         <v>0.02214</v>
       </c>
       <c r="M176" s="1" t="n">
-        <v>0.02215</v>
+        <v>0.0222</v>
       </c>
       <c r="N176" s="1" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="O176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -8597,9 +9128,12 @@
         <v>0.5502</v>
       </c>
       <c r="M177" s="1" t="n">
-        <v>0.5502</v>
+        <v>0.5507</v>
       </c>
       <c r="N177" s="1" t="n">
+        <v>0.5507</v>
+      </c>
+      <c r="O177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -8643,9 +9177,12 @@
         <v>0.08202</v>
       </c>
       <c r="M178" s="1" t="n">
+        <v>0.08202</v>
+      </c>
+      <c r="N178" s="1" t="n">
         <v>0.08276</v>
       </c>
-      <c r="N178" s="1" t="n">
+      <c r="O178" s="1" t="n">
         <v>0.08202</v>
       </c>
     </row>
@@ -8689,9 +9226,12 @@
         <v>0.02139</v>
       </c>
       <c r="M179" s="1" t="n">
-        <v>0.02142</v>
+        <v>0.02152</v>
       </c>
       <c r="N179" s="1" t="n">
+        <v>0.02152</v>
+      </c>
+      <c r="O179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -8735,9 +9275,12 @@
         <v>0.27464</v>
       </c>
       <c r="M180" s="1" t="n">
+        <v>0.27202</v>
+      </c>
+      <c r="N180" s="1" t="n">
         <v>0.27464</v>
       </c>
-      <c r="N180" s="1" t="n">
+      <c r="O180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -8781,9 +9324,12 @@
         <v>0.00422</v>
       </c>
       <c r="M181" s="1" t="n">
-        <v>0.00422</v>
+        <v>0.00423</v>
       </c>
       <c r="N181" s="1" t="n">
+        <v>0.00423</v>
+      </c>
+      <c r="O181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -8827,9 +9373,12 @@
         <v>0.07906000000000001</v>
       </c>
       <c r="M182" s="1" t="n">
+        <v>0.07914</v>
+      </c>
+      <c r="N182" s="1" t="n">
         <v>0.07981000000000001</v>
       </c>
-      <c r="N182" s="1" t="n">
+      <c r="O182" s="1" t="n">
         <v>0.07901</v>
       </c>
     </row>
@@ -8873,9 +9422,12 @@
         <v>0.02369</v>
       </c>
       <c r="M183" s="1" t="n">
+        <v>0.02363</v>
+      </c>
+      <c r="N183" s="1" t="n">
         <v>0.02369</v>
       </c>
-      <c r="N183" s="1" t="n">
+      <c r="O183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -8919,9 +9471,12 @@
         <v>6.989e-05</v>
       </c>
       <c r="M184" s="1" t="n">
+        <v>6.991e-05</v>
+      </c>
+      <c r="N184" s="1" t="n">
         <v>7.016000000000001e-05</v>
       </c>
-      <c r="N184" s="1" t="n">
+      <c r="O184" s="1" t="n">
         <v>6.957e-05</v>
       </c>
     </row>
@@ -8965,9 +9520,12 @@
         <v>0.02136</v>
       </c>
       <c r="M185" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="N185" s="1" t="n">
         <v>0.0214</v>
       </c>
-      <c r="N185" s="1" t="n">
+      <c r="O185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -9011,9 +9569,12 @@
         <v>0.01642</v>
       </c>
       <c r="M186" s="1" t="n">
+        <v>0.01637</v>
+      </c>
+      <c r="N186" s="1" t="n">
         <v>0.01644</v>
       </c>
-      <c r="N186" s="1" t="n">
+      <c r="O186" s="1" t="n">
         <v>0.01623</v>
       </c>
     </row>
@@ -9057,9 +9618,12 @@
         <v>0.972</v>
       </c>
       <c r="M187" s="1" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N187" s="1" t="n">
         <v>0.981</v>
       </c>
-      <c r="N187" s="1" t="n">
+      <c r="O187" s="1" t="n">
         <v>0.971</v>
       </c>
     </row>
@@ -9103,9 +9667,12 @@
         <v>0.0238</v>
       </c>
       <c r="M188" s="1" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="N188" s="1" t="n">
         <v>0.024</v>
       </c>
-      <c r="N188" s="1" t="n">
+      <c r="O188" s="1" t="n">
         <v>0.0237</v>
       </c>
     </row>
@@ -9149,9 +9716,12 @@
         <v>1.8863</v>
       </c>
       <c r="M189" s="1" t="n">
-        <v>1.8888</v>
+        <v>1.8941</v>
       </c>
       <c r="N189" s="1" t="n">
+        <v>1.8941</v>
+      </c>
+      <c r="O189" s="1" t="n">
         <v>1.8609</v>
       </c>
     </row>
@@ -9195,9 +9765,12 @@
         <v>1.84</v>
       </c>
       <c r="M190" s="1" t="n">
+        <v>1.843</v>
+      </c>
+      <c r="N190" s="1" t="n">
         <v>1.844</v>
       </c>
-      <c r="N190" s="1" t="n">
+      <c r="O190" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -9241,9 +9814,12 @@
         <v>0.02677</v>
       </c>
       <c r="M191" s="1" t="n">
+        <v>0.02677</v>
+      </c>
+      <c r="N191" s="1" t="n">
         <v>0.02685</v>
       </c>
-      <c r="N191" s="1" t="n">
+      <c r="O191" s="1" t="n">
         <v>0.02662</v>
       </c>
     </row>
@@ -9287,9 +9863,12 @@
         <v>0.0973</v>
       </c>
       <c r="M192" s="1" t="n">
-        <v>0.0975</v>
+        <v>0.0978</v>
       </c>
       <c r="N192" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="O192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -9333,9 +9912,12 @@
         <v>0.1709</v>
       </c>
       <c r="M193" s="1" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="N193" s="1" t="n">
         <v>0.1722</v>
       </c>
-      <c r="N193" s="1" t="n">
+      <c r="O193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -9379,9 +9961,12 @@
         <v>16.352</v>
       </c>
       <c r="M194" s="1" t="n">
+        <v>16.374</v>
+      </c>
+      <c r="N194" s="1" t="n">
         <v>16.407</v>
       </c>
-      <c r="N194" s="1" t="n">
+      <c r="O194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -9425,9 +10010,12 @@
         <v>4.109</v>
       </c>
       <c r="M195" s="1" t="n">
+        <v>4.102</v>
+      </c>
+      <c r="N195" s="1" t="n">
         <v>4.136</v>
       </c>
-      <c r="N195" s="1" t="n">
+      <c r="O195" s="1" t="n">
         <v>4.087</v>
       </c>
     </row>
@@ -9471,9 +10059,12 @@
         <v>1.2751</v>
       </c>
       <c r="M196" s="1" t="n">
-        <v>1.2794</v>
+        <v>1.2802</v>
       </c>
       <c r="N196" s="1" t="n">
+        <v>1.2802</v>
+      </c>
+      <c r="O196" s="1" t="n">
         <v>1.2663</v>
       </c>
     </row>
@@ -9517,9 +10108,12 @@
         <v>3.108</v>
       </c>
       <c r="M197" s="1" t="n">
-        <v>3.108</v>
+        <v>3.112</v>
       </c>
       <c r="N197" s="1" t="n">
+        <v>3.112</v>
+      </c>
+      <c r="O197" s="1" t="n">
         <v>3.063</v>
       </c>
     </row>
@@ -9563,9 +10157,12 @@
         <v>0.01257</v>
       </c>
       <c r="M198" s="1" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="N198" s="1" t="n">
         <v>0.01266</v>
       </c>
-      <c r="N198" s="1" t="n">
+      <c r="O198" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -9609,9 +10206,12 @@
         <v>0.0001766</v>
       </c>
       <c r="M199" s="1" t="n">
+        <v>0.0001766</v>
+      </c>
+      <c r="N199" s="1" t="n">
         <v>0.000177</v>
       </c>
-      <c r="N199" s="1" t="n">
+      <c r="O199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -9655,9 +10255,12 @@
         <v>115.85</v>
       </c>
       <c r="M200" s="1" t="n">
-        <v>115.85</v>
+        <v>115.89</v>
       </c>
       <c r="N200" s="1" t="n">
+        <v>115.89</v>
+      </c>
+      <c r="O200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -9701,10 +10304,13 @@
         <v>0.0102</v>
       </c>
       <c r="M201" s="1" t="n">
+        <v>0.01019</v>
+      </c>
+      <c r="N201" s="1" t="n">
         <v>0.01031</v>
       </c>
-      <c r="N201" s="1" t="n">
-        <v>0.0102</v>
+      <c r="O201" s="1" t="n">
+        <v>0.01019</v>
       </c>
     </row>
     <row r="202">
@@ -9747,9 +10353,12 @@
         <v>0.01067</v>
       </c>
       <c r="M202" s="1" t="n">
+        <v>0.01063</v>
+      </c>
+      <c r="N202" s="1" t="n">
         <v>0.01073</v>
       </c>
-      <c r="N202" s="1" t="n">
+      <c r="O202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -9793,9 +10402,12 @@
         <v>0.003138</v>
       </c>
       <c r="M203" s="1" t="n">
+        <v>0.003147</v>
+      </c>
+      <c r="N203" s="1" t="n">
         <v>0.003153</v>
       </c>
-      <c r="N203" s="1" t="n">
+      <c r="O203" s="1" t="n">
         <v>0.003131</v>
       </c>
     </row>
@@ -9839,9 +10451,12 @@
         <v>28.34</v>
       </c>
       <c r="M204" s="1" t="n">
+        <v>28.37</v>
+      </c>
+      <c r="N204" s="1" t="n">
         <v>28.39</v>
       </c>
-      <c r="N204" s="1" t="n">
+      <c r="O204" s="1" t="n">
         <v>28.23</v>
       </c>
     </row>
@@ -9885,9 +10500,12 @@
         <v>0.5582</v>
       </c>
       <c r="M205" s="1" t="n">
+        <v>0.5579</v>
+      </c>
+      <c r="N205" s="1" t="n">
         <v>0.5636</v>
       </c>
-      <c r="N205" s="1" t="n">
+      <c r="O205" s="1" t="n">
         <v>0.5578</v>
       </c>
     </row>
@@ -9931,9 +10549,12 @@
         <v>0.0004424</v>
       </c>
       <c r="M206" s="1" t="n">
+        <v>0.0004421</v>
+      </c>
+      <c r="N206" s="1" t="n">
         <v>0.0004438</v>
       </c>
-      <c r="N206" s="1" t="n">
+      <c r="O206" s="1" t="n">
         <v>0.0004387</v>
       </c>
     </row>
@@ -9977,9 +10598,12 @@
         <v>0.04675</v>
       </c>
       <c r="M207" s="1" t="n">
+        <v>0.04674</v>
+      </c>
+      <c r="N207" s="1" t="n">
         <v>0.04689</v>
       </c>
-      <c r="N207" s="1" t="n">
+      <c r="O207" s="1" t="n">
         <v>0.04648</v>
       </c>
     </row>
@@ -10023,9 +10647,12 @@
         <v>0.091</v>
       </c>
       <c r="M208" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N208" s="1" t="n">
         <v>0.091</v>
       </c>
-      <c r="N208" s="1" t="n">
+      <c r="O208" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -10069,9 +10696,12 @@
         <v>0.02586</v>
       </c>
       <c r="M209" s="1" t="n">
+        <v>0.02577</v>
+      </c>
+      <c r="N209" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="N209" s="1" t="n">
+      <c r="O209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -10115,9 +10745,12 @@
         <v>0.012678</v>
       </c>
       <c r="M210" s="1" t="n">
+        <v>0.012681</v>
+      </c>
+      <c r="N210" s="1" t="n">
         <v>0.012745</v>
       </c>
-      <c r="N210" s="1" t="n">
+      <c r="O210" s="1" t="n">
         <v>0.012645</v>
       </c>
     </row>
@@ -10164,6 +10797,9 @@
         <v>0.0921</v>
       </c>
       <c r="N211" s="1" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="O211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -10210,6 +10846,9 @@
         <v>0.007076</v>
       </c>
       <c r="N212" s="1" t="n">
+        <v>0.007076</v>
+      </c>
+      <c r="O212" s="1" t="n">
         <v>0.007038</v>
       </c>
     </row>
@@ -10253,9 +10892,12 @@
         <v>0.02969</v>
       </c>
       <c r="M213" s="1" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="N213" s="1" t="n">
         <v>0.02978</v>
       </c>
-      <c r="N213" s="1" t="n">
+      <c r="O213" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -10299,9 +10941,12 @@
         <v>0.2701</v>
       </c>
       <c r="M214" s="1" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="N214" s="1" t="n">
         <v>0.271</v>
       </c>
-      <c r="N214" s="1" t="n">
+      <c r="O214" s="1" t="n">
         <v>0.2698</v>
       </c>
     </row>
@@ -10345,9 +10990,12 @@
         <v>0.02225</v>
       </c>
       <c r="M215" s="1" t="n">
+        <v>0.02232</v>
+      </c>
+      <c r="N215" s="1" t="n">
         <v>0.02256</v>
       </c>
-      <c r="N215" s="1" t="n">
+      <c r="O215" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -10391,9 +11039,12 @@
         <v>0.01463</v>
       </c>
       <c r="M216" s="1" t="n">
+        <v>0.01464</v>
+      </c>
+      <c r="N216" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="N216" s="1" t="n">
+      <c r="O216" s="1" t="n">
         <v>0.01463</v>
       </c>
     </row>
@@ -10437,9 +11088,12 @@
         <v>0.2547</v>
       </c>
       <c r="M217" s="1" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="N217" s="1" t="n">
         <v>0.255</v>
       </c>
-      <c r="N217" s="1" t="n">
+      <c r="O217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -10483,9 +11137,12 @@
         <v>0.3116</v>
       </c>
       <c r="M218" s="1" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="N218" s="1" t="n">
         <v>0.3116</v>
       </c>
-      <c r="N218" s="1" t="n">
+      <c r="O218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -10529,9 +11186,12 @@
         <v>0.1786</v>
       </c>
       <c r="M219" s="1" t="n">
+        <v>0.1786</v>
+      </c>
+      <c r="N219" s="1" t="n">
         <v>0.179</v>
       </c>
-      <c r="N219" s="1" t="n">
+      <c r="O219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -10575,9 +11235,12 @@
         <v>15</v>
       </c>
       <c r="M220" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N220" s="1" t="n">
         <v>15.02</v>
       </c>
-      <c r="N220" s="1" t="n">
+      <c r="O220" s="1" t="n">
         <v>14.95</v>
       </c>
     </row>
@@ -10621,9 +11284,12 @@
         <v>0.01612</v>
       </c>
       <c r="M221" s="1" t="n">
+        <v>0.01613</v>
+      </c>
+      <c r="N221" s="1" t="n">
         <v>0.01614</v>
       </c>
-      <c r="N221" s="1" t="n">
+      <c r="O221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -10667,10 +11333,13 @@
         <v>66.34999999999999</v>
       </c>
       <c r="M222" s="1" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="N222" s="1" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="N222" s="1" t="n">
-        <v>66.17</v>
+      <c r="O222" s="1" t="n">
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="223">
@@ -10713,9 +11382,12 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="M223" s="1" t="n">
-        <v>0.09379</v>
+        <v>0.09428</v>
       </c>
       <c r="N223" s="1" t="n">
+        <v>0.09428</v>
+      </c>
+      <c r="O223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -10759,9 +11431,12 @@
         <v>0.03993</v>
       </c>
       <c r="M224" s="1" t="n">
+        <v>0.03985</v>
+      </c>
+      <c r="N224" s="1" t="n">
         <v>0.03993</v>
       </c>
-      <c r="N224" s="1" t="n">
+      <c r="O224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -10805,9 +11480,12 @@
         <v>0.5711000000000001</v>
       </c>
       <c r="M225" s="1" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="N225" s="1" t="n">
         <v>0.5725</v>
       </c>
-      <c r="N225" s="1" t="n">
+      <c r="O225" s="1" t="n">
         <v>0.5695</v>
       </c>
     </row>
@@ -10851,9 +11529,12 @@
         <v>0.118</v>
       </c>
       <c r="M226" s="1" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="N226" s="1" t="n">
         <v>0.1184</v>
       </c>
-      <c r="N226" s="1" t="n">
+      <c r="O226" s="1" t="n">
         <v>0.1166</v>
       </c>
     </row>
@@ -10897,10 +11578,13 @@
         <v>0.3165</v>
       </c>
       <c r="M227" s="1" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="N227" s="1" t="n">
         <v>0.3201</v>
       </c>
-      <c r="N227" s="1" t="n">
-        <v>0.3165</v>
+      <c r="O227" s="1" t="n">
+        <v>0.3162</v>
       </c>
     </row>
     <row r="228">
@@ -10943,9 +11627,12 @@
         <v>6.105</v>
       </c>
       <c r="M228" s="1" t="n">
-        <v>6.108</v>
+        <v>6.112</v>
       </c>
       <c r="N228" s="1" t="n">
+        <v>6.112</v>
+      </c>
+      <c r="O228" s="1" t="n">
         <v>6.062</v>
       </c>
     </row>
@@ -10989,9 +11676,12 @@
         <v>0.0293</v>
       </c>
       <c r="M229" s="1" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="N229" s="1" t="n">
         <v>0.0294</v>
       </c>
-      <c r="N229" s="1" t="n">
+      <c r="O229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -11035,9 +11725,12 @@
         <v>0.3317</v>
       </c>
       <c r="M230" s="1" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="N230" s="1" t="n">
         <v>0.3325</v>
       </c>
-      <c r="N230" s="1" t="n">
+      <c r="O230" s="1" t="n">
         <v>0.3288</v>
       </c>
     </row>
@@ -11081,9 +11774,12 @@
         <v>0.12015</v>
       </c>
       <c r="M231" s="1" t="n">
+        <v>0.12016</v>
+      </c>
+      <c r="N231" s="1" t="n">
         <v>0.12089</v>
       </c>
-      <c r="N231" s="1" t="n">
+      <c r="O231" s="1" t="n">
         <v>0.11986</v>
       </c>
     </row>
@@ -11127,9 +11823,12 @@
         <v>0.1204</v>
       </c>
       <c r="M232" s="1" t="n">
+        <v>0.1194</v>
+      </c>
+      <c r="N232" s="1" t="n">
         <v>0.1204</v>
       </c>
-      <c r="N232" s="1" t="n">
+      <c r="O232" s="1" t="n">
         <v>0.1182</v>
       </c>
     </row>
@@ -11173,9 +11872,12 @@
         <v>0.0303</v>
       </c>
       <c r="M233" s="1" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="N233" s="1" t="n">
         <v>0.03039</v>
       </c>
-      <c r="N233" s="1" t="n">
+      <c r="O233" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -11219,10 +11921,13 @@
         <v>0.015748</v>
       </c>
       <c r="M234" s="1" t="n">
+        <v>0.015234</v>
+      </c>
+      <c r="N234" s="1" t="n">
         <v>0.016171</v>
       </c>
-      <c r="N234" s="1" t="n">
-        <v>0.0156</v>
+      <c r="O234" s="1" t="n">
+        <v>0.015234</v>
       </c>
     </row>
     <row r="235">
@@ -11265,10 +11970,13 @@
         <v>0.01264</v>
       </c>
       <c r="M235" s="1" t="n">
+        <v>0.01261</v>
+      </c>
+      <c r="N235" s="1" t="n">
         <v>0.01281</v>
       </c>
-      <c r="N235" s="1" t="n">
-        <v>0.01263</v>
+      <c r="O235" s="1" t="n">
+        <v>0.01261</v>
       </c>
     </row>
     <row r="236">
@@ -11311,9 +12019,12 @@
         <v>0.0194</v>
       </c>
       <c r="M236" s="1" t="n">
-        <v>0.0194</v>
+        <v>0.01943</v>
       </c>
       <c r="N236" s="1" t="n">
+        <v>0.01943</v>
+      </c>
+      <c r="O236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -11357,9 +12068,12 @@
         <v>0.08551</v>
       </c>
       <c r="M237" s="1" t="n">
-        <v>0.08551</v>
+        <v>0.08604000000000001</v>
       </c>
       <c r="N237" s="1" t="n">
+        <v>0.08604000000000001</v>
+      </c>
+      <c r="O237" s="1" t="n">
         <v>0.08427999999999999</v>
       </c>
     </row>
@@ -11403,9 +12117,12 @@
         <v>0.05879</v>
       </c>
       <c r="M238" s="1" t="n">
+        <v>0.05874</v>
+      </c>
+      <c r="N238" s="1" t="n">
         <v>0.05892</v>
       </c>
-      <c r="N238" s="1" t="n">
+      <c r="O238" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>
@@ -11449,9 +12166,12 @@
         <v>0.009018</v>
       </c>
       <c r="M239" s="1" t="n">
+        <v>0.009039</v>
+      </c>
+      <c r="N239" s="1" t="n">
         <v>0.009131999999999999</v>
       </c>
-      <c r="N239" s="1" t="n">
+      <c r="O239" s="1" t="n">
         <v>0.008954</v>
       </c>
     </row>
@@ -11495,9 +12215,12 @@
         <v>0.00419</v>
       </c>
       <c r="M240" s="1" t="n">
-        <v>0.00419</v>
+        <v>0.004204</v>
       </c>
       <c r="N240" s="1" t="n">
+        <v>0.004204</v>
+      </c>
+      <c r="O240" s="1" t="n">
         <v>0.004154</v>
       </c>
     </row>
@@ -11541,9 +12264,12 @@
         <v>0.2435</v>
       </c>
       <c r="M241" s="1" t="n">
-        <v>0.2435</v>
+        <v>0.2436</v>
       </c>
       <c r="N241" s="1" t="n">
+        <v>0.2436</v>
+      </c>
+      <c r="O241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -11587,9 +12313,12 @@
         <v>0.0584</v>
       </c>
       <c r="M242" s="1" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="N242" s="1" t="n">
         <v>0.0589</v>
       </c>
-      <c r="N242" s="1" t="n">
+      <c r="O242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -11633,9 +12362,12 @@
         <v>0.02355</v>
       </c>
       <c r="M243" s="1" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="N243" s="1" t="n">
         <v>0.02363</v>
       </c>
-      <c r="N243" s="1" t="n">
+      <c r="O243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -11679,9 +12411,12 @@
         <v>0.05591</v>
       </c>
       <c r="M244" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="N244" s="1" t="n">
         <v>0.05671</v>
       </c>
-      <c r="N244" s="1" t="n">
+      <c r="O244" s="1" t="n">
         <v>0.05547</v>
       </c>
     </row>
@@ -11725,9 +12460,12 @@
         <v>0.03496</v>
       </c>
       <c r="M245" s="1" t="n">
+        <v>0.03495</v>
+      </c>
+      <c r="N245" s="1" t="n">
         <v>0.03499</v>
       </c>
-      <c r="N245" s="1" t="n">
+      <c r="O245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -11771,9 +12509,12 @@
         <v>0.06018</v>
       </c>
       <c r="M246" s="1" t="n">
+        <v>0.06023</v>
+      </c>
+      <c r="N246" s="1" t="n">
         <v>0.0604</v>
       </c>
-      <c r="N246" s="1" t="n">
+      <c r="O246" s="1" t="n">
         <v>0.0599</v>
       </c>
     </row>
@@ -11817,9 +12558,12 @@
         <v>0.382</v>
       </c>
       <c r="M247" s="1" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="N247" s="1" t="n">
         <v>0.385</v>
       </c>
-      <c r="N247" s="1" t="n">
+      <c r="O247" s="1" t="n">
         <v>0.382</v>
       </c>
     </row>
@@ -11863,9 +12607,12 @@
         <v>0.5233</v>
       </c>
       <c r="M248" s="1" t="n">
+        <v>0.5223</v>
+      </c>
+      <c r="N248" s="1" t="n">
         <v>0.5233</v>
       </c>
-      <c r="N248" s="1" t="n">
+      <c r="O248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -11909,9 +12656,12 @@
         <v>0.02861</v>
       </c>
       <c r="M249" s="1" t="n">
+        <v>0.02869</v>
+      </c>
+      <c r="N249" s="1" t="n">
         <v>0.02884</v>
       </c>
-      <c r="N249" s="1" t="n">
+      <c r="O249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -11955,9 +12705,12 @@
         <v>0.01298</v>
       </c>
       <c r="M250" s="1" t="n">
-        <v>0.01317</v>
+        <v>0.0132</v>
       </c>
       <c r="N250" s="1" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="O250" s="1" t="n">
         <v>0.01288</v>
       </c>
     </row>
@@ -12001,9 +12754,12 @@
         <v>0.1005</v>
       </c>
       <c r="M251" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="N251" s="1" t="n">
         <v>0.1006</v>
       </c>
-      <c r="N251" s="1" t="n">
+      <c r="O251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -12047,9 +12803,12 @@
         <v>0.00716</v>
       </c>
       <c r="M252" s="1" t="n">
+        <v>0.00717</v>
+      </c>
+      <c r="N252" s="1" t="n">
         <v>0.00719</v>
       </c>
-      <c r="N252" s="1" t="n">
+      <c r="O252" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -12093,10 +12852,13 @@
         <v>0.005553</v>
       </c>
       <c r="M253" s="1" t="n">
+        <v>0.005543</v>
+      </c>
+      <c r="N253" s="1" t="n">
         <v>0.005571</v>
       </c>
-      <c r="N253" s="1" t="n">
-        <v>0.005552</v>
+      <c r="O253" s="1" t="n">
+        <v>0.005543</v>
       </c>
     </row>
     <row r="254">
@@ -12139,9 +12901,12 @@
         <v>0.0643</v>
       </c>
       <c r="M254" s="1" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="N254" s="1" t="n">
         <v>0.0646</v>
       </c>
-      <c r="N254" s="1" t="n">
+      <c r="O254" s="1" t="n">
         <v>0.0641</v>
       </c>
     </row>
@@ -12185,9 +12950,12 @@
         <v>0.01438</v>
       </c>
       <c r="M255" s="1" t="n">
+        <v>0.01433</v>
+      </c>
+      <c r="N255" s="1" t="n">
         <v>0.01454</v>
       </c>
-      <c r="N255" s="1" t="n">
+      <c r="O255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -12231,9 +12999,12 @@
         <v>0.9992760000000001</v>
       </c>
       <c r="M256" s="1" t="n">
+        <v>0.9992760000000001</v>
+      </c>
+      <c r="N256" s="1" t="n">
         <v>0.999297</v>
       </c>
-      <c r="N256" s="1" t="n">
+      <c r="O256" s="1" t="n">
         <v>0.999275</v>
       </c>
     </row>
@@ -12277,9 +13048,12 @@
         <v>0.02111</v>
       </c>
       <c r="M257" s="1" t="n">
+        <v>0.02114</v>
+      </c>
+      <c r="N257" s="1" t="n">
         <v>0.02118</v>
       </c>
-      <c r="N257" s="1" t="n">
+      <c r="O257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -12323,9 +13097,12 @@
         <v>0.01152</v>
       </c>
       <c r="M258" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="N258" s="1" t="n">
         <v>0.01152</v>
       </c>
-      <c r="N258" s="1" t="n">
+      <c r="O258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -12369,9 +13146,12 @@
         <v>0.5062</v>
       </c>
       <c r="M259" s="1" t="n">
+        <v>0.5082</v>
+      </c>
+      <c r="N259" s="1" t="n">
         <v>0.5119</v>
       </c>
-      <c r="N259" s="1" t="n">
+      <c r="O259" s="1" t="n">
         <v>0.5062</v>
       </c>
     </row>
@@ -12415,10 +13195,13 @@
         <v>0.08444</v>
       </c>
       <c r="M260" s="1" t="n">
+        <v>0.08415</v>
+      </c>
+      <c r="N260" s="1" t="n">
         <v>0.08537</v>
       </c>
-      <c r="N260" s="1" t="n">
-        <v>0.08436</v>
+      <c r="O260" s="1" t="n">
+        <v>0.08415</v>
       </c>
     </row>
     <row r="261">
@@ -12461,9 +13244,12 @@
         <v>0.04136</v>
       </c>
       <c r="M261" s="1" t="n">
-        <v>0.04138</v>
+        <v>0.04141</v>
       </c>
       <c r="N261" s="1" t="n">
+        <v>0.04141</v>
+      </c>
+      <c r="O261" s="1" t="n">
         <v>0.04121</v>
       </c>
     </row>
@@ -12507,9 +13293,12 @@
         <v>2.294</v>
       </c>
       <c r="M262" s="1" t="n">
-        <v>2.297</v>
+        <v>2.298</v>
       </c>
       <c r="N262" s="1" t="n">
+        <v>2.298</v>
+      </c>
+      <c r="O262" s="1" t="n">
         <v>2.279</v>
       </c>
     </row>
@@ -12556,6 +13345,9 @@
         <v>18.73</v>
       </c>
       <c r="N263" s="1" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="O263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -12599,9 +13391,12 @@
         <v>0.008510999999999999</v>
       </c>
       <c r="M264" s="1" t="n">
+        <v>0.008532</v>
+      </c>
+      <c r="N264" s="1" t="n">
         <v>0.008562999999999999</v>
       </c>
-      <c r="N264" s="1" t="n">
+      <c r="O264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -12645,9 +13440,12 @@
         <v>0.3647</v>
       </c>
       <c r="M265" s="1" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="N265" s="1" t="n">
         <v>0.3659</v>
       </c>
-      <c r="N265" s="1" t="n">
+      <c r="O265" s="1" t="n">
         <v>0.3627</v>
       </c>
     </row>
@@ -12691,9 +13489,12 @@
         <v>0.055235</v>
       </c>
       <c r="M266" s="1" t="n">
-        <v>0.055369</v>
+        <v>0.055423</v>
       </c>
       <c r="N266" s="1" t="n">
+        <v>0.055423</v>
+      </c>
+      <c r="O266" s="1" t="n">
         <v>0.053765</v>
       </c>
     </row>
@@ -12740,6 +13541,9 @@
         <v>0.1321</v>
       </c>
       <c r="N267" s="1" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="O267" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -12783,9 +13587,12 @@
         <v>0.007990000000000001</v>
       </c>
       <c r="M268" s="1" t="n">
+        <v>0.007891</v>
+      </c>
+      <c r="N268" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="N268" s="1" t="n">
+      <c r="O268" s="1" t="n">
         <v>0.00775</v>
       </c>
     </row>
@@ -12829,9 +13636,12 @@
         <v>0.001264</v>
       </c>
       <c r="M269" s="1" t="n">
-        <v>0.001264</v>
+        <v>0.001289</v>
       </c>
       <c r="N269" s="1" t="n">
+        <v>0.001289</v>
+      </c>
+      <c r="O269" s="1" t="n">
         <v>0.001232</v>
       </c>
     </row>
@@ -12875,10 +13685,13 @@
         <v>0.28869</v>
       </c>
       <c r="M270" s="1" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="N270" s="1" t="n">
         <v>0.28999</v>
       </c>
-      <c r="N270" s="1" t="n">
-        <v>0.28865</v>
+      <c r="O270" s="1" t="n">
+        <v>0.2882</v>
       </c>
     </row>
     <row r="271">
@@ -12921,9 +13734,12 @@
         <v>0.03924</v>
       </c>
       <c r="M271" s="1" t="n">
-        <v>0.03924</v>
+        <v>0.03927</v>
       </c>
       <c r="N271" s="1" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="O271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -12967,9 +13783,12 @@
         <v>0.05182</v>
       </c>
       <c r="M272" s="1" t="n">
+        <v>0.05163</v>
+      </c>
+      <c r="N272" s="1" t="n">
         <v>0.05182</v>
       </c>
-      <c r="N272" s="1" t="n">
+      <c r="O272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -13016,6 +13835,9 @@
         <v>0.00776</v>
       </c>
       <c r="N273" s="1" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="O273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -13059,9 +13881,12 @@
         <v>0.005786</v>
       </c>
       <c r="M274" s="1" t="n">
+        <v>0.005784</v>
+      </c>
+      <c r="N274" s="1" t="n">
         <v>0.005813</v>
       </c>
-      <c r="N274" s="1" t="n">
+      <c r="O274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -13105,9 +13930,12 @@
         <v>0.0005865999999999999</v>
       </c>
       <c r="M275" s="1" t="n">
+        <v>0.000587</v>
+      </c>
+      <c r="N275" s="1" t="n">
         <v>0.0005895</v>
       </c>
-      <c r="N275" s="1" t="n">
+      <c r="O275" s="1" t="n">
         <v>0.0005863</v>
       </c>
     </row>
@@ -13151,10 +13979,13 @@
         <v>0.15013</v>
       </c>
       <c r="M276" s="1" t="n">
+        <v>0.14973</v>
+      </c>
+      <c r="N276" s="1" t="n">
         <v>0.15167</v>
       </c>
-      <c r="N276" s="1" t="n">
-        <v>0.15004</v>
+      <c r="O276" s="1" t="n">
+        <v>0.14973</v>
       </c>
     </row>
     <row r="277">
@@ -13197,9 +14028,12 @@
         <v>0.023083</v>
       </c>
       <c r="M277" s="1" t="n">
-        <v>0.023083</v>
+        <v>0.023185</v>
       </c>
       <c r="N277" s="1" t="n">
+        <v>0.023185</v>
+      </c>
+      <c r="O277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -13243,9 +14077,12 @@
         <v>0.04199</v>
       </c>
       <c r="M278" s="1" t="n">
+        <v>0.04205</v>
+      </c>
+      <c r="N278" s="1" t="n">
         <v>0.04242</v>
       </c>
-      <c r="N278" s="1" t="n">
+      <c r="O278" s="1" t="n">
         <v>0.04179</v>
       </c>
     </row>
@@ -13289,9 +14126,12 @@
         <v>0.0003985</v>
       </c>
       <c r="M279" s="1" t="n">
+        <v>0.000399</v>
+      </c>
+      <c r="N279" s="1" t="n">
         <v>0.0004006</v>
       </c>
-      <c r="N279" s="1" t="n">
+      <c r="O279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -13335,9 +14175,12 @@
         <v>0.02202</v>
       </c>
       <c r="M280" s="1" t="n">
-        <v>0.02218</v>
+        <v>0.02221</v>
       </c>
       <c r="N280" s="1" t="n">
+        <v>0.02221</v>
+      </c>
+      <c r="O280" s="1" t="n">
         <v>0.0219</v>
       </c>
     </row>
@@ -13381,9 +14224,12 @@
         <v>0.07084</v>
       </c>
       <c r="M281" s="1" t="n">
+        <v>0.07072000000000001</v>
+      </c>
+      <c r="N281" s="1" t="n">
         <v>0.07128</v>
       </c>
-      <c r="N281" s="1" t="n">
+      <c r="O281" s="1" t="n">
         <v>0.06936</v>
       </c>
     </row>
@@ -13427,9 +14273,12 @@
         <v>0.006737</v>
       </c>
       <c r="M282" s="1" t="n">
+        <v>0.006725</v>
+      </c>
+      <c r="N282" s="1" t="n">
         <v>0.006804</v>
       </c>
-      <c r="N282" s="1" t="n">
+      <c r="O282" s="1" t="n">
         <v>0.006688</v>
       </c>
     </row>
@@ -13476,6 +14325,9 @@
         <v>0.12</v>
       </c>
       <c r="N283" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O283" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -13519,9 +14371,12 @@
         <v>0.005489</v>
       </c>
       <c r="M284" s="1" t="n">
+        <v>0.005489</v>
+      </c>
+      <c r="N284" s="1" t="n">
         <v>0.005499</v>
       </c>
-      <c r="N284" s="1" t="n">
+      <c r="O284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -13565,9 +14420,12 @@
         <v>1.265</v>
       </c>
       <c r="M285" s="1" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="N285" s="1" t="n">
         <v>1.272</v>
       </c>
-      <c r="N285" s="1" t="n">
+      <c r="O285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -13611,9 +14469,12 @@
         <v>0.4454</v>
       </c>
       <c r="M286" s="1" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="N286" s="1" t="n">
         <v>0.4458</v>
       </c>
-      <c r="N286" s="1" t="n">
+      <c r="O286" s="1" t="n">
         <v>0.4423</v>
       </c>
     </row>
@@ -13657,9 +14518,12 @@
         <v>0.007962</v>
       </c>
       <c r="M287" s="1" t="n">
+        <v>0.007924</v>
+      </c>
+      <c r="N287" s="1" t="n">
         <v>0.007998999999999999</v>
       </c>
-      <c r="N287" s="1" t="n">
+      <c r="O287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -13703,9 +14567,12 @@
         <v>0.02933</v>
       </c>
       <c r="M288" s="1" t="n">
+        <v>0.02931</v>
+      </c>
+      <c r="N288" s="1" t="n">
         <v>0.0295</v>
       </c>
-      <c r="N288" s="1" t="n">
+      <c r="O288" s="1" t="n">
         <v>0.02914</v>
       </c>
     </row>
@@ -13749,9 +14616,12 @@
         <v>0.2823</v>
       </c>
       <c r="M289" s="1" t="n">
-        <v>0.2827</v>
+        <v>0.2829</v>
       </c>
       <c r="N289" s="1" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="O289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -13795,9 +14665,12 @@
         <v>2.759</v>
       </c>
       <c r="M290" s="1" t="n">
+        <v>2.761</v>
+      </c>
+      <c r="N290" s="1" t="n">
         <v>2.783</v>
       </c>
-      <c r="N290" s="1" t="n">
+      <c r="O290" s="1" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -13841,9 +14714,12 @@
         <v>0.00319</v>
       </c>
       <c r="M291" s="1" t="n">
-        <v>0.003191</v>
+        <v>0.003194</v>
       </c>
       <c r="N291" s="1" t="n">
+        <v>0.003194</v>
+      </c>
+      <c r="O291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -13887,10 +14763,13 @@
         <v>0.447</v>
       </c>
       <c r="M292" s="1" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="N292" s="1" t="n">
         <v>0.4488</v>
       </c>
-      <c r="N292" s="1" t="n">
-        <v>0.447</v>
+      <c r="O292" s="1" t="n">
+        <v>0.4469</v>
       </c>
     </row>
     <row r="293">
@@ -13933,9 +14812,12 @@
         <v>0.08278000000000001</v>
       </c>
       <c r="M293" s="1" t="n">
+        <v>0.08289000000000001</v>
+      </c>
+      <c r="N293" s="1" t="n">
         <v>0.08298</v>
       </c>
-      <c r="N293" s="1" t="n">
+      <c r="O293" s="1" t="n">
         <v>0.08136</v>
       </c>
     </row>
@@ -13979,9 +14861,12 @@
         <v>0.0279</v>
       </c>
       <c r="M294" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="N294" s="1" t="n">
         <v>0.02801</v>
       </c>
-      <c r="N294" s="1" t="n">
+      <c r="O294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -14025,9 +14910,12 @@
         <v>0.95</v>
       </c>
       <c r="M295" s="1" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="N295" s="1" t="n">
         <v>0.958</v>
       </c>
-      <c r="N295" s="1" t="n">
+      <c r="O295" s="1" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -14071,9 +14959,12 @@
         <v>0.006976</v>
       </c>
       <c r="M296" s="1" t="n">
+        <v>0.006979</v>
+      </c>
+      <c r="N296" s="1" t="n">
         <v>0.007008</v>
       </c>
-      <c r="N296" s="1" t="n">
+      <c r="O296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -14117,9 +15008,12 @@
         <v>0.1213</v>
       </c>
       <c r="M297" s="1" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="N297" s="1" t="n">
         <v>0.1215</v>
       </c>
-      <c r="N297" s="1" t="n">
+      <c r="O297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -14163,9 +15057,12 @@
         <v>0.01557</v>
       </c>
       <c r="M298" s="1" t="n">
+        <v>0.01552</v>
+      </c>
+      <c r="N298" s="1" t="n">
         <v>0.01563</v>
       </c>
-      <c r="N298" s="1" t="n">
+      <c r="O298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -14209,9 +15106,12 @@
         <v>0.4405</v>
       </c>
       <c r="M299" s="1" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="N299" s="1" t="n">
         <v>0.4431</v>
       </c>
-      <c r="N299" s="1" t="n">
+      <c r="O299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -14255,9 +15155,12 @@
         <v>0.009129999999999999</v>
       </c>
       <c r="M300" s="1" t="n">
+        <v>0.00916</v>
+      </c>
+      <c r="N300" s="1" t="n">
         <v>0.00924</v>
       </c>
-      <c r="N300" s="1" t="n">
+      <c r="O300" s="1" t="n">
         <v>0.009129999999999999</v>
       </c>
     </row>
@@ -14301,9 +15204,12 @@
         <v>0.1886</v>
       </c>
       <c r="M301" s="1" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="N301" s="1" t="n">
         <v>0.1905</v>
       </c>
-      <c r="N301" s="1" t="n">
+      <c r="O301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -14347,9 +15253,12 @@
         <v>0.0076</v>
       </c>
       <c r="M302" s="1" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="N302" s="1" t="n">
         <v>0.00765</v>
       </c>
-      <c r="N302" s="1" t="n">
+      <c r="O302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -14393,10 +15302,13 @@
         <v>0.0002147</v>
       </c>
       <c r="M303" s="1" t="n">
+        <v>0.0002141</v>
+      </c>
+      <c r="N303" s="1" t="n">
         <v>0.0002171</v>
       </c>
-      <c r="N303" s="1" t="n">
-        <v>0.0002147</v>
+      <c r="O303" s="1" t="n">
+        <v>0.0002141</v>
       </c>
     </row>
     <row r="304">
@@ -14439,9 +15351,12 @@
         <v>0.01545</v>
       </c>
       <c r="M304" s="1" t="n">
+        <v>0.01552</v>
+      </c>
+      <c r="N304" s="1" t="n">
         <v>0.01555</v>
       </c>
-      <c r="N304" s="1" t="n">
+      <c r="O304" s="1" t="n">
         <v>0.01542</v>
       </c>
     </row>
@@ -14485,9 +15400,12 @@
         <v>0.07401000000000001</v>
       </c>
       <c r="M305" s="1" t="n">
-        <v>0.07401000000000001</v>
+        <v>0.07407</v>
       </c>
       <c r="N305" s="1" t="n">
+        <v>0.07407</v>
+      </c>
+      <c r="O305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -14531,9 +15449,12 @@
         <v>0.08344</v>
       </c>
       <c r="M306" s="1" t="n">
-        <v>0.08347</v>
+        <v>0.08348999999999999</v>
       </c>
       <c r="N306" s="1" t="n">
+        <v>0.08348999999999999</v>
+      </c>
+      <c r="O306" s="1" t="n">
         <v>0.08275</v>
       </c>
     </row>
@@ -14577,9 +15498,12 @@
         <v>0.01801</v>
       </c>
       <c r="M307" s="1" t="n">
+        <v>0.01801</v>
+      </c>
+      <c r="N307" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="N307" s="1" t="n">
+      <c r="O307" s="1" t="n">
         <v>0.01801</v>
       </c>
     </row>
@@ -14623,9 +15547,12 @@
         <v>0.0006261</v>
       </c>
       <c r="M308" s="1" t="n">
+        <v>0.0006257</v>
+      </c>
+      <c r="N308" s="1" t="n">
         <v>0.0006274</v>
       </c>
-      <c r="N308" s="1" t="n">
+      <c r="O308" s="1" t="n">
         <v>0.0006212</v>
       </c>
     </row>
@@ -14669,9 +15596,12 @@
         <v>0.08223</v>
       </c>
       <c r="M309" s="1" t="n">
+        <v>0.08243</v>
+      </c>
+      <c r="N309" s="1" t="n">
         <v>0.08294</v>
       </c>
-      <c r="N309" s="1" t="n">
+      <c r="O309" s="1" t="n">
         <v>0.0822</v>
       </c>
     </row>
@@ -14715,9 +15645,12 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="M310" s="1" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0982</v>
       </c>
       <c r="N310" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="O310" s="1" t="n">
         <v>0.0973</v>
       </c>
     </row>
@@ -14761,9 +15694,12 @@
         <v>0.2123</v>
       </c>
       <c r="M311" s="1" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="N311" s="1" t="n">
         <v>0.2126</v>
       </c>
-      <c r="N311" s="1" t="n">
+      <c r="O311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -14807,9 +15743,12 @@
         <v>0.3956</v>
       </c>
       <c r="M312" s="1" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="N312" s="1" t="n">
         <v>0.3958</v>
       </c>
-      <c r="N312" s="1" t="n">
+      <c r="O312" s="1" t="n">
         <v>0.387</v>
       </c>
     </row>
@@ -14853,9 +15792,12 @@
         <v>0.10458</v>
       </c>
       <c r="M313" s="1" t="n">
+        <v>0.10473</v>
+      </c>
+      <c r="N313" s="1" t="n">
         <v>0.10542</v>
       </c>
-      <c r="N313" s="1" t="n">
+      <c r="O313" s="1" t="n">
         <v>0.10455</v>
       </c>
     </row>
@@ -14899,9 +15841,12 @@
         <v>0.08711000000000001</v>
       </c>
       <c r="M314" s="1" t="n">
-        <v>0.08711000000000001</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="N314" s="1" t="n">
+        <v>0.08740000000000001</v>
+      </c>
+      <c r="O314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -14948,6 +15893,9 @@
         <v>0.1187</v>
       </c>
       <c r="N315" s="1" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="O315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -14991,10 +15939,13 @@
         <v>0.03602</v>
       </c>
       <c r="M316" s="1" t="n">
+        <v>0.03597</v>
+      </c>
+      <c r="N316" s="1" t="n">
         <v>0.03681</v>
       </c>
-      <c r="N316" s="1" t="n">
-        <v>0.03602</v>
+      <c r="O316" s="1" t="n">
+        <v>0.03597</v>
       </c>
     </row>
     <row r="317">
@@ -15037,9 +15988,12 @@
         <v>0.08137999999999999</v>
       </c>
       <c r="M317" s="1" t="n">
+        <v>0.08143</v>
+      </c>
+      <c r="N317" s="1" t="n">
         <v>0.08164</v>
       </c>
-      <c r="N317" s="1" t="n">
+      <c r="O317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -15083,9 +16037,12 @@
         <v>0.03746</v>
       </c>
       <c r="M318" s="1" t="n">
+        <v>0.03739</v>
+      </c>
+      <c r="N318" s="1" t="n">
         <v>0.03766</v>
       </c>
-      <c r="N318" s="1" t="n">
+      <c r="O318" s="1" t="n">
         <v>0.03736</v>
       </c>
     </row>
@@ -15129,9 +16086,12 @@
         <v>0.4296</v>
       </c>
       <c r="M319" s="1" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="N319" s="1" t="n">
         <v>0.4347</v>
       </c>
-      <c r="N319" s="1" t="n">
+      <c r="O319" s="1" t="n">
         <v>0.4296</v>
       </c>
     </row>
@@ -15175,9 +16135,12 @@
         <v>0.1604</v>
       </c>
       <c r="M320" s="1" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="N320" s="1" t="n">
         <v>0.1614</v>
       </c>
-      <c r="N320" s="1" t="n">
+      <c r="O320" s="1" t="n">
         <v>0.1598</v>
       </c>
     </row>
@@ -15221,9 +16184,12 @@
         <v>5.681</v>
       </c>
       <c r="M321" s="1" t="n">
+        <v>5.678</v>
+      </c>
+      <c r="N321" s="1" t="n">
         <v>5.688</v>
       </c>
-      <c r="N321" s="1" t="n">
+      <c r="O321" s="1" t="n">
         <v>5.677</v>
       </c>
     </row>
@@ -15267,9 +16233,12 @@
         <v>0.003742</v>
       </c>
       <c r="M322" s="1" t="n">
-        <v>0.003754</v>
+        <v>0.003756</v>
       </c>
       <c r="N322" s="1" t="n">
+        <v>0.003756</v>
+      </c>
+      <c r="O322" s="1" t="n">
         <v>0.003714</v>
       </c>
     </row>
@@ -15313,9 +16282,12 @@
         <v>0.001758</v>
       </c>
       <c r="M323" s="1" t="n">
+        <v>0.001757</v>
+      </c>
+      <c r="N323" s="1" t="n">
         <v>0.001762</v>
       </c>
-      <c r="N323" s="1" t="n">
+      <c r="O323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -15362,6 +16334,9 @@
         <v>1.2e-05</v>
       </c>
       <c r="N324" s="1" t="n">
+        <v>1.2e-05</v>
+      </c>
+      <c r="O324" s="1" t="n">
         <v>1.19e-05</v>
       </c>
     </row>
@@ -15405,9 +16380,12 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="M325" s="1" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="N325" s="1" t="n">
         <v>0.08649999999999999</v>
       </c>
-      <c r="N325" s="1" t="n">
+      <c r="O325" s="1" t="n">
         <v>0.0857</v>
       </c>
     </row>
@@ -15451,9 +16429,12 @@
         <v>0.01732</v>
       </c>
       <c r="M326" s="1" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="N326" s="1" t="n">
         <v>0.01736</v>
       </c>
-      <c r="N326" s="1" t="n">
+      <c r="O326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -15497,9 +16478,12 @@
         <v>0.01684</v>
       </c>
       <c r="M327" s="1" t="n">
+        <v>0.01686</v>
+      </c>
+      <c r="N327" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="N327" s="1" t="n">
+      <c r="O327" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -15543,9 +16527,12 @@
         <v>4.449</v>
       </c>
       <c r="M328" s="1" t="n">
+        <v>4.456</v>
+      </c>
+      <c r="N328" s="1" t="n">
         <v>4.462</v>
       </c>
-      <c r="N328" s="1" t="n">
+      <c r="O328" s="1" t="n">
         <v>4.446</v>
       </c>
     </row>
@@ -15589,9 +16576,12 @@
         <v>0.009730000000000001</v>
       </c>
       <c r="M329" s="1" t="n">
+        <v>0.009712999999999999</v>
+      </c>
+      <c r="N329" s="1" t="n">
         <v>0.009861</v>
       </c>
-      <c r="N329" s="1" t="n">
+      <c r="O329" s="1" t="n">
         <v>0.009532000000000001</v>
       </c>
     </row>
@@ -15635,10 +16625,13 @@
         <v>5181.1</v>
       </c>
       <c r="M330" s="1" t="n">
+        <v>5177.4</v>
+      </c>
+      <c r="N330" s="1" t="n">
         <v>5192.9</v>
       </c>
-      <c r="N330" s="1" t="n">
-        <v>5180</v>
+      <c r="O330" s="1" t="n">
+        <v>5177.4</v>
       </c>
     </row>
     <row r="331">
@@ -15681,9 +16674,12 @@
         <v>0.07092</v>
       </c>
       <c r="M331" s="1" t="n">
-        <v>0.07092</v>
+        <v>0.07098</v>
       </c>
       <c r="N331" s="1" t="n">
+        <v>0.07098</v>
+      </c>
+      <c r="O331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -15727,9 +16723,12 @@
         <v>0.06084</v>
       </c>
       <c r="M332" s="1" t="n">
+        <v>0.06085</v>
+      </c>
+      <c r="N332" s="1" t="n">
         <v>0.06106</v>
       </c>
-      <c r="N332" s="1" t="n">
+      <c r="O332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -15773,9 +16772,12 @@
         <v>0.10531</v>
       </c>
       <c r="M333" s="1" t="n">
-        <v>0.10558</v>
+        <v>0.10584</v>
       </c>
       <c r="N333" s="1" t="n">
+        <v>0.10584</v>
+      </c>
+      <c r="O333" s="1" t="n">
         <v>0.10341</v>
       </c>
     </row>
@@ -15819,9 +16821,12 @@
         <v>0.08755</v>
       </c>
       <c r="M334" s="1" t="n">
+        <v>0.08746</v>
+      </c>
+      <c r="N334" s="1" t="n">
         <v>0.08837</v>
       </c>
-      <c r="N334" s="1" t="n">
+      <c r="O334" s="1" t="n">
         <v>0.08734</v>
       </c>
     </row>
@@ -15865,9 +16870,12 @@
         <v>0.016489</v>
       </c>
       <c r="M335" s="1" t="n">
-        <v>0.016489</v>
+        <v>0.01649</v>
       </c>
       <c r="N335" s="1" t="n">
+        <v>0.01649</v>
+      </c>
+      <c r="O335" s="1" t="n">
         <v>0.016391</v>
       </c>
     </row>
@@ -15911,9 +16919,12 @@
         <v>0.04618</v>
       </c>
       <c r="M336" s="1" t="n">
+        <v>0.04617</v>
+      </c>
+      <c r="N336" s="1" t="n">
         <v>0.04619</v>
       </c>
-      <c r="N336" s="1" t="n">
+      <c r="O336" s="1" t="n">
         <v>0.04583</v>
       </c>
     </row>
@@ -15957,9 +16968,12 @@
         <v>0.1942</v>
       </c>
       <c r="M337" s="1" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="N337" s="1" t="n">
         <v>0.1942</v>
       </c>
-      <c r="N337" s="1" t="n">
+      <c r="O337" s="1" t="n">
         <v>0.1838</v>
       </c>
     </row>
@@ -16003,9 +17017,12 @@
         <v>0.1837</v>
       </c>
       <c r="M338" s="1" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="N338" s="1" t="n">
         <v>0.1843</v>
       </c>
-      <c r="N338" s="1" t="n">
+      <c r="O338" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -16049,9 +17066,12 @@
         <v>0.01842</v>
       </c>
       <c r="M339" s="1" t="n">
-        <v>0.01843</v>
+        <v>0.01845</v>
       </c>
       <c r="N339" s="1" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="O339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -16095,9 +17115,12 @@
         <v>0.02326</v>
       </c>
       <c r="M340" s="1" t="n">
-        <v>0.02326</v>
+        <v>0.02329</v>
       </c>
       <c r="N340" s="1" t="n">
+        <v>0.02329</v>
+      </c>
+      <c r="O340" s="1" t="n">
         <v>0.02305</v>
       </c>
     </row>
@@ -16141,9 +17164,12 @@
         <v>0.4561</v>
       </c>
       <c r="M341" s="1" t="n">
+        <v>0.4568</v>
+      </c>
+      <c r="N341" s="1" t="n">
         <v>0.4577</v>
       </c>
-      <c r="N341" s="1" t="n">
+      <c r="O341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -16187,9 +17213,12 @@
         <v>0.0135</v>
       </c>
       <c r="M342" s="1" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="N342" s="1" t="n">
         <v>0.01352</v>
       </c>
-      <c r="N342" s="1" t="n">
+      <c r="O342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -16233,9 +17262,12 @@
         <v>2.884</v>
       </c>
       <c r="M343" s="1" t="n">
+        <v>2.889</v>
+      </c>
+      <c r="N343" s="1" t="n">
         <v>2.89</v>
       </c>
-      <c r="N343" s="1" t="n">
+      <c r="O343" s="1" t="n">
         <v>2.872</v>
       </c>
     </row>
@@ -16279,9 +17311,12 @@
         <v>0.1526</v>
       </c>
       <c r="M344" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="N344" s="1" t="n">
         <v>0.1577</v>
       </c>
-      <c r="N344" s="1" t="n">
+      <c r="O344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -16325,9 +17360,12 @@
         <v>0.005394</v>
       </c>
       <c r="M345" s="1" t="n">
+        <v>0.005378</v>
+      </c>
+      <c r="N345" s="1" t="n">
         <v>0.005407</v>
       </c>
-      <c r="N345" s="1" t="n">
+      <c r="O345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -16371,9 +17409,12 @@
         <v>0.05776</v>
       </c>
       <c r="M346" s="1" t="n">
+        <v>0.05778</v>
+      </c>
+      <c r="N346" s="1" t="n">
         <v>0.0579</v>
       </c>
-      <c r="N346" s="1" t="n">
+      <c r="O346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -16417,9 +17458,12 @@
         <v>2600</v>
       </c>
       <c r="M347" s="1" t="n">
+        <v>2604</v>
+      </c>
+      <c r="N347" s="1" t="n">
         <v>2613</v>
       </c>
-      <c r="N347" s="1" t="n">
+      <c r="O347" s="1" t="n">
         <v>2597</v>
       </c>
     </row>
@@ -16463,9 +17507,12 @@
         <v>0.0463</v>
       </c>
       <c r="M348" s="1" t="n">
+        <v>0.04633</v>
+      </c>
+      <c r="N348" s="1" t="n">
         <v>0.04642</v>
       </c>
-      <c r="N348" s="1" t="n">
+      <c r="O348" s="1" t="n">
         <v>0.04595</v>
       </c>
     </row>
@@ -16509,9 +17556,12 @@
         <v>0.005661</v>
       </c>
       <c r="M349" s="1" t="n">
+        <v>0.005639</v>
+      </c>
+      <c r="N349" s="1" t="n">
         <v>0.005714</v>
       </c>
-      <c r="N349" s="1" t="n">
+      <c r="O349" s="1" t="n">
         <v>0.005625</v>
       </c>
     </row>
@@ -16555,9 +17605,12 @@
         <v>195.79</v>
       </c>
       <c r="M350" s="1" t="n">
+        <v>195.76</v>
+      </c>
+      <c r="N350" s="1" t="n">
         <v>195.95</v>
       </c>
-      <c r="N350" s="1" t="n">
+      <c r="O350" s="1" t="n">
         <v>195.23</v>
       </c>
     </row>
@@ -16601,9 +17654,12 @@
         <v>0.08235000000000001</v>
       </c>
       <c r="M351" s="1" t="n">
+        <v>0.08239</v>
+      </c>
+      <c r="N351" s="1" t="n">
         <v>0.08245</v>
       </c>
-      <c r="N351" s="1" t="n">
+      <c r="O351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -16647,9 +17703,12 @@
         <v>0.00741</v>
       </c>
       <c r="M352" s="1" t="n">
+        <v>0.007425</v>
+      </c>
+      <c r="N352" s="1" t="n">
         <v>0.007571</v>
       </c>
-      <c r="N352" s="1" t="n">
+      <c r="O352" s="1" t="n">
         <v>0.00741</v>
       </c>
     </row>
@@ -16693,9 +17752,12 @@
         <v>1.4827</v>
       </c>
       <c r="M353" s="1" t="n">
+        <v>1.4839</v>
+      </c>
+      <c r="N353" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="N353" s="1" t="n">
+      <c r="O353" s="1" t="n">
         <v>1.4807</v>
       </c>
     </row>
@@ -16739,9 +17801,12 @@
         <v>0.07656</v>
       </c>
       <c r="M354" s="1" t="n">
+        <v>0.07663</v>
+      </c>
+      <c r="N354" s="1" t="n">
         <v>0.07677</v>
       </c>
-      <c r="N354" s="1" t="n">
+      <c r="O354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -16785,9 +17850,12 @@
         <v>0.04839</v>
       </c>
       <c r="M355" s="1" t="n">
+        <v>0.04857</v>
+      </c>
+      <c r="N355" s="1" t="n">
         <v>0.04921</v>
       </c>
-      <c r="N355" s="1" t="n">
+      <c r="O355" s="1" t="n">
         <v>0.04839</v>
       </c>
     </row>
@@ -16831,9 +17899,12 @@
         <v>0.2872</v>
       </c>
       <c r="M356" s="1" t="n">
-        <v>0.2872</v>
+        <v>0.2874</v>
       </c>
       <c r="N356" s="1" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="O356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -16877,9 +17948,12 @@
         <v>0.1472</v>
       </c>
       <c r="M357" s="1" t="n">
+        <v>0.1472</v>
+      </c>
+      <c r="N357" s="1" t="n">
         <v>0.1473</v>
       </c>
-      <c r="N357" s="1" t="n">
+      <c r="O357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -16923,10 +17997,13 @@
         <v>1.348</v>
       </c>
       <c r="M358" s="1" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="N358" s="1" t="n">
         <v>1.355</v>
       </c>
-      <c r="N358" s="1" t="n">
-        <v>1.348</v>
+      <c r="O358" s="1" t="n">
+        <v>1.345</v>
       </c>
     </row>
     <row r="359">
@@ -16969,9 +18046,12 @@
         <v>0.6136</v>
       </c>
       <c r="M359" s="1" t="n">
-        <v>0.6136</v>
+        <v>0.6143</v>
       </c>
       <c r="N359" s="1" t="n">
+        <v>0.6143</v>
+      </c>
+      <c r="O359" s="1" t="n">
         <v>0.6081</v>
       </c>
     </row>
@@ -17015,9 +18095,12 @@
         <v>0.1147</v>
       </c>
       <c r="M360" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="N360" s="1" t="n">
         <v>0.1149</v>
       </c>
-      <c r="N360" s="1" t="n">
+      <c r="O360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -17061,9 +18144,12 @@
         <v>0.0265</v>
       </c>
       <c r="M361" s="1" t="n">
+        <v>0.02658</v>
+      </c>
+      <c r="N361" s="1" t="n">
         <v>0.02678</v>
       </c>
-      <c r="N361" s="1" t="n">
+      <c r="O361" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -17107,9 +18193,12 @@
         <v>3.05e-05</v>
       </c>
       <c r="M362" s="1" t="n">
+        <v>3.04e-05</v>
+      </c>
+      <c r="N362" s="1" t="n">
         <v>3.05e-05</v>
       </c>
-      <c r="N362" s="1" t="n">
+      <c r="O362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -17153,9 +18242,12 @@
         <v>0.01025</v>
       </c>
       <c r="M363" s="1" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="N363" s="1" t="n">
         <v>0.01047</v>
       </c>
-      <c r="N363" s="1" t="n">
+      <c r="O363" s="1" t="n">
         <v>0.01018</v>
       </c>
     </row>
@@ -17199,9 +18291,12 @@
         <v>0.06227</v>
       </c>
       <c r="M364" s="1" t="n">
-        <v>0.06233</v>
+        <v>0.06238</v>
       </c>
       <c r="N364" s="1" t="n">
+        <v>0.06238</v>
+      </c>
+      <c r="O364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -17245,9 +18340,12 @@
         <v>0.03275</v>
       </c>
       <c r="M365" s="1" t="n">
+        <v>0.03277</v>
+      </c>
+      <c r="N365" s="1" t="n">
         <v>0.03299</v>
       </c>
-      <c r="N365" s="1" t="n">
+      <c r="O365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -17291,9 +18389,12 @@
         <v>0.0334</v>
       </c>
       <c r="M366" s="1" t="n">
+        <v>0.03332</v>
+      </c>
+      <c r="N366" s="1" t="n">
         <v>0.0334</v>
       </c>
-      <c r="N366" s="1" t="n">
+      <c r="O366" s="1" t="n">
         <v>0.03283</v>
       </c>
     </row>
@@ -17337,9 +18438,12 @@
         <v>0.012295</v>
       </c>
       <c r="M367" s="1" t="n">
+        <v>0.012327</v>
+      </c>
+      <c r="N367" s="1" t="n">
         <v>0.012357</v>
       </c>
-      <c r="N367" s="1" t="n">
+      <c r="O367" s="1" t="n">
         <v>0.012155</v>
       </c>
     </row>
@@ -17383,9 +18487,12 @@
         <v>0.03571</v>
       </c>
       <c r="M368" s="1" t="n">
-        <v>0.03574</v>
+        <v>0.03627</v>
       </c>
       <c r="N368" s="1" t="n">
+        <v>0.03627</v>
+      </c>
+      <c r="O368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -17429,9 +18536,12 @@
         <v>0.6279</v>
       </c>
       <c r="M369" s="1" t="n">
+        <v>0.6274999999999999</v>
+      </c>
+      <c r="N369" s="1" t="n">
         <v>0.6307</v>
       </c>
-      <c r="N369" s="1" t="n">
+      <c r="O369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -17475,10 +18585,13 @@
         <v>0.008149999999999999</v>
       </c>
       <c r="M370" s="1" t="n">
+        <v>0.00812</v>
+      </c>
+      <c r="N370" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="N370" s="1" t="n">
-        <v>0.008149999999999999</v>
+      <c r="O370" s="1" t="n">
+        <v>0.00812</v>
       </c>
     </row>
     <row r="371">
@@ -17521,9 +18634,12 @@
         <v>0.004139</v>
       </c>
       <c r="M371" s="1" t="n">
+        <v>0.004115</v>
+      </c>
+      <c r="N371" s="1" t="n">
         <v>0.004166</v>
       </c>
-      <c r="N371" s="1" t="n">
+      <c r="O371" s="1" t="n">
         <v>0.003242</v>
       </c>
     </row>
@@ -17567,9 +18683,12 @@
         <v>0.13362</v>
       </c>
       <c r="M372" s="1" t="n">
+        <v>0.13329</v>
+      </c>
+      <c r="N372" s="1" t="n">
         <v>0.13391</v>
       </c>
-      <c r="N372" s="1" t="n">
+      <c r="O372" s="1" t="n">
         <v>0.13227</v>
       </c>
     </row>
@@ -17613,10 +18732,13 @@
         <v>0.00776</v>
       </c>
       <c r="M373" s="1" t="n">
+        <v>0.007717</v>
+      </c>
+      <c r="N373" s="1" t="n">
         <v>0.007822000000000001</v>
       </c>
-      <c r="N373" s="1" t="n">
-        <v>0.00776</v>
+      <c r="O373" s="1" t="n">
+        <v>0.007717</v>
       </c>
     </row>
     <row r="374">
@@ -17659,9 +18781,12 @@
         <v>0.01994</v>
       </c>
       <c r="M374" s="1" t="n">
+        <v>0.01998</v>
+      </c>
+      <c r="N374" s="1" t="n">
         <v>0.02003</v>
       </c>
-      <c r="N374" s="1" t="n">
+      <c r="O374" s="1" t="n">
         <v>0.01969</v>
       </c>
     </row>
@@ -17705,9 +18830,12 @@
         <v>0.0005922</v>
       </c>
       <c r="M375" s="1" t="n">
+        <v>0.000592</v>
+      </c>
+      <c r="N375" s="1" t="n">
         <v>0.000594</v>
       </c>
-      <c r="N375" s="1" t="n">
+      <c r="O375" s="1" t="n">
         <v>0.0005910000000000001</v>
       </c>
     </row>
@@ -17754,6 +18882,9 @@
         <v>0.0363</v>
       </c>
       <c r="N376" s="1" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="O376" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -17797,9 +18928,12 @@
         <v>0.000796</v>
       </c>
       <c r="M377" s="1" t="n">
-        <v>0.000796</v>
+        <v>0.0007999</v>
       </c>
       <c r="N377" s="1" t="n">
+        <v>0.0007999</v>
+      </c>
+      <c r="O377" s="1" t="n">
         <v>0.0007848</v>
       </c>
     </row>
@@ -17843,9 +18977,12 @@
         <v>2.04</v>
       </c>
       <c r="M378" s="1" t="n">
-        <v>2.044</v>
+        <v>2.051</v>
       </c>
       <c r="N378" s="1" t="n">
+        <v>2.051</v>
+      </c>
+      <c r="O378" s="1" t="n">
         <v>1.973</v>
       </c>
     </row>
@@ -17889,9 +19026,12 @@
         <v>0.0005928</v>
       </c>
       <c r="M379" s="1" t="n">
+        <v>0.0005926</v>
+      </c>
+      <c r="N379" s="1" t="n">
         <v>0.0005932</v>
       </c>
-      <c r="N379" s="1" t="n">
+      <c r="O379" s="1" t="n">
         <v>0.0005881</v>
       </c>
     </row>
@@ -17935,9 +19075,12 @@
         <v>0.03764</v>
       </c>
       <c r="M380" s="1" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="N380" s="1" t="n">
         <v>0.03764</v>
       </c>
-      <c r="N380" s="1" t="n">
+      <c r="O380" s="1" t="n">
         <v>0.03737</v>
       </c>
     </row>
@@ -17981,9 +19124,12 @@
         <v>0.05473</v>
       </c>
       <c r="M381" s="1" t="n">
+        <v>0.05475</v>
+      </c>
+      <c r="N381" s="1" t="n">
         <v>0.05486</v>
       </c>
-      <c r="N381" s="1" t="n">
+      <c r="O381" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -18027,9 +19173,12 @@
         <v>0.01213</v>
       </c>
       <c r="M382" s="1" t="n">
-        <v>0.01214</v>
+        <v>0.01217</v>
       </c>
       <c r="N382" s="1" t="n">
+        <v>0.01217</v>
+      </c>
+      <c r="O382" s="1" t="n">
         <v>0.01202</v>
       </c>
     </row>
@@ -18073,9 +19222,12 @@
         <v>0.001553</v>
       </c>
       <c r="M383" s="1" t="n">
+        <v>0.001553</v>
+      </c>
+      <c r="N383" s="1" t="n">
         <v>0.001559</v>
       </c>
-      <c r="N383" s="1" t="n">
+      <c r="O383" s="1" t="n">
         <v>0.001549</v>
       </c>
     </row>
@@ -18119,9 +19271,12 @@
         <v>0.0002166</v>
       </c>
       <c r="M384" s="1" t="n">
-        <v>0.0002167</v>
+        <v>0.0002168</v>
       </c>
       <c r="N384" s="1" t="n">
+        <v>0.0002168</v>
+      </c>
+      <c r="O384" s="1" t="n">
         <v>0.0002154</v>
       </c>
     </row>
@@ -18165,9 +19320,12 @@
         <v>0.00243</v>
       </c>
       <c r="M385" s="1" t="n">
-        <v>0.00243</v>
+        <v>0.00244</v>
       </c>
       <c r="N385" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="O385" s="1" t="n">
         <v>0.0024</v>
       </c>
     </row>
@@ -18211,9 +19369,12 @@
         <v>3.955</v>
       </c>
       <c r="M386" s="1" t="n">
-        <v>3.955</v>
+        <v>3.966</v>
       </c>
       <c r="N386" s="1" t="n">
+        <v>3.966</v>
+      </c>
+      <c r="O386" s="1" t="n">
         <v>3.892</v>
       </c>
     </row>
@@ -18260,6 +19421,9 @@
         <v>0.0006316</v>
       </c>
       <c r="N387" s="1" t="n">
+        <v>0.0006316</v>
+      </c>
+      <c r="O387" s="1" t="n">
         <v>0.0006236</v>
       </c>
     </row>
@@ -18303,9 +19467,12 @@
         <v>0.00656</v>
       </c>
       <c r="M388" s="1" t="n">
+        <v>0.00656</v>
+      </c>
+      <c r="N388" s="1" t="n">
         <v>0.00673</v>
       </c>
-      <c r="N388" s="1" t="n">
+      <c r="O388" s="1" t="n">
         <v>0.00653</v>
       </c>
     </row>
@@ -18349,9 +19516,12 @@
         <v>0.1325</v>
       </c>
       <c r="M389" s="1" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="N389" s="1" t="n">
         <v>0.1325</v>
       </c>
-      <c r="N389" s="1" t="n">
+      <c r="O389" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -18395,9 +19565,12 @@
         <v>0.03229</v>
       </c>
       <c r="M390" s="1" t="n">
+        <v>0.03223</v>
+      </c>
+      <c r="N390" s="1" t="n">
         <v>0.03248</v>
       </c>
-      <c r="N390" s="1" t="n">
+      <c r="O390" s="1" t="n">
         <v>0.03201</v>
       </c>
     </row>
@@ -18444,6 +19617,9 @@
         <v>0.06401999999999999</v>
       </c>
       <c r="N391" s="1" t="n">
+        <v>0.06401999999999999</v>
+      </c>
+      <c r="O391" s="1" t="n">
         <v>0.06344</v>
       </c>
     </row>
@@ -18490,6 +19666,9 @@
         <v>27.95</v>
       </c>
       <c r="N392" s="1" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="O392" s="1" t="n">
         <v>27.57</v>
       </c>
     </row>
@@ -18533,9 +19712,12 @@
         <v>0.000416</v>
       </c>
       <c r="M393" s="1" t="n">
-        <v>0.000416</v>
+        <v>0.000417</v>
       </c>
       <c r="N393" s="1" t="n">
+        <v>0.000417</v>
+      </c>
+      <c r="O393" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -18579,9 +19761,12 @@
         <v>0.06970999999999999</v>
       </c>
       <c r="M394" s="1" t="n">
+        <v>0.07002</v>
+      </c>
+      <c r="N394" s="1" t="n">
         <v>0.07005</v>
       </c>
-      <c r="N394" s="1" t="n">
+      <c r="O394" s="1" t="n">
         <v>0.06926</v>
       </c>
     </row>
@@ -18628,6 +19813,9 @@
         <v>0.2614</v>
       </c>
       <c r="N395" s="1" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="O395" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -18671,9 +19859,12 @@
         <v>0.004688</v>
       </c>
       <c r="M396" s="1" t="n">
-        <v>0.004693</v>
+        <v>0.004694</v>
       </c>
       <c r="N396" s="1" t="n">
+        <v>0.004694</v>
+      </c>
+      <c r="O396" s="1" t="n">
         <v>0.004677</v>
       </c>
     </row>
@@ -18717,9 +19908,12 @@
         <v>0.2354</v>
       </c>
       <c r="M397" s="1" t="n">
+        <v>0.2357</v>
+      </c>
+      <c r="N397" s="1" t="n">
         <v>0.2367</v>
       </c>
-      <c r="N397" s="1" t="n">
+      <c r="O397" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
@@ -18763,9 +19957,12 @@
         <v>0.18218</v>
       </c>
       <c r="M398" s="1" t="n">
+        <v>0.18204</v>
+      </c>
+      <c r="N398" s="1" t="n">
         <v>0.18235</v>
       </c>
-      <c r="N398" s="1" t="n">
+      <c r="O398" s="1" t="n">
         <v>0.18106</v>
       </c>
     </row>
@@ -18809,9 +20006,12 @@
         <v>0.04151</v>
       </c>
       <c r="M399" s="1" t="n">
+        <v>0.04145</v>
+      </c>
+      <c r="N399" s="1" t="n">
         <v>0.04151</v>
       </c>
-      <c r="N399" s="1" t="n">
+      <c r="O399" s="1" t="n">
         <v>0.04108</v>
       </c>
     </row>
@@ -18858,6 +20058,9 @@
         <v>0.076</v>
       </c>
       <c r="N400" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="O400" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -18901,9 +20104,12 @@
         <v>0.001752</v>
       </c>
       <c r="M401" s="1" t="n">
+        <v>0.001763</v>
+      </c>
+      <c r="N401" s="1" t="n">
         <v>0.001766</v>
       </c>
-      <c r="N401" s="1" t="n">
+      <c r="O401" s="1" t="n">
         <v>0.001739</v>
       </c>
     </row>
@@ -18947,9 +20153,12 @@
         <v>0.05403</v>
       </c>
       <c r="M402" s="1" t="n">
-        <v>0.05403</v>
+        <v>0.05408</v>
       </c>
       <c r="N402" s="1" t="n">
+        <v>0.05408</v>
+      </c>
+      <c r="O402" s="1" t="n">
         <v>0.05362</v>
       </c>
     </row>
@@ -18993,10 +20202,13 @@
         <v>2027.2</v>
       </c>
       <c r="M403" s="1" t="n">
+        <v>2026.33</v>
+      </c>
+      <c r="N403" s="1" t="n">
         <v>2031.8</v>
       </c>
-      <c r="N403" s="1" t="n">
-        <v>2026.65</v>
+      <c r="O403" s="1" t="n">
+        <v>2026.33</v>
       </c>
     </row>
     <row r="404">
@@ -19039,9 +20251,12 @@
         <v>1.079</v>
       </c>
       <c r="M404" s="1" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="N404" s="1" t="n">
         <v>1.082</v>
       </c>
-      <c r="N404" s="1" t="n">
+      <c r="O404" s="1" t="n">
         <v>1.078</v>
       </c>
     </row>
@@ -19085,10 +20300,13 @@
         <v>7.645</v>
       </c>
       <c r="M405" s="1" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="N405" s="1" t="n">
         <v>7.673</v>
       </c>
-      <c r="N405" s="1" t="n">
-        <v>7.645</v>
+      <c r="O405" s="1" t="n">
+        <v>7.63</v>
       </c>
     </row>
     <row r="406">
@@ -19131,9 +20349,12 @@
         <v>3.259</v>
       </c>
       <c r="M406" s="1" t="n">
+        <v>3.261</v>
+      </c>
+      <c r="N406" s="1" t="n">
         <v>3.274</v>
       </c>
-      <c r="N406" s="1" t="n">
+      <c r="O406" s="1" t="n">
         <v>3.238</v>
       </c>
     </row>
@@ -19177,9 +20398,12 @@
         <v>0.1822</v>
       </c>
       <c r="M407" s="1" t="n">
-        <v>0.1825</v>
+        <v>0.1827</v>
       </c>
       <c r="N407" s="1" t="n">
+        <v>0.1827</v>
+      </c>
+      <c r="O407" s="1" t="n">
         <v>0.1814</v>
       </c>
     </row>
@@ -19223,10 +20447,13 @@
         <v>0.1526</v>
       </c>
       <c r="M408" s="1" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="N408" s="1" t="n">
         <v>0.1537</v>
       </c>
-      <c r="N408" s="1" t="n">
-        <v>0.1525</v>
+      <c r="O408" s="1" t="n">
+        <v>0.1524</v>
       </c>
     </row>
     <row r="409">
@@ -19269,9 +20496,12 @@
         <v>0.07382</v>
       </c>
       <c r="M409" s="1" t="n">
-        <v>0.07385</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="N409" s="1" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="O409" s="1" t="n">
         <v>0.07315000000000001</v>
       </c>
     </row>
@@ -19315,9 +20545,12 @@
         <v>0.02118</v>
       </c>
       <c r="M410" s="1" t="n">
+        <v>0.02104</v>
+      </c>
+      <c r="N410" s="1" t="n">
         <v>0.02124</v>
       </c>
-      <c r="N410" s="1" t="n">
+      <c r="O410" s="1" t="n">
         <v>0.02076</v>
       </c>
     </row>
@@ -19361,9 +20594,12 @@
         <v>0.268</v>
       </c>
       <c r="M411" s="1" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="N411" s="1" t="n">
         <v>0.2683</v>
       </c>
-      <c r="N411" s="1" t="n">
+      <c r="O411" s="1" t="n">
         <v>0.2642</v>
       </c>
     </row>
@@ -19407,9 +20643,12 @@
         <v>0.007401</v>
       </c>
       <c r="M412" s="1" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="N412" s="1" t="n">
         <v>0.007404</v>
       </c>
-      <c r="N412" s="1" t="n">
+      <c r="O412" s="1" t="n">
         <v>0.007302</v>
       </c>
     </row>
@@ -19453,9 +20692,12 @@
         <v>0.0139</v>
       </c>
       <c r="M413" s="1" t="n">
+        <v>0.01391</v>
+      </c>
+      <c r="N413" s="1" t="n">
         <v>0.01392</v>
       </c>
-      <c r="N413" s="1" t="n">
+      <c r="O413" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -19502,6 +20744,9 @@
         <v>0.093</v>
       </c>
       <c r="N414" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O414" s="1" t="n">
         <v>0.092</v>
       </c>
     </row>
@@ -19545,9 +20790,12 @@
         <v>0.04009</v>
       </c>
       <c r="M415" s="1" t="n">
+        <v>0.03996</v>
+      </c>
+      <c r="N415" s="1" t="n">
         <v>0.04015</v>
       </c>
-      <c r="N415" s="1" t="n">
+      <c r="O415" s="1" t="n">
         <v>0.03985</v>
       </c>
     </row>
@@ -19591,10 +20839,13 @@
         <v>0.284</v>
       </c>
       <c r="M416" s="1" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="N416" s="1" t="n">
         <v>0.2854</v>
       </c>
-      <c r="N416" s="1" t="n">
-        <v>0.2839</v>
+      <c r="O416" s="1" t="n">
+        <v>0.2837</v>
       </c>
     </row>
     <row r="417">
@@ -19637,10 +20888,13 @@
         <v>1.815</v>
       </c>
       <c r="M417" s="1" t="n">
+        <v>1.807</v>
+      </c>
+      <c r="N417" s="1" t="n">
         <v>1.831</v>
       </c>
-      <c r="N417" s="1" t="n">
-        <v>1.813</v>
+      <c r="O417" s="1" t="n">
+        <v>1.807</v>
       </c>
     </row>
     <row r="418">
@@ -19683,9 +20937,12 @@
         <v>0.06712</v>
       </c>
       <c r="M418" s="1" t="n">
+        <v>0.06713</v>
+      </c>
+      <c r="N418" s="1" t="n">
         <v>0.06718</v>
       </c>
-      <c r="N418" s="1" t="n">
+      <c r="O418" s="1" t="n">
         <v>0.06668</v>
       </c>
     </row>
@@ -19729,9 +20986,12 @@
         <v>207.59</v>
       </c>
       <c r="M419" s="1" t="n">
-        <v>207.59</v>
+        <v>207.6</v>
       </c>
       <c r="N419" s="1" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="O419" s="1" t="n">
         <v>207.35</v>
       </c>
     </row>
@@ -19775,9 +21035,12 @@
         <v>73.34</v>
       </c>
       <c r="M420" s="1" t="n">
+        <v>73.34</v>
+      </c>
+      <c r="N420" s="1" t="n">
         <v>73.37</v>
       </c>
-      <c r="N420" s="1" t="n">
+      <c r="O420" s="1" t="n">
         <v>73.15000000000001</v>
       </c>
     </row>
@@ -19821,10 +21084,13 @@
         <v>0.07227</v>
       </c>
       <c r="M421" s="1" t="n">
+        <v>0.07223</v>
+      </c>
+      <c r="N421" s="1" t="n">
         <v>0.07251000000000001</v>
       </c>
-      <c r="N421" s="1" t="n">
-        <v>0.07226</v>
+      <c r="O421" s="1" t="n">
+        <v>0.07223</v>
       </c>
     </row>
     <row r="422">
@@ -19867,9 +21133,12 @@
         <v>0.05031</v>
       </c>
       <c r="M422" s="1" t="n">
+        <v>0.05003</v>
+      </c>
+      <c r="N422" s="1" t="n">
         <v>0.05076</v>
       </c>
-      <c r="N422" s="1" t="n">
+      <c r="O422" s="1" t="n">
         <v>0.04998</v>
       </c>
     </row>
@@ -19913,9 +21182,12 @@
         <v>0.001152</v>
       </c>
       <c r="M423" s="1" t="n">
+        <v>0.001151</v>
+      </c>
+      <c r="N423" s="1" t="n">
         <v>0.001153</v>
       </c>
-      <c r="N423" s="1" t="n">
+      <c r="O423" s="1" t="n">
         <v>0.001148</v>
       </c>
     </row>
@@ -19959,9 +21231,12 @@
         <v>0.00504</v>
       </c>
       <c r="M424" s="1" t="n">
+        <v>0.00504</v>
+      </c>
+      <c r="N424" s="1" t="n">
         <v>0.00505</v>
       </c>
-      <c r="N424" s="1" t="n">
+      <c r="O424" s="1" t="n">
         <v>0.00501</v>
       </c>
     </row>
@@ -20005,9 +21280,12 @@
         <v>0.1277</v>
       </c>
       <c r="M425" s="1" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="N425" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="N425" s="1" t="n">
+      <c r="O425" s="1" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -20054,6 +21332,9 @@
         <v>1.301</v>
       </c>
       <c r="N426" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="O426" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -20100,6 +21381,9 @@
         <v>0.004421</v>
       </c>
       <c r="N427" s="1" t="n">
+        <v>0.004421</v>
+      </c>
+      <c r="O427" s="1" t="n">
         <v>0.004393</v>
       </c>
     </row>
@@ -20146,6 +21430,9 @@
         <v>0.005072</v>
       </c>
       <c r="N428" s="1" t="n">
+        <v>0.005072</v>
+      </c>
+      <c r="O428" s="1" t="n">
         <v>0.005017</v>
       </c>
     </row>
@@ -20189,9 +21476,12 @@
         <v>0.02322</v>
       </c>
       <c r="M429" s="1" t="n">
-        <v>0.02329</v>
+        <v>0.02332</v>
       </c>
       <c r="N429" s="1" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="O429" s="1" t="n">
         <v>0.02288</v>
       </c>
     </row>
@@ -20235,9 +21525,12 @@
         <v>0.02509</v>
       </c>
       <c r="M430" s="1" t="n">
+        <v>0.02505</v>
+      </c>
+      <c r="N430" s="1" t="n">
         <v>0.02517</v>
       </c>
-      <c r="N430" s="1" t="n">
+      <c r="O430" s="1" t="n">
         <v>0.02499</v>
       </c>
     </row>
@@ -20284,6 +21577,9 @@
         <v>0.016</v>
       </c>
       <c r="N431" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="O431" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -20327,9 +21623,12 @@
         <v>0.54</v>
       </c>
       <c r="M432" s="1" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="N432" s="1" t="n">
         <v>0.546</v>
       </c>
-      <c r="N432" s="1" t="n">
+      <c r="O432" s="1" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -20373,9 +21672,12 @@
         <v>0.001388</v>
       </c>
       <c r="M433" s="1" t="n">
-        <v>0.00139</v>
+        <v>0.001395</v>
       </c>
       <c r="N433" s="1" t="n">
+        <v>0.001395</v>
+      </c>
+      <c r="O433" s="1" t="n">
         <v>0.001383</v>
       </c>
     </row>
@@ -20419,9 +21721,12 @@
         <v>0.3971</v>
       </c>
       <c r="M434" s="1" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="N434" s="1" t="n">
         <v>0.3975</v>
       </c>
-      <c r="N434" s="1" t="n">
+      <c r="O434" s="1" t="n">
         <v>0.3925</v>
       </c>
     </row>
@@ -20465,9 +21770,12 @@
         <v>0.001393</v>
       </c>
       <c r="M435" s="1" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="N435" s="1" t="n">
         <v>0.001393</v>
       </c>
-      <c r="N435" s="1" t="n">
+      <c r="O435" s="1" t="n">
         <v>0.001388</v>
       </c>
     </row>
@@ -20511,9 +21819,12 @@
         <v>0.00718</v>
       </c>
       <c r="M436" s="1" t="n">
-        <v>0.00718</v>
+        <v>0.00719</v>
       </c>
       <c r="N436" s="1" t="n">
+        <v>0.00719</v>
+      </c>
+      <c r="O436" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -20557,9 +21868,12 @@
         <v>0.002006</v>
       </c>
       <c r="M437" s="1" t="n">
+        <v>0.002005</v>
+      </c>
+      <c r="N437" s="1" t="n">
         <v>0.002012</v>
       </c>
-      <c r="N437" s="1" t="n">
+      <c r="O437" s="1" t="n">
         <v>0.001982</v>
       </c>
     </row>
@@ -20603,9 +21917,12 @@
         <v>0.3147</v>
       </c>
       <c r="M438" s="1" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="N438" s="1" t="n">
         <v>0.3147</v>
       </c>
-      <c r="N438" s="1" t="n">
+      <c r="O438" s="1" t="n">
         <v>0.3122</v>
       </c>
     </row>
@@ -20649,9 +21966,12 @@
         <v>0.04447</v>
       </c>
       <c r="M439" s="1" t="n">
-        <v>0.04448</v>
+        <v>0.04466</v>
       </c>
       <c r="N439" s="1" t="n">
+        <v>0.04466</v>
+      </c>
+      <c r="O439" s="1" t="n">
         <v>0.04426</v>
       </c>
     </row>
@@ -20695,9 +22015,12 @@
         <v>0.914</v>
       </c>
       <c r="M440" s="1" t="n">
-        <v>0.914</v>
+        <v>0.916</v>
       </c>
       <c r="N440" s="1" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="O440" s="1" t="n">
         <v>0.906</v>
       </c>
     </row>
@@ -20741,9 +22064,12 @@
         <v>1551.41</v>
       </c>
       <c r="M441" s="1" t="n">
+        <v>1550.67</v>
+      </c>
+      <c r="N441" s="1" t="n">
         <v>1552.4</v>
       </c>
-      <c r="N441" s="1" t="n">
+      <c r="O441" s="1" t="n">
         <v>1548.06</v>
       </c>
     </row>
@@ -20787,9 +22113,12 @@
         <v>0.0008050000000000001</v>
       </c>
       <c r="M442" s="1" t="n">
-        <v>0.0008061</v>
+        <v>0.0008076</v>
       </c>
       <c r="N442" s="1" t="n">
+        <v>0.0008076</v>
+      </c>
+      <c r="O442" s="1" t="n">
         <v>0.0007877</v>
       </c>
     </row>
@@ -20836,6 +22165,9 @@
         <v>0.003558</v>
       </c>
       <c r="N443" s="1" t="n">
+        <v>0.003558</v>
+      </c>
+      <c r="O443" s="1" t="n">
         <v>0.003515</v>
       </c>
     </row>
@@ -20879,9 +22211,12 @@
         <v>1.991</v>
       </c>
       <c r="M444" s="1" t="n">
+        <v>1.991</v>
+      </c>
+      <c r="N444" s="1" t="n">
         <v>1.994</v>
       </c>
-      <c r="N444" s="1" t="n">
+      <c r="O444" s="1" t="n">
         <v>1.977</v>
       </c>
     </row>
@@ -20925,9 +22260,12 @@
         <v>1.32</v>
       </c>
       <c r="M445" s="1" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="N445" s="1" t="n">
         <v>1.321</v>
       </c>
-      <c r="N445" s="1" t="n">
+      <c r="O445" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -20971,10 +22309,13 @@
         <v>0.06902</v>
       </c>
       <c r="M446" s="1" t="n">
+        <v>0.06806</v>
+      </c>
+      <c r="N446" s="1" t="n">
         <v>0.06929</v>
       </c>
-      <c r="N446" s="1" t="n">
-        <v>0.0689</v>
+      <c r="O446" s="1" t="n">
+        <v>0.06806</v>
       </c>
     </row>
     <row r="447">
@@ -21017,9 +22358,12 @@
         <v>0.02412</v>
       </c>
       <c r="M447" s="1" t="n">
+        <v>0.02398</v>
+      </c>
+      <c r="N447" s="1" t="n">
         <v>0.02412</v>
       </c>
-      <c r="N447" s="1" t="n">
+      <c r="O447" s="1" t="n">
         <v>0.02347</v>
       </c>
     </row>
@@ -21063,9 +22407,12 @@
         <v>0.01403</v>
       </c>
       <c r="M448" s="1" t="n">
+        <v>0.01408</v>
+      </c>
+      <c r="N448" s="1" t="n">
         <v>0.0141</v>
       </c>
-      <c r="N448" s="1" t="n">
+      <c r="O448" s="1" t="n">
         <v>0.01384</v>
       </c>
     </row>
@@ -21109,9 +22456,12 @@
         <v>3.737</v>
       </c>
       <c r="M449" s="1" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N449" s="1" t="n">
         <v>3.748</v>
       </c>
-      <c r="N449" s="1" t="n">
+      <c r="O449" s="1" t="n">
         <v>3.726</v>
       </c>
     </row>
@@ -21155,9 +22505,12 @@
         <v>0.0114</v>
       </c>
       <c r="M450" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="N450" s="1" t="n">
         <v>0.0115</v>
       </c>
-      <c r="N450" s="1" t="n">
+      <c r="O450" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -21201,9 +22554,12 @@
         <v>0.01041</v>
       </c>
       <c r="M451" s="1" t="n">
-        <v>0.01041</v>
+        <v>0.01042</v>
       </c>
       <c r="N451" s="1" t="n">
+        <v>0.01042</v>
+      </c>
+      <c r="O451" s="1" t="n">
         <v>0.01024</v>
       </c>
     </row>
@@ -21250,6 +22606,9 @@
         <v>0.1532</v>
       </c>
       <c r="N452" s="1" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="O452" s="1" t="n">
         <v>0.1522</v>
       </c>
     </row>
@@ -21293,9 +22652,12 @@
         <v>151.3</v>
       </c>
       <c r="M453" s="1" t="n">
+        <v>151.25</v>
+      </c>
+      <c r="N453" s="1" t="n">
         <v>151.3</v>
       </c>
-      <c r="N453" s="1" t="n">
+      <c r="O453" s="1" t="n">
         <v>150.85</v>
       </c>
     </row>
@@ -21339,9 +22701,12 @@
         <v>0.008629</v>
       </c>
       <c r="M454" s="1" t="n">
-        <v>0.008639000000000001</v>
+        <v>0.008645</v>
       </c>
       <c r="N454" s="1" t="n">
+        <v>0.008645</v>
+      </c>
+      <c r="O454" s="1" t="n">
         <v>0.008593999999999999</v>
       </c>
     </row>
@@ -21385,9 +22750,12 @@
         <v>0.0526</v>
       </c>
       <c r="M455" s="1" t="n">
+        <v>0.05259</v>
+      </c>
+      <c r="N455" s="1" t="n">
         <v>0.0526</v>
       </c>
-      <c r="N455" s="1" t="n">
+      <c r="O455" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -21431,9 +22799,12 @@
         <v>0.3095</v>
       </c>
       <c r="M456" s="1" t="n">
-        <v>0.3095</v>
+        <v>0.30984</v>
       </c>
       <c r="N456" s="1" t="n">
+        <v>0.30984</v>
+      </c>
+      <c r="O456" s="1" t="n">
         <v>0.30269</v>
       </c>
     </row>
@@ -21480,6 +22851,9 @@
         <v>0.00552</v>
       </c>
       <c r="N457" s="1" t="n">
+        <v>0.00552</v>
+      </c>
+      <c r="O457" s="1" t="n">
         <v>0.00544</v>
       </c>
     </row>
@@ -21523,9 +22897,12 @@
         <v>0.1005</v>
       </c>
       <c r="M458" s="1" t="n">
+        <v>0.1007</v>
+      </c>
+      <c r="N458" s="1" t="n">
         <v>0.1008</v>
       </c>
-      <c r="N458" s="1" t="n">
+      <c r="O458" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -21569,9 +22946,12 @@
         <v>0.001846</v>
       </c>
       <c r="M459" s="1" t="n">
-        <v>0.001846</v>
+        <v>0.00185</v>
       </c>
       <c r="N459" s="1" t="n">
+        <v>0.00185</v>
+      </c>
+      <c r="O459" s="1" t="n">
         <v>0.001825</v>
       </c>
     </row>
@@ -21615,9 +22995,12 @@
         <v>0.01845</v>
       </c>
       <c r="M460" s="1" t="n">
+        <v>0.01847</v>
+      </c>
+      <c r="N460" s="1" t="n">
         <v>0.01848</v>
       </c>
-      <c r="N460" s="1" t="n">
+      <c r="O460" s="1" t="n">
         <v>0.01822</v>
       </c>
     </row>
@@ -21661,9 +23044,12 @@
         <v>0.0004882</v>
       </c>
       <c r="M461" s="1" t="n">
+        <v>0.0004857</v>
+      </c>
+      <c r="N461" s="1" t="n">
         <v>0.0004888</v>
       </c>
-      <c r="N461" s="1" t="n">
+      <c r="O461" s="1" t="n">
         <v>0.0004842</v>
       </c>
     </row>
@@ -21707,9 +23093,12 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="M462" s="1" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="N462" s="1" t="n">
         <v>0.0968</v>
       </c>
-      <c r="N462" s="1" t="n">
+      <c r="O462" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -21753,9 +23142,12 @@
         <v>0.07933999999999999</v>
       </c>
       <c r="M463" s="1" t="n">
+        <v>0.07946</v>
+      </c>
+      <c r="N463" s="1" t="n">
         <v>0.07954</v>
       </c>
-      <c r="N463" s="1" t="n">
+      <c r="O463" s="1" t="n">
         <v>0.07888000000000001</v>
       </c>
     </row>
@@ -21799,9 +23191,12 @@
         <v>0.03212</v>
       </c>
       <c r="M464" s="1" t="n">
+        <v>0.03179</v>
+      </c>
+      <c r="N464" s="1" t="n">
         <v>0.03235</v>
       </c>
-      <c r="N464" s="1" t="n">
+      <c r="O464" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -21845,9 +23240,12 @@
         <v>0.01622</v>
       </c>
       <c r="M465" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="N465" s="1" t="n">
         <v>0.01623</v>
       </c>
-      <c r="N465" s="1" t="n">
+      <c r="O465" s="1" t="n">
         <v>0.01613</v>
       </c>
     </row>
@@ -21891,9 +23289,12 @@
         <v>0.06788</v>
       </c>
       <c r="M466" s="1" t="n">
+        <v>0.06787</v>
+      </c>
+      <c r="N466" s="1" t="n">
         <v>0.06794</v>
       </c>
-      <c r="N466" s="1" t="n">
+      <c r="O466" s="1" t="n">
         <v>0.06763</v>
       </c>
     </row>
@@ -21937,9 +23338,12 @@
         <v>0.04338</v>
       </c>
       <c r="M467" s="1" t="n">
+        <v>0.0434</v>
+      </c>
+      <c r="N467" s="1" t="n">
         <v>0.04344</v>
       </c>
-      <c r="N467" s="1" t="n">
+      <c r="O467" s="1" t="n">
         <v>0.04322</v>
       </c>
     </row>
@@ -21983,9 +23387,12 @@
         <v>0.05693</v>
       </c>
       <c r="M468" s="1" t="n">
+        <v>0.05671</v>
+      </c>
+      <c r="N468" s="1" t="n">
         <v>0.05795</v>
       </c>
-      <c r="N468" s="1" t="n">
+      <c r="O468" s="1" t="n">
         <v>0.05587</v>
       </c>
     </row>
@@ -22029,9 +23436,12 @@
         <v>0.2317</v>
       </c>
       <c r="M469" s="1" t="n">
-        <v>0.232</v>
+        <v>0.2322</v>
       </c>
       <c r="N469" s="1" t="n">
+        <v>0.2322</v>
+      </c>
+      <c r="O469" s="1" t="n">
         <v>0.2294</v>
       </c>
     </row>
@@ -22075,9 +23485,12 @@
         <v>0.0905</v>
       </c>
       <c r="M470" s="1" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="N470" s="1" t="n">
         <v>0.0906</v>
       </c>
-      <c r="N470" s="1" t="n">
+      <c r="O470" s="1" t="n">
         <v>0.0902</v>
       </c>
     </row>
@@ -22121,9 +23534,12 @@
         <v>0.06682</v>
       </c>
       <c r="M471" s="1" t="n">
-        <v>0.06693</v>
+        <v>0.06694</v>
       </c>
       <c r="N471" s="1" t="n">
+        <v>0.06694</v>
+      </c>
+      <c r="O471" s="1" t="n">
         <v>0.06660000000000001</v>
       </c>
     </row>
@@ -22167,9 +23583,12 @@
         <v>6.57</v>
       </c>
       <c r="M472" s="1" t="n">
+        <v>6.579</v>
+      </c>
+      <c r="N472" s="1" t="n">
         <v>6.595</v>
       </c>
-      <c r="N472" s="1" t="n">
+      <c r="O472" s="1" t="n">
         <v>6.486</v>
       </c>
     </row>
@@ -22213,9 +23632,12 @@
         <v>0.01948</v>
       </c>
       <c r="M473" s="1" t="n">
-        <v>0.01949</v>
+        <v>0.0195</v>
       </c>
       <c r="N473" s="1" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="O473" s="1" t="n">
         <v>0.01937</v>
       </c>
     </row>
@@ -22259,9 +23681,12 @@
         <v>1.43</v>
       </c>
       <c r="M474" s="1" t="n">
-        <v>1.431</v>
+        <v>1.432</v>
       </c>
       <c r="N474" s="1" t="n">
+        <v>1.432</v>
+      </c>
+      <c r="O474" s="1" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -22305,9 +23730,12 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="M475" s="1" t="n">
+        <v>0.08978</v>
+      </c>
+      <c r="N475" s="1" t="n">
         <v>0.09001000000000001</v>
       </c>
-      <c r="N475" s="1" t="n">
+      <c r="O475" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -22351,9 +23779,12 @@
         <v>0.1067</v>
       </c>
       <c r="M476" s="1" t="n">
-        <v>0.1067</v>
+        <v>0.107</v>
       </c>
       <c r="N476" s="1" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="O476" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -22397,10 +23828,13 @@
         <v>0.09407</v>
       </c>
       <c r="M477" s="1" t="n">
+        <v>0.09390999999999999</v>
+      </c>
+      <c r="N477" s="1" t="n">
         <v>0.09451</v>
       </c>
-      <c r="N477" s="1" t="n">
-        <v>0.094</v>
+      <c r="O477" s="1" t="n">
+        <v>0.09390999999999999</v>
       </c>
     </row>
     <row r="478">
@@ -22443,9 +23877,12 @@
         <v>0.0001641</v>
       </c>
       <c r="M478" s="1" t="n">
-        <v>0.0001641</v>
+        <v>0.0001643</v>
       </c>
       <c r="N478" s="1" t="n">
+        <v>0.0001643</v>
+      </c>
+      <c r="O478" s="1" t="n">
         <v>0.0001624</v>
       </c>
     </row>
@@ -22489,9 +23926,12 @@
         <v>0.04032</v>
       </c>
       <c r="M479" s="1" t="n">
+        <v>0.04032</v>
+      </c>
+      <c r="N479" s="1" t="n">
         <v>0.04034</v>
       </c>
-      <c r="N479" s="1" t="n">
+      <c r="O479" s="1" t="n">
         <v>0.04007</v>
       </c>
     </row>
@@ -22535,9 +23975,12 @@
         <v>0.007422</v>
       </c>
       <c r="M480" s="1" t="n">
+        <v>0.007431</v>
+      </c>
+      <c r="N480" s="1" t="n">
         <v>0.007442</v>
       </c>
-      <c r="N480" s="1" t="n">
+      <c r="O480" s="1" t="n">
         <v>0.007389</v>
       </c>
     </row>
@@ -22584,6 +24027,9 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="N481" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="O481" s="1" t="n">
         <v>0.0953</v>
       </c>
     </row>
@@ -22627,9 +24073,12 @@
         <v>0.0562</v>
       </c>
       <c r="M482" s="1" t="n">
-        <v>0.05621</v>
+        <v>0.05625</v>
       </c>
       <c r="N482" s="1" t="n">
+        <v>0.05625</v>
+      </c>
+      <c r="O482" s="1" t="n">
         <v>0.05569</v>
       </c>
     </row>
@@ -22673,10 +24122,13 @@
         <v>0.006194</v>
       </c>
       <c r="M483" s="1" t="n">
+        <v>0.00616</v>
+      </c>
+      <c r="N483" s="1" t="n">
         <v>0.006209</v>
       </c>
-      <c r="N483" s="1" t="n">
-        <v>0.006161</v>
+      <c r="O483" s="1" t="n">
+        <v>0.00616</v>
       </c>
     </row>
     <row r="484">
@@ -22719,9 +24171,12 @@
         <v>0.01495</v>
       </c>
       <c r="M484" s="1" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="N484" s="1" t="n">
         <v>0.01497</v>
       </c>
-      <c r="N484" s="1" t="n">
+      <c r="O484" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -22765,9 +24220,12 @@
         <v>0.02406</v>
       </c>
       <c r="M485" s="1" t="n">
+        <v>0.02417</v>
+      </c>
+      <c r="N485" s="1" t="n">
         <v>0.02427</v>
       </c>
-      <c r="N485" s="1" t="n">
+      <c r="O485" s="1" t="n">
         <v>0.02403</v>
       </c>
     </row>
@@ -22811,9 +24269,12 @@
         <v>0.06713</v>
       </c>
       <c r="M486" s="1" t="n">
+        <v>0.06712</v>
+      </c>
+      <c r="N486" s="1" t="n">
         <v>0.06713</v>
       </c>
-      <c r="N486" s="1" t="n">
+      <c r="O486" s="1" t="n">
         <v>0.0667</v>
       </c>
     </row>
@@ -22857,9 +24318,12 @@
         <v>0.03693</v>
       </c>
       <c r="M487" s="1" t="n">
+        <v>0.03699</v>
+      </c>
+      <c r="N487" s="1" t="n">
         <v>0.03709</v>
       </c>
-      <c r="N487" s="1" t="n">
+      <c r="O487" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -22903,9 +24367,12 @@
         <v>0.01823</v>
       </c>
       <c r="M488" s="1" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="N488" s="1" t="n">
         <v>0.01826</v>
       </c>
-      <c r="N488" s="1" t="n">
+      <c r="O488" s="1" t="n">
         <v>0.01814</v>
       </c>
     </row>
@@ -22949,9 +24416,12 @@
         <v>0.03292</v>
       </c>
       <c r="M489" s="1" t="n">
-        <v>0.03299</v>
+        <v>0.03303</v>
       </c>
       <c r="N489" s="1" t="n">
+        <v>0.03303</v>
+      </c>
+      <c r="O489" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -22995,9 +24465,12 @@
         <v>0.01517</v>
       </c>
       <c r="M490" s="1" t="n">
-        <v>0.01517</v>
+        <v>0.01549</v>
       </c>
       <c r="N490" s="1" t="n">
+        <v>0.01549</v>
+      </c>
+      <c r="O490" s="1" t="n">
         <v>0.01458</v>
       </c>
     </row>
@@ -23041,9 +24514,12 @@
         <v>0.01885</v>
       </c>
       <c r="M491" s="1" t="n">
+        <v>0.01884</v>
+      </c>
+      <c r="N491" s="1" t="n">
         <v>0.019</v>
       </c>
-      <c r="N491" s="1" t="n">
+      <c r="O491" s="1" t="n">
         <v>0.01851</v>
       </c>
     </row>
@@ -23087,9 +24563,12 @@
         <v>0.08817</v>
       </c>
       <c r="M492" s="1" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="N492" s="1" t="n">
         <v>0.08935</v>
       </c>
-      <c r="N492" s="1" t="n">
+      <c r="O492" s="1" t="n">
         <v>0.08784</v>
       </c>
     </row>
@@ -23133,9 +24612,12 @@
         <v>0.006502</v>
       </c>
       <c r="M493" s="1" t="n">
+        <v>0.006514</v>
+      </c>
+      <c r="N493" s="1" t="n">
         <v>0.006521</v>
       </c>
-      <c r="N493" s="1" t="n">
+      <c r="O493" s="1" t="n">
         <v>0.006497</v>
       </c>
     </row>
@@ -23179,9 +24661,12 @@
         <v>0.1331</v>
       </c>
       <c r="M494" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="N494" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="N494" s="1" t="n">
+      <c r="O494" s="1" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -23225,9 +24710,12 @@
         <v>0.2856</v>
       </c>
       <c r="M495" s="1" t="n">
-        <v>0.2859</v>
+        <v>0.286</v>
       </c>
       <c r="N495" s="1" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="O495" s="1" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -23271,9 +24759,12 @@
         <v>0.004547</v>
       </c>
       <c r="M496" s="1" t="n">
+        <v>0.004557</v>
+      </c>
+      <c r="N496" s="1" t="n">
         <v>0.004562</v>
       </c>
-      <c r="N496" s="1" t="n">
+      <c r="O496" s="1" t="n">
         <v>0.004516</v>
       </c>
     </row>
@@ -23317,9 +24808,12 @@
         <v>0.1268</v>
       </c>
       <c r="M497" s="1" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="N497" s="1" t="n">
         <v>0.1283</v>
       </c>
-      <c r="N497" s="1" t="n">
+      <c r="O497" s="1" t="n">
         <v>0.1264</v>
       </c>
     </row>
@@ -23363,9 +24857,12 @@
         <v>0.03464</v>
       </c>
       <c r="M498" s="1" t="n">
-        <v>0.03464</v>
+        <v>0.03466</v>
       </c>
       <c r="N498" s="1" t="n">
+        <v>0.03466</v>
+      </c>
+      <c r="O498" s="1" t="n">
         <v>0.03423</v>
       </c>
     </row>
@@ -23409,9 +24906,12 @@
         <v>0.03551</v>
       </c>
       <c r="M499" s="1" t="n">
+        <v>0.03556</v>
+      </c>
+      <c r="N499" s="1" t="n">
         <v>0.03576</v>
       </c>
-      <c r="N499" s="1" t="n">
+      <c r="O499" s="1" t="n">
         <v>0.03551</v>
       </c>
     </row>
@@ -23455,9 +24955,12 @@
         <v>0.003422</v>
       </c>
       <c r="M500" s="1" t="n">
-        <v>0.003422</v>
+        <v>0.003424</v>
       </c>
       <c r="N500" s="1" t="n">
+        <v>0.003424</v>
+      </c>
+      <c r="O500" s="1" t="n">
         <v>0.003413</v>
       </c>
     </row>
@@ -23501,9 +25004,12 @@
         <v>0.0003867</v>
       </c>
       <c r="M501" s="1" t="n">
-        <v>0.0003867</v>
+        <v>0.0003883</v>
       </c>
       <c r="N501" s="1" t="n">
+        <v>0.0003883</v>
+      </c>
+      <c r="O501" s="1" t="n">
         <v>0.0003786</v>
       </c>
     </row>
@@ -23547,9 +25053,12 @@
         <v>0.3001</v>
       </c>
       <c r="M502" s="1" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="N502" s="1" t="n">
         <v>0.3011</v>
       </c>
-      <c r="N502" s="1" t="n">
+      <c r="O502" s="1" t="n">
         <v>0.2986</v>
       </c>
     </row>
@@ -23593,9 +25102,12 @@
         <v>0.06494</v>
       </c>
       <c r="M503" s="1" t="n">
+        <v>0.06493</v>
+      </c>
+      <c r="N503" s="1" t="n">
         <v>0.06507</v>
       </c>
-      <c r="N503" s="1" t="n">
+      <c r="O503" s="1" t="n">
         <v>0.06485</v>
       </c>
     </row>
@@ -23639,9 +25151,12 @@
         <v>0.1787</v>
       </c>
       <c r="M504" s="1" t="n">
-        <v>0.1787</v>
+        <v>0.1789</v>
       </c>
       <c r="N504" s="1" t="n">
+        <v>0.1789</v>
+      </c>
+      <c r="O504" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -23685,9 +25200,12 @@
         <v>0.1517</v>
       </c>
       <c r="M505" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="N505" s="1" t="n">
         <v>0.1519</v>
       </c>
-      <c r="N505" s="1" t="n">
+      <c r="O505" s="1" t="n">
         <v>0.1511</v>
       </c>
     </row>
@@ -23734,6 +25252,9 @@
         <v>0.01205</v>
       </c>
       <c r="N506" s="1" t="n">
+        <v>0.01205</v>
+      </c>
+      <c r="O506" s="1" t="n">
         <v>0.01193</v>
       </c>
     </row>
@@ -23777,9 +25298,12 @@
         <v>0.2897</v>
       </c>
       <c r="M507" s="1" t="n">
-        <v>0.2899</v>
+        <v>0.2902</v>
       </c>
       <c r="N507" s="1" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="O507" s="1" t="n">
         <v>0.2871</v>
       </c>
     </row>
@@ -23823,9 +25347,12 @@
         <v>0.009379999999999999</v>
       </c>
       <c r="M508" s="1" t="n">
-        <v>0.00942</v>
+        <v>0.00944</v>
       </c>
       <c r="N508" s="1" t="n">
+        <v>0.00944</v>
+      </c>
+      <c r="O508" s="1" t="n">
         <v>0.009310000000000001</v>
       </c>
     </row>
@@ -23869,9 +25396,12 @@
         <v>0.006838</v>
       </c>
       <c r="M509" s="1" t="n">
+        <v>0.006842</v>
+      </c>
+      <c r="N509" s="1" t="n">
         <v>0.006851</v>
       </c>
-      <c r="N509" s="1" t="n">
+      <c r="O509" s="1" t="n">
         <v>0.006783</v>
       </c>
     </row>
@@ -23915,9 +25445,12 @@
         <v>0.3019</v>
       </c>
       <c r="M510" s="1" t="n">
-        <v>0.3019</v>
+        <v>0.3034</v>
       </c>
       <c r="N510" s="1" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="O510" s="1" t="n">
         <v>0.2934</v>
       </c>
     </row>
@@ -23964,6 +25497,9 @@
         <v>0.01471</v>
       </c>
       <c r="N511" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="O511" s="1" t="n">
         <v>0.01465</v>
       </c>
     </row>
@@ -24007,9 +25543,12 @@
         <v>0.1403</v>
       </c>
       <c r="M512" s="1" t="n">
-        <v>0.1403</v>
+        <v>0.1404</v>
       </c>
       <c r="N512" s="1" t="n">
+        <v>0.1404</v>
+      </c>
+      <c r="O512" s="1" t="n">
         <v>0.1394</v>
       </c>
     </row>
@@ -24053,9 +25592,12 @@
         <v>0.081</v>
       </c>
       <c r="M513" s="1" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="N513" s="1" t="n">
         <v>0.08144999999999999</v>
       </c>
-      <c r="N513" s="1" t="n">
+      <c r="O513" s="1" t="n">
         <v>0.08069</v>
       </c>
     </row>
@@ -24102,6 +25644,9 @@
         <v>0.0251</v>
       </c>
       <c r="N514" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="O514" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -24145,9 +25690,12 @@
         <v>0.06314</v>
       </c>
       <c r="M515" s="1" t="n">
+        <v>0.06318</v>
+      </c>
+      <c r="N515" s="1" t="n">
         <v>0.06329</v>
       </c>
-      <c r="N515" s="1" t="n">
+      <c r="O515" s="1" t="n">
         <v>0.06301</v>
       </c>
     </row>
@@ -24191,9 +25739,12 @@
         <v>0.04728</v>
       </c>
       <c r="M516" s="1" t="n">
+        <v>0.04729</v>
+      </c>
+      <c r="N516" s="1" t="n">
         <v>0.04752</v>
       </c>
-      <c r="N516" s="1" t="n">
+      <c r="O516" s="1" t="n">
         <v>0.04707</v>
       </c>
     </row>
@@ -24237,9 +25788,12 @@
         <v>0.004942</v>
       </c>
       <c r="M517" s="1" t="n">
-        <v>0.004942</v>
+        <v>0.004944</v>
       </c>
       <c r="N517" s="1" t="n">
+        <v>0.004944</v>
+      </c>
+      <c r="O517" s="1" t="n">
         <v>0.004902</v>
       </c>
     </row>
@@ -24283,9 +25837,12 @@
         <v>0.00945</v>
       </c>
       <c r="M518" s="1" t="n">
+        <v>0.009434</v>
+      </c>
+      <c r="N518" s="1" t="n">
         <v>0.009504</v>
       </c>
-      <c r="N518" s="1" t="n">
+      <c r="O518" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -24329,9 +25886,12 @@
         <v>0.01811</v>
       </c>
       <c r="M519" s="1" t="n">
-        <v>0.01811</v>
+        <v>0.01813</v>
       </c>
       <c r="N519" s="1" t="n">
+        <v>0.01813</v>
+      </c>
+      <c r="O519" s="1" t="n">
         <v>0.01798</v>
       </c>
     </row>
@@ -24375,9 +25935,12 @@
         <v>0.06723</v>
       </c>
       <c r="M520" s="1" t="n">
-        <v>0.06723</v>
+        <v>0.06726</v>
       </c>
       <c r="N520" s="1" t="n">
+        <v>0.06726</v>
+      </c>
+      <c r="O520" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -24421,9 +25984,12 @@
         <v>0.1374</v>
       </c>
       <c r="M521" s="1" t="n">
-        <v>0.1374</v>
+        <v>0.1376</v>
       </c>
       <c r="N521" s="1" t="n">
+        <v>0.1376</v>
+      </c>
+      <c r="O521" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -24467,9 +26033,12 @@
         <v>0.04772</v>
       </c>
       <c r="M522" s="1" t="n">
-        <v>0.04772</v>
+        <v>0.04799</v>
       </c>
       <c r="N522" s="1" t="n">
+        <v>0.04799</v>
+      </c>
+      <c r="O522" s="1" t="n">
         <v>0.04718</v>
       </c>
     </row>
@@ -24513,9 +26082,12 @@
         <v>0.06819</v>
       </c>
       <c r="M523" s="1" t="n">
+        <v>0.06809</v>
+      </c>
+      <c r="N523" s="1" t="n">
         <v>0.06827</v>
       </c>
-      <c r="N523" s="1" t="n">
+      <c r="O523" s="1" t="n">
         <v>0.06784999999999999</v>
       </c>
     </row>
@@ -24559,9 +26131,12 @@
         <v>0.7055</v>
       </c>
       <c r="M524" s="1" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="N524" s="1" t="n">
         <v>0.7055</v>
       </c>
-      <c r="N524" s="1" t="n">
+      <c r="O524" s="1" t="n">
         <v>0.6966</v>
       </c>
     </row>
@@ -24605,9 +26180,12 @@
         <v>0.00269</v>
       </c>
       <c r="M525" s="1" t="n">
-        <v>0.00269</v>
+        <v>0.0027</v>
       </c>
       <c r="N525" s="1" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="O525" s="1" t="n">
         <v>0.00267</v>
       </c>
     </row>
@@ -24651,9 +26229,12 @@
         <v>0.4877</v>
       </c>
       <c r="M526" s="1" t="n">
+        <v>0.4878</v>
+      </c>
+      <c r="N526" s="1" t="n">
         <v>0.488</v>
       </c>
-      <c r="N526" s="1" t="n">
+      <c r="O526" s="1" t="n">
         <v>0.4856</v>
       </c>
     </row>
@@ -24697,9 +26278,12 @@
         <v>45.83</v>
       </c>
       <c r="M527" s="1" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="N527" s="1" t="n">
         <v>45.85</v>
       </c>
-      <c r="N527" s="1" t="n">
+      <c r="O527" s="1" t="n">
         <v>45.76</v>
       </c>
     </row>
@@ -24743,9 +26327,12 @@
         <v>0.02439</v>
       </c>
       <c r="M528" s="1" t="n">
+        <v>0.02438</v>
+      </c>
+      <c r="N528" s="1" t="n">
         <v>0.02447</v>
       </c>
-      <c r="N528" s="1" t="n">
+      <c r="O528" s="1" t="n">
         <v>0.02429</v>
       </c>
     </row>
@@ -24789,9 +26376,12 @@
         <v>0.006427</v>
       </c>
       <c r="M529" s="1" t="n">
-        <v>0.006427</v>
+        <v>0.006431</v>
       </c>
       <c r="N529" s="1" t="n">
+        <v>0.006431</v>
+      </c>
+      <c r="O529" s="1" t="n">
         <v>0.00638</v>
       </c>
     </row>
@@ -24835,9 +26425,12 @@
         <v>0.2011</v>
       </c>
       <c r="M530" s="1" t="n">
-        <v>0.2011</v>
+        <v>0.2013</v>
       </c>
       <c r="N530" s="1" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="O530" s="1" t="n">
         <v>0.1993</v>
       </c>
     </row>
@@ -24881,9 +26474,12 @@
         <v>0.007676</v>
       </c>
       <c r="M531" s="1" t="n">
+        <v>0.007673</v>
+      </c>
+      <c r="N531" s="1" t="n">
         <v>0.007727</v>
       </c>
-      <c r="N531" s="1" t="n">
+      <c r="O531" s="1" t="n">
         <v>0.007657</v>
       </c>
     </row>
@@ -24927,9 +26523,12 @@
         <v>2.291</v>
       </c>
       <c r="M532" s="1" t="n">
+        <v>2.292</v>
+      </c>
+      <c r="N532" s="1" t="n">
         <v>2.302</v>
       </c>
-      <c r="N532" s="1" t="n">
+      <c r="O532" s="1" t="n">
         <v>2.275</v>
       </c>
     </row>
@@ -24973,9 +26572,12 @@
         <v>0.04177</v>
       </c>
       <c r="M533" s="1" t="n">
+        <v>0.04182</v>
+      </c>
+      <c r="N533" s="1" t="n">
         <v>0.04186</v>
       </c>
-      <c r="N533" s="1" t="n">
+      <c r="O533" s="1" t="n">
         <v>0.04138</v>
       </c>
     </row>
@@ -25019,9 +26621,12 @@
         <v>0.1828</v>
       </c>
       <c r="M534" s="1" t="n">
-        <v>0.1833</v>
+        <v>0.1834</v>
       </c>
       <c r="N534" s="1" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="O534" s="1" t="n">
         <v>0.1811</v>
       </c>
     </row>
@@ -25065,9 +26670,12 @@
         <v>0.04373</v>
       </c>
       <c r="M535" s="1" t="n">
-        <v>0.04373</v>
+        <v>0.0445</v>
       </c>
       <c r="N535" s="1" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="O535" s="1" t="n">
         <v>0.04287</v>
       </c>
     </row>
@@ -25111,9 +26719,12 @@
         <v>0.05421</v>
       </c>
       <c r="M536" s="1" t="n">
+        <v>0.05418</v>
+      </c>
+      <c r="N536" s="1" t="n">
         <v>0.05438</v>
       </c>
-      <c r="N536" s="1" t="n">
+      <c r="O536" s="1" t="n">
         <v>0.05409</v>
       </c>
     </row>
@@ -25157,9 +26768,12 @@
         <v>0.1607</v>
       </c>
       <c r="M537" s="1" t="n">
+        <v>0.1609</v>
+      </c>
+      <c r="N537" s="1" t="n">
         <v>0.1611</v>
       </c>
-      <c r="N537" s="1" t="n">
+      <c r="O537" s="1" t="n">
         <v>0.1602</v>
       </c>
     </row>
@@ -25203,9 +26817,12 @@
         <v>0.03673</v>
       </c>
       <c r="M538" s="1" t="n">
+        <v>0.03674</v>
+      </c>
+      <c r="N538" s="1" t="n">
         <v>0.03687</v>
       </c>
-      <c r="N538" s="1" t="n">
+      <c r="O538" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -25249,9 +26866,12 @@
         <v>0.05839</v>
       </c>
       <c r="M539" s="1" t="n">
+        <v>0.05829</v>
+      </c>
+      <c r="N539" s="1" t="n">
         <v>0.0587</v>
       </c>
-      <c r="N539" s="1" t="n">
+      <c r="O539" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -25295,9 +26915,12 @@
         <v>0.04281</v>
       </c>
       <c r="M540" s="1" t="n">
-        <v>0.04286</v>
+        <v>0.04289</v>
       </c>
       <c r="N540" s="1" t="n">
+        <v>0.04289</v>
+      </c>
+      <c r="O540" s="1" t="n">
         <v>0.04256</v>
       </c>
     </row>
@@ -25341,9 +26964,12 @@
         <v>0.01728</v>
       </c>
       <c r="M541" s="1" t="n">
+        <v>0.01727</v>
+      </c>
+      <c r="N541" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="N541" s="1" t="n">
+      <c r="O541" s="1" t="n">
         <v>0.0172</v>
       </c>
     </row>
@@ -25387,9 +27013,12 @@
         <v>0.003968</v>
       </c>
       <c r="M542" s="1" t="n">
+        <v>0.00397</v>
+      </c>
+      <c r="N542" s="1" t="n">
         <v>0.003975</v>
       </c>
-      <c r="N542" s="1" t="n">
+      <c r="O542" s="1" t="n">
         <v>0.003963</v>
       </c>
     </row>
@@ -25433,9 +27062,12 @@
         <v>0.05773</v>
       </c>
       <c r="M543" s="1" t="n">
+        <v>0.05776</v>
+      </c>
+      <c r="N543" s="1" t="n">
         <v>0.05835</v>
       </c>
-      <c r="N543" s="1" t="n">
+      <c r="O543" s="1" t="n">
         <v>0.05735</v>
       </c>
     </row>
@@ -25479,9 +27111,12 @@
         <v>0.05024</v>
       </c>
       <c r="M544" s="1" t="n">
+        <v>0.05026</v>
+      </c>
+      <c r="N544" s="1" t="n">
         <v>0.05042</v>
       </c>
-      <c r="N544" s="1" t="n">
+      <c r="O544" s="1" t="n">
         <v>0.05016</v>
       </c>
     </row>
@@ -25525,9 +27160,12 @@
         <v>0.04079</v>
       </c>
       <c r="M545" s="1" t="n">
+        <v>0.04078</v>
+      </c>
+      <c r="N545" s="1" t="n">
         <v>0.04089</v>
       </c>
-      <c r="N545" s="1" t="n">
+      <c r="O545" s="1" t="n">
         <v>0.04038</v>
       </c>
     </row>
@@ -25571,9 +27209,12 @@
         <v>0.007426</v>
       </c>
       <c r="M546" s="1" t="n">
-        <v>0.007436</v>
+        <v>0.007456</v>
       </c>
       <c r="N546" s="1" t="n">
+        <v>0.007456</v>
+      </c>
+      <c r="O546" s="1" t="n">
         <v>0.007402</v>
       </c>
     </row>
@@ -25617,9 +27258,12 @@
         <v>0.01484</v>
       </c>
       <c r="M547" s="1" t="n">
-        <v>0.01486</v>
+        <v>0.01493</v>
       </c>
       <c r="N547" s="1" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="O547" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -25663,9 +27307,12 @@
         <v>0.0157</v>
       </c>
       <c r="M548" s="1" t="n">
+        <v>0.01571</v>
+      </c>
+      <c r="N548" s="1" t="n">
         <v>0.01576</v>
       </c>
-      <c r="N548" s="1" t="n">
+      <c r="O548" s="1" t="n">
         <v>0.0157</v>
       </c>
     </row>
@@ -25709,9 +27356,12 @@
         <v>0.13569</v>
       </c>
       <c r="M549" s="1" t="n">
+        <v>0.13555</v>
+      </c>
+      <c r="N549" s="1" t="n">
         <v>0.13569</v>
       </c>
-      <c r="N549" s="1" t="n">
+      <c r="O549" s="1" t="n">
         <v>0.13271</v>
       </c>
     </row>
@@ -25755,9 +27405,12 @@
         <v>0.1703</v>
       </c>
       <c r="M550" s="1" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="N550" s="1" t="n">
         <v>0.1706</v>
       </c>
-      <c r="N550" s="1" t="n">
+      <c r="O550" s="1" t="n">
         <v>0.1693</v>
       </c>
     </row>
@@ -25801,9 +27454,12 @@
         <v>0.003581</v>
       </c>
       <c r="M551" s="1" t="n">
+        <v>0.003586</v>
+      </c>
+      <c r="N551" s="1" t="n">
         <v>0.003593</v>
       </c>
-      <c r="N551" s="1" t="n">
+      <c r="O551" s="1" t="n">
         <v>0.003576</v>
       </c>
     </row>
@@ -25847,9 +27503,12 @@
         <v>0.03053</v>
       </c>
       <c r="M552" s="1" t="n">
+        <v>0.03052</v>
+      </c>
+      <c r="N552" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="N552" s="1" t="n">
+      <c r="O552" s="1" t="n">
         <v>0.0303</v>
       </c>
     </row>
@@ -25893,9 +27552,12 @@
         <v>0.01316</v>
       </c>
       <c r="M553" s="1" t="n">
+        <v>0.01317</v>
+      </c>
+      <c r="N553" s="1" t="n">
         <v>0.01325</v>
       </c>
-      <c r="N553" s="1" t="n">
+      <c r="O553" s="1" t="n">
         <v>0.01316</v>
       </c>
     </row>
@@ -25939,9 +27601,12 @@
         <v>0.1044</v>
       </c>
       <c r="M554" s="1" t="n">
+        <v>0.1045</v>
+      </c>
+      <c r="N554" s="1" t="n">
         <v>0.1046</v>
       </c>
-      <c r="N554" s="1" t="n">
+      <c r="O554" s="1" t="n">
         <v>0.1039</v>
       </c>
     </row>
@@ -25985,9 +27650,12 @@
         <v>0.0531</v>
       </c>
       <c r="M555" s="1" t="n">
+        <v>0.05307</v>
+      </c>
+      <c r="N555" s="1" t="n">
         <v>0.05319</v>
       </c>
-      <c r="N555" s="1" t="n">
+      <c r="O555" s="1" t="n">
         <v>0.05291</v>
       </c>
     </row>
@@ -26031,9 +27699,12 @@
         <v>0.01222</v>
       </c>
       <c r="M556" s="1" t="n">
+        <v>0.01226</v>
+      </c>
+      <c r="N556" s="1" t="n">
         <v>0.01234</v>
       </c>
-      <c r="N556" s="1" t="n">
+      <c r="O556" s="1" t="n">
         <v>0.01218</v>
       </c>
     </row>

--- a/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
+++ b/records/weeks/2026-03-16_2026-03-22/2026-03-16.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O556"/>
+  <dimension ref="A1:P556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -432,8 +432,9 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,10 +505,15 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>price_03:00</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -556,10 +562,13 @@
         <v>71655.39999999999</v>
       </c>
       <c r="N2" s="1" t="n">
+        <v>71346.7</v>
+      </c>
+      <c r="O2" s="1" t="n">
         <v>71788</v>
       </c>
-      <c r="O2" s="1" t="n">
-        <v>71364.39999999999</v>
+      <c r="P2" s="1" t="n">
+        <v>71346.7</v>
       </c>
     </row>
     <row r="3">
@@ -605,9 +614,12 @@
         <v>2108.53</v>
       </c>
       <c r="N3" s="1" t="n">
+        <v>2098.14</v>
+      </c>
+      <c r="O3" s="1" t="n">
         <v>2109.75</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="P3" s="1" t="n">
         <v>2090.41</v>
       </c>
     </row>
@@ -654,9 +666,12 @@
         <v>88.51000000000001</v>
       </c>
       <c r="N4" s="1" t="n">
+        <v>87.86</v>
+      </c>
+      <c r="O4" s="1" t="n">
         <v>88.51000000000001</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="P4" s="1" t="n">
         <v>87.47</v>
       </c>
     </row>
@@ -703,9 +718,12 @@
         <v>23.052</v>
       </c>
       <c r="N5" s="1" t="n">
+        <v>23.114</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>23.579</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="P5" s="1" t="n">
         <v>23.043</v>
       </c>
     </row>
@@ -752,10 +770,13 @@
         <v>0.001817</v>
       </c>
       <c r="N6" s="1" t="n">
+        <v>0.00181</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>0.001892</v>
       </c>
-      <c r="O6" s="1" t="n">
-        <v>0.001811</v>
+      <c r="P6" s="1" t="n">
+        <v>0.00181</v>
       </c>
     </row>
     <row r="7">
@@ -801,10 +822,13 @@
         <v>1.4175</v>
       </c>
       <c r="N7" s="1" t="n">
+        <v>1.4099</v>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>1.4184</v>
       </c>
-      <c r="O7" s="1" t="n">
-        <v>1.4117</v>
+      <c r="P7" s="1" t="n">
+        <v>1.4099</v>
       </c>
     </row>
     <row r="8">
@@ -850,9 +874,12 @@
         <v>0.010498</v>
       </c>
       <c r="N8" s="1" t="n">
+        <v>0.01044</v>
+      </c>
+      <c r="O8" s="1" t="n">
         <v>0.011244</v>
       </c>
-      <c r="O8" s="1" t="n">
+      <c r="P8" s="1" t="n">
         <v>0.010407</v>
       </c>
     </row>
@@ -899,9 +926,12 @@
         <v>4.017</v>
       </c>
       <c r="N9" s="1" t="n">
+        <v>3.991</v>
+      </c>
+      <c r="O9" s="1" t="n">
         <v>4.062</v>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="P9" s="1" t="n">
         <v>3.954</v>
       </c>
     </row>
@@ -948,9 +978,12 @@
         <v>288.82</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>288.82</v>
+        <v>290.67</v>
       </c>
       <c r="O10" s="1" t="n">
+        <v>290.67</v>
+      </c>
+      <c r="P10" s="1" t="n">
         <v>272.11</v>
       </c>
     </row>
@@ -997,10 +1030,13 @@
         <v>0.07757</v>
       </c>
       <c r="N11" s="1" t="n">
+        <v>0.07625999999999999</v>
+      </c>
+      <c r="O11" s="1" t="n">
         <v>0.08047</v>
       </c>
-      <c r="O11" s="1" t="n">
-        <v>0.07757</v>
+      <c r="P11" s="1" t="n">
+        <v>0.07625999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1046,9 +1082,12 @@
         <v>227.74</v>
       </c>
       <c r="N12" s="1" t="n">
+        <v>226.27</v>
+      </c>
+      <c r="O12" s="1" t="n">
         <v>227.74</v>
       </c>
-      <c r="O12" s="1" t="n">
+      <c r="P12" s="1" t="n">
         <v>223.76</v>
       </c>
     </row>
@@ -1095,9 +1134,12 @@
         <v>0.09524000000000001</v>
       </c>
       <c r="N13" s="1" t="n">
+        <v>0.09472</v>
+      </c>
+      <c r="O13" s="1" t="n">
         <v>0.09543</v>
       </c>
-      <c r="O13" s="1" t="n">
+      <c r="P13" s="1" t="n">
         <v>0.0946</v>
       </c>
     </row>
@@ -1144,10 +1186,13 @@
         <v>37.103</v>
       </c>
       <c r="N14" s="1" t="n">
+        <v>36.854</v>
+      </c>
+      <c r="O14" s="1" t="n">
         <v>37.361</v>
       </c>
-      <c r="O14" s="1" t="n">
-        <v>37.059</v>
+      <c r="P14" s="1" t="n">
+        <v>36.854</v>
       </c>
     </row>
     <row r="15">
@@ -1193,10 +1238,13 @@
         <v>0.08894000000000001</v>
       </c>
       <c r="N15" s="1" t="n">
+        <v>0.08772000000000001</v>
+      </c>
+      <c r="O15" s="1" t="n">
         <v>0.09845</v>
       </c>
-      <c r="O15" s="1" t="n">
-        <v>0.08894000000000001</v>
+      <c r="P15" s="1" t="n">
+        <v>0.08772000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1242,10 +1290,13 @@
         <v>0.2267</v>
       </c>
       <c r="N16" s="1" t="n">
+        <v>0.2247</v>
+      </c>
+      <c r="O16" s="1" t="n">
         <v>0.2339</v>
       </c>
-      <c r="O16" s="1" t="n">
-        <v>0.2256</v>
+      <c r="P16" s="1" t="n">
+        <v>0.2247</v>
       </c>
     </row>
     <row r="17">
@@ -1291,9 +1342,12 @@
         <v>0.011627</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.011627</v>
+        <v>0.011689</v>
       </c>
       <c r="O17" s="1" t="n">
+        <v>0.011689</v>
+      </c>
+      <c r="P17" s="1" t="n">
         <v>0.011379</v>
       </c>
     </row>
@@ -1340,10 +1394,13 @@
         <v>661.25</v>
       </c>
       <c r="N18" s="1" t="n">
+        <v>658.36</v>
+      </c>
+      <c r="O18" s="1" t="n">
         <v>661.9</v>
       </c>
-      <c r="O18" s="1" t="n">
-        <v>658.89</v>
+      <c r="P18" s="1" t="n">
+        <v>658.36</v>
       </c>
     </row>
     <row r="19">
@@ -1389,9 +1446,12 @@
         <v>0.003363</v>
       </c>
       <c r="N19" s="1" t="n">
+        <v>0.0033416</v>
+      </c>
+      <c r="O19" s="1" t="n">
         <v>0.003368</v>
       </c>
-      <c r="O19" s="1" t="n">
+      <c r="P19" s="1" t="n">
         <v>0.0033271</v>
       </c>
     </row>
@@ -1438,9 +1498,12 @@
         <v>0.17083</v>
       </c>
       <c r="N20" s="1" t="n">
+        <v>0.17211</v>
+      </c>
+      <c r="O20" s="1" t="n">
         <v>0.18066</v>
       </c>
-      <c r="O20" s="1" t="n">
+      <c r="P20" s="1" t="n">
         <v>0.17083</v>
       </c>
     </row>
@@ -1487,9 +1550,12 @@
         <v>0.009871</v>
       </c>
       <c r="N21" s="1" t="n">
+        <v>0.009815000000000001</v>
+      </c>
+      <c r="O21" s="1" t="n">
         <v>0.010044</v>
       </c>
-      <c r="O21" s="1" t="n">
+      <c r="P21" s="1" t="n">
         <v>0.009778</v>
       </c>
     </row>
@@ -1536,9 +1602,12 @@
         <v>1.008</v>
       </c>
       <c r="N22" s="1" t="n">
+        <v>1.0008</v>
+      </c>
+      <c r="O22" s="1" t="n">
         <v>1.009</v>
       </c>
-      <c r="O22" s="1" t="n">
+      <c r="P22" s="1" t="n">
         <v>0.9985000000000001</v>
       </c>
     </row>
@@ -1585,9 +1654,12 @@
         <v>5005.92</v>
       </c>
       <c r="N23" s="1" t="n">
+        <v>5004.17</v>
+      </c>
+      <c r="O23" s="1" t="n">
         <v>5012.25</v>
       </c>
-      <c r="O23" s="1" t="n">
+      <c r="P23" s="1" t="n">
         <v>5002.67</v>
       </c>
     </row>
@@ -1634,9 +1706,12 @@
         <v>0.2642</v>
       </c>
       <c r="N24" s="1" t="n">
+        <v>0.2626</v>
+      </c>
+      <c r="O24" s="1" t="n">
         <v>0.2645</v>
       </c>
-      <c r="O24" s="1" t="n">
+      <c r="P24" s="1" t="n">
         <v>0.2625</v>
       </c>
     </row>
@@ -1683,10 +1758,13 @@
         <v>2.881</v>
       </c>
       <c r="N25" s="1" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O25" s="1" t="n">
         <v>2.924</v>
       </c>
-      <c r="O25" s="1" t="n">
-        <v>2.873</v>
+      <c r="P25" s="1" t="n">
+        <v>2.87</v>
       </c>
     </row>
     <row r="26">
@@ -1732,9 +1810,12 @@
         <v>0.3925</v>
       </c>
       <c r="N26" s="1" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="O26" s="1" t="n">
         <v>0.4096</v>
       </c>
-      <c r="O26" s="1" t="n">
+      <c r="P26" s="1" t="n">
         <v>0.3825</v>
       </c>
     </row>
@@ -1781,9 +1862,12 @@
         <v>0.887</v>
       </c>
       <c r="N27" s="1" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="O27" s="1" t="n">
         <v>0.889</v>
       </c>
-      <c r="O27" s="1" t="n">
+      <c r="P27" s="1" t="n">
         <v>0.881</v>
       </c>
     </row>
@@ -1830,10 +1914,13 @@
         <v>1.342</v>
       </c>
       <c r="N28" s="1" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="O28" s="1" t="n">
         <v>1.346</v>
       </c>
-      <c r="O28" s="1" t="n">
-        <v>1.335</v>
+      <c r="P28" s="1" t="n">
+        <v>1.334</v>
       </c>
     </row>
     <row r="29">
@@ -1879,9 +1966,12 @@
         <v>9.196</v>
       </c>
       <c r="N29" s="1" t="n">
+        <v>9.146000000000001</v>
+      </c>
+      <c r="O29" s="1" t="n">
         <v>9.205</v>
       </c>
-      <c r="O29" s="1" t="n">
+      <c r="P29" s="1" t="n">
         <v>9.131</v>
       </c>
     </row>
@@ -1928,10 +2018,13 @@
         <v>462.45</v>
       </c>
       <c r="N30" s="1" t="n">
+        <v>461.02</v>
+      </c>
+      <c r="O30" s="1" t="n">
         <v>463.35</v>
       </c>
-      <c r="O30" s="1" t="n">
-        <v>461.24</v>
+      <c r="P30" s="1" t="n">
+        <v>461.02</v>
       </c>
     </row>
     <row r="31">
@@ -1977,10 +2070,13 @@
         <v>9.763999999999999</v>
       </c>
       <c r="N31" s="1" t="n">
+        <v>9.686</v>
+      </c>
+      <c r="O31" s="1" t="n">
         <v>9.771000000000001</v>
       </c>
-      <c r="O31" s="1" t="n">
-        <v>9.696999999999999</v>
+      <c r="P31" s="1" t="n">
+        <v>9.686</v>
       </c>
     </row>
     <row r="32">
@@ -2026,10 +2122,13 @@
         <v>0.36079</v>
       </c>
       <c r="N32" s="1" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="O32" s="1" t="n">
         <v>0.36683</v>
       </c>
-      <c r="O32" s="1" t="n">
-        <v>0.35998</v>
+      <c r="P32" s="1" t="n">
+        <v>0.35778</v>
       </c>
     </row>
     <row r="33">
@@ -2075,9 +2174,12 @@
         <v>1.419</v>
       </c>
       <c r="N33" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O33" s="1" t="n">
         <v>1.421</v>
       </c>
-      <c r="O33" s="1" t="n">
+      <c r="P33" s="1" t="n">
         <v>1.409</v>
       </c>
     </row>
@@ -2124,9 +2226,12 @@
         <v>0.59116</v>
       </c>
       <c r="N34" s="1" t="n">
+        <v>0.59044</v>
+      </c>
+      <c r="O34" s="1" t="n">
         <v>0.59693</v>
       </c>
-      <c r="O34" s="1" t="n">
+      <c r="P34" s="1" t="n">
         <v>0.58086</v>
       </c>
     </row>
@@ -2173,9 +2278,12 @@
         <v>1.2261</v>
       </c>
       <c r="N35" s="1" t="n">
+        <v>1.2236</v>
+      </c>
+      <c r="O35" s="1" t="n">
         <v>1.2283</v>
       </c>
-      <c r="O35" s="1" t="n">
+      <c r="P35" s="1" t="n">
         <v>1.2186</v>
       </c>
     </row>
@@ -2222,10 +2330,13 @@
         <v>80.36</v>
       </c>
       <c r="N36" s="1" t="n">
+        <v>80.23999999999999</v>
+      </c>
+      <c r="O36" s="1" t="n">
         <v>80.5</v>
       </c>
-      <c r="O36" s="1" t="n">
-        <v>80.27</v>
+      <c r="P36" s="1" t="n">
+        <v>80.23999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2271,9 +2382,12 @@
         <v>0.2</v>
       </c>
       <c r="N37" s="1" t="n">
+        <v>0.1976</v>
+      </c>
+      <c r="O37" s="1" t="n">
         <v>0.204</v>
       </c>
-      <c r="O37" s="1" t="n">
+      <c r="P37" s="1" t="n">
         <v>0.1967</v>
       </c>
     </row>
@@ -2320,9 +2434,12 @@
         <v>1.897</v>
       </c>
       <c r="N38" s="1" t="n">
+        <v>1.882</v>
+      </c>
+      <c r="O38" s="1" t="n">
         <v>1.897</v>
       </c>
-      <c r="O38" s="1" t="n">
+      <c r="P38" s="1" t="n">
         <v>1.844</v>
       </c>
     </row>
@@ -2369,9 +2486,12 @@
         <v>0.3332</v>
       </c>
       <c r="N39" s="1" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="O39" s="1" t="n">
         <v>0.3382</v>
       </c>
-      <c r="O39" s="1" t="n">
+      <c r="P39" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -2418,10 +2538,13 @@
         <v>0.8845</v>
       </c>
       <c r="N40" s="1" t="n">
+        <v>0.8812</v>
+      </c>
+      <c r="O40" s="1" t="n">
         <v>0.9115</v>
       </c>
-      <c r="O40" s="1" t="n">
-        <v>0.8845</v>
+      <c r="P40" s="1" t="n">
+        <v>0.8812</v>
       </c>
     </row>
     <row r="41">
@@ -2467,10 +2590,13 @@
         <v>0.7117</v>
       </c>
       <c r="N41" s="1" t="n">
+        <v>0.7096</v>
+      </c>
+      <c r="O41" s="1" t="n">
         <v>0.7151999999999999</v>
       </c>
-      <c r="O41" s="1" t="n">
-        <v>0.7115</v>
+      <c r="P41" s="1" t="n">
+        <v>0.7096</v>
       </c>
     </row>
     <row r="42">
@@ -2516,10 +2642,13 @@
         <v>0.06544</v>
       </c>
       <c r="N42" s="1" t="n">
+        <v>0.06543</v>
+      </c>
+      <c r="O42" s="1" t="n">
         <v>0.06769</v>
       </c>
-      <c r="O42" s="1" t="n">
-        <v>0.06544</v>
+      <c r="P42" s="1" t="n">
+        <v>0.06543</v>
       </c>
     </row>
     <row r="43">
@@ -2565,9 +2694,12 @@
         <v>115.35</v>
       </c>
       <c r="N43" s="1" t="n">
+        <v>113.93</v>
+      </c>
+      <c r="O43" s="1" t="n">
         <v>115.35</v>
       </c>
-      <c r="O43" s="1" t="n">
+      <c r="P43" s="1" t="n">
         <v>112.81</v>
       </c>
     </row>
@@ -2614,9 +2746,12 @@
         <v>0.6572</v>
       </c>
       <c r="N44" s="1" t="n">
+        <v>0.6554</v>
+      </c>
+      <c r="O44" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="O44" s="1" t="n">
+      <c r="P44" s="1" t="n">
         <v>0.6536999999999999</v>
       </c>
     </row>
@@ -2663,9 +2798,12 @@
         <v>1.227</v>
       </c>
       <c r="N45" s="1" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="O45" s="1" t="n">
         <v>1.227</v>
       </c>
-      <c r="O45" s="1" t="n">
+      <c r="P45" s="1" t="n">
         <v>1.206</v>
       </c>
     </row>
@@ -2712,9 +2850,12 @@
         <v>0.02385</v>
       </c>
       <c r="N46" s="1" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="O46" s="1" t="n">
         <v>0.02392</v>
       </c>
-      <c r="O46" s="1" t="n">
+      <c r="P46" s="1" t="n">
         <v>0.02375</v>
       </c>
     </row>
@@ -2761,10 +2902,13 @@
         <v>55.23</v>
       </c>
       <c r="N47" s="1" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="O47" s="1" t="n">
         <v>55.23</v>
       </c>
-      <c r="O47" s="1" t="n">
-        <v>54.99</v>
+      <c r="P47" s="1" t="n">
+        <v>54.97</v>
       </c>
     </row>
     <row r="48">
@@ -2810,9 +2954,12 @@
         <v>0.06112</v>
       </c>
       <c r="N48" s="1" t="n">
+        <v>0.06082</v>
+      </c>
+      <c r="O48" s="1" t="n">
         <v>0.06112</v>
       </c>
-      <c r="O48" s="1" t="n">
+      <c r="P48" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -2859,9 +3006,12 @@
         <v>0.1088</v>
       </c>
       <c r="N49" s="1" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="O49" s="1" t="n">
         <v>0.1088</v>
       </c>
-      <c r="O49" s="1" t="n">
+      <c r="P49" s="1" t="n">
         <v>0.1076</v>
       </c>
     </row>
@@ -2908,10 +3058,13 @@
         <v>0.018</v>
       </c>
       <c r="N50" s="1" t="n">
+        <v>0.01787</v>
+      </c>
+      <c r="O50" s="1" t="n">
         <v>0.01815</v>
       </c>
-      <c r="O50" s="1" t="n">
-        <v>0.01795</v>
+      <c r="P50" s="1" t="n">
+        <v>0.01787</v>
       </c>
     </row>
     <row r="51">
@@ -2957,9 +3110,12 @@
         <v>1.4748</v>
       </c>
       <c r="N51" s="1" t="n">
+        <v>1.4708</v>
+      </c>
+      <c r="O51" s="1" t="n">
         <v>1.4817</v>
       </c>
-      <c r="O51" s="1" t="n">
+      <c r="P51" s="1" t="n">
         <v>1.4618</v>
       </c>
     </row>
@@ -3006,9 +3162,12 @@
         <v>0.3617</v>
       </c>
       <c r="N52" s="1" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="O52" s="1" t="n">
         <v>0.3617</v>
       </c>
-      <c r="O52" s="1" t="n">
+      <c r="P52" s="1" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -3055,10 +3214,13 @@
         <v>0.001943</v>
       </c>
       <c r="N53" s="1" t="n">
+        <v>0.001923</v>
+      </c>
+      <c r="O53" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="O53" s="1" t="n">
-        <v>0.001939</v>
+      <c r="P53" s="1" t="n">
+        <v>0.001923</v>
       </c>
     </row>
     <row r="54">
@@ -3104,9 +3266,12 @@
         <v>0.09594999999999999</v>
       </c>
       <c r="N54" s="1" t="n">
+        <v>0.09519</v>
+      </c>
+      <c r="O54" s="1" t="n">
         <v>0.09594999999999999</v>
       </c>
-      <c r="O54" s="1" t="n">
+      <c r="P54" s="1" t="n">
         <v>0.09514</v>
       </c>
     </row>
@@ -3153,9 +3318,12 @@
         <v>0.04081</v>
       </c>
       <c r="N55" s="1" t="n">
+        <v>0.04067</v>
+      </c>
+      <c r="O55" s="1" t="n">
         <v>0.04099</v>
       </c>
-      <c r="O55" s="1" t="n">
+      <c r="P55" s="1" t="n">
         <v>0.04003</v>
       </c>
     </row>
@@ -3202,9 +3370,12 @@
         <v>0.29817</v>
       </c>
       <c r="N56" s="1" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="O56" s="1" t="n">
         <v>0.29861</v>
       </c>
-      <c r="O56" s="1" t="n">
+      <c r="P56" s="1" t="n">
         <v>0.29817</v>
       </c>
     </row>
@@ -3251,9 +3422,12 @@
         <v>0.005692</v>
       </c>
       <c r="N57" s="1" t="n">
+        <v>0.005662</v>
+      </c>
+      <c r="O57" s="1" t="n">
         <v>0.005824</v>
       </c>
-      <c r="O57" s="1" t="n">
+      <c r="P57" s="1" t="n">
         <v>0.005633</v>
       </c>
     </row>
@@ -3300,9 +3474,12 @@
         <v>4990.01</v>
       </c>
       <c r="N58" s="1" t="n">
+        <v>4988.9</v>
+      </c>
+      <c r="O58" s="1" t="n">
         <v>4998.37</v>
       </c>
-      <c r="O58" s="1" t="n">
+      <c r="P58" s="1" t="n">
         <v>4988.64</v>
       </c>
     </row>
@@ -3349,10 +3526,13 @@
         <v>0.4087</v>
       </c>
       <c r="N59" s="1" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="O59" s="1" t="n">
         <v>0.4246</v>
       </c>
-      <c r="O59" s="1" t="n">
-        <v>0.4067</v>
+      <c r="P59" s="1" t="n">
+        <v>0.4048</v>
       </c>
     </row>
     <row r="60">
@@ -3398,9 +3578,12 @@
         <v>0.04655</v>
       </c>
       <c r="N60" s="1" t="n">
+        <v>0.04652</v>
+      </c>
+      <c r="O60" s="1" t="n">
         <v>0.04686</v>
       </c>
-      <c r="O60" s="1" t="n">
+      <c r="P60" s="1" t="n">
         <v>0.04598</v>
       </c>
     </row>
@@ -3447,10 +3630,13 @@
         <v>0.21338</v>
       </c>
       <c r="N61" s="1" t="n">
+        <v>0.21236</v>
+      </c>
+      <c r="O61" s="1" t="n">
         <v>0.21708</v>
       </c>
-      <c r="O61" s="1" t="n">
-        <v>0.21309</v>
+      <c r="P61" s="1" t="n">
+        <v>0.21236</v>
       </c>
     </row>
     <row r="62">
@@ -3496,10 +3682,13 @@
         <v>0.1073</v>
       </c>
       <c r="N62" s="1" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="O62" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="O62" s="1" t="n">
-        <v>0.1065</v>
+      <c r="P62" s="1" t="n">
+        <v>0.1062</v>
       </c>
     </row>
     <row r="63">
@@ -3545,9 +3734,12 @@
         <v>0.7376</v>
       </c>
       <c r="N63" s="1" t="n">
+        <v>0.7317</v>
+      </c>
+      <c r="O63" s="1" t="n">
         <v>0.7376</v>
       </c>
-      <c r="O63" s="1" t="n">
+      <c r="P63" s="1" t="n">
         <v>0.7255</v>
       </c>
     </row>
@@ -3594,10 +3786,13 @@
         <v>0.1665</v>
       </c>
       <c r="N64" s="1" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="O64" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="O64" s="1" t="n">
-        <v>0.1658</v>
+      <c r="P64" s="1" t="n">
+        <v>0.1657</v>
       </c>
     </row>
     <row r="65">
@@ -3643,9 +3838,12 @@
         <v>2.675</v>
       </c>
       <c r="N65" s="1" t="n">
+        <v>2.664</v>
+      </c>
+      <c r="O65" s="1" t="n">
         <v>2.679</v>
       </c>
-      <c r="O65" s="1" t="n">
+      <c r="P65" s="1" t="n">
         <v>2.65</v>
       </c>
     </row>
@@ -3692,10 +3890,13 @@
         <v>0.04029</v>
       </c>
       <c r="N66" s="1" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="O66" s="1" t="n">
         <v>0.04072</v>
       </c>
-      <c r="O66" s="1" t="n">
-        <v>0.04018</v>
+      <c r="P66" s="1" t="n">
+        <v>0.04012</v>
       </c>
     </row>
     <row r="67">
@@ -3741,9 +3942,12 @@
         <v>0.04279</v>
       </c>
       <c r="N67" s="1" t="n">
+        <v>0.04274</v>
+      </c>
+      <c r="O67" s="1" t="n">
         <v>0.04314</v>
       </c>
-      <c r="O67" s="1" t="n">
+      <c r="P67" s="1" t="n">
         <v>0.04217</v>
       </c>
     </row>
@@ -3790,9 +3994,12 @@
         <v>4.001</v>
       </c>
       <c r="N68" s="1" t="n">
+        <v>3.975</v>
+      </c>
+      <c r="O68" s="1" t="n">
         <v>4.001</v>
       </c>
-      <c r="O68" s="1" t="n">
+      <c r="P68" s="1" t="n">
         <v>3.951</v>
       </c>
     </row>
@@ -3839,9 +4046,12 @@
         <v>0.1274</v>
       </c>
       <c r="N69" s="1" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="O69" s="1" t="n">
         <v>0.1274</v>
       </c>
-      <c r="O69" s="1" t="n">
+      <c r="P69" s="1" t="n">
         <v>0.1253</v>
       </c>
     </row>
@@ -3888,9 +4098,12 @@
         <v>6.318</v>
       </c>
       <c r="N70" s="1" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="O70" s="1" t="n">
         <v>6.338</v>
       </c>
-      <c r="O70" s="1" t="n">
+      <c r="P70" s="1" t="n">
         <v>6.114</v>
       </c>
     </row>
@@ -3937,9 +4150,12 @@
         <v>0.0501</v>
       </c>
       <c r="N71" s="1" t="n">
+        <v>0.04997</v>
+      </c>
+      <c r="O71" s="1" t="n">
         <v>0.05015</v>
       </c>
-      <c r="O71" s="1" t="n">
+      <c r="P71" s="1" t="n">
         <v>0.04959</v>
       </c>
     </row>
@@ -3986,9 +4202,12 @@
         <v>0.004122</v>
       </c>
       <c r="N72" s="1" t="n">
+        <v>0.004132</v>
+      </c>
+      <c r="O72" s="1" t="n">
         <v>0.004181</v>
       </c>
-      <c r="O72" s="1" t="n">
+      <c r="P72" s="1" t="n">
         <v>0.004098</v>
       </c>
     </row>
@@ -4035,9 +4254,12 @@
         <v>6.056</v>
       </c>
       <c r="N73" s="1" t="n">
+        <v>6.013</v>
+      </c>
+      <c r="O73" s="1" t="n">
         <v>6.056</v>
       </c>
-      <c r="O73" s="1" t="n">
+      <c r="P73" s="1" t="n">
         <v>5.96</v>
       </c>
     </row>
@@ -4084,9 +4306,12 @@
         <v>0.1653</v>
       </c>
       <c r="N74" s="1" t="n">
+        <v>0.1638</v>
+      </c>
+      <c r="O74" s="1" t="n">
         <v>0.1655</v>
       </c>
-      <c r="O74" s="1" t="n">
+      <c r="P74" s="1" t="n">
         <v>0.1619</v>
       </c>
     </row>
@@ -4133,9 +4358,12 @@
         <v>0.007362</v>
       </c>
       <c r="N75" s="1" t="n">
+        <v>0.007301</v>
+      </c>
+      <c r="O75" s="1" t="n">
         <v>0.007365</v>
       </c>
-      <c r="O75" s="1" t="n">
+      <c r="P75" s="1" t="n">
         <v>0.007261</v>
       </c>
     </row>
@@ -4182,9 +4410,12 @@
         <v>0.2151</v>
       </c>
       <c r="N76" s="1" t="n">
+        <v>0.2126</v>
+      </c>
+      <c r="O76" s="1" t="n">
         <v>0.2199</v>
       </c>
-      <c r="O76" s="1" t="n">
+      <c r="P76" s="1" t="n">
         <v>0.2024</v>
       </c>
     </row>
@@ -4231,9 +4462,12 @@
         <v>0.005827</v>
       </c>
       <c r="N77" s="1" t="n">
+        <v>0.005803</v>
+      </c>
+      <c r="O77" s="1" t="n">
         <v>0.005844</v>
       </c>
-      <c r="O77" s="1" t="n">
+      <c r="P77" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -4280,9 +4514,12 @@
         <v>0.1021</v>
       </c>
       <c r="N78" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="O78" s="1" t="n">
         <v>0.1023</v>
       </c>
-      <c r="O78" s="1" t="n">
+      <c r="P78" s="1" t="n">
         <v>0.1013</v>
       </c>
     </row>
@@ -4329,9 +4566,12 @@
         <v>0.006304</v>
       </c>
       <c r="N79" s="1" t="n">
+        <v>0.006253</v>
+      </c>
+      <c r="O79" s="1" t="n">
         <v>0.006315</v>
       </c>
-      <c r="O79" s="1" t="n">
+      <c r="P79" s="1" t="n">
         <v>0.006237</v>
       </c>
     </row>
@@ -4378,10 +4618,13 @@
         <v>33.64</v>
       </c>
       <c r="N80" s="1" t="n">
+        <v>33.27</v>
+      </c>
+      <c r="O80" s="1" t="n">
         <v>33.66</v>
       </c>
-      <c r="O80" s="1" t="n">
-        <v>33.33</v>
+      <c r="P80" s="1" t="n">
+        <v>33.27</v>
       </c>
     </row>
     <row r="81">
@@ -4427,9 +4670,12 @@
         <v>0.04058</v>
       </c>
       <c r="N81" s="1" t="n">
+        <v>0.04048</v>
+      </c>
+      <c r="O81" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="O81" s="1" t="n">
+      <c r="P81" s="1" t="n">
         <v>0.04037</v>
       </c>
     </row>
@@ -4476,10 +4722,13 @@
         <v>0.16741</v>
       </c>
       <c r="N82" s="1" t="n">
+        <v>0.1663</v>
+      </c>
+      <c r="O82" s="1" t="n">
         <v>0.16759</v>
       </c>
-      <c r="O82" s="1" t="n">
-        <v>0.16679</v>
+      <c r="P82" s="1" t="n">
+        <v>0.1663</v>
       </c>
     </row>
     <row r="83">
@@ -4525,10 +4774,13 @@
         <v>0.1037</v>
       </c>
       <c r="N83" s="1" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="O83" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="O83" s="1" t="n">
-        <v>0.1032</v>
+      <c r="P83" s="1" t="n">
+        <v>0.1031</v>
       </c>
     </row>
     <row r="84">
@@ -4574,10 +4826,13 @@
         <v>0.08722000000000001</v>
       </c>
       <c r="N84" s="1" t="n">
+        <v>0.08677</v>
+      </c>
+      <c r="O84" s="1" t="n">
         <v>0.08848</v>
       </c>
-      <c r="O84" s="1" t="n">
-        <v>0.08722000000000001</v>
+      <c r="P84" s="1" t="n">
+        <v>0.08677</v>
       </c>
     </row>
     <row r="85">
@@ -4623,10 +4878,13 @@
         <v>0.02288</v>
       </c>
       <c r="N85" s="1" t="n">
+        <v>0.02286</v>
+      </c>
+      <c r="O85" s="1" t="n">
         <v>0.02331</v>
       </c>
-      <c r="O85" s="1" t="n">
-        <v>0.02288</v>
+      <c r="P85" s="1" t="n">
+        <v>0.02286</v>
       </c>
     </row>
     <row r="86">
@@ -4672,9 +4930,12 @@
         <v>0.247</v>
       </c>
       <c r="N86" s="1" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="O86" s="1" t="n">
         <v>0.247</v>
       </c>
-      <c r="O86" s="1" t="n">
+      <c r="P86" s="1" t="n">
         <v>0.236</v>
       </c>
     </row>
@@ -4721,10 +4982,13 @@
         <v>356.65</v>
       </c>
       <c r="N87" s="1" t="n">
+        <v>354.83</v>
+      </c>
+      <c r="O87" s="1" t="n">
         <v>358.65</v>
       </c>
-      <c r="O87" s="1" t="n">
-        <v>355.75</v>
+      <c r="P87" s="1" t="n">
+        <v>354.83</v>
       </c>
     </row>
     <row r="88">
@@ -4770,9 +5034,12 @@
         <v>0.0035</v>
       </c>
       <c r="N88" s="1" t="n">
+        <v>0.00346</v>
+      </c>
+      <c r="O88" s="1" t="n">
         <v>0.00352</v>
       </c>
-      <c r="O88" s="1" t="n">
+      <c r="P88" s="1" t="n">
         <v>0.00342</v>
       </c>
     </row>
@@ -4819,9 +5086,12 @@
         <v>8.327</v>
       </c>
       <c r="N89" s="1" t="n">
+        <v>8.273999999999999</v>
+      </c>
+      <c r="O89" s="1" t="n">
         <v>8.327</v>
       </c>
-      <c r="O89" s="1" t="n">
+      <c r="P89" s="1" t="n">
         <v>8.257</v>
       </c>
     </row>
@@ -4868,10 +5138,13 @@
         <v>0.005935</v>
       </c>
       <c r="N90" s="1" t="n">
+        <v>0.005904</v>
+      </c>
+      <c r="O90" s="1" t="n">
         <v>0.005958</v>
       </c>
-      <c r="O90" s="1" t="n">
-        <v>0.005905</v>
+      <c r="P90" s="1" t="n">
+        <v>0.005904</v>
       </c>
     </row>
     <row r="91">
@@ -4917,9 +5190,12 @@
         <v>0.06863</v>
       </c>
       <c r="N91" s="1" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="O91" s="1" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="O91" s="1" t="n">
+      <c r="P91" s="1" t="n">
         <v>0.06812</v>
       </c>
     </row>
@@ -4966,9 +5242,12 @@
         <v>0.02858</v>
       </c>
       <c r="N92" s="1" t="n">
+        <v>0.02858</v>
+      </c>
+      <c r="O92" s="1" t="n">
         <v>0.02905</v>
       </c>
-      <c r="O92" s="1" t="n">
+      <c r="P92" s="1" t="n">
         <v>0.02851</v>
       </c>
     </row>
@@ -5015,9 +5294,12 @@
         <v>5.182</v>
       </c>
       <c r="N93" s="1" t="n">
+        <v>5.183</v>
+      </c>
+      <c r="O93" s="1" t="n">
         <v>5.228</v>
       </c>
-      <c r="O93" s="1" t="n">
+      <c r="P93" s="1" t="n">
         <v>5.159</v>
       </c>
     </row>
@@ -5064,9 +5346,12 @@
         <v>0.000226</v>
       </c>
       <c r="N94" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="O94" s="1" t="n">
         <v>0.000228</v>
       </c>
-      <c r="O94" s="1" t="n">
+      <c r="P94" s="1" t="n">
         <v>0.000225</v>
       </c>
     </row>
@@ -5113,9 +5398,12 @@
         <v>0.9267</v>
       </c>
       <c r="N95" s="1" t="n">
+        <v>0.9208</v>
+      </c>
+      <c r="O95" s="1" t="n">
         <v>0.9278999999999999</v>
       </c>
-      <c r="O95" s="1" t="n">
+      <c r="P95" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -5162,9 +5450,12 @@
         <v>2.1792</v>
       </c>
       <c r="N96" s="1" t="n">
+        <v>2.1421</v>
+      </c>
+      <c r="O96" s="1" t="n">
         <v>2.1985</v>
       </c>
-      <c r="O96" s="1" t="n">
+      <c r="P96" s="1" t="n">
         <v>2.0598</v>
       </c>
     </row>
@@ -5211,10 +5502,13 @@
         <v>0.3673</v>
       </c>
       <c r="N97" s="1" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="O97" s="1" t="n">
         <v>0.3722</v>
       </c>
-      <c r="O97" s="1" t="n">
-        <v>0.3673</v>
+      <c r="P97" s="1" t="n">
+        <v>0.3648</v>
       </c>
     </row>
     <row r="98">
@@ -5260,10 +5554,13 @@
         <v>1.623</v>
       </c>
       <c r="N98" s="1" t="n">
+        <v>1.612</v>
+      </c>
+      <c r="O98" s="1" t="n">
         <v>1.625</v>
       </c>
-      <c r="O98" s="1" t="n">
-        <v>1.613</v>
+      <c r="P98" s="1" t="n">
+        <v>1.612</v>
       </c>
     </row>
     <row r="99">
@@ -5309,10 +5606,13 @@
         <v>0.2314</v>
       </c>
       <c r="N99" s="1" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="O99" s="1" t="n">
         <v>0.2368</v>
       </c>
-      <c r="O99" s="1" t="n">
-        <v>0.2314</v>
+      <c r="P99" s="1" t="n">
+        <v>0.2305</v>
       </c>
     </row>
     <row r="100">
@@ -5358,9 +5658,12 @@
         <v>0.13647</v>
       </c>
       <c r="N100" s="1" t="n">
+        <v>0.13621</v>
+      </c>
+      <c r="O100" s="1" t="n">
         <v>0.13748</v>
       </c>
-      <c r="O100" s="1" t="n">
+      <c r="P100" s="1" t="n">
         <v>0.13539</v>
       </c>
     </row>
@@ -5407,9 +5710,12 @@
         <v>0.07020999999999999</v>
       </c>
       <c r="N101" s="1" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="O101" s="1" t="n">
         <v>0.07115</v>
       </c>
-      <c r="O101" s="1" t="n">
+      <c r="P101" s="1" t="n">
         <v>0.06851</v>
       </c>
     </row>
@@ -5456,10 +5762,13 @@
         <v>0.0010831</v>
       </c>
       <c r="N102" s="1" t="n">
+        <v>0.0010773</v>
+      </c>
+      <c r="O102" s="1" t="n">
         <v>0.0010886</v>
       </c>
-      <c r="O102" s="1" t="n">
-        <v>0.0010822</v>
+      <c r="P102" s="1" t="n">
+        <v>0.0010773</v>
       </c>
     </row>
     <row r="103">
@@ -5505,9 +5814,12 @@
         <v>0.003413</v>
       </c>
       <c r="N103" s="1" t="n">
+        <v>0.003417</v>
+      </c>
+      <c r="O103" s="1" t="n">
         <v>0.003427</v>
       </c>
-      <c r="O103" s="1" t="n">
+      <c r="P103" s="1" t="n">
         <v>0.003403</v>
       </c>
     </row>
@@ -5554,10 +5866,13 @@
         <v>0.27209</v>
       </c>
       <c r="N104" s="1" t="n">
+        <v>0.27064</v>
+      </c>
+      <c r="O104" s="1" t="n">
         <v>0.27751</v>
       </c>
-      <c r="O104" s="1" t="n">
-        <v>0.27209</v>
+      <c r="P104" s="1" t="n">
+        <v>0.27064</v>
       </c>
     </row>
     <row r="105">
@@ -5603,9 +5918,12 @@
         <v>0.01254</v>
       </c>
       <c r="N105" s="1" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="O105" s="1" t="n">
         <v>0.01257</v>
       </c>
-      <c r="O105" s="1" t="n">
+      <c r="P105" s="1" t="n">
         <v>0.01243</v>
       </c>
     </row>
@@ -5652,9 +5970,12 @@
         <v>0.13568</v>
       </c>
       <c r="N106" s="1" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="O106" s="1" t="n">
         <v>0.13615</v>
       </c>
-      <c r="O106" s="1" t="n">
+      <c r="P106" s="1" t="n">
         <v>0.13329</v>
       </c>
     </row>
@@ -5701,9 +6022,12 @@
         <v>0.3511</v>
       </c>
       <c r="N107" s="1" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="O107" s="1" t="n">
         <v>0.3522</v>
       </c>
-      <c r="O107" s="1" t="n">
+      <c r="P107" s="1" t="n">
         <v>0.3476</v>
       </c>
     </row>
@@ -5750,9 +6074,12 @@
         <v>0.1422</v>
       </c>
       <c r="N108" s="1" t="n">
+        <v>0.1419</v>
+      </c>
+      <c r="O108" s="1" t="n">
         <v>0.1436</v>
       </c>
-      <c r="O108" s="1" t="n">
+      <c r="P108" s="1" t="n">
         <v>0.1413</v>
       </c>
     </row>
@@ -5799,9 +6126,12 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="N109" s="1" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="O109" s="1" t="n">
         <v>0.9379999999999999</v>
       </c>
-      <c r="O109" s="1" t="n">
+      <c r="P109" s="1" t="n">
         <v>0.928</v>
       </c>
     </row>
@@ -5848,10 +6178,13 @@
         <v>0.016195</v>
       </c>
       <c r="N110" s="1" t="n">
+        <v>0.016154</v>
+      </c>
+      <c r="O110" s="1" t="n">
         <v>0.016308</v>
       </c>
-      <c r="O110" s="1" t="n">
-        <v>0.016195</v>
+      <c r="P110" s="1" t="n">
+        <v>0.016154</v>
       </c>
     </row>
     <row r="111">
@@ -5897,9 +6230,12 @@
         <v>0.039116</v>
       </c>
       <c r="N111" s="1" t="n">
-        <v>0.039116</v>
+        <v>0.0393</v>
       </c>
       <c r="O111" s="1" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="P111" s="1" t="n">
         <v>0.03774</v>
       </c>
     </row>
@@ -5946,9 +6282,12 @@
         <v>0.11917</v>
       </c>
       <c r="N112" s="1" t="n">
+        <v>0.11932</v>
+      </c>
+      <c r="O112" s="1" t="n">
         <v>0.12031</v>
       </c>
-      <c r="O112" s="1" t="n">
+      <c r="P112" s="1" t="n">
         <v>0.11917</v>
       </c>
     </row>
@@ -5995,9 +6334,12 @@
         <v>0.09383</v>
       </c>
       <c r="N113" s="1" t="n">
+        <v>0.09347</v>
+      </c>
+      <c r="O113" s="1" t="n">
         <v>0.09574000000000001</v>
       </c>
-      <c r="O113" s="1" t="n">
+      <c r="P113" s="1" t="n">
         <v>0.09342</v>
       </c>
     </row>
@@ -6044,9 +6386,12 @@
         <v>0.13047</v>
       </c>
       <c r="N114" s="1" t="n">
+        <v>0.13011</v>
+      </c>
+      <c r="O114" s="1" t="n">
         <v>0.13063</v>
       </c>
-      <c r="O114" s="1" t="n">
+      <c r="P114" s="1" t="n">
         <v>0.12895</v>
       </c>
     </row>
@@ -6093,9 +6438,12 @@
         <v>0.2663</v>
       </c>
       <c r="N115" s="1" t="n">
+        <v>0.2643</v>
+      </c>
+      <c r="O115" s="1" t="n">
         <v>0.2663</v>
       </c>
-      <c r="O115" s="1" t="n">
+      <c r="P115" s="1" t="n">
         <v>0.2638</v>
       </c>
     </row>
@@ -6142,10 +6490,13 @@
         <v>0.04779</v>
       </c>
       <c r="N116" s="1" t="n">
+        <v>0.04751</v>
+      </c>
+      <c r="O116" s="1" t="n">
         <v>0.0529</v>
       </c>
-      <c r="O116" s="1" t="n">
-        <v>0.04779</v>
+      <c r="P116" s="1" t="n">
+        <v>0.04751</v>
       </c>
     </row>
     <row r="117">
@@ -6191,10 +6542,13 @@
         <v>0.0914</v>
       </c>
       <c r="N117" s="1" t="n">
+        <v>0.0911</v>
+      </c>
+      <c r="O117" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="O117" s="1" t="n">
-        <v>0.09130000000000001</v>
+      <c r="P117" s="1" t="n">
+        <v>0.0911</v>
       </c>
     </row>
     <row r="118">
@@ -6240,10 +6594,13 @@
         <v>0.05523</v>
       </c>
       <c r="N118" s="1" t="n">
+        <v>0.05491</v>
+      </c>
+      <c r="O118" s="1" t="n">
         <v>0.05573</v>
       </c>
-      <c r="O118" s="1" t="n">
-        <v>0.05501</v>
+      <c r="P118" s="1" t="n">
+        <v>0.05491</v>
       </c>
     </row>
     <row r="119">
@@ -6289,9 +6646,12 @@
         <v>0.01511</v>
       </c>
       <c r="N119" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="O119" s="1" t="n">
         <v>0.01515</v>
       </c>
-      <c r="O119" s="1" t="n">
+      <c r="P119" s="1" t="n">
         <v>0.01505</v>
       </c>
     </row>
@@ -6338,9 +6698,12 @@
         <v>3.079</v>
       </c>
       <c r="N120" s="1" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="O120" s="1" t="n">
         <v>3.079</v>
       </c>
-      <c r="O120" s="1" t="n">
+      <c r="P120" s="1" t="n">
         <v>3.049</v>
       </c>
     </row>
@@ -6387,10 +6750,13 @@
         <v>1.85</v>
       </c>
       <c r="N121" s="1" t="n">
+        <v>1.844</v>
+      </c>
+      <c r="O121" s="1" t="n">
         <v>1.855</v>
       </c>
-      <c r="O121" s="1" t="n">
-        <v>1.848</v>
+      <c r="P121" s="1" t="n">
+        <v>1.844</v>
       </c>
     </row>
     <row r="122">
@@ -6436,9 +6802,12 @@
         <v>1.307</v>
       </c>
       <c r="N122" s="1" t="n">
+        <v>1.3025</v>
+      </c>
+      <c r="O122" s="1" t="n">
         <v>1.307</v>
       </c>
-      <c r="O122" s="1" t="n">
+      <c r="P122" s="1" t="n">
         <v>1.2934</v>
       </c>
     </row>
@@ -6485,9 +6854,12 @@
         <v>0.319</v>
       </c>
       <c r="N123" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="O123" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="O123" s="1" t="n">
+      <c r="P123" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -6534,9 +6906,12 @@
         <v>0.1255</v>
       </c>
       <c r="N124" s="1" t="n">
+        <v>0.12483</v>
+      </c>
+      <c r="O124" s="1" t="n">
         <v>0.12601</v>
       </c>
-      <c r="O124" s="1" t="n">
+      <c r="P124" s="1" t="n">
         <v>0.12202</v>
       </c>
     </row>
@@ -6583,9 +6958,12 @@
         <v>0.008576</v>
       </c>
       <c r="N125" s="1" t="n">
+        <v>0.008528000000000001</v>
+      </c>
+      <c r="O125" s="1" t="n">
         <v>0.008626999999999999</v>
       </c>
-      <c r="O125" s="1" t="n">
+      <c r="P125" s="1" t="n">
         <v>0.008168999999999999</v>
       </c>
     </row>
@@ -6632,9 +7010,12 @@
         <v>0.01628</v>
       </c>
       <c r="N126" s="1" t="n">
-        <v>0.01628</v>
+        <v>0.01635</v>
       </c>
       <c r="O126" s="1" t="n">
+        <v>0.01635</v>
+      </c>
+      <c r="P126" s="1" t="n">
         <v>0.01574</v>
       </c>
     </row>
@@ -6681,10 +7062,13 @@
         <v>0.04402</v>
       </c>
       <c r="N127" s="1" t="n">
+        <v>0.04387</v>
+      </c>
+      <c r="O127" s="1" t="n">
         <v>0.04468</v>
       </c>
-      <c r="O127" s="1" t="n">
-        <v>0.04394</v>
+      <c r="P127" s="1" t="n">
+        <v>0.04387</v>
       </c>
     </row>
     <row r="128">
@@ -6730,9 +7114,12 @@
         <v>0.04656</v>
       </c>
       <c r="N128" s="1" t="n">
+        <v>0.04657</v>
+      </c>
+      <c r="O128" s="1" t="n">
         <v>0.04727</v>
       </c>
-      <c r="O128" s="1" t="n">
+      <c r="P128" s="1" t="n">
         <v>0.04577</v>
       </c>
     </row>
@@ -6779,9 +7166,12 @@
         <v>0.09678</v>
       </c>
       <c r="N129" s="1" t="n">
+        <v>0.09606000000000001</v>
+      </c>
+      <c r="O129" s="1" t="n">
         <v>0.09680999999999999</v>
       </c>
-      <c r="O129" s="1" t="n">
+      <c r="P129" s="1" t="n">
         <v>0.09543</v>
       </c>
     </row>
@@ -6828,10 +7218,13 @@
         <v>0.09903000000000001</v>
       </c>
       <c r="N130" s="1" t="n">
+        <v>0.09846000000000001</v>
+      </c>
+      <c r="O130" s="1" t="n">
         <v>0.09927</v>
       </c>
-      <c r="O130" s="1" t="n">
-        <v>0.09848</v>
+      <c r="P130" s="1" t="n">
+        <v>0.09846000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -6877,9 +7270,12 @@
         <v>0.16644</v>
       </c>
       <c r="N131" s="1" t="n">
+        <v>0.16634</v>
+      </c>
+      <c r="O131" s="1" t="n">
         <v>0.16707</v>
       </c>
-      <c r="O131" s="1" t="n">
+      <c r="P131" s="1" t="n">
         <v>0.16444</v>
       </c>
     </row>
@@ -6926,9 +7322,12 @@
         <v>0.01706</v>
       </c>
       <c r="N132" s="1" t="n">
+        <v>0.01696</v>
+      </c>
+      <c r="O132" s="1" t="n">
         <v>0.01708</v>
       </c>
-      <c r="O132" s="1" t="n">
+      <c r="P132" s="1" t="n">
         <v>0.01678</v>
       </c>
     </row>
@@ -6975,9 +7374,12 @@
         <v>0.06721000000000001</v>
       </c>
       <c r="N133" s="1" t="n">
+        <v>0.06697</v>
+      </c>
+      <c r="O133" s="1" t="n">
         <v>0.06721000000000001</v>
       </c>
-      <c r="O133" s="1" t="n">
+      <c r="P133" s="1" t="n">
         <v>0.06635000000000001</v>
       </c>
     </row>
@@ -7024,9 +7426,12 @@
         <v>0.3038</v>
       </c>
       <c r="N134" s="1" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="O134" s="1" t="n">
         <v>0.3043</v>
       </c>
-      <c r="O134" s="1" t="n">
+      <c r="P134" s="1" t="n">
         <v>0.3008</v>
       </c>
     </row>
@@ -7073,9 +7478,12 @@
         <v>0.0454</v>
       </c>
       <c r="N135" s="1" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="O135" s="1" t="n">
         <v>0.04563</v>
       </c>
-      <c r="O135" s="1" t="n">
+      <c r="P135" s="1" t="n">
         <v>0.04502</v>
       </c>
     </row>
@@ -7122,9 +7530,12 @@
         <v>0.783</v>
       </c>
       <c r="N136" s="1" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="O136" s="1" t="n">
         <v>0.783</v>
       </c>
-      <c r="O136" s="1" t="n">
+      <c r="P136" s="1" t="n">
         <v>0.781</v>
       </c>
     </row>
@@ -7171,9 +7582,12 @@
         <v>0.1176</v>
       </c>
       <c r="N137" s="1" t="n">
+        <v>0.1172</v>
+      </c>
+      <c r="O137" s="1" t="n">
         <v>0.1181</v>
       </c>
-      <c r="O137" s="1" t="n">
+      <c r="P137" s="1" t="n">
         <v>0.1162</v>
       </c>
     </row>
@@ -7220,9 +7634,12 @@
         <v>0.14817</v>
       </c>
       <c r="N138" s="1" t="n">
-        <v>0.14817</v>
+        <v>0.1491</v>
       </c>
       <c r="O138" s="1" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="P138" s="1" t="n">
         <v>0.14528</v>
       </c>
     </row>
@@ -7269,9 +7686,12 @@
         <v>0.05787</v>
       </c>
       <c r="N139" s="1" t="n">
-        <v>0.05787</v>
+        <v>0.05799</v>
       </c>
       <c r="O139" s="1" t="n">
+        <v>0.05799</v>
+      </c>
+      <c r="P139" s="1" t="n">
         <v>0.05699</v>
       </c>
     </row>
@@ -7318,10 +7738,13 @@
         <v>0.007282</v>
       </c>
       <c r="N140" s="1" t="n">
+        <v>0.007252</v>
+      </c>
+      <c r="O140" s="1" t="n">
         <v>0.007302</v>
       </c>
-      <c r="O140" s="1" t="n">
-        <v>0.00726</v>
+      <c r="P140" s="1" t="n">
+        <v>0.007252</v>
       </c>
     </row>
     <row r="141">
@@ -7367,9 +7790,12 @@
         <v>0.09622</v>
       </c>
       <c r="N141" s="1" t="n">
+        <v>0.09594</v>
+      </c>
+      <c r="O141" s="1" t="n">
         <v>0.09637</v>
       </c>
-      <c r="O141" s="1" t="n">
+      <c r="P141" s="1" t="n">
         <v>0.09569</v>
       </c>
     </row>
@@ -7416,9 +7842,12 @@
         <v>0.08393</v>
       </c>
       <c r="N142" s="1" t="n">
+        <v>0.08348</v>
+      </c>
+      <c r="O142" s="1" t="n">
         <v>0.08393</v>
       </c>
-      <c r="O142" s="1" t="n">
+      <c r="P142" s="1" t="n">
         <v>0.08314000000000001</v>
       </c>
     </row>
@@ -7465,9 +7894,12 @@
         <v>0.008500000000000001</v>
       </c>
       <c r="N143" s="1" t="n">
+        <v>0.008489999999999999</v>
+      </c>
+      <c r="O143" s="1" t="n">
         <v>0.00861</v>
       </c>
-      <c r="O143" s="1" t="n">
+      <c r="P143" s="1" t="n">
         <v>0.00847</v>
       </c>
     </row>
@@ -7514,10 +7946,13 @@
         <v>0.07231</v>
       </c>
       <c r="N144" s="1" t="n">
+        <v>0.07219</v>
+      </c>
+      <c r="O144" s="1" t="n">
         <v>0.07288</v>
       </c>
-      <c r="O144" s="1" t="n">
-        <v>0.07224999999999999</v>
+      <c r="P144" s="1" t="n">
+        <v>0.07219</v>
       </c>
     </row>
     <row r="145">
@@ -7563,9 +7998,12 @@
         <v>0.426</v>
       </c>
       <c r="N145" s="1" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="O145" s="1" t="n">
         <v>0.4305</v>
       </c>
-      <c r="O145" s="1" t="n">
+      <c r="P145" s="1" t="n">
         <v>0.425</v>
       </c>
     </row>
@@ -7612,10 +8050,13 @@
         <v>0.03238</v>
       </c>
       <c r="N146" s="1" t="n">
+        <v>0.03206</v>
+      </c>
+      <c r="O146" s="1" t="n">
         <v>0.03276</v>
       </c>
-      <c r="O146" s="1" t="n">
-        <v>0.0322</v>
+      <c r="P146" s="1" t="n">
+        <v>0.03206</v>
       </c>
     </row>
     <row r="147">
@@ -7661,9 +8102,12 @@
         <v>390.58</v>
       </c>
       <c r="N147" s="1" t="n">
+        <v>390.51</v>
+      </c>
+      <c r="O147" s="1" t="n">
         <v>390.58</v>
       </c>
-      <c r="O147" s="1" t="n">
+      <c r="P147" s="1" t="n">
         <v>390.16</v>
       </c>
     </row>
@@ -7710,10 +8154,13 @@
         <v>0.03268</v>
       </c>
       <c r="N148" s="1" t="n">
+        <v>0.03264</v>
+      </c>
+      <c r="O148" s="1" t="n">
         <v>0.0333</v>
       </c>
-      <c r="O148" s="1" t="n">
-        <v>0.03268</v>
+      <c r="P148" s="1" t="n">
+        <v>0.03264</v>
       </c>
     </row>
     <row r="149">
@@ -7759,10 +8206,13 @@
         <v>0.05295</v>
       </c>
       <c r="N149" s="1" t="n">
+        <v>0.05278</v>
+      </c>
+      <c r="O149" s="1" t="n">
         <v>0.05322</v>
       </c>
-      <c r="O149" s="1" t="n">
-        <v>0.05289</v>
+      <c r="P149" s="1" t="n">
+        <v>0.05278</v>
       </c>
     </row>
     <row r="150">
@@ -7808,10 +8258,13 @@
         <v>0.0004377</v>
       </c>
       <c r="N150" s="1" t="n">
+        <v>0.0004358</v>
+      </c>
+      <c r="O150" s="1" t="n">
         <v>0.000443</v>
       </c>
-      <c r="O150" s="1" t="n">
-        <v>0.0004377</v>
+      <c r="P150" s="1" t="n">
+        <v>0.0004358</v>
       </c>
     </row>
     <row r="151">
@@ -7857,9 +8310,12 @@
         <v>0.02193</v>
       </c>
       <c r="N151" s="1" t="n">
+        <v>0.02187</v>
+      </c>
+      <c r="O151" s="1" t="n">
         <v>0.02197</v>
       </c>
-      <c r="O151" s="1" t="n">
+      <c r="P151" s="1" t="n">
         <v>0.02173</v>
       </c>
     </row>
@@ -7906,10 +8362,13 @@
         <v>0.00178</v>
       </c>
       <c r="N152" s="1" t="n">
+        <v>0.001767</v>
+      </c>
+      <c r="O152" s="1" t="n">
         <v>0.001793</v>
       </c>
-      <c r="O152" s="1" t="n">
-        <v>0.001768</v>
+      <c r="P152" s="1" t="n">
+        <v>0.001767</v>
       </c>
     </row>
     <row r="153">
@@ -7955,9 +8414,12 @@
         <v>6e-06</v>
       </c>
       <c r="N153" s="1" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="O153" s="1" t="n">
         <v>6.4e-06</v>
       </c>
-      <c r="O153" s="1" t="n">
+      <c r="P153" s="1" t="n">
         <v>6e-06</v>
       </c>
     </row>
@@ -8004,9 +8466,12 @@
         <v>0.1599</v>
       </c>
       <c r="N154" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="O154" s="1" t="n">
         <v>0.1609</v>
       </c>
-      <c r="O154" s="1" t="n">
+      <c r="P154" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -8053,9 +8518,12 @@
         <v>0.03781</v>
       </c>
       <c r="N155" s="1" t="n">
+        <v>0.03769</v>
+      </c>
+      <c r="O155" s="1" t="n">
         <v>0.03781</v>
       </c>
-      <c r="O155" s="1" t="n">
+      <c r="P155" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -8102,9 +8570,12 @@
         <v>0.005384</v>
       </c>
       <c r="N156" s="1" t="n">
+        <v>0.005369</v>
+      </c>
+      <c r="O156" s="1" t="n">
         <v>0.005404</v>
       </c>
-      <c r="O156" s="1" t="n">
+      <c r="P156" s="1" t="n">
         <v>0.005364</v>
       </c>
     </row>
@@ -8151,9 +8622,12 @@
         <v>0.02289</v>
       </c>
       <c r="N157" s="1" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="O157" s="1" t="n">
         <v>0.02294</v>
       </c>
-      <c r="O157" s="1" t="n">
+      <c r="P157" s="1" t="n">
         <v>0.02263</v>
       </c>
     </row>
@@ -8200,9 +8674,12 @@
         <v>1.101</v>
       </c>
       <c r="N158" s="1" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="O158" s="1" t="n">
         <v>1.101</v>
       </c>
-      <c r="O158" s="1" t="n">
+      <c r="P158" s="1" t="n">
         <v>1.086</v>
       </c>
     </row>
@@ -8249,9 +8726,12 @@
         <v>2.572</v>
       </c>
       <c r="N159" s="1" t="n">
+        <v>2.564</v>
+      </c>
+      <c r="O159" s="1" t="n">
         <v>2.577</v>
       </c>
-      <c r="O159" s="1" t="n">
+      <c r="P159" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -8298,10 +8778,13 @@
         <v>4.846</v>
       </c>
       <c r="N160" s="1" t="n">
+        <v>4.825</v>
+      </c>
+      <c r="O160" s="1" t="n">
         <v>4.858</v>
       </c>
-      <c r="O160" s="1" t="n">
-        <v>4.836</v>
+      <c r="P160" s="1" t="n">
+        <v>4.825</v>
       </c>
     </row>
     <row r="161">
@@ -8347,9 +8830,12 @@
         <v>0.1608</v>
       </c>
       <c r="N161" s="1" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="O161" s="1" t="n">
         <v>0.1608</v>
       </c>
-      <c r="O161" s="1" t="n">
+      <c r="P161" s="1" t="n">
         <v>0.159</v>
       </c>
     </row>
@@ -8396,10 +8882,13 @@
         <v>0.20382</v>
       </c>
       <c r="N162" s="1" t="n">
+        <v>0.20101</v>
+      </c>
+      <c r="O162" s="1" t="n">
         <v>0.20754</v>
       </c>
-      <c r="O162" s="1" t="n">
-        <v>0.20382</v>
+      <c r="P162" s="1" t="n">
+        <v>0.20101</v>
       </c>
     </row>
     <row r="163">
@@ -8445,9 +8934,12 @@
         <v>0.03948</v>
       </c>
       <c r="N163" s="1" t="n">
+        <v>0.03928</v>
+      </c>
+      <c r="O163" s="1" t="n">
         <v>0.03955</v>
       </c>
-      <c r="O163" s="1" t="n">
+      <c r="P163" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -8494,9 +8986,12 @@
         <v>0.06325</v>
       </c>
       <c r="N164" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="O164" s="1" t="n">
         <v>0.0636</v>
       </c>
-      <c r="O164" s="1" t="n">
+      <c r="P164" s="1" t="n">
         <v>0.06271</v>
       </c>
     </row>
@@ -8543,9 +9038,12 @@
         <v>0.3674</v>
       </c>
       <c r="N165" s="1" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="O165" s="1" t="n">
         <v>0.3674</v>
       </c>
-      <c r="O165" s="1" t="n">
+      <c r="P165" s="1" t="n">
         <v>0.3525</v>
       </c>
     </row>
@@ -8592,9 +9090,12 @@
         <v>139.48</v>
       </c>
       <c r="N166" s="1" t="n">
+        <v>138.95</v>
+      </c>
+      <c r="O166" s="1" t="n">
         <v>139.63</v>
       </c>
-      <c r="O166" s="1" t="n">
+      <c r="P166" s="1" t="n">
         <v>138.82</v>
       </c>
     </row>
@@ -8641,10 +9142,13 @@
         <v>0.0006414</v>
       </c>
       <c r="N167" s="1" t="n">
+        <v>0.000641</v>
+      </c>
+      <c r="O167" s="1" t="n">
         <v>0.0006533</v>
       </c>
-      <c r="O167" s="1" t="n">
-        <v>0.0006414</v>
+      <c r="P167" s="1" t="n">
+        <v>0.000641</v>
       </c>
     </row>
     <row r="168">
@@ -8690,9 +9194,12 @@
         <v>0.01648</v>
       </c>
       <c r="N168" s="1" t="n">
+        <v>0.01642</v>
+      </c>
+      <c r="O168" s="1" t="n">
         <v>0.01678</v>
       </c>
-      <c r="O168" s="1" t="n">
+      <c r="P168" s="1" t="n">
         <v>0.01629</v>
       </c>
     </row>
@@ -8739,9 +9246,12 @@
         <v>0.04824</v>
       </c>
       <c r="N169" s="1" t="n">
+        <v>0.04803</v>
+      </c>
+      <c r="O169" s="1" t="n">
         <v>0.04824</v>
       </c>
-      <c r="O169" s="1" t="n">
+      <c r="P169" s="1" t="n">
         <v>0.04785</v>
       </c>
     </row>
@@ -8788,10 +9298,13 @@
         <v>4.272</v>
       </c>
       <c r="N170" s="1" t="n">
+        <v>4.263</v>
+      </c>
+      <c r="O170" s="1" t="n">
         <v>4.298</v>
       </c>
-      <c r="O170" s="1" t="n">
-        <v>4.265</v>
+      <c r="P170" s="1" t="n">
+        <v>4.263</v>
       </c>
     </row>
     <row r="171">
@@ -8837,9 +9350,12 @@
         <v>0.03862</v>
       </c>
       <c r="N171" s="1" t="n">
+        <v>0.03838</v>
+      </c>
+      <c r="O171" s="1" t="n">
         <v>0.03875</v>
       </c>
-      <c r="O171" s="1" t="n">
+      <c r="P171" s="1" t="n">
         <v>0.03825</v>
       </c>
     </row>
@@ -8886,9 +9402,12 @@
         <v>0.0432</v>
       </c>
       <c r="N172" s="1" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="O172" s="1" t="n">
         <v>0.0432</v>
       </c>
-      <c r="O172" s="1" t="n">
+      <c r="P172" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -8935,9 +9454,12 @@
         <v>0.023863</v>
       </c>
       <c r="N173" s="1" t="n">
+        <v>0.023876</v>
+      </c>
+      <c r="O173" s="1" t="n">
         <v>0.024556</v>
       </c>
-      <c r="O173" s="1" t="n">
+      <c r="P173" s="1" t="n">
         <v>0.02354</v>
       </c>
     </row>
@@ -8984,9 +9506,12 @@
         <v>1.0794</v>
       </c>
       <c r="N174" s="1" t="n">
-        <v>1.0809</v>
+        <v>1.0812</v>
       </c>
       <c r="O174" s="1" t="n">
+        <v>1.0812</v>
+      </c>
+      <c r="P174" s="1" t="n">
         <v>1.0704</v>
       </c>
     </row>
@@ -9033,10 +9558,13 @@
         <v>0.028024</v>
       </c>
       <c r="N175" s="1" t="n">
+        <v>0.027517</v>
+      </c>
+      <c r="O175" s="1" t="n">
         <v>0.028967</v>
       </c>
-      <c r="O175" s="1" t="n">
-        <v>0.028008</v>
+      <c r="P175" s="1" t="n">
+        <v>0.027517</v>
       </c>
     </row>
     <row r="176">
@@ -9082,9 +9610,12 @@
         <v>0.0222</v>
       </c>
       <c r="N176" s="1" t="n">
+        <v>0.02194</v>
+      </c>
+      <c r="O176" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="O176" s="1" t="n">
+      <c r="P176" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -9131,9 +9662,12 @@
         <v>0.5507</v>
       </c>
       <c r="N177" s="1" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="O177" s="1" t="n">
         <v>0.5507</v>
       </c>
-      <c r="O177" s="1" t="n">
+      <c r="P177" s="1" t="n">
         <v>0.5416</v>
       </c>
     </row>
@@ -9180,10 +9714,13 @@
         <v>0.08202</v>
       </c>
       <c r="N178" s="1" t="n">
+        <v>0.08176</v>
+      </c>
+      <c r="O178" s="1" t="n">
         <v>0.08276</v>
       </c>
-      <c r="O178" s="1" t="n">
-        <v>0.08202</v>
+      <c r="P178" s="1" t="n">
+        <v>0.08176</v>
       </c>
     </row>
     <row r="179">
@@ -9229,9 +9766,12 @@
         <v>0.02152</v>
       </c>
       <c r="N179" s="1" t="n">
+        <v>0.02136</v>
+      </c>
+      <c r="O179" s="1" t="n">
         <v>0.02152</v>
       </c>
-      <c r="O179" s="1" t="n">
+      <c r="P179" s="1" t="n">
         <v>0.02119</v>
       </c>
     </row>
@@ -9278,9 +9818,12 @@
         <v>0.27202</v>
       </c>
       <c r="N180" s="1" t="n">
+        <v>0.27016</v>
+      </c>
+      <c r="O180" s="1" t="n">
         <v>0.27464</v>
       </c>
-      <c r="O180" s="1" t="n">
+      <c r="P180" s="1" t="n">
         <v>0.26951</v>
       </c>
     </row>
@@ -9327,9 +9870,12 @@
         <v>0.00423</v>
       </c>
       <c r="N181" s="1" t="n">
+        <v>0.00421</v>
+      </c>
+      <c r="O181" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="O181" s="1" t="n">
+      <c r="P181" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -9376,9 +9922,12 @@
         <v>0.07914</v>
       </c>
       <c r="N182" s="1" t="n">
+        <v>0.07924</v>
+      </c>
+      <c r="O182" s="1" t="n">
         <v>0.07981000000000001</v>
       </c>
-      <c r="O182" s="1" t="n">
+      <c r="P182" s="1" t="n">
         <v>0.07901</v>
       </c>
     </row>
@@ -9425,9 +9974,12 @@
         <v>0.02363</v>
       </c>
       <c r="N183" s="1" t="n">
+        <v>0.02338</v>
+      </c>
+      <c r="O183" s="1" t="n">
         <v>0.02369</v>
       </c>
-      <c r="O183" s="1" t="n">
+      <c r="P183" s="1" t="n">
         <v>0.02334</v>
       </c>
     </row>
@@ -9474,10 +10026,13 @@
         <v>6.991e-05</v>
       </c>
       <c r="N184" s="1" t="n">
+        <v>6.944999999999999e-05</v>
+      </c>
+      <c r="O184" s="1" t="n">
         <v>7.016000000000001e-05</v>
       </c>
-      <c r="O184" s="1" t="n">
-        <v>6.957e-05</v>
+      <c r="P184" s="1" t="n">
+        <v>6.944999999999999e-05</v>
       </c>
     </row>
     <row r="185">
@@ -9523,9 +10078,12 @@
         <v>0.02135</v>
       </c>
       <c r="N185" s="1" t="n">
+        <v>0.02133</v>
+      </c>
+      <c r="O185" s="1" t="n">
         <v>0.0214</v>
       </c>
-      <c r="O185" s="1" t="n">
+      <c r="P185" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -9572,9 +10130,12 @@
         <v>0.01637</v>
       </c>
       <c r="N186" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="O186" s="1" t="n">
         <v>0.01644</v>
       </c>
-      <c r="O186" s="1" t="n">
+      <c r="P186" s="1" t="n">
         <v>0.01623</v>
       </c>
     </row>
@@ -9621,10 +10182,13 @@
         <v>0.978</v>
       </c>
       <c r="N187" s="1" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O187" s="1" t="n">
         <v>0.981</v>
       </c>
-      <c r="O187" s="1" t="n">
-        <v>0.971</v>
+      <c r="P187" s="1" t="n">
+        <v>0.97</v>
       </c>
     </row>
     <row r="188">
@@ -9670,10 +10234,13 @@
         <v>0.0238</v>
       </c>
       <c r="N188" s="1" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="O188" s="1" t="n">
         <v>0.024</v>
       </c>
-      <c r="O188" s="1" t="n">
-        <v>0.0237</v>
+      <c r="P188" s="1" t="n">
+        <v>0.0236</v>
       </c>
     </row>
     <row r="189">
@@ -9719,9 +10286,12 @@
         <v>1.8941</v>
       </c>
       <c r="N189" s="1" t="n">
-        <v>1.8941</v>
+        <v>1.8951</v>
       </c>
       <c r="O189" s="1" t="n">
+        <v>1.8951</v>
+      </c>
+      <c r="P189" s="1" t="n">
         <v>1.8609</v>
       </c>
     </row>
@@ -9768,9 +10338,12 @@
         <v>1.843</v>
       </c>
       <c r="N190" s="1" t="n">
+        <v>1.834</v>
+      </c>
+      <c r="O190" s="1" t="n">
         <v>1.844</v>
       </c>
-      <c r="O190" s="1" t="n">
+      <c r="P190" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -9817,9 +10390,12 @@
         <v>0.02677</v>
       </c>
       <c r="N191" s="1" t="n">
+        <v>0.02662</v>
+      </c>
+      <c r="O191" s="1" t="n">
         <v>0.02685</v>
       </c>
-      <c r="O191" s="1" t="n">
+      <c r="P191" s="1" t="n">
         <v>0.02662</v>
       </c>
     </row>
@@ -9866,9 +10442,12 @@
         <v>0.0978</v>
       </c>
       <c r="N192" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="O192" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="O192" s="1" t="n">
+      <c r="P192" s="1" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -9915,9 +10494,12 @@
         <v>0.171</v>
       </c>
       <c r="N193" s="1" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="O193" s="1" t="n">
         <v>0.1722</v>
       </c>
-      <c r="O193" s="1" t="n">
+      <c r="P193" s="1" t="n">
         <v>0.1668</v>
       </c>
     </row>
@@ -9964,9 +10546,12 @@
         <v>16.374</v>
       </c>
       <c r="N194" s="1" t="n">
+        <v>16.313</v>
+      </c>
+      <c r="O194" s="1" t="n">
         <v>16.407</v>
       </c>
-      <c r="O194" s="1" t="n">
+      <c r="P194" s="1" t="n">
         <v>16.237</v>
       </c>
     </row>
@@ -10013,10 +10598,13 @@
         <v>4.102</v>
       </c>
       <c r="N195" s="1" t="n">
+        <v>4.076</v>
+      </c>
+      <c r="O195" s="1" t="n">
         <v>4.136</v>
       </c>
-      <c r="O195" s="1" t="n">
-        <v>4.087</v>
+      <c r="P195" s="1" t="n">
+        <v>4.076</v>
       </c>
     </row>
     <row r="196">
@@ -10062,9 +10650,12 @@
         <v>1.2802</v>
       </c>
       <c r="N196" s="1" t="n">
+        <v>1.2709</v>
+      </c>
+      <c r="O196" s="1" t="n">
         <v>1.2802</v>
       </c>
-      <c r="O196" s="1" t="n">
+      <c r="P196" s="1" t="n">
         <v>1.2663</v>
       </c>
     </row>
@@ -10111,9 +10702,12 @@
         <v>3.112</v>
       </c>
       <c r="N197" s="1" t="n">
+        <v>3.096</v>
+      </c>
+      <c r="O197" s="1" t="n">
         <v>3.112</v>
       </c>
-      <c r="O197" s="1" t="n">
+      <c r="P197" s="1" t="n">
         <v>3.063</v>
       </c>
     </row>
@@ -10160,10 +10754,13 @@
         <v>0.01257</v>
       </c>
       <c r="N198" s="1" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="O198" s="1" t="n">
         <v>0.01266</v>
       </c>
-      <c r="O198" s="1" t="n">
-        <v>0.01257</v>
+      <c r="P198" s="1" t="n">
+        <v>0.0125</v>
       </c>
     </row>
     <row r="199">
@@ -10209,9 +10806,12 @@
         <v>0.0001766</v>
       </c>
       <c r="N199" s="1" t="n">
+        <v>0.0001762</v>
+      </c>
+      <c r="O199" s="1" t="n">
         <v>0.000177</v>
       </c>
-      <c r="O199" s="1" t="n">
+      <c r="P199" s="1" t="n">
         <v>0.0001756</v>
       </c>
     </row>
@@ -10258,9 +10858,12 @@
         <v>115.89</v>
       </c>
       <c r="N200" s="1" t="n">
+        <v>115.45</v>
+      </c>
+      <c r="O200" s="1" t="n">
         <v>115.89</v>
       </c>
-      <c r="O200" s="1" t="n">
+      <c r="P200" s="1" t="n">
         <v>115.11</v>
       </c>
     </row>
@@ -10307,10 +10910,13 @@
         <v>0.01019</v>
       </c>
       <c r="N201" s="1" t="n">
+        <v>0.01018</v>
+      </c>
+      <c r="O201" s="1" t="n">
         <v>0.01031</v>
       </c>
-      <c r="O201" s="1" t="n">
-        <v>0.01019</v>
+      <c r="P201" s="1" t="n">
+        <v>0.01018</v>
       </c>
     </row>
     <row r="202">
@@ -10356,9 +10962,12 @@
         <v>0.01063</v>
       </c>
       <c r="N202" s="1" t="n">
+        <v>0.01064</v>
+      </c>
+      <c r="O202" s="1" t="n">
         <v>0.01073</v>
       </c>
-      <c r="O202" s="1" t="n">
+      <c r="P202" s="1" t="n">
         <v>0.01061</v>
       </c>
     </row>
@@ -10405,9 +11014,12 @@
         <v>0.003147</v>
       </c>
       <c r="N203" s="1" t="n">
+        <v>0.003143</v>
+      </c>
+      <c r="O203" s="1" t="n">
         <v>0.003153</v>
       </c>
-      <c r="O203" s="1" t="n">
+      <c r="P203" s="1" t="n">
         <v>0.003131</v>
       </c>
     </row>
@@ -10454,10 +11066,13 @@
         <v>28.37</v>
       </c>
       <c r="N204" s="1" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="O204" s="1" t="n">
         <v>28.39</v>
       </c>
-      <c r="O204" s="1" t="n">
-        <v>28.23</v>
+      <c r="P204" s="1" t="n">
+        <v>28.21</v>
       </c>
     </row>
     <row r="205">
@@ -10503,10 +11118,13 @@
         <v>0.5579</v>
       </c>
       <c r="N205" s="1" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="O205" s="1" t="n">
         <v>0.5636</v>
       </c>
-      <c r="O205" s="1" t="n">
-        <v>0.5578</v>
+      <c r="P205" s="1" t="n">
+        <v>0.5575</v>
       </c>
     </row>
     <row r="206">
@@ -10552,9 +11170,12 @@
         <v>0.0004421</v>
       </c>
       <c r="N206" s="1" t="n">
+        <v>0.0004396</v>
+      </c>
+      <c r="O206" s="1" t="n">
         <v>0.0004438</v>
       </c>
-      <c r="O206" s="1" t="n">
+      <c r="P206" s="1" t="n">
         <v>0.0004387</v>
       </c>
     </row>
@@ -10601,10 +11222,13 @@
         <v>0.04674</v>
       </c>
       <c r="N207" s="1" t="n">
+        <v>0.04646</v>
+      </c>
+      <c r="O207" s="1" t="n">
         <v>0.04689</v>
       </c>
-      <c r="O207" s="1" t="n">
-        <v>0.04648</v>
+      <c r="P207" s="1" t="n">
+        <v>0.04646</v>
       </c>
     </row>
     <row r="208">
@@ -10650,9 +11274,12 @@
         <v>0.09</v>
       </c>
       <c r="N208" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="O208" s="1" t="n">
         <v>0.091</v>
       </c>
-      <c r="O208" s="1" t="n">
+      <c r="P208" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -10699,9 +11326,12 @@
         <v>0.02577</v>
       </c>
       <c r="N209" s="1" t="n">
+        <v>0.02573</v>
+      </c>
+      <c r="O209" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="O209" s="1" t="n">
+      <c r="P209" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -10748,10 +11378,13 @@
         <v>0.012681</v>
       </c>
       <c r="N210" s="1" t="n">
+        <v>0.012597</v>
+      </c>
+      <c r="O210" s="1" t="n">
         <v>0.012745</v>
       </c>
-      <c r="O210" s="1" t="n">
-        <v>0.012645</v>
+      <c r="P210" s="1" t="n">
+        <v>0.012597</v>
       </c>
     </row>
     <row r="211">
@@ -10797,9 +11430,12 @@
         <v>0.0921</v>
       </c>
       <c r="N211" s="1" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="O211" s="1" t="n">
         <v>0.0921</v>
       </c>
-      <c r="O211" s="1" t="n">
+      <c r="P211" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -10846,10 +11482,13 @@
         <v>0.007076</v>
       </c>
       <c r="N212" s="1" t="n">
+        <v>0.007031</v>
+      </c>
+      <c r="O212" s="1" t="n">
         <v>0.007076</v>
       </c>
-      <c r="O212" s="1" t="n">
-        <v>0.007038</v>
+      <c r="P212" s="1" t="n">
+        <v>0.007031</v>
       </c>
     </row>
     <row r="213">
@@ -10895,9 +11534,12 @@
         <v>0.0297</v>
       </c>
       <c r="N213" s="1" t="n">
+        <v>0.02952</v>
+      </c>
+      <c r="O213" s="1" t="n">
         <v>0.02978</v>
       </c>
-      <c r="O213" s="1" t="n">
+      <c r="P213" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -10944,9 +11586,12 @@
         <v>0.2699</v>
       </c>
       <c r="N214" s="1" t="n">
+        <v>0.2708</v>
+      </c>
+      <c r="O214" s="1" t="n">
         <v>0.271</v>
       </c>
-      <c r="O214" s="1" t="n">
+      <c r="P214" s="1" t="n">
         <v>0.2698</v>
       </c>
     </row>
@@ -10993,9 +11638,12 @@
         <v>0.02232</v>
       </c>
       <c r="N215" s="1" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="O215" s="1" t="n">
         <v>0.02256</v>
       </c>
-      <c r="O215" s="1" t="n">
+      <c r="P215" s="1" t="n">
         <v>0.02158</v>
       </c>
     </row>
@@ -11042,10 +11690,13 @@
         <v>0.01464</v>
       </c>
       <c r="N216" s="1" t="n">
+        <v>0.01461</v>
+      </c>
+      <c r="O216" s="1" t="n">
         <v>0.01492</v>
       </c>
-      <c r="O216" s="1" t="n">
-        <v>0.01463</v>
+      <c r="P216" s="1" t="n">
+        <v>0.01461</v>
       </c>
     </row>
     <row r="217">
@@ -11091,9 +11742,12 @@
         <v>0.2548</v>
       </c>
       <c r="N217" s="1" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="O217" s="1" t="n">
         <v>0.255</v>
       </c>
-      <c r="O217" s="1" t="n">
+      <c r="P217" s="1" t="n">
         <v>0.2532</v>
       </c>
     </row>
@@ -11140,9 +11794,12 @@
         <v>0.3115</v>
       </c>
       <c r="N218" s="1" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="O218" s="1" t="n">
         <v>0.3116</v>
       </c>
-      <c r="O218" s="1" t="n">
+      <c r="P218" s="1" t="n">
         <v>0.3065</v>
       </c>
     </row>
@@ -11189,9 +11846,12 @@
         <v>0.1786</v>
       </c>
       <c r="N219" s="1" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="O219" s="1" t="n">
         <v>0.179</v>
       </c>
-      <c r="O219" s="1" t="n">
+      <c r="P219" s="1" t="n">
         <v>0.1773</v>
       </c>
     </row>
@@ -11238,9 +11898,12 @@
         <v>15</v>
       </c>
       <c r="N220" s="1" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="O220" s="1" t="n">
         <v>15.02</v>
       </c>
-      <c r="O220" s="1" t="n">
+      <c r="P220" s="1" t="n">
         <v>14.95</v>
       </c>
     </row>
@@ -11290,6 +11953,9 @@
         <v>0.01614</v>
       </c>
       <c r="O221" s="1" t="n">
+        <v>0.01614</v>
+      </c>
+      <c r="P221" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -11336,10 +12002,13 @@
         <v>66.09999999999999</v>
       </c>
       <c r="N222" s="1" t="n">
+        <v>65.93000000000001</v>
+      </c>
+      <c r="O222" s="1" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="O222" s="1" t="n">
-        <v>66.09999999999999</v>
+      <c r="P222" s="1" t="n">
+        <v>65.93000000000001</v>
       </c>
     </row>
     <row r="223">
@@ -11385,9 +12054,12 @@
         <v>0.09428</v>
       </c>
       <c r="N223" s="1" t="n">
+        <v>0.09422999999999999</v>
+      </c>
+      <c r="O223" s="1" t="n">
         <v>0.09428</v>
       </c>
-      <c r="O223" s="1" t="n">
+      <c r="P223" s="1" t="n">
         <v>0.09203</v>
       </c>
     </row>
@@ -11434,9 +12106,12 @@
         <v>0.03985</v>
       </c>
       <c r="N224" s="1" t="n">
+        <v>0.03974</v>
+      </c>
+      <c r="O224" s="1" t="n">
         <v>0.03993</v>
       </c>
-      <c r="O224" s="1" t="n">
+      <c r="P224" s="1" t="n">
         <v>0.03913</v>
       </c>
     </row>
@@ -11483,10 +12158,13 @@
         <v>0.5711000000000001</v>
       </c>
       <c r="N225" s="1" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="O225" s="1" t="n">
         <v>0.5725</v>
       </c>
-      <c r="O225" s="1" t="n">
-        <v>0.5695</v>
+      <c r="P225" s="1" t="n">
+        <v>0.5682</v>
       </c>
     </row>
     <row r="226">
@@ -11532,9 +12210,12 @@
         <v>0.1176</v>
       </c>
       <c r="N226" s="1" t="n">
+        <v>0.1172</v>
+      </c>
+      <c r="O226" s="1" t="n">
         <v>0.1184</v>
       </c>
-      <c r="O226" s="1" t="n">
+      <c r="P226" s="1" t="n">
         <v>0.1166</v>
       </c>
     </row>
@@ -11581,10 +12262,13 @@
         <v>0.3162</v>
       </c>
       <c r="N227" s="1" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="O227" s="1" t="n">
         <v>0.3201</v>
       </c>
-      <c r="O227" s="1" t="n">
-        <v>0.3162</v>
+      <c r="P227" s="1" t="n">
+        <v>0.3139</v>
       </c>
     </row>
     <row r="228">
@@ -11630,9 +12314,12 @@
         <v>6.112</v>
       </c>
       <c r="N228" s="1" t="n">
+        <v>6.073</v>
+      </c>
+      <c r="O228" s="1" t="n">
         <v>6.112</v>
       </c>
-      <c r="O228" s="1" t="n">
+      <c r="P228" s="1" t="n">
         <v>6.062</v>
       </c>
     </row>
@@ -11679,9 +12366,12 @@
         <v>0.0291</v>
       </c>
       <c r="N229" s="1" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="O229" s="1" t="n">
         <v>0.0294</v>
       </c>
-      <c r="O229" s="1" t="n">
+      <c r="P229" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
@@ -11728,9 +12418,12 @@
         <v>0.3318</v>
       </c>
       <c r="N230" s="1" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="O230" s="1" t="n">
         <v>0.3325</v>
       </c>
-      <c r="O230" s="1" t="n">
+      <c r="P230" s="1" t="n">
         <v>0.3288</v>
       </c>
     </row>
@@ -11777,9 +12470,12 @@
         <v>0.12016</v>
       </c>
       <c r="N231" s="1" t="n">
+        <v>0.12005</v>
+      </c>
+      <c r="O231" s="1" t="n">
         <v>0.12089</v>
       </c>
-      <c r="O231" s="1" t="n">
+      <c r="P231" s="1" t="n">
         <v>0.11986</v>
       </c>
     </row>
@@ -11826,9 +12522,12 @@
         <v>0.1194</v>
       </c>
       <c r="N232" s="1" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="O232" s="1" t="n">
         <v>0.1204</v>
       </c>
-      <c r="O232" s="1" t="n">
+      <c r="P232" s="1" t="n">
         <v>0.1182</v>
       </c>
     </row>
@@ -11875,9 +12574,12 @@
         <v>0.0303</v>
       </c>
       <c r="N233" s="1" t="n">
+        <v>0.03019</v>
+      </c>
+      <c r="O233" s="1" t="n">
         <v>0.03039</v>
       </c>
-      <c r="O233" s="1" t="n">
+      <c r="P233" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -11924,10 +12626,13 @@
         <v>0.015234</v>
       </c>
       <c r="N234" s="1" t="n">
+        <v>0.015102</v>
+      </c>
+      <c r="O234" s="1" t="n">
         <v>0.016171</v>
       </c>
-      <c r="O234" s="1" t="n">
-        <v>0.015234</v>
+      <c r="P234" s="1" t="n">
+        <v>0.015102</v>
       </c>
     </row>
     <row r="235">
@@ -11973,9 +12678,12 @@
         <v>0.01261</v>
       </c>
       <c r="N235" s="1" t="n">
+        <v>0.01262</v>
+      </c>
+      <c r="O235" s="1" t="n">
         <v>0.01281</v>
       </c>
-      <c r="O235" s="1" t="n">
+      <c r="P235" s="1" t="n">
         <v>0.01261</v>
       </c>
     </row>
@@ -12022,9 +12730,12 @@
         <v>0.01943</v>
       </c>
       <c r="N236" s="1" t="n">
+        <v>0.01937</v>
+      </c>
+      <c r="O236" s="1" t="n">
         <v>0.01943</v>
       </c>
-      <c r="O236" s="1" t="n">
+      <c r="P236" s="1" t="n">
         <v>0.01924</v>
       </c>
     </row>
@@ -12071,9 +12782,12 @@
         <v>0.08604000000000001</v>
       </c>
       <c r="N237" s="1" t="n">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="O237" s="1" t="n">
         <v>0.08604000000000001</v>
       </c>
-      <c r="O237" s="1" t="n">
+      <c r="P237" s="1" t="n">
         <v>0.08427999999999999</v>
       </c>
     </row>
@@ -12120,10 +12834,13 @@
         <v>0.05874</v>
       </c>
       <c r="N238" s="1" t="n">
+        <v>0.05847</v>
+      </c>
+      <c r="O238" s="1" t="n">
         <v>0.05892</v>
       </c>
-      <c r="O238" s="1" t="n">
-        <v>0.05852</v>
+      <c r="P238" s="1" t="n">
+        <v>0.05847</v>
       </c>
     </row>
     <row r="239">
@@ -12169,9 +12886,12 @@
         <v>0.009039</v>
       </c>
       <c r="N239" s="1" t="n">
+        <v>0.009004</v>
+      </c>
+      <c r="O239" s="1" t="n">
         <v>0.009131999999999999</v>
       </c>
-      <c r="O239" s="1" t="n">
+      <c r="P239" s="1" t="n">
         <v>0.008954</v>
       </c>
     </row>
@@ -12218,9 +12938,12 @@
         <v>0.004204</v>
       </c>
       <c r="N240" s="1" t="n">
+        <v>0.004193</v>
+      </c>
+      <c r="O240" s="1" t="n">
         <v>0.004204</v>
       </c>
-      <c r="O240" s="1" t="n">
+      <c r="P240" s="1" t="n">
         <v>0.004154</v>
       </c>
     </row>
@@ -12267,9 +12990,12 @@
         <v>0.2436</v>
       </c>
       <c r="N241" s="1" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="O241" s="1" t="n">
         <v>0.2436</v>
       </c>
-      <c r="O241" s="1" t="n">
+      <c r="P241" s="1" t="n">
         <v>0.2392</v>
       </c>
     </row>
@@ -12316,9 +13042,12 @@
         <v>0.0584</v>
       </c>
       <c r="N242" s="1" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="O242" s="1" t="n">
         <v>0.0589</v>
       </c>
-      <c r="O242" s="1" t="n">
+      <c r="P242" s="1" t="n">
         <v>0.058</v>
       </c>
     </row>
@@ -12365,9 +13094,12 @@
         <v>0.0235</v>
       </c>
       <c r="N243" s="1" t="n">
+        <v>0.02345</v>
+      </c>
+      <c r="O243" s="1" t="n">
         <v>0.02363</v>
       </c>
-      <c r="O243" s="1" t="n">
+      <c r="P243" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -12414,9 +13146,12 @@
         <v>0.056</v>
       </c>
       <c r="N244" s="1" t="n">
+        <v>0.05557</v>
+      </c>
+      <c r="O244" s="1" t="n">
         <v>0.05671</v>
       </c>
-      <c r="O244" s="1" t="n">
+      <c r="P244" s="1" t="n">
         <v>0.05547</v>
       </c>
     </row>
@@ -12463,9 +13198,12 @@
         <v>0.03495</v>
       </c>
       <c r="N245" s="1" t="n">
+        <v>0.03467</v>
+      </c>
+      <c r="O245" s="1" t="n">
         <v>0.03499</v>
       </c>
-      <c r="O245" s="1" t="n">
+      <c r="P245" s="1" t="n">
         <v>0.03414</v>
       </c>
     </row>
@@ -12512,9 +13250,12 @@
         <v>0.06023</v>
       </c>
       <c r="N246" s="1" t="n">
+        <v>0.05994</v>
+      </c>
+      <c r="O246" s="1" t="n">
         <v>0.0604</v>
       </c>
-      <c r="O246" s="1" t="n">
+      <c r="P246" s="1" t="n">
         <v>0.0599</v>
       </c>
     </row>
@@ -12561,10 +13302,13 @@
         <v>0.382</v>
       </c>
       <c r="N247" s="1" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="O247" s="1" t="n">
         <v>0.385</v>
       </c>
-      <c r="O247" s="1" t="n">
-        <v>0.382</v>
+      <c r="P247" s="1" t="n">
+        <v>0.381</v>
       </c>
     </row>
     <row r="248">
@@ -12610,9 +13354,12 @@
         <v>0.5223</v>
       </c>
       <c r="N248" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O248" s="1" t="n">
         <v>0.5233</v>
       </c>
-      <c r="O248" s="1" t="n">
+      <c r="P248" s="1" t="n">
         <v>0.5167</v>
       </c>
     </row>
@@ -12662,6 +13409,9 @@
         <v>0.02884</v>
       </c>
       <c r="O249" s="1" t="n">
+        <v>0.02884</v>
+      </c>
+      <c r="P249" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -12708,9 +13458,12 @@
         <v>0.0132</v>
       </c>
       <c r="N250" s="1" t="n">
-        <v>0.0132</v>
+        <v>0.01322</v>
       </c>
       <c r="O250" s="1" t="n">
+        <v>0.01322</v>
+      </c>
+      <c r="P250" s="1" t="n">
         <v>0.01288</v>
       </c>
     </row>
@@ -12757,9 +13510,12 @@
         <v>0.1005</v>
       </c>
       <c r="N251" s="1" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="O251" s="1" t="n">
         <v>0.1006</v>
       </c>
-      <c r="O251" s="1" t="n">
+      <c r="P251" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -12806,10 +13562,13 @@
         <v>0.00717</v>
       </c>
       <c r="N252" s="1" t="n">
+        <v>0.00713</v>
+      </c>
+      <c r="O252" s="1" t="n">
         <v>0.00719</v>
       </c>
-      <c r="O252" s="1" t="n">
-        <v>0.00714</v>
+      <c r="P252" s="1" t="n">
+        <v>0.00713</v>
       </c>
     </row>
     <row r="253">
@@ -12855,10 +13614,13 @@
         <v>0.005543</v>
       </c>
       <c r="N253" s="1" t="n">
+        <v>0.005542</v>
+      </c>
+      <c r="O253" s="1" t="n">
         <v>0.005571</v>
       </c>
-      <c r="O253" s="1" t="n">
-        <v>0.005543</v>
+      <c r="P253" s="1" t="n">
+        <v>0.005542</v>
       </c>
     </row>
     <row r="254">
@@ -12904,10 +13666,13 @@
         <v>0.0643</v>
       </c>
       <c r="N254" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="O254" s="1" t="n">
         <v>0.0646</v>
       </c>
-      <c r="O254" s="1" t="n">
-        <v>0.0641</v>
+      <c r="P254" s="1" t="n">
+        <v>0.064</v>
       </c>
     </row>
     <row r="255">
@@ -12953,9 +13718,12 @@
         <v>0.01433</v>
       </c>
       <c r="N255" s="1" t="n">
+        <v>0.01427</v>
+      </c>
+      <c r="O255" s="1" t="n">
         <v>0.01454</v>
       </c>
-      <c r="O255" s="1" t="n">
+      <c r="P255" s="1" t="n">
         <v>0.01425</v>
       </c>
     </row>
@@ -13002,9 +13770,12 @@
         <v>0.9992760000000001</v>
       </c>
       <c r="N256" s="1" t="n">
+        <v>0.9992760000000001</v>
+      </c>
+      <c r="O256" s="1" t="n">
         <v>0.999297</v>
       </c>
-      <c r="O256" s="1" t="n">
+      <c r="P256" s="1" t="n">
         <v>0.999275</v>
       </c>
     </row>
@@ -13051,9 +13822,12 @@
         <v>0.02114</v>
       </c>
       <c r="N257" s="1" t="n">
+        <v>0.02103</v>
+      </c>
+      <c r="O257" s="1" t="n">
         <v>0.02118</v>
       </c>
-      <c r="O257" s="1" t="n">
+      <c r="P257" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -13100,9 +13874,12 @@
         <v>0.0115</v>
       </c>
       <c r="N258" s="1" t="n">
+        <v>0.01146</v>
+      </c>
+      <c r="O258" s="1" t="n">
         <v>0.01152</v>
       </c>
-      <c r="O258" s="1" t="n">
+      <c r="P258" s="1" t="n">
         <v>0.01133</v>
       </c>
     </row>
@@ -13149,10 +13926,13 @@
         <v>0.5082</v>
       </c>
       <c r="N259" s="1" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="O259" s="1" t="n">
         <v>0.5119</v>
       </c>
-      <c r="O259" s="1" t="n">
-        <v>0.5062</v>
+      <c r="P259" s="1" t="n">
+        <v>0.5061</v>
       </c>
     </row>
     <row r="260">
@@ -13198,9 +13978,12 @@
         <v>0.08415</v>
       </c>
       <c r="N260" s="1" t="n">
+        <v>0.08501</v>
+      </c>
+      <c r="O260" s="1" t="n">
         <v>0.08537</v>
       </c>
-      <c r="O260" s="1" t="n">
+      <c r="P260" s="1" t="n">
         <v>0.08415</v>
       </c>
     </row>
@@ -13247,9 +14030,12 @@
         <v>0.04141</v>
       </c>
       <c r="N261" s="1" t="n">
+        <v>0.04121</v>
+      </c>
+      <c r="O261" s="1" t="n">
         <v>0.04141</v>
       </c>
-      <c r="O261" s="1" t="n">
+      <c r="P261" s="1" t="n">
         <v>0.04121</v>
       </c>
     </row>
@@ -13296,9 +14082,12 @@
         <v>2.298</v>
       </c>
       <c r="N262" s="1" t="n">
+        <v>2.288</v>
+      </c>
+      <c r="O262" s="1" t="n">
         <v>2.298</v>
       </c>
-      <c r="O262" s="1" t="n">
+      <c r="P262" s="1" t="n">
         <v>2.279</v>
       </c>
     </row>
@@ -13345,9 +14134,12 @@
         <v>18.73</v>
       </c>
       <c r="N263" s="1" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="O263" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="O263" s="1" t="n">
+      <c r="P263" s="1" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -13394,9 +14186,12 @@
         <v>0.008532</v>
       </c>
       <c r="N264" s="1" t="n">
+        <v>0.008532</v>
+      </c>
+      <c r="O264" s="1" t="n">
         <v>0.008562999999999999</v>
       </c>
-      <c r="O264" s="1" t="n">
+      <c r="P264" s="1" t="n">
         <v>0.008377000000000001</v>
       </c>
     </row>
@@ -13443,9 +14238,12 @@
         <v>0.3643</v>
       </c>
       <c r="N265" s="1" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="O265" s="1" t="n">
         <v>0.3659</v>
       </c>
-      <c r="O265" s="1" t="n">
+      <c r="P265" s="1" t="n">
         <v>0.3627</v>
       </c>
     </row>
@@ -13492,9 +14290,12 @@
         <v>0.055423</v>
       </c>
       <c r="N266" s="1" t="n">
+        <v>0.055395</v>
+      </c>
+      <c r="O266" s="1" t="n">
         <v>0.055423</v>
       </c>
-      <c r="O266" s="1" t="n">
+      <c r="P266" s="1" t="n">
         <v>0.053765</v>
       </c>
     </row>
@@ -13541,10 +14342,13 @@
         <v>0.1321</v>
       </c>
       <c r="N267" s="1" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="O267" s="1" t="n">
         <v>0.1321</v>
       </c>
-      <c r="O267" s="1" t="n">
-        <v>0.1313</v>
+      <c r="P267" s="1" t="n">
+        <v>0.1312</v>
       </c>
     </row>
     <row r="268">
@@ -13590,9 +14394,12 @@
         <v>0.007891</v>
       </c>
       <c r="N268" s="1" t="n">
+        <v>0.007841000000000001</v>
+      </c>
+      <c r="O268" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="O268" s="1" t="n">
+      <c r="P268" s="1" t="n">
         <v>0.00775</v>
       </c>
     </row>
@@ -13639,9 +14446,12 @@
         <v>0.001289</v>
       </c>
       <c r="N269" s="1" t="n">
-        <v>0.001289</v>
+        <v>0.001299</v>
       </c>
       <c r="O269" s="1" t="n">
+        <v>0.001299</v>
+      </c>
+      <c r="P269" s="1" t="n">
         <v>0.001232</v>
       </c>
     </row>
@@ -13688,10 +14498,13 @@
         <v>0.2882</v>
       </c>
       <c r="N270" s="1" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="O270" s="1" t="n">
         <v>0.28999</v>
       </c>
-      <c r="O270" s="1" t="n">
-        <v>0.2882</v>
+      <c r="P270" s="1" t="n">
+        <v>0.28791</v>
       </c>
     </row>
     <row r="271">
@@ -13737,9 +14550,12 @@
         <v>0.03927</v>
       </c>
       <c r="N271" s="1" t="n">
+        <v>0.03916</v>
+      </c>
+      <c r="O271" s="1" t="n">
         <v>0.03927</v>
       </c>
-      <c r="O271" s="1" t="n">
+      <c r="P271" s="1" t="n">
         <v>0.03868</v>
       </c>
     </row>
@@ -13786,9 +14602,12 @@
         <v>0.05163</v>
       </c>
       <c r="N272" s="1" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="O272" s="1" t="n">
         <v>0.05182</v>
       </c>
-      <c r="O272" s="1" t="n">
+      <c r="P272" s="1" t="n">
         <v>0.05111</v>
       </c>
     </row>
@@ -13835,9 +14654,12 @@
         <v>0.00776</v>
       </c>
       <c r="N273" s="1" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="O273" s="1" t="n">
         <v>0.00776</v>
       </c>
-      <c r="O273" s="1" t="n">
+      <c r="P273" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -13884,9 +14706,12 @@
         <v>0.005784</v>
       </c>
       <c r="N274" s="1" t="n">
+        <v>0.005768</v>
+      </c>
+      <c r="O274" s="1" t="n">
         <v>0.005813</v>
       </c>
-      <c r="O274" s="1" t="n">
+      <c r="P274" s="1" t="n">
         <v>0.005721</v>
       </c>
     </row>
@@ -13933,10 +14758,13 @@
         <v>0.000587</v>
       </c>
       <c r="N275" s="1" t="n">
+        <v>0.0005841</v>
+      </c>
+      <c r="O275" s="1" t="n">
         <v>0.0005895</v>
       </c>
-      <c r="O275" s="1" t="n">
-        <v>0.0005863</v>
+      <c r="P275" s="1" t="n">
+        <v>0.0005841</v>
       </c>
     </row>
     <row r="276">
@@ -13982,10 +14810,13 @@
         <v>0.14973</v>
       </c>
       <c r="N276" s="1" t="n">
+        <v>0.14967</v>
+      </c>
+      <c r="O276" s="1" t="n">
         <v>0.15167</v>
       </c>
-      <c r="O276" s="1" t="n">
-        <v>0.14973</v>
+      <c r="P276" s="1" t="n">
+        <v>0.14967</v>
       </c>
     </row>
     <row r="277">
@@ -14031,9 +14862,12 @@
         <v>0.023185</v>
       </c>
       <c r="N277" s="1" t="n">
+        <v>0.023001</v>
+      </c>
+      <c r="O277" s="1" t="n">
         <v>0.023185</v>
       </c>
-      <c r="O277" s="1" t="n">
+      <c r="P277" s="1" t="n">
         <v>0.022666</v>
       </c>
     </row>
@@ -14080,9 +14914,12 @@
         <v>0.04205</v>
       </c>
       <c r="N278" s="1" t="n">
+        <v>0.04185</v>
+      </c>
+      <c r="O278" s="1" t="n">
         <v>0.04242</v>
       </c>
-      <c r="O278" s="1" t="n">
+      <c r="P278" s="1" t="n">
         <v>0.04179</v>
       </c>
     </row>
@@ -14129,9 +14966,12 @@
         <v>0.000399</v>
       </c>
       <c r="N279" s="1" t="n">
+        <v>0.0003978</v>
+      </c>
+      <c r="O279" s="1" t="n">
         <v>0.0004006</v>
       </c>
-      <c r="O279" s="1" t="n">
+      <c r="P279" s="1" t="n">
         <v>0.0003954</v>
       </c>
     </row>
@@ -14178,9 +15018,12 @@
         <v>0.02221</v>
       </c>
       <c r="N280" s="1" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="O280" s="1" t="n">
         <v>0.02221</v>
       </c>
-      <c r="O280" s="1" t="n">
+      <c r="P280" s="1" t="n">
         <v>0.0219</v>
       </c>
     </row>
@@ -14227,9 +15070,12 @@
         <v>0.07072000000000001</v>
       </c>
       <c r="N281" s="1" t="n">
+        <v>0.07065</v>
+      </c>
+      <c r="O281" s="1" t="n">
         <v>0.07128</v>
       </c>
-      <c r="O281" s="1" t="n">
+      <c r="P281" s="1" t="n">
         <v>0.06936</v>
       </c>
     </row>
@@ -14276,9 +15122,12 @@
         <v>0.006725</v>
       </c>
       <c r="N282" s="1" t="n">
+        <v>0.006716</v>
+      </c>
+      <c r="O282" s="1" t="n">
         <v>0.006804</v>
       </c>
-      <c r="O282" s="1" t="n">
+      <c r="P282" s="1" t="n">
         <v>0.006688</v>
       </c>
     </row>
@@ -14325,10 +15174,13 @@
         <v>0.12</v>
       </c>
       <c r="N283" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="O283" s="1" t="n">
         <v>0.12</v>
       </c>
-      <c r="O283" s="1" t="n">
-        <v>0.119</v>
+      <c r="P283" s="1" t="n">
+        <v>0.118</v>
       </c>
     </row>
     <row r="284">
@@ -14374,9 +15226,12 @@
         <v>0.005489</v>
       </c>
       <c r="N284" s="1" t="n">
+        <v>0.005471</v>
+      </c>
+      <c r="O284" s="1" t="n">
         <v>0.005499</v>
       </c>
-      <c r="O284" s="1" t="n">
+      <c r="P284" s="1" t="n">
         <v>0.005456</v>
       </c>
     </row>
@@ -14423,9 +15278,12 @@
         <v>1.264</v>
       </c>
       <c r="N285" s="1" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="O285" s="1" t="n">
         <v>1.272</v>
       </c>
-      <c r="O285" s="1" t="n">
+      <c r="P285" s="1" t="n">
         <v>1.237</v>
       </c>
     </row>
@@ -14472,9 +15330,12 @@
         <v>0.4451</v>
       </c>
       <c r="N286" s="1" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="O286" s="1" t="n">
         <v>0.4458</v>
       </c>
-      <c r="O286" s="1" t="n">
+      <c r="P286" s="1" t="n">
         <v>0.4423</v>
       </c>
     </row>
@@ -14521,9 +15382,12 @@
         <v>0.007924</v>
       </c>
       <c r="N287" s="1" t="n">
+        <v>0.007887999999999999</v>
+      </c>
+      <c r="O287" s="1" t="n">
         <v>0.007998999999999999</v>
       </c>
-      <c r="O287" s="1" t="n">
+      <c r="P287" s="1" t="n">
         <v>0.007835</v>
       </c>
     </row>
@@ -14570,9 +15434,12 @@
         <v>0.02931</v>
       </c>
       <c r="N288" s="1" t="n">
+        <v>0.02925</v>
+      </c>
+      <c r="O288" s="1" t="n">
         <v>0.0295</v>
       </c>
-      <c r="O288" s="1" t="n">
+      <c r="P288" s="1" t="n">
         <v>0.02914</v>
       </c>
     </row>
@@ -14619,9 +15486,12 @@
         <v>0.2829</v>
       </c>
       <c r="N289" s="1" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="O289" s="1" t="n">
         <v>0.2829</v>
       </c>
-      <c r="O289" s="1" t="n">
+      <c r="P289" s="1" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -14668,10 +15538,13 @@
         <v>2.761</v>
       </c>
       <c r="N290" s="1" t="n">
+        <v>2.744</v>
+      </c>
+      <c r="O290" s="1" t="n">
         <v>2.783</v>
       </c>
-      <c r="O290" s="1" t="n">
-        <v>2.75</v>
+      <c r="P290" s="1" t="n">
+        <v>2.744</v>
       </c>
     </row>
     <row r="291">
@@ -14717,9 +15590,12 @@
         <v>0.003194</v>
       </c>
       <c r="N291" s="1" t="n">
+        <v>0.003175</v>
+      </c>
+      <c r="O291" s="1" t="n">
         <v>0.003194</v>
       </c>
-      <c r="O291" s="1" t="n">
+      <c r="P291" s="1" t="n">
         <v>0.003155</v>
       </c>
     </row>
@@ -14766,10 +15642,13 @@
         <v>0.4469</v>
       </c>
       <c r="N292" s="1" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="O292" s="1" t="n">
         <v>0.4488</v>
       </c>
-      <c r="O292" s="1" t="n">
-        <v>0.4469</v>
+      <c r="P292" s="1" t="n">
+        <v>0.446</v>
       </c>
     </row>
     <row r="293">
@@ -14815,9 +15694,12 @@
         <v>0.08289000000000001</v>
       </c>
       <c r="N293" s="1" t="n">
+        <v>0.08229</v>
+      </c>
+      <c r="O293" s="1" t="n">
         <v>0.08298</v>
       </c>
-      <c r="O293" s="1" t="n">
+      <c r="P293" s="1" t="n">
         <v>0.08136</v>
       </c>
     </row>
@@ -14864,9 +15746,12 @@
         <v>0.028</v>
       </c>
       <c r="N294" s="1" t="n">
-        <v>0.02801</v>
+        <v>0.0281</v>
       </c>
       <c r="O294" s="1" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="P294" s="1" t="n">
         <v>0.02779</v>
       </c>
     </row>
@@ -14913,9 +15798,12 @@
         <v>0.951</v>
       </c>
       <c r="N295" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O295" s="1" t="n">
         <v>0.958</v>
       </c>
-      <c r="O295" s="1" t="n">
+      <c r="P295" s="1" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -14962,9 +15850,12 @@
         <v>0.006979</v>
       </c>
       <c r="N296" s="1" t="n">
+        <v>0.00695</v>
+      </c>
+      <c r="O296" s="1" t="n">
         <v>0.007008</v>
       </c>
-      <c r="O296" s="1" t="n">
+      <c r="P296" s="1" t="n">
         <v>0.00679</v>
       </c>
     </row>
@@ -15011,9 +15902,12 @@
         <v>0.1212</v>
       </c>
       <c r="N297" s="1" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="O297" s="1" t="n">
         <v>0.1215</v>
       </c>
-      <c r="O297" s="1" t="n">
+      <c r="P297" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -15060,9 +15954,12 @@
         <v>0.01552</v>
       </c>
       <c r="N298" s="1" t="n">
+        <v>0.01542</v>
+      </c>
+      <c r="O298" s="1" t="n">
         <v>0.01563</v>
       </c>
-      <c r="O298" s="1" t="n">
+      <c r="P298" s="1" t="n">
         <v>0.01526</v>
       </c>
     </row>
@@ -15109,9 +16006,12 @@
         <v>0.4402</v>
       </c>
       <c r="N299" s="1" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="O299" s="1" t="n">
         <v>0.4431</v>
       </c>
-      <c r="O299" s="1" t="n">
+      <c r="P299" s="1" t="n">
         <v>0.4389</v>
       </c>
     </row>
@@ -15158,9 +16058,12 @@
         <v>0.00916</v>
       </c>
       <c r="N300" s="1" t="n">
+        <v>0.00915</v>
+      </c>
+      <c r="O300" s="1" t="n">
         <v>0.00924</v>
       </c>
-      <c r="O300" s="1" t="n">
+      <c r="P300" s="1" t="n">
         <v>0.009129999999999999</v>
       </c>
     </row>
@@ -15207,9 +16110,12 @@
         <v>0.1881</v>
       </c>
       <c r="N301" s="1" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="O301" s="1" t="n">
         <v>0.1905</v>
       </c>
-      <c r="O301" s="1" t="n">
+      <c r="P301" s="1" t="n">
         <v>0.1845</v>
       </c>
     </row>
@@ -15256,9 +16162,12 @@
         <v>0.00758</v>
       </c>
       <c r="N302" s="1" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="O302" s="1" t="n">
         <v>0.00765</v>
       </c>
-      <c r="O302" s="1" t="n">
+      <c r="P302" s="1" t="n">
         <v>0.00744</v>
       </c>
     </row>
@@ -15305,9 +16214,12 @@
         <v>0.0002141</v>
       </c>
       <c r="N303" s="1" t="n">
+        <v>0.0002145</v>
+      </c>
+      <c r="O303" s="1" t="n">
         <v>0.0002171</v>
       </c>
-      <c r="O303" s="1" t="n">
+      <c r="P303" s="1" t="n">
         <v>0.0002141</v>
       </c>
     </row>
@@ -15354,9 +16266,12 @@
         <v>0.01552</v>
       </c>
       <c r="N304" s="1" t="n">
+        <v>0.01548</v>
+      </c>
+      <c r="O304" s="1" t="n">
         <v>0.01555</v>
       </c>
-      <c r="O304" s="1" t="n">
+      <c r="P304" s="1" t="n">
         <v>0.01542</v>
       </c>
     </row>
@@ -15403,9 +16318,12 @@
         <v>0.07407</v>
       </c>
       <c r="N305" s="1" t="n">
+        <v>0.07393</v>
+      </c>
+      <c r="O305" s="1" t="n">
         <v>0.07407</v>
       </c>
-      <c r="O305" s="1" t="n">
+      <c r="P305" s="1" t="n">
         <v>0.0738</v>
       </c>
     </row>
@@ -15452,9 +16370,12 @@
         <v>0.08348999999999999</v>
       </c>
       <c r="N306" s="1" t="n">
+        <v>0.08315</v>
+      </c>
+      <c r="O306" s="1" t="n">
         <v>0.08348999999999999</v>
       </c>
-      <c r="O306" s="1" t="n">
+      <c r="P306" s="1" t="n">
         <v>0.08275</v>
       </c>
     </row>
@@ -15501,10 +16422,13 @@
         <v>0.01801</v>
       </c>
       <c r="N307" s="1" t="n">
+        <v>0.01795</v>
+      </c>
+      <c r="O307" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="O307" s="1" t="n">
-        <v>0.01801</v>
+      <c r="P307" s="1" t="n">
+        <v>0.01795</v>
       </c>
     </row>
     <row r="308">
@@ -15550,9 +16474,12 @@
         <v>0.0006257</v>
       </c>
       <c r="N308" s="1" t="n">
+        <v>0.0006229</v>
+      </c>
+      <c r="O308" s="1" t="n">
         <v>0.0006274</v>
       </c>
-      <c r="O308" s="1" t="n">
+      <c r="P308" s="1" t="n">
         <v>0.0006212</v>
       </c>
     </row>
@@ -15599,10 +16526,13 @@
         <v>0.08243</v>
       </c>
       <c r="N309" s="1" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="O309" s="1" t="n">
         <v>0.08294</v>
       </c>
-      <c r="O309" s="1" t="n">
-        <v>0.0822</v>
+      <c r="P309" s="1" t="n">
+        <v>0.082</v>
       </c>
     </row>
     <row r="310">
@@ -15648,9 +16578,12 @@
         <v>0.0982</v>
       </c>
       <c r="N310" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="O310" s="1" t="n">
         <v>0.0982</v>
       </c>
-      <c r="O310" s="1" t="n">
+      <c r="P310" s="1" t="n">
         <v>0.0973</v>
       </c>
     </row>
@@ -15697,9 +16630,12 @@
         <v>0.2125</v>
       </c>
       <c r="N311" s="1" t="n">
+        <v>0.2117</v>
+      </c>
+      <c r="O311" s="1" t="n">
         <v>0.2126</v>
       </c>
-      <c r="O311" s="1" t="n">
+      <c r="P311" s="1" t="n">
         <v>0.2109</v>
       </c>
     </row>
@@ -15746,9 +16682,12 @@
         <v>0.3952</v>
       </c>
       <c r="N312" s="1" t="n">
-        <v>0.3958</v>
+        <v>0.3967</v>
       </c>
       <c r="O312" s="1" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="P312" s="1" t="n">
         <v>0.387</v>
       </c>
     </row>
@@ -15795,10 +16734,13 @@
         <v>0.10473</v>
       </c>
       <c r="N313" s="1" t="n">
+        <v>0.10415</v>
+      </c>
+      <c r="O313" s="1" t="n">
         <v>0.10542</v>
       </c>
-      <c r="O313" s="1" t="n">
-        <v>0.10455</v>
+      <c r="P313" s="1" t="n">
+        <v>0.10415</v>
       </c>
     </row>
     <row r="314">
@@ -15844,9 +16786,12 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="N314" s="1" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.08798</v>
       </c>
       <c r="O314" s="1" t="n">
+        <v>0.08798</v>
+      </c>
+      <c r="P314" s="1" t="n">
         <v>0.08487</v>
       </c>
     </row>
@@ -15893,9 +16838,12 @@
         <v>0.1187</v>
       </c>
       <c r="N315" s="1" t="n">
+        <v>0.1182</v>
+      </c>
+      <c r="O315" s="1" t="n">
         <v>0.1187</v>
       </c>
-      <c r="O315" s="1" t="n">
+      <c r="P315" s="1" t="n">
         <v>0.1178</v>
       </c>
     </row>
@@ -15942,9 +16890,12 @@
         <v>0.03597</v>
       </c>
       <c r="N316" s="1" t="n">
+        <v>0.03601</v>
+      </c>
+      <c r="O316" s="1" t="n">
         <v>0.03681</v>
       </c>
-      <c r="O316" s="1" t="n">
+      <c r="P316" s="1" t="n">
         <v>0.03597</v>
       </c>
     </row>
@@ -15991,9 +16942,12 @@
         <v>0.08143</v>
       </c>
       <c r="N317" s="1" t="n">
+        <v>0.08122</v>
+      </c>
+      <c r="O317" s="1" t="n">
         <v>0.08164</v>
       </c>
-      <c r="O317" s="1" t="n">
+      <c r="P317" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -16040,10 +16994,13 @@
         <v>0.03739</v>
       </c>
       <c r="N318" s="1" t="n">
+        <v>0.03733</v>
+      </c>
+      <c r="O318" s="1" t="n">
         <v>0.03766</v>
       </c>
-      <c r="O318" s="1" t="n">
-        <v>0.03736</v>
+      <c r="P318" s="1" t="n">
+        <v>0.03733</v>
       </c>
     </row>
     <row r="319">
@@ -16089,9 +17046,12 @@
         <v>0.4307</v>
       </c>
       <c r="N319" s="1" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="O319" s="1" t="n">
         <v>0.4347</v>
       </c>
-      <c r="O319" s="1" t="n">
+      <c r="P319" s="1" t="n">
         <v>0.4296</v>
       </c>
     </row>
@@ -16138,9 +17098,12 @@
         <v>0.1607</v>
       </c>
       <c r="N320" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="O320" s="1" t="n">
         <v>0.1614</v>
       </c>
-      <c r="O320" s="1" t="n">
+      <c r="P320" s="1" t="n">
         <v>0.1598</v>
       </c>
     </row>
@@ -16187,9 +17150,12 @@
         <v>5.678</v>
       </c>
       <c r="N321" s="1" t="n">
+        <v>5.683</v>
+      </c>
+      <c r="O321" s="1" t="n">
         <v>5.688</v>
       </c>
-      <c r="O321" s="1" t="n">
+      <c r="P321" s="1" t="n">
         <v>5.677</v>
       </c>
     </row>
@@ -16236,9 +17202,12 @@
         <v>0.003756</v>
       </c>
       <c r="N322" s="1" t="n">
+        <v>0.003737</v>
+      </c>
+      <c r="O322" s="1" t="n">
         <v>0.003756</v>
       </c>
-      <c r="O322" s="1" t="n">
+      <c r="P322" s="1" t="n">
         <v>0.003714</v>
       </c>
     </row>
@@ -16285,9 +17254,12 @@
         <v>0.001757</v>
       </c>
       <c r="N323" s="1" t="n">
+        <v>0.001758</v>
+      </c>
+      <c r="O323" s="1" t="n">
         <v>0.001762</v>
       </c>
-      <c r="O323" s="1" t="n">
+      <c r="P323" s="1" t="n">
         <v>0.001743</v>
       </c>
     </row>
@@ -16334,9 +17306,12 @@
         <v>1.2e-05</v>
       </c>
       <c r="N324" s="1" t="n">
+        <v>1.19e-05</v>
+      </c>
+      <c r="O324" s="1" t="n">
         <v>1.2e-05</v>
       </c>
-      <c r="O324" s="1" t="n">
+      <c r="P324" s="1" t="n">
         <v>1.19e-05</v>
       </c>
     </row>
@@ -16383,9 +17358,12 @@
         <v>0.0864</v>
       </c>
       <c r="N325" s="1" t="n">
+        <v>0.0859</v>
+      </c>
+      <c r="O325" s="1" t="n">
         <v>0.08649999999999999</v>
       </c>
-      <c r="O325" s="1" t="n">
+      <c r="P325" s="1" t="n">
         <v>0.0857</v>
       </c>
     </row>
@@ -16432,9 +17410,12 @@
         <v>0.01729</v>
       </c>
       <c r="N326" s="1" t="n">
+        <v>0.01724</v>
+      </c>
+      <c r="O326" s="1" t="n">
         <v>0.01736</v>
       </c>
-      <c r="O326" s="1" t="n">
+      <c r="P326" s="1" t="n">
         <v>0.01723</v>
       </c>
     </row>
@@ -16481,9 +17462,12 @@
         <v>0.01686</v>
       </c>
       <c r="N327" s="1" t="n">
+        <v>0.01679</v>
+      </c>
+      <c r="O327" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="O327" s="1" t="n">
+      <c r="P327" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -16530,10 +17514,13 @@
         <v>4.456</v>
       </c>
       <c r="N328" s="1" t="n">
+        <v>4.432</v>
+      </c>
+      <c r="O328" s="1" t="n">
         <v>4.462</v>
       </c>
-      <c r="O328" s="1" t="n">
-        <v>4.446</v>
+      <c r="P328" s="1" t="n">
+        <v>4.432</v>
       </c>
     </row>
     <row r="329">
@@ -16579,9 +17566,12 @@
         <v>0.009712999999999999</v>
       </c>
       <c r="N329" s="1" t="n">
+        <v>0.009695</v>
+      </c>
+      <c r="O329" s="1" t="n">
         <v>0.009861</v>
       </c>
-      <c r="O329" s="1" t="n">
+      <c r="P329" s="1" t="n">
         <v>0.009532000000000001</v>
       </c>
     </row>
@@ -16628,9 +17618,12 @@
         <v>5177.4</v>
       </c>
       <c r="N330" s="1" t="n">
+        <v>5180.1</v>
+      </c>
+      <c r="O330" s="1" t="n">
         <v>5192.9</v>
       </c>
-      <c r="O330" s="1" t="n">
+      <c r="P330" s="1" t="n">
         <v>5177.4</v>
       </c>
     </row>
@@ -16677,9 +17670,12 @@
         <v>0.07098</v>
       </c>
       <c r="N331" s="1" t="n">
-        <v>0.07098</v>
+        <v>0.07119</v>
       </c>
       <c r="O331" s="1" t="n">
+        <v>0.07119</v>
+      </c>
+      <c r="P331" s="1" t="n">
         <v>0.07047</v>
       </c>
     </row>
@@ -16726,9 +17722,12 @@
         <v>0.06085</v>
       </c>
       <c r="N332" s="1" t="n">
+        <v>0.06064</v>
+      </c>
+      <c r="O332" s="1" t="n">
         <v>0.06106</v>
       </c>
-      <c r="O332" s="1" t="n">
+      <c r="P332" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -16775,9 +17774,12 @@
         <v>0.10584</v>
       </c>
       <c r="N333" s="1" t="n">
+        <v>0.10543</v>
+      </c>
+      <c r="O333" s="1" t="n">
         <v>0.10584</v>
       </c>
-      <c r="O333" s="1" t="n">
+      <c r="P333" s="1" t="n">
         <v>0.10341</v>
       </c>
     </row>
@@ -16824,10 +17826,13 @@
         <v>0.08746</v>
       </c>
       <c r="N334" s="1" t="n">
+        <v>0.08727</v>
+      </c>
+      <c r="O334" s="1" t="n">
         <v>0.08837</v>
       </c>
-      <c r="O334" s="1" t="n">
-        <v>0.08734</v>
+      <c r="P334" s="1" t="n">
+        <v>0.08727</v>
       </c>
     </row>
     <row r="335">
@@ -16873,9 +17878,12 @@
         <v>0.01649</v>
       </c>
       <c r="N335" s="1" t="n">
+        <v>0.016479</v>
+      </c>
+      <c r="O335" s="1" t="n">
         <v>0.01649</v>
       </c>
-      <c r="O335" s="1" t="n">
+      <c r="P335" s="1" t="n">
         <v>0.016391</v>
       </c>
     </row>
@@ -16922,9 +17930,12 @@
         <v>0.04617</v>
       </c>
       <c r="N336" s="1" t="n">
-        <v>0.04619</v>
+        <v>0.04696</v>
       </c>
       <c r="O336" s="1" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="P336" s="1" t="n">
         <v>0.04583</v>
       </c>
     </row>
@@ -16971,9 +17982,12 @@
         <v>0.193</v>
       </c>
       <c r="N337" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="O337" s="1" t="n">
         <v>0.1942</v>
       </c>
-      <c r="O337" s="1" t="n">
+      <c r="P337" s="1" t="n">
         <v>0.1838</v>
       </c>
     </row>
@@ -17020,10 +18034,13 @@
         <v>0.1839</v>
       </c>
       <c r="N338" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="O338" s="1" t="n">
         <v>0.1843</v>
       </c>
-      <c r="O338" s="1" t="n">
-        <v>0.183</v>
+      <c r="P338" s="1" t="n">
+        <v>0.1829</v>
       </c>
     </row>
     <row r="339">
@@ -17069,9 +18086,12 @@
         <v>0.01845</v>
       </c>
       <c r="N339" s="1" t="n">
+        <v>0.01836</v>
+      </c>
+      <c r="O339" s="1" t="n">
         <v>0.01845</v>
       </c>
-      <c r="O339" s="1" t="n">
+      <c r="P339" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -17121,6 +18141,9 @@
         <v>0.02329</v>
       </c>
       <c r="O340" s="1" t="n">
+        <v>0.02329</v>
+      </c>
+      <c r="P340" s="1" t="n">
         <v>0.02305</v>
       </c>
     </row>
@@ -17167,9 +18190,12 @@
         <v>0.4568</v>
       </c>
       <c r="N341" s="1" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="O341" s="1" t="n">
         <v>0.4577</v>
       </c>
-      <c r="O341" s="1" t="n">
+      <c r="P341" s="1" t="n">
         <v>0.453</v>
       </c>
     </row>
@@ -17216,9 +18242,12 @@
         <v>0.0135</v>
       </c>
       <c r="N342" s="1" t="n">
+        <v>0.01343</v>
+      </c>
+      <c r="O342" s="1" t="n">
         <v>0.01352</v>
       </c>
-      <c r="O342" s="1" t="n">
+      <c r="P342" s="1" t="n">
         <v>0.01336</v>
       </c>
     </row>
@@ -17265,9 +18294,12 @@
         <v>2.889</v>
       </c>
       <c r="N343" s="1" t="n">
+        <v>2.886</v>
+      </c>
+      <c r="O343" s="1" t="n">
         <v>2.89</v>
       </c>
-      <c r="O343" s="1" t="n">
+      <c r="P343" s="1" t="n">
         <v>2.872</v>
       </c>
     </row>
@@ -17314,9 +18346,12 @@
         <v>0.153</v>
       </c>
       <c r="N344" s="1" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="O344" s="1" t="n">
         <v>0.1577</v>
       </c>
-      <c r="O344" s="1" t="n">
+      <c r="P344" s="1" t="n">
         <v>0.1482</v>
       </c>
     </row>
@@ -17363,9 +18398,12 @@
         <v>0.005378</v>
       </c>
       <c r="N345" s="1" t="n">
+        <v>0.005386</v>
+      </c>
+      <c r="O345" s="1" t="n">
         <v>0.005407</v>
       </c>
-      <c r="O345" s="1" t="n">
+      <c r="P345" s="1" t="n">
         <v>0.005339</v>
       </c>
     </row>
@@ -17412,9 +18450,12 @@
         <v>0.05778</v>
       </c>
       <c r="N346" s="1" t="n">
+        <v>0.05761</v>
+      </c>
+      <c r="O346" s="1" t="n">
         <v>0.0579</v>
       </c>
-      <c r="O346" s="1" t="n">
+      <c r="P346" s="1" t="n">
         <v>0.05755</v>
       </c>
     </row>
@@ -17461,10 +18502,13 @@
         <v>2604</v>
       </c>
       <c r="N347" s="1" t="n">
+        <v>2590</v>
+      </c>
+      <c r="O347" s="1" t="n">
         <v>2613</v>
       </c>
-      <c r="O347" s="1" t="n">
-        <v>2597</v>
+      <c r="P347" s="1" t="n">
+        <v>2590</v>
       </c>
     </row>
     <row r="348">
@@ -17510,9 +18554,12 @@
         <v>0.04633</v>
       </c>
       <c r="N348" s="1" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="O348" s="1" t="n">
         <v>0.04642</v>
       </c>
-      <c r="O348" s="1" t="n">
+      <c r="P348" s="1" t="n">
         <v>0.04595</v>
       </c>
     </row>
@@ -17559,10 +18606,13 @@
         <v>0.005639</v>
       </c>
       <c r="N349" s="1" t="n">
+        <v>0.005594</v>
+      </c>
+      <c r="O349" s="1" t="n">
         <v>0.005714</v>
       </c>
-      <c r="O349" s="1" t="n">
-        <v>0.005625</v>
+      <c r="P349" s="1" t="n">
+        <v>0.005594</v>
       </c>
     </row>
     <row r="350">
@@ -17608,9 +18658,12 @@
         <v>195.76</v>
       </c>
       <c r="N350" s="1" t="n">
+        <v>195.24</v>
+      </c>
+      <c r="O350" s="1" t="n">
         <v>195.95</v>
       </c>
-      <c r="O350" s="1" t="n">
+      <c r="P350" s="1" t="n">
         <v>195.23</v>
       </c>
     </row>
@@ -17657,9 +18710,12 @@
         <v>0.08239</v>
       </c>
       <c r="N351" s="1" t="n">
+        <v>0.08205999999999999</v>
+      </c>
+      <c r="O351" s="1" t="n">
         <v>0.08245</v>
       </c>
-      <c r="O351" s="1" t="n">
+      <c r="P351" s="1" t="n">
         <v>0.08193</v>
       </c>
     </row>
@@ -17706,9 +18762,12 @@
         <v>0.007425</v>
       </c>
       <c r="N352" s="1" t="n">
+        <v>0.007448</v>
+      </c>
+      <c r="O352" s="1" t="n">
         <v>0.007571</v>
       </c>
-      <c r="O352" s="1" t="n">
+      <c r="P352" s="1" t="n">
         <v>0.00741</v>
       </c>
     </row>
@@ -17755,9 +18814,12 @@
         <v>1.4839</v>
       </c>
       <c r="N353" s="1" t="n">
+        <v>1.4829</v>
+      </c>
+      <c r="O353" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="O353" s="1" t="n">
+      <c r="P353" s="1" t="n">
         <v>1.4807</v>
       </c>
     </row>
@@ -17804,9 +18866,12 @@
         <v>0.07663</v>
       </c>
       <c r="N354" s="1" t="n">
+        <v>0.07624</v>
+      </c>
+      <c r="O354" s="1" t="n">
         <v>0.07677</v>
       </c>
-      <c r="O354" s="1" t="n">
+      <c r="P354" s="1" t="n">
         <v>0.07597</v>
       </c>
     </row>
@@ -17853,10 +18918,13 @@
         <v>0.04857</v>
       </c>
       <c r="N355" s="1" t="n">
+        <v>0.04819</v>
+      </c>
+      <c r="O355" s="1" t="n">
         <v>0.04921</v>
       </c>
-      <c r="O355" s="1" t="n">
-        <v>0.04839</v>
+      <c r="P355" s="1" t="n">
+        <v>0.04819</v>
       </c>
     </row>
     <row r="356">
@@ -17902,9 +18970,12 @@
         <v>0.2874</v>
       </c>
       <c r="N356" s="1" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="O356" s="1" t="n">
         <v>0.2874</v>
       </c>
-      <c r="O356" s="1" t="n">
+      <c r="P356" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -17954,6 +19025,9 @@
         <v>0.1473</v>
       </c>
       <c r="O357" s="1" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="P357" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -18000,10 +19074,13 @@
         <v>1.345</v>
       </c>
       <c r="N358" s="1" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="O358" s="1" t="n">
         <v>1.355</v>
       </c>
-      <c r="O358" s="1" t="n">
-        <v>1.345</v>
+      <c r="P358" s="1" t="n">
+        <v>1.341</v>
       </c>
     </row>
     <row r="359">
@@ -18049,9 +19126,12 @@
         <v>0.6143</v>
       </c>
       <c r="N359" s="1" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="O359" s="1" t="n">
         <v>0.6143</v>
       </c>
-      <c r="O359" s="1" t="n">
+      <c r="P359" s="1" t="n">
         <v>0.6081</v>
       </c>
     </row>
@@ -18098,9 +19178,12 @@
         <v>0.1147</v>
       </c>
       <c r="N360" s="1" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="O360" s="1" t="n">
         <v>0.1149</v>
       </c>
-      <c r="O360" s="1" t="n">
+      <c r="P360" s="1" t="n">
         <v>0.1142</v>
       </c>
     </row>
@@ -18147,9 +19230,12 @@
         <v>0.02658</v>
       </c>
       <c r="N361" s="1" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="O361" s="1" t="n">
         <v>0.02678</v>
       </c>
-      <c r="O361" s="1" t="n">
+      <c r="P361" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -18196,9 +19282,12 @@
         <v>3.04e-05</v>
       </c>
       <c r="N362" s="1" t="n">
+        <v>3.04e-05</v>
+      </c>
+      <c r="O362" s="1" t="n">
         <v>3.05e-05</v>
       </c>
-      <c r="O362" s="1" t="n">
+      <c r="P362" s="1" t="n">
         <v>3.03e-05</v>
       </c>
     </row>
@@ -18245,10 +19334,13 @@
         <v>0.01024</v>
       </c>
       <c r="N363" s="1" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="O363" s="1" t="n">
         <v>0.01047</v>
       </c>
-      <c r="O363" s="1" t="n">
-        <v>0.01018</v>
+      <c r="P363" s="1" t="n">
+        <v>0.01015</v>
       </c>
     </row>
     <row r="364">
@@ -18294,9 +19386,12 @@
         <v>0.06238</v>
       </c>
       <c r="N364" s="1" t="n">
+        <v>0.06208</v>
+      </c>
+      <c r="O364" s="1" t="n">
         <v>0.06238</v>
       </c>
-      <c r="O364" s="1" t="n">
+      <c r="P364" s="1" t="n">
         <v>0.06199</v>
       </c>
     </row>
@@ -18343,9 +19438,12 @@
         <v>0.03277</v>
       </c>
       <c r="N365" s="1" t="n">
+        <v>0.03261</v>
+      </c>
+      <c r="O365" s="1" t="n">
         <v>0.03299</v>
       </c>
-      <c r="O365" s="1" t="n">
+      <c r="P365" s="1" t="n">
         <v>0.03255</v>
       </c>
     </row>
@@ -18392,9 +19490,12 @@
         <v>0.03332</v>
       </c>
       <c r="N366" s="1" t="n">
-        <v>0.0334</v>
+        <v>0.03383</v>
       </c>
       <c r="O366" s="1" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="P366" s="1" t="n">
         <v>0.03283</v>
       </c>
     </row>
@@ -18441,9 +19542,12 @@
         <v>0.012327</v>
       </c>
       <c r="N367" s="1" t="n">
+        <v>0.012332</v>
+      </c>
+      <c r="O367" s="1" t="n">
         <v>0.012357</v>
       </c>
-      <c r="O367" s="1" t="n">
+      <c r="P367" s="1" t="n">
         <v>0.012155</v>
       </c>
     </row>
@@ -18490,9 +19594,12 @@
         <v>0.03627</v>
       </c>
       <c r="N368" s="1" t="n">
-        <v>0.03627</v>
+        <v>0.03982</v>
       </c>
       <c r="O368" s="1" t="n">
+        <v>0.03982</v>
+      </c>
+      <c r="P368" s="1" t="n">
         <v>0.03513</v>
       </c>
     </row>
@@ -18539,9 +19646,12 @@
         <v>0.6274999999999999</v>
       </c>
       <c r="N369" s="1" t="n">
+        <v>0.6274999999999999</v>
+      </c>
+      <c r="O369" s="1" t="n">
         <v>0.6307</v>
       </c>
-      <c r="O369" s="1" t="n">
+      <c r="P369" s="1" t="n">
         <v>0.6182</v>
       </c>
     </row>
@@ -18588,9 +19698,12 @@
         <v>0.00812</v>
       </c>
       <c r="N370" s="1" t="n">
+        <v>0.008149999999999999</v>
+      </c>
+      <c r="O370" s="1" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="O370" s="1" t="n">
+      <c r="P370" s="1" t="n">
         <v>0.00812</v>
       </c>
     </row>
@@ -18637,9 +19750,12 @@
         <v>0.004115</v>
       </c>
       <c r="N371" s="1" t="n">
-        <v>0.004166</v>
+        <v>0.004167</v>
       </c>
       <c r="O371" s="1" t="n">
+        <v>0.004167</v>
+      </c>
+      <c r="P371" s="1" t="n"